--- a/assets/data/bcv/excel/ove_bcv_inpc_nacional_mensual.xlsx
+++ b/assets/data/bcv/excel/ove_bcv_inpc_nacional_mensual.xlsx
@@ -650,7 +650,7 @@
       </c>
       <c r="K7" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:00Z</t>
+          <t>2026-09-13T22:31:31Z</t>
         </is>
       </c>
     </row>
@@ -699,7 +699,7 @@
       </c>
       <c r="K8" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:00Z</t>
+          <t>2026-09-13T22:31:31Z</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="K9" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:00Z</t>
+          <t>2026-09-13T22:31:31Z</t>
         </is>
       </c>
     </row>
@@ -797,7 +797,7 @@
       </c>
       <c r="K10" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:00Z</t>
+          <t>2026-09-13T22:31:31Z</t>
         </is>
       </c>
     </row>
@@ -846,7 +846,7 @@
       </c>
       <c r="K11" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:00Z</t>
+          <t>2026-09-13T22:31:31Z</t>
         </is>
       </c>
     </row>
@@ -895,7 +895,7 @@
       </c>
       <c r="K12" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:00Z</t>
+          <t>2026-09-13T22:31:31Z</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="K13" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:00Z</t>
+          <t>2026-09-13T22:31:31Z</t>
         </is>
       </c>
     </row>
@@ -993,7 +993,7 @@
       </c>
       <c r="K14" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:00Z</t>
+          <t>2026-09-13T22:31:31Z</t>
         </is>
       </c>
     </row>
@@ -1042,7 +1042,7 @@
       </c>
       <c r="K15" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:00Z</t>
+          <t>2026-09-13T22:31:31Z</t>
         </is>
       </c>
     </row>
@@ -1091,7 +1091,7 @@
       </c>
       <c r="K16" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:00Z</t>
+          <t>2026-09-13T22:31:31Z</t>
         </is>
       </c>
     </row>
@@ -1140,7 +1140,7 @@
       </c>
       <c r="K17" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:00Z</t>
+          <t>2026-09-13T22:31:31Z</t>
         </is>
       </c>
     </row>
@@ -1189,7 +1189,7 @@
       </c>
       <c r="K18" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:00Z</t>
+          <t>2026-09-13T22:31:31Z</t>
         </is>
       </c>
     </row>
@@ -1238,7 +1238,7 @@
       </c>
       <c r="K19" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:00Z</t>
+          <t>2026-09-13T22:31:31Z</t>
         </is>
       </c>
     </row>
@@ -1287,7 +1287,7 @@
       </c>
       <c r="K20" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:00Z</t>
+          <t>2026-09-13T22:31:31Z</t>
         </is>
       </c>
     </row>
@@ -1336,7 +1336,7 @@
       </c>
       <c r="K21" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:00Z</t>
+          <t>2026-09-13T22:31:31Z</t>
         </is>
       </c>
     </row>
@@ -1385,7 +1385,7 @@
       </c>
       <c r="K22" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:00Z</t>
+          <t>2026-09-13T22:31:31Z</t>
         </is>
       </c>
     </row>
@@ -1434,7 +1434,7 @@
       </c>
       <c r="K23" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:00Z</t>
+          <t>2026-09-13T22:31:31Z</t>
         </is>
       </c>
     </row>
@@ -1483,7 +1483,7 @@
       </c>
       <c r="K24" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:00Z</t>
+          <t>2026-09-13T22:31:31Z</t>
         </is>
       </c>
     </row>
@@ -1532,7 +1532,7 @@
       </c>
       <c r="K25" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:00Z</t>
+          <t>2026-09-13T22:31:31Z</t>
         </is>
       </c>
     </row>
@@ -1581,7 +1581,7 @@
       </c>
       <c r="K26" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:00Z</t>
+          <t>2026-09-13T22:31:31Z</t>
         </is>
       </c>
     </row>
@@ -1630,7 +1630,7 @@
       </c>
       <c r="K27" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:00Z</t>
+          <t>2026-09-13T22:31:31Z</t>
         </is>
       </c>
     </row>
@@ -1679,7 +1679,7 @@
       </c>
       <c r="K28" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:00Z</t>
+          <t>2026-09-13T22:31:31Z</t>
         </is>
       </c>
     </row>
@@ -1728,7 +1728,7 @@
       </c>
       <c r="K29" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:00Z</t>
+          <t>2026-09-13T22:31:31Z</t>
         </is>
       </c>
     </row>
@@ -1777,7 +1777,7 @@
       </c>
       <c r="K30" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:00Z</t>
+          <t>2026-09-13T22:31:31Z</t>
         </is>
       </c>
     </row>
@@ -1826,7 +1826,7 @@
       </c>
       <c r="K31" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:00Z</t>
+          <t>2026-09-13T22:31:31Z</t>
         </is>
       </c>
     </row>
@@ -1875,7 +1875,7 @@
       </c>
       <c r="K32" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:00Z</t>
+          <t>2026-09-13T22:31:31Z</t>
         </is>
       </c>
     </row>
@@ -1924,7 +1924,7 @@
       </c>
       <c r="K33" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:00Z</t>
+          <t>2026-09-13T22:31:31Z</t>
         </is>
       </c>
     </row>
@@ -1973,7 +1973,7 @@
       </c>
       <c r="K34" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:00Z</t>
+          <t>2026-09-13T22:31:31Z</t>
         </is>
       </c>
     </row>
@@ -2022,7 +2022,7 @@
       </c>
       <c r="K35" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:00Z</t>
+          <t>2026-09-13T22:31:31Z</t>
         </is>
       </c>
     </row>
@@ -2071,7 +2071,7 @@
       </c>
       <c r="K36" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:00Z</t>
+          <t>2026-09-13T22:31:31Z</t>
         </is>
       </c>
     </row>
@@ -2120,7 +2120,7 @@
       </c>
       <c r="K37" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:00Z</t>
+          <t>2026-09-13T22:31:31Z</t>
         </is>
       </c>
     </row>
@@ -2169,7 +2169,7 @@
       </c>
       <c r="K38" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:00Z</t>
+          <t>2026-09-13T22:31:31Z</t>
         </is>
       </c>
     </row>
@@ -2218,7 +2218,7 @@
       </c>
       <c r="K39" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:00Z</t>
+          <t>2026-09-13T22:31:31Z</t>
         </is>
       </c>
     </row>
@@ -2267,7 +2267,7 @@
       </c>
       <c r="K40" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:00Z</t>
+          <t>2026-09-13T22:31:31Z</t>
         </is>
       </c>
     </row>
@@ -2316,7 +2316,7 @@
       </c>
       <c r="K41" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:00Z</t>
+          <t>2026-09-13T22:31:31Z</t>
         </is>
       </c>
     </row>
@@ -2365,7 +2365,7 @@
       </c>
       <c r="K42" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:00Z</t>
+          <t>2026-09-13T22:31:31Z</t>
         </is>
       </c>
     </row>
@@ -2414,7 +2414,7 @@
       </c>
       <c r="K43" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:00Z</t>
+          <t>2026-09-13T22:31:31Z</t>
         </is>
       </c>
     </row>
@@ -2463,7 +2463,7 @@
       </c>
       <c r="K44" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:00Z</t>
+          <t>2026-09-13T22:31:31Z</t>
         </is>
       </c>
     </row>
@@ -2512,7 +2512,7 @@
       </c>
       <c r="K45" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:00Z</t>
+          <t>2026-09-13T22:31:31Z</t>
         </is>
       </c>
     </row>
@@ -2561,7 +2561,7 @@
       </c>
       <c r="K46" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:00Z</t>
+          <t>2026-09-13T22:31:31Z</t>
         </is>
       </c>
     </row>
@@ -2610,7 +2610,7 @@
       </c>
       <c r="K47" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:00Z</t>
+          <t>2026-09-13T22:31:31Z</t>
         </is>
       </c>
     </row>
@@ -2659,7 +2659,7 @@
       </c>
       <c r="K48" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:00Z</t>
+          <t>2026-09-13T22:31:31Z</t>
         </is>
       </c>
     </row>
@@ -2708,7 +2708,7 @@
       </c>
       <c r="K49" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:00Z</t>
+          <t>2026-09-13T22:31:31Z</t>
         </is>
       </c>
     </row>
@@ -2757,7 +2757,7 @@
       </c>
       <c r="K50" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:00Z</t>
+          <t>2026-09-13T22:31:31Z</t>
         </is>
       </c>
     </row>
@@ -2806,7 +2806,7 @@
       </c>
       <c r="K51" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:00Z</t>
+          <t>2026-09-13T22:31:31Z</t>
         </is>
       </c>
     </row>
@@ -2855,7 +2855,7 @@
       </c>
       <c r="K52" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:00Z</t>
+          <t>2026-09-13T22:31:31Z</t>
         </is>
       </c>
     </row>
@@ -2904,7 +2904,7 @@
       </c>
       <c r="K53" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:00Z</t>
+          <t>2026-09-13T22:31:31Z</t>
         </is>
       </c>
     </row>
@@ -2953,7 +2953,7 @@
       </c>
       <c r="K54" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:00Z</t>
+          <t>2026-09-13T22:31:31Z</t>
         </is>
       </c>
     </row>
@@ -3002,7 +3002,7 @@
       </c>
       <c r="K55" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:00Z</t>
+          <t>2026-09-13T22:31:31Z</t>
         </is>
       </c>
     </row>
@@ -3051,7 +3051,7 @@
       </c>
       <c r="K56" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:00Z</t>
+          <t>2026-09-13T22:31:31Z</t>
         </is>
       </c>
     </row>
@@ -3100,7 +3100,7 @@
       </c>
       <c r="K57" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:00Z</t>
+          <t>2026-09-13T22:31:31Z</t>
         </is>
       </c>
     </row>
@@ -3149,7 +3149,7 @@
       </c>
       <c r="K58" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:00Z</t>
+          <t>2026-09-13T22:31:31Z</t>
         </is>
       </c>
     </row>
@@ -3198,7 +3198,7 @@
       </c>
       <c r="K59" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:00Z</t>
+          <t>2026-09-13T22:31:31Z</t>
         </is>
       </c>
     </row>
@@ -3247,7 +3247,7 @@
       </c>
       <c r="K60" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:00Z</t>
+          <t>2026-09-13T22:31:31Z</t>
         </is>
       </c>
     </row>
@@ -3296,7 +3296,7 @@
       </c>
       <c r="K61" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:00Z</t>
+          <t>2026-09-13T22:31:31Z</t>
         </is>
       </c>
     </row>
@@ -3345,7 +3345,7 @@
       </c>
       <c r="K62" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:00Z</t>
+          <t>2026-09-13T22:31:31Z</t>
         </is>
       </c>
     </row>
@@ -3394,7 +3394,7 @@
       </c>
       <c r="K63" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:00Z</t>
+          <t>2026-09-13T22:31:31Z</t>
         </is>
       </c>
     </row>
@@ -3443,7 +3443,7 @@
       </c>
       <c r="K64" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:00Z</t>
+          <t>2026-09-13T22:31:31Z</t>
         </is>
       </c>
     </row>
@@ -3492,7 +3492,7 @@
       </c>
       <c r="K65" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:00Z</t>
+          <t>2026-09-13T22:31:31Z</t>
         </is>
       </c>
     </row>
@@ -3541,7 +3541,7 @@
       </c>
       <c r="K66" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:00Z</t>
+          <t>2026-09-13T22:31:31Z</t>
         </is>
       </c>
     </row>
@@ -3590,7 +3590,7 @@
       </c>
       <c r="K67" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:00Z</t>
+          <t>2026-09-13T22:31:31Z</t>
         </is>
       </c>
     </row>
@@ -3639,7 +3639,7 @@
       </c>
       <c r="K68" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:00Z</t>
+          <t>2026-09-13T22:31:31Z</t>
         </is>
       </c>
     </row>
@@ -3688,7 +3688,7 @@
       </c>
       <c r="K69" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:00Z</t>
+          <t>2026-09-13T22:31:31Z</t>
         </is>
       </c>
     </row>
@@ -3737,7 +3737,7 @@
       </c>
       <c r="K70" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:00Z</t>
+          <t>2026-09-13T22:31:31Z</t>
         </is>
       </c>
     </row>
@@ -3786,7 +3786,7 @@
       </c>
       <c r="K71" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:00Z</t>
+          <t>2026-09-13T22:31:31Z</t>
         </is>
       </c>
     </row>
@@ -3835,7 +3835,7 @@
       </c>
       <c r="K72" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:00Z</t>
+          <t>2026-09-13T22:31:31Z</t>
         </is>
       </c>
     </row>
@@ -3884,7 +3884,7 @@
       </c>
       <c r="K73" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:00Z</t>
+          <t>2026-09-13T22:31:31Z</t>
         </is>
       </c>
     </row>
@@ -3933,7 +3933,7 @@
       </c>
       <c r="K74" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:00Z</t>
+          <t>2026-09-13T22:31:31Z</t>
         </is>
       </c>
     </row>
@@ -3982,7 +3982,7 @@
       </c>
       <c r="K75" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:00Z</t>
+          <t>2026-09-13T22:31:31Z</t>
         </is>
       </c>
     </row>
@@ -4031,7 +4031,7 @@
       </c>
       <c r="K76" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:00Z</t>
+          <t>2026-09-13T22:31:31Z</t>
         </is>
       </c>
     </row>
@@ -4080,7 +4080,7 @@
       </c>
       <c r="K77" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:00Z</t>
+          <t>2026-09-13T22:31:31Z</t>
         </is>
       </c>
     </row>
@@ -4129,7 +4129,7 @@
       </c>
       <c r="K78" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:00Z</t>
+          <t>2026-09-13T22:31:31Z</t>
         </is>
       </c>
     </row>
@@ -4178,7 +4178,7 @@
       </c>
       <c r="K79" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:00Z</t>
+          <t>2026-09-13T22:31:31Z</t>
         </is>
       </c>
     </row>
@@ -4227,7 +4227,7 @@
       </c>
       <c r="K80" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:00Z</t>
+          <t>2026-09-13T22:31:31Z</t>
         </is>
       </c>
     </row>
@@ -4276,7 +4276,7 @@
       </c>
       <c r="K81" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:00Z</t>
+          <t>2026-09-13T22:31:31Z</t>
         </is>
       </c>
     </row>
@@ -4325,7 +4325,7 @@
       </c>
       <c r="K82" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:00Z</t>
+          <t>2026-09-13T22:31:31Z</t>
         </is>
       </c>
     </row>
@@ -4374,7 +4374,7 @@
       </c>
       <c r="K83" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:00Z</t>
+          <t>2026-09-13T22:31:31Z</t>
         </is>
       </c>
     </row>
@@ -4423,7 +4423,7 @@
       </c>
       <c r="K84" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:00Z</t>
+          <t>2026-09-13T22:31:31Z</t>
         </is>
       </c>
     </row>
@@ -4472,7 +4472,7 @@
       </c>
       <c r="K85" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:00Z</t>
+          <t>2026-09-13T22:31:31Z</t>
         </is>
       </c>
     </row>
@@ -4521,7 +4521,7 @@
       </c>
       <c r="K86" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:00Z</t>
+          <t>2026-09-13T22:31:31Z</t>
         </is>
       </c>
     </row>
@@ -4570,7 +4570,7 @@
       </c>
       <c r="K87" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:00Z</t>
+          <t>2026-09-13T22:31:31Z</t>
         </is>
       </c>
     </row>
@@ -4619,7 +4619,7 @@
       </c>
       <c r="K88" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:00Z</t>
+          <t>2026-09-13T22:31:31Z</t>
         </is>
       </c>
     </row>
@@ -4668,7 +4668,7 @@
       </c>
       <c r="K89" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:00Z</t>
+          <t>2026-09-13T22:31:31Z</t>
         </is>
       </c>
     </row>
@@ -4717,7 +4717,7 @@
       </c>
       <c r="K90" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:00Z</t>
+          <t>2026-09-13T22:31:31Z</t>
         </is>
       </c>
     </row>
@@ -4766,7 +4766,7 @@
       </c>
       <c r="K91" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:00Z</t>
+          <t>2026-09-13T22:31:31Z</t>
         </is>
       </c>
     </row>
@@ -4815,7 +4815,7 @@
       </c>
       <c r="K92" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:00Z</t>
+          <t>2026-09-13T22:31:31Z</t>
         </is>
       </c>
     </row>
@@ -4864,7 +4864,7 @@
       </c>
       <c r="K93" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:00Z</t>
+          <t>2026-09-13T22:31:31Z</t>
         </is>
       </c>
     </row>
@@ -4913,7 +4913,7 @@
       </c>
       <c r="K94" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:00Z</t>
+          <t>2026-09-13T22:31:31Z</t>
         </is>
       </c>
     </row>
@@ -4962,7 +4962,7 @@
       </c>
       <c r="K95" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:00Z</t>
+          <t>2026-09-13T22:31:31Z</t>
         </is>
       </c>
     </row>
@@ -5011,7 +5011,7 @@
       </c>
       <c r="K96" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:00Z</t>
+          <t>2026-09-13T22:31:31Z</t>
         </is>
       </c>
     </row>
@@ -5060,7 +5060,7 @@
       </c>
       <c r="K97" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:00Z</t>
+          <t>2026-09-13T22:31:31Z</t>
         </is>
       </c>
     </row>
@@ -5109,7 +5109,7 @@
       </c>
       <c r="K98" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:00Z</t>
+          <t>2026-09-13T22:31:31Z</t>
         </is>
       </c>
     </row>
@@ -5158,7 +5158,7 @@
       </c>
       <c r="K99" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:00Z</t>
+          <t>2026-09-13T22:31:31Z</t>
         </is>
       </c>
     </row>
@@ -5207,7 +5207,7 @@
       </c>
       <c r="K100" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:00Z</t>
+          <t>2026-09-13T22:31:31Z</t>
         </is>
       </c>
     </row>
@@ -5256,7 +5256,7 @@
       </c>
       <c r="K101" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:00Z</t>
+          <t>2026-09-13T22:31:31Z</t>
         </is>
       </c>
     </row>
@@ -5305,7 +5305,7 @@
       </c>
       <c r="K102" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:00Z</t>
+          <t>2026-09-13T22:31:31Z</t>
         </is>
       </c>
     </row>
@@ -5354,7 +5354,7 @@
       </c>
       <c r="K103" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:00Z</t>
+          <t>2026-09-13T22:31:31Z</t>
         </is>
       </c>
     </row>
@@ -5403,7 +5403,7 @@
       </c>
       <c r="K104" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:00Z</t>
+          <t>2026-09-13T22:31:31Z</t>
         </is>
       </c>
     </row>
@@ -5452,7 +5452,7 @@
       </c>
       <c r="K105" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:00Z</t>
+          <t>2026-09-13T22:31:31Z</t>
         </is>
       </c>
     </row>
@@ -5501,7 +5501,7 @@
       </c>
       <c r="K106" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:00Z</t>
+          <t>2026-09-13T22:31:31Z</t>
         </is>
       </c>
     </row>
@@ -5550,7 +5550,7 @@
       </c>
       <c r="K107" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:00Z</t>
+          <t>2026-09-13T22:31:31Z</t>
         </is>
       </c>
     </row>
@@ -5599,7 +5599,7 @@
       </c>
       <c r="K108" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:00Z</t>
+          <t>2026-09-13T22:31:31Z</t>
         </is>
       </c>
     </row>
@@ -5648,7 +5648,7 @@
       </c>
       <c r="K109" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:00Z</t>
+          <t>2026-09-13T22:31:31Z</t>
         </is>
       </c>
     </row>
@@ -5697,7 +5697,7 @@
       </c>
       <c r="K110" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:00Z</t>
+          <t>2026-09-13T22:31:31Z</t>
         </is>
       </c>
     </row>
@@ -5746,7 +5746,7 @@
       </c>
       <c r="K111" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:00Z</t>
+          <t>2026-09-13T22:31:31Z</t>
         </is>
       </c>
     </row>
@@ -5795,7 +5795,7 @@
       </c>
       <c r="K112" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:00Z</t>
+          <t>2026-09-13T22:31:31Z</t>
         </is>
       </c>
     </row>
@@ -5844,7 +5844,7 @@
       </c>
       <c r="K113" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:00Z</t>
+          <t>2026-09-13T22:31:31Z</t>
         </is>
       </c>
     </row>
@@ -5893,7 +5893,7 @@
       </c>
       <c r="K114" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:00Z</t>
+          <t>2026-09-13T22:31:31Z</t>
         </is>
       </c>
     </row>
@@ -5942,7 +5942,7 @@
       </c>
       <c r="K115" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:00Z</t>
+          <t>2026-09-13T22:31:31Z</t>
         </is>
       </c>
     </row>
@@ -5991,7 +5991,7 @@
       </c>
       <c r="K116" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:00Z</t>
+          <t>2026-09-13T22:31:31Z</t>
         </is>
       </c>
     </row>
@@ -6040,7 +6040,7 @@
       </c>
       <c r="K117" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:00Z</t>
+          <t>2026-09-13T22:31:31Z</t>
         </is>
       </c>
     </row>
@@ -6089,7 +6089,7 @@
       </c>
       <c r="K118" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:00Z</t>
+          <t>2026-09-13T22:31:31Z</t>
         </is>
       </c>
     </row>
@@ -6138,7 +6138,7 @@
       </c>
       <c r="K119" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:00Z</t>
+          <t>2026-09-13T22:31:31Z</t>
         </is>
       </c>
     </row>
@@ -6187,7 +6187,7 @@
       </c>
       <c r="K120" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:00Z</t>
+          <t>2026-09-13T22:31:31Z</t>
         </is>
       </c>
     </row>
@@ -6236,7 +6236,7 @@
       </c>
       <c r="K121" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:00Z</t>
+          <t>2026-09-13T22:31:31Z</t>
         </is>
       </c>
     </row>
@@ -6285,7 +6285,7 @@
       </c>
       <c r="K122" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:00Z</t>
+          <t>2026-09-13T22:31:31Z</t>
         </is>
       </c>
     </row>
@@ -6334,7 +6334,7 @@
       </c>
       <c r="K123" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:00Z</t>
+          <t>2026-09-13T22:31:31Z</t>
         </is>
       </c>
     </row>
@@ -6383,7 +6383,7 @@
       </c>
       <c r="K124" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:00Z</t>
+          <t>2026-09-13T22:31:31Z</t>
         </is>
       </c>
     </row>
@@ -6432,7 +6432,7 @@
       </c>
       <c r="K125" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:00Z</t>
+          <t>2026-09-13T22:31:31Z</t>
         </is>
       </c>
     </row>
@@ -6481,7 +6481,7 @@
       </c>
       <c r="K126" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:00Z</t>
+          <t>2026-09-13T22:31:31Z</t>
         </is>
       </c>
     </row>
@@ -6530,7 +6530,7 @@
       </c>
       <c r="K127" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:00Z</t>
+          <t>2026-09-13T22:31:31Z</t>
         </is>
       </c>
     </row>
@@ -6579,7 +6579,7 @@
       </c>
       <c r="K128" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:00Z</t>
+          <t>2026-09-13T22:31:31Z</t>
         </is>
       </c>
     </row>
@@ -6628,7 +6628,7 @@
       </c>
       <c r="K129" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:00Z</t>
+          <t>2026-09-13T22:31:31Z</t>
         </is>
       </c>
     </row>
@@ -6677,7 +6677,7 @@
       </c>
       <c r="K130" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:00Z</t>
+          <t>2026-09-13T22:31:31Z</t>
         </is>
       </c>
     </row>
@@ -6726,7 +6726,7 @@
       </c>
       <c r="K131" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:00Z</t>
+          <t>2026-09-13T22:31:31Z</t>
         </is>
       </c>
     </row>
@@ -6775,7 +6775,7 @@
       </c>
       <c r="K132" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:00Z</t>
+          <t>2026-09-13T22:31:31Z</t>
         </is>
       </c>
     </row>
@@ -6824,7 +6824,7 @@
       </c>
       <c r="K133" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:00Z</t>
+          <t>2026-09-13T22:31:31Z</t>
         </is>
       </c>
     </row>
@@ -6873,7 +6873,7 @@
       </c>
       <c r="K134" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:00Z</t>
+          <t>2026-09-13T22:31:31Z</t>
         </is>
       </c>
     </row>
@@ -6922,7 +6922,7 @@
       </c>
       <c r="K135" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:00Z</t>
+          <t>2026-09-13T22:31:31Z</t>
         </is>
       </c>
     </row>
@@ -6971,7 +6971,7 @@
       </c>
       <c r="K136" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:00Z</t>
+          <t>2026-09-13T22:31:31Z</t>
         </is>
       </c>
     </row>
@@ -7020,7 +7020,7 @@
       </c>
       <c r="K137" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:00Z</t>
+          <t>2026-09-13T22:31:31Z</t>
         </is>
       </c>
     </row>
@@ -7069,7 +7069,7 @@
       </c>
       <c r="K138" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:00Z</t>
+          <t>2026-09-13T22:31:31Z</t>
         </is>
       </c>
     </row>
@@ -7118,7 +7118,7 @@
       </c>
       <c r="K139" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:00Z</t>
+          <t>2026-09-13T22:31:31Z</t>
         </is>
       </c>
     </row>
@@ -7167,7 +7167,7 @@
       </c>
       <c r="K140" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:00Z</t>
+          <t>2026-09-13T22:31:31Z</t>
         </is>
       </c>
     </row>
@@ -7216,7 +7216,7 @@
       </c>
       <c r="K141" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:00Z</t>
+          <t>2026-09-13T22:31:31Z</t>
         </is>
       </c>
     </row>
@@ -7265,7 +7265,7 @@
       </c>
       <c r="K142" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:00Z</t>
+          <t>2026-09-13T22:31:31Z</t>
         </is>
       </c>
     </row>
@@ -7314,7 +7314,7 @@
       </c>
       <c r="K143" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:00Z</t>
+          <t>2026-09-13T22:31:31Z</t>
         </is>
       </c>
     </row>
@@ -7363,7 +7363,7 @@
       </c>
       <c r="K144" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:00Z</t>
+          <t>2026-09-13T22:31:31Z</t>
         </is>
       </c>
     </row>
@@ -7412,7 +7412,7 @@
       </c>
       <c r="K145" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:00Z</t>
+          <t>2026-09-13T22:31:31Z</t>
         </is>
       </c>
     </row>
@@ -7461,7 +7461,7 @@
       </c>
       <c r="K146" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:00Z</t>
+          <t>2026-09-13T22:31:31Z</t>
         </is>
       </c>
     </row>
@@ -7510,7 +7510,7 @@
       </c>
       <c r="K147" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:00Z</t>
+          <t>2026-09-13T22:31:31Z</t>
         </is>
       </c>
     </row>
@@ -7559,7 +7559,7 @@
       </c>
       <c r="K148" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:00Z</t>
+          <t>2026-09-13T22:31:31Z</t>
         </is>
       </c>
     </row>
@@ -7608,7 +7608,7 @@
       </c>
       <c r="K149" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:00Z</t>
+          <t>2026-09-13T22:31:31Z</t>
         </is>
       </c>
     </row>
@@ -7657,7 +7657,7 @@
       </c>
       <c r="K150" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:00Z</t>
+          <t>2026-09-13T22:31:31Z</t>
         </is>
       </c>
     </row>
@@ -7706,7 +7706,7 @@
       </c>
       <c r="K151" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:00Z</t>
+          <t>2026-09-13T22:31:31Z</t>
         </is>
       </c>
     </row>
@@ -7755,7 +7755,7 @@
       </c>
       <c r="K152" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:00Z</t>
+          <t>2026-09-13T22:31:31Z</t>
         </is>
       </c>
     </row>
@@ -7804,7 +7804,7 @@
       </c>
       <c r="K153" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:00Z</t>
+          <t>2026-09-13T22:31:31Z</t>
         </is>
       </c>
     </row>
@@ -7853,7 +7853,7 @@
       </c>
       <c r="K154" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:00Z</t>
+          <t>2026-09-13T22:31:31Z</t>
         </is>
       </c>
     </row>
@@ -7902,7 +7902,7 @@
       </c>
       <c r="K155" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:00Z</t>
+          <t>2026-09-13T22:31:31Z</t>
         </is>
       </c>
     </row>
@@ -7951,7 +7951,7 @@
       </c>
       <c r="K156" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:00Z</t>
+          <t>2026-09-13T22:31:31Z</t>
         </is>
       </c>
     </row>
@@ -8000,7 +8000,7 @@
       </c>
       <c r="K157" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:00Z</t>
+          <t>2026-09-13T22:31:31Z</t>
         </is>
       </c>
     </row>
@@ -8049,7 +8049,7 @@
       </c>
       <c r="K158" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:00Z</t>
+          <t>2026-09-13T22:31:31Z</t>
         </is>
       </c>
     </row>
@@ -8098,7 +8098,7 @@
       </c>
       <c r="K159" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:00Z</t>
+          <t>2026-09-13T22:31:31Z</t>
         </is>
       </c>
     </row>
@@ -8147,7 +8147,7 @@
       </c>
       <c r="K160" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:00Z</t>
+          <t>2026-09-13T22:31:31Z</t>
         </is>
       </c>
     </row>
@@ -8196,7 +8196,7 @@
       </c>
       <c r="K161" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:00Z</t>
+          <t>2026-09-13T22:31:31Z</t>
         </is>
       </c>
     </row>
@@ -8245,7 +8245,7 @@
       </c>
       <c r="K162" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:00Z</t>
+          <t>2026-09-13T22:31:31Z</t>
         </is>
       </c>
     </row>
@@ -8294,7 +8294,7 @@
       </c>
       <c r="K163" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:00Z</t>
+          <t>2026-09-13T22:31:31Z</t>
         </is>
       </c>
     </row>
@@ -8343,7 +8343,7 @@
       </c>
       <c r="K164" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:00Z</t>
+          <t>2026-09-13T22:31:31Z</t>
         </is>
       </c>
     </row>
@@ -8392,7 +8392,7 @@
       </c>
       <c r="K165" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:00Z</t>
+          <t>2026-09-13T22:31:31Z</t>
         </is>
       </c>
     </row>
@@ -8441,7 +8441,7 @@
       </c>
       <c r="K166" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:00Z</t>
+          <t>2026-09-13T22:31:31Z</t>
         </is>
       </c>
     </row>
@@ -8490,7 +8490,7 @@
       </c>
       <c r="K167" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:00Z</t>
+          <t>2026-09-13T22:31:31Z</t>
         </is>
       </c>
     </row>
@@ -8539,7 +8539,7 @@
       </c>
       <c r="K168" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:00Z</t>
+          <t>2026-09-13T22:31:31Z</t>
         </is>
       </c>
     </row>
@@ -8588,7 +8588,7 @@
       </c>
       <c r="K169" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:00Z</t>
+          <t>2026-09-13T22:31:31Z</t>
         </is>
       </c>
     </row>
@@ -8637,7 +8637,7 @@
       </c>
       <c r="K170" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:00Z</t>
+          <t>2026-09-13T22:31:31Z</t>
         </is>
       </c>
     </row>
@@ -8686,7 +8686,7 @@
       </c>
       <c r="K171" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:00Z</t>
+          <t>2026-09-13T22:31:31Z</t>
         </is>
       </c>
     </row>
@@ -8735,7 +8735,7 @@
       </c>
       <c r="K172" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:00Z</t>
+          <t>2026-09-13T22:31:31Z</t>
         </is>
       </c>
     </row>
@@ -8784,7 +8784,7 @@
       </c>
       <c r="K173" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:00Z</t>
+          <t>2026-09-13T22:31:31Z</t>
         </is>
       </c>
     </row>
@@ -8833,7 +8833,7 @@
       </c>
       <c r="K174" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:00Z</t>
+          <t>2026-09-13T22:31:31Z</t>
         </is>
       </c>
     </row>
@@ -8882,7 +8882,7 @@
       </c>
       <c r="K175" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:00Z</t>
+          <t>2026-09-13T22:31:31Z</t>
         </is>
       </c>
     </row>
@@ -8931,7 +8931,7 @@
       </c>
       <c r="K176" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:00Z</t>
+          <t>2026-09-13T22:31:31Z</t>
         </is>
       </c>
     </row>
@@ -8980,7 +8980,7 @@
       </c>
       <c r="K177" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:00Z</t>
+          <t>2026-09-13T22:31:31Z</t>
         </is>
       </c>
     </row>
@@ -9029,7 +9029,7 @@
       </c>
       <c r="K178" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:00Z</t>
+          <t>2026-09-13T22:31:31Z</t>
         </is>
       </c>
     </row>
@@ -9078,7 +9078,7 @@
       </c>
       <c r="K179" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:00Z</t>
+          <t>2026-09-13T22:31:31Z</t>
         </is>
       </c>
     </row>
@@ -9127,7 +9127,7 @@
       </c>
       <c r="K180" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:00Z</t>
+          <t>2026-09-13T22:31:31Z</t>
         </is>
       </c>
     </row>
@@ -9176,7 +9176,7 @@
       </c>
       <c r="K181" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:00Z</t>
+          <t>2026-09-13T22:31:31Z</t>
         </is>
       </c>
     </row>
@@ -9225,7 +9225,7 @@
       </c>
       <c r="K182" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:00Z</t>
+          <t>2026-09-13T22:31:31Z</t>
         </is>
       </c>
     </row>
@@ -9274,7 +9274,7 @@
       </c>
       <c r="K183" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:00Z</t>
+          <t>2026-09-13T22:31:31Z</t>
         </is>
       </c>
     </row>
@@ -9323,7 +9323,7 @@
       </c>
       <c r="K184" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:00Z</t>
+          <t>2026-09-13T22:31:31Z</t>
         </is>
       </c>
     </row>
@@ -9372,7 +9372,7 @@
       </c>
       <c r="K185" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:00Z</t>
+          <t>2026-09-13T22:31:31Z</t>
         </is>
       </c>
     </row>
@@ -9421,7 +9421,7 @@
       </c>
       <c r="K186" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:00Z</t>
+          <t>2026-09-13T22:31:31Z</t>
         </is>
       </c>
     </row>
@@ -9470,7 +9470,7 @@
       </c>
       <c r="K187" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:00Z</t>
+          <t>2026-09-13T22:31:31Z</t>
         </is>
       </c>
     </row>
@@ -9519,7 +9519,7 @@
       </c>
       <c r="K188" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:00Z</t>
+          <t>2026-09-13T22:31:31Z</t>
         </is>
       </c>
     </row>
@@ -9568,7 +9568,7 @@
       </c>
       <c r="K189" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:00Z</t>
+          <t>2026-09-13T22:31:31Z</t>
         </is>
       </c>
     </row>
@@ -9617,7 +9617,7 @@
       </c>
       <c r="K190" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:00Z</t>
+          <t>2026-09-13T22:31:31Z</t>
         </is>
       </c>
     </row>
@@ -9666,7 +9666,7 @@
       </c>
       <c r="K191" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:00Z</t>
+          <t>2026-09-13T22:31:31Z</t>
         </is>
       </c>
     </row>
@@ -9715,7 +9715,7 @@
       </c>
       <c r="K192" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:00Z</t>
+          <t>2026-09-13T22:31:31Z</t>
         </is>
       </c>
     </row>
@@ -9764,7 +9764,7 @@
       </c>
       <c r="K193" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:00Z</t>
+          <t>2026-09-13T22:31:31Z</t>
         </is>
       </c>
     </row>
@@ -9813,7 +9813,7 @@
       </c>
       <c r="K194" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:00Z</t>
+          <t>2026-09-13T22:31:31Z</t>
         </is>
       </c>
     </row>
@@ -9862,7 +9862,7 @@
       </c>
       <c r="K195" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:00Z</t>
+          <t>2026-09-13T22:31:31Z</t>
         </is>
       </c>
     </row>
@@ -9911,7 +9911,7 @@
       </c>
       <c r="K196" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:00Z</t>
+          <t>2026-09-13T22:31:31Z</t>
         </is>
       </c>
     </row>
@@ -9960,7 +9960,7 @@
       </c>
       <c r="K197" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:00Z</t>
+          <t>2026-09-13T22:31:31Z</t>
         </is>
       </c>
     </row>
@@ -10009,7 +10009,7 @@
       </c>
       <c r="K198" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:00Z</t>
+          <t>2026-09-13T22:31:31Z</t>
         </is>
       </c>
     </row>
@@ -10058,7 +10058,7 @@
       </c>
       <c r="K199" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:00Z</t>
+          <t>2026-09-13T22:31:31Z</t>
         </is>
       </c>
     </row>
@@ -10107,7 +10107,7 @@
       </c>
       <c r="K200" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:00Z</t>
+          <t>2026-09-13T22:31:31Z</t>
         </is>
       </c>
     </row>
@@ -10156,7 +10156,7 @@
       </c>
       <c r="K201" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:00Z</t>
+          <t>2026-09-13T22:31:31Z</t>
         </is>
       </c>
     </row>
@@ -10205,7 +10205,7 @@
       </c>
       <c r="K202" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:00Z</t>
+          <t>2026-09-13T22:31:31Z</t>
         </is>
       </c>
     </row>
@@ -10254,7 +10254,7 @@
       </c>
       <c r="K203" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:00Z</t>
+          <t>2026-09-13T22:31:31Z</t>
         </is>
       </c>
     </row>
@@ -10303,7 +10303,7 @@
       </c>
       <c r="K204" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:00Z</t>
+          <t>2026-09-13T22:31:31Z</t>
         </is>
       </c>
     </row>
@@ -10352,7 +10352,7 @@
       </c>
       <c r="K205" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:00Z</t>
+          <t>2026-09-13T22:31:31Z</t>
         </is>
       </c>
     </row>
@@ -10401,7 +10401,7 @@
       </c>
       <c r="K206" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:00Z</t>
+          <t>2026-09-13T22:31:31Z</t>
         </is>
       </c>
     </row>
@@ -10450,7 +10450,7 @@
       </c>
       <c r="K207" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:00Z</t>
+          <t>2026-09-13T22:31:31Z</t>
         </is>
       </c>
     </row>
@@ -10499,7 +10499,7 @@
       </c>
       <c r="K208" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:00Z</t>
+          <t>2026-09-13T22:31:31Z</t>
         </is>
       </c>
     </row>
@@ -10548,7 +10548,7 @@
       </c>
       <c r="K209" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:00Z</t>
+          <t>2026-09-13T22:31:31Z</t>
         </is>
       </c>
     </row>
@@ -10597,7 +10597,7 @@
       </c>
       <c r="K210" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:00Z</t>
+          <t>2026-09-13T22:31:31Z</t>
         </is>
       </c>
     </row>
@@ -10646,7 +10646,7 @@
       </c>
       <c r="K211" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:00Z</t>
+          <t>2026-09-13T22:31:31Z</t>
         </is>
       </c>
     </row>
@@ -10695,7 +10695,7 @@
       </c>
       <c r="K212" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:00Z</t>
+          <t>2026-09-13T22:31:31Z</t>
         </is>
       </c>
     </row>
@@ -10744,7 +10744,7 @@
       </c>
       <c r="K213" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:00Z</t>
+          <t>2026-09-13T22:31:31Z</t>
         </is>
       </c>
     </row>
@@ -10793,7 +10793,7 @@
       </c>
       <c r="K214" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:00Z</t>
+          <t>2026-09-13T22:31:31Z</t>
         </is>
       </c>
     </row>
@@ -10842,7 +10842,7 @@
       </c>
       <c r="K215" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:00Z</t>
+          <t>2026-09-13T22:31:31Z</t>
         </is>
       </c>
     </row>
@@ -10891,7 +10891,7 @@
       </c>
       <c r="K216" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:00Z</t>
+          <t>2026-09-13T22:31:31Z</t>
         </is>
       </c>
     </row>
@@ -10940,7 +10940,7 @@
       </c>
       <c r="K217" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:00Z</t>
+          <t>2026-09-13T22:31:31Z</t>
         </is>
       </c>
     </row>
@@ -10989,7 +10989,7 @@
       </c>
       <c r="K218" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:00Z</t>
+          <t>2026-09-13T22:31:31Z</t>
         </is>
       </c>
     </row>
@@ -11038,7 +11038,7 @@
       </c>
       <c r="K219" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:00Z</t>
+          <t>2026-09-13T22:31:31Z</t>
         </is>
       </c>
     </row>
@@ -11087,7 +11087,7 @@
       </c>
       <c r="K220" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:00Z</t>
+          <t>2026-09-13T22:31:31Z</t>
         </is>
       </c>
     </row>
@@ -11136,7 +11136,7 @@
       </c>
       <c r="K221" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:00Z</t>
+          <t>2026-09-13T22:31:31Z</t>
         </is>
       </c>
     </row>
@@ -11185,7 +11185,7 @@
       </c>
       <c r="K222" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:00Z</t>
+          <t>2026-09-13T22:31:31Z</t>
         </is>
       </c>
     </row>
@@ -11234,7 +11234,7 @@
       </c>
       <c r="K223" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:00Z</t>
+          <t>2026-09-13T22:31:31Z</t>
         </is>
       </c>
     </row>
@@ -11283,7 +11283,7 @@
       </c>
       <c r="K224" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:00Z</t>
+          <t>2026-09-13T22:31:31Z</t>
         </is>
       </c>
     </row>
@@ -11332,7 +11332,7 @@
       </c>
       <c r="K225" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:00Z</t>
+          <t>2026-09-13T22:31:31Z</t>
         </is>
       </c>
     </row>
@@ -11381,7 +11381,7 @@
       </c>
       <c r="K226" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:00Z</t>
+          <t>2026-09-13T22:31:31Z</t>
         </is>
       </c>
     </row>
@@ -11430,7 +11430,7 @@
       </c>
       <c r="K227" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:00Z</t>
+          <t>2026-09-13T22:31:31Z</t>
         </is>
       </c>
     </row>
@@ -11479,7 +11479,7 @@
       </c>
       <c r="K228" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:00Z</t>
+          <t>2026-09-13T22:31:31Z</t>
         </is>
       </c>
     </row>
@@ -11528,7 +11528,7 @@
       </c>
       <c r="K229" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:00Z</t>
+          <t>2026-09-13T22:31:31Z</t>
         </is>
       </c>
     </row>
@@ -11577,7 +11577,7 @@
       </c>
       <c r="K230" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:00Z</t>
+          <t>2026-09-13T22:31:31Z</t>
         </is>
       </c>
     </row>
@@ -11626,7 +11626,7 @@
       </c>
       <c r="K231" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:00Z</t>
+          <t>2026-09-13T22:31:31Z</t>
         </is>
       </c>
     </row>
@@ -11758,7 +11758,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:00Z</t>
+          <t>2026-09-13T22:31:31Z</t>
         </is>
       </c>
     </row>
@@ -11804,7 +11804,7 @@
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>{"date": "2026-08-01", "year": 2026, "month": 8, "month_name": "Agosto", "index_value": 637409769724325.1, "monthly_variation_pct": 8.9, "unit": "Índice base diciembre 2007=100 y variación mensual %", "frequency": "monthly", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/precios_consumidor/4_5_7_2.xls", "fetched_at": "2026-09-12T22:27:00Z"}</t>
+          <t>{"date": "2026-08-01", "year": 2026, "month": 8, "month_name": "Agosto", "index_value": 637409769724325.1, "monthly_variation_pct": 8.9, "unit": "Índice base diciembre 2007=100 y variación mensual %", "frequency": "monthly", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/precios_consumidor/4_5_7_2.xls", "fetched_at": "2026-09-13T22:31:31Z"}</t>
         </is>
       </c>
     </row>

--- a/assets/data/bcv/excel/ove_bcv_inpc_nacional_mensual.xlsx
+++ b/assets/data/bcv/excel/ove_bcv_inpc_nacional_mensual.xlsx
@@ -650,7 +650,7 @@
       </c>
       <c r="K7" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:31Z</t>
+          <t>2026-09-14T23:16:42Z</t>
         </is>
       </c>
     </row>
@@ -699,7 +699,7 @@
       </c>
       <c r="K8" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:31Z</t>
+          <t>2026-09-14T23:16:42Z</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="K9" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:31Z</t>
+          <t>2026-09-14T23:16:42Z</t>
         </is>
       </c>
     </row>
@@ -797,7 +797,7 @@
       </c>
       <c r="K10" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:31Z</t>
+          <t>2026-09-14T23:16:42Z</t>
         </is>
       </c>
     </row>
@@ -846,7 +846,7 @@
       </c>
       <c r="K11" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:31Z</t>
+          <t>2026-09-14T23:16:42Z</t>
         </is>
       </c>
     </row>
@@ -895,7 +895,7 @@
       </c>
       <c r="K12" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:31Z</t>
+          <t>2026-09-14T23:16:42Z</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="K13" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:31Z</t>
+          <t>2026-09-14T23:16:42Z</t>
         </is>
       </c>
     </row>
@@ -993,7 +993,7 @@
       </c>
       <c r="K14" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:31Z</t>
+          <t>2026-09-14T23:16:42Z</t>
         </is>
       </c>
     </row>
@@ -1042,7 +1042,7 @@
       </c>
       <c r="K15" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:31Z</t>
+          <t>2026-09-14T23:16:42Z</t>
         </is>
       </c>
     </row>
@@ -1091,7 +1091,7 @@
       </c>
       <c r="K16" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:31Z</t>
+          <t>2026-09-14T23:16:42Z</t>
         </is>
       </c>
     </row>
@@ -1140,7 +1140,7 @@
       </c>
       <c r="K17" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:31Z</t>
+          <t>2026-09-14T23:16:42Z</t>
         </is>
       </c>
     </row>
@@ -1189,7 +1189,7 @@
       </c>
       <c r="K18" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:31Z</t>
+          <t>2026-09-14T23:16:42Z</t>
         </is>
       </c>
     </row>
@@ -1238,7 +1238,7 @@
       </c>
       <c r="K19" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:31Z</t>
+          <t>2026-09-14T23:16:42Z</t>
         </is>
       </c>
     </row>
@@ -1287,7 +1287,7 @@
       </c>
       <c r="K20" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:31Z</t>
+          <t>2026-09-14T23:16:42Z</t>
         </is>
       </c>
     </row>
@@ -1336,7 +1336,7 @@
       </c>
       <c r="K21" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:31Z</t>
+          <t>2026-09-14T23:16:42Z</t>
         </is>
       </c>
     </row>
@@ -1385,7 +1385,7 @@
       </c>
       <c r="K22" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:31Z</t>
+          <t>2026-09-14T23:16:42Z</t>
         </is>
       </c>
     </row>
@@ -1434,7 +1434,7 @@
       </c>
       <c r="K23" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:31Z</t>
+          <t>2026-09-14T23:16:42Z</t>
         </is>
       </c>
     </row>
@@ -1483,7 +1483,7 @@
       </c>
       <c r="K24" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:31Z</t>
+          <t>2026-09-14T23:16:42Z</t>
         </is>
       </c>
     </row>
@@ -1532,7 +1532,7 @@
       </c>
       <c r="K25" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:31Z</t>
+          <t>2026-09-14T23:16:42Z</t>
         </is>
       </c>
     </row>
@@ -1581,7 +1581,7 @@
       </c>
       <c r="K26" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:31Z</t>
+          <t>2026-09-14T23:16:42Z</t>
         </is>
       </c>
     </row>
@@ -1630,7 +1630,7 @@
       </c>
       <c r="K27" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:31Z</t>
+          <t>2026-09-14T23:16:42Z</t>
         </is>
       </c>
     </row>
@@ -1679,7 +1679,7 @@
       </c>
       <c r="K28" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:31Z</t>
+          <t>2026-09-14T23:16:42Z</t>
         </is>
       </c>
     </row>
@@ -1728,7 +1728,7 @@
       </c>
       <c r="K29" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:31Z</t>
+          <t>2026-09-14T23:16:42Z</t>
         </is>
       </c>
     </row>
@@ -1777,7 +1777,7 @@
       </c>
       <c r="K30" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:31Z</t>
+          <t>2026-09-14T23:16:42Z</t>
         </is>
       </c>
     </row>
@@ -1826,7 +1826,7 @@
       </c>
       <c r="K31" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:31Z</t>
+          <t>2026-09-14T23:16:42Z</t>
         </is>
       </c>
     </row>
@@ -1875,7 +1875,7 @@
       </c>
       <c r="K32" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:31Z</t>
+          <t>2026-09-14T23:16:42Z</t>
         </is>
       </c>
     </row>
@@ -1924,7 +1924,7 @@
       </c>
       <c r="K33" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:31Z</t>
+          <t>2026-09-14T23:16:42Z</t>
         </is>
       </c>
     </row>
@@ -1973,7 +1973,7 @@
       </c>
       <c r="K34" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:31Z</t>
+          <t>2026-09-14T23:16:42Z</t>
         </is>
       </c>
     </row>
@@ -2022,7 +2022,7 @@
       </c>
       <c r="K35" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:31Z</t>
+          <t>2026-09-14T23:16:42Z</t>
         </is>
       </c>
     </row>
@@ -2071,7 +2071,7 @@
       </c>
       <c r="K36" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:31Z</t>
+          <t>2026-09-14T23:16:42Z</t>
         </is>
       </c>
     </row>
@@ -2120,7 +2120,7 @@
       </c>
       <c r="K37" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:31Z</t>
+          <t>2026-09-14T23:16:42Z</t>
         </is>
       </c>
     </row>
@@ -2169,7 +2169,7 @@
       </c>
       <c r="K38" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:31Z</t>
+          <t>2026-09-14T23:16:42Z</t>
         </is>
       </c>
     </row>
@@ -2218,7 +2218,7 @@
       </c>
       <c r="K39" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:31Z</t>
+          <t>2026-09-14T23:16:42Z</t>
         </is>
       </c>
     </row>
@@ -2267,7 +2267,7 @@
       </c>
       <c r="K40" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:31Z</t>
+          <t>2026-09-14T23:16:42Z</t>
         </is>
       </c>
     </row>
@@ -2316,7 +2316,7 @@
       </c>
       <c r="K41" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:31Z</t>
+          <t>2026-09-14T23:16:42Z</t>
         </is>
       </c>
     </row>
@@ -2365,7 +2365,7 @@
       </c>
       <c r="K42" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:31Z</t>
+          <t>2026-09-14T23:16:42Z</t>
         </is>
       </c>
     </row>
@@ -2414,7 +2414,7 @@
       </c>
       <c r="K43" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:31Z</t>
+          <t>2026-09-14T23:16:42Z</t>
         </is>
       </c>
     </row>
@@ -2463,7 +2463,7 @@
       </c>
       <c r="K44" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:31Z</t>
+          <t>2026-09-14T23:16:42Z</t>
         </is>
       </c>
     </row>
@@ -2512,7 +2512,7 @@
       </c>
       <c r="K45" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:31Z</t>
+          <t>2026-09-14T23:16:42Z</t>
         </is>
       </c>
     </row>
@@ -2561,7 +2561,7 @@
       </c>
       <c r="K46" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:31Z</t>
+          <t>2026-09-14T23:16:42Z</t>
         </is>
       </c>
     </row>
@@ -2610,7 +2610,7 @@
       </c>
       <c r="K47" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:31Z</t>
+          <t>2026-09-14T23:16:42Z</t>
         </is>
       </c>
     </row>
@@ -2659,7 +2659,7 @@
       </c>
       <c r="K48" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:31Z</t>
+          <t>2026-09-14T23:16:42Z</t>
         </is>
       </c>
     </row>
@@ -2708,7 +2708,7 @@
       </c>
       <c r="K49" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:31Z</t>
+          <t>2026-09-14T23:16:42Z</t>
         </is>
       </c>
     </row>
@@ -2757,7 +2757,7 @@
       </c>
       <c r="K50" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:31Z</t>
+          <t>2026-09-14T23:16:42Z</t>
         </is>
       </c>
     </row>
@@ -2806,7 +2806,7 @@
       </c>
       <c r="K51" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:31Z</t>
+          <t>2026-09-14T23:16:42Z</t>
         </is>
       </c>
     </row>
@@ -2855,7 +2855,7 @@
       </c>
       <c r="K52" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:31Z</t>
+          <t>2026-09-14T23:16:42Z</t>
         </is>
       </c>
     </row>
@@ -2904,7 +2904,7 @@
       </c>
       <c r="K53" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:31Z</t>
+          <t>2026-09-14T23:16:42Z</t>
         </is>
       </c>
     </row>
@@ -2953,7 +2953,7 @@
       </c>
       <c r="K54" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:31Z</t>
+          <t>2026-09-14T23:16:42Z</t>
         </is>
       </c>
     </row>
@@ -3002,7 +3002,7 @@
       </c>
       <c r="K55" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:31Z</t>
+          <t>2026-09-14T23:16:42Z</t>
         </is>
       </c>
     </row>
@@ -3051,7 +3051,7 @@
       </c>
       <c r="K56" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:31Z</t>
+          <t>2026-09-14T23:16:42Z</t>
         </is>
       </c>
     </row>
@@ -3100,7 +3100,7 @@
       </c>
       <c r="K57" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:31Z</t>
+          <t>2026-09-14T23:16:42Z</t>
         </is>
       </c>
     </row>
@@ -3149,7 +3149,7 @@
       </c>
       <c r="K58" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:31Z</t>
+          <t>2026-09-14T23:16:42Z</t>
         </is>
       </c>
     </row>
@@ -3198,7 +3198,7 @@
       </c>
       <c r="K59" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:31Z</t>
+          <t>2026-09-14T23:16:42Z</t>
         </is>
       </c>
     </row>
@@ -3247,7 +3247,7 @@
       </c>
       <c r="K60" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:31Z</t>
+          <t>2026-09-14T23:16:42Z</t>
         </is>
       </c>
     </row>
@@ -3296,7 +3296,7 @@
       </c>
       <c r="K61" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:31Z</t>
+          <t>2026-09-14T23:16:42Z</t>
         </is>
       </c>
     </row>
@@ -3345,7 +3345,7 @@
       </c>
       <c r="K62" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:31Z</t>
+          <t>2026-09-14T23:16:42Z</t>
         </is>
       </c>
     </row>
@@ -3394,7 +3394,7 @@
       </c>
       <c r="K63" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:31Z</t>
+          <t>2026-09-14T23:16:42Z</t>
         </is>
       </c>
     </row>
@@ -3443,7 +3443,7 @@
       </c>
       <c r="K64" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:31Z</t>
+          <t>2026-09-14T23:16:42Z</t>
         </is>
       </c>
     </row>
@@ -3492,7 +3492,7 @@
       </c>
       <c r="K65" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:31Z</t>
+          <t>2026-09-14T23:16:42Z</t>
         </is>
       </c>
     </row>
@@ -3541,7 +3541,7 @@
       </c>
       <c r="K66" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:31Z</t>
+          <t>2026-09-14T23:16:42Z</t>
         </is>
       </c>
     </row>
@@ -3590,7 +3590,7 @@
       </c>
       <c r="K67" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:31Z</t>
+          <t>2026-09-14T23:16:42Z</t>
         </is>
       </c>
     </row>
@@ -3639,7 +3639,7 @@
       </c>
       <c r="K68" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:31Z</t>
+          <t>2026-09-14T23:16:42Z</t>
         </is>
       </c>
     </row>
@@ -3688,7 +3688,7 @@
       </c>
       <c r="K69" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:31Z</t>
+          <t>2026-09-14T23:16:42Z</t>
         </is>
       </c>
     </row>
@@ -3737,7 +3737,7 @@
       </c>
       <c r="K70" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:31Z</t>
+          <t>2026-09-14T23:16:42Z</t>
         </is>
       </c>
     </row>
@@ -3786,7 +3786,7 @@
       </c>
       <c r="K71" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:31Z</t>
+          <t>2026-09-14T23:16:42Z</t>
         </is>
       </c>
     </row>
@@ -3835,7 +3835,7 @@
       </c>
       <c r="K72" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:31Z</t>
+          <t>2026-09-14T23:16:42Z</t>
         </is>
       </c>
     </row>
@@ -3884,7 +3884,7 @@
       </c>
       <c r="K73" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:31Z</t>
+          <t>2026-09-14T23:16:42Z</t>
         </is>
       </c>
     </row>
@@ -3933,7 +3933,7 @@
       </c>
       <c r="K74" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:31Z</t>
+          <t>2026-09-14T23:16:42Z</t>
         </is>
       </c>
     </row>
@@ -3982,7 +3982,7 @@
       </c>
       <c r="K75" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:31Z</t>
+          <t>2026-09-14T23:16:42Z</t>
         </is>
       </c>
     </row>
@@ -4031,7 +4031,7 @@
       </c>
       <c r="K76" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:31Z</t>
+          <t>2026-09-14T23:16:42Z</t>
         </is>
       </c>
     </row>
@@ -4080,7 +4080,7 @@
       </c>
       <c r="K77" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:31Z</t>
+          <t>2026-09-14T23:16:42Z</t>
         </is>
       </c>
     </row>
@@ -4129,7 +4129,7 @@
       </c>
       <c r="K78" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:31Z</t>
+          <t>2026-09-14T23:16:42Z</t>
         </is>
       </c>
     </row>
@@ -4178,7 +4178,7 @@
       </c>
       <c r="K79" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:31Z</t>
+          <t>2026-09-14T23:16:42Z</t>
         </is>
       </c>
     </row>
@@ -4227,7 +4227,7 @@
       </c>
       <c r="K80" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:31Z</t>
+          <t>2026-09-14T23:16:42Z</t>
         </is>
       </c>
     </row>
@@ -4276,7 +4276,7 @@
       </c>
       <c r="K81" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:31Z</t>
+          <t>2026-09-14T23:16:42Z</t>
         </is>
       </c>
     </row>
@@ -4325,7 +4325,7 @@
       </c>
       <c r="K82" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:31Z</t>
+          <t>2026-09-14T23:16:42Z</t>
         </is>
       </c>
     </row>
@@ -4374,7 +4374,7 @@
       </c>
       <c r="K83" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:31Z</t>
+          <t>2026-09-14T23:16:42Z</t>
         </is>
       </c>
     </row>
@@ -4423,7 +4423,7 @@
       </c>
       <c r="K84" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:31Z</t>
+          <t>2026-09-14T23:16:42Z</t>
         </is>
       </c>
     </row>
@@ -4472,7 +4472,7 @@
       </c>
       <c r="K85" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:31Z</t>
+          <t>2026-09-14T23:16:42Z</t>
         </is>
       </c>
     </row>
@@ -4521,7 +4521,7 @@
       </c>
       <c r="K86" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:31Z</t>
+          <t>2026-09-14T23:16:42Z</t>
         </is>
       </c>
     </row>
@@ -4570,7 +4570,7 @@
       </c>
       <c r="K87" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:31Z</t>
+          <t>2026-09-14T23:16:42Z</t>
         </is>
       </c>
     </row>
@@ -4619,7 +4619,7 @@
       </c>
       <c r="K88" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:31Z</t>
+          <t>2026-09-14T23:16:42Z</t>
         </is>
       </c>
     </row>
@@ -4668,7 +4668,7 @@
       </c>
       <c r="K89" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:31Z</t>
+          <t>2026-09-14T23:16:42Z</t>
         </is>
       </c>
     </row>
@@ -4717,7 +4717,7 @@
       </c>
       <c r="K90" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:31Z</t>
+          <t>2026-09-14T23:16:42Z</t>
         </is>
       </c>
     </row>
@@ -4766,7 +4766,7 @@
       </c>
       <c r="K91" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:31Z</t>
+          <t>2026-09-14T23:16:42Z</t>
         </is>
       </c>
     </row>
@@ -4815,7 +4815,7 @@
       </c>
       <c r="K92" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:31Z</t>
+          <t>2026-09-14T23:16:42Z</t>
         </is>
       </c>
     </row>
@@ -4864,7 +4864,7 @@
       </c>
       <c r="K93" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:31Z</t>
+          <t>2026-09-14T23:16:42Z</t>
         </is>
       </c>
     </row>
@@ -4913,7 +4913,7 @@
       </c>
       <c r="K94" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:31Z</t>
+          <t>2026-09-14T23:16:42Z</t>
         </is>
       </c>
     </row>
@@ -4962,7 +4962,7 @@
       </c>
       <c r="K95" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:31Z</t>
+          <t>2026-09-14T23:16:42Z</t>
         </is>
       </c>
     </row>
@@ -5011,7 +5011,7 @@
       </c>
       <c r="K96" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:31Z</t>
+          <t>2026-09-14T23:16:42Z</t>
         </is>
       </c>
     </row>
@@ -5060,7 +5060,7 @@
       </c>
       <c r="K97" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:31Z</t>
+          <t>2026-09-14T23:16:42Z</t>
         </is>
       </c>
     </row>
@@ -5109,7 +5109,7 @@
       </c>
       <c r="K98" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:31Z</t>
+          <t>2026-09-14T23:16:42Z</t>
         </is>
       </c>
     </row>
@@ -5158,7 +5158,7 @@
       </c>
       <c r="K99" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:31Z</t>
+          <t>2026-09-14T23:16:42Z</t>
         </is>
       </c>
     </row>
@@ -5207,7 +5207,7 @@
       </c>
       <c r="K100" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:31Z</t>
+          <t>2026-09-14T23:16:42Z</t>
         </is>
       </c>
     </row>
@@ -5256,7 +5256,7 @@
       </c>
       <c r="K101" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:31Z</t>
+          <t>2026-09-14T23:16:42Z</t>
         </is>
       </c>
     </row>
@@ -5305,7 +5305,7 @@
       </c>
       <c r="K102" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:31Z</t>
+          <t>2026-09-14T23:16:42Z</t>
         </is>
       </c>
     </row>
@@ -5354,7 +5354,7 @@
       </c>
       <c r="K103" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:31Z</t>
+          <t>2026-09-14T23:16:42Z</t>
         </is>
       </c>
     </row>
@@ -5403,7 +5403,7 @@
       </c>
       <c r="K104" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:31Z</t>
+          <t>2026-09-14T23:16:42Z</t>
         </is>
       </c>
     </row>
@@ -5452,7 +5452,7 @@
       </c>
       <c r="K105" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:31Z</t>
+          <t>2026-09-14T23:16:42Z</t>
         </is>
       </c>
     </row>
@@ -5501,7 +5501,7 @@
       </c>
       <c r="K106" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:31Z</t>
+          <t>2026-09-14T23:16:42Z</t>
         </is>
       </c>
     </row>
@@ -5550,7 +5550,7 @@
       </c>
       <c r="K107" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:31Z</t>
+          <t>2026-09-14T23:16:42Z</t>
         </is>
       </c>
     </row>
@@ -5599,7 +5599,7 @@
       </c>
       <c r="K108" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:31Z</t>
+          <t>2026-09-14T23:16:42Z</t>
         </is>
       </c>
     </row>
@@ -5648,7 +5648,7 @@
       </c>
       <c r="K109" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:31Z</t>
+          <t>2026-09-14T23:16:42Z</t>
         </is>
       </c>
     </row>
@@ -5697,7 +5697,7 @@
       </c>
       <c r="K110" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:31Z</t>
+          <t>2026-09-14T23:16:42Z</t>
         </is>
       </c>
     </row>
@@ -5746,7 +5746,7 @@
       </c>
       <c r="K111" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:31Z</t>
+          <t>2026-09-14T23:16:42Z</t>
         </is>
       </c>
     </row>
@@ -5795,7 +5795,7 @@
       </c>
       <c r="K112" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:31Z</t>
+          <t>2026-09-14T23:16:42Z</t>
         </is>
       </c>
     </row>
@@ -5844,7 +5844,7 @@
       </c>
       <c r="K113" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:31Z</t>
+          <t>2026-09-14T23:16:42Z</t>
         </is>
       </c>
     </row>
@@ -5893,7 +5893,7 @@
       </c>
       <c r="K114" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:31Z</t>
+          <t>2026-09-14T23:16:42Z</t>
         </is>
       </c>
     </row>
@@ -5942,7 +5942,7 @@
       </c>
       <c r="K115" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:31Z</t>
+          <t>2026-09-14T23:16:42Z</t>
         </is>
       </c>
     </row>
@@ -5991,7 +5991,7 @@
       </c>
       <c r="K116" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:31Z</t>
+          <t>2026-09-14T23:16:42Z</t>
         </is>
       </c>
     </row>
@@ -6040,7 +6040,7 @@
       </c>
       <c r="K117" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:31Z</t>
+          <t>2026-09-14T23:16:42Z</t>
         </is>
       </c>
     </row>
@@ -6089,7 +6089,7 @@
       </c>
       <c r="K118" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:31Z</t>
+          <t>2026-09-14T23:16:42Z</t>
         </is>
       </c>
     </row>
@@ -6138,7 +6138,7 @@
       </c>
       <c r="K119" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:31Z</t>
+          <t>2026-09-14T23:16:42Z</t>
         </is>
       </c>
     </row>
@@ -6187,7 +6187,7 @@
       </c>
       <c r="K120" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:31Z</t>
+          <t>2026-09-14T23:16:42Z</t>
         </is>
       </c>
     </row>
@@ -6236,7 +6236,7 @@
       </c>
       <c r="K121" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:31Z</t>
+          <t>2026-09-14T23:16:42Z</t>
         </is>
       </c>
     </row>
@@ -6285,7 +6285,7 @@
       </c>
       <c r="K122" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:31Z</t>
+          <t>2026-09-14T23:16:42Z</t>
         </is>
       </c>
     </row>
@@ -6334,7 +6334,7 @@
       </c>
       <c r="K123" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:31Z</t>
+          <t>2026-09-14T23:16:42Z</t>
         </is>
       </c>
     </row>
@@ -6383,7 +6383,7 @@
       </c>
       <c r="K124" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:31Z</t>
+          <t>2026-09-14T23:16:42Z</t>
         </is>
       </c>
     </row>
@@ -6432,7 +6432,7 @@
       </c>
       <c r="K125" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:31Z</t>
+          <t>2026-09-14T23:16:42Z</t>
         </is>
       </c>
     </row>
@@ -6481,7 +6481,7 @@
       </c>
       <c r="K126" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:31Z</t>
+          <t>2026-09-14T23:16:42Z</t>
         </is>
       </c>
     </row>
@@ -6530,7 +6530,7 @@
       </c>
       <c r="K127" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:31Z</t>
+          <t>2026-09-14T23:16:42Z</t>
         </is>
       </c>
     </row>
@@ -6579,7 +6579,7 @@
       </c>
       <c r="K128" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:31Z</t>
+          <t>2026-09-14T23:16:42Z</t>
         </is>
       </c>
     </row>
@@ -6628,7 +6628,7 @@
       </c>
       <c r="K129" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:31Z</t>
+          <t>2026-09-14T23:16:42Z</t>
         </is>
       </c>
     </row>
@@ -6677,7 +6677,7 @@
       </c>
       <c r="K130" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:31Z</t>
+          <t>2026-09-14T23:16:42Z</t>
         </is>
       </c>
     </row>
@@ -6726,7 +6726,7 @@
       </c>
       <c r="K131" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:31Z</t>
+          <t>2026-09-14T23:16:42Z</t>
         </is>
       </c>
     </row>
@@ -6775,7 +6775,7 @@
       </c>
       <c r="K132" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:31Z</t>
+          <t>2026-09-14T23:16:42Z</t>
         </is>
       </c>
     </row>
@@ -6824,7 +6824,7 @@
       </c>
       <c r="K133" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:31Z</t>
+          <t>2026-09-14T23:16:42Z</t>
         </is>
       </c>
     </row>
@@ -6873,7 +6873,7 @@
       </c>
       <c r="K134" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:31Z</t>
+          <t>2026-09-14T23:16:42Z</t>
         </is>
       </c>
     </row>
@@ -6922,7 +6922,7 @@
       </c>
       <c r="K135" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:31Z</t>
+          <t>2026-09-14T23:16:42Z</t>
         </is>
       </c>
     </row>
@@ -6971,7 +6971,7 @@
       </c>
       <c r="K136" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:31Z</t>
+          <t>2026-09-14T23:16:42Z</t>
         </is>
       </c>
     </row>
@@ -7020,7 +7020,7 @@
       </c>
       <c r="K137" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:31Z</t>
+          <t>2026-09-14T23:16:42Z</t>
         </is>
       </c>
     </row>
@@ -7069,7 +7069,7 @@
       </c>
       <c r="K138" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:31Z</t>
+          <t>2026-09-14T23:16:42Z</t>
         </is>
       </c>
     </row>
@@ -7118,7 +7118,7 @@
       </c>
       <c r="K139" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:31Z</t>
+          <t>2026-09-14T23:16:42Z</t>
         </is>
       </c>
     </row>
@@ -7167,7 +7167,7 @@
       </c>
       <c r="K140" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:31Z</t>
+          <t>2026-09-14T23:16:42Z</t>
         </is>
       </c>
     </row>
@@ -7216,7 +7216,7 @@
       </c>
       <c r="K141" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:31Z</t>
+          <t>2026-09-14T23:16:42Z</t>
         </is>
       </c>
     </row>
@@ -7265,7 +7265,7 @@
       </c>
       <c r="K142" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:31Z</t>
+          <t>2026-09-14T23:16:42Z</t>
         </is>
       </c>
     </row>
@@ -7314,7 +7314,7 @@
       </c>
       <c r="K143" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:31Z</t>
+          <t>2026-09-14T23:16:42Z</t>
         </is>
       </c>
     </row>
@@ -7363,7 +7363,7 @@
       </c>
       <c r="K144" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:31Z</t>
+          <t>2026-09-14T23:16:42Z</t>
         </is>
       </c>
     </row>
@@ -7412,7 +7412,7 @@
       </c>
       <c r="K145" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:31Z</t>
+          <t>2026-09-14T23:16:42Z</t>
         </is>
       </c>
     </row>
@@ -7461,7 +7461,7 @@
       </c>
       <c r="K146" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:31Z</t>
+          <t>2026-09-14T23:16:42Z</t>
         </is>
       </c>
     </row>
@@ -7510,7 +7510,7 @@
       </c>
       <c r="K147" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:31Z</t>
+          <t>2026-09-14T23:16:42Z</t>
         </is>
       </c>
     </row>
@@ -7559,7 +7559,7 @@
       </c>
       <c r="K148" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:31Z</t>
+          <t>2026-09-14T23:16:42Z</t>
         </is>
       </c>
     </row>
@@ -7608,7 +7608,7 @@
       </c>
       <c r="K149" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:31Z</t>
+          <t>2026-09-14T23:16:42Z</t>
         </is>
       </c>
     </row>
@@ -7657,7 +7657,7 @@
       </c>
       <c r="K150" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:31Z</t>
+          <t>2026-09-14T23:16:42Z</t>
         </is>
       </c>
     </row>
@@ -7706,7 +7706,7 @@
       </c>
       <c r="K151" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:31Z</t>
+          <t>2026-09-14T23:16:42Z</t>
         </is>
       </c>
     </row>
@@ -7755,7 +7755,7 @@
       </c>
       <c r="K152" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:31Z</t>
+          <t>2026-09-14T23:16:42Z</t>
         </is>
       </c>
     </row>
@@ -7804,7 +7804,7 @@
       </c>
       <c r="K153" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:31Z</t>
+          <t>2026-09-14T23:16:42Z</t>
         </is>
       </c>
     </row>
@@ -7853,7 +7853,7 @@
       </c>
       <c r="K154" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:31Z</t>
+          <t>2026-09-14T23:16:42Z</t>
         </is>
       </c>
     </row>
@@ -7902,7 +7902,7 @@
       </c>
       <c r="K155" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:31Z</t>
+          <t>2026-09-14T23:16:42Z</t>
         </is>
       </c>
     </row>
@@ -7951,7 +7951,7 @@
       </c>
       <c r="K156" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:31Z</t>
+          <t>2026-09-14T23:16:42Z</t>
         </is>
       </c>
     </row>
@@ -8000,7 +8000,7 @@
       </c>
       <c r="K157" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:31Z</t>
+          <t>2026-09-14T23:16:42Z</t>
         </is>
       </c>
     </row>
@@ -8049,7 +8049,7 @@
       </c>
       <c r="K158" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:31Z</t>
+          <t>2026-09-14T23:16:42Z</t>
         </is>
       </c>
     </row>
@@ -8098,7 +8098,7 @@
       </c>
       <c r="K159" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:31Z</t>
+          <t>2026-09-14T23:16:42Z</t>
         </is>
       </c>
     </row>
@@ -8147,7 +8147,7 @@
       </c>
       <c r="K160" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:31Z</t>
+          <t>2026-09-14T23:16:42Z</t>
         </is>
       </c>
     </row>
@@ -8196,7 +8196,7 @@
       </c>
       <c r="K161" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:31Z</t>
+          <t>2026-09-14T23:16:42Z</t>
         </is>
       </c>
     </row>
@@ -8245,7 +8245,7 @@
       </c>
       <c r="K162" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:31Z</t>
+          <t>2026-09-14T23:16:42Z</t>
         </is>
       </c>
     </row>
@@ -8294,7 +8294,7 @@
       </c>
       <c r="K163" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:31Z</t>
+          <t>2026-09-14T23:16:42Z</t>
         </is>
       </c>
     </row>
@@ -8343,7 +8343,7 @@
       </c>
       <c r="K164" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:31Z</t>
+          <t>2026-09-14T23:16:42Z</t>
         </is>
       </c>
     </row>
@@ -8392,7 +8392,7 @@
       </c>
       <c r="K165" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:31Z</t>
+          <t>2026-09-14T23:16:42Z</t>
         </is>
       </c>
     </row>
@@ -8441,7 +8441,7 @@
       </c>
       <c r="K166" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:31Z</t>
+          <t>2026-09-14T23:16:42Z</t>
         </is>
       </c>
     </row>
@@ -8490,7 +8490,7 @@
       </c>
       <c r="K167" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:31Z</t>
+          <t>2026-09-14T23:16:42Z</t>
         </is>
       </c>
     </row>
@@ -8539,7 +8539,7 @@
       </c>
       <c r="K168" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:31Z</t>
+          <t>2026-09-14T23:16:42Z</t>
         </is>
       </c>
     </row>
@@ -8588,7 +8588,7 @@
       </c>
       <c r="K169" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:31Z</t>
+          <t>2026-09-14T23:16:42Z</t>
         </is>
       </c>
     </row>
@@ -8637,7 +8637,7 @@
       </c>
       <c r="K170" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:31Z</t>
+          <t>2026-09-14T23:16:42Z</t>
         </is>
       </c>
     </row>
@@ -8686,7 +8686,7 @@
       </c>
       <c r="K171" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:31Z</t>
+          <t>2026-09-14T23:16:42Z</t>
         </is>
       </c>
     </row>
@@ -8735,7 +8735,7 @@
       </c>
       <c r="K172" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:31Z</t>
+          <t>2026-09-14T23:16:42Z</t>
         </is>
       </c>
     </row>
@@ -8784,7 +8784,7 @@
       </c>
       <c r="K173" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:31Z</t>
+          <t>2026-09-14T23:16:42Z</t>
         </is>
       </c>
     </row>
@@ -8833,7 +8833,7 @@
       </c>
       <c r="K174" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:31Z</t>
+          <t>2026-09-14T23:16:42Z</t>
         </is>
       </c>
     </row>
@@ -8882,7 +8882,7 @@
       </c>
       <c r="K175" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:31Z</t>
+          <t>2026-09-14T23:16:42Z</t>
         </is>
       </c>
     </row>
@@ -8931,7 +8931,7 @@
       </c>
       <c r="K176" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:31Z</t>
+          <t>2026-09-14T23:16:42Z</t>
         </is>
       </c>
     </row>
@@ -8980,7 +8980,7 @@
       </c>
       <c r="K177" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:31Z</t>
+          <t>2026-09-14T23:16:42Z</t>
         </is>
       </c>
     </row>
@@ -9029,7 +9029,7 @@
       </c>
       <c r="K178" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:31Z</t>
+          <t>2026-09-14T23:16:42Z</t>
         </is>
       </c>
     </row>
@@ -9078,7 +9078,7 @@
       </c>
       <c r="K179" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:31Z</t>
+          <t>2026-09-14T23:16:42Z</t>
         </is>
       </c>
     </row>
@@ -9127,7 +9127,7 @@
       </c>
       <c r="K180" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:31Z</t>
+          <t>2026-09-14T23:16:42Z</t>
         </is>
       </c>
     </row>
@@ -9176,7 +9176,7 @@
       </c>
       <c r="K181" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:31Z</t>
+          <t>2026-09-14T23:16:42Z</t>
         </is>
       </c>
     </row>
@@ -9225,7 +9225,7 @@
       </c>
       <c r="K182" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:31Z</t>
+          <t>2026-09-14T23:16:42Z</t>
         </is>
       </c>
     </row>
@@ -9274,7 +9274,7 @@
       </c>
       <c r="K183" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:31Z</t>
+          <t>2026-09-14T23:16:42Z</t>
         </is>
       </c>
     </row>
@@ -9323,7 +9323,7 @@
       </c>
       <c r="K184" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:31Z</t>
+          <t>2026-09-14T23:16:42Z</t>
         </is>
       </c>
     </row>
@@ -9372,7 +9372,7 @@
       </c>
       <c r="K185" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:31Z</t>
+          <t>2026-09-14T23:16:42Z</t>
         </is>
       </c>
     </row>
@@ -9421,7 +9421,7 @@
       </c>
       <c r="K186" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:31Z</t>
+          <t>2026-09-14T23:16:42Z</t>
         </is>
       </c>
     </row>
@@ -9470,7 +9470,7 @@
       </c>
       <c r="K187" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:31Z</t>
+          <t>2026-09-14T23:16:42Z</t>
         </is>
       </c>
     </row>
@@ -9519,7 +9519,7 @@
       </c>
       <c r="K188" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:31Z</t>
+          <t>2026-09-14T23:16:42Z</t>
         </is>
       </c>
     </row>
@@ -9568,7 +9568,7 @@
       </c>
       <c r="K189" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:31Z</t>
+          <t>2026-09-14T23:16:42Z</t>
         </is>
       </c>
     </row>
@@ -9617,7 +9617,7 @@
       </c>
       <c r="K190" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:31Z</t>
+          <t>2026-09-14T23:16:42Z</t>
         </is>
       </c>
     </row>
@@ -9666,7 +9666,7 @@
       </c>
       <c r="K191" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:31Z</t>
+          <t>2026-09-14T23:16:42Z</t>
         </is>
       </c>
     </row>
@@ -9715,7 +9715,7 @@
       </c>
       <c r="K192" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:31Z</t>
+          <t>2026-09-14T23:16:42Z</t>
         </is>
       </c>
     </row>
@@ -9764,7 +9764,7 @@
       </c>
       <c r="K193" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:31Z</t>
+          <t>2026-09-14T23:16:42Z</t>
         </is>
       </c>
     </row>
@@ -9813,7 +9813,7 @@
       </c>
       <c r="K194" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:31Z</t>
+          <t>2026-09-14T23:16:42Z</t>
         </is>
       </c>
     </row>
@@ -9862,7 +9862,7 @@
       </c>
       <c r="K195" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:31Z</t>
+          <t>2026-09-14T23:16:42Z</t>
         </is>
       </c>
     </row>
@@ -9911,7 +9911,7 @@
       </c>
       <c r="K196" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:31Z</t>
+          <t>2026-09-14T23:16:42Z</t>
         </is>
       </c>
     </row>
@@ -9960,7 +9960,7 @@
       </c>
       <c r="K197" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:31Z</t>
+          <t>2026-09-14T23:16:42Z</t>
         </is>
       </c>
     </row>
@@ -10009,7 +10009,7 @@
       </c>
       <c r="K198" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:31Z</t>
+          <t>2026-09-14T23:16:42Z</t>
         </is>
       </c>
     </row>
@@ -10058,7 +10058,7 @@
       </c>
       <c r="K199" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:31Z</t>
+          <t>2026-09-14T23:16:42Z</t>
         </is>
       </c>
     </row>
@@ -10107,7 +10107,7 @@
       </c>
       <c r="K200" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:31Z</t>
+          <t>2026-09-14T23:16:42Z</t>
         </is>
       </c>
     </row>
@@ -10156,7 +10156,7 @@
       </c>
       <c r="K201" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:31Z</t>
+          <t>2026-09-14T23:16:42Z</t>
         </is>
       </c>
     </row>
@@ -10205,7 +10205,7 @@
       </c>
       <c r="K202" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:31Z</t>
+          <t>2026-09-14T23:16:42Z</t>
         </is>
       </c>
     </row>
@@ -10254,7 +10254,7 @@
       </c>
       <c r="K203" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:31Z</t>
+          <t>2026-09-14T23:16:42Z</t>
         </is>
       </c>
     </row>
@@ -10303,7 +10303,7 @@
       </c>
       <c r="K204" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:31Z</t>
+          <t>2026-09-14T23:16:42Z</t>
         </is>
       </c>
     </row>
@@ -10352,7 +10352,7 @@
       </c>
       <c r="K205" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:31Z</t>
+          <t>2026-09-14T23:16:42Z</t>
         </is>
       </c>
     </row>
@@ -10401,7 +10401,7 @@
       </c>
       <c r="K206" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:31Z</t>
+          <t>2026-09-14T23:16:42Z</t>
         </is>
       </c>
     </row>
@@ -10450,7 +10450,7 @@
       </c>
       <c r="K207" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:31Z</t>
+          <t>2026-09-14T23:16:42Z</t>
         </is>
       </c>
     </row>
@@ -10499,7 +10499,7 @@
       </c>
       <c r="K208" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:31Z</t>
+          <t>2026-09-14T23:16:42Z</t>
         </is>
       </c>
     </row>
@@ -10548,7 +10548,7 @@
       </c>
       <c r="K209" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:31Z</t>
+          <t>2026-09-14T23:16:42Z</t>
         </is>
       </c>
     </row>
@@ -10597,7 +10597,7 @@
       </c>
       <c r="K210" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:31Z</t>
+          <t>2026-09-14T23:16:42Z</t>
         </is>
       </c>
     </row>
@@ -10646,7 +10646,7 @@
       </c>
       <c r="K211" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:31Z</t>
+          <t>2026-09-14T23:16:42Z</t>
         </is>
       </c>
     </row>
@@ -10695,7 +10695,7 @@
       </c>
       <c r="K212" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:31Z</t>
+          <t>2026-09-14T23:16:42Z</t>
         </is>
       </c>
     </row>
@@ -10744,7 +10744,7 @@
       </c>
       <c r="K213" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:31Z</t>
+          <t>2026-09-14T23:16:42Z</t>
         </is>
       </c>
     </row>
@@ -10793,7 +10793,7 @@
       </c>
       <c r="K214" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:31Z</t>
+          <t>2026-09-14T23:16:42Z</t>
         </is>
       </c>
     </row>
@@ -10842,7 +10842,7 @@
       </c>
       <c r="K215" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:31Z</t>
+          <t>2026-09-14T23:16:42Z</t>
         </is>
       </c>
     </row>
@@ -10891,7 +10891,7 @@
       </c>
       <c r="K216" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:31Z</t>
+          <t>2026-09-14T23:16:42Z</t>
         </is>
       </c>
     </row>
@@ -10940,7 +10940,7 @@
       </c>
       <c r="K217" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:31Z</t>
+          <t>2026-09-14T23:16:42Z</t>
         </is>
       </c>
     </row>
@@ -10989,7 +10989,7 @@
       </c>
       <c r="K218" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:31Z</t>
+          <t>2026-09-14T23:16:42Z</t>
         </is>
       </c>
     </row>
@@ -11038,7 +11038,7 @@
       </c>
       <c r="K219" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:31Z</t>
+          <t>2026-09-14T23:16:42Z</t>
         </is>
       </c>
     </row>
@@ -11087,7 +11087,7 @@
       </c>
       <c r="K220" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:31Z</t>
+          <t>2026-09-14T23:16:42Z</t>
         </is>
       </c>
     </row>
@@ -11136,7 +11136,7 @@
       </c>
       <c r="K221" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:31Z</t>
+          <t>2026-09-14T23:16:42Z</t>
         </is>
       </c>
     </row>
@@ -11185,7 +11185,7 @@
       </c>
       <c r="K222" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:31Z</t>
+          <t>2026-09-14T23:16:42Z</t>
         </is>
       </c>
     </row>
@@ -11234,7 +11234,7 @@
       </c>
       <c r="K223" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:31Z</t>
+          <t>2026-09-14T23:16:42Z</t>
         </is>
       </c>
     </row>
@@ -11283,7 +11283,7 @@
       </c>
       <c r="K224" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:31Z</t>
+          <t>2026-09-14T23:16:42Z</t>
         </is>
       </c>
     </row>
@@ -11332,7 +11332,7 @@
       </c>
       <c r="K225" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:31Z</t>
+          <t>2026-09-14T23:16:42Z</t>
         </is>
       </c>
     </row>
@@ -11381,7 +11381,7 @@
       </c>
       <c r="K226" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:31Z</t>
+          <t>2026-09-14T23:16:42Z</t>
         </is>
       </c>
     </row>
@@ -11430,7 +11430,7 @@
       </c>
       <c r="K227" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:31Z</t>
+          <t>2026-09-14T23:16:42Z</t>
         </is>
       </c>
     </row>
@@ -11479,7 +11479,7 @@
       </c>
       <c r="K228" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:31Z</t>
+          <t>2026-09-14T23:16:42Z</t>
         </is>
       </c>
     </row>
@@ -11528,7 +11528,7 @@
       </c>
       <c r="K229" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:31Z</t>
+          <t>2026-09-14T23:16:42Z</t>
         </is>
       </c>
     </row>
@@ -11577,7 +11577,7 @@
       </c>
       <c r="K230" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:31Z</t>
+          <t>2026-09-14T23:16:42Z</t>
         </is>
       </c>
     </row>
@@ -11626,7 +11626,7 @@
       </c>
       <c r="K231" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:31Z</t>
+          <t>2026-09-14T23:16:42Z</t>
         </is>
       </c>
     </row>
@@ -11758,7 +11758,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:31Z</t>
+          <t>2026-09-14T23:16:42Z</t>
         </is>
       </c>
     </row>
@@ -11804,7 +11804,7 @@
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>{"date": "2026-08-01", "year": 2026, "month": 8, "month_name": "Agosto", "index_value": 637409769724325.1, "monthly_variation_pct": 8.9, "unit": "Índice base diciembre 2007=100 y variación mensual %", "frequency": "monthly", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/precios_consumidor/4_5_7_2.xls", "fetched_at": "2026-09-13T22:31:31Z"}</t>
+          <t>{"date": "2026-08-01", "year": 2026, "month": 8, "month_name": "Agosto", "index_value": 637409769724325.1, "monthly_variation_pct": 8.9, "unit": "Índice base diciembre 2007=100 y variación mensual %", "frequency": "monthly", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/precios_consumidor/4_5_7_2.xls", "fetched_at": "2026-09-14T23:16:42Z"}</t>
         </is>
       </c>
     </row>

--- a/assets/data/bcv/excel/ove_bcv_inpc_nacional_mensual.xlsx
+++ b/assets/data/bcv/excel/ove_bcv_inpc_nacional_mensual.xlsx
@@ -650,7 +650,7 @@
       </c>
       <c r="K7" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:42Z</t>
+          <t>2026-09-15T23:01:38Z</t>
         </is>
       </c>
     </row>
@@ -699,7 +699,7 @@
       </c>
       <c r="K8" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:42Z</t>
+          <t>2026-09-15T23:01:38Z</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="K9" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:42Z</t>
+          <t>2026-09-15T23:01:38Z</t>
         </is>
       </c>
     </row>
@@ -797,7 +797,7 @@
       </c>
       <c r="K10" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:42Z</t>
+          <t>2026-09-15T23:01:38Z</t>
         </is>
       </c>
     </row>
@@ -846,7 +846,7 @@
       </c>
       <c r="K11" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:42Z</t>
+          <t>2026-09-15T23:01:38Z</t>
         </is>
       </c>
     </row>
@@ -895,7 +895,7 @@
       </c>
       <c r="K12" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:42Z</t>
+          <t>2026-09-15T23:01:38Z</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="K13" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:42Z</t>
+          <t>2026-09-15T23:01:38Z</t>
         </is>
       </c>
     </row>
@@ -993,7 +993,7 @@
       </c>
       <c r="K14" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:42Z</t>
+          <t>2026-09-15T23:01:38Z</t>
         </is>
       </c>
     </row>
@@ -1042,7 +1042,7 @@
       </c>
       <c r="K15" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:42Z</t>
+          <t>2026-09-15T23:01:38Z</t>
         </is>
       </c>
     </row>
@@ -1091,7 +1091,7 @@
       </c>
       <c r="K16" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:42Z</t>
+          <t>2026-09-15T23:01:38Z</t>
         </is>
       </c>
     </row>
@@ -1140,7 +1140,7 @@
       </c>
       <c r="K17" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:42Z</t>
+          <t>2026-09-15T23:01:38Z</t>
         </is>
       </c>
     </row>
@@ -1189,7 +1189,7 @@
       </c>
       <c r="K18" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:42Z</t>
+          <t>2026-09-15T23:01:38Z</t>
         </is>
       </c>
     </row>
@@ -1238,7 +1238,7 @@
       </c>
       <c r="K19" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:42Z</t>
+          <t>2026-09-15T23:01:38Z</t>
         </is>
       </c>
     </row>
@@ -1287,7 +1287,7 @@
       </c>
       <c r="K20" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:42Z</t>
+          <t>2026-09-15T23:01:38Z</t>
         </is>
       </c>
     </row>
@@ -1336,7 +1336,7 @@
       </c>
       <c r="K21" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:42Z</t>
+          <t>2026-09-15T23:01:38Z</t>
         </is>
       </c>
     </row>
@@ -1385,7 +1385,7 @@
       </c>
       <c r="K22" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:42Z</t>
+          <t>2026-09-15T23:01:38Z</t>
         </is>
       </c>
     </row>
@@ -1434,7 +1434,7 @@
       </c>
       <c r="K23" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:42Z</t>
+          <t>2026-09-15T23:01:38Z</t>
         </is>
       </c>
     </row>
@@ -1483,7 +1483,7 @@
       </c>
       <c r="K24" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:42Z</t>
+          <t>2026-09-15T23:01:38Z</t>
         </is>
       </c>
     </row>
@@ -1532,7 +1532,7 @@
       </c>
       <c r="K25" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:42Z</t>
+          <t>2026-09-15T23:01:38Z</t>
         </is>
       </c>
     </row>
@@ -1581,7 +1581,7 @@
       </c>
       <c r="K26" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:42Z</t>
+          <t>2026-09-15T23:01:38Z</t>
         </is>
       </c>
     </row>
@@ -1630,7 +1630,7 @@
       </c>
       <c r="K27" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:42Z</t>
+          <t>2026-09-15T23:01:38Z</t>
         </is>
       </c>
     </row>
@@ -1679,7 +1679,7 @@
       </c>
       <c r="K28" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:42Z</t>
+          <t>2026-09-15T23:01:38Z</t>
         </is>
       </c>
     </row>
@@ -1728,7 +1728,7 @@
       </c>
       <c r="K29" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:42Z</t>
+          <t>2026-09-15T23:01:38Z</t>
         </is>
       </c>
     </row>
@@ -1777,7 +1777,7 @@
       </c>
       <c r="K30" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:42Z</t>
+          <t>2026-09-15T23:01:38Z</t>
         </is>
       </c>
     </row>
@@ -1826,7 +1826,7 @@
       </c>
       <c r="K31" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:42Z</t>
+          <t>2026-09-15T23:01:38Z</t>
         </is>
       </c>
     </row>
@@ -1875,7 +1875,7 @@
       </c>
       <c r="K32" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:42Z</t>
+          <t>2026-09-15T23:01:38Z</t>
         </is>
       </c>
     </row>
@@ -1924,7 +1924,7 @@
       </c>
       <c r="K33" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:42Z</t>
+          <t>2026-09-15T23:01:38Z</t>
         </is>
       </c>
     </row>
@@ -1973,7 +1973,7 @@
       </c>
       <c r="K34" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:42Z</t>
+          <t>2026-09-15T23:01:38Z</t>
         </is>
       </c>
     </row>
@@ -2022,7 +2022,7 @@
       </c>
       <c r="K35" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:42Z</t>
+          <t>2026-09-15T23:01:38Z</t>
         </is>
       </c>
     </row>
@@ -2071,7 +2071,7 @@
       </c>
       <c r="K36" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:42Z</t>
+          <t>2026-09-15T23:01:38Z</t>
         </is>
       </c>
     </row>
@@ -2120,7 +2120,7 @@
       </c>
       <c r="K37" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:42Z</t>
+          <t>2026-09-15T23:01:38Z</t>
         </is>
       </c>
     </row>
@@ -2169,7 +2169,7 @@
       </c>
       <c r="K38" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:42Z</t>
+          <t>2026-09-15T23:01:38Z</t>
         </is>
       </c>
     </row>
@@ -2218,7 +2218,7 @@
       </c>
       <c r="K39" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:42Z</t>
+          <t>2026-09-15T23:01:38Z</t>
         </is>
       </c>
     </row>
@@ -2267,7 +2267,7 @@
       </c>
       <c r="K40" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:42Z</t>
+          <t>2026-09-15T23:01:38Z</t>
         </is>
       </c>
     </row>
@@ -2316,7 +2316,7 @@
       </c>
       <c r="K41" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:42Z</t>
+          <t>2026-09-15T23:01:38Z</t>
         </is>
       </c>
     </row>
@@ -2365,7 +2365,7 @@
       </c>
       <c r="K42" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:42Z</t>
+          <t>2026-09-15T23:01:38Z</t>
         </is>
       </c>
     </row>
@@ -2414,7 +2414,7 @@
       </c>
       <c r="K43" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:42Z</t>
+          <t>2026-09-15T23:01:38Z</t>
         </is>
       </c>
     </row>
@@ -2463,7 +2463,7 @@
       </c>
       <c r="K44" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:42Z</t>
+          <t>2026-09-15T23:01:38Z</t>
         </is>
       </c>
     </row>
@@ -2512,7 +2512,7 @@
       </c>
       <c r="K45" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:42Z</t>
+          <t>2026-09-15T23:01:38Z</t>
         </is>
       </c>
     </row>
@@ -2561,7 +2561,7 @@
       </c>
       <c r="K46" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:42Z</t>
+          <t>2026-09-15T23:01:38Z</t>
         </is>
       </c>
     </row>
@@ -2610,7 +2610,7 @@
       </c>
       <c r="K47" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:42Z</t>
+          <t>2026-09-15T23:01:38Z</t>
         </is>
       </c>
     </row>
@@ -2659,7 +2659,7 @@
       </c>
       <c r="K48" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:42Z</t>
+          <t>2026-09-15T23:01:38Z</t>
         </is>
       </c>
     </row>
@@ -2708,7 +2708,7 @@
       </c>
       <c r="K49" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:42Z</t>
+          <t>2026-09-15T23:01:38Z</t>
         </is>
       </c>
     </row>
@@ -2757,7 +2757,7 @@
       </c>
       <c r="K50" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:42Z</t>
+          <t>2026-09-15T23:01:38Z</t>
         </is>
       </c>
     </row>
@@ -2806,7 +2806,7 @@
       </c>
       <c r="K51" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:42Z</t>
+          <t>2026-09-15T23:01:38Z</t>
         </is>
       </c>
     </row>
@@ -2855,7 +2855,7 @@
       </c>
       <c r="K52" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:42Z</t>
+          <t>2026-09-15T23:01:38Z</t>
         </is>
       </c>
     </row>
@@ -2904,7 +2904,7 @@
       </c>
       <c r="K53" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:42Z</t>
+          <t>2026-09-15T23:01:38Z</t>
         </is>
       </c>
     </row>
@@ -2953,7 +2953,7 @@
       </c>
       <c r="K54" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:42Z</t>
+          <t>2026-09-15T23:01:38Z</t>
         </is>
       </c>
     </row>
@@ -3002,7 +3002,7 @@
       </c>
       <c r="K55" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:42Z</t>
+          <t>2026-09-15T23:01:38Z</t>
         </is>
       </c>
     </row>
@@ -3051,7 +3051,7 @@
       </c>
       <c r="K56" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:42Z</t>
+          <t>2026-09-15T23:01:38Z</t>
         </is>
       </c>
     </row>
@@ -3100,7 +3100,7 @@
       </c>
       <c r="K57" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:42Z</t>
+          <t>2026-09-15T23:01:38Z</t>
         </is>
       </c>
     </row>
@@ -3149,7 +3149,7 @@
       </c>
       <c r="K58" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:42Z</t>
+          <t>2026-09-15T23:01:38Z</t>
         </is>
       </c>
     </row>
@@ -3198,7 +3198,7 @@
       </c>
       <c r="K59" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:42Z</t>
+          <t>2026-09-15T23:01:38Z</t>
         </is>
       </c>
     </row>
@@ -3247,7 +3247,7 @@
       </c>
       <c r="K60" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:42Z</t>
+          <t>2026-09-15T23:01:38Z</t>
         </is>
       </c>
     </row>
@@ -3296,7 +3296,7 @@
       </c>
       <c r="K61" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:42Z</t>
+          <t>2026-09-15T23:01:38Z</t>
         </is>
       </c>
     </row>
@@ -3345,7 +3345,7 @@
       </c>
       <c r="K62" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:42Z</t>
+          <t>2026-09-15T23:01:38Z</t>
         </is>
       </c>
     </row>
@@ -3394,7 +3394,7 @@
       </c>
       <c r="K63" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:42Z</t>
+          <t>2026-09-15T23:01:38Z</t>
         </is>
       </c>
     </row>
@@ -3443,7 +3443,7 @@
       </c>
       <c r="K64" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:42Z</t>
+          <t>2026-09-15T23:01:38Z</t>
         </is>
       </c>
     </row>
@@ -3492,7 +3492,7 @@
       </c>
       <c r="K65" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:42Z</t>
+          <t>2026-09-15T23:01:38Z</t>
         </is>
       </c>
     </row>
@@ -3541,7 +3541,7 @@
       </c>
       <c r="K66" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:42Z</t>
+          <t>2026-09-15T23:01:38Z</t>
         </is>
       </c>
     </row>
@@ -3590,7 +3590,7 @@
       </c>
       <c r="K67" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:42Z</t>
+          <t>2026-09-15T23:01:38Z</t>
         </is>
       </c>
     </row>
@@ -3639,7 +3639,7 @@
       </c>
       <c r="K68" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:42Z</t>
+          <t>2026-09-15T23:01:38Z</t>
         </is>
       </c>
     </row>
@@ -3688,7 +3688,7 @@
       </c>
       <c r="K69" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:42Z</t>
+          <t>2026-09-15T23:01:38Z</t>
         </is>
       </c>
     </row>
@@ -3737,7 +3737,7 @@
       </c>
       <c r="K70" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:42Z</t>
+          <t>2026-09-15T23:01:38Z</t>
         </is>
       </c>
     </row>
@@ -3786,7 +3786,7 @@
       </c>
       <c r="K71" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:42Z</t>
+          <t>2026-09-15T23:01:38Z</t>
         </is>
       </c>
     </row>
@@ -3835,7 +3835,7 @@
       </c>
       <c r="K72" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:42Z</t>
+          <t>2026-09-15T23:01:38Z</t>
         </is>
       </c>
     </row>
@@ -3884,7 +3884,7 @@
       </c>
       <c r="K73" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:42Z</t>
+          <t>2026-09-15T23:01:38Z</t>
         </is>
       </c>
     </row>
@@ -3933,7 +3933,7 @@
       </c>
       <c r="K74" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:42Z</t>
+          <t>2026-09-15T23:01:38Z</t>
         </is>
       </c>
     </row>
@@ -3982,7 +3982,7 @@
       </c>
       <c r="K75" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:42Z</t>
+          <t>2026-09-15T23:01:38Z</t>
         </is>
       </c>
     </row>
@@ -4031,7 +4031,7 @@
       </c>
       <c r="K76" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:42Z</t>
+          <t>2026-09-15T23:01:38Z</t>
         </is>
       </c>
     </row>
@@ -4080,7 +4080,7 @@
       </c>
       <c r="K77" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:42Z</t>
+          <t>2026-09-15T23:01:38Z</t>
         </is>
       </c>
     </row>
@@ -4129,7 +4129,7 @@
       </c>
       <c r="K78" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:42Z</t>
+          <t>2026-09-15T23:01:38Z</t>
         </is>
       </c>
     </row>
@@ -4178,7 +4178,7 @@
       </c>
       <c r="K79" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:42Z</t>
+          <t>2026-09-15T23:01:38Z</t>
         </is>
       </c>
     </row>
@@ -4227,7 +4227,7 @@
       </c>
       <c r="K80" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:42Z</t>
+          <t>2026-09-15T23:01:38Z</t>
         </is>
       </c>
     </row>
@@ -4276,7 +4276,7 @@
       </c>
       <c r="K81" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:42Z</t>
+          <t>2026-09-15T23:01:38Z</t>
         </is>
       </c>
     </row>
@@ -4325,7 +4325,7 @@
       </c>
       <c r="K82" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:42Z</t>
+          <t>2026-09-15T23:01:38Z</t>
         </is>
       </c>
     </row>
@@ -4374,7 +4374,7 @@
       </c>
       <c r="K83" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:42Z</t>
+          <t>2026-09-15T23:01:38Z</t>
         </is>
       </c>
     </row>
@@ -4423,7 +4423,7 @@
       </c>
       <c r="K84" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:42Z</t>
+          <t>2026-09-15T23:01:38Z</t>
         </is>
       </c>
     </row>
@@ -4472,7 +4472,7 @@
       </c>
       <c r="K85" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:42Z</t>
+          <t>2026-09-15T23:01:38Z</t>
         </is>
       </c>
     </row>
@@ -4521,7 +4521,7 @@
       </c>
       <c r="K86" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:42Z</t>
+          <t>2026-09-15T23:01:38Z</t>
         </is>
       </c>
     </row>
@@ -4570,7 +4570,7 @@
       </c>
       <c r="K87" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:42Z</t>
+          <t>2026-09-15T23:01:38Z</t>
         </is>
       </c>
     </row>
@@ -4619,7 +4619,7 @@
       </c>
       <c r="K88" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:42Z</t>
+          <t>2026-09-15T23:01:38Z</t>
         </is>
       </c>
     </row>
@@ -4668,7 +4668,7 @@
       </c>
       <c r="K89" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:42Z</t>
+          <t>2026-09-15T23:01:38Z</t>
         </is>
       </c>
     </row>
@@ -4717,7 +4717,7 @@
       </c>
       <c r="K90" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:42Z</t>
+          <t>2026-09-15T23:01:38Z</t>
         </is>
       </c>
     </row>
@@ -4766,7 +4766,7 @@
       </c>
       <c r="K91" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:42Z</t>
+          <t>2026-09-15T23:01:38Z</t>
         </is>
       </c>
     </row>
@@ -4815,7 +4815,7 @@
       </c>
       <c r="K92" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:42Z</t>
+          <t>2026-09-15T23:01:38Z</t>
         </is>
       </c>
     </row>
@@ -4864,7 +4864,7 @@
       </c>
       <c r="K93" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:42Z</t>
+          <t>2026-09-15T23:01:38Z</t>
         </is>
       </c>
     </row>
@@ -4913,7 +4913,7 @@
       </c>
       <c r="K94" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:42Z</t>
+          <t>2026-09-15T23:01:38Z</t>
         </is>
       </c>
     </row>
@@ -4962,7 +4962,7 @@
       </c>
       <c r="K95" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:42Z</t>
+          <t>2026-09-15T23:01:38Z</t>
         </is>
       </c>
     </row>
@@ -5011,7 +5011,7 @@
       </c>
       <c r="K96" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:42Z</t>
+          <t>2026-09-15T23:01:38Z</t>
         </is>
       </c>
     </row>
@@ -5060,7 +5060,7 @@
       </c>
       <c r="K97" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:42Z</t>
+          <t>2026-09-15T23:01:38Z</t>
         </is>
       </c>
     </row>
@@ -5109,7 +5109,7 @@
       </c>
       <c r="K98" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:42Z</t>
+          <t>2026-09-15T23:01:38Z</t>
         </is>
       </c>
     </row>
@@ -5158,7 +5158,7 @@
       </c>
       <c r="K99" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:42Z</t>
+          <t>2026-09-15T23:01:38Z</t>
         </is>
       </c>
     </row>
@@ -5207,7 +5207,7 @@
       </c>
       <c r="K100" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:42Z</t>
+          <t>2026-09-15T23:01:38Z</t>
         </is>
       </c>
     </row>
@@ -5256,7 +5256,7 @@
       </c>
       <c r="K101" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:42Z</t>
+          <t>2026-09-15T23:01:38Z</t>
         </is>
       </c>
     </row>
@@ -5305,7 +5305,7 @@
       </c>
       <c r="K102" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:42Z</t>
+          <t>2026-09-15T23:01:38Z</t>
         </is>
       </c>
     </row>
@@ -5354,7 +5354,7 @@
       </c>
       <c r="K103" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:42Z</t>
+          <t>2026-09-15T23:01:38Z</t>
         </is>
       </c>
     </row>
@@ -5403,7 +5403,7 @@
       </c>
       <c r="K104" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:42Z</t>
+          <t>2026-09-15T23:01:38Z</t>
         </is>
       </c>
     </row>
@@ -5452,7 +5452,7 @@
       </c>
       <c r="K105" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:42Z</t>
+          <t>2026-09-15T23:01:38Z</t>
         </is>
       </c>
     </row>
@@ -5501,7 +5501,7 @@
       </c>
       <c r="K106" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:42Z</t>
+          <t>2026-09-15T23:01:38Z</t>
         </is>
       </c>
     </row>
@@ -5550,7 +5550,7 @@
       </c>
       <c r="K107" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:42Z</t>
+          <t>2026-09-15T23:01:38Z</t>
         </is>
       </c>
     </row>
@@ -5599,7 +5599,7 @@
       </c>
       <c r="K108" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:42Z</t>
+          <t>2026-09-15T23:01:38Z</t>
         </is>
       </c>
     </row>
@@ -5648,7 +5648,7 @@
       </c>
       <c r="K109" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:42Z</t>
+          <t>2026-09-15T23:01:38Z</t>
         </is>
       </c>
     </row>
@@ -5697,7 +5697,7 @@
       </c>
       <c r="K110" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:42Z</t>
+          <t>2026-09-15T23:01:38Z</t>
         </is>
       </c>
     </row>
@@ -5746,7 +5746,7 @@
       </c>
       <c r="K111" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:42Z</t>
+          <t>2026-09-15T23:01:38Z</t>
         </is>
       </c>
     </row>
@@ -5795,7 +5795,7 @@
       </c>
       <c r="K112" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:42Z</t>
+          <t>2026-09-15T23:01:38Z</t>
         </is>
       </c>
     </row>
@@ -5844,7 +5844,7 @@
       </c>
       <c r="K113" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:42Z</t>
+          <t>2026-09-15T23:01:38Z</t>
         </is>
       </c>
     </row>
@@ -5893,7 +5893,7 @@
       </c>
       <c r="K114" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:42Z</t>
+          <t>2026-09-15T23:01:38Z</t>
         </is>
       </c>
     </row>
@@ -5942,7 +5942,7 @@
       </c>
       <c r="K115" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:42Z</t>
+          <t>2026-09-15T23:01:38Z</t>
         </is>
       </c>
     </row>
@@ -5991,7 +5991,7 @@
       </c>
       <c r="K116" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:42Z</t>
+          <t>2026-09-15T23:01:38Z</t>
         </is>
       </c>
     </row>
@@ -6040,7 +6040,7 @@
       </c>
       <c r="K117" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:42Z</t>
+          <t>2026-09-15T23:01:38Z</t>
         </is>
       </c>
     </row>
@@ -6089,7 +6089,7 @@
       </c>
       <c r="K118" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:42Z</t>
+          <t>2026-09-15T23:01:38Z</t>
         </is>
       </c>
     </row>
@@ -6138,7 +6138,7 @@
       </c>
       <c r="K119" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:42Z</t>
+          <t>2026-09-15T23:01:38Z</t>
         </is>
       </c>
     </row>
@@ -6187,7 +6187,7 @@
       </c>
       <c r="K120" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:42Z</t>
+          <t>2026-09-15T23:01:38Z</t>
         </is>
       </c>
     </row>
@@ -6236,7 +6236,7 @@
       </c>
       <c r="K121" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:42Z</t>
+          <t>2026-09-15T23:01:38Z</t>
         </is>
       </c>
     </row>
@@ -6285,7 +6285,7 @@
       </c>
       <c r="K122" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:42Z</t>
+          <t>2026-09-15T23:01:38Z</t>
         </is>
       </c>
     </row>
@@ -6334,7 +6334,7 @@
       </c>
       <c r="K123" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:42Z</t>
+          <t>2026-09-15T23:01:38Z</t>
         </is>
       </c>
     </row>
@@ -6383,7 +6383,7 @@
       </c>
       <c r="K124" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:42Z</t>
+          <t>2026-09-15T23:01:38Z</t>
         </is>
       </c>
     </row>
@@ -6432,7 +6432,7 @@
       </c>
       <c r="K125" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:42Z</t>
+          <t>2026-09-15T23:01:38Z</t>
         </is>
       </c>
     </row>
@@ -6481,7 +6481,7 @@
       </c>
       <c r="K126" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:42Z</t>
+          <t>2026-09-15T23:01:38Z</t>
         </is>
       </c>
     </row>
@@ -6530,7 +6530,7 @@
       </c>
       <c r="K127" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:42Z</t>
+          <t>2026-09-15T23:01:38Z</t>
         </is>
       </c>
     </row>
@@ -6579,7 +6579,7 @@
       </c>
       <c r="K128" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:42Z</t>
+          <t>2026-09-15T23:01:38Z</t>
         </is>
       </c>
     </row>
@@ -6628,7 +6628,7 @@
       </c>
       <c r="K129" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:42Z</t>
+          <t>2026-09-15T23:01:38Z</t>
         </is>
       </c>
     </row>
@@ -6677,7 +6677,7 @@
       </c>
       <c r="K130" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:42Z</t>
+          <t>2026-09-15T23:01:38Z</t>
         </is>
       </c>
     </row>
@@ -6726,7 +6726,7 @@
       </c>
       <c r="K131" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:42Z</t>
+          <t>2026-09-15T23:01:38Z</t>
         </is>
       </c>
     </row>
@@ -6775,7 +6775,7 @@
       </c>
       <c r="K132" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:42Z</t>
+          <t>2026-09-15T23:01:38Z</t>
         </is>
       </c>
     </row>
@@ -6824,7 +6824,7 @@
       </c>
       <c r="K133" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:42Z</t>
+          <t>2026-09-15T23:01:38Z</t>
         </is>
       </c>
     </row>
@@ -6873,7 +6873,7 @@
       </c>
       <c r="K134" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:42Z</t>
+          <t>2026-09-15T23:01:38Z</t>
         </is>
       </c>
     </row>
@@ -6922,7 +6922,7 @@
       </c>
       <c r="K135" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:42Z</t>
+          <t>2026-09-15T23:01:38Z</t>
         </is>
       </c>
     </row>
@@ -6971,7 +6971,7 @@
       </c>
       <c r="K136" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:42Z</t>
+          <t>2026-09-15T23:01:38Z</t>
         </is>
       </c>
     </row>
@@ -7020,7 +7020,7 @@
       </c>
       <c r="K137" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:42Z</t>
+          <t>2026-09-15T23:01:38Z</t>
         </is>
       </c>
     </row>
@@ -7069,7 +7069,7 @@
       </c>
       <c r="K138" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:42Z</t>
+          <t>2026-09-15T23:01:38Z</t>
         </is>
       </c>
     </row>
@@ -7118,7 +7118,7 @@
       </c>
       <c r="K139" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:42Z</t>
+          <t>2026-09-15T23:01:38Z</t>
         </is>
       </c>
     </row>
@@ -7167,7 +7167,7 @@
       </c>
       <c r="K140" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:42Z</t>
+          <t>2026-09-15T23:01:38Z</t>
         </is>
       </c>
     </row>
@@ -7216,7 +7216,7 @@
       </c>
       <c r="K141" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:42Z</t>
+          <t>2026-09-15T23:01:38Z</t>
         </is>
       </c>
     </row>
@@ -7265,7 +7265,7 @@
       </c>
       <c r="K142" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:42Z</t>
+          <t>2026-09-15T23:01:38Z</t>
         </is>
       </c>
     </row>
@@ -7314,7 +7314,7 @@
       </c>
       <c r="K143" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:42Z</t>
+          <t>2026-09-15T23:01:38Z</t>
         </is>
       </c>
     </row>
@@ -7363,7 +7363,7 @@
       </c>
       <c r="K144" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:42Z</t>
+          <t>2026-09-15T23:01:38Z</t>
         </is>
       </c>
     </row>
@@ -7412,7 +7412,7 @@
       </c>
       <c r="K145" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:42Z</t>
+          <t>2026-09-15T23:01:38Z</t>
         </is>
       </c>
     </row>
@@ -7461,7 +7461,7 @@
       </c>
       <c r="K146" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:42Z</t>
+          <t>2026-09-15T23:01:38Z</t>
         </is>
       </c>
     </row>
@@ -7510,7 +7510,7 @@
       </c>
       <c r="K147" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:42Z</t>
+          <t>2026-09-15T23:01:38Z</t>
         </is>
       </c>
     </row>
@@ -7559,7 +7559,7 @@
       </c>
       <c r="K148" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:42Z</t>
+          <t>2026-09-15T23:01:38Z</t>
         </is>
       </c>
     </row>
@@ -7608,7 +7608,7 @@
       </c>
       <c r="K149" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:42Z</t>
+          <t>2026-09-15T23:01:38Z</t>
         </is>
       </c>
     </row>
@@ -7657,7 +7657,7 @@
       </c>
       <c r="K150" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:42Z</t>
+          <t>2026-09-15T23:01:38Z</t>
         </is>
       </c>
     </row>
@@ -7706,7 +7706,7 @@
       </c>
       <c r="K151" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:42Z</t>
+          <t>2026-09-15T23:01:38Z</t>
         </is>
       </c>
     </row>
@@ -7755,7 +7755,7 @@
       </c>
       <c r="K152" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:42Z</t>
+          <t>2026-09-15T23:01:38Z</t>
         </is>
       </c>
     </row>
@@ -7804,7 +7804,7 @@
       </c>
       <c r="K153" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:42Z</t>
+          <t>2026-09-15T23:01:38Z</t>
         </is>
       </c>
     </row>
@@ -7853,7 +7853,7 @@
       </c>
       <c r="K154" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:42Z</t>
+          <t>2026-09-15T23:01:38Z</t>
         </is>
       </c>
     </row>
@@ -7902,7 +7902,7 @@
       </c>
       <c r="K155" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:42Z</t>
+          <t>2026-09-15T23:01:38Z</t>
         </is>
       </c>
     </row>
@@ -7951,7 +7951,7 @@
       </c>
       <c r="K156" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:42Z</t>
+          <t>2026-09-15T23:01:38Z</t>
         </is>
       </c>
     </row>
@@ -8000,7 +8000,7 @@
       </c>
       <c r="K157" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:42Z</t>
+          <t>2026-09-15T23:01:38Z</t>
         </is>
       </c>
     </row>
@@ -8049,7 +8049,7 @@
       </c>
       <c r="K158" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:42Z</t>
+          <t>2026-09-15T23:01:38Z</t>
         </is>
       </c>
     </row>
@@ -8098,7 +8098,7 @@
       </c>
       <c r="K159" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:42Z</t>
+          <t>2026-09-15T23:01:38Z</t>
         </is>
       </c>
     </row>
@@ -8147,7 +8147,7 @@
       </c>
       <c r="K160" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:42Z</t>
+          <t>2026-09-15T23:01:38Z</t>
         </is>
       </c>
     </row>
@@ -8196,7 +8196,7 @@
       </c>
       <c r="K161" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:42Z</t>
+          <t>2026-09-15T23:01:38Z</t>
         </is>
       </c>
     </row>
@@ -8245,7 +8245,7 @@
       </c>
       <c r="K162" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:42Z</t>
+          <t>2026-09-15T23:01:38Z</t>
         </is>
       </c>
     </row>
@@ -8294,7 +8294,7 @@
       </c>
       <c r="K163" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:42Z</t>
+          <t>2026-09-15T23:01:38Z</t>
         </is>
       </c>
     </row>
@@ -8343,7 +8343,7 @@
       </c>
       <c r="K164" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:42Z</t>
+          <t>2026-09-15T23:01:38Z</t>
         </is>
       </c>
     </row>
@@ -8392,7 +8392,7 @@
       </c>
       <c r="K165" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:42Z</t>
+          <t>2026-09-15T23:01:38Z</t>
         </is>
       </c>
     </row>
@@ -8441,7 +8441,7 @@
       </c>
       <c r="K166" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:42Z</t>
+          <t>2026-09-15T23:01:38Z</t>
         </is>
       </c>
     </row>
@@ -8490,7 +8490,7 @@
       </c>
       <c r="K167" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:42Z</t>
+          <t>2026-09-15T23:01:38Z</t>
         </is>
       </c>
     </row>
@@ -8539,7 +8539,7 @@
       </c>
       <c r="K168" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:42Z</t>
+          <t>2026-09-15T23:01:38Z</t>
         </is>
       </c>
     </row>
@@ -8588,7 +8588,7 @@
       </c>
       <c r="K169" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:42Z</t>
+          <t>2026-09-15T23:01:38Z</t>
         </is>
       </c>
     </row>
@@ -8637,7 +8637,7 @@
       </c>
       <c r="K170" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:42Z</t>
+          <t>2026-09-15T23:01:38Z</t>
         </is>
       </c>
     </row>
@@ -8686,7 +8686,7 @@
       </c>
       <c r="K171" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:42Z</t>
+          <t>2026-09-15T23:01:38Z</t>
         </is>
       </c>
     </row>
@@ -8735,7 +8735,7 @@
       </c>
       <c r="K172" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:42Z</t>
+          <t>2026-09-15T23:01:38Z</t>
         </is>
       </c>
     </row>
@@ -8784,7 +8784,7 @@
       </c>
       <c r="K173" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:42Z</t>
+          <t>2026-09-15T23:01:38Z</t>
         </is>
       </c>
     </row>
@@ -8833,7 +8833,7 @@
       </c>
       <c r="K174" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:42Z</t>
+          <t>2026-09-15T23:01:38Z</t>
         </is>
       </c>
     </row>
@@ -8882,7 +8882,7 @@
       </c>
       <c r="K175" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:42Z</t>
+          <t>2026-09-15T23:01:38Z</t>
         </is>
       </c>
     </row>
@@ -8931,7 +8931,7 @@
       </c>
       <c r="K176" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:42Z</t>
+          <t>2026-09-15T23:01:38Z</t>
         </is>
       </c>
     </row>
@@ -8980,7 +8980,7 @@
       </c>
       <c r="K177" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:42Z</t>
+          <t>2026-09-15T23:01:38Z</t>
         </is>
       </c>
     </row>
@@ -9029,7 +9029,7 @@
       </c>
       <c r="K178" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:42Z</t>
+          <t>2026-09-15T23:01:38Z</t>
         </is>
       </c>
     </row>
@@ -9078,7 +9078,7 @@
       </c>
       <c r="K179" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:42Z</t>
+          <t>2026-09-15T23:01:38Z</t>
         </is>
       </c>
     </row>
@@ -9127,7 +9127,7 @@
       </c>
       <c r="K180" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:42Z</t>
+          <t>2026-09-15T23:01:38Z</t>
         </is>
       </c>
     </row>
@@ -9176,7 +9176,7 @@
       </c>
       <c r="K181" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:42Z</t>
+          <t>2026-09-15T23:01:38Z</t>
         </is>
       </c>
     </row>
@@ -9225,7 +9225,7 @@
       </c>
       <c r="K182" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:42Z</t>
+          <t>2026-09-15T23:01:38Z</t>
         </is>
       </c>
     </row>
@@ -9274,7 +9274,7 @@
       </c>
       <c r="K183" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:42Z</t>
+          <t>2026-09-15T23:01:38Z</t>
         </is>
       </c>
     </row>
@@ -9323,7 +9323,7 @@
       </c>
       <c r="K184" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:42Z</t>
+          <t>2026-09-15T23:01:38Z</t>
         </is>
       </c>
     </row>
@@ -9372,7 +9372,7 @@
       </c>
       <c r="K185" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:42Z</t>
+          <t>2026-09-15T23:01:38Z</t>
         </is>
       </c>
     </row>
@@ -9421,7 +9421,7 @@
       </c>
       <c r="K186" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:42Z</t>
+          <t>2026-09-15T23:01:38Z</t>
         </is>
       </c>
     </row>
@@ -9470,7 +9470,7 @@
       </c>
       <c r="K187" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:42Z</t>
+          <t>2026-09-15T23:01:38Z</t>
         </is>
       </c>
     </row>
@@ -9519,7 +9519,7 @@
       </c>
       <c r="K188" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:42Z</t>
+          <t>2026-09-15T23:01:38Z</t>
         </is>
       </c>
     </row>
@@ -9568,7 +9568,7 @@
       </c>
       <c r="K189" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:42Z</t>
+          <t>2026-09-15T23:01:38Z</t>
         </is>
       </c>
     </row>
@@ -9617,7 +9617,7 @@
       </c>
       <c r="K190" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:42Z</t>
+          <t>2026-09-15T23:01:38Z</t>
         </is>
       </c>
     </row>
@@ -9666,7 +9666,7 @@
       </c>
       <c r="K191" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:42Z</t>
+          <t>2026-09-15T23:01:38Z</t>
         </is>
       </c>
     </row>
@@ -9715,7 +9715,7 @@
       </c>
       <c r="K192" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:42Z</t>
+          <t>2026-09-15T23:01:38Z</t>
         </is>
       </c>
     </row>
@@ -9764,7 +9764,7 @@
       </c>
       <c r="K193" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:42Z</t>
+          <t>2026-09-15T23:01:38Z</t>
         </is>
       </c>
     </row>
@@ -9813,7 +9813,7 @@
       </c>
       <c r="K194" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:42Z</t>
+          <t>2026-09-15T23:01:38Z</t>
         </is>
       </c>
     </row>
@@ -9862,7 +9862,7 @@
       </c>
       <c r="K195" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:42Z</t>
+          <t>2026-09-15T23:01:38Z</t>
         </is>
       </c>
     </row>
@@ -9911,7 +9911,7 @@
       </c>
       <c r="K196" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:42Z</t>
+          <t>2026-09-15T23:01:38Z</t>
         </is>
       </c>
     </row>
@@ -9960,7 +9960,7 @@
       </c>
       <c r="K197" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:42Z</t>
+          <t>2026-09-15T23:01:38Z</t>
         </is>
       </c>
     </row>
@@ -10009,7 +10009,7 @@
       </c>
       <c r="K198" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:42Z</t>
+          <t>2026-09-15T23:01:38Z</t>
         </is>
       </c>
     </row>
@@ -10058,7 +10058,7 @@
       </c>
       <c r="K199" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:42Z</t>
+          <t>2026-09-15T23:01:38Z</t>
         </is>
       </c>
     </row>
@@ -10107,7 +10107,7 @@
       </c>
       <c r="K200" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:42Z</t>
+          <t>2026-09-15T23:01:38Z</t>
         </is>
       </c>
     </row>
@@ -10156,7 +10156,7 @@
       </c>
       <c r="K201" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:42Z</t>
+          <t>2026-09-15T23:01:38Z</t>
         </is>
       </c>
     </row>
@@ -10205,7 +10205,7 @@
       </c>
       <c r="K202" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:42Z</t>
+          <t>2026-09-15T23:01:38Z</t>
         </is>
       </c>
     </row>
@@ -10254,7 +10254,7 @@
       </c>
       <c r="K203" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:42Z</t>
+          <t>2026-09-15T23:01:38Z</t>
         </is>
       </c>
     </row>
@@ -10303,7 +10303,7 @@
       </c>
       <c r="K204" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:42Z</t>
+          <t>2026-09-15T23:01:38Z</t>
         </is>
       </c>
     </row>
@@ -10352,7 +10352,7 @@
       </c>
       <c r="K205" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:42Z</t>
+          <t>2026-09-15T23:01:38Z</t>
         </is>
       </c>
     </row>
@@ -10401,7 +10401,7 @@
       </c>
       <c r="K206" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:42Z</t>
+          <t>2026-09-15T23:01:38Z</t>
         </is>
       </c>
     </row>
@@ -10450,7 +10450,7 @@
       </c>
       <c r="K207" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:42Z</t>
+          <t>2026-09-15T23:01:38Z</t>
         </is>
       </c>
     </row>
@@ -10499,7 +10499,7 @@
       </c>
       <c r="K208" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:42Z</t>
+          <t>2026-09-15T23:01:38Z</t>
         </is>
       </c>
     </row>
@@ -10548,7 +10548,7 @@
       </c>
       <c r="K209" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:42Z</t>
+          <t>2026-09-15T23:01:38Z</t>
         </is>
       </c>
     </row>
@@ -10597,7 +10597,7 @@
       </c>
       <c r="K210" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:42Z</t>
+          <t>2026-09-15T23:01:38Z</t>
         </is>
       </c>
     </row>
@@ -10646,7 +10646,7 @@
       </c>
       <c r="K211" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:42Z</t>
+          <t>2026-09-15T23:01:38Z</t>
         </is>
       </c>
     </row>
@@ -10695,7 +10695,7 @@
       </c>
       <c r="K212" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:42Z</t>
+          <t>2026-09-15T23:01:38Z</t>
         </is>
       </c>
     </row>
@@ -10744,7 +10744,7 @@
       </c>
       <c r="K213" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:42Z</t>
+          <t>2026-09-15T23:01:38Z</t>
         </is>
       </c>
     </row>
@@ -10793,7 +10793,7 @@
       </c>
       <c r="K214" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:42Z</t>
+          <t>2026-09-15T23:01:38Z</t>
         </is>
       </c>
     </row>
@@ -10842,7 +10842,7 @@
       </c>
       <c r="K215" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:42Z</t>
+          <t>2026-09-15T23:01:38Z</t>
         </is>
       </c>
     </row>
@@ -10891,7 +10891,7 @@
       </c>
       <c r="K216" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:42Z</t>
+          <t>2026-09-15T23:01:38Z</t>
         </is>
       </c>
     </row>
@@ -10940,7 +10940,7 @@
       </c>
       <c r="K217" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:42Z</t>
+          <t>2026-09-15T23:01:38Z</t>
         </is>
       </c>
     </row>
@@ -10989,7 +10989,7 @@
       </c>
       <c r="K218" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:42Z</t>
+          <t>2026-09-15T23:01:38Z</t>
         </is>
       </c>
     </row>
@@ -11038,7 +11038,7 @@
       </c>
       <c r="K219" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:42Z</t>
+          <t>2026-09-15T23:01:38Z</t>
         </is>
       </c>
     </row>
@@ -11087,7 +11087,7 @@
       </c>
       <c r="K220" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:42Z</t>
+          <t>2026-09-15T23:01:38Z</t>
         </is>
       </c>
     </row>
@@ -11136,7 +11136,7 @@
       </c>
       <c r="K221" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:42Z</t>
+          <t>2026-09-15T23:01:38Z</t>
         </is>
       </c>
     </row>
@@ -11185,7 +11185,7 @@
       </c>
       <c r="K222" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:42Z</t>
+          <t>2026-09-15T23:01:38Z</t>
         </is>
       </c>
     </row>
@@ -11234,7 +11234,7 @@
       </c>
       <c r="K223" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:42Z</t>
+          <t>2026-09-15T23:01:38Z</t>
         </is>
       </c>
     </row>
@@ -11283,7 +11283,7 @@
       </c>
       <c r="K224" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:42Z</t>
+          <t>2026-09-15T23:01:38Z</t>
         </is>
       </c>
     </row>
@@ -11332,7 +11332,7 @@
       </c>
       <c r="K225" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:42Z</t>
+          <t>2026-09-15T23:01:38Z</t>
         </is>
       </c>
     </row>
@@ -11381,7 +11381,7 @@
       </c>
       <c r="K226" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:42Z</t>
+          <t>2026-09-15T23:01:38Z</t>
         </is>
       </c>
     </row>
@@ -11430,7 +11430,7 @@
       </c>
       <c r="K227" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:42Z</t>
+          <t>2026-09-15T23:01:38Z</t>
         </is>
       </c>
     </row>
@@ -11479,7 +11479,7 @@
       </c>
       <c r="K228" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:42Z</t>
+          <t>2026-09-15T23:01:38Z</t>
         </is>
       </c>
     </row>
@@ -11528,7 +11528,7 @@
       </c>
       <c r="K229" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:42Z</t>
+          <t>2026-09-15T23:01:38Z</t>
         </is>
       </c>
     </row>
@@ -11577,7 +11577,7 @@
       </c>
       <c r="K230" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:42Z</t>
+          <t>2026-09-15T23:01:38Z</t>
         </is>
       </c>
     </row>
@@ -11626,7 +11626,7 @@
       </c>
       <c r="K231" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:42Z</t>
+          <t>2026-09-15T23:01:38Z</t>
         </is>
       </c>
     </row>
@@ -11758,7 +11758,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:42Z</t>
+          <t>2026-09-15T23:01:38Z</t>
         </is>
       </c>
     </row>
@@ -11804,7 +11804,7 @@
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>{"date": "2026-08-01", "year": 2026, "month": 8, "month_name": "Agosto", "index_value": 637409769724325.1, "monthly_variation_pct": 8.9, "unit": "Índice base diciembre 2007=100 y variación mensual %", "frequency": "monthly", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/precios_consumidor/4_5_7_2.xls", "fetched_at": "2026-09-14T23:16:42Z"}</t>
+          <t>{"date": "2026-08-01", "year": 2026, "month": 8, "month_name": "Agosto", "index_value": 637409769724325.1, "monthly_variation_pct": 8.9, "unit": "Índice base diciembre 2007=100 y variación mensual %", "frequency": "monthly", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/precios_consumidor/4_5_7_2.xls", "fetched_at": "2026-09-15T23:01:38Z"}</t>
         </is>
       </c>
     </row>

--- a/assets/data/bcv/excel/ove_bcv_inpc_nacional_mensual.xlsx
+++ b/assets/data/bcv/excel/ove_bcv_inpc_nacional_mensual.xlsx
@@ -650,7 +650,7 @@
       </c>
       <c r="K7" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:38Z</t>
+          <t>2026-09-16T23:07:47Z</t>
         </is>
       </c>
     </row>
@@ -699,7 +699,7 @@
       </c>
       <c r="K8" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:38Z</t>
+          <t>2026-09-16T23:07:47Z</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="K9" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:38Z</t>
+          <t>2026-09-16T23:07:47Z</t>
         </is>
       </c>
     </row>
@@ -797,7 +797,7 @@
       </c>
       <c r="K10" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:38Z</t>
+          <t>2026-09-16T23:07:47Z</t>
         </is>
       </c>
     </row>
@@ -846,7 +846,7 @@
       </c>
       <c r="K11" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:38Z</t>
+          <t>2026-09-16T23:07:47Z</t>
         </is>
       </c>
     </row>
@@ -895,7 +895,7 @@
       </c>
       <c r="K12" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:38Z</t>
+          <t>2026-09-16T23:07:47Z</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="K13" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:38Z</t>
+          <t>2026-09-16T23:07:47Z</t>
         </is>
       </c>
     </row>
@@ -993,7 +993,7 @@
       </c>
       <c r="K14" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:38Z</t>
+          <t>2026-09-16T23:07:47Z</t>
         </is>
       </c>
     </row>
@@ -1042,7 +1042,7 @@
       </c>
       <c r="K15" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:38Z</t>
+          <t>2026-09-16T23:07:47Z</t>
         </is>
       </c>
     </row>
@@ -1091,7 +1091,7 @@
       </c>
       <c r="K16" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:38Z</t>
+          <t>2026-09-16T23:07:47Z</t>
         </is>
       </c>
     </row>
@@ -1140,7 +1140,7 @@
       </c>
       <c r="K17" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:38Z</t>
+          <t>2026-09-16T23:07:47Z</t>
         </is>
       </c>
     </row>
@@ -1189,7 +1189,7 @@
       </c>
       <c r="K18" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:38Z</t>
+          <t>2026-09-16T23:07:47Z</t>
         </is>
       </c>
     </row>
@@ -1238,7 +1238,7 @@
       </c>
       <c r="K19" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:38Z</t>
+          <t>2026-09-16T23:07:47Z</t>
         </is>
       </c>
     </row>
@@ -1287,7 +1287,7 @@
       </c>
       <c r="K20" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:38Z</t>
+          <t>2026-09-16T23:07:47Z</t>
         </is>
       </c>
     </row>
@@ -1336,7 +1336,7 @@
       </c>
       <c r="K21" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:38Z</t>
+          <t>2026-09-16T23:07:47Z</t>
         </is>
       </c>
     </row>
@@ -1385,7 +1385,7 @@
       </c>
       <c r="K22" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:38Z</t>
+          <t>2026-09-16T23:07:47Z</t>
         </is>
       </c>
     </row>
@@ -1434,7 +1434,7 @@
       </c>
       <c r="K23" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:38Z</t>
+          <t>2026-09-16T23:07:47Z</t>
         </is>
       </c>
     </row>
@@ -1483,7 +1483,7 @@
       </c>
       <c r="K24" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:38Z</t>
+          <t>2026-09-16T23:07:47Z</t>
         </is>
       </c>
     </row>
@@ -1532,7 +1532,7 @@
       </c>
       <c r="K25" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:38Z</t>
+          <t>2026-09-16T23:07:47Z</t>
         </is>
       </c>
     </row>
@@ -1581,7 +1581,7 @@
       </c>
       <c r="K26" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:38Z</t>
+          <t>2026-09-16T23:07:47Z</t>
         </is>
       </c>
     </row>
@@ -1630,7 +1630,7 @@
       </c>
       <c r="K27" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:38Z</t>
+          <t>2026-09-16T23:07:47Z</t>
         </is>
       </c>
     </row>
@@ -1679,7 +1679,7 @@
       </c>
       <c r="K28" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:38Z</t>
+          <t>2026-09-16T23:07:47Z</t>
         </is>
       </c>
     </row>
@@ -1728,7 +1728,7 @@
       </c>
       <c r="K29" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:38Z</t>
+          <t>2026-09-16T23:07:47Z</t>
         </is>
       </c>
     </row>
@@ -1777,7 +1777,7 @@
       </c>
       <c r="K30" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:38Z</t>
+          <t>2026-09-16T23:07:47Z</t>
         </is>
       </c>
     </row>
@@ -1826,7 +1826,7 @@
       </c>
       <c r="K31" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:38Z</t>
+          <t>2026-09-16T23:07:47Z</t>
         </is>
       </c>
     </row>
@@ -1875,7 +1875,7 @@
       </c>
       <c r="K32" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:38Z</t>
+          <t>2026-09-16T23:07:47Z</t>
         </is>
       </c>
     </row>
@@ -1924,7 +1924,7 @@
       </c>
       <c r="K33" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:38Z</t>
+          <t>2026-09-16T23:07:47Z</t>
         </is>
       </c>
     </row>
@@ -1973,7 +1973,7 @@
       </c>
       <c r="K34" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:38Z</t>
+          <t>2026-09-16T23:07:47Z</t>
         </is>
       </c>
     </row>
@@ -2022,7 +2022,7 @@
       </c>
       <c r="K35" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:38Z</t>
+          <t>2026-09-16T23:07:47Z</t>
         </is>
       </c>
     </row>
@@ -2071,7 +2071,7 @@
       </c>
       <c r="K36" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:38Z</t>
+          <t>2026-09-16T23:07:47Z</t>
         </is>
       </c>
     </row>
@@ -2120,7 +2120,7 @@
       </c>
       <c r="K37" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:38Z</t>
+          <t>2026-09-16T23:07:47Z</t>
         </is>
       </c>
     </row>
@@ -2169,7 +2169,7 @@
       </c>
       <c r="K38" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:38Z</t>
+          <t>2026-09-16T23:07:47Z</t>
         </is>
       </c>
     </row>
@@ -2218,7 +2218,7 @@
       </c>
       <c r="K39" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:38Z</t>
+          <t>2026-09-16T23:07:47Z</t>
         </is>
       </c>
     </row>
@@ -2267,7 +2267,7 @@
       </c>
       <c r="K40" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:38Z</t>
+          <t>2026-09-16T23:07:47Z</t>
         </is>
       </c>
     </row>
@@ -2316,7 +2316,7 @@
       </c>
       <c r="K41" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:38Z</t>
+          <t>2026-09-16T23:07:47Z</t>
         </is>
       </c>
     </row>
@@ -2365,7 +2365,7 @@
       </c>
       <c r="K42" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:38Z</t>
+          <t>2026-09-16T23:07:47Z</t>
         </is>
       </c>
     </row>
@@ -2414,7 +2414,7 @@
       </c>
       <c r="K43" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:38Z</t>
+          <t>2026-09-16T23:07:47Z</t>
         </is>
       </c>
     </row>
@@ -2463,7 +2463,7 @@
       </c>
       <c r="K44" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:38Z</t>
+          <t>2026-09-16T23:07:47Z</t>
         </is>
       </c>
     </row>
@@ -2512,7 +2512,7 @@
       </c>
       <c r="K45" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:38Z</t>
+          <t>2026-09-16T23:07:47Z</t>
         </is>
       </c>
     </row>
@@ -2561,7 +2561,7 @@
       </c>
       <c r="K46" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:38Z</t>
+          <t>2026-09-16T23:07:47Z</t>
         </is>
       </c>
     </row>
@@ -2610,7 +2610,7 @@
       </c>
       <c r="K47" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:38Z</t>
+          <t>2026-09-16T23:07:47Z</t>
         </is>
       </c>
     </row>
@@ -2659,7 +2659,7 @@
       </c>
       <c r="K48" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:38Z</t>
+          <t>2026-09-16T23:07:47Z</t>
         </is>
       </c>
     </row>
@@ -2708,7 +2708,7 @@
       </c>
       <c r="K49" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:38Z</t>
+          <t>2026-09-16T23:07:47Z</t>
         </is>
       </c>
     </row>
@@ -2757,7 +2757,7 @@
       </c>
       <c r="K50" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:38Z</t>
+          <t>2026-09-16T23:07:47Z</t>
         </is>
       </c>
     </row>
@@ -2806,7 +2806,7 @@
       </c>
       <c r="K51" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:38Z</t>
+          <t>2026-09-16T23:07:47Z</t>
         </is>
       </c>
     </row>
@@ -2855,7 +2855,7 @@
       </c>
       <c r="K52" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:38Z</t>
+          <t>2026-09-16T23:07:47Z</t>
         </is>
       </c>
     </row>
@@ -2904,7 +2904,7 @@
       </c>
       <c r="K53" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:38Z</t>
+          <t>2026-09-16T23:07:47Z</t>
         </is>
       </c>
     </row>
@@ -2953,7 +2953,7 @@
       </c>
       <c r="K54" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:38Z</t>
+          <t>2026-09-16T23:07:47Z</t>
         </is>
       </c>
     </row>
@@ -3002,7 +3002,7 @@
       </c>
       <c r="K55" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:38Z</t>
+          <t>2026-09-16T23:07:47Z</t>
         </is>
       </c>
     </row>
@@ -3051,7 +3051,7 @@
       </c>
       <c r="K56" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:38Z</t>
+          <t>2026-09-16T23:07:47Z</t>
         </is>
       </c>
     </row>
@@ -3100,7 +3100,7 @@
       </c>
       <c r="K57" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:38Z</t>
+          <t>2026-09-16T23:07:47Z</t>
         </is>
       </c>
     </row>
@@ -3149,7 +3149,7 @@
       </c>
       <c r="K58" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:38Z</t>
+          <t>2026-09-16T23:07:47Z</t>
         </is>
       </c>
     </row>
@@ -3198,7 +3198,7 @@
       </c>
       <c r="K59" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:38Z</t>
+          <t>2026-09-16T23:07:47Z</t>
         </is>
       </c>
     </row>
@@ -3247,7 +3247,7 @@
       </c>
       <c r="K60" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:38Z</t>
+          <t>2026-09-16T23:07:47Z</t>
         </is>
       </c>
     </row>
@@ -3296,7 +3296,7 @@
       </c>
       <c r="K61" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:38Z</t>
+          <t>2026-09-16T23:07:47Z</t>
         </is>
       </c>
     </row>
@@ -3345,7 +3345,7 @@
       </c>
       <c r="K62" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:38Z</t>
+          <t>2026-09-16T23:07:47Z</t>
         </is>
       </c>
     </row>
@@ -3394,7 +3394,7 @@
       </c>
       <c r="K63" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:38Z</t>
+          <t>2026-09-16T23:07:47Z</t>
         </is>
       </c>
     </row>
@@ -3443,7 +3443,7 @@
       </c>
       <c r="K64" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:38Z</t>
+          <t>2026-09-16T23:07:47Z</t>
         </is>
       </c>
     </row>
@@ -3492,7 +3492,7 @@
       </c>
       <c r="K65" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:38Z</t>
+          <t>2026-09-16T23:07:47Z</t>
         </is>
       </c>
     </row>
@@ -3541,7 +3541,7 @@
       </c>
       <c r="K66" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:38Z</t>
+          <t>2026-09-16T23:07:47Z</t>
         </is>
       </c>
     </row>
@@ -3590,7 +3590,7 @@
       </c>
       <c r="K67" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:38Z</t>
+          <t>2026-09-16T23:07:47Z</t>
         </is>
       </c>
     </row>
@@ -3639,7 +3639,7 @@
       </c>
       <c r="K68" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:38Z</t>
+          <t>2026-09-16T23:07:47Z</t>
         </is>
       </c>
     </row>
@@ -3688,7 +3688,7 @@
       </c>
       <c r="K69" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:38Z</t>
+          <t>2026-09-16T23:07:47Z</t>
         </is>
       </c>
     </row>
@@ -3737,7 +3737,7 @@
       </c>
       <c r="K70" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:38Z</t>
+          <t>2026-09-16T23:07:47Z</t>
         </is>
       </c>
     </row>
@@ -3786,7 +3786,7 @@
       </c>
       <c r="K71" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:38Z</t>
+          <t>2026-09-16T23:07:47Z</t>
         </is>
       </c>
     </row>
@@ -3835,7 +3835,7 @@
       </c>
       <c r="K72" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:38Z</t>
+          <t>2026-09-16T23:07:47Z</t>
         </is>
       </c>
     </row>
@@ -3884,7 +3884,7 @@
       </c>
       <c r="K73" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:38Z</t>
+          <t>2026-09-16T23:07:47Z</t>
         </is>
       </c>
     </row>
@@ -3933,7 +3933,7 @@
       </c>
       <c r="K74" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:38Z</t>
+          <t>2026-09-16T23:07:47Z</t>
         </is>
       </c>
     </row>
@@ -3982,7 +3982,7 @@
       </c>
       <c r="K75" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:38Z</t>
+          <t>2026-09-16T23:07:47Z</t>
         </is>
       </c>
     </row>
@@ -4031,7 +4031,7 @@
       </c>
       <c r="K76" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:38Z</t>
+          <t>2026-09-16T23:07:47Z</t>
         </is>
       </c>
     </row>
@@ -4080,7 +4080,7 @@
       </c>
       <c r="K77" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:38Z</t>
+          <t>2026-09-16T23:07:47Z</t>
         </is>
       </c>
     </row>
@@ -4129,7 +4129,7 @@
       </c>
       <c r="K78" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:38Z</t>
+          <t>2026-09-16T23:07:47Z</t>
         </is>
       </c>
     </row>
@@ -4178,7 +4178,7 @@
       </c>
       <c r="K79" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:38Z</t>
+          <t>2026-09-16T23:07:47Z</t>
         </is>
       </c>
     </row>
@@ -4227,7 +4227,7 @@
       </c>
       <c r="K80" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:38Z</t>
+          <t>2026-09-16T23:07:47Z</t>
         </is>
       </c>
     </row>
@@ -4276,7 +4276,7 @@
       </c>
       <c r="K81" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:38Z</t>
+          <t>2026-09-16T23:07:47Z</t>
         </is>
       </c>
     </row>
@@ -4325,7 +4325,7 @@
       </c>
       <c r="K82" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:38Z</t>
+          <t>2026-09-16T23:07:47Z</t>
         </is>
       </c>
     </row>
@@ -4374,7 +4374,7 @@
       </c>
       <c r="K83" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:38Z</t>
+          <t>2026-09-16T23:07:47Z</t>
         </is>
       </c>
     </row>
@@ -4423,7 +4423,7 @@
       </c>
       <c r="K84" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:38Z</t>
+          <t>2026-09-16T23:07:47Z</t>
         </is>
       </c>
     </row>
@@ -4472,7 +4472,7 @@
       </c>
       <c r="K85" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:38Z</t>
+          <t>2026-09-16T23:07:47Z</t>
         </is>
       </c>
     </row>
@@ -4521,7 +4521,7 @@
       </c>
       <c r="K86" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:38Z</t>
+          <t>2026-09-16T23:07:47Z</t>
         </is>
       </c>
     </row>
@@ -4570,7 +4570,7 @@
       </c>
       <c r="K87" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:38Z</t>
+          <t>2026-09-16T23:07:47Z</t>
         </is>
       </c>
     </row>
@@ -4619,7 +4619,7 @@
       </c>
       <c r="K88" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:38Z</t>
+          <t>2026-09-16T23:07:47Z</t>
         </is>
       </c>
     </row>
@@ -4668,7 +4668,7 @@
       </c>
       <c r="K89" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:38Z</t>
+          <t>2026-09-16T23:07:47Z</t>
         </is>
       </c>
     </row>
@@ -4717,7 +4717,7 @@
       </c>
       <c r="K90" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:38Z</t>
+          <t>2026-09-16T23:07:47Z</t>
         </is>
       </c>
     </row>
@@ -4766,7 +4766,7 @@
       </c>
       <c r="K91" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:38Z</t>
+          <t>2026-09-16T23:07:47Z</t>
         </is>
       </c>
     </row>
@@ -4815,7 +4815,7 @@
       </c>
       <c r="K92" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:38Z</t>
+          <t>2026-09-16T23:07:47Z</t>
         </is>
       </c>
     </row>
@@ -4864,7 +4864,7 @@
       </c>
       <c r="K93" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:38Z</t>
+          <t>2026-09-16T23:07:47Z</t>
         </is>
       </c>
     </row>
@@ -4913,7 +4913,7 @@
       </c>
       <c r="K94" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:38Z</t>
+          <t>2026-09-16T23:07:47Z</t>
         </is>
       </c>
     </row>
@@ -4962,7 +4962,7 @@
       </c>
       <c r="K95" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:38Z</t>
+          <t>2026-09-16T23:07:47Z</t>
         </is>
       </c>
     </row>
@@ -5011,7 +5011,7 @@
       </c>
       <c r="K96" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:38Z</t>
+          <t>2026-09-16T23:07:47Z</t>
         </is>
       </c>
     </row>
@@ -5060,7 +5060,7 @@
       </c>
       <c r="K97" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:38Z</t>
+          <t>2026-09-16T23:07:47Z</t>
         </is>
       </c>
     </row>
@@ -5109,7 +5109,7 @@
       </c>
       <c r="K98" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:38Z</t>
+          <t>2026-09-16T23:07:47Z</t>
         </is>
       </c>
     </row>
@@ -5158,7 +5158,7 @@
       </c>
       <c r="K99" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:38Z</t>
+          <t>2026-09-16T23:07:47Z</t>
         </is>
       </c>
     </row>
@@ -5207,7 +5207,7 @@
       </c>
       <c r="K100" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:38Z</t>
+          <t>2026-09-16T23:07:47Z</t>
         </is>
       </c>
     </row>
@@ -5256,7 +5256,7 @@
       </c>
       <c r="K101" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:38Z</t>
+          <t>2026-09-16T23:07:47Z</t>
         </is>
       </c>
     </row>
@@ -5305,7 +5305,7 @@
       </c>
       <c r="K102" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:38Z</t>
+          <t>2026-09-16T23:07:47Z</t>
         </is>
       </c>
     </row>
@@ -5354,7 +5354,7 @@
       </c>
       <c r="K103" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:38Z</t>
+          <t>2026-09-16T23:07:47Z</t>
         </is>
       </c>
     </row>
@@ -5403,7 +5403,7 @@
       </c>
       <c r="K104" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:38Z</t>
+          <t>2026-09-16T23:07:47Z</t>
         </is>
       </c>
     </row>
@@ -5452,7 +5452,7 @@
       </c>
       <c r="K105" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:38Z</t>
+          <t>2026-09-16T23:07:47Z</t>
         </is>
       </c>
     </row>
@@ -5501,7 +5501,7 @@
       </c>
       <c r="K106" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:38Z</t>
+          <t>2026-09-16T23:07:47Z</t>
         </is>
       </c>
     </row>
@@ -5550,7 +5550,7 @@
       </c>
       <c r="K107" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:38Z</t>
+          <t>2026-09-16T23:07:47Z</t>
         </is>
       </c>
     </row>
@@ -5599,7 +5599,7 @@
       </c>
       <c r="K108" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:38Z</t>
+          <t>2026-09-16T23:07:47Z</t>
         </is>
       </c>
     </row>
@@ -5648,7 +5648,7 @@
       </c>
       <c r="K109" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:38Z</t>
+          <t>2026-09-16T23:07:47Z</t>
         </is>
       </c>
     </row>
@@ -5697,7 +5697,7 @@
       </c>
       <c r="K110" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:38Z</t>
+          <t>2026-09-16T23:07:47Z</t>
         </is>
       </c>
     </row>
@@ -5746,7 +5746,7 @@
       </c>
       <c r="K111" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:38Z</t>
+          <t>2026-09-16T23:07:47Z</t>
         </is>
       </c>
     </row>
@@ -5795,7 +5795,7 @@
       </c>
       <c r="K112" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:38Z</t>
+          <t>2026-09-16T23:07:47Z</t>
         </is>
       </c>
     </row>
@@ -5844,7 +5844,7 @@
       </c>
       <c r="K113" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:38Z</t>
+          <t>2026-09-16T23:07:47Z</t>
         </is>
       </c>
     </row>
@@ -5893,7 +5893,7 @@
       </c>
       <c r="K114" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:38Z</t>
+          <t>2026-09-16T23:07:47Z</t>
         </is>
       </c>
     </row>
@@ -5942,7 +5942,7 @@
       </c>
       <c r="K115" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:38Z</t>
+          <t>2026-09-16T23:07:47Z</t>
         </is>
       </c>
     </row>
@@ -5991,7 +5991,7 @@
       </c>
       <c r="K116" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:38Z</t>
+          <t>2026-09-16T23:07:47Z</t>
         </is>
       </c>
     </row>
@@ -6040,7 +6040,7 @@
       </c>
       <c r="K117" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:38Z</t>
+          <t>2026-09-16T23:07:47Z</t>
         </is>
       </c>
     </row>
@@ -6089,7 +6089,7 @@
       </c>
       <c r="K118" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:38Z</t>
+          <t>2026-09-16T23:07:47Z</t>
         </is>
       </c>
     </row>
@@ -6138,7 +6138,7 @@
       </c>
       <c r="K119" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:38Z</t>
+          <t>2026-09-16T23:07:47Z</t>
         </is>
       </c>
     </row>
@@ -6187,7 +6187,7 @@
       </c>
       <c r="K120" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:38Z</t>
+          <t>2026-09-16T23:07:47Z</t>
         </is>
       </c>
     </row>
@@ -6236,7 +6236,7 @@
       </c>
       <c r="K121" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:38Z</t>
+          <t>2026-09-16T23:07:47Z</t>
         </is>
       </c>
     </row>
@@ -6285,7 +6285,7 @@
       </c>
       <c r="K122" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:38Z</t>
+          <t>2026-09-16T23:07:47Z</t>
         </is>
       </c>
     </row>
@@ -6334,7 +6334,7 @@
       </c>
       <c r="K123" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:38Z</t>
+          <t>2026-09-16T23:07:47Z</t>
         </is>
       </c>
     </row>
@@ -6383,7 +6383,7 @@
       </c>
       <c r="K124" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:38Z</t>
+          <t>2026-09-16T23:07:47Z</t>
         </is>
       </c>
     </row>
@@ -6432,7 +6432,7 @@
       </c>
       <c r="K125" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:38Z</t>
+          <t>2026-09-16T23:07:47Z</t>
         </is>
       </c>
     </row>
@@ -6481,7 +6481,7 @@
       </c>
       <c r="K126" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:38Z</t>
+          <t>2026-09-16T23:07:47Z</t>
         </is>
       </c>
     </row>
@@ -6530,7 +6530,7 @@
       </c>
       <c r="K127" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:38Z</t>
+          <t>2026-09-16T23:07:47Z</t>
         </is>
       </c>
     </row>
@@ -6579,7 +6579,7 @@
       </c>
       <c r="K128" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:38Z</t>
+          <t>2026-09-16T23:07:47Z</t>
         </is>
       </c>
     </row>
@@ -6628,7 +6628,7 @@
       </c>
       <c r="K129" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:38Z</t>
+          <t>2026-09-16T23:07:47Z</t>
         </is>
       </c>
     </row>
@@ -6677,7 +6677,7 @@
       </c>
       <c r="K130" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:38Z</t>
+          <t>2026-09-16T23:07:47Z</t>
         </is>
       </c>
     </row>
@@ -6726,7 +6726,7 @@
       </c>
       <c r="K131" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:38Z</t>
+          <t>2026-09-16T23:07:47Z</t>
         </is>
       </c>
     </row>
@@ -6775,7 +6775,7 @@
       </c>
       <c r="K132" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:38Z</t>
+          <t>2026-09-16T23:07:47Z</t>
         </is>
       </c>
     </row>
@@ -6824,7 +6824,7 @@
       </c>
       <c r="K133" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:38Z</t>
+          <t>2026-09-16T23:07:47Z</t>
         </is>
       </c>
     </row>
@@ -6873,7 +6873,7 @@
       </c>
       <c r="K134" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:38Z</t>
+          <t>2026-09-16T23:07:47Z</t>
         </is>
       </c>
     </row>
@@ -6922,7 +6922,7 @@
       </c>
       <c r="K135" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:38Z</t>
+          <t>2026-09-16T23:07:47Z</t>
         </is>
       </c>
     </row>
@@ -6971,7 +6971,7 @@
       </c>
       <c r="K136" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:38Z</t>
+          <t>2026-09-16T23:07:47Z</t>
         </is>
       </c>
     </row>
@@ -7020,7 +7020,7 @@
       </c>
       <c r="K137" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:38Z</t>
+          <t>2026-09-16T23:07:47Z</t>
         </is>
       </c>
     </row>
@@ -7069,7 +7069,7 @@
       </c>
       <c r="K138" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:38Z</t>
+          <t>2026-09-16T23:07:47Z</t>
         </is>
       </c>
     </row>
@@ -7118,7 +7118,7 @@
       </c>
       <c r="K139" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:38Z</t>
+          <t>2026-09-16T23:07:47Z</t>
         </is>
       </c>
     </row>
@@ -7167,7 +7167,7 @@
       </c>
       <c r="K140" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:38Z</t>
+          <t>2026-09-16T23:07:47Z</t>
         </is>
       </c>
     </row>
@@ -7216,7 +7216,7 @@
       </c>
       <c r="K141" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:38Z</t>
+          <t>2026-09-16T23:07:47Z</t>
         </is>
       </c>
     </row>
@@ -7265,7 +7265,7 @@
       </c>
       <c r="K142" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:38Z</t>
+          <t>2026-09-16T23:07:47Z</t>
         </is>
       </c>
     </row>
@@ -7314,7 +7314,7 @@
       </c>
       <c r="K143" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:38Z</t>
+          <t>2026-09-16T23:07:47Z</t>
         </is>
       </c>
     </row>
@@ -7363,7 +7363,7 @@
       </c>
       <c r="K144" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:38Z</t>
+          <t>2026-09-16T23:07:47Z</t>
         </is>
       </c>
     </row>
@@ -7412,7 +7412,7 @@
       </c>
       <c r="K145" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:38Z</t>
+          <t>2026-09-16T23:07:47Z</t>
         </is>
       </c>
     </row>
@@ -7461,7 +7461,7 @@
       </c>
       <c r="K146" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:38Z</t>
+          <t>2026-09-16T23:07:47Z</t>
         </is>
       </c>
     </row>
@@ -7510,7 +7510,7 @@
       </c>
       <c r="K147" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:38Z</t>
+          <t>2026-09-16T23:07:47Z</t>
         </is>
       </c>
     </row>
@@ -7559,7 +7559,7 @@
       </c>
       <c r="K148" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:38Z</t>
+          <t>2026-09-16T23:07:47Z</t>
         </is>
       </c>
     </row>
@@ -7608,7 +7608,7 @@
       </c>
       <c r="K149" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:38Z</t>
+          <t>2026-09-16T23:07:47Z</t>
         </is>
       </c>
     </row>
@@ -7657,7 +7657,7 @@
       </c>
       <c r="K150" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:38Z</t>
+          <t>2026-09-16T23:07:47Z</t>
         </is>
       </c>
     </row>
@@ -7706,7 +7706,7 @@
       </c>
       <c r="K151" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:38Z</t>
+          <t>2026-09-16T23:07:47Z</t>
         </is>
       </c>
     </row>
@@ -7755,7 +7755,7 @@
       </c>
       <c r="K152" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:38Z</t>
+          <t>2026-09-16T23:07:47Z</t>
         </is>
       </c>
     </row>
@@ -7804,7 +7804,7 @@
       </c>
       <c r="K153" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:38Z</t>
+          <t>2026-09-16T23:07:47Z</t>
         </is>
       </c>
     </row>
@@ -7853,7 +7853,7 @@
       </c>
       <c r="K154" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:38Z</t>
+          <t>2026-09-16T23:07:47Z</t>
         </is>
       </c>
     </row>
@@ -7902,7 +7902,7 @@
       </c>
       <c r="K155" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:38Z</t>
+          <t>2026-09-16T23:07:47Z</t>
         </is>
       </c>
     </row>
@@ -7951,7 +7951,7 @@
       </c>
       <c r="K156" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:38Z</t>
+          <t>2026-09-16T23:07:47Z</t>
         </is>
       </c>
     </row>
@@ -8000,7 +8000,7 @@
       </c>
       <c r="K157" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:38Z</t>
+          <t>2026-09-16T23:07:47Z</t>
         </is>
       </c>
     </row>
@@ -8049,7 +8049,7 @@
       </c>
       <c r="K158" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:38Z</t>
+          <t>2026-09-16T23:07:47Z</t>
         </is>
       </c>
     </row>
@@ -8098,7 +8098,7 @@
       </c>
       <c r="K159" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:38Z</t>
+          <t>2026-09-16T23:07:47Z</t>
         </is>
       </c>
     </row>
@@ -8147,7 +8147,7 @@
       </c>
       <c r="K160" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:38Z</t>
+          <t>2026-09-16T23:07:47Z</t>
         </is>
       </c>
     </row>
@@ -8196,7 +8196,7 @@
       </c>
       <c r="K161" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:38Z</t>
+          <t>2026-09-16T23:07:47Z</t>
         </is>
       </c>
     </row>
@@ -8245,7 +8245,7 @@
       </c>
       <c r="K162" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:38Z</t>
+          <t>2026-09-16T23:07:47Z</t>
         </is>
       </c>
     </row>
@@ -8294,7 +8294,7 @@
       </c>
       <c r="K163" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:38Z</t>
+          <t>2026-09-16T23:07:47Z</t>
         </is>
       </c>
     </row>
@@ -8343,7 +8343,7 @@
       </c>
       <c r="K164" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:38Z</t>
+          <t>2026-09-16T23:07:47Z</t>
         </is>
       </c>
     </row>
@@ -8392,7 +8392,7 @@
       </c>
       <c r="K165" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:38Z</t>
+          <t>2026-09-16T23:07:47Z</t>
         </is>
       </c>
     </row>
@@ -8441,7 +8441,7 @@
       </c>
       <c r="K166" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:38Z</t>
+          <t>2026-09-16T23:07:47Z</t>
         </is>
       </c>
     </row>
@@ -8490,7 +8490,7 @@
       </c>
       <c r="K167" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:38Z</t>
+          <t>2026-09-16T23:07:47Z</t>
         </is>
       </c>
     </row>
@@ -8539,7 +8539,7 @@
       </c>
       <c r="K168" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:38Z</t>
+          <t>2026-09-16T23:07:47Z</t>
         </is>
       </c>
     </row>
@@ -8588,7 +8588,7 @@
       </c>
       <c r="K169" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:38Z</t>
+          <t>2026-09-16T23:07:47Z</t>
         </is>
       </c>
     </row>
@@ -8637,7 +8637,7 @@
       </c>
       <c r="K170" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:38Z</t>
+          <t>2026-09-16T23:07:47Z</t>
         </is>
       </c>
     </row>
@@ -8686,7 +8686,7 @@
       </c>
       <c r="K171" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:38Z</t>
+          <t>2026-09-16T23:07:47Z</t>
         </is>
       </c>
     </row>
@@ -8735,7 +8735,7 @@
       </c>
       <c r="K172" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:38Z</t>
+          <t>2026-09-16T23:07:47Z</t>
         </is>
       </c>
     </row>
@@ -8784,7 +8784,7 @@
       </c>
       <c r="K173" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:38Z</t>
+          <t>2026-09-16T23:07:47Z</t>
         </is>
       </c>
     </row>
@@ -8833,7 +8833,7 @@
       </c>
       <c r="K174" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:38Z</t>
+          <t>2026-09-16T23:07:47Z</t>
         </is>
       </c>
     </row>
@@ -8882,7 +8882,7 @@
       </c>
       <c r="K175" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:38Z</t>
+          <t>2026-09-16T23:07:47Z</t>
         </is>
       </c>
     </row>
@@ -8931,7 +8931,7 @@
       </c>
       <c r="K176" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:38Z</t>
+          <t>2026-09-16T23:07:47Z</t>
         </is>
       </c>
     </row>
@@ -8980,7 +8980,7 @@
       </c>
       <c r="K177" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:38Z</t>
+          <t>2026-09-16T23:07:47Z</t>
         </is>
       </c>
     </row>
@@ -9029,7 +9029,7 @@
       </c>
       <c r="K178" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:38Z</t>
+          <t>2026-09-16T23:07:47Z</t>
         </is>
       </c>
     </row>
@@ -9078,7 +9078,7 @@
       </c>
       <c r="K179" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:38Z</t>
+          <t>2026-09-16T23:07:47Z</t>
         </is>
       </c>
     </row>
@@ -9127,7 +9127,7 @@
       </c>
       <c r="K180" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:38Z</t>
+          <t>2026-09-16T23:07:47Z</t>
         </is>
       </c>
     </row>
@@ -9176,7 +9176,7 @@
       </c>
       <c r="K181" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:38Z</t>
+          <t>2026-09-16T23:07:47Z</t>
         </is>
       </c>
     </row>
@@ -9225,7 +9225,7 @@
       </c>
       <c r="K182" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:38Z</t>
+          <t>2026-09-16T23:07:47Z</t>
         </is>
       </c>
     </row>
@@ -9274,7 +9274,7 @@
       </c>
       <c r="K183" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:38Z</t>
+          <t>2026-09-16T23:07:47Z</t>
         </is>
       </c>
     </row>
@@ -9323,7 +9323,7 @@
       </c>
       <c r="K184" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:38Z</t>
+          <t>2026-09-16T23:07:47Z</t>
         </is>
       </c>
     </row>
@@ -9372,7 +9372,7 @@
       </c>
       <c r="K185" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:38Z</t>
+          <t>2026-09-16T23:07:47Z</t>
         </is>
       </c>
     </row>
@@ -9421,7 +9421,7 @@
       </c>
       <c r="K186" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:38Z</t>
+          <t>2026-09-16T23:07:47Z</t>
         </is>
       </c>
     </row>
@@ -9470,7 +9470,7 @@
       </c>
       <c r="K187" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:38Z</t>
+          <t>2026-09-16T23:07:47Z</t>
         </is>
       </c>
     </row>
@@ -9519,7 +9519,7 @@
       </c>
       <c r="K188" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:38Z</t>
+          <t>2026-09-16T23:07:47Z</t>
         </is>
       </c>
     </row>
@@ -9568,7 +9568,7 @@
       </c>
       <c r="K189" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:38Z</t>
+          <t>2026-09-16T23:07:47Z</t>
         </is>
       </c>
     </row>
@@ -9617,7 +9617,7 @@
       </c>
       <c r="K190" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:38Z</t>
+          <t>2026-09-16T23:07:47Z</t>
         </is>
       </c>
     </row>
@@ -9666,7 +9666,7 @@
       </c>
       <c r="K191" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:38Z</t>
+          <t>2026-09-16T23:07:47Z</t>
         </is>
       </c>
     </row>
@@ -9715,7 +9715,7 @@
       </c>
       <c r="K192" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:38Z</t>
+          <t>2026-09-16T23:07:47Z</t>
         </is>
       </c>
     </row>
@@ -9764,7 +9764,7 @@
       </c>
       <c r="K193" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:38Z</t>
+          <t>2026-09-16T23:07:47Z</t>
         </is>
       </c>
     </row>
@@ -9813,7 +9813,7 @@
       </c>
       <c r="K194" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:38Z</t>
+          <t>2026-09-16T23:07:47Z</t>
         </is>
       </c>
     </row>
@@ -9862,7 +9862,7 @@
       </c>
       <c r="K195" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:38Z</t>
+          <t>2026-09-16T23:07:47Z</t>
         </is>
       </c>
     </row>
@@ -9911,7 +9911,7 @@
       </c>
       <c r="K196" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:38Z</t>
+          <t>2026-09-16T23:07:47Z</t>
         </is>
       </c>
     </row>
@@ -9960,7 +9960,7 @@
       </c>
       <c r="K197" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:38Z</t>
+          <t>2026-09-16T23:07:47Z</t>
         </is>
       </c>
     </row>
@@ -10009,7 +10009,7 @@
       </c>
       <c r="K198" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:38Z</t>
+          <t>2026-09-16T23:07:47Z</t>
         </is>
       </c>
     </row>
@@ -10058,7 +10058,7 @@
       </c>
       <c r="K199" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:38Z</t>
+          <t>2026-09-16T23:07:47Z</t>
         </is>
       </c>
     </row>
@@ -10107,7 +10107,7 @@
       </c>
       <c r="K200" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:38Z</t>
+          <t>2026-09-16T23:07:47Z</t>
         </is>
       </c>
     </row>
@@ -10156,7 +10156,7 @@
       </c>
       <c r="K201" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:38Z</t>
+          <t>2026-09-16T23:07:47Z</t>
         </is>
       </c>
     </row>
@@ -10205,7 +10205,7 @@
       </c>
       <c r="K202" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:38Z</t>
+          <t>2026-09-16T23:07:47Z</t>
         </is>
       </c>
     </row>
@@ -10254,7 +10254,7 @@
       </c>
       <c r="K203" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:38Z</t>
+          <t>2026-09-16T23:07:47Z</t>
         </is>
       </c>
     </row>
@@ -10303,7 +10303,7 @@
       </c>
       <c r="K204" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:38Z</t>
+          <t>2026-09-16T23:07:47Z</t>
         </is>
       </c>
     </row>
@@ -10352,7 +10352,7 @@
       </c>
       <c r="K205" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:38Z</t>
+          <t>2026-09-16T23:07:47Z</t>
         </is>
       </c>
     </row>
@@ -10401,7 +10401,7 @@
       </c>
       <c r="K206" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:38Z</t>
+          <t>2026-09-16T23:07:47Z</t>
         </is>
       </c>
     </row>
@@ -10450,7 +10450,7 @@
       </c>
       <c r="K207" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:38Z</t>
+          <t>2026-09-16T23:07:47Z</t>
         </is>
       </c>
     </row>
@@ -10499,7 +10499,7 @@
       </c>
       <c r="K208" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:38Z</t>
+          <t>2026-09-16T23:07:47Z</t>
         </is>
       </c>
     </row>
@@ -10548,7 +10548,7 @@
       </c>
       <c r="K209" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:38Z</t>
+          <t>2026-09-16T23:07:47Z</t>
         </is>
       </c>
     </row>
@@ -10597,7 +10597,7 @@
       </c>
       <c r="K210" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:38Z</t>
+          <t>2026-09-16T23:07:47Z</t>
         </is>
       </c>
     </row>
@@ -10646,7 +10646,7 @@
       </c>
       <c r="K211" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:38Z</t>
+          <t>2026-09-16T23:07:47Z</t>
         </is>
       </c>
     </row>
@@ -10695,7 +10695,7 @@
       </c>
       <c r="K212" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:38Z</t>
+          <t>2026-09-16T23:07:47Z</t>
         </is>
       </c>
     </row>
@@ -10744,7 +10744,7 @@
       </c>
       <c r="K213" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:38Z</t>
+          <t>2026-09-16T23:07:47Z</t>
         </is>
       </c>
     </row>
@@ -10793,7 +10793,7 @@
       </c>
       <c r="K214" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:38Z</t>
+          <t>2026-09-16T23:07:47Z</t>
         </is>
       </c>
     </row>
@@ -10842,7 +10842,7 @@
       </c>
       <c r="K215" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:38Z</t>
+          <t>2026-09-16T23:07:47Z</t>
         </is>
       </c>
     </row>
@@ -10891,7 +10891,7 @@
       </c>
       <c r="K216" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:38Z</t>
+          <t>2026-09-16T23:07:47Z</t>
         </is>
       </c>
     </row>
@@ -10940,7 +10940,7 @@
       </c>
       <c r="K217" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:38Z</t>
+          <t>2026-09-16T23:07:47Z</t>
         </is>
       </c>
     </row>
@@ -10989,7 +10989,7 @@
       </c>
       <c r="K218" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:38Z</t>
+          <t>2026-09-16T23:07:47Z</t>
         </is>
       </c>
     </row>
@@ -11038,7 +11038,7 @@
       </c>
       <c r="K219" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:38Z</t>
+          <t>2026-09-16T23:07:47Z</t>
         </is>
       </c>
     </row>
@@ -11087,7 +11087,7 @@
       </c>
       <c r="K220" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:38Z</t>
+          <t>2026-09-16T23:07:47Z</t>
         </is>
       </c>
     </row>
@@ -11136,7 +11136,7 @@
       </c>
       <c r="K221" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:38Z</t>
+          <t>2026-09-16T23:07:47Z</t>
         </is>
       </c>
     </row>
@@ -11185,7 +11185,7 @@
       </c>
       <c r="K222" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:38Z</t>
+          <t>2026-09-16T23:07:47Z</t>
         </is>
       </c>
     </row>
@@ -11234,7 +11234,7 @@
       </c>
       <c r="K223" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:38Z</t>
+          <t>2026-09-16T23:07:47Z</t>
         </is>
       </c>
     </row>
@@ -11283,7 +11283,7 @@
       </c>
       <c r="K224" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:38Z</t>
+          <t>2026-09-16T23:07:47Z</t>
         </is>
       </c>
     </row>
@@ -11332,7 +11332,7 @@
       </c>
       <c r="K225" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:38Z</t>
+          <t>2026-09-16T23:07:47Z</t>
         </is>
       </c>
     </row>
@@ -11381,7 +11381,7 @@
       </c>
       <c r="K226" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:38Z</t>
+          <t>2026-09-16T23:07:47Z</t>
         </is>
       </c>
     </row>
@@ -11430,7 +11430,7 @@
       </c>
       <c r="K227" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:38Z</t>
+          <t>2026-09-16T23:07:47Z</t>
         </is>
       </c>
     </row>
@@ -11479,7 +11479,7 @@
       </c>
       <c r="K228" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:38Z</t>
+          <t>2026-09-16T23:07:47Z</t>
         </is>
       </c>
     </row>
@@ -11528,7 +11528,7 @@
       </c>
       <c r="K229" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:38Z</t>
+          <t>2026-09-16T23:07:47Z</t>
         </is>
       </c>
     </row>
@@ -11577,7 +11577,7 @@
       </c>
       <c r="K230" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:38Z</t>
+          <t>2026-09-16T23:07:47Z</t>
         </is>
       </c>
     </row>
@@ -11626,7 +11626,7 @@
       </c>
       <c r="K231" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:38Z</t>
+          <t>2026-09-16T23:07:47Z</t>
         </is>
       </c>
     </row>
@@ -11758,7 +11758,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:38Z</t>
+          <t>2026-09-16T23:07:47Z</t>
         </is>
       </c>
     </row>
@@ -11804,7 +11804,7 @@
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>{"date": "2026-08-01", "year": 2026, "month": 8, "month_name": "Agosto", "index_value": 637409769724325.1, "monthly_variation_pct": 8.9, "unit": "Índice base diciembre 2007=100 y variación mensual %", "frequency": "monthly", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/precios_consumidor/4_5_7_2.xls", "fetched_at": "2026-09-15T23:01:38Z"}</t>
+          <t>{"date": "2026-08-01", "year": 2026, "month": 8, "month_name": "Agosto", "index_value": 637409769724325.1, "monthly_variation_pct": 8.9, "unit": "Índice base diciembre 2007=100 y variación mensual %", "frequency": "monthly", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/precios_consumidor/4_5_7_2.xls", "fetched_at": "2026-09-16T23:07:47Z"}</t>
         </is>
       </c>
     </row>

--- a/assets/data/bcv/excel/ove_bcv_inpc_nacional_mensual.xlsx
+++ b/assets/data/bcv/excel/ove_bcv_inpc_nacional_mensual.xlsx
@@ -650,7 +650,7 @@
       </c>
       <c r="K7" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:47Z</t>
+          <t>2026-09-17T17:37:54Z</t>
         </is>
       </c>
     </row>
@@ -699,7 +699,7 @@
       </c>
       <c r="K8" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:47Z</t>
+          <t>2026-09-17T17:37:54Z</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="K9" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:47Z</t>
+          <t>2026-09-17T17:37:54Z</t>
         </is>
       </c>
     </row>
@@ -797,7 +797,7 @@
       </c>
       <c r="K10" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:47Z</t>
+          <t>2026-09-17T17:37:54Z</t>
         </is>
       </c>
     </row>
@@ -846,7 +846,7 @@
       </c>
       <c r="K11" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:47Z</t>
+          <t>2026-09-17T17:37:54Z</t>
         </is>
       </c>
     </row>
@@ -895,7 +895,7 @@
       </c>
       <c r="K12" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:47Z</t>
+          <t>2026-09-17T17:37:54Z</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="K13" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:47Z</t>
+          <t>2026-09-17T17:37:54Z</t>
         </is>
       </c>
     </row>
@@ -993,7 +993,7 @@
       </c>
       <c r="K14" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:47Z</t>
+          <t>2026-09-17T17:37:54Z</t>
         </is>
       </c>
     </row>
@@ -1042,7 +1042,7 @@
       </c>
       <c r="K15" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:47Z</t>
+          <t>2026-09-17T17:37:54Z</t>
         </is>
       </c>
     </row>
@@ -1091,7 +1091,7 @@
       </c>
       <c r="K16" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:47Z</t>
+          <t>2026-09-17T17:37:54Z</t>
         </is>
       </c>
     </row>
@@ -1140,7 +1140,7 @@
       </c>
       <c r="K17" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:47Z</t>
+          <t>2026-09-17T17:37:54Z</t>
         </is>
       </c>
     </row>
@@ -1189,7 +1189,7 @@
       </c>
       <c r="K18" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:47Z</t>
+          <t>2026-09-17T17:37:54Z</t>
         </is>
       </c>
     </row>
@@ -1238,7 +1238,7 @@
       </c>
       <c r="K19" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:47Z</t>
+          <t>2026-09-17T17:37:54Z</t>
         </is>
       </c>
     </row>
@@ -1287,7 +1287,7 @@
       </c>
       <c r="K20" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:47Z</t>
+          <t>2026-09-17T17:37:54Z</t>
         </is>
       </c>
     </row>
@@ -1336,7 +1336,7 @@
       </c>
       <c r="K21" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:47Z</t>
+          <t>2026-09-17T17:37:54Z</t>
         </is>
       </c>
     </row>
@@ -1385,7 +1385,7 @@
       </c>
       <c r="K22" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:47Z</t>
+          <t>2026-09-17T17:37:54Z</t>
         </is>
       </c>
     </row>
@@ -1434,7 +1434,7 @@
       </c>
       <c r="K23" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:47Z</t>
+          <t>2026-09-17T17:37:54Z</t>
         </is>
       </c>
     </row>
@@ -1483,7 +1483,7 @@
       </c>
       <c r="K24" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:47Z</t>
+          <t>2026-09-17T17:37:54Z</t>
         </is>
       </c>
     </row>
@@ -1532,7 +1532,7 @@
       </c>
       <c r="K25" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:47Z</t>
+          <t>2026-09-17T17:37:54Z</t>
         </is>
       </c>
     </row>
@@ -1581,7 +1581,7 @@
       </c>
       <c r="K26" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:47Z</t>
+          <t>2026-09-17T17:37:54Z</t>
         </is>
       </c>
     </row>
@@ -1630,7 +1630,7 @@
       </c>
       <c r="K27" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:47Z</t>
+          <t>2026-09-17T17:37:54Z</t>
         </is>
       </c>
     </row>
@@ -1679,7 +1679,7 @@
       </c>
       <c r="K28" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:47Z</t>
+          <t>2026-09-17T17:37:54Z</t>
         </is>
       </c>
     </row>
@@ -1728,7 +1728,7 @@
       </c>
       <c r="K29" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:47Z</t>
+          <t>2026-09-17T17:37:54Z</t>
         </is>
       </c>
     </row>
@@ -1777,7 +1777,7 @@
       </c>
       <c r="K30" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:47Z</t>
+          <t>2026-09-17T17:37:54Z</t>
         </is>
       </c>
     </row>
@@ -1826,7 +1826,7 @@
       </c>
       <c r="K31" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:47Z</t>
+          <t>2026-09-17T17:37:54Z</t>
         </is>
       </c>
     </row>
@@ -1875,7 +1875,7 @@
       </c>
       <c r="K32" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:47Z</t>
+          <t>2026-09-17T17:37:54Z</t>
         </is>
       </c>
     </row>
@@ -1924,7 +1924,7 @@
       </c>
       <c r="K33" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:47Z</t>
+          <t>2026-09-17T17:37:54Z</t>
         </is>
       </c>
     </row>
@@ -1973,7 +1973,7 @@
       </c>
       <c r="K34" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:47Z</t>
+          <t>2026-09-17T17:37:54Z</t>
         </is>
       </c>
     </row>
@@ -2022,7 +2022,7 @@
       </c>
       <c r="K35" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:47Z</t>
+          <t>2026-09-17T17:37:54Z</t>
         </is>
       </c>
     </row>
@@ -2071,7 +2071,7 @@
       </c>
       <c r="K36" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:47Z</t>
+          <t>2026-09-17T17:37:54Z</t>
         </is>
       </c>
     </row>
@@ -2120,7 +2120,7 @@
       </c>
       <c r="K37" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:47Z</t>
+          <t>2026-09-17T17:37:54Z</t>
         </is>
       </c>
     </row>
@@ -2169,7 +2169,7 @@
       </c>
       <c r="K38" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:47Z</t>
+          <t>2026-09-17T17:37:54Z</t>
         </is>
       </c>
     </row>
@@ -2218,7 +2218,7 @@
       </c>
       <c r="K39" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:47Z</t>
+          <t>2026-09-17T17:37:54Z</t>
         </is>
       </c>
     </row>
@@ -2267,7 +2267,7 @@
       </c>
       <c r="K40" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:47Z</t>
+          <t>2026-09-17T17:37:54Z</t>
         </is>
       </c>
     </row>
@@ -2316,7 +2316,7 @@
       </c>
       <c r="K41" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:47Z</t>
+          <t>2026-09-17T17:37:54Z</t>
         </is>
       </c>
     </row>
@@ -2365,7 +2365,7 @@
       </c>
       <c r="K42" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:47Z</t>
+          <t>2026-09-17T17:37:54Z</t>
         </is>
       </c>
     </row>
@@ -2414,7 +2414,7 @@
       </c>
       <c r="K43" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:47Z</t>
+          <t>2026-09-17T17:37:54Z</t>
         </is>
       </c>
     </row>
@@ -2463,7 +2463,7 @@
       </c>
       <c r="K44" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:47Z</t>
+          <t>2026-09-17T17:37:54Z</t>
         </is>
       </c>
     </row>
@@ -2512,7 +2512,7 @@
       </c>
       <c r="K45" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:47Z</t>
+          <t>2026-09-17T17:37:54Z</t>
         </is>
       </c>
     </row>
@@ -2561,7 +2561,7 @@
       </c>
       <c r="K46" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:47Z</t>
+          <t>2026-09-17T17:37:54Z</t>
         </is>
       </c>
     </row>
@@ -2610,7 +2610,7 @@
       </c>
       <c r="K47" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:47Z</t>
+          <t>2026-09-17T17:37:54Z</t>
         </is>
       </c>
     </row>
@@ -2659,7 +2659,7 @@
       </c>
       <c r="K48" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:47Z</t>
+          <t>2026-09-17T17:37:54Z</t>
         </is>
       </c>
     </row>
@@ -2708,7 +2708,7 @@
       </c>
       <c r="K49" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:47Z</t>
+          <t>2026-09-17T17:37:54Z</t>
         </is>
       </c>
     </row>
@@ -2757,7 +2757,7 @@
       </c>
       <c r="K50" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:47Z</t>
+          <t>2026-09-17T17:37:54Z</t>
         </is>
       </c>
     </row>
@@ -2806,7 +2806,7 @@
       </c>
       <c r="K51" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:47Z</t>
+          <t>2026-09-17T17:37:54Z</t>
         </is>
       </c>
     </row>
@@ -2855,7 +2855,7 @@
       </c>
       <c r="K52" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:47Z</t>
+          <t>2026-09-17T17:37:54Z</t>
         </is>
       </c>
     </row>
@@ -2904,7 +2904,7 @@
       </c>
       <c r="K53" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:47Z</t>
+          <t>2026-09-17T17:37:54Z</t>
         </is>
       </c>
     </row>
@@ -2953,7 +2953,7 @@
       </c>
       <c r="K54" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:47Z</t>
+          <t>2026-09-17T17:37:54Z</t>
         </is>
       </c>
     </row>
@@ -3002,7 +3002,7 @@
       </c>
       <c r="K55" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:47Z</t>
+          <t>2026-09-17T17:37:54Z</t>
         </is>
       </c>
     </row>
@@ -3051,7 +3051,7 @@
       </c>
       <c r="K56" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:47Z</t>
+          <t>2026-09-17T17:37:54Z</t>
         </is>
       </c>
     </row>
@@ -3100,7 +3100,7 @@
       </c>
       <c r="K57" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:47Z</t>
+          <t>2026-09-17T17:37:54Z</t>
         </is>
       </c>
     </row>
@@ -3149,7 +3149,7 @@
       </c>
       <c r="K58" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:47Z</t>
+          <t>2026-09-17T17:37:54Z</t>
         </is>
       </c>
     </row>
@@ -3198,7 +3198,7 @@
       </c>
       <c r="K59" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:47Z</t>
+          <t>2026-09-17T17:37:54Z</t>
         </is>
       </c>
     </row>
@@ -3247,7 +3247,7 @@
       </c>
       <c r="K60" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:47Z</t>
+          <t>2026-09-17T17:37:54Z</t>
         </is>
       </c>
     </row>
@@ -3296,7 +3296,7 @@
       </c>
       <c r="K61" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:47Z</t>
+          <t>2026-09-17T17:37:54Z</t>
         </is>
       </c>
     </row>
@@ -3345,7 +3345,7 @@
       </c>
       <c r="K62" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:47Z</t>
+          <t>2026-09-17T17:37:54Z</t>
         </is>
       </c>
     </row>
@@ -3394,7 +3394,7 @@
       </c>
       <c r="K63" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:47Z</t>
+          <t>2026-09-17T17:37:54Z</t>
         </is>
       </c>
     </row>
@@ -3443,7 +3443,7 @@
       </c>
       <c r="K64" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:47Z</t>
+          <t>2026-09-17T17:37:54Z</t>
         </is>
       </c>
     </row>
@@ -3492,7 +3492,7 @@
       </c>
       <c r="K65" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:47Z</t>
+          <t>2026-09-17T17:37:54Z</t>
         </is>
       </c>
     </row>
@@ -3541,7 +3541,7 @@
       </c>
       <c r="K66" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:47Z</t>
+          <t>2026-09-17T17:37:54Z</t>
         </is>
       </c>
     </row>
@@ -3590,7 +3590,7 @@
       </c>
       <c r="K67" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:47Z</t>
+          <t>2026-09-17T17:37:54Z</t>
         </is>
       </c>
     </row>
@@ -3639,7 +3639,7 @@
       </c>
       <c r="K68" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:47Z</t>
+          <t>2026-09-17T17:37:54Z</t>
         </is>
       </c>
     </row>
@@ -3688,7 +3688,7 @@
       </c>
       <c r="K69" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:47Z</t>
+          <t>2026-09-17T17:37:54Z</t>
         </is>
       </c>
     </row>
@@ -3737,7 +3737,7 @@
       </c>
       <c r="K70" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:47Z</t>
+          <t>2026-09-17T17:37:54Z</t>
         </is>
       </c>
     </row>
@@ -3786,7 +3786,7 @@
       </c>
       <c r="K71" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:47Z</t>
+          <t>2026-09-17T17:37:54Z</t>
         </is>
       </c>
     </row>
@@ -3835,7 +3835,7 @@
       </c>
       <c r="K72" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:47Z</t>
+          <t>2026-09-17T17:37:54Z</t>
         </is>
       </c>
     </row>
@@ -3884,7 +3884,7 @@
       </c>
       <c r="K73" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:47Z</t>
+          <t>2026-09-17T17:37:54Z</t>
         </is>
       </c>
     </row>
@@ -3933,7 +3933,7 @@
       </c>
       <c r="K74" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:47Z</t>
+          <t>2026-09-17T17:37:54Z</t>
         </is>
       </c>
     </row>
@@ -3982,7 +3982,7 @@
       </c>
       <c r="K75" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:47Z</t>
+          <t>2026-09-17T17:37:54Z</t>
         </is>
       </c>
     </row>
@@ -4031,7 +4031,7 @@
       </c>
       <c r="K76" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:47Z</t>
+          <t>2026-09-17T17:37:54Z</t>
         </is>
       </c>
     </row>
@@ -4080,7 +4080,7 @@
       </c>
       <c r="K77" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:47Z</t>
+          <t>2026-09-17T17:37:54Z</t>
         </is>
       </c>
     </row>
@@ -4129,7 +4129,7 @@
       </c>
       <c r="K78" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:47Z</t>
+          <t>2026-09-17T17:37:54Z</t>
         </is>
       </c>
     </row>
@@ -4178,7 +4178,7 @@
       </c>
       <c r="K79" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:47Z</t>
+          <t>2026-09-17T17:37:54Z</t>
         </is>
       </c>
     </row>
@@ -4227,7 +4227,7 @@
       </c>
       <c r="K80" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:47Z</t>
+          <t>2026-09-17T17:37:54Z</t>
         </is>
       </c>
     </row>
@@ -4276,7 +4276,7 @@
       </c>
       <c r="K81" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:47Z</t>
+          <t>2026-09-17T17:37:54Z</t>
         </is>
       </c>
     </row>
@@ -4325,7 +4325,7 @@
       </c>
       <c r="K82" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:47Z</t>
+          <t>2026-09-17T17:37:54Z</t>
         </is>
       </c>
     </row>
@@ -4374,7 +4374,7 @@
       </c>
       <c r="K83" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:47Z</t>
+          <t>2026-09-17T17:37:54Z</t>
         </is>
       </c>
     </row>
@@ -4423,7 +4423,7 @@
       </c>
       <c r="K84" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:47Z</t>
+          <t>2026-09-17T17:37:54Z</t>
         </is>
       </c>
     </row>
@@ -4472,7 +4472,7 @@
       </c>
       <c r="K85" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:47Z</t>
+          <t>2026-09-17T17:37:54Z</t>
         </is>
       </c>
     </row>
@@ -4521,7 +4521,7 @@
       </c>
       <c r="K86" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:47Z</t>
+          <t>2026-09-17T17:37:54Z</t>
         </is>
       </c>
     </row>
@@ -4570,7 +4570,7 @@
       </c>
       <c r="K87" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:47Z</t>
+          <t>2026-09-17T17:37:54Z</t>
         </is>
       </c>
     </row>
@@ -4619,7 +4619,7 @@
       </c>
       <c r="K88" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:47Z</t>
+          <t>2026-09-17T17:37:54Z</t>
         </is>
       </c>
     </row>
@@ -4668,7 +4668,7 @@
       </c>
       <c r="K89" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:47Z</t>
+          <t>2026-09-17T17:37:54Z</t>
         </is>
       </c>
     </row>
@@ -4717,7 +4717,7 @@
       </c>
       <c r="K90" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:47Z</t>
+          <t>2026-09-17T17:37:54Z</t>
         </is>
       </c>
     </row>
@@ -4766,7 +4766,7 @@
       </c>
       <c r="K91" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:47Z</t>
+          <t>2026-09-17T17:37:54Z</t>
         </is>
       </c>
     </row>
@@ -4815,7 +4815,7 @@
       </c>
       <c r="K92" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:47Z</t>
+          <t>2026-09-17T17:37:54Z</t>
         </is>
       </c>
     </row>
@@ -4864,7 +4864,7 @@
       </c>
       <c r="K93" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:47Z</t>
+          <t>2026-09-17T17:37:54Z</t>
         </is>
       </c>
     </row>
@@ -4913,7 +4913,7 @@
       </c>
       <c r="K94" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:47Z</t>
+          <t>2026-09-17T17:37:54Z</t>
         </is>
       </c>
     </row>
@@ -4962,7 +4962,7 @@
       </c>
       <c r="K95" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:47Z</t>
+          <t>2026-09-17T17:37:54Z</t>
         </is>
       </c>
     </row>
@@ -5011,7 +5011,7 @@
       </c>
       <c r="K96" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:47Z</t>
+          <t>2026-09-17T17:37:54Z</t>
         </is>
       </c>
     </row>
@@ -5060,7 +5060,7 @@
       </c>
       <c r="K97" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:47Z</t>
+          <t>2026-09-17T17:37:54Z</t>
         </is>
       </c>
     </row>
@@ -5109,7 +5109,7 @@
       </c>
       <c r="K98" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:47Z</t>
+          <t>2026-09-17T17:37:54Z</t>
         </is>
       </c>
     </row>
@@ -5158,7 +5158,7 @@
       </c>
       <c r="K99" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:47Z</t>
+          <t>2026-09-17T17:37:54Z</t>
         </is>
       </c>
     </row>
@@ -5207,7 +5207,7 @@
       </c>
       <c r="K100" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:47Z</t>
+          <t>2026-09-17T17:37:54Z</t>
         </is>
       </c>
     </row>
@@ -5256,7 +5256,7 @@
       </c>
       <c r="K101" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:47Z</t>
+          <t>2026-09-17T17:37:54Z</t>
         </is>
       </c>
     </row>
@@ -5305,7 +5305,7 @@
       </c>
       <c r="K102" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:47Z</t>
+          <t>2026-09-17T17:37:54Z</t>
         </is>
       </c>
     </row>
@@ -5354,7 +5354,7 @@
       </c>
       <c r="K103" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:47Z</t>
+          <t>2026-09-17T17:37:54Z</t>
         </is>
       </c>
     </row>
@@ -5403,7 +5403,7 @@
       </c>
       <c r="K104" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:47Z</t>
+          <t>2026-09-17T17:37:54Z</t>
         </is>
       </c>
     </row>
@@ -5452,7 +5452,7 @@
       </c>
       <c r="K105" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:47Z</t>
+          <t>2026-09-17T17:37:54Z</t>
         </is>
       </c>
     </row>
@@ -5501,7 +5501,7 @@
       </c>
       <c r="K106" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:47Z</t>
+          <t>2026-09-17T17:37:54Z</t>
         </is>
       </c>
     </row>
@@ -5550,7 +5550,7 @@
       </c>
       <c r="K107" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:47Z</t>
+          <t>2026-09-17T17:37:54Z</t>
         </is>
       </c>
     </row>
@@ -5599,7 +5599,7 @@
       </c>
       <c r="K108" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:47Z</t>
+          <t>2026-09-17T17:37:54Z</t>
         </is>
       </c>
     </row>
@@ -5648,7 +5648,7 @@
       </c>
       <c r="K109" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:47Z</t>
+          <t>2026-09-17T17:37:54Z</t>
         </is>
       </c>
     </row>
@@ -5697,7 +5697,7 @@
       </c>
       <c r="K110" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:47Z</t>
+          <t>2026-09-17T17:37:54Z</t>
         </is>
       </c>
     </row>
@@ -5746,7 +5746,7 @@
       </c>
       <c r="K111" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:47Z</t>
+          <t>2026-09-17T17:37:54Z</t>
         </is>
       </c>
     </row>
@@ -5795,7 +5795,7 @@
       </c>
       <c r="K112" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:47Z</t>
+          <t>2026-09-17T17:37:54Z</t>
         </is>
       </c>
     </row>
@@ -5844,7 +5844,7 @@
       </c>
       <c r="K113" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:47Z</t>
+          <t>2026-09-17T17:37:54Z</t>
         </is>
       </c>
     </row>
@@ -5893,7 +5893,7 @@
       </c>
       <c r="K114" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:47Z</t>
+          <t>2026-09-17T17:37:54Z</t>
         </is>
       </c>
     </row>
@@ -5942,7 +5942,7 @@
       </c>
       <c r="K115" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:47Z</t>
+          <t>2026-09-17T17:37:54Z</t>
         </is>
       </c>
     </row>
@@ -5991,7 +5991,7 @@
       </c>
       <c r="K116" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:47Z</t>
+          <t>2026-09-17T17:37:54Z</t>
         </is>
       </c>
     </row>
@@ -6040,7 +6040,7 @@
       </c>
       <c r="K117" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:47Z</t>
+          <t>2026-09-17T17:37:54Z</t>
         </is>
       </c>
     </row>
@@ -6089,7 +6089,7 @@
       </c>
       <c r="K118" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:47Z</t>
+          <t>2026-09-17T17:37:54Z</t>
         </is>
       </c>
     </row>
@@ -6138,7 +6138,7 @@
       </c>
       <c r="K119" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:47Z</t>
+          <t>2026-09-17T17:37:54Z</t>
         </is>
       </c>
     </row>
@@ -6187,7 +6187,7 @@
       </c>
       <c r="K120" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:47Z</t>
+          <t>2026-09-17T17:37:54Z</t>
         </is>
       </c>
     </row>
@@ -6236,7 +6236,7 @@
       </c>
       <c r="K121" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:47Z</t>
+          <t>2026-09-17T17:37:54Z</t>
         </is>
       </c>
     </row>
@@ -6285,7 +6285,7 @@
       </c>
       <c r="K122" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:47Z</t>
+          <t>2026-09-17T17:37:54Z</t>
         </is>
       </c>
     </row>
@@ -6334,7 +6334,7 @@
       </c>
       <c r="K123" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:47Z</t>
+          <t>2026-09-17T17:37:54Z</t>
         </is>
       </c>
     </row>
@@ -6383,7 +6383,7 @@
       </c>
       <c r="K124" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:47Z</t>
+          <t>2026-09-17T17:37:54Z</t>
         </is>
       </c>
     </row>
@@ -6432,7 +6432,7 @@
       </c>
       <c r="K125" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:47Z</t>
+          <t>2026-09-17T17:37:54Z</t>
         </is>
       </c>
     </row>
@@ -6481,7 +6481,7 @@
       </c>
       <c r="K126" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:47Z</t>
+          <t>2026-09-17T17:37:54Z</t>
         </is>
       </c>
     </row>
@@ -6530,7 +6530,7 @@
       </c>
       <c r="K127" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:47Z</t>
+          <t>2026-09-17T17:37:54Z</t>
         </is>
       </c>
     </row>
@@ -6579,7 +6579,7 @@
       </c>
       <c r="K128" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:47Z</t>
+          <t>2026-09-17T17:37:54Z</t>
         </is>
       </c>
     </row>
@@ -6628,7 +6628,7 @@
       </c>
       <c r="K129" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:47Z</t>
+          <t>2026-09-17T17:37:54Z</t>
         </is>
       </c>
     </row>
@@ -6677,7 +6677,7 @@
       </c>
       <c r="K130" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:47Z</t>
+          <t>2026-09-17T17:37:54Z</t>
         </is>
       </c>
     </row>
@@ -6726,7 +6726,7 @@
       </c>
       <c r="K131" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:47Z</t>
+          <t>2026-09-17T17:37:54Z</t>
         </is>
       </c>
     </row>
@@ -6775,7 +6775,7 @@
       </c>
       <c r="K132" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:47Z</t>
+          <t>2026-09-17T17:37:54Z</t>
         </is>
       </c>
     </row>
@@ -6824,7 +6824,7 @@
       </c>
       <c r="K133" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:47Z</t>
+          <t>2026-09-17T17:37:54Z</t>
         </is>
       </c>
     </row>
@@ -6873,7 +6873,7 @@
       </c>
       <c r="K134" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:47Z</t>
+          <t>2026-09-17T17:37:54Z</t>
         </is>
       </c>
     </row>
@@ -6922,7 +6922,7 @@
       </c>
       <c r="K135" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:47Z</t>
+          <t>2026-09-17T17:37:54Z</t>
         </is>
       </c>
     </row>
@@ -6971,7 +6971,7 @@
       </c>
       <c r="K136" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:47Z</t>
+          <t>2026-09-17T17:37:54Z</t>
         </is>
       </c>
     </row>
@@ -7020,7 +7020,7 @@
       </c>
       <c r="K137" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:47Z</t>
+          <t>2026-09-17T17:37:54Z</t>
         </is>
       </c>
     </row>
@@ -7069,7 +7069,7 @@
       </c>
       <c r="K138" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:47Z</t>
+          <t>2026-09-17T17:37:54Z</t>
         </is>
       </c>
     </row>
@@ -7118,7 +7118,7 @@
       </c>
       <c r="K139" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:47Z</t>
+          <t>2026-09-17T17:37:54Z</t>
         </is>
       </c>
     </row>
@@ -7167,7 +7167,7 @@
       </c>
       <c r="K140" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:47Z</t>
+          <t>2026-09-17T17:37:54Z</t>
         </is>
       </c>
     </row>
@@ -7216,7 +7216,7 @@
       </c>
       <c r="K141" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:47Z</t>
+          <t>2026-09-17T17:37:54Z</t>
         </is>
       </c>
     </row>
@@ -7265,7 +7265,7 @@
       </c>
       <c r="K142" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:47Z</t>
+          <t>2026-09-17T17:37:54Z</t>
         </is>
       </c>
     </row>
@@ -7314,7 +7314,7 @@
       </c>
       <c r="K143" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:47Z</t>
+          <t>2026-09-17T17:37:54Z</t>
         </is>
       </c>
     </row>
@@ -7363,7 +7363,7 @@
       </c>
       <c r="K144" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:47Z</t>
+          <t>2026-09-17T17:37:54Z</t>
         </is>
       </c>
     </row>
@@ -7412,7 +7412,7 @@
       </c>
       <c r="K145" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:47Z</t>
+          <t>2026-09-17T17:37:54Z</t>
         </is>
       </c>
     </row>
@@ -7461,7 +7461,7 @@
       </c>
       <c r="K146" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:47Z</t>
+          <t>2026-09-17T17:37:54Z</t>
         </is>
       </c>
     </row>
@@ -7510,7 +7510,7 @@
       </c>
       <c r="K147" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:47Z</t>
+          <t>2026-09-17T17:37:54Z</t>
         </is>
       </c>
     </row>
@@ -7559,7 +7559,7 @@
       </c>
       <c r="K148" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:47Z</t>
+          <t>2026-09-17T17:37:54Z</t>
         </is>
       </c>
     </row>
@@ -7608,7 +7608,7 @@
       </c>
       <c r="K149" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:47Z</t>
+          <t>2026-09-17T17:37:54Z</t>
         </is>
       </c>
     </row>
@@ -7657,7 +7657,7 @@
       </c>
       <c r="K150" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:47Z</t>
+          <t>2026-09-17T17:37:54Z</t>
         </is>
       </c>
     </row>
@@ -7706,7 +7706,7 @@
       </c>
       <c r="K151" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:47Z</t>
+          <t>2026-09-17T17:37:54Z</t>
         </is>
       </c>
     </row>
@@ -7755,7 +7755,7 @@
       </c>
       <c r="K152" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:47Z</t>
+          <t>2026-09-17T17:37:54Z</t>
         </is>
       </c>
     </row>
@@ -7804,7 +7804,7 @@
       </c>
       <c r="K153" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:47Z</t>
+          <t>2026-09-17T17:37:54Z</t>
         </is>
       </c>
     </row>
@@ -7853,7 +7853,7 @@
       </c>
       <c r="K154" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:47Z</t>
+          <t>2026-09-17T17:37:54Z</t>
         </is>
       </c>
     </row>
@@ -7902,7 +7902,7 @@
       </c>
       <c r="K155" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:47Z</t>
+          <t>2026-09-17T17:37:54Z</t>
         </is>
       </c>
     </row>
@@ -7951,7 +7951,7 @@
       </c>
       <c r="K156" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:47Z</t>
+          <t>2026-09-17T17:37:54Z</t>
         </is>
       </c>
     </row>
@@ -8000,7 +8000,7 @@
       </c>
       <c r="K157" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:47Z</t>
+          <t>2026-09-17T17:37:54Z</t>
         </is>
       </c>
     </row>
@@ -8049,7 +8049,7 @@
       </c>
       <c r="K158" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:47Z</t>
+          <t>2026-09-17T17:37:54Z</t>
         </is>
       </c>
     </row>
@@ -8098,7 +8098,7 @@
       </c>
       <c r="K159" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:47Z</t>
+          <t>2026-09-17T17:37:54Z</t>
         </is>
       </c>
     </row>
@@ -8147,7 +8147,7 @@
       </c>
       <c r="K160" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:47Z</t>
+          <t>2026-09-17T17:37:54Z</t>
         </is>
       </c>
     </row>
@@ -8196,7 +8196,7 @@
       </c>
       <c r="K161" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:47Z</t>
+          <t>2026-09-17T17:37:54Z</t>
         </is>
       </c>
     </row>
@@ -8245,7 +8245,7 @@
       </c>
       <c r="K162" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:47Z</t>
+          <t>2026-09-17T17:37:54Z</t>
         </is>
       </c>
     </row>
@@ -8294,7 +8294,7 @@
       </c>
       <c r="K163" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:47Z</t>
+          <t>2026-09-17T17:37:54Z</t>
         </is>
       </c>
     </row>
@@ -8343,7 +8343,7 @@
       </c>
       <c r="K164" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:47Z</t>
+          <t>2026-09-17T17:37:54Z</t>
         </is>
       </c>
     </row>
@@ -8392,7 +8392,7 @@
       </c>
       <c r="K165" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:47Z</t>
+          <t>2026-09-17T17:37:54Z</t>
         </is>
       </c>
     </row>
@@ -8441,7 +8441,7 @@
       </c>
       <c r="K166" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:47Z</t>
+          <t>2026-09-17T17:37:54Z</t>
         </is>
       </c>
     </row>
@@ -8490,7 +8490,7 @@
       </c>
       <c r="K167" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:47Z</t>
+          <t>2026-09-17T17:37:54Z</t>
         </is>
       </c>
     </row>
@@ -8539,7 +8539,7 @@
       </c>
       <c r="K168" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:47Z</t>
+          <t>2026-09-17T17:37:54Z</t>
         </is>
       </c>
     </row>
@@ -8588,7 +8588,7 @@
       </c>
       <c r="K169" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:47Z</t>
+          <t>2026-09-17T17:37:54Z</t>
         </is>
       </c>
     </row>
@@ -8637,7 +8637,7 @@
       </c>
       <c r="K170" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:47Z</t>
+          <t>2026-09-17T17:37:54Z</t>
         </is>
       </c>
     </row>
@@ -8686,7 +8686,7 @@
       </c>
       <c r="K171" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:47Z</t>
+          <t>2026-09-17T17:37:54Z</t>
         </is>
       </c>
     </row>
@@ -8735,7 +8735,7 @@
       </c>
       <c r="K172" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:47Z</t>
+          <t>2026-09-17T17:37:54Z</t>
         </is>
       </c>
     </row>
@@ -8784,7 +8784,7 @@
       </c>
       <c r="K173" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:47Z</t>
+          <t>2026-09-17T17:37:54Z</t>
         </is>
       </c>
     </row>
@@ -8833,7 +8833,7 @@
       </c>
       <c r="K174" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:47Z</t>
+          <t>2026-09-17T17:37:54Z</t>
         </is>
       </c>
     </row>
@@ -8882,7 +8882,7 @@
       </c>
       <c r="K175" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:47Z</t>
+          <t>2026-09-17T17:37:54Z</t>
         </is>
       </c>
     </row>
@@ -8931,7 +8931,7 @@
       </c>
       <c r="K176" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:47Z</t>
+          <t>2026-09-17T17:37:54Z</t>
         </is>
       </c>
     </row>
@@ -8980,7 +8980,7 @@
       </c>
       <c r="K177" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:47Z</t>
+          <t>2026-09-17T17:37:54Z</t>
         </is>
       </c>
     </row>
@@ -9029,7 +9029,7 @@
       </c>
       <c r="K178" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:47Z</t>
+          <t>2026-09-17T17:37:54Z</t>
         </is>
       </c>
     </row>
@@ -9078,7 +9078,7 @@
       </c>
       <c r="K179" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:47Z</t>
+          <t>2026-09-17T17:37:54Z</t>
         </is>
       </c>
     </row>
@@ -9127,7 +9127,7 @@
       </c>
       <c r="K180" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:47Z</t>
+          <t>2026-09-17T17:37:54Z</t>
         </is>
       </c>
     </row>
@@ -9176,7 +9176,7 @@
       </c>
       <c r="K181" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:47Z</t>
+          <t>2026-09-17T17:37:54Z</t>
         </is>
       </c>
     </row>
@@ -9225,7 +9225,7 @@
       </c>
       <c r="K182" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:47Z</t>
+          <t>2026-09-17T17:37:54Z</t>
         </is>
       </c>
     </row>
@@ -9274,7 +9274,7 @@
       </c>
       <c r="K183" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:47Z</t>
+          <t>2026-09-17T17:37:54Z</t>
         </is>
       </c>
     </row>
@@ -9323,7 +9323,7 @@
       </c>
       <c r="K184" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:47Z</t>
+          <t>2026-09-17T17:37:54Z</t>
         </is>
       </c>
     </row>
@@ -9372,7 +9372,7 @@
       </c>
       <c r="K185" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:47Z</t>
+          <t>2026-09-17T17:37:54Z</t>
         </is>
       </c>
     </row>
@@ -9421,7 +9421,7 @@
       </c>
       <c r="K186" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:47Z</t>
+          <t>2026-09-17T17:37:54Z</t>
         </is>
       </c>
     </row>
@@ -9470,7 +9470,7 @@
       </c>
       <c r="K187" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:47Z</t>
+          <t>2026-09-17T17:37:54Z</t>
         </is>
       </c>
     </row>
@@ -9519,7 +9519,7 @@
       </c>
       <c r="K188" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:47Z</t>
+          <t>2026-09-17T17:37:54Z</t>
         </is>
       </c>
     </row>
@@ -9568,7 +9568,7 @@
       </c>
       <c r="K189" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:47Z</t>
+          <t>2026-09-17T17:37:54Z</t>
         </is>
       </c>
     </row>
@@ -9617,7 +9617,7 @@
       </c>
       <c r="K190" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:47Z</t>
+          <t>2026-09-17T17:37:54Z</t>
         </is>
       </c>
     </row>
@@ -9666,7 +9666,7 @@
       </c>
       <c r="K191" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:47Z</t>
+          <t>2026-09-17T17:37:54Z</t>
         </is>
       </c>
     </row>
@@ -9715,7 +9715,7 @@
       </c>
       <c r="K192" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:47Z</t>
+          <t>2026-09-17T17:37:54Z</t>
         </is>
       </c>
     </row>
@@ -9764,7 +9764,7 @@
       </c>
       <c r="K193" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:47Z</t>
+          <t>2026-09-17T17:37:54Z</t>
         </is>
       </c>
     </row>
@@ -9813,7 +9813,7 @@
       </c>
       <c r="K194" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:47Z</t>
+          <t>2026-09-17T17:37:54Z</t>
         </is>
       </c>
     </row>
@@ -9862,7 +9862,7 @@
       </c>
       <c r="K195" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:47Z</t>
+          <t>2026-09-17T17:37:54Z</t>
         </is>
       </c>
     </row>
@@ -9911,7 +9911,7 @@
       </c>
       <c r="K196" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:47Z</t>
+          <t>2026-09-17T17:37:54Z</t>
         </is>
       </c>
     </row>
@@ -9960,7 +9960,7 @@
       </c>
       <c r="K197" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:47Z</t>
+          <t>2026-09-17T17:37:54Z</t>
         </is>
       </c>
     </row>
@@ -10009,7 +10009,7 @@
       </c>
       <c r="K198" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:47Z</t>
+          <t>2026-09-17T17:37:54Z</t>
         </is>
       </c>
     </row>
@@ -10058,7 +10058,7 @@
       </c>
       <c r="K199" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:47Z</t>
+          <t>2026-09-17T17:37:54Z</t>
         </is>
       </c>
     </row>
@@ -10107,7 +10107,7 @@
       </c>
       <c r="K200" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:47Z</t>
+          <t>2026-09-17T17:37:54Z</t>
         </is>
       </c>
     </row>
@@ -10156,7 +10156,7 @@
       </c>
       <c r="K201" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:47Z</t>
+          <t>2026-09-17T17:37:54Z</t>
         </is>
       </c>
     </row>
@@ -10205,7 +10205,7 @@
       </c>
       <c r="K202" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:47Z</t>
+          <t>2026-09-17T17:37:54Z</t>
         </is>
       </c>
     </row>
@@ -10254,7 +10254,7 @@
       </c>
       <c r="K203" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:47Z</t>
+          <t>2026-09-17T17:37:54Z</t>
         </is>
       </c>
     </row>
@@ -10303,7 +10303,7 @@
       </c>
       <c r="K204" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:47Z</t>
+          <t>2026-09-17T17:37:54Z</t>
         </is>
       </c>
     </row>
@@ -10352,7 +10352,7 @@
       </c>
       <c r="K205" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:47Z</t>
+          <t>2026-09-17T17:37:54Z</t>
         </is>
       </c>
     </row>
@@ -10401,7 +10401,7 @@
       </c>
       <c r="K206" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:47Z</t>
+          <t>2026-09-17T17:37:54Z</t>
         </is>
       </c>
     </row>
@@ -10450,7 +10450,7 @@
       </c>
       <c r="K207" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:47Z</t>
+          <t>2026-09-17T17:37:54Z</t>
         </is>
       </c>
     </row>
@@ -10499,7 +10499,7 @@
       </c>
       <c r="K208" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:47Z</t>
+          <t>2026-09-17T17:37:54Z</t>
         </is>
       </c>
     </row>
@@ -10548,7 +10548,7 @@
       </c>
       <c r="K209" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:47Z</t>
+          <t>2026-09-17T17:37:54Z</t>
         </is>
       </c>
     </row>
@@ -10597,7 +10597,7 @@
       </c>
       <c r="K210" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:47Z</t>
+          <t>2026-09-17T17:37:54Z</t>
         </is>
       </c>
     </row>
@@ -10646,7 +10646,7 @@
       </c>
       <c r="K211" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:47Z</t>
+          <t>2026-09-17T17:37:54Z</t>
         </is>
       </c>
     </row>
@@ -10695,7 +10695,7 @@
       </c>
       <c r="K212" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:47Z</t>
+          <t>2026-09-17T17:37:54Z</t>
         </is>
       </c>
     </row>
@@ -10744,7 +10744,7 @@
       </c>
       <c r="K213" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:47Z</t>
+          <t>2026-09-17T17:37:54Z</t>
         </is>
       </c>
     </row>
@@ -10793,7 +10793,7 @@
       </c>
       <c r="K214" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:47Z</t>
+          <t>2026-09-17T17:37:54Z</t>
         </is>
       </c>
     </row>
@@ -10842,7 +10842,7 @@
       </c>
       <c r="K215" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:47Z</t>
+          <t>2026-09-17T17:37:54Z</t>
         </is>
       </c>
     </row>
@@ -10891,7 +10891,7 @@
       </c>
       <c r="K216" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:47Z</t>
+          <t>2026-09-17T17:37:54Z</t>
         </is>
       </c>
     </row>
@@ -10940,7 +10940,7 @@
       </c>
       <c r="K217" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:47Z</t>
+          <t>2026-09-17T17:37:54Z</t>
         </is>
       </c>
     </row>
@@ -10989,7 +10989,7 @@
       </c>
       <c r="K218" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:47Z</t>
+          <t>2026-09-17T17:37:54Z</t>
         </is>
       </c>
     </row>
@@ -11038,7 +11038,7 @@
       </c>
       <c r="K219" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:47Z</t>
+          <t>2026-09-17T17:37:54Z</t>
         </is>
       </c>
     </row>
@@ -11087,7 +11087,7 @@
       </c>
       <c r="K220" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:47Z</t>
+          <t>2026-09-17T17:37:54Z</t>
         </is>
       </c>
     </row>
@@ -11136,7 +11136,7 @@
       </c>
       <c r="K221" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:47Z</t>
+          <t>2026-09-17T17:37:54Z</t>
         </is>
       </c>
     </row>
@@ -11185,7 +11185,7 @@
       </c>
       <c r="K222" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:47Z</t>
+          <t>2026-09-17T17:37:54Z</t>
         </is>
       </c>
     </row>
@@ -11234,7 +11234,7 @@
       </c>
       <c r="K223" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:47Z</t>
+          <t>2026-09-17T17:37:54Z</t>
         </is>
       </c>
     </row>
@@ -11283,7 +11283,7 @@
       </c>
       <c r="K224" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:47Z</t>
+          <t>2026-09-17T17:37:54Z</t>
         </is>
       </c>
     </row>
@@ -11332,7 +11332,7 @@
       </c>
       <c r="K225" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:47Z</t>
+          <t>2026-09-17T17:37:54Z</t>
         </is>
       </c>
     </row>
@@ -11381,7 +11381,7 @@
       </c>
       <c r="K226" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:47Z</t>
+          <t>2026-09-17T17:37:54Z</t>
         </is>
       </c>
     </row>
@@ -11430,7 +11430,7 @@
       </c>
       <c r="K227" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:47Z</t>
+          <t>2026-09-17T17:37:54Z</t>
         </is>
       </c>
     </row>
@@ -11479,7 +11479,7 @@
       </c>
       <c r="K228" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:47Z</t>
+          <t>2026-09-17T17:37:54Z</t>
         </is>
       </c>
     </row>
@@ -11528,7 +11528,7 @@
       </c>
       <c r="K229" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:47Z</t>
+          <t>2026-09-17T17:37:54Z</t>
         </is>
       </c>
     </row>
@@ -11577,7 +11577,7 @@
       </c>
       <c r="K230" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:47Z</t>
+          <t>2026-09-17T17:37:54Z</t>
         </is>
       </c>
     </row>
@@ -11626,7 +11626,7 @@
       </c>
       <c r="K231" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:47Z</t>
+          <t>2026-09-17T17:37:54Z</t>
         </is>
       </c>
     </row>
@@ -11758,7 +11758,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:47Z</t>
+          <t>2026-09-17T17:37:54Z</t>
         </is>
       </c>
     </row>
@@ -11804,7 +11804,7 @@
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>{"date": "2026-08-01", "year": 2026, "month": 8, "month_name": "Agosto", "index_value": 637409769724325.1, "monthly_variation_pct": 8.9, "unit": "Índice base diciembre 2007=100 y variación mensual %", "frequency": "monthly", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/precios_consumidor/4_5_7_2.xls", "fetched_at": "2026-09-16T23:07:47Z"}</t>
+          <t>{"date": "2026-08-01", "year": 2026, "month": 8, "month_name": "Agosto", "index_value": 637409769724325.1, "monthly_variation_pct": 8.9, "unit": "Índice base diciembre 2007=100 y variación mensual %", "frequency": "monthly", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/precios_consumidor/4_5_7_2.xls", "fetched_at": "2026-09-17T17:37:54Z"}</t>
         </is>
       </c>
     </row>

--- a/assets/data/bcv/excel/ove_bcv_inpc_nacional_mensual.xlsx
+++ b/assets/data/bcv/excel/ove_bcv_inpc_nacional_mensual.xlsx
@@ -650,7 +650,7 @@
       </c>
       <c r="K7" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:54Z</t>
+          <t>2026-09-17T22:58:09Z</t>
         </is>
       </c>
     </row>
@@ -699,7 +699,7 @@
       </c>
       <c r="K8" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:54Z</t>
+          <t>2026-09-17T22:58:09Z</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="K9" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:54Z</t>
+          <t>2026-09-17T22:58:09Z</t>
         </is>
       </c>
     </row>
@@ -797,7 +797,7 @@
       </c>
       <c r="K10" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:54Z</t>
+          <t>2026-09-17T22:58:09Z</t>
         </is>
       </c>
     </row>
@@ -846,7 +846,7 @@
       </c>
       <c r="K11" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:54Z</t>
+          <t>2026-09-17T22:58:09Z</t>
         </is>
       </c>
     </row>
@@ -895,7 +895,7 @@
       </c>
       <c r="K12" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:54Z</t>
+          <t>2026-09-17T22:58:09Z</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="K13" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:54Z</t>
+          <t>2026-09-17T22:58:09Z</t>
         </is>
       </c>
     </row>
@@ -993,7 +993,7 @@
       </c>
       <c r="K14" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:54Z</t>
+          <t>2026-09-17T22:58:09Z</t>
         </is>
       </c>
     </row>
@@ -1042,7 +1042,7 @@
       </c>
       <c r="K15" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:54Z</t>
+          <t>2026-09-17T22:58:09Z</t>
         </is>
       </c>
     </row>
@@ -1091,7 +1091,7 @@
       </c>
       <c r="K16" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:54Z</t>
+          <t>2026-09-17T22:58:09Z</t>
         </is>
       </c>
     </row>
@@ -1140,7 +1140,7 @@
       </c>
       <c r="K17" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:54Z</t>
+          <t>2026-09-17T22:58:09Z</t>
         </is>
       </c>
     </row>
@@ -1189,7 +1189,7 @@
       </c>
       <c r="K18" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:54Z</t>
+          <t>2026-09-17T22:58:09Z</t>
         </is>
       </c>
     </row>
@@ -1238,7 +1238,7 @@
       </c>
       <c r="K19" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:54Z</t>
+          <t>2026-09-17T22:58:09Z</t>
         </is>
       </c>
     </row>
@@ -1287,7 +1287,7 @@
       </c>
       <c r="K20" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:54Z</t>
+          <t>2026-09-17T22:58:09Z</t>
         </is>
       </c>
     </row>
@@ -1336,7 +1336,7 @@
       </c>
       <c r="K21" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:54Z</t>
+          <t>2026-09-17T22:58:09Z</t>
         </is>
       </c>
     </row>
@@ -1385,7 +1385,7 @@
       </c>
       <c r="K22" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:54Z</t>
+          <t>2026-09-17T22:58:09Z</t>
         </is>
       </c>
     </row>
@@ -1434,7 +1434,7 @@
       </c>
       <c r="K23" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:54Z</t>
+          <t>2026-09-17T22:58:09Z</t>
         </is>
       </c>
     </row>
@@ -1483,7 +1483,7 @@
       </c>
       <c r="K24" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:54Z</t>
+          <t>2026-09-17T22:58:09Z</t>
         </is>
       </c>
     </row>
@@ -1532,7 +1532,7 @@
       </c>
       <c r="K25" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:54Z</t>
+          <t>2026-09-17T22:58:09Z</t>
         </is>
       </c>
     </row>
@@ -1581,7 +1581,7 @@
       </c>
       <c r="K26" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:54Z</t>
+          <t>2026-09-17T22:58:09Z</t>
         </is>
       </c>
     </row>
@@ -1630,7 +1630,7 @@
       </c>
       <c r="K27" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:54Z</t>
+          <t>2026-09-17T22:58:09Z</t>
         </is>
       </c>
     </row>
@@ -1679,7 +1679,7 @@
       </c>
       <c r="K28" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:54Z</t>
+          <t>2026-09-17T22:58:09Z</t>
         </is>
       </c>
     </row>
@@ -1728,7 +1728,7 @@
       </c>
       <c r="K29" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:54Z</t>
+          <t>2026-09-17T22:58:09Z</t>
         </is>
       </c>
     </row>
@@ -1777,7 +1777,7 @@
       </c>
       <c r="K30" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:54Z</t>
+          <t>2026-09-17T22:58:09Z</t>
         </is>
       </c>
     </row>
@@ -1826,7 +1826,7 @@
       </c>
       <c r="K31" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:54Z</t>
+          <t>2026-09-17T22:58:09Z</t>
         </is>
       </c>
     </row>
@@ -1875,7 +1875,7 @@
       </c>
       <c r="K32" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:54Z</t>
+          <t>2026-09-17T22:58:09Z</t>
         </is>
       </c>
     </row>
@@ -1924,7 +1924,7 @@
       </c>
       <c r="K33" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:54Z</t>
+          <t>2026-09-17T22:58:09Z</t>
         </is>
       </c>
     </row>
@@ -1973,7 +1973,7 @@
       </c>
       <c r="K34" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:54Z</t>
+          <t>2026-09-17T22:58:09Z</t>
         </is>
       </c>
     </row>
@@ -2022,7 +2022,7 @@
       </c>
       <c r="K35" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:54Z</t>
+          <t>2026-09-17T22:58:09Z</t>
         </is>
       </c>
     </row>
@@ -2071,7 +2071,7 @@
       </c>
       <c r="K36" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:54Z</t>
+          <t>2026-09-17T22:58:09Z</t>
         </is>
       </c>
     </row>
@@ -2120,7 +2120,7 @@
       </c>
       <c r="K37" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:54Z</t>
+          <t>2026-09-17T22:58:09Z</t>
         </is>
       </c>
     </row>
@@ -2169,7 +2169,7 @@
       </c>
       <c r="K38" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:54Z</t>
+          <t>2026-09-17T22:58:09Z</t>
         </is>
       </c>
     </row>
@@ -2218,7 +2218,7 @@
       </c>
       <c r="K39" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:54Z</t>
+          <t>2026-09-17T22:58:09Z</t>
         </is>
       </c>
     </row>
@@ -2267,7 +2267,7 @@
       </c>
       <c r="K40" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:54Z</t>
+          <t>2026-09-17T22:58:09Z</t>
         </is>
       </c>
     </row>
@@ -2316,7 +2316,7 @@
       </c>
       <c r="K41" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:54Z</t>
+          <t>2026-09-17T22:58:09Z</t>
         </is>
       </c>
     </row>
@@ -2365,7 +2365,7 @@
       </c>
       <c r="K42" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:54Z</t>
+          <t>2026-09-17T22:58:09Z</t>
         </is>
       </c>
     </row>
@@ -2414,7 +2414,7 @@
       </c>
       <c r="K43" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:54Z</t>
+          <t>2026-09-17T22:58:09Z</t>
         </is>
       </c>
     </row>
@@ -2463,7 +2463,7 @@
       </c>
       <c r="K44" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:54Z</t>
+          <t>2026-09-17T22:58:09Z</t>
         </is>
       </c>
     </row>
@@ -2512,7 +2512,7 @@
       </c>
       <c r="K45" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:54Z</t>
+          <t>2026-09-17T22:58:09Z</t>
         </is>
       </c>
     </row>
@@ -2561,7 +2561,7 @@
       </c>
       <c r="K46" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:54Z</t>
+          <t>2026-09-17T22:58:09Z</t>
         </is>
       </c>
     </row>
@@ -2610,7 +2610,7 @@
       </c>
       <c r="K47" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:54Z</t>
+          <t>2026-09-17T22:58:09Z</t>
         </is>
       </c>
     </row>
@@ -2659,7 +2659,7 @@
       </c>
       <c r="K48" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:54Z</t>
+          <t>2026-09-17T22:58:09Z</t>
         </is>
       </c>
     </row>
@@ -2708,7 +2708,7 @@
       </c>
       <c r="K49" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:54Z</t>
+          <t>2026-09-17T22:58:09Z</t>
         </is>
       </c>
     </row>
@@ -2757,7 +2757,7 @@
       </c>
       <c r="K50" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:54Z</t>
+          <t>2026-09-17T22:58:09Z</t>
         </is>
       </c>
     </row>
@@ -2806,7 +2806,7 @@
       </c>
       <c r="K51" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:54Z</t>
+          <t>2026-09-17T22:58:09Z</t>
         </is>
       </c>
     </row>
@@ -2855,7 +2855,7 @@
       </c>
       <c r="K52" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:54Z</t>
+          <t>2026-09-17T22:58:09Z</t>
         </is>
       </c>
     </row>
@@ -2904,7 +2904,7 @@
       </c>
       <c r="K53" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:54Z</t>
+          <t>2026-09-17T22:58:09Z</t>
         </is>
       </c>
     </row>
@@ -2953,7 +2953,7 @@
       </c>
       <c r="K54" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:54Z</t>
+          <t>2026-09-17T22:58:09Z</t>
         </is>
       </c>
     </row>
@@ -3002,7 +3002,7 @@
       </c>
       <c r="K55" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:54Z</t>
+          <t>2026-09-17T22:58:09Z</t>
         </is>
       </c>
     </row>
@@ -3051,7 +3051,7 @@
       </c>
       <c r="K56" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:54Z</t>
+          <t>2026-09-17T22:58:09Z</t>
         </is>
       </c>
     </row>
@@ -3100,7 +3100,7 @@
       </c>
       <c r="K57" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:54Z</t>
+          <t>2026-09-17T22:58:09Z</t>
         </is>
       </c>
     </row>
@@ -3149,7 +3149,7 @@
       </c>
       <c r="K58" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:54Z</t>
+          <t>2026-09-17T22:58:09Z</t>
         </is>
       </c>
     </row>
@@ -3198,7 +3198,7 @@
       </c>
       <c r="K59" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:54Z</t>
+          <t>2026-09-17T22:58:09Z</t>
         </is>
       </c>
     </row>
@@ -3247,7 +3247,7 @@
       </c>
       <c r="K60" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:54Z</t>
+          <t>2026-09-17T22:58:09Z</t>
         </is>
       </c>
     </row>
@@ -3296,7 +3296,7 @@
       </c>
       <c r="K61" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:54Z</t>
+          <t>2026-09-17T22:58:09Z</t>
         </is>
       </c>
     </row>
@@ -3345,7 +3345,7 @@
       </c>
       <c r="K62" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:54Z</t>
+          <t>2026-09-17T22:58:09Z</t>
         </is>
       </c>
     </row>
@@ -3394,7 +3394,7 @@
       </c>
       <c r="K63" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:54Z</t>
+          <t>2026-09-17T22:58:09Z</t>
         </is>
       </c>
     </row>
@@ -3443,7 +3443,7 @@
       </c>
       <c r="K64" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:54Z</t>
+          <t>2026-09-17T22:58:09Z</t>
         </is>
       </c>
     </row>
@@ -3492,7 +3492,7 @@
       </c>
       <c r="K65" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:54Z</t>
+          <t>2026-09-17T22:58:09Z</t>
         </is>
       </c>
     </row>
@@ -3541,7 +3541,7 @@
       </c>
       <c r="K66" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:54Z</t>
+          <t>2026-09-17T22:58:09Z</t>
         </is>
       </c>
     </row>
@@ -3590,7 +3590,7 @@
       </c>
       <c r="K67" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:54Z</t>
+          <t>2026-09-17T22:58:09Z</t>
         </is>
       </c>
     </row>
@@ -3639,7 +3639,7 @@
       </c>
       <c r="K68" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:54Z</t>
+          <t>2026-09-17T22:58:09Z</t>
         </is>
       </c>
     </row>
@@ -3688,7 +3688,7 @@
       </c>
       <c r="K69" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:54Z</t>
+          <t>2026-09-17T22:58:09Z</t>
         </is>
       </c>
     </row>
@@ -3737,7 +3737,7 @@
       </c>
       <c r="K70" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:54Z</t>
+          <t>2026-09-17T22:58:09Z</t>
         </is>
       </c>
     </row>
@@ -3786,7 +3786,7 @@
       </c>
       <c r="K71" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:54Z</t>
+          <t>2026-09-17T22:58:09Z</t>
         </is>
       </c>
     </row>
@@ -3835,7 +3835,7 @@
       </c>
       <c r="K72" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:54Z</t>
+          <t>2026-09-17T22:58:09Z</t>
         </is>
       </c>
     </row>
@@ -3884,7 +3884,7 @@
       </c>
       <c r="K73" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:54Z</t>
+          <t>2026-09-17T22:58:09Z</t>
         </is>
       </c>
     </row>
@@ -3933,7 +3933,7 @@
       </c>
       <c r="K74" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:54Z</t>
+          <t>2026-09-17T22:58:09Z</t>
         </is>
       </c>
     </row>
@@ -3982,7 +3982,7 @@
       </c>
       <c r="K75" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:54Z</t>
+          <t>2026-09-17T22:58:09Z</t>
         </is>
       </c>
     </row>
@@ -4031,7 +4031,7 @@
       </c>
       <c r="K76" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:54Z</t>
+          <t>2026-09-17T22:58:09Z</t>
         </is>
       </c>
     </row>
@@ -4080,7 +4080,7 @@
       </c>
       <c r="K77" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:54Z</t>
+          <t>2026-09-17T22:58:09Z</t>
         </is>
       </c>
     </row>
@@ -4129,7 +4129,7 @@
       </c>
       <c r="K78" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:54Z</t>
+          <t>2026-09-17T22:58:09Z</t>
         </is>
       </c>
     </row>
@@ -4178,7 +4178,7 @@
       </c>
       <c r="K79" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:54Z</t>
+          <t>2026-09-17T22:58:09Z</t>
         </is>
       </c>
     </row>
@@ -4227,7 +4227,7 @@
       </c>
       <c r="K80" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:54Z</t>
+          <t>2026-09-17T22:58:09Z</t>
         </is>
       </c>
     </row>
@@ -4276,7 +4276,7 @@
       </c>
       <c r="K81" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:54Z</t>
+          <t>2026-09-17T22:58:09Z</t>
         </is>
       </c>
     </row>
@@ -4325,7 +4325,7 @@
       </c>
       <c r="K82" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:54Z</t>
+          <t>2026-09-17T22:58:09Z</t>
         </is>
       </c>
     </row>
@@ -4374,7 +4374,7 @@
       </c>
       <c r="K83" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:54Z</t>
+          <t>2026-09-17T22:58:09Z</t>
         </is>
       </c>
     </row>
@@ -4423,7 +4423,7 @@
       </c>
       <c r="K84" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:54Z</t>
+          <t>2026-09-17T22:58:09Z</t>
         </is>
       </c>
     </row>
@@ -4472,7 +4472,7 @@
       </c>
       <c r="K85" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:54Z</t>
+          <t>2026-09-17T22:58:09Z</t>
         </is>
       </c>
     </row>
@@ -4521,7 +4521,7 @@
       </c>
       <c r="K86" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:54Z</t>
+          <t>2026-09-17T22:58:09Z</t>
         </is>
       </c>
     </row>
@@ -4570,7 +4570,7 @@
       </c>
       <c r="K87" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:54Z</t>
+          <t>2026-09-17T22:58:09Z</t>
         </is>
       </c>
     </row>
@@ -4619,7 +4619,7 @@
       </c>
       <c r="K88" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:54Z</t>
+          <t>2026-09-17T22:58:09Z</t>
         </is>
       </c>
     </row>
@@ -4668,7 +4668,7 @@
       </c>
       <c r="K89" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:54Z</t>
+          <t>2026-09-17T22:58:09Z</t>
         </is>
       </c>
     </row>
@@ -4717,7 +4717,7 @@
       </c>
       <c r="K90" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:54Z</t>
+          <t>2026-09-17T22:58:09Z</t>
         </is>
       </c>
     </row>
@@ -4766,7 +4766,7 @@
       </c>
       <c r="K91" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:54Z</t>
+          <t>2026-09-17T22:58:09Z</t>
         </is>
       </c>
     </row>
@@ -4815,7 +4815,7 @@
       </c>
       <c r="K92" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:54Z</t>
+          <t>2026-09-17T22:58:09Z</t>
         </is>
       </c>
     </row>
@@ -4864,7 +4864,7 @@
       </c>
       <c r="K93" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:54Z</t>
+          <t>2026-09-17T22:58:09Z</t>
         </is>
       </c>
     </row>
@@ -4913,7 +4913,7 @@
       </c>
       <c r="K94" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:54Z</t>
+          <t>2026-09-17T22:58:09Z</t>
         </is>
       </c>
     </row>
@@ -4962,7 +4962,7 @@
       </c>
       <c r="K95" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:54Z</t>
+          <t>2026-09-17T22:58:09Z</t>
         </is>
       </c>
     </row>
@@ -5011,7 +5011,7 @@
       </c>
       <c r="K96" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:54Z</t>
+          <t>2026-09-17T22:58:09Z</t>
         </is>
       </c>
     </row>
@@ -5060,7 +5060,7 @@
       </c>
       <c r="K97" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:54Z</t>
+          <t>2026-09-17T22:58:09Z</t>
         </is>
       </c>
     </row>
@@ -5109,7 +5109,7 @@
       </c>
       <c r="K98" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:54Z</t>
+          <t>2026-09-17T22:58:09Z</t>
         </is>
       </c>
     </row>
@@ -5158,7 +5158,7 @@
       </c>
       <c r="K99" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:54Z</t>
+          <t>2026-09-17T22:58:09Z</t>
         </is>
       </c>
     </row>
@@ -5207,7 +5207,7 @@
       </c>
       <c r="K100" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:54Z</t>
+          <t>2026-09-17T22:58:09Z</t>
         </is>
       </c>
     </row>
@@ -5256,7 +5256,7 @@
       </c>
       <c r="K101" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:54Z</t>
+          <t>2026-09-17T22:58:09Z</t>
         </is>
       </c>
     </row>
@@ -5305,7 +5305,7 @@
       </c>
       <c r="K102" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:54Z</t>
+          <t>2026-09-17T22:58:09Z</t>
         </is>
       </c>
     </row>
@@ -5354,7 +5354,7 @@
       </c>
       <c r="K103" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:54Z</t>
+          <t>2026-09-17T22:58:09Z</t>
         </is>
       </c>
     </row>
@@ -5403,7 +5403,7 @@
       </c>
       <c r="K104" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:54Z</t>
+          <t>2026-09-17T22:58:09Z</t>
         </is>
       </c>
     </row>
@@ -5452,7 +5452,7 @@
       </c>
       <c r="K105" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:54Z</t>
+          <t>2026-09-17T22:58:09Z</t>
         </is>
       </c>
     </row>
@@ -5501,7 +5501,7 @@
       </c>
       <c r="K106" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:54Z</t>
+          <t>2026-09-17T22:58:09Z</t>
         </is>
       </c>
     </row>
@@ -5550,7 +5550,7 @@
       </c>
       <c r="K107" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:54Z</t>
+          <t>2026-09-17T22:58:09Z</t>
         </is>
       </c>
     </row>
@@ -5599,7 +5599,7 @@
       </c>
       <c r="K108" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:54Z</t>
+          <t>2026-09-17T22:58:09Z</t>
         </is>
       </c>
     </row>
@@ -5648,7 +5648,7 @@
       </c>
       <c r="K109" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:54Z</t>
+          <t>2026-09-17T22:58:09Z</t>
         </is>
       </c>
     </row>
@@ -5697,7 +5697,7 @@
       </c>
       <c r="K110" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:54Z</t>
+          <t>2026-09-17T22:58:09Z</t>
         </is>
       </c>
     </row>
@@ -5746,7 +5746,7 @@
       </c>
       <c r="K111" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:54Z</t>
+          <t>2026-09-17T22:58:09Z</t>
         </is>
       </c>
     </row>
@@ -5795,7 +5795,7 @@
       </c>
       <c r="K112" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:54Z</t>
+          <t>2026-09-17T22:58:09Z</t>
         </is>
       </c>
     </row>
@@ -5844,7 +5844,7 @@
       </c>
       <c r="K113" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:54Z</t>
+          <t>2026-09-17T22:58:09Z</t>
         </is>
       </c>
     </row>
@@ -5893,7 +5893,7 @@
       </c>
       <c r="K114" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:54Z</t>
+          <t>2026-09-17T22:58:09Z</t>
         </is>
       </c>
     </row>
@@ -5942,7 +5942,7 @@
       </c>
       <c r="K115" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:54Z</t>
+          <t>2026-09-17T22:58:09Z</t>
         </is>
       </c>
     </row>
@@ -5991,7 +5991,7 @@
       </c>
       <c r="K116" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:54Z</t>
+          <t>2026-09-17T22:58:09Z</t>
         </is>
       </c>
     </row>
@@ -6040,7 +6040,7 @@
       </c>
       <c r="K117" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:54Z</t>
+          <t>2026-09-17T22:58:09Z</t>
         </is>
       </c>
     </row>
@@ -6089,7 +6089,7 @@
       </c>
       <c r="K118" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:54Z</t>
+          <t>2026-09-17T22:58:09Z</t>
         </is>
       </c>
     </row>
@@ -6138,7 +6138,7 @@
       </c>
       <c r="K119" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:54Z</t>
+          <t>2026-09-17T22:58:09Z</t>
         </is>
       </c>
     </row>
@@ -6187,7 +6187,7 @@
       </c>
       <c r="K120" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:54Z</t>
+          <t>2026-09-17T22:58:09Z</t>
         </is>
       </c>
     </row>
@@ -6236,7 +6236,7 @@
       </c>
       <c r="K121" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:54Z</t>
+          <t>2026-09-17T22:58:09Z</t>
         </is>
       </c>
     </row>
@@ -6285,7 +6285,7 @@
       </c>
       <c r="K122" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:54Z</t>
+          <t>2026-09-17T22:58:09Z</t>
         </is>
       </c>
     </row>
@@ -6334,7 +6334,7 @@
       </c>
       <c r="K123" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:54Z</t>
+          <t>2026-09-17T22:58:09Z</t>
         </is>
       </c>
     </row>
@@ -6383,7 +6383,7 @@
       </c>
       <c r="K124" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:54Z</t>
+          <t>2026-09-17T22:58:09Z</t>
         </is>
       </c>
     </row>
@@ -6432,7 +6432,7 @@
       </c>
       <c r="K125" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:54Z</t>
+          <t>2026-09-17T22:58:09Z</t>
         </is>
       </c>
     </row>
@@ -6481,7 +6481,7 @@
       </c>
       <c r="K126" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:54Z</t>
+          <t>2026-09-17T22:58:09Z</t>
         </is>
       </c>
     </row>
@@ -6530,7 +6530,7 @@
       </c>
       <c r="K127" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:54Z</t>
+          <t>2026-09-17T22:58:09Z</t>
         </is>
       </c>
     </row>
@@ -6579,7 +6579,7 @@
       </c>
       <c r="K128" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:54Z</t>
+          <t>2026-09-17T22:58:09Z</t>
         </is>
       </c>
     </row>
@@ -6628,7 +6628,7 @@
       </c>
       <c r="K129" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:54Z</t>
+          <t>2026-09-17T22:58:09Z</t>
         </is>
       </c>
     </row>
@@ -6677,7 +6677,7 @@
       </c>
       <c r="K130" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:54Z</t>
+          <t>2026-09-17T22:58:09Z</t>
         </is>
       </c>
     </row>
@@ -6726,7 +6726,7 @@
       </c>
       <c r="K131" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:54Z</t>
+          <t>2026-09-17T22:58:09Z</t>
         </is>
       </c>
     </row>
@@ -6775,7 +6775,7 @@
       </c>
       <c r="K132" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:54Z</t>
+          <t>2026-09-17T22:58:09Z</t>
         </is>
       </c>
     </row>
@@ -6824,7 +6824,7 @@
       </c>
       <c r="K133" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:54Z</t>
+          <t>2026-09-17T22:58:09Z</t>
         </is>
       </c>
     </row>
@@ -6873,7 +6873,7 @@
       </c>
       <c r="K134" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:54Z</t>
+          <t>2026-09-17T22:58:09Z</t>
         </is>
       </c>
     </row>
@@ -6922,7 +6922,7 @@
       </c>
       <c r="K135" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:54Z</t>
+          <t>2026-09-17T22:58:09Z</t>
         </is>
       </c>
     </row>
@@ -6971,7 +6971,7 @@
       </c>
       <c r="K136" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:54Z</t>
+          <t>2026-09-17T22:58:09Z</t>
         </is>
       </c>
     </row>
@@ -7020,7 +7020,7 @@
       </c>
       <c r="K137" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:54Z</t>
+          <t>2026-09-17T22:58:09Z</t>
         </is>
       </c>
     </row>
@@ -7069,7 +7069,7 @@
       </c>
       <c r="K138" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:54Z</t>
+          <t>2026-09-17T22:58:09Z</t>
         </is>
       </c>
     </row>
@@ -7118,7 +7118,7 @@
       </c>
       <c r="K139" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:54Z</t>
+          <t>2026-09-17T22:58:09Z</t>
         </is>
       </c>
     </row>
@@ -7167,7 +7167,7 @@
       </c>
       <c r="K140" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:54Z</t>
+          <t>2026-09-17T22:58:09Z</t>
         </is>
       </c>
     </row>
@@ -7216,7 +7216,7 @@
       </c>
       <c r="K141" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:54Z</t>
+          <t>2026-09-17T22:58:09Z</t>
         </is>
       </c>
     </row>
@@ -7265,7 +7265,7 @@
       </c>
       <c r="K142" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:54Z</t>
+          <t>2026-09-17T22:58:09Z</t>
         </is>
       </c>
     </row>
@@ -7314,7 +7314,7 @@
       </c>
       <c r="K143" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:54Z</t>
+          <t>2026-09-17T22:58:09Z</t>
         </is>
       </c>
     </row>
@@ -7363,7 +7363,7 @@
       </c>
       <c r="K144" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:54Z</t>
+          <t>2026-09-17T22:58:09Z</t>
         </is>
       </c>
     </row>
@@ -7412,7 +7412,7 @@
       </c>
       <c r="K145" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:54Z</t>
+          <t>2026-09-17T22:58:09Z</t>
         </is>
       </c>
     </row>
@@ -7461,7 +7461,7 @@
       </c>
       <c r="K146" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:54Z</t>
+          <t>2026-09-17T22:58:09Z</t>
         </is>
       </c>
     </row>
@@ -7510,7 +7510,7 @@
       </c>
       <c r="K147" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:54Z</t>
+          <t>2026-09-17T22:58:09Z</t>
         </is>
       </c>
     </row>
@@ -7559,7 +7559,7 @@
       </c>
       <c r="K148" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:54Z</t>
+          <t>2026-09-17T22:58:09Z</t>
         </is>
       </c>
     </row>
@@ -7608,7 +7608,7 @@
       </c>
       <c r="K149" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:54Z</t>
+          <t>2026-09-17T22:58:09Z</t>
         </is>
       </c>
     </row>
@@ -7657,7 +7657,7 @@
       </c>
       <c r="K150" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:54Z</t>
+          <t>2026-09-17T22:58:09Z</t>
         </is>
       </c>
     </row>
@@ -7706,7 +7706,7 @@
       </c>
       <c r="K151" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:54Z</t>
+          <t>2026-09-17T22:58:09Z</t>
         </is>
       </c>
     </row>
@@ -7755,7 +7755,7 @@
       </c>
       <c r="K152" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:54Z</t>
+          <t>2026-09-17T22:58:09Z</t>
         </is>
       </c>
     </row>
@@ -7804,7 +7804,7 @@
       </c>
       <c r="K153" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:54Z</t>
+          <t>2026-09-17T22:58:09Z</t>
         </is>
       </c>
     </row>
@@ -7853,7 +7853,7 @@
       </c>
       <c r="K154" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:54Z</t>
+          <t>2026-09-17T22:58:09Z</t>
         </is>
       </c>
     </row>
@@ -7902,7 +7902,7 @@
       </c>
       <c r="K155" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:54Z</t>
+          <t>2026-09-17T22:58:09Z</t>
         </is>
       </c>
     </row>
@@ -7951,7 +7951,7 @@
       </c>
       <c r="K156" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:54Z</t>
+          <t>2026-09-17T22:58:09Z</t>
         </is>
       </c>
     </row>
@@ -8000,7 +8000,7 @@
       </c>
       <c r="K157" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:54Z</t>
+          <t>2026-09-17T22:58:09Z</t>
         </is>
       </c>
     </row>
@@ -8049,7 +8049,7 @@
       </c>
       <c r="K158" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:54Z</t>
+          <t>2026-09-17T22:58:09Z</t>
         </is>
       </c>
     </row>
@@ -8098,7 +8098,7 @@
       </c>
       <c r="K159" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:54Z</t>
+          <t>2026-09-17T22:58:09Z</t>
         </is>
       </c>
     </row>
@@ -8147,7 +8147,7 @@
       </c>
       <c r="K160" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:54Z</t>
+          <t>2026-09-17T22:58:09Z</t>
         </is>
       </c>
     </row>
@@ -8196,7 +8196,7 @@
       </c>
       <c r="K161" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:54Z</t>
+          <t>2026-09-17T22:58:09Z</t>
         </is>
       </c>
     </row>
@@ -8245,7 +8245,7 @@
       </c>
       <c r="K162" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:54Z</t>
+          <t>2026-09-17T22:58:09Z</t>
         </is>
       </c>
     </row>
@@ -8294,7 +8294,7 @@
       </c>
       <c r="K163" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:54Z</t>
+          <t>2026-09-17T22:58:09Z</t>
         </is>
       </c>
     </row>
@@ -8343,7 +8343,7 @@
       </c>
       <c r="K164" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:54Z</t>
+          <t>2026-09-17T22:58:09Z</t>
         </is>
       </c>
     </row>
@@ -8392,7 +8392,7 @@
       </c>
       <c r="K165" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:54Z</t>
+          <t>2026-09-17T22:58:09Z</t>
         </is>
       </c>
     </row>
@@ -8441,7 +8441,7 @@
       </c>
       <c r="K166" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:54Z</t>
+          <t>2026-09-17T22:58:09Z</t>
         </is>
       </c>
     </row>
@@ -8490,7 +8490,7 @@
       </c>
       <c r="K167" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:54Z</t>
+          <t>2026-09-17T22:58:09Z</t>
         </is>
       </c>
     </row>
@@ -8539,7 +8539,7 @@
       </c>
       <c r="K168" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:54Z</t>
+          <t>2026-09-17T22:58:09Z</t>
         </is>
       </c>
     </row>
@@ -8588,7 +8588,7 @@
       </c>
       <c r="K169" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:54Z</t>
+          <t>2026-09-17T22:58:09Z</t>
         </is>
       </c>
     </row>
@@ -8637,7 +8637,7 @@
       </c>
       <c r="K170" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:54Z</t>
+          <t>2026-09-17T22:58:09Z</t>
         </is>
       </c>
     </row>
@@ -8686,7 +8686,7 @@
       </c>
       <c r="K171" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:54Z</t>
+          <t>2026-09-17T22:58:09Z</t>
         </is>
       </c>
     </row>
@@ -8735,7 +8735,7 @@
       </c>
       <c r="K172" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:54Z</t>
+          <t>2026-09-17T22:58:09Z</t>
         </is>
       </c>
     </row>
@@ -8784,7 +8784,7 @@
       </c>
       <c r="K173" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:54Z</t>
+          <t>2026-09-17T22:58:09Z</t>
         </is>
       </c>
     </row>
@@ -8833,7 +8833,7 @@
       </c>
       <c r="K174" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:54Z</t>
+          <t>2026-09-17T22:58:09Z</t>
         </is>
       </c>
     </row>
@@ -8882,7 +8882,7 @@
       </c>
       <c r="K175" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:54Z</t>
+          <t>2026-09-17T22:58:09Z</t>
         </is>
       </c>
     </row>
@@ -8931,7 +8931,7 @@
       </c>
       <c r="K176" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:54Z</t>
+          <t>2026-09-17T22:58:09Z</t>
         </is>
       </c>
     </row>
@@ -8980,7 +8980,7 @@
       </c>
       <c r="K177" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:54Z</t>
+          <t>2026-09-17T22:58:09Z</t>
         </is>
       </c>
     </row>
@@ -9029,7 +9029,7 @@
       </c>
       <c r="K178" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:54Z</t>
+          <t>2026-09-17T22:58:09Z</t>
         </is>
       </c>
     </row>
@@ -9078,7 +9078,7 @@
       </c>
       <c r="K179" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:54Z</t>
+          <t>2026-09-17T22:58:09Z</t>
         </is>
       </c>
     </row>
@@ -9127,7 +9127,7 @@
       </c>
       <c r="K180" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:54Z</t>
+          <t>2026-09-17T22:58:09Z</t>
         </is>
       </c>
     </row>
@@ -9176,7 +9176,7 @@
       </c>
       <c r="K181" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:54Z</t>
+          <t>2026-09-17T22:58:09Z</t>
         </is>
       </c>
     </row>
@@ -9225,7 +9225,7 @@
       </c>
       <c r="K182" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:54Z</t>
+          <t>2026-09-17T22:58:09Z</t>
         </is>
       </c>
     </row>
@@ -9274,7 +9274,7 @@
       </c>
       <c r="K183" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:54Z</t>
+          <t>2026-09-17T22:58:09Z</t>
         </is>
       </c>
     </row>
@@ -9323,7 +9323,7 @@
       </c>
       <c r="K184" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:54Z</t>
+          <t>2026-09-17T22:58:09Z</t>
         </is>
       </c>
     </row>
@@ -9372,7 +9372,7 @@
       </c>
       <c r="K185" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:54Z</t>
+          <t>2026-09-17T22:58:09Z</t>
         </is>
       </c>
     </row>
@@ -9421,7 +9421,7 @@
       </c>
       <c r="K186" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:54Z</t>
+          <t>2026-09-17T22:58:09Z</t>
         </is>
       </c>
     </row>
@@ -9470,7 +9470,7 @@
       </c>
       <c r="K187" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:54Z</t>
+          <t>2026-09-17T22:58:09Z</t>
         </is>
       </c>
     </row>
@@ -9519,7 +9519,7 @@
       </c>
       <c r="K188" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:54Z</t>
+          <t>2026-09-17T22:58:09Z</t>
         </is>
       </c>
     </row>
@@ -9568,7 +9568,7 @@
       </c>
       <c r="K189" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:54Z</t>
+          <t>2026-09-17T22:58:09Z</t>
         </is>
       </c>
     </row>
@@ -9617,7 +9617,7 @@
       </c>
       <c r="K190" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:54Z</t>
+          <t>2026-09-17T22:58:09Z</t>
         </is>
       </c>
     </row>
@@ -9666,7 +9666,7 @@
       </c>
       <c r="K191" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:54Z</t>
+          <t>2026-09-17T22:58:09Z</t>
         </is>
       </c>
     </row>
@@ -9715,7 +9715,7 @@
       </c>
       <c r="K192" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:54Z</t>
+          <t>2026-09-17T22:58:09Z</t>
         </is>
       </c>
     </row>
@@ -9764,7 +9764,7 @@
       </c>
       <c r="K193" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:54Z</t>
+          <t>2026-09-17T22:58:09Z</t>
         </is>
       </c>
     </row>
@@ -9813,7 +9813,7 @@
       </c>
       <c r="K194" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:54Z</t>
+          <t>2026-09-17T22:58:09Z</t>
         </is>
       </c>
     </row>
@@ -9862,7 +9862,7 @@
       </c>
       <c r="K195" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:54Z</t>
+          <t>2026-09-17T22:58:09Z</t>
         </is>
       </c>
     </row>
@@ -9911,7 +9911,7 @@
       </c>
       <c r="K196" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:54Z</t>
+          <t>2026-09-17T22:58:09Z</t>
         </is>
       </c>
     </row>
@@ -9960,7 +9960,7 @@
       </c>
       <c r="K197" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:54Z</t>
+          <t>2026-09-17T22:58:09Z</t>
         </is>
       </c>
     </row>
@@ -10009,7 +10009,7 @@
       </c>
       <c r="K198" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:54Z</t>
+          <t>2026-09-17T22:58:09Z</t>
         </is>
       </c>
     </row>
@@ -10058,7 +10058,7 @@
       </c>
       <c r="K199" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:54Z</t>
+          <t>2026-09-17T22:58:09Z</t>
         </is>
       </c>
     </row>
@@ -10107,7 +10107,7 @@
       </c>
       <c r="K200" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:54Z</t>
+          <t>2026-09-17T22:58:09Z</t>
         </is>
       </c>
     </row>
@@ -10156,7 +10156,7 @@
       </c>
       <c r="K201" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:54Z</t>
+          <t>2026-09-17T22:58:09Z</t>
         </is>
       </c>
     </row>
@@ -10205,7 +10205,7 @@
       </c>
       <c r="K202" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:54Z</t>
+          <t>2026-09-17T22:58:09Z</t>
         </is>
       </c>
     </row>
@@ -10254,7 +10254,7 @@
       </c>
       <c r="K203" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:54Z</t>
+          <t>2026-09-17T22:58:09Z</t>
         </is>
       </c>
     </row>
@@ -10303,7 +10303,7 @@
       </c>
       <c r="K204" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:54Z</t>
+          <t>2026-09-17T22:58:09Z</t>
         </is>
       </c>
     </row>
@@ -10352,7 +10352,7 @@
       </c>
       <c r="K205" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:54Z</t>
+          <t>2026-09-17T22:58:09Z</t>
         </is>
       </c>
     </row>
@@ -10401,7 +10401,7 @@
       </c>
       <c r="K206" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:54Z</t>
+          <t>2026-09-17T22:58:09Z</t>
         </is>
       </c>
     </row>
@@ -10450,7 +10450,7 @@
       </c>
       <c r="K207" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:54Z</t>
+          <t>2026-09-17T22:58:09Z</t>
         </is>
       </c>
     </row>
@@ -10499,7 +10499,7 @@
       </c>
       <c r="K208" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:54Z</t>
+          <t>2026-09-17T22:58:09Z</t>
         </is>
       </c>
     </row>
@@ -10548,7 +10548,7 @@
       </c>
       <c r="K209" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:54Z</t>
+          <t>2026-09-17T22:58:09Z</t>
         </is>
       </c>
     </row>
@@ -10597,7 +10597,7 @@
       </c>
       <c r="K210" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:54Z</t>
+          <t>2026-09-17T22:58:09Z</t>
         </is>
       </c>
     </row>
@@ -10646,7 +10646,7 @@
       </c>
       <c r="K211" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:54Z</t>
+          <t>2026-09-17T22:58:09Z</t>
         </is>
       </c>
     </row>
@@ -10695,7 +10695,7 @@
       </c>
       <c r="K212" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:54Z</t>
+          <t>2026-09-17T22:58:09Z</t>
         </is>
       </c>
     </row>
@@ -10744,7 +10744,7 @@
       </c>
       <c r="K213" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:54Z</t>
+          <t>2026-09-17T22:58:09Z</t>
         </is>
       </c>
     </row>
@@ -10793,7 +10793,7 @@
       </c>
       <c r="K214" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:54Z</t>
+          <t>2026-09-17T22:58:09Z</t>
         </is>
       </c>
     </row>
@@ -10842,7 +10842,7 @@
       </c>
       <c r="K215" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:54Z</t>
+          <t>2026-09-17T22:58:09Z</t>
         </is>
       </c>
     </row>
@@ -10891,7 +10891,7 @@
       </c>
       <c r="K216" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:54Z</t>
+          <t>2026-09-17T22:58:09Z</t>
         </is>
       </c>
     </row>
@@ -10940,7 +10940,7 @@
       </c>
       <c r="K217" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:54Z</t>
+          <t>2026-09-17T22:58:09Z</t>
         </is>
       </c>
     </row>
@@ -10989,7 +10989,7 @@
       </c>
       <c r="K218" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:54Z</t>
+          <t>2026-09-17T22:58:09Z</t>
         </is>
       </c>
     </row>
@@ -11038,7 +11038,7 @@
       </c>
       <c r="K219" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:54Z</t>
+          <t>2026-09-17T22:58:09Z</t>
         </is>
       </c>
     </row>
@@ -11087,7 +11087,7 @@
       </c>
       <c r="K220" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:54Z</t>
+          <t>2026-09-17T22:58:09Z</t>
         </is>
       </c>
     </row>
@@ -11136,7 +11136,7 @@
       </c>
       <c r="K221" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:54Z</t>
+          <t>2026-09-17T22:58:09Z</t>
         </is>
       </c>
     </row>
@@ -11185,7 +11185,7 @@
       </c>
       <c r="K222" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:54Z</t>
+          <t>2026-09-17T22:58:09Z</t>
         </is>
       </c>
     </row>
@@ -11234,7 +11234,7 @@
       </c>
       <c r="K223" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:54Z</t>
+          <t>2026-09-17T22:58:09Z</t>
         </is>
       </c>
     </row>
@@ -11283,7 +11283,7 @@
       </c>
       <c r="K224" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:54Z</t>
+          <t>2026-09-17T22:58:09Z</t>
         </is>
       </c>
     </row>
@@ -11332,7 +11332,7 @@
       </c>
       <c r="K225" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:54Z</t>
+          <t>2026-09-17T22:58:09Z</t>
         </is>
       </c>
     </row>
@@ -11381,7 +11381,7 @@
       </c>
       <c r="K226" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:54Z</t>
+          <t>2026-09-17T22:58:09Z</t>
         </is>
       </c>
     </row>
@@ -11430,7 +11430,7 @@
       </c>
       <c r="K227" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:54Z</t>
+          <t>2026-09-17T22:58:09Z</t>
         </is>
       </c>
     </row>
@@ -11479,7 +11479,7 @@
       </c>
       <c r="K228" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:54Z</t>
+          <t>2026-09-17T22:58:09Z</t>
         </is>
       </c>
     </row>
@@ -11528,7 +11528,7 @@
       </c>
       <c r="K229" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:54Z</t>
+          <t>2026-09-17T22:58:09Z</t>
         </is>
       </c>
     </row>
@@ -11577,7 +11577,7 @@
       </c>
       <c r="K230" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:54Z</t>
+          <t>2026-09-17T22:58:09Z</t>
         </is>
       </c>
     </row>
@@ -11626,7 +11626,7 @@
       </c>
       <c r="K231" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:54Z</t>
+          <t>2026-09-17T22:58:09Z</t>
         </is>
       </c>
     </row>
@@ -11758,7 +11758,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:54Z</t>
+          <t>2026-09-17T22:58:09Z</t>
         </is>
       </c>
     </row>
@@ -11804,7 +11804,7 @@
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>{"date": "2026-08-01", "year": 2026, "month": 8, "month_name": "Agosto", "index_value": 637409769724325.1, "monthly_variation_pct": 8.9, "unit": "Índice base diciembre 2007=100 y variación mensual %", "frequency": "monthly", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/precios_consumidor/4_5_7_2.xls", "fetched_at": "2026-09-17T17:37:54Z"}</t>
+          <t>{"date": "2026-08-01", "year": 2026, "month": 8, "month_name": "Agosto", "index_value": 637409769724325.1, "monthly_variation_pct": 8.9, "unit": "Índice base diciembre 2007=100 y variación mensual %", "frequency": "monthly", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/precios_consumidor/4_5_7_2.xls", "fetched_at": "2026-09-17T22:58:09Z"}</t>
         </is>
       </c>
     </row>

--- a/assets/data/bcv/excel/ove_bcv_inpc_nacional_mensual.xlsx
+++ b/assets/data/bcv/excel/ove_bcv_inpc_nacional_mensual.xlsx
@@ -650,7 +650,7 @@
       </c>
       <c r="K7" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:09Z</t>
+          <t>2026-09-18T22:43:52Z</t>
         </is>
       </c>
     </row>
@@ -699,7 +699,7 @@
       </c>
       <c r="K8" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:09Z</t>
+          <t>2026-09-18T22:43:52Z</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="K9" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:09Z</t>
+          <t>2026-09-18T22:43:52Z</t>
         </is>
       </c>
     </row>
@@ -797,7 +797,7 @@
       </c>
       <c r="K10" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:09Z</t>
+          <t>2026-09-18T22:43:52Z</t>
         </is>
       </c>
     </row>
@@ -846,7 +846,7 @@
       </c>
       <c r="K11" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:09Z</t>
+          <t>2026-09-18T22:43:52Z</t>
         </is>
       </c>
     </row>
@@ -895,7 +895,7 @@
       </c>
       <c r="K12" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:09Z</t>
+          <t>2026-09-18T22:43:52Z</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="K13" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:09Z</t>
+          <t>2026-09-18T22:43:52Z</t>
         </is>
       </c>
     </row>
@@ -993,7 +993,7 @@
       </c>
       <c r="K14" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:09Z</t>
+          <t>2026-09-18T22:43:52Z</t>
         </is>
       </c>
     </row>
@@ -1042,7 +1042,7 @@
       </c>
       <c r="K15" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:09Z</t>
+          <t>2026-09-18T22:43:52Z</t>
         </is>
       </c>
     </row>
@@ -1091,7 +1091,7 @@
       </c>
       <c r="K16" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:09Z</t>
+          <t>2026-09-18T22:43:52Z</t>
         </is>
       </c>
     </row>
@@ -1140,7 +1140,7 @@
       </c>
       <c r="K17" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:09Z</t>
+          <t>2026-09-18T22:43:52Z</t>
         </is>
       </c>
     </row>
@@ -1189,7 +1189,7 @@
       </c>
       <c r="K18" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:09Z</t>
+          <t>2026-09-18T22:43:52Z</t>
         </is>
       </c>
     </row>
@@ -1238,7 +1238,7 @@
       </c>
       <c r="K19" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:09Z</t>
+          <t>2026-09-18T22:43:52Z</t>
         </is>
       </c>
     </row>
@@ -1287,7 +1287,7 @@
       </c>
       <c r="K20" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:09Z</t>
+          <t>2026-09-18T22:43:52Z</t>
         </is>
       </c>
     </row>
@@ -1336,7 +1336,7 @@
       </c>
       <c r="K21" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:09Z</t>
+          <t>2026-09-18T22:43:52Z</t>
         </is>
       </c>
     </row>
@@ -1385,7 +1385,7 @@
       </c>
       <c r="K22" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:09Z</t>
+          <t>2026-09-18T22:43:52Z</t>
         </is>
       </c>
     </row>
@@ -1434,7 +1434,7 @@
       </c>
       <c r="K23" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:09Z</t>
+          <t>2026-09-18T22:43:52Z</t>
         </is>
       </c>
     </row>
@@ -1483,7 +1483,7 @@
       </c>
       <c r="K24" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:09Z</t>
+          <t>2026-09-18T22:43:52Z</t>
         </is>
       </c>
     </row>
@@ -1532,7 +1532,7 @@
       </c>
       <c r="K25" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:09Z</t>
+          <t>2026-09-18T22:43:52Z</t>
         </is>
       </c>
     </row>
@@ -1581,7 +1581,7 @@
       </c>
       <c r="K26" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:09Z</t>
+          <t>2026-09-18T22:43:52Z</t>
         </is>
       </c>
     </row>
@@ -1630,7 +1630,7 @@
       </c>
       <c r="K27" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:09Z</t>
+          <t>2026-09-18T22:43:52Z</t>
         </is>
       </c>
     </row>
@@ -1679,7 +1679,7 @@
       </c>
       <c r="K28" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:09Z</t>
+          <t>2026-09-18T22:43:52Z</t>
         </is>
       </c>
     </row>
@@ -1728,7 +1728,7 @@
       </c>
       <c r="K29" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:09Z</t>
+          <t>2026-09-18T22:43:52Z</t>
         </is>
       </c>
     </row>
@@ -1777,7 +1777,7 @@
       </c>
       <c r="K30" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:09Z</t>
+          <t>2026-09-18T22:43:52Z</t>
         </is>
       </c>
     </row>
@@ -1826,7 +1826,7 @@
       </c>
       <c r="K31" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:09Z</t>
+          <t>2026-09-18T22:43:52Z</t>
         </is>
       </c>
     </row>
@@ -1875,7 +1875,7 @@
       </c>
       <c r="K32" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:09Z</t>
+          <t>2026-09-18T22:43:52Z</t>
         </is>
       </c>
     </row>
@@ -1924,7 +1924,7 @@
       </c>
       <c r="K33" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:09Z</t>
+          <t>2026-09-18T22:43:52Z</t>
         </is>
       </c>
     </row>
@@ -1973,7 +1973,7 @@
       </c>
       <c r="K34" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:09Z</t>
+          <t>2026-09-18T22:43:52Z</t>
         </is>
       </c>
     </row>
@@ -2022,7 +2022,7 @@
       </c>
       <c r="K35" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:09Z</t>
+          <t>2026-09-18T22:43:52Z</t>
         </is>
       </c>
     </row>
@@ -2071,7 +2071,7 @@
       </c>
       <c r="K36" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:09Z</t>
+          <t>2026-09-18T22:43:52Z</t>
         </is>
       </c>
     </row>
@@ -2120,7 +2120,7 @@
       </c>
       <c r="K37" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:09Z</t>
+          <t>2026-09-18T22:43:52Z</t>
         </is>
       </c>
     </row>
@@ -2169,7 +2169,7 @@
       </c>
       <c r="K38" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:09Z</t>
+          <t>2026-09-18T22:43:52Z</t>
         </is>
       </c>
     </row>
@@ -2218,7 +2218,7 @@
       </c>
       <c r="K39" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:09Z</t>
+          <t>2026-09-18T22:43:52Z</t>
         </is>
       </c>
     </row>
@@ -2267,7 +2267,7 @@
       </c>
       <c r="K40" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:09Z</t>
+          <t>2026-09-18T22:43:52Z</t>
         </is>
       </c>
     </row>
@@ -2316,7 +2316,7 @@
       </c>
       <c r="K41" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:09Z</t>
+          <t>2026-09-18T22:43:52Z</t>
         </is>
       </c>
     </row>
@@ -2365,7 +2365,7 @@
       </c>
       <c r="K42" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:09Z</t>
+          <t>2026-09-18T22:43:52Z</t>
         </is>
       </c>
     </row>
@@ -2414,7 +2414,7 @@
       </c>
       <c r="K43" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:09Z</t>
+          <t>2026-09-18T22:43:52Z</t>
         </is>
       </c>
     </row>
@@ -2463,7 +2463,7 @@
       </c>
       <c r="K44" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:09Z</t>
+          <t>2026-09-18T22:43:52Z</t>
         </is>
       </c>
     </row>
@@ -2512,7 +2512,7 @@
       </c>
       <c r="K45" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:09Z</t>
+          <t>2026-09-18T22:43:52Z</t>
         </is>
       </c>
     </row>
@@ -2561,7 +2561,7 @@
       </c>
       <c r="K46" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:09Z</t>
+          <t>2026-09-18T22:43:52Z</t>
         </is>
       </c>
     </row>
@@ -2610,7 +2610,7 @@
       </c>
       <c r="K47" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:09Z</t>
+          <t>2026-09-18T22:43:52Z</t>
         </is>
       </c>
     </row>
@@ -2659,7 +2659,7 @@
       </c>
       <c r="K48" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:09Z</t>
+          <t>2026-09-18T22:43:52Z</t>
         </is>
       </c>
     </row>
@@ -2708,7 +2708,7 @@
       </c>
       <c r="K49" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:09Z</t>
+          <t>2026-09-18T22:43:52Z</t>
         </is>
       </c>
     </row>
@@ -2757,7 +2757,7 @@
       </c>
       <c r="K50" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:09Z</t>
+          <t>2026-09-18T22:43:52Z</t>
         </is>
       </c>
     </row>
@@ -2806,7 +2806,7 @@
       </c>
       <c r="K51" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:09Z</t>
+          <t>2026-09-18T22:43:52Z</t>
         </is>
       </c>
     </row>
@@ -2855,7 +2855,7 @@
       </c>
       <c r="K52" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:09Z</t>
+          <t>2026-09-18T22:43:52Z</t>
         </is>
       </c>
     </row>
@@ -2904,7 +2904,7 @@
       </c>
       <c r="K53" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:09Z</t>
+          <t>2026-09-18T22:43:52Z</t>
         </is>
       </c>
     </row>
@@ -2953,7 +2953,7 @@
       </c>
       <c r="K54" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:09Z</t>
+          <t>2026-09-18T22:43:52Z</t>
         </is>
       </c>
     </row>
@@ -3002,7 +3002,7 @@
       </c>
       <c r="K55" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:09Z</t>
+          <t>2026-09-18T22:43:52Z</t>
         </is>
       </c>
     </row>
@@ -3051,7 +3051,7 @@
       </c>
       <c r="K56" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:09Z</t>
+          <t>2026-09-18T22:43:52Z</t>
         </is>
       </c>
     </row>
@@ -3100,7 +3100,7 @@
       </c>
       <c r="K57" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:09Z</t>
+          <t>2026-09-18T22:43:52Z</t>
         </is>
       </c>
     </row>
@@ -3149,7 +3149,7 @@
       </c>
       <c r="K58" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:09Z</t>
+          <t>2026-09-18T22:43:52Z</t>
         </is>
       </c>
     </row>
@@ -3198,7 +3198,7 @@
       </c>
       <c r="K59" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:09Z</t>
+          <t>2026-09-18T22:43:52Z</t>
         </is>
       </c>
     </row>
@@ -3247,7 +3247,7 @@
       </c>
       <c r="K60" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:09Z</t>
+          <t>2026-09-18T22:43:52Z</t>
         </is>
       </c>
     </row>
@@ -3296,7 +3296,7 @@
       </c>
       <c r="K61" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:09Z</t>
+          <t>2026-09-18T22:43:52Z</t>
         </is>
       </c>
     </row>
@@ -3345,7 +3345,7 @@
       </c>
       <c r="K62" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:09Z</t>
+          <t>2026-09-18T22:43:52Z</t>
         </is>
       </c>
     </row>
@@ -3394,7 +3394,7 @@
       </c>
       <c r="K63" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:09Z</t>
+          <t>2026-09-18T22:43:52Z</t>
         </is>
       </c>
     </row>
@@ -3443,7 +3443,7 @@
       </c>
       <c r="K64" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:09Z</t>
+          <t>2026-09-18T22:43:52Z</t>
         </is>
       </c>
     </row>
@@ -3492,7 +3492,7 @@
       </c>
       <c r="K65" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:09Z</t>
+          <t>2026-09-18T22:43:52Z</t>
         </is>
       </c>
     </row>
@@ -3541,7 +3541,7 @@
       </c>
       <c r="K66" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:09Z</t>
+          <t>2026-09-18T22:43:52Z</t>
         </is>
       </c>
     </row>
@@ -3590,7 +3590,7 @@
       </c>
       <c r="K67" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:09Z</t>
+          <t>2026-09-18T22:43:52Z</t>
         </is>
       </c>
     </row>
@@ -3639,7 +3639,7 @@
       </c>
       <c r="K68" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:09Z</t>
+          <t>2026-09-18T22:43:52Z</t>
         </is>
       </c>
     </row>
@@ -3688,7 +3688,7 @@
       </c>
       <c r="K69" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:09Z</t>
+          <t>2026-09-18T22:43:52Z</t>
         </is>
       </c>
     </row>
@@ -3737,7 +3737,7 @@
       </c>
       <c r="K70" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:09Z</t>
+          <t>2026-09-18T22:43:52Z</t>
         </is>
       </c>
     </row>
@@ -3786,7 +3786,7 @@
       </c>
       <c r="K71" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:09Z</t>
+          <t>2026-09-18T22:43:52Z</t>
         </is>
       </c>
     </row>
@@ -3835,7 +3835,7 @@
       </c>
       <c r="K72" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:09Z</t>
+          <t>2026-09-18T22:43:52Z</t>
         </is>
       </c>
     </row>
@@ -3884,7 +3884,7 @@
       </c>
       <c r="K73" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:09Z</t>
+          <t>2026-09-18T22:43:52Z</t>
         </is>
       </c>
     </row>
@@ -3933,7 +3933,7 @@
       </c>
       <c r="K74" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:09Z</t>
+          <t>2026-09-18T22:43:52Z</t>
         </is>
       </c>
     </row>
@@ -3982,7 +3982,7 @@
       </c>
       <c r="K75" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:09Z</t>
+          <t>2026-09-18T22:43:52Z</t>
         </is>
       </c>
     </row>
@@ -4031,7 +4031,7 @@
       </c>
       <c r="K76" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:09Z</t>
+          <t>2026-09-18T22:43:52Z</t>
         </is>
       </c>
     </row>
@@ -4080,7 +4080,7 @@
       </c>
       <c r="K77" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:09Z</t>
+          <t>2026-09-18T22:43:52Z</t>
         </is>
       </c>
     </row>
@@ -4129,7 +4129,7 @@
       </c>
       <c r="K78" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:09Z</t>
+          <t>2026-09-18T22:43:52Z</t>
         </is>
       </c>
     </row>
@@ -4178,7 +4178,7 @@
       </c>
       <c r="K79" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:09Z</t>
+          <t>2026-09-18T22:43:52Z</t>
         </is>
       </c>
     </row>
@@ -4227,7 +4227,7 @@
       </c>
       <c r="K80" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:09Z</t>
+          <t>2026-09-18T22:43:52Z</t>
         </is>
       </c>
     </row>
@@ -4276,7 +4276,7 @@
       </c>
       <c r="K81" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:09Z</t>
+          <t>2026-09-18T22:43:52Z</t>
         </is>
       </c>
     </row>
@@ -4325,7 +4325,7 @@
       </c>
       <c r="K82" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:09Z</t>
+          <t>2026-09-18T22:43:52Z</t>
         </is>
       </c>
     </row>
@@ -4374,7 +4374,7 @@
       </c>
       <c r="K83" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:09Z</t>
+          <t>2026-09-18T22:43:52Z</t>
         </is>
       </c>
     </row>
@@ -4423,7 +4423,7 @@
       </c>
       <c r="K84" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:09Z</t>
+          <t>2026-09-18T22:43:52Z</t>
         </is>
       </c>
     </row>
@@ -4472,7 +4472,7 @@
       </c>
       <c r="K85" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:09Z</t>
+          <t>2026-09-18T22:43:52Z</t>
         </is>
       </c>
     </row>
@@ -4521,7 +4521,7 @@
       </c>
       <c r="K86" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:09Z</t>
+          <t>2026-09-18T22:43:52Z</t>
         </is>
       </c>
     </row>
@@ -4570,7 +4570,7 @@
       </c>
       <c r="K87" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:09Z</t>
+          <t>2026-09-18T22:43:52Z</t>
         </is>
       </c>
     </row>
@@ -4619,7 +4619,7 @@
       </c>
       <c r="K88" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:09Z</t>
+          <t>2026-09-18T22:43:52Z</t>
         </is>
       </c>
     </row>
@@ -4668,7 +4668,7 @@
       </c>
       <c r="K89" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:09Z</t>
+          <t>2026-09-18T22:43:52Z</t>
         </is>
       </c>
     </row>
@@ -4717,7 +4717,7 @@
       </c>
       <c r="K90" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:09Z</t>
+          <t>2026-09-18T22:43:52Z</t>
         </is>
       </c>
     </row>
@@ -4766,7 +4766,7 @@
       </c>
       <c r="K91" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:09Z</t>
+          <t>2026-09-18T22:43:52Z</t>
         </is>
       </c>
     </row>
@@ -4815,7 +4815,7 @@
       </c>
       <c r="K92" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:09Z</t>
+          <t>2026-09-18T22:43:52Z</t>
         </is>
       </c>
     </row>
@@ -4864,7 +4864,7 @@
       </c>
       <c r="K93" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:09Z</t>
+          <t>2026-09-18T22:43:52Z</t>
         </is>
       </c>
     </row>
@@ -4913,7 +4913,7 @@
       </c>
       <c r="K94" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:09Z</t>
+          <t>2026-09-18T22:43:52Z</t>
         </is>
       </c>
     </row>
@@ -4962,7 +4962,7 @@
       </c>
       <c r="K95" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:09Z</t>
+          <t>2026-09-18T22:43:52Z</t>
         </is>
       </c>
     </row>
@@ -5011,7 +5011,7 @@
       </c>
       <c r="K96" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:09Z</t>
+          <t>2026-09-18T22:43:52Z</t>
         </is>
       </c>
     </row>
@@ -5060,7 +5060,7 @@
       </c>
       <c r="K97" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:09Z</t>
+          <t>2026-09-18T22:43:52Z</t>
         </is>
       </c>
     </row>
@@ -5109,7 +5109,7 @@
       </c>
       <c r="K98" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:09Z</t>
+          <t>2026-09-18T22:43:52Z</t>
         </is>
       </c>
     </row>
@@ -5158,7 +5158,7 @@
       </c>
       <c r="K99" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:09Z</t>
+          <t>2026-09-18T22:43:52Z</t>
         </is>
       </c>
     </row>
@@ -5207,7 +5207,7 @@
       </c>
       <c r="K100" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:09Z</t>
+          <t>2026-09-18T22:43:52Z</t>
         </is>
       </c>
     </row>
@@ -5256,7 +5256,7 @@
       </c>
       <c r="K101" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:09Z</t>
+          <t>2026-09-18T22:43:52Z</t>
         </is>
       </c>
     </row>
@@ -5305,7 +5305,7 @@
       </c>
       <c r="K102" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:09Z</t>
+          <t>2026-09-18T22:43:52Z</t>
         </is>
       </c>
     </row>
@@ -5354,7 +5354,7 @@
       </c>
       <c r="K103" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:09Z</t>
+          <t>2026-09-18T22:43:52Z</t>
         </is>
       </c>
     </row>
@@ -5403,7 +5403,7 @@
       </c>
       <c r="K104" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:09Z</t>
+          <t>2026-09-18T22:43:52Z</t>
         </is>
       </c>
     </row>
@@ -5452,7 +5452,7 @@
       </c>
       <c r="K105" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:09Z</t>
+          <t>2026-09-18T22:43:52Z</t>
         </is>
       </c>
     </row>
@@ -5501,7 +5501,7 @@
       </c>
       <c r="K106" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:09Z</t>
+          <t>2026-09-18T22:43:52Z</t>
         </is>
       </c>
     </row>
@@ -5550,7 +5550,7 @@
       </c>
       <c r="K107" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:09Z</t>
+          <t>2026-09-18T22:43:52Z</t>
         </is>
       </c>
     </row>
@@ -5599,7 +5599,7 @@
       </c>
       <c r="K108" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:09Z</t>
+          <t>2026-09-18T22:43:52Z</t>
         </is>
       </c>
     </row>
@@ -5648,7 +5648,7 @@
       </c>
       <c r="K109" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:09Z</t>
+          <t>2026-09-18T22:43:52Z</t>
         </is>
       </c>
     </row>
@@ -5697,7 +5697,7 @@
       </c>
       <c r="K110" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:09Z</t>
+          <t>2026-09-18T22:43:52Z</t>
         </is>
       </c>
     </row>
@@ -5746,7 +5746,7 @@
       </c>
       <c r="K111" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:09Z</t>
+          <t>2026-09-18T22:43:52Z</t>
         </is>
       </c>
     </row>
@@ -5795,7 +5795,7 @@
       </c>
       <c r="K112" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:09Z</t>
+          <t>2026-09-18T22:43:52Z</t>
         </is>
       </c>
     </row>
@@ -5844,7 +5844,7 @@
       </c>
       <c r="K113" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:09Z</t>
+          <t>2026-09-18T22:43:52Z</t>
         </is>
       </c>
     </row>
@@ -5893,7 +5893,7 @@
       </c>
       <c r="K114" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:09Z</t>
+          <t>2026-09-18T22:43:52Z</t>
         </is>
       </c>
     </row>
@@ -5942,7 +5942,7 @@
       </c>
       <c r="K115" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:09Z</t>
+          <t>2026-09-18T22:43:52Z</t>
         </is>
       </c>
     </row>
@@ -5991,7 +5991,7 @@
       </c>
       <c r="K116" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:09Z</t>
+          <t>2026-09-18T22:43:52Z</t>
         </is>
       </c>
     </row>
@@ -6040,7 +6040,7 @@
       </c>
       <c r="K117" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:09Z</t>
+          <t>2026-09-18T22:43:52Z</t>
         </is>
       </c>
     </row>
@@ -6089,7 +6089,7 @@
       </c>
       <c r="K118" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:09Z</t>
+          <t>2026-09-18T22:43:52Z</t>
         </is>
       </c>
     </row>
@@ -6138,7 +6138,7 @@
       </c>
       <c r="K119" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:09Z</t>
+          <t>2026-09-18T22:43:52Z</t>
         </is>
       </c>
     </row>
@@ -6187,7 +6187,7 @@
       </c>
       <c r="K120" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:09Z</t>
+          <t>2026-09-18T22:43:52Z</t>
         </is>
       </c>
     </row>
@@ -6236,7 +6236,7 @@
       </c>
       <c r="K121" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:09Z</t>
+          <t>2026-09-18T22:43:52Z</t>
         </is>
       </c>
     </row>
@@ -6285,7 +6285,7 @@
       </c>
       <c r="K122" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:09Z</t>
+          <t>2026-09-18T22:43:52Z</t>
         </is>
       </c>
     </row>
@@ -6334,7 +6334,7 @@
       </c>
       <c r="K123" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:09Z</t>
+          <t>2026-09-18T22:43:52Z</t>
         </is>
       </c>
     </row>
@@ -6383,7 +6383,7 @@
       </c>
       <c r="K124" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:09Z</t>
+          <t>2026-09-18T22:43:52Z</t>
         </is>
       </c>
     </row>
@@ -6432,7 +6432,7 @@
       </c>
       <c r="K125" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:09Z</t>
+          <t>2026-09-18T22:43:52Z</t>
         </is>
       </c>
     </row>
@@ -6481,7 +6481,7 @@
       </c>
       <c r="K126" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:09Z</t>
+          <t>2026-09-18T22:43:52Z</t>
         </is>
       </c>
     </row>
@@ -6530,7 +6530,7 @@
       </c>
       <c r="K127" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:09Z</t>
+          <t>2026-09-18T22:43:52Z</t>
         </is>
       </c>
     </row>
@@ -6579,7 +6579,7 @@
       </c>
       <c r="K128" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:09Z</t>
+          <t>2026-09-18T22:43:52Z</t>
         </is>
       </c>
     </row>
@@ -6628,7 +6628,7 @@
       </c>
       <c r="K129" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:09Z</t>
+          <t>2026-09-18T22:43:52Z</t>
         </is>
       </c>
     </row>
@@ -6677,7 +6677,7 @@
       </c>
       <c r="K130" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:09Z</t>
+          <t>2026-09-18T22:43:52Z</t>
         </is>
       </c>
     </row>
@@ -6726,7 +6726,7 @@
       </c>
       <c r="K131" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:09Z</t>
+          <t>2026-09-18T22:43:52Z</t>
         </is>
       </c>
     </row>
@@ -6775,7 +6775,7 @@
       </c>
       <c r="K132" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:09Z</t>
+          <t>2026-09-18T22:43:52Z</t>
         </is>
       </c>
     </row>
@@ -6824,7 +6824,7 @@
       </c>
       <c r="K133" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:09Z</t>
+          <t>2026-09-18T22:43:52Z</t>
         </is>
       </c>
     </row>
@@ -6873,7 +6873,7 @@
       </c>
       <c r="K134" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:09Z</t>
+          <t>2026-09-18T22:43:52Z</t>
         </is>
       </c>
     </row>
@@ -6922,7 +6922,7 @@
       </c>
       <c r="K135" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:09Z</t>
+          <t>2026-09-18T22:43:52Z</t>
         </is>
       </c>
     </row>
@@ -6971,7 +6971,7 @@
       </c>
       <c r="K136" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:09Z</t>
+          <t>2026-09-18T22:43:52Z</t>
         </is>
       </c>
     </row>
@@ -7020,7 +7020,7 @@
       </c>
       <c r="K137" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:09Z</t>
+          <t>2026-09-18T22:43:52Z</t>
         </is>
       </c>
     </row>
@@ -7069,7 +7069,7 @@
       </c>
       <c r="K138" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:09Z</t>
+          <t>2026-09-18T22:43:52Z</t>
         </is>
       </c>
     </row>
@@ -7118,7 +7118,7 @@
       </c>
       <c r="K139" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:09Z</t>
+          <t>2026-09-18T22:43:52Z</t>
         </is>
       </c>
     </row>
@@ -7167,7 +7167,7 @@
       </c>
       <c r="K140" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:09Z</t>
+          <t>2026-09-18T22:43:52Z</t>
         </is>
       </c>
     </row>
@@ -7216,7 +7216,7 @@
       </c>
       <c r="K141" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:09Z</t>
+          <t>2026-09-18T22:43:52Z</t>
         </is>
       </c>
     </row>
@@ -7265,7 +7265,7 @@
       </c>
       <c r="K142" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:09Z</t>
+          <t>2026-09-18T22:43:52Z</t>
         </is>
       </c>
     </row>
@@ -7314,7 +7314,7 @@
       </c>
       <c r="K143" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:09Z</t>
+          <t>2026-09-18T22:43:52Z</t>
         </is>
       </c>
     </row>
@@ -7363,7 +7363,7 @@
       </c>
       <c r="K144" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:09Z</t>
+          <t>2026-09-18T22:43:52Z</t>
         </is>
       </c>
     </row>
@@ -7412,7 +7412,7 @@
       </c>
       <c r="K145" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:09Z</t>
+          <t>2026-09-18T22:43:52Z</t>
         </is>
       </c>
     </row>
@@ -7461,7 +7461,7 @@
       </c>
       <c r="K146" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:09Z</t>
+          <t>2026-09-18T22:43:52Z</t>
         </is>
       </c>
     </row>
@@ -7510,7 +7510,7 @@
       </c>
       <c r="K147" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:09Z</t>
+          <t>2026-09-18T22:43:52Z</t>
         </is>
       </c>
     </row>
@@ -7559,7 +7559,7 @@
       </c>
       <c r="K148" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:09Z</t>
+          <t>2026-09-18T22:43:52Z</t>
         </is>
       </c>
     </row>
@@ -7608,7 +7608,7 @@
       </c>
       <c r="K149" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:09Z</t>
+          <t>2026-09-18T22:43:52Z</t>
         </is>
       </c>
     </row>
@@ -7657,7 +7657,7 @@
       </c>
       <c r="K150" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:09Z</t>
+          <t>2026-09-18T22:43:52Z</t>
         </is>
       </c>
     </row>
@@ -7706,7 +7706,7 @@
       </c>
       <c r="K151" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:09Z</t>
+          <t>2026-09-18T22:43:52Z</t>
         </is>
       </c>
     </row>
@@ -7755,7 +7755,7 @@
       </c>
       <c r="K152" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:09Z</t>
+          <t>2026-09-18T22:43:52Z</t>
         </is>
       </c>
     </row>
@@ -7804,7 +7804,7 @@
       </c>
       <c r="K153" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:09Z</t>
+          <t>2026-09-18T22:43:52Z</t>
         </is>
       </c>
     </row>
@@ -7853,7 +7853,7 @@
       </c>
       <c r="K154" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:09Z</t>
+          <t>2026-09-18T22:43:52Z</t>
         </is>
       </c>
     </row>
@@ -7902,7 +7902,7 @@
       </c>
       <c r="K155" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:09Z</t>
+          <t>2026-09-18T22:43:52Z</t>
         </is>
       </c>
     </row>
@@ -7951,7 +7951,7 @@
       </c>
       <c r="K156" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:09Z</t>
+          <t>2026-09-18T22:43:52Z</t>
         </is>
       </c>
     </row>
@@ -8000,7 +8000,7 @@
       </c>
       <c r="K157" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:09Z</t>
+          <t>2026-09-18T22:43:52Z</t>
         </is>
       </c>
     </row>
@@ -8049,7 +8049,7 @@
       </c>
       <c r="K158" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:09Z</t>
+          <t>2026-09-18T22:43:52Z</t>
         </is>
       </c>
     </row>
@@ -8098,7 +8098,7 @@
       </c>
       <c r="K159" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:09Z</t>
+          <t>2026-09-18T22:43:52Z</t>
         </is>
       </c>
     </row>
@@ -8147,7 +8147,7 @@
       </c>
       <c r="K160" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:09Z</t>
+          <t>2026-09-18T22:43:52Z</t>
         </is>
       </c>
     </row>
@@ -8196,7 +8196,7 @@
       </c>
       <c r="K161" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:09Z</t>
+          <t>2026-09-18T22:43:52Z</t>
         </is>
       </c>
     </row>
@@ -8245,7 +8245,7 @@
       </c>
       <c r="K162" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:09Z</t>
+          <t>2026-09-18T22:43:52Z</t>
         </is>
       </c>
     </row>
@@ -8294,7 +8294,7 @@
       </c>
       <c r="K163" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:09Z</t>
+          <t>2026-09-18T22:43:52Z</t>
         </is>
       </c>
     </row>
@@ -8343,7 +8343,7 @@
       </c>
       <c r="K164" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:09Z</t>
+          <t>2026-09-18T22:43:52Z</t>
         </is>
       </c>
     </row>
@@ -8392,7 +8392,7 @@
       </c>
       <c r="K165" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:09Z</t>
+          <t>2026-09-18T22:43:52Z</t>
         </is>
       </c>
     </row>
@@ -8441,7 +8441,7 @@
       </c>
       <c r="K166" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:09Z</t>
+          <t>2026-09-18T22:43:52Z</t>
         </is>
       </c>
     </row>
@@ -8490,7 +8490,7 @@
       </c>
       <c r="K167" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:09Z</t>
+          <t>2026-09-18T22:43:52Z</t>
         </is>
       </c>
     </row>
@@ -8539,7 +8539,7 @@
       </c>
       <c r="K168" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:09Z</t>
+          <t>2026-09-18T22:43:52Z</t>
         </is>
       </c>
     </row>
@@ -8588,7 +8588,7 @@
       </c>
       <c r="K169" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:09Z</t>
+          <t>2026-09-18T22:43:52Z</t>
         </is>
       </c>
     </row>
@@ -8637,7 +8637,7 @@
       </c>
       <c r="K170" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:09Z</t>
+          <t>2026-09-18T22:43:52Z</t>
         </is>
       </c>
     </row>
@@ -8686,7 +8686,7 @@
       </c>
       <c r="K171" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:09Z</t>
+          <t>2026-09-18T22:43:52Z</t>
         </is>
       </c>
     </row>
@@ -8735,7 +8735,7 @@
       </c>
       <c r="K172" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:09Z</t>
+          <t>2026-09-18T22:43:52Z</t>
         </is>
       </c>
     </row>
@@ -8784,7 +8784,7 @@
       </c>
       <c r="K173" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:09Z</t>
+          <t>2026-09-18T22:43:52Z</t>
         </is>
       </c>
     </row>
@@ -8833,7 +8833,7 @@
       </c>
       <c r="K174" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:09Z</t>
+          <t>2026-09-18T22:43:52Z</t>
         </is>
       </c>
     </row>
@@ -8882,7 +8882,7 @@
       </c>
       <c r="K175" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:09Z</t>
+          <t>2026-09-18T22:43:52Z</t>
         </is>
       </c>
     </row>
@@ -8931,7 +8931,7 @@
       </c>
       <c r="K176" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:09Z</t>
+          <t>2026-09-18T22:43:52Z</t>
         </is>
       </c>
     </row>
@@ -8980,7 +8980,7 @@
       </c>
       <c r="K177" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:09Z</t>
+          <t>2026-09-18T22:43:52Z</t>
         </is>
       </c>
     </row>
@@ -9029,7 +9029,7 @@
       </c>
       <c r="K178" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:09Z</t>
+          <t>2026-09-18T22:43:52Z</t>
         </is>
       </c>
     </row>
@@ -9078,7 +9078,7 @@
       </c>
       <c r="K179" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:09Z</t>
+          <t>2026-09-18T22:43:52Z</t>
         </is>
       </c>
     </row>
@@ -9127,7 +9127,7 @@
       </c>
       <c r="K180" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:09Z</t>
+          <t>2026-09-18T22:43:52Z</t>
         </is>
       </c>
     </row>
@@ -9176,7 +9176,7 @@
       </c>
       <c r="K181" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:09Z</t>
+          <t>2026-09-18T22:43:52Z</t>
         </is>
       </c>
     </row>
@@ -9225,7 +9225,7 @@
       </c>
       <c r="K182" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:09Z</t>
+          <t>2026-09-18T22:43:52Z</t>
         </is>
       </c>
     </row>
@@ -9274,7 +9274,7 @@
       </c>
       <c r="K183" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:09Z</t>
+          <t>2026-09-18T22:43:52Z</t>
         </is>
       </c>
     </row>
@@ -9323,7 +9323,7 @@
       </c>
       <c r="K184" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:09Z</t>
+          <t>2026-09-18T22:43:52Z</t>
         </is>
       </c>
     </row>
@@ -9372,7 +9372,7 @@
       </c>
       <c r="K185" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:09Z</t>
+          <t>2026-09-18T22:43:52Z</t>
         </is>
       </c>
     </row>
@@ -9421,7 +9421,7 @@
       </c>
       <c r="K186" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:09Z</t>
+          <t>2026-09-18T22:43:52Z</t>
         </is>
       </c>
     </row>
@@ -9470,7 +9470,7 @@
       </c>
       <c r="K187" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:09Z</t>
+          <t>2026-09-18T22:43:52Z</t>
         </is>
       </c>
     </row>
@@ -9519,7 +9519,7 @@
       </c>
       <c r="K188" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:09Z</t>
+          <t>2026-09-18T22:43:52Z</t>
         </is>
       </c>
     </row>
@@ -9568,7 +9568,7 @@
       </c>
       <c r="K189" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:09Z</t>
+          <t>2026-09-18T22:43:52Z</t>
         </is>
       </c>
     </row>
@@ -9617,7 +9617,7 @@
       </c>
       <c r="K190" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:09Z</t>
+          <t>2026-09-18T22:43:52Z</t>
         </is>
       </c>
     </row>
@@ -9666,7 +9666,7 @@
       </c>
       <c r="K191" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:09Z</t>
+          <t>2026-09-18T22:43:52Z</t>
         </is>
       </c>
     </row>
@@ -9715,7 +9715,7 @@
       </c>
       <c r="K192" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:09Z</t>
+          <t>2026-09-18T22:43:52Z</t>
         </is>
       </c>
     </row>
@@ -9764,7 +9764,7 @@
       </c>
       <c r="K193" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:09Z</t>
+          <t>2026-09-18T22:43:52Z</t>
         </is>
       </c>
     </row>
@@ -9813,7 +9813,7 @@
       </c>
       <c r="K194" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:09Z</t>
+          <t>2026-09-18T22:43:52Z</t>
         </is>
       </c>
     </row>
@@ -9862,7 +9862,7 @@
       </c>
       <c r="K195" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:09Z</t>
+          <t>2026-09-18T22:43:52Z</t>
         </is>
       </c>
     </row>
@@ -9911,7 +9911,7 @@
       </c>
       <c r="K196" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:09Z</t>
+          <t>2026-09-18T22:43:52Z</t>
         </is>
       </c>
     </row>
@@ -9960,7 +9960,7 @@
       </c>
       <c r="K197" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:09Z</t>
+          <t>2026-09-18T22:43:52Z</t>
         </is>
       </c>
     </row>
@@ -10009,7 +10009,7 @@
       </c>
       <c r="K198" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:09Z</t>
+          <t>2026-09-18T22:43:52Z</t>
         </is>
       </c>
     </row>
@@ -10058,7 +10058,7 @@
       </c>
       <c r="K199" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:09Z</t>
+          <t>2026-09-18T22:43:52Z</t>
         </is>
       </c>
     </row>
@@ -10107,7 +10107,7 @@
       </c>
       <c r="K200" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:09Z</t>
+          <t>2026-09-18T22:43:52Z</t>
         </is>
       </c>
     </row>
@@ -10156,7 +10156,7 @@
       </c>
       <c r="K201" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:09Z</t>
+          <t>2026-09-18T22:43:52Z</t>
         </is>
       </c>
     </row>
@@ -10205,7 +10205,7 @@
       </c>
       <c r="K202" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:09Z</t>
+          <t>2026-09-18T22:43:52Z</t>
         </is>
       </c>
     </row>
@@ -10254,7 +10254,7 @@
       </c>
       <c r="K203" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:09Z</t>
+          <t>2026-09-18T22:43:52Z</t>
         </is>
       </c>
     </row>
@@ -10303,7 +10303,7 @@
       </c>
       <c r="K204" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:09Z</t>
+          <t>2026-09-18T22:43:52Z</t>
         </is>
       </c>
     </row>
@@ -10352,7 +10352,7 @@
       </c>
       <c r="K205" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:09Z</t>
+          <t>2026-09-18T22:43:52Z</t>
         </is>
       </c>
     </row>
@@ -10401,7 +10401,7 @@
       </c>
       <c r="K206" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:09Z</t>
+          <t>2026-09-18T22:43:52Z</t>
         </is>
       </c>
     </row>
@@ -10450,7 +10450,7 @@
       </c>
       <c r="K207" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:09Z</t>
+          <t>2026-09-18T22:43:52Z</t>
         </is>
       </c>
     </row>
@@ -10499,7 +10499,7 @@
       </c>
       <c r="K208" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:09Z</t>
+          <t>2026-09-18T22:43:52Z</t>
         </is>
       </c>
     </row>
@@ -10548,7 +10548,7 @@
       </c>
       <c r="K209" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:09Z</t>
+          <t>2026-09-18T22:43:52Z</t>
         </is>
       </c>
     </row>
@@ -10597,7 +10597,7 @@
       </c>
       <c r="K210" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:09Z</t>
+          <t>2026-09-18T22:43:52Z</t>
         </is>
       </c>
     </row>
@@ -10646,7 +10646,7 @@
       </c>
       <c r="K211" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:09Z</t>
+          <t>2026-09-18T22:43:52Z</t>
         </is>
       </c>
     </row>
@@ -10695,7 +10695,7 @@
       </c>
       <c r="K212" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:09Z</t>
+          <t>2026-09-18T22:43:52Z</t>
         </is>
       </c>
     </row>
@@ -10744,7 +10744,7 @@
       </c>
       <c r="K213" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:09Z</t>
+          <t>2026-09-18T22:43:52Z</t>
         </is>
       </c>
     </row>
@@ -10793,7 +10793,7 @@
       </c>
       <c r="K214" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:09Z</t>
+          <t>2026-09-18T22:43:52Z</t>
         </is>
       </c>
     </row>
@@ -10842,7 +10842,7 @@
       </c>
       <c r="K215" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:09Z</t>
+          <t>2026-09-18T22:43:52Z</t>
         </is>
       </c>
     </row>
@@ -10891,7 +10891,7 @@
       </c>
       <c r="K216" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:09Z</t>
+          <t>2026-09-18T22:43:52Z</t>
         </is>
       </c>
     </row>
@@ -10940,7 +10940,7 @@
       </c>
       <c r="K217" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:09Z</t>
+          <t>2026-09-18T22:43:52Z</t>
         </is>
       </c>
     </row>
@@ -10989,7 +10989,7 @@
       </c>
       <c r="K218" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:09Z</t>
+          <t>2026-09-18T22:43:52Z</t>
         </is>
       </c>
     </row>
@@ -11038,7 +11038,7 @@
       </c>
       <c r="K219" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:09Z</t>
+          <t>2026-09-18T22:43:52Z</t>
         </is>
       </c>
     </row>
@@ -11087,7 +11087,7 @@
       </c>
       <c r="K220" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:09Z</t>
+          <t>2026-09-18T22:43:52Z</t>
         </is>
       </c>
     </row>
@@ -11136,7 +11136,7 @@
       </c>
       <c r="K221" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:09Z</t>
+          <t>2026-09-18T22:43:52Z</t>
         </is>
       </c>
     </row>
@@ -11185,7 +11185,7 @@
       </c>
       <c r="K222" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:09Z</t>
+          <t>2026-09-18T22:43:52Z</t>
         </is>
       </c>
     </row>
@@ -11234,7 +11234,7 @@
       </c>
       <c r="K223" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:09Z</t>
+          <t>2026-09-18T22:43:52Z</t>
         </is>
       </c>
     </row>
@@ -11283,7 +11283,7 @@
       </c>
       <c r="K224" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:09Z</t>
+          <t>2026-09-18T22:43:52Z</t>
         </is>
       </c>
     </row>
@@ -11332,7 +11332,7 @@
       </c>
       <c r="K225" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:09Z</t>
+          <t>2026-09-18T22:43:52Z</t>
         </is>
       </c>
     </row>
@@ -11381,7 +11381,7 @@
       </c>
       <c r="K226" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:09Z</t>
+          <t>2026-09-18T22:43:52Z</t>
         </is>
       </c>
     </row>
@@ -11430,7 +11430,7 @@
       </c>
       <c r="K227" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:09Z</t>
+          <t>2026-09-18T22:43:52Z</t>
         </is>
       </c>
     </row>
@@ -11479,7 +11479,7 @@
       </c>
       <c r="K228" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:09Z</t>
+          <t>2026-09-18T22:43:52Z</t>
         </is>
       </c>
     </row>
@@ -11528,7 +11528,7 @@
       </c>
       <c r="K229" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:09Z</t>
+          <t>2026-09-18T22:43:52Z</t>
         </is>
       </c>
     </row>
@@ -11577,7 +11577,7 @@
       </c>
       <c r="K230" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:09Z</t>
+          <t>2026-09-18T22:43:52Z</t>
         </is>
       </c>
     </row>
@@ -11626,7 +11626,7 @@
       </c>
       <c r="K231" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:09Z</t>
+          <t>2026-09-18T22:43:52Z</t>
         </is>
       </c>
     </row>
@@ -11758,7 +11758,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:09Z</t>
+          <t>2026-09-18T22:43:52Z</t>
         </is>
       </c>
     </row>
@@ -11804,7 +11804,7 @@
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>{"date": "2026-08-01", "year": 2026, "month": 8, "month_name": "Agosto", "index_value": 637409769724325.1, "monthly_variation_pct": 8.9, "unit": "Índice base diciembre 2007=100 y variación mensual %", "frequency": "monthly", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/precios_consumidor/4_5_7_2.xls", "fetched_at": "2026-09-17T22:58:09Z"}</t>
+          <t>{"date": "2026-08-01", "year": 2026, "month": 8, "month_name": "Agosto", "index_value": 637409769724325.1, "monthly_variation_pct": 8.9, "unit": "Índice base diciembre 2007=100 y variación mensual %", "frequency": "monthly", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/precios_consumidor/4_5_7_2.xls", "fetched_at": "2026-09-18T22:43:52Z"}</t>
         </is>
       </c>
     </row>

--- a/assets/data/bcv/excel/ove_bcv_inpc_nacional_mensual.xlsx
+++ b/assets/data/bcv/excel/ove_bcv_inpc_nacional_mensual.xlsx
@@ -650,7 +650,7 @@
       </c>
       <c r="K7" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:52Z</t>
+          <t>2026-09-19T22:23:11Z</t>
         </is>
       </c>
     </row>
@@ -699,7 +699,7 @@
       </c>
       <c r="K8" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:52Z</t>
+          <t>2026-09-19T22:23:11Z</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="K9" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:52Z</t>
+          <t>2026-09-19T22:23:11Z</t>
         </is>
       </c>
     </row>
@@ -797,7 +797,7 @@
       </c>
       <c r="K10" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:52Z</t>
+          <t>2026-09-19T22:23:11Z</t>
         </is>
       </c>
     </row>
@@ -846,7 +846,7 @@
       </c>
       <c r="K11" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:52Z</t>
+          <t>2026-09-19T22:23:11Z</t>
         </is>
       </c>
     </row>
@@ -895,7 +895,7 @@
       </c>
       <c r="K12" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:52Z</t>
+          <t>2026-09-19T22:23:11Z</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="K13" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:52Z</t>
+          <t>2026-09-19T22:23:11Z</t>
         </is>
       </c>
     </row>
@@ -993,7 +993,7 @@
       </c>
       <c r="K14" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:52Z</t>
+          <t>2026-09-19T22:23:11Z</t>
         </is>
       </c>
     </row>
@@ -1042,7 +1042,7 @@
       </c>
       <c r="K15" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:52Z</t>
+          <t>2026-09-19T22:23:11Z</t>
         </is>
       </c>
     </row>
@@ -1091,7 +1091,7 @@
       </c>
       <c r="K16" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:52Z</t>
+          <t>2026-09-19T22:23:11Z</t>
         </is>
       </c>
     </row>
@@ -1140,7 +1140,7 @@
       </c>
       <c r="K17" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:52Z</t>
+          <t>2026-09-19T22:23:11Z</t>
         </is>
       </c>
     </row>
@@ -1189,7 +1189,7 @@
       </c>
       <c r="K18" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:52Z</t>
+          <t>2026-09-19T22:23:11Z</t>
         </is>
       </c>
     </row>
@@ -1238,7 +1238,7 @@
       </c>
       <c r="K19" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:52Z</t>
+          <t>2026-09-19T22:23:11Z</t>
         </is>
       </c>
     </row>
@@ -1287,7 +1287,7 @@
       </c>
       <c r="K20" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:52Z</t>
+          <t>2026-09-19T22:23:11Z</t>
         </is>
       </c>
     </row>
@@ -1336,7 +1336,7 @@
       </c>
       <c r="K21" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:52Z</t>
+          <t>2026-09-19T22:23:11Z</t>
         </is>
       </c>
     </row>
@@ -1385,7 +1385,7 @@
       </c>
       <c r="K22" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:52Z</t>
+          <t>2026-09-19T22:23:11Z</t>
         </is>
       </c>
     </row>
@@ -1434,7 +1434,7 @@
       </c>
       <c r="K23" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:52Z</t>
+          <t>2026-09-19T22:23:11Z</t>
         </is>
       </c>
     </row>
@@ -1483,7 +1483,7 @@
       </c>
       <c r="K24" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:52Z</t>
+          <t>2026-09-19T22:23:11Z</t>
         </is>
       </c>
     </row>
@@ -1532,7 +1532,7 @@
       </c>
       <c r="K25" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:52Z</t>
+          <t>2026-09-19T22:23:11Z</t>
         </is>
       </c>
     </row>
@@ -1581,7 +1581,7 @@
       </c>
       <c r="K26" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:52Z</t>
+          <t>2026-09-19T22:23:11Z</t>
         </is>
       </c>
     </row>
@@ -1630,7 +1630,7 @@
       </c>
       <c r="K27" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:52Z</t>
+          <t>2026-09-19T22:23:11Z</t>
         </is>
       </c>
     </row>
@@ -1679,7 +1679,7 @@
       </c>
       <c r="K28" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:52Z</t>
+          <t>2026-09-19T22:23:11Z</t>
         </is>
       </c>
     </row>
@@ -1728,7 +1728,7 @@
       </c>
       <c r="K29" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:52Z</t>
+          <t>2026-09-19T22:23:11Z</t>
         </is>
       </c>
     </row>
@@ -1777,7 +1777,7 @@
       </c>
       <c r="K30" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:52Z</t>
+          <t>2026-09-19T22:23:11Z</t>
         </is>
       </c>
     </row>
@@ -1826,7 +1826,7 @@
       </c>
       <c r="K31" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:52Z</t>
+          <t>2026-09-19T22:23:11Z</t>
         </is>
       </c>
     </row>
@@ -1875,7 +1875,7 @@
       </c>
       <c r="K32" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:52Z</t>
+          <t>2026-09-19T22:23:11Z</t>
         </is>
       </c>
     </row>
@@ -1924,7 +1924,7 @@
       </c>
       <c r="K33" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:52Z</t>
+          <t>2026-09-19T22:23:11Z</t>
         </is>
       </c>
     </row>
@@ -1973,7 +1973,7 @@
       </c>
       <c r="K34" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:52Z</t>
+          <t>2026-09-19T22:23:11Z</t>
         </is>
       </c>
     </row>
@@ -2022,7 +2022,7 @@
       </c>
       <c r="K35" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:52Z</t>
+          <t>2026-09-19T22:23:11Z</t>
         </is>
       </c>
     </row>
@@ -2071,7 +2071,7 @@
       </c>
       <c r="K36" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:52Z</t>
+          <t>2026-09-19T22:23:11Z</t>
         </is>
       </c>
     </row>
@@ -2120,7 +2120,7 @@
       </c>
       <c r="K37" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:52Z</t>
+          <t>2026-09-19T22:23:11Z</t>
         </is>
       </c>
     </row>
@@ -2169,7 +2169,7 @@
       </c>
       <c r="K38" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:52Z</t>
+          <t>2026-09-19T22:23:11Z</t>
         </is>
       </c>
     </row>
@@ -2218,7 +2218,7 @@
       </c>
       <c r="K39" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:52Z</t>
+          <t>2026-09-19T22:23:11Z</t>
         </is>
       </c>
     </row>
@@ -2267,7 +2267,7 @@
       </c>
       <c r="K40" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:52Z</t>
+          <t>2026-09-19T22:23:11Z</t>
         </is>
       </c>
     </row>
@@ -2316,7 +2316,7 @@
       </c>
       <c r="K41" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:52Z</t>
+          <t>2026-09-19T22:23:11Z</t>
         </is>
       </c>
     </row>
@@ -2365,7 +2365,7 @@
       </c>
       <c r="K42" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:52Z</t>
+          <t>2026-09-19T22:23:11Z</t>
         </is>
       </c>
     </row>
@@ -2414,7 +2414,7 @@
       </c>
       <c r="K43" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:52Z</t>
+          <t>2026-09-19T22:23:11Z</t>
         </is>
       </c>
     </row>
@@ -2463,7 +2463,7 @@
       </c>
       <c r="K44" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:52Z</t>
+          <t>2026-09-19T22:23:11Z</t>
         </is>
       </c>
     </row>
@@ -2512,7 +2512,7 @@
       </c>
       <c r="K45" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:52Z</t>
+          <t>2026-09-19T22:23:11Z</t>
         </is>
       </c>
     </row>
@@ -2561,7 +2561,7 @@
       </c>
       <c r="K46" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:52Z</t>
+          <t>2026-09-19T22:23:11Z</t>
         </is>
       </c>
     </row>
@@ -2610,7 +2610,7 @@
       </c>
       <c r="K47" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:52Z</t>
+          <t>2026-09-19T22:23:11Z</t>
         </is>
       </c>
     </row>
@@ -2659,7 +2659,7 @@
       </c>
       <c r="K48" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:52Z</t>
+          <t>2026-09-19T22:23:11Z</t>
         </is>
       </c>
     </row>
@@ -2708,7 +2708,7 @@
       </c>
       <c r="K49" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:52Z</t>
+          <t>2026-09-19T22:23:11Z</t>
         </is>
       </c>
     </row>
@@ -2757,7 +2757,7 @@
       </c>
       <c r="K50" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:52Z</t>
+          <t>2026-09-19T22:23:11Z</t>
         </is>
       </c>
     </row>
@@ -2806,7 +2806,7 @@
       </c>
       <c r="K51" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:52Z</t>
+          <t>2026-09-19T22:23:11Z</t>
         </is>
       </c>
     </row>
@@ -2855,7 +2855,7 @@
       </c>
       <c r="K52" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:52Z</t>
+          <t>2026-09-19T22:23:11Z</t>
         </is>
       </c>
     </row>
@@ -2904,7 +2904,7 @@
       </c>
       <c r="K53" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:52Z</t>
+          <t>2026-09-19T22:23:11Z</t>
         </is>
       </c>
     </row>
@@ -2953,7 +2953,7 @@
       </c>
       <c r="K54" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:52Z</t>
+          <t>2026-09-19T22:23:11Z</t>
         </is>
       </c>
     </row>
@@ -3002,7 +3002,7 @@
       </c>
       <c r="K55" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:52Z</t>
+          <t>2026-09-19T22:23:11Z</t>
         </is>
       </c>
     </row>
@@ -3051,7 +3051,7 @@
       </c>
       <c r="K56" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:52Z</t>
+          <t>2026-09-19T22:23:11Z</t>
         </is>
       </c>
     </row>
@@ -3100,7 +3100,7 @@
       </c>
       <c r="K57" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:52Z</t>
+          <t>2026-09-19T22:23:11Z</t>
         </is>
       </c>
     </row>
@@ -3149,7 +3149,7 @@
       </c>
       <c r="K58" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:52Z</t>
+          <t>2026-09-19T22:23:11Z</t>
         </is>
       </c>
     </row>
@@ -3198,7 +3198,7 @@
       </c>
       <c r="K59" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:52Z</t>
+          <t>2026-09-19T22:23:11Z</t>
         </is>
       </c>
     </row>
@@ -3247,7 +3247,7 @@
       </c>
       <c r="K60" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:52Z</t>
+          <t>2026-09-19T22:23:11Z</t>
         </is>
       </c>
     </row>
@@ -3296,7 +3296,7 @@
       </c>
       <c r="K61" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:52Z</t>
+          <t>2026-09-19T22:23:11Z</t>
         </is>
       </c>
     </row>
@@ -3345,7 +3345,7 @@
       </c>
       <c r="K62" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:52Z</t>
+          <t>2026-09-19T22:23:11Z</t>
         </is>
       </c>
     </row>
@@ -3394,7 +3394,7 @@
       </c>
       <c r="K63" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:52Z</t>
+          <t>2026-09-19T22:23:11Z</t>
         </is>
       </c>
     </row>
@@ -3443,7 +3443,7 @@
       </c>
       <c r="K64" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:52Z</t>
+          <t>2026-09-19T22:23:11Z</t>
         </is>
       </c>
     </row>
@@ -3492,7 +3492,7 @@
       </c>
       <c r="K65" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:52Z</t>
+          <t>2026-09-19T22:23:11Z</t>
         </is>
       </c>
     </row>
@@ -3541,7 +3541,7 @@
       </c>
       <c r="K66" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:52Z</t>
+          <t>2026-09-19T22:23:11Z</t>
         </is>
       </c>
     </row>
@@ -3590,7 +3590,7 @@
       </c>
       <c r="K67" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:52Z</t>
+          <t>2026-09-19T22:23:11Z</t>
         </is>
       </c>
     </row>
@@ -3639,7 +3639,7 @@
       </c>
       <c r="K68" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:52Z</t>
+          <t>2026-09-19T22:23:11Z</t>
         </is>
       </c>
     </row>
@@ -3688,7 +3688,7 @@
       </c>
       <c r="K69" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:52Z</t>
+          <t>2026-09-19T22:23:11Z</t>
         </is>
       </c>
     </row>
@@ -3737,7 +3737,7 @@
       </c>
       <c r="K70" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:52Z</t>
+          <t>2026-09-19T22:23:11Z</t>
         </is>
       </c>
     </row>
@@ -3786,7 +3786,7 @@
       </c>
       <c r="K71" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:52Z</t>
+          <t>2026-09-19T22:23:11Z</t>
         </is>
       </c>
     </row>
@@ -3835,7 +3835,7 @@
       </c>
       <c r="K72" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:52Z</t>
+          <t>2026-09-19T22:23:11Z</t>
         </is>
       </c>
     </row>
@@ -3884,7 +3884,7 @@
       </c>
       <c r="K73" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:52Z</t>
+          <t>2026-09-19T22:23:11Z</t>
         </is>
       </c>
     </row>
@@ -3933,7 +3933,7 @@
       </c>
       <c r="K74" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:52Z</t>
+          <t>2026-09-19T22:23:11Z</t>
         </is>
       </c>
     </row>
@@ -3982,7 +3982,7 @@
       </c>
       <c r="K75" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:52Z</t>
+          <t>2026-09-19T22:23:11Z</t>
         </is>
       </c>
     </row>
@@ -4031,7 +4031,7 @@
       </c>
       <c r="K76" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:52Z</t>
+          <t>2026-09-19T22:23:11Z</t>
         </is>
       </c>
     </row>
@@ -4080,7 +4080,7 @@
       </c>
       <c r="K77" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:52Z</t>
+          <t>2026-09-19T22:23:11Z</t>
         </is>
       </c>
     </row>
@@ -4129,7 +4129,7 @@
       </c>
       <c r="K78" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:52Z</t>
+          <t>2026-09-19T22:23:11Z</t>
         </is>
       </c>
     </row>
@@ -4178,7 +4178,7 @@
       </c>
       <c r="K79" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:52Z</t>
+          <t>2026-09-19T22:23:11Z</t>
         </is>
       </c>
     </row>
@@ -4227,7 +4227,7 @@
       </c>
       <c r="K80" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:52Z</t>
+          <t>2026-09-19T22:23:11Z</t>
         </is>
       </c>
     </row>
@@ -4276,7 +4276,7 @@
       </c>
       <c r="K81" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:52Z</t>
+          <t>2026-09-19T22:23:11Z</t>
         </is>
       </c>
     </row>
@@ -4325,7 +4325,7 @@
       </c>
       <c r="K82" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:52Z</t>
+          <t>2026-09-19T22:23:11Z</t>
         </is>
       </c>
     </row>
@@ -4374,7 +4374,7 @@
       </c>
       <c r="K83" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:52Z</t>
+          <t>2026-09-19T22:23:11Z</t>
         </is>
       </c>
     </row>
@@ -4423,7 +4423,7 @@
       </c>
       <c r="K84" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:52Z</t>
+          <t>2026-09-19T22:23:11Z</t>
         </is>
       </c>
     </row>
@@ -4472,7 +4472,7 @@
       </c>
       <c r="K85" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:52Z</t>
+          <t>2026-09-19T22:23:11Z</t>
         </is>
       </c>
     </row>
@@ -4521,7 +4521,7 @@
       </c>
       <c r="K86" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:52Z</t>
+          <t>2026-09-19T22:23:11Z</t>
         </is>
       </c>
     </row>
@@ -4570,7 +4570,7 @@
       </c>
       <c r="K87" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:52Z</t>
+          <t>2026-09-19T22:23:11Z</t>
         </is>
       </c>
     </row>
@@ -4619,7 +4619,7 @@
       </c>
       <c r="K88" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:52Z</t>
+          <t>2026-09-19T22:23:11Z</t>
         </is>
       </c>
     </row>
@@ -4668,7 +4668,7 @@
       </c>
       <c r="K89" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:52Z</t>
+          <t>2026-09-19T22:23:11Z</t>
         </is>
       </c>
     </row>
@@ -4717,7 +4717,7 @@
       </c>
       <c r="K90" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:52Z</t>
+          <t>2026-09-19T22:23:11Z</t>
         </is>
       </c>
     </row>
@@ -4766,7 +4766,7 @@
       </c>
       <c r="K91" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:52Z</t>
+          <t>2026-09-19T22:23:11Z</t>
         </is>
       </c>
     </row>
@@ -4815,7 +4815,7 @@
       </c>
       <c r="K92" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:52Z</t>
+          <t>2026-09-19T22:23:11Z</t>
         </is>
       </c>
     </row>
@@ -4864,7 +4864,7 @@
       </c>
       <c r="K93" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:52Z</t>
+          <t>2026-09-19T22:23:11Z</t>
         </is>
       </c>
     </row>
@@ -4913,7 +4913,7 @@
       </c>
       <c r="K94" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:52Z</t>
+          <t>2026-09-19T22:23:11Z</t>
         </is>
       </c>
     </row>
@@ -4962,7 +4962,7 @@
       </c>
       <c r="K95" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:52Z</t>
+          <t>2026-09-19T22:23:11Z</t>
         </is>
       </c>
     </row>
@@ -5011,7 +5011,7 @@
       </c>
       <c r="K96" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:52Z</t>
+          <t>2026-09-19T22:23:11Z</t>
         </is>
       </c>
     </row>
@@ -5060,7 +5060,7 @@
       </c>
       <c r="K97" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:52Z</t>
+          <t>2026-09-19T22:23:11Z</t>
         </is>
       </c>
     </row>
@@ -5109,7 +5109,7 @@
       </c>
       <c r="K98" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:52Z</t>
+          <t>2026-09-19T22:23:11Z</t>
         </is>
       </c>
     </row>
@@ -5158,7 +5158,7 @@
       </c>
       <c r="K99" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:52Z</t>
+          <t>2026-09-19T22:23:11Z</t>
         </is>
       </c>
     </row>
@@ -5207,7 +5207,7 @@
       </c>
       <c r="K100" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:52Z</t>
+          <t>2026-09-19T22:23:11Z</t>
         </is>
       </c>
     </row>
@@ -5256,7 +5256,7 @@
       </c>
       <c r="K101" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:52Z</t>
+          <t>2026-09-19T22:23:11Z</t>
         </is>
       </c>
     </row>
@@ -5305,7 +5305,7 @@
       </c>
       <c r="K102" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:52Z</t>
+          <t>2026-09-19T22:23:11Z</t>
         </is>
       </c>
     </row>
@@ -5354,7 +5354,7 @@
       </c>
       <c r="K103" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:52Z</t>
+          <t>2026-09-19T22:23:11Z</t>
         </is>
       </c>
     </row>
@@ -5403,7 +5403,7 @@
       </c>
       <c r="K104" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:52Z</t>
+          <t>2026-09-19T22:23:11Z</t>
         </is>
       </c>
     </row>
@@ -5452,7 +5452,7 @@
       </c>
       <c r="K105" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:52Z</t>
+          <t>2026-09-19T22:23:11Z</t>
         </is>
       </c>
     </row>
@@ -5501,7 +5501,7 @@
       </c>
       <c r="K106" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:52Z</t>
+          <t>2026-09-19T22:23:11Z</t>
         </is>
       </c>
     </row>
@@ -5550,7 +5550,7 @@
       </c>
       <c r="K107" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:52Z</t>
+          <t>2026-09-19T22:23:11Z</t>
         </is>
       </c>
     </row>
@@ -5599,7 +5599,7 @@
       </c>
       <c r="K108" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:52Z</t>
+          <t>2026-09-19T22:23:11Z</t>
         </is>
       </c>
     </row>
@@ -5648,7 +5648,7 @@
       </c>
       <c r="K109" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:52Z</t>
+          <t>2026-09-19T22:23:11Z</t>
         </is>
       </c>
     </row>
@@ -5697,7 +5697,7 @@
       </c>
       <c r="K110" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:52Z</t>
+          <t>2026-09-19T22:23:11Z</t>
         </is>
       </c>
     </row>
@@ -5746,7 +5746,7 @@
       </c>
       <c r="K111" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:52Z</t>
+          <t>2026-09-19T22:23:11Z</t>
         </is>
       </c>
     </row>
@@ -5795,7 +5795,7 @@
       </c>
       <c r="K112" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:52Z</t>
+          <t>2026-09-19T22:23:11Z</t>
         </is>
       </c>
     </row>
@@ -5844,7 +5844,7 @@
       </c>
       <c r="K113" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:52Z</t>
+          <t>2026-09-19T22:23:11Z</t>
         </is>
       </c>
     </row>
@@ -5893,7 +5893,7 @@
       </c>
       <c r="K114" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:52Z</t>
+          <t>2026-09-19T22:23:11Z</t>
         </is>
       </c>
     </row>
@@ -5942,7 +5942,7 @@
       </c>
       <c r="K115" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:52Z</t>
+          <t>2026-09-19T22:23:11Z</t>
         </is>
       </c>
     </row>
@@ -5991,7 +5991,7 @@
       </c>
       <c r="K116" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:52Z</t>
+          <t>2026-09-19T22:23:11Z</t>
         </is>
       </c>
     </row>
@@ -6040,7 +6040,7 @@
       </c>
       <c r="K117" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:52Z</t>
+          <t>2026-09-19T22:23:11Z</t>
         </is>
       </c>
     </row>
@@ -6089,7 +6089,7 @@
       </c>
       <c r="K118" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:52Z</t>
+          <t>2026-09-19T22:23:11Z</t>
         </is>
       </c>
     </row>
@@ -6138,7 +6138,7 @@
       </c>
       <c r="K119" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:52Z</t>
+          <t>2026-09-19T22:23:11Z</t>
         </is>
       </c>
     </row>
@@ -6187,7 +6187,7 @@
       </c>
       <c r="K120" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:52Z</t>
+          <t>2026-09-19T22:23:11Z</t>
         </is>
       </c>
     </row>
@@ -6236,7 +6236,7 @@
       </c>
       <c r="K121" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:52Z</t>
+          <t>2026-09-19T22:23:11Z</t>
         </is>
       </c>
     </row>
@@ -6285,7 +6285,7 @@
       </c>
       <c r="K122" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:52Z</t>
+          <t>2026-09-19T22:23:11Z</t>
         </is>
       </c>
     </row>
@@ -6334,7 +6334,7 @@
       </c>
       <c r="K123" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:52Z</t>
+          <t>2026-09-19T22:23:11Z</t>
         </is>
       </c>
     </row>
@@ -6383,7 +6383,7 @@
       </c>
       <c r="K124" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:52Z</t>
+          <t>2026-09-19T22:23:11Z</t>
         </is>
       </c>
     </row>
@@ -6432,7 +6432,7 @@
       </c>
       <c r="K125" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:52Z</t>
+          <t>2026-09-19T22:23:11Z</t>
         </is>
       </c>
     </row>
@@ -6481,7 +6481,7 @@
       </c>
       <c r="K126" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:52Z</t>
+          <t>2026-09-19T22:23:11Z</t>
         </is>
       </c>
     </row>
@@ -6530,7 +6530,7 @@
       </c>
       <c r="K127" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:52Z</t>
+          <t>2026-09-19T22:23:11Z</t>
         </is>
       </c>
     </row>
@@ -6579,7 +6579,7 @@
       </c>
       <c r="K128" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:52Z</t>
+          <t>2026-09-19T22:23:11Z</t>
         </is>
       </c>
     </row>
@@ -6628,7 +6628,7 @@
       </c>
       <c r="K129" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:52Z</t>
+          <t>2026-09-19T22:23:11Z</t>
         </is>
       </c>
     </row>
@@ -6677,7 +6677,7 @@
       </c>
       <c r="K130" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:52Z</t>
+          <t>2026-09-19T22:23:11Z</t>
         </is>
       </c>
     </row>
@@ -6726,7 +6726,7 @@
       </c>
       <c r="K131" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:52Z</t>
+          <t>2026-09-19T22:23:11Z</t>
         </is>
       </c>
     </row>
@@ -6775,7 +6775,7 @@
       </c>
       <c r="K132" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:52Z</t>
+          <t>2026-09-19T22:23:11Z</t>
         </is>
       </c>
     </row>
@@ -6824,7 +6824,7 @@
       </c>
       <c r="K133" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:52Z</t>
+          <t>2026-09-19T22:23:11Z</t>
         </is>
       </c>
     </row>
@@ -6873,7 +6873,7 @@
       </c>
       <c r="K134" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:52Z</t>
+          <t>2026-09-19T22:23:11Z</t>
         </is>
       </c>
     </row>
@@ -6922,7 +6922,7 @@
       </c>
       <c r="K135" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:52Z</t>
+          <t>2026-09-19T22:23:11Z</t>
         </is>
       </c>
     </row>
@@ -6971,7 +6971,7 @@
       </c>
       <c r="K136" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:52Z</t>
+          <t>2026-09-19T22:23:11Z</t>
         </is>
       </c>
     </row>
@@ -7020,7 +7020,7 @@
       </c>
       <c r="K137" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:52Z</t>
+          <t>2026-09-19T22:23:11Z</t>
         </is>
       </c>
     </row>
@@ -7069,7 +7069,7 @@
       </c>
       <c r="K138" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:52Z</t>
+          <t>2026-09-19T22:23:11Z</t>
         </is>
       </c>
     </row>
@@ -7118,7 +7118,7 @@
       </c>
       <c r="K139" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:52Z</t>
+          <t>2026-09-19T22:23:11Z</t>
         </is>
       </c>
     </row>
@@ -7167,7 +7167,7 @@
       </c>
       <c r="K140" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:52Z</t>
+          <t>2026-09-19T22:23:11Z</t>
         </is>
       </c>
     </row>
@@ -7216,7 +7216,7 @@
       </c>
       <c r="K141" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:52Z</t>
+          <t>2026-09-19T22:23:11Z</t>
         </is>
       </c>
     </row>
@@ -7265,7 +7265,7 @@
       </c>
       <c r="K142" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:52Z</t>
+          <t>2026-09-19T22:23:11Z</t>
         </is>
       </c>
     </row>
@@ -7314,7 +7314,7 @@
       </c>
       <c r="K143" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:52Z</t>
+          <t>2026-09-19T22:23:11Z</t>
         </is>
       </c>
     </row>
@@ -7363,7 +7363,7 @@
       </c>
       <c r="K144" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:52Z</t>
+          <t>2026-09-19T22:23:11Z</t>
         </is>
       </c>
     </row>
@@ -7412,7 +7412,7 @@
       </c>
       <c r="K145" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:52Z</t>
+          <t>2026-09-19T22:23:11Z</t>
         </is>
       </c>
     </row>
@@ -7461,7 +7461,7 @@
       </c>
       <c r="K146" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:52Z</t>
+          <t>2026-09-19T22:23:11Z</t>
         </is>
       </c>
     </row>
@@ -7510,7 +7510,7 @@
       </c>
       <c r="K147" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:52Z</t>
+          <t>2026-09-19T22:23:11Z</t>
         </is>
       </c>
     </row>
@@ -7559,7 +7559,7 @@
       </c>
       <c r="K148" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:52Z</t>
+          <t>2026-09-19T22:23:11Z</t>
         </is>
       </c>
     </row>
@@ -7608,7 +7608,7 @@
       </c>
       <c r="K149" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:52Z</t>
+          <t>2026-09-19T22:23:11Z</t>
         </is>
       </c>
     </row>
@@ -7657,7 +7657,7 @@
       </c>
       <c r="K150" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:52Z</t>
+          <t>2026-09-19T22:23:11Z</t>
         </is>
       </c>
     </row>
@@ -7706,7 +7706,7 @@
       </c>
       <c r="K151" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:52Z</t>
+          <t>2026-09-19T22:23:11Z</t>
         </is>
       </c>
     </row>
@@ -7755,7 +7755,7 @@
       </c>
       <c r="K152" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:52Z</t>
+          <t>2026-09-19T22:23:11Z</t>
         </is>
       </c>
     </row>
@@ -7804,7 +7804,7 @@
       </c>
       <c r="K153" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:52Z</t>
+          <t>2026-09-19T22:23:11Z</t>
         </is>
       </c>
     </row>
@@ -7853,7 +7853,7 @@
       </c>
       <c r="K154" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:52Z</t>
+          <t>2026-09-19T22:23:11Z</t>
         </is>
       </c>
     </row>
@@ -7902,7 +7902,7 @@
       </c>
       <c r="K155" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:52Z</t>
+          <t>2026-09-19T22:23:11Z</t>
         </is>
       </c>
     </row>
@@ -7951,7 +7951,7 @@
       </c>
       <c r="K156" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:52Z</t>
+          <t>2026-09-19T22:23:11Z</t>
         </is>
       </c>
     </row>
@@ -8000,7 +8000,7 @@
       </c>
       <c r="K157" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:52Z</t>
+          <t>2026-09-19T22:23:11Z</t>
         </is>
       </c>
     </row>
@@ -8049,7 +8049,7 @@
       </c>
       <c r="K158" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:52Z</t>
+          <t>2026-09-19T22:23:11Z</t>
         </is>
       </c>
     </row>
@@ -8098,7 +8098,7 @@
       </c>
       <c r="K159" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:52Z</t>
+          <t>2026-09-19T22:23:11Z</t>
         </is>
       </c>
     </row>
@@ -8147,7 +8147,7 @@
       </c>
       <c r="K160" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:52Z</t>
+          <t>2026-09-19T22:23:11Z</t>
         </is>
       </c>
     </row>
@@ -8196,7 +8196,7 @@
       </c>
       <c r="K161" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:52Z</t>
+          <t>2026-09-19T22:23:11Z</t>
         </is>
       </c>
     </row>
@@ -8245,7 +8245,7 @@
       </c>
       <c r="K162" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:52Z</t>
+          <t>2026-09-19T22:23:11Z</t>
         </is>
       </c>
     </row>
@@ -8294,7 +8294,7 @@
       </c>
       <c r="K163" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:52Z</t>
+          <t>2026-09-19T22:23:11Z</t>
         </is>
       </c>
     </row>
@@ -8343,7 +8343,7 @@
       </c>
       <c r="K164" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:52Z</t>
+          <t>2026-09-19T22:23:11Z</t>
         </is>
       </c>
     </row>
@@ -8392,7 +8392,7 @@
       </c>
       <c r="K165" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:52Z</t>
+          <t>2026-09-19T22:23:11Z</t>
         </is>
       </c>
     </row>
@@ -8441,7 +8441,7 @@
       </c>
       <c r="K166" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:52Z</t>
+          <t>2026-09-19T22:23:11Z</t>
         </is>
       </c>
     </row>
@@ -8490,7 +8490,7 @@
       </c>
       <c r="K167" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:52Z</t>
+          <t>2026-09-19T22:23:11Z</t>
         </is>
       </c>
     </row>
@@ -8539,7 +8539,7 @@
       </c>
       <c r="K168" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:52Z</t>
+          <t>2026-09-19T22:23:11Z</t>
         </is>
       </c>
     </row>
@@ -8588,7 +8588,7 @@
       </c>
       <c r="K169" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:52Z</t>
+          <t>2026-09-19T22:23:11Z</t>
         </is>
       </c>
     </row>
@@ -8637,7 +8637,7 @@
       </c>
       <c r="K170" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:52Z</t>
+          <t>2026-09-19T22:23:11Z</t>
         </is>
       </c>
     </row>
@@ -8686,7 +8686,7 @@
       </c>
       <c r="K171" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:52Z</t>
+          <t>2026-09-19T22:23:11Z</t>
         </is>
       </c>
     </row>
@@ -8735,7 +8735,7 @@
       </c>
       <c r="K172" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:52Z</t>
+          <t>2026-09-19T22:23:11Z</t>
         </is>
       </c>
     </row>
@@ -8784,7 +8784,7 @@
       </c>
       <c r="K173" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:52Z</t>
+          <t>2026-09-19T22:23:11Z</t>
         </is>
       </c>
     </row>
@@ -8833,7 +8833,7 @@
       </c>
       <c r="K174" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:52Z</t>
+          <t>2026-09-19T22:23:11Z</t>
         </is>
       </c>
     </row>
@@ -8882,7 +8882,7 @@
       </c>
       <c r="K175" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:52Z</t>
+          <t>2026-09-19T22:23:11Z</t>
         </is>
       </c>
     </row>
@@ -8931,7 +8931,7 @@
       </c>
       <c r="K176" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:52Z</t>
+          <t>2026-09-19T22:23:11Z</t>
         </is>
       </c>
     </row>
@@ -8980,7 +8980,7 @@
       </c>
       <c r="K177" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:52Z</t>
+          <t>2026-09-19T22:23:11Z</t>
         </is>
       </c>
     </row>
@@ -9029,7 +9029,7 @@
       </c>
       <c r="K178" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:52Z</t>
+          <t>2026-09-19T22:23:11Z</t>
         </is>
       </c>
     </row>
@@ -9078,7 +9078,7 @@
       </c>
       <c r="K179" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:52Z</t>
+          <t>2026-09-19T22:23:11Z</t>
         </is>
       </c>
     </row>
@@ -9127,7 +9127,7 @@
       </c>
       <c r="K180" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:52Z</t>
+          <t>2026-09-19T22:23:11Z</t>
         </is>
       </c>
     </row>
@@ -9176,7 +9176,7 @@
       </c>
       <c r="K181" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:52Z</t>
+          <t>2026-09-19T22:23:11Z</t>
         </is>
       </c>
     </row>
@@ -9225,7 +9225,7 @@
       </c>
       <c r="K182" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:52Z</t>
+          <t>2026-09-19T22:23:11Z</t>
         </is>
       </c>
     </row>
@@ -9274,7 +9274,7 @@
       </c>
       <c r="K183" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:52Z</t>
+          <t>2026-09-19T22:23:11Z</t>
         </is>
       </c>
     </row>
@@ -9323,7 +9323,7 @@
       </c>
       <c r="K184" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:52Z</t>
+          <t>2026-09-19T22:23:11Z</t>
         </is>
       </c>
     </row>
@@ -9372,7 +9372,7 @@
       </c>
       <c r="K185" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:52Z</t>
+          <t>2026-09-19T22:23:11Z</t>
         </is>
       </c>
     </row>
@@ -9421,7 +9421,7 @@
       </c>
       <c r="K186" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:52Z</t>
+          <t>2026-09-19T22:23:11Z</t>
         </is>
       </c>
     </row>
@@ -9470,7 +9470,7 @@
       </c>
       <c r="K187" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:52Z</t>
+          <t>2026-09-19T22:23:11Z</t>
         </is>
       </c>
     </row>
@@ -9519,7 +9519,7 @@
       </c>
       <c r="K188" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:52Z</t>
+          <t>2026-09-19T22:23:11Z</t>
         </is>
       </c>
     </row>
@@ -9568,7 +9568,7 @@
       </c>
       <c r="K189" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:52Z</t>
+          <t>2026-09-19T22:23:11Z</t>
         </is>
       </c>
     </row>
@@ -9617,7 +9617,7 @@
       </c>
       <c r="K190" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:52Z</t>
+          <t>2026-09-19T22:23:11Z</t>
         </is>
       </c>
     </row>
@@ -9666,7 +9666,7 @@
       </c>
       <c r="K191" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:52Z</t>
+          <t>2026-09-19T22:23:11Z</t>
         </is>
       </c>
     </row>
@@ -9715,7 +9715,7 @@
       </c>
       <c r="K192" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:52Z</t>
+          <t>2026-09-19T22:23:11Z</t>
         </is>
       </c>
     </row>
@@ -9764,7 +9764,7 @@
       </c>
       <c r="K193" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:52Z</t>
+          <t>2026-09-19T22:23:11Z</t>
         </is>
       </c>
     </row>
@@ -9813,7 +9813,7 @@
       </c>
       <c r="K194" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:52Z</t>
+          <t>2026-09-19T22:23:11Z</t>
         </is>
       </c>
     </row>
@@ -9862,7 +9862,7 @@
       </c>
       <c r="K195" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:52Z</t>
+          <t>2026-09-19T22:23:11Z</t>
         </is>
       </c>
     </row>
@@ -9911,7 +9911,7 @@
       </c>
       <c r="K196" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:52Z</t>
+          <t>2026-09-19T22:23:11Z</t>
         </is>
       </c>
     </row>
@@ -9960,7 +9960,7 @@
       </c>
       <c r="K197" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:52Z</t>
+          <t>2026-09-19T22:23:11Z</t>
         </is>
       </c>
     </row>
@@ -10009,7 +10009,7 @@
       </c>
       <c r="K198" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:52Z</t>
+          <t>2026-09-19T22:23:11Z</t>
         </is>
       </c>
     </row>
@@ -10058,7 +10058,7 @@
       </c>
       <c r="K199" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:52Z</t>
+          <t>2026-09-19T22:23:11Z</t>
         </is>
       </c>
     </row>
@@ -10107,7 +10107,7 @@
       </c>
       <c r="K200" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:52Z</t>
+          <t>2026-09-19T22:23:11Z</t>
         </is>
       </c>
     </row>
@@ -10156,7 +10156,7 @@
       </c>
       <c r="K201" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:52Z</t>
+          <t>2026-09-19T22:23:11Z</t>
         </is>
       </c>
     </row>
@@ -10205,7 +10205,7 @@
       </c>
       <c r="K202" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:52Z</t>
+          <t>2026-09-19T22:23:11Z</t>
         </is>
       </c>
     </row>
@@ -10254,7 +10254,7 @@
       </c>
       <c r="K203" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:52Z</t>
+          <t>2026-09-19T22:23:11Z</t>
         </is>
       </c>
     </row>
@@ -10303,7 +10303,7 @@
       </c>
       <c r="K204" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:52Z</t>
+          <t>2026-09-19T22:23:11Z</t>
         </is>
       </c>
     </row>
@@ -10352,7 +10352,7 @@
       </c>
       <c r="K205" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:52Z</t>
+          <t>2026-09-19T22:23:11Z</t>
         </is>
       </c>
     </row>
@@ -10401,7 +10401,7 @@
       </c>
       <c r="K206" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:52Z</t>
+          <t>2026-09-19T22:23:11Z</t>
         </is>
       </c>
     </row>
@@ -10450,7 +10450,7 @@
       </c>
       <c r="K207" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:52Z</t>
+          <t>2026-09-19T22:23:11Z</t>
         </is>
       </c>
     </row>
@@ -10499,7 +10499,7 @@
       </c>
       <c r="K208" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:52Z</t>
+          <t>2026-09-19T22:23:11Z</t>
         </is>
       </c>
     </row>
@@ -10548,7 +10548,7 @@
       </c>
       <c r="K209" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:52Z</t>
+          <t>2026-09-19T22:23:11Z</t>
         </is>
       </c>
     </row>
@@ -10597,7 +10597,7 @@
       </c>
       <c r="K210" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:52Z</t>
+          <t>2026-09-19T22:23:11Z</t>
         </is>
       </c>
     </row>
@@ -10646,7 +10646,7 @@
       </c>
       <c r="K211" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:52Z</t>
+          <t>2026-09-19T22:23:11Z</t>
         </is>
       </c>
     </row>
@@ -10695,7 +10695,7 @@
       </c>
       <c r="K212" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:52Z</t>
+          <t>2026-09-19T22:23:11Z</t>
         </is>
       </c>
     </row>
@@ -10744,7 +10744,7 @@
       </c>
       <c r="K213" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:52Z</t>
+          <t>2026-09-19T22:23:11Z</t>
         </is>
       </c>
     </row>
@@ -10793,7 +10793,7 @@
       </c>
       <c r="K214" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:52Z</t>
+          <t>2026-09-19T22:23:11Z</t>
         </is>
       </c>
     </row>
@@ -10842,7 +10842,7 @@
       </c>
       <c r="K215" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:52Z</t>
+          <t>2026-09-19T22:23:11Z</t>
         </is>
       </c>
     </row>
@@ -10891,7 +10891,7 @@
       </c>
       <c r="K216" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:52Z</t>
+          <t>2026-09-19T22:23:11Z</t>
         </is>
       </c>
     </row>
@@ -10940,7 +10940,7 @@
       </c>
       <c r="K217" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:52Z</t>
+          <t>2026-09-19T22:23:11Z</t>
         </is>
       </c>
     </row>
@@ -10989,7 +10989,7 @@
       </c>
       <c r="K218" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:52Z</t>
+          <t>2026-09-19T22:23:11Z</t>
         </is>
       </c>
     </row>
@@ -11038,7 +11038,7 @@
       </c>
       <c r="K219" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:52Z</t>
+          <t>2026-09-19T22:23:11Z</t>
         </is>
       </c>
     </row>
@@ -11087,7 +11087,7 @@
       </c>
       <c r="K220" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:52Z</t>
+          <t>2026-09-19T22:23:11Z</t>
         </is>
       </c>
     </row>
@@ -11136,7 +11136,7 @@
       </c>
       <c r="K221" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:52Z</t>
+          <t>2026-09-19T22:23:11Z</t>
         </is>
       </c>
     </row>
@@ -11185,7 +11185,7 @@
       </c>
       <c r="K222" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:52Z</t>
+          <t>2026-09-19T22:23:11Z</t>
         </is>
       </c>
     </row>
@@ -11234,7 +11234,7 @@
       </c>
       <c r="K223" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:52Z</t>
+          <t>2026-09-19T22:23:11Z</t>
         </is>
       </c>
     </row>
@@ -11283,7 +11283,7 @@
       </c>
       <c r="K224" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:52Z</t>
+          <t>2026-09-19T22:23:11Z</t>
         </is>
       </c>
     </row>
@@ -11332,7 +11332,7 @@
       </c>
       <c r="K225" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:52Z</t>
+          <t>2026-09-19T22:23:11Z</t>
         </is>
       </c>
     </row>
@@ -11381,7 +11381,7 @@
       </c>
       <c r="K226" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:52Z</t>
+          <t>2026-09-19T22:23:11Z</t>
         </is>
       </c>
     </row>
@@ -11430,7 +11430,7 @@
       </c>
       <c r="K227" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:52Z</t>
+          <t>2026-09-19T22:23:11Z</t>
         </is>
       </c>
     </row>
@@ -11479,7 +11479,7 @@
       </c>
       <c r="K228" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:52Z</t>
+          <t>2026-09-19T22:23:11Z</t>
         </is>
       </c>
     </row>
@@ -11528,7 +11528,7 @@
       </c>
       <c r="K229" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:52Z</t>
+          <t>2026-09-19T22:23:11Z</t>
         </is>
       </c>
     </row>
@@ -11577,7 +11577,7 @@
       </c>
       <c r="K230" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:52Z</t>
+          <t>2026-09-19T22:23:11Z</t>
         </is>
       </c>
     </row>
@@ -11626,7 +11626,7 @@
       </c>
       <c r="K231" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:52Z</t>
+          <t>2026-09-19T22:23:11Z</t>
         </is>
       </c>
     </row>
@@ -11758,7 +11758,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:52Z</t>
+          <t>2026-09-19T22:23:11Z</t>
         </is>
       </c>
     </row>
@@ -11804,7 +11804,7 @@
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>{"date": "2026-08-01", "year": 2026, "month": 8, "month_name": "Agosto", "index_value": 637409769724325.1, "monthly_variation_pct": 8.9, "unit": "Índice base diciembre 2007=100 y variación mensual %", "frequency": "monthly", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/precios_consumidor/4_5_7_2.xls", "fetched_at": "2026-09-18T22:43:52Z"}</t>
+          <t>{"date": "2026-08-01", "year": 2026, "month": 8, "month_name": "Agosto", "index_value": 637409769724325.1, "monthly_variation_pct": 8.9, "unit": "Índice base diciembre 2007=100 y variación mensual %", "frequency": "monthly", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/precios_consumidor/4_5_7_2.xls", "fetched_at": "2026-09-19T22:23:11Z"}</t>
         </is>
       </c>
     </row>

--- a/assets/data/bcv/excel/ove_bcv_inpc_nacional_mensual.xlsx
+++ b/assets/data/bcv/excel/ove_bcv_inpc_nacional_mensual.xlsx
@@ -650,7 +650,7 @@
       </c>
       <c r="K7" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:11Z</t>
+          <t>2026-09-20T22:35:40Z</t>
         </is>
       </c>
     </row>
@@ -699,7 +699,7 @@
       </c>
       <c r="K8" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:11Z</t>
+          <t>2026-09-20T22:35:40Z</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="K9" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:11Z</t>
+          <t>2026-09-20T22:35:40Z</t>
         </is>
       </c>
     </row>
@@ -797,7 +797,7 @@
       </c>
       <c r="K10" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:11Z</t>
+          <t>2026-09-20T22:35:40Z</t>
         </is>
       </c>
     </row>
@@ -846,7 +846,7 @@
       </c>
       <c r="K11" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:11Z</t>
+          <t>2026-09-20T22:35:40Z</t>
         </is>
       </c>
     </row>
@@ -895,7 +895,7 @@
       </c>
       <c r="K12" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:11Z</t>
+          <t>2026-09-20T22:35:40Z</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="K13" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:11Z</t>
+          <t>2026-09-20T22:35:40Z</t>
         </is>
       </c>
     </row>
@@ -993,7 +993,7 @@
       </c>
       <c r="K14" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:11Z</t>
+          <t>2026-09-20T22:35:40Z</t>
         </is>
       </c>
     </row>
@@ -1042,7 +1042,7 @@
       </c>
       <c r="K15" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:11Z</t>
+          <t>2026-09-20T22:35:40Z</t>
         </is>
       </c>
     </row>
@@ -1091,7 +1091,7 @@
       </c>
       <c r="K16" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:11Z</t>
+          <t>2026-09-20T22:35:40Z</t>
         </is>
       </c>
     </row>
@@ -1140,7 +1140,7 @@
       </c>
       <c r="K17" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:11Z</t>
+          <t>2026-09-20T22:35:40Z</t>
         </is>
       </c>
     </row>
@@ -1189,7 +1189,7 @@
       </c>
       <c r="K18" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:11Z</t>
+          <t>2026-09-20T22:35:40Z</t>
         </is>
       </c>
     </row>
@@ -1238,7 +1238,7 @@
       </c>
       <c r="K19" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:11Z</t>
+          <t>2026-09-20T22:35:40Z</t>
         </is>
       </c>
     </row>
@@ -1287,7 +1287,7 @@
       </c>
       <c r="K20" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:11Z</t>
+          <t>2026-09-20T22:35:40Z</t>
         </is>
       </c>
     </row>
@@ -1336,7 +1336,7 @@
       </c>
       <c r="K21" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:11Z</t>
+          <t>2026-09-20T22:35:40Z</t>
         </is>
       </c>
     </row>
@@ -1385,7 +1385,7 @@
       </c>
       <c r="K22" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:11Z</t>
+          <t>2026-09-20T22:35:40Z</t>
         </is>
       </c>
     </row>
@@ -1434,7 +1434,7 @@
       </c>
       <c r="K23" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:11Z</t>
+          <t>2026-09-20T22:35:40Z</t>
         </is>
       </c>
     </row>
@@ -1483,7 +1483,7 @@
       </c>
       <c r="K24" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:11Z</t>
+          <t>2026-09-20T22:35:40Z</t>
         </is>
       </c>
     </row>
@@ -1532,7 +1532,7 @@
       </c>
       <c r="K25" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:11Z</t>
+          <t>2026-09-20T22:35:40Z</t>
         </is>
       </c>
     </row>
@@ -1581,7 +1581,7 @@
       </c>
       <c r="K26" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:11Z</t>
+          <t>2026-09-20T22:35:40Z</t>
         </is>
       </c>
     </row>
@@ -1630,7 +1630,7 @@
       </c>
       <c r="K27" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:11Z</t>
+          <t>2026-09-20T22:35:40Z</t>
         </is>
       </c>
     </row>
@@ -1679,7 +1679,7 @@
       </c>
       <c r="K28" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:11Z</t>
+          <t>2026-09-20T22:35:40Z</t>
         </is>
       </c>
     </row>
@@ -1728,7 +1728,7 @@
       </c>
       <c r="K29" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:11Z</t>
+          <t>2026-09-20T22:35:40Z</t>
         </is>
       </c>
     </row>
@@ -1777,7 +1777,7 @@
       </c>
       <c r="K30" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:11Z</t>
+          <t>2026-09-20T22:35:40Z</t>
         </is>
       </c>
     </row>
@@ -1826,7 +1826,7 @@
       </c>
       <c r="K31" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:11Z</t>
+          <t>2026-09-20T22:35:40Z</t>
         </is>
       </c>
     </row>
@@ -1875,7 +1875,7 @@
       </c>
       <c r="K32" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:11Z</t>
+          <t>2026-09-20T22:35:40Z</t>
         </is>
       </c>
     </row>
@@ -1924,7 +1924,7 @@
       </c>
       <c r="K33" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:11Z</t>
+          <t>2026-09-20T22:35:40Z</t>
         </is>
       </c>
     </row>
@@ -1973,7 +1973,7 @@
       </c>
       <c r="K34" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:11Z</t>
+          <t>2026-09-20T22:35:40Z</t>
         </is>
       </c>
     </row>
@@ -2022,7 +2022,7 @@
       </c>
       <c r="K35" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:11Z</t>
+          <t>2026-09-20T22:35:40Z</t>
         </is>
       </c>
     </row>
@@ -2071,7 +2071,7 @@
       </c>
       <c r="K36" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:11Z</t>
+          <t>2026-09-20T22:35:40Z</t>
         </is>
       </c>
     </row>
@@ -2120,7 +2120,7 @@
       </c>
       <c r="K37" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:11Z</t>
+          <t>2026-09-20T22:35:40Z</t>
         </is>
       </c>
     </row>
@@ -2169,7 +2169,7 @@
       </c>
       <c r="K38" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:11Z</t>
+          <t>2026-09-20T22:35:40Z</t>
         </is>
       </c>
     </row>
@@ -2218,7 +2218,7 @@
       </c>
       <c r="K39" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:11Z</t>
+          <t>2026-09-20T22:35:40Z</t>
         </is>
       </c>
     </row>
@@ -2267,7 +2267,7 @@
       </c>
       <c r="K40" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:11Z</t>
+          <t>2026-09-20T22:35:40Z</t>
         </is>
       </c>
     </row>
@@ -2316,7 +2316,7 @@
       </c>
       <c r="K41" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:11Z</t>
+          <t>2026-09-20T22:35:40Z</t>
         </is>
       </c>
     </row>
@@ -2365,7 +2365,7 @@
       </c>
       <c r="K42" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:11Z</t>
+          <t>2026-09-20T22:35:40Z</t>
         </is>
       </c>
     </row>
@@ -2414,7 +2414,7 @@
       </c>
       <c r="K43" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:11Z</t>
+          <t>2026-09-20T22:35:40Z</t>
         </is>
       </c>
     </row>
@@ -2463,7 +2463,7 @@
       </c>
       <c r="K44" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:11Z</t>
+          <t>2026-09-20T22:35:40Z</t>
         </is>
       </c>
     </row>
@@ -2512,7 +2512,7 @@
       </c>
       <c r="K45" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:11Z</t>
+          <t>2026-09-20T22:35:40Z</t>
         </is>
       </c>
     </row>
@@ -2561,7 +2561,7 @@
       </c>
       <c r="K46" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:11Z</t>
+          <t>2026-09-20T22:35:40Z</t>
         </is>
       </c>
     </row>
@@ -2610,7 +2610,7 @@
       </c>
       <c r="K47" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:11Z</t>
+          <t>2026-09-20T22:35:40Z</t>
         </is>
       </c>
     </row>
@@ -2659,7 +2659,7 @@
       </c>
       <c r="K48" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:11Z</t>
+          <t>2026-09-20T22:35:40Z</t>
         </is>
       </c>
     </row>
@@ -2708,7 +2708,7 @@
       </c>
       <c r="K49" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:11Z</t>
+          <t>2026-09-20T22:35:40Z</t>
         </is>
       </c>
     </row>
@@ -2757,7 +2757,7 @@
       </c>
       <c r="K50" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:11Z</t>
+          <t>2026-09-20T22:35:40Z</t>
         </is>
       </c>
     </row>
@@ -2806,7 +2806,7 @@
       </c>
       <c r="K51" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:11Z</t>
+          <t>2026-09-20T22:35:40Z</t>
         </is>
       </c>
     </row>
@@ -2855,7 +2855,7 @@
       </c>
       <c r="K52" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:11Z</t>
+          <t>2026-09-20T22:35:40Z</t>
         </is>
       </c>
     </row>
@@ -2904,7 +2904,7 @@
       </c>
       <c r="K53" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:11Z</t>
+          <t>2026-09-20T22:35:40Z</t>
         </is>
       </c>
     </row>
@@ -2953,7 +2953,7 @@
       </c>
       <c r="K54" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:11Z</t>
+          <t>2026-09-20T22:35:40Z</t>
         </is>
       </c>
     </row>
@@ -3002,7 +3002,7 @@
       </c>
       <c r="K55" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:11Z</t>
+          <t>2026-09-20T22:35:40Z</t>
         </is>
       </c>
     </row>
@@ -3051,7 +3051,7 @@
       </c>
       <c r="K56" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:11Z</t>
+          <t>2026-09-20T22:35:40Z</t>
         </is>
       </c>
     </row>
@@ -3100,7 +3100,7 @@
       </c>
       <c r="K57" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:11Z</t>
+          <t>2026-09-20T22:35:40Z</t>
         </is>
       </c>
     </row>
@@ -3149,7 +3149,7 @@
       </c>
       <c r="K58" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:11Z</t>
+          <t>2026-09-20T22:35:40Z</t>
         </is>
       </c>
     </row>
@@ -3198,7 +3198,7 @@
       </c>
       <c r="K59" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:11Z</t>
+          <t>2026-09-20T22:35:40Z</t>
         </is>
       </c>
     </row>
@@ -3247,7 +3247,7 @@
       </c>
       <c r="K60" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:11Z</t>
+          <t>2026-09-20T22:35:40Z</t>
         </is>
       </c>
     </row>
@@ -3296,7 +3296,7 @@
       </c>
       <c r="K61" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:11Z</t>
+          <t>2026-09-20T22:35:40Z</t>
         </is>
       </c>
     </row>
@@ -3345,7 +3345,7 @@
       </c>
       <c r="K62" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:11Z</t>
+          <t>2026-09-20T22:35:40Z</t>
         </is>
       </c>
     </row>
@@ -3394,7 +3394,7 @@
       </c>
       <c r="K63" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:11Z</t>
+          <t>2026-09-20T22:35:40Z</t>
         </is>
       </c>
     </row>
@@ -3443,7 +3443,7 @@
       </c>
       <c r="K64" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:11Z</t>
+          <t>2026-09-20T22:35:40Z</t>
         </is>
       </c>
     </row>
@@ -3492,7 +3492,7 @@
       </c>
       <c r="K65" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:11Z</t>
+          <t>2026-09-20T22:35:40Z</t>
         </is>
       </c>
     </row>
@@ -3541,7 +3541,7 @@
       </c>
       <c r="K66" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:11Z</t>
+          <t>2026-09-20T22:35:40Z</t>
         </is>
       </c>
     </row>
@@ -3590,7 +3590,7 @@
       </c>
       <c r="K67" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:11Z</t>
+          <t>2026-09-20T22:35:40Z</t>
         </is>
       </c>
     </row>
@@ -3639,7 +3639,7 @@
       </c>
       <c r="K68" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:11Z</t>
+          <t>2026-09-20T22:35:40Z</t>
         </is>
       </c>
     </row>
@@ -3688,7 +3688,7 @@
       </c>
       <c r="K69" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:11Z</t>
+          <t>2026-09-20T22:35:40Z</t>
         </is>
       </c>
     </row>
@@ -3737,7 +3737,7 @@
       </c>
       <c r="K70" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:11Z</t>
+          <t>2026-09-20T22:35:40Z</t>
         </is>
       </c>
     </row>
@@ -3786,7 +3786,7 @@
       </c>
       <c r="K71" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:11Z</t>
+          <t>2026-09-20T22:35:40Z</t>
         </is>
       </c>
     </row>
@@ -3835,7 +3835,7 @@
       </c>
       <c r="K72" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:11Z</t>
+          <t>2026-09-20T22:35:40Z</t>
         </is>
       </c>
     </row>
@@ -3884,7 +3884,7 @@
       </c>
       <c r="K73" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:11Z</t>
+          <t>2026-09-20T22:35:40Z</t>
         </is>
       </c>
     </row>
@@ -3933,7 +3933,7 @@
       </c>
       <c r="K74" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:11Z</t>
+          <t>2026-09-20T22:35:40Z</t>
         </is>
       </c>
     </row>
@@ -3982,7 +3982,7 @@
       </c>
       <c r="K75" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:11Z</t>
+          <t>2026-09-20T22:35:40Z</t>
         </is>
       </c>
     </row>
@@ -4031,7 +4031,7 @@
       </c>
       <c r="K76" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:11Z</t>
+          <t>2026-09-20T22:35:40Z</t>
         </is>
       </c>
     </row>
@@ -4080,7 +4080,7 @@
       </c>
       <c r="K77" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:11Z</t>
+          <t>2026-09-20T22:35:40Z</t>
         </is>
       </c>
     </row>
@@ -4129,7 +4129,7 @@
       </c>
       <c r="K78" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:11Z</t>
+          <t>2026-09-20T22:35:40Z</t>
         </is>
       </c>
     </row>
@@ -4178,7 +4178,7 @@
       </c>
       <c r="K79" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:11Z</t>
+          <t>2026-09-20T22:35:40Z</t>
         </is>
       </c>
     </row>
@@ -4227,7 +4227,7 @@
       </c>
       <c r="K80" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:11Z</t>
+          <t>2026-09-20T22:35:40Z</t>
         </is>
       </c>
     </row>
@@ -4276,7 +4276,7 @@
       </c>
       <c r="K81" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:11Z</t>
+          <t>2026-09-20T22:35:40Z</t>
         </is>
       </c>
     </row>
@@ -4325,7 +4325,7 @@
       </c>
       <c r="K82" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:11Z</t>
+          <t>2026-09-20T22:35:40Z</t>
         </is>
       </c>
     </row>
@@ -4374,7 +4374,7 @@
       </c>
       <c r="K83" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:11Z</t>
+          <t>2026-09-20T22:35:40Z</t>
         </is>
       </c>
     </row>
@@ -4423,7 +4423,7 @@
       </c>
       <c r="K84" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:11Z</t>
+          <t>2026-09-20T22:35:40Z</t>
         </is>
       </c>
     </row>
@@ -4472,7 +4472,7 @@
       </c>
       <c r="K85" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:11Z</t>
+          <t>2026-09-20T22:35:40Z</t>
         </is>
       </c>
     </row>
@@ -4521,7 +4521,7 @@
       </c>
       <c r="K86" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:11Z</t>
+          <t>2026-09-20T22:35:40Z</t>
         </is>
       </c>
     </row>
@@ -4570,7 +4570,7 @@
       </c>
       <c r="K87" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:11Z</t>
+          <t>2026-09-20T22:35:40Z</t>
         </is>
       </c>
     </row>
@@ -4619,7 +4619,7 @@
       </c>
       <c r="K88" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:11Z</t>
+          <t>2026-09-20T22:35:40Z</t>
         </is>
       </c>
     </row>
@@ -4668,7 +4668,7 @@
       </c>
       <c r="K89" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:11Z</t>
+          <t>2026-09-20T22:35:40Z</t>
         </is>
       </c>
     </row>
@@ -4717,7 +4717,7 @@
       </c>
       <c r="K90" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:11Z</t>
+          <t>2026-09-20T22:35:40Z</t>
         </is>
       </c>
     </row>
@@ -4766,7 +4766,7 @@
       </c>
       <c r="K91" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:11Z</t>
+          <t>2026-09-20T22:35:40Z</t>
         </is>
       </c>
     </row>
@@ -4815,7 +4815,7 @@
       </c>
       <c r="K92" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:11Z</t>
+          <t>2026-09-20T22:35:40Z</t>
         </is>
       </c>
     </row>
@@ -4864,7 +4864,7 @@
       </c>
       <c r="K93" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:11Z</t>
+          <t>2026-09-20T22:35:40Z</t>
         </is>
       </c>
     </row>
@@ -4913,7 +4913,7 @@
       </c>
       <c r="K94" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:11Z</t>
+          <t>2026-09-20T22:35:40Z</t>
         </is>
       </c>
     </row>
@@ -4962,7 +4962,7 @@
       </c>
       <c r="K95" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:11Z</t>
+          <t>2026-09-20T22:35:40Z</t>
         </is>
       </c>
     </row>
@@ -5011,7 +5011,7 @@
       </c>
       <c r="K96" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:11Z</t>
+          <t>2026-09-20T22:35:40Z</t>
         </is>
       </c>
     </row>
@@ -5060,7 +5060,7 @@
       </c>
       <c r="K97" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:11Z</t>
+          <t>2026-09-20T22:35:40Z</t>
         </is>
       </c>
     </row>
@@ -5109,7 +5109,7 @@
       </c>
       <c r="K98" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:11Z</t>
+          <t>2026-09-20T22:35:40Z</t>
         </is>
       </c>
     </row>
@@ -5158,7 +5158,7 @@
       </c>
       <c r="K99" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:11Z</t>
+          <t>2026-09-20T22:35:40Z</t>
         </is>
       </c>
     </row>
@@ -5207,7 +5207,7 @@
       </c>
       <c r="K100" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:11Z</t>
+          <t>2026-09-20T22:35:40Z</t>
         </is>
       </c>
     </row>
@@ -5256,7 +5256,7 @@
       </c>
       <c r="K101" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:11Z</t>
+          <t>2026-09-20T22:35:40Z</t>
         </is>
       </c>
     </row>
@@ -5305,7 +5305,7 @@
       </c>
       <c r="K102" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:11Z</t>
+          <t>2026-09-20T22:35:40Z</t>
         </is>
       </c>
     </row>
@@ -5354,7 +5354,7 @@
       </c>
       <c r="K103" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:11Z</t>
+          <t>2026-09-20T22:35:40Z</t>
         </is>
       </c>
     </row>
@@ -5403,7 +5403,7 @@
       </c>
       <c r="K104" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:11Z</t>
+          <t>2026-09-20T22:35:40Z</t>
         </is>
       </c>
     </row>
@@ -5452,7 +5452,7 @@
       </c>
       <c r="K105" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:11Z</t>
+          <t>2026-09-20T22:35:40Z</t>
         </is>
       </c>
     </row>
@@ -5501,7 +5501,7 @@
       </c>
       <c r="K106" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:11Z</t>
+          <t>2026-09-20T22:35:40Z</t>
         </is>
       </c>
     </row>
@@ -5550,7 +5550,7 @@
       </c>
       <c r="K107" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:11Z</t>
+          <t>2026-09-20T22:35:40Z</t>
         </is>
       </c>
     </row>
@@ -5599,7 +5599,7 @@
       </c>
       <c r="K108" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:11Z</t>
+          <t>2026-09-20T22:35:40Z</t>
         </is>
       </c>
     </row>
@@ -5648,7 +5648,7 @@
       </c>
       <c r="K109" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:11Z</t>
+          <t>2026-09-20T22:35:40Z</t>
         </is>
       </c>
     </row>
@@ -5697,7 +5697,7 @@
       </c>
       <c r="K110" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:11Z</t>
+          <t>2026-09-20T22:35:40Z</t>
         </is>
       </c>
     </row>
@@ -5746,7 +5746,7 @@
       </c>
       <c r="K111" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:11Z</t>
+          <t>2026-09-20T22:35:40Z</t>
         </is>
       </c>
     </row>
@@ -5795,7 +5795,7 @@
       </c>
       <c r="K112" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:11Z</t>
+          <t>2026-09-20T22:35:40Z</t>
         </is>
       </c>
     </row>
@@ -5844,7 +5844,7 @@
       </c>
       <c r="K113" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:11Z</t>
+          <t>2026-09-20T22:35:40Z</t>
         </is>
       </c>
     </row>
@@ -5893,7 +5893,7 @@
       </c>
       <c r="K114" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:11Z</t>
+          <t>2026-09-20T22:35:40Z</t>
         </is>
       </c>
     </row>
@@ -5942,7 +5942,7 @@
       </c>
       <c r="K115" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:11Z</t>
+          <t>2026-09-20T22:35:40Z</t>
         </is>
       </c>
     </row>
@@ -5991,7 +5991,7 @@
       </c>
       <c r="K116" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:11Z</t>
+          <t>2026-09-20T22:35:40Z</t>
         </is>
       </c>
     </row>
@@ -6040,7 +6040,7 @@
       </c>
       <c r="K117" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:11Z</t>
+          <t>2026-09-20T22:35:40Z</t>
         </is>
       </c>
     </row>
@@ -6089,7 +6089,7 @@
       </c>
       <c r="K118" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:11Z</t>
+          <t>2026-09-20T22:35:40Z</t>
         </is>
       </c>
     </row>
@@ -6138,7 +6138,7 @@
       </c>
       <c r="K119" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:11Z</t>
+          <t>2026-09-20T22:35:40Z</t>
         </is>
       </c>
     </row>
@@ -6187,7 +6187,7 @@
       </c>
       <c r="K120" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:11Z</t>
+          <t>2026-09-20T22:35:40Z</t>
         </is>
       </c>
     </row>
@@ -6236,7 +6236,7 @@
       </c>
       <c r="K121" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:11Z</t>
+          <t>2026-09-20T22:35:40Z</t>
         </is>
       </c>
     </row>
@@ -6285,7 +6285,7 @@
       </c>
       <c r="K122" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:11Z</t>
+          <t>2026-09-20T22:35:40Z</t>
         </is>
       </c>
     </row>
@@ -6334,7 +6334,7 @@
       </c>
       <c r="K123" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:11Z</t>
+          <t>2026-09-20T22:35:40Z</t>
         </is>
       </c>
     </row>
@@ -6383,7 +6383,7 @@
       </c>
       <c r="K124" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:11Z</t>
+          <t>2026-09-20T22:35:40Z</t>
         </is>
       </c>
     </row>
@@ -6432,7 +6432,7 @@
       </c>
       <c r="K125" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:11Z</t>
+          <t>2026-09-20T22:35:40Z</t>
         </is>
       </c>
     </row>
@@ -6481,7 +6481,7 @@
       </c>
       <c r="K126" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:11Z</t>
+          <t>2026-09-20T22:35:40Z</t>
         </is>
       </c>
     </row>
@@ -6530,7 +6530,7 @@
       </c>
       <c r="K127" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:11Z</t>
+          <t>2026-09-20T22:35:40Z</t>
         </is>
       </c>
     </row>
@@ -6579,7 +6579,7 @@
       </c>
       <c r="K128" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:11Z</t>
+          <t>2026-09-20T22:35:40Z</t>
         </is>
       </c>
     </row>
@@ -6628,7 +6628,7 @@
       </c>
       <c r="K129" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:11Z</t>
+          <t>2026-09-20T22:35:40Z</t>
         </is>
       </c>
     </row>
@@ -6677,7 +6677,7 @@
       </c>
       <c r="K130" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:11Z</t>
+          <t>2026-09-20T22:35:40Z</t>
         </is>
       </c>
     </row>
@@ -6726,7 +6726,7 @@
       </c>
       <c r="K131" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:11Z</t>
+          <t>2026-09-20T22:35:40Z</t>
         </is>
       </c>
     </row>
@@ -6775,7 +6775,7 @@
       </c>
       <c r="K132" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:11Z</t>
+          <t>2026-09-20T22:35:40Z</t>
         </is>
       </c>
     </row>
@@ -6824,7 +6824,7 @@
       </c>
       <c r="K133" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:11Z</t>
+          <t>2026-09-20T22:35:40Z</t>
         </is>
       </c>
     </row>
@@ -6873,7 +6873,7 @@
       </c>
       <c r="K134" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:11Z</t>
+          <t>2026-09-20T22:35:40Z</t>
         </is>
       </c>
     </row>
@@ -6922,7 +6922,7 @@
       </c>
       <c r="K135" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:11Z</t>
+          <t>2026-09-20T22:35:40Z</t>
         </is>
       </c>
     </row>
@@ -6971,7 +6971,7 @@
       </c>
       <c r="K136" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:11Z</t>
+          <t>2026-09-20T22:35:40Z</t>
         </is>
       </c>
     </row>
@@ -7020,7 +7020,7 @@
       </c>
       <c r="K137" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:11Z</t>
+          <t>2026-09-20T22:35:40Z</t>
         </is>
       </c>
     </row>
@@ -7069,7 +7069,7 @@
       </c>
       <c r="K138" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:11Z</t>
+          <t>2026-09-20T22:35:40Z</t>
         </is>
       </c>
     </row>
@@ -7118,7 +7118,7 @@
       </c>
       <c r="K139" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:11Z</t>
+          <t>2026-09-20T22:35:40Z</t>
         </is>
       </c>
     </row>
@@ -7167,7 +7167,7 @@
       </c>
       <c r="K140" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:11Z</t>
+          <t>2026-09-20T22:35:40Z</t>
         </is>
       </c>
     </row>
@@ -7216,7 +7216,7 @@
       </c>
       <c r="K141" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:11Z</t>
+          <t>2026-09-20T22:35:40Z</t>
         </is>
       </c>
     </row>
@@ -7265,7 +7265,7 @@
       </c>
       <c r="K142" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:11Z</t>
+          <t>2026-09-20T22:35:40Z</t>
         </is>
       </c>
     </row>
@@ -7314,7 +7314,7 @@
       </c>
       <c r="K143" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:11Z</t>
+          <t>2026-09-20T22:35:40Z</t>
         </is>
       </c>
     </row>
@@ -7363,7 +7363,7 @@
       </c>
       <c r="K144" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:11Z</t>
+          <t>2026-09-20T22:35:40Z</t>
         </is>
       </c>
     </row>
@@ -7412,7 +7412,7 @@
       </c>
       <c r="K145" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:11Z</t>
+          <t>2026-09-20T22:35:40Z</t>
         </is>
       </c>
     </row>
@@ -7461,7 +7461,7 @@
       </c>
       <c r="K146" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:11Z</t>
+          <t>2026-09-20T22:35:40Z</t>
         </is>
       </c>
     </row>
@@ -7510,7 +7510,7 @@
       </c>
       <c r="K147" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:11Z</t>
+          <t>2026-09-20T22:35:40Z</t>
         </is>
       </c>
     </row>
@@ -7559,7 +7559,7 @@
       </c>
       <c r="K148" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:11Z</t>
+          <t>2026-09-20T22:35:40Z</t>
         </is>
       </c>
     </row>
@@ -7608,7 +7608,7 @@
       </c>
       <c r="K149" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:11Z</t>
+          <t>2026-09-20T22:35:40Z</t>
         </is>
       </c>
     </row>
@@ -7657,7 +7657,7 @@
       </c>
       <c r="K150" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:11Z</t>
+          <t>2026-09-20T22:35:40Z</t>
         </is>
       </c>
     </row>
@@ -7706,7 +7706,7 @@
       </c>
       <c r="K151" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:11Z</t>
+          <t>2026-09-20T22:35:40Z</t>
         </is>
       </c>
     </row>
@@ -7755,7 +7755,7 @@
       </c>
       <c r="K152" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:11Z</t>
+          <t>2026-09-20T22:35:40Z</t>
         </is>
       </c>
     </row>
@@ -7804,7 +7804,7 @@
       </c>
       <c r="K153" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:11Z</t>
+          <t>2026-09-20T22:35:40Z</t>
         </is>
       </c>
     </row>
@@ -7853,7 +7853,7 @@
       </c>
       <c r="K154" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:11Z</t>
+          <t>2026-09-20T22:35:40Z</t>
         </is>
       </c>
     </row>
@@ -7902,7 +7902,7 @@
       </c>
       <c r="K155" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:11Z</t>
+          <t>2026-09-20T22:35:40Z</t>
         </is>
       </c>
     </row>
@@ -7951,7 +7951,7 @@
       </c>
       <c r="K156" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:11Z</t>
+          <t>2026-09-20T22:35:40Z</t>
         </is>
       </c>
     </row>
@@ -8000,7 +8000,7 @@
       </c>
       <c r="K157" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:11Z</t>
+          <t>2026-09-20T22:35:40Z</t>
         </is>
       </c>
     </row>
@@ -8049,7 +8049,7 @@
       </c>
       <c r="K158" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:11Z</t>
+          <t>2026-09-20T22:35:40Z</t>
         </is>
       </c>
     </row>
@@ -8098,7 +8098,7 @@
       </c>
       <c r="K159" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:11Z</t>
+          <t>2026-09-20T22:35:40Z</t>
         </is>
       </c>
     </row>
@@ -8147,7 +8147,7 @@
       </c>
       <c r="K160" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:11Z</t>
+          <t>2026-09-20T22:35:40Z</t>
         </is>
       </c>
     </row>
@@ -8196,7 +8196,7 @@
       </c>
       <c r="K161" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:11Z</t>
+          <t>2026-09-20T22:35:40Z</t>
         </is>
       </c>
     </row>
@@ -8245,7 +8245,7 @@
       </c>
       <c r="K162" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:11Z</t>
+          <t>2026-09-20T22:35:40Z</t>
         </is>
       </c>
     </row>
@@ -8294,7 +8294,7 @@
       </c>
       <c r="K163" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:11Z</t>
+          <t>2026-09-20T22:35:40Z</t>
         </is>
       </c>
     </row>
@@ -8343,7 +8343,7 @@
       </c>
       <c r="K164" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:11Z</t>
+          <t>2026-09-20T22:35:40Z</t>
         </is>
       </c>
     </row>
@@ -8392,7 +8392,7 @@
       </c>
       <c r="K165" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:11Z</t>
+          <t>2026-09-20T22:35:40Z</t>
         </is>
       </c>
     </row>
@@ -8441,7 +8441,7 @@
       </c>
       <c r="K166" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:11Z</t>
+          <t>2026-09-20T22:35:40Z</t>
         </is>
       </c>
     </row>
@@ -8490,7 +8490,7 @@
       </c>
       <c r="K167" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:11Z</t>
+          <t>2026-09-20T22:35:40Z</t>
         </is>
       </c>
     </row>
@@ -8539,7 +8539,7 @@
       </c>
       <c r="K168" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:11Z</t>
+          <t>2026-09-20T22:35:40Z</t>
         </is>
       </c>
     </row>
@@ -8588,7 +8588,7 @@
       </c>
       <c r="K169" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:11Z</t>
+          <t>2026-09-20T22:35:40Z</t>
         </is>
       </c>
     </row>
@@ -8637,7 +8637,7 @@
       </c>
       <c r="K170" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:11Z</t>
+          <t>2026-09-20T22:35:40Z</t>
         </is>
       </c>
     </row>
@@ -8686,7 +8686,7 @@
       </c>
       <c r="K171" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:11Z</t>
+          <t>2026-09-20T22:35:40Z</t>
         </is>
       </c>
     </row>
@@ -8735,7 +8735,7 @@
       </c>
       <c r="K172" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:11Z</t>
+          <t>2026-09-20T22:35:40Z</t>
         </is>
       </c>
     </row>
@@ -8784,7 +8784,7 @@
       </c>
       <c r="K173" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:11Z</t>
+          <t>2026-09-20T22:35:40Z</t>
         </is>
       </c>
     </row>
@@ -8833,7 +8833,7 @@
       </c>
       <c r="K174" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:11Z</t>
+          <t>2026-09-20T22:35:40Z</t>
         </is>
       </c>
     </row>
@@ -8882,7 +8882,7 @@
       </c>
       <c r="K175" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:11Z</t>
+          <t>2026-09-20T22:35:40Z</t>
         </is>
       </c>
     </row>
@@ -8931,7 +8931,7 @@
       </c>
       <c r="K176" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:11Z</t>
+          <t>2026-09-20T22:35:40Z</t>
         </is>
       </c>
     </row>
@@ -8980,7 +8980,7 @@
       </c>
       <c r="K177" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:11Z</t>
+          <t>2026-09-20T22:35:40Z</t>
         </is>
       </c>
     </row>
@@ -9029,7 +9029,7 @@
       </c>
       <c r="K178" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:11Z</t>
+          <t>2026-09-20T22:35:40Z</t>
         </is>
       </c>
     </row>
@@ -9078,7 +9078,7 @@
       </c>
       <c r="K179" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:11Z</t>
+          <t>2026-09-20T22:35:40Z</t>
         </is>
       </c>
     </row>
@@ -9127,7 +9127,7 @@
       </c>
       <c r="K180" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:11Z</t>
+          <t>2026-09-20T22:35:40Z</t>
         </is>
       </c>
     </row>
@@ -9176,7 +9176,7 @@
       </c>
       <c r="K181" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:11Z</t>
+          <t>2026-09-20T22:35:40Z</t>
         </is>
       </c>
     </row>
@@ -9225,7 +9225,7 @@
       </c>
       <c r="K182" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:11Z</t>
+          <t>2026-09-20T22:35:40Z</t>
         </is>
       </c>
     </row>
@@ -9274,7 +9274,7 @@
       </c>
       <c r="K183" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:11Z</t>
+          <t>2026-09-20T22:35:40Z</t>
         </is>
       </c>
     </row>
@@ -9323,7 +9323,7 @@
       </c>
       <c r="K184" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:11Z</t>
+          <t>2026-09-20T22:35:40Z</t>
         </is>
       </c>
     </row>
@@ -9372,7 +9372,7 @@
       </c>
       <c r="K185" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:11Z</t>
+          <t>2026-09-20T22:35:40Z</t>
         </is>
       </c>
     </row>
@@ -9421,7 +9421,7 @@
       </c>
       <c r="K186" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:11Z</t>
+          <t>2026-09-20T22:35:40Z</t>
         </is>
       </c>
     </row>
@@ -9470,7 +9470,7 @@
       </c>
       <c r="K187" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:11Z</t>
+          <t>2026-09-20T22:35:40Z</t>
         </is>
       </c>
     </row>
@@ -9519,7 +9519,7 @@
       </c>
       <c r="K188" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:11Z</t>
+          <t>2026-09-20T22:35:40Z</t>
         </is>
       </c>
     </row>
@@ -9568,7 +9568,7 @@
       </c>
       <c r="K189" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:11Z</t>
+          <t>2026-09-20T22:35:40Z</t>
         </is>
       </c>
     </row>
@@ -9617,7 +9617,7 @@
       </c>
       <c r="K190" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:11Z</t>
+          <t>2026-09-20T22:35:40Z</t>
         </is>
       </c>
     </row>
@@ -9666,7 +9666,7 @@
       </c>
       <c r="K191" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:11Z</t>
+          <t>2026-09-20T22:35:40Z</t>
         </is>
       </c>
     </row>
@@ -9715,7 +9715,7 @@
       </c>
       <c r="K192" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:11Z</t>
+          <t>2026-09-20T22:35:40Z</t>
         </is>
       </c>
     </row>
@@ -9764,7 +9764,7 @@
       </c>
       <c r="K193" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:11Z</t>
+          <t>2026-09-20T22:35:40Z</t>
         </is>
       </c>
     </row>
@@ -9813,7 +9813,7 @@
       </c>
       <c r="K194" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:11Z</t>
+          <t>2026-09-20T22:35:40Z</t>
         </is>
       </c>
     </row>
@@ -9862,7 +9862,7 @@
       </c>
       <c r="K195" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:11Z</t>
+          <t>2026-09-20T22:35:40Z</t>
         </is>
       </c>
     </row>
@@ -9911,7 +9911,7 @@
       </c>
       <c r="K196" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:11Z</t>
+          <t>2026-09-20T22:35:40Z</t>
         </is>
       </c>
     </row>
@@ -9960,7 +9960,7 @@
       </c>
       <c r="K197" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:11Z</t>
+          <t>2026-09-20T22:35:40Z</t>
         </is>
       </c>
     </row>
@@ -10009,7 +10009,7 @@
       </c>
       <c r="K198" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:11Z</t>
+          <t>2026-09-20T22:35:40Z</t>
         </is>
       </c>
     </row>
@@ -10058,7 +10058,7 @@
       </c>
       <c r="K199" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:11Z</t>
+          <t>2026-09-20T22:35:40Z</t>
         </is>
       </c>
     </row>
@@ -10107,7 +10107,7 @@
       </c>
       <c r="K200" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:11Z</t>
+          <t>2026-09-20T22:35:40Z</t>
         </is>
       </c>
     </row>
@@ -10156,7 +10156,7 @@
       </c>
       <c r="K201" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:11Z</t>
+          <t>2026-09-20T22:35:40Z</t>
         </is>
       </c>
     </row>
@@ -10205,7 +10205,7 @@
       </c>
       <c r="K202" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:11Z</t>
+          <t>2026-09-20T22:35:40Z</t>
         </is>
       </c>
     </row>
@@ -10254,7 +10254,7 @@
       </c>
       <c r="K203" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:11Z</t>
+          <t>2026-09-20T22:35:40Z</t>
         </is>
       </c>
     </row>
@@ -10303,7 +10303,7 @@
       </c>
       <c r="K204" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:11Z</t>
+          <t>2026-09-20T22:35:40Z</t>
         </is>
       </c>
     </row>
@@ -10352,7 +10352,7 @@
       </c>
       <c r="K205" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:11Z</t>
+          <t>2026-09-20T22:35:40Z</t>
         </is>
       </c>
     </row>
@@ -10401,7 +10401,7 @@
       </c>
       <c r="K206" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:11Z</t>
+          <t>2026-09-20T22:35:40Z</t>
         </is>
       </c>
     </row>
@@ -10450,7 +10450,7 @@
       </c>
       <c r="K207" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:11Z</t>
+          <t>2026-09-20T22:35:40Z</t>
         </is>
       </c>
     </row>
@@ -10499,7 +10499,7 @@
       </c>
       <c r="K208" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:11Z</t>
+          <t>2026-09-20T22:35:40Z</t>
         </is>
       </c>
     </row>
@@ -10548,7 +10548,7 @@
       </c>
       <c r="K209" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:11Z</t>
+          <t>2026-09-20T22:35:40Z</t>
         </is>
       </c>
     </row>
@@ -10597,7 +10597,7 @@
       </c>
       <c r="K210" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:11Z</t>
+          <t>2026-09-20T22:35:40Z</t>
         </is>
       </c>
     </row>
@@ -10646,7 +10646,7 @@
       </c>
       <c r="K211" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:11Z</t>
+          <t>2026-09-20T22:35:40Z</t>
         </is>
       </c>
     </row>
@@ -10695,7 +10695,7 @@
       </c>
       <c r="K212" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:11Z</t>
+          <t>2026-09-20T22:35:40Z</t>
         </is>
       </c>
     </row>
@@ -10744,7 +10744,7 @@
       </c>
       <c r="K213" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:11Z</t>
+          <t>2026-09-20T22:35:40Z</t>
         </is>
       </c>
     </row>
@@ -10793,7 +10793,7 @@
       </c>
       <c r="K214" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:11Z</t>
+          <t>2026-09-20T22:35:40Z</t>
         </is>
       </c>
     </row>
@@ -10842,7 +10842,7 @@
       </c>
       <c r="K215" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:11Z</t>
+          <t>2026-09-20T22:35:40Z</t>
         </is>
       </c>
     </row>
@@ -10891,7 +10891,7 @@
       </c>
       <c r="K216" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:11Z</t>
+          <t>2026-09-20T22:35:40Z</t>
         </is>
       </c>
     </row>
@@ -10940,7 +10940,7 @@
       </c>
       <c r="K217" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:11Z</t>
+          <t>2026-09-20T22:35:40Z</t>
         </is>
       </c>
     </row>
@@ -10989,7 +10989,7 @@
       </c>
       <c r="K218" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:11Z</t>
+          <t>2026-09-20T22:35:40Z</t>
         </is>
       </c>
     </row>
@@ -11038,7 +11038,7 @@
       </c>
       <c r="K219" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:11Z</t>
+          <t>2026-09-20T22:35:40Z</t>
         </is>
       </c>
     </row>
@@ -11087,7 +11087,7 @@
       </c>
       <c r="K220" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:11Z</t>
+          <t>2026-09-20T22:35:40Z</t>
         </is>
       </c>
     </row>
@@ -11136,7 +11136,7 @@
       </c>
       <c r="K221" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:11Z</t>
+          <t>2026-09-20T22:35:40Z</t>
         </is>
       </c>
     </row>
@@ -11185,7 +11185,7 @@
       </c>
       <c r="K222" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:11Z</t>
+          <t>2026-09-20T22:35:40Z</t>
         </is>
       </c>
     </row>
@@ -11234,7 +11234,7 @@
       </c>
       <c r="K223" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:11Z</t>
+          <t>2026-09-20T22:35:40Z</t>
         </is>
       </c>
     </row>
@@ -11283,7 +11283,7 @@
       </c>
       <c r="K224" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:11Z</t>
+          <t>2026-09-20T22:35:40Z</t>
         </is>
       </c>
     </row>
@@ -11332,7 +11332,7 @@
       </c>
       <c r="K225" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:11Z</t>
+          <t>2026-09-20T22:35:40Z</t>
         </is>
       </c>
     </row>
@@ -11381,7 +11381,7 @@
       </c>
       <c r="K226" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:11Z</t>
+          <t>2026-09-20T22:35:40Z</t>
         </is>
       </c>
     </row>
@@ -11430,7 +11430,7 @@
       </c>
       <c r="K227" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:11Z</t>
+          <t>2026-09-20T22:35:40Z</t>
         </is>
       </c>
     </row>
@@ -11479,7 +11479,7 @@
       </c>
       <c r="K228" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:11Z</t>
+          <t>2026-09-20T22:35:40Z</t>
         </is>
       </c>
     </row>
@@ -11528,7 +11528,7 @@
       </c>
       <c r="K229" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:11Z</t>
+          <t>2026-09-20T22:35:40Z</t>
         </is>
       </c>
     </row>
@@ -11577,7 +11577,7 @@
       </c>
       <c r="K230" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:11Z</t>
+          <t>2026-09-20T22:35:40Z</t>
         </is>
       </c>
     </row>
@@ -11626,7 +11626,7 @@
       </c>
       <c r="K231" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:11Z</t>
+          <t>2026-09-20T22:35:40Z</t>
         </is>
       </c>
     </row>
@@ -11758,7 +11758,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:11Z</t>
+          <t>2026-09-20T22:35:40Z</t>
         </is>
       </c>
     </row>
@@ -11804,7 +11804,7 @@
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>{"date": "2026-08-01", "year": 2026, "month": 8, "month_name": "Agosto", "index_value": 637409769724325.1, "monthly_variation_pct": 8.9, "unit": "Índice base diciembre 2007=100 y variación mensual %", "frequency": "monthly", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/precios_consumidor/4_5_7_2.xls", "fetched_at": "2026-09-19T22:23:11Z"}</t>
+          <t>{"date": "2026-08-01", "year": 2026, "month": 8, "month_name": "Agosto", "index_value": 637409769724325.1, "monthly_variation_pct": 8.9, "unit": "Índice base diciembre 2007=100 y variación mensual %", "frequency": "monthly", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/precios_consumidor/4_5_7_2.xls", "fetched_at": "2026-09-20T22:35:40Z"}</t>
         </is>
       </c>
     </row>

--- a/assets/data/bcv/excel/ove_bcv_inpc_nacional_mensual.xlsx
+++ b/assets/data/bcv/excel/ove_bcv_inpc_nacional_mensual.xlsx
@@ -650,7 +650,7 @@
       </c>
       <c r="K7" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:40Z</t>
+          <t>2026-09-21T23:27:46Z</t>
         </is>
       </c>
     </row>
@@ -699,7 +699,7 @@
       </c>
       <c r="K8" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:40Z</t>
+          <t>2026-09-21T23:27:46Z</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="K9" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:40Z</t>
+          <t>2026-09-21T23:27:46Z</t>
         </is>
       </c>
     </row>
@@ -797,7 +797,7 @@
       </c>
       <c r="K10" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:40Z</t>
+          <t>2026-09-21T23:27:46Z</t>
         </is>
       </c>
     </row>
@@ -846,7 +846,7 @@
       </c>
       <c r="K11" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:40Z</t>
+          <t>2026-09-21T23:27:46Z</t>
         </is>
       </c>
     </row>
@@ -895,7 +895,7 @@
       </c>
       <c r="K12" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:40Z</t>
+          <t>2026-09-21T23:27:46Z</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="K13" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:40Z</t>
+          <t>2026-09-21T23:27:46Z</t>
         </is>
       </c>
     </row>
@@ -993,7 +993,7 @@
       </c>
       <c r="K14" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:40Z</t>
+          <t>2026-09-21T23:27:46Z</t>
         </is>
       </c>
     </row>
@@ -1042,7 +1042,7 @@
       </c>
       <c r="K15" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:40Z</t>
+          <t>2026-09-21T23:27:46Z</t>
         </is>
       </c>
     </row>
@@ -1091,7 +1091,7 @@
       </c>
       <c r="K16" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:40Z</t>
+          <t>2026-09-21T23:27:46Z</t>
         </is>
       </c>
     </row>
@@ -1140,7 +1140,7 @@
       </c>
       <c r="K17" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:40Z</t>
+          <t>2026-09-21T23:27:46Z</t>
         </is>
       </c>
     </row>
@@ -1189,7 +1189,7 @@
       </c>
       <c r="K18" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:40Z</t>
+          <t>2026-09-21T23:27:46Z</t>
         </is>
       </c>
     </row>
@@ -1238,7 +1238,7 @@
       </c>
       <c r="K19" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:40Z</t>
+          <t>2026-09-21T23:27:46Z</t>
         </is>
       </c>
     </row>
@@ -1287,7 +1287,7 @@
       </c>
       <c r="K20" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:40Z</t>
+          <t>2026-09-21T23:27:46Z</t>
         </is>
       </c>
     </row>
@@ -1336,7 +1336,7 @@
       </c>
       <c r="K21" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:40Z</t>
+          <t>2026-09-21T23:27:46Z</t>
         </is>
       </c>
     </row>
@@ -1385,7 +1385,7 @@
       </c>
       <c r="K22" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:40Z</t>
+          <t>2026-09-21T23:27:46Z</t>
         </is>
       </c>
     </row>
@@ -1434,7 +1434,7 @@
       </c>
       <c r="K23" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:40Z</t>
+          <t>2026-09-21T23:27:46Z</t>
         </is>
       </c>
     </row>
@@ -1483,7 +1483,7 @@
       </c>
       <c r="K24" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:40Z</t>
+          <t>2026-09-21T23:27:46Z</t>
         </is>
       </c>
     </row>
@@ -1532,7 +1532,7 @@
       </c>
       <c r="K25" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:40Z</t>
+          <t>2026-09-21T23:27:46Z</t>
         </is>
       </c>
     </row>
@@ -1581,7 +1581,7 @@
       </c>
       <c r="K26" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:40Z</t>
+          <t>2026-09-21T23:27:46Z</t>
         </is>
       </c>
     </row>
@@ -1630,7 +1630,7 @@
       </c>
       <c r="K27" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:40Z</t>
+          <t>2026-09-21T23:27:46Z</t>
         </is>
       </c>
     </row>
@@ -1679,7 +1679,7 @@
       </c>
       <c r="K28" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:40Z</t>
+          <t>2026-09-21T23:27:46Z</t>
         </is>
       </c>
     </row>
@@ -1728,7 +1728,7 @@
       </c>
       <c r="K29" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:40Z</t>
+          <t>2026-09-21T23:27:46Z</t>
         </is>
       </c>
     </row>
@@ -1777,7 +1777,7 @@
       </c>
       <c r="K30" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:40Z</t>
+          <t>2026-09-21T23:27:46Z</t>
         </is>
       </c>
     </row>
@@ -1826,7 +1826,7 @@
       </c>
       <c r="K31" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:40Z</t>
+          <t>2026-09-21T23:27:46Z</t>
         </is>
       </c>
     </row>
@@ -1875,7 +1875,7 @@
       </c>
       <c r="K32" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:40Z</t>
+          <t>2026-09-21T23:27:46Z</t>
         </is>
       </c>
     </row>
@@ -1924,7 +1924,7 @@
       </c>
       <c r="K33" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:40Z</t>
+          <t>2026-09-21T23:27:46Z</t>
         </is>
       </c>
     </row>
@@ -1973,7 +1973,7 @@
       </c>
       <c r="K34" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:40Z</t>
+          <t>2026-09-21T23:27:46Z</t>
         </is>
       </c>
     </row>
@@ -2022,7 +2022,7 @@
       </c>
       <c r="K35" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:40Z</t>
+          <t>2026-09-21T23:27:46Z</t>
         </is>
       </c>
     </row>
@@ -2071,7 +2071,7 @@
       </c>
       <c r="K36" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:40Z</t>
+          <t>2026-09-21T23:27:46Z</t>
         </is>
       </c>
     </row>
@@ -2120,7 +2120,7 @@
       </c>
       <c r="K37" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:40Z</t>
+          <t>2026-09-21T23:27:46Z</t>
         </is>
       </c>
     </row>
@@ -2169,7 +2169,7 @@
       </c>
       <c r="K38" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:40Z</t>
+          <t>2026-09-21T23:27:46Z</t>
         </is>
       </c>
     </row>
@@ -2218,7 +2218,7 @@
       </c>
       <c r="K39" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:40Z</t>
+          <t>2026-09-21T23:27:46Z</t>
         </is>
       </c>
     </row>
@@ -2267,7 +2267,7 @@
       </c>
       <c r="K40" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:40Z</t>
+          <t>2026-09-21T23:27:46Z</t>
         </is>
       </c>
     </row>
@@ -2316,7 +2316,7 @@
       </c>
       <c r="K41" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:40Z</t>
+          <t>2026-09-21T23:27:46Z</t>
         </is>
       </c>
     </row>
@@ -2365,7 +2365,7 @@
       </c>
       <c r="K42" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:40Z</t>
+          <t>2026-09-21T23:27:46Z</t>
         </is>
       </c>
     </row>
@@ -2414,7 +2414,7 @@
       </c>
       <c r="K43" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:40Z</t>
+          <t>2026-09-21T23:27:46Z</t>
         </is>
       </c>
     </row>
@@ -2463,7 +2463,7 @@
       </c>
       <c r="K44" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:40Z</t>
+          <t>2026-09-21T23:27:46Z</t>
         </is>
       </c>
     </row>
@@ -2512,7 +2512,7 @@
       </c>
       <c r="K45" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:40Z</t>
+          <t>2026-09-21T23:27:46Z</t>
         </is>
       </c>
     </row>
@@ -2561,7 +2561,7 @@
       </c>
       <c r="K46" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:40Z</t>
+          <t>2026-09-21T23:27:46Z</t>
         </is>
       </c>
     </row>
@@ -2610,7 +2610,7 @@
       </c>
       <c r="K47" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:40Z</t>
+          <t>2026-09-21T23:27:46Z</t>
         </is>
       </c>
     </row>
@@ -2659,7 +2659,7 @@
       </c>
       <c r="K48" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:40Z</t>
+          <t>2026-09-21T23:27:46Z</t>
         </is>
       </c>
     </row>
@@ -2708,7 +2708,7 @@
       </c>
       <c r="K49" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:40Z</t>
+          <t>2026-09-21T23:27:46Z</t>
         </is>
       </c>
     </row>
@@ -2757,7 +2757,7 @@
       </c>
       <c r="K50" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:40Z</t>
+          <t>2026-09-21T23:27:46Z</t>
         </is>
       </c>
     </row>
@@ -2806,7 +2806,7 @@
       </c>
       <c r="K51" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:40Z</t>
+          <t>2026-09-21T23:27:46Z</t>
         </is>
       </c>
     </row>
@@ -2855,7 +2855,7 @@
       </c>
       <c r="K52" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:40Z</t>
+          <t>2026-09-21T23:27:46Z</t>
         </is>
       </c>
     </row>
@@ -2904,7 +2904,7 @@
       </c>
       <c r="K53" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:40Z</t>
+          <t>2026-09-21T23:27:46Z</t>
         </is>
       </c>
     </row>
@@ -2953,7 +2953,7 @@
       </c>
       <c r="K54" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:40Z</t>
+          <t>2026-09-21T23:27:46Z</t>
         </is>
       </c>
     </row>
@@ -3002,7 +3002,7 @@
       </c>
       <c r="K55" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:40Z</t>
+          <t>2026-09-21T23:27:46Z</t>
         </is>
       </c>
     </row>
@@ -3051,7 +3051,7 @@
       </c>
       <c r="K56" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:40Z</t>
+          <t>2026-09-21T23:27:46Z</t>
         </is>
       </c>
     </row>
@@ -3100,7 +3100,7 @@
       </c>
       <c r="K57" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:40Z</t>
+          <t>2026-09-21T23:27:46Z</t>
         </is>
       </c>
     </row>
@@ -3149,7 +3149,7 @@
       </c>
       <c r="K58" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:40Z</t>
+          <t>2026-09-21T23:27:46Z</t>
         </is>
       </c>
     </row>
@@ -3198,7 +3198,7 @@
       </c>
       <c r="K59" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:40Z</t>
+          <t>2026-09-21T23:27:46Z</t>
         </is>
       </c>
     </row>
@@ -3247,7 +3247,7 @@
       </c>
       <c r="K60" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:40Z</t>
+          <t>2026-09-21T23:27:46Z</t>
         </is>
       </c>
     </row>
@@ -3296,7 +3296,7 @@
       </c>
       <c r="K61" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:40Z</t>
+          <t>2026-09-21T23:27:46Z</t>
         </is>
       </c>
     </row>
@@ -3345,7 +3345,7 @@
       </c>
       <c r="K62" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:40Z</t>
+          <t>2026-09-21T23:27:46Z</t>
         </is>
       </c>
     </row>
@@ -3394,7 +3394,7 @@
       </c>
       <c r="K63" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:40Z</t>
+          <t>2026-09-21T23:27:46Z</t>
         </is>
       </c>
     </row>
@@ -3443,7 +3443,7 @@
       </c>
       <c r="K64" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:40Z</t>
+          <t>2026-09-21T23:27:46Z</t>
         </is>
       </c>
     </row>
@@ -3492,7 +3492,7 @@
       </c>
       <c r="K65" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:40Z</t>
+          <t>2026-09-21T23:27:46Z</t>
         </is>
       </c>
     </row>
@@ -3541,7 +3541,7 @@
       </c>
       <c r="K66" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:40Z</t>
+          <t>2026-09-21T23:27:46Z</t>
         </is>
       </c>
     </row>
@@ -3590,7 +3590,7 @@
       </c>
       <c r="K67" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:40Z</t>
+          <t>2026-09-21T23:27:46Z</t>
         </is>
       </c>
     </row>
@@ -3639,7 +3639,7 @@
       </c>
       <c r="K68" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:40Z</t>
+          <t>2026-09-21T23:27:46Z</t>
         </is>
       </c>
     </row>
@@ -3688,7 +3688,7 @@
       </c>
       <c r="K69" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:40Z</t>
+          <t>2026-09-21T23:27:46Z</t>
         </is>
       </c>
     </row>
@@ -3737,7 +3737,7 @@
       </c>
       <c r="K70" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:40Z</t>
+          <t>2026-09-21T23:27:46Z</t>
         </is>
       </c>
     </row>
@@ -3786,7 +3786,7 @@
       </c>
       <c r="K71" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:40Z</t>
+          <t>2026-09-21T23:27:46Z</t>
         </is>
       </c>
     </row>
@@ -3835,7 +3835,7 @@
       </c>
       <c r="K72" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:40Z</t>
+          <t>2026-09-21T23:27:46Z</t>
         </is>
       </c>
     </row>
@@ -3884,7 +3884,7 @@
       </c>
       <c r="K73" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:40Z</t>
+          <t>2026-09-21T23:27:46Z</t>
         </is>
       </c>
     </row>
@@ -3933,7 +3933,7 @@
       </c>
       <c r="K74" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:40Z</t>
+          <t>2026-09-21T23:27:46Z</t>
         </is>
       </c>
     </row>
@@ -3982,7 +3982,7 @@
       </c>
       <c r="K75" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:40Z</t>
+          <t>2026-09-21T23:27:46Z</t>
         </is>
       </c>
     </row>
@@ -4031,7 +4031,7 @@
       </c>
       <c r="K76" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:40Z</t>
+          <t>2026-09-21T23:27:46Z</t>
         </is>
       </c>
     </row>
@@ -4080,7 +4080,7 @@
       </c>
       <c r="K77" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:40Z</t>
+          <t>2026-09-21T23:27:46Z</t>
         </is>
       </c>
     </row>
@@ -4129,7 +4129,7 @@
       </c>
       <c r="K78" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:40Z</t>
+          <t>2026-09-21T23:27:46Z</t>
         </is>
       </c>
     </row>
@@ -4178,7 +4178,7 @@
       </c>
       <c r="K79" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:40Z</t>
+          <t>2026-09-21T23:27:46Z</t>
         </is>
       </c>
     </row>
@@ -4227,7 +4227,7 @@
       </c>
       <c r="K80" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:40Z</t>
+          <t>2026-09-21T23:27:46Z</t>
         </is>
       </c>
     </row>
@@ -4276,7 +4276,7 @@
       </c>
       <c r="K81" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:40Z</t>
+          <t>2026-09-21T23:27:46Z</t>
         </is>
       </c>
     </row>
@@ -4325,7 +4325,7 @@
       </c>
       <c r="K82" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:40Z</t>
+          <t>2026-09-21T23:27:46Z</t>
         </is>
       </c>
     </row>
@@ -4374,7 +4374,7 @@
       </c>
       <c r="K83" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:40Z</t>
+          <t>2026-09-21T23:27:46Z</t>
         </is>
       </c>
     </row>
@@ -4423,7 +4423,7 @@
       </c>
       <c r="K84" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:40Z</t>
+          <t>2026-09-21T23:27:46Z</t>
         </is>
       </c>
     </row>
@@ -4472,7 +4472,7 @@
       </c>
       <c r="K85" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:40Z</t>
+          <t>2026-09-21T23:27:46Z</t>
         </is>
       </c>
     </row>
@@ -4521,7 +4521,7 @@
       </c>
       <c r="K86" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:40Z</t>
+          <t>2026-09-21T23:27:46Z</t>
         </is>
       </c>
     </row>
@@ -4570,7 +4570,7 @@
       </c>
       <c r="K87" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:40Z</t>
+          <t>2026-09-21T23:27:46Z</t>
         </is>
       </c>
     </row>
@@ -4619,7 +4619,7 @@
       </c>
       <c r="K88" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:40Z</t>
+          <t>2026-09-21T23:27:46Z</t>
         </is>
       </c>
     </row>
@@ -4668,7 +4668,7 @@
       </c>
       <c r="K89" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:40Z</t>
+          <t>2026-09-21T23:27:46Z</t>
         </is>
       </c>
     </row>
@@ -4717,7 +4717,7 @@
       </c>
       <c r="K90" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:40Z</t>
+          <t>2026-09-21T23:27:46Z</t>
         </is>
       </c>
     </row>
@@ -4766,7 +4766,7 @@
       </c>
       <c r="K91" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:40Z</t>
+          <t>2026-09-21T23:27:46Z</t>
         </is>
       </c>
     </row>
@@ -4815,7 +4815,7 @@
       </c>
       <c r="K92" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:40Z</t>
+          <t>2026-09-21T23:27:46Z</t>
         </is>
       </c>
     </row>
@@ -4864,7 +4864,7 @@
       </c>
       <c r="K93" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:40Z</t>
+          <t>2026-09-21T23:27:46Z</t>
         </is>
       </c>
     </row>
@@ -4913,7 +4913,7 @@
       </c>
       <c r="K94" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:40Z</t>
+          <t>2026-09-21T23:27:46Z</t>
         </is>
       </c>
     </row>
@@ -4962,7 +4962,7 @@
       </c>
       <c r="K95" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:40Z</t>
+          <t>2026-09-21T23:27:46Z</t>
         </is>
       </c>
     </row>
@@ -5011,7 +5011,7 @@
       </c>
       <c r="K96" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:40Z</t>
+          <t>2026-09-21T23:27:46Z</t>
         </is>
       </c>
     </row>
@@ -5060,7 +5060,7 @@
       </c>
       <c r="K97" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:40Z</t>
+          <t>2026-09-21T23:27:46Z</t>
         </is>
       </c>
     </row>
@@ -5109,7 +5109,7 @@
       </c>
       <c r="K98" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:40Z</t>
+          <t>2026-09-21T23:27:46Z</t>
         </is>
       </c>
     </row>
@@ -5158,7 +5158,7 @@
       </c>
       <c r="K99" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:40Z</t>
+          <t>2026-09-21T23:27:46Z</t>
         </is>
       </c>
     </row>
@@ -5207,7 +5207,7 @@
       </c>
       <c r="K100" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:40Z</t>
+          <t>2026-09-21T23:27:46Z</t>
         </is>
       </c>
     </row>
@@ -5256,7 +5256,7 @@
       </c>
       <c r="K101" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:40Z</t>
+          <t>2026-09-21T23:27:46Z</t>
         </is>
       </c>
     </row>
@@ -5305,7 +5305,7 @@
       </c>
       <c r="K102" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:40Z</t>
+          <t>2026-09-21T23:27:46Z</t>
         </is>
       </c>
     </row>
@@ -5354,7 +5354,7 @@
       </c>
       <c r="K103" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:40Z</t>
+          <t>2026-09-21T23:27:46Z</t>
         </is>
       </c>
     </row>
@@ -5403,7 +5403,7 @@
       </c>
       <c r="K104" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:40Z</t>
+          <t>2026-09-21T23:27:46Z</t>
         </is>
       </c>
     </row>
@@ -5452,7 +5452,7 @@
       </c>
       <c r="K105" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:40Z</t>
+          <t>2026-09-21T23:27:46Z</t>
         </is>
       </c>
     </row>
@@ -5501,7 +5501,7 @@
       </c>
       <c r="K106" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:40Z</t>
+          <t>2026-09-21T23:27:46Z</t>
         </is>
       </c>
     </row>
@@ -5550,7 +5550,7 @@
       </c>
       <c r="K107" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:40Z</t>
+          <t>2026-09-21T23:27:46Z</t>
         </is>
       </c>
     </row>
@@ -5599,7 +5599,7 @@
       </c>
       <c r="K108" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:40Z</t>
+          <t>2026-09-21T23:27:46Z</t>
         </is>
       </c>
     </row>
@@ -5648,7 +5648,7 @@
       </c>
       <c r="K109" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:40Z</t>
+          <t>2026-09-21T23:27:46Z</t>
         </is>
       </c>
     </row>
@@ -5697,7 +5697,7 @@
       </c>
       <c r="K110" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:40Z</t>
+          <t>2026-09-21T23:27:46Z</t>
         </is>
       </c>
     </row>
@@ -5746,7 +5746,7 @@
       </c>
       <c r="K111" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:40Z</t>
+          <t>2026-09-21T23:27:46Z</t>
         </is>
       </c>
     </row>
@@ -5795,7 +5795,7 @@
       </c>
       <c r="K112" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:40Z</t>
+          <t>2026-09-21T23:27:46Z</t>
         </is>
       </c>
     </row>
@@ -5844,7 +5844,7 @@
       </c>
       <c r="K113" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:40Z</t>
+          <t>2026-09-21T23:27:46Z</t>
         </is>
       </c>
     </row>
@@ -5893,7 +5893,7 @@
       </c>
       <c r="K114" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:40Z</t>
+          <t>2026-09-21T23:27:46Z</t>
         </is>
       </c>
     </row>
@@ -5942,7 +5942,7 @@
       </c>
       <c r="K115" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:40Z</t>
+          <t>2026-09-21T23:27:46Z</t>
         </is>
       </c>
     </row>
@@ -5991,7 +5991,7 @@
       </c>
       <c r="K116" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:40Z</t>
+          <t>2026-09-21T23:27:46Z</t>
         </is>
       </c>
     </row>
@@ -6040,7 +6040,7 @@
       </c>
       <c r="K117" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:40Z</t>
+          <t>2026-09-21T23:27:46Z</t>
         </is>
       </c>
     </row>
@@ -6089,7 +6089,7 @@
       </c>
       <c r="K118" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:40Z</t>
+          <t>2026-09-21T23:27:46Z</t>
         </is>
       </c>
     </row>
@@ -6138,7 +6138,7 @@
       </c>
       <c r="K119" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:40Z</t>
+          <t>2026-09-21T23:27:46Z</t>
         </is>
       </c>
     </row>
@@ -6187,7 +6187,7 @@
       </c>
       <c r="K120" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:40Z</t>
+          <t>2026-09-21T23:27:46Z</t>
         </is>
       </c>
     </row>
@@ -6236,7 +6236,7 @@
       </c>
       <c r="K121" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:40Z</t>
+          <t>2026-09-21T23:27:46Z</t>
         </is>
       </c>
     </row>
@@ -6285,7 +6285,7 @@
       </c>
       <c r="K122" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:40Z</t>
+          <t>2026-09-21T23:27:46Z</t>
         </is>
       </c>
     </row>
@@ -6334,7 +6334,7 @@
       </c>
       <c r="K123" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:40Z</t>
+          <t>2026-09-21T23:27:46Z</t>
         </is>
       </c>
     </row>
@@ -6383,7 +6383,7 @@
       </c>
       <c r="K124" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:40Z</t>
+          <t>2026-09-21T23:27:46Z</t>
         </is>
       </c>
     </row>
@@ -6432,7 +6432,7 @@
       </c>
       <c r="K125" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:40Z</t>
+          <t>2026-09-21T23:27:46Z</t>
         </is>
       </c>
     </row>
@@ -6481,7 +6481,7 @@
       </c>
       <c r="K126" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:40Z</t>
+          <t>2026-09-21T23:27:46Z</t>
         </is>
       </c>
     </row>
@@ -6530,7 +6530,7 @@
       </c>
       <c r="K127" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:40Z</t>
+          <t>2026-09-21T23:27:46Z</t>
         </is>
       </c>
     </row>
@@ -6579,7 +6579,7 @@
       </c>
       <c r="K128" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:40Z</t>
+          <t>2026-09-21T23:27:46Z</t>
         </is>
       </c>
     </row>
@@ -6628,7 +6628,7 @@
       </c>
       <c r="K129" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:40Z</t>
+          <t>2026-09-21T23:27:46Z</t>
         </is>
       </c>
     </row>
@@ -6677,7 +6677,7 @@
       </c>
       <c r="K130" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:40Z</t>
+          <t>2026-09-21T23:27:46Z</t>
         </is>
       </c>
     </row>
@@ -6726,7 +6726,7 @@
       </c>
       <c r="K131" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:40Z</t>
+          <t>2026-09-21T23:27:46Z</t>
         </is>
       </c>
     </row>
@@ -6775,7 +6775,7 @@
       </c>
       <c r="K132" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:40Z</t>
+          <t>2026-09-21T23:27:46Z</t>
         </is>
       </c>
     </row>
@@ -6824,7 +6824,7 @@
       </c>
       <c r="K133" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:40Z</t>
+          <t>2026-09-21T23:27:46Z</t>
         </is>
       </c>
     </row>
@@ -6873,7 +6873,7 @@
       </c>
       <c r="K134" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:40Z</t>
+          <t>2026-09-21T23:27:46Z</t>
         </is>
       </c>
     </row>
@@ -6922,7 +6922,7 @@
       </c>
       <c r="K135" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:40Z</t>
+          <t>2026-09-21T23:27:46Z</t>
         </is>
       </c>
     </row>
@@ -6971,7 +6971,7 @@
       </c>
       <c r="K136" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:40Z</t>
+          <t>2026-09-21T23:27:46Z</t>
         </is>
       </c>
     </row>
@@ -7020,7 +7020,7 @@
       </c>
       <c r="K137" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:40Z</t>
+          <t>2026-09-21T23:27:46Z</t>
         </is>
       </c>
     </row>
@@ -7069,7 +7069,7 @@
       </c>
       <c r="K138" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:40Z</t>
+          <t>2026-09-21T23:27:46Z</t>
         </is>
       </c>
     </row>
@@ -7118,7 +7118,7 @@
       </c>
       <c r="K139" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:40Z</t>
+          <t>2026-09-21T23:27:46Z</t>
         </is>
       </c>
     </row>
@@ -7167,7 +7167,7 @@
       </c>
       <c r="K140" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:40Z</t>
+          <t>2026-09-21T23:27:46Z</t>
         </is>
       </c>
     </row>
@@ -7216,7 +7216,7 @@
       </c>
       <c r="K141" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:40Z</t>
+          <t>2026-09-21T23:27:46Z</t>
         </is>
       </c>
     </row>
@@ -7265,7 +7265,7 @@
       </c>
       <c r="K142" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:40Z</t>
+          <t>2026-09-21T23:27:46Z</t>
         </is>
       </c>
     </row>
@@ -7314,7 +7314,7 @@
       </c>
       <c r="K143" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:40Z</t>
+          <t>2026-09-21T23:27:46Z</t>
         </is>
       </c>
     </row>
@@ -7363,7 +7363,7 @@
       </c>
       <c r="K144" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:40Z</t>
+          <t>2026-09-21T23:27:46Z</t>
         </is>
       </c>
     </row>
@@ -7412,7 +7412,7 @@
       </c>
       <c r="K145" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:40Z</t>
+          <t>2026-09-21T23:27:46Z</t>
         </is>
       </c>
     </row>
@@ -7461,7 +7461,7 @@
       </c>
       <c r="K146" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:40Z</t>
+          <t>2026-09-21T23:27:46Z</t>
         </is>
       </c>
     </row>
@@ -7510,7 +7510,7 @@
       </c>
       <c r="K147" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:40Z</t>
+          <t>2026-09-21T23:27:46Z</t>
         </is>
       </c>
     </row>
@@ -7559,7 +7559,7 @@
       </c>
       <c r="K148" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:40Z</t>
+          <t>2026-09-21T23:27:46Z</t>
         </is>
       </c>
     </row>
@@ -7608,7 +7608,7 @@
       </c>
       <c r="K149" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:40Z</t>
+          <t>2026-09-21T23:27:46Z</t>
         </is>
       </c>
     </row>
@@ -7657,7 +7657,7 @@
       </c>
       <c r="K150" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:40Z</t>
+          <t>2026-09-21T23:27:46Z</t>
         </is>
       </c>
     </row>
@@ -7706,7 +7706,7 @@
       </c>
       <c r="K151" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:40Z</t>
+          <t>2026-09-21T23:27:46Z</t>
         </is>
       </c>
     </row>
@@ -7755,7 +7755,7 @@
       </c>
       <c r="K152" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:40Z</t>
+          <t>2026-09-21T23:27:46Z</t>
         </is>
       </c>
     </row>
@@ -7804,7 +7804,7 @@
       </c>
       <c r="K153" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:40Z</t>
+          <t>2026-09-21T23:27:46Z</t>
         </is>
       </c>
     </row>
@@ -7853,7 +7853,7 @@
       </c>
       <c r="K154" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:40Z</t>
+          <t>2026-09-21T23:27:46Z</t>
         </is>
       </c>
     </row>
@@ -7902,7 +7902,7 @@
       </c>
       <c r="K155" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:40Z</t>
+          <t>2026-09-21T23:27:46Z</t>
         </is>
       </c>
     </row>
@@ -7951,7 +7951,7 @@
       </c>
       <c r="K156" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:40Z</t>
+          <t>2026-09-21T23:27:46Z</t>
         </is>
       </c>
     </row>
@@ -8000,7 +8000,7 @@
       </c>
       <c r="K157" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:40Z</t>
+          <t>2026-09-21T23:27:46Z</t>
         </is>
       </c>
     </row>
@@ -8049,7 +8049,7 @@
       </c>
       <c r="K158" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:40Z</t>
+          <t>2026-09-21T23:27:46Z</t>
         </is>
       </c>
     </row>
@@ -8098,7 +8098,7 @@
       </c>
       <c r="K159" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:40Z</t>
+          <t>2026-09-21T23:27:46Z</t>
         </is>
       </c>
     </row>
@@ -8147,7 +8147,7 @@
       </c>
       <c r="K160" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:40Z</t>
+          <t>2026-09-21T23:27:46Z</t>
         </is>
       </c>
     </row>
@@ -8196,7 +8196,7 @@
       </c>
       <c r="K161" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:40Z</t>
+          <t>2026-09-21T23:27:46Z</t>
         </is>
       </c>
     </row>
@@ -8245,7 +8245,7 @@
       </c>
       <c r="K162" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:40Z</t>
+          <t>2026-09-21T23:27:46Z</t>
         </is>
       </c>
     </row>
@@ -8294,7 +8294,7 @@
       </c>
       <c r="K163" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:40Z</t>
+          <t>2026-09-21T23:27:46Z</t>
         </is>
       </c>
     </row>
@@ -8343,7 +8343,7 @@
       </c>
       <c r="K164" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:40Z</t>
+          <t>2026-09-21T23:27:46Z</t>
         </is>
       </c>
     </row>
@@ -8392,7 +8392,7 @@
       </c>
       <c r="K165" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:40Z</t>
+          <t>2026-09-21T23:27:46Z</t>
         </is>
       </c>
     </row>
@@ -8441,7 +8441,7 @@
       </c>
       <c r="K166" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:40Z</t>
+          <t>2026-09-21T23:27:46Z</t>
         </is>
       </c>
     </row>
@@ -8490,7 +8490,7 @@
       </c>
       <c r="K167" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:40Z</t>
+          <t>2026-09-21T23:27:46Z</t>
         </is>
       </c>
     </row>
@@ -8539,7 +8539,7 @@
       </c>
       <c r="K168" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:40Z</t>
+          <t>2026-09-21T23:27:46Z</t>
         </is>
       </c>
     </row>
@@ -8588,7 +8588,7 @@
       </c>
       <c r="K169" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:40Z</t>
+          <t>2026-09-21T23:27:46Z</t>
         </is>
       </c>
     </row>
@@ -8637,7 +8637,7 @@
       </c>
       <c r="K170" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:40Z</t>
+          <t>2026-09-21T23:27:46Z</t>
         </is>
       </c>
     </row>
@@ -8686,7 +8686,7 @@
       </c>
       <c r="K171" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:40Z</t>
+          <t>2026-09-21T23:27:46Z</t>
         </is>
       </c>
     </row>
@@ -8735,7 +8735,7 @@
       </c>
       <c r="K172" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:40Z</t>
+          <t>2026-09-21T23:27:46Z</t>
         </is>
       </c>
     </row>
@@ -8784,7 +8784,7 @@
       </c>
       <c r="K173" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:40Z</t>
+          <t>2026-09-21T23:27:46Z</t>
         </is>
       </c>
     </row>
@@ -8833,7 +8833,7 @@
       </c>
       <c r="K174" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:40Z</t>
+          <t>2026-09-21T23:27:46Z</t>
         </is>
       </c>
     </row>
@@ -8882,7 +8882,7 @@
       </c>
       <c r="K175" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:40Z</t>
+          <t>2026-09-21T23:27:46Z</t>
         </is>
       </c>
     </row>
@@ -8931,7 +8931,7 @@
       </c>
       <c r="K176" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:40Z</t>
+          <t>2026-09-21T23:27:46Z</t>
         </is>
       </c>
     </row>
@@ -8980,7 +8980,7 @@
       </c>
       <c r="K177" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:40Z</t>
+          <t>2026-09-21T23:27:46Z</t>
         </is>
       </c>
     </row>
@@ -9029,7 +9029,7 @@
       </c>
       <c r="K178" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:40Z</t>
+          <t>2026-09-21T23:27:46Z</t>
         </is>
       </c>
     </row>
@@ -9078,7 +9078,7 @@
       </c>
       <c r="K179" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:40Z</t>
+          <t>2026-09-21T23:27:46Z</t>
         </is>
       </c>
     </row>
@@ -9127,7 +9127,7 @@
       </c>
       <c r="K180" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:40Z</t>
+          <t>2026-09-21T23:27:46Z</t>
         </is>
       </c>
     </row>
@@ -9176,7 +9176,7 @@
       </c>
       <c r="K181" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:40Z</t>
+          <t>2026-09-21T23:27:46Z</t>
         </is>
       </c>
     </row>
@@ -9225,7 +9225,7 @@
       </c>
       <c r="K182" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:40Z</t>
+          <t>2026-09-21T23:27:46Z</t>
         </is>
       </c>
     </row>
@@ -9274,7 +9274,7 @@
       </c>
       <c r="K183" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:40Z</t>
+          <t>2026-09-21T23:27:46Z</t>
         </is>
       </c>
     </row>
@@ -9323,7 +9323,7 @@
       </c>
       <c r="K184" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:40Z</t>
+          <t>2026-09-21T23:27:46Z</t>
         </is>
       </c>
     </row>
@@ -9372,7 +9372,7 @@
       </c>
       <c r="K185" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:40Z</t>
+          <t>2026-09-21T23:27:46Z</t>
         </is>
       </c>
     </row>
@@ -9421,7 +9421,7 @@
       </c>
       <c r="K186" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:40Z</t>
+          <t>2026-09-21T23:27:46Z</t>
         </is>
       </c>
     </row>
@@ -9470,7 +9470,7 @@
       </c>
       <c r="K187" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:40Z</t>
+          <t>2026-09-21T23:27:46Z</t>
         </is>
       </c>
     </row>
@@ -9519,7 +9519,7 @@
       </c>
       <c r="K188" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:40Z</t>
+          <t>2026-09-21T23:27:46Z</t>
         </is>
       </c>
     </row>
@@ -9568,7 +9568,7 @@
       </c>
       <c r="K189" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:40Z</t>
+          <t>2026-09-21T23:27:46Z</t>
         </is>
       </c>
     </row>
@@ -9617,7 +9617,7 @@
       </c>
       <c r="K190" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:40Z</t>
+          <t>2026-09-21T23:27:46Z</t>
         </is>
       </c>
     </row>
@@ -9666,7 +9666,7 @@
       </c>
       <c r="K191" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:40Z</t>
+          <t>2026-09-21T23:27:46Z</t>
         </is>
       </c>
     </row>
@@ -9715,7 +9715,7 @@
       </c>
       <c r="K192" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:40Z</t>
+          <t>2026-09-21T23:27:46Z</t>
         </is>
       </c>
     </row>
@@ -9764,7 +9764,7 @@
       </c>
       <c r="K193" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:40Z</t>
+          <t>2026-09-21T23:27:46Z</t>
         </is>
       </c>
     </row>
@@ -9813,7 +9813,7 @@
       </c>
       <c r="K194" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:40Z</t>
+          <t>2026-09-21T23:27:46Z</t>
         </is>
       </c>
     </row>
@@ -9862,7 +9862,7 @@
       </c>
       <c r="K195" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:40Z</t>
+          <t>2026-09-21T23:27:46Z</t>
         </is>
       </c>
     </row>
@@ -9911,7 +9911,7 @@
       </c>
       <c r="K196" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:40Z</t>
+          <t>2026-09-21T23:27:46Z</t>
         </is>
       </c>
     </row>
@@ -9960,7 +9960,7 @@
       </c>
       <c r="K197" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:40Z</t>
+          <t>2026-09-21T23:27:46Z</t>
         </is>
       </c>
     </row>
@@ -10009,7 +10009,7 @@
       </c>
       <c r="K198" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:40Z</t>
+          <t>2026-09-21T23:27:46Z</t>
         </is>
       </c>
     </row>
@@ -10058,7 +10058,7 @@
       </c>
       <c r="K199" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:40Z</t>
+          <t>2026-09-21T23:27:46Z</t>
         </is>
       </c>
     </row>
@@ -10107,7 +10107,7 @@
       </c>
       <c r="K200" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:40Z</t>
+          <t>2026-09-21T23:27:46Z</t>
         </is>
       </c>
     </row>
@@ -10156,7 +10156,7 @@
       </c>
       <c r="K201" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:40Z</t>
+          <t>2026-09-21T23:27:46Z</t>
         </is>
       </c>
     </row>
@@ -10205,7 +10205,7 @@
       </c>
       <c r="K202" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:40Z</t>
+          <t>2026-09-21T23:27:46Z</t>
         </is>
       </c>
     </row>
@@ -10254,7 +10254,7 @@
       </c>
       <c r="K203" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:40Z</t>
+          <t>2026-09-21T23:27:46Z</t>
         </is>
       </c>
     </row>
@@ -10303,7 +10303,7 @@
       </c>
       <c r="K204" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:40Z</t>
+          <t>2026-09-21T23:27:46Z</t>
         </is>
       </c>
     </row>
@@ -10352,7 +10352,7 @@
       </c>
       <c r="K205" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:40Z</t>
+          <t>2026-09-21T23:27:46Z</t>
         </is>
       </c>
     </row>
@@ -10401,7 +10401,7 @@
       </c>
       <c r="K206" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:40Z</t>
+          <t>2026-09-21T23:27:46Z</t>
         </is>
       </c>
     </row>
@@ -10450,7 +10450,7 @@
       </c>
       <c r="K207" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:40Z</t>
+          <t>2026-09-21T23:27:46Z</t>
         </is>
       </c>
     </row>
@@ -10499,7 +10499,7 @@
       </c>
       <c r="K208" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:40Z</t>
+          <t>2026-09-21T23:27:46Z</t>
         </is>
       </c>
     </row>
@@ -10548,7 +10548,7 @@
       </c>
       <c r="K209" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:40Z</t>
+          <t>2026-09-21T23:27:46Z</t>
         </is>
       </c>
     </row>
@@ -10597,7 +10597,7 @@
       </c>
       <c r="K210" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:40Z</t>
+          <t>2026-09-21T23:27:46Z</t>
         </is>
       </c>
     </row>
@@ -10646,7 +10646,7 @@
       </c>
       <c r="K211" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:40Z</t>
+          <t>2026-09-21T23:27:46Z</t>
         </is>
       </c>
     </row>
@@ -10695,7 +10695,7 @@
       </c>
       <c r="K212" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:40Z</t>
+          <t>2026-09-21T23:27:46Z</t>
         </is>
       </c>
     </row>
@@ -10744,7 +10744,7 @@
       </c>
       <c r="K213" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:40Z</t>
+          <t>2026-09-21T23:27:46Z</t>
         </is>
       </c>
     </row>
@@ -10793,7 +10793,7 @@
       </c>
       <c r="K214" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:40Z</t>
+          <t>2026-09-21T23:27:46Z</t>
         </is>
       </c>
     </row>
@@ -10842,7 +10842,7 @@
       </c>
       <c r="K215" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:40Z</t>
+          <t>2026-09-21T23:27:46Z</t>
         </is>
       </c>
     </row>
@@ -10891,7 +10891,7 @@
       </c>
       <c r="K216" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:40Z</t>
+          <t>2026-09-21T23:27:46Z</t>
         </is>
       </c>
     </row>
@@ -10940,7 +10940,7 @@
       </c>
       <c r="K217" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:40Z</t>
+          <t>2026-09-21T23:27:46Z</t>
         </is>
       </c>
     </row>
@@ -10989,7 +10989,7 @@
       </c>
       <c r="K218" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:40Z</t>
+          <t>2026-09-21T23:27:46Z</t>
         </is>
       </c>
     </row>
@@ -11038,7 +11038,7 @@
       </c>
       <c r="K219" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:40Z</t>
+          <t>2026-09-21T23:27:46Z</t>
         </is>
       </c>
     </row>
@@ -11087,7 +11087,7 @@
       </c>
       <c r="K220" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:40Z</t>
+          <t>2026-09-21T23:27:46Z</t>
         </is>
       </c>
     </row>
@@ -11136,7 +11136,7 @@
       </c>
       <c r="K221" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:40Z</t>
+          <t>2026-09-21T23:27:46Z</t>
         </is>
       </c>
     </row>
@@ -11185,7 +11185,7 @@
       </c>
       <c r="K222" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:40Z</t>
+          <t>2026-09-21T23:27:46Z</t>
         </is>
       </c>
     </row>
@@ -11234,7 +11234,7 @@
       </c>
       <c r="K223" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:40Z</t>
+          <t>2026-09-21T23:27:46Z</t>
         </is>
       </c>
     </row>
@@ -11283,7 +11283,7 @@
       </c>
       <c r="K224" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:40Z</t>
+          <t>2026-09-21T23:27:46Z</t>
         </is>
       </c>
     </row>
@@ -11332,7 +11332,7 @@
       </c>
       <c r="K225" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:40Z</t>
+          <t>2026-09-21T23:27:46Z</t>
         </is>
       </c>
     </row>
@@ -11381,7 +11381,7 @@
       </c>
       <c r="K226" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:40Z</t>
+          <t>2026-09-21T23:27:46Z</t>
         </is>
       </c>
     </row>
@@ -11430,7 +11430,7 @@
       </c>
       <c r="K227" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:40Z</t>
+          <t>2026-09-21T23:27:46Z</t>
         </is>
       </c>
     </row>
@@ -11479,7 +11479,7 @@
       </c>
       <c r="K228" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:40Z</t>
+          <t>2026-09-21T23:27:46Z</t>
         </is>
       </c>
     </row>
@@ -11528,7 +11528,7 @@
       </c>
       <c r="K229" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:40Z</t>
+          <t>2026-09-21T23:27:46Z</t>
         </is>
       </c>
     </row>
@@ -11577,7 +11577,7 @@
       </c>
       <c r="K230" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:40Z</t>
+          <t>2026-09-21T23:27:46Z</t>
         </is>
       </c>
     </row>
@@ -11626,7 +11626,7 @@
       </c>
       <c r="K231" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:40Z</t>
+          <t>2026-09-21T23:27:46Z</t>
         </is>
       </c>
     </row>
@@ -11758,7 +11758,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:40Z</t>
+          <t>2026-09-21T23:27:46Z</t>
         </is>
       </c>
     </row>
@@ -11804,7 +11804,7 @@
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>{"date": "2026-08-01", "year": 2026, "month": 8, "month_name": "Agosto", "index_value": 637409769724325.1, "monthly_variation_pct": 8.9, "unit": "Índice base diciembre 2007=100 y variación mensual %", "frequency": "monthly", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/precios_consumidor/4_5_7_2.xls", "fetched_at": "2026-09-20T22:35:40Z"}</t>
+          <t>{"date": "2026-08-01", "year": 2026, "month": 8, "month_name": "Agosto", "index_value": 637409769724325.1, "monthly_variation_pct": 8.9, "unit": "Índice base diciembre 2007=100 y variación mensual %", "frequency": "monthly", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/precios_consumidor/4_5_7_2.xls", "fetched_at": "2026-09-21T23:27:46Z"}</t>
         </is>
       </c>
     </row>

--- a/assets/data/bcv/excel/ove_bcv_inpc_nacional_mensual.xlsx
+++ b/assets/data/bcv/excel/ove_bcv_inpc_nacional_mensual.xlsx
@@ -650,7 +650,7 @@
       </c>
       <c r="K7" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:46Z</t>
+          <t>2026-09-22T17:38:13Z</t>
         </is>
       </c>
     </row>
@@ -699,7 +699,7 @@
       </c>
       <c r="K8" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:46Z</t>
+          <t>2026-09-22T17:38:13Z</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="K9" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:46Z</t>
+          <t>2026-09-22T17:38:13Z</t>
         </is>
       </c>
     </row>
@@ -797,7 +797,7 @@
       </c>
       <c r="K10" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:46Z</t>
+          <t>2026-09-22T17:38:13Z</t>
         </is>
       </c>
     </row>
@@ -846,7 +846,7 @@
       </c>
       <c r="K11" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:46Z</t>
+          <t>2026-09-22T17:38:13Z</t>
         </is>
       </c>
     </row>
@@ -895,7 +895,7 @@
       </c>
       <c r="K12" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:46Z</t>
+          <t>2026-09-22T17:38:13Z</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="K13" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:46Z</t>
+          <t>2026-09-22T17:38:13Z</t>
         </is>
       </c>
     </row>
@@ -993,7 +993,7 @@
       </c>
       <c r="K14" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:46Z</t>
+          <t>2026-09-22T17:38:13Z</t>
         </is>
       </c>
     </row>
@@ -1042,7 +1042,7 @@
       </c>
       <c r="K15" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:46Z</t>
+          <t>2026-09-22T17:38:13Z</t>
         </is>
       </c>
     </row>
@@ -1091,7 +1091,7 @@
       </c>
       <c r="K16" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:46Z</t>
+          <t>2026-09-22T17:38:13Z</t>
         </is>
       </c>
     </row>
@@ -1140,7 +1140,7 @@
       </c>
       <c r="K17" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:46Z</t>
+          <t>2026-09-22T17:38:13Z</t>
         </is>
       </c>
     </row>
@@ -1189,7 +1189,7 @@
       </c>
       <c r="K18" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:46Z</t>
+          <t>2026-09-22T17:38:13Z</t>
         </is>
       </c>
     </row>
@@ -1238,7 +1238,7 @@
       </c>
       <c r="K19" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:46Z</t>
+          <t>2026-09-22T17:38:13Z</t>
         </is>
       </c>
     </row>
@@ -1287,7 +1287,7 @@
       </c>
       <c r="K20" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:46Z</t>
+          <t>2026-09-22T17:38:13Z</t>
         </is>
       </c>
     </row>
@@ -1336,7 +1336,7 @@
       </c>
       <c r="K21" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:46Z</t>
+          <t>2026-09-22T17:38:13Z</t>
         </is>
       </c>
     </row>
@@ -1385,7 +1385,7 @@
       </c>
       <c r="K22" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:46Z</t>
+          <t>2026-09-22T17:38:13Z</t>
         </is>
       </c>
     </row>
@@ -1434,7 +1434,7 @@
       </c>
       <c r="K23" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:46Z</t>
+          <t>2026-09-22T17:38:13Z</t>
         </is>
       </c>
     </row>
@@ -1483,7 +1483,7 @@
       </c>
       <c r="K24" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:46Z</t>
+          <t>2026-09-22T17:38:13Z</t>
         </is>
       </c>
     </row>
@@ -1532,7 +1532,7 @@
       </c>
       <c r="K25" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:46Z</t>
+          <t>2026-09-22T17:38:13Z</t>
         </is>
       </c>
     </row>
@@ -1581,7 +1581,7 @@
       </c>
       <c r="K26" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:46Z</t>
+          <t>2026-09-22T17:38:13Z</t>
         </is>
       </c>
     </row>
@@ -1630,7 +1630,7 @@
       </c>
       <c r="K27" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:46Z</t>
+          <t>2026-09-22T17:38:13Z</t>
         </is>
       </c>
     </row>
@@ -1679,7 +1679,7 @@
       </c>
       <c r="K28" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:46Z</t>
+          <t>2026-09-22T17:38:13Z</t>
         </is>
       </c>
     </row>
@@ -1728,7 +1728,7 @@
       </c>
       <c r="K29" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:46Z</t>
+          <t>2026-09-22T17:38:13Z</t>
         </is>
       </c>
     </row>
@@ -1777,7 +1777,7 @@
       </c>
       <c r="K30" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:46Z</t>
+          <t>2026-09-22T17:38:13Z</t>
         </is>
       </c>
     </row>
@@ -1826,7 +1826,7 @@
       </c>
       <c r="K31" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:46Z</t>
+          <t>2026-09-22T17:38:13Z</t>
         </is>
       </c>
     </row>
@@ -1875,7 +1875,7 @@
       </c>
       <c r="K32" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:46Z</t>
+          <t>2026-09-22T17:38:13Z</t>
         </is>
       </c>
     </row>
@@ -1924,7 +1924,7 @@
       </c>
       <c r="K33" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:46Z</t>
+          <t>2026-09-22T17:38:13Z</t>
         </is>
       </c>
     </row>
@@ -1973,7 +1973,7 @@
       </c>
       <c r="K34" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:46Z</t>
+          <t>2026-09-22T17:38:13Z</t>
         </is>
       </c>
     </row>
@@ -2022,7 +2022,7 @@
       </c>
       <c r="K35" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:46Z</t>
+          <t>2026-09-22T17:38:13Z</t>
         </is>
       </c>
     </row>
@@ -2071,7 +2071,7 @@
       </c>
       <c r="K36" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:46Z</t>
+          <t>2026-09-22T17:38:13Z</t>
         </is>
       </c>
     </row>
@@ -2120,7 +2120,7 @@
       </c>
       <c r="K37" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:46Z</t>
+          <t>2026-09-22T17:38:13Z</t>
         </is>
       </c>
     </row>
@@ -2169,7 +2169,7 @@
       </c>
       <c r="K38" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:46Z</t>
+          <t>2026-09-22T17:38:13Z</t>
         </is>
       </c>
     </row>
@@ -2218,7 +2218,7 @@
       </c>
       <c r="K39" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:46Z</t>
+          <t>2026-09-22T17:38:13Z</t>
         </is>
       </c>
     </row>
@@ -2267,7 +2267,7 @@
       </c>
       <c r="K40" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:46Z</t>
+          <t>2026-09-22T17:38:13Z</t>
         </is>
       </c>
     </row>
@@ -2316,7 +2316,7 @@
       </c>
       <c r="K41" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:46Z</t>
+          <t>2026-09-22T17:38:13Z</t>
         </is>
       </c>
     </row>
@@ -2365,7 +2365,7 @@
       </c>
       <c r="K42" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:46Z</t>
+          <t>2026-09-22T17:38:13Z</t>
         </is>
       </c>
     </row>
@@ -2414,7 +2414,7 @@
       </c>
       <c r="K43" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:46Z</t>
+          <t>2026-09-22T17:38:13Z</t>
         </is>
       </c>
     </row>
@@ -2463,7 +2463,7 @@
       </c>
       <c r="K44" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:46Z</t>
+          <t>2026-09-22T17:38:13Z</t>
         </is>
       </c>
     </row>
@@ -2512,7 +2512,7 @@
       </c>
       <c r="K45" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:46Z</t>
+          <t>2026-09-22T17:38:13Z</t>
         </is>
       </c>
     </row>
@@ -2561,7 +2561,7 @@
       </c>
       <c r="K46" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:46Z</t>
+          <t>2026-09-22T17:38:13Z</t>
         </is>
       </c>
     </row>
@@ -2610,7 +2610,7 @@
       </c>
       <c r="K47" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:46Z</t>
+          <t>2026-09-22T17:38:13Z</t>
         </is>
       </c>
     </row>
@@ -2659,7 +2659,7 @@
       </c>
       <c r="K48" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:46Z</t>
+          <t>2026-09-22T17:38:13Z</t>
         </is>
       </c>
     </row>
@@ -2708,7 +2708,7 @@
       </c>
       <c r="K49" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:46Z</t>
+          <t>2026-09-22T17:38:13Z</t>
         </is>
       </c>
     </row>
@@ -2757,7 +2757,7 @@
       </c>
       <c r="K50" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:46Z</t>
+          <t>2026-09-22T17:38:13Z</t>
         </is>
       </c>
     </row>
@@ -2806,7 +2806,7 @@
       </c>
       <c r="K51" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:46Z</t>
+          <t>2026-09-22T17:38:13Z</t>
         </is>
       </c>
     </row>
@@ -2855,7 +2855,7 @@
       </c>
       <c r="K52" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:46Z</t>
+          <t>2026-09-22T17:38:13Z</t>
         </is>
       </c>
     </row>
@@ -2904,7 +2904,7 @@
       </c>
       <c r="K53" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:46Z</t>
+          <t>2026-09-22T17:38:13Z</t>
         </is>
       </c>
     </row>
@@ -2953,7 +2953,7 @@
       </c>
       <c r="K54" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:46Z</t>
+          <t>2026-09-22T17:38:13Z</t>
         </is>
       </c>
     </row>
@@ -3002,7 +3002,7 @@
       </c>
       <c r="K55" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:46Z</t>
+          <t>2026-09-22T17:38:13Z</t>
         </is>
       </c>
     </row>
@@ -3051,7 +3051,7 @@
       </c>
       <c r="K56" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:46Z</t>
+          <t>2026-09-22T17:38:13Z</t>
         </is>
       </c>
     </row>
@@ -3100,7 +3100,7 @@
       </c>
       <c r="K57" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:46Z</t>
+          <t>2026-09-22T17:38:13Z</t>
         </is>
       </c>
     </row>
@@ -3149,7 +3149,7 @@
       </c>
       <c r="K58" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:46Z</t>
+          <t>2026-09-22T17:38:13Z</t>
         </is>
       </c>
     </row>
@@ -3198,7 +3198,7 @@
       </c>
       <c r="K59" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:46Z</t>
+          <t>2026-09-22T17:38:13Z</t>
         </is>
       </c>
     </row>
@@ -3247,7 +3247,7 @@
       </c>
       <c r="K60" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:46Z</t>
+          <t>2026-09-22T17:38:13Z</t>
         </is>
       </c>
     </row>
@@ -3296,7 +3296,7 @@
       </c>
       <c r="K61" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:46Z</t>
+          <t>2026-09-22T17:38:13Z</t>
         </is>
       </c>
     </row>
@@ -3345,7 +3345,7 @@
       </c>
       <c r="K62" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:46Z</t>
+          <t>2026-09-22T17:38:13Z</t>
         </is>
       </c>
     </row>
@@ -3394,7 +3394,7 @@
       </c>
       <c r="K63" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:46Z</t>
+          <t>2026-09-22T17:38:13Z</t>
         </is>
       </c>
     </row>
@@ -3443,7 +3443,7 @@
       </c>
       <c r="K64" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:46Z</t>
+          <t>2026-09-22T17:38:13Z</t>
         </is>
       </c>
     </row>
@@ -3492,7 +3492,7 @@
       </c>
       <c r="K65" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:46Z</t>
+          <t>2026-09-22T17:38:13Z</t>
         </is>
       </c>
     </row>
@@ -3541,7 +3541,7 @@
       </c>
       <c r="K66" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:46Z</t>
+          <t>2026-09-22T17:38:13Z</t>
         </is>
       </c>
     </row>
@@ -3590,7 +3590,7 @@
       </c>
       <c r="K67" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:46Z</t>
+          <t>2026-09-22T17:38:13Z</t>
         </is>
       </c>
     </row>
@@ -3639,7 +3639,7 @@
       </c>
       <c r="K68" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:46Z</t>
+          <t>2026-09-22T17:38:13Z</t>
         </is>
       </c>
     </row>
@@ -3688,7 +3688,7 @@
       </c>
       <c r="K69" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:46Z</t>
+          <t>2026-09-22T17:38:13Z</t>
         </is>
       </c>
     </row>
@@ -3737,7 +3737,7 @@
       </c>
       <c r="K70" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:46Z</t>
+          <t>2026-09-22T17:38:13Z</t>
         </is>
       </c>
     </row>
@@ -3786,7 +3786,7 @@
       </c>
       <c r="K71" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:46Z</t>
+          <t>2026-09-22T17:38:13Z</t>
         </is>
       </c>
     </row>
@@ -3835,7 +3835,7 @@
       </c>
       <c r="K72" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:46Z</t>
+          <t>2026-09-22T17:38:13Z</t>
         </is>
       </c>
     </row>
@@ -3884,7 +3884,7 @@
       </c>
       <c r="K73" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:46Z</t>
+          <t>2026-09-22T17:38:13Z</t>
         </is>
       </c>
     </row>
@@ -3933,7 +3933,7 @@
       </c>
       <c r="K74" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:46Z</t>
+          <t>2026-09-22T17:38:13Z</t>
         </is>
       </c>
     </row>
@@ -3982,7 +3982,7 @@
       </c>
       <c r="K75" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:46Z</t>
+          <t>2026-09-22T17:38:13Z</t>
         </is>
       </c>
     </row>
@@ -4031,7 +4031,7 @@
       </c>
       <c r="K76" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:46Z</t>
+          <t>2026-09-22T17:38:13Z</t>
         </is>
       </c>
     </row>
@@ -4080,7 +4080,7 @@
       </c>
       <c r="K77" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:46Z</t>
+          <t>2026-09-22T17:38:13Z</t>
         </is>
       </c>
     </row>
@@ -4129,7 +4129,7 @@
       </c>
       <c r="K78" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:46Z</t>
+          <t>2026-09-22T17:38:13Z</t>
         </is>
       </c>
     </row>
@@ -4178,7 +4178,7 @@
       </c>
       <c r="K79" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:46Z</t>
+          <t>2026-09-22T17:38:13Z</t>
         </is>
       </c>
     </row>
@@ -4227,7 +4227,7 @@
       </c>
       <c r="K80" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:46Z</t>
+          <t>2026-09-22T17:38:13Z</t>
         </is>
       </c>
     </row>
@@ -4276,7 +4276,7 @@
       </c>
       <c r="K81" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:46Z</t>
+          <t>2026-09-22T17:38:13Z</t>
         </is>
       </c>
     </row>
@@ -4325,7 +4325,7 @@
       </c>
       <c r="K82" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:46Z</t>
+          <t>2026-09-22T17:38:13Z</t>
         </is>
       </c>
     </row>
@@ -4374,7 +4374,7 @@
       </c>
       <c r="K83" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:46Z</t>
+          <t>2026-09-22T17:38:13Z</t>
         </is>
       </c>
     </row>
@@ -4423,7 +4423,7 @@
       </c>
       <c r="K84" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:46Z</t>
+          <t>2026-09-22T17:38:13Z</t>
         </is>
       </c>
     </row>
@@ -4472,7 +4472,7 @@
       </c>
       <c r="K85" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:46Z</t>
+          <t>2026-09-22T17:38:13Z</t>
         </is>
       </c>
     </row>
@@ -4521,7 +4521,7 @@
       </c>
       <c r="K86" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:46Z</t>
+          <t>2026-09-22T17:38:13Z</t>
         </is>
       </c>
     </row>
@@ -4570,7 +4570,7 @@
       </c>
       <c r="K87" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:46Z</t>
+          <t>2026-09-22T17:38:13Z</t>
         </is>
       </c>
     </row>
@@ -4619,7 +4619,7 @@
       </c>
       <c r="K88" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:46Z</t>
+          <t>2026-09-22T17:38:13Z</t>
         </is>
       </c>
     </row>
@@ -4668,7 +4668,7 @@
       </c>
       <c r="K89" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:46Z</t>
+          <t>2026-09-22T17:38:13Z</t>
         </is>
       </c>
     </row>
@@ -4717,7 +4717,7 @@
       </c>
       <c r="K90" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:46Z</t>
+          <t>2026-09-22T17:38:13Z</t>
         </is>
       </c>
     </row>
@@ -4766,7 +4766,7 @@
       </c>
       <c r="K91" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:46Z</t>
+          <t>2026-09-22T17:38:13Z</t>
         </is>
       </c>
     </row>
@@ -4815,7 +4815,7 @@
       </c>
       <c r="K92" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:46Z</t>
+          <t>2026-09-22T17:38:13Z</t>
         </is>
       </c>
     </row>
@@ -4864,7 +4864,7 @@
       </c>
       <c r="K93" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:46Z</t>
+          <t>2026-09-22T17:38:13Z</t>
         </is>
       </c>
     </row>
@@ -4913,7 +4913,7 @@
       </c>
       <c r="K94" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:46Z</t>
+          <t>2026-09-22T17:38:13Z</t>
         </is>
       </c>
     </row>
@@ -4962,7 +4962,7 @@
       </c>
       <c r="K95" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:46Z</t>
+          <t>2026-09-22T17:38:13Z</t>
         </is>
       </c>
     </row>
@@ -5011,7 +5011,7 @@
       </c>
       <c r="K96" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:46Z</t>
+          <t>2026-09-22T17:38:13Z</t>
         </is>
       </c>
     </row>
@@ -5060,7 +5060,7 @@
       </c>
       <c r="K97" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:46Z</t>
+          <t>2026-09-22T17:38:13Z</t>
         </is>
       </c>
     </row>
@@ -5109,7 +5109,7 @@
       </c>
       <c r="K98" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:46Z</t>
+          <t>2026-09-22T17:38:13Z</t>
         </is>
       </c>
     </row>
@@ -5158,7 +5158,7 @@
       </c>
       <c r="K99" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:46Z</t>
+          <t>2026-09-22T17:38:13Z</t>
         </is>
       </c>
     </row>
@@ -5207,7 +5207,7 @@
       </c>
       <c r="K100" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:46Z</t>
+          <t>2026-09-22T17:38:13Z</t>
         </is>
       </c>
     </row>
@@ -5256,7 +5256,7 @@
       </c>
       <c r="K101" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:46Z</t>
+          <t>2026-09-22T17:38:13Z</t>
         </is>
       </c>
     </row>
@@ -5305,7 +5305,7 @@
       </c>
       <c r="K102" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:46Z</t>
+          <t>2026-09-22T17:38:13Z</t>
         </is>
       </c>
     </row>
@@ -5354,7 +5354,7 @@
       </c>
       <c r="K103" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:46Z</t>
+          <t>2026-09-22T17:38:13Z</t>
         </is>
       </c>
     </row>
@@ -5403,7 +5403,7 @@
       </c>
       <c r="K104" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:46Z</t>
+          <t>2026-09-22T17:38:13Z</t>
         </is>
       </c>
     </row>
@@ -5452,7 +5452,7 @@
       </c>
       <c r="K105" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:46Z</t>
+          <t>2026-09-22T17:38:13Z</t>
         </is>
       </c>
     </row>
@@ -5501,7 +5501,7 @@
       </c>
       <c r="K106" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:46Z</t>
+          <t>2026-09-22T17:38:13Z</t>
         </is>
       </c>
     </row>
@@ -5550,7 +5550,7 @@
       </c>
       <c r="K107" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:46Z</t>
+          <t>2026-09-22T17:38:13Z</t>
         </is>
       </c>
     </row>
@@ -5599,7 +5599,7 @@
       </c>
       <c r="K108" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:46Z</t>
+          <t>2026-09-22T17:38:13Z</t>
         </is>
       </c>
     </row>
@@ -5648,7 +5648,7 @@
       </c>
       <c r="K109" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:46Z</t>
+          <t>2026-09-22T17:38:13Z</t>
         </is>
       </c>
     </row>
@@ -5697,7 +5697,7 @@
       </c>
       <c r="K110" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:46Z</t>
+          <t>2026-09-22T17:38:13Z</t>
         </is>
       </c>
     </row>
@@ -5746,7 +5746,7 @@
       </c>
       <c r="K111" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:46Z</t>
+          <t>2026-09-22T17:38:13Z</t>
         </is>
       </c>
     </row>
@@ -5795,7 +5795,7 @@
       </c>
       <c r="K112" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:46Z</t>
+          <t>2026-09-22T17:38:13Z</t>
         </is>
       </c>
     </row>
@@ -5844,7 +5844,7 @@
       </c>
       <c r="K113" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:46Z</t>
+          <t>2026-09-22T17:38:13Z</t>
         </is>
       </c>
     </row>
@@ -5893,7 +5893,7 @@
       </c>
       <c r="K114" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:46Z</t>
+          <t>2026-09-22T17:38:13Z</t>
         </is>
       </c>
     </row>
@@ -5942,7 +5942,7 @@
       </c>
       <c r="K115" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:46Z</t>
+          <t>2026-09-22T17:38:13Z</t>
         </is>
       </c>
     </row>
@@ -5991,7 +5991,7 @@
       </c>
       <c r="K116" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:46Z</t>
+          <t>2026-09-22T17:38:13Z</t>
         </is>
       </c>
     </row>
@@ -6040,7 +6040,7 @@
       </c>
       <c r="K117" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:46Z</t>
+          <t>2026-09-22T17:38:13Z</t>
         </is>
       </c>
     </row>
@@ -6089,7 +6089,7 @@
       </c>
       <c r="K118" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:46Z</t>
+          <t>2026-09-22T17:38:13Z</t>
         </is>
       </c>
     </row>
@@ -6138,7 +6138,7 @@
       </c>
       <c r="K119" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:46Z</t>
+          <t>2026-09-22T17:38:13Z</t>
         </is>
       </c>
     </row>
@@ -6187,7 +6187,7 @@
       </c>
       <c r="K120" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:46Z</t>
+          <t>2026-09-22T17:38:13Z</t>
         </is>
       </c>
     </row>
@@ -6236,7 +6236,7 @@
       </c>
       <c r="K121" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:46Z</t>
+          <t>2026-09-22T17:38:13Z</t>
         </is>
       </c>
     </row>
@@ -6285,7 +6285,7 @@
       </c>
       <c r="K122" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:46Z</t>
+          <t>2026-09-22T17:38:13Z</t>
         </is>
       </c>
     </row>
@@ -6334,7 +6334,7 @@
       </c>
       <c r="K123" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:46Z</t>
+          <t>2026-09-22T17:38:13Z</t>
         </is>
       </c>
     </row>
@@ -6383,7 +6383,7 @@
       </c>
       <c r="K124" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:46Z</t>
+          <t>2026-09-22T17:38:13Z</t>
         </is>
       </c>
     </row>
@@ -6432,7 +6432,7 @@
       </c>
       <c r="K125" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:46Z</t>
+          <t>2026-09-22T17:38:13Z</t>
         </is>
       </c>
     </row>
@@ -6481,7 +6481,7 @@
       </c>
       <c r="K126" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:46Z</t>
+          <t>2026-09-22T17:38:13Z</t>
         </is>
       </c>
     </row>
@@ -6530,7 +6530,7 @@
       </c>
       <c r="K127" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:46Z</t>
+          <t>2026-09-22T17:38:13Z</t>
         </is>
       </c>
     </row>
@@ -6579,7 +6579,7 @@
       </c>
       <c r="K128" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:46Z</t>
+          <t>2026-09-22T17:38:13Z</t>
         </is>
       </c>
     </row>
@@ -6628,7 +6628,7 @@
       </c>
       <c r="K129" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:46Z</t>
+          <t>2026-09-22T17:38:13Z</t>
         </is>
       </c>
     </row>
@@ -6677,7 +6677,7 @@
       </c>
       <c r="K130" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:46Z</t>
+          <t>2026-09-22T17:38:13Z</t>
         </is>
       </c>
     </row>
@@ -6726,7 +6726,7 @@
       </c>
       <c r="K131" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:46Z</t>
+          <t>2026-09-22T17:38:13Z</t>
         </is>
       </c>
     </row>
@@ -6775,7 +6775,7 @@
       </c>
       <c r="K132" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:46Z</t>
+          <t>2026-09-22T17:38:13Z</t>
         </is>
       </c>
     </row>
@@ -6824,7 +6824,7 @@
       </c>
       <c r="K133" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:46Z</t>
+          <t>2026-09-22T17:38:13Z</t>
         </is>
       </c>
     </row>
@@ -6873,7 +6873,7 @@
       </c>
       <c r="K134" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:46Z</t>
+          <t>2026-09-22T17:38:13Z</t>
         </is>
       </c>
     </row>
@@ -6922,7 +6922,7 @@
       </c>
       <c r="K135" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:46Z</t>
+          <t>2026-09-22T17:38:13Z</t>
         </is>
       </c>
     </row>
@@ -6971,7 +6971,7 @@
       </c>
       <c r="K136" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:46Z</t>
+          <t>2026-09-22T17:38:13Z</t>
         </is>
       </c>
     </row>
@@ -7020,7 +7020,7 @@
       </c>
       <c r="K137" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:46Z</t>
+          <t>2026-09-22T17:38:13Z</t>
         </is>
       </c>
     </row>
@@ -7069,7 +7069,7 @@
       </c>
       <c r="K138" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:46Z</t>
+          <t>2026-09-22T17:38:13Z</t>
         </is>
       </c>
     </row>
@@ -7118,7 +7118,7 @@
       </c>
       <c r="K139" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:46Z</t>
+          <t>2026-09-22T17:38:13Z</t>
         </is>
       </c>
     </row>
@@ -7167,7 +7167,7 @@
       </c>
       <c r="K140" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:46Z</t>
+          <t>2026-09-22T17:38:13Z</t>
         </is>
       </c>
     </row>
@@ -7216,7 +7216,7 @@
       </c>
       <c r="K141" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:46Z</t>
+          <t>2026-09-22T17:38:13Z</t>
         </is>
       </c>
     </row>
@@ -7265,7 +7265,7 @@
       </c>
       <c r="K142" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:46Z</t>
+          <t>2026-09-22T17:38:13Z</t>
         </is>
       </c>
     </row>
@@ -7314,7 +7314,7 @@
       </c>
       <c r="K143" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:46Z</t>
+          <t>2026-09-22T17:38:13Z</t>
         </is>
       </c>
     </row>
@@ -7363,7 +7363,7 @@
       </c>
       <c r="K144" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:46Z</t>
+          <t>2026-09-22T17:38:13Z</t>
         </is>
       </c>
     </row>
@@ -7412,7 +7412,7 @@
       </c>
       <c r="K145" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:46Z</t>
+          <t>2026-09-22T17:38:13Z</t>
         </is>
       </c>
     </row>
@@ -7461,7 +7461,7 @@
       </c>
       <c r="K146" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:46Z</t>
+          <t>2026-09-22T17:38:13Z</t>
         </is>
       </c>
     </row>
@@ -7510,7 +7510,7 @@
       </c>
       <c r="K147" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:46Z</t>
+          <t>2026-09-22T17:38:13Z</t>
         </is>
       </c>
     </row>
@@ -7559,7 +7559,7 @@
       </c>
       <c r="K148" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:46Z</t>
+          <t>2026-09-22T17:38:13Z</t>
         </is>
       </c>
     </row>
@@ -7608,7 +7608,7 @@
       </c>
       <c r="K149" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:46Z</t>
+          <t>2026-09-22T17:38:13Z</t>
         </is>
       </c>
     </row>
@@ -7657,7 +7657,7 @@
       </c>
       <c r="K150" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:46Z</t>
+          <t>2026-09-22T17:38:13Z</t>
         </is>
       </c>
     </row>
@@ -7706,7 +7706,7 @@
       </c>
       <c r="K151" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:46Z</t>
+          <t>2026-09-22T17:38:13Z</t>
         </is>
       </c>
     </row>
@@ -7755,7 +7755,7 @@
       </c>
       <c r="K152" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:46Z</t>
+          <t>2026-09-22T17:38:13Z</t>
         </is>
       </c>
     </row>
@@ -7804,7 +7804,7 @@
       </c>
       <c r="K153" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:46Z</t>
+          <t>2026-09-22T17:38:13Z</t>
         </is>
       </c>
     </row>
@@ -7853,7 +7853,7 @@
       </c>
       <c r="K154" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:46Z</t>
+          <t>2026-09-22T17:38:13Z</t>
         </is>
       </c>
     </row>
@@ -7902,7 +7902,7 @@
       </c>
       <c r="K155" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:46Z</t>
+          <t>2026-09-22T17:38:13Z</t>
         </is>
       </c>
     </row>
@@ -7951,7 +7951,7 @@
       </c>
       <c r="K156" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:46Z</t>
+          <t>2026-09-22T17:38:13Z</t>
         </is>
       </c>
     </row>
@@ -8000,7 +8000,7 @@
       </c>
       <c r="K157" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:46Z</t>
+          <t>2026-09-22T17:38:13Z</t>
         </is>
       </c>
     </row>
@@ -8049,7 +8049,7 @@
       </c>
       <c r="K158" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:46Z</t>
+          <t>2026-09-22T17:38:13Z</t>
         </is>
       </c>
     </row>
@@ -8098,7 +8098,7 @@
       </c>
       <c r="K159" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:46Z</t>
+          <t>2026-09-22T17:38:13Z</t>
         </is>
       </c>
     </row>
@@ -8147,7 +8147,7 @@
       </c>
       <c r="K160" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:46Z</t>
+          <t>2026-09-22T17:38:13Z</t>
         </is>
       </c>
     </row>
@@ -8196,7 +8196,7 @@
       </c>
       <c r="K161" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:46Z</t>
+          <t>2026-09-22T17:38:13Z</t>
         </is>
       </c>
     </row>
@@ -8245,7 +8245,7 @@
       </c>
       <c r="K162" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:46Z</t>
+          <t>2026-09-22T17:38:13Z</t>
         </is>
       </c>
     </row>
@@ -8294,7 +8294,7 @@
       </c>
       <c r="K163" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:46Z</t>
+          <t>2026-09-22T17:38:13Z</t>
         </is>
       </c>
     </row>
@@ -8343,7 +8343,7 @@
       </c>
       <c r="K164" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:46Z</t>
+          <t>2026-09-22T17:38:13Z</t>
         </is>
       </c>
     </row>
@@ -8392,7 +8392,7 @@
       </c>
       <c r="K165" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:46Z</t>
+          <t>2026-09-22T17:38:13Z</t>
         </is>
       </c>
     </row>
@@ -8441,7 +8441,7 @@
       </c>
       <c r="K166" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:46Z</t>
+          <t>2026-09-22T17:38:13Z</t>
         </is>
       </c>
     </row>
@@ -8490,7 +8490,7 @@
       </c>
       <c r="K167" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:46Z</t>
+          <t>2026-09-22T17:38:13Z</t>
         </is>
       </c>
     </row>
@@ -8539,7 +8539,7 @@
       </c>
       <c r="K168" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:46Z</t>
+          <t>2026-09-22T17:38:13Z</t>
         </is>
       </c>
     </row>
@@ -8588,7 +8588,7 @@
       </c>
       <c r="K169" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:46Z</t>
+          <t>2026-09-22T17:38:13Z</t>
         </is>
       </c>
     </row>
@@ -8637,7 +8637,7 @@
       </c>
       <c r="K170" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:46Z</t>
+          <t>2026-09-22T17:38:13Z</t>
         </is>
       </c>
     </row>
@@ -8686,7 +8686,7 @@
       </c>
       <c r="K171" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:46Z</t>
+          <t>2026-09-22T17:38:13Z</t>
         </is>
       </c>
     </row>
@@ -8735,7 +8735,7 @@
       </c>
       <c r="K172" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:46Z</t>
+          <t>2026-09-22T17:38:13Z</t>
         </is>
       </c>
     </row>
@@ -8784,7 +8784,7 @@
       </c>
       <c r="K173" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:46Z</t>
+          <t>2026-09-22T17:38:13Z</t>
         </is>
       </c>
     </row>
@@ -8833,7 +8833,7 @@
       </c>
       <c r="K174" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:46Z</t>
+          <t>2026-09-22T17:38:13Z</t>
         </is>
       </c>
     </row>
@@ -8882,7 +8882,7 @@
       </c>
       <c r="K175" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:46Z</t>
+          <t>2026-09-22T17:38:13Z</t>
         </is>
       </c>
     </row>
@@ -8931,7 +8931,7 @@
       </c>
       <c r="K176" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:46Z</t>
+          <t>2026-09-22T17:38:13Z</t>
         </is>
       </c>
     </row>
@@ -8980,7 +8980,7 @@
       </c>
       <c r="K177" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:46Z</t>
+          <t>2026-09-22T17:38:13Z</t>
         </is>
       </c>
     </row>
@@ -9029,7 +9029,7 @@
       </c>
       <c r="K178" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:46Z</t>
+          <t>2026-09-22T17:38:13Z</t>
         </is>
       </c>
     </row>
@@ -9078,7 +9078,7 @@
       </c>
       <c r="K179" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:46Z</t>
+          <t>2026-09-22T17:38:13Z</t>
         </is>
       </c>
     </row>
@@ -9127,7 +9127,7 @@
       </c>
       <c r="K180" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:46Z</t>
+          <t>2026-09-22T17:38:13Z</t>
         </is>
       </c>
     </row>
@@ -9176,7 +9176,7 @@
       </c>
       <c r="K181" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:46Z</t>
+          <t>2026-09-22T17:38:13Z</t>
         </is>
       </c>
     </row>
@@ -9225,7 +9225,7 @@
       </c>
       <c r="K182" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:46Z</t>
+          <t>2026-09-22T17:38:13Z</t>
         </is>
       </c>
     </row>
@@ -9274,7 +9274,7 @@
       </c>
       <c r="K183" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:46Z</t>
+          <t>2026-09-22T17:38:13Z</t>
         </is>
       </c>
     </row>
@@ -9323,7 +9323,7 @@
       </c>
       <c r="K184" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:46Z</t>
+          <t>2026-09-22T17:38:13Z</t>
         </is>
       </c>
     </row>
@@ -9372,7 +9372,7 @@
       </c>
       <c r="K185" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:46Z</t>
+          <t>2026-09-22T17:38:13Z</t>
         </is>
       </c>
     </row>
@@ -9421,7 +9421,7 @@
       </c>
       <c r="K186" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:46Z</t>
+          <t>2026-09-22T17:38:13Z</t>
         </is>
       </c>
     </row>
@@ -9470,7 +9470,7 @@
       </c>
       <c r="K187" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:46Z</t>
+          <t>2026-09-22T17:38:13Z</t>
         </is>
       </c>
     </row>
@@ -9519,7 +9519,7 @@
       </c>
       <c r="K188" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:46Z</t>
+          <t>2026-09-22T17:38:13Z</t>
         </is>
       </c>
     </row>
@@ -9568,7 +9568,7 @@
       </c>
       <c r="K189" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:46Z</t>
+          <t>2026-09-22T17:38:13Z</t>
         </is>
       </c>
     </row>
@@ -9617,7 +9617,7 @@
       </c>
       <c r="K190" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:46Z</t>
+          <t>2026-09-22T17:38:13Z</t>
         </is>
       </c>
     </row>
@@ -9666,7 +9666,7 @@
       </c>
       <c r="K191" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:46Z</t>
+          <t>2026-09-22T17:38:13Z</t>
         </is>
       </c>
     </row>
@@ -9715,7 +9715,7 @@
       </c>
       <c r="K192" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:46Z</t>
+          <t>2026-09-22T17:38:13Z</t>
         </is>
       </c>
     </row>
@@ -9764,7 +9764,7 @@
       </c>
       <c r="K193" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:46Z</t>
+          <t>2026-09-22T17:38:13Z</t>
         </is>
       </c>
     </row>
@@ -9813,7 +9813,7 @@
       </c>
       <c r="K194" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:46Z</t>
+          <t>2026-09-22T17:38:13Z</t>
         </is>
       </c>
     </row>
@@ -9862,7 +9862,7 @@
       </c>
       <c r="K195" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:46Z</t>
+          <t>2026-09-22T17:38:13Z</t>
         </is>
       </c>
     </row>
@@ -9911,7 +9911,7 @@
       </c>
       <c r="K196" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:46Z</t>
+          <t>2026-09-22T17:38:13Z</t>
         </is>
       </c>
     </row>
@@ -9960,7 +9960,7 @@
       </c>
       <c r="K197" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:46Z</t>
+          <t>2026-09-22T17:38:13Z</t>
         </is>
       </c>
     </row>
@@ -10009,7 +10009,7 @@
       </c>
       <c r="K198" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:46Z</t>
+          <t>2026-09-22T17:38:13Z</t>
         </is>
       </c>
     </row>
@@ -10058,7 +10058,7 @@
       </c>
       <c r="K199" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:46Z</t>
+          <t>2026-09-22T17:38:13Z</t>
         </is>
       </c>
     </row>
@@ -10107,7 +10107,7 @@
       </c>
       <c r="K200" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:46Z</t>
+          <t>2026-09-22T17:38:13Z</t>
         </is>
       </c>
     </row>
@@ -10156,7 +10156,7 @@
       </c>
       <c r="K201" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:46Z</t>
+          <t>2026-09-22T17:38:13Z</t>
         </is>
       </c>
     </row>
@@ -10205,7 +10205,7 @@
       </c>
       <c r="K202" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:46Z</t>
+          <t>2026-09-22T17:38:13Z</t>
         </is>
       </c>
     </row>
@@ -10254,7 +10254,7 @@
       </c>
       <c r="K203" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:46Z</t>
+          <t>2026-09-22T17:38:13Z</t>
         </is>
       </c>
     </row>
@@ -10303,7 +10303,7 @@
       </c>
       <c r="K204" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:46Z</t>
+          <t>2026-09-22T17:38:13Z</t>
         </is>
       </c>
     </row>
@@ -10352,7 +10352,7 @@
       </c>
       <c r="K205" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:46Z</t>
+          <t>2026-09-22T17:38:13Z</t>
         </is>
       </c>
     </row>
@@ -10401,7 +10401,7 @@
       </c>
       <c r="K206" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:46Z</t>
+          <t>2026-09-22T17:38:13Z</t>
         </is>
       </c>
     </row>
@@ -10450,7 +10450,7 @@
       </c>
       <c r="K207" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:46Z</t>
+          <t>2026-09-22T17:38:13Z</t>
         </is>
       </c>
     </row>
@@ -10499,7 +10499,7 @@
       </c>
       <c r="K208" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:46Z</t>
+          <t>2026-09-22T17:38:13Z</t>
         </is>
       </c>
     </row>
@@ -10548,7 +10548,7 @@
       </c>
       <c r="K209" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:46Z</t>
+          <t>2026-09-22T17:38:13Z</t>
         </is>
       </c>
     </row>
@@ -10597,7 +10597,7 @@
       </c>
       <c r="K210" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:46Z</t>
+          <t>2026-09-22T17:38:13Z</t>
         </is>
       </c>
     </row>
@@ -10646,7 +10646,7 @@
       </c>
       <c r="K211" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:46Z</t>
+          <t>2026-09-22T17:38:13Z</t>
         </is>
       </c>
     </row>
@@ -10695,7 +10695,7 @@
       </c>
       <c r="K212" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:46Z</t>
+          <t>2026-09-22T17:38:13Z</t>
         </is>
       </c>
     </row>
@@ -10744,7 +10744,7 @@
       </c>
       <c r="K213" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:46Z</t>
+          <t>2026-09-22T17:38:13Z</t>
         </is>
       </c>
     </row>
@@ -10793,7 +10793,7 @@
       </c>
       <c r="K214" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:46Z</t>
+          <t>2026-09-22T17:38:13Z</t>
         </is>
       </c>
     </row>
@@ -10842,7 +10842,7 @@
       </c>
       <c r="K215" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:46Z</t>
+          <t>2026-09-22T17:38:13Z</t>
         </is>
       </c>
     </row>
@@ -10891,7 +10891,7 @@
       </c>
       <c r="K216" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:46Z</t>
+          <t>2026-09-22T17:38:13Z</t>
         </is>
       </c>
     </row>
@@ -10940,7 +10940,7 @@
       </c>
       <c r="K217" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:46Z</t>
+          <t>2026-09-22T17:38:13Z</t>
         </is>
       </c>
     </row>
@@ -10989,7 +10989,7 @@
       </c>
       <c r="K218" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:46Z</t>
+          <t>2026-09-22T17:38:13Z</t>
         </is>
       </c>
     </row>
@@ -11038,7 +11038,7 @@
       </c>
       <c r="K219" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:46Z</t>
+          <t>2026-09-22T17:38:13Z</t>
         </is>
       </c>
     </row>
@@ -11087,7 +11087,7 @@
       </c>
       <c r="K220" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:46Z</t>
+          <t>2026-09-22T17:38:13Z</t>
         </is>
       </c>
     </row>
@@ -11136,7 +11136,7 @@
       </c>
       <c r="K221" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:46Z</t>
+          <t>2026-09-22T17:38:13Z</t>
         </is>
       </c>
     </row>
@@ -11185,7 +11185,7 @@
       </c>
       <c r="K222" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:46Z</t>
+          <t>2026-09-22T17:38:13Z</t>
         </is>
       </c>
     </row>
@@ -11234,7 +11234,7 @@
       </c>
       <c r="K223" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:46Z</t>
+          <t>2026-09-22T17:38:13Z</t>
         </is>
       </c>
     </row>
@@ -11283,7 +11283,7 @@
       </c>
       <c r="K224" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:46Z</t>
+          <t>2026-09-22T17:38:13Z</t>
         </is>
       </c>
     </row>
@@ -11332,7 +11332,7 @@
       </c>
       <c r="K225" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:46Z</t>
+          <t>2026-09-22T17:38:13Z</t>
         </is>
       </c>
     </row>
@@ -11381,7 +11381,7 @@
       </c>
       <c r="K226" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:46Z</t>
+          <t>2026-09-22T17:38:13Z</t>
         </is>
       </c>
     </row>
@@ -11430,7 +11430,7 @@
       </c>
       <c r="K227" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:46Z</t>
+          <t>2026-09-22T17:38:13Z</t>
         </is>
       </c>
     </row>
@@ -11479,7 +11479,7 @@
       </c>
       <c r="K228" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:46Z</t>
+          <t>2026-09-22T17:38:13Z</t>
         </is>
       </c>
     </row>
@@ -11528,7 +11528,7 @@
       </c>
       <c r="K229" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:46Z</t>
+          <t>2026-09-22T17:38:13Z</t>
         </is>
       </c>
     </row>
@@ -11577,7 +11577,7 @@
       </c>
       <c r="K230" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:46Z</t>
+          <t>2026-09-22T17:38:13Z</t>
         </is>
       </c>
     </row>
@@ -11626,7 +11626,7 @@
       </c>
       <c r="K231" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:46Z</t>
+          <t>2026-09-22T17:38:13Z</t>
         </is>
       </c>
     </row>
@@ -11758,7 +11758,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:46Z</t>
+          <t>2026-09-22T17:38:13Z</t>
         </is>
       </c>
     </row>
@@ -11804,7 +11804,7 @@
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>{"date": "2026-08-01", "year": 2026, "month": 8, "month_name": "Agosto", "index_value": 637409769724325.1, "monthly_variation_pct": 8.9, "unit": "Índice base diciembre 2007=100 y variación mensual %", "frequency": "monthly", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/precios_consumidor/4_5_7_2.xls", "fetched_at": "2026-09-21T23:27:46Z"}</t>
+          <t>{"date": "2026-08-01", "year": 2026, "month": 8, "month_name": "Agosto", "index_value": 637409769724325.1, "monthly_variation_pct": 8.9, "unit": "Índice base diciembre 2007=100 y variación mensual %", "frequency": "monthly", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/precios_consumidor/4_5_7_2.xls", "fetched_at": "2026-09-22T17:38:13Z"}</t>
         </is>
       </c>
     </row>

--- a/assets/data/bcv/excel/ove_bcv_inpc_nacional_mensual.xlsx
+++ b/assets/data/bcv/excel/ove_bcv_inpc_nacional_mensual.xlsx
@@ -650,7 +650,7 @@
       </c>
       <c r="K7" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:13Z</t>
+          <t>2026-09-22T23:08:01Z</t>
         </is>
       </c>
     </row>
@@ -699,7 +699,7 @@
       </c>
       <c r="K8" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:13Z</t>
+          <t>2026-09-22T23:08:01Z</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="K9" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:13Z</t>
+          <t>2026-09-22T23:08:01Z</t>
         </is>
       </c>
     </row>
@@ -797,7 +797,7 @@
       </c>
       <c r="K10" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:13Z</t>
+          <t>2026-09-22T23:08:01Z</t>
         </is>
       </c>
     </row>
@@ -846,7 +846,7 @@
       </c>
       <c r="K11" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:13Z</t>
+          <t>2026-09-22T23:08:01Z</t>
         </is>
       </c>
     </row>
@@ -895,7 +895,7 @@
       </c>
       <c r="K12" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:13Z</t>
+          <t>2026-09-22T23:08:01Z</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="K13" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:13Z</t>
+          <t>2026-09-22T23:08:01Z</t>
         </is>
       </c>
     </row>
@@ -993,7 +993,7 @@
       </c>
       <c r="K14" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:13Z</t>
+          <t>2026-09-22T23:08:01Z</t>
         </is>
       </c>
     </row>
@@ -1042,7 +1042,7 @@
       </c>
       <c r="K15" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:13Z</t>
+          <t>2026-09-22T23:08:01Z</t>
         </is>
       </c>
     </row>
@@ -1091,7 +1091,7 @@
       </c>
       <c r="K16" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:13Z</t>
+          <t>2026-09-22T23:08:01Z</t>
         </is>
       </c>
     </row>
@@ -1140,7 +1140,7 @@
       </c>
       <c r="K17" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:13Z</t>
+          <t>2026-09-22T23:08:01Z</t>
         </is>
       </c>
     </row>
@@ -1189,7 +1189,7 @@
       </c>
       <c r="K18" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:13Z</t>
+          <t>2026-09-22T23:08:01Z</t>
         </is>
       </c>
     </row>
@@ -1238,7 +1238,7 @@
       </c>
       <c r="K19" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:13Z</t>
+          <t>2026-09-22T23:08:01Z</t>
         </is>
       </c>
     </row>
@@ -1287,7 +1287,7 @@
       </c>
       <c r="K20" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:13Z</t>
+          <t>2026-09-22T23:08:01Z</t>
         </is>
       </c>
     </row>
@@ -1336,7 +1336,7 @@
       </c>
       <c r="K21" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:13Z</t>
+          <t>2026-09-22T23:08:01Z</t>
         </is>
       </c>
     </row>
@@ -1385,7 +1385,7 @@
       </c>
       <c r="K22" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:13Z</t>
+          <t>2026-09-22T23:08:01Z</t>
         </is>
       </c>
     </row>
@@ -1434,7 +1434,7 @@
       </c>
       <c r="K23" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:13Z</t>
+          <t>2026-09-22T23:08:01Z</t>
         </is>
       </c>
     </row>
@@ -1483,7 +1483,7 @@
       </c>
       <c r="K24" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:13Z</t>
+          <t>2026-09-22T23:08:01Z</t>
         </is>
       </c>
     </row>
@@ -1532,7 +1532,7 @@
       </c>
       <c r="K25" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:13Z</t>
+          <t>2026-09-22T23:08:01Z</t>
         </is>
       </c>
     </row>
@@ -1581,7 +1581,7 @@
       </c>
       <c r="K26" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:13Z</t>
+          <t>2026-09-22T23:08:01Z</t>
         </is>
       </c>
     </row>
@@ -1630,7 +1630,7 @@
       </c>
       <c r="K27" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:13Z</t>
+          <t>2026-09-22T23:08:01Z</t>
         </is>
       </c>
     </row>
@@ -1679,7 +1679,7 @@
       </c>
       <c r="K28" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:13Z</t>
+          <t>2026-09-22T23:08:01Z</t>
         </is>
       </c>
     </row>
@@ -1728,7 +1728,7 @@
       </c>
       <c r="K29" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:13Z</t>
+          <t>2026-09-22T23:08:01Z</t>
         </is>
       </c>
     </row>
@@ -1777,7 +1777,7 @@
       </c>
       <c r="K30" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:13Z</t>
+          <t>2026-09-22T23:08:01Z</t>
         </is>
       </c>
     </row>
@@ -1826,7 +1826,7 @@
       </c>
       <c r="K31" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:13Z</t>
+          <t>2026-09-22T23:08:01Z</t>
         </is>
       </c>
     </row>
@@ -1875,7 +1875,7 @@
       </c>
       <c r="K32" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:13Z</t>
+          <t>2026-09-22T23:08:01Z</t>
         </is>
       </c>
     </row>
@@ -1924,7 +1924,7 @@
       </c>
       <c r="K33" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:13Z</t>
+          <t>2026-09-22T23:08:01Z</t>
         </is>
       </c>
     </row>
@@ -1973,7 +1973,7 @@
       </c>
       <c r="K34" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:13Z</t>
+          <t>2026-09-22T23:08:01Z</t>
         </is>
       </c>
     </row>
@@ -2022,7 +2022,7 @@
       </c>
       <c r="K35" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:13Z</t>
+          <t>2026-09-22T23:08:01Z</t>
         </is>
       </c>
     </row>
@@ -2071,7 +2071,7 @@
       </c>
       <c r="K36" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:13Z</t>
+          <t>2026-09-22T23:08:01Z</t>
         </is>
       </c>
     </row>
@@ -2120,7 +2120,7 @@
       </c>
       <c r="K37" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:13Z</t>
+          <t>2026-09-22T23:08:01Z</t>
         </is>
       </c>
     </row>
@@ -2169,7 +2169,7 @@
       </c>
       <c r="K38" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:13Z</t>
+          <t>2026-09-22T23:08:01Z</t>
         </is>
       </c>
     </row>
@@ -2218,7 +2218,7 @@
       </c>
       <c r="K39" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:13Z</t>
+          <t>2026-09-22T23:08:01Z</t>
         </is>
       </c>
     </row>
@@ -2267,7 +2267,7 @@
       </c>
       <c r="K40" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:13Z</t>
+          <t>2026-09-22T23:08:01Z</t>
         </is>
       </c>
     </row>
@@ -2316,7 +2316,7 @@
       </c>
       <c r="K41" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:13Z</t>
+          <t>2026-09-22T23:08:01Z</t>
         </is>
       </c>
     </row>
@@ -2365,7 +2365,7 @@
       </c>
       <c r="K42" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:13Z</t>
+          <t>2026-09-22T23:08:01Z</t>
         </is>
       </c>
     </row>
@@ -2414,7 +2414,7 @@
       </c>
       <c r="K43" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:13Z</t>
+          <t>2026-09-22T23:08:01Z</t>
         </is>
       </c>
     </row>
@@ -2463,7 +2463,7 @@
       </c>
       <c r="K44" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:13Z</t>
+          <t>2026-09-22T23:08:01Z</t>
         </is>
       </c>
     </row>
@@ -2512,7 +2512,7 @@
       </c>
       <c r="K45" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:13Z</t>
+          <t>2026-09-22T23:08:01Z</t>
         </is>
       </c>
     </row>
@@ -2561,7 +2561,7 @@
       </c>
       <c r="K46" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:13Z</t>
+          <t>2026-09-22T23:08:01Z</t>
         </is>
       </c>
     </row>
@@ -2610,7 +2610,7 @@
       </c>
       <c r="K47" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:13Z</t>
+          <t>2026-09-22T23:08:01Z</t>
         </is>
       </c>
     </row>
@@ -2659,7 +2659,7 @@
       </c>
       <c r="K48" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:13Z</t>
+          <t>2026-09-22T23:08:01Z</t>
         </is>
       </c>
     </row>
@@ -2708,7 +2708,7 @@
       </c>
       <c r="K49" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:13Z</t>
+          <t>2026-09-22T23:08:01Z</t>
         </is>
       </c>
     </row>
@@ -2757,7 +2757,7 @@
       </c>
       <c r="K50" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:13Z</t>
+          <t>2026-09-22T23:08:01Z</t>
         </is>
       </c>
     </row>
@@ -2806,7 +2806,7 @@
       </c>
       <c r="K51" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:13Z</t>
+          <t>2026-09-22T23:08:01Z</t>
         </is>
       </c>
     </row>
@@ -2855,7 +2855,7 @@
       </c>
       <c r="K52" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:13Z</t>
+          <t>2026-09-22T23:08:01Z</t>
         </is>
       </c>
     </row>
@@ -2904,7 +2904,7 @@
       </c>
       <c r="K53" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:13Z</t>
+          <t>2026-09-22T23:08:01Z</t>
         </is>
       </c>
     </row>
@@ -2953,7 +2953,7 @@
       </c>
       <c r="K54" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:13Z</t>
+          <t>2026-09-22T23:08:01Z</t>
         </is>
       </c>
     </row>
@@ -3002,7 +3002,7 @@
       </c>
       <c r="K55" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:13Z</t>
+          <t>2026-09-22T23:08:01Z</t>
         </is>
       </c>
     </row>
@@ -3051,7 +3051,7 @@
       </c>
       <c r="K56" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:13Z</t>
+          <t>2026-09-22T23:08:01Z</t>
         </is>
       </c>
     </row>
@@ -3100,7 +3100,7 @@
       </c>
       <c r="K57" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:13Z</t>
+          <t>2026-09-22T23:08:01Z</t>
         </is>
       </c>
     </row>
@@ -3149,7 +3149,7 @@
       </c>
       <c r="K58" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:13Z</t>
+          <t>2026-09-22T23:08:01Z</t>
         </is>
       </c>
     </row>
@@ -3198,7 +3198,7 @@
       </c>
       <c r="K59" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:13Z</t>
+          <t>2026-09-22T23:08:01Z</t>
         </is>
       </c>
     </row>
@@ -3247,7 +3247,7 @@
       </c>
       <c r="K60" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:13Z</t>
+          <t>2026-09-22T23:08:01Z</t>
         </is>
       </c>
     </row>
@@ -3296,7 +3296,7 @@
       </c>
       <c r="K61" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:13Z</t>
+          <t>2026-09-22T23:08:01Z</t>
         </is>
       </c>
     </row>
@@ -3345,7 +3345,7 @@
       </c>
       <c r="K62" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:13Z</t>
+          <t>2026-09-22T23:08:01Z</t>
         </is>
       </c>
     </row>
@@ -3394,7 +3394,7 @@
       </c>
       <c r="K63" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:13Z</t>
+          <t>2026-09-22T23:08:01Z</t>
         </is>
       </c>
     </row>
@@ -3443,7 +3443,7 @@
       </c>
       <c r="K64" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:13Z</t>
+          <t>2026-09-22T23:08:01Z</t>
         </is>
       </c>
     </row>
@@ -3492,7 +3492,7 @@
       </c>
       <c r="K65" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:13Z</t>
+          <t>2026-09-22T23:08:01Z</t>
         </is>
       </c>
     </row>
@@ -3541,7 +3541,7 @@
       </c>
       <c r="K66" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:13Z</t>
+          <t>2026-09-22T23:08:01Z</t>
         </is>
       </c>
     </row>
@@ -3590,7 +3590,7 @@
       </c>
       <c r="K67" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:13Z</t>
+          <t>2026-09-22T23:08:01Z</t>
         </is>
       </c>
     </row>
@@ -3639,7 +3639,7 @@
       </c>
       <c r="K68" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:13Z</t>
+          <t>2026-09-22T23:08:01Z</t>
         </is>
       </c>
     </row>
@@ -3688,7 +3688,7 @@
       </c>
       <c r="K69" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:13Z</t>
+          <t>2026-09-22T23:08:01Z</t>
         </is>
       </c>
     </row>
@@ -3737,7 +3737,7 @@
       </c>
       <c r="K70" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:13Z</t>
+          <t>2026-09-22T23:08:01Z</t>
         </is>
       </c>
     </row>
@@ -3786,7 +3786,7 @@
       </c>
       <c r="K71" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:13Z</t>
+          <t>2026-09-22T23:08:01Z</t>
         </is>
       </c>
     </row>
@@ -3835,7 +3835,7 @@
       </c>
       <c r="K72" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:13Z</t>
+          <t>2026-09-22T23:08:01Z</t>
         </is>
       </c>
     </row>
@@ -3884,7 +3884,7 @@
       </c>
       <c r="K73" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:13Z</t>
+          <t>2026-09-22T23:08:01Z</t>
         </is>
       </c>
     </row>
@@ -3933,7 +3933,7 @@
       </c>
       <c r="K74" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:13Z</t>
+          <t>2026-09-22T23:08:01Z</t>
         </is>
       </c>
     </row>
@@ -3982,7 +3982,7 @@
       </c>
       <c r="K75" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:13Z</t>
+          <t>2026-09-22T23:08:01Z</t>
         </is>
       </c>
     </row>
@@ -4031,7 +4031,7 @@
       </c>
       <c r="K76" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:13Z</t>
+          <t>2026-09-22T23:08:01Z</t>
         </is>
       </c>
     </row>
@@ -4080,7 +4080,7 @@
       </c>
       <c r="K77" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:13Z</t>
+          <t>2026-09-22T23:08:01Z</t>
         </is>
       </c>
     </row>
@@ -4129,7 +4129,7 @@
       </c>
       <c r="K78" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:13Z</t>
+          <t>2026-09-22T23:08:01Z</t>
         </is>
       </c>
     </row>
@@ -4178,7 +4178,7 @@
       </c>
       <c r="K79" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:13Z</t>
+          <t>2026-09-22T23:08:01Z</t>
         </is>
       </c>
     </row>
@@ -4227,7 +4227,7 @@
       </c>
       <c r="K80" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:13Z</t>
+          <t>2026-09-22T23:08:01Z</t>
         </is>
       </c>
     </row>
@@ -4276,7 +4276,7 @@
       </c>
       <c r="K81" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:13Z</t>
+          <t>2026-09-22T23:08:01Z</t>
         </is>
       </c>
     </row>
@@ -4325,7 +4325,7 @@
       </c>
       <c r="K82" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:13Z</t>
+          <t>2026-09-22T23:08:01Z</t>
         </is>
       </c>
     </row>
@@ -4374,7 +4374,7 @@
       </c>
       <c r="K83" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:13Z</t>
+          <t>2026-09-22T23:08:01Z</t>
         </is>
       </c>
     </row>
@@ -4423,7 +4423,7 @@
       </c>
       <c r="K84" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:13Z</t>
+          <t>2026-09-22T23:08:01Z</t>
         </is>
       </c>
     </row>
@@ -4472,7 +4472,7 @@
       </c>
       <c r="K85" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:13Z</t>
+          <t>2026-09-22T23:08:01Z</t>
         </is>
       </c>
     </row>
@@ -4521,7 +4521,7 @@
       </c>
       <c r="K86" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:13Z</t>
+          <t>2026-09-22T23:08:01Z</t>
         </is>
       </c>
     </row>
@@ -4570,7 +4570,7 @@
       </c>
       <c r="K87" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:13Z</t>
+          <t>2026-09-22T23:08:01Z</t>
         </is>
       </c>
     </row>
@@ -4619,7 +4619,7 @@
       </c>
       <c r="K88" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:13Z</t>
+          <t>2026-09-22T23:08:01Z</t>
         </is>
       </c>
     </row>
@@ -4668,7 +4668,7 @@
       </c>
       <c r="K89" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:13Z</t>
+          <t>2026-09-22T23:08:01Z</t>
         </is>
       </c>
     </row>
@@ -4717,7 +4717,7 @@
       </c>
       <c r="K90" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:13Z</t>
+          <t>2026-09-22T23:08:01Z</t>
         </is>
       </c>
     </row>
@@ -4766,7 +4766,7 @@
       </c>
       <c r="K91" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:13Z</t>
+          <t>2026-09-22T23:08:01Z</t>
         </is>
       </c>
     </row>
@@ -4815,7 +4815,7 @@
       </c>
       <c r="K92" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:13Z</t>
+          <t>2026-09-22T23:08:01Z</t>
         </is>
       </c>
     </row>
@@ -4864,7 +4864,7 @@
       </c>
       <c r="K93" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:13Z</t>
+          <t>2026-09-22T23:08:01Z</t>
         </is>
       </c>
     </row>
@@ -4913,7 +4913,7 @@
       </c>
       <c r="K94" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:13Z</t>
+          <t>2026-09-22T23:08:01Z</t>
         </is>
       </c>
     </row>
@@ -4962,7 +4962,7 @@
       </c>
       <c r="K95" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:13Z</t>
+          <t>2026-09-22T23:08:01Z</t>
         </is>
       </c>
     </row>
@@ -5011,7 +5011,7 @@
       </c>
       <c r="K96" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:13Z</t>
+          <t>2026-09-22T23:08:01Z</t>
         </is>
       </c>
     </row>
@@ -5060,7 +5060,7 @@
       </c>
       <c r="K97" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:13Z</t>
+          <t>2026-09-22T23:08:01Z</t>
         </is>
       </c>
     </row>
@@ -5109,7 +5109,7 @@
       </c>
       <c r="K98" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:13Z</t>
+          <t>2026-09-22T23:08:01Z</t>
         </is>
       </c>
     </row>
@@ -5158,7 +5158,7 @@
       </c>
       <c r="K99" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:13Z</t>
+          <t>2026-09-22T23:08:01Z</t>
         </is>
       </c>
     </row>
@@ -5207,7 +5207,7 @@
       </c>
       <c r="K100" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:13Z</t>
+          <t>2026-09-22T23:08:01Z</t>
         </is>
       </c>
     </row>
@@ -5256,7 +5256,7 @@
       </c>
       <c r="K101" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:13Z</t>
+          <t>2026-09-22T23:08:01Z</t>
         </is>
       </c>
     </row>
@@ -5305,7 +5305,7 @@
       </c>
       <c r="K102" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:13Z</t>
+          <t>2026-09-22T23:08:01Z</t>
         </is>
       </c>
     </row>
@@ -5354,7 +5354,7 @@
       </c>
       <c r="K103" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:13Z</t>
+          <t>2026-09-22T23:08:01Z</t>
         </is>
       </c>
     </row>
@@ -5403,7 +5403,7 @@
       </c>
       <c r="K104" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:13Z</t>
+          <t>2026-09-22T23:08:01Z</t>
         </is>
       </c>
     </row>
@@ -5452,7 +5452,7 @@
       </c>
       <c r="K105" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:13Z</t>
+          <t>2026-09-22T23:08:01Z</t>
         </is>
       </c>
     </row>
@@ -5501,7 +5501,7 @@
       </c>
       <c r="K106" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:13Z</t>
+          <t>2026-09-22T23:08:01Z</t>
         </is>
       </c>
     </row>
@@ -5550,7 +5550,7 @@
       </c>
       <c r="K107" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:13Z</t>
+          <t>2026-09-22T23:08:01Z</t>
         </is>
       </c>
     </row>
@@ -5599,7 +5599,7 @@
       </c>
       <c r="K108" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:13Z</t>
+          <t>2026-09-22T23:08:01Z</t>
         </is>
       </c>
     </row>
@@ -5648,7 +5648,7 @@
       </c>
       <c r="K109" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:13Z</t>
+          <t>2026-09-22T23:08:01Z</t>
         </is>
       </c>
     </row>
@@ -5697,7 +5697,7 @@
       </c>
       <c r="K110" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:13Z</t>
+          <t>2026-09-22T23:08:01Z</t>
         </is>
       </c>
     </row>
@@ -5746,7 +5746,7 @@
       </c>
       <c r="K111" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:13Z</t>
+          <t>2026-09-22T23:08:01Z</t>
         </is>
       </c>
     </row>
@@ -5795,7 +5795,7 @@
       </c>
       <c r="K112" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:13Z</t>
+          <t>2026-09-22T23:08:01Z</t>
         </is>
       </c>
     </row>
@@ -5844,7 +5844,7 @@
       </c>
       <c r="K113" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:13Z</t>
+          <t>2026-09-22T23:08:01Z</t>
         </is>
       </c>
     </row>
@@ -5893,7 +5893,7 @@
       </c>
       <c r="K114" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:13Z</t>
+          <t>2026-09-22T23:08:01Z</t>
         </is>
       </c>
     </row>
@@ -5942,7 +5942,7 @@
       </c>
       <c r="K115" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:13Z</t>
+          <t>2026-09-22T23:08:01Z</t>
         </is>
       </c>
     </row>
@@ -5991,7 +5991,7 @@
       </c>
       <c r="K116" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:13Z</t>
+          <t>2026-09-22T23:08:01Z</t>
         </is>
       </c>
     </row>
@@ -6040,7 +6040,7 @@
       </c>
       <c r="K117" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:13Z</t>
+          <t>2026-09-22T23:08:01Z</t>
         </is>
       </c>
     </row>
@@ -6089,7 +6089,7 @@
       </c>
       <c r="K118" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:13Z</t>
+          <t>2026-09-22T23:08:01Z</t>
         </is>
       </c>
     </row>
@@ -6138,7 +6138,7 @@
       </c>
       <c r="K119" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:13Z</t>
+          <t>2026-09-22T23:08:01Z</t>
         </is>
       </c>
     </row>
@@ -6187,7 +6187,7 @@
       </c>
       <c r="K120" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:13Z</t>
+          <t>2026-09-22T23:08:01Z</t>
         </is>
       </c>
     </row>
@@ -6236,7 +6236,7 @@
       </c>
       <c r="K121" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:13Z</t>
+          <t>2026-09-22T23:08:01Z</t>
         </is>
       </c>
     </row>
@@ -6285,7 +6285,7 @@
       </c>
       <c r="K122" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:13Z</t>
+          <t>2026-09-22T23:08:01Z</t>
         </is>
       </c>
     </row>
@@ -6334,7 +6334,7 @@
       </c>
       <c r="K123" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:13Z</t>
+          <t>2026-09-22T23:08:01Z</t>
         </is>
       </c>
     </row>
@@ -6383,7 +6383,7 @@
       </c>
       <c r="K124" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:13Z</t>
+          <t>2026-09-22T23:08:01Z</t>
         </is>
       </c>
     </row>
@@ -6432,7 +6432,7 @@
       </c>
       <c r="K125" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:13Z</t>
+          <t>2026-09-22T23:08:01Z</t>
         </is>
       </c>
     </row>
@@ -6481,7 +6481,7 @@
       </c>
       <c r="K126" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:13Z</t>
+          <t>2026-09-22T23:08:01Z</t>
         </is>
       </c>
     </row>
@@ -6530,7 +6530,7 @@
       </c>
       <c r="K127" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:13Z</t>
+          <t>2026-09-22T23:08:01Z</t>
         </is>
       </c>
     </row>
@@ -6579,7 +6579,7 @@
       </c>
       <c r="K128" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:13Z</t>
+          <t>2026-09-22T23:08:01Z</t>
         </is>
       </c>
     </row>
@@ -6628,7 +6628,7 @@
       </c>
       <c r="K129" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:13Z</t>
+          <t>2026-09-22T23:08:01Z</t>
         </is>
       </c>
     </row>
@@ -6677,7 +6677,7 @@
       </c>
       <c r="K130" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:13Z</t>
+          <t>2026-09-22T23:08:01Z</t>
         </is>
       </c>
     </row>
@@ -6726,7 +6726,7 @@
       </c>
       <c r="K131" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:13Z</t>
+          <t>2026-09-22T23:08:01Z</t>
         </is>
       </c>
     </row>
@@ -6775,7 +6775,7 @@
       </c>
       <c r="K132" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:13Z</t>
+          <t>2026-09-22T23:08:01Z</t>
         </is>
       </c>
     </row>
@@ -6824,7 +6824,7 @@
       </c>
       <c r="K133" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:13Z</t>
+          <t>2026-09-22T23:08:01Z</t>
         </is>
       </c>
     </row>
@@ -6873,7 +6873,7 @@
       </c>
       <c r="K134" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:13Z</t>
+          <t>2026-09-22T23:08:01Z</t>
         </is>
       </c>
     </row>
@@ -6922,7 +6922,7 @@
       </c>
       <c r="K135" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:13Z</t>
+          <t>2026-09-22T23:08:01Z</t>
         </is>
       </c>
     </row>
@@ -6971,7 +6971,7 @@
       </c>
       <c r="K136" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:13Z</t>
+          <t>2026-09-22T23:08:01Z</t>
         </is>
       </c>
     </row>
@@ -7020,7 +7020,7 @@
       </c>
       <c r="K137" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:13Z</t>
+          <t>2026-09-22T23:08:01Z</t>
         </is>
       </c>
     </row>
@@ -7069,7 +7069,7 @@
       </c>
       <c r="K138" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:13Z</t>
+          <t>2026-09-22T23:08:01Z</t>
         </is>
       </c>
     </row>
@@ -7118,7 +7118,7 @@
       </c>
       <c r="K139" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:13Z</t>
+          <t>2026-09-22T23:08:01Z</t>
         </is>
       </c>
     </row>
@@ -7167,7 +7167,7 @@
       </c>
       <c r="K140" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:13Z</t>
+          <t>2026-09-22T23:08:01Z</t>
         </is>
       </c>
     </row>
@@ -7216,7 +7216,7 @@
       </c>
       <c r="K141" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:13Z</t>
+          <t>2026-09-22T23:08:01Z</t>
         </is>
       </c>
     </row>
@@ -7265,7 +7265,7 @@
       </c>
       <c r="K142" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:13Z</t>
+          <t>2026-09-22T23:08:01Z</t>
         </is>
       </c>
     </row>
@@ -7314,7 +7314,7 @@
       </c>
       <c r="K143" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:13Z</t>
+          <t>2026-09-22T23:08:01Z</t>
         </is>
       </c>
     </row>
@@ -7363,7 +7363,7 @@
       </c>
       <c r="K144" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:13Z</t>
+          <t>2026-09-22T23:08:01Z</t>
         </is>
       </c>
     </row>
@@ -7412,7 +7412,7 @@
       </c>
       <c r="K145" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:13Z</t>
+          <t>2026-09-22T23:08:01Z</t>
         </is>
       </c>
     </row>
@@ -7461,7 +7461,7 @@
       </c>
       <c r="K146" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:13Z</t>
+          <t>2026-09-22T23:08:01Z</t>
         </is>
       </c>
     </row>
@@ -7510,7 +7510,7 @@
       </c>
       <c r="K147" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:13Z</t>
+          <t>2026-09-22T23:08:01Z</t>
         </is>
       </c>
     </row>
@@ -7559,7 +7559,7 @@
       </c>
       <c r="K148" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:13Z</t>
+          <t>2026-09-22T23:08:01Z</t>
         </is>
       </c>
     </row>
@@ -7608,7 +7608,7 @@
       </c>
       <c r="K149" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:13Z</t>
+          <t>2026-09-22T23:08:01Z</t>
         </is>
       </c>
     </row>
@@ -7657,7 +7657,7 @@
       </c>
       <c r="K150" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:13Z</t>
+          <t>2026-09-22T23:08:01Z</t>
         </is>
       </c>
     </row>
@@ -7706,7 +7706,7 @@
       </c>
       <c r="K151" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:13Z</t>
+          <t>2026-09-22T23:08:01Z</t>
         </is>
       </c>
     </row>
@@ -7755,7 +7755,7 @@
       </c>
       <c r="K152" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:13Z</t>
+          <t>2026-09-22T23:08:01Z</t>
         </is>
       </c>
     </row>
@@ -7804,7 +7804,7 @@
       </c>
       <c r="K153" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:13Z</t>
+          <t>2026-09-22T23:08:01Z</t>
         </is>
       </c>
     </row>
@@ -7853,7 +7853,7 @@
       </c>
       <c r="K154" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:13Z</t>
+          <t>2026-09-22T23:08:01Z</t>
         </is>
       </c>
     </row>
@@ -7902,7 +7902,7 @@
       </c>
       <c r="K155" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:13Z</t>
+          <t>2026-09-22T23:08:01Z</t>
         </is>
       </c>
     </row>
@@ -7951,7 +7951,7 @@
       </c>
       <c r="K156" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:13Z</t>
+          <t>2026-09-22T23:08:01Z</t>
         </is>
       </c>
     </row>
@@ -8000,7 +8000,7 @@
       </c>
       <c r="K157" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:13Z</t>
+          <t>2026-09-22T23:08:01Z</t>
         </is>
       </c>
     </row>
@@ -8049,7 +8049,7 @@
       </c>
       <c r="K158" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:13Z</t>
+          <t>2026-09-22T23:08:01Z</t>
         </is>
       </c>
     </row>
@@ -8098,7 +8098,7 @@
       </c>
       <c r="K159" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:13Z</t>
+          <t>2026-09-22T23:08:01Z</t>
         </is>
       </c>
     </row>
@@ -8147,7 +8147,7 @@
       </c>
       <c r="K160" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:13Z</t>
+          <t>2026-09-22T23:08:01Z</t>
         </is>
       </c>
     </row>
@@ -8196,7 +8196,7 @@
       </c>
       <c r="K161" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:13Z</t>
+          <t>2026-09-22T23:08:01Z</t>
         </is>
       </c>
     </row>
@@ -8245,7 +8245,7 @@
       </c>
       <c r="K162" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:13Z</t>
+          <t>2026-09-22T23:08:01Z</t>
         </is>
       </c>
     </row>
@@ -8294,7 +8294,7 @@
       </c>
       <c r="K163" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:13Z</t>
+          <t>2026-09-22T23:08:01Z</t>
         </is>
       </c>
     </row>
@@ -8343,7 +8343,7 @@
       </c>
       <c r="K164" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:13Z</t>
+          <t>2026-09-22T23:08:01Z</t>
         </is>
       </c>
     </row>
@@ -8392,7 +8392,7 @@
       </c>
       <c r="K165" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:13Z</t>
+          <t>2026-09-22T23:08:01Z</t>
         </is>
       </c>
     </row>
@@ -8441,7 +8441,7 @@
       </c>
       <c r="K166" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:13Z</t>
+          <t>2026-09-22T23:08:01Z</t>
         </is>
       </c>
     </row>
@@ -8490,7 +8490,7 @@
       </c>
       <c r="K167" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:13Z</t>
+          <t>2026-09-22T23:08:01Z</t>
         </is>
       </c>
     </row>
@@ -8539,7 +8539,7 @@
       </c>
       <c r="K168" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:13Z</t>
+          <t>2026-09-22T23:08:01Z</t>
         </is>
       </c>
     </row>
@@ -8588,7 +8588,7 @@
       </c>
       <c r="K169" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:13Z</t>
+          <t>2026-09-22T23:08:01Z</t>
         </is>
       </c>
     </row>
@@ -8637,7 +8637,7 @@
       </c>
       <c r="K170" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:13Z</t>
+          <t>2026-09-22T23:08:01Z</t>
         </is>
       </c>
     </row>
@@ -8686,7 +8686,7 @@
       </c>
       <c r="K171" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:13Z</t>
+          <t>2026-09-22T23:08:01Z</t>
         </is>
       </c>
     </row>
@@ -8735,7 +8735,7 @@
       </c>
       <c r="K172" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:13Z</t>
+          <t>2026-09-22T23:08:01Z</t>
         </is>
       </c>
     </row>
@@ -8784,7 +8784,7 @@
       </c>
       <c r="K173" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:13Z</t>
+          <t>2026-09-22T23:08:01Z</t>
         </is>
       </c>
     </row>
@@ -8833,7 +8833,7 @@
       </c>
       <c r="K174" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:13Z</t>
+          <t>2026-09-22T23:08:01Z</t>
         </is>
       </c>
     </row>
@@ -8882,7 +8882,7 @@
       </c>
       <c r="K175" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:13Z</t>
+          <t>2026-09-22T23:08:01Z</t>
         </is>
       </c>
     </row>
@@ -8931,7 +8931,7 @@
       </c>
       <c r="K176" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:13Z</t>
+          <t>2026-09-22T23:08:01Z</t>
         </is>
       </c>
     </row>
@@ -8980,7 +8980,7 @@
       </c>
       <c r="K177" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:13Z</t>
+          <t>2026-09-22T23:08:01Z</t>
         </is>
       </c>
     </row>
@@ -9029,7 +9029,7 @@
       </c>
       <c r="K178" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:13Z</t>
+          <t>2026-09-22T23:08:01Z</t>
         </is>
       </c>
     </row>
@@ -9078,7 +9078,7 @@
       </c>
       <c r="K179" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:13Z</t>
+          <t>2026-09-22T23:08:01Z</t>
         </is>
       </c>
     </row>
@@ -9127,7 +9127,7 @@
       </c>
       <c r="K180" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:13Z</t>
+          <t>2026-09-22T23:08:01Z</t>
         </is>
       </c>
     </row>
@@ -9176,7 +9176,7 @@
       </c>
       <c r="K181" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:13Z</t>
+          <t>2026-09-22T23:08:01Z</t>
         </is>
       </c>
     </row>
@@ -9225,7 +9225,7 @@
       </c>
       <c r="K182" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:13Z</t>
+          <t>2026-09-22T23:08:01Z</t>
         </is>
       </c>
     </row>
@@ -9274,7 +9274,7 @@
       </c>
       <c r="K183" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:13Z</t>
+          <t>2026-09-22T23:08:01Z</t>
         </is>
       </c>
     </row>
@@ -9323,7 +9323,7 @@
       </c>
       <c r="K184" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:13Z</t>
+          <t>2026-09-22T23:08:01Z</t>
         </is>
       </c>
     </row>
@@ -9372,7 +9372,7 @@
       </c>
       <c r="K185" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:13Z</t>
+          <t>2026-09-22T23:08:01Z</t>
         </is>
       </c>
     </row>
@@ -9421,7 +9421,7 @@
       </c>
       <c r="K186" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:13Z</t>
+          <t>2026-09-22T23:08:01Z</t>
         </is>
       </c>
     </row>
@@ -9470,7 +9470,7 @@
       </c>
       <c r="K187" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:13Z</t>
+          <t>2026-09-22T23:08:01Z</t>
         </is>
       </c>
     </row>
@@ -9519,7 +9519,7 @@
       </c>
       <c r="K188" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:13Z</t>
+          <t>2026-09-22T23:08:01Z</t>
         </is>
       </c>
     </row>
@@ -9568,7 +9568,7 @@
       </c>
       <c r="K189" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:13Z</t>
+          <t>2026-09-22T23:08:01Z</t>
         </is>
       </c>
     </row>
@@ -9617,7 +9617,7 @@
       </c>
       <c r="K190" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:13Z</t>
+          <t>2026-09-22T23:08:01Z</t>
         </is>
       </c>
     </row>
@@ -9666,7 +9666,7 @@
       </c>
       <c r="K191" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:13Z</t>
+          <t>2026-09-22T23:08:01Z</t>
         </is>
       </c>
     </row>
@@ -9715,7 +9715,7 @@
       </c>
       <c r="K192" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:13Z</t>
+          <t>2026-09-22T23:08:01Z</t>
         </is>
       </c>
     </row>
@@ -9764,7 +9764,7 @@
       </c>
       <c r="K193" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:13Z</t>
+          <t>2026-09-22T23:08:01Z</t>
         </is>
       </c>
     </row>
@@ -9813,7 +9813,7 @@
       </c>
       <c r="K194" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:13Z</t>
+          <t>2026-09-22T23:08:01Z</t>
         </is>
       </c>
     </row>
@@ -9862,7 +9862,7 @@
       </c>
       <c r="K195" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:13Z</t>
+          <t>2026-09-22T23:08:01Z</t>
         </is>
       </c>
     </row>
@@ -9911,7 +9911,7 @@
       </c>
       <c r="K196" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:13Z</t>
+          <t>2026-09-22T23:08:01Z</t>
         </is>
       </c>
     </row>
@@ -9960,7 +9960,7 @@
       </c>
       <c r="K197" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:13Z</t>
+          <t>2026-09-22T23:08:01Z</t>
         </is>
       </c>
     </row>
@@ -10009,7 +10009,7 @@
       </c>
       <c r="K198" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:13Z</t>
+          <t>2026-09-22T23:08:01Z</t>
         </is>
       </c>
     </row>
@@ -10058,7 +10058,7 @@
       </c>
       <c r="K199" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:13Z</t>
+          <t>2026-09-22T23:08:01Z</t>
         </is>
       </c>
     </row>
@@ -10107,7 +10107,7 @@
       </c>
       <c r="K200" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:13Z</t>
+          <t>2026-09-22T23:08:01Z</t>
         </is>
       </c>
     </row>
@@ -10156,7 +10156,7 @@
       </c>
       <c r="K201" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:13Z</t>
+          <t>2026-09-22T23:08:01Z</t>
         </is>
       </c>
     </row>
@@ -10205,7 +10205,7 @@
       </c>
       <c r="K202" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:13Z</t>
+          <t>2026-09-22T23:08:01Z</t>
         </is>
       </c>
     </row>
@@ -10254,7 +10254,7 @@
       </c>
       <c r="K203" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:13Z</t>
+          <t>2026-09-22T23:08:01Z</t>
         </is>
       </c>
     </row>
@@ -10303,7 +10303,7 @@
       </c>
       <c r="K204" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:13Z</t>
+          <t>2026-09-22T23:08:01Z</t>
         </is>
       </c>
     </row>
@@ -10352,7 +10352,7 @@
       </c>
       <c r="K205" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:13Z</t>
+          <t>2026-09-22T23:08:01Z</t>
         </is>
       </c>
     </row>
@@ -10401,7 +10401,7 @@
       </c>
       <c r="K206" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:13Z</t>
+          <t>2026-09-22T23:08:01Z</t>
         </is>
       </c>
     </row>
@@ -10450,7 +10450,7 @@
       </c>
       <c r="K207" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:13Z</t>
+          <t>2026-09-22T23:08:01Z</t>
         </is>
       </c>
     </row>
@@ -10499,7 +10499,7 @@
       </c>
       <c r="K208" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:13Z</t>
+          <t>2026-09-22T23:08:01Z</t>
         </is>
       </c>
     </row>
@@ -10548,7 +10548,7 @@
       </c>
       <c r="K209" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:13Z</t>
+          <t>2026-09-22T23:08:01Z</t>
         </is>
       </c>
     </row>
@@ -10597,7 +10597,7 @@
       </c>
       <c r="K210" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:13Z</t>
+          <t>2026-09-22T23:08:01Z</t>
         </is>
       </c>
     </row>
@@ -10646,7 +10646,7 @@
       </c>
       <c r="K211" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:13Z</t>
+          <t>2026-09-22T23:08:01Z</t>
         </is>
       </c>
     </row>
@@ -10695,7 +10695,7 @@
       </c>
       <c r="K212" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:13Z</t>
+          <t>2026-09-22T23:08:01Z</t>
         </is>
       </c>
     </row>
@@ -10744,7 +10744,7 @@
       </c>
       <c r="K213" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:13Z</t>
+          <t>2026-09-22T23:08:01Z</t>
         </is>
       </c>
     </row>
@@ -10793,7 +10793,7 @@
       </c>
       <c r="K214" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:13Z</t>
+          <t>2026-09-22T23:08:01Z</t>
         </is>
       </c>
     </row>
@@ -10842,7 +10842,7 @@
       </c>
       <c r="K215" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:13Z</t>
+          <t>2026-09-22T23:08:01Z</t>
         </is>
       </c>
     </row>
@@ -10891,7 +10891,7 @@
       </c>
       <c r="K216" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:13Z</t>
+          <t>2026-09-22T23:08:01Z</t>
         </is>
       </c>
     </row>
@@ -10940,7 +10940,7 @@
       </c>
       <c r="K217" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:13Z</t>
+          <t>2026-09-22T23:08:01Z</t>
         </is>
       </c>
     </row>
@@ -10989,7 +10989,7 @@
       </c>
       <c r="K218" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:13Z</t>
+          <t>2026-09-22T23:08:01Z</t>
         </is>
       </c>
     </row>
@@ -11038,7 +11038,7 @@
       </c>
       <c r="K219" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:13Z</t>
+          <t>2026-09-22T23:08:01Z</t>
         </is>
       </c>
     </row>
@@ -11087,7 +11087,7 @@
       </c>
       <c r="K220" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:13Z</t>
+          <t>2026-09-22T23:08:01Z</t>
         </is>
       </c>
     </row>
@@ -11136,7 +11136,7 @@
       </c>
       <c r="K221" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:13Z</t>
+          <t>2026-09-22T23:08:01Z</t>
         </is>
       </c>
     </row>
@@ -11185,7 +11185,7 @@
       </c>
       <c r="K222" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:13Z</t>
+          <t>2026-09-22T23:08:01Z</t>
         </is>
       </c>
     </row>
@@ -11234,7 +11234,7 @@
       </c>
       <c r="K223" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:13Z</t>
+          <t>2026-09-22T23:08:01Z</t>
         </is>
       </c>
     </row>
@@ -11283,7 +11283,7 @@
       </c>
       <c r="K224" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:13Z</t>
+          <t>2026-09-22T23:08:01Z</t>
         </is>
       </c>
     </row>
@@ -11332,7 +11332,7 @@
       </c>
       <c r="K225" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:13Z</t>
+          <t>2026-09-22T23:08:01Z</t>
         </is>
       </c>
     </row>
@@ -11381,7 +11381,7 @@
       </c>
       <c r="K226" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:13Z</t>
+          <t>2026-09-22T23:08:01Z</t>
         </is>
       </c>
     </row>
@@ -11430,7 +11430,7 @@
       </c>
       <c r="K227" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:13Z</t>
+          <t>2026-09-22T23:08:01Z</t>
         </is>
       </c>
     </row>
@@ -11479,7 +11479,7 @@
       </c>
       <c r="K228" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:13Z</t>
+          <t>2026-09-22T23:08:01Z</t>
         </is>
       </c>
     </row>
@@ -11528,7 +11528,7 @@
       </c>
       <c r="K229" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:13Z</t>
+          <t>2026-09-22T23:08:01Z</t>
         </is>
       </c>
     </row>
@@ -11577,7 +11577,7 @@
       </c>
       <c r="K230" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:13Z</t>
+          <t>2026-09-22T23:08:01Z</t>
         </is>
       </c>
     </row>
@@ -11626,7 +11626,7 @@
       </c>
       <c r="K231" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:13Z</t>
+          <t>2026-09-22T23:08:01Z</t>
         </is>
       </c>
     </row>
@@ -11758,7 +11758,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:13Z</t>
+          <t>2026-09-22T23:08:01Z</t>
         </is>
       </c>
     </row>
@@ -11804,7 +11804,7 @@
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>{"date": "2026-08-01", "year": 2026, "month": 8, "month_name": "Agosto", "index_value": 637409769724325.1, "monthly_variation_pct": 8.9, "unit": "Índice base diciembre 2007=100 y variación mensual %", "frequency": "monthly", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/precios_consumidor/4_5_7_2.xls", "fetched_at": "2026-09-22T17:38:13Z"}</t>
+          <t>{"date": "2026-08-01", "year": 2026, "month": 8, "month_name": "Agosto", "index_value": 637409769724325.1, "monthly_variation_pct": 8.9, "unit": "Índice base diciembre 2007=100 y variación mensual %", "frequency": "monthly", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/precios_consumidor/4_5_7_2.xls", "fetched_at": "2026-09-22T23:08:01Z"}</t>
         </is>
       </c>
     </row>

--- a/assets/data/bcv/excel/ove_bcv_inpc_nacional_mensual.xlsx
+++ b/assets/data/bcv/excel/ove_bcv_inpc_nacional_mensual.xlsx
@@ -650,7 +650,7 @@
       </c>
       <c r="K7" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:01Z</t>
+          <t>2026-09-23T23:02:37Z</t>
         </is>
       </c>
     </row>
@@ -699,7 +699,7 @@
       </c>
       <c r="K8" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:01Z</t>
+          <t>2026-09-23T23:02:37Z</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="K9" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:01Z</t>
+          <t>2026-09-23T23:02:37Z</t>
         </is>
       </c>
     </row>
@@ -797,7 +797,7 @@
       </c>
       <c r="K10" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:01Z</t>
+          <t>2026-09-23T23:02:37Z</t>
         </is>
       </c>
     </row>
@@ -846,7 +846,7 @@
       </c>
       <c r="K11" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:01Z</t>
+          <t>2026-09-23T23:02:37Z</t>
         </is>
       </c>
     </row>
@@ -895,7 +895,7 @@
       </c>
       <c r="K12" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:01Z</t>
+          <t>2026-09-23T23:02:37Z</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="K13" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:01Z</t>
+          <t>2026-09-23T23:02:37Z</t>
         </is>
       </c>
     </row>
@@ -993,7 +993,7 @@
       </c>
       <c r="K14" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:01Z</t>
+          <t>2026-09-23T23:02:37Z</t>
         </is>
       </c>
     </row>
@@ -1042,7 +1042,7 @@
       </c>
       <c r="K15" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:01Z</t>
+          <t>2026-09-23T23:02:37Z</t>
         </is>
       </c>
     </row>
@@ -1091,7 +1091,7 @@
       </c>
       <c r="K16" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:01Z</t>
+          <t>2026-09-23T23:02:37Z</t>
         </is>
       </c>
     </row>
@@ -1140,7 +1140,7 @@
       </c>
       <c r="K17" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:01Z</t>
+          <t>2026-09-23T23:02:37Z</t>
         </is>
       </c>
     </row>
@@ -1189,7 +1189,7 @@
       </c>
       <c r="K18" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:01Z</t>
+          <t>2026-09-23T23:02:37Z</t>
         </is>
       </c>
     </row>
@@ -1238,7 +1238,7 @@
       </c>
       <c r="K19" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:01Z</t>
+          <t>2026-09-23T23:02:37Z</t>
         </is>
       </c>
     </row>
@@ -1287,7 +1287,7 @@
       </c>
       <c r="K20" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:01Z</t>
+          <t>2026-09-23T23:02:37Z</t>
         </is>
       </c>
     </row>
@@ -1336,7 +1336,7 @@
       </c>
       <c r="K21" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:01Z</t>
+          <t>2026-09-23T23:02:37Z</t>
         </is>
       </c>
     </row>
@@ -1385,7 +1385,7 @@
       </c>
       <c r="K22" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:01Z</t>
+          <t>2026-09-23T23:02:37Z</t>
         </is>
       </c>
     </row>
@@ -1434,7 +1434,7 @@
       </c>
       <c r="K23" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:01Z</t>
+          <t>2026-09-23T23:02:37Z</t>
         </is>
       </c>
     </row>
@@ -1483,7 +1483,7 @@
       </c>
       <c r="K24" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:01Z</t>
+          <t>2026-09-23T23:02:37Z</t>
         </is>
       </c>
     </row>
@@ -1532,7 +1532,7 @@
       </c>
       <c r="K25" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:01Z</t>
+          <t>2026-09-23T23:02:37Z</t>
         </is>
       </c>
     </row>
@@ -1581,7 +1581,7 @@
       </c>
       <c r="K26" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:01Z</t>
+          <t>2026-09-23T23:02:37Z</t>
         </is>
       </c>
     </row>
@@ -1630,7 +1630,7 @@
       </c>
       <c r="K27" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:01Z</t>
+          <t>2026-09-23T23:02:37Z</t>
         </is>
       </c>
     </row>
@@ -1679,7 +1679,7 @@
       </c>
       <c r="K28" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:01Z</t>
+          <t>2026-09-23T23:02:37Z</t>
         </is>
       </c>
     </row>
@@ -1728,7 +1728,7 @@
       </c>
       <c r="K29" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:01Z</t>
+          <t>2026-09-23T23:02:37Z</t>
         </is>
       </c>
     </row>
@@ -1777,7 +1777,7 @@
       </c>
       <c r="K30" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:01Z</t>
+          <t>2026-09-23T23:02:37Z</t>
         </is>
       </c>
     </row>
@@ -1826,7 +1826,7 @@
       </c>
       <c r="K31" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:01Z</t>
+          <t>2026-09-23T23:02:37Z</t>
         </is>
       </c>
     </row>
@@ -1875,7 +1875,7 @@
       </c>
       <c r="K32" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:01Z</t>
+          <t>2026-09-23T23:02:37Z</t>
         </is>
       </c>
     </row>
@@ -1924,7 +1924,7 @@
       </c>
       <c r="K33" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:01Z</t>
+          <t>2026-09-23T23:02:37Z</t>
         </is>
       </c>
     </row>
@@ -1973,7 +1973,7 @@
       </c>
       <c r="K34" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:01Z</t>
+          <t>2026-09-23T23:02:37Z</t>
         </is>
       </c>
     </row>
@@ -2022,7 +2022,7 @@
       </c>
       <c r="K35" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:01Z</t>
+          <t>2026-09-23T23:02:37Z</t>
         </is>
       </c>
     </row>
@@ -2071,7 +2071,7 @@
       </c>
       <c r="K36" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:01Z</t>
+          <t>2026-09-23T23:02:37Z</t>
         </is>
       </c>
     </row>
@@ -2120,7 +2120,7 @@
       </c>
       <c r="K37" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:01Z</t>
+          <t>2026-09-23T23:02:37Z</t>
         </is>
       </c>
     </row>
@@ -2169,7 +2169,7 @@
       </c>
       <c r="K38" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:01Z</t>
+          <t>2026-09-23T23:02:37Z</t>
         </is>
       </c>
     </row>
@@ -2218,7 +2218,7 @@
       </c>
       <c r="K39" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:01Z</t>
+          <t>2026-09-23T23:02:37Z</t>
         </is>
       </c>
     </row>
@@ -2267,7 +2267,7 @@
       </c>
       <c r="K40" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:01Z</t>
+          <t>2026-09-23T23:02:37Z</t>
         </is>
       </c>
     </row>
@@ -2316,7 +2316,7 @@
       </c>
       <c r="K41" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:01Z</t>
+          <t>2026-09-23T23:02:37Z</t>
         </is>
       </c>
     </row>
@@ -2365,7 +2365,7 @@
       </c>
       <c r="K42" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:01Z</t>
+          <t>2026-09-23T23:02:37Z</t>
         </is>
       </c>
     </row>
@@ -2414,7 +2414,7 @@
       </c>
       <c r="K43" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:01Z</t>
+          <t>2026-09-23T23:02:37Z</t>
         </is>
       </c>
     </row>
@@ -2463,7 +2463,7 @@
       </c>
       <c r="K44" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:01Z</t>
+          <t>2026-09-23T23:02:37Z</t>
         </is>
       </c>
     </row>
@@ -2512,7 +2512,7 @@
       </c>
       <c r="K45" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:01Z</t>
+          <t>2026-09-23T23:02:37Z</t>
         </is>
       </c>
     </row>
@@ -2561,7 +2561,7 @@
       </c>
       <c r="K46" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:01Z</t>
+          <t>2026-09-23T23:02:37Z</t>
         </is>
       </c>
     </row>
@@ -2610,7 +2610,7 @@
       </c>
       <c r="K47" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:01Z</t>
+          <t>2026-09-23T23:02:37Z</t>
         </is>
       </c>
     </row>
@@ -2659,7 +2659,7 @@
       </c>
       <c r="K48" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:01Z</t>
+          <t>2026-09-23T23:02:37Z</t>
         </is>
       </c>
     </row>
@@ -2708,7 +2708,7 @@
       </c>
       <c r="K49" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:01Z</t>
+          <t>2026-09-23T23:02:37Z</t>
         </is>
       </c>
     </row>
@@ -2757,7 +2757,7 @@
       </c>
       <c r="K50" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:01Z</t>
+          <t>2026-09-23T23:02:37Z</t>
         </is>
       </c>
     </row>
@@ -2806,7 +2806,7 @@
       </c>
       <c r="K51" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:01Z</t>
+          <t>2026-09-23T23:02:37Z</t>
         </is>
       </c>
     </row>
@@ -2855,7 +2855,7 @@
       </c>
       <c r="K52" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:01Z</t>
+          <t>2026-09-23T23:02:37Z</t>
         </is>
       </c>
     </row>
@@ -2904,7 +2904,7 @@
       </c>
       <c r="K53" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:01Z</t>
+          <t>2026-09-23T23:02:37Z</t>
         </is>
       </c>
     </row>
@@ -2953,7 +2953,7 @@
       </c>
       <c r="K54" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:01Z</t>
+          <t>2026-09-23T23:02:37Z</t>
         </is>
       </c>
     </row>
@@ -3002,7 +3002,7 @@
       </c>
       <c r="K55" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:01Z</t>
+          <t>2026-09-23T23:02:37Z</t>
         </is>
       </c>
     </row>
@@ -3051,7 +3051,7 @@
       </c>
       <c r="K56" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:01Z</t>
+          <t>2026-09-23T23:02:37Z</t>
         </is>
       </c>
     </row>
@@ -3100,7 +3100,7 @@
       </c>
       <c r="K57" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:01Z</t>
+          <t>2026-09-23T23:02:37Z</t>
         </is>
       </c>
     </row>
@@ -3149,7 +3149,7 @@
       </c>
       <c r="K58" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:01Z</t>
+          <t>2026-09-23T23:02:37Z</t>
         </is>
       </c>
     </row>
@@ -3198,7 +3198,7 @@
       </c>
       <c r="K59" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:01Z</t>
+          <t>2026-09-23T23:02:37Z</t>
         </is>
       </c>
     </row>
@@ -3247,7 +3247,7 @@
       </c>
       <c r="K60" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:01Z</t>
+          <t>2026-09-23T23:02:37Z</t>
         </is>
       </c>
     </row>
@@ -3296,7 +3296,7 @@
       </c>
       <c r="K61" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:01Z</t>
+          <t>2026-09-23T23:02:37Z</t>
         </is>
       </c>
     </row>
@@ -3345,7 +3345,7 @@
       </c>
       <c r="K62" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:01Z</t>
+          <t>2026-09-23T23:02:37Z</t>
         </is>
       </c>
     </row>
@@ -3394,7 +3394,7 @@
       </c>
       <c r="K63" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:01Z</t>
+          <t>2026-09-23T23:02:37Z</t>
         </is>
       </c>
     </row>
@@ -3443,7 +3443,7 @@
       </c>
       <c r="K64" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:01Z</t>
+          <t>2026-09-23T23:02:37Z</t>
         </is>
       </c>
     </row>
@@ -3492,7 +3492,7 @@
       </c>
       <c r="K65" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:01Z</t>
+          <t>2026-09-23T23:02:37Z</t>
         </is>
       </c>
     </row>
@@ -3541,7 +3541,7 @@
       </c>
       <c r="K66" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:01Z</t>
+          <t>2026-09-23T23:02:37Z</t>
         </is>
       </c>
     </row>
@@ -3590,7 +3590,7 @@
       </c>
       <c r="K67" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:01Z</t>
+          <t>2026-09-23T23:02:37Z</t>
         </is>
       </c>
     </row>
@@ -3639,7 +3639,7 @@
       </c>
       <c r="K68" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:01Z</t>
+          <t>2026-09-23T23:02:37Z</t>
         </is>
       </c>
     </row>
@@ -3688,7 +3688,7 @@
       </c>
       <c r="K69" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:01Z</t>
+          <t>2026-09-23T23:02:37Z</t>
         </is>
       </c>
     </row>
@@ -3737,7 +3737,7 @@
       </c>
       <c r="K70" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:01Z</t>
+          <t>2026-09-23T23:02:37Z</t>
         </is>
       </c>
     </row>
@@ -3786,7 +3786,7 @@
       </c>
       <c r="K71" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:01Z</t>
+          <t>2026-09-23T23:02:37Z</t>
         </is>
       </c>
     </row>
@@ -3835,7 +3835,7 @@
       </c>
       <c r="K72" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:01Z</t>
+          <t>2026-09-23T23:02:37Z</t>
         </is>
       </c>
     </row>
@@ -3884,7 +3884,7 @@
       </c>
       <c r="K73" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:01Z</t>
+          <t>2026-09-23T23:02:37Z</t>
         </is>
       </c>
     </row>
@@ -3933,7 +3933,7 @@
       </c>
       <c r="K74" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:01Z</t>
+          <t>2026-09-23T23:02:37Z</t>
         </is>
       </c>
     </row>
@@ -3982,7 +3982,7 @@
       </c>
       <c r="K75" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:01Z</t>
+          <t>2026-09-23T23:02:37Z</t>
         </is>
       </c>
     </row>
@@ -4031,7 +4031,7 @@
       </c>
       <c r="K76" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:01Z</t>
+          <t>2026-09-23T23:02:37Z</t>
         </is>
       </c>
     </row>
@@ -4080,7 +4080,7 @@
       </c>
       <c r="K77" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:01Z</t>
+          <t>2026-09-23T23:02:37Z</t>
         </is>
       </c>
     </row>
@@ -4129,7 +4129,7 @@
       </c>
       <c r="K78" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:01Z</t>
+          <t>2026-09-23T23:02:37Z</t>
         </is>
       </c>
     </row>
@@ -4178,7 +4178,7 @@
       </c>
       <c r="K79" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:01Z</t>
+          <t>2026-09-23T23:02:37Z</t>
         </is>
       </c>
     </row>
@@ -4227,7 +4227,7 @@
       </c>
       <c r="K80" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:01Z</t>
+          <t>2026-09-23T23:02:37Z</t>
         </is>
       </c>
     </row>
@@ -4276,7 +4276,7 @@
       </c>
       <c r="K81" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:01Z</t>
+          <t>2026-09-23T23:02:37Z</t>
         </is>
       </c>
     </row>
@@ -4325,7 +4325,7 @@
       </c>
       <c r="K82" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:01Z</t>
+          <t>2026-09-23T23:02:37Z</t>
         </is>
       </c>
     </row>
@@ -4374,7 +4374,7 @@
       </c>
       <c r="K83" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:01Z</t>
+          <t>2026-09-23T23:02:37Z</t>
         </is>
       </c>
     </row>
@@ -4423,7 +4423,7 @@
       </c>
       <c r="K84" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:01Z</t>
+          <t>2026-09-23T23:02:37Z</t>
         </is>
       </c>
     </row>
@@ -4472,7 +4472,7 @@
       </c>
       <c r="K85" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:01Z</t>
+          <t>2026-09-23T23:02:37Z</t>
         </is>
       </c>
     </row>
@@ -4521,7 +4521,7 @@
       </c>
       <c r="K86" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:01Z</t>
+          <t>2026-09-23T23:02:37Z</t>
         </is>
       </c>
     </row>
@@ -4570,7 +4570,7 @@
       </c>
       <c r="K87" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:01Z</t>
+          <t>2026-09-23T23:02:37Z</t>
         </is>
       </c>
     </row>
@@ -4619,7 +4619,7 @@
       </c>
       <c r="K88" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:01Z</t>
+          <t>2026-09-23T23:02:37Z</t>
         </is>
       </c>
     </row>
@@ -4668,7 +4668,7 @@
       </c>
       <c r="K89" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:01Z</t>
+          <t>2026-09-23T23:02:37Z</t>
         </is>
       </c>
     </row>
@@ -4717,7 +4717,7 @@
       </c>
       <c r="K90" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:01Z</t>
+          <t>2026-09-23T23:02:37Z</t>
         </is>
       </c>
     </row>
@@ -4766,7 +4766,7 @@
       </c>
       <c r="K91" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:01Z</t>
+          <t>2026-09-23T23:02:37Z</t>
         </is>
       </c>
     </row>
@@ -4815,7 +4815,7 @@
       </c>
       <c r="K92" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:01Z</t>
+          <t>2026-09-23T23:02:37Z</t>
         </is>
       </c>
     </row>
@@ -4864,7 +4864,7 @@
       </c>
       <c r="K93" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:01Z</t>
+          <t>2026-09-23T23:02:37Z</t>
         </is>
       </c>
     </row>
@@ -4913,7 +4913,7 @@
       </c>
       <c r="K94" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:01Z</t>
+          <t>2026-09-23T23:02:37Z</t>
         </is>
       </c>
     </row>
@@ -4962,7 +4962,7 @@
       </c>
       <c r="K95" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:01Z</t>
+          <t>2026-09-23T23:02:37Z</t>
         </is>
       </c>
     </row>
@@ -5011,7 +5011,7 @@
       </c>
       <c r="K96" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:01Z</t>
+          <t>2026-09-23T23:02:37Z</t>
         </is>
       </c>
     </row>
@@ -5060,7 +5060,7 @@
       </c>
       <c r="K97" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:01Z</t>
+          <t>2026-09-23T23:02:37Z</t>
         </is>
       </c>
     </row>
@@ -5109,7 +5109,7 @@
       </c>
       <c r="K98" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:01Z</t>
+          <t>2026-09-23T23:02:37Z</t>
         </is>
       </c>
     </row>
@@ -5158,7 +5158,7 @@
       </c>
       <c r="K99" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:01Z</t>
+          <t>2026-09-23T23:02:37Z</t>
         </is>
       </c>
     </row>
@@ -5207,7 +5207,7 @@
       </c>
       <c r="K100" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:01Z</t>
+          <t>2026-09-23T23:02:37Z</t>
         </is>
       </c>
     </row>
@@ -5256,7 +5256,7 @@
       </c>
       <c r="K101" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:01Z</t>
+          <t>2026-09-23T23:02:37Z</t>
         </is>
       </c>
     </row>
@@ -5305,7 +5305,7 @@
       </c>
       <c r="K102" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:01Z</t>
+          <t>2026-09-23T23:02:37Z</t>
         </is>
       </c>
     </row>
@@ -5354,7 +5354,7 @@
       </c>
       <c r="K103" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:01Z</t>
+          <t>2026-09-23T23:02:37Z</t>
         </is>
       </c>
     </row>
@@ -5403,7 +5403,7 @@
       </c>
       <c r="K104" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:01Z</t>
+          <t>2026-09-23T23:02:37Z</t>
         </is>
       </c>
     </row>
@@ -5452,7 +5452,7 @@
       </c>
       <c r="K105" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:01Z</t>
+          <t>2026-09-23T23:02:37Z</t>
         </is>
       </c>
     </row>
@@ -5501,7 +5501,7 @@
       </c>
       <c r="K106" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:01Z</t>
+          <t>2026-09-23T23:02:37Z</t>
         </is>
       </c>
     </row>
@@ -5550,7 +5550,7 @@
       </c>
       <c r="K107" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:01Z</t>
+          <t>2026-09-23T23:02:37Z</t>
         </is>
       </c>
     </row>
@@ -5599,7 +5599,7 @@
       </c>
       <c r="K108" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:01Z</t>
+          <t>2026-09-23T23:02:37Z</t>
         </is>
       </c>
     </row>
@@ -5648,7 +5648,7 @@
       </c>
       <c r="K109" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:01Z</t>
+          <t>2026-09-23T23:02:37Z</t>
         </is>
       </c>
     </row>
@@ -5697,7 +5697,7 @@
       </c>
       <c r="K110" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:01Z</t>
+          <t>2026-09-23T23:02:37Z</t>
         </is>
       </c>
     </row>
@@ -5746,7 +5746,7 @@
       </c>
       <c r="K111" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:01Z</t>
+          <t>2026-09-23T23:02:37Z</t>
         </is>
       </c>
     </row>
@@ -5795,7 +5795,7 @@
       </c>
       <c r="K112" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:01Z</t>
+          <t>2026-09-23T23:02:37Z</t>
         </is>
       </c>
     </row>
@@ -5844,7 +5844,7 @@
       </c>
       <c r="K113" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:01Z</t>
+          <t>2026-09-23T23:02:37Z</t>
         </is>
       </c>
     </row>
@@ -5893,7 +5893,7 @@
       </c>
       <c r="K114" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:01Z</t>
+          <t>2026-09-23T23:02:37Z</t>
         </is>
       </c>
     </row>
@@ -5942,7 +5942,7 @@
       </c>
       <c r="K115" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:01Z</t>
+          <t>2026-09-23T23:02:37Z</t>
         </is>
       </c>
     </row>
@@ -5991,7 +5991,7 @@
       </c>
       <c r="K116" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:01Z</t>
+          <t>2026-09-23T23:02:37Z</t>
         </is>
       </c>
     </row>
@@ -6040,7 +6040,7 @@
       </c>
       <c r="K117" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:01Z</t>
+          <t>2026-09-23T23:02:37Z</t>
         </is>
       </c>
     </row>
@@ -6089,7 +6089,7 @@
       </c>
       <c r="K118" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:01Z</t>
+          <t>2026-09-23T23:02:37Z</t>
         </is>
       </c>
     </row>
@@ -6138,7 +6138,7 @@
       </c>
       <c r="K119" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:01Z</t>
+          <t>2026-09-23T23:02:37Z</t>
         </is>
       </c>
     </row>
@@ -6187,7 +6187,7 @@
       </c>
       <c r="K120" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:01Z</t>
+          <t>2026-09-23T23:02:37Z</t>
         </is>
       </c>
     </row>
@@ -6236,7 +6236,7 @@
       </c>
       <c r="K121" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:01Z</t>
+          <t>2026-09-23T23:02:37Z</t>
         </is>
       </c>
     </row>
@@ -6285,7 +6285,7 @@
       </c>
       <c r="K122" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:01Z</t>
+          <t>2026-09-23T23:02:37Z</t>
         </is>
       </c>
     </row>
@@ -6334,7 +6334,7 @@
       </c>
       <c r="K123" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:01Z</t>
+          <t>2026-09-23T23:02:37Z</t>
         </is>
       </c>
     </row>
@@ -6383,7 +6383,7 @@
       </c>
       <c r="K124" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:01Z</t>
+          <t>2026-09-23T23:02:37Z</t>
         </is>
       </c>
     </row>
@@ -6432,7 +6432,7 @@
       </c>
       <c r="K125" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:01Z</t>
+          <t>2026-09-23T23:02:37Z</t>
         </is>
       </c>
     </row>
@@ -6481,7 +6481,7 @@
       </c>
       <c r="K126" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:01Z</t>
+          <t>2026-09-23T23:02:37Z</t>
         </is>
       </c>
     </row>
@@ -6530,7 +6530,7 @@
       </c>
       <c r="K127" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:01Z</t>
+          <t>2026-09-23T23:02:37Z</t>
         </is>
       </c>
     </row>
@@ -6579,7 +6579,7 @@
       </c>
       <c r="K128" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:01Z</t>
+          <t>2026-09-23T23:02:37Z</t>
         </is>
       </c>
     </row>
@@ -6628,7 +6628,7 @@
       </c>
       <c r="K129" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:01Z</t>
+          <t>2026-09-23T23:02:37Z</t>
         </is>
       </c>
     </row>
@@ -6677,7 +6677,7 @@
       </c>
       <c r="K130" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:01Z</t>
+          <t>2026-09-23T23:02:37Z</t>
         </is>
       </c>
     </row>
@@ -6726,7 +6726,7 @@
       </c>
       <c r="K131" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:01Z</t>
+          <t>2026-09-23T23:02:37Z</t>
         </is>
       </c>
     </row>
@@ -6775,7 +6775,7 @@
       </c>
       <c r="K132" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:01Z</t>
+          <t>2026-09-23T23:02:37Z</t>
         </is>
       </c>
     </row>
@@ -6824,7 +6824,7 @@
       </c>
       <c r="K133" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:01Z</t>
+          <t>2026-09-23T23:02:37Z</t>
         </is>
       </c>
     </row>
@@ -6873,7 +6873,7 @@
       </c>
       <c r="K134" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:01Z</t>
+          <t>2026-09-23T23:02:37Z</t>
         </is>
       </c>
     </row>
@@ -6922,7 +6922,7 @@
       </c>
       <c r="K135" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:01Z</t>
+          <t>2026-09-23T23:02:37Z</t>
         </is>
       </c>
     </row>
@@ -6971,7 +6971,7 @@
       </c>
       <c r="K136" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:01Z</t>
+          <t>2026-09-23T23:02:37Z</t>
         </is>
       </c>
     </row>
@@ -7020,7 +7020,7 @@
       </c>
       <c r="K137" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:01Z</t>
+          <t>2026-09-23T23:02:37Z</t>
         </is>
       </c>
     </row>
@@ -7069,7 +7069,7 @@
       </c>
       <c r="K138" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:01Z</t>
+          <t>2026-09-23T23:02:37Z</t>
         </is>
       </c>
     </row>
@@ -7118,7 +7118,7 @@
       </c>
       <c r="K139" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:01Z</t>
+          <t>2026-09-23T23:02:37Z</t>
         </is>
       </c>
     </row>
@@ -7167,7 +7167,7 @@
       </c>
       <c r="K140" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:01Z</t>
+          <t>2026-09-23T23:02:37Z</t>
         </is>
       </c>
     </row>
@@ -7216,7 +7216,7 @@
       </c>
       <c r="K141" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:01Z</t>
+          <t>2026-09-23T23:02:37Z</t>
         </is>
       </c>
     </row>
@@ -7265,7 +7265,7 @@
       </c>
       <c r="K142" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:01Z</t>
+          <t>2026-09-23T23:02:37Z</t>
         </is>
       </c>
     </row>
@@ -7314,7 +7314,7 @@
       </c>
       <c r="K143" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:01Z</t>
+          <t>2026-09-23T23:02:37Z</t>
         </is>
       </c>
     </row>
@@ -7363,7 +7363,7 @@
       </c>
       <c r="K144" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:01Z</t>
+          <t>2026-09-23T23:02:37Z</t>
         </is>
       </c>
     </row>
@@ -7412,7 +7412,7 @@
       </c>
       <c r="K145" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:01Z</t>
+          <t>2026-09-23T23:02:37Z</t>
         </is>
       </c>
     </row>
@@ -7461,7 +7461,7 @@
       </c>
       <c r="K146" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:01Z</t>
+          <t>2026-09-23T23:02:37Z</t>
         </is>
       </c>
     </row>
@@ -7510,7 +7510,7 @@
       </c>
       <c r="K147" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:01Z</t>
+          <t>2026-09-23T23:02:37Z</t>
         </is>
       </c>
     </row>
@@ -7559,7 +7559,7 @@
       </c>
       <c r="K148" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:01Z</t>
+          <t>2026-09-23T23:02:37Z</t>
         </is>
       </c>
     </row>
@@ -7608,7 +7608,7 @@
       </c>
       <c r="K149" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:01Z</t>
+          <t>2026-09-23T23:02:37Z</t>
         </is>
       </c>
     </row>
@@ -7657,7 +7657,7 @@
       </c>
       <c r="K150" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:01Z</t>
+          <t>2026-09-23T23:02:37Z</t>
         </is>
       </c>
     </row>
@@ -7706,7 +7706,7 @@
       </c>
       <c r="K151" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:01Z</t>
+          <t>2026-09-23T23:02:37Z</t>
         </is>
       </c>
     </row>
@@ -7755,7 +7755,7 @@
       </c>
       <c r="K152" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:01Z</t>
+          <t>2026-09-23T23:02:37Z</t>
         </is>
       </c>
     </row>
@@ -7804,7 +7804,7 @@
       </c>
       <c r="K153" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:01Z</t>
+          <t>2026-09-23T23:02:37Z</t>
         </is>
       </c>
     </row>
@@ -7853,7 +7853,7 @@
       </c>
       <c r="K154" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:01Z</t>
+          <t>2026-09-23T23:02:37Z</t>
         </is>
       </c>
     </row>
@@ -7902,7 +7902,7 @@
       </c>
       <c r="K155" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:01Z</t>
+          <t>2026-09-23T23:02:37Z</t>
         </is>
       </c>
     </row>
@@ -7951,7 +7951,7 @@
       </c>
       <c r="K156" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:01Z</t>
+          <t>2026-09-23T23:02:37Z</t>
         </is>
       </c>
     </row>
@@ -8000,7 +8000,7 @@
       </c>
       <c r="K157" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:01Z</t>
+          <t>2026-09-23T23:02:37Z</t>
         </is>
       </c>
     </row>
@@ -8049,7 +8049,7 @@
       </c>
       <c r="K158" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:01Z</t>
+          <t>2026-09-23T23:02:37Z</t>
         </is>
       </c>
     </row>
@@ -8098,7 +8098,7 @@
       </c>
       <c r="K159" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:01Z</t>
+          <t>2026-09-23T23:02:37Z</t>
         </is>
       </c>
     </row>
@@ -8147,7 +8147,7 @@
       </c>
       <c r="K160" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:01Z</t>
+          <t>2026-09-23T23:02:37Z</t>
         </is>
       </c>
     </row>
@@ -8196,7 +8196,7 @@
       </c>
       <c r="K161" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:01Z</t>
+          <t>2026-09-23T23:02:37Z</t>
         </is>
       </c>
     </row>
@@ -8245,7 +8245,7 @@
       </c>
       <c r="K162" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:01Z</t>
+          <t>2026-09-23T23:02:37Z</t>
         </is>
       </c>
     </row>
@@ -8294,7 +8294,7 @@
       </c>
       <c r="K163" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:01Z</t>
+          <t>2026-09-23T23:02:37Z</t>
         </is>
       </c>
     </row>
@@ -8343,7 +8343,7 @@
       </c>
       <c r="K164" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:01Z</t>
+          <t>2026-09-23T23:02:37Z</t>
         </is>
       </c>
     </row>
@@ -8392,7 +8392,7 @@
       </c>
       <c r="K165" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:01Z</t>
+          <t>2026-09-23T23:02:37Z</t>
         </is>
       </c>
     </row>
@@ -8441,7 +8441,7 @@
       </c>
       <c r="K166" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:01Z</t>
+          <t>2026-09-23T23:02:37Z</t>
         </is>
       </c>
     </row>
@@ -8490,7 +8490,7 @@
       </c>
       <c r="K167" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:01Z</t>
+          <t>2026-09-23T23:02:37Z</t>
         </is>
       </c>
     </row>
@@ -8539,7 +8539,7 @@
       </c>
       <c r="K168" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:01Z</t>
+          <t>2026-09-23T23:02:37Z</t>
         </is>
       </c>
     </row>
@@ -8588,7 +8588,7 @@
       </c>
       <c r="K169" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:01Z</t>
+          <t>2026-09-23T23:02:37Z</t>
         </is>
       </c>
     </row>
@@ -8637,7 +8637,7 @@
       </c>
       <c r="K170" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:01Z</t>
+          <t>2026-09-23T23:02:37Z</t>
         </is>
       </c>
     </row>
@@ -8686,7 +8686,7 @@
       </c>
       <c r="K171" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:01Z</t>
+          <t>2026-09-23T23:02:37Z</t>
         </is>
       </c>
     </row>
@@ -8735,7 +8735,7 @@
       </c>
       <c r="K172" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:01Z</t>
+          <t>2026-09-23T23:02:37Z</t>
         </is>
       </c>
     </row>
@@ -8784,7 +8784,7 @@
       </c>
       <c r="K173" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:01Z</t>
+          <t>2026-09-23T23:02:37Z</t>
         </is>
       </c>
     </row>
@@ -8833,7 +8833,7 @@
       </c>
       <c r="K174" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:01Z</t>
+          <t>2026-09-23T23:02:37Z</t>
         </is>
       </c>
     </row>
@@ -8882,7 +8882,7 @@
       </c>
       <c r="K175" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:01Z</t>
+          <t>2026-09-23T23:02:37Z</t>
         </is>
       </c>
     </row>
@@ -8931,7 +8931,7 @@
       </c>
       <c r="K176" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:01Z</t>
+          <t>2026-09-23T23:02:37Z</t>
         </is>
       </c>
     </row>
@@ -8980,7 +8980,7 @@
       </c>
       <c r="K177" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:01Z</t>
+          <t>2026-09-23T23:02:37Z</t>
         </is>
       </c>
     </row>
@@ -9029,7 +9029,7 @@
       </c>
       <c r="K178" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:01Z</t>
+          <t>2026-09-23T23:02:37Z</t>
         </is>
       </c>
     </row>
@@ -9078,7 +9078,7 @@
       </c>
       <c r="K179" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:01Z</t>
+          <t>2026-09-23T23:02:37Z</t>
         </is>
       </c>
     </row>
@@ -9127,7 +9127,7 @@
       </c>
       <c r="K180" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:01Z</t>
+          <t>2026-09-23T23:02:37Z</t>
         </is>
       </c>
     </row>
@@ -9176,7 +9176,7 @@
       </c>
       <c r="K181" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:01Z</t>
+          <t>2026-09-23T23:02:37Z</t>
         </is>
       </c>
     </row>
@@ -9225,7 +9225,7 @@
       </c>
       <c r="K182" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:01Z</t>
+          <t>2026-09-23T23:02:37Z</t>
         </is>
       </c>
     </row>
@@ -9274,7 +9274,7 @@
       </c>
       <c r="K183" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:01Z</t>
+          <t>2026-09-23T23:02:37Z</t>
         </is>
       </c>
     </row>
@@ -9323,7 +9323,7 @@
       </c>
       <c r="K184" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:01Z</t>
+          <t>2026-09-23T23:02:37Z</t>
         </is>
       </c>
     </row>
@@ -9372,7 +9372,7 @@
       </c>
       <c r="K185" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:01Z</t>
+          <t>2026-09-23T23:02:37Z</t>
         </is>
       </c>
     </row>
@@ -9421,7 +9421,7 @@
       </c>
       <c r="K186" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:01Z</t>
+          <t>2026-09-23T23:02:37Z</t>
         </is>
       </c>
     </row>
@@ -9470,7 +9470,7 @@
       </c>
       <c r="K187" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:01Z</t>
+          <t>2026-09-23T23:02:37Z</t>
         </is>
       </c>
     </row>
@@ -9519,7 +9519,7 @@
       </c>
       <c r="K188" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:01Z</t>
+          <t>2026-09-23T23:02:37Z</t>
         </is>
       </c>
     </row>
@@ -9568,7 +9568,7 @@
       </c>
       <c r="K189" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:01Z</t>
+          <t>2026-09-23T23:02:37Z</t>
         </is>
       </c>
     </row>
@@ -9617,7 +9617,7 @@
       </c>
       <c r="K190" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:01Z</t>
+          <t>2026-09-23T23:02:37Z</t>
         </is>
       </c>
     </row>
@@ -9666,7 +9666,7 @@
       </c>
       <c r="K191" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:01Z</t>
+          <t>2026-09-23T23:02:37Z</t>
         </is>
       </c>
     </row>
@@ -9715,7 +9715,7 @@
       </c>
       <c r="K192" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:01Z</t>
+          <t>2026-09-23T23:02:37Z</t>
         </is>
       </c>
     </row>
@@ -9764,7 +9764,7 @@
       </c>
       <c r="K193" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:01Z</t>
+          <t>2026-09-23T23:02:37Z</t>
         </is>
       </c>
     </row>
@@ -9813,7 +9813,7 @@
       </c>
       <c r="K194" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:01Z</t>
+          <t>2026-09-23T23:02:37Z</t>
         </is>
       </c>
     </row>
@@ -9862,7 +9862,7 @@
       </c>
       <c r="K195" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:01Z</t>
+          <t>2026-09-23T23:02:37Z</t>
         </is>
       </c>
     </row>
@@ -9911,7 +9911,7 @@
       </c>
       <c r="K196" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:01Z</t>
+          <t>2026-09-23T23:02:37Z</t>
         </is>
       </c>
     </row>
@@ -9960,7 +9960,7 @@
       </c>
       <c r="K197" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:01Z</t>
+          <t>2026-09-23T23:02:37Z</t>
         </is>
       </c>
     </row>
@@ -10009,7 +10009,7 @@
       </c>
       <c r="K198" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:01Z</t>
+          <t>2026-09-23T23:02:37Z</t>
         </is>
       </c>
     </row>
@@ -10058,7 +10058,7 @@
       </c>
       <c r="K199" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:01Z</t>
+          <t>2026-09-23T23:02:37Z</t>
         </is>
       </c>
     </row>
@@ -10107,7 +10107,7 @@
       </c>
       <c r="K200" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:01Z</t>
+          <t>2026-09-23T23:02:37Z</t>
         </is>
       </c>
     </row>
@@ -10156,7 +10156,7 @@
       </c>
       <c r="K201" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:01Z</t>
+          <t>2026-09-23T23:02:37Z</t>
         </is>
       </c>
     </row>
@@ -10205,7 +10205,7 @@
       </c>
       <c r="K202" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:01Z</t>
+          <t>2026-09-23T23:02:37Z</t>
         </is>
       </c>
     </row>
@@ -10254,7 +10254,7 @@
       </c>
       <c r="K203" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:01Z</t>
+          <t>2026-09-23T23:02:37Z</t>
         </is>
       </c>
     </row>
@@ -10303,7 +10303,7 @@
       </c>
       <c r="K204" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:01Z</t>
+          <t>2026-09-23T23:02:37Z</t>
         </is>
       </c>
     </row>
@@ -10352,7 +10352,7 @@
       </c>
       <c r="K205" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:01Z</t>
+          <t>2026-09-23T23:02:37Z</t>
         </is>
       </c>
     </row>
@@ -10401,7 +10401,7 @@
       </c>
       <c r="K206" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:01Z</t>
+          <t>2026-09-23T23:02:37Z</t>
         </is>
       </c>
     </row>
@@ -10450,7 +10450,7 @@
       </c>
       <c r="K207" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:01Z</t>
+          <t>2026-09-23T23:02:37Z</t>
         </is>
       </c>
     </row>
@@ -10499,7 +10499,7 @@
       </c>
       <c r="K208" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:01Z</t>
+          <t>2026-09-23T23:02:37Z</t>
         </is>
       </c>
     </row>
@@ -10548,7 +10548,7 @@
       </c>
       <c r="K209" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:01Z</t>
+          <t>2026-09-23T23:02:37Z</t>
         </is>
       </c>
     </row>
@@ -10597,7 +10597,7 @@
       </c>
       <c r="K210" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:01Z</t>
+          <t>2026-09-23T23:02:37Z</t>
         </is>
       </c>
     </row>
@@ -10646,7 +10646,7 @@
       </c>
       <c r="K211" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:01Z</t>
+          <t>2026-09-23T23:02:37Z</t>
         </is>
       </c>
     </row>
@@ -10695,7 +10695,7 @@
       </c>
       <c r="K212" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:01Z</t>
+          <t>2026-09-23T23:02:37Z</t>
         </is>
       </c>
     </row>
@@ -10744,7 +10744,7 @@
       </c>
       <c r="K213" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:01Z</t>
+          <t>2026-09-23T23:02:37Z</t>
         </is>
       </c>
     </row>
@@ -10793,7 +10793,7 @@
       </c>
       <c r="K214" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:01Z</t>
+          <t>2026-09-23T23:02:37Z</t>
         </is>
       </c>
     </row>
@@ -10842,7 +10842,7 @@
       </c>
       <c r="K215" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:01Z</t>
+          <t>2026-09-23T23:02:37Z</t>
         </is>
       </c>
     </row>
@@ -10891,7 +10891,7 @@
       </c>
       <c r="K216" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:01Z</t>
+          <t>2026-09-23T23:02:37Z</t>
         </is>
       </c>
     </row>
@@ -10940,7 +10940,7 @@
       </c>
       <c r="K217" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:01Z</t>
+          <t>2026-09-23T23:02:37Z</t>
         </is>
       </c>
     </row>
@@ -10989,7 +10989,7 @@
       </c>
       <c r="K218" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:01Z</t>
+          <t>2026-09-23T23:02:37Z</t>
         </is>
       </c>
     </row>
@@ -11038,7 +11038,7 @@
       </c>
       <c r="K219" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:01Z</t>
+          <t>2026-09-23T23:02:37Z</t>
         </is>
       </c>
     </row>
@@ -11087,7 +11087,7 @@
       </c>
       <c r="K220" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:01Z</t>
+          <t>2026-09-23T23:02:37Z</t>
         </is>
       </c>
     </row>
@@ -11136,7 +11136,7 @@
       </c>
       <c r="K221" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:01Z</t>
+          <t>2026-09-23T23:02:37Z</t>
         </is>
       </c>
     </row>
@@ -11185,7 +11185,7 @@
       </c>
       <c r="K222" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:01Z</t>
+          <t>2026-09-23T23:02:37Z</t>
         </is>
       </c>
     </row>
@@ -11234,7 +11234,7 @@
       </c>
       <c r="K223" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:01Z</t>
+          <t>2026-09-23T23:02:37Z</t>
         </is>
       </c>
     </row>
@@ -11283,7 +11283,7 @@
       </c>
       <c r="K224" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:01Z</t>
+          <t>2026-09-23T23:02:37Z</t>
         </is>
       </c>
     </row>
@@ -11332,7 +11332,7 @@
       </c>
       <c r="K225" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:01Z</t>
+          <t>2026-09-23T23:02:37Z</t>
         </is>
       </c>
     </row>
@@ -11381,7 +11381,7 @@
       </c>
       <c r="K226" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:01Z</t>
+          <t>2026-09-23T23:02:37Z</t>
         </is>
       </c>
     </row>
@@ -11430,7 +11430,7 @@
       </c>
       <c r="K227" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:01Z</t>
+          <t>2026-09-23T23:02:37Z</t>
         </is>
       </c>
     </row>
@@ -11479,7 +11479,7 @@
       </c>
       <c r="K228" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:01Z</t>
+          <t>2026-09-23T23:02:37Z</t>
         </is>
       </c>
     </row>
@@ -11528,7 +11528,7 @@
       </c>
       <c r="K229" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:01Z</t>
+          <t>2026-09-23T23:02:37Z</t>
         </is>
       </c>
     </row>
@@ -11577,7 +11577,7 @@
       </c>
       <c r="K230" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:01Z</t>
+          <t>2026-09-23T23:02:37Z</t>
         </is>
       </c>
     </row>
@@ -11626,7 +11626,7 @@
       </c>
       <c r="K231" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:01Z</t>
+          <t>2026-09-23T23:02:37Z</t>
         </is>
       </c>
     </row>
@@ -11758,7 +11758,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:01Z</t>
+          <t>2026-09-23T23:02:37Z</t>
         </is>
       </c>
     </row>
@@ -11804,7 +11804,7 @@
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>{"date": "2026-08-01", "year": 2026, "month": 8, "month_name": "Agosto", "index_value": 637409769724325.1, "monthly_variation_pct": 8.9, "unit": "Índice base diciembre 2007=100 y variación mensual %", "frequency": "monthly", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/precios_consumidor/4_5_7_2.xls", "fetched_at": "2026-09-22T23:08:01Z"}</t>
+          <t>{"date": "2026-08-01", "year": 2026, "month": 8, "month_name": "Agosto", "index_value": 637409769724325.1, "monthly_variation_pct": 8.9, "unit": "Índice base diciembre 2007=100 y variación mensual %", "frequency": "monthly", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/precios_consumidor/4_5_7_2.xls", "fetched_at": "2026-09-23T23:02:37Z"}</t>
         </is>
       </c>
     </row>

--- a/assets/data/bcv/excel/ove_bcv_inpc_nacional_mensual.xlsx
+++ b/assets/data/bcv/excel/ove_bcv_inpc_nacional_mensual.xlsx
@@ -650,7 +650,7 @@
       </c>
       <c r="K7" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:37Z</t>
+          <t>2026-09-24T23:17:56Z</t>
         </is>
       </c>
     </row>
@@ -699,7 +699,7 @@
       </c>
       <c r="K8" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:37Z</t>
+          <t>2026-09-24T23:17:56Z</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="K9" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:37Z</t>
+          <t>2026-09-24T23:17:56Z</t>
         </is>
       </c>
     </row>
@@ -797,7 +797,7 @@
       </c>
       <c r="K10" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:37Z</t>
+          <t>2026-09-24T23:17:56Z</t>
         </is>
       </c>
     </row>
@@ -846,7 +846,7 @@
       </c>
       <c r="K11" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:37Z</t>
+          <t>2026-09-24T23:17:56Z</t>
         </is>
       </c>
     </row>
@@ -895,7 +895,7 @@
       </c>
       <c r="K12" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:37Z</t>
+          <t>2026-09-24T23:17:56Z</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="K13" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:37Z</t>
+          <t>2026-09-24T23:17:56Z</t>
         </is>
       </c>
     </row>
@@ -993,7 +993,7 @@
       </c>
       <c r="K14" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:37Z</t>
+          <t>2026-09-24T23:17:56Z</t>
         </is>
       </c>
     </row>
@@ -1042,7 +1042,7 @@
       </c>
       <c r="K15" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:37Z</t>
+          <t>2026-09-24T23:17:56Z</t>
         </is>
       </c>
     </row>
@@ -1091,7 +1091,7 @@
       </c>
       <c r="K16" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:37Z</t>
+          <t>2026-09-24T23:17:56Z</t>
         </is>
       </c>
     </row>
@@ -1140,7 +1140,7 @@
       </c>
       <c r="K17" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:37Z</t>
+          <t>2026-09-24T23:17:56Z</t>
         </is>
       </c>
     </row>
@@ -1189,7 +1189,7 @@
       </c>
       <c r="K18" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:37Z</t>
+          <t>2026-09-24T23:17:56Z</t>
         </is>
       </c>
     </row>
@@ -1238,7 +1238,7 @@
       </c>
       <c r="K19" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:37Z</t>
+          <t>2026-09-24T23:17:56Z</t>
         </is>
       </c>
     </row>
@@ -1287,7 +1287,7 @@
       </c>
       <c r="K20" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:37Z</t>
+          <t>2026-09-24T23:17:56Z</t>
         </is>
       </c>
     </row>
@@ -1336,7 +1336,7 @@
       </c>
       <c r="K21" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:37Z</t>
+          <t>2026-09-24T23:17:56Z</t>
         </is>
       </c>
     </row>
@@ -1385,7 +1385,7 @@
       </c>
       <c r="K22" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:37Z</t>
+          <t>2026-09-24T23:17:56Z</t>
         </is>
       </c>
     </row>
@@ -1434,7 +1434,7 @@
       </c>
       <c r="K23" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:37Z</t>
+          <t>2026-09-24T23:17:56Z</t>
         </is>
       </c>
     </row>
@@ -1483,7 +1483,7 @@
       </c>
       <c r="K24" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:37Z</t>
+          <t>2026-09-24T23:17:56Z</t>
         </is>
       </c>
     </row>
@@ -1532,7 +1532,7 @@
       </c>
       <c r="K25" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:37Z</t>
+          <t>2026-09-24T23:17:56Z</t>
         </is>
       </c>
     </row>
@@ -1581,7 +1581,7 @@
       </c>
       <c r="K26" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:37Z</t>
+          <t>2026-09-24T23:17:56Z</t>
         </is>
       </c>
     </row>
@@ -1630,7 +1630,7 @@
       </c>
       <c r="K27" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:37Z</t>
+          <t>2026-09-24T23:17:56Z</t>
         </is>
       </c>
     </row>
@@ -1679,7 +1679,7 @@
       </c>
       <c r="K28" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:37Z</t>
+          <t>2026-09-24T23:17:56Z</t>
         </is>
       </c>
     </row>
@@ -1728,7 +1728,7 @@
       </c>
       <c r="K29" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:37Z</t>
+          <t>2026-09-24T23:17:56Z</t>
         </is>
       </c>
     </row>
@@ -1777,7 +1777,7 @@
       </c>
       <c r="K30" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:37Z</t>
+          <t>2026-09-24T23:17:56Z</t>
         </is>
       </c>
     </row>
@@ -1826,7 +1826,7 @@
       </c>
       <c r="K31" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:37Z</t>
+          <t>2026-09-24T23:17:56Z</t>
         </is>
       </c>
     </row>
@@ -1875,7 +1875,7 @@
       </c>
       <c r="K32" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:37Z</t>
+          <t>2026-09-24T23:17:56Z</t>
         </is>
       </c>
     </row>
@@ -1924,7 +1924,7 @@
       </c>
       <c r="K33" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:37Z</t>
+          <t>2026-09-24T23:17:56Z</t>
         </is>
       </c>
     </row>
@@ -1973,7 +1973,7 @@
       </c>
       <c r="K34" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:37Z</t>
+          <t>2026-09-24T23:17:56Z</t>
         </is>
       </c>
     </row>
@@ -2022,7 +2022,7 @@
       </c>
       <c r="K35" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:37Z</t>
+          <t>2026-09-24T23:17:56Z</t>
         </is>
       </c>
     </row>
@@ -2071,7 +2071,7 @@
       </c>
       <c r="K36" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:37Z</t>
+          <t>2026-09-24T23:17:56Z</t>
         </is>
       </c>
     </row>
@@ -2120,7 +2120,7 @@
       </c>
       <c r="K37" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:37Z</t>
+          <t>2026-09-24T23:17:56Z</t>
         </is>
       </c>
     </row>
@@ -2169,7 +2169,7 @@
       </c>
       <c r="K38" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:37Z</t>
+          <t>2026-09-24T23:17:56Z</t>
         </is>
       </c>
     </row>
@@ -2218,7 +2218,7 @@
       </c>
       <c r="K39" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:37Z</t>
+          <t>2026-09-24T23:17:56Z</t>
         </is>
       </c>
     </row>
@@ -2267,7 +2267,7 @@
       </c>
       <c r="K40" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:37Z</t>
+          <t>2026-09-24T23:17:56Z</t>
         </is>
       </c>
     </row>
@@ -2316,7 +2316,7 @@
       </c>
       <c r="K41" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:37Z</t>
+          <t>2026-09-24T23:17:56Z</t>
         </is>
       </c>
     </row>
@@ -2365,7 +2365,7 @@
       </c>
       <c r="K42" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:37Z</t>
+          <t>2026-09-24T23:17:56Z</t>
         </is>
       </c>
     </row>
@@ -2414,7 +2414,7 @@
       </c>
       <c r="K43" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:37Z</t>
+          <t>2026-09-24T23:17:56Z</t>
         </is>
       </c>
     </row>
@@ -2463,7 +2463,7 @@
       </c>
       <c r="K44" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:37Z</t>
+          <t>2026-09-24T23:17:56Z</t>
         </is>
       </c>
     </row>
@@ -2512,7 +2512,7 @@
       </c>
       <c r="K45" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:37Z</t>
+          <t>2026-09-24T23:17:56Z</t>
         </is>
       </c>
     </row>
@@ -2561,7 +2561,7 @@
       </c>
       <c r="K46" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:37Z</t>
+          <t>2026-09-24T23:17:56Z</t>
         </is>
       </c>
     </row>
@@ -2610,7 +2610,7 @@
       </c>
       <c r="K47" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:37Z</t>
+          <t>2026-09-24T23:17:56Z</t>
         </is>
       </c>
     </row>
@@ -2659,7 +2659,7 @@
       </c>
       <c r="K48" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:37Z</t>
+          <t>2026-09-24T23:17:56Z</t>
         </is>
       </c>
     </row>
@@ -2708,7 +2708,7 @@
       </c>
       <c r="K49" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:37Z</t>
+          <t>2026-09-24T23:17:56Z</t>
         </is>
       </c>
     </row>
@@ -2757,7 +2757,7 @@
       </c>
       <c r="K50" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:37Z</t>
+          <t>2026-09-24T23:17:56Z</t>
         </is>
       </c>
     </row>
@@ -2806,7 +2806,7 @@
       </c>
       <c r="K51" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:37Z</t>
+          <t>2026-09-24T23:17:56Z</t>
         </is>
       </c>
     </row>
@@ -2855,7 +2855,7 @@
       </c>
       <c r="K52" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:37Z</t>
+          <t>2026-09-24T23:17:56Z</t>
         </is>
       </c>
     </row>
@@ -2904,7 +2904,7 @@
       </c>
       <c r="K53" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:37Z</t>
+          <t>2026-09-24T23:17:56Z</t>
         </is>
       </c>
     </row>
@@ -2953,7 +2953,7 @@
       </c>
       <c r="K54" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:37Z</t>
+          <t>2026-09-24T23:17:56Z</t>
         </is>
       </c>
     </row>
@@ -3002,7 +3002,7 @@
       </c>
       <c r="K55" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:37Z</t>
+          <t>2026-09-24T23:17:56Z</t>
         </is>
       </c>
     </row>
@@ -3051,7 +3051,7 @@
       </c>
       <c r="K56" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:37Z</t>
+          <t>2026-09-24T23:17:56Z</t>
         </is>
       </c>
     </row>
@@ -3100,7 +3100,7 @@
       </c>
       <c r="K57" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:37Z</t>
+          <t>2026-09-24T23:17:56Z</t>
         </is>
       </c>
     </row>
@@ -3149,7 +3149,7 @@
       </c>
       <c r="K58" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:37Z</t>
+          <t>2026-09-24T23:17:56Z</t>
         </is>
       </c>
     </row>
@@ -3198,7 +3198,7 @@
       </c>
       <c r="K59" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:37Z</t>
+          <t>2026-09-24T23:17:56Z</t>
         </is>
       </c>
     </row>
@@ -3247,7 +3247,7 @@
       </c>
       <c r="K60" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:37Z</t>
+          <t>2026-09-24T23:17:56Z</t>
         </is>
       </c>
     </row>
@@ -3296,7 +3296,7 @@
       </c>
       <c r="K61" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:37Z</t>
+          <t>2026-09-24T23:17:56Z</t>
         </is>
       </c>
     </row>
@@ -3345,7 +3345,7 @@
       </c>
       <c r="K62" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:37Z</t>
+          <t>2026-09-24T23:17:56Z</t>
         </is>
       </c>
     </row>
@@ -3394,7 +3394,7 @@
       </c>
       <c r="K63" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:37Z</t>
+          <t>2026-09-24T23:17:56Z</t>
         </is>
       </c>
     </row>
@@ -3443,7 +3443,7 @@
       </c>
       <c r="K64" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:37Z</t>
+          <t>2026-09-24T23:17:56Z</t>
         </is>
       </c>
     </row>
@@ -3492,7 +3492,7 @@
       </c>
       <c r="K65" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:37Z</t>
+          <t>2026-09-24T23:17:56Z</t>
         </is>
       </c>
     </row>
@@ -3541,7 +3541,7 @@
       </c>
       <c r="K66" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:37Z</t>
+          <t>2026-09-24T23:17:56Z</t>
         </is>
       </c>
     </row>
@@ -3590,7 +3590,7 @@
       </c>
       <c r="K67" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:37Z</t>
+          <t>2026-09-24T23:17:56Z</t>
         </is>
       </c>
     </row>
@@ -3639,7 +3639,7 @@
       </c>
       <c r="K68" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:37Z</t>
+          <t>2026-09-24T23:17:56Z</t>
         </is>
       </c>
     </row>
@@ -3688,7 +3688,7 @@
       </c>
       <c r="K69" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:37Z</t>
+          <t>2026-09-24T23:17:56Z</t>
         </is>
       </c>
     </row>
@@ -3737,7 +3737,7 @@
       </c>
       <c r="K70" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:37Z</t>
+          <t>2026-09-24T23:17:56Z</t>
         </is>
       </c>
     </row>
@@ -3786,7 +3786,7 @@
       </c>
       <c r="K71" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:37Z</t>
+          <t>2026-09-24T23:17:56Z</t>
         </is>
       </c>
     </row>
@@ -3835,7 +3835,7 @@
       </c>
       <c r="K72" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:37Z</t>
+          <t>2026-09-24T23:17:56Z</t>
         </is>
       </c>
     </row>
@@ -3884,7 +3884,7 @@
       </c>
       <c r="K73" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:37Z</t>
+          <t>2026-09-24T23:17:56Z</t>
         </is>
       </c>
     </row>
@@ -3933,7 +3933,7 @@
       </c>
       <c r="K74" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:37Z</t>
+          <t>2026-09-24T23:17:56Z</t>
         </is>
       </c>
     </row>
@@ -3982,7 +3982,7 @@
       </c>
       <c r="K75" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:37Z</t>
+          <t>2026-09-24T23:17:56Z</t>
         </is>
       </c>
     </row>
@@ -4031,7 +4031,7 @@
       </c>
       <c r="K76" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:37Z</t>
+          <t>2026-09-24T23:17:56Z</t>
         </is>
       </c>
     </row>
@@ -4080,7 +4080,7 @@
       </c>
       <c r="K77" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:37Z</t>
+          <t>2026-09-24T23:17:56Z</t>
         </is>
       </c>
     </row>
@@ -4129,7 +4129,7 @@
       </c>
       <c r="K78" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:37Z</t>
+          <t>2026-09-24T23:17:56Z</t>
         </is>
       </c>
     </row>
@@ -4178,7 +4178,7 @@
       </c>
       <c r="K79" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:37Z</t>
+          <t>2026-09-24T23:17:56Z</t>
         </is>
       </c>
     </row>
@@ -4227,7 +4227,7 @@
       </c>
       <c r="K80" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:37Z</t>
+          <t>2026-09-24T23:17:56Z</t>
         </is>
       </c>
     </row>
@@ -4276,7 +4276,7 @@
       </c>
       <c r="K81" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:37Z</t>
+          <t>2026-09-24T23:17:56Z</t>
         </is>
       </c>
     </row>
@@ -4325,7 +4325,7 @@
       </c>
       <c r="K82" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:37Z</t>
+          <t>2026-09-24T23:17:56Z</t>
         </is>
       </c>
     </row>
@@ -4374,7 +4374,7 @@
       </c>
       <c r="K83" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:37Z</t>
+          <t>2026-09-24T23:17:56Z</t>
         </is>
       </c>
     </row>
@@ -4423,7 +4423,7 @@
       </c>
       <c r="K84" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:37Z</t>
+          <t>2026-09-24T23:17:56Z</t>
         </is>
       </c>
     </row>
@@ -4472,7 +4472,7 @@
       </c>
       <c r="K85" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:37Z</t>
+          <t>2026-09-24T23:17:56Z</t>
         </is>
       </c>
     </row>
@@ -4521,7 +4521,7 @@
       </c>
       <c r="K86" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:37Z</t>
+          <t>2026-09-24T23:17:56Z</t>
         </is>
       </c>
     </row>
@@ -4570,7 +4570,7 @@
       </c>
       <c r="K87" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:37Z</t>
+          <t>2026-09-24T23:17:56Z</t>
         </is>
       </c>
     </row>
@@ -4619,7 +4619,7 @@
       </c>
       <c r="K88" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:37Z</t>
+          <t>2026-09-24T23:17:56Z</t>
         </is>
       </c>
     </row>
@@ -4668,7 +4668,7 @@
       </c>
       <c r="K89" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:37Z</t>
+          <t>2026-09-24T23:17:56Z</t>
         </is>
       </c>
     </row>
@@ -4717,7 +4717,7 @@
       </c>
       <c r="K90" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:37Z</t>
+          <t>2026-09-24T23:17:56Z</t>
         </is>
       </c>
     </row>
@@ -4766,7 +4766,7 @@
       </c>
       <c r="K91" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:37Z</t>
+          <t>2026-09-24T23:17:56Z</t>
         </is>
       </c>
     </row>
@@ -4815,7 +4815,7 @@
       </c>
       <c r="K92" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:37Z</t>
+          <t>2026-09-24T23:17:56Z</t>
         </is>
       </c>
     </row>
@@ -4864,7 +4864,7 @@
       </c>
       <c r="K93" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:37Z</t>
+          <t>2026-09-24T23:17:56Z</t>
         </is>
       </c>
     </row>
@@ -4913,7 +4913,7 @@
       </c>
       <c r="K94" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:37Z</t>
+          <t>2026-09-24T23:17:56Z</t>
         </is>
       </c>
     </row>
@@ -4962,7 +4962,7 @@
       </c>
       <c r="K95" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:37Z</t>
+          <t>2026-09-24T23:17:56Z</t>
         </is>
       </c>
     </row>
@@ -5011,7 +5011,7 @@
       </c>
       <c r="K96" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:37Z</t>
+          <t>2026-09-24T23:17:56Z</t>
         </is>
       </c>
     </row>
@@ -5060,7 +5060,7 @@
       </c>
       <c r="K97" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:37Z</t>
+          <t>2026-09-24T23:17:56Z</t>
         </is>
       </c>
     </row>
@@ -5109,7 +5109,7 @@
       </c>
       <c r="K98" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:37Z</t>
+          <t>2026-09-24T23:17:56Z</t>
         </is>
       </c>
     </row>
@@ -5158,7 +5158,7 @@
       </c>
       <c r="K99" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:37Z</t>
+          <t>2026-09-24T23:17:56Z</t>
         </is>
       </c>
     </row>
@@ -5207,7 +5207,7 @@
       </c>
       <c r="K100" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:37Z</t>
+          <t>2026-09-24T23:17:56Z</t>
         </is>
       </c>
     </row>
@@ -5256,7 +5256,7 @@
       </c>
       <c r="K101" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:37Z</t>
+          <t>2026-09-24T23:17:56Z</t>
         </is>
       </c>
     </row>
@@ -5305,7 +5305,7 @@
       </c>
       <c r="K102" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:37Z</t>
+          <t>2026-09-24T23:17:56Z</t>
         </is>
       </c>
     </row>
@@ -5354,7 +5354,7 @@
       </c>
       <c r="K103" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:37Z</t>
+          <t>2026-09-24T23:17:56Z</t>
         </is>
       </c>
     </row>
@@ -5403,7 +5403,7 @@
       </c>
       <c r="K104" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:37Z</t>
+          <t>2026-09-24T23:17:56Z</t>
         </is>
       </c>
     </row>
@@ -5452,7 +5452,7 @@
       </c>
       <c r="K105" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:37Z</t>
+          <t>2026-09-24T23:17:56Z</t>
         </is>
       </c>
     </row>
@@ -5501,7 +5501,7 @@
       </c>
       <c r="K106" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:37Z</t>
+          <t>2026-09-24T23:17:56Z</t>
         </is>
       </c>
     </row>
@@ -5550,7 +5550,7 @@
       </c>
       <c r="K107" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:37Z</t>
+          <t>2026-09-24T23:17:56Z</t>
         </is>
       </c>
     </row>
@@ -5599,7 +5599,7 @@
       </c>
       <c r="K108" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:37Z</t>
+          <t>2026-09-24T23:17:56Z</t>
         </is>
       </c>
     </row>
@@ -5648,7 +5648,7 @@
       </c>
       <c r="K109" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:37Z</t>
+          <t>2026-09-24T23:17:56Z</t>
         </is>
       </c>
     </row>
@@ -5697,7 +5697,7 @@
       </c>
       <c r="K110" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:37Z</t>
+          <t>2026-09-24T23:17:56Z</t>
         </is>
       </c>
     </row>
@@ -5746,7 +5746,7 @@
       </c>
       <c r="K111" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:37Z</t>
+          <t>2026-09-24T23:17:56Z</t>
         </is>
       </c>
     </row>
@@ -5795,7 +5795,7 @@
       </c>
       <c r="K112" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:37Z</t>
+          <t>2026-09-24T23:17:56Z</t>
         </is>
       </c>
     </row>
@@ -5844,7 +5844,7 @@
       </c>
       <c r="K113" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:37Z</t>
+          <t>2026-09-24T23:17:56Z</t>
         </is>
       </c>
     </row>
@@ -5893,7 +5893,7 @@
       </c>
       <c r="K114" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:37Z</t>
+          <t>2026-09-24T23:17:56Z</t>
         </is>
       </c>
     </row>
@@ -5942,7 +5942,7 @@
       </c>
       <c r="K115" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:37Z</t>
+          <t>2026-09-24T23:17:56Z</t>
         </is>
       </c>
     </row>
@@ -5991,7 +5991,7 @@
       </c>
       <c r="K116" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:37Z</t>
+          <t>2026-09-24T23:17:56Z</t>
         </is>
       </c>
     </row>
@@ -6040,7 +6040,7 @@
       </c>
       <c r="K117" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:37Z</t>
+          <t>2026-09-24T23:17:56Z</t>
         </is>
       </c>
     </row>
@@ -6089,7 +6089,7 @@
       </c>
       <c r="K118" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:37Z</t>
+          <t>2026-09-24T23:17:56Z</t>
         </is>
       </c>
     </row>
@@ -6138,7 +6138,7 @@
       </c>
       <c r="K119" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:37Z</t>
+          <t>2026-09-24T23:17:56Z</t>
         </is>
       </c>
     </row>
@@ -6187,7 +6187,7 @@
       </c>
       <c r="K120" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:37Z</t>
+          <t>2026-09-24T23:17:56Z</t>
         </is>
       </c>
     </row>
@@ -6236,7 +6236,7 @@
       </c>
       <c r="K121" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:37Z</t>
+          <t>2026-09-24T23:17:56Z</t>
         </is>
       </c>
     </row>
@@ -6285,7 +6285,7 @@
       </c>
       <c r="K122" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:37Z</t>
+          <t>2026-09-24T23:17:56Z</t>
         </is>
       </c>
     </row>
@@ -6334,7 +6334,7 @@
       </c>
       <c r="K123" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:37Z</t>
+          <t>2026-09-24T23:17:56Z</t>
         </is>
       </c>
     </row>
@@ -6383,7 +6383,7 @@
       </c>
       <c r="K124" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:37Z</t>
+          <t>2026-09-24T23:17:56Z</t>
         </is>
       </c>
     </row>
@@ -6432,7 +6432,7 @@
       </c>
       <c r="K125" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:37Z</t>
+          <t>2026-09-24T23:17:56Z</t>
         </is>
       </c>
     </row>
@@ -6481,7 +6481,7 @@
       </c>
       <c r="K126" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:37Z</t>
+          <t>2026-09-24T23:17:56Z</t>
         </is>
       </c>
     </row>
@@ -6530,7 +6530,7 @@
       </c>
       <c r="K127" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:37Z</t>
+          <t>2026-09-24T23:17:56Z</t>
         </is>
       </c>
     </row>
@@ -6579,7 +6579,7 @@
       </c>
       <c r="K128" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:37Z</t>
+          <t>2026-09-24T23:17:56Z</t>
         </is>
       </c>
     </row>
@@ -6628,7 +6628,7 @@
       </c>
       <c r="K129" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:37Z</t>
+          <t>2026-09-24T23:17:56Z</t>
         </is>
       </c>
     </row>
@@ -6677,7 +6677,7 @@
       </c>
       <c r="K130" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:37Z</t>
+          <t>2026-09-24T23:17:56Z</t>
         </is>
       </c>
     </row>
@@ -6726,7 +6726,7 @@
       </c>
       <c r="K131" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:37Z</t>
+          <t>2026-09-24T23:17:56Z</t>
         </is>
       </c>
     </row>
@@ -6775,7 +6775,7 @@
       </c>
       <c r="K132" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:37Z</t>
+          <t>2026-09-24T23:17:56Z</t>
         </is>
       </c>
     </row>
@@ -6824,7 +6824,7 @@
       </c>
       <c r="K133" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:37Z</t>
+          <t>2026-09-24T23:17:56Z</t>
         </is>
       </c>
     </row>
@@ -6873,7 +6873,7 @@
       </c>
       <c r="K134" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:37Z</t>
+          <t>2026-09-24T23:17:56Z</t>
         </is>
       </c>
     </row>
@@ -6922,7 +6922,7 @@
       </c>
       <c r="K135" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:37Z</t>
+          <t>2026-09-24T23:17:56Z</t>
         </is>
       </c>
     </row>
@@ -6971,7 +6971,7 @@
       </c>
       <c r="K136" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:37Z</t>
+          <t>2026-09-24T23:17:56Z</t>
         </is>
       </c>
     </row>
@@ -7020,7 +7020,7 @@
       </c>
       <c r="K137" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:37Z</t>
+          <t>2026-09-24T23:17:56Z</t>
         </is>
       </c>
     </row>
@@ -7069,7 +7069,7 @@
       </c>
       <c r="K138" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:37Z</t>
+          <t>2026-09-24T23:17:56Z</t>
         </is>
       </c>
     </row>
@@ -7118,7 +7118,7 @@
       </c>
       <c r="K139" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:37Z</t>
+          <t>2026-09-24T23:17:56Z</t>
         </is>
       </c>
     </row>
@@ -7167,7 +7167,7 @@
       </c>
       <c r="K140" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:37Z</t>
+          <t>2026-09-24T23:17:56Z</t>
         </is>
       </c>
     </row>
@@ -7216,7 +7216,7 @@
       </c>
       <c r="K141" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:37Z</t>
+          <t>2026-09-24T23:17:56Z</t>
         </is>
       </c>
     </row>
@@ -7265,7 +7265,7 @@
       </c>
       <c r="K142" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:37Z</t>
+          <t>2026-09-24T23:17:56Z</t>
         </is>
       </c>
     </row>
@@ -7314,7 +7314,7 @@
       </c>
       <c r="K143" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:37Z</t>
+          <t>2026-09-24T23:17:56Z</t>
         </is>
       </c>
     </row>
@@ -7363,7 +7363,7 @@
       </c>
       <c r="K144" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:37Z</t>
+          <t>2026-09-24T23:17:56Z</t>
         </is>
       </c>
     </row>
@@ -7412,7 +7412,7 @@
       </c>
       <c r="K145" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:37Z</t>
+          <t>2026-09-24T23:17:56Z</t>
         </is>
       </c>
     </row>
@@ -7461,7 +7461,7 @@
       </c>
       <c r="K146" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:37Z</t>
+          <t>2026-09-24T23:17:56Z</t>
         </is>
       </c>
     </row>
@@ -7510,7 +7510,7 @@
       </c>
       <c r="K147" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:37Z</t>
+          <t>2026-09-24T23:17:56Z</t>
         </is>
       </c>
     </row>
@@ -7559,7 +7559,7 @@
       </c>
       <c r="K148" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:37Z</t>
+          <t>2026-09-24T23:17:56Z</t>
         </is>
       </c>
     </row>
@@ -7608,7 +7608,7 @@
       </c>
       <c r="K149" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:37Z</t>
+          <t>2026-09-24T23:17:56Z</t>
         </is>
       </c>
     </row>
@@ -7657,7 +7657,7 @@
       </c>
       <c r="K150" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:37Z</t>
+          <t>2026-09-24T23:17:56Z</t>
         </is>
       </c>
     </row>
@@ -7706,7 +7706,7 @@
       </c>
       <c r="K151" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:37Z</t>
+          <t>2026-09-24T23:17:56Z</t>
         </is>
       </c>
     </row>
@@ -7755,7 +7755,7 @@
       </c>
       <c r="K152" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:37Z</t>
+          <t>2026-09-24T23:17:56Z</t>
         </is>
       </c>
     </row>
@@ -7804,7 +7804,7 @@
       </c>
       <c r="K153" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:37Z</t>
+          <t>2026-09-24T23:17:56Z</t>
         </is>
       </c>
     </row>
@@ -7853,7 +7853,7 @@
       </c>
       <c r="K154" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:37Z</t>
+          <t>2026-09-24T23:17:56Z</t>
         </is>
       </c>
     </row>
@@ -7902,7 +7902,7 @@
       </c>
       <c r="K155" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:37Z</t>
+          <t>2026-09-24T23:17:56Z</t>
         </is>
       </c>
     </row>
@@ -7951,7 +7951,7 @@
       </c>
       <c r="K156" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:37Z</t>
+          <t>2026-09-24T23:17:56Z</t>
         </is>
       </c>
     </row>
@@ -8000,7 +8000,7 @@
       </c>
       <c r="K157" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:37Z</t>
+          <t>2026-09-24T23:17:56Z</t>
         </is>
       </c>
     </row>
@@ -8049,7 +8049,7 @@
       </c>
       <c r="K158" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:37Z</t>
+          <t>2026-09-24T23:17:56Z</t>
         </is>
       </c>
     </row>
@@ -8098,7 +8098,7 @@
       </c>
       <c r="K159" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:37Z</t>
+          <t>2026-09-24T23:17:56Z</t>
         </is>
       </c>
     </row>
@@ -8147,7 +8147,7 @@
       </c>
       <c r="K160" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:37Z</t>
+          <t>2026-09-24T23:17:56Z</t>
         </is>
       </c>
     </row>
@@ -8196,7 +8196,7 @@
       </c>
       <c r="K161" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:37Z</t>
+          <t>2026-09-24T23:17:56Z</t>
         </is>
       </c>
     </row>
@@ -8245,7 +8245,7 @@
       </c>
       <c r="K162" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:37Z</t>
+          <t>2026-09-24T23:17:56Z</t>
         </is>
       </c>
     </row>
@@ -8294,7 +8294,7 @@
       </c>
       <c r="K163" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:37Z</t>
+          <t>2026-09-24T23:17:56Z</t>
         </is>
       </c>
     </row>
@@ -8343,7 +8343,7 @@
       </c>
       <c r="K164" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:37Z</t>
+          <t>2026-09-24T23:17:56Z</t>
         </is>
       </c>
     </row>
@@ -8392,7 +8392,7 @@
       </c>
       <c r="K165" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:37Z</t>
+          <t>2026-09-24T23:17:56Z</t>
         </is>
       </c>
     </row>
@@ -8441,7 +8441,7 @@
       </c>
       <c r="K166" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:37Z</t>
+          <t>2026-09-24T23:17:56Z</t>
         </is>
       </c>
     </row>
@@ -8490,7 +8490,7 @@
       </c>
       <c r="K167" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:37Z</t>
+          <t>2026-09-24T23:17:56Z</t>
         </is>
       </c>
     </row>
@@ -8539,7 +8539,7 @@
       </c>
       <c r="K168" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:37Z</t>
+          <t>2026-09-24T23:17:56Z</t>
         </is>
       </c>
     </row>
@@ -8588,7 +8588,7 @@
       </c>
       <c r="K169" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:37Z</t>
+          <t>2026-09-24T23:17:56Z</t>
         </is>
       </c>
     </row>
@@ -8637,7 +8637,7 @@
       </c>
       <c r="K170" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:37Z</t>
+          <t>2026-09-24T23:17:56Z</t>
         </is>
       </c>
     </row>
@@ -8686,7 +8686,7 @@
       </c>
       <c r="K171" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:37Z</t>
+          <t>2026-09-24T23:17:56Z</t>
         </is>
       </c>
     </row>
@@ -8735,7 +8735,7 @@
       </c>
       <c r="K172" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:37Z</t>
+          <t>2026-09-24T23:17:56Z</t>
         </is>
       </c>
     </row>
@@ -8784,7 +8784,7 @@
       </c>
       <c r="K173" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:37Z</t>
+          <t>2026-09-24T23:17:56Z</t>
         </is>
       </c>
     </row>
@@ -8833,7 +8833,7 @@
       </c>
       <c r="K174" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:37Z</t>
+          <t>2026-09-24T23:17:56Z</t>
         </is>
       </c>
     </row>
@@ -8882,7 +8882,7 @@
       </c>
       <c r="K175" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:37Z</t>
+          <t>2026-09-24T23:17:56Z</t>
         </is>
       </c>
     </row>
@@ -8931,7 +8931,7 @@
       </c>
       <c r="K176" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:37Z</t>
+          <t>2026-09-24T23:17:56Z</t>
         </is>
       </c>
     </row>
@@ -8980,7 +8980,7 @@
       </c>
       <c r="K177" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:37Z</t>
+          <t>2026-09-24T23:17:56Z</t>
         </is>
       </c>
     </row>
@@ -9029,7 +9029,7 @@
       </c>
       <c r="K178" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:37Z</t>
+          <t>2026-09-24T23:17:56Z</t>
         </is>
       </c>
     </row>
@@ -9078,7 +9078,7 @@
       </c>
       <c r="K179" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:37Z</t>
+          <t>2026-09-24T23:17:56Z</t>
         </is>
       </c>
     </row>
@@ -9127,7 +9127,7 @@
       </c>
       <c r="K180" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:37Z</t>
+          <t>2026-09-24T23:17:56Z</t>
         </is>
       </c>
     </row>
@@ -9176,7 +9176,7 @@
       </c>
       <c r="K181" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:37Z</t>
+          <t>2026-09-24T23:17:56Z</t>
         </is>
       </c>
     </row>
@@ -9225,7 +9225,7 @@
       </c>
       <c r="K182" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:37Z</t>
+          <t>2026-09-24T23:17:56Z</t>
         </is>
       </c>
     </row>
@@ -9274,7 +9274,7 @@
       </c>
       <c r="K183" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:37Z</t>
+          <t>2026-09-24T23:17:56Z</t>
         </is>
       </c>
     </row>
@@ -9323,7 +9323,7 @@
       </c>
       <c r="K184" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:37Z</t>
+          <t>2026-09-24T23:17:56Z</t>
         </is>
       </c>
     </row>
@@ -9372,7 +9372,7 @@
       </c>
       <c r="K185" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:37Z</t>
+          <t>2026-09-24T23:17:56Z</t>
         </is>
       </c>
     </row>
@@ -9421,7 +9421,7 @@
       </c>
       <c r="K186" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:37Z</t>
+          <t>2026-09-24T23:17:56Z</t>
         </is>
       </c>
     </row>
@@ -9470,7 +9470,7 @@
       </c>
       <c r="K187" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:37Z</t>
+          <t>2026-09-24T23:17:56Z</t>
         </is>
       </c>
     </row>
@@ -9519,7 +9519,7 @@
       </c>
       <c r="K188" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:37Z</t>
+          <t>2026-09-24T23:17:56Z</t>
         </is>
       </c>
     </row>
@@ -9568,7 +9568,7 @@
       </c>
       <c r="K189" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:37Z</t>
+          <t>2026-09-24T23:17:56Z</t>
         </is>
       </c>
     </row>
@@ -9617,7 +9617,7 @@
       </c>
       <c r="K190" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:37Z</t>
+          <t>2026-09-24T23:17:56Z</t>
         </is>
       </c>
     </row>
@@ -9666,7 +9666,7 @@
       </c>
       <c r="K191" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:37Z</t>
+          <t>2026-09-24T23:17:56Z</t>
         </is>
       </c>
     </row>
@@ -9715,7 +9715,7 @@
       </c>
       <c r="K192" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:37Z</t>
+          <t>2026-09-24T23:17:56Z</t>
         </is>
       </c>
     </row>
@@ -9764,7 +9764,7 @@
       </c>
       <c r="K193" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:37Z</t>
+          <t>2026-09-24T23:17:56Z</t>
         </is>
       </c>
     </row>
@@ -9813,7 +9813,7 @@
       </c>
       <c r="K194" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:37Z</t>
+          <t>2026-09-24T23:17:56Z</t>
         </is>
       </c>
     </row>
@@ -9862,7 +9862,7 @@
       </c>
       <c r="K195" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:37Z</t>
+          <t>2026-09-24T23:17:56Z</t>
         </is>
       </c>
     </row>
@@ -9911,7 +9911,7 @@
       </c>
       <c r="K196" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:37Z</t>
+          <t>2026-09-24T23:17:56Z</t>
         </is>
       </c>
     </row>
@@ -9960,7 +9960,7 @@
       </c>
       <c r="K197" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:37Z</t>
+          <t>2026-09-24T23:17:56Z</t>
         </is>
       </c>
     </row>
@@ -10009,7 +10009,7 @@
       </c>
       <c r="K198" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:37Z</t>
+          <t>2026-09-24T23:17:56Z</t>
         </is>
       </c>
     </row>
@@ -10058,7 +10058,7 @@
       </c>
       <c r="K199" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:37Z</t>
+          <t>2026-09-24T23:17:56Z</t>
         </is>
       </c>
     </row>
@@ -10107,7 +10107,7 @@
       </c>
       <c r="K200" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:37Z</t>
+          <t>2026-09-24T23:17:56Z</t>
         </is>
       </c>
     </row>
@@ -10156,7 +10156,7 @@
       </c>
       <c r="K201" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:37Z</t>
+          <t>2026-09-24T23:17:56Z</t>
         </is>
       </c>
     </row>
@@ -10205,7 +10205,7 @@
       </c>
       <c r="K202" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:37Z</t>
+          <t>2026-09-24T23:17:56Z</t>
         </is>
       </c>
     </row>
@@ -10254,7 +10254,7 @@
       </c>
       <c r="K203" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:37Z</t>
+          <t>2026-09-24T23:17:56Z</t>
         </is>
       </c>
     </row>
@@ -10303,7 +10303,7 @@
       </c>
       <c r="K204" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:37Z</t>
+          <t>2026-09-24T23:17:56Z</t>
         </is>
       </c>
     </row>
@@ -10352,7 +10352,7 @@
       </c>
       <c r="K205" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:37Z</t>
+          <t>2026-09-24T23:17:56Z</t>
         </is>
       </c>
     </row>
@@ -10401,7 +10401,7 @@
       </c>
       <c r="K206" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:37Z</t>
+          <t>2026-09-24T23:17:56Z</t>
         </is>
       </c>
     </row>
@@ -10450,7 +10450,7 @@
       </c>
       <c r="K207" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:37Z</t>
+          <t>2026-09-24T23:17:56Z</t>
         </is>
       </c>
     </row>
@@ -10499,7 +10499,7 @@
       </c>
       <c r="K208" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:37Z</t>
+          <t>2026-09-24T23:17:56Z</t>
         </is>
       </c>
     </row>
@@ -10548,7 +10548,7 @@
       </c>
       <c r="K209" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:37Z</t>
+          <t>2026-09-24T23:17:56Z</t>
         </is>
       </c>
     </row>
@@ -10597,7 +10597,7 @@
       </c>
       <c r="K210" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:37Z</t>
+          <t>2026-09-24T23:17:56Z</t>
         </is>
       </c>
     </row>
@@ -10646,7 +10646,7 @@
       </c>
       <c r="K211" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:37Z</t>
+          <t>2026-09-24T23:17:56Z</t>
         </is>
       </c>
     </row>
@@ -10695,7 +10695,7 @@
       </c>
       <c r="K212" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:37Z</t>
+          <t>2026-09-24T23:17:56Z</t>
         </is>
       </c>
     </row>
@@ -10744,7 +10744,7 @@
       </c>
       <c r="K213" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:37Z</t>
+          <t>2026-09-24T23:17:56Z</t>
         </is>
       </c>
     </row>
@@ -10793,7 +10793,7 @@
       </c>
       <c r="K214" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:37Z</t>
+          <t>2026-09-24T23:17:56Z</t>
         </is>
       </c>
     </row>
@@ -10842,7 +10842,7 @@
       </c>
       <c r="K215" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:37Z</t>
+          <t>2026-09-24T23:17:56Z</t>
         </is>
       </c>
     </row>
@@ -10891,7 +10891,7 @@
       </c>
       <c r="K216" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:37Z</t>
+          <t>2026-09-24T23:17:56Z</t>
         </is>
       </c>
     </row>
@@ -10940,7 +10940,7 @@
       </c>
       <c r="K217" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:37Z</t>
+          <t>2026-09-24T23:17:56Z</t>
         </is>
       </c>
     </row>
@@ -10989,7 +10989,7 @@
       </c>
       <c r="K218" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:37Z</t>
+          <t>2026-09-24T23:17:56Z</t>
         </is>
       </c>
     </row>
@@ -11038,7 +11038,7 @@
       </c>
       <c r="K219" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:37Z</t>
+          <t>2026-09-24T23:17:56Z</t>
         </is>
       </c>
     </row>
@@ -11087,7 +11087,7 @@
       </c>
       <c r="K220" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:37Z</t>
+          <t>2026-09-24T23:17:56Z</t>
         </is>
       </c>
     </row>
@@ -11136,7 +11136,7 @@
       </c>
       <c r="K221" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:37Z</t>
+          <t>2026-09-24T23:17:56Z</t>
         </is>
       </c>
     </row>
@@ -11185,7 +11185,7 @@
       </c>
       <c r="K222" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:37Z</t>
+          <t>2026-09-24T23:17:56Z</t>
         </is>
       </c>
     </row>
@@ -11234,7 +11234,7 @@
       </c>
       <c r="K223" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:37Z</t>
+          <t>2026-09-24T23:17:56Z</t>
         </is>
       </c>
     </row>
@@ -11283,7 +11283,7 @@
       </c>
       <c r="K224" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:37Z</t>
+          <t>2026-09-24T23:17:56Z</t>
         </is>
       </c>
     </row>
@@ -11332,7 +11332,7 @@
       </c>
       <c r="K225" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:37Z</t>
+          <t>2026-09-24T23:17:56Z</t>
         </is>
       </c>
     </row>
@@ -11381,7 +11381,7 @@
       </c>
       <c r="K226" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:37Z</t>
+          <t>2026-09-24T23:17:56Z</t>
         </is>
       </c>
     </row>
@@ -11430,7 +11430,7 @@
       </c>
       <c r="K227" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:37Z</t>
+          <t>2026-09-24T23:17:56Z</t>
         </is>
       </c>
     </row>
@@ -11479,7 +11479,7 @@
       </c>
       <c r="K228" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:37Z</t>
+          <t>2026-09-24T23:17:56Z</t>
         </is>
       </c>
     </row>
@@ -11528,7 +11528,7 @@
       </c>
       <c r="K229" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:37Z</t>
+          <t>2026-09-24T23:17:56Z</t>
         </is>
       </c>
     </row>
@@ -11577,7 +11577,7 @@
       </c>
       <c r="K230" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:37Z</t>
+          <t>2026-09-24T23:17:56Z</t>
         </is>
       </c>
     </row>
@@ -11626,7 +11626,7 @@
       </c>
       <c r="K231" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:37Z</t>
+          <t>2026-09-24T23:17:56Z</t>
         </is>
       </c>
     </row>
@@ -11758,7 +11758,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:37Z</t>
+          <t>2026-09-24T23:17:56Z</t>
         </is>
       </c>
     </row>
@@ -11804,7 +11804,7 @@
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>{"date": "2026-08-01", "year": 2026, "month": 8, "month_name": "Agosto", "index_value": 637409769724325.1, "monthly_variation_pct": 8.9, "unit": "Índice base diciembre 2007=100 y variación mensual %", "frequency": "monthly", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/precios_consumidor/4_5_7_2.xls", "fetched_at": "2026-09-23T23:02:37Z"}</t>
+          <t>{"date": "2026-08-01", "year": 2026, "month": 8, "month_name": "Agosto", "index_value": 637409769724325.1, "monthly_variation_pct": 8.9, "unit": "Índice base diciembre 2007=100 y variación mensual %", "frequency": "monthly", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/precios_consumidor/4_5_7_2.xls", "fetched_at": "2026-09-24T23:17:56Z"}</t>
         </is>
       </c>
     </row>

--- a/assets/data/bcv/excel/ove_bcv_inpc_nacional_mensual.xlsx
+++ b/assets/data/bcv/excel/ove_bcv_inpc_nacional_mensual.xlsx
@@ -650,7 +650,7 @@
       </c>
       <c r="K7" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:56Z</t>
+          <t>2026-09-25T23:23:38Z</t>
         </is>
       </c>
     </row>
@@ -699,7 +699,7 @@
       </c>
       <c r="K8" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:56Z</t>
+          <t>2026-09-25T23:23:38Z</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="K9" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:56Z</t>
+          <t>2026-09-25T23:23:38Z</t>
         </is>
       </c>
     </row>
@@ -797,7 +797,7 @@
       </c>
       <c r="K10" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:56Z</t>
+          <t>2026-09-25T23:23:38Z</t>
         </is>
       </c>
     </row>
@@ -846,7 +846,7 @@
       </c>
       <c r="K11" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:56Z</t>
+          <t>2026-09-25T23:23:38Z</t>
         </is>
       </c>
     </row>
@@ -895,7 +895,7 @@
       </c>
       <c r="K12" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:56Z</t>
+          <t>2026-09-25T23:23:38Z</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="K13" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:56Z</t>
+          <t>2026-09-25T23:23:38Z</t>
         </is>
       </c>
     </row>
@@ -993,7 +993,7 @@
       </c>
       <c r="K14" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:56Z</t>
+          <t>2026-09-25T23:23:38Z</t>
         </is>
       </c>
     </row>
@@ -1042,7 +1042,7 @@
       </c>
       <c r="K15" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:56Z</t>
+          <t>2026-09-25T23:23:38Z</t>
         </is>
       </c>
     </row>
@@ -1091,7 +1091,7 @@
       </c>
       <c r="K16" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:56Z</t>
+          <t>2026-09-25T23:23:38Z</t>
         </is>
       </c>
     </row>
@@ -1140,7 +1140,7 @@
       </c>
       <c r="K17" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:56Z</t>
+          <t>2026-09-25T23:23:38Z</t>
         </is>
       </c>
     </row>
@@ -1189,7 +1189,7 @@
       </c>
       <c r="K18" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:56Z</t>
+          <t>2026-09-25T23:23:38Z</t>
         </is>
       </c>
     </row>
@@ -1238,7 +1238,7 @@
       </c>
       <c r="K19" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:56Z</t>
+          <t>2026-09-25T23:23:38Z</t>
         </is>
       </c>
     </row>
@@ -1287,7 +1287,7 @@
       </c>
       <c r="K20" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:56Z</t>
+          <t>2026-09-25T23:23:38Z</t>
         </is>
       </c>
     </row>
@@ -1336,7 +1336,7 @@
       </c>
       <c r="K21" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:56Z</t>
+          <t>2026-09-25T23:23:38Z</t>
         </is>
       </c>
     </row>
@@ -1385,7 +1385,7 @@
       </c>
       <c r="K22" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:56Z</t>
+          <t>2026-09-25T23:23:38Z</t>
         </is>
       </c>
     </row>
@@ -1434,7 +1434,7 @@
       </c>
       <c r="K23" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:56Z</t>
+          <t>2026-09-25T23:23:38Z</t>
         </is>
       </c>
     </row>
@@ -1483,7 +1483,7 @@
       </c>
       <c r="K24" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:56Z</t>
+          <t>2026-09-25T23:23:38Z</t>
         </is>
       </c>
     </row>
@@ -1532,7 +1532,7 @@
       </c>
       <c r="K25" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:56Z</t>
+          <t>2026-09-25T23:23:38Z</t>
         </is>
       </c>
     </row>
@@ -1581,7 +1581,7 @@
       </c>
       <c r="K26" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:56Z</t>
+          <t>2026-09-25T23:23:38Z</t>
         </is>
       </c>
     </row>
@@ -1630,7 +1630,7 @@
       </c>
       <c r="K27" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:56Z</t>
+          <t>2026-09-25T23:23:38Z</t>
         </is>
       </c>
     </row>
@@ -1679,7 +1679,7 @@
       </c>
       <c r="K28" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:56Z</t>
+          <t>2026-09-25T23:23:38Z</t>
         </is>
       </c>
     </row>
@@ -1728,7 +1728,7 @@
       </c>
       <c r="K29" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:56Z</t>
+          <t>2026-09-25T23:23:38Z</t>
         </is>
       </c>
     </row>
@@ -1777,7 +1777,7 @@
       </c>
       <c r="K30" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:56Z</t>
+          <t>2026-09-25T23:23:38Z</t>
         </is>
       </c>
     </row>
@@ -1826,7 +1826,7 @@
       </c>
       <c r="K31" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:56Z</t>
+          <t>2026-09-25T23:23:38Z</t>
         </is>
       </c>
     </row>
@@ -1875,7 +1875,7 @@
       </c>
       <c r="K32" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:56Z</t>
+          <t>2026-09-25T23:23:38Z</t>
         </is>
       </c>
     </row>
@@ -1924,7 +1924,7 @@
       </c>
       <c r="K33" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:56Z</t>
+          <t>2026-09-25T23:23:38Z</t>
         </is>
       </c>
     </row>
@@ -1973,7 +1973,7 @@
       </c>
       <c r="K34" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:56Z</t>
+          <t>2026-09-25T23:23:38Z</t>
         </is>
       </c>
     </row>
@@ -2022,7 +2022,7 @@
       </c>
       <c r="K35" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:56Z</t>
+          <t>2026-09-25T23:23:38Z</t>
         </is>
       </c>
     </row>
@@ -2071,7 +2071,7 @@
       </c>
       <c r="K36" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:56Z</t>
+          <t>2026-09-25T23:23:38Z</t>
         </is>
       </c>
     </row>
@@ -2120,7 +2120,7 @@
       </c>
       <c r="K37" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:56Z</t>
+          <t>2026-09-25T23:23:38Z</t>
         </is>
       </c>
     </row>
@@ -2169,7 +2169,7 @@
       </c>
       <c r="K38" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:56Z</t>
+          <t>2026-09-25T23:23:38Z</t>
         </is>
       </c>
     </row>
@@ -2218,7 +2218,7 @@
       </c>
       <c r="K39" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:56Z</t>
+          <t>2026-09-25T23:23:38Z</t>
         </is>
       </c>
     </row>
@@ -2267,7 +2267,7 @@
       </c>
       <c r="K40" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:56Z</t>
+          <t>2026-09-25T23:23:38Z</t>
         </is>
       </c>
     </row>
@@ -2316,7 +2316,7 @@
       </c>
       <c r="K41" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:56Z</t>
+          <t>2026-09-25T23:23:38Z</t>
         </is>
       </c>
     </row>
@@ -2365,7 +2365,7 @@
       </c>
       <c r="K42" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:56Z</t>
+          <t>2026-09-25T23:23:38Z</t>
         </is>
       </c>
     </row>
@@ -2414,7 +2414,7 @@
       </c>
       <c r="K43" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:56Z</t>
+          <t>2026-09-25T23:23:38Z</t>
         </is>
       </c>
     </row>
@@ -2463,7 +2463,7 @@
       </c>
       <c r="K44" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:56Z</t>
+          <t>2026-09-25T23:23:38Z</t>
         </is>
       </c>
     </row>
@@ -2512,7 +2512,7 @@
       </c>
       <c r="K45" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:56Z</t>
+          <t>2026-09-25T23:23:38Z</t>
         </is>
       </c>
     </row>
@@ -2561,7 +2561,7 @@
       </c>
       <c r="K46" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:56Z</t>
+          <t>2026-09-25T23:23:38Z</t>
         </is>
       </c>
     </row>
@@ -2610,7 +2610,7 @@
       </c>
       <c r="K47" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:56Z</t>
+          <t>2026-09-25T23:23:38Z</t>
         </is>
       </c>
     </row>
@@ -2659,7 +2659,7 @@
       </c>
       <c r="K48" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:56Z</t>
+          <t>2026-09-25T23:23:38Z</t>
         </is>
       </c>
     </row>
@@ -2708,7 +2708,7 @@
       </c>
       <c r="K49" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:56Z</t>
+          <t>2026-09-25T23:23:38Z</t>
         </is>
       </c>
     </row>
@@ -2757,7 +2757,7 @@
       </c>
       <c r="K50" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:56Z</t>
+          <t>2026-09-25T23:23:38Z</t>
         </is>
       </c>
     </row>
@@ -2806,7 +2806,7 @@
       </c>
       <c r="K51" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:56Z</t>
+          <t>2026-09-25T23:23:38Z</t>
         </is>
       </c>
     </row>
@@ -2855,7 +2855,7 @@
       </c>
       <c r="K52" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:56Z</t>
+          <t>2026-09-25T23:23:38Z</t>
         </is>
       </c>
     </row>
@@ -2904,7 +2904,7 @@
       </c>
       <c r="K53" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:56Z</t>
+          <t>2026-09-25T23:23:38Z</t>
         </is>
       </c>
     </row>
@@ -2953,7 +2953,7 @@
       </c>
       <c r="K54" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:56Z</t>
+          <t>2026-09-25T23:23:38Z</t>
         </is>
       </c>
     </row>
@@ -3002,7 +3002,7 @@
       </c>
       <c r="K55" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:56Z</t>
+          <t>2026-09-25T23:23:38Z</t>
         </is>
       </c>
     </row>
@@ -3051,7 +3051,7 @@
       </c>
       <c r="K56" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:56Z</t>
+          <t>2026-09-25T23:23:38Z</t>
         </is>
       </c>
     </row>
@@ -3100,7 +3100,7 @@
       </c>
       <c r="K57" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:56Z</t>
+          <t>2026-09-25T23:23:38Z</t>
         </is>
       </c>
     </row>
@@ -3149,7 +3149,7 @@
       </c>
       <c r="K58" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:56Z</t>
+          <t>2026-09-25T23:23:38Z</t>
         </is>
       </c>
     </row>
@@ -3198,7 +3198,7 @@
       </c>
       <c r="K59" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:56Z</t>
+          <t>2026-09-25T23:23:38Z</t>
         </is>
       </c>
     </row>
@@ -3247,7 +3247,7 @@
       </c>
       <c r="K60" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:56Z</t>
+          <t>2026-09-25T23:23:38Z</t>
         </is>
       </c>
     </row>
@@ -3296,7 +3296,7 @@
       </c>
       <c r="K61" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:56Z</t>
+          <t>2026-09-25T23:23:38Z</t>
         </is>
       </c>
     </row>
@@ -3345,7 +3345,7 @@
       </c>
       <c r="K62" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:56Z</t>
+          <t>2026-09-25T23:23:38Z</t>
         </is>
       </c>
     </row>
@@ -3394,7 +3394,7 @@
       </c>
       <c r="K63" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:56Z</t>
+          <t>2026-09-25T23:23:38Z</t>
         </is>
       </c>
     </row>
@@ -3443,7 +3443,7 @@
       </c>
       <c r="K64" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:56Z</t>
+          <t>2026-09-25T23:23:38Z</t>
         </is>
       </c>
     </row>
@@ -3492,7 +3492,7 @@
       </c>
       <c r="K65" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:56Z</t>
+          <t>2026-09-25T23:23:38Z</t>
         </is>
       </c>
     </row>
@@ -3541,7 +3541,7 @@
       </c>
       <c r="K66" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:56Z</t>
+          <t>2026-09-25T23:23:38Z</t>
         </is>
       </c>
     </row>
@@ -3590,7 +3590,7 @@
       </c>
       <c r="K67" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:56Z</t>
+          <t>2026-09-25T23:23:38Z</t>
         </is>
       </c>
     </row>
@@ -3639,7 +3639,7 @@
       </c>
       <c r="K68" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:56Z</t>
+          <t>2026-09-25T23:23:38Z</t>
         </is>
       </c>
     </row>
@@ -3688,7 +3688,7 @@
       </c>
       <c r="K69" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:56Z</t>
+          <t>2026-09-25T23:23:38Z</t>
         </is>
       </c>
     </row>
@@ -3737,7 +3737,7 @@
       </c>
       <c r="K70" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:56Z</t>
+          <t>2026-09-25T23:23:38Z</t>
         </is>
       </c>
     </row>
@@ -3786,7 +3786,7 @@
       </c>
       <c r="K71" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:56Z</t>
+          <t>2026-09-25T23:23:38Z</t>
         </is>
       </c>
     </row>
@@ -3835,7 +3835,7 @@
       </c>
       <c r="K72" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:56Z</t>
+          <t>2026-09-25T23:23:38Z</t>
         </is>
       </c>
     </row>
@@ -3884,7 +3884,7 @@
       </c>
       <c r="K73" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:56Z</t>
+          <t>2026-09-25T23:23:38Z</t>
         </is>
       </c>
     </row>
@@ -3933,7 +3933,7 @@
       </c>
       <c r="K74" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:56Z</t>
+          <t>2026-09-25T23:23:38Z</t>
         </is>
       </c>
     </row>
@@ -3982,7 +3982,7 @@
       </c>
       <c r="K75" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:56Z</t>
+          <t>2026-09-25T23:23:38Z</t>
         </is>
       </c>
     </row>
@@ -4031,7 +4031,7 @@
       </c>
       <c r="K76" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:56Z</t>
+          <t>2026-09-25T23:23:38Z</t>
         </is>
       </c>
     </row>
@@ -4080,7 +4080,7 @@
       </c>
       <c r="K77" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:56Z</t>
+          <t>2026-09-25T23:23:38Z</t>
         </is>
       </c>
     </row>
@@ -4129,7 +4129,7 @@
       </c>
       <c r="K78" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:56Z</t>
+          <t>2026-09-25T23:23:38Z</t>
         </is>
       </c>
     </row>
@@ -4178,7 +4178,7 @@
       </c>
       <c r="K79" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:56Z</t>
+          <t>2026-09-25T23:23:38Z</t>
         </is>
       </c>
     </row>
@@ -4227,7 +4227,7 @@
       </c>
       <c r="K80" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:56Z</t>
+          <t>2026-09-25T23:23:38Z</t>
         </is>
       </c>
     </row>
@@ -4276,7 +4276,7 @@
       </c>
       <c r="K81" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:56Z</t>
+          <t>2026-09-25T23:23:38Z</t>
         </is>
       </c>
     </row>
@@ -4325,7 +4325,7 @@
       </c>
       <c r="K82" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:56Z</t>
+          <t>2026-09-25T23:23:38Z</t>
         </is>
       </c>
     </row>
@@ -4374,7 +4374,7 @@
       </c>
       <c r="K83" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:56Z</t>
+          <t>2026-09-25T23:23:38Z</t>
         </is>
       </c>
     </row>
@@ -4423,7 +4423,7 @@
       </c>
       <c r="K84" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:56Z</t>
+          <t>2026-09-25T23:23:38Z</t>
         </is>
       </c>
     </row>
@@ -4472,7 +4472,7 @@
       </c>
       <c r="K85" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:56Z</t>
+          <t>2026-09-25T23:23:38Z</t>
         </is>
       </c>
     </row>
@@ -4521,7 +4521,7 @@
       </c>
       <c r="K86" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:56Z</t>
+          <t>2026-09-25T23:23:38Z</t>
         </is>
       </c>
     </row>
@@ -4570,7 +4570,7 @@
       </c>
       <c r="K87" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:56Z</t>
+          <t>2026-09-25T23:23:38Z</t>
         </is>
       </c>
     </row>
@@ -4619,7 +4619,7 @@
       </c>
       <c r="K88" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:56Z</t>
+          <t>2026-09-25T23:23:38Z</t>
         </is>
       </c>
     </row>
@@ -4668,7 +4668,7 @@
       </c>
       <c r="K89" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:56Z</t>
+          <t>2026-09-25T23:23:38Z</t>
         </is>
       </c>
     </row>
@@ -4717,7 +4717,7 @@
       </c>
       <c r="K90" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:56Z</t>
+          <t>2026-09-25T23:23:38Z</t>
         </is>
       </c>
     </row>
@@ -4766,7 +4766,7 @@
       </c>
       <c r="K91" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:56Z</t>
+          <t>2026-09-25T23:23:38Z</t>
         </is>
       </c>
     </row>
@@ -4815,7 +4815,7 @@
       </c>
       <c r="K92" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:56Z</t>
+          <t>2026-09-25T23:23:38Z</t>
         </is>
       </c>
     </row>
@@ -4864,7 +4864,7 @@
       </c>
       <c r="K93" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:56Z</t>
+          <t>2026-09-25T23:23:38Z</t>
         </is>
       </c>
     </row>
@@ -4913,7 +4913,7 @@
       </c>
       <c r="K94" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:56Z</t>
+          <t>2026-09-25T23:23:38Z</t>
         </is>
       </c>
     </row>
@@ -4962,7 +4962,7 @@
       </c>
       <c r="K95" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:56Z</t>
+          <t>2026-09-25T23:23:38Z</t>
         </is>
       </c>
     </row>
@@ -5011,7 +5011,7 @@
       </c>
       <c r="K96" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:56Z</t>
+          <t>2026-09-25T23:23:38Z</t>
         </is>
       </c>
     </row>
@@ -5060,7 +5060,7 @@
       </c>
       <c r="K97" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:56Z</t>
+          <t>2026-09-25T23:23:38Z</t>
         </is>
       </c>
     </row>
@@ -5109,7 +5109,7 @@
       </c>
       <c r="K98" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:56Z</t>
+          <t>2026-09-25T23:23:38Z</t>
         </is>
       </c>
     </row>
@@ -5158,7 +5158,7 @@
       </c>
       <c r="K99" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:56Z</t>
+          <t>2026-09-25T23:23:38Z</t>
         </is>
       </c>
     </row>
@@ -5207,7 +5207,7 @@
       </c>
       <c r="K100" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:56Z</t>
+          <t>2026-09-25T23:23:38Z</t>
         </is>
       </c>
     </row>
@@ -5256,7 +5256,7 @@
       </c>
       <c r="K101" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:56Z</t>
+          <t>2026-09-25T23:23:38Z</t>
         </is>
       </c>
     </row>
@@ -5305,7 +5305,7 @@
       </c>
       <c r="K102" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:56Z</t>
+          <t>2026-09-25T23:23:38Z</t>
         </is>
       </c>
     </row>
@@ -5354,7 +5354,7 @@
       </c>
       <c r="K103" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:56Z</t>
+          <t>2026-09-25T23:23:38Z</t>
         </is>
       </c>
     </row>
@@ -5403,7 +5403,7 @@
       </c>
       <c r="K104" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:56Z</t>
+          <t>2026-09-25T23:23:38Z</t>
         </is>
       </c>
     </row>
@@ -5452,7 +5452,7 @@
       </c>
       <c r="K105" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:56Z</t>
+          <t>2026-09-25T23:23:38Z</t>
         </is>
       </c>
     </row>
@@ -5501,7 +5501,7 @@
       </c>
       <c r="K106" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:56Z</t>
+          <t>2026-09-25T23:23:38Z</t>
         </is>
       </c>
     </row>
@@ -5550,7 +5550,7 @@
       </c>
       <c r="K107" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:56Z</t>
+          <t>2026-09-25T23:23:38Z</t>
         </is>
       </c>
     </row>
@@ -5599,7 +5599,7 @@
       </c>
       <c r="K108" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:56Z</t>
+          <t>2026-09-25T23:23:38Z</t>
         </is>
       </c>
     </row>
@@ -5648,7 +5648,7 @@
       </c>
       <c r="K109" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:56Z</t>
+          <t>2026-09-25T23:23:38Z</t>
         </is>
       </c>
     </row>
@@ -5697,7 +5697,7 @@
       </c>
       <c r="K110" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:56Z</t>
+          <t>2026-09-25T23:23:38Z</t>
         </is>
       </c>
     </row>
@@ -5746,7 +5746,7 @@
       </c>
       <c r="K111" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:56Z</t>
+          <t>2026-09-25T23:23:38Z</t>
         </is>
       </c>
     </row>
@@ -5795,7 +5795,7 @@
       </c>
       <c r="K112" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:56Z</t>
+          <t>2026-09-25T23:23:38Z</t>
         </is>
       </c>
     </row>
@@ -5844,7 +5844,7 @@
       </c>
       <c r="K113" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:56Z</t>
+          <t>2026-09-25T23:23:38Z</t>
         </is>
       </c>
     </row>
@@ -5893,7 +5893,7 @@
       </c>
       <c r="K114" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:56Z</t>
+          <t>2026-09-25T23:23:38Z</t>
         </is>
       </c>
     </row>
@@ -5942,7 +5942,7 @@
       </c>
       <c r="K115" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:56Z</t>
+          <t>2026-09-25T23:23:38Z</t>
         </is>
       </c>
     </row>
@@ -5991,7 +5991,7 @@
       </c>
       <c r="K116" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:56Z</t>
+          <t>2026-09-25T23:23:38Z</t>
         </is>
       </c>
     </row>
@@ -6040,7 +6040,7 @@
       </c>
       <c r="K117" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:56Z</t>
+          <t>2026-09-25T23:23:38Z</t>
         </is>
       </c>
     </row>
@@ -6089,7 +6089,7 @@
       </c>
       <c r="K118" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:56Z</t>
+          <t>2026-09-25T23:23:38Z</t>
         </is>
       </c>
     </row>
@@ -6138,7 +6138,7 @@
       </c>
       <c r="K119" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:56Z</t>
+          <t>2026-09-25T23:23:38Z</t>
         </is>
       </c>
     </row>
@@ -6187,7 +6187,7 @@
       </c>
       <c r="K120" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:56Z</t>
+          <t>2026-09-25T23:23:38Z</t>
         </is>
       </c>
     </row>
@@ -6236,7 +6236,7 @@
       </c>
       <c r="K121" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:56Z</t>
+          <t>2026-09-25T23:23:38Z</t>
         </is>
       </c>
     </row>
@@ -6285,7 +6285,7 @@
       </c>
       <c r="K122" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:56Z</t>
+          <t>2026-09-25T23:23:38Z</t>
         </is>
       </c>
     </row>
@@ -6334,7 +6334,7 @@
       </c>
       <c r="K123" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:56Z</t>
+          <t>2026-09-25T23:23:38Z</t>
         </is>
       </c>
     </row>
@@ -6383,7 +6383,7 @@
       </c>
       <c r="K124" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:56Z</t>
+          <t>2026-09-25T23:23:38Z</t>
         </is>
       </c>
     </row>
@@ -6432,7 +6432,7 @@
       </c>
       <c r="K125" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:56Z</t>
+          <t>2026-09-25T23:23:38Z</t>
         </is>
       </c>
     </row>
@@ -6481,7 +6481,7 @@
       </c>
       <c r="K126" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:56Z</t>
+          <t>2026-09-25T23:23:38Z</t>
         </is>
       </c>
     </row>
@@ -6530,7 +6530,7 @@
       </c>
       <c r="K127" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:56Z</t>
+          <t>2026-09-25T23:23:38Z</t>
         </is>
       </c>
     </row>
@@ -6579,7 +6579,7 @@
       </c>
       <c r="K128" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:56Z</t>
+          <t>2026-09-25T23:23:38Z</t>
         </is>
       </c>
     </row>
@@ -6628,7 +6628,7 @@
       </c>
       <c r="K129" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:56Z</t>
+          <t>2026-09-25T23:23:38Z</t>
         </is>
       </c>
     </row>
@@ -6677,7 +6677,7 @@
       </c>
       <c r="K130" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:56Z</t>
+          <t>2026-09-25T23:23:38Z</t>
         </is>
       </c>
     </row>
@@ -6726,7 +6726,7 @@
       </c>
       <c r="K131" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:56Z</t>
+          <t>2026-09-25T23:23:38Z</t>
         </is>
       </c>
     </row>
@@ -6775,7 +6775,7 @@
       </c>
       <c r="K132" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:56Z</t>
+          <t>2026-09-25T23:23:38Z</t>
         </is>
       </c>
     </row>
@@ -6824,7 +6824,7 @@
       </c>
       <c r="K133" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:56Z</t>
+          <t>2026-09-25T23:23:38Z</t>
         </is>
       </c>
     </row>
@@ -6873,7 +6873,7 @@
       </c>
       <c r="K134" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:56Z</t>
+          <t>2026-09-25T23:23:38Z</t>
         </is>
       </c>
     </row>
@@ -6922,7 +6922,7 @@
       </c>
       <c r="K135" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:56Z</t>
+          <t>2026-09-25T23:23:38Z</t>
         </is>
       </c>
     </row>
@@ -6971,7 +6971,7 @@
       </c>
       <c r="K136" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:56Z</t>
+          <t>2026-09-25T23:23:38Z</t>
         </is>
       </c>
     </row>
@@ -7020,7 +7020,7 @@
       </c>
       <c r="K137" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:56Z</t>
+          <t>2026-09-25T23:23:38Z</t>
         </is>
       </c>
     </row>
@@ -7069,7 +7069,7 @@
       </c>
       <c r="K138" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:56Z</t>
+          <t>2026-09-25T23:23:38Z</t>
         </is>
       </c>
     </row>
@@ -7118,7 +7118,7 @@
       </c>
       <c r="K139" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:56Z</t>
+          <t>2026-09-25T23:23:38Z</t>
         </is>
       </c>
     </row>
@@ -7167,7 +7167,7 @@
       </c>
       <c r="K140" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:56Z</t>
+          <t>2026-09-25T23:23:38Z</t>
         </is>
       </c>
     </row>
@@ -7216,7 +7216,7 @@
       </c>
       <c r="K141" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:56Z</t>
+          <t>2026-09-25T23:23:38Z</t>
         </is>
       </c>
     </row>
@@ -7265,7 +7265,7 @@
       </c>
       <c r="K142" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:56Z</t>
+          <t>2026-09-25T23:23:38Z</t>
         </is>
       </c>
     </row>
@@ -7314,7 +7314,7 @@
       </c>
       <c r="K143" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:56Z</t>
+          <t>2026-09-25T23:23:38Z</t>
         </is>
       </c>
     </row>
@@ -7363,7 +7363,7 @@
       </c>
       <c r="K144" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:56Z</t>
+          <t>2026-09-25T23:23:38Z</t>
         </is>
       </c>
     </row>
@@ -7412,7 +7412,7 @@
       </c>
       <c r="K145" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:56Z</t>
+          <t>2026-09-25T23:23:38Z</t>
         </is>
       </c>
     </row>
@@ -7461,7 +7461,7 @@
       </c>
       <c r="K146" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:56Z</t>
+          <t>2026-09-25T23:23:38Z</t>
         </is>
       </c>
     </row>
@@ -7510,7 +7510,7 @@
       </c>
       <c r="K147" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:56Z</t>
+          <t>2026-09-25T23:23:38Z</t>
         </is>
       </c>
     </row>
@@ -7559,7 +7559,7 @@
       </c>
       <c r="K148" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:56Z</t>
+          <t>2026-09-25T23:23:38Z</t>
         </is>
       </c>
     </row>
@@ -7608,7 +7608,7 @@
       </c>
       <c r="K149" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:56Z</t>
+          <t>2026-09-25T23:23:38Z</t>
         </is>
       </c>
     </row>
@@ -7657,7 +7657,7 @@
       </c>
       <c r="K150" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:56Z</t>
+          <t>2026-09-25T23:23:38Z</t>
         </is>
       </c>
     </row>
@@ -7706,7 +7706,7 @@
       </c>
       <c r="K151" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:56Z</t>
+          <t>2026-09-25T23:23:38Z</t>
         </is>
       </c>
     </row>
@@ -7755,7 +7755,7 @@
       </c>
       <c r="K152" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:56Z</t>
+          <t>2026-09-25T23:23:38Z</t>
         </is>
       </c>
     </row>
@@ -7804,7 +7804,7 @@
       </c>
       <c r="K153" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:56Z</t>
+          <t>2026-09-25T23:23:38Z</t>
         </is>
       </c>
     </row>
@@ -7853,7 +7853,7 @@
       </c>
       <c r="K154" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:56Z</t>
+          <t>2026-09-25T23:23:38Z</t>
         </is>
       </c>
     </row>
@@ -7902,7 +7902,7 @@
       </c>
       <c r="K155" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:56Z</t>
+          <t>2026-09-25T23:23:38Z</t>
         </is>
       </c>
     </row>
@@ -7951,7 +7951,7 @@
       </c>
       <c r="K156" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:56Z</t>
+          <t>2026-09-25T23:23:38Z</t>
         </is>
       </c>
     </row>
@@ -8000,7 +8000,7 @@
       </c>
       <c r="K157" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:56Z</t>
+          <t>2026-09-25T23:23:38Z</t>
         </is>
       </c>
     </row>
@@ -8049,7 +8049,7 @@
       </c>
       <c r="K158" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:56Z</t>
+          <t>2026-09-25T23:23:38Z</t>
         </is>
       </c>
     </row>
@@ -8098,7 +8098,7 @@
       </c>
       <c r="K159" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:56Z</t>
+          <t>2026-09-25T23:23:38Z</t>
         </is>
       </c>
     </row>
@@ -8147,7 +8147,7 @@
       </c>
       <c r="K160" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:56Z</t>
+          <t>2026-09-25T23:23:38Z</t>
         </is>
       </c>
     </row>
@@ -8196,7 +8196,7 @@
       </c>
       <c r="K161" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:56Z</t>
+          <t>2026-09-25T23:23:38Z</t>
         </is>
       </c>
     </row>
@@ -8245,7 +8245,7 @@
       </c>
       <c r="K162" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:56Z</t>
+          <t>2026-09-25T23:23:38Z</t>
         </is>
       </c>
     </row>
@@ -8294,7 +8294,7 @@
       </c>
       <c r="K163" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:56Z</t>
+          <t>2026-09-25T23:23:38Z</t>
         </is>
       </c>
     </row>
@@ -8343,7 +8343,7 @@
       </c>
       <c r="K164" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:56Z</t>
+          <t>2026-09-25T23:23:38Z</t>
         </is>
       </c>
     </row>
@@ -8392,7 +8392,7 @@
       </c>
       <c r="K165" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:56Z</t>
+          <t>2026-09-25T23:23:38Z</t>
         </is>
       </c>
     </row>
@@ -8441,7 +8441,7 @@
       </c>
       <c r="K166" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:56Z</t>
+          <t>2026-09-25T23:23:38Z</t>
         </is>
       </c>
     </row>
@@ -8490,7 +8490,7 @@
       </c>
       <c r="K167" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:56Z</t>
+          <t>2026-09-25T23:23:38Z</t>
         </is>
       </c>
     </row>
@@ -8539,7 +8539,7 @@
       </c>
       <c r="K168" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:56Z</t>
+          <t>2026-09-25T23:23:38Z</t>
         </is>
       </c>
     </row>
@@ -8588,7 +8588,7 @@
       </c>
       <c r="K169" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:56Z</t>
+          <t>2026-09-25T23:23:38Z</t>
         </is>
       </c>
     </row>
@@ -8637,7 +8637,7 @@
       </c>
       <c r="K170" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:56Z</t>
+          <t>2026-09-25T23:23:38Z</t>
         </is>
       </c>
     </row>
@@ -8686,7 +8686,7 @@
       </c>
       <c r="K171" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:56Z</t>
+          <t>2026-09-25T23:23:38Z</t>
         </is>
       </c>
     </row>
@@ -8735,7 +8735,7 @@
       </c>
       <c r="K172" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:56Z</t>
+          <t>2026-09-25T23:23:38Z</t>
         </is>
       </c>
     </row>
@@ -8784,7 +8784,7 @@
       </c>
       <c r="K173" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:56Z</t>
+          <t>2026-09-25T23:23:38Z</t>
         </is>
       </c>
     </row>
@@ -8833,7 +8833,7 @@
       </c>
       <c r="K174" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:56Z</t>
+          <t>2026-09-25T23:23:38Z</t>
         </is>
       </c>
     </row>
@@ -8882,7 +8882,7 @@
       </c>
       <c r="K175" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:56Z</t>
+          <t>2026-09-25T23:23:38Z</t>
         </is>
       </c>
     </row>
@@ -8931,7 +8931,7 @@
       </c>
       <c r="K176" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:56Z</t>
+          <t>2026-09-25T23:23:38Z</t>
         </is>
       </c>
     </row>
@@ -8980,7 +8980,7 @@
       </c>
       <c r="K177" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:56Z</t>
+          <t>2026-09-25T23:23:38Z</t>
         </is>
       </c>
     </row>
@@ -9029,7 +9029,7 @@
       </c>
       <c r="K178" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:56Z</t>
+          <t>2026-09-25T23:23:38Z</t>
         </is>
       </c>
     </row>
@@ -9078,7 +9078,7 @@
       </c>
       <c r="K179" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:56Z</t>
+          <t>2026-09-25T23:23:38Z</t>
         </is>
       </c>
     </row>
@@ -9127,7 +9127,7 @@
       </c>
       <c r="K180" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:56Z</t>
+          <t>2026-09-25T23:23:38Z</t>
         </is>
       </c>
     </row>
@@ -9176,7 +9176,7 @@
       </c>
       <c r="K181" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:56Z</t>
+          <t>2026-09-25T23:23:38Z</t>
         </is>
       </c>
     </row>
@@ -9225,7 +9225,7 @@
       </c>
       <c r="K182" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:56Z</t>
+          <t>2026-09-25T23:23:38Z</t>
         </is>
       </c>
     </row>
@@ -9274,7 +9274,7 @@
       </c>
       <c r="K183" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:56Z</t>
+          <t>2026-09-25T23:23:38Z</t>
         </is>
       </c>
     </row>
@@ -9323,7 +9323,7 @@
       </c>
       <c r="K184" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:56Z</t>
+          <t>2026-09-25T23:23:38Z</t>
         </is>
       </c>
     </row>
@@ -9372,7 +9372,7 @@
       </c>
       <c r="K185" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:56Z</t>
+          <t>2026-09-25T23:23:38Z</t>
         </is>
       </c>
     </row>
@@ -9421,7 +9421,7 @@
       </c>
       <c r="K186" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:56Z</t>
+          <t>2026-09-25T23:23:38Z</t>
         </is>
       </c>
     </row>
@@ -9470,7 +9470,7 @@
       </c>
       <c r="K187" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:56Z</t>
+          <t>2026-09-25T23:23:38Z</t>
         </is>
       </c>
     </row>
@@ -9519,7 +9519,7 @@
       </c>
       <c r="K188" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:56Z</t>
+          <t>2026-09-25T23:23:38Z</t>
         </is>
       </c>
     </row>
@@ -9568,7 +9568,7 @@
       </c>
       <c r="K189" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:56Z</t>
+          <t>2026-09-25T23:23:38Z</t>
         </is>
       </c>
     </row>
@@ -9617,7 +9617,7 @@
       </c>
       <c r="K190" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:56Z</t>
+          <t>2026-09-25T23:23:38Z</t>
         </is>
       </c>
     </row>
@@ -9666,7 +9666,7 @@
       </c>
       <c r="K191" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:56Z</t>
+          <t>2026-09-25T23:23:38Z</t>
         </is>
       </c>
     </row>
@@ -9715,7 +9715,7 @@
       </c>
       <c r="K192" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:56Z</t>
+          <t>2026-09-25T23:23:38Z</t>
         </is>
       </c>
     </row>
@@ -9764,7 +9764,7 @@
       </c>
       <c r="K193" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:56Z</t>
+          <t>2026-09-25T23:23:38Z</t>
         </is>
       </c>
     </row>
@@ -9813,7 +9813,7 @@
       </c>
       <c r="K194" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:56Z</t>
+          <t>2026-09-25T23:23:38Z</t>
         </is>
       </c>
     </row>
@@ -9862,7 +9862,7 @@
       </c>
       <c r="K195" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:56Z</t>
+          <t>2026-09-25T23:23:38Z</t>
         </is>
       </c>
     </row>
@@ -9911,7 +9911,7 @@
       </c>
       <c r="K196" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:56Z</t>
+          <t>2026-09-25T23:23:38Z</t>
         </is>
       </c>
     </row>
@@ -9960,7 +9960,7 @@
       </c>
       <c r="K197" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:56Z</t>
+          <t>2026-09-25T23:23:38Z</t>
         </is>
       </c>
     </row>
@@ -10009,7 +10009,7 @@
       </c>
       <c r="K198" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:56Z</t>
+          <t>2026-09-25T23:23:38Z</t>
         </is>
       </c>
     </row>
@@ -10058,7 +10058,7 @@
       </c>
       <c r="K199" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:56Z</t>
+          <t>2026-09-25T23:23:38Z</t>
         </is>
       </c>
     </row>
@@ -10107,7 +10107,7 @@
       </c>
       <c r="K200" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:56Z</t>
+          <t>2026-09-25T23:23:38Z</t>
         </is>
       </c>
     </row>
@@ -10156,7 +10156,7 @@
       </c>
       <c r="K201" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:56Z</t>
+          <t>2026-09-25T23:23:38Z</t>
         </is>
       </c>
     </row>
@@ -10205,7 +10205,7 @@
       </c>
       <c r="K202" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:56Z</t>
+          <t>2026-09-25T23:23:38Z</t>
         </is>
       </c>
     </row>
@@ -10254,7 +10254,7 @@
       </c>
       <c r="K203" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:56Z</t>
+          <t>2026-09-25T23:23:38Z</t>
         </is>
       </c>
     </row>
@@ -10303,7 +10303,7 @@
       </c>
       <c r="K204" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:56Z</t>
+          <t>2026-09-25T23:23:38Z</t>
         </is>
       </c>
     </row>
@@ -10352,7 +10352,7 @@
       </c>
       <c r="K205" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:56Z</t>
+          <t>2026-09-25T23:23:38Z</t>
         </is>
       </c>
     </row>
@@ -10401,7 +10401,7 @@
       </c>
       <c r="K206" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:56Z</t>
+          <t>2026-09-25T23:23:38Z</t>
         </is>
       </c>
     </row>
@@ -10450,7 +10450,7 @@
       </c>
       <c r="K207" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:56Z</t>
+          <t>2026-09-25T23:23:38Z</t>
         </is>
       </c>
     </row>
@@ -10499,7 +10499,7 @@
       </c>
       <c r="K208" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:56Z</t>
+          <t>2026-09-25T23:23:38Z</t>
         </is>
       </c>
     </row>
@@ -10548,7 +10548,7 @@
       </c>
       <c r="K209" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:56Z</t>
+          <t>2026-09-25T23:23:38Z</t>
         </is>
       </c>
     </row>
@@ -10597,7 +10597,7 @@
       </c>
       <c r="K210" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:56Z</t>
+          <t>2026-09-25T23:23:38Z</t>
         </is>
       </c>
     </row>
@@ -10646,7 +10646,7 @@
       </c>
       <c r="K211" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:56Z</t>
+          <t>2026-09-25T23:23:38Z</t>
         </is>
       </c>
     </row>
@@ -10695,7 +10695,7 @@
       </c>
       <c r="K212" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:56Z</t>
+          <t>2026-09-25T23:23:38Z</t>
         </is>
       </c>
     </row>
@@ -10744,7 +10744,7 @@
       </c>
       <c r="K213" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:56Z</t>
+          <t>2026-09-25T23:23:38Z</t>
         </is>
       </c>
     </row>
@@ -10793,7 +10793,7 @@
       </c>
       <c r="K214" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:56Z</t>
+          <t>2026-09-25T23:23:38Z</t>
         </is>
       </c>
     </row>
@@ -10842,7 +10842,7 @@
       </c>
       <c r="K215" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:56Z</t>
+          <t>2026-09-25T23:23:38Z</t>
         </is>
       </c>
     </row>
@@ -10891,7 +10891,7 @@
       </c>
       <c r="K216" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:56Z</t>
+          <t>2026-09-25T23:23:38Z</t>
         </is>
       </c>
     </row>
@@ -10940,7 +10940,7 @@
       </c>
       <c r="K217" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:56Z</t>
+          <t>2026-09-25T23:23:38Z</t>
         </is>
       </c>
     </row>
@@ -10989,7 +10989,7 @@
       </c>
       <c r="K218" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:56Z</t>
+          <t>2026-09-25T23:23:38Z</t>
         </is>
       </c>
     </row>
@@ -11038,7 +11038,7 @@
       </c>
       <c r="K219" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:56Z</t>
+          <t>2026-09-25T23:23:38Z</t>
         </is>
       </c>
     </row>
@@ -11087,7 +11087,7 @@
       </c>
       <c r="K220" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:56Z</t>
+          <t>2026-09-25T23:23:38Z</t>
         </is>
       </c>
     </row>
@@ -11136,7 +11136,7 @@
       </c>
       <c r="K221" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:56Z</t>
+          <t>2026-09-25T23:23:38Z</t>
         </is>
       </c>
     </row>
@@ -11185,7 +11185,7 @@
       </c>
       <c r="K222" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:56Z</t>
+          <t>2026-09-25T23:23:38Z</t>
         </is>
       </c>
     </row>
@@ -11234,7 +11234,7 @@
       </c>
       <c r="K223" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:56Z</t>
+          <t>2026-09-25T23:23:38Z</t>
         </is>
       </c>
     </row>
@@ -11283,7 +11283,7 @@
       </c>
       <c r="K224" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:56Z</t>
+          <t>2026-09-25T23:23:38Z</t>
         </is>
       </c>
     </row>
@@ -11332,7 +11332,7 @@
       </c>
       <c r="K225" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:56Z</t>
+          <t>2026-09-25T23:23:38Z</t>
         </is>
       </c>
     </row>
@@ -11381,7 +11381,7 @@
       </c>
       <c r="K226" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:56Z</t>
+          <t>2026-09-25T23:23:38Z</t>
         </is>
       </c>
     </row>
@@ -11430,7 +11430,7 @@
       </c>
       <c r="K227" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:56Z</t>
+          <t>2026-09-25T23:23:38Z</t>
         </is>
       </c>
     </row>
@@ -11479,7 +11479,7 @@
       </c>
       <c r="K228" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:56Z</t>
+          <t>2026-09-25T23:23:38Z</t>
         </is>
       </c>
     </row>
@@ -11528,7 +11528,7 @@
       </c>
       <c r="K229" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:56Z</t>
+          <t>2026-09-25T23:23:38Z</t>
         </is>
       </c>
     </row>
@@ -11577,7 +11577,7 @@
       </c>
       <c r="K230" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:56Z</t>
+          <t>2026-09-25T23:23:38Z</t>
         </is>
       </c>
     </row>
@@ -11626,7 +11626,7 @@
       </c>
       <c r="K231" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:56Z</t>
+          <t>2026-09-25T23:23:38Z</t>
         </is>
       </c>
     </row>
@@ -11758,7 +11758,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:56Z</t>
+          <t>2026-09-25T23:23:38Z</t>
         </is>
       </c>
     </row>
@@ -11804,7 +11804,7 @@
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>{"date": "2026-08-01", "year": 2026, "month": 8, "month_name": "Agosto", "index_value": 637409769724325.1, "monthly_variation_pct": 8.9, "unit": "Índice base diciembre 2007=100 y variación mensual %", "frequency": "monthly", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/precios_consumidor/4_5_7_2.xls", "fetched_at": "2026-09-24T23:17:56Z"}</t>
+          <t>{"date": "2026-08-01", "year": 2026, "month": 8, "month_name": "Agosto", "index_value": 637409769724325.1, "monthly_variation_pct": 8.9, "unit": "Índice base diciembre 2007=100 y variación mensual %", "frequency": "monthly", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/precios_consumidor/4_5_7_2.xls", "fetched_at": "2026-09-25T23:23:38Z"}</t>
         </is>
       </c>
     </row>

--- a/assets/data/bcv/excel/ove_bcv_inpc_nacional_mensual.xlsx
+++ b/assets/data/bcv/excel/ove_bcv_inpc_nacional_mensual.xlsx
@@ -650,7 +650,7 @@
       </c>
       <c r="K7" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:38Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -699,7 +699,7 @@
       </c>
       <c r="K8" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:38Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="K9" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:38Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -797,7 +797,7 @@
       </c>
       <c r="K10" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:38Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -846,7 +846,7 @@
       </c>
       <c r="K11" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:38Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -895,7 +895,7 @@
       </c>
       <c r="K12" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:38Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="K13" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:38Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -993,7 +993,7 @@
       </c>
       <c r="K14" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:38Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -1042,7 +1042,7 @@
       </c>
       <c r="K15" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:38Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -1091,7 +1091,7 @@
       </c>
       <c r="K16" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:38Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -1140,7 +1140,7 @@
       </c>
       <c r="K17" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:38Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -1189,7 +1189,7 @@
       </c>
       <c r="K18" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:38Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -1238,7 +1238,7 @@
       </c>
       <c r="K19" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:38Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -1287,7 +1287,7 @@
       </c>
       <c r="K20" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:38Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -1336,7 +1336,7 @@
       </c>
       <c r="K21" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:38Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -1385,7 +1385,7 @@
       </c>
       <c r="K22" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:38Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -1434,7 +1434,7 @@
       </c>
       <c r="K23" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:38Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -1483,7 +1483,7 @@
       </c>
       <c r="K24" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:38Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -1532,7 +1532,7 @@
       </c>
       <c r="K25" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:38Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -1581,7 +1581,7 @@
       </c>
       <c r="K26" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:38Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -1630,7 +1630,7 @@
       </c>
       <c r="K27" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:38Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -1679,7 +1679,7 @@
       </c>
       <c r="K28" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:38Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -1728,7 +1728,7 @@
       </c>
       <c r="K29" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:38Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -1777,7 +1777,7 @@
       </c>
       <c r="K30" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:38Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -1826,7 +1826,7 @@
       </c>
       <c r="K31" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:38Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -1875,7 +1875,7 @@
       </c>
       <c r="K32" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:38Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -1924,7 +1924,7 @@
       </c>
       <c r="K33" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:38Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -1973,7 +1973,7 @@
       </c>
       <c r="K34" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:38Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -2022,7 +2022,7 @@
       </c>
       <c r="K35" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:38Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -2071,7 +2071,7 @@
       </c>
       <c r="K36" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:38Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -2120,7 +2120,7 @@
       </c>
       <c r="K37" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:38Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -2169,7 +2169,7 @@
       </c>
       <c r="K38" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:38Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -2218,7 +2218,7 @@
       </c>
       <c r="K39" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:38Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -2267,7 +2267,7 @@
       </c>
       <c r="K40" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:38Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -2316,7 +2316,7 @@
       </c>
       <c r="K41" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:38Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -2365,7 +2365,7 @@
       </c>
       <c r="K42" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:38Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -2414,7 +2414,7 @@
       </c>
       <c r="K43" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:38Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -2463,7 +2463,7 @@
       </c>
       <c r="K44" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:38Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -2512,7 +2512,7 @@
       </c>
       <c r="K45" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:38Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -2561,7 +2561,7 @@
       </c>
       <c r="K46" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:38Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -2610,7 +2610,7 @@
       </c>
       <c r="K47" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:38Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -2659,7 +2659,7 @@
       </c>
       <c r="K48" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:38Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -2708,7 +2708,7 @@
       </c>
       <c r="K49" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:38Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -2757,7 +2757,7 @@
       </c>
       <c r="K50" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:38Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -2806,7 +2806,7 @@
       </c>
       <c r="K51" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:38Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -2855,7 +2855,7 @@
       </c>
       <c r="K52" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:38Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -2904,7 +2904,7 @@
       </c>
       <c r="K53" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:38Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -2953,7 +2953,7 @@
       </c>
       <c r="K54" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:38Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -3002,7 +3002,7 @@
       </c>
       <c r="K55" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:38Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -3051,7 +3051,7 @@
       </c>
       <c r="K56" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:38Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -3100,7 +3100,7 @@
       </c>
       <c r="K57" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:38Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -3149,7 +3149,7 @@
       </c>
       <c r="K58" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:38Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -3198,7 +3198,7 @@
       </c>
       <c r="K59" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:38Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -3247,7 +3247,7 @@
       </c>
       <c r="K60" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:38Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -3296,7 +3296,7 @@
       </c>
       <c r="K61" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:38Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -3345,7 +3345,7 @@
       </c>
       <c r="K62" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:38Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -3394,7 +3394,7 @@
       </c>
       <c r="K63" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:38Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -3443,7 +3443,7 @@
       </c>
       <c r="K64" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:38Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -3492,7 +3492,7 @@
       </c>
       <c r="K65" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:38Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -3541,7 +3541,7 @@
       </c>
       <c r="K66" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:38Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -3590,7 +3590,7 @@
       </c>
       <c r="K67" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:38Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -3639,7 +3639,7 @@
       </c>
       <c r="K68" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:38Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -3688,7 +3688,7 @@
       </c>
       <c r="K69" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:38Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -3737,7 +3737,7 @@
       </c>
       <c r="K70" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:38Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -3786,7 +3786,7 @@
       </c>
       <c r="K71" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:38Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -3835,7 +3835,7 @@
       </c>
       <c r="K72" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:38Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -3884,7 +3884,7 @@
       </c>
       <c r="K73" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:38Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -3933,7 +3933,7 @@
       </c>
       <c r="K74" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:38Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -3982,7 +3982,7 @@
       </c>
       <c r="K75" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:38Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -4031,7 +4031,7 @@
       </c>
       <c r="K76" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:38Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -4080,7 +4080,7 @@
       </c>
       <c r="K77" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:38Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -4129,7 +4129,7 @@
       </c>
       <c r="K78" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:38Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -4178,7 +4178,7 @@
       </c>
       <c r="K79" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:38Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -4227,7 +4227,7 @@
       </c>
       <c r="K80" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:38Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -4276,7 +4276,7 @@
       </c>
       <c r="K81" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:38Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -4325,7 +4325,7 @@
       </c>
       <c r="K82" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:38Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -4374,7 +4374,7 @@
       </c>
       <c r="K83" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:38Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -4423,7 +4423,7 @@
       </c>
       <c r="K84" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:38Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -4472,7 +4472,7 @@
       </c>
       <c r="K85" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:38Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -4521,7 +4521,7 @@
       </c>
       <c r="K86" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:38Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -4570,7 +4570,7 @@
       </c>
       <c r="K87" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:38Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -4619,7 +4619,7 @@
       </c>
       <c r="K88" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:38Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -4668,7 +4668,7 @@
       </c>
       <c r="K89" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:38Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -4717,7 +4717,7 @@
       </c>
       <c r="K90" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:38Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -4766,7 +4766,7 @@
       </c>
       <c r="K91" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:38Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -4815,7 +4815,7 @@
       </c>
       <c r="K92" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:38Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -4864,7 +4864,7 @@
       </c>
       <c r="K93" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:38Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -4913,7 +4913,7 @@
       </c>
       <c r="K94" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:38Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -4962,7 +4962,7 @@
       </c>
       <c r="K95" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:38Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -5011,7 +5011,7 @@
       </c>
       <c r="K96" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:38Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -5060,7 +5060,7 @@
       </c>
       <c r="K97" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:38Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -5109,7 +5109,7 @@
       </c>
       <c r="K98" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:38Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -5158,7 +5158,7 @@
       </c>
       <c r="K99" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:38Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -5207,7 +5207,7 @@
       </c>
       <c r="K100" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:38Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -5256,7 +5256,7 @@
       </c>
       <c r="K101" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:38Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -5305,7 +5305,7 @@
       </c>
       <c r="K102" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:38Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -5354,7 +5354,7 @@
       </c>
       <c r="K103" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:38Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -5403,7 +5403,7 @@
       </c>
       <c r="K104" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:38Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -5452,7 +5452,7 @@
       </c>
       <c r="K105" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:38Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -5501,7 +5501,7 @@
       </c>
       <c r="K106" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:38Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -5550,7 +5550,7 @@
       </c>
       <c r="K107" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:38Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -5599,7 +5599,7 @@
       </c>
       <c r="K108" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:38Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -5648,7 +5648,7 @@
       </c>
       <c r="K109" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:38Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -5697,7 +5697,7 @@
       </c>
       <c r="K110" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:38Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -5746,7 +5746,7 @@
       </c>
       <c r="K111" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:38Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -5795,7 +5795,7 @@
       </c>
       <c r="K112" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:38Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -5844,7 +5844,7 @@
       </c>
       <c r="K113" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:38Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -5893,7 +5893,7 @@
       </c>
       <c r="K114" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:38Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -5942,7 +5942,7 @@
       </c>
       <c r="K115" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:38Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -5991,7 +5991,7 @@
       </c>
       <c r="K116" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:38Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -6040,7 +6040,7 @@
       </c>
       <c r="K117" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:38Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -6089,7 +6089,7 @@
       </c>
       <c r="K118" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:38Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -6138,7 +6138,7 @@
       </c>
       <c r="K119" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:38Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -6187,7 +6187,7 @@
       </c>
       <c r="K120" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:38Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -6236,7 +6236,7 @@
       </c>
       <c r="K121" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:38Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -6285,7 +6285,7 @@
       </c>
       <c r="K122" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:38Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -6334,7 +6334,7 @@
       </c>
       <c r="K123" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:38Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -6383,7 +6383,7 @@
       </c>
       <c r="K124" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:38Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -6432,7 +6432,7 @@
       </c>
       <c r="K125" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:38Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -6481,7 +6481,7 @@
       </c>
       <c r="K126" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:38Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -6530,7 +6530,7 @@
       </c>
       <c r="K127" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:38Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -6579,7 +6579,7 @@
       </c>
       <c r="K128" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:38Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -6628,7 +6628,7 @@
       </c>
       <c r="K129" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:38Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -6677,7 +6677,7 @@
       </c>
       <c r="K130" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:38Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -6726,7 +6726,7 @@
       </c>
       <c r="K131" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:38Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -6775,7 +6775,7 @@
       </c>
       <c r="K132" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:38Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -6824,7 +6824,7 @@
       </c>
       <c r="K133" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:38Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -6873,7 +6873,7 @@
       </c>
       <c r="K134" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:38Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -6922,7 +6922,7 @@
       </c>
       <c r="K135" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:38Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -6971,7 +6971,7 @@
       </c>
       <c r="K136" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:38Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -7020,7 +7020,7 @@
       </c>
       <c r="K137" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:38Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -7069,7 +7069,7 @@
       </c>
       <c r="K138" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:38Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -7118,7 +7118,7 @@
       </c>
       <c r="K139" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:38Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -7167,7 +7167,7 @@
       </c>
       <c r="K140" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:38Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -7216,7 +7216,7 @@
       </c>
       <c r="K141" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:38Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -7265,7 +7265,7 @@
       </c>
       <c r="K142" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:38Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -7314,7 +7314,7 @@
       </c>
       <c r="K143" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:38Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -7363,7 +7363,7 @@
       </c>
       <c r="K144" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:38Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -7412,7 +7412,7 @@
       </c>
       <c r="K145" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:38Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -7461,7 +7461,7 @@
       </c>
       <c r="K146" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:38Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -7510,7 +7510,7 @@
       </c>
       <c r="K147" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:38Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -7559,7 +7559,7 @@
       </c>
       <c r="K148" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:38Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -7608,7 +7608,7 @@
       </c>
       <c r="K149" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:38Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -7657,7 +7657,7 @@
       </c>
       <c r="K150" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:38Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -7706,7 +7706,7 @@
       </c>
       <c r="K151" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:38Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -7755,7 +7755,7 @@
       </c>
       <c r="K152" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:38Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -7804,7 +7804,7 @@
       </c>
       <c r="K153" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:38Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -7853,7 +7853,7 @@
       </c>
       <c r="K154" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:38Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -7902,7 +7902,7 @@
       </c>
       <c r="K155" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:38Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -7951,7 +7951,7 @@
       </c>
       <c r="K156" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:38Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -8000,7 +8000,7 @@
       </c>
       <c r="K157" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:38Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -8049,7 +8049,7 @@
       </c>
       <c r="K158" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:38Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -8098,7 +8098,7 @@
       </c>
       <c r="K159" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:38Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -8147,7 +8147,7 @@
       </c>
       <c r="K160" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:38Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -8196,7 +8196,7 @@
       </c>
       <c r="K161" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:38Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -8245,7 +8245,7 @@
       </c>
       <c r="K162" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:38Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -8294,7 +8294,7 @@
       </c>
       <c r="K163" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:38Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -8343,7 +8343,7 @@
       </c>
       <c r="K164" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:38Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -8392,7 +8392,7 @@
       </c>
       <c r="K165" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:38Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -8441,7 +8441,7 @@
       </c>
       <c r="K166" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:38Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -8490,7 +8490,7 @@
       </c>
       <c r="K167" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:38Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -8539,7 +8539,7 @@
       </c>
       <c r="K168" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:38Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -8588,7 +8588,7 @@
       </c>
       <c r="K169" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:38Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -8637,7 +8637,7 @@
       </c>
       <c r="K170" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:38Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -8686,7 +8686,7 @@
       </c>
       <c r="K171" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:38Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -8735,7 +8735,7 @@
       </c>
       <c r="K172" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:38Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -8784,7 +8784,7 @@
       </c>
       <c r="K173" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:38Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -8833,7 +8833,7 @@
       </c>
       <c r="K174" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:38Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -8882,7 +8882,7 @@
       </c>
       <c r="K175" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:38Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -8931,7 +8931,7 @@
       </c>
       <c r="K176" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:38Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -8980,7 +8980,7 @@
       </c>
       <c r="K177" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:38Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -9029,7 +9029,7 @@
       </c>
       <c r="K178" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:38Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -9078,7 +9078,7 @@
       </c>
       <c r="K179" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:38Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -9127,7 +9127,7 @@
       </c>
       <c r="K180" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:38Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -9176,7 +9176,7 @@
       </c>
       <c r="K181" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:38Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -9225,7 +9225,7 @@
       </c>
       <c r="K182" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:38Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -9274,7 +9274,7 @@
       </c>
       <c r="K183" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:38Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -9323,7 +9323,7 @@
       </c>
       <c r="K184" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:38Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -9372,7 +9372,7 @@
       </c>
       <c r="K185" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:38Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -9421,7 +9421,7 @@
       </c>
       <c r="K186" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:38Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -9470,7 +9470,7 @@
       </c>
       <c r="K187" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:38Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -9519,7 +9519,7 @@
       </c>
       <c r="K188" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:38Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -9568,7 +9568,7 @@
       </c>
       <c r="K189" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:38Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -9617,7 +9617,7 @@
       </c>
       <c r="K190" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:38Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -9666,7 +9666,7 @@
       </c>
       <c r="K191" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:38Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -9715,7 +9715,7 @@
       </c>
       <c r="K192" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:38Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -9764,7 +9764,7 @@
       </c>
       <c r="K193" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:38Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -9813,7 +9813,7 @@
       </c>
       <c r="K194" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:38Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -9862,7 +9862,7 @@
       </c>
       <c r="K195" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:38Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -9911,7 +9911,7 @@
       </c>
       <c r="K196" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:38Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -9960,7 +9960,7 @@
       </c>
       <c r="K197" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:38Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -10009,7 +10009,7 @@
       </c>
       <c r="K198" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:38Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -10058,7 +10058,7 @@
       </c>
       <c r="K199" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:38Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -10107,7 +10107,7 @@
       </c>
       <c r="K200" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:38Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -10156,7 +10156,7 @@
       </c>
       <c r="K201" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:38Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -10205,7 +10205,7 @@
       </c>
       <c r="K202" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:38Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -10254,7 +10254,7 @@
       </c>
       <c r="K203" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:38Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -10303,7 +10303,7 @@
       </c>
       <c r="K204" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:38Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -10352,7 +10352,7 @@
       </c>
       <c r="K205" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:38Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -10401,7 +10401,7 @@
       </c>
       <c r="K206" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:38Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -10450,7 +10450,7 @@
       </c>
       <c r="K207" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:38Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -10499,7 +10499,7 @@
       </c>
       <c r="K208" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:38Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -10548,7 +10548,7 @@
       </c>
       <c r="K209" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:38Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -10597,7 +10597,7 @@
       </c>
       <c r="K210" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:38Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -10646,7 +10646,7 @@
       </c>
       <c r="K211" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:38Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -10695,7 +10695,7 @@
       </c>
       <c r="K212" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:38Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -10744,7 +10744,7 @@
       </c>
       <c r="K213" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:38Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -10793,7 +10793,7 @@
       </c>
       <c r="K214" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:38Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -10842,7 +10842,7 @@
       </c>
       <c r="K215" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:38Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -10891,7 +10891,7 @@
       </c>
       <c r="K216" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:38Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -10940,7 +10940,7 @@
       </c>
       <c r="K217" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:38Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -10989,7 +10989,7 @@
       </c>
       <c r="K218" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:38Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -11038,7 +11038,7 @@
       </c>
       <c r="K219" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:38Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -11087,7 +11087,7 @@
       </c>
       <c r="K220" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:38Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -11136,7 +11136,7 @@
       </c>
       <c r="K221" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:38Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -11185,7 +11185,7 @@
       </c>
       <c r="K222" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:38Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -11234,7 +11234,7 @@
       </c>
       <c r="K223" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:38Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -11283,7 +11283,7 @@
       </c>
       <c r="K224" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:38Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -11332,7 +11332,7 @@
       </c>
       <c r="K225" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:38Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -11381,7 +11381,7 @@
       </c>
       <c r="K226" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:38Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -11430,7 +11430,7 @@
       </c>
       <c r="K227" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:38Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -11479,7 +11479,7 @@
       </c>
       <c r="K228" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:38Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -11528,7 +11528,7 @@
       </c>
       <c r="K229" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:38Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -11577,7 +11577,7 @@
       </c>
       <c r="K230" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:38Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -11626,7 +11626,7 @@
       </c>
       <c r="K231" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:38Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -11758,7 +11758,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:38Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -11804,7 +11804,7 @@
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>{"date": "2026-08-01", "year": 2026, "month": 8, "month_name": "Agosto", "index_value": 637409769724325.1, "monthly_variation_pct": 8.9, "unit": "Índice base diciembre 2007=100 y variación mensual %", "frequency": "monthly", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/precios_consumidor/4_5_7_2.xls", "fetched_at": "2026-09-25T23:23:38Z"}</t>
+          <t>{"date": "2026-08-01", "year": 2026, "month": 8, "month_name": "Agosto", "index_value": 637409769724325.1, "monthly_variation_pct": 8.9, "unit": "Índice base diciembre 2007=100 y variación mensual %", "frequency": "monthly", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/precios_consumidor/4_5_7_2.xls", "fetched_at": "2026-09-26T23:03:46Z"}</t>
         </is>
       </c>
     </row>

--- a/assets/data/bcv/excel/ove_bcv_inpc_nacional_mensual.xlsx
+++ b/assets/data/bcv/excel/ove_bcv_inpc_nacional_mensual.xlsx
@@ -650,7 +650,7 @@
       </c>
       <c r="K7" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:00Z</t>
         </is>
       </c>
     </row>
@@ -699,7 +699,7 @@
       </c>
       <c r="K8" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:00Z</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="K9" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:00Z</t>
         </is>
       </c>
     </row>
@@ -797,7 +797,7 @@
       </c>
       <c r="K10" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:00Z</t>
         </is>
       </c>
     </row>
@@ -846,7 +846,7 @@
       </c>
       <c r="K11" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:00Z</t>
         </is>
       </c>
     </row>
@@ -895,7 +895,7 @@
       </c>
       <c r="K12" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:00Z</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="K13" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:00Z</t>
         </is>
       </c>
     </row>
@@ -993,7 +993,7 @@
       </c>
       <c r="K14" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:00Z</t>
         </is>
       </c>
     </row>
@@ -1042,7 +1042,7 @@
       </c>
       <c r="K15" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:00Z</t>
         </is>
       </c>
     </row>
@@ -1091,7 +1091,7 @@
       </c>
       <c r="K16" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:00Z</t>
         </is>
       </c>
     </row>
@@ -1140,7 +1140,7 @@
       </c>
       <c r="K17" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:00Z</t>
         </is>
       </c>
     </row>
@@ -1189,7 +1189,7 @@
       </c>
       <c r="K18" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:00Z</t>
         </is>
       </c>
     </row>
@@ -1238,7 +1238,7 @@
       </c>
       <c r="K19" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:00Z</t>
         </is>
       </c>
     </row>
@@ -1287,7 +1287,7 @@
       </c>
       <c r="K20" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:00Z</t>
         </is>
       </c>
     </row>
@@ -1336,7 +1336,7 @@
       </c>
       <c r="K21" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:00Z</t>
         </is>
       </c>
     </row>
@@ -1385,7 +1385,7 @@
       </c>
       <c r="K22" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:00Z</t>
         </is>
       </c>
     </row>
@@ -1434,7 +1434,7 @@
       </c>
       <c r="K23" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:00Z</t>
         </is>
       </c>
     </row>
@@ -1483,7 +1483,7 @@
       </c>
       <c r="K24" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:00Z</t>
         </is>
       </c>
     </row>
@@ -1532,7 +1532,7 @@
       </c>
       <c r="K25" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:00Z</t>
         </is>
       </c>
     </row>
@@ -1581,7 +1581,7 @@
       </c>
       <c r="K26" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:00Z</t>
         </is>
       </c>
     </row>
@@ -1630,7 +1630,7 @@
       </c>
       <c r="K27" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:00Z</t>
         </is>
       </c>
     </row>
@@ -1679,7 +1679,7 @@
       </c>
       <c r="K28" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:00Z</t>
         </is>
       </c>
     </row>
@@ -1728,7 +1728,7 @@
       </c>
       <c r="K29" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:00Z</t>
         </is>
       </c>
     </row>
@@ -1777,7 +1777,7 @@
       </c>
       <c r="K30" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:00Z</t>
         </is>
       </c>
     </row>
@@ -1826,7 +1826,7 @@
       </c>
       <c r="K31" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:00Z</t>
         </is>
       </c>
     </row>
@@ -1875,7 +1875,7 @@
       </c>
       <c r="K32" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:00Z</t>
         </is>
       </c>
     </row>
@@ -1924,7 +1924,7 @@
       </c>
       <c r="K33" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:00Z</t>
         </is>
       </c>
     </row>
@@ -1973,7 +1973,7 @@
       </c>
       <c r="K34" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:00Z</t>
         </is>
       </c>
     </row>
@@ -2022,7 +2022,7 @@
       </c>
       <c r="K35" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:00Z</t>
         </is>
       </c>
     </row>
@@ -2071,7 +2071,7 @@
       </c>
       <c r="K36" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:00Z</t>
         </is>
       </c>
     </row>
@@ -2120,7 +2120,7 @@
       </c>
       <c r="K37" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:00Z</t>
         </is>
       </c>
     </row>
@@ -2169,7 +2169,7 @@
       </c>
       <c r="K38" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:00Z</t>
         </is>
       </c>
     </row>
@@ -2218,7 +2218,7 @@
       </c>
       <c r="K39" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:00Z</t>
         </is>
       </c>
     </row>
@@ -2267,7 +2267,7 @@
       </c>
       <c r="K40" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:00Z</t>
         </is>
       </c>
     </row>
@@ -2316,7 +2316,7 @@
       </c>
       <c r="K41" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:00Z</t>
         </is>
       </c>
     </row>
@@ -2365,7 +2365,7 @@
       </c>
       <c r="K42" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:00Z</t>
         </is>
       </c>
     </row>
@@ -2414,7 +2414,7 @@
       </c>
       <c r="K43" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:00Z</t>
         </is>
       </c>
     </row>
@@ -2463,7 +2463,7 @@
       </c>
       <c r="K44" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:00Z</t>
         </is>
       </c>
     </row>
@@ -2512,7 +2512,7 @@
       </c>
       <c r="K45" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:00Z</t>
         </is>
       </c>
     </row>
@@ -2561,7 +2561,7 @@
       </c>
       <c r="K46" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:00Z</t>
         </is>
       </c>
     </row>
@@ -2610,7 +2610,7 @@
       </c>
       <c r="K47" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:00Z</t>
         </is>
       </c>
     </row>
@@ -2659,7 +2659,7 @@
       </c>
       <c r="K48" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:00Z</t>
         </is>
       </c>
     </row>
@@ -2708,7 +2708,7 @@
       </c>
       <c r="K49" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:00Z</t>
         </is>
       </c>
     </row>
@@ -2757,7 +2757,7 @@
       </c>
       <c r="K50" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:00Z</t>
         </is>
       </c>
     </row>
@@ -2806,7 +2806,7 @@
       </c>
       <c r="K51" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:00Z</t>
         </is>
       </c>
     </row>
@@ -2855,7 +2855,7 @@
       </c>
       <c r="K52" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:00Z</t>
         </is>
       </c>
     </row>
@@ -2904,7 +2904,7 @@
       </c>
       <c r="K53" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:00Z</t>
         </is>
       </c>
     </row>
@@ -2953,7 +2953,7 @@
       </c>
       <c r="K54" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:00Z</t>
         </is>
       </c>
     </row>
@@ -3002,7 +3002,7 @@
       </c>
       <c r="K55" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:00Z</t>
         </is>
       </c>
     </row>
@@ -3051,7 +3051,7 @@
       </c>
       <c r="K56" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:00Z</t>
         </is>
       </c>
     </row>
@@ -3100,7 +3100,7 @@
       </c>
       <c r="K57" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:00Z</t>
         </is>
       </c>
     </row>
@@ -3149,7 +3149,7 @@
       </c>
       <c r="K58" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:00Z</t>
         </is>
       </c>
     </row>
@@ -3198,7 +3198,7 @@
       </c>
       <c r="K59" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:00Z</t>
         </is>
       </c>
     </row>
@@ -3247,7 +3247,7 @@
       </c>
       <c r="K60" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:00Z</t>
         </is>
       </c>
     </row>
@@ -3296,7 +3296,7 @@
       </c>
       <c r="K61" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:00Z</t>
         </is>
       </c>
     </row>
@@ -3345,7 +3345,7 @@
       </c>
       <c r="K62" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:00Z</t>
         </is>
       </c>
     </row>
@@ -3394,7 +3394,7 @@
       </c>
       <c r="K63" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:00Z</t>
         </is>
       </c>
     </row>
@@ -3443,7 +3443,7 @@
       </c>
       <c r="K64" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:00Z</t>
         </is>
       </c>
     </row>
@@ -3492,7 +3492,7 @@
       </c>
       <c r="K65" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:00Z</t>
         </is>
       </c>
     </row>
@@ -3541,7 +3541,7 @@
       </c>
       <c r="K66" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:00Z</t>
         </is>
       </c>
     </row>
@@ -3590,7 +3590,7 @@
       </c>
       <c r="K67" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:00Z</t>
         </is>
       </c>
     </row>
@@ -3639,7 +3639,7 @@
       </c>
       <c r="K68" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:00Z</t>
         </is>
       </c>
     </row>
@@ -3688,7 +3688,7 @@
       </c>
       <c r="K69" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:00Z</t>
         </is>
       </c>
     </row>
@@ -3737,7 +3737,7 @@
       </c>
       <c r="K70" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:00Z</t>
         </is>
       </c>
     </row>
@@ -3786,7 +3786,7 @@
       </c>
       <c r="K71" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:00Z</t>
         </is>
       </c>
     </row>
@@ -3835,7 +3835,7 @@
       </c>
       <c r="K72" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:00Z</t>
         </is>
       </c>
     </row>
@@ -3884,7 +3884,7 @@
       </c>
       <c r="K73" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:00Z</t>
         </is>
       </c>
     </row>
@@ -3933,7 +3933,7 @@
       </c>
       <c r="K74" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:00Z</t>
         </is>
       </c>
     </row>
@@ -3982,7 +3982,7 @@
       </c>
       <c r="K75" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:00Z</t>
         </is>
       </c>
     </row>
@@ -4031,7 +4031,7 @@
       </c>
       <c r="K76" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:00Z</t>
         </is>
       </c>
     </row>
@@ -4080,7 +4080,7 @@
       </c>
       <c r="K77" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:00Z</t>
         </is>
       </c>
     </row>
@@ -4129,7 +4129,7 @@
       </c>
       <c r="K78" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:00Z</t>
         </is>
       </c>
     </row>
@@ -4178,7 +4178,7 @@
       </c>
       <c r="K79" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:00Z</t>
         </is>
       </c>
     </row>
@@ -4227,7 +4227,7 @@
       </c>
       <c r="K80" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:00Z</t>
         </is>
       </c>
     </row>
@@ -4276,7 +4276,7 @@
       </c>
       <c r="K81" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:00Z</t>
         </is>
       </c>
     </row>
@@ -4325,7 +4325,7 @@
       </c>
       <c r="K82" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:00Z</t>
         </is>
       </c>
     </row>
@@ -4374,7 +4374,7 @@
       </c>
       <c r="K83" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:00Z</t>
         </is>
       </c>
     </row>
@@ -4423,7 +4423,7 @@
       </c>
       <c r="K84" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:00Z</t>
         </is>
       </c>
     </row>
@@ -4472,7 +4472,7 @@
       </c>
       <c r="K85" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:00Z</t>
         </is>
       </c>
     </row>
@@ -4521,7 +4521,7 @@
       </c>
       <c r="K86" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:00Z</t>
         </is>
       </c>
     </row>
@@ -4570,7 +4570,7 @@
       </c>
       <c r="K87" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:00Z</t>
         </is>
       </c>
     </row>
@@ -4619,7 +4619,7 @@
       </c>
       <c r="K88" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:00Z</t>
         </is>
       </c>
     </row>
@@ -4668,7 +4668,7 @@
       </c>
       <c r="K89" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:00Z</t>
         </is>
       </c>
     </row>
@@ -4717,7 +4717,7 @@
       </c>
       <c r="K90" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:00Z</t>
         </is>
       </c>
     </row>
@@ -4766,7 +4766,7 @@
       </c>
       <c r="K91" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:00Z</t>
         </is>
       </c>
     </row>
@@ -4815,7 +4815,7 @@
       </c>
       <c r="K92" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:00Z</t>
         </is>
       </c>
     </row>
@@ -4864,7 +4864,7 @@
       </c>
       <c r="K93" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:00Z</t>
         </is>
       </c>
     </row>
@@ -4913,7 +4913,7 @@
       </c>
       <c r="K94" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:00Z</t>
         </is>
       </c>
     </row>
@@ -4962,7 +4962,7 @@
       </c>
       <c r="K95" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:00Z</t>
         </is>
       </c>
     </row>
@@ -5011,7 +5011,7 @@
       </c>
       <c r="K96" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:00Z</t>
         </is>
       </c>
     </row>
@@ -5060,7 +5060,7 @@
       </c>
       <c r="K97" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:00Z</t>
         </is>
       </c>
     </row>
@@ -5109,7 +5109,7 @@
       </c>
       <c r="K98" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:00Z</t>
         </is>
       </c>
     </row>
@@ -5158,7 +5158,7 @@
       </c>
       <c r="K99" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:00Z</t>
         </is>
       </c>
     </row>
@@ -5207,7 +5207,7 @@
       </c>
       <c r="K100" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:00Z</t>
         </is>
       </c>
     </row>
@@ -5256,7 +5256,7 @@
       </c>
       <c r="K101" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:00Z</t>
         </is>
       </c>
     </row>
@@ -5305,7 +5305,7 @@
       </c>
       <c r="K102" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:00Z</t>
         </is>
       </c>
     </row>
@@ -5354,7 +5354,7 @@
       </c>
       <c r="K103" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:00Z</t>
         </is>
       </c>
     </row>
@@ -5403,7 +5403,7 @@
       </c>
       <c r="K104" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:00Z</t>
         </is>
       </c>
     </row>
@@ -5452,7 +5452,7 @@
       </c>
       <c r="K105" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:00Z</t>
         </is>
       </c>
     </row>
@@ -5501,7 +5501,7 @@
       </c>
       <c r="K106" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:00Z</t>
         </is>
       </c>
     </row>
@@ -5550,7 +5550,7 @@
       </c>
       <c r="K107" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:00Z</t>
         </is>
       </c>
     </row>
@@ -5599,7 +5599,7 @@
       </c>
       <c r="K108" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:00Z</t>
         </is>
       </c>
     </row>
@@ -5648,7 +5648,7 @@
       </c>
       <c r="K109" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:00Z</t>
         </is>
       </c>
     </row>
@@ -5697,7 +5697,7 @@
       </c>
       <c r="K110" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:00Z</t>
         </is>
       </c>
     </row>
@@ -5746,7 +5746,7 @@
       </c>
       <c r="K111" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:00Z</t>
         </is>
       </c>
     </row>
@@ -5795,7 +5795,7 @@
       </c>
       <c r="K112" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:00Z</t>
         </is>
       </c>
     </row>
@@ -5844,7 +5844,7 @@
       </c>
       <c r="K113" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:00Z</t>
         </is>
       </c>
     </row>
@@ -5893,7 +5893,7 @@
       </c>
       <c r="K114" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:00Z</t>
         </is>
       </c>
     </row>
@@ -5942,7 +5942,7 @@
       </c>
       <c r="K115" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:00Z</t>
         </is>
       </c>
     </row>
@@ -5991,7 +5991,7 @@
       </c>
       <c r="K116" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:00Z</t>
         </is>
       </c>
     </row>
@@ -6040,7 +6040,7 @@
       </c>
       <c r="K117" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:00Z</t>
         </is>
       </c>
     </row>
@@ -6089,7 +6089,7 @@
       </c>
       <c r="K118" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:00Z</t>
         </is>
       </c>
     </row>
@@ -6138,7 +6138,7 @@
       </c>
       <c r="K119" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:00Z</t>
         </is>
       </c>
     </row>
@@ -6187,7 +6187,7 @@
       </c>
       <c r="K120" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:00Z</t>
         </is>
       </c>
     </row>
@@ -6236,7 +6236,7 @@
       </c>
       <c r="K121" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:00Z</t>
         </is>
       </c>
     </row>
@@ -6285,7 +6285,7 @@
       </c>
       <c r="K122" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:00Z</t>
         </is>
       </c>
     </row>
@@ -6334,7 +6334,7 @@
       </c>
       <c r="K123" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:00Z</t>
         </is>
       </c>
     </row>
@@ -6383,7 +6383,7 @@
       </c>
       <c r="K124" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:00Z</t>
         </is>
       </c>
     </row>
@@ -6432,7 +6432,7 @@
       </c>
       <c r="K125" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:00Z</t>
         </is>
       </c>
     </row>
@@ -6481,7 +6481,7 @@
       </c>
       <c r="K126" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:00Z</t>
         </is>
       </c>
     </row>
@@ -6530,7 +6530,7 @@
       </c>
       <c r="K127" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:00Z</t>
         </is>
       </c>
     </row>
@@ -6579,7 +6579,7 @@
       </c>
       <c r="K128" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:00Z</t>
         </is>
       </c>
     </row>
@@ -6628,7 +6628,7 @@
       </c>
       <c r="K129" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:00Z</t>
         </is>
       </c>
     </row>
@@ -6677,7 +6677,7 @@
       </c>
       <c r="K130" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:00Z</t>
         </is>
       </c>
     </row>
@@ -6726,7 +6726,7 @@
       </c>
       <c r="K131" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:00Z</t>
         </is>
       </c>
     </row>
@@ -6775,7 +6775,7 @@
       </c>
       <c r="K132" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:00Z</t>
         </is>
       </c>
     </row>
@@ -6824,7 +6824,7 @@
       </c>
       <c r="K133" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:00Z</t>
         </is>
       </c>
     </row>
@@ -6873,7 +6873,7 @@
       </c>
       <c r="K134" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:00Z</t>
         </is>
       </c>
     </row>
@@ -6922,7 +6922,7 @@
       </c>
       <c r="K135" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:00Z</t>
         </is>
       </c>
     </row>
@@ -6971,7 +6971,7 @@
       </c>
       <c r="K136" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:00Z</t>
         </is>
       </c>
     </row>
@@ -7020,7 +7020,7 @@
       </c>
       <c r="K137" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:00Z</t>
         </is>
       </c>
     </row>
@@ -7069,7 +7069,7 @@
       </c>
       <c r="K138" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:00Z</t>
         </is>
       </c>
     </row>
@@ -7118,7 +7118,7 @@
       </c>
       <c r="K139" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:00Z</t>
         </is>
       </c>
     </row>
@@ -7167,7 +7167,7 @@
       </c>
       <c r="K140" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:00Z</t>
         </is>
       </c>
     </row>
@@ -7216,7 +7216,7 @@
       </c>
       <c r="K141" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:00Z</t>
         </is>
       </c>
     </row>
@@ -7265,7 +7265,7 @@
       </c>
       <c r="K142" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:00Z</t>
         </is>
       </c>
     </row>
@@ -7314,7 +7314,7 @@
       </c>
       <c r="K143" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:00Z</t>
         </is>
       </c>
     </row>
@@ -7363,7 +7363,7 @@
       </c>
       <c r="K144" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:00Z</t>
         </is>
       </c>
     </row>
@@ -7412,7 +7412,7 @@
       </c>
       <c r="K145" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:00Z</t>
         </is>
       </c>
     </row>
@@ -7461,7 +7461,7 @@
       </c>
       <c r="K146" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:00Z</t>
         </is>
       </c>
     </row>
@@ -7510,7 +7510,7 @@
       </c>
       <c r="K147" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:00Z</t>
         </is>
       </c>
     </row>
@@ -7559,7 +7559,7 @@
       </c>
       <c r="K148" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:00Z</t>
         </is>
       </c>
     </row>
@@ -7608,7 +7608,7 @@
       </c>
       <c r="K149" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:00Z</t>
         </is>
       </c>
     </row>
@@ -7657,7 +7657,7 @@
       </c>
       <c r="K150" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:00Z</t>
         </is>
       </c>
     </row>
@@ -7706,7 +7706,7 @@
       </c>
       <c r="K151" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:00Z</t>
         </is>
       </c>
     </row>
@@ -7755,7 +7755,7 @@
       </c>
       <c r="K152" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:00Z</t>
         </is>
       </c>
     </row>
@@ -7804,7 +7804,7 @@
       </c>
       <c r="K153" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:00Z</t>
         </is>
       </c>
     </row>
@@ -7853,7 +7853,7 @@
       </c>
       <c r="K154" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:00Z</t>
         </is>
       </c>
     </row>
@@ -7902,7 +7902,7 @@
       </c>
       <c r="K155" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:00Z</t>
         </is>
       </c>
     </row>
@@ -7951,7 +7951,7 @@
       </c>
       <c r="K156" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:00Z</t>
         </is>
       </c>
     </row>
@@ -8000,7 +8000,7 @@
       </c>
       <c r="K157" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:00Z</t>
         </is>
       </c>
     </row>
@@ -8049,7 +8049,7 @@
       </c>
       <c r="K158" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:00Z</t>
         </is>
       </c>
     </row>
@@ -8098,7 +8098,7 @@
       </c>
       <c r="K159" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:00Z</t>
         </is>
       </c>
     </row>
@@ -8147,7 +8147,7 @@
       </c>
       <c r="K160" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:00Z</t>
         </is>
       </c>
     </row>
@@ -8196,7 +8196,7 @@
       </c>
       <c r="K161" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:00Z</t>
         </is>
       </c>
     </row>
@@ -8245,7 +8245,7 @@
       </c>
       <c r="K162" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:00Z</t>
         </is>
       </c>
     </row>
@@ -8294,7 +8294,7 @@
       </c>
       <c r="K163" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:00Z</t>
         </is>
       </c>
     </row>
@@ -8343,7 +8343,7 @@
       </c>
       <c r="K164" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:00Z</t>
         </is>
       </c>
     </row>
@@ -8392,7 +8392,7 @@
       </c>
       <c r="K165" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:00Z</t>
         </is>
       </c>
     </row>
@@ -8441,7 +8441,7 @@
       </c>
       <c r="K166" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:00Z</t>
         </is>
       </c>
     </row>
@@ -8490,7 +8490,7 @@
       </c>
       <c r="K167" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:00Z</t>
         </is>
       </c>
     </row>
@@ -8539,7 +8539,7 @@
       </c>
       <c r="K168" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:00Z</t>
         </is>
       </c>
     </row>
@@ -8588,7 +8588,7 @@
       </c>
       <c r="K169" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:00Z</t>
         </is>
       </c>
     </row>
@@ -8637,7 +8637,7 @@
       </c>
       <c r="K170" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:00Z</t>
         </is>
       </c>
     </row>
@@ -8686,7 +8686,7 @@
       </c>
       <c r="K171" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:00Z</t>
         </is>
       </c>
     </row>
@@ -8735,7 +8735,7 @@
       </c>
       <c r="K172" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:00Z</t>
         </is>
       </c>
     </row>
@@ -8784,7 +8784,7 @@
       </c>
       <c r="K173" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:00Z</t>
         </is>
       </c>
     </row>
@@ -8833,7 +8833,7 @@
       </c>
       <c r="K174" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:00Z</t>
         </is>
       </c>
     </row>
@@ -8882,7 +8882,7 @@
       </c>
       <c r="K175" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:00Z</t>
         </is>
       </c>
     </row>
@@ -8931,7 +8931,7 @@
       </c>
       <c r="K176" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:00Z</t>
         </is>
       </c>
     </row>
@@ -8980,7 +8980,7 @@
       </c>
       <c r="K177" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:00Z</t>
         </is>
       </c>
     </row>
@@ -9029,7 +9029,7 @@
       </c>
       <c r="K178" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:00Z</t>
         </is>
       </c>
     </row>
@@ -9078,7 +9078,7 @@
       </c>
       <c r="K179" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:00Z</t>
         </is>
       </c>
     </row>
@@ -9127,7 +9127,7 @@
       </c>
       <c r="K180" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:00Z</t>
         </is>
       </c>
     </row>
@@ -9176,7 +9176,7 @@
       </c>
       <c r="K181" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:00Z</t>
         </is>
       </c>
     </row>
@@ -9225,7 +9225,7 @@
       </c>
       <c r="K182" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:00Z</t>
         </is>
       </c>
     </row>
@@ -9274,7 +9274,7 @@
       </c>
       <c r="K183" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:00Z</t>
         </is>
       </c>
     </row>
@@ -9323,7 +9323,7 @@
       </c>
       <c r="K184" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:00Z</t>
         </is>
       </c>
     </row>
@@ -9372,7 +9372,7 @@
       </c>
       <c r="K185" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:00Z</t>
         </is>
       </c>
     </row>
@@ -9421,7 +9421,7 @@
       </c>
       <c r="K186" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:00Z</t>
         </is>
       </c>
     </row>
@@ -9470,7 +9470,7 @@
       </c>
       <c r="K187" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:00Z</t>
         </is>
       </c>
     </row>
@@ -9519,7 +9519,7 @@
       </c>
       <c r="K188" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:00Z</t>
         </is>
       </c>
     </row>
@@ -9568,7 +9568,7 @@
       </c>
       <c r="K189" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:00Z</t>
         </is>
       </c>
     </row>
@@ -9617,7 +9617,7 @@
       </c>
       <c r="K190" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:00Z</t>
         </is>
       </c>
     </row>
@@ -9666,7 +9666,7 @@
       </c>
       <c r="K191" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:00Z</t>
         </is>
       </c>
     </row>
@@ -9715,7 +9715,7 @@
       </c>
       <c r="K192" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:00Z</t>
         </is>
       </c>
     </row>
@@ -9764,7 +9764,7 @@
       </c>
       <c r="K193" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:00Z</t>
         </is>
       </c>
     </row>
@@ -9813,7 +9813,7 @@
       </c>
       <c r="K194" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:00Z</t>
         </is>
       </c>
     </row>
@@ -9862,7 +9862,7 @@
       </c>
       <c r="K195" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:00Z</t>
         </is>
       </c>
     </row>
@@ -9911,7 +9911,7 @@
       </c>
       <c r="K196" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:00Z</t>
         </is>
       </c>
     </row>
@@ -9960,7 +9960,7 @@
       </c>
       <c r="K197" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:00Z</t>
         </is>
       </c>
     </row>
@@ -10009,7 +10009,7 @@
       </c>
       <c r="K198" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:00Z</t>
         </is>
       </c>
     </row>
@@ -10058,7 +10058,7 @@
       </c>
       <c r="K199" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:00Z</t>
         </is>
       </c>
     </row>
@@ -10107,7 +10107,7 @@
       </c>
       <c r="K200" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:00Z</t>
         </is>
       </c>
     </row>
@@ -10156,7 +10156,7 @@
       </c>
       <c r="K201" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:00Z</t>
         </is>
       </c>
     </row>
@@ -10205,7 +10205,7 @@
       </c>
       <c r="K202" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:00Z</t>
         </is>
       </c>
     </row>
@@ -10254,7 +10254,7 @@
       </c>
       <c r="K203" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:00Z</t>
         </is>
       </c>
     </row>
@@ -10303,7 +10303,7 @@
       </c>
       <c r="K204" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:00Z</t>
         </is>
       </c>
     </row>
@@ -10352,7 +10352,7 @@
       </c>
       <c r="K205" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:00Z</t>
         </is>
       </c>
     </row>
@@ -10401,7 +10401,7 @@
       </c>
       <c r="K206" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:00Z</t>
         </is>
       </c>
     </row>
@@ -10450,7 +10450,7 @@
       </c>
       <c r="K207" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:00Z</t>
         </is>
       </c>
     </row>
@@ -10499,7 +10499,7 @@
       </c>
       <c r="K208" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:00Z</t>
         </is>
       </c>
     </row>
@@ -10548,7 +10548,7 @@
       </c>
       <c r="K209" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:00Z</t>
         </is>
       </c>
     </row>
@@ -10597,7 +10597,7 @@
       </c>
       <c r="K210" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:00Z</t>
         </is>
       </c>
     </row>
@@ -10646,7 +10646,7 @@
       </c>
       <c r="K211" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:00Z</t>
         </is>
       </c>
     </row>
@@ -10695,7 +10695,7 @@
       </c>
       <c r="K212" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:00Z</t>
         </is>
       </c>
     </row>
@@ -10744,7 +10744,7 @@
       </c>
       <c r="K213" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:00Z</t>
         </is>
       </c>
     </row>
@@ -10793,7 +10793,7 @@
       </c>
       <c r="K214" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:00Z</t>
         </is>
       </c>
     </row>
@@ -10842,7 +10842,7 @@
       </c>
       <c r="K215" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:00Z</t>
         </is>
       </c>
     </row>
@@ -10891,7 +10891,7 @@
       </c>
       <c r="K216" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:00Z</t>
         </is>
       </c>
     </row>
@@ -10940,7 +10940,7 @@
       </c>
       <c r="K217" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:00Z</t>
         </is>
       </c>
     </row>
@@ -10989,7 +10989,7 @@
       </c>
       <c r="K218" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:00Z</t>
         </is>
       </c>
     </row>
@@ -11038,7 +11038,7 @@
       </c>
       <c r="K219" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:00Z</t>
         </is>
       </c>
     </row>
@@ -11087,7 +11087,7 @@
       </c>
       <c r="K220" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:00Z</t>
         </is>
       </c>
     </row>
@@ -11136,7 +11136,7 @@
       </c>
       <c r="K221" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:00Z</t>
         </is>
       </c>
     </row>
@@ -11185,7 +11185,7 @@
       </c>
       <c r="K222" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:00Z</t>
         </is>
       </c>
     </row>
@@ -11234,7 +11234,7 @@
       </c>
       <c r="K223" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:00Z</t>
         </is>
       </c>
     </row>
@@ -11283,7 +11283,7 @@
       </c>
       <c r="K224" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:00Z</t>
         </is>
       </c>
     </row>
@@ -11332,7 +11332,7 @@
       </c>
       <c r="K225" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:00Z</t>
         </is>
       </c>
     </row>
@@ -11381,7 +11381,7 @@
       </c>
       <c r="K226" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:00Z</t>
         </is>
       </c>
     </row>
@@ -11430,7 +11430,7 @@
       </c>
       <c r="K227" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:00Z</t>
         </is>
       </c>
     </row>
@@ -11479,7 +11479,7 @@
       </c>
       <c r="K228" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:00Z</t>
         </is>
       </c>
     </row>
@@ -11528,7 +11528,7 @@
       </c>
       <c r="K229" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:00Z</t>
         </is>
       </c>
     </row>
@@ -11577,7 +11577,7 @@
       </c>
       <c r="K230" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:00Z</t>
         </is>
       </c>
     </row>
@@ -11626,7 +11626,7 @@
       </c>
       <c r="K231" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:00Z</t>
         </is>
       </c>
     </row>
@@ -11758,7 +11758,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:00Z</t>
         </is>
       </c>
     </row>
@@ -11804,7 +11804,7 @@
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>{"date": "2026-08-01", "year": 2026, "month": 8, "month_name": "Agosto", "index_value": 637409769724325.1, "monthly_variation_pct": 8.9, "unit": "Índice base diciembre 2007=100 y variación mensual %", "frequency": "monthly", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/precios_consumidor/4_5_7_2.xls", "fetched_at": "2026-09-26T23:03:46Z"}</t>
+          <t>{"date": "2026-08-01", "year": 2026, "month": 8, "month_name": "Agosto", "index_value": 637409769724325.1, "monthly_variation_pct": 8.9, "unit": "Índice base diciembre 2007=100 y variación mensual %", "frequency": "monthly", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/precios_consumidor/4_5_7_2.xls", "fetched_at": "2026-09-27T23:13:00Z"}</t>
         </is>
       </c>
     </row>

--- a/assets/data/bcv/excel/ove_bcv_inpc_nacional_mensual.xlsx
+++ b/assets/data/bcv/excel/ove_bcv_inpc_nacional_mensual.xlsx
@@ -650,7 +650,7 @@
       </c>
       <c r="K7" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:00Z</t>
+          <t>2026-09-29T00:28:21Z</t>
         </is>
       </c>
     </row>
@@ -699,7 +699,7 @@
       </c>
       <c r="K8" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:00Z</t>
+          <t>2026-09-29T00:28:21Z</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="K9" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:00Z</t>
+          <t>2026-09-29T00:28:21Z</t>
         </is>
       </c>
     </row>
@@ -797,7 +797,7 @@
       </c>
       <c r="K10" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:00Z</t>
+          <t>2026-09-29T00:28:21Z</t>
         </is>
       </c>
     </row>
@@ -846,7 +846,7 @@
       </c>
       <c r="K11" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:00Z</t>
+          <t>2026-09-29T00:28:21Z</t>
         </is>
       </c>
     </row>
@@ -895,7 +895,7 @@
       </c>
       <c r="K12" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:00Z</t>
+          <t>2026-09-29T00:28:21Z</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="K13" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:00Z</t>
+          <t>2026-09-29T00:28:21Z</t>
         </is>
       </c>
     </row>
@@ -993,7 +993,7 @@
       </c>
       <c r="K14" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:00Z</t>
+          <t>2026-09-29T00:28:21Z</t>
         </is>
       </c>
     </row>
@@ -1042,7 +1042,7 @@
       </c>
       <c r="K15" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:00Z</t>
+          <t>2026-09-29T00:28:21Z</t>
         </is>
       </c>
     </row>
@@ -1091,7 +1091,7 @@
       </c>
       <c r="K16" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:00Z</t>
+          <t>2026-09-29T00:28:21Z</t>
         </is>
       </c>
     </row>
@@ -1140,7 +1140,7 @@
       </c>
       <c r="K17" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:00Z</t>
+          <t>2026-09-29T00:28:21Z</t>
         </is>
       </c>
     </row>
@@ -1189,7 +1189,7 @@
       </c>
       <c r="K18" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:00Z</t>
+          <t>2026-09-29T00:28:21Z</t>
         </is>
       </c>
     </row>
@@ -1238,7 +1238,7 @@
       </c>
       <c r="K19" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:00Z</t>
+          <t>2026-09-29T00:28:21Z</t>
         </is>
       </c>
     </row>
@@ -1287,7 +1287,7 @@
       </c>
       <c r="K20" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:00Z</t>
+          <t>2026-09-29T00:28:21Z</t>
         </is>
       </c>
     </row>
@@ -1336,7 +1336,7 @@
       </c>
       <c r="K21" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:00Z</t>
+          <t>2026-09-29T00:28:21Z</t>
         </is>
       </c>
     </row>
@@ -1385,7 +1385,7 @@
       </c>
       <c r="K22" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:00Z</t>
+          <t>2026-09-29T00:28:21Z</t>
         </is>
       </c>
     </row>
@@ -1434,7 +1434,7 @@
       </c>
       <c r="K23" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:00Z</t>
+          <t>2026-09-29T00:28:21Z</t>
         </is>
       </c>
     </row>
@@ -1483,7 +1483,7 @@
       </c>
       <c r="K24" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:00Z</t>
+          <t>2026-09-29T00:28:21Z</t>
         </is>
       </c>
     </row>
@@ -1532,7 +1532,7 @@
       </c>
       <c r="K25" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:00Z</t>
+          <t>2026-09-29T00:28:21Z</t>
         </is>
       </c>
     </row>
@@ -1581,7 +1581,7 @@
       </c>
       <c r="K26" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:00Z</t>
+          <t>2026-09-29T00:28:21Z</t>
         </is>
       </c>
     </row>
@@ -1630,7 +1630,7 @@
       </c>
       <c r="K27" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:00Z</t>
+          <t>2026-09-29T00:28:21Z</t>
         </is>
       </c>
     </row>
@@ -1679,7 +1679,7 @@
       </c>
       <c r="K28" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:00Z</t>
+          <t>2026-09-29T00:28:21Z</t>
         </is>
       </c>
     </row>
@@ -1728,7 +1728,7 @@
       </c>
       <c r="K29" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:00Z</t>
+          <t>2026-09-29T00:28:21Z</t>
         </is>
       </c>
     </row>
@@ -1777,7 +1777,7 @@
       </c>
       <c r="K30" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:00Z</t>
+          <t>2026-09-29T00:28:21Z</t>
         </is>
       </c>
     </row>
@@ -1826,7 +1826,7 @@
       </c>
       <c r="K31" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:00Z</t>
+          <t>2026-09-29T00:28:21Z</t>
         </is>
       </c>
     </row>
@@ -1875,7 +1875,7 @@
       </c>
       <c r="K32" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:00Z</t>
+          <t>2026-09-29T00:28:21Z</t>
         </is>
       </c>
     </row>
@@ -1924,7 +1924,7 @@
       </c>
       <c r="K33" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:00Z</t>
+          <t>2026-09-29T00:28:21Z</t>
         </is>
       </c>
     </row>
@@ -1973,7 +1973,7 @@
       </c>
       <c r="K34" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:00Z</t>
+          <t>2026-09-29T00:28:21Z</t>
         </is>
       </c>
     </row>
@@ -2022,7 +2022,7 @@
       </c>
       <c r="K35" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:00Z</t>
+          <t>2026-09-29T00:28:21Z</t>
         </is>
       </c>
     </row>
@@ -2071,7 +2071,7 @@
       </c>
       <c r="K36" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:00Z</t>
+          <t>2026-09-29T00:28:21Z</t>
         </is>
       </c>
     </row>
@@ -2120,7 +2120,7 @@
       </c>
       <c r="K37" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:00Z</t>
+          <t>2026-09-29T00:28:21Z</t>
         </is>
       </c>
     </row>
@@ -2169,7 +2169,7 @@
       </c>
       <c r="K38" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:00Z</t>
+          <t>2026-09-29T00:28:21Z</t>
         </is>
       </c>
     </row>
@@ -2218,7 +2218,7 @@
       </c>
       <c r="K39" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:00Z</t>
+          <t>2026-09-29T00:28:21Z</t>
         </is>
       </c>
     </row>
@@ -2267,7 +2267,7 @@
       </c>
       <c r="K40" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:00Z</t>
+          <t>2026-09-29T00:28:21Z</t>
         </is>
       </c>
     </row>
@@ -2316,7 +2316,7 @@
       </c>
       <c r="K41" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:00Z</t>
+          <t>2026-09-29T00:28:21Z</t>
         </is>
       </c>
     </row>
@@ -2365,7 +2365,7 @@
       </c>
       <c r="K42" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:00Z</t>
+          <t>2026-09-29T00:28:21Z</t>
         </is>
       </c>
     </row>
@@ -2414,7 +2414,7 @@
       </c>
       <c r="K43" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:00Z</t>
+          <t>2026-09-29T00:28:21Z</t>
         </is>
       </c>
     </row>
@@ -2463,7 +2463,7 @@
       </c>
       <c r="K44" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:00Z</t>
+          <t>2026-09-29T00:28:21Z</t>
         </is>
       </c>
     </row>
@@ -2512,7 +2512,7 @@
       </c>
       <c r="K45" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:00Z</t>
+          <t>2026-09-29T00:28:21Z</t>
         </is>
       </c>
     </row>
@@ -2561,7 +2561,7 @@
       </c>
       <c r="K46" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:00Z</t>
+          <t>2026-09-29T00:28:21Z</t>
         </is>
       </c>
     </row>
@@ -2610,7 +2610,7 @@
       </c>
       <c r="K47" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:00Z</t>
+          <t>2026-09-29T00:28:21Z</t>
         </is>
       </c>
     </row>
@@ -2659,7 +2659,7 @@
       </c>
       <c r="K48" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:00Z</t>
+          <t>2026-09-29T00:28:21Z</t>
         </is>
       </c>
     </row>
@@ -2708,7 +2708,7 @@
       </c>
       <c r="K49" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:00Z</t>
+          <t>2026-09-29T00:28:21Z</t>
         </is>
       </c>
     </row>
@@ -2757,7 +2757,7 @@
       </c>
       <c r="K50" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:00Z</t>
+          <t>2026-09-29T00:28:21Z</t>
         </is>
       </c>
     </row>
@@ -2806,7 +2806,7 @@
       </c>
       <c r="K51" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:00Z</t>
+          <t>2026-09-29T00:28:21Z</t>
         </is>
       </c>
     </row>
@@ -2855,7 +2855,7 @@
       </c>
       <c r="K52" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:00Z</t>
+          <t>2026-09-29T00:28:21Z</t>
         </is>
       </c>
     </row>
@@ -2904,7 +2904,7 @@
       </c>
       <c r="K53" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:00Z</t>
+          <t>2026-09-29T00:28:21Z</t>
         </is>
       </c>
     </row>
@@ -2953,7 +2953,7 @@
       </c>
       <c r="K54" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:00Z</t>
+          <t>2026-09-29T00:28:21Z</t>
         </is>
       </c>
     </row>
@@ -3002,7 +3002,7 @@
       </c>
       <c r="K55" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:00Z</t>
+          <t>2026-09-29T00:28:21Z</t>
         </is>
       </c>
     </row>
@@ -3051,7 +3051,7 @@
       </c>
       <c r="K56" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:00Z</t>
+          <t>2026-09-29T00:28:21Z</t>
         </is>
       </c>
     </row>
@@ -3100,7 +3100,7 @@
       </c>
       <c r="K57" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:00Z</t>
+          <t>2026-09-29T00:28:21Z</t>
         </is>
       </c>
     </row>
@@ -3149,7 +3149,7 @@
       </c>
       <c r="K58" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:00Z</t>
+          <t>2026-09-29T00:28:21Z</t>
         </is>
       </c>
     </row>
@@ -3198,7 +3198,7 @@
       </c>
       <c r="K59" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:00Z</t>
+          <t>2026-09-29T00:28:21Z</t>
         </is>
       </c>
     </row>
@@ -3247,7 +3247,7 @@
       </c>
       <c r="K60" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:00Z</t>
+          <t>2026-09-29T00:28:21Z</t>
         </is>
       </c>
     </row>
@@ -3296,7 +3296,7 @@
       </c>
       <c r="K61" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:00Z</t>
+          <t>2026-09-29T00:28:21Z</t>
         </is>
       </c>
     </row>
@@ -3345,7 +3345,7 @@
       </c>
       <c r="K62" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:00Z</t>
+          <t>2026-09-29T00:28:21Z</t>
         </is>
       </c>
     </row>
@@ -3394,7 +3394,7 @@
       </c>
       <c r="K63" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:00Z</t>
+          <t>2026-09-29T00:28:21Z</t>
         </is>
       </c>
     </row>
@@ -3443,7 +3443,7 @@
       </c>
       <c r="K64" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:00Z</t>
+          <t>2026-09-29T00:28:21Z</t>
         </is>
       </c>
     </row>
@@ -3492,7 +3492,7 @@
       </c>
       <c r="K65" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:00Z</t>
+          <t>2026-09-29T00:28:21Z</t>
         </is>
       </c>
     </row>
@@ -3541,7 +3541,7 @@
       </c>
       <c r="K66" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:00Z</t>
+          <t>2026-09-29T00:28:21Z</t>
         </is>
       </c>
     </row>
@@ -3590,7 +3590,7 @@
       </c>
       <c r="K67" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:00Z</t>
+          <t>2026-09-29T00:28:21Z</t>
         </is>
       </c>
     </row>
@@ -3639,7 +3639,7 @@
       </c>
       <c r="K68" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:00Z</t>
+          <t>2026-09-29T00:28:21Z</t>
         </is>
       </c>
     </row>
@@ -3688,7 +3688,7 @@
       </c>
       <c r="K69" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:00Z</t>
+          <t>2026-09-29T00:28:21Z</t>
         </is>
       </c>
     </row>
@@ -3737,7 +3737,7 @@
       </c>
       <c r="K70" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:00Z</t>
+          <t>2026-09-29T00:28:21Z</t>
         </is>
       </c>
     </row>
@@ -3786,7 +3786,7 @@
       </c>
       <c r="K71" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:00Z</t>
+          <t>2026-09-29T00:28:21Z</t>
         </is>
       </c>
     </row>
@@ -3835,7 +3835,7 @@
       </c>
       <c r="K72" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:00Z</t>
+          <t>2026-09-29T00:28:21Z</t>
         </is>
       </c>
     </row>
@@ -3884,7 +3884,7 @@
       </c>
       <c r="K73" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:00Z</t>
+          <t>2026-09-29T00:28:21Z</t>
         </is>
       </c>
     </row>
@@ -3933,7 +3933,7 @@
       </c>
       <c r="K74" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:00Z</t>
+          <t>2026-09-29T00:28:21Z</t>
         </is>
       </c>
     </row>
@@ -3982,7 +3982,7 @@
       </c>
       <c r="K75" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:00Z</t>
+          <t>2026-09-29T00:28:21Z</t>
         </is>
       </c>
     </row>
@@ -4031,7 +4031,7 @@
       </c>
       <c r="K76" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:00Z</t>
+          <t>2026-09-29T00:28:21Z</t>
         </is>
       </c>
     </row>
@@ -4080,7 +4080,7 @@
       </c>
       <c r="K77" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:00Z</t>
+          <t>2026-09-29T00:28:21Z</t>
         </is>
       </c>
     </row>
@@ -4129,7 +4129,7 @@
       </c>
       <c r="K78" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:00Z</t>
+          <t>2026-09-29T00:28:21Z</t>
         </is>
       </c>
     </row>
@@ -4178,7 +4178,7 @@
       </c>
       <c r="K79" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:00Z</t>
+          <t>2026-09-29T00:28:21Z</t>
         </is>
       </c>
     </row>
@@ -4227,7 +4227,7 @@
       </c>
       <c r="K80" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:00Z</t>
+          <t>2026-09-29T00:28:21Z</t>
         </is>
       </c>
     </row>
@@ -4276,7 +4276,7 @@
       </c>
       <c r="K81" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:00Z</t>
+          <t>2026-09-29T00:28:21Z</t>
         </is>
       </c>
     </row>
@@ -4325,7 +4325,7 @@
       </c>
       <c r="K82" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:00Z</t>
+          <t>2026-09-29T00:28:21Z</t>
         </is>
       </c>
     </row>
@@ -4374,7 +4374,7 @@
       </c>
       <c r="K83" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:00Z</t>
+          <t>2026-09-29T00:28:21Z</t>
         </is>
       </c>
     </row>
@@ -4423,7 +4423,7 @@
       </c>
       <c r="K84" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:00Z</t>
+          <t>2026-09-29T00:28:21Z</t>
         </is>
       </c>
     </row>
@@ -4472,7 +4472,7 @@
       </c>
       <c r="K85" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:00Z</t>
+          <t>2026-09-29T00:28:21Z</t>
         </is>
       </c>
     </row>
@@ -4521,7 +4521,7 @@
       </c>
       <c r="K86" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:00Z</t>
+          <t>2026-09-29T00:28:21Z</t>
         </is>
       </c>
     </row>
@@ -4570,7 +4570,7 @@
       </c>
       <c r="K87" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:00Z</t>
+          <t>2026-09-29T00:28:21Z</t>
         </is>
       </c>
     </row>
@@ -4619,7 +4619,7 @@
       </c>
       <c r="K88" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:00Z</t>
+          <t>2026-09-29T00:28:21Z</t>
         </is>
       </c>
     </row>
@@ -4668,7 +4668,7 @@
       </c>
       <c r="K89" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:00Z</t>
+          <t>2026-09-29T00:28:21Z</t>
         </is>
       </c>
     </row>
@@ -4717,7 +4717,7 @@
       </c>
       <c r="K90" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:00Z</t>
+          <t>2026-09-29T00:28:21Z</t>
         </is>
       </c>
     </row>
@@ -4766,7 +4766,7 @@
       </c>
       <c r="K91" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:00Z</t>
+          <t>2026-09-29T00:28:21Z</t>
         </is>
       </c>
     </row>
@@ -4815,7 +4815,7 @@
       </c>
       <c r="K92" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:00Z</t>
+          <t>2026-09-29T00:28:21Z</t>
         </is>
       </c>
     </row>
@@ -4864,7 +4864,7 @@
       </c>
       <c r="K93" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:00Z</t>
+          <t>2026-09-29T00:28:21Z</t>
         </is>
       </c>
     </row>
@@ -4913,7 +4913,7 @@
       </c>
       <c r="K94" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:00Z</t>
+          <t>2026-09-29T00:28:21Z</t>
         </is>
       </c>
     </row>
@@ -4962,7 +4962,7 @@
       </c>
       <c r="K95" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:00Z</t>
+          <t>2026-09-29T00:28:21Z</t>
         </is>
       </c>
     </row>
@@ -5011,7 +5011,7 @@
       </c>
       <c r="K96" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:00Z</t>
+          <t>2026-09-29T00:28:21Z</t>
         </is>
       </c>
     </row>
@@ -5060,7 +5060,7 @@
       </c>
       <c r="K97" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:00Z</t>
+          <t>2026-09-29T00:28:21Z</t>
         </is>
       </c>
     </row>
@@ -5109,7 +5109,7 @@
       </c>
       <c r="K98" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:00Z</t>
+          <t>2026-09-29T00:28:21Z</t>
         </is>
       </c>
     </row>
@@ -5158,7 +5158,7 @@
       </c>
       <c r="K99" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:00Z</t>
+          <t>2026-09-29T00:28:21Z</t>
         </is>
       </c>
     </row>
@@ -5207,7 +5207,7 @@
       </c>
       <c r="K100" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:00Z</t>
+          <t>2026-09-29T00:28:21Z</t>
         </is>
       </c>
     </row>
@@ -5256,7 +5256,7 @@
       </c>
       <c r="K101" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:00Z</t>
+          <t>2026-09-29T00:28:21Z</t>
         </is>
       </c>
     </row>
@@ -5305,7 +5305,7 @@
       </c>
       <c r="K102" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:00Z</t>
+          <t>2026-09-29T00:28:21Z</t>
         </is>
       </c>
     </row>
@@ -5354,7 +5354,7 @@
       </c>
       <c r="K103" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:00Z</t>
+          <t>2026-09-29T00:28:21Z</t>
         </is>
       </c>
     </row>
@@ -5403,7 +5403,7 @@
       </c>
       <c r="K104" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:00Z</t>
+          <t>2026-09-29T00:28:21Z</t>
         </is>
       </c>
     </row>
@@ -5452,7 +5452,7 @@
       </c>
       <c r="K105" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:00Z</t>
+          <t>2026-09-29T00:28:21Z</t>
         </is>
       </c>
     </row>
@@ -5501,7 +5501,7 @@
       </c>
       <c r="K106" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:00Z</t>
+          <t>2026-09-29T00:28:21Z</t>
         </is>
       </c>
     </row>
@@ -5550,7 +5550,7 @@
       </c>
       <c r="K107" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:00Z</t>
+          <t>2026-09-29T00:28:21Z</t>
         </is>
       </c>
     </row>
@@ -5599,7 +5599,7 @@
       </c>
       <c r="K108" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:00Z</t>
+          <t>2026-09-29T00:28:21Z</t>
         </is>
       </c>
     </row>
@@ -5648,7 +5648,7 @@
       </c>
       <c r="K109" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:00Z</t>
+          <t>2026-09-29T00:28:21Z</t>
         </is>
       </c>
     </row>
@@ -5697,7 +5697,7 @@
       </c>
       <c r="K110" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:00Z</t>
+          <t>2026-09-29T00:28:21Z</t>
         </is>
       </c>
     </row>
@@ -5746,7 +5746,7 @@
       </c>
       <c r="K111" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:00Z</t>
+          <t>2026-09-29T00:28:21Z</t>
         </is>
       </c>
     </row>
@@ -5795,7 +5795,7 @@
       </c>
       <c r="K112" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:00Z</t>
+          <t>2026-09-29T00:28:21Z</t>
         </is>
       </c>
     </row>
@@ -5844,7 +5844,7 @@
       </c>
       <c r="K113" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:00Z</t>
+          <t>2026-09-29T00:28:21Z</t>
         </is>
       </c>
     </row>
@@ -5893,7 +5893,7 @@
       </c>
       <c r="K114" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:00Z</t>
+          <t>2026-09-29T00:28:21Z</t>
         </is>
       </c>
     </row>
@@ -5942,7 +5942,7 @@
       </c>
       <c r="K115" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:00Z</t>
+          <t>2026-09-29T00:28:21Z</t>
         </is>
       </c>
     </row>
@@ -5991,7 +5991,7 @@
       </c>
       <c r="K116" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:00Z</t>
+          <t>2026-09-29T00:28:21Z</t>
         </is>
       </c>
     </row>
@@ -6040,7 +6040,7 @@
       </c>
       <c r="K117" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:00Z</t>
+          <t>2026-09-29T00:28:21Z</t>
         </is>
       </c>
     </row>
@@ -6089,7 +6089,7 @@
       </c>
       <c r="K118" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:00Z</t>
+          <t>2026-09-29T00:28:21Z</t>
         </is>
       </c>
     </row>
@@ -6138,7 +6138,7 @@
       </c>
       <c r="K119" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:00Z</t>
+          <t>2026-09-29T00:28:21Z</t>
         </is>
       </c>
     </row>
@@ -6187,7 +6187,7 @@
       </c>
       <c r="K120" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:00Z</t>
+          <t>2026-09-29T00:28:21Z</t>
         </is>
       </c>
     </row>
@@ -6236,7 +6236,7 @@
       </c>
       <c r="K121" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:00Z</t>
+          <t>2026-09-29T00:28:21Z</t>
         </is>
       </c>
     </row>
@@ -6285,7 +6285,7 @@
       </c>
       <c r="K122" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:00Z</t>
+          <t>2026-09-29T00:28:21Z</t>
         </is>
       </c>
     </row>
@@ -6334,7 +6334,7 @@
       </c>
       <c r="K123" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:00Z</t>
+          <t>2026-09-29T00:28:21Z</t>
         </is>
       </c>
     </row>
@@ -6383,7 +6383,7 @@
       </c>
       <c r="K124" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:00Z</t>
+          <t>2026-09-29T00:28:21Z</t>
         </is>
       </c>
     </row>
@@ -6432,7 +6432,7 @@
       </c>
       <c r="K125" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:00Z</t>
+          <t>2026-09-29T00:28:21Z</t>
         </is>
       </c>
     </row>
@@ -6481,7 +6481,7 @@
       </c>
       <c r="K126" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:00Z</t>
+          <t>2026-09-29T00:28:21Z</t>
         </is>
       </c>
     </row>
@@ -6530,7 +6530,7 @@
       </c>
       <c r="K127" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:00Z</t>
+          <t>2026-09-29T00:28:21Z</t>
         </is>
       </c>
     </row>
@@ -6579,7 +6579,7 @@
       </c>
       <c r="K128" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:00Z</t>
+          <t>2026-09-29T00:28:21Z</t>
         </is>
       </c>
     </row>
@@ -6628,7 +6628,7 @@
       </c>
       <c r="K129" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:00Z</t>
+          <t>2026-09-29T00:28:21Z</t>
         </is>
       </c>
     </row>
@@ -6677,7 +6677,7 @@
       </c>
       <c r="K130" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:00Z</t>
+          <t>2026-09-29T00:28:21Z</t>
         </is>
       </c>
     </row>
@@ -6726,7 +6726,7 @@
       </c>
       <c r="K131" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:00Z</t>
+          <t>2026-09-29T00:28:21Z</t>
         </is>
       </c>
     </row>
@@ -6775,7 +6775,7 @@
       </c>
       <c r="K132" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:00Z</t>
+          <t>2026-09-29T00:28:21Z</t>
         </is>
       </c>
     </row>
@@ -6824,7 +6824,7 @@
       </c>
       <c r="K133" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:00Z</t>
+          <t>2026-09-29T00:28:21Z</t>
         </is>
       </c>
     </row>
@@ -6873,7 +6873,7 @@
       </c>
       <c r="K134" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:00Z</t>
+          <t>2026-09-29T00:28:21Z</t>
         </is>
       </c>
     </row>
@@ -6922,7 +6922,7 @@
       </c>
       <c r="K135" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:00Z</t>
+          <t>2026-09-29T00:28:21Z</t>
         </is>
       </c>
     </row>
@@ -6971,7 +6971,7 @@
       </c>
       <c r="K136" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:00Z</t>
+          <t>2026-09-29T00:28:21Z</t>
         </is>
       </c>
     </row>
@@ -7020,7 +7020,7 @@
       </c>
       <c r="K137" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:00Z</t>
+          <t>2026-09-29T00:28:21Z</t>
         </is>
       </c>
     </row>
@@ -7069,7 +7069,7 @@
       </c>
       <c r="K138" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:00Z</t>
+          <t>2026-09-29T00:28:21Z</t>
         </is>
       </c>
     </row>
@@ -7118,7 +7118,7 @@
       </c>
       <c r="K139" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:00Z</t>
+          <t>2026-09-29T00:28:21Z</t>
         </is>
       </c>
     </row>
@@ -7167,7 +7167,7 @@
       </c>
       <c r="K140" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:00Z</t>
+          <t>2026-09-29T00:28:21Z</t>
         </is>
       </c>
     </row>
@@ -7216,7 +7216,7 @@
       </c>
       <c r="K141" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:00Z</t>
+          <t>2026-09-29T00:28:21Z</t>
         </is>
       </c>
     </row>
@@ -7265,7 +7265,7 @@
       </c>
       <c r="K142" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:00Z</t>
+          <t>2026-09-29T00:28:21Z</t>
         </is>
       </c>
     </row>
@@ -7314,7 +7314,7 @@
       </c>
       <c r="K143" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:00Z</t>
+          <t>2026-09-29T00:28:21Z</t>
         </is>
       </c>
     </row>
@@ -7363,7 +7363,7 @@
       </c>
       <c r="K144" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:00Z</t>
+          <t>2026-09-29T00:28:21Z</t>
         </is>
       </c>
     </row>
@@ -7412,7 +7412,7 @@
       </c>
       <c r="K145" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:00Z</t>
+          <t>2026-09-29T00:28:21Z</t>
         </is>
       </c>
     </row>
@@ -7461,7 +7461,7 @@
       </c>
       <c r="K146" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:00Z</t>
+          <t>2026-09-29T00:28:21Z</t>
         </is>
       </c>
     </row>
@@ -7510,7 +7510,7 @@
       </c>
       <c r="K147" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:00Z</t>
+          <t>2026-09-29T00:28:21Z</t>
         </is>
       </c>
     </row>
@@ -7559,7 +7559,7 @@
       </c>
       <c r="K148" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:00Z</t>
+          <t>2026-09-29T00:28:21Z</t>
         </is>
       </c>
     </row>
@@ -7608,7 +7608,7 @@
       </c>
       <c r="K149" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:00Z</t>
+          <t>2026-09-29T00:28:21Z</t>
         </is>
       </c>
     </row>
@@ -7657,7 +7657,7 @@
       </c>
       <c r="K150" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:00Z</t>
+          <t>2026-09-29T00:28:21Z</t>
         </is>
       </c>
     </row>
@@ -7706,7 +7706,7 @@
       </c>
       <c r="K151" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:00Z</t>
+          <t>2026-09-29T00:28:21Z</t>
         </is>
       </c>
     </row>
@@ -7755,7 +7755,7 @@
       </c>
       <c r="K152" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:00Z</t>
+          <t>2026-09-29T00:28:21Z</t>
         </is>
       </c>
     </row>
@@ -7804,7 +7804,7 @@
       </c>
       <c r="K153" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:00Z</t>
+          <t>2026-09-29T00:28:21Z</t>
         </is>
       </c>
     </row>
@@ -7853,7 +7853,7 @@
       </c>
       <c r="K154" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:00Z</t>
+          <t>2026-09-29T00:28:21Z</t>
         </is>
       </c>
     </row>
@@ -7902,7 +7902,7 @@
       </c>
       <c r="K155" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:00Z</t>
+          <t>2026-09-29T00:28:21Z</t>
         </is>
       </c>
     </row>
@@ -7951,7 +7951,7 @@
       </c>
       <c r="K156" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:00Z</t>
+          <t>2026-09-29T00:28:21Z</t>
         </is>
       </c>
     </row>
@@ -8000,7 +8000,7 @@
       </c>
       <c r="K157" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:00Z</t>
+          <t>2026-09-29T00:28:21Z</t>
         </is>
       </c>
     </row>
@@ -8049,7 +8049,7 @@
       </c>
       <c r="K158" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:00Z</t>
+          <t>2026-09-29T00:28:21Z</t>
         </is>
       </c>
     </row>
@@ -8098,7 +8098,7 @@
       </c>
       <c r="K159" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:00Z</t>
+          <t>2026-09-29T00:28:21Z</t>
         </is>
       </c>
     </row>
@@ -8147,7 +8147,7 @@
       </c>
       <c r="K160" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:00Z</t>
+          <t>2026-09-29T00:28:21Z</t>
         </is>
       </c>
     </row>
@@ -8196,7 +8196,7 @@
       </c>
       <c r="K161" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:00Z</t>
+          <t>2026-09-29T00:28:21Z</t>
         </is>
       </c>
     </row>
@@ -8245,7 +8245,7 @@
       </c>
       <c r="K162" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:00Z</t>
+          <t>2026-09-29T00:28:21Z</t>
         </is>
       </c>
     </row>
@@ -8294,7 +8294,7 @@
       </c>
       <c r="K163" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:00Z</t>
+          <t>2026-09-29T00:28:21Z</t>
         </is>
       </c>
     </row>
@@ -8343,7 +8343,7 @@
       </c>
       <c r="K164" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:00Z</t>
+          <t>2026-09-29T00:28:21Z</t>
         </is>
       </c>
     </row>
@@ -8392,7 +8392,7 @@
       </c>
       <c r="K165" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:00Z</t>
+          <t>2026-09-29T00:28:21Z</t>
         </is>
       </c>
     </row>
@@ -8441,7 +8441,7 @@
       </c>
       <c r="K166" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:00Z</t>
+          <t>2026-09-29T00:28:21Z</t>
         </is>
       </c>
     </row>
@@ -8490,7 +8490,7 @@
       </c>
       <c r="K167" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:00Z</t>
+          <t>2026-09-29T00:28:21Z</t>
         </is>
       </c>
     </row>
@@ -8539,7 +8539,7 @@
       </c>
       <c r="K168" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:00Z</t>
+          <t>2026-09-29T00:28:21Z</t>
         </is>
       </c>
     </row>
@@ -8588,7 +8588,7 @@
       </c>
       <c r="K169" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:00Z</t>
+          <t>2026-09-29T00:28:21Z</t>
         </is>
       </c>
     </row>
@@ -8637,7 +8637,7 @@
       </c>
       <c r="K170" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:00Z</t>
+          <t>2026-09-29T00:28:21Z</t>
         </is>
       </c>
     </row>
@@ -8686,7 +8686,7 @@
       </c>
       <c r="K171" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:00Z</t>
+          <t>2026-09-29T00:28:21Z</t>
         </is>
       </c>
     </row>
@@ -8735,7 +8735,7 @@
       </c>
       <c r="K172" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:00Z</t>
+          <t>2026-09-29T00:28:21Z</t>
         </is>
       </c>
     </row>
@@ -8784,7 +8784,7 @@
       </c>
       <c r="K173" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:00Z</t>
+          <t>2026-09-29T00:28:21Z</t>
         </is>
       </c>
     </row>
@@ -8833,7 +8833,7 @@
       </c>
       <c r="K174" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:00Z</t>
+          <t>2026-09-29T00:28:21Z</t>
         </is>
       </c>
     </row>
@@ -8882,7 +8882,7 @@
       </c>
       <c r="K175" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:00Z</t>
+          <t>2026-09-29T00:28:21Z</t>
         </is>
       </c>
     </row>
@@ -8931,7 +8931,7 @@
       </c>
       <c r="K176" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:00Z</t>
+          <t>2026-09-29T00:28:21Z</t>
         </is>
       </c>
     </row>
@@ -8980,7 +8980,7 @@
       </c>
       <c r="K177" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:00Z</t>
+          <t>2026-09-29T00:28:21Z</t>
         </is>
       </c>
     </row>
@@ -9029,7 +9029,7 @@
       </c>
       <c r="K178" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:00Z</t>
+          <t>2026-09-29T00:28:21Z</t>
         </is>
       </c>
     </row>
@@ -9078,7 +9078,7 @@
       </c>
       <c r="K179" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:00Z</t>
+          <t>2026-09-29T00:28:21Z</t>
         </is>
       </c>
     </row>
@@ -9127,7 +9127,7 @@
       </c>
       <c r="K180" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:00Z</t>
+          <t>2026-09-29T00:28:21Z</t>
         </is>
       </c>
     </row>
@@ -9176,7 +9176,7 @@
       </c>
       <c r="K181" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:00Z</t>
+          <t>2026-09-29T00:28:21Z</t>
         </is>
       </c>
     </row>
@@ -9225,7 +9225,7 @@
       </c>
       <c r="K182" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:00Z</t>
+          <t>2026-09-29T00:28:21Z</t>
         </is>
       </c>
     </row>
@@ -9274,7 +9274,7 @@
       </c>
       <c r="K183" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:00Z</t>
+          <t>2026-09-29T00:28:21Z</t>
         </is>
       </c>
     </row>
@@ -9323,7 +9323,7 @@
       </c>
       <c r="K184" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:00Z</t>
+          <t>2026-09-29T00:28:21Z</t>
         </is>
       </c>
     </row>
@@ -9372,7 +9372,7 @@
       </c>
       <c r="K185" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:00Z</t>
+          <t>2026-09-29T00:28:21Z</t>
         </is>
       </c>
     </row>
@@ -9421,7 +9421,7 @@
       </c>
       <c r="K186" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:00Z</t>
+          <t>2026-09-29T00:28:21Z</t>
         </is>
       </c>
     </row>
@@ -9470,7 +9470,7 @@
       </c>
       <c r="K187" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:00Z</t>
+          <t>2026-09-29T00:28:21Z</t>
         </is>
       </c>
     </row>
@@ -9519,7 +9519,7 @@
       </c>
       <c r="K188" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:00Z</t>
+          <t>2026-09-29T00:28:21Z</t>
         </is>
       </c>
     </row>
@@ -9568,7 +9568,7 @@
       </c>
       <c r="K189" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:00Z</t>
+          <t>2026-09-29T00:28:21Z</t>
         </is>
       </c>
     </row>
@@ -9617,7 +9617,7 @@
       </c>
       <c r="K190" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:00Z</t>
+          <t>2026-09-29T00:28:21Z</t>
         </is>
       </c>
     </row>
@@ -9666,7 +9666,7 @@
       </c>
       <c r="K191" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:00Z</t>
+          <t>2026-09-29T00:28:21Z</t>
         </is>
       </c>
     </row>
@@ -9715,7 +9715,7 @@
       </c>
       <c r="K192" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:00Z</t>
+          <t>2026-09-29T00:28:21Z</t>
         </is>
       </c>
     </row>
@@ -9764,7 +9764,7 @@
       </c>
       <c r="K193" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:00Z</t>
+          <t>2026-09-29T00:28:21Z</t>
         </is>
       </c>
     </row>
@@ -9813,7 +9813,7 @@
       </c>
       <c r="K194" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:00Z</t>
+          <t>2026-09-29T00:28:21Z</t>
         </is>
       </c>
     </row>
@@ -9862,7 +9862,7 @@
       </c>
       <c r="K195" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:00Z</t>
+          <t>2026-09-29T00:28:21Z</t>
         </is>
       </c>
     </row>
@@ -9911,7 +9911,7 @@
       </c>
       <c r="K196" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:00Z</t>
+          <t>2026-09-29T00:28:21Z</t>
         </is>
       </c>
     </row>
@@ -9960,7 +9960,7 @@
       </c>
       <c r="K197" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:00Z</t>
+          <t>2026-09-29T00:28:21Z</t>
         </is>
       </c>
     </row>
@@ -10009,7 +10009,7 @@
       </c>
       <c r="K198" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:00Z</t>
+          <t>2026-09-29T00:28:21Z</t>
         </is>
       </c>
     </row>
@@ -10058,7 +10058,7 @@
       </c>
       <c r="K199" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:00Z</t>
+          <t>2026-09-29T00:28:21Z</t>
         </is>
       </c>
     </row>
@@ -10107,7 +10107,7 @@
       </c>
       <c r="K200" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:00Z</t>
+          <t>2026-09-29T00:28:21Z</t>
         </is>
       </c>
     </row>
@@ -10156,7 +10156,7 @@
       </c>
       <c r="K201" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:00Z</t>
+          <t>2026-09-29T00:28:21Z</t>
         </is>
       </c>
     </row>
@@ -10205,7 +10205,7 @@
       </c>
       <c r="K202" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:00Z</t>
+          <t>2026-09-29T00:28:21Z</t>
         </is>
       </c>
     </row>
@@ -10254,7 +10254,7 @@
       </c>
       <c r="K203" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:00Z</t>
+          <t>2026-09-29T00:28:21Z</t>
         </is>
       </c>
     </row>
@@ -10303,7 +10303,7 @@
       </c>
       <c r="K204" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:00Z</t>
+          <t>2026-09-29T00:28:21Z</t>
         </is>
       </c>
     </row>
@@ -10352,7 +10352,7 @@
       </c>
       <c r="K205" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:00Z</t>
+          <t>2026-09-29T00:28:21Z</t>
         </is>
       </c>
     </row>
@@ -10401,7 +10401,7 @@
       </c>
       <c r="K206" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:00Z</t>
+          <t>2026-09-29T00:28:21Z</t>
         </is>
       </c>
     </row>
@@ -10450,7 +10450,7 @@
       </c>
       <c r="K207" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:00Z</t>
+          <t>2026-09-29T00:28:21Z</t>
         </is>
       </c>
     </row>
@@ -10499,7 +10499,7 @@
       </c>
       <c r="K208" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:00Z</t>
+          <t>2026-09-29T00:28:21Z</t>
         </is>
       </c>
     </row>
@@ -10548,7 +10548,7 @@
       </c>
       <c r="K209" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:00Z</t>
+          <t>2026-09-29T00:28:21Z</t>
         </is>
       </c>
     </row>
@@ -10597,7 +10597,7 @@
       </c>
       <c r="K210" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:00Z</t>
+          <t>2026-09-29T00:28:21Z</t>
         </is>
       </c>
     </row>
@@ -10646,7 +10646,7 @@
       </c>
       <c r="K211" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:00Z</t>
+          <t>2026-09-29T00:28:21Z</t>
         </is>
       </c>
     </row>
@@ -10695,7 +10695,7 @@
       </c>
       <c r="K212" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:00Z</t>
+          <t>2026-09-29T00:28:21Z</t>
         </is>
       </c>
     </row>
@@ -10744,7 +10744,7 @@
       </c>
       <c r="K213" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:00Z</t>
+          <t>2026-09-29T00:28:21Z</t>
         </is>
       </c>
     </row>
@@ -10793,7 +10793,7 @@
       </c>
       <c r="K214" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:00Z</t>
+          <t>2026-09-29T00:28:21Z</t>
         </is>
       </c>
     </row>
@@ -10842,7 +10842,7 @@
       </c>
       <c r="K215" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:00Z</t>
+          <t>2026-09-29T00:28:21Z</t>
         </is>
       </c>
     </row>
@@ -10891,7 +10891,7 @@
       </c>
       <c r="K216" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:00Z</t>
+          <t>2026-09-29T00:28:21Z</t>
         </is>
       </c>
     </row>
@@ -10940,7 +10940,7 @@
       </c>
       <c r="K217" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:00Z</t>
+          <t>2026-09-29T00:28:21Z</t>
         </is>
       </c>
     </row>
@@ -10989,7 +10989,7 @@
       </c>
       <c r="K218" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:00Z</t>
+          <t>2026-09-29T00:28:21Z</t>
         </is>
       </c>
     </row>
@@ -11038,7 +11038,7 @@
       </c>
       <c r="K219" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:00Z</t>
+          <t>2026-09-29T00:28:21Z</t>
         </is>
       </c>
     </row>
@@ -11087,7 +11087,7 @@
       </c>
       <c r="K220" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:00Z</t>
+          <t>2026-09-29T00:28:21Z</t>
         </is>
       </c>
     </row>
@@ -11136,7 +11136,7 @@
       </c>
       <c r="K221" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:00Z</t>
+          <t>2026-09-29T00:28:21Z</t>
         </is>
       </c>
     </row>
@@ -11185,7 +11185,7 @@
       </c>
       <c r="K222" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:00Z</t>
+          <t>2026-09-29T00:28:21Z</t>
         </is>
       </c>
     </row>
@@ -11234,7 +11234,7 @@
       </c>
       <c r="K223" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:00Z</t>
+          <t>2026-09-29T00:28:21Z</t>
         </is>
       </c>
     </row>
@@ -11283,7 +11283,7 @@
       </c>
       <c r="K224" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:00Z</t>
+          <t>2026-09-29T00:28:21Z</t>
         </is>
       </c>
     </row>
@@ -11332,7 +11332,7 @@
       </c>
       <c r="K225" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:00Z</t>
+          <t>2026-09-29T00:28:21Z</t>
         </is>
       </c>
     </row>
@@ -11381,7 +11381,7 @@
       </c>
       <c r="K226" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:00Z</t>
+          <t>2026-09-29T00:28:21Z</t>
         </is>
       </c>
     </row>
@@ -11430,7 +11430,7 @@
       </c>
       <c r="K227" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:00Z</t>
+          <t>2026-09-29T00:28:21Z</t>
         </is>
       </c>
     </row>
@@ -11479,7 +11479,7 @@
       </c>
       <c r="K228" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:00Z</t>
+          <t>2026-09-29T00:28:21Z</t>
         </is>
       </c>
     </row>
@@ -11528,7 +11528,7 @@
       </c>
       <c r="K229" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:00Z</t>
+          <t>2026-09-29T00:28:21Z</t>
         </is>
       </c>
     </row>
@@ -11577,7 +11577,7 @@
       </c>
       <c r="K230" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:00Z</t>
+          <t>2026-09-29T00:28:21Z</t>
         </is>
       </c>
     </row>
@@ -11626,7 +11626,7 @@
       </c>
       <c r="K231" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:00Z</t>
+          <t>2026-09-29T00:28:21Z</t>
         </is>
       </c>
     </row>
@@ -11758,7 +11758,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:00Z</t>
+          <t>2026-09-29T00:28:21Z</t>
         </is>
       </c>
     </row>
@@ -11804,7 +11804,7 @@
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>{"date": "2026-08-01", "year": 2026, "month": 8, "month_name": "Agosto", "index_value": 637409769724325.1, "monthly_variation_pct": 8.9, "unit": "Índice base diciembre 2007=100 y variación mensual %", "frequency": "monthly", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/precios_consumidor/4_5_7_2.xls", "fetched_at": "2026-09-27T23:13:00Z"}</t>
+          <t>{"date": "2026-08-01", "year": 2026, "month": 8, "month_name": "Agosto", "index_value": 637409769724325.1, "monthly_variation_pct": 8.9, "unit": "Índice base diciembre 2007=100 y variación mensual %", "frequency": "monthly", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/precios_consumidor/4_5_7_2.xls", "fetched_at": "2026-09-29T00:28:21Z"}</t>
         </is>
       </c>
     </row>

--- a/assets/data/bcv/excel/ove_bcv_inpc_nacional_mensual.xlsx
+++ b/assets/data/bcv/excel/ove_bcv_inpc_nacional_mensual.xlsx
@@ -650,7 +650,7 @@
       </c>
       <c r="K7" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:21Z</t>
+          <t>2026-09-29T23:51:56Z</t>
         </is>
       </c>
     </row>
@@ -699,7 +699,7 @@
       </c>
       <c r="K8" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:21Z</t>
+          <t>2026-09-29T23:51:56Z</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="K9" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:21Z</t>
+          <t>2026-09-29T23:51:56Z</t>
         </is>
       </c>
     </row>
@@ -797,7 +797,7 @@
       </c>
       <c r="K10" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:21Z</t>
+          <t>2026-09-29T23:51:56Z</t>
         </is>
       </c>
     </row>
@@ -846,7 +846,7 @@
       </c>
       <c r="K11" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:21Z</t>
+          <t>2026-09-29T23:51:56Z</t>
         </is>
       </c>
     </row>
@@ -895,7 +895,7 @@
       </c>
       <c r="K12" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:21Z</t>
+          <t>2026-09-29T23:51:56Z</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="K13" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:21Z</t>
+          <t>2026-09-29T23:51:56Z</t>
         </is>
       </c>
     </row>
@@ -993,7 +993,7 @@
       </c>
       <c r="K14" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:21Z</t>
+          <t>2026-09-29T23:51:56Z</t>
         </is>
       </c>
     </row>
@@ -1042,7 +1042,7 @@
       </c>
       <c r="K15" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:21Z</t>
+          <t>2026-09-29T23:51:56Z</t>
         </is>
       </c>
     </row>
@@ -1091,7 +1091,7 @@
       </c>
       <c r="K16" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:21Z</t>
+          <t>2026-09-29T23:51:56Z</t>
         </is>
       </c>
     </row>
@@ -1140,7 +1140,7 @@
       </c>
       <c r="K17" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:21Z</t>
+          <t>2026-09-29T23:51:56Z</t>
         </is>
       </c>
     </row>
@@ -1189,7 +1189,7 @@
       </c>
       <c r="K18" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:21Z</t>
+          <t>2026-09-29T23:51:56Z</t>
         </is>
       </c>
     </row>
@@ -1238,7 +1238,7 @@
       </c>
       <c r="K19" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:21Z</t>
+          <t>2026-09-29T23:51:56Z</t>
         </is>
       </c>
     </row>
@@ -1287,7 +1287,7 @@
       </c>
       <c r="K20" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:21Z</t>
+          <t>2026-09-29T23:51:56Z</t>
         </is>
       </c>
     </row>
@@ -1336,7 +1336,7 @@
       </c>
       <c r="K21" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:21Z</t>
+          <t>2026-09-29T23:51:56Z</t>
         </is>
       </c>
     </row>
@@ -1385,7 +1385,7 @@
       </c>
       <c r="K22" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:21Z</t>
+          <t>2026-09-29T23:51:56Z</t>
         </is>
       </c>
     </row>
@@ -1434,7 +1434,7 @@
       </c>
       <c r="K23" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:21Z</t>
+          <t>2026-09-29T23:51:56Z</t>
         </is>
       </c>
     </row>
@@ -1483,7 +1483,7 @@
       </c>
       <c r="K24" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:21Z</t>
+          <t>2026-09-29T23:51:56Z</t>
         </is>
       </c>
     </row>
@@ -1532,7 +1532,7 @@
       </c>
       <c r="K25" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:21Z</t>
+          <t>2026-09-29T23:51:56Z</t>
         </is>
       </c>
     </row>
@@ -1581,7 +1581,7 @@
       </c>
       <c r="K26" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:21Z</t>
+          <t>2026-09-29T23:51:56Z</t>
         </is>
       </c>
     </row>
@@ -1630,7 +1630,7 @@
       </c>
       <c r="K27" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:21Z</t>
+          <t>2026-09-29T23:51:56Z</t>
         </is>
       </c>
     </row>
@@ -1679,7 +1679,7 @@
       </c>
       <c r="K28" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:21Z</t>
+          <t>2026-09-29T23:51:56Z</t>
         </is>
       </c>
     </row>
@@ -1728,7 +1728,7 @@
       </c>
       <c r="K29" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:21Z</t>
+          <t>2026-09-29T23:51:56Z</t>
         </is>
       </c>
     </row>
@@ -1777,7 +1777,7 @@
       </c>
       <c r="K30" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:21Z</t>
+          <t>2026-09-29T23:51:56Z</t>
         </is>
       </c>
     </row>
@@ -1826,7 +1826,7 @@
       </c>
       <c r="K31" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:21Z</t>
+          <t>2026-09-29T23:51:56Z</t>
         </is>
       </c>
     </row>
@@ -1875,7 +1875,7 @@
       </c>
       <c r="K32" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:21Z</t>
+          <t>2026-09-29T23:51:56Z</t>
         </is>
       </c>
     </row>
@@ -1924,7 +1924,7 @@
       </c>
       <c r="K33" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:21Z</t>
+          <t>2026-09-29T23:51:56Z</t>
         </is>
       </c>
     </row>
@@ -1973,7 +1973,7 @@
       </c>
       <c r="K34" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:21Z</t>
+          <t>2026-09-29T23:51:56Z</t>
         </is>
       </c>
     </row>
@@ -2022,7 +2022,7 @@
       </c>
       <c r="K35" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:21Z</t>
+          <t>2026-09-29T23:51:56Z</t>
         </is>
       </c>
     </row>
@@ -2071,7 +2071,7 @@
       </c>
       <c r="K36" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:21Z</t>
+          <t>2026-09-29T23:51:56Z</t>
         </is>
       </c>
     </row>
@@ -2120,7 +2120,7 @@
       </c>
       <c r="K37" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:21Z</t>
+          <t>2026-09-29T23:51:56Z</t>
         </is>
       </c>
     </row>
@@ -2169,7 +2169,7 @@
       </c>
       <c r="K38" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:21Z</t>
+          <t>2026-09-29T23:51:56Z</t>
         </is>
       </c>
     </row>
@@ -2218,7 +2218,7 @@
       </c>
       <c r="K39" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:21Z</t>
+          <t>2026-09-29T23:51:56Z</t>
         </is>
       </c>
     </row>
@@ -2267,7 +2267,7 @@
       </c>
       <c r="K40" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:21Z</t>
+          <t>2026-09-29T23:51:56Z</t>
         </is>
       </c>
     </row>
@@ -2316,7 +2316,7 @@
       </c>
       <c r="K41" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:21Z</t>
+          <t>2026-09-29T23:51:56Z</t>
         </is>
       </c>
     </row>
@@ -2365,7 +2365,7 @@
       </c>
       <c r="K42" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:21Z</t>
+          <t>2026-09-29T23:51:56Z</t>
         </is>
       </c>
     </row>
@@ -2414,7 +2414,7 @@
       </c>
       <c r="K43" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:21Z</t>
+          <t>2026-09-29T23:51:56Z</t>
         </is>
       </c>
     </row>
@@ -2463,7 +2463,7 @@
       </c>
       <c r="K44" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:21Z</t>
+          <t>2026-09-29T23:51:56Z</t>
         </is>
       </c>
     </row>
@@ -2512,7 +2512,7 @@
       </c>
       <c r="K45" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:21Z</t>
+          <t>2026-09-29T23:51:56Z</t>
         </is>
       </c>
     </row>
@@ -2561,7 +2561,7 @@
       </c>
       <c r="K46" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:21Z</t>
+          <t>2026-09-29T23:51:56Z</t>
         </is>
       </c>
     </row>
@@ -2610,7 +2610,7 @@
       </c>
       <c r="K47" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:21Z</t>
+          <t>2026-09-29T23:51:56Z</t>
         </is>
       </c>
     </row>
@@ -2659,7 +2659,7 @@
       </c>
       <c r="K48" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:21Z</t>
+          <t>2026-09-29T23:51:56Z</t>
         </is>
       </c>
     </row>
@@ -2708,7 +2708,7 @@
       </c>
       <c r="K49" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:21Z</t>
+          <t>2026-09-29T23:51:56Z</t>
         </is>
       </c>
     </row>
@@ -2757,7 +2757,7 @@
       </c>
       <c r="K50" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:21Z</t>
+          <t>2026-09-29T23:51:56Z</t>
         </is>
       </c>
     </row>
@@ -2806,7 +2806,7 @@
       </c>
       <c r="K51" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:21Z</t>
+          <t>2026-09-29T23:51:56Z</t>
         </is>
       </c>
     </row>
@@ -2855,7 +2855,7 @@
       </c>
       <c r="K52" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:21Z</t>
+          <t>2026-09-29T23:51:56Z</t>
         </is>
       </c>
     </row>
@@ -2904,7 +2904,7 @@
       </c>
       <c r="K53" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:21Z</t>
+          <t>2026-09-29T23:51:56Z</t>
         </is>
       </c>
     </row>
@@ -2953,7 +2953,7 @@
       </c>
       <c r="K54" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:21Z</t>
+          <t>2026-09-29T23:51:56Z</t>
         </is>
       </c>
     </row>
@@ -3002,7 +3002,7 @@
       </c>
       <c r="K55" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:21Z</t>
+          <t>2026-09-29T23:51:56Z</t>
         </is>
       </c>
     </row>
@@ -3051,7 +3051,7 @@
       </c>
       <c r="K56" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:21Z</t>
+          <t>2026-09-29T23:51:56Z</t>
         </is>
       </c>
     </row>
@@ -3100,7 +3100,7 @@
       </c>
       <c r="K57" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:21Z</t>
+          <t>2026-09-29T23:51:56Z</t>
         </is>
       </c>
     </row>
@@ -3149,7 +3149,7 @@
       </c>
       <c r="K58" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:21Z</t>
+          <t>2026-09-29T23:51:56Z</t>
         </is>
       </c>
     </row>
@@ -3198,7 +3198,7 @@
       </c>
       <c r="K59" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:21Z</t>
+          <t>2026-09-29T23:51:56Z</t>
         </is>
       </c>
     </row>
@@ -3247,7 +3247,7 @@
       </c>
       <c r="K60" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:21Z</t>
+          <t>2026-09-29T23:51:56Z</t>
         </is>
       </c>
     </row>
@@ -3296,7 +3296,7 @@
       </c>
       <c r="K61" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:21Z</t>
+          <t>2026-09-29T23:51:56Z</t>
         </is>
       </c>
     </row>
@@ -3345,7 +3345,7 @@
       </c>
       <c r="K62" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:21Z</t>
+          <t>2026-09-29T23:51:56Z</t>
         </is>
       </c>
     </row>
@@ -3394,7 +3394,7 @@
       </c>
       <c r="K63" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:21Z</t>
+          <t>2026-09-29T23:51:56Z</t>
         </is>
       </c>
     </row>
@@ -3443,7 +3443,7 @@
       </c>
       <c r="K64" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:21Z</t>
+          <t>2026-09-29T23:51:56Z</t>
         </is>
       </c>
     </row>
@@ -3492,7 +3492,7 @@
       </c>
       <c r="K65" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:21Z</t>
+          <t>2026-09-29T23:51:56Z</t>
         </is>
       </c>
     </row>
@@ -3541,7 +3541,7 @@
       </c>
       <c r="K66" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:21Z</t>
+          <t>2026-09-29T23:51:56Z</t>
         </is>
       </c>
     </row>
@@ -3590,7 +3590,7 @@
       </c>
       <c r="K67" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:21Z</t>
+          <t>2026-09-29T23:51:56Z</t>
         </is>
       </c>
     </row>
@@ -3639,7 +3639,7 @@
       </c>
       <c r="K68" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:21Z</t>
+          <t>2026-09-29T23:51:56Z</t>
         </is>
       </c>
     </row>
@@ -3688,7 +3688,7 @@
       </c>
       <c r="K69" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:21Z</t>
+          <t>2026-09-29T23:51:56Z</t>
         </is>
       </c>
     </row>
@@ -3737,7 +3737,7 @@
       </c>
       <c r="K70" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:21Z</t>
+          <t>2026-09-29T23:51:56Z</t>
         </is>
       </c>
     </row>
@@ -3786,7 +3786,7 @@
       </c>
       <c r="K71" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:21Z</t>
+          <t>2026-09-29T23:51:56Z</t>
         </is>
       </c>
     </row>
@@ -3835,7 +3835,7 @@
       </c>
       <c r="K72" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:21Z</t>
+          <t>2026-09-29T23:51:56Z</t>
         </is>
       </c>
     </row>
@@ -3884,7 +3884,7 @@
       </c>
       <c r="K73" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:21Z</t>
+          <t>2026-09-29T23:51:56Z</t>
         </is>
       </c>
     </row>
@@ -3933,7 +3933,7 @@
       </c>
       <c r="K74" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:21Z</t>
+          <t>2026-09-29T23:51:56Z</t>
         </is>
       </c>
     </row>
@@ -3982,7 +3982,7 @@
       </c>
       <c r="K75" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:21Z</t>
+          <t>2026-09-29T23:51:56Z</t>
         </is>
       </c>
     </row>
@@ -4031,7 +4031,7 @@
       </c>
       <c r="K76" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:21Z</t>
+          <t>2026-09-29T23:51:56Z</t>
         </is>
       </c>
     </row>
@@ -4080,7 +4080,7 @@
       </c>
       <c r="K77" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:21Z</t>
+          <t>2026-09-29T23:51:56Z</t>
         </is>
       </c>
     </row>
@@ -4129,7 +4129,7 @@
       </c>
       <c r="K78" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:21Z</t>
+          <t>2026-09-29T23:51:56Z</t>
         </is>
       </c>
     </row>
@@ -4178,7 +4178,7 @@
       </c>
       <c r="K79" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:21Z</t>
+          <t>2026-09-29T23:51:56Z</t>
         </is>
       </c>
     </row>
@@ -4227,7 +4227,7 @@
       </c>
       <c r="K80" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:21Z</t>
+          <t>2026-09-29T23:51:56Z</t>
         </is>
       </c>
     </row>
@@ -4276,7 +4276,7 @@
       </c>
       <c r="K81" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:21Z</t>
+          <t>2026-09-29T23:51:56Z</t>
         </is>
       </c>
     </row>
@@ -4325,7 +4325,7 @@
       </c>
       <c r="K82" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:21Z</t>
+          <t>2026-09-29T23:51:56Z</t>
         </is>
       </c>
     </row>
@@ -4374,7 +4374,7 @@
       </c>
       <c r="K83" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:21Z</t>
+          <t>2026-09-29T23:51:56Z</t>
         </is>
       </c>
     </row>
@@ -4423,7 +4423,7 @@
       </c>
       <c r="K84" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:21Z</t>
+          <t>2026-09-29T23:51:56Z</t>
         </is>
       </c>
     </row>
@@ -4472,7 +4472,7 @@
       </c>
       <c r="K85" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:21Z</t>
+          <t>2026-09-29T23:51:56Z</t>
         </is>
       </c>
     </row>
@@ -4521,7 +4521,7 @@
       </c>
       <c r="K86" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:21Z</t>
+          <t>2026-09-29T23:51:56Z</t>
         </is>
       </c>
     </row>
@@ -4570,7 +4570,7 @@
       </c>
       <c r="K87" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:21Z</t>
+          <t>2026-09-29T23:51:56Z</t>
         </is>
       </c>
     </row>
@@ -4619,7 +4619,7 @@
       </c>
       <c r="K88" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:21Z</t>
+          <t>2026-09-29T23:51:56Z</t>
         </is>
       </c>
     </row>
@@ -4668,7 +4668,7 @@
       </c>
       <c r="K89" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:21Z</t>
+          <t>2026-09-29T23:51:56Z</t>
         </is>
       </c>
     </row>
@@ -4717,7 +4717,7 @@
       </c>
       <c r="K90" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:21Z</t>
+          <t>2026-09-29T23:51:56Z</t>
         </is>
       </c>
     </row>
@@ -4766,7 +4766,7 @@
       </c>
       <c r="K91" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:21Z</t>
+          <t>2026-09-29T23:51:56Z</t>
         </is>
       </c>
     </row>
@@ -4815,7 +4815,7 @@
       </c>
       <c r="K92" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:21Z</t>
+          <t>2026-09-29T23:51:56Z</t>
         </is>
       </c>
     </row>
@@ -4864,7 +4864,7 @@
       </c>
       <c r="K93" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:21Z</t>
+          <t>2026-09-29T23:51:56Z</t>
         </is>
       </c>
     </row>
@@ -4913,7 +4913,7 @@
       </c>
       <c r="K94" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:21Z</t>
+          <t>2026-09-29T23:51:56Z</t>
         </is>
       </c>
     </row>
@@ -4962,7 +4962,7 @@
       </c>
       <c r="K95" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:21Z</t>
+          <t>2026-09-29T23:51:56Z</t>
         </is>
       </c>
     </row>
@@ -5011,7 +5011,7 @@
       </c>
       <c r="K96" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:21Z</t>
+          <t>2026-09-29T23:51:56Z</t>
         </is>
       </c>
     </row>
@@ -5060,7 +5060,7 @@
       </c>
       <c r="K97" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:21Z</t>
+          <t>2026-09-29T23:51:56Z</t>
         </is>
       </c>
     </row>
@@ -5109,7 +5109,7 @@
       </c>
       <c r="K98" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:21Z</t>
+          <t>2026-09-29T23:51:56Z</t>
         </is>
       </c>
     </row>
@@ -5158,7 +5158,7 @@
       </c>
       <c r="K99" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:21Z</t>
+          <t>2026-09-29T23:51:56Z</t>
         </is>
       </c>
     </row>
@@ -5207,7 +5207,7 @@
       </c>
       <c r="K100" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:21Z</t>
+          <t>2026-09-29T23:51:56Z</t>
         </is>
       </c>
     </row>
@@ -5256,7 +5256,7 @@
       </c>
       <c r="K101" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:21Z</t>
+          <t>2026-09-29T23:51:56Z</t>
         </is>
       </c>
     </row>
@@ -5305,7 +5305,7 @@
       </c>
       <c r="K102" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:21Z</t>
+          <t>2026-09-29T23:51:56Z</t>
         </is>
       </c>
     </row>
@@ -5354,7 +5354,7 @@
       </c>
       <c r="K103" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:21Z</t>
+          <t>2026-09-29T23:51:56Z</t>
         </is>
       </c>
     </row>
@@ -5403,7 +5403,7 @@
       </c>
       <c r="K104" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:21Z</t>
+          <t>2026-09-29T23:51:56Z</t>
         </is>
       </c>
     </row>
@@ -5452,7 +5452,7 @@
       </c>
       <c r="K105" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:21Z</t>
+          <t>2026-09-29T23:51:56Z</t>
         </is>
       </c>
     </row>
@@ -5501,7 +5501,7 @@
       </c>
       <c r="K106" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:21Z</t>
+          <t>2026-09-29T23:51:56Z</t>
         </is>
       </c>
     </row>
@@ -5550,7 +5550,7 @@
       </c>
       <c r="K107" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:21Z</t>
+          <t>2026-09-29T23:51:56Z</t>
         </is>
       </c>
     </row>
@@ -5599,7 +5599,7 @@
       </c>
       <c r="K108" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:21Z</t>
+          <t>2026-09-29T23:51:56Z</t>
         </is>
       </c>
     </row>
@@ -5648,7 +5648,7 @@
       </c>
       <c r="K109" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:21Z</t>
+          <t>2026-09-29T23:51:56Z</t>
         </is>
       </c>
     </row>
@@ -5697,7 +5697,7 @@
       </c>
       <c r="K110" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:21Z</t>
+          <t>2026-09-29T23:51:56Z</t>
         </is>
       </c>
     </row>
@@ -5746,7 +5746,7 @@
       </c>
       <c r="K111" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:21Z</t>
+          <t>2026-09-29T23:51:56Z</t>
         </is>
       </c>
     </row>
@@ -5795,7 +5795,7 @@
       </c>
       <c r="K112" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:21Z</t>
+          <t>2026-09-29T23:51:56Z</t>
         </is>
       </c>
     </row>
@@ -5844,7 +5844,7 @@
       </c>
       <c r="K113" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:21Z</t>
+          <t>2026-09-29T23:51:56Z</t>
         </is>
       </c>
     </row>
@@ -5893,7 +5893,7 @@
       </c>
       <c r="K114" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:21Z</t>
+          <t>2026-09-29T23:51:56Z</t>
         </is>
       </c>
     </row>
@@ -5942,7 +5942,7 @@
       </c>
       <c r="K115" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:21Z</t>
+          <t>2026-09-29T23:51:56Z</t>
         </is>
       </c>
     </row>
@@ -5991,7 +5991,7 @@
       </c>
       <c r="K116" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:21Z</t>
+          <t>2026-09-29T23:51:56Z</t>
         </is>
       </c>
     </row>
@@ -6040,7 +6040,7 @@
       </c>
       <c r="K117" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:21Z</t>
+          <t>2026-09-29T23:51:56Z</t>
         </is>
       </c>
     </row>
@@ -6089,7 +6089,7 @@
       </c>
       <c r="K118" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:21Z</t>
+          <t>2026-09-29T23:51:56Z</t>
         </is>
       </c>
     </row>
@@ -6138,7 +6138,7 @@
       </c>
       <c r="K119" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:21Z</t>
+          <t>2026-09-29T23:51:56Z</t>
         </is>
       </c>
     </row>
@@ -6187,7 +6187,7 @@
       </c>
       <c r="K120" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:21Z</t>
+          <t>2026-09-29T23:51:56Z</t>
         </is>
       </c>
     </row>
@@ -6236,7 +6236,7 @@
       </c>
       <c r="K121" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:21Z</t>
+          <t>2026-09-29T23:51:56Z</t>
         </is>
       </c>
     </row>
@@ -6285,7 +6285,7 @@
       </c>
       <c r="K122" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:21Z</t>
+          <t>2026-09-29T23:51:56Z</t>
         </is>
       </c>
     </row>
@@ -6334,7 +6334,7 @@
       </c>
       <c r="K123" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:21Z</t>
+          <t>2026-09-29T23:51:56Z</t>
         </is>
       </c>
     </row>
@@ -6383,7 +6383,7 @@
       </c>
       <c r="K124" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:21Z</t>
+          <t>2026-09-29T23:51:56Z</t>
         </is>
       </c>
     </row>
@@ -6432,7 +6432,7 @@
       </c>
       <c r="K125" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:21Z</t>
+          <t>2026-09-29T23:51:56Z</t>
         </is>
       </c>
     </row>
@@ -6481,7 +6481,7 @@
       </c>
       <c r="K126" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:21Z</t>
+          <t>2026-09-29T23:51:56Z</t>
         </is>
       </c>
     </row>
@@ -6530,7 +6530,7 @@
       </c>
       <c r="K127" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:21Z</t>
+          <t>2026-09-29T23:51:56Z</t>
         </is>
       </c>
     </row>
@@ -6579,7 +6579,7 @@
       </c>
       <c r="K128" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:21Z</t>
+          <t>2026-09-29T23:51:56Z</t>
         </is>
       </c>
     </row>
@@ -6628,7 +6628,7 @@
       </c>
       <c r="K129" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:21Z</t>
+          <t>2026-09-29T23:51:56Z</t>
         </is>
       </c>
     </row>
@@ -6677,7 +6677,7 @@
       </c>
       <c r="K130" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:21Z</t>
+          <t>2026-09-29T23:51:56Z</t>
         </is>
       </c>
     </row>
@@ -6726,7 +6726,7 @@
       </c>
       <c r="K131" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:21Z</t>
+          <t>2026-09-29T23:51:56Z</t>
         </is>
       </c>
     </row>
@@ -6775,7 +6775,7 @@
       </c>
       <c r="K132" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:21Z</t>
+          <t>2026-09-29T23:51:56Z</t>
         </is>
       </c>
     </row>
@@ -6824,7 +6824,7 @@
       </c>
       <c r="K133" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:21Z</t>
+          <t>2026-09-29T23:51:56Z</t>
         </is>
       </c>
     </row>
@@ -6873,7 +6873,7 @@
       </c>
       <c r="K134" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:21Z</t>
+          <t>2026-09-29T23:51:56Z</t>
         </is>
       </c>
     </row>
@@ -6922,7 +6922,7 @@
       </c>
       <c r="K135" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:21Z</t>
+          <t>2026-09-29T23:51:56Z</t>
         </is>
       </c>
     </row>
@@ -6971,7 +6971,7 @@
       </c>
       <c r="K136" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:21Z</t>
+          <t>2026-09-29T23:51:56Z</t>
         </is>
       </c>
     </row>
@@ -7020,7 +7020,7 @@
       </c>
       <c r="K137" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:21Z</t>
+          <t>2026-09-29T23:51:56Z</t>
         </is>
       </c>
     </row>
@@ -7069,7 +7069,7 @@
       </c>
       <c r="K138" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:21Z</t>
+          <t>2026-09-29T23:51:56Z</t>
         </is>
       </c>
     </row>
@@ -7118,7 +7118,7 @@
       </c>
       <c r="K139" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:21Z</t>
+          <t>2026-09-29T23:51:56Z</t>
         </is>
       </c>
     </row>
@@ -7167,7 +7167,7 @@
       </c>
       <c r="K140" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:21Z</t>
+          <t>2026-09-29T23:51:56Z</t>
         </is>
       </c>
     </row>
@@ -7216,7 +7216,7 @@
       </c>
       <c r="K141" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:21Z</t>
+          <t>2026-09-29T23:51:56Z</t>
         </is>
       </c>
     </row>
@@ -7265,7 +7265,7 @@
       </c>
       <c r="K142" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:21Z</t>
+          <t>2026-09-29T23:51:56Z</t>
         </is>
       </c>
     </row>
@@ -7314,7 +7314,7 @@
       </c>
       <c r="K143" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:21Z</t>
+          <t>2026-09-29T23:51:56Z</t>
         </is>
       </c>
     </row>
@@ -7363,7 +7363,7 @@
       </c>
       <c r="K144" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:21Z</t>
+          <t>2026-09-29T23:51:56Z</t>
         </is>
       </c>
     </row>
@@ -7412,7 +7412,7 @@
       </c>
       <c r="K145" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:21Z</t>
+          <t>2026-09-29T23:51:56Z</t>
         </is>
       </c>
     </row>
@@ -7461,7 +7461,7 @@
       </c>
       <c r="K146" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:21Z</t>
+          <t>2026-09-29T23:51:56Z</t>
         </is>
       </c>
     </row>
@@ -7510,7 +7510,7 @@
       </c>
       <c r="K147" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:21Z</t>
+          <t>2026-09-29T23:51:56Z</t>
         </is>
       </c>
     </row>
@@ -7559,7 +7559,7 @@
       </c>
       <c r="K148" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:21Z</t>
+          <t>2026-09-29T23:51:56Z</t>
         </is>
       </c>
     </row>
@@ -7608,7 +7608,7 @@
       </c>
       <c r="K149" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:21Z</t>
+          <t>2026-09-29T23:51:56Z</t>
         </is>
       </c>
     </row>
@@ -7657,7 +7657,7 @@
       </c>
       <c r="K150" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:21Z</t>
+          <t>2026-09-29T23:51:56Z</t>
         </is>
       </c>
     </row>
@@ -7706,7 +7706,7 @@
       </c>
       <c r="K151" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:21Z</t>
+          <t>2026-09-29T23:51:56Z</t>
         </is>
       </c>
     </row>
@@ -7755,7 +7755,7 @@
       </c>
       <c r="K152" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:21Z</t>
+          <t>2026-09-29T23:51:56Z</t>
         </is>
       </c>
     </row>
@@ -7804,7 +7804,7 @@
       </c>
       <c r="K153" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:21Z</t>
+          <t>2026-09-29T23:51:56Z</t>
         </is>
       </c>
     </row>
@@ -7853,7 +7853,7 @@
       </c>
       <c r="K154" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:21Z</t>
+          <t>2026-09-29T23:51:56Z</t>
         </is>
       </c>
     </row>
@@ -7902,7 +7902,7 @@
       </c>
       <c r="K155" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:21Z</t>
+          <t>2026-09-29T23:51:56Z</t>
         </is>
       </c>
     </row>
@@ -7951,7 +7951,7 @@
       </c>
       <c r="K156" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:21Z</t>
+          <t>2026-09-29T23:51:56Z</t>
         </is>
       </c>
     </row>
@@ -8000,7 +8000,7 @@
       </c>
       <c r="K157" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:21Z</t>
+          <t>2026-09-29T23:51:56Z</t>
         </is>
       </c>
     </row>
@@ -8049,7 +8049,7 @@
       </c>
       <c r="K158" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:21Z</t>
+          <t>2026-09-29T23:51:56Z</t>
         </is>
       </c>
     </row>
@@ -8098,7 +8098,7 @@
       </c>
       <c r="K159" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:21Z</t>
+          <t>2026-09-29T23:51:56Z</t>
         </is>
       </c>
     </row>
@@ -8147,7 +8147,7 @@
       </c>
       <c r="K160" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:21Z</t>
+          <t>2026-09-29T23:51:56Z</t>
         </is>
       </c>
     </row>
@@ -8196,7 +8196,7 @@
       </c>
       <c r="K161" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:21Z</t>
+          <t>2026-09-29T23:51:56Z</t>
         </is>
       </c>
     </row>
@@ -8245,7 +8245,7 @@
       </c>
       <c r="K162" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:21Z</t>
+          <t>2026-09-29T23:51:56Z</t>
         </is>
       </c>
     </row>
@@ -8294,7 +8294,7 @@
       </c>
       <c r="K163" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:21Z</t>
+          <t>2026-09-29T23:51:56Z</t>
         </is>
       </c>
     </row>
@@ -8343,7 +8343,7 @@
       </c>
       <c r="K164" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:21Z</t>
+          <t>2026-09-29T23:51:56Z</t>
         </is>
       </c>
     </row>
@@ -8392,7 +8392,7 @@
       </c>
       <c r="K165" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:21Z</t>
+          <t>2026-09-29T23:51:56Z</t>
         </is>
       </c>
     </row>
@@ -8441,7 +8441,7 @@
       </c>
       <c r="K166" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:21Z</t>
+          <t>2026-09-29T23:51:56Z</t>
         </is>
       </c>
     </row>
@@ -8490,7 +8490,7 @@
       </c>
       <c r="K167" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:21Z</t>
+          <t>2026-09-29T23:51:56Z</t>
         </is>
       </c>
     </row>
@@ -8539,7 +8539,7 @@
       </c>
       <c r="K168" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:21Z</t>
+          <t>2026-09-29T23:51:56Z</t>
         </is>
       </c>
     </row>
@@ -8588,7 +8588,7 @@
       </c>
       <c r="K169" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:21Z</t>
+          <t>2026-09-29T23:51:56Z</t>
         </is>
       </c>
     </row>
@@ -8637,7 +8637,7 @@
       </c>
       <c r="K170" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:21Z</t>
+          <t>2026-09-29T23:51:56Z</t>
         </is>
       </c>
     </row>
@@ -8686,7 +8686,7 @@
       </c>
       <c r="K171" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:21Z</t>
+          <t>2026-09-29T23:51:56Z</t>
         </is>
       </c>
     </row>
@@ -8735,7 +8735,7 @@
       </c>
       <c r="K172" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:21Z</t>
+          <t>2026-09-29T23:51:56Z</t>
         </is>
       </c>
     </row>
@@ -8784,7 +8784,7 @@
       </c>
       <c r="K173" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:21Z</t>
+          <t>2026-09-29T23:51:56Z</t>
         </is>
       </c>
     </row>
@@ -8833,7 +8833,7 @@
       </c>
       <c r="K174" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:21Z</t>
+          <t>2026-09-29T23:51:56Z</t>
         </is>
       </c>
     </row>
@@ -8882,7 +8882,7 @@
       </c>
       <c r="K175" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:21Z</t>
+          <t>2026-09-29T23:51:56Z</t>
         </is>
       </c>
     </row>
@@ -8931,7 +8931,7 @@
       </c>
       <c r="K176" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:21Z</t>
+          <t>2026-09-29T23:51:56Z</t>
         </is>
       </c>
     </row>
@@ -8980,7 +8980,7 @@
       </c>
       <c r="K177" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:21Z</t>
+          <t>2026-09-29T23:51:56Z</t>
         </is>
       </c>
     </row>
@@ -9029,7 +9029,7 @@
       </c>
       <c r="K178" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:21Z</t>
+          <t>2026-09-29T23:51:56Z</t>
         </is>
       </c>
     </row>
@@ -9078,7 +9078,7 @@
       </c>
       <c r="K179" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:21Z</t>
+          <t>2026-09-29T23:51:56Z</t>
         </is>
       </c>
     </row>
@@ -9127,7 +9127,7 @@
       </c>
       <c r="K180" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:21Z</t>
+          <t>2026-09-29T23:51:56Z</t>
         </is>
       </c>
     </row>
@@ -9176,7 +9176,7 @@
       </c>
       <c r="K181" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:21Z</t>
+          <t>2026-09-29T23:51:56Z</t>
         </is>
       </c>
     </row>
@@ -9225,7 +9225,7 @@
       </c>
       <c r="K182" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:21Z</t>
+          <t>2026-09-29T23:51:56Z</t>
         </is>
       </c>
     </row>
@@ -9274,7 +9274,7 @@
       </c>
       <c r="K183" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:21Z</t>
+          <t>2026-09-29T23:51:56Z</t>
         </is>
       </c>
     </row>
@@ -9323,7 +9323,7 @@
       </c>
       <c r="K184" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:21Z</t>
+          <t>2026-09-29T23:51:56Z</t>
         </is>
       </c>
     </row>
@@ -9372,7 +9372,7 @@
       </c>
       <c r="K185" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:21Z</t>
+          <t>2026-09-29T23:51:56Z</t>
         </is>
       </c>
     </row>
@@ -9421,7 +9421,7 @@
       </c>
       <c r="K186" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:21Z</t>
+          <t>2026-09-29T23:51:56Z</t>
         </is>
       </c>
     </row>
@@ -9470,7 +9470,7 @@
       </c>
       <c r="K187" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:21Z</t>
+          <t>2026-09-29T23:51:56Z</t>
         </is>
       </c>
     </row>
@@ -9519,7 +9519,7 @@
       </c>
       <c r="K188" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:21Z</t>
+          <t>2026-09-29T23:51:56Z</t>
         </is>
       </c>
     </row>
@@ -9568,7 +9568,7 @@
       </c>
       <c r="K189" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:21Z</t>
+          <t>2026-09-29T23:51:56Z</t>
         </is>
       </c>
     </row>
@@ -9617,7 +9617,7 @@
       </c>
       <c r="K190" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:21Z</t>
+          <t>2026-09-29T23:51:56Z</t>
         </is>
       </c>
     </row>
@@ -9666,7 +9666,7 @@
       </c>
       <c r="K191" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:21Z</t>
+          <t>2026-09-29T23:51:56Z</t>
         </is>
       </c>
     </row>
@@ -9715,7 +9715,7 @@
       </c>
       <c r="K192" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:21Z</t>
+          <t>2026-09-29T23:51:56Z</t>
         </is>
       </c>
     </row>
@@ -9764,7 +9764,7 @@
       </c>
       <c r="K193" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:21Z</t>
+          <t>2026-09-29T23:51:56Z</t>
         </is>
       </c>
     </row>
@@ -9813,7 +9813,7 @@
       </c>
       <c r="K194" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:21Z</t>
+          <t>2026-09-29T23:51:56Z</t>
         </is>
       </c>
     </row>
@@ -9862,7 +9862,7 @@
       </c>
       <c r="K195" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:21Z</t>
+          <t>2026-09-29T23:51:56Z</t>
         </is>
       </c>
     </row>
@@ -9911,7 +9911,7 @@
       </c>
       <c r="K196" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:21Z</t>
+          <t>2026-09-29T23:51:56Z</t>
         </is>
       </c>
     </row>
@@ -9960,7 +9960,7 @@
       </c>
       <c r="K197" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:21Z</t>
+          <t>2026-09-29T23:51:56Z</t>
         </is>
       </c>
     </row>
@@ -10009,7 +10009,7 @@
       </c>
       <c r="K198" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:21Z</t>
+          <t>2026-09-29T23:51:56Z</t>
         </is>
       </c>
     </row>
@@ -10058,7 +10058,7 @@
       </c>
       <c r="K199" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:21Z</t>
+          <t>2026-09-29T23:51:56Z</t>
         </is>
       </c>
     </row>
@@ -10107,7 +10107,7 @@
       </c>
       <c r="K200" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:21Z</t>
+          <t>2026-09-29T23:51:56Z</t>
         </is>
       </c>
     </row>
@@ -10156,7 +10156,7 @@
       </c>
       <c r="K201" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:21Z</t>
+          <t>2026-09-29T23:51:56Z</t>
         </is>
       </c>
     </row>
@@ -10205,7 +10205,7 @@
       </c>
       <c r="K202" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:21Z</t>
+          <t>2026-09-29T23:51:56Z</t>
         </is>
       </c>
     </row>
@@ -10254,7 +10254,7 @@
       </c>
       <c r="K203" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:21Z</t>
+          <t>2026-09-29T23:51:56Z</t>
         </is>
       </c>
     </row>
@@ -10303,7 +10303,7 @@
       </c>
       <c r="K204" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:21Z</t>
+          <t>2026-09-29T23:51:56Z</t>
         </is>
       </c>
     </row>
@@ -10352,7 +10352,7 @@
       </c>
       <c r="K205" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:21Z</t>
+          <t>2026-09-29T23:51:56Z</t>
         </is>
       </c>
     </row>
@@ -10401,7 +10401,7 @@
       </c>
       <c r="K206" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:21Z</t>
+          <t>2026-09-29T23:51:56Z</t>
         </is>
       </c>
     </row>
@@ -10450,7 +10450,7 @@
       </c>
       <c r="K207" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:21Z</t>
+          <t>2026-09-29T23:51:56Z</t>
         </is>
       </c>
     </row>
@@ -10499,7 +10499,7 @@
       </c>
       <c r="K208" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:21Z</t>
+          <t>2026-09-29T23:51:56Z</t>
         </is>
       </c>
     </row>
@@ -10548,7 +10548,7 @@
       </c>
       <c r="K209" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:21Z</t>
+          <t>2026-09-29T23:51:56Z</t>
         </is>
       </c>
     </row>
@@ -10597,7 +10597,7 @@
       </c>
       <c r="K210" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:21Z</t>
+          <t>2026-09-29T23:51:56Z</t>
         </is>
       </c>
     </row>
@@ -10646,7 +10646,7 @@
       </c>
       <c r="K211" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:21Z</t>
+          <t>2026-09-29T23:51:56Z</t>
         </is>
       </c>
     </row>
@@ -10695,7 +10695,7 @@
       </c>
       <c r="K212" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:21Z</t>
+          <t>2026-09-29T23:51:56Z</t>
         </is>
       </c>
     </row>
@@ -10744,7 +10744,7 @@
       </c>
       <c r="K213" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:21Z</t>
+          <t>2026-09-29T23:51:56Z</t>
         </is>
       </c>
     </row>
@@ -10793,7 +10793,7 @@
       </c>
       <c r="K214" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:21Z</t>
+          <t>2026-09-29T23:51:56Z</t>
         </is>
       </c>
     </row>
@@ -10842,7 +10842,7 @@
       </c>
       <c r="K215" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:21Z</t>
+          <t>2026-09-29T23:51:56Z</t>
         </is>
       </c>
     </row>
@@ -10891,7 +10891,7 @@
       </c>
       <c r="K216" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:21Z</t>
+          <t>2026-09-29T23:51:56Z</t>
         </is>
       </c>
     </row>
@@ -10940,7 +10940,7 @@
       </c>
       <c r="K217" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:21Z</t>
+          <t>2026-09-29T23:51:56Z</t>
         </is>
       </c>
     </row>
@@ -10989,7 +10989,7 @@
       </c>
       <c r="K218" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:21Z</t>
+          <t>2026-09-29T23:51:56Z</t>
         </is>
       </c>
     </row>
@@ -11038,7 +11038,7 @@
       </c>
       <c r="K219" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:21Z</t>
+          <t>2026-09-29T23:51:56Z</t>
         </is>
       </c>
     </row>
@@ -11087,7 +11087,7 @@
       </c>
       <c r="K220" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:21Z</t>
+          <t>2026-09-29T23:51:56Z</t>
         </is>
       </c>
     </row>
@@ -11136,7 +11136,7 @@
       </c>
       <c r="K221" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:21Z</t>
+          <t>2026-09-29T23:51:56Z</t>
         </is>
       </c>
     </row>
@@ -11185,7 +11185,7 @@
       </c>
       <c r="K222" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:21Z</t>
+          <t>2026-09-29T23:51:56Z</t>
         </is>
       </c>
     </row>
@@ -11234,7 +11234,7 @@
       </c>
       <c r="K223" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:21Z</t>
+          <t>2026-09-29T23:51:56Z</t>
         </is>
       </c>
     </row>
@@ -11283,7 +11283,7 @@
       </c>
       <c r="K224" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:21Z</t>
+          <t>2026-09-29T23:51:56Z</t>
         </is>
       </c>
     </row>
@@ -11332,7 +11332,7 @@
       </c>
       <c r="K225" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:21Z</t>
+          <t>2026-09-29T23:51:56Z</t>
         </is>
       </c>
     </row>
@@ -11381,7 +11381,7 @@
       </c>
       <c r="K226" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:21Z</t>
+          <t>2026-09-29T23:51:56Z</t>
         </is>
       </c>
     </row>
@@ -11430,7 +11430,7 @@
       </c>
       <c r="K227" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:21Z</t>
+          <t>2026-09-29T23:51:56Z</t>
         </is>
       </c>
     </row>
@@ -11479,7 +11479,7 @@
       </c>
       <c r="K228" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:21Z</t>
+          <t>2026-09-29T23:51:56Z</t>
         </is>
       </c>
     </row>
@@ -11528,7 +11528,7 @@
       </c>
       <c r="K229" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:21Z</t>
+          <t>2026-09-29T23:51:56Z</t>
         </is>
       </c>
     </row>
@@ -11577,7 +11577,7 @@
       </c>
       <c r="K230" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:21Z</t>
+          <t>2026-09-29T23:51:56Z</t>
         </is>
       </c>
     </row>
@@ -11626,7 +11626,7 @@
       </c>
       <c r="K231" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:21Z</t>
+          <t>2026-09-29T23:51:56Z</t>
         </is>
       </c>
     </row>
@@ -11758,7 +11758,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:21Z</t>
+          <t>2026-09-29T23:51:56Z</t>
         </is>
       </c>
     </row>
@@ -11804,7 +11804,7 @@
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>{"date": "2026-08-01", "year": 2026, "month": 8, "month_name": "Agosto", "index_value": 637409769724325.1, "monthly_variation_pct": 8.9, "unit": "Índice base diciembre 2007=100 y variación mensual %", "frequency": "monthly", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/precios_consumidor/4_5_7_2.xls", "fetched_at": "2026-09-29T00:28:21Z"}</t>
+          <t>{"date": "2026-08-01", "year": 2026, "month": 8, "month_name": "Agosto", "index_value": 637409769724325.1, "monthly_variation_pct": 8.9, "unit": "Índice base diciembre 2007=100 y variación mensual %", "frequency": "monthly", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/precios_consumidor/4_5_7_2.xls", "fetched_at": "2026-09-29T23:51:56Z"}</t>
         </is>
       </c>
     </row>

--- a/assets/data/bcv/excel/ove_bcv_inpc_nacional_mensual.xlsx
+++ b/assets/data/bcv/excel/ove_bcv_inpc_nacional_mensual.xlsx
@@ -650,7 +650,7 @@
       </c>
       <c r="K7" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:56Z</t>
+          <t>2026-10-01T00:02:18Z</t>
         </is>
       </c>
     </row>
@@ -699,7 +699,7 @@
       </c>
       <c r="K8" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:56Z</t>
+          <t>2026-10-01T00:02:18Z</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="K9" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:56Z</t>
+          <t>2026-10-01T00:02:18Z</t>
         </is>
       </c>
     </row>
@@ -797,7 +797,7 @@
       </c>
       <c r="K10" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:56Z</t>
+          <t>2026-10-01T00:02:18Z</t>
         </is>
       </c>
     </row>
@@ -846,7 +846,7 @@
       </c>
       <c r="K11" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:56Z</t>
+          <t>2026-10-01T00:02:18Z</t>
         </is>
       </c>
     </row>
@@ -895,7 +895,7 @@
       </c>
       <c r="K12" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:56Z</t>
+          <t>2026-10-01T00:02:18Z</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="K13" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:56Z</t>
+          <t>2026-10-01T00:02:18Z</t>
         </is>
       </c>
     </row>
@@ -993,7 +993,7 @@
       </c>
       <c r="K14" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:56Z</t>
+          <t>2026-10-01T00:02:18Z</t>
         </is>
       </c>
     </row>
@@ -1042,7 +1042,7 @@
       </c>
       <c r="K15" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:56Z</t>
+          <t>2026-10-01T00:02:18Z</t>
         </is>
       </c>
     </row>
@@ -1091,7 +1091,7 @@
       </c>
       <c r="K16" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:56Z</t>
+          <t>2026-10-01T00:02:18Z</t>
         </is>
       </c>
     </row>
@@ -1140,7 +1140,7 @@
       </c>
       <c r="K17" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:56Z</t>
+          <t>2026-10-01T00:02:18Z</t>
         </is>
       </c>
     </row>
@@ -1189,7 +1189,7 @@
       </c>
       <c r="K18" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:56Z</t>
+          <t>2026-10-01T00:02:18Z</t>
         </is>
       </c>
     </row>
@@ -1238,7 +1238,7 @@
       </c>
       <c r="K19" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:56Z</t>
+          <t>2026-10-01T00:02:18Z</t>
         </is>
       </c>
     </row>
@@ -1287,7 +1287,7 @@
       </c>
       <c r="K20" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:56Z</t>
+          <t>2026-10-01T00:02:18Z</t>
         </is>
       </c>
     </row>
@@ -1336,7 +1336,7 @@
       </c>
       <c r="K21" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:56Z</t>
+          <t>2026-10-01T00:02:18Z</t>
         </is>
       </c>
     </row>
@@ -1385,7 +1385,7 @@
       </c>
       <c r="K22" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:56Z</t>
+          <t>2026-10-01T00:02:18Z</t>
         </is>
       </c>
     </row>
@@ -1434,7 +1434,7 @@
       </c>
       <c r="K23" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:56Z</t>
+          <t>2026-10-01T00:02:18Z</t>
         </is>
       </c>
     </row>
@@ -1483,7 +1483,7 @@
       </c>
       <c r="K24" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:56Z</t>
+          <t>2026-10-01T00:02:18Z</t>
         </is>
       </c>
     </row>
@@ -1532,7 +1532,7 @@
       </c>
       <c r="K25" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:56Z</t>
+          <t>2026-10-01T00:02:18Z</t>
         </is>
       </c>
     </row>
@@ -1581,7 +1581,7 @@
       </c>
       <c r="K26" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:56Z</t>
+          <t>2026-10-01T00:02:18Z</t>
         </is>
       </c>
     </row>
@@ -1630,7 +1630,7 @@
       </c>
       <c r="K27" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:56Z</t>
+          <t>2026-10-01T00:02:18Z</t>
         </is>
       </c>
     </row>
@@ -1679,7 +1679,7 @@
       </c>
       <c r="K28" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:56Z</t>
+          <t>2026-10-01T00:02:18Z</t>
         </is>
       </c>
     </row>
@@ -1728,7 +1728,7 @@
       </c>
       <c r="K29" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:56Z</t>
+          <t>2026-10-01T00:02:18Z</t>
         </is>
       </c>
     </row>
@@ -1777,7 +1777,7 @@
       </c>
       <c r="K30" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:56Z</t>
+          <t>2026-10-01T00:02:18Z</t>
         </is>
       </c>
     </row>
@@ -1826,7 +1826,7 @@
       </c>
       <c r="K31" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:56Z</t>
+          <t>2026-10-01T00:02:18Z</t>
         </is>
       </c>
     </row>
@@ -1875,7 +1875,7 @@
       </c>
       <c r="K32" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:56Z</t>
+          <t>2026-10-01T00:02:18Z</t>
         </is>
       </c>
     </row>
@@ -1924,7 +1924,7 @@
       </c>
       <c r="K33" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:56Z</t>
+          <t>2026-10-01T00:02:18Z</t>
         </is>
       </c>
     </row>
@@ -1973,7 +1973,7 @@
       </c>
       <c r="K34" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:56Z</t>
+          <t>2026-10-01T00:02:18Z</t>
         </is>
       </c>
     </row>
@@ -2022,7 +2022,7 @@
       </c>
       <c r="K35" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:56Z</t>
+          <t>2026-10-01T00:02:18Z</t>
         </is>
       </c>
     </row>
@@ -2071,7 +2071,7 @@
       </c>
       <c r="K36" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:56Z</t>
+          <t>2026-10-01T00:02:18Z</t>
         </is>
       </c>
     </row>
@@ -2120,7 +2120,7 @@
       </c>
       <c r="K37" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:56Z</t>
+          <t>2026-10-01T00:02:18Z</t>
         </is>
       </c>
     </row>
@@ -2169,7 +2169,7 @@
       </c>
       <c r="K38" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:56Z</t>
+          <t>2026-10-01T00:02:18Z</t>
         </is>
       </c>
     </row>
@@ -2218,7 +2218,7 @@
       </c>
       <c r="K39" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:56Z</t>
+          <t>2026-10-01T00:02:18Z</t>
         </is>
       </c>
     </row>
@@ -2267,7 +2267,7 @@
       </c>
       <c r="K40" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:56Z</t>
+          <t>2026-10-01T00:02:18Z</t>
         </is>
       </c>
     </row>
@@ -2316,7 +2316,7 @@
       </c>
       <c r="K41" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:56Z</t>
+          <t>2026-10-01T00:02:18Z</t>
         </is>
       </c>
     </row>
@@ -2365,7 +2365,7 @@
       </c>
       <c r="K42" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:56Z</t>
+          <t>2026-10-01T00:02:18Z</t>
         </is>
       </c>
     </row>
@@ -2414,7 +2414,7 @@
       </c>
       <c r="K43" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:56Z</t>
+          <t>2026-10-01T00:02:18Z</t>
         </is>
       </c>
     </row>
@@ -2463,7 +2463,7 @@
       </c>
       <c r="K44" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:56Z</t>
+          <t>2026-10-01T00:02:18Z</t>
         </is>
       </c>
     </row>
@@ -2512,7 +2512,7 @@
       </c>
       <c r="K45" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:56Z</t>
+          <t>2026-10-01T00:02:18Z</t>
         </is>
       </c>
     </row>
@@ -2561,7 +2561,7 @@
       </c>
       <c r="K46" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:56Z</t>
+          <t>2026-10-01T00:02:18Z</t>
         </is>
       </c>
     </row>
@@ -2610,7 +2610,7 @@
       </c>
       <c r="K47" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:56Z</t>
+          <t>2026-10-01T00:02:18Z</t>
         </is>
       </c>
     </row>
@@ -2659,7 +2659,7 @@
       </c>
       <c r="K48" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:56Z</t>
+          <t>2026-10-01T00:02:18Z</t>
         </is>
       </c>
     </row>
@@ -2708,7 +2708,7 @@
       </c>
       <c r="K49" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:56Z</t>
+          <t>2026-10-01T00:02:18Z</t>
         </is>
       </c>
     </row>
@@ -2757,7 +2757,7 @@
       </c>
       <c r="K50" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:56Z</t>
+          <t>2026-10-01T00:02:18Z</t>
         </is>
       </c>
     </row>
@@ -2806,7 +2806,7 @@
       </c>
       <c r="K51" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:56Z</t>
+          <t>2026-10-01T00:02:18Z</t>
         </is>
       </c>
     </row>
@@ -2855,7 +2855,7 @@
       </c>
       <c r="K52" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:56Z</t>
+          <t>2026-10-01T00:02:18Z</t>
         </is>
       </c>
     </row>
@@ -2904,7 +2904,7 @@
       </c>
       <c r="K53" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:56Z</t>
+          <t>2026-10-01T00:02:18Z</t>
         </is>
       </c>
     </row>
@@ -2953,7 +2953,7 @@
       </c>
       <c r="K54" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:56Z</t>
+          <t>2026-10-01T00:02:18Z</t>
         </is>
       </c>
     </row>
@@ -3002,7 +3002,7 @@
       </c>
       <c r="K55" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:56Z</t>
+          <t>2026-10-01T00:02:18Z</t>
         </is>
       </c>
     </row>
@@ -3051,7 +3051,7 @@
       </c>
       <c r="K56" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:56Z</t>
+          <t>2026-10-01T00:02:18Z</t>
         </is>
       </c>
     </row>
@@ -3100,7 +3100,7 @@
       </c>
       <c r="K57" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:56Z</t>
+          <t>2026-10-01T00:02:18Z</t>
         </is>
       </c>
     </row>
@@ -3149,7 +3149,7 @@
       </c>
       <c r="K58" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:56Z</t>
+          <t>2026-10-01T00:02:18Z</t>
         </is>
       </c>
     </row>
@@ -3198,7 +3198,7 @@
       </c>
       <c r="K59" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:56Z</t>
+          <t>2026-10-01T00:02:18Z</t>
         </is>
       </c>
     </row>
@@ -3247,7 +3247,7 @@
       </c>
       <c r="K60" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:56Z</t>
+          <t>2026-10-01T00:02:18Z</t>
         </is>
       </c>
     </row>
@@ -3296,7 +3296,7 @@
       </c>
       <c r="K61" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:56Z</t>
+          <t>2026-10-01T00:02:18Z</t>
         </is>
       </c>
     </row>
@@ -3345,7 +3345,7 @@
       </c>
       <c r="K62" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:56Z</t>
+          <t>2026-10-01T00:02:18Z</t>
         </is>
       </c>
     </row>
@@ -3394,7 +3394,7 @@
       </c>
       <c r="K63" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:56Z</t>
+          <t>2026-10-01T00:02:18Z</t>
         </is>
       </c>
     </row>
@@ -3443,7 +3443,7 @@
       </c>
       <c r="K64" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:56Z</t>
+          <t>2026-10-01T00:02:18Z</t>
         </is>
       </c>
     </row>
@@ -3492,7 +3492,7 @@
       </c>
       <c r="K65" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:56Z</t>
+          <t>2026-10-01T00:02:18Z</t>
         </is>
       </c>
     </row>
@@ -3541,7 +3541,7 @@
       </c>
       <c r="K66" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:56Z</t>
+          <t>2026-10-01T00:02:18Z</t>
         </is>
       </c>
     </row>
@@ -3590,7 +3590,7 @@
       </c>
       <c r="K67" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:56Z</t>
+          <t>2026-10-01T00:02:18Z</t>
         </is>
       </c>
     </row>
@@ -3639,7 +3639,7 @@
       </c>
       <c r="K68" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:56Z</t>
+          <t>2026-10-01T00:02:18Z</t>
         </is>
       </c>
     </row>
@@ -3688,7 +3688,7 @@
       </c>
       <c r="K69" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:56Z</t>
+          <t>2026-10-01T00:02:18Z</t>
         </is>
       </c>
     </row>
@@ -3737,7 +3737,7 @@
       </c>
       <c r="K70" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:56Z</t>
+          <t>2026-10-01T00:02:18Z</t>
         </is>
       </c>
     </row>
@@ -3786,7 +3786,7 @@
       </c>
       <c r="K71" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:56Z</t>
+          <t>2026-10-01T00:02:18Z</t>
         </is>
       </c>
     </row>
@@ -3835,7 +3835,7 @@
       </c>
       <c r="K72" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:56Z</t>
+          <t>2026-10-01T00:02:18Z</t>
         </is>
       </c>
     </row>
@@ -3884,7 +3884,7 @@
       </c>
       <c r="K73" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:56Z</t>
+          <t>2026-10-01T00:02:18Z</t>
         </is>
       </c>
     </row>
@@ -3933,7 +3933,7 @@
       </c>
       <c r="K74" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:56Z</t>
+          <t>2026-10-01T00:02:18Z</t>
         </is>
       </c>
     </row>
@@ -3982,7 +3982,7 @@
       </c>
       <c r="K75" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:56Z</t>
+          <t>2026-10-01T00:02:18Z</t>
         </is>
       </c>
     </row>
@@ -4031,7 +4031,7 @@
       </c>
       <c r="K76" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:56Z</t>
+          <t>2026-10-01T00:02:18Z</t>
         </is>
       </c>
     </row>
@@ -4080,7 +4080,7 @@
       </c>
       <c r="K77" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:56Z</t>
+          <t>2026-10-01T00:02:18Z</t>
         </is>
       </c>
     </row>
@@ -4129,7 +4129,7 @@
       </c>
       <c r="K78" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:56Z</t>
+          <t>2026-10-01T00:02:18Z</t>
         </is>
       </c>
     </row>
@@ -4178,7 +4178,7 @@
       </c>
       <c r="K79" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:56Z</t>
+          <t>2026-10-01T00:02:18Z</t>
         </is>
       </c>
     </row>
@@ -4227,7 +4227,7 @@
       </c>
       <c r="K80" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:56Z</t>
+          <t>2026-10-01T00:02:18Z</t>
         </is>
       </c>
     </row>
@@ -4276,7 +4276,7 @@
       </c>
       <c r="K81" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:56Z</t>
+          <t>2026-10-01T00:02:18Z</t>
         </is>
       </c>
     </row>
@@ -4325,7 +4325,7 @@
       </c>
       <c r="K82" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:56Z</t>
+          <t>2026-10-01T00:02:18Z</t>
         </is>
       </c>
     </row>
@@ -4374,7 +4374,7 @@
       </c>
       <c r="K83" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:56Z</t>
+          <t>2026-10-01T00:02:18Z</t>
         </is>
       </c>
     </row>
@@ -4423,7 +4423,7 @@
       </c>
       <c r="K84" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:56Z</t>
+          <t>2026-10-01T00:02:18Z</t>
         </is>
       </c>
     </row>
@@ -4472,7 +4472,7 @@
       </c>
       <c r="K85" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:56Z</t>
+          <t>2026-10-01T00:02:18Z</t>
         </is>
       </c>
     </row>
@@ -4521,7 +4521,7 @@
       </c>
       <c r="K86" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:56Z</t>
+          <t>2026-10-01T00:02:18Z</t>
         </is>
       </c>
     </row>
@@ -4570,7 +4570,7 @@
       </c>
       <c r="K87" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:56Z</t>
+          <t>2026-10-01T00:02:18Z</t>
         </is>
       </c>
     </row>
@@ -4619,7 +4619,7 @@
       </c>
       <c r="K88" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:56Z</t>
+          <t>2026-10-01T00:02:18Z</t>
         </is>
       </c>
     </row>
@@ -4668,7 +4668,7 @@
       </c>
       <c r="K89" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:56Z</t>
+          <t>2026-10-01T00:02:18Z</t>
         </is>
       </c>
     </row>
@@ -4717,7 +4717,7 @@
       </c>
       <c r="K90" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:56Z</t>
+          <t>2026-10-01T00:02:18Z</t>
         </is>
       </c>
     </row>
@@ -4766,7 +4766,7 @@
       </c>
       <c r="K91" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:56Z</t>
+          <t>2026-10-01T00:02:18Z</t>
         </is>
       </c>
     </row>
@@ -4815,7 +4815,7 @@
       </c>
       <c r="K92" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:56Z</t>
+          <t>2026-10-01T00:02:18Z</t>
         </is>
       </c>
     </row>
@@ -4864,7 +4864,7 @@
       </c>
       <c r="K93" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:56Z</t>
+          <t>2026-10-01T00:02:18Z</t>
         </is>
       </c>
     </row>
@@ -4913,7 +4913,7 @@
       </c>
       <c r="K94" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:56Z</t>
+          <t>2026-10-01T00:02:18Z</t>
         </is>
       </c>
     </row>
@@ -4962,7 +4962,7 @@
       </c>
       <c r="K95" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:56Z</t>
+          <t>2026-10-01T00:02:18Z</t>
         </is>
       </c>
     </row>
@@ -5011,7 +5011,7 @@
       </c>
       <c r="K96" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:56Z</t>
+          <t>2026-10-01T00:02:18Z</t>
         </is>
       </c>
     </row>
@@ -5060,7 +5060,7 @@
       </c>
       <c r="K97" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:56Z</t>
+          <t>2026-10-01T00:02:18Z</t>
         </is>
       </c>
     </row>
@@ -5109,7 +5109,7 @@
       </c>
       <c r="K98" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:56Z</t>
+          <t>2026-10-01T00:02:18Z</t>
         </is>
       </c>
     </row>
@@ -5158,7 +5158,7 @@
       </c>
       <c r="K99" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:56Z</t>
+          <t>2026-10-01T00:02:18Z</t>
         </is>
       </c>
     </row>
@@ -5207,7 +5207,7 @@
       </c>
       <c r="K100" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:56Z</t>
+          <t>2026-10-01T00:02:18Z</t>
         </is>
       </c>
     </row>
@@ -5256,7 +5256,7 @@
       </c>
       <c r="K101" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:56Z</t>
+          <t>2026-10-01T00:02:18Z</t>
         </is>
       </c>
     </row>
@@ -5305,7 +5305,7 @@
       </c>
       <c r="K102" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:56Z</t>
+          <t>2026-10-01T00:02:18Z</t>
         </is>
       </c>
     </row>
@@ -5354,7 +5354,7 @@
       </c>
       <c r="K103" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:56Z</t>
+          <t>2026-10-01T00:02:18Z</t>
         </is>
       </c>
     </row>
@@ -5403,7 +5403,7 @@
       </c>
       <c r="K104" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:56Z</t>
+          <t>2026-10-01T00:02:18Z</t>
         </is>
       </c>
     </row>
@@ -5452,7 +5452,7 @@
       </c>
       <c r="K105" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:56Z</t>
+          <t>2026-10-01T00:02:18Z</t>
         </is>
       </c>
     </row>
@@ -5501,7 +5501,7 @@
       </c>
       <c r="K106" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:56Z</t>
+          <t>2026-10-01T00:02:18Z</t>
         </is>
       </c>
     </row>
@@ -5550,7 +5550,7 @@
       </c>
       <c r="K107" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:56Z</t>
+          <t>2026-10-01T00:02:18Z</t>
         </is>
       </c>
     </row>
@@ -5599,7 +5599,7 @@
       </c>
       <c r="K108" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:56Z</t>
+          <t>2026-10-01T00:02:18Z</t>
         </is>
       </c>
     </row>
@@ -5648,7 +5648,7 @@
       </c>
       <c r="K109" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:56Z</t>
+          <t>2026-10-01T00:02:18Z</t>
         </is>
       </c>
     </row>
@@ -5697,7 +5697,7 @@
       </c>
       <c r="K110" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:56Z</t>
+          <t>2026-10-01T00:02:18Z</t>
         </is>
       </c>
     </row>
@@ -5746,7 +5746,7 @@
       </c>
       <c r="K111" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:56Z</t>
+          <t>2026-10-01T00:02:18Z</t>
         </is>
       </c>
     </row>
@@ -5795,7 +5795,7 @@
       </c>
       <c r="K112" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:56Z</t>
+          <t>2026-10-01T00:02:18Z</t>
         </is>
       </c>
     </row>
@@ -5844,7 +5844,7 @@
       </c>
       <c r="K113" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:56Z</t>
+          <t>2026-10-01T00:02:18Z</t>
         </is>
       </c>
     </row>
@@ -5893,7 +5893,7 @@
       </c>
       <c r="K114" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:56Z</t>
+          <t>2026-10-01T00:02:18Z</t>
         </is>
       </c>
     </row>
@@ -5942,7 +5942,7 @@
       </c>
       <c r="K115" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:56Z</t>
+          <t>2026-10-01T00:02:18Z</t>
         </is>
       </c>
     </row>
@@ -5991,7 +5991,7 @@
       </c>
       <c r="K116" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:56Z</t>
+          <t>2026-10-01T00:02:18Z</t>
         </is>
       </c>
     </row>
@@ -6040,7 +6040,7 @@
       </c>
       <c r="K117" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:56Z</t>
+          <t>2026-10-01T00:02:18Z</t>
         </is>
       </c>
     </row>
@@ -6089,7 +6089,7 @@
       </c>
       <c r="K118" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:56Z</t>
+          <t>2026-10-01T00:02:18Z</t>
         </is>
       </c>
     </row>
@@ -6138,7 +6138,7 @@
       </c>
       <c r="K119" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:56Z</t>
+          <t>2026-10-01T00:02:18Z</t>
         </is>
       </c>
     </row>
@@ -6187,7 +6187,7 @@
       </c>
       <c r="K120" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:56Z</t>
+          <t>2026-10-01T00:02:18Z</t>
         </is>
       </c>
     </row>
@@ -6236,7 +6236,7 @@
       </c>
       <c r="K121" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:56Z</t>
+          <t>2026-10-01T00:02:18Z</t>
         </is>
       </c>
     </row>
@@ -6285,7 +6285,7 @@
       </c>
       <c r="K122" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:56Z</t>
+          <t>2026-10-01T00:02:18Z</t>
         </is>
       </c>
     </row>
@@ -6334,7 +6334,7 @@
       </c>
       <c r="K123" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:56Z</t>
+          <t>2026-10-01T00:02:18Z</t>
         </is>
       </c>
     </row>
@@ -6383,7 +6383,7 @@
       </c>
       <c r="K124" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:56Z</t>
+          <t>2026-10-01T00:02:18Z</t>
         </is>
       </c>
     </row>
@@ -6432,7 +6432,7 @@
       </c>
       <c r="K125" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:56Z</t>
+          <t>2026-10-01T00:02:18Z</t>
         </is>
       </c>
     </row>
@@ -6481,7 +6481,7 @@
       </c>
       <c r="K126" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:56Z</t>
+          <t>2026-10-01T00:02:18Z</t>
         </is>
       </c>
     </row>
@@ -6530,7 +6530,7 @@
       </c>
       <c r="K127" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:56Z</t>
+          <t>2026-10-01T00:02:18Z</t>
         </is>
       </c>
     </row>
@@ -6579,7 +6579,7 @@
       </c>
       <c r="K128" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:56Z</t>
+          <t>2026-10-01T00:02:18Z</t>
         </is>
       </c>
     </row>
@@ -6628,7 +6628,7 @@
       </c>
       <c r="K129" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:56Z</t>
+          <t>2026-10-01T00:02:18Z</t>
         </is>
       </c>
     </row>
@@ -6677,7 +6677,7 @@
       </c>
       <c r="K130" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:56Z</t>
+          <t>2026-10-01T00:02:18Z</t>
         </is>
       </c>
     </row>
@@ -6726,7 +6726,7 @@
       </c>
       <c r="K131" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:56Z</t>
+          <t>2026-10-01T00:02:18Z</t>
         </is>
       </c>
     </row>
@@ -6775,7 +6775,7 @@
       </c>
       <c r="K132" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:56Z</t>
+          <t>2026-10-01T00:02:18Z</t>
         </is>
       </c>
     </row>
@@ -6824,7 +6824,7 @@
       </c>
       <c r="K133" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:56Z</t>
+          <t>2026-10-01T00:02:18Z</t>
         </is>
       </c>
     </row>
@@ -6873,7 +6873,7 @@
       </c>
       <c r="K134" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:56Z</t>
+          <t>2026-10-01T00:02:18Z</t>
         </is>
       </c>
     </row>
@@ -6922,7 +6922,7 @@
       </c>
       <c r="K135" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:56Z</t>
+          <t>2026-10-01T00:02:18Z</t>
         </is>
       </c>
     </row>
@@ -6971,7 +6971,7 @@
       </c>
       <c r="K136" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:56Z</t>
+          <t>2026-10-01T00:02:18Z</t>
         </is>
       </c>
     </row>
@@ -7020,7 +7020,7 @@
       </c>
       <c r="K137" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:56Z</t>
+          <t>2026-10-01T00:02:18Z</t>
         </is>
       </c>
     </row>
@@ -7069,7 +7069,7 @@
       </c>
       <c r="K138" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:56Z</t>
+          <t>2026-10-01T00:02:18Z</t>
         </is>
       </c>
     </row>
@@ -7118,7 +7118,7 @@
       </c>
       <c r="K139" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:56Z</t>
+          <t>2026-10-01T00:02:18Z</t>
         </is>
       </c>
     </row>
@@ -7167,7 +7167,7 @@
       </c>
       <c r="K140" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:56Z</t>
+          <t>2026-10-01T00:02:18Z</t>
         </is>
       </c>
     </row>
@@ -7216,7 +7216,7 @@
       </c>
       <c r="K141" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:56Z</t>
+          <t>2026-10-01T00:02:18Z</t>
         </is>
       </c>
     </row>
@@ -7265,7 +7265,7 @@
       </c>
       <c r="K142" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:56Z</t>
+          <t>2026-10-01T00:02:18Z</t>
         </is>
       </c>
     </row>
@@ -7314,7 +7314,7 @@
       </c>
       <c r="K143" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:56Z</t>
+          <t>2026-10-01T00:02:18Z</t>
         </is>
       </c>
     </row>
@@ -7363,7 +7363,7 @@
       </c>
       <c r="K144" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:56Z</t>
+          <t>2026-10-01T00:02:18Z</t>
         </is>
       </c>
     </row>
@@ -7412,7 +7412,7 @@
       </c>
       <c r="K145" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:56Z</t>
+          <t>2026-10-01T00:02:18Z</t>
         </is>
       </c>
     </row>
@@ -7461,7 +7461,7 @@
       </c>
       <c r="K146" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:56Z</t>
+          <t>2026-10-01T00:02:18Z</t>
         </is>
       </c>
     </row>
@@ -7510,7 +7510,7 @@
       </c>
       <c r="K147" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:56Z</t>
+          <t>2026-10-01T00:02:18Z</t>
         </is>
       </c>
     </row>
@@ -7559,7 +7559,7 @@
       </c>
       <c r="K148" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:56Z</t>
+          <t>2026-10-01T00:02:18Z</t>
         </is>
       </c>
     </row>
@@ -7608,7 +7608,7 @@
       </c>
       <c r="K149" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:56Z</t>
+          <t>2026-10-01T00:02:18Z</t>
         </is>
       </c>
     </row>
@@ -7657,7 +7657,7 @@
       </c>
       <c r="K150" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:56Z</t>
+          <t>2026-10-01T00:02:18Z</t>
         </is>
       </c>
     </row>
@@ -7706,7 +7706,7 @@
       </c>
       <c r="K151" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:56Z</t>
+          <t>2026-10-01T00:02:18Z</t>
         </is>
       </c>
     </row>
@@ -7755,7 +7755,7 @@
       </c>
       <c r="K152" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:56Z</t>
+          <t>2026-10-01T00:02:18Z</t>
         </is>
       </c>
     </row>
@@ -7804,7 +7804,7 @@
       </c>
       <c r="K153" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:56Z</t>
+          <t>2026-10-01T00:02:18Z</t>
         </is>
       </c>
     </row>
@@ -7853,7 +7853,7 @@
       </c>
       <c r="K154" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:56Z</t>
+          <t>2026-10-01T00:02:18Z</t>
         </is>
       </c>
     </row>
@@ -7902,7 +7902,7 @@
       </c>
       <c r="K155" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:56Z</t>
+          <t>2026-10-01T00:02:18Z</t>
         </is>
       </c>
     </row>
@@ -7951,7 +7951,7 @@
       </c>
       <c r="K156" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:56Z</t>
+          <t>2026-10-01T00:02:18Z</t>
         </is>
       </c>
     </row>
@@ -8000,7 +8000,7 @@
       </c>
       <c r="K157" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:56Z</t>
+          <t>2026-10-01T00:02:18Z</t>
         </is>
       </c>
     </row>
@@ -8049,7 +8049,7 @@
       </c>
       <c r="K158" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:56Z</t>
+          <t>2026-10-01T00:02:18Z</t>
         </is>
       </c>
     </row>
@@ -8098,7 +8098,7 @@
       </c>
       <c r="K159" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:56Z</t>
+          <t>2026-10-01T00:02:18Z</t>
         </is>
       </c>
     </row>
@@ -8147,7 +8147,7 @@
       </c>
       <c r="K160" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:56Z</t>
+          <t>2026-10-01T00:02:18Z</t>
         </is>
       </c>
     </row>
@@ -8196,7 +8196,7 @@
       </c>
       <c r="K161" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:56Z</t>
+          <t>2026-10-01T00:02:18Z</t>
         </is>
       </c>
     </row>
@@ -8245,7 +8245,7 @@
       </c>
       <c r="K162" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:56Z</t>
+          <t>2026-10-01T00:02:18Z</t>
         </is>
       </c>
     </row>
@@ -8294,7 +8294,7 @@
       </c>
       <c r="K163" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:56Z</t>
+          <t>2026-10-01T00:02:18Z</t>
         </is>
       </c>
     </row>
@@ -8343,7 +8343,7 @@
       </c>
       <c r="K164" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:56Z</t>
+          <t>2026-10-01T00:02:18Z</t>
         </is>
       </c>
     </row>
@@ -8392,7 +8392,7 @@
       </c>
       <c r="K165" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:56Z</t>
+          <t>2026-10-01T00:02:18Z</t>
         </is>
       </c>
     </row>
@@ -8441,7 +8441,7 @@
       </c>
       <c r="K166" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:56Z</t>
+          <t>2026-10-01T00:02:18Z</t>
         </is>
       </c>
     </row>
@@ -8490,7 +8490,7 @@
       </c>
       <c r="K167" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:56Z</t>
+          <t>2026-10-01T00:02:18Z</t>
         </is>
       </c>
     </row>
@@ -8539,7 +8539,7 @@
       </c>
       <c r="K168" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:56Z</t>
+          <t>2026-10-01T00:02:18Z</t>
         </is>
       </c>
     </row>
@@ -8588,7 +8588,7 @@
       </c>
       <c r="K169" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:56Z</t>
+          <t>2026-10-01T00:02:18Z</t>
         </is>
       </c>
     </row>
@@ -8637,7 +8637,7 @@
       </c>
       <c r="K170" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:56Z</t>
+          <t>2026-10-01T00:02:18Z</t>
         </is>
       </c>
     </row>
@@ -8686,7 +8686,7 @@
       </c>
       <c r="K171" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:56Z</t>
+          <t>2026-10-01T00:02:18Z</t>
         </is>
       </c>
     </row>
@@ -8735,7 +8735,7 @@
       </c>
       <c r="K172" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:56Z</t>
+          <t>2026-10-01T00:02:18Z</t>
         </is>
       </c>
     </row>
@@ -8784,7 +8784,7 @@
       </c>
       <c r="K173" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:56Z</t>
+          <t>2026-10-01T00:02:18Z</t>
         </is>
       </c>
     </row>
@@ -8833,7 +8833,7 @@
       </c>
       <c r="K174" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:56Z</t>
+          <t>2026-10-01T00:02:18Z</t>
         </is>
       </c>
     </row>
@@ -8882,7 +8882,7 @@
       </c>
       <c r="K175" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:56Z</t>
+          <t>2026-10-01T00:02:18Z</t>
         </is>
       </c>
     </row>
@@ -8931,7 +8931,7 @@
       </c>
       <c r="K176" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:56Z</t>
+          <t>2026-10-01T00:02:18Z</t>
         </is>
       </c>
     </row>
@@ -8980,7 +8980,7 @@
       </c>
       <c r="K177" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:56Z</t>
+          <t>2026-10-01T00:02:18Z</t>
         </is>
       </c>
     </row>
@@ -9029,7 +9029,7 @@
       </c>
       <c r="K178" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:56Z</t>
+          <t>2026-10-01T00:02:18Z</t>
         </is>
       </c>
     </row>
@@ -9078,7 +9078,7 @@
       </c>
       <c r="K179" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:56Z</t>
+          <t>2026-10-01T00:02:18Z</t>
         </is>
       </c>
     </row>
@@ -9127,7 +9127,7 @@
       </c>
       <c r="K180" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:56Z</t>
+          <t>2026-10-01T00:02:18Z</t>
         </is>
       </c>
     </row>
@@ -9176,7 +9176,7 @@
       </c>
       <c r="K181" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:56Z</t>
+          <t>2026-10-01T00:02:18Z</t>
         </is>
       </c>
     </row>
@@ -9225,7 +9225,7 @@
       </c>
       <c r="K182" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:56Z</t>
+          <t>2026-10-01T00:02:18Z</t>
         </is>
       </c>
     </row>
@@ -9274,7 +9274,7 @@
       </c>
       <c r="K183" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:56Z</t>
+          <t>2026-10-01T00:02:18Z</t>
         </is>
       </c>
     </row>
@@ -9323,7 +9323,7 @@
       </c>
       <c r="K184" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:56Z</t>
+          <t>2026-10-01T00:02:18Z</t>
         </is>
       </c>
     </row>
@@ -9372,7 +9372,7 @@
       </c>
       <c r="K185" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:56Z</t>
+          <t>2026-10-01T00:02:18Z</t>
         </is>
       </c>
     </row>
@@ -9421,7 +9421,7 @@
       </c>
       <c r="K186" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:56Z</t>
+          <t>2026-10-01T00:02:18Z</t>
         </is>
       </c>
     </row>
@@ -9470,7 +9470,7 @@
       </c>
       <c r="K187" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:56Z</t>
+          <t>2026-10-01T00:02:18Z</t>
         </is>
       </c>
     </row>
@@ -9519,7 +9519,7 @@
       </c>
       <c r="K188" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:56Z</t>
+          <t>2026-10-01T00:02:18Z</t>
         </is>
       </c>
     </row>
@@ -9568,7 +9568,7 @@
       </c>
       <c r="K189" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:56Z</t>
+          <t>2026-10-01T00:02:18Z</t>
         </is>
       </c>
     </row>
@@ -9617,7 +9617,7 @@
       </c>
       <c r="K190" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:56Z</t>
+          <t>2026-10-01T00:02:18Z</t>
         </is>
       </c>
     </row>
@@ -9666,7 +9666,7 @@
       </c>
       <c r="K191" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:56Z</t>
+          <t>2026-10-01T00:02:18Z</t>
         </is>
       </c>
     </row>
@@ -9715,7 +9715,7 @@
       </c>
       <c r="K192" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:56Z</t>
+          <t>2026-10-01T00:02:18Z</t>
         </is>
       </c>
     </row>
@@ -9764,7 +9764,7 @@
       </c>
       <c r="K193" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:56Z</t>
+          <t>2026-10-01T00:02:18Z</t>
         </is>
       </c>
     </row>
@@ -9813,7 +9813,7 @@
       </c>
       <c r="K194" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:56Z</t>
+          <t>2026-10-01T00:02:18Z</t>
         </is>
       </c>
     </row>
@@ -9862,7 +9862,7 @@
       </c>
       <c r="K195" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:56Z</t>
+          <t>2026-10-01T00:02:18Z</t>
         </is>
       </c>
     </row>
@@ -9911,7 +9911,7 @@
       </c>
       <c r="K196" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:56Z</t>
+          <t>2026-10-01T00:02:18Z</t>
         </is>
       </c>
     </row>
@@ -9960,7 +9960,7 @@
       </c>
       <c r="K197" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:56Z</t>
+          <t>2026-10-01T00:02:18Z</t>
         </is>
       </c>
     </row>
@@ -10009,7 +10009,7 @@
       </c>
       <c r="K198" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:56Z</t>
+          <t>2026-10-01T00:02:18Z</t>
         </is>
       </c>
     </row>
@@ -10058,7 +10058,7 @@
       </c>
       <c r="K199" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:56Z</t>
+          <t>2026-10-01T00:02:18Z</t>
         </is>
       </c>
     </row>
@@ -10107,7 +10107,7 @@
       </c>
       <c r="K200" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:56Z</t>
+          <t>2026-10-01T00:02:18Z</t>
         </is>
       </c>
     </row>
@@ -10156,7 +10156,7 @@
       </c>
       <c r="K201" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:56Z</t>
+          <t>2026-10-01T00:02:18Z</t>
         </is>
       </c>
     </row>
@@ -10205,7 +10205,7 @@
       </c>
       <c r="K202" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:56Z</t>
+          <t>2026-10-01T00:02:18Z</t>
         </is>
       </c>
     </row>
@@ -10254,7 +10254,7 @@
       </c>
       <c r="K203" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:56Z</t>
+          <t>2026-10-01T00:02:18Z</t>
         </is>
       </c>
     </row>
@@ -10303,7 +10303,7 @@
       </c>
       <c r="K204" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:56Z</t>
+          <t>2026-10-01T00:02:18Z</t>
         </is>
       </c>
     </row>
@@ -10352,7 +10352,7 @@
       </c>
       <c r="K205" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:56Z</t>
+          <t>2026-10-01T00:02:18Z</t>
         </is>
       </c>
     </row>
@@ -10401,7 +10401,7 @@
       </c>
       <c r="K206" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:56Z</t>
+          <t>2026-10-01T00:02:18Z</t>
         </is>
       </c>
     </row>
@@ -10450,7 +10450,7 @@
       </c>
       <c r="K207" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:56Z</t>
+          <t>2026-10-01T00:02:18Z</t>
         </is>
       </c>
     </row>
@@ -10499,7 +10499,7 @@
       </c>
       <c r="K208" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:56Z</t>
+          <t>2026-10-01T00:02:18Z</t>
         </is>
       </c>
     </row>
@@ -10548,7 +10548,7 @@
       </c>
       <c r="K209" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:56Z</t>
+          <t>2026-10-01T00:02:18Z</t>
         </is>
       </c>
     </row>
@@ -10597,7 +10597,7 @@
       </c>
       <c r="K210" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:56Z</t>
+          <t>2026-10-01T00:02:18Z</t>
         </is>
       </c>
     </row>
@@ -10646,7 +10646,7 @@
       </c>
       <c r="K211" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:56Z</t>
+          <t>2026-10-01T00:02:18Z</t>
         </is>
       </c>
     </row>
@@ -10695,7 +10695,7 @@
       </c>
       <c r="K212" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:56Z</t>
+          <t>2026-10-01T00:02:18Z</t>
         </is>
       </c>
     </row>
@@ -10744,7 +10744,7 @@
       </c>
       <c r="K213" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:56Z</t>
+          <t>2026-10-01T00:02:18Z</t>
         </is>
       </c>
     </row>
@@ -10793,7 +10793,7 @@
       </c>
       <c r="K214" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:56Z</t>
+          <t>2026-10-01T00:02:18Z</t>
         </is>
       </c>
     </row>
@@ -10842,7 +10842,7 @@
       </c>
       <c r="K215" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:56Z</t>
+          <t>2026-10-01T00:02:18Z</t>
         </is>
       </c>
     </row>
@@ -10891,7 +10891,7 @@
       </c>
       <c r="K216" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:56Z</t>
+          <t>2026-10-01T00:02:18Z</t>
         </is>
       </c>
     </row>
@@ -10940,7 +10940,7 @@
       </c>
       <c r="K217" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:56Z</t>
+          <t>2026-10-01T00:02:18Z</t>
         </is>
       </c>
     </row>
@@ -10989,7 +10989,7 @@
       </c>
       <c r="K218" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:56Z</t>
+          <t>2026-10-01T00:02:18Z</t>
         </is>
       </c>
     </row>
@@ -11038,7 +11038,7 @@
       </c>
       <c r="K219" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:56Z</t>
+          <t>2026-10-01T00:02:18Z</t>
         </is>
       </c>
     </row>
@@ -11087,7 +11087,7 @@
       </c>
       <c r="K220" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:56Z</t>
+          <t>2026-10-01T00:02:18Z</t>
         </is>
       </c>
     </row>
@@ -11136,7 +11136,7 @@
       </c>
       <c r="K221" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:56Z</t>
+          <t>2026-10-01T00:02:18Z</t>
         </is>
       </c>
     </row>
@@ -11185,7 +11185,7 @@
       </c>
       <c r="K222" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:56Z</t>
+          <t>2026-10-01T00:02:18Z</t>
         </is>
       </c>
     </row>
@@ -11234,7 +11234,7 @@
       </c>
       <c r="K223" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:56Z</t>
+          <t>2026-10-01T00:02:18Z</t>
         </is>
       </c>
     </row>
@@ -11283,7 +11283,7 @@
       </c>
       <c r="K224" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:56Z</t>
+          <t>2026-10-01T00:02:18Z</t>
         </is>
       </c>
     </row>
@@ -11332,7 +11332,7 @@
       </c>
       <c r="K225" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:56Z</t>
+          <t>2026-10-01T00:02:18Z</t>
         </is>
       </c>
     </row>
@@ -11381,7 +11381,7 @@
       </c>
       <c r="K226" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:56Z</t>
+          <t>2026-10-01T00:02:18Z</t>
         </is>
       </c>
     </row>
@@ -11430,7 +11430,7 @@
       </c>
       <c r="K227" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:56Z</t>
+          <t>2026-10-01T00:02:18Z</t>
         </is>
       </c>
     </row>
@@ -11479,7 +11479,7 @@
       </c>
       <c r="K228" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:56Z</t>
+          <t>2026-10-01T00:02:18Z</t>
         </is>
       </c>
     </row>
@@ -11528,7 +11528,7 @@
       </c>
       <c r="K229" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:56Z</t>
+          <t>2026-10-01T00:02:18Z</t>
         </is>
       </c>
     </row>
@@ -11577,7 +11577,7 @@
       </c>
       <c r="K230" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:56Z</t>
+          <t>2026-10-01T00:02:18Z</t>
         </is>
       </c>
     </row>
@@ -11626,7 +11626,7 @@
       </c>
       <c r="K231" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:56Z</t>
+          <t>2026-10-01T00:02:18Z</t>
         </is>
       </c>
     </row>
@@ -11758,7 +11758,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:56Z</t>
+          <t>2026-10-01T00:02:18Z</t>
         </is>
       </c>
     </row>
@@ -11804,7 +11804,7 @@
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>{"date": "2026-08-01", "year": 2026, "month": 8, "month_name": "Agosto", "index_value": 637409769724325.1, "monthly_variation_pct": 8.9, "unit": "Índice base diciembre 2007=100 y variación mensual %", "frequency": "monthly", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/precios_consumidor/4_5_7_2.xls", "fetched_at": "2026-09-29T23:51:56Z"}</t>
+          <t>{"date": "2026-08-01", "year": 2026, "month": 8, "month_name": "Agosto", "index_value": 637409769724325.1, "monthly_variation_pct": 8.9, "unit": "Índice base diciembre 2007=100 y variación mensual %", "frequency": "monthly", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/precios_consumidor/4_5_7_2.xls", "fetched_at": "2026-10-01T00:02:18Z"}</t>
         </is>
       </c>
     </row>

--- a/assets/data/bcv/excel/ove_bcv_inpc_nacional_mensual.xlsx
+++ b/assets/data/bcv/excel/ove_bcv_inpc_nacional_mensual.xlsx
@@ -650,7 +650,7 @@
       </c>
       <c r="K7" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:18Z</t>
+          <t>2026-10-02T00:01:22Z</t>
         </is>
       </c>
     </row>
@@ -699,7 +699,7 @@
       </c>
       <c r="K8" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:18Z</t>
+          <t>2026-10-02T00:01:22Z</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="K9" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:18Z</t>
+          <t>2026-10-02T00:01:22Z</t>
         </is>
       </c>
     </row>
@@ -797,7 +797,7 @@
       </c>
       <c r="K10" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:18Z</t>
+          <t>2026-10-02T00:01:22Z</t>
         </is>
       </c>
     </row>
@@ -846,7 +846,7 @@
       </c>
       <c r="K11" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:18Z</t>
+          <t>2026-10-02T00:01:22Z</t>
         </is>
       </c>
     </row>
@@ -895,7 +895,7 @@
       </c>
       <c r="K12" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:18Z</t>
+          <t>2026-10-02T00:01:22Z</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="K13" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:18Z</t>
+          <t>2026-10-02T00:01:22Z</t>
         </is>
       </c>
     </row>
@@ -993,7 +993,7 @@
       </c>
       <c r="K14" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:18Z</t>
+          <t>2026-10-02T00:01:22Z</t>
         </is>
       </c>
     </row>
@@ -1042,7 +1042,7 @@
       </c>
       <c r="K15" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:18Z</t>
+          <t>2026-10-02T00:01:22Z</t>
         </is>
       </c>
     </row>
@@ -1091,7 +1091,7 @@
       </c>
       <c r="K16" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:18Z</t>
+          <t>2026-10-02T00:01:22Z</t>
         </is>
       </c>
     </row>
@@ -1140,7 +1140,7 @@
       </c>
       <c r="K17" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:18Z</t>
+          <t>2026-10-02T00:01:22Z</t>
         </is>
       </c>
     </row>
@@ -1189,7 +1189,7 @@
       </c>
       <c r="K18" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:18Z</t>
+          <t>2026-10-02T00:01:22Z</t>
         </is>
       </c>
     </row>
@@ -1238,7 +1238,7 @@
       </c>
       <c r="K19" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:18Z</t>
+          <t>2026-10-02T00:01:22Z</t>
         </is>
       </c>
     </row>
@@ -1287,7 +1287,7 @@
       </c>
       <c r="K20" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:18Z</t>
+          <t>2026-10-02T00:01:22Z</t>
         </is>
       </c>
     </row>
@@ -1336,7 +1336,7 @@
       </c>
       <c r="K21" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:18Z</t>
+          <t>2026-10-02T00:01:22Z</t>
         </is>
       </c>
     </row>
@@ -1385,7 +1385,7 @@
       </c>
       <c r="K22" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:18Z</t>
+          <t>2026-10-02T00:01:22Z</t>
         </is>
       </c>
     </row>
@@ -1434,7 +1434,7 @@
       </c>
       <c r="K23" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:18Z</t>
+          <t>2026-10-02T00:01:22Z</t>
         </is>
       </c>
     </row>
@@ -1483,7 +1483,7 @@
       </c>
       <c r="K24" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:18Z</t>
+          <t>2026-10-02T00:01:22Z</t>
         </is>
       </c>
     </row>
@@ -1532,7 +1532,7 @@
       </c>
       <c r="K25" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:18Z</t>
+          <t>2026-10-02T00:01:22Z</t>
         </is>
       </c>
     </row>
@@ -1581,7 +1581,7 @@
       </c>
       <c r="K26" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:18Z</t>
+          <t>2026-10-02T00:01:22Z</t>
         </is>
       </c>
     </row>
@@ -1630,7 +1630,7 @@
       </c>
       <c r="K27" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:18Z</t>
+          <t>2026-10-02T00:01:22Z</t>
         </is>
       </c>
     </row>
@@ -1679,7 +1679,7 @@
       </c>
       <c r="K28" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:18Z</t>
+          <t>2026-10-02T00:01:22Z</t>
         </is>
       </c>
     </row>
@@ -1728,7 +1728,7 @@
       </c>
       <c r="K29" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:18Z</t>
+          <t>2026-10-02T00:01:22Z</t>
         </is>
       </c>
     </row>
@@ -1777,7 +1777,7 @@
       </c>
       <c r="K30" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:18Z</t>
+          <t>2026-10-02T00:01:22Z</t>
         </is>
       </c>
     </row>
@@ -1826,7 +1826,7 @@
       </c>
       <c r="K31" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:18Z</t>
+          <t>2026-10-02T00:01:22Z</t>
         </is>
       </c>
     </row>
@@ -1875,7 +1875,7 @@
       </c>
       <c r="K32" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:18Z</t>
+          <t>2026-10-02T00:01:22Z</t>
         </is>
       </c>
     </row>
@@ -1924,7 +1924,7 @@
       </c>
       <c r="K33" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:18Z</t>
+          <t>2026-10-02T00:01:22Z</t>
         </is>
       </c>
     </row>
@@ -1973,7 +1973,7 @@
       </c>
       <c r="K34" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:18Z</t>
+          <t>2026-10-02T00:01:22Z</t>
         </is>
       </c>
     </row>
@@ -2022,7 +2022,7 @@
       </c>
       <c r="K35" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:18Z</t>
+          <t>2026-10-02T00:01:22Z</t>
         </is>
       </c>
     </row>
@@ -2071,7 +2071,7 @@
       </c>
       <c r="K36" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:18Z</t>
+          <t>2026-10-02T00:01:22Z</t>
         </is>
       </c>
     </row>
@@ -2120,7 +2120,7 @@
       </c>
       <c r="K37" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:18Z</t>
+          <t>2026-10-02T00:01:22Z</t>
         </is>
       </c>
     </row>
@@ -2169,7 +2169,7 @@
       </c>
       <c r="K38" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:18Z</t>
+          <t>2026-10-02T00:01:22Z</t>
         </is>
       </c>
     </row>
@@ -2218,7 +2218,7 @@
       </c>
       <c r="K39" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:18Z</t>
+          <t>2026-10-02T00:01:22Z</t>
         </is>
       </c>
     </row>
@@ -2267,7 +2267,7 @@
       </c>
       <c r="K40" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:18Z</t>
+          <t>2026-10-02T00:01:22Z</t>
         </is>
       </c>
     </row>
@@ -2316,7 +2316,7 @@
       </c>
       <c r="K41" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:18Z</t>
+          <t>2026-10-02T00:01:22Z</t>
         </is>
       </c>
     </row>
@@ -2365,7 +2365,7 @@
       </c>
       <c r="K42" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:18Z</t>
+          <t>2026-10-02T00:01:22Z</t>
         </is>
       </c>
     </row>
@@ -2414,7 +2414,7 @@
       </c>
       <c r="K43" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:18Z</t>
+          <t>2026-10-02T00:01:22Z</t>
         </is>
       </c>
     </row>
@@ -2463,7 +2463,7 @@
       </c>
       <c r="K44" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:18Z</t>
+          <t>2026-10-02T00:01:22Z</t>
         </is>
       </c>
     </row>
@@ -2512,7 +2512,7 @@
       </c>
       <c r="K45" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:18Z</t>
+          <t>2026-10-02T00:01:22Z</t>
         </is>
       </c>
     </row>
@@ -2561,7 +2561,7 @@
       </c>
       <c r="K46" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:18Z</t>
+          <t>2026-10-02T00:01:22Z</t>
         </is>
       </c>
     </row>
@@ -2610,7 +2610,7 @@
       </c>
       <c r="K47" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:18Z</t>
+          <t>2026-10-02T00:01:22Z</t>
         </is>
       </c>
     </row>
@@ -2659,7 +2659,7 @@
       </c>
       <c r="K48" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:18Z</t>
+          <t>2026-10-02T00:01:22Z</t>
         </is>
       </c>
     </row>
@@ -2708,7 +2708,7 @@
       </c>
       <c r="K49" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:18Z</t>
+          <t>2026-10-02T00:01:22Z</t>
         </is>
       </c>
     </row>
@@ -2757,7 +2757,7 @@
       </c>
       <c r="K50" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:18Z</t>
+          <t>2026-10-02T00:01:22Z</t>
         </is>
       </c>
     </row>
@@ -2806,7 +2806,7 @@
       </c>
       <c r="K51" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:18Z</t>
+          <t>2026-10-02T00:01:22Z</t>
         </is>
       </c>
     </row>
@@ -2855,7 +2855,7 @@
       </c>
       <c r="K52" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:18Z</t>
+          <t>2026-10-02T00:01:22Z</t>
         </is>
       </c>
     </row>
@@ -2904,7 +2904,7 @@
       </c>
       <c r="K53" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:18Z</t>
+          <t>2026-10-02T00:01:22Z</t>
         </is>
       </c>
     </row>
@@ -2953,7 +2953,7 @@
       </c>
       <c r="K54" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:18Z</t>
+          <t>2026-10-02T00:01:22Z</t>
         </is>
       </c>
     </row>
@@ -3002,7 +3002,7 @@
       </c>
       <c r="K55" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:18Z</t>
+          <t>2026-10-02T00:01:22Z</t>
         </is>
       </c>
     </row>
@@ -3051,7 +3051,7 @@
       </c>
       <c r="K56" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:18Z</t>
+          <t>2026-10-02T00:01:22Z</t>
         </is>
       </c>
     </row>
@@ -3100,7 +3100,7 @@
       </c>
       <c r="K57" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:18Z</t>
+          <t>2026-10-02T00:01:22Z</t>
         </is>
       </c>
     </row>
@@ -3149,7 +3149,7 @@
       </c>
       <c r="K58" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:18Z</t>
+          <t>2026-10-02T00:01:22Z</t>
         </is>
       </c>
     </row>
@@ -3198,7 +3198,7 @@
       </c>
       <c r="K59" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:18Z</t>
+          <t>2026-10-02T00:01:22Z</t>
         </is>
       </c>
     </row>
@@ -3247,7 +3247,7 @@
       </c>
       <c r="K60" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:18Z</t>
+          <t>2026-10-02T00:01:22Z</t>
         </is>
       </c>
     </row>
@@ -3296,7 +3296,7 @@
       </c>
       <c r="K61" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:18Z</t>
+          <t>2026-10-02T00:01:22Z</t>
         </is>
       </c>
     </row>
@@ -3345,7 +3345,7 @@
       </c>
       <c r="K62" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:18Z</t>
+          <t>2026-10-02T00:01:22Z</t>
         </is>
       </c>
     </row>
@@ -3394,7 +3394,7 @@
       </c>
       <c r="K63" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:18Z</t>
+          <t>2026-10-02T00:01:22Z</t>
         </is>
       </c>
     </row>
@@ -3443,7 +3443,7 @@
       </c>
       <c r="K64" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:18Z</t>
+          <t>2026-10-02T00:01:22Z</t>
         </is>
       </c>
     </row>
@@ -3492,7 +3492,7 @@
       </c>
       <c r="K65" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:18Z</t>
+          <t>2026-10-02T00:01:22Z</t>
         </is>
       </c>
     </row>
@@ -3541,7 +3541,7 @@
       </c>
       <c r="K66" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:18Z</t>
+          <t>2026-10-02T00:01:22Z</t>
         </is>
       </c>
     </row>
@@ -3590,7 +3590,7 @@
       </c>
       <c r="K67" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:18Z</t>
+          <t>2026-10-02T00:01:22Z</t>
         </is>
       </c>
     </row>
@@ -3639,7 +3639,7 @@
       </c>
       <c r="K68" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:18Z</t>
+          <t>2026-10-02T00:01:22Z</t>
         </is>
       </c>
     </row>
@@ -3688,7 +3688,7 @@
       </c>
       <c r="K69" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:18Z</t>
+          <t>2026-10-02T00:01:22Z</t>
         </is>
       </c>
     </row>
@@ -3737,7 +3737,7 @@
       </c>
       <c r="K70" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:18Z</t>
+          <t>2026-10-02T00:01:22Z</t>
         </is>
       </c>
     </row>
@@ -3786,7 +3786,7 @@
       </c>
       <c r="K71" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:18Z</t>
+          <t>2026-10-02T00:01:22Z</t>
         </is>
       </c>
     </row>
@@ -3835,7 +3835,7 @@
       </c>
       <c r="K72" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:18Z</t>
+          <t>2026-10-02T00:01:22Z</t>
         </is>
       </c>
     </row>
@@ -3884,7 +3884,7 @@
       </c>
       <c r="K73" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:18Z</t>
+          <t>2026-10-02T00:01:22Z</t>
         </is>
       </c>
     </row>
@@ -3933,7 +3933,7 @@
       </c>
       <c r="K74" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:18Z</t>
+          <t>2026-10-02T00:01:22Z</t>
         </is>
       </c>
     </row>
@@ -3982,7 +3982,7 @@
       </c>
       <c r="K75" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:18Z</t>
+          <t>2026-10-02T00:01:22Z</t>
         </is>
       </c>
     </row>
@@ -4031,7 +4031,7 @@
       </c>
       <c r="K76" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:18Z</t>
+          <t>2026-10-02T00:01:22Z</t>
         </is>
       </c>
     </row>
@@ -4080,7 +4080,7 @@
       </c>
       <c r="K77" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:18Z</t>
+          <t>2026-10-02T00:01:22Z</t>
         </is>
       </c>
     </row>
@@ -4129,7 +4129,7 @@
       </c>
       <c r="K78" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:18Z</t>
+          <t>2026-10-02T00:01:22Z</t>
         </is>
       </c>
     </row>
@@ -4178,7 +4178,7 @@
       </c>
       <c r="K79" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:18Z</t>
+          <t>2026-10-02T00:01:22Z</t>
         </is>
       </c>
     </row>
@@ -4227,7 +4227,7 @@
       </c>
       <c r="K80" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:18Z</t>
+          <t>2026-10-02T00:01:22Z</t>
         </is>
       </c>
     </row>
@@ -4276,7 +4276,7 @@
       </c>
       <c r="K81" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:18Z</t>
+          <t>2026-10-02T00:01:22Z</t>
         </is>
       </c>
     </row>
@@ -4325,7 +4325,7 @@
       </c>
       <c r="K82" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:18Z</t>
+          <t>2026-10-02T00:01:22Z</t>
         </is>
       </c>
     </row>
@@ -4374,7 +4374,7 @@
       </c>
       <c r="K83" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:18Z</t>
+          <t>2026-10-02T00:01:22Z</t>
         </is>
       </c>
     </row>
@@ -4423,7 +4423,7 @@
       </c>
       <c r="K84" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:18Z</t>
+          <t>2026-10-02T00:01:22Z</t>
         </is>
       </c>
     </row>
@@ -4472,7 +4472,7 @@
       </c>
       <c r="K85" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:18Z</t>
+          <t>2026-10-02T00:01:22Z</t>
         </is>
       </c>
     </row>
@@ -4521,7 +4521,7 @@
       </c>
       <c r="K86" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:18Z</t>
+          <t>2026-10-02T00:01:22Z</t>
         </is>
       </c>
     </row>
@@ -4570,7 +4570,7 @@
       </c>
       <c r="K87" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:18Z</t>
+          <t>2026-10-02T00:01:22Z</t>
         </is>
       </c>
     </row>
@@ -4619,7 +4619,7 @@
       </c>
       <c r="K88" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:18Z</t>
+          <t>2026-10-02T00:01:22Z</t>
         </is>
       </c>
     </row>
@@ -4668,7 +4668,7 @@
       </c>
       <c r="K89" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:18Z</t>
+          <t>2026-10-02T00:01:22Z</t>
         </is>
       </c>
     </row>
@@ -4717,7 +4717,7 @@
       </c>
       <c r="K90" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:18Z</t>
+          <t>2026-10-02T00:01:22Z</t>
         </is>
       </c>
     </row>
@@ -4766,7 +4766,7 @@
       </c>
       <c r="K91" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:18Z</t>
+          <t>2026-10-02T00:01:22Z</t>
         </is>
       </c>
     </row>
@@ -4815,7 +4815,7 @@
       </c>
       <c r="K92" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:18Z</t>
+          <t>2026-10-02T00:01:22Z</t>
         </is>
       </c>
     </row>
@@ -4864,7 +4864,7 @@
       </c>
       <c r="K93" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:18Z</t>
+          <t>2026-10-02T00:01:22Z</t>
         </is>
       </c>
     </row>
@@ -4913,7 +4913,7 @@
       </c>
       <c r="K94" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:18Z</t>
+          <t>2026-10-02T00:01:22Z</t>
         </is>
       </c>
     </row>
@@ -4962,7 +4962,7 @@
       </c>
       <c r="K95" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:18Z</t>
+          <t>2026-10-02T00:01:22Z</t>
         </is>
       </c>
     </row>
@@ -5011,7 +5011,7 @@
       </c>
       <c r="K96" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:18Z</t>
+          <t>2026-10-02T00:01:22Z</t>
         </is>
       </c>
     </row>
@@ -5060,7 +5060,7 @@
       </c>
       <c r="K97" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:18Z</t>
+          <t>2026-10-02T00:01:22Z</t>
         </is>
       </c>
     </row>
@@ -5109,7 +5109,7 @@
       </c>
       <c r="K98" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:18Z</t>
+          <t>2026-10-02T00:01:22Z</t>
         </is>
       </c>
     </row>
@@ -5158,7 +5158,7 @@
       </c>
       <c r="K99" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:18Z</t>
+          <t>2026-10-02T00:01:22Z</t>
         </is>
       </c>
     </row>
@@ -5207,7 +5207,7 @@
       </c>
       <c r="K100" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:18Z</t>
+          <t>2026-10-02T00:01:22Z</t>
         </is>
       </c>
     </row>
@@ -5256,7 +5256,7 @@
       </c>
       <c r="K101" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:18Z</t>
+          <t>2026-10-02T00:01:22Z</t>
         </is>
       </c>
     </row>
@@ -5305,7 +5305,7 @@
       </c>
       <c r="K102" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:18Z</t>
+          <t>2026-10-02T00:01:22Z</t>
         </is>
       </c>
     </row>
@@ -5354,7 +5354,7 @@
       </c>
       <c r="K103" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:18Z</t>
+          <t>2026-10-02T00:01:22Z</t>
         </is>
       </c>
     </row>
@@ -5403,7 +5403,7 @@
       </c>
       <c r="K104" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:18Z</t>
+          <t>2026-10-02T00:01:22Z</t>
         </is>
       </c>
     </row>
@@ -5452,7 +5452,7 @@
       </c>
       <c r="K105" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:18Z</t>
+          <t>2026-10-02T00:01:22Z</t>
         </is>
       </c>
     </row>
@@ -5501,7 +5501,7 @@
       </c>
       <c r="K106" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:18Z</t>
+          <t>2026-10-02T00:01:22Z</t>
         </is>
       </c>
     </row>
@@ -5550,7 +5550,7 @@
       </c>
       <c r="K107" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:18Z</t>
+          <t>2026-10-02T00:01:22Z</t>
         </is>
       </c>
     </row>
@@ -5599,7 +5599,7 @@
       </c>
       <c r="K108" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:18Z</t>
+          <t>2026-10-02T00:01:22Z</t>
         </is>
       </c>
     </row>
@@ -5648,7 +5648,7 @@
       </c>
       <c r="K109" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:18Z</t>
+          <t>2026-10-02T00:01:22Z</t>
         </is>
       </c>
     </row>
@@ -5697,7 +5697,7 @@
       </c>
       <c r="K110" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:18Z</t>
+          <t>2026-10-02T00:01:22Z</t>
         </is>
       </c>
     </row>
@@ -5746,7 +5746,7 @@
       </c>
       <c r="K111" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:18Z</t>
+          <t>2026-10-02T00:01:22Z</t>
         </is>
       </c>
     </row>
@@ -5795,7 +5795,7 @@
       </c>
       <c r="K112" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:18Z</t>
+          <t>2026-10-02T00:01:22Z</t>
         </is>
       </c>
     </row>
@@ -5844,7 +5844,7 @@
       </c>
       <c r="K113" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:18Z</t>
+          <t>2026-10-02T00:01:22Z</t>
         </is>
       </c>
     </row>
@@ -5893,7 +5893,7 @@
       </c>
       <c r="K114" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:18Z</t>
+          <t>2026-10-02T00:01:22Z</t>
         </is>
       </c>
     </row>
@@ -5942,7 +5942,7 @@
       </c>
       <c r="K115" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:18Z</t>
+          <t>2026-10-02T00:01:22Z</t>
         </is>
       </c>
     </row>
@@ -5991,7 +5991,7 @@
       </c>
       <c r="K116" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:18Z</t>
+          <t>2026-10-02T00:01:22Z</t>
         </is>
       </c>
     </row>
@@ -6040,7 +6040,7 @@
       </c>
       <c r="K117" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:18Z</t>
+          <t>2026-10-02T00:01:22Z</t>
         </is>
       </c>
     </row>
@@ -6089,7 +6089,7 @@
       </c>
       <c r="K118" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:18Z</t>
+          <t>2026-10-02T00:01:22Z</t>
         </is>
       </c>
     </row>
@@ -6138,7 +6138,7 @@
       </c>
       <c r="K119" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:18Z</t>
+          <t>2026-10-02T00:01:22Z</t>
         </is>
       </c>
     </row>
@@ -6187,7 +6187,7 @@
       </c>
       <c r="K120" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:18Z</t>
+          <t>2026-10-02T00:01:22Z</t>
         </is>
       </c>
     </row>
@@ -6236,7 +6236,7 @@
       </c>
       <c r="K121" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:18Z</t>
+          <t>2026-10-02T00:01:22Z</t>
         </is>
       </c>
     </row>
@@ -6285,7 +6285,7 @@
       </c>
       <c r="K122" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:18Z</t>
+          <t>2026-10-02T00:01:22Z</t>
         </is>
       </c>
     </row>
@@ -6334,7 +6334,7 @@
       </c>
       <c r="K123" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:18Z</t>
+          <t>2026-10-02T00:01:22Z</t>
         </is>
       </c>
     </row>
@@ -6383,7 +6383,7 @@
       </c>
       <c r="K124" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:18Z</t>
+          <t>2026-10-02T00:01:22Z</t>
         </is>
       </c>
     </row>
@@ -6432,7 +6432,7 @@
       </c>
       <c r="K125" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:18Z</t>
+          <t>2026-10-02T00:01:22Z</t>
         </is>
       </c>
     </row>
@@ -6481,7 +6481,7 @@
       </c>
       <c r="K126" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:18Z</t>
+          <t>2026-10-02T00:01:22Z</t>
         </is>
       </c>
     </row>
@@ -6530,7 +6530,7 @@
       </c>
       <c r="K127" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:18Z</t>
+          <t>2026-10-02T00:01:22Z</t>
         </is>
       </c>
     </row>
@@ -6579,7 +6579,7 @@
       </c>
       <c r="K128" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:18Z</t>
+          <t>2026-10-02T00:01:22Z</t>
         </is>
       </c>
     </row>
@@ -6628,7 +6628,7 @@
       </c>
       <c r="K129" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:18Z</t>
+          <t>2026-10-02T00:01:22Z</t>
         </is>
       </c>
     </row>
@@ -6677,7 +6677,7 @@
       </c>
       <c r="K130" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:18Z</t>
+          <t>2026-10-02T00:01:22Z</t>
         </is>
       </c>
     </row>
@@ -6726,7 +6726,7 @@
       </c>
       <c r="K131" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:18Z</t>
+          <t>2026-10-02T00:01:22Z</t>
         </is>
       </c>
     </row>
@@ -6775,7 +6775,7 @@
       </c>
       <c r="K132" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:18Z</t>
+          <t>2026-10-02T00:01:22Z</t>
         </is>
       </c>
     </row>
@@ -6824,7 +6824,7 @@
       </c>
       <c r="K133" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:18Z</t>
+          <t>2026-10-02T00:01:22Z</t>
         </is>
       </c>
     </row>
@@ -6873,7 +6873,7 @@
       </c>
       <c r="K134" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:18Z</t>
+          <t>2026-10-02T00:01:22Z</t>
         </is>
       </c>
     </row>
@@ -6922,7 +6922,7 @@
       </c>
       <c r="K135" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:18Z</t>
+          <t>2026-10-02T00:01:22Z</t>
         </is>
       </c>
     </row>
@@ -6971,7 +6971,7 @@
       </c>
       <c r="K136" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:18Z</t>
+          <t>2026-10-02T00:01:22Z</t>
         </is>
       </c>
     </row>
@@ -7020,7 +7020,7 @@
       </c>
       <c r="K137" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:18Z</t>
+          <t>2026-10-02T00:01:22Z</t>
         </is>
       </c>
     </row>
@@ -7069,7 +7069,7 @@
       </c>
       <c r="K138" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:18Z</t>
+          <t>2026-10-02T00:01:22Z</t>
         </is>
       </c>
     </row>
@@ -7118,7 +7118,7 @@
       </c>
       <c r="K139" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:18Z</t>
+          <t>2026-10-02T00:01:22Z</t>
         </is>
       </c>
     </row>
@@ -7167,7 +7167,7 @@
       </c>
       <c r="K140" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:18Z</t>
+          <t>2026-10-02T00:01:22Z</t>
         </is>
       </c>
     </row>
@@ -7216,7 +7216,7 @@
       </c>
       <c r="K141" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:18Z</t>
+          <t>2026-10-02T00:01:22Z</t>
         </is>
       </c>
     </row>
@@ -7265,7 +7265,7 @@
       </c>
       <c r="K142" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:18Z</t>
+          <t>2026-10-02T00:01:22Z</t>
         </is>
       </c>
     </row>
@@ -7314,7 +7314,7 @@
       </c>
       <c r="K143" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:18Z</t>
+          <t>2026-10-02T00:01:22Z</t>
         </is>
       </c>
     </row>
@@ -7363,7 +7363,7 @@
       </c>
       <c r="K144" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:18Z</t>
+          <t>2026-10-02T00:01:22Z</t>
         </is>
       </c>
     </row>
@@ -7412,7 +7412,7 @@
       </c>
       <c r="K145" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:18Z</t>
+          <t>2026-10-02T00:01:22Z</t>
         </is>
       </c>
     </row>
@@ -7461,7 +7461,7 @@
       </c>
       <c r="K146" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:18Z</t>
+          <t>2026-10-02T00:01:22Z</t>
         </is>
       </c>
     </row>
@@ -7510,7 +7510,7 @@
       </c>
       <c r="K147" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:18Z</t>
+          <t>2026-10-02T00:01:22Z</t>
         </is>
       </c>
     </row>
@@ -7559,7 +7559,7 @@
       </c>
       <c r="K148" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:18Z</t>
+          <t>2026-10-02T00:01:22Z</t>
         </is>
       </c>
     </row>
@@ -7608,7 +7608,7 @@
       </c>
       <c r="K149" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:18Z</t>
+          <t>2026-10-02T00:01:22Z</t>
         </is>
       </c>
     </row>
@@ -7657,7 +7657,7 @@
       </c>
       <c r="K150" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:18Z</t>
+          <t>2026-10-02T00:01:22Z</t>
         </is>
       </c>
     </row>
@@ -7706,7 +7706,7 @@
       </c>
       <c r="K151" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:18Z</t>
+          <t>2026-10-02T00:01:22Z</t>
         </is>
       </c>
     </row>
@@ -7755,7 +7755,7 @@
       </c>
       <c r="K152" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:18Z</t>
+          <t>2026-10-02T00:01:22Z</t>
         </is>
       </c>
     </row>
@@ -7804,7 +7804,7 @@
       </c>
       <c r="K153" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:18Z</t>
+          <t>2026-10-02T00:01:22Z</t>
         </is>
       </c>
     </row>
@@ -7853,7 +7853,7 @@
       </c>
       <c r="K154" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:18Z</t>
+          <t>2026-10-02T00:01:22Z</t>
         </is>
       </c>
     </row>
@@ -7902,7 +7902,7 @@
       </c>
       <c r="K155" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:18Z</t>
+          <t>2026-10-02T00:01:22Z</t>
         </is>
       </c>
     </row>
@@ -7951,7 +7951,7 @@
       </c>
       <c r="K156" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:18Z</t>
+          <t>2026-10-02T00:01:22Z</t>
         </is>
       </c>
     </row>
@@ -8000,7 +8000,7 @@
       </c>
       <c r="K157" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:18Z</t>
+          <t>2026-10-02T00:01:22Z</t>
         </is>
       </c>
     </row>
@@ -8049,7 +8049,7 @@
       </c>
       <c r="K158" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:18Z</t>
+          <t>2026-10-02T00:01:22Z</t>
         </is>
       </c>
     </row>
@@ -8098,7 +8098,7 @@
       </c>
       <c r="K159" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:18Z</t>
+          <t>2026-10-02T00:01:22Z</t>
         </is>
       </c>
     </row>
@@ -8147,7 +8147,7 @@
       </c>
       <c r="K160" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:18Z</t>
+          <t>2026-10-02T00:01:22Z</t>
         </is>
       </c>
     </row>
@@ -8196,7 +8196,7 @@
       </c>
       <c r="K161" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:18Z</t>
+          <t>2026-10-02T00:01:22Z</t>
         </is>
       </c>
     </row>
@@ -8245,7 +8245,7 @@
       </c>
       <c r="K162" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:18Z</t>
+          <t>2026-10-02T00:01:22Z</t>
         </is>
       </c>
     </row>
@@ -8294,7 +8294,7 @@
       </c>
       <c r="K163" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:18Z</t>
+          <t>2026-10-02T00:01:22Z</t>
         </is>
       </c>
     </row>
@@ -8343,7 +8343,7 @@
       </c>
       <c r="K164" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:18Z</t>
+          <t>2026-10-02T00:01:22Z</t>
         </is>
       </c>
     </row>
@@ -8392,7 +8392,7 @@
       </c>
       <c r="K165" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:18Z</t>
+          <t>2026-10-02T00:01:22Z</t>
         </is>
       </c>
     </row>
@@ -8441,7 +8441,7 @@
       </c>
       <c r="K166" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:18Z</t>
+          <t>2026-10-02T00:01:22Z</t>
         </is>
       </c>
     </row>
@@ -8490,7 +8490,7 @@
       </c>
       <c r="K167" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:18Z</t>
+          <t>2026-10-02T00:01:22Z</t>
         </is>
       </c>
     </row>
@@ -8539,7 +8539,7 @@
       </c>
       <c r="K168" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:18Z</t>
+          <t>2026-10-02T00:01:22Z</t>
         </is>
       </c>
     </row>
@@ -8588,7 +8588,7 @@
       </c>
       <c r="K169" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:18Z</t>
+          <t>2026-10-02T00:01:22Z</t>
         </is>
       </c>
     </row>
@@ -8637,7 +8637,7 @@
       </c>
       <c r="K170" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:18Z</t>
+          <t>2026-10-02T00:01:22Z</t>
         </is>
       </c>
     </row>
@@ -8686,7 +8686,7 @@
       </c>
       <c r="K171" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:18Z</t>
+          <t>2026-10-02T00:01:22Z</t>
         </is>
       </c>
     </row>
@@ -8735,7 +8735,7 @@
       </c>
       <c r="K172" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:18Z</t>
+          <t>2026-10-02T00:01:22Z</t>
         </is>
       </c>
     </row>
@@ -8784,7 +8784,7 @@
       </c>
       <c r="K173" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:18Z</t>
+          <t>2026-10-02T00:01:22Z</t>
         </is>
       </c>
     </row>
@@ -8833,7 +8833,7 @@
       </c>
       <c r="K174" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:18Z</t>
+          <t>2026-10-02T00:01:22Z</t>
         </is>
       </c>
     </row>
@@ -8882,7 +8882,7 @@
       </c>
       <c r="K175" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:18Z</t>
+          <t>2026-10-02T00:01:22Z</t>
         </is>
       </c>
     </row>
@@ -8931,7 +8931,7 @@
       </c>
       <c r="K176" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:18Z</t>
+          <t>2026-10-02T00:01:22Z</t>
         </is>
       </c>
     </row>
@@ -8980,7 +8980,7 @@
       </c>
       <c r="K177" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:18Z</t>
+          <t>2026-10-02T00:01:22Z</t>
         </is>
       </c>
     </row>
@@ -9029,7 +9029,7 @@
       </c>
       <c r="K178" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:18Z</t>
+          <t>2026-10-02T00:01:22Z</t>
         </is>
       </c>
     </row>
@@ -9078,7 +9078,7 @@
       </c>
       <c r="K179" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:18Z</t>
+          <t>2026-10-02T00:01:22Z</t>
         </is>
       </c>
     </row>
@@ -9127,7 +9127,7 @@
       </c>
       <c r="K180" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:18Z</t>
+          <t>2026-10-02T00:01:22Z</t>
         </is>
       </c>
     </row>
@@ -9176,7 +9176,7 @@
       </c>
       <c r="K181" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:18Z</t>
+          <t>2026-10-02T00:01:22Z</t>
         </is>
       </c>
     </row>
@@ -9225,7 +9225,7 @@
       </c>
       <c r="K182" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:18Z</t>
+          <t>2026-10-02T00:01:22Z</t>
         </is>
       </c>
     </row>
@@ -9274,7 +9274,7 @@
       </c>
       <c r="K183" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:18Z</t>
+          <t>2026-10-02T00:01:22Z</t>
         </is>
       </c>
     </row>
@@ -9323,7 +9323,7 @@
       </c>
       <c r="K184" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:18Z</t>
+          <t>2026-10-02T00:01:22Z</t>
         </is>
       </c>
     </row>
@@ -9372,7 +9372,7 @@
       </c>
       <c r="K185" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:18Z</t>
+          <t>2026-10-02T00:01:22Z</t>
         </is>
       </c>
     </row>
@@ -9421,7 +9421,7 @@
       </c>
       <c r="K186" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:18Z</t>
+          <t>2026-10-02T00:01:22Z</t>
         </is>
       </c>
     </row>
@@ -9470,7 +9470,7 @@
       </c>
       <c r="K187" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:18Z</t>
+          <t>2026-10-02T00:01:22Z</t>
         </is>
       </c>
     </row>
@@ -9519,7 +9519,7 @@
       </c>
       <c r="K188" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:18Z</t>
+          <t>2026-10-02T00:01:22Z</t>
         </is>
       </c>
     </row>
@@ -9568,7 +9568,7 @@
       </c>
       <c r="K189" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:18Z</t>
+          <t>2026-10-02T00:01:22Z</t>
         </is>
       </c>
     </row>
@@ -9617,7 +9617,7 @@
       </c>
       <c r="K190" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:18Z</t>
+          <t>2026-10-02T00:01:22Z</t>
         </is>
       </c>
     </row>
@@ -9666,7 +9666,7 @@
       </c>
       <c r="K191" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:18Z</t>
+          <t>2026-10-02T00:01:22Z</t>
         </is>
       </c>
     </row>
@@ -9715,7 +9715,7 @@
       </c>
       <c r="K192" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:18Z</t>
+          <t>2026-10-02T00:01:22Z</t>
         </is>
       </c>
     </row>
@@ -9764,7 +9764,7 @@
       </c>
       <c r="K193" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:18Z</t>
+          <t>2026-10-02T00:01:22Z</t>
         </is>
       </c>
     </row>
@@ -9813,7 +9813,7 @@
       </c>
       <c r="K194" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:18Z</t>
+          <t>2026-10-02T00:01:22Z</t>
         </is>
       </c>
     </row>
@@ -9862,7 +9862,7 @@
       </c>
       <c r="K195" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:18Z</t>
+          <t>2026-10-02T00:01:22Z</t>
         </is>
       </c>
     </row>
@@ -9911,7 +9911,7 @@
       </c>
       <c r="K196" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:18Z</t>
+          <t>2026-10-02T00:01:22Z</t>
         </is>
       </c>
     </row>
@@ -9960,7 +9960,7 @@
       </c>
       <c r="K197" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:18Z</t>
+          <t>2026-10-02T00:01:22Z</t>
         </is>
       </c>
     </row>
@@ -10009,7 +10009,7 @@
       </c>
       <c r="K198" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:18Z</t>
+          <t>2026-10-02T00:01:22Z</t>
         </is>
       </c>
     </row>
@@ -10058,7 +10058,7 @@
       </c>
       <c r="K199" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:18Z</t>
+          <t>2026-10-02T00:01:22Z</t>
         </is>
       </c>
     </row>
@@ -10107,7 +10107,7 @@
       </c>
       <c r="K200" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:18Z</t>
+          <t>2026-10-02T00:01:22Z</t>
         </is>
       </c>
     </row>
@@ -10156,7 +10156,7 @@
       </c>
       <c r="K201" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:18Z</t>
+          <t>2026-10-02T00:01:22Z</t>
         </is>
       </c>
     </row>
@@ -10205,7 +10205,7 @@
       </c>
       <c r="K202" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:18Z</t>
+          <t>2026-10-02T00:01:22Z</t>
         </is>
       </c>
     </row>
@@ -10254,7 +10254,7 @@
       </c>
       <c r="K203" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:18Z</t>
+          <t>2026-10-02T00:01:22Z</t>
         </is>
       </c>
     </row>
@@ -10303,7 +10303,7 @@
       </c>
       <c r="K204" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:18Z</t>
+          <t>2026-10-02T00:01:22Z</t>
         </is>
       </c>
     </row>
@@ -10352,7 +10352,7 @@
       </c>
       <c r="K205" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:18Z</t>
+          <t>2026-10-02T00:01:22Z</t>
         </is>
       </c>
     </row>
@@ -10401,7 +10401,7 @@
       </c>
       <c r="K206" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:18Z</t>
+          <t>2026-10-02T00:01:22Z</t>
         </is>
       </c>
     </row>
@@ -10450,7 +10450,7 @@
       </c>
       <c r="K207" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:18Z</t>
+          <t>2026-10-02T00:01:22Z</t>
         </is>
       </c>
     </row>
@@ -10499,7 +10499,7 @@
       </c>
       <c r="K208" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:18Z</t>
+          <t>2026-10-02T00:01:22Z</t>
         </is>
       </c>
     </row>
@@ -10548,7 +10548,7 @@
       </c>
       <c r="K209" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:18Z</t>
+          <t>2026-10-02T00:01:22Z</t>
         </is>
       </c>
     </row>
@@ -10597,7 +10597,7 @@
       </c>
       <c r="K210" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:18Z</t>
+          <t>2026-10-02T00:01:22Z</t>
         </is>
       </c>
     </row>
@@ -10646,7 +10646,7 @@
       </c>
       <c r="K211" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:18Z</t>
+          <t>2026-10-02T00:01:22Z</t>
         </is>
       </c>
     </row>
@@ -10695,7 +10695,7 @@
       </c>
       <c r="K212" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:18Z</t>
+          <t>2026-10-02T00:01:22Z</t>
         </is>
       </c>
     </row>
@@ -10744,7 +10744,7 @@
       </c>
       <c r="K213" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:18Z</t>
+          <t>2026-10-02T00:01:22Z</t>
         </is>
       </c>
     </row>
@@ -10793,7 +10793,7 @@
       </c>
       <c r="K214" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:18Z</t>
+          <t>2026-10-02T00:01:22Z</t>
         </is>
       </c>
     </row>
@@ -10842,7 +10842,7 @@
       </c>
       <c r="K215" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:18Z</t>
+          <t>2026-10-02T00:01:22Z</t>
         </is>
       </c>
     </row>
@@ -10891,7 +10891,7 @@
       </c>
       <c r="K216" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:18Z</t>
+          <t>2026-10-02T00:01:22Z</t>
         </is>
       </c>
     </row>
@@ -10940,7 +10940,7 @@
       </c>
       <c r="K217" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:18Z</t>
+          <t>2026-10-02T00:01:22Z</t>
         </is>
       </c>
     </row>
@@ -10989,7 +10989,7 @@
       </c>
       <c r="K218" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:18Z</t>
+          <t>2026-10-02T00:01:22Z</t>
         </is>
       </c>
     </row>
@@ -11038,7 +11038,7 @@
       </c>
       <c r="K219" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:18Z</t>
+          <t>2026-10-02T00:01:22Z</t>
         </is>
       </c>
     </row>
@@ -11087,7 +11087,7 @@
       </c>
       <c r="K220" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:18Z</t>
+          <t>2026-10-02T00:01:22Z</t>
         </is>
       </c>
     </row>
@@ -11136,7 +11136,7 @@
       </c>
       <c r="K221" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:18Z</t>
+          <t>2026-10-02T00:01:22Z</t>
         </is>
       </c>
     </row>
@@ -11185,7 +11185,7 @@
       </c>
       <c r="K222" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:18Z</t>
+          <t>2026-10-02T00:01:22Z</t>
         </is>
       </c>
     </row>
@@ -11234,7 +11234,7 @@
       </c>
       <c r="K223" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:18Z</t>
+          <t>2026-10-02T00:01:22Z</t>
         </is>
       </c>
     </row>
@@ -11283,7 +11283,7 @@
       </c>
       <c r="K224" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:18Z</t>
+          <t>2026-10-02T00:01:22Z</t>
         </is>
       </c>
     </row>
@@ -11332,7 +11332,7 @@
       </c>
       <c r="K225" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:18Z</t>
+          <t>2026-10-02T00:01:22Z</t>
         </is>
       </c>
     </row>
@@ -11381,7 +11381,7 @@
       </c>
       <c r="K226" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:18Z</t>
+          <t>2026-10-02T00:01:22Z</t>
         </is>
       </c>
     </row>
@@ -11430,7 +11430,7 @@
       </c>
       <c r="K227" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:18Z</t>
+          <t>2026-10-02T00:01:22Z</t>
         </is>
       </c>
     </row>
@@ -11479,7 +11479,7 @@
       </c>
       <c r="K228" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:18Z</t>
+          <t>2026-10-02T00:01:22Z</t>
         </is>
       </c>
     </row>
@@ -11528,7 +11528,7 @@
       </c>
       <c r="K229" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:18Z</t>
+          <t>2026-10-02T00:01:22Z</t>
         </is>
       </c>
     </row>
@@ -11577,7 +11577,7 @@
       </c>
       <c r="K230" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:18Z</t>
+          <t>2026-10-02T00:01:22Z</t>
         </is>
       </c>
     </row>
@@ -11626,7 +11626,7 @@
       </c>
       <c r="K231" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:18Z</t>
+          <t>2026-10-02T00:01:22Z</t>
         </is>
       </c>
     </row>
@@ -11758,7 +11758,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:18Z</t>
+          <t>2026-10-02T00:01:22Z</t>
         </is>
       </c>
     </row>
@@ -11804,7 +11804,7 @@
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>{"date": "2026-08-01", "year": 2026, "month": 8, "month_name": "Agosto", "index_value": 637409769724325.1, "monthly_variation_pct": 8.9, "unit": "Índice base diciembre 2007=100 y variación mensual %", "frequency": "monthly", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/precios_consumidor/4_5_7_2.xls", "fetched_at": "2026-10-01T00:02:18Z"}</t>
+          <t>{"date": "2026-08-01", "year": 2026, "month": 8, "month_name": "Agosto", "index_value": 637409769724325.1, "monthly_variation_pct": 8.9, "unit": "Índice base diciembre 2007=100 y variación mensual %", "frequency": "monthly", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/precios_consumidor/4_5_7_2.xls", "fetched_at": "2026-10-02T00:01:22Z"}</t>
         </is>
       </c>
     </row>

--- a/assets/data/bcv/excel/ove_bcv_inpc_nacional_mensual.xlsx
+++ b/assets/data/bcv/excel/ove_bcv_inpc_nacional_mensual.xlsx
@@ -650,7 +650,7 @@
       </c>
       <c r="K7" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:22Z</t>
+          <t>2026-10-02T18:24:22Z</t>
         </is>
       </c>
     </row>
@@ -699,7 +699,7 @@
       </c>
       <c r="K8" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:22Z</t>
+          <t>2026-10-02T18:24:22Z</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="K9" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:22Z</t>
+          <t>2026-10-02T18:24:22Z</t>
         </is>
       </c>
     </row>
@@ -797,7 +797,7 @@
       </c>
       <c r="K10" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:22Z</t>
+          <t>2026-10-02T18:24:22Z</t>
         </is>
       </c>
     </row>
@@ -846,7 +846,7 @@
       </c>
       <c r="K11" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:22Z</t>
+          <t>2026-10-02T18:24:22Z</t>
         </is>
       </c>
     </row>
@@ -895,7 +895,7 @@
       </c>
       <c r="K12" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:22Z</t>
+          <t>2026-10-02T18:24:22Z</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="K13" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:22Z</t>
+          <t>2026-10-02T18:24:22Z</t>
         </is>
       </c>
     </row>
@@ -993,7 +993,7 @@
       </c>
       <c r="K14" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:22Z</t>
+          <t>2026-10-02T18:24:22Z</t>
         </is>
       </c>
     </row>
@@ -1042,7 +1042,7 @@
       </c>
       <c r="K15" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:22Z</t>
+          <t>2026-10-02T18:24:22Z</t>
         </is>
       </c>
     </row>
@@ -1091,7 +1091,7 @@
       </c>
       <c r="K16" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:22Z</t>
+          <t>2026-10-02T18:24:22Z</t>
         </is>
       </c>
     </row>
@@ -1140,7 +1140,7 @@
       </c>
       <c r="K17" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:22Z</t>
+          <t>2026-10-02T18:24:22Z</t>
         </is>
       </c>
     </row>
@@ -1189,7 +1189,7 @@
       </c>
       <c r="K18" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:22Z</t>
+          <t>2026-10-02T18:24:22Z</t>
         </is>
       </c>
     </row>
@@ -1238,7 +1238,7 @@
       </c>
       <c r="K19" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:22Z</t>
+          <t>2026-10-02T18:24:22Z</t>
         </is>
       </c>
     </row>
@@ -1287,7 +1287,7 @@
       </c>
       <c r="K20" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:22Z</t>
+          <t>2026-10-02T18:24:22Z</t>
         </is>
       </c>
     </row>
@@ -1336,7 +1336,7 @@
       </c>
       <c r="K21" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:22Z</t>
+          <t>2026-10-02T18:24:22Z</t>
         </is>
       </c>
     </row>
@@ -1385,7 +1385,7 @@
       </c>
       <c r="K22" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:22Z</t>
+          <t>2026-10-02T18:24:22Z</t>
         </is>
       </c>
     </row>
@@ -1434,7 +1434,7 @@
       </c>
       <c r="K23" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:22Z</t>
+          <t>2026-10-02T18:24:22Z</t>
         </is>
       </c>
     </row>
@@ -1483,7 +1483,7 @@
       </c>
       <c r="K24" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:22Z</t>
+          <t>2026-10-02T18:24:22Z</t>
         </is>
       </c>
     </row>
@@ -1532,7 +1532,7 @@
       </c>
       <c r="K25" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:22Z</t>
+          <t>2026-10-02T18:24:22Z</t>
         </is>
       </c>
     </row>
@@ -1581,7 +1581,7 @@
       </c>
       <c r="K26" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:22Z</t>
+          <t>2026-10-02T18:24:22Z</t>
         </is>
       </c>
     </row>
@@ -1630,7 +1630,7 @@
       </c>
       <c r="K27" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:22Z</t>
+          <t>2026-10-02T18:24:22Z</t>
         </is>
       </c>
     </row>
@@ -1679,7 +1679,7 @@
       </c>
       <c r="K28" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:22Z</t>
+          <t>2026-10-02T18:24:22Z</t>
         </is>
       </c>
     </row>
@@ -1728,7 +1728,7 @@
       </c>
       <c r="K29" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:22Z</t>
+          <t>2026-10-02T18:24:22Z</t>
         </is>
       </c>
     </row>
@@ -1777,7 +1777,7 @@
       </c>
       <c r="K30" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:22Z</t>
+          <t>2026-10-02T18:24:22Z</t>
         </is>
       </c>
     </row>
@@ -1826,7 +1826,7 @@
       </c>
       <c r="K31" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:22Z</t>
+          <t>2026-10-02T18:24:22Z</t>
         </is>
       </c>
     </row>
@@ -1875,7 +1875,7 @@
       </c>
       <c r="K32" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:22Z</t>
+          <t>2026-10-02T18:24:22Z</t>
         </is>
       </c>
     </row>
@@ -1924,7 +1924,7 @@
       </c>
       <c r="K33" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:22Z</t>
+          <t>2026-10-02T18:24:22Z</t>
         </is>
       </c>
     </row>
@@ -1973,7 +1973,7 @@
       </c>
       <c r="K34" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:22Z</t>
+          <t>2026-10-02T18:24:22Z</t>
         </is>
       </c>
     </row>
@@ -2022,7 +2022,7 @@
       </c>
       <c r="K35" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:22Z</t>
+          <t>2026-10-02T18:24:22Z</t>
         </is>
       </c>
     </row>
@@ -2071,7 +2071,7 @@
       </c>
       <c r="K36" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:22Z</t>
+          <t>2026-10-02T18:24:22Z</t>
         </is>
       </c>
     </row>
@@ -2120,7 +2120,7 @@
       </c>
       <c r="K37" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:22Z</t>
+          <t>2026-10-02T18:24:22Z</t>
         </is>
       </c>
     </row>
@@ -2169,7 +2169,7 @@
       </c>
       <c r="K38" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:22Z</t>
+          <t>2026-10-02T18:24:22Z</t>
         </is>
       </c>
     </row>
@@ -2218,7 +2218,7 @@
       </c>
       <c r="K39" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:22Z</t>
+          <t>2026-10-02T18:24:22Z</t>
         </is>
       </c>
     </row>
@@ -2267,7 +2267,7 @@
       </c>
       <c r="K40" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:22Z</t>
+          <t>2026-10-02T18:24:22Z</t>
         </is>
       </c>
     </row>
@@ -2316,7 +2316,7 @@
       </c>
       <c r="K41" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:22Z</t>
+          <t>2026-10-02T18:24:22Z</t>
         </is>
       </c>
     </row>
@@ -2365,7 +2365,7 @@
       </c>
       <c r="K42" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:22Z</t>
+          <t>2026-10-02T18:24:22Z</t>
         </is>
       </c>
     </row>
@@ -2414,7 +2414,7 @@
       </c>
       <c r="K43" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:22Z</t>
+          <t>2026-10-02T18:24:22Z</t>
         </is>
       </c>
     </row>
@@ -2463,7 +2463,7 @@
       </c>
       <c r="K44" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:22Z</t>
+          <t>2026-10-02T18:24:22Z</t>
         </is>
       </c>
     </row>
@@ -2512,7 +2512,7 @@
       </c>
       <c r="K45" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:22Z</t>
+          <t>2026-10-02T18:24:22Z</t>
         </is>
       </c>
     </row>
@@ -2561,7 +2561,7 @@
       </c>
       <c r="K46" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:22Z</t>
+          <t>2026-10-02T18:24:22Z</t>
         </is>
       </c>
     </row>
@@ -2610,7 +2610,7 @@
       </c>
       <c r="K47" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:22Z</t>
+          <t>2026-10-02T18:24:22Z</t>
         </is>
       </c>
     </row>
@@ -2659,7 +2659,7 @@
       </c>
       <c r="K48" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:22Z</t>
+          <t>2026-10-02T18:24:22Z</t>
         </is>
       </c>
     </row>
@@ -2708,7 +2708,7 @@
       </c>
       <c r="K49" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:22Z</t>
+          <t>2026-10-02T18:24:22Z</t>
         </is>
       </c>
     </row>
@@ -2757,7 +2757,7 @@
       </c>
       <c r="K50" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:22Z</t>
+          <t>2026-10-02T18:24:22Z</t>
         </is>
       </c>
     </row>
@@ -2806,7 +2806,7 @@
       </c>
       <c r="K51" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:22Z</t>
+          <t>2026-10-02T18:24:22Z</t>
         </is>
       </c>
     </row>
@@ -2855,7 +2855,7 @@
       </c>
       <c r="K52" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:22Z</t>
+          <t>2026-10-02T18:24:22Z</t>
         </is>
       </c>
     </row>
@@ -2904,7 +2904,7 @@
       </c>
       <c r="K53" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:22Z</t>
+          <t>2026-10-02T18:24:22Z</t>
         </is>
       </c>
     </row>
@@ -2953,7 +2953,7 @@
       </c>
       <c r="K54" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:22Z</t>
+          <t>2026-10-02T18:24:22Z</t>
         </is>
       </c>
     </row>
@@ -3002,7 +3002,7 @@
       </c>
       <c r="K55" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:22Z</t>
+          <t>2026-10-02T18:24:22Z</t>
         </is>
       </c>
     </row>
@@ -3051,7 +3051,7 @@
       </c>
       <c r="K56" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:22Z</t>
+          <t>2026-10-02T18:24:22Z</t>
         </is>
       </c>
     </row>
@@ -3100,7 +3100,7 @@
       </c>
       <c r="K57" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:22Z</t>
+          <t>2026-10-02T18:24:22Z</t>
         </is>
       </c>
     </row>
@@ -3149,7 +3149,7 @@
       </c>
       <c r="K58" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:22Z</t>
+          <t>2026-10-02T18:24:22Z</t>
         </is>
       </c>
     </row>
@@ -3198,7 +3198,7 @@
       </c>
       <c r="K59" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:22Z</t>
+          <t>2026-10-02T18:24:22Z</t>
         </is>
       </c>
     </row>
@@ -3247,7 +3247,7 @@
       </c>
       <c r="K60" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:22Z</t>
+          <t>2026-10-02T18:24:22Z</t>
         </is>
       </c>
     </row>
@@ -3296,7 +3296,7 @@
       </c>
       <c r="K61" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:22Z</t>
+          <t>2026-10-02T18:24:22Z</t>
         </is>
       </c>
     </row>
@@ -3345,7 +3345,7 @@
       </c>
       <c r="K62" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:22Z</t>
+          <t>2026-10-02T18:24:22Z</t>
         </is>
       </c>
     </row>
@@ -3394,7 +3394,7 @@
       </c>
       <c r="K63" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:22Z</t>
+          <t>2026-10-02T18:24:22Z</t>
         </is>
       </c>
     </row>
@@ -3443,7 +3443,7 @@
       </c>
       <c r="K64" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:22Z</t>
+          <t>2026-10-02T18:24:22Z</t>
         </is>
       </c>
     </row>
@@ -3492,7 +3492,7 @@
       </c>
       <c r="K65" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:22Z</t>
+          <t>2026-10-02T18:24:22Z</t>
         </is>
       </c>
     </row>
@@ -3541,7 +3541,7 @@
       </c>
       <c r="K66" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:22Z</t>
+          <t>2026-10-02T18:24:22Z</t>
         </is>
       </c>
     </row>
@@ -3590,7 +3590,7 @@
       </c>
       <c r="K67" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:22Z</t>
+          <t>2026-10-02T18:24:22Z</t>
         </is>
       </c>
     </row>
@@ -3639,7 +3639,7 @@
       </c>
       <c r="K68" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:22Z</t>
+          <t>2026-10-02T18:24:22Z</t>
         </is>
       </c>
     </row>
@@ -3688,7 +3688,7 @@
       </c>
       <c r="K69" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:22Z</t>
+          <t>2026-10-02T18:24:22Z</t>
         </is>
       </c>
     </row>
@@ -3737,7 +3737,7 @@
       </c>
       <c r="K70" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:22Z</t>
+          <t>2026-10-02T18:24:22Z</t>
         </is>
       </c>
     </row>
@@ -3786,7 +3786,7 @@
       </c>
       <c r="K71" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:22Z</t>
+          <t>2026-10-02T18:24:22Z</t>
         </is>
       </c>
     </row>
@@ -3835,7 +3835,7 @@
       </c>
       <c r="K72" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:22Z</t>
+          <t>2026-10-02T18:24:22Z</t>
         </is>
       </c>
     </row>
@@ -3884,7 +3884,7 @@
       </c>
       <c r="K73" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:22Z</t>
+          <t>2026-10-02T18:24:22Z</t>
         </is>
       </c>
     </row>
@@ -3933,7 +3933,7 @@
       </c>
       <c r="K74" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:22Z</t>
+          <t>2026-10-02T18:24:22Z</t>
         </is>
       </c>
     </row>
@@ -3982,7 +3982,7 @@
       </c>
       <c r="K75" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:22Z</t>
+          <t>2026-10-02T18:24:22Z</t>
         </is>
       </c>
     </row>
@@ -4031,7 +4031,7 @@
       </c>
       <c r="K76" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:22Z</t>
+          <t>2026-10-02T18:24:22Z</t>
         </is>
       </c>
     </row>
@@ -4080,7 +4080,7 @@
       </c>
       <c r="K77" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:22Z</t>
+          <t>2026-10-02T18:24:22Z</t>
         </is>
       </c>
     </row>
@@ -4129,7 +4129,7 @@
       </c>
       <c r="K78" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:22Z</t>
+          <t>2026-10-02T18:24:22Z</t>
         </is>
       </c>
     </row>
@@ -4178,7 +4178,7 @@
       </c>
       <c r="K79" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:22Z</t>
+          <t>2026-10-02T18:24:22Z</t>
         </is>
       </c>
     </row>
@@ -4227,7 +4227,7 @@
       </c>
       <c r="K80" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:22Z</t>
+          <t>2026-10-02T18:24:22Z</t>
         </is>
       </c>
     </row>
@@ -4276,7 +4276,7 @@
       </c>
       <c r="K81" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:22Z</t>
+          <t>2026-10-02T18:24:22Z</t>
         </is>
       </c>
     </row>
@@ -4325,7 +4325,7 @@
       </c>
       <c r="K82" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:22Z</t>
+          <t>2026-10-02T18:24:22Z</t>
         </is>
       </c>
     </row>
@@ -4374,7 +4374,7 @@
       </c>
       <c r="K83" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:22Z</t>
+          <t>2026-10-02T18:24:22Z</t>
         </is>
       </c>
     </row>
@@ -4423,7 +4423,7 @@
       </c>
       <c r="K84" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:22Z</t>
+          <t>2026-10-02T18:24:22Z</t>
         </is>
       </c>
     </row>
@@ -4472,7 +4472,7 @@
       </c>
       <c r="K85" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:22Z</t>
+          <t>2026-10-02T18:24:22Z</t>
         </is>
       </c>
     </row>
@@ -4521,7 +4521,7 @@
       </c>
       <c r="K86" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:22Z</t>
+          <t>2026-10-02T18:24:22Z</t>
         </is>
       </c>
     </row>
@@ -4570,7 +4570,7 @@
       </c>
       <c r="K87" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:22Z</t>
+          <t>2026-10-02T18:24:22Z</t>
         </is>
       </c>
     </row>
@@ -4619,7 +4619,7 @@
       </c>
       <c r="K88" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:22Z</t>
+          <t>2026-10-02T18:24:22Z</t>
         </is>
       </c>
     </row>
@@ -4668,7 +4668,7 @@
       </c>
       <c r="K89" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:22Z</t>
+          <t>2026-10-02T18:24:22Z</t>
         </is>
       </c>
     </row>
@@ -4717,7 +4717,7 @@
       </c>
       <c r="K90" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:22Z</t>
+          <t>2026-10-02T18:24:22Z</t>
         </is>
       </c>
     </row>
@@ -4766,7 +4766,7 @@
       </c>
       <c r="K91" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:22Z</t>
+          <t>2026-10-02T18:24:22Z</t>
         </is>
       </c>
     </row>
@@ -4815,7 +4815,7 @@
       </c>
       <c r="K92" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:22Z</t>
+          <t>2026-10-02T18:24:22Z</t>
         </is>
       </c>
     </row>
@@ -4864,7 +4864,7 @@
       </c>
       <c r="K93" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:22Z</t>
+          <t>2026-10-02T18:24:22Z</t>
         </is>
       </c>
     </row>
@@ -4913,7 +4913,7 @@
       </c>
       <c r="K94" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:22Z</t>
+          <t>2026-10-02T18:24:22Z</t>
         </is>
       </c>
     </row>
@@ -4962,7 +4962,7 @@
       </c>
       <c r="K95" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:22Z</t>
+          <t>2026-10-02T18:24:22Z</t>
         </is>
       </c>
     </row>
@@ -5011,7 +5011,7 @@
       </c>
       <c r="K96" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:22Z</t>
+          <t>2026-10-02T18:24:22Z</t>
         </is>
       </c>
     </row>
@@ -5060,7 +5060,7 @@
       </c>
       <c r="K97" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:22Z</t>
+          <t>2026-10-02T18:24:22Z</t>
         </is>
       </c>
     </row>
@@ -5109,7 +5109,7 @@
       </c>
       <c r="K98" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:22Z</t>
+          <t>2026-10-02T18:24:22Z</t>
         </is>
       </c>
     </row>
@@ -5158,7 +5158,7 @@
       </c>
       <c r="K99" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:22Z</t>
+          <t>2026-10-02T18:24:22Z</t>
         </is>
       </c>
     </row>
@@ -5207,7 +5207,7 @@
       </c>
       <c r="K100" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:22Z</t>
+          <t>2026-10-02T18:24:22Z</t>
         </is>
       </c>
     </row>
@@ -5256,7 +5256,7 @@
       </c>
       <c r="K101" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:22Z</t>
+          <t>2026-10-02T18:24:22Z</t>
         </is>
       </c>
     </row>
@@ -5305,7 +5305,7 @@
       </c>
       <c r="K102" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:22Z</t>
+          <t>2026-10-02T18:24:22Z</t>
         </is>
       </c>
     </row>
@@ -5354,7 +5354,7 @@
       </c>
       <c r="K103" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:22Z</t>
+          <t>2026-10-02T18:24:22Z</t>
         </is>
       </c>
     </row>
@@ -5403,7 +5403,7 @@
       </c>
       <c r="K104" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:22Z</t>
+          <t>2026-10-02T18:24:22Z</t>
         </is>
       </c>
     </row>
@@ -5452,7 +5452,7 @@
       </c>
       <c r="K105" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:22Z</t>
+          <t>2026-10-02T18:24:22Z</t>
         </is>
       </c>
     </row>
@@ -5501,7 +5501,7 @@
       </c>
       <c r="K106" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:22Z</t>
+          <t>2026-10-02T18:24:22Z</t>
         </is>
       </c>
     </row>
@@ -5550,7 +5550,7 @@
       </c>
       <c r="K107" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:22Z</t>
+          <t>2026-10-02T18:24:22Z</t>
         </is>
       </c>
     </row>
@@ -5599,7 +5599,7 @@
       </c>
       <c r="K108" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:22Z</t>
+          <t>2026-10-02T18:24:22Z</t>
         </is>
       </c>
     </row>
@@ -5648,7 +5648,7 @@
       </c>
       <c r="K109" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:22Z</t>
+          <t>2026-10-02T18:24:22Z</t>
         </is>
       </c>
     </row>
@@ -5697,7 +5697,7 @@
       </c>
       <c r="K110" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:22Z</t>
+          <t>2026-10-02T18:24:22Z</t>
         </is>
       </c>
     </row>
@@ -5746,7 +5746,7 @@
       </c>
       <c r="K111" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:22Z</t>
+          <t>2026-10-02T18:24:22Z</t>
         </is>
       </c>
     </row>
@@ -5795,7 +5795,7 @@
       </c>
       <c r="K112" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:22Z</t>
+          <t>2026-10-02T18:24:22Z</t>
         </is>
       </c>
     </row>
@@ -5844,7 +5844,7 @@
       </c>
       <c r="K113" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:22Z</t>
+          <t>2026-10-02T18:24:22Z</t>
         </is>
       </c>
     </row>
@@ -5893,7 +5893,7 @@
       </c>
       <c r="K114" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:22Z</t>
+          <t>2026-10-02T18:24:22Z</t>
         </is>
       </c>
     </row>
@@ -5942,7 +5942,7 @@
       </c>
       <c r="K115" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:22Z</t>
+          <t>2026-10-02T18:24:22Z</t>
         </is>
       </c>
     </row>
@@ -5991,7 +5991,7 @@
       </c>
       <c r="K116" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:22Z</t>
+          <t>2026-10-02T18:24:22Z</t>
         </is>
       </c>
     </row>
@@ -6040,7 +6040,7 @@
       </c>
       <c r="K117" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:22Z</t>
+          <t>2026-10-02T18:24:22Z</t>
         </is>
       </c>
     </row>
@@ -6089,7 +6089,7 @@
       </c>
       <c r="K118" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:22Z</t>
+          <t>2026-10-02T18:24:22Z</t>
         </is>
       </c>
     </row>
@@ -6138,7 +6138,7 @@
       </c>
       <c r="K119" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:22Z</t>
+          <t>2026-10-02T18:24:22Z</t>
         </is>
       </c>
     </row>
@@ -6187,7 +6187,7 @@
       </c>
       <c r="K120" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:22Z</t>
+          <t>2026-10-02T18:24:22Z</t>
         </is>
       </c>
     </row>
@@ -6236,7 +6236,7 @@
       </c>
       <c r="K121" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:22Z</t>
+          <t>2026-10-02T18:24:22Z</t>
         </is>
       </c>
     </row>
@@ -6285,7 +6285,7 @@
       </c>
       <c r="K122" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:22Z</t>
+          <t>2026-10-02T18:24:22Z</t>
         </is>
       </c>
     </row>
@@ -6334,7 +6334,7 @@
       </c>
       <c r="K123" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:22Z</t>
+          <t>2026-10-02T18:24:22Z</t>
         </is>
       </c>
     </row>
@@ -6383,7 +6383,7 @@
       </c>
       <c r="K124" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:22Z</t>
+          <t>2026-10-02T18:24:22Z</t>
         </is>
       </c>
     </row>
@@ -6432,7 +6432,7 @@
       </c>
       <c r="K125" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:22Z</t>
+          <t>2026-10-02T18:24:22Z</t>
         </is>
       </c>
     </row>
@@ -6481,7 +6481,7 @@
       </c>
       <c r="K126" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:22Z</t>
+          <t>2026-10-02T18:24:22Z</t>
         </is>
       </c>
     </row>
@@ -6530,7 +6530,7 @@
       </c>
       <c r="K127" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:22Z</t>
+          <t>2026-10-02T18:24:22Z</t>
         </is>
       </c>
     </row>
@@ -6579,7 +6579,7 @@
       </c>
       <c r="K128" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:22Z</t>
+          <t>2026-10-02T18:24:22Z</t>
         </is>
       </c>
     </row>
@@ -6628,7 +6628,7 @@
       </c>
       <c r="K129" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:22Z</t>
+          <t>2026-10-02T18:24:22Z</t>
         </is>
       </c>
     </row>
@@ -6677,7 +6677,7 @@
       </c>
       <c r="K130" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:22Z</t>
+          <t>2026-10-02T18:24:22Z</t>
         </is>
       </c>
     </row>
@@ -6726,7 +6726,7 @@
       </c>
       <c r="K131" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:22Z</t>
+          <t>2026-10-02T18:24:22Z</t>
         </is>
       </c>
     </row>
@@ -6775,7 +6775,7 @@
       </c>
       <c r="K132" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:22Z</t>
+          <t>2026-10-02T18:24:22Z</t>
         </is>
       </c>
     </row>
@@ -6824,7 +6824,7 @@
       </c>
       <c r="K133" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:22Z</t>
+          <t>2026-10-02T18:24:22Z</t>
         </is>
       </c>
     </row>
@@ -6873,7 +6873,7 @@
       </c>
       <c r="K134" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:22Z</t>
+          <t>2026-10-02T18:24:22Z</t>
         </is>
       </c>
     </row>
@@ -6922,7 +6922,7 @@
       </c>
       <c r="K135" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:22Z</t>
+          <t>2026-10-02T18:24:22Z</t>
         </is>
       </c>
     </row>
@@ -6971,7 +6971,7 @@
       </c>
       <c r="K136" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:22Z</t>
+          <t>2026-10-02T18:24:22Z</t>
         </is>
       </c>
     </row>
@@ -7020,7 +7020,7 @@
       </c>
       <c r="K137" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:22Z</t>
+          <t>2026-10-02T18:24:22Z</t>
         </is>
       </c>
     </row>
@@ -7069,7 +7069,7 @@
       </c>
       <c r="K138" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:22Z</t>
+          <t>2026-10-02T18:24:22Z</t>
         </is>
       </c>
     </row>
@@ -7118,7 +7118,7 @@
       </c>
       <c r="K139" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:22Z</t>
+          <t>2026-10-02T18:24:22Z</t>
         </is>
       </c>
     </row>
@@ -7167,7 +7167,7 @@
       </c>
       <c r="K140" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:22Z</t>
+          <t>2026-10-02T18:24:22Z</t>
         </is>
       </c>
     </row>
@@ -7216,7 +7216,7 @@
       </c>
       <c r="K141" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:22Z</t>
+          <t>2026-10-02T18:24:22Z</t>
         </is>
       </c>
     </row>
@@ -7265,7 +7265,7 @@
       </c>
       <c r="K142" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:22Z</t>
+          <t>2026-10-02T18:24:22Z</t>
         </is>
       </c>
     </row>
@@ -7314,7 +7314,7 @@
       </c>
       <c r="K143" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:22Z</t>
+          <t>2026-10-02T18:24:22Z</t>
         </is>
       </c>
     </row>
@@ -7363,7 +7363,7 @@
       </c>
       <c r="K144" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:22Z</t>
+          <t>2026-10-02T18:24:22Z</t>
         </is>
       </c>
     </row>
@@ -7412,7 +7412,7 @@
       </c>
       <c r="K145" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:22Z</t>
+          <t>2026-10-02T18:24:22Z</t>
         </is>
       </c>
     </row>
@@ -7461,7 +7461,7 @@
       </c>
       <c r="K146" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:22Z</t>
+          <t>2026-10-02T18:24:22Z</t>
         </is>
       </c>
     </row>
@@ -7510,7 +7510,7 @@
       </c>
       <c r="K147" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:22Z</t>
+          <t>2026-10-02T18:24:22Z</t>
         </is>
       </c>
     </row>
@@ -7559,7 +7559,7 @@
       </c>
       <c r="K148" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:22Z</t>
+          <t>2026-10-02T18:24:22Z</t>
         </is>
       </c>
     </row>
@@ -7608,7 +7608,7 @@
       </c>
       <c r="K149" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:22Z</t>
+          <t>2026-10-02T18:24:22Z</t>
         </is>
       </c>
     </row>
@@ -7657,7 +7657,7 @@
       </c>
       <c r="K150" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:22Z</t>
+          <t>2026-10-02T18:24:22Z</t>
         </is>
       </c>
     </row>
@@ -7706,7 +7706,7 @@
       </c>
       <c r="K151" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:22Z</t>
+          <t>2026-10-02T18:24:22Z</t>
         </is>
       </c>
     </row>
@@ -7755,7 +7755,7 @@
       </c>
       <c r="K152" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:22Z</t>
+          <t>2026-10-02T18:24:22Z</t>
         </is>
       </c>
     </row>
@@ -7804,7 +7804,7 @@
       </c>
       <c r="K153" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:22Z</t>
+          <t>2026-10-02T18:24:22Z</t>
         </is>
       </c>
     </row>
@@ -7853,7 +7853,7 @@
       </c>
       <c r="K154" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:22Z</t>
+          <t>2026-10-02T18:24:22Z</t>
         </is>
       </c>
     </row>
@@ -7902,7 +7902,7 @@
       </c>
       <c r="K155" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:22Z</t>
+          <t>2026-10-02T18:24:22Z</t>
         </is>
       </c>
     </row>
@@ -7951,7 +7951,7 @@
       </c>
       <c r="K156" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:22Z</t>
+          <t>2026-10-02T18:24:22Z</t>
         </is>
       </c>
     </row>
@@ -8000,7 +8000,7 @@
       </c>
       <c r="K157" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:22Z</t>
+          <t>2026-10-02T18:24:22Z</t>
         </is>
       </c>
     </row>
@@ -8049,7 +8049,7 @@
       </c>
       <c r="K158" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:22Z</t>
+          <t>2026-10-02T18:24:22Z</t>
         </is>
       </c>
     </row>
@@ -8098,7 +8098,7 @@
       </c>
       <c r="K159" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:22Z</t>
+          <t>2026-10-02T18:24:22Z</t>
         </is>
       </c>
     </row>
@@ -8147,7 +8147,7 @@
       </c>
       <c r="K160" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:22Z</t>
+          <t>2026-10-02T18:24:22Z</t>
         </is>
       </c>
     </row>
@@ -8196,7 +8196,7 @@
       </c>
       <c r="K161" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:22Z</t>
+          <t>2026-10-02T18:24:22Z</t>
         </is>
       </c>
     </row>
@@ -8245,7 +8245,7 @@
       </c>
       <c r="K162" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:22Z</t>
+          <t>2026-10-02T18:24:22Z</t>
         </is>
       </c>
     </row>
@@ -8294,7 +8294,7 @@
       </c>
       <c r="K163" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:22Z</t>
+          <t>2026-10-02T18:24:22Z</t>
         </is>
       </c>
     </row>
@@ -8343,7 +8343,7 @@
       </c>
       <c r="K164" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:22Z</t>
+          <t>2026-10-02T18:24:22Z</t>
         </is>
       </c>
     </row>
@@ -8392,7 +8392,7 @@
       </c>
       <c r="K165" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:22Z</t>
+          <t>2026-10-02T18:24:22Z</t>
         </is>
       </c>
     </row>
@@ -8441,7 +8441,7 @@
       </c>
       <c r="K166" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:22Z</t>
+          <t>2026-10-02T18:24:22Z</t>
         </is>
       </c>
     </row>
@@ -8490,7 +8490,7 @@
       </c>
       <c r="K167" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:22Z</t>
+          <t>2026-10-02T18:24:22Z</t>
         </is>
       </c>
     </row>
@@ -8539,7 +8539,7 @@
       </c>
       <c r="K168" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:22Z</t>
+          <t>2026-10-02T18:24:22Z</t>
         </is>
       </c>
     </row>
@@ -8588,7 +8588,7 @@
       </c>
       <c r="K169" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:22Z</t>
+          <t>2026-10-02T18:24:22Z</t>
         </is>
       </c>
     </row>
@@ -8637,7 +8637,7 @@
       </c>
       <c r="K170" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:22Z</t>
+          <t>2026-10-02T18:24:22Z</t>
         </is>
       </c>
     </row>
@@ -8686,7 +8686,7 @@
       </c>
       <c r="K171" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:22Z</t>
+          <t>2026-10-02T18:24:22Z</t>
         </is>
       </c>
     </row>
@@ -8735,7 +8735,7 @@
       </c>
       <c r="K172" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:22Z</t>
+          <t>2026-10-02T18:24:22Z</t>
         </is>
       </c>
     </row>
@@ -8784,7 +8784,7 @@
       </c>
       <c r="K173" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:22Z</t>
+          <t>2026-10-02T18:24:22Z</t>
         </is>
       </c>
     </row>
@@ -8833,7 +8833,7 @@
       </c>
       <c r="K174" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:22Z</t>
+          <t>2026-10-02T18:24:22Z</t>
         </is>
       </c>
     </row>
@@ -8882,7 +8882,7 @@
       </c>
       <c r="K175" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:22Z</t>
+          <t>2026-10-02T18:24:22Z</t>
         </is>
       </c>
     </row>
@@ -8931,7 +8931,7 @@
       </c>
       <c r="K176" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:22Z</t>
+          <t>2026-10-02T18:24:22Z</t>
         </is>
       </c>
     </row>
@@ -8980,7 +8980,7 @@
       </c>
       <c r="K177" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:22Z</t>
+          <t>2026-10-02T18:24:22Z</t>
         </is>
       </c>
     </row>
@@ -9029,7 +9029,7 @@
       </c>
       <c r="K178" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:22Z</t>
+          <t>2026-10-02T18:24:22Z</t>
         </is>
       </c>
     </row>
@@ -9078,7 +9078,7 @@
       </c>
       <c r="K179" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:22Z</t>
+          <t>2026-10-02T18:24:22Z</t>
         </is>
       </c>
     </row>
@@ -9127,7 +9127,7 @@
       </c>
       <c r="K180" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:22Z</t>
+          <t>2026-10-02T18:24:22Z</t>
         </is>
       </c>
     </row>
@@ -9176,7 +9176,7 @@
       </c>
       <c r="K181" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:22Z</t>
+          <t>2026-10-02T18:24:22Z</t>
         </is>
       </c>
     </row>
@@ -9225,7 +9225,7 @@
       </c>
       <c r="K182" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:22Z</t>
+          <t>2026-10-02T18:24:22Z</t>
         </is>
       </c>
     </row>
@@ -9274,7 +9274,7 @@
       </c>
       <c r="K183" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:22Z</t>
+          <t>2026-10-02T18:24:22Z</t>
         </is>
       </c>
     </row>
@@ -9323,7 +9323,7 @@
       </c>
       <c r="K184" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:22Z</t>
+          <t>2026-10-02T18:24:22Z</t>
         </is>
       </c>
     </row>
@@ -9372,7 +9372,7 @@
       </c>
       <c r="K185" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:22Z</t>
+          <t>2026-10-02T18:24:22Z</t>
         </is>
       </c>
     </row>
@@ -9421,7 +9421,7 @@
       </c>
       <c r="K186" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:22Z</t>
+          <t>2026-10-02T18:24:22Z</t>
         </is>
       </c>
     </row>
@@ -9470,7 +9470,7 @@
       </c>
       <c r="K187" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:22Z</t>
+          <t>2026-10-02T18:24:22Z</t>
         </is>
       </c>
     </row>
@@ -9519,7 +9519,7 @@
       </c>
       <c r="K188" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:22Z</t>
+          <t>2026-10-02T18:24:22Z</t>
         </is>
       </c>
     </row>
@@ -9568,7 +9568,7 @@
       </c>
       <c r="K189" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:22Z</t>
+          <t>2026-10-02T18:24:22Z</t>
         </is>
       </c>
     </row>
@@ -9617,7 +9617,7 @@
       </c>
       <c r="K190" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:22Z</t>
+          <t>2026-10-02T18:24:22Z</t>
         </is>
       </c>
     </row>
@@ -9666,7 +9666,7 @@
       </c>
       <c r="K191" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:22Z</t>
+          <t>2026-10-02T18:24:22Z</t>
         </is>
       </c>
     </row>
@@ -9715,7 +9715,7 @@
       </c>
       <c r="K192" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:22Z</t>
+          <t>2026-10-02T18:24:22Z</t>
         </is>
       </c>
     </row>
@@ -9764,7 +9764,7 @@
       </c>
       <c r="K193" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:22Z</t>
+          <t>2026-10-02T18:24:22Z</t>
         </is>
       </c>
     </row>
@@ -9813,7 +9813,7 @@
       </c>
       <c r="K194" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:22Z</t>
+          <t>2026-10-02T18:24:22Z</t>
         </is>
       </c>
     </row>
@@ -9862,7 +9862,7 @@
       </c>
       <c r="K195" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:22Z</t>
+          <t>2026-10-02T18:24:22Z</t>
         </is>
       </c>
     </row>
@@ -9911,7 +9911,7 @@
       </c>
       <c r="K196" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:22Z</t>
+          <t>2026-10-02T18:24:22Z</t>
         </is>
       </c>
     </row>
@@ -9960,7 +9960,7 @@
       </c>
       <c r="K197" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:22Z</t>
+          <t>2026-10-02T18:24:22Z</t>
         </is>
       </c>
     </row>
@@ -10009,7 +10009,7 @@
       </c>
       <c r="K198" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:22Z</t>
+          <t>2026-10-02T18:24:22Z</t>
         </is>
       </c>
     </row>
@@ -10058,7 +10058,7 @@
       </c>
       <c r="K199" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:22Z</t>
+          <t>2026-10-02T18:24:22Z</t>
         </is>
       </c>
     </row>
@@ -10107,7 +10107,7 @@
       </c>
       <c r="K200" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:22Z</t>
+          <t>2026-10-02T18:24:22Z</t>
         </is>
       </c>
     </row>
@@ -10156,7 +10156,7 @@
       </c>
       <c r="K201" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:22Z</t>
+          <t>2026-10-02T18:24:22Z</t>
         </is>
       </c>
     </row>
@@ -10205,7 +10205,7 @@
       </c>
       <c r="K202" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:22Z</t>
+          <t>2026-10-02T18:24:22Z</t>
         </is>
       </c>
     </row>
@@ -10254,7 +10254,7 @@
       </c>
       <c r="K203" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:22Z</t>
+          <t>2026-10-02T18:24:22Z</t>
         </is>
       </c>
     </row>
@@ -10303,7 +10303,7 @@
       </c>
       <c r="K204" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:22Z</t>
+          <t>2026-10-02T18:24:22Z</t>
         </is>
       </c>
     </row>
@@ -10352,7 +10352,7 @@
       </c>
       <c r="K205" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:22Z</t>
+          <t>2026-10-02T18:24:22Z</t>
         </is>
       </c>
     </row>
@@ -10401,7 +10401,7 @@
       </c>
       <c r="K206" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:22Z</t>
+          <t>2026-10-02T18:24:22Z</t>
         </is>
       </c>
     </row>
@@ -10450,7 +10450,7 @@
       </c>
       <c r="K207" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:22Z</t>
+          <t>2026-10-02T18:24:22Z</t>
         </is>
       </c>
     </row>
@@ -10499,7 +10499,7 @@
       </c>
       <c r="K208" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:22Z</t>
+          <t>2026-10-02T18:24:22Z</t>
         </is>
       </c>
     </row>
@@ -10548,7 +10548,7 @@
       </c>
       <c r="K209" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:22Z</t>
+          <t>2026-10-02T18:24:22Z</t>
         </is>
       </c>
     </row>
@@ -10597,7 +10597,7 @@
       </c>
       <c r="K210" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:22Z</t>
+          <t>2026-10-02T18:24:22Z</t>
         </is>
       </c>
     </row>
@@ -10646,7 +10646,7 @@
       </c>
       <c r="K211" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:22Z</t>
+          <t>2026-10-02T18:24:22Z</t>
         </is>
       </c>
     </row>
@@ -10695,7 +10695,7 @@
       </c>
       <c r="K212" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:22Z</t>
+          <t>2026-10-02T18:24:22Z</t>
         </is>
       </c>
     </row>
@@ -10744,7 +10744,7 @@
       </c>
       <c r="K213" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:22Z</t>
+          <t>2026-10-02T18:24:22Z</t>
         </is>
       </c>
     </row>
@@ -10793,7 +10793,7 @@
       </c>
       <c r="K214" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:22Z</t>
+          <t>2026-10-02T18:24:22Z</t>
         </is>
       </c>
     </row>
@@ -10842,7 +10842,7 @@
       </c>
       <c r="K215" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:22Z</t>
+          <t>2026-10-02T18:24:22Z</t>
         </is>
       </c>
     </row>
@@ -10891,7 +10891,7 @@
       </c>
       <c r="K216" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:22Z</t>
+          <t>2026-10-02T18:24:22Z</t>
         </is>
       </c>
     </row>
@@ -10940,7 +10940,7 @@
       </c>
       <c r="K217" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:22Z</t>
+          <t>2026-10-02T18:24:22Z</t>
         </is>
       </c>
     </row>
@@ -10989,7 +10989,7 @@
       </c>
       <c r="K218" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:22Z</t>
+          <t>2026-10-02T18:24:22Z</t>
         </is>
       </c>
     </row>
@@ -11038,7 +11038,7 @@
       </c>
       <c r="K219" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:22Z</t>
+          <t>2026-10-02T18:24:22Z</t>
         </is>
       </c>
     </row>
@@ -11087,7 +11087,7 @@
       </c>
       <c r="K220" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:22Z</t>
+          <t>2026-10-02T18:24:22Z</t>
         </is>
       </c>
     </row>
@@ -11136,7 +11136,7 @@
       </c>
       <c r="K221" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:22Z</t>
+          <t>2026-10-02T18:24:22Z</t>
         </is>
       </c>
     </row>
@@ -11185,7 +11185,7 @@
       </c>
       <c r="K222" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:22Z</t>
+          <t>2026-10-02T18:24:22Z</t>
         </is>
       </c>
     </row>
@@ -11234,7 +11234,7 @@
       </c>
       <c r="K223" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:22Z</t>
+          <t>2026-10-02T18:24:22Z</t>
         </is>
       </c>
     </row>
@@ -11283,7 +11283,7 @@
       </c>
       <c r="K224" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:22Z</t>
+          <t>2026-10-02T18:24:22Z</t>
         </is>
       </c>
     </row>
@@ -11332,7 +11332,7 @@
       </c>
       <c r="K225" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:22Z</t>
+          <t>2026-10-02T18:24:22Z</t>
         </is>
       </c>
     </row>
@@ -11381,7 +11381,7 @@
       </c>
       <c r="K226" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:22Z</t>
+          <t>2026-10-02T18:24:22Z</t>
         </is>
       </c>
     </row>
@@ -11430,7 +11430,7 @@
       </c>
       <c r="K227" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:22Z</t>
+          <t>2026-10-02T18:24:22Z</t>
         </is>
       </c>
     </row>
@@ -11479,7 +11479,7 @@
       </c>
       <c r="K228" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:22Z</t>
+          <t>2026-10-02T18:24:22Z</t>
         </is>
       </c>
     </row>
@@ -11528,7 +11528,7 @@
       </c>
       <c r="K229" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:22Z</t>
+          <t>2026-10-02T18:24:22Z</t>
         </is>
       </c>
     </row>
@@ -11577,7 +11577,7 @@
       </c>
       <c r="K230" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:22Z</t>
+          <t>2026-10-02T18:24:22Z</t>
         </is>
       </c>
     </row>
@@ -11626,7 +11626,7 @@
       </c>
       <c r="K231" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:22Z</t>
+          <t>2026-10-02T18:24:22Z</t>
         </is>
       </c>
     </row>
@@ -11758,7 +11758,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:22Z</t>
+          <t>2026-10-02T18:24:22Z</t>
         </is>
       </c>
     </row>
@@ -11804,7 +11804,7 @@
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>{"date": "2026-08-01", "year": 2026, "month": 8, "month_name": "Agosto", "index_value": 637409769724325.1, "monthly_variation_pct": 8.9, "unit": "Índice base diciembre 2007=100 y variación mensual %", "frequency": "monthly", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/precios_consumidor/4_5_7_2.xls", "fetched_at": "2026-10-02T00:01:22Z"}</t>
+          <t>{"date": "2026-08-01", "year": 2026, "month": 8, "month_name": "Agosto", "index_value": 637409769724325.1, "monthly_variation_pct": 8.9, "unit": "Índice base diciembre 2007=100 y variación mensual %", "frequency": "monthly", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/precios_consumidor/4_5_7_2.xls", "fetched_at": "2026-10-02T18:24:22Z"}</t>
         </is>
       </c>
     </row>

--- a/assets/data/bcv/excel/ove_bcv_inpc_nacional_mensual.xlsx
+++ b/assets/data/bcv/excel/ove_bcv_inpc_nacional_mensual.xlsx
@@ -650,7 +650,7 @@
       </c>
       <c r="K7" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:22Z</t>
+          <t>2026-10-02T23:55:29Z</t>
         </is>
       </c>
     </row>
@@ -699,7 +699,7 @@
       </c>
       <c r="K8" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:22Z</t>
+          <t>2026-10-02T23:55:29Z</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="K9" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:22Z</t>
+          <t>2026-10-02T23:55:29Z</t>
         </is>
       </c>
     </row>
@@ -797,7 +797,7 @@
       </c>
       <c r="K10" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:22Z</t>
+          <t>2026-10-02T23:55:29Z</t>
         </is>
       </c>
     </row>
@@ -846,7 +846,7 @@
       </c>
       <c r="K11" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:22Z</t>
+          <t>2026-10-02T23:55:29Z</t>
         </is>
       </c>
     </row>
@@ -895,7 +895,7 @@
       </c>
       <c r="K12" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:22Z</t>
+          <t>2026-10-02T23:55:29Z</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="K13" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:22Z</t>
+          <t>2026-10-02T23:55:29Z</t>
         </is>
       </c>
     </row>
@@ -993,7 +993,7 @@
       </c>
       <c r="K14" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:22Z</t>
+          <t>2026-10-02T23:55:29Z</t>
         </is>
       </c>
     </row>
@@ -1042,7 +1042,7 @@
       </c>
       <c r="K15" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:22Z</t>
+          <t>2026-10-02T23:55:29Z</t>
         </is>
       </c>
     </row>
@@ -1091,7 +1091,7 @@
       </c>
       <c r="K16" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:22Z</t>
+          <t>2026-10-02T23:55:29Z</t>
         </is>
       </c>
     </row>
@@ -1140,7 +1140,7 @@
       </c>
       <c r="K17" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:22Z</t>
+          <t>2026-10-02T23:55:29Z</t>
         </is>
       </c>
     </row>
@@ -1189,7 +1189,7 @@
       </c>
       <c r="K18" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:22Z</t>
+          <t>2026-10-02T23:55:29Z</t>
         </is>
       </c>
     </row>
@@ -1238,7 +1238,7 @@
       </c>
       <c r="K19" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:22Z</t>
+          <t>2026-10-02T23:55:29Z</t>
         </is>
       </c>
     </row>
@@ -1287,7 +1287,7 @@
       </c>
       <c r="K20" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:22Z</t>
+          <t>2026-10-02T23:55:29Z</t>
         </is>
       </c>
     </row>
@@ -1336,7 +1336,7 @@
       </c>
       <c r="K21" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:22Z</t>
+          <t>2026-10-02T23:55:29Z</t>
         </is>
       </c>
     </row>
@@ -1385,7 +1385,7 @@
       </c>
       <c r="K22" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:22Z</t>
+          <t>2026-10-02T23:55:29Z</t>
         </is>
       </c>
     </row>
@@ -1434,7 +1434,7 @@
       </c>
       <c r="K23" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:22Z</t>
+          <t>2026-10-02T23:55:29Z</t>
         </is>
       </c>
     </row>
@@ -1483,7 +1483,7 @@
       </c>
       <c r="K24" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:22Z</t>
+          <t>2026-10-02T23:55:29Z</t>
         </is>
       </c>
     </row>
@@ -1532,7 +1532,7 @@
       </c>
       <c r="K25" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:22Z</t>
+          <t>2026-10-02T23:55:29Z</t>
         </is>
       </c>
     </row>
@@ -1581,7 +1581,7 @@
       </c>
       <c r="K26" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:22Z</t>
+          <t>2026-10-02T23:55:29Z</t>
         </is>
       </c>
     </row>
@@ -1630,7 +1630,7 @@
       </c>
       <c r="K27" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:22Z</t>
+          <t>2026-10-02T23:55:29Z</t>
         </is>
       </c>
     </row>
@@ -1679,7 +1679,7 @@
       </c>
       <c r="K28" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:22Z</t>
+          <t>2026-10-02T23:55:29Z</t>
         </is>
       </c>
     </row>
@@ -1728,7 +1728,7 @@
       </c>
       <c r="K29" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:22Z</t>
+          <t>2026-10-02T23:55:29Z</t>
         </is>
       </c>
     </row>
@@ -1777,7 +1777,7 @@
       </c>
       <c r="K30" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:22Z</t>
+          <t>2026-10-02T23:55:29Z</t>
         </is>
       </c>
     </row>
@@ -1826,7 +1826,7 @@
       </c>
       <c r="K31" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:22Z</t>
+          <t>2026-10-02T23:55:29Z</t>
         </is>
       </c>
     </row>
@@ -1875,7 +1875,7 @@
       </c>
       <c r="K32" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:22Z</t>
+          <t>2026-10-02T23:55:29Z</t>
         </is>
       </c>
     </row>
@@ -1924,7 +1924,7 @@
       </c>
       <c r="K33" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:22Z</t>
+          <t>2026-10-02T23:55:29Z</t>
         </is>
       </c>
     </row>
@@ -1973,7 +1973,7 @@
       </c>
       <c r="K34" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:22Z</t>
+          <t>2026-10-02T23:55:29Z</t>
         </is>
       </c>
     </row>
@@ -2022,7 +2022,7 @@
       </c>
       <c r="K35" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:22Z</t>
+          <t>2026-10-02T23:55:29Z</t>
         </is>
       </c>
     </row>
@@ -2071,7 +2071,7 @@
       </c>
       <c r="K36" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:22Z</t>
+          <t>2026-10-02T23:55:29Z</t>
         </is>
       </c>
     </row>
@@ -2120,7 +2120,7 @@
       </c>
       <c r="K37" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:22Z</t>
+          <t>2026-10-02T23:55:29Z</t>
         </is>
       </c>
     </row>
@@ -2169,7 +2169,7 @@
       </c>
       <c r="K38" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:22Z</t>
+          <t>2026-10-02T23:55:29Z</t>
         </is>
       </c>
     </row>
@@ -2218,7 +2218,7 @@
       </c>
       <c r="K39" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:22Z</t>
+          <t>2026-10-02T23:55:29Z</t>
         </is>
       </c>
     </row>
@@ -2267,7 +2267,7 @@
       </c>
       <c r="K40" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:22Z</t>
+          <t>2026-10-02T23:55:29Z</t>
         </is>
       </c>
     </row>
@@ -2316,7 +2316,7 @@
       </c>
       <c r="K41" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:22Z</t>
+          <t>2026-10-02T23:55:29Z</t>
         </is>
       </c>
     </row>
@@ -2365,7 +2365,7 @@
       </c>
       <c r="K42" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:22Z</t>
+          <t>2026-10-02T23:55:29Z</t>
         </is>
       </c>
     </row>
@@ -2414,7 +2414,7 @@
       </c>
       <c r="K43" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:22Z</t>
+          <t>2026-10-02T23:55:29Z</t>
         </is>
       </c>
     </row>
@@ -2463,7 +2463,7 @@
       </c>
       <c r="K44" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:22Z</t>
+          <t>2026-10-02T23:55:29Z</t>
         </is>
       </c>
     </row>
@@ -2512,7 +2512,7 @@
       </c>
       <c r="K45" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:22Z</t>
+          <t>2026-10-02T23:55:29Z</t>
         </is>
       </c>
     </row>
@@ -2561,7 +2561,7 @@
       </c>
       <c r="K46" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:22Z</t>
+          <t>2026-10-02T23:55:29Z</t>
         </is>
       </c>
     </row>
@@ -2610,7 +2610,7 @@
       </c>
       <c r="K47" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:22Z</t>
+          <t>2026-10-02T23:55:29Z</t>
         </is>
       </c>
     </row>
@@ -2659,7 +2659,7 @@
       </c>
       <c r="K48" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:22Z</t>
+          <t>2026-10-02T23:55:29Z</t>
         </is>
       </c>
     </row>
@@ -2708,7 +2708,7 @@
       </c>
       <c r="K49" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:22Z</t>
+          <t>2026-10-02T23:55:29Z</t>
         </is>
       </c>
     </row>
@@ -2757,7 +2757,7 @@
       </c>
       <c r="K50" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:22Z</t>
+          <t>2026-10-02T23:55:29Z</t>
         </is>
       </c>
     </row>
@@ -2806,7 +2806,7 @@
       </c>
       <c r="K51" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:22Z</t>
+          <t>2026-10-02T23:55:29Z</t>
         </is>
       </c>
     </row>
@@ -2855,7 +2855,7 @@
       </c>
       <c r="K52" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:22Z</t>
+          <t>2026-10-02T23:55:29Z</t>
         </is>
       </c>
     </row>
@@ -2904,7 +2904,7 @@
       </c>
       <c r="K53" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:22Z</t>
+          <t>2026-10-02T23:55:29Z</t>
         </is>
       </c>
     </row>
@@ -2953,7 +2953,7 @@
       </c>
       <c r="K54" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:22Z</t>
+          <t>2026-10-02T23:55:29Z</t>
         </is>
       </c>
     </row>
@@ -3002,7 +3002,7 @@
       </c>
       <c r="K55" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:22Z</t>
+          <t>2026-10-02T23:55:29Z</t>
         </is>
       </c>
     </row>
@@ -3051,7 +3051,7 @@
       </c>
       <c r="K56" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:22Z</t>
+          <t>2026-10-02T23:55:29Z</t>
         </is>
       </c>
     </row>
@@ -3100,7 +3100,7 @@
       </c>
       <c r="K57" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:22Z</t>
+          <t>2026-10-02T23:55:29Z</t>
         </is>
       </c>
     </row>
@@ -3149,7 +3149,7 @@
       </c>
       <c r="K58" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:22Z</t>
+          <t>2026-10-02T23:55:29Z</t>
         </is>
       </c>
     </row>
@@ -3198,7 +3198,7 @@
       </c>
       <c r="K59" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:22Z</t>
+          <t>2026-10-02T23:55:29Z</t>
         </is>
       </c>
     </row>
@@ -3247,7 +3247,7 @@
       </c>
       <c r="K60" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:22Z</t>
+          <t>2026-10-02T23:55:29Z</t>
         </is>
       </c>
     </row>
@@ -3296,7 +3296,7 @@
       </c>
       <c r="K61" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:22Z</t>
+          <t>2026-10-02T23:55:29Z</t>
         </is>
       </c>
     </row>
@@ -3345,7 +3345,7 @@
       </c>
       <c r="K62" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:22Z</t>
+          <t>2026-10-02T23:55:29Z</t>
         </is>
       </c>
     </row>
@@ -3394,7 +3394,7 @@
       </c>
       <c r="K63" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:22Z</t>
+          <t>2026-10-02T23:55:29Z</t>
         </is>
       </c>
     </row>
@@ -3443,7 +3443,7 @@
       </c>
       <c r="K64" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:22Z</t>
+          <t>2026-10-02T23:55:29Z</t>
         </is>
       </c>
     </row>
@@ -3492,7 +3492,7 @@
       </c>
       <c r="K65" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:22Z</t>
+          <t>2026-10-02T23:55:29Z</t>
         </is>
       </c>
     </row>
@@ -3541,7 +3541,7 @@
       </c>
       <c r="K66" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:22Z</t>
+          <t>2026-10-02T23:55:29Z</t>
         </is>
       </c>
     </row>
@@ -3590,7 +3590,7 @@
       </c>
       <c r="K67" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:22Z</t>
+          <t>2026-10-02T23:55:29Z</t>
         </is>
       </c>
     </row>
@@ -3639,7 +3639,7 @@
       </c>
       <c r="K68" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:22Z</t>
+          <t>2026-10-02T23:55:29Z</t>
         </is>
       </c>
     </row>
@@ -3688,7 +3688,7 @@
       </c>
       <c r="K69" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:22Z</t>
+          <t>2026-10-02T23:55:29Z</t>
         </is>
       </c>
     </row>
@@ -3737,7 +3737,7 @@
       </c>
       <c r="K70" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:22Z</t>
+          <t>2026-10-02T23:55:29Z</t>
         </is>
       </c>
     </row>
@@ -3786,7 +3786,7 @@
       </c>
       <c r="K71" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:22Z</t>
+          <t>2026-10-02T23:55:29Z</t>
         </is>
       </c>
     </row>
@@ -3835,7 +3835,7 @@
       </c>
       <c r="K72" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:22Z</t>
+          <t>2026-10-02T23:55:29Z</t>
         </is>
       </c>
     </row>
@@ -3884,7 +3884,7 @@
       </c>
       <c r="K73" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:22Z</t>
+          <t>2026-10-02T23:55:29Z</t>
         </is>
       </c>
     </row>
@@ -3933,7 +3933,7 @@
       </c>
       <c r="K74" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:22Z</t>
+          <t>2026-10-02T23:55:29Z</t>
         </is>
       </c>
     </row>
@@ -3982,7 +3982,7 @@
       </c>
       <c r="K75" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:22Z</t>
+          <t>2026-10-02T23:55:29Z</t>
         </is>
       </c>
     </row>
@@ -4031,7 +4031,7 @@
       </c>
       <c r="K76" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:22Z</t>
+          <t>2026-10-02T23:55:29Z</t>
         </is>
       </c>
     </row>
@@ -4080,7 +4080,7 @@
       </c>
       <c r="K77" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:22Z</t>
+          <t>2026-10-02T23:55:29Z</t>
         </is>
       </c>
     </row>
@@ -4129,7 +4129,7 @@
       </c>
       <c r="K78" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:22Z</t>
+          <t>2026-10-02T23:55:29Z</t>
         </is>
       </c>
     </row>
@@ -4178,7 +4178,7 @@
       </c>
       <c r="K79" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:22Z</t>
+          <t>2026-10-02T23:55:29Z</t>
         </is>
       </c>
     </row>
@@ -4227,7 +4227,7 @@
       </c>
       <c r="K80" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:22Z</t>
+          <t>2026-10-02T23:55:29Z</t>
         </is>
       </c>
     </row>
@@ -4276,7 +4276,7 @@
       </c>
       <c r="K81" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:22Z</t>
+          <t>2026-10-02T23:55:29Z</t>
         </is>
       </c>
     </row>
@@ -4325,7 +4325,7 @@
       </c>
       <c r="K82" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:22Z</t>
+          <t>2026-10-02T23:55:29Z</t>
         </is>
       </c>
     </row>
@@ -4374,7 +4374,7 @@
       </c>
       <c r="K83" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:22Z</t>
+          <t>2026-10-02T23:55:29Z</t>
         </is>
       </c>
     </row>
@@ -4423,7 +4423,7 @@
       </c>
       <c r="K84" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:22Z</t>
+          <t>2026-10-02T23:55:29Z</t>
         </is>
       </c>
     </row>
@@ -4472,7 +4472,7 @@
       </c>
       <c r="K85" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:22Z</t>
+          <t>2026-10-02T23:55:29Z</t>
         </is>
       </c>
     </row>
@@ -4521,7 +4521,7 @@
       </c>
       <c r="K86" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:22Z</t>
+          <t>2026-10-02T23:55:29Z</t>
         </is>
       </c>
     </row>
@@ -4570,7 +4570,7 @@
       </c>
       <c r="K87" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:22Z</t>
+          <t>2026-10-02T23:55:29Z</t>
         </is>
       </c>
     </row>
@@ -4619,7 +4619,7 @@
       </c>
       <c r="K88" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:22Z</t>
+          <t>2026-10-02T23:55:29Z</t>
         </is>
       </c>
     </row>
@@ -4668,7 +4668,7 @@
       </c>
       <c r="K89" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:22Z</t>
+          <t>2026-10-02T23:55:29Z</t>
         </is>
       </c>
     </row>
@@ -4717,7 +4717,7 @@
       </c>
       <c r="K90" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:22Z</t>
+          <t>2026-10-02T23:55:29Z</t>
         </is>
       </c>
     </row>
@@ -4766,7 +4766,7 @@
       </c>
       <c r="K91" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:22Z</t>
+          <t>2026-10-02T23:55:29Z</t>
         </is>
       </c>
     </row>
@@ -4815,7 +4815,7 @@
       </c>
       <c r="K92" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:22Z</t>
+          <t>2026-10-02T23:55:29Z</t>
         </is>
       </c>
     </row>
@@ -4864,7 +4864,7 @@
       </c>
       <c r="K93" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:22Z</t>
+          <t>2026-10-02T23:55:29Z</t>
         </is>
       </c>
     </row>
@@ -4913,7 +4913,7 @@
       </c>
       <c r="K94" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:22Z</t>
+          <t>2026-10-02T23:55:29Z</t>
         </is>
       </c>
     </row>
@@ -4962,7 +4962,7 @@
       </c>
       <c r="K95" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:22Z</t>
+          <t>2026-10-02T23:55:29Z</t>
         </is>
       </c>
     </row>
@@ -5011,7 +5011,7 @@
       </c>
       <c r="K96" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:22Z</t>
+          <t>2026-10-02T23:55:29Z</t>
         </is>
       </c>
     </row>
@@ -5060,7 +5060,7 @@
       </c>
       <c r="K97" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:22Z</t>
+          <t>2026-10-02T23:55:29Z</t>
         </is>
       </c>
     </row>
@@ -5109,7 +5109,7 @@
       </c>
       <c r="K98" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:22Z</t>
+          <t>2026-10-02T23:55:29Z</t>
         </is>
       </c>
     </row>
@@ -5158,7 +5158,7 @@
       </c>
       <c r="K99" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:22Z</t>
+          <t>2026-10-02T23:55:29Z</t>
         </is>
       </c>
     </row>
@@ -5207,7 +5207,7 @@
       </c>
       <c r="K100" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:22Z</t>
+          <t>2026-10-02T23:55:29Z</t>
         </is>
       </c>
     </row>
@@ -5256,7 +5256,7 @@
       </c>
       <c r="K101" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:22Z</t>
+          <t>2026-10-02T23:55:29Z</t>
         </is>
       </c>
     </row>
@@ -5305,7 +5305,7 @@
       </c>
       <c r="K102" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:22Z</t>
+          <t>2026-10-02T23:55:29Z</t>
         </is>
       </c>
     </row>
@@ -5354,7 +5354,7 @@
       </c>
       <c r="K103" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:22Z</t>
+          <t>2026-10-02T23:55:29Z</t>
         </is>
       </c>
     </row>
@@ -5403,7 +5403,7 @@
       </c>
       <c r="K104" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:22Z</t>
+          <t>2026-10-02T23:55:29Z</t>
         </is>
       </c>
     </row>
@@ -5452,7 +5452,7 @@
       </c>
       <c r="K105" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:22Z</t>
+          <t>2026-10-02T23:55:29Z</t>
         </is>
       </c>
     </row>
@@ -5501,7 +5501,7 @@
       </c>
       <c r="K106" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:22Z</t>
+          <t>2026-10-02T23:55:29Z</t>
         </is>
       </c>
     </row>
@@ -5550,7 +5550,7 @@
       </c>
       <c r="K107" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:22Z</t>
+          <t>2026-10-02T23:55:29Z</t>
         </is>
       </c>
     </row>
@@ -5599,7 +5599,7 @@
       </c>
       <c r="K108" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:22Z</t>
+          <t>2026-10-02T23:55:29Z</t>
         </is>
       </c>
     </row>
@@ -5648,7 +5648,7 @@
       </c>
       <c r="K109" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:22Z</t>
+          <t>2026-10-02T23:55:29Z</t>
         </is>
       </c>
     </row>
@@ -5697,7 +5697,7 @@
       </c>
       <c r="K110" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:22Z</t>
+          <t>2026-10-02T23:55:29Z</t>
         </is>
       </c>
     </row>
@@ -5746,7 +5746,7 @@
       </c>
       <c r="K111" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:22Z</t>
+          <t>2026-10-02T23:55:29Z</t>
         </is>
       </c>
     </row>
@@ -5795,7 +5795,7 @@
       </c>
       <c r="K112" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:22Z</t>
+          <t>2026-10-02T23:55:29Z</t>
         </is>
       </c>
     </row>
@@ -5844,7 +5844,7 @@
       </c>
       <c r="K113" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:22Z</t>
+          <t>2026-10-02T23:55:29Z</t>
         </is>
       </c>
     </row>
@@ -5893,7 +5893,7 @@
       </c>
       <c r="K114" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:22Z</t>
+          <t>2026-10-02T23:55:29Z</t>
         </is>
       </c>
     </row>
@@ -5942,7 +5942,7 @@
       </c>
       <c r="K115" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:22Z</t>
+          <t>2026-10-02T23:55:29Z</t>
         </is>
       </c>
     </row>
@@ -5991,7 +5991,7 @@
       </c>
       <c r="K116" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:22Z</t>
+          <t>2026-10-02T23:55:29Z</t>
         </is>
       </c>
     </row>
@@ -6040,7 +6040,7 @@
       </c>
       <c r="K117" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:22Z</t>
+          <t>2026-10-02T23:55:29Z</t>
         </is>
       </c>
     </row>
@@ -6089,7 +6089,7 @@
       </c>
       <c r="K118" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:22Z</t>
+          <t>2026-10-02T23:55:29Z</t>
         </is>
       </c>
     </row>
@@ -6138,7 +6138,7 @@
       </c>
       <c r="K119" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:22Z</t>
+          <t>2026-10-02T23:55:29Z</t>
         </is>
       </c>
     </row>
@@ -6187,7 +6187,7 @@
       </c>
       <c r="K120" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:22Z</t>
+          <t>2026-10-02T23:55:29Z</t>
         </is>
       </c>
     </row>
@@ -6236,7 +6236,7 @@
       </c>
       <c r="K121" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:22Z</t>
+          <t>2026-10-02T23:55:29Z</t>
         </is>
       </c>
     </row>
@@ -6285,7 +6285,7 @@
       </c>
       <c r="K122" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:22Z</t>
+          <t>2026-10-02T23:55:29Z</t>
         </is>
       </c>
     </row>
@@ -6334,7 +6334,7 @@
       </c>
       <c r="K123" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:22Z</t>
+          <t>2026-10-02T23:55:29Z</t>
         </is>
       </c>
     </row>
@@ -6383,7 +6383,7 @@
       </c>
       <c r="K124" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:22Z</t>
+          <t>2026-10-02T23:55:29Z</t>
         </is>
       </c>
     </row>
@@ -6432,7 +6432,7 @@
       </c>
       <c r="K125" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:22Z</t>
+          <t>2026-10-02T23:55:29Z</t>
         </is>
       </c>
     </row>
@@ -6481,7 +6481,7 @@
       </c>
       <c r="K126" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:22Z</t>
+          <t>2026-10-02T23:55:29Z</t>
         </is>
       </c>
     </row>
@@ -6530,7 +6530,7 @@
       </c>
       <c r="K127" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:22Z</t>
+          <t>2026-10-02T23:55:29Z</t>
         </is>
       </c>
     </row>
@@ -6579,7 +6579,7 @@
       </c>
       <c r="K128" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:22Z</t>
+          <t>2026-10-02T23:55:29Z</t>
         </is>
       </c>
     </row>
@@ -6628,7 +6628,7 @@
       </c>
       <c r="K129" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:22Z</t>
+          <t>2026-10-02T23:55:29Z</t>
         </is>
       </c>
     </row>
@@ -6677,7 +6677,7 @@
       </c>
       <c r="K130" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:22Z</t>
+          <t>2026-10-02T23:55:29Z</t>
         </is>
       </c>
     </row>
@@ -6726,7 +6726,7 @@
       </c>
       <c r="K131" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:22Z</t>
+          <t>2026-10-02T23:55:29Z</t>
         </is>
       </c>
     </row>
@@ -6775,7 +6775,7 @@
       </c>
       <c r="K132" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:22Z</t>
+          <t>2026-10-02T23:55:29Z</t>
         </is>
       </c>
     </row>
@@ -6824,7 +6824,7 @@
       </c>
       <c r="K133" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:22Z</t>
+          <t>2026-10-02T23:55:29Z</t>
         </is>
       </c>
     </row>
@@ -6873,7 +6873,7 @@
       </c>
       <c r="K134" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:22Z</t>
+          <t>2026-10-02T23:55:29Z</t>
         </is>
       </c>
     </row>
@@ -6922,7 +6922,7 @@
       </c>
       <c r="K135" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:22Z</t>
+          <t>2026-10-02T23:55:29Z</t>
         </is>
       </c>
     </row>
@@ -6971,7 +6971,7 @@
       </c>
       <c r="K136" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:22Z</t>
+          <t>2026-10-02T23:55:29Z</t>
         </is>
       </c>
     </row>
@@ -7020,7 +7020,7 @@
       </c>
       <c r="K137" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:22Z</t>
+          <t>2026-10-02T23:55:29Z</t>
         </is>
       </c>
     </row>
@@ -7069,7 +7069,7 @@
       </c>
       <c r="K138" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:22Z</t>
+          <t>2026-10-02T23:55:29Z</t>
         </is>
       </c>
     </row>
@@ -7118,7 +7118,7 @@
       </c>
       <c r="K139" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:22Z</t>
+          <t>2026-10-02T23:55:29Z</t>
         </is>
       </c>
     </row>
@@ -7167,7 +7167,7 @@
       </c>
       <c r="K140" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:22Z</t>
+          <t>2026-10-02T23:55:29Z</t>
         </is>
       </c>
     </row>
@@ -7216,7 +7216,7 @@
       </c>
       <c r="K141" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:22Z</t>
+          <t>2026-10-02T23:55:29Z</t>
         </is>
       </c>
     </row>
@@ -7265,7 +7265,7 @@
       </c>
       <c r="K142" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:22Z</t>
+          <t>2026-10-02T23:55:29Z</t>
         </is>
       </c>
     </row>
@@ -7314,7 +7314,7 @@
       </c>
       <c r="K143" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:22Z</t>
+          <t>2026-10-02T23:55:29Z</t>
         </is>
       </c>
     </row>
@@ -7363,7 +7363,7 @@
       </c>
       <c r="K144" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:22Z</t>
+          <t>2026-10-02T23:55:29Z</t>
         </is>
       </c>
     </row>
@@ -7412,7 +7412,7 @@
       </c>
       <c r="K145" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:22Z</t>
+          <t>2026-10-02T23:55:29Z</t>
         </is>
       </c>
     </row>
@@ -7461,7 +7461,7 @@
       </c>
       <c r="K146" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:22Z</t>
+          <t>2026-10-02T23:55:29Z</t>
         </is>
       </c>
     </row>
@@ -7510,7 +7510,7 @@
       </c>
       <c r="K147" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:22Z</t>
+          <t>2026-10-02T23:55:29Z</t>
         </is>
       </c>
     </row>
@@ -7559,7 +7559,7 @@
       </c>
       <c r="K148" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:22Z</t>
+          <t>2026-10-02T23:55:29Z</t>
         </is>
       </c>
     </row>
@@ -7608,7 +7608,7 @@
       </c>
       <c r="K149" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:22Z</t>
+          <t>2026-10-02T23:55:29Z</t>
         </is>
       </c>
     </row>
@@ -7657,7 +7657,7 @@
       </c>
       <c r="K150" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:22Z</t>
+          <t>2026-10-02T23:55:29Z</t>
         </is>
       </c>
     </row>
@@ -7706,7 +7706,7 @@
       </c>
       <c r="K151" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:22Z</t>
+          <t>2026-10-02T23:55:29Z</t>
         </is>
       </c>
     </row>
@@ -7755,7 +7755,7 @@
       </c>
       <c r="K152" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:22Z</t>
+          <t>2026-10-02T23:55:29Z</t>
         </is>
       </c>
     </row>
@@ -7804,7 +7804,7 @@
       </c>
       <c r="K153" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:22Z</t>
+          <t>2026-10-02T23:55:29Z</t>
         </is>
       </c>
     </row>
@@ -7853,7 +7853,7 @@
       </c>
       <c r="K154" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:22Z</t>
+          <t>2026-10-02T23:55:29Z</t>
         </is>
       </c>
     </row>
@@ -7902,7 +7902,7 @@
       </c>
       <c r="K155" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:22Z</t>
+          <t>2026-10-02T23:55:29Z</t>
         </is>
       </c>
     </row>
@@ -7951,7 +7951,7 @@
       </c>
       <c r="K156" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:22Z</t>
+          <t>2026-10-02T23:55:29Z</t>
         </is>
       </c>
     </row>
@@ -8000,7 +8000,7 @@
       </c>
       <c r="K157" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:22Z</t>
+          <t>2026-10-02T23:55:29Z</t>
         </is>
       </c>
     </row>
@@ -8049,7 +8049,7 @@
       </c>
       <c r="K158" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:22Z</t>
+          <t>2026-10-02T23:55:29Z</t>
         </is>
       </c>
     </row>
@@ -8098,7 +8098,7 @@
       </c>
       <c r="K159" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:22Z</t>
+          <t>2026-10-02T23:55:29Z</t>
         </is>
       </c>
     </row>
@@ -8147,7 +8147,7 @@
       </c>
       <c r="K160" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:22Z</t>
+          <t>2026-10-02T23:55:29Z</t>
         </is>
       </c>
     </row>
@@ -8196,7 +8196,7 @@
       </c>
       <c r="K161" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:22Z</t>
+          <t>2026-10-02T23:55:29Z</t>
         </is>
       </c>
     </row>
@@ -8245,7 +8245,7 @@
       </c>
       <c r="K162" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:22Z</t>
+          <t>2026-10-02T23:55:29Z</t>
         </is>
       </c>
     </row>
@@ -8294,7 +8294,7 @@
       </c>
       <c r="K163" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:22Z</t>
+          <t>2026-10-02T23:55:29Z</t>
         </is>
       </c>
     </row>
@@ -8343,7 +8343,7 @@
       </c>
       <c r="K164" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:22Z</t>
+          <t>2026-10-02T23:55:29Z</t>
         </is>
       </c>
     </row>
@@ -8392,7 +8392,7 @@
       </c>
       <c r="K165" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:22Z</t>
+          <t>2026-10-02T23:55:29Z</t>
         </is>
       </c>
     </row>
@@ -8441,7 +8441,7 @@
       </c>
       <c r="K166" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:22Z</t>
+          <t>2026-10-02T23:55:29Z</t>
         </is>
       </c>
     </row>
@@ -8490,7 +8490,7 @@
       </c>
       <c r="K167" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:22Z</t>
+          <t>2026-10-02T23:55:29Z</t>
         </is>
       </c>
     </row>
@@ -8539,7 +8539,7 @@
       </c>
       <c r="K168" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:22Z</t>
+          <t>2026-10-02T23:55:29Z</t>
         </is>
       </c>
     </row>
@@ -8588,7 +8588,7 @@
       </c>
       <c r="K169" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:22Z</t>
+          <t>2026-10-02T23:55:29Z</t>
         </is>
       </c>
     </row>
@@ -8637,7 +8637,7 @@
       </c>
       <c r="K170" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:22Z</t>
+          <t>2026-10-02T23:55:29Z</t>
         </is>
       </c>
     </row>
@@ -8686,7 +8686,7 @@
       </c>
       <c r="K171" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:22Z</t>
+          <t>2026-10-02T23:55:29Z</t>
         </is>
       </c>
     </row>
@@ -8735,7 +8735,7 @@
       </c>
       <c r="K172" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:22Z</t>
+          <t>2026-10-02T23:55:29Z</t>
         </is>
       </c>
     </row>
@@ -8784,7 +8784,7 @@
       </c>
       <c r="K173" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:22Z</t>
+          <t>2026-10-02T23:55:29Z</t>
         </is>
       </c>
     </row>
@@ -8833,7 +8833,7 @@
       </c>
       <c r="K174" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:22Z</t>
+          <t>2026-10-02T23:55:29Z</t>
         </is>
       </c>
     </row>
@@ -8882,7 +8882,7 @@
       </c>
       <c r="K175" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:22Z</t>
+          <t>2026-10-02T23:55:29Z</t>
         </is>
       </c>
     </row>
@@ -8931,7 +8931,7 @@
       </c>
       <c r="K176" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:22Z</t>
+          <t>2026-10-02T23:55:29Z</t>
         </is>
       </c>
     </row>
@@ -8980,7 +8980,7 @@
       </c>
       <c r="K177" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:22Z</t>
+          <t>2026-10-02T23:55:29Z</t>
         </is>
       </c>
     </row>
@@ -9029,7 +9029,7 @@
       </c>
       <c r="K178" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:22Z</t>
+          <t>2026-10-02T23:55:29Z</t>
         </is>
       </c>
     </row>
@@ -9078,7 +9078,7 @@
       </c>
       <c r="K179" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:22Z</t>
+          <t>2026-10-02T23:55:29Z</t>
         </is>
       </c>
     </row>
@@ -9127,7 +9127,7 @@
       </c>
       <c r="K180" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:22Z</t>
+          <t>2026-10-02T23:55:29Z</t>
         </is>
       </c>
     </row>
@@ -9176,7 +9176,7 @@
       </c>
       <c r="K181" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:22Z</t>
+          <t>2026-10-02T23:55:29Z</t>
         </is>
       </c>
     </row>
@@ -9225,7 +9225,7 @@
       </c>
       <c r="K182" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:22Z</t>
+          <t>2026-10-02T23:55:29Z</t>
         </is>
       </c>
     </row>
@@ -9274,7 +9274,7 @@
       </c>
       <c r="K183" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:22Z</t>
+          <t>2026-10-02T23:55:29Z</t>
         </is>
       </c>
     </row>
@@ -9323,7 +9323,7 @@
       </c>
       <c r="K184" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:22Z</t>
+          <t>2026-10-02T23:55:29Z</t>
         </is>
       </c>
     </row>
@@ -9372,7 +9372,7 @@
       </c>
       <c r="K185" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:22Z</t>
+          <t>2026-10-02T23:55:29Z</t>
         </is>
       </c>
     </row>
@@ -9421,7 +9421,7 @@
       </c>
       <c r="K186" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:22Z</t>
+          <t>2026-10-02T23:55:29Z</t>
         </is>
       </c>
     </row>
@@ -9470,7 +9470,7 @@
       </c>
       <c r="K187" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:22Z</t>
+          <t>2026-10-02T23:55:29Z</t>
         </is>
       </c>
     </row>
@@ -9519,7 +9519,7 @@
       </c>
       <c r="K188" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:22Z</t>
+          <t>2026-10-02T23:55:29Z</t>
         </is>
       </c>
     </row>
@@ -9568,7 +9568,7 @@
       </c>
       <c r="K189" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:22Z</t>
+          <t>2026-10-02T23:55:29Z</t>
         </is>
       </c>
     </row>
@@ -9617,7 +9617,7 @@
       </c>
       <c r="K190" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:22Z</t>
+          <t>2026-10-02T23:55:29Z</t>
         </is>
       </c>
     </row>
@@ -9666,7 +9666,7 @@
       </c>
       <c r="K191" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:22Z</t>
+          <t>2026-10-02T23:55:29Z</t>
         </is>
       </c>
     </row>
@@ -9715,7 +9715,7 @@
       </c>
       <c r="K192" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:22Z</t>
+          <t>2026-10-02T23:55:29Z</t>
         </is>
       </c>
     </row>
@@ -9764,7 +9764,7 @@
       </c>
       <c r="K193" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:22Z</t>
+          <t>2026-10-02T23:55:29Z</t>
         </is>
       </c>
     </row>
@@ -9813,7 +9813,7 @@
       </c>
       <c r="K194" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:22Z</t>
+          <t>2026-10-02T23:55:29Z</t>
         </is>
       </c>
     </row>
@@ -9862,7 +9862,7 @@
       </c>
       <c r="K195" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:22Z</t>
+          <t>2026-10-02T23:55:29Z</t>
         </is>
       </c>
     </row>
@@ -9911,7 +9911,7 @@
       </c>
       <c r="K196" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:22Z</t>
+          <t>2026-10-02T23:55:29Z</t>
         </is>
       </c>
     </row>
@@ -9960,7 +9960,7 @@
       </c>
       <c r="K197" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:22Z</t>
+          <t>2026-10-02T23:55:29Z</t>
         </is>
       </c>
     </row>
@@ -10009,7 +10009,7 @@
       </c>
       <c r="K198" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:22Z</t>
+          <t>2026-10-02T23:55:29Z</t>
         </is>
       </c>
     </row>
@@ -10058,7 +10058,7 @@
       </c>
       <c r="K199" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:22Z</t>
+          <t>2026-10-02T23:55:29Z</t>
         </is>
       </c>
     </row>
@@ -10107,7 +10107,7 @@
       </c>
       <c r="K200" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:22Z</t>
+          <t>2026-10-02T23:55:29Z</t>
         </is>
       </c>
     </row>
@@ -10156,7 +10156,7 @@
       </c>
       <c r="K201" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:22Z</t>
+          <t>2026-10-02T23:55:29Z</t>
         </is>
       </c>
     </row>
@@ -10205,7 +10205,7 @@
       </c>
       <c r="K202" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:22Z</t>
+          <t>2026-10-02T23:55:29Z</t>
         </is>
       </c>
     </row>
@@ -10254,7 +10254,7 @@
       </c>
       <c r="K203" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:22Z</t>
+          <t>2026-10-02T23:55:29Z</t>
         </is>
       </c>
     </row>
@@ -10303,7 +10303,7 @@
       </c>
       <c r="K204" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:22Z</t>
+          <t>2026-10-02T23:55:29Z</t>
         </is>
       </c>
     </row>
@@ -10352,7 +10352,7 @@
       </c>
       <c r="K205" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:22Z</t>
+          <t>2026-10-02T23:55:29Z</t>
         </is>
       </c>
     </row>
@@ -10401,7 +10401,7 @@
       </c>
       <c r="K206" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:22Z</t>
+          <t>2026-10-02T23:55:29Z</t>
         </is>
       </c>
     </row>
@@ -10450,7 +10450,7 @@
       </c>
       <c r="K207" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:22Z</t>
+          <t>2026-10-02T23:55:29Z</t>
         </is>
       </c>
     </row>
@@ -10499,7 +10499,7 @@
       </c>
       <c r="K208" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:22Z</t>
+          <t>2026-10-02T23:55:29Z</t>
         </is>
       </c>
     </row>
@@ -10548,7 +10548,7 @@
       </c>
       <c r="K209" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:22Z</t>
+          <t>2026-10-02T23:55:29Z</t>
         </is>
       </c>
     </row>
@@ -10597,7 +10597,7 @@
       </c>
       <c r="K210" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:22Z</t>
+          <t>2026-10-02T23:55:29Z</t>
         </is>
       </c>
     </row>
@@ -10646,7 +10646,7 @@
       </c>
       <c r="K211" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:22Z</t>
+          <t>2026-10-02T23:55:29Z</t>
         </is>
       </c>
     </row>
@@ -10695,7 +10695,7 @@
       </c>
       <c r="K212" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:22Z</t>
+          <t>2026-10-02T23:55:29Z</t>
         </is>
       </c>
     </row>
@@ -10744,7 +10744,7 @@
       </c>
       <c r="K213" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:22Z</t>
+          <t>2026-10-02T23:55:29Z</t>
         </is>
       </c>
     </row>
@@ -10793,7 +10793,7 @@
       </c>
       <c r="K214" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:22Z</t>
+          <t>2026-10-02T23:55:29Z</t>
         </is>
       </c>
     </row>
@@ -10842,7 +10842,7 @@
       </c>
       <c r="K215" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:22Z</t>
+          <t>2026-10-02T23:55:29Z</t>
         </is>
       </c>
     </row>
@@ -10891,7 +10891,7 @@
       </c>
       <c r="K216" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:22Z</t>
+          <t>2026-10-02T23:55:29Z</t>
         </is>
       </c>
     </row>
@@ -10940,7 +10940,7 @@
       </c>
       <c r="K217" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:22Z</t>
+          <t>2026-10-02T23:55:29Z</t>
         </is>
       </c>
     </row>
@@ -10989,7 +10989,7 @@
       </c>
       <c r="K218" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:22Z</t>
+          <t>2026-10-02T23:55:29Z</t>
         </is>
       </c>
     </row>
@@ -11038,7 +11038,7 @@
       </c>
       <c r="K219" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:22Z</t>
+          <t>2026-10-02T23:55:29Z</t>
         </is>
       </c>
     </row>
@@ -11087,7 +11087,7 @@
       </c>
       <c r="K220" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:22Z</t>
+          <t>2026-10-02T23:55:29Z</t>
         </is>
       </c>
     </row>
@@ -11136,7 +11136,7 @@
       </c>
       <c r="K221" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:22Z</t>
+          <t>2026-10-02T23:55:29Z</t>
         </is>
       </c>
     </row>
@@ -11185,7 +11185,7 @@
       </c>
       <c r="K222" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:22Z</t>
+          <t>2026-10-02T23:55:29Z</t>
         </is>
       </c>
     </row>
@@ -11234,7 +11234,7 @@
       </c>
       <c r="K223" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:22Z</t>
+          <t>2026-10-02T23:55:29Z</t>
         </is>
       </c>
     </row>
@@ -11283,7 +11283,7 @@
       </c>
       <c r="K224" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:22Z</t>
+          <t>2026-10-02T23:55:29Z</t>
         </is>
       </c>
     </row>
@@ -11332,7 +11332,7 @@
       </c>
       <c r="K225" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:22Z</t>
+          <t>2026-10-02T23:55:29Z</t>
         </is>
       </c>
     </row>
@@ -11381,7 +11381,7 @@
       </c>
       <c r="K226" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:22Z</t>
+          <t>2026-10-02T23:55:29Z</t>
         </is>
       </c>
     </row>
@@ -11430,7 +11430,7 @@
       </c>
       <c r="K227" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:22Z</t>
+          <t>2026-10-02T23:55:29Z</t>
         </is>
       </c>
     </row>
@@ -11479,7 +11479,7 @@
       </c>
       <c r="K228" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:22Z</t>
+          <t>2026-10-02T23:55:29Z</t>
         </is>
       </c>
     </row>
@@ -11528,7 +11528,7 @@
       </c>
       <c r="K229" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:22Z</t>
+          <t>2026-10-02T23:55:29Z</t>
         </is>
       </c>
     </row>
@@ -11577,7 +11577,7 @@
       </c>
       <c r="K230" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:22Z</t>
+          <t>2026-10-02T23:55:29Z</t>
         </is>
       </c>
     </row>
@@ -11626,7 +11626,7 @@
       </c>
       <c r="K231" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:22Z</t>
+          <t>2026-10-02T23:55:29Z</t>
         </is>
       </c>
     </row>
@@ -11758,7 +11758,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:22Z</t>
+          <t>2026-10-02T23:55:29Z</t>
         </is>
       </c>
     </row>
@@ -11804,7 +11804,7 @@
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>{"date": "2026-08-01", "year": 2026, "month": 8, "month_name": "Agosto", "index_value": 637409769724325.1, "monthly_variation_pct": 8.9, "unit": "Índice base diciembre 2007=100 y variación mensual %", "frequency": "monthly", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/precios_consumidor/4_5_7_2.xls", "fetched_at": "2026-10-02T18:24:22Z"}</t>
+          <t>{"date": "2026-08-01", "year": 2026, "month": 8, "month_name": "Agosto", "index_value": 637409769724325.1, "monthly_variation_pct": 8.9, "unit": "Índice base diciembre 2007=100 y variación mensual %", "frequency": "monthly", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/precios_consumidor/4_5_7_2.xls", "fetched_at": "2026-10-02T23:55:29Z"}</t>
         </is>
       </c>
     </row>

--- a/assets/data/bcv/excel/ove_bcv_inpc_nacional_mensual.xlsx
+++ b/assets/data/bcv/excel/ove_bcv_inpc_nacional_mensual.xlsx
@@ -650,7 +650,7 @@
       </c>
       <c r="K7" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:29Z</t>
+          <t>2026-10-03T23:14:12Z</t>
         </is>
       </c>
     </row>
@@ -699,7 +699,7 @@
       </c>
       <c r="K8" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:29Z</t>
+          <t>2026-10-03T23:14:12Z</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="K9" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:29Z</t>
+          <t>2026-10-03T23:14:12Z</t>
         </is>
       </c>
     </row>
@@ -797,7 +797,7 @@
       </c>
       <c r="K10" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:29Z</t>
+          <t>2026-10-03T23:14:12Z</t>
         </is>
       </c>
     </row>
@@ -846,7 +846,7 @@
       </c>
       <c r="K11" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:29Z</t>
+          <t>2026-10-03T23:14:12Z</t>
         </is>
       </c>
     </row>
@@ -895,7 +895,7 @@
       </c>
       <c r="K12" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:29Z</t>
+          <t>2026-10-03T23:14:12Z</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="K13" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:29Z</t>
+          <t>2026-10-03T23:14:12Z</t>
         </is>
       </c>
     </row>
@@ -993,7 +993,7 @@
       </c>
       <c r="K14" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:29Z</t>
+          <t>2026-10-03T23:14:12Z</t>
         </is>
       </c>
     </row>
@@ -1042,7 +1042,7 @@
       </c>
       <c r="K15" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:29Z</t>
+          <t>2026-10-03T23:14:12Z</t>
         </is>
       </c>
     </row>
@@ -1091,7 +1091,7 @@
       </c>
       <c r="K16" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:29Z</t>
+          <t>2026-10-03T23:14:12Z</t>
         </is>
       </c>
     </row>
@@ -1140,7 +1140,7 @@
       </c>
       <c r="K17" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:29Z</t>
+          <t>2026-10-03T23:14:12Z</t>
         </is>
       </c>
     </row>
@@ -1189,7 +1189,7 @@
       </c>
       <c r="K18" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:29Z</t>
+          <t>2026-10-03T23:14:12Z</t>
         </is>
       </c>
     </row>
@@ -1238,7 +1238,7 @@
       </c>
       <c r="K19" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:29Z</t>
+          <t>2026-10-03T23:14:12Z</t>
         </is>
       </c>
     </row>
@@ -1287,7 +1287,7 @@
       </c>
       <c r="K20" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:29Z</t>
+          <t>2026-10-03T23:14:12Z</t>
         </is>
       </c>
     </row>
@@ -1336,7 +1336,7 @@
       </c>
       <c r="K21" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:29Z</t>
+          <t>2026-10-03T23:14:12Z</t>
         </is>
       </c>
     </row>
@@ -1385,7 +1385,7 @@
       </c>
       <c r="K22" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:29Z</t>
+          <t>2026-10-03T23:14:12Z</t>
         </is>
       </c>
     </row>
@@ -1434,7 +1434,7 @@
       </c>
       <c r="K23" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:29Z</t>
+          <t>2026-10-03T23:14:12Z</t>
         </is>
       </c>
     </row>
@@ -1483,7 +1483,7 @@
       </c>
       <c r="K24" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:29Z</t>
+          <t>2026-10-03T23:14:12Z</t>
         </is>
       </c>
     </row>
@@ -1532,7 +1532,7 @@
       </c>
       <c r="K25" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:29Z</t>
+          <t>2026-10-03T23:14:12Z</t>
         </is>
       </c>
     </row>
@@ -1581,7 +1581,7 @@
       </c>
       <c r="K26" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:29Z</t>
+          <t>2026-10-03T23:14:12Z</t>
         </is>
       </c>
     </row>
@@ -1630,7 +1630,7 @@
       </c>
       <c r="K27" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:29Z</t>
+          <t>2026-10-03T23:14:12Z</t>
         </is>
       </c>
     </row>
@@ -1679,7 +1679,7 @@
       </c>
       <c r="K28" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:29Z</t>
+          <t>2026-10-03T23:14:12Z</t>
         </is>
       </c>
     </row>
@@ -1728,7 +1728,7 @@
       </c>
       <c r="K29" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:29Z</t>
+          <t>2026-10-03T23:14:12Z</t>
         </is>
       </c>
     </row>
@@ -1777,7 +1777,7 @@
       </c>
       <c r="K30" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:29Z</t>
+          <t>2026-10-03T23:14:12Z</t>
         </is>
       </c>
     </row>
@@ -1826,7 +1826,7 @@
       </c>
       <c r="K31" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:29Z</t>
+          <t>2026-10-03T23:14:12Z</t>
         </is>
       </c>
     </row>
@@ -1875,7 +1875,7 @@
       </c>
       <c r="K32" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:29Z</t>
+          <t>2026-10-03T23:14:12Z</t>
         </is>
       </c>
     </row>
@@ -1924,7 +1924,7 @@
       </c>
       <c r="K33" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:29Z</t>
+          <t>2026-10-03T23:14:12Z</t>
         </is>
       </c>
     </row>
@@ -1973,7 +1973,7 @@
       </c>
       <c r="K34" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:29Z</t>
+          <t>2026-10-03T23:14:12Z</t>
         </is>
       </c>
     </row>
@@ -2022,7 +2022,7 @@
       </c>
       <c r="K35" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:29Z</t>
+          <t>2026-10-03T23:14:12Z</t>
         </is>
       </c>
     </row>
@@ -2071,7 +2071,7 @@
       </c>
       <c r="K36" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:29Z</t>
+          <t>2026-10-03T23:14:12Z</t>
         </is>
       </c>
     </row>
@@ -2120,7 +2120,7 @@
       </c>
       <c r="K37" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:29Z</t>
+          <t>2026-10-03T23:14:12Z</t>
         </is>
       </c>
     </row>
@@ -2169,7 +2169,7 @@
       </c>
       <c r="K38" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:29Z</t>
+          <t>2026-10-03T23:14:12Z</t>
         </is>
       </c>
     </row>
@@ -2218,7 +2218,7 @@
       </c>
       <c r="K39" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:29Z</t>
+          <t>2026-10-03T23:14:12Z</t>
         </is>
       </c>
     </row>
@@ -2267,7 +2267,7 @@
       </c>
       <c r="K40" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:29Z</t>
+          <t>2026-10-03T23:14:12Z</t>
         </is>
       </c>
     </row>
@@ -2316,7 +2316,7 @@
       </c>
       <c r="K41" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:29Z</t>
+          <t>2026-10-03T23:14:12Z</t>
         </is>
       </c>
     </row>
@@ -2365,7 +2365,7 @@
       </c>
       <c r="K42" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:29Z</t>
+          <t>2026-10-03T23:14:12Z</t>
         </is>
       </c>
     </row>
@@ -2414,7 +2414,7 @@
       </c>
       <c r="K43" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:29Z</t>
+          <t>2026-10-03T23:14:12Z</t>
         </is>
       </c>
     </row>
@@ -2463,7 +2463,7 @@
       </c>
       <c r="K44" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:29Z</t>
+          <t>2026-10-03T23:14:12Z</t>
         </is>
       </c>
     </row>
@@ -2512,7 +2512,7 @@
       </c>
       <c r="K45" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:29Z</t>
+          <t>2026-10-03T23:14:12Z</t>
         </is>
       </c>
     </row>
@@ -2561,7 +2561,7 @@
       </c>
       <c r="K46" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:29Z</t>
+          <t>2026-10-03T23:14:12Z</t>
         </is>
       </c>
     </row>
@@ -2610,7 +2610,7 @@
       </c>
       <c r="K47" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:29Z</t>
+          <t>2026-10-03T23:14:12Z</t>
         </is>
       </c>
     </row>
@@ -2659,7 +2659,7 @@
       </c>
       <c r="K48" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:29Z</t>
+          <t>2026-10-03T23:14:12Z</t>
         </is>
       </c>
     </row>
@@ -2708,7 +2708,7 @@
       </c>
       <c r="K49" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:29Z</t>
+          <t>2026-10-03T23:14:12Z</t>
         </is>
       </c>
     </row>
@@ -2757,7 +2757,7 @@
       </c>
       <c r="K50" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:29Z</t>
+          <t>2026-10-03T23:14:12Z</t>
         </is>
       </c>
     </row>
@@ -2806,7 +2806,7 @@
       </c>
       <c r="K51" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:29Z</t>
+          <t>2026-10-03T23:14:12Z</t>
         </is>
       </c>
     </row>
@@ -2855,7 +2855,7 @@
       </c>
       <c r="K52" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:29Z</t>
+          <t>2026-10-03T23:14:12Z</t>
         </is>
       </c>
     </row>
@@ -2904,7 +2904,7 @@
       </c>
       <c r="K53" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:29Z</t>
+          <t>2026-10-03T23:14:12Z</t>
         </is>
       </c>
     </row>
@@ -2953,7 +2953,7 @@
       </c>
       <c r="K54" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:29Z</t>
+          <t>2026-10-03T23:14:12Z</t>
         </is>
       </c>
     </row>
@@ -3002,7 +3002,7 @@
       </c>
       <c r="K55" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:29Z</t>
+          <t>2026-10-03T23:14:12Z</t>
         </is>
       </c>
     </row>
@@ -3051,7 +3051,7 @@
       </c>
       <c r="K56" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:29Z</t>
+          <t>2026-10-03T23:14:12Z</t>
         </is>
       </c>
     </row>
@@ -3100,7 +3100,7 @@
       </c>
       <c r="K57" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:29Z</t>
+          <t>2026-10-03T23:14:12Z</t>
         </is>
       </c>
     </row>
@@ -3149,7 +3149,7 @@
       </c>
       <c r="K58" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:29Z</t>
+          <t>2026-10-03T23:14:12Z</t>
         </is>
       </c>
     </row>
@@ -3198,7 +3198,7 @@
       </c>
       <c r="K59" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:29Z</t>
+          <t>2026-10-03T23:14:12Z</t>
         </is>
       </c>
     </row>
@@ -3247,7 +3247,7 @@
       </c>
       <c r="K60" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:29Z</t>
+          <t>2026-10-03T23:14:12Z</t>
         </is>
       </c>
     </row>
@@ -3296,7 +3296,7 @@
       </c>
       <c r="K61" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:29Z</t>
+          <t>2026-10-03T23:14:12Z</t>
         </is>
       </c>
     </row>
@@ -3345,7 +3345,7 @@
       </c>
       <c r="K62" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:29Z</t>
+          <t>2026-10-03T23:14:12Z</t>
         </is>
       </c>
     </row>
@@ -3394,7 +3394,7 @@
       </c>
       <c r="K63" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:29Z</t>
+          <t>2026-10-03T23:14:12Z</t>
         </is>
       </c>
     </row>
@@ -3443,7 +3443,7 @@
       </c>
       <c r="K64" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:29Z</t>
+          <t>2026-10-03T23:14:12Z</t>
         </is>
       </c>
     </row>
@@ -3492,7 +3492,7 @@
       </c>
       <c r="K65" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:29Z</t>
+          <t>2026-10-03T23:14:12Z</t>
         </is>
       </c>
     </row>
@@ -3541,7 +3541,7 @@
       </c>
       <c r="K66" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:29Z</t>
+          <t>2026-10-03T23:14:12Z</t>
         </is>
       </c>
     </row>
@@ -3590,7 +3590,7 @@
       </c>
       <c r="K67" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:29Z</t>
+          <t>2026-10-03T23:14:12Z</t>
         </is>
       </c>
     </row>
@@ -3639,7 +3639,7 @@
       </c>
       <c r="K68" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:29Z</t>
+          <t>2026-10-03T23:14:12Z</t>
         </is>
       </c>
     </row>
@@ -3688,7 +3688,7 @@
       </c>
       <c r="K69" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:29Z</t>
+          <t>2026-10-03T23:14:12Z</t>
         </is>
       </c>
     </row>
@@ -3737,7 +3737,7 @@
       </c>
       <c r="K70" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:29Z</t>
+          <t>2026-10-03T23:14:12Z</t>
         </is>
       </c>
     </row>
@@ -3786,7 +3786,7 @@
       </c>
       <c r="K71" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:29Z</t>
+          <t>2026-10-03T23:14:12Z</t>
         </is>
       </c>
     </row>
@@ -3835,7 +3835,7 @@
       </c>
       <c r="K72" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:29Z</t>
+          <t>2026-10-03T23:14:12Z</t>
         </is>
       </c>
     </row>
@@ -3884,7 +3884,7 @@
       </c>
       <c r="K73" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:29Z</t>
+          <t>2026-10-03T23:14:12Z</t>
         </is>
       </c>
     </row>
@@ -3933,7 +3933,7 @@
       </c>
       <c r="K74" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:29Z</t>
+          <t>2026-10-03T23:14:12Z</t>
         </is>
       </c>
     </row>
@@ -3982,7 +3982,7 @@
       </c>
       <c r="K75" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:29Z</t>
+          <t>2026-10-03T23:14:12Z</t>
         </is>
       </c>
     </row>
@@ -4031,7 +4031,7 @@
       </c>
       <c r="K76" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:29Z</t>
+          <t>2026-10-03T23:14:12Z</t>
         </is>
       </c>
     </row>
@@ -4080,7 +4080,7 @@
       </c>
       <c r="K77" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:29Z</t>
+          <t>2026-10-03T23:14:12Z</t>
         </is>
       </c>
     </row>
@@ -4129,7 +4129,7 @@
       </c>
       <c r="K78" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:29Z</t>
+          <t>2026-10-03T23:14:12Z</t>
         </is>
       </c>
     </row>
@@ -4178,7 +4178,7 @@
       </c>
       <c r="K79" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:29Z</t>
+          <t>2026-10-03T23:14:12Z</t>
         </is>
       </c>
     </row>
@@ -4227,7 +4227,7 @@
       </c>
       <c r="K80" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:29Z</t>
+          <t>2026-10-03T23:14:12Z</t>
         </is>
       </c>
     </row>
@@ -4276,7 +4276,7 @@
       </c>
       <c r="K81" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:29Z</t>
+          <t>2026-10-03T23:14:12Z</t>
         </is>
       </c>
     </row>
@@ -4325,7 +4325,7 @@
       </c>
       <c r="K82" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:29Z</t>
+          <t>2026-10-03T23:14:12Z</t>
         </is>
       </c>
     </row>
@@ -4374,7 +4374,7 @@
       </c>
       <c r="K83" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:29Z</t>
+          <t>2026-10-03T23:14:12Z</t>
         </is>
       </c>
     </row>
@@ -4423,7 +4423,7 @@
       </c>
       <c r="K84" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:29Z</t>
+          <t>2026-10-03T23:14:12Z</t>
         </is>
       </c>
     </row>
@@ -4472,7 +4472,7 @@
       </c>
       <c r="K85" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:29Z</t>
+          <t>2026-10-03T23:14:12Z</t>
         </is>
       </c>
     </row>
@@ -4521,7 +4521,7 @@
       </c>
       <c r="K86" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:29Z</t>
+          <t>2026-10-03T23:14:12Z</t>
         </is>
       </c>
     </row>
@@ -4570,7 +4570,7 @@
       </c>
       <c r="K87" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:29Z</t>
+          <t>2026-10-03T23:14:12Z</t>
         </is>
       </c>
     </row>
@@ -4619,7 +4619,7 @@
       </c>
       <c r="K88" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:29Z</t>
+          <t>2026-10-03T23:14:12Z</t>
         </is>
       </c>
     </row>
@@ -4668,7 +4668,7 @@
       </c>
       <c r="K89" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:29Z</t>
+          <t>2026-10-03T23:14:12Z</t>
         </is>
       </c>
     </row>
@@ -4717,7 +4717,7 @@
       </c>
       <c r="K90" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:29Z</t>
+          <t>2026-10-03T23:14:12Z</t>
         </is>
       </c>
     </row>
@@ -4766,7 +4766,7 @@
       </c>
       <c r="K91" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:29Z</t>
+          <t>2026-10-03T23:14:12Z</t>
         </is>
       </c>
     </row>
@@ -4815,7 +4815,7 @@
       </c>
       <c r="K92" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:29Z</t>
+          <t>2026-10-03T23:14:12Z</t>
         </is>
       </c>
     </row>
@@ -4864,7 +4864,7 @@
       </c>
       <c r="K93" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:29Z</t>
+          <t>2026-10-03T23:14:12Z</t>
         </is>
       </c>
     </row>
@@ -4913,7 +4913,7 @@
       </c>
       <c r="K94" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:29Z</t>
+          <t>2026-10-03T23:14:12Z</t>
         </is>
       </c>
     </row>
@@ -4962,7 +4962,7 @@
       </c>
       <c r="K95" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:29Z</t>
+          <t>2026-10-03T23:14:12Z</t>
         </is>
       </c>
     </row>
@@ -5011,7 +5011,7 @@
       </c>
       <c r="K96" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:29Z</t>
+          <t>2026-10-03T23:14:12Z</t>
         </is>
       </c>
     </row>
@@ -5060,7 +5060,7 @@
       </c>
       <c r="K97" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:29Z</t>
+          <t>2026-10-03T23:14:12Z</t>
         </is>
       </c>
     </row>
@@ -5109,7 +5109,7 @@
       </c>
       <c r="K98" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:29Z</t>
+          <t>2026-10-03T23:14:12Z</t>
         </is>
       </c>
     </row>
@@ -5158,7 +5158,7 @@
       </c>
       <c r="K99" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:29Z</t>
+          <t>2026-10-03T23:14:12Z</t>
         </is>
       </c>
     </row>
@@ -5207,7 +5207,7 @@
       </c>
       <c r="K100" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:29Z</t>
+          <t>2026-10-03T23:14:12Z</t>
         </is>
       </c>
     </row>
@@ -5256,7 +5256,7 @@
       </c>
       <c r="K101" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:29Z</t>
+          <t>2026-10-03T23:14:12Z</t>
         </is>
       </c>
     </row>
@@ -5305,7 +5305,7 @@
       </c>
       <c r="K102" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:29Z</t>
+          <t>2026-10-03T23:14:12Z</t>
         </is>
       </c>
     </row>
@@ -5354,7 +5354,7 @@
       </c>
       <c r="K103" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:29Z</t>
+          <t>2026-10-03T23:14:12Z</t>
         </is>
       </c>
     </row>
@@ -5403,7 +5403,7 @@
       </c>
       <c r="K104" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:29Z</t>
+          <t>2026-10-03T23:14:12Z</t>
         </is>
       </c>
     </row>
@@ -5452,7 +5452,7 @@
       </c>
       <c r="K105" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:29Z</t>
+          <t>2026-10-03T23:14:12Z</t>
         </is>
       </c>
     </row>
@@ -5501,7 +5501,7 @@
       </c>
       <c r="K106" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:29Z</t>
+          <t>2026-10-03T23:14:12Z</t>
         </is>
       </c>
     </row>
@@ -5550,7 +5550,7 @@
       </c>
       <c r="K107" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:29Z</t>
+          <t>2026-10-03T23:14:12Z</t>
         </is>
       </c>
     </row>
@@ -5599,7 +5599,7 @@
       </c>
       <c r="K108" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:29Z</t>
+          <t>2026-10-03T23:14:12Z</t>
         </is>
       </c>
     </row>
@@ -5648,7 +5648,7 @@
       </c>
       <c r="K109" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:29Z</t>
+          <t>2026-10-03T23:14:12Z</t>
         </is>
       </c>
     </row>
@@ -5697,7 +5697,7 @@
       </c>
       <c r="K110" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:29Z</t>
+          <t>2026-10-03T23:14:12Z</t>
         </is>
       </c>
     </row>
@@ -5746,7 +5746,7 @@
       </c>
       <c r="K111" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:29Z</t>
+          <t>2026-10-03T23:14:12Z</t>
         </is>
       </c>
     </row>
@@ -5795,7 +5795,7 @@
       </c>
       <c r="K112" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:29Z</t>
+          <t>2026-10-03T23:14:12Z</t>
         </is>
       </c>
     </row>
@@ -5844,7 +5844,7 @@
       </c>
       <c r="K113" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:29Z</t>
+          <t>2026-10-03T23:14:12Z</t>
         </is>
       </c>
     </row>
@@ -5893,7 +5893,7 @@
       </c>
       <c r="K114" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:29Z</t>
+          <t>2026-10-03T23:14:12Z</t>
         </is>
       </c>
     </row>
@@ -5942,7 +5942,7 @@
       </c>
       <c r="K115" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:29Z</t>
+          <t>2026-10-03T23:14:12Z</t>
         </is>
       </c>
     </row>
@@ -5991,7 +5991,7 @@
       </c>
       <c r="K116" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:29Z</t>
+          <t>2026-10-03T23:14:12Z</t>
         </is>
       </c>
     </row>
@@ -6040,7 +6040,7 @@
       </c>
       <c r="K117" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:29Z</t>
+          <t>2026-10-03T23:14:12Z</t>
         </is>
       </c>
     </row>
@@ -6089,7 +6089,7 @@
       </c>
       <c r="K118" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:29Z</t>
+          <t>2026-10-03T23:14:12Z</t>
         </is>
       </c>
     </row>
@@ -6138,7 +6138,7 @@
       </c>
       <c r="K119" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:29Z</t>
+          <t>2026-10-03T23:14:12Z</t>
         </is>
       </c>
     </row>
@@ -6187,7 +6187,7 @@
       </c>
       <c r="K120" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:29Z</t>
+          <t>2026-10-03T23:14:12Z</t>
         </is>
       </c>
     </row>
@@ -6236,7 +6236,7 @@
       </c>
       <c r="K121" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:29Z</t>
+          <t>2026-10-03T23:14:12Z</t>
         </is>
       </c>
     </row>
@@ -6285,7 +6285,7 @@
       </c>
       <c r="K122" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:29Z</t>
+          <t>2026-10-03T23:14:12Z</t>
         </is>
       </c>
     </row>
@@ -6334,7 +6334,7 @@
       </c>
       <c r="K123" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:29Z</t>
+          <t>2026-10-03T23:14:12Z</t>
         </is>
       </c>
     </row>
@@ -6383,7 +6383,7 @@
       </c>
       <c r="K124" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:29Z</t>
+          <t>2026-10-03T23:14:12Z</t>
         </is>
       </c>
     </row>
@@ -6432,7 +6432,7 @@
       </c>
       <c r="K125" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:29Z</t>
+          <t>2026-10-03T23:14:12Z</t>
         </is>
       </c>
     </row>
@@ -6481,7 +6481,7 @@
       </c>
       <c r="K126" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:29Z</t>
+          <t>2026-10-03T23:14:12Z</t>
         </is>
       </c>
     </row>
@@ -6530,7 +6530,7 @@
       </c>
       <c r="K127" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:29Z</t>
+          <t>2026-10-03T23:14:12Z</t>
         </is>
       </c>
     </row>
@@ -6579,7 +6579,7 @@
       </c>
       <c r="K128" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:29Z</t>
+          <t>2026-10-03T23:14:12Z</t>
         </is>
       </c>
     </row>
@@ -6628,7 +6628,7 @@
       </c>
       <c r="K129" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:29Z</t>
+          <t>2026-10-03T23:14:12Z</t>
         </is>
       </c>
     </row>
@@ -6677,7 +6677,7 @@
       </c>
       <c r="K130" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:29Z</t>
+          <t>2026-10-03T23:14:12Z</t>
         </is>
       </c>
     </row>
@@ -6726,7 +6726,7 @@
       </c>
       <c r="K131" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:29Z</t>
+          <t>2026-10-03T23:14:12Z</t>
         </is>
       </c>
     </row>
@@ -6775,7 +6775,7 @@
       </c>
       <c r="K132" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:29Z</t>
+          <t>2026-10-03T23:14:12Z</t>
         </is>
       </c>
     </row>
@@ -6824,7 +6824,7 @@
       </c>
       <c r="K133" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:29Z</t>
+          <t>2026-10-03T23:14:12Z</t>
         </is>
       </c>
     </row>
@@ -6873,7 +6873,7 @@
       </c>
       <c r="K134" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:29Z</t>
+          <t>2026-10-03T23:14:12Z</t>
         </is>
       </c>
     </row>
@@ -6922,7 +6922,7 @@
       </c>
       <c r="K135" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:29Z</t>
+          <t>2026-10-03T23:14:12Z</t>
         </is>
       </c>
     </row>
@@ -6971,7 +6971,7 @@
       </c>
       <c r="K136" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:29Z</t>
+          <t>2026-10-03T23:14:12Z</t>
         </is>
       </c>
     </row>
@@ -7020,7 +7020,7 @@
       </c>
       <c r="K137" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:29Z</t>
+          <t>2026-10-03T23:14:12Z</t>
         </is>
       </c>
     </row>
@@ -7069,7 +7069,7 @@
       </c>
       <c r="K138" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:29Z</t>
+          <t>2026-10-03T23:14:12Z</t>
         </is>
       </c>
     </row>
@@ -7118,7 +7118,7 @@
       </c>
       <c r="K139" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:29Z</t>
+          <t>2026-10-03T23:14:12Z</t>
         </is>
       </c>
     </row>
@@ -7167,7 +7167,7 @@
       </c>
       <c r="K140" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:29Z</t>
+          <t>2026-10-03T23:14:12Z</t>
         </is>
       </c>
     </row>
@@ -7216,7 +7216,7 @@
       </c>
       <c r="K141" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:29Z</t>
+          <t>2026-10-03T23:14:12Z</t>
         </is>
       </c>
     </row>
@@ -7265,7 +7265,7 @@
       </c>
       <c r="K142" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:29Z</t>
+          <t>2026-10-03T23:14:12Z</t>
         </is>
       </c>
     </row>
@@ -7314,7 +7314,7 @@
       </c>
       <c r="K143" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:29Z</t>
+          <t>2026-10-03T23:14:12Z</t>
         </is>
       </c>
     </row>
@@ -7363,7 +7363,7 @@
       </c>
       <c r="K144" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:29Z</t>
+          <t>2026-10-03T23:14:12Z</t>
         </is>
       </c>
     </row>
@@ -7412,7 +7412,7 @@
       </c>
       <c r="K145" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:29Z</t>
+          <t>2026-10-03T23:14:12Z</t>
         </is>
       </c>
     </row>
@@ -7461,7 +7461,7 @@
       </c>
       <c r="K146" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:29Z</t>
+          <t>2026-10-03T23:14:12Z</t>
         </is>
       </c>
     </row>
@@ -7510,7 +7510,7 @@
       </c>
       <c r="K147" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:29Z</t>
+          <t>2026-10-03T23:14:12Z</t>
         </is>
       </c>
     </row>
@@ -7559,7 +7559,7 @@
       </c>
       <c r="K148" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:29Z</t>
+          <t>2026-10-03T23:14:12Z</t>
         </is>
       </c>
     </row>
@@ -7608,7 +7608,7 @@
       </c>
       <c r="K149" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:29Z</t>
+          <t>2026-10-03T23:14:12Z</t>
         </is>
       </c>
     </row>
@@ -7657,7 +7657,7 @@
       </c>
       <c r="K150" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:29Z</t>
+          <t>2026-10-03T23:14:12Z</t>
         </is>
       </c>
     </row>
@@ -7706,7 +7706,7 @@
       </c>
       <c r="K151" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:29Z</t>
+          <t>2026-10-03T23:14:12Z</t>
         </is>
       </c>
     </row>
@@ -7755,7 +7755,7 @@
       </c>
       <c r="K152" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:29Z</t>
+          <t>2026-10-03T23:14:12Z</t>
         </is>
       </c>
     </row>
@@ -7804,7 +7804,7 @@
       </c>
       <c r="K153" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:29Z</t>
+          <t>2026-10-03T23:14:12Z</t>
         </is>
       </c>
     </row>
@@ -7853,7 +7853,7 @@
       </c>
       <c r="K154" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:29Z</t>
+          <t>2026-10-03T23:14:12Z</t>
         </is>
       </c>
     </row>
@@ -7902,7 +7902,7 @@
       </c>
       <c r="K155" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:29Z</t>
+          <t>2026-10-03T23:14:12Z</t>
         </is>
       </c>
     </row>
@@ -7951,7 +7951,7 @@
       </c>
       <c r="K156" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:29Z</t>
+          <t>2026-10-03T23:14:12Z</t>
         </is>
       </c>
     </row>
@@ -8000,7 +8000,7 @@
       </c>
       <c r="K157" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:29Z</t>
+          <t>2026-10-03T23:14:12Z</t>
         </is>
       </c>
     </row>
@@ -8049,7 +8049,7 @@
       </c>
       <c r="K158" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:29Z</t>
+          <t>2026-10-03T23:14:12Z</t>
         </is>
       </c>
     </row>
@@ -8098,7 +8098,7 @@
       </c>
       <c r="K159" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:29Z</t>
+          <t>2026-10-03T23:14:12Z</t>
         </is>
       </c>
     </row>
@@ -8147,7 +8147,7 @@
       </c>
       <c r="K160" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:29Z</t>
+          <t>2026-10-03T23:14:12Z</t>
         </is>
       </c>
     </row>
@@ -8196,7 +8196,7 @@
       </c>
       <c r="K161" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:29Z</t>
+          <t>2026-10-03T23:14:12Z</t>
         </is>
       </c>
     </row>
@@ -8245,7 +8245,7 @@
       </c>
       <c r="K162" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:29Z</t>
+          <t>2026-10-03T23:14:12Z</t>
         </is>
       </c>
     </row>
@@ -8294,7 +8294,7 @@
       </c>
       <c r="K163" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:29Z</t>
+          <t>2026-10-03T23:14:12Z</t>
         </is>
       </c>
     </row>
@@ -8343,7 +8343,7 @@
       </c>
       <c r="K164" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:29Z</t>
+          <t>2026-10-03T23:14:12Z</t>
         </is>
       </c>
     </row>
@@ -8392,7 +8392,7 @@
       </c>
       <c r="K165" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:29Z</t>
+          <t>2026-10-03T23:14:12Z</t>
         </is>
       </c>
     </row>
@@ -8441,7 +8441,7 @@
       </c>
       <c r="K166" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:29Z</t>
+          <t>2026-10-03T23:14:12Z</t>
         </is>
       </c>
     </row>
@@ -8490,7 +8490,7 @@
       </c>
       <c r="K167" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:29Z</t>
+          <t>2026-10-03T23:14:12Z</t>
         </is>
       </c>
     </row>
@@ -8539,7 +8539,7 @@
       </c>
       <c r="K168" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:29Z</t>
+          <t>2026-10-03T23:14:12Z</t>
         </is>
       </c>
     </row>
@@ -8588,7 +8588,7 @@
       </c>
       <c r="K169" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:29Z</t>
+          <t>2026-10-03T23:14:12Z</t>
         </is>
       </c>
     </row>
@@ -8637,7 +8637,7 @@
       </c>
       <c r="K170" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:29Z</t>
+          <t>2026-10-03T23:14:12Z</t>
         </is>
       </c>
     </row>
@@ -8686,7 +8686,7 @@
       </c>
       <c r="K171" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:29Z</t>
+          <t>2026-10-03T23:14:12Z</t>
         </is>
       </c>
     </row>
@@ -8735,7 +8735,7 @@
       </c>
       <c r="K172" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:29Z</t>
+          <t>2026-10-03T23:14:12Z</t>
         </is>
       </c>
     </row>
@@ -8784,7 +8784,7 @@
       </c>
       <c r="K173" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:29Z</t>
+          <t>2026-10-03T23:14:12Z</t>
         </is>
       </c>
     </row>
@@ -8833,7 +8833,7 @@
       </c>
       <c r="K174" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:29Z</t>
+          <t>2026-10-03T23:14:12Z</t>
         </is>
       </c>
     </row>
@@ -8882,7 +8882,7 @@
       </c>
       <c r="K175" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:29Z</t>
+          <t>2026-10-03T23:14:12Z</t>
         </is>
       </c>
     </row>
@@ -8931,7 +8931,7 @@
       </c>
       <c r="K176" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:29Z</t>
+          <t>2026-10-03T23:14:12Z</t>
         </is>
       </c>
     </row>
@@ -8980,7 +8980,7 @@
       </c>
       <c r="K177" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:29Z</t>
+          <t>2026-10-03T23:14:12Z</t>
         </is>
       </c>
     </row>
@@ -9029,7 +9029,7 @@
       </c>
       <c r="K178" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:29Z</t>
+          <t>2026-10-03T23:14:12Z</t>
         </is>
       </c>
     </row>
@@ -9078,7 +9078,7 @@
       </c>
       <c r="K179" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:29Z</t>
+          <t>2026-10-03T23:14:12Z</t>
         </is>
       </c>
     </row>
@@ -9127,7 +9127,7 @@
       </c>
       <c r="K180" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:29Z</t>
+          <t>2026-10-03T23:14:12Z</t>
         </is>
       </c>
     </row>
@@ -9176,7 +9176,7 @@
       </c>
       <c r="K181" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:29Z</t>
+          <t>2026-10-03T23:14:12Z</t>
         </is>
       </c>
     </row>
@@ -9225,7 +9225,7 @@
       </c>
       <c r="K182" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:29Z</t>
+          <t>2026-10-03T23:14:12Z</t>
         </is>
       </c>
     </row>
@@ -9274,7 +9274,7 @@
       </c>
       <c r="K183" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:29Z</t>
+          <t>2026-10-03T23:14:12Z</t>
         </is>
       </c>
     </row>
@@ -9323,7 +9323,7 @@
       </c>
       <c r="K184" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:29Z</t>
+          <t>2026-10-03T23:14:12Z</t>
         </is>
       </c>
     </row>
@@ -9372,7 +9372,7 @@
       </c>
       <c r="K185" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:29Z</t>
+          <t>2026-10-03T23:14:12Z</t>
         </is>
       </c>
     </row>
@@ -9421,7 +9421,7 @@
       </c>
       <c r="K186" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:29Z</t>
+          <t>2026-10-03T23:14:12Z</t>
         </is>
       </c>
     </row>
@@ -9470,7 +9470,7 @@
       </c>
       <c r="K187" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:29Z</t>
+          <t>2026-10-03T23:14:12Z</t>
         </is>
       </c>
     </row>
@@ -9519,7 +9519,7 @@
       </c>
       <c r="K188" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:29Z</t>
+          <t>2026-10-03T23:14:12Z</t>
         </is>
       </c>
     </row>
@@ -9568,7 +9568,7 @@
       </c>
       <c r="K189" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:29Z</t>
+          <t>2026-10-03T23:14:12Z</t>
         </is>
       </c>
     </row>
@@ -9617,7 +9617,7 @@
       </c>
       <c r="K190" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:29Z</t>
+          <t>2026-10-03T23:14:12Z</t>
         </is>
       </c>
     </row>
@@ -9666,7 +9666,7 @@
       </c>
       <c r="K191" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:29Z</t>
+          <t>2026-10-03T23:14:12Z</t>
         </is>
       </c>
     </row>
@@ -9715,7 +9715,7 @@
       </c>
       <c r="K192" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:29Z</t>
+          <t>2026-10-03T23:14:12Z</t>
         </is>
       </c>
     </row>
@@ -9764,7 +9764,7 @@
       </c>
       <c r="K193" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:29Z</t>
+          <t>2026-10-03T23:14:12Z</t>
         </is>
       </c>
     </row>
@@ -9813,7 +9813,7 @@
       </c>
       <c r="K194" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:29Z</t>
+          <t>2026-10-03T23:14:12Z</t>
         </is>
       </c>
     </row>
@@ -9862,7 +9862,7 @@
       </c>
       <c r="K195" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:29Z</t>
+          <t>2026-10-03T23:14:12Z</t>
         </is>
       </c>
     </row>
@@ -9911,7 +9911,7 @@
       </c>
       <c r="K196" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:29Z</t>
+          <t>2026-10-03T23:14:12Z</t>
         </is>
       </c>
     </row>
@@ -9960,7 +9960,7 @@
       </c>
       <c r="K197" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:29Z</t>
+          <t>2026-10-03T23:14:12Z</t>
         </is>
       </c>
     </row>
@@ -10009,7 +10009,7 @@
       </c>
       <c r="K198" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:29Z</t>
+          <t>2026-10-03T23:14:12Z</t>
         </is>
       </c>
     </row>
@@ -10058,7 +10058,7 @@
       </c>
       <c r="K199" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:29Z</t>
+          <t>2026-10-03T23:14:12Z</t>
         </is>
       </c>
     </row>
@@ -10107,7 +10107,7 @@
       </c>
       <c r="K200" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:29Z</t>
+          <t>2026-10-03T23:14:12Z</t>
         </is>
       </c>
     </row>
@@ -10156,7 +10156,7 @@
       </c>
       <c r="K201" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:29Z</t>
+          <t>2026-10-03T23:14:12Z</t>
         </is>
       </c>
     </row>
@@ -10205,7 +10205,7 @@
       </c>
       <c r="K202" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:29Z</t>
+          <t>2026-10-03T23:14:12Z</t>
         </is>
       </c>
     </row>
@@ -10254,7 +10254,7 @@
       </c>
       <c r="K203" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:29Z</t>
+          <t>2026-10-03T23:14:12Z</t>
         </is>
       </c>
     </row>
@@ -10303,7 +10303,7 @@
       </c>
       <c r="K204" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:29Z</t>
+          <t>2026-10-03T23:14:12Z</t>
         </is>
       </c>
     </row>
@@ -10352,7 +10352,7 @@
       </c>
       <c r="K205" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:29Z</t>
+          <t>2026-10-03T23:14:12Z</t>
         </is>
       </c>
     </row>
@@ -10401,7 +10401,7 @@
       </c>
       <c r="K206" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:29Z</t>
+          <t>2026-10-03T23:14:12Z</t>
         </is>
       </c>
     </row>
@@ -10450,7 +10450,7 @@
       </c>
       <c r="K207" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:29Z</t>
+          <t>2026-10-03T23:14:12Z</t>
         </is>
       </c>
     </row>
@@ -10499,7 +10499,7 @@
       </c>
       <c r="K208" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:29Z</t>
+          <t>2026-10-03T23:14:12Z</t>
         </is>
       </c>
     </row>
@@ -10548,7 +10548,7 @@
       </c>
       <c r="K209" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:29Z</t>
+          <t>2026-10-03T23:14:12Z</t>
         </is>
       </c>
     </row>
@@ -10597,7 +10597,7 @@
       </c>
       <c r="K210" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:29Z</t>
+          <t>2026-10-03T23:14:12Z</t>
         </is>
       </c>
     </row>
@@ -10646,7 +10646,7 @@
       </c>
       <c r="K211" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:29Z</t>
+          <t>2026-10-03T23:14:12Z</t>
         </is>
       </c>
     </row>
@@ -10695,7 +10695,7 @@
       </c>
       <c r="K212" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:29Z</t>
+          <t>2026-10-03T23:14:12Z</t>
         </is>
       </c>
     </row>
@@ -10744,7 +10744,7 @@
       </c>
       <c r="K213" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:29Z</t>
+          <t>2026-10-03T23:14:12Z</t>
         </is>
       </c>
     </row>
@@ -10793,7 +10793,7 @@
       </c>
       <c r="K214" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:29Z</t>
+          <t>2026-10-03T23:14:12Z</t>
         </is>
       </c>
     </row>
@@ -10842,7 +10842,7 @@
       </c>
       <c r="K215" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:29Z</t>
+          <t>2026-10-03T23:14:12Z</t>
         </is>
       </c>
     </row>
@@ -10891,7 +10891,7 @@
       </c>
       <c r="K216" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:29Z</t>
+          <t>2026-10-03T23:14:12Z</t>
         </is>
       </c>
     </row>
@@ -10940,7 +10940,7 @@
       </c>
       <c r="K217" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:29Z</t>
+          <t>2026-10-03T23:14:12Z</t>
         </is>
       </c>
     </row>
@@ -10989,7 +10989,7 @@
       </c>
       <c r="K218" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:29Z</t>
+          <t>2026-10-03T23:14:12Z</t>
         </is>
       </c>
     </row>
@@ -11038,7 +11038,7 @@
       </c>
       <c r="K219" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:29Z</t>
+          <t>2026-10-03T23:14:12Z</t>
         </is>
       </c>
     </row>
@@ -11087,7 +11087,7 @@
       </c>
       <c r="K220" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:29Z</t>
+          <t>2026-10-03T23:14:12Z</t>
         </is>
       </c>
     </row>
@@ -11136,7 +11136,7 @@
       </c>
       <c r="K221" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:29Z</t>
+          <t>2026-10-03T23:14:12Z</t>
         </is>
       </c>
     </row>
@@ -11185,7 +11185,7 @@
       </c>
       <c r="K222" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:29Z</t>
+          <t>2026-10-03T23:14:12Z</t>
         </is>
       </c>
     </row>
@@ -11234,7 +11234,7 @@
       </c>
       <c r="K223" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:29Z</t>
+          <t>2026-10-03T23:14:12Z</t>
         </is>
       </c>
     </row>
@@ -11283,7 +11283,7 @@
       </c>
       <c r="K224" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:29Z</t>
+          <t>2026-10-03T23:14:12Z</t>
         </is>
       </c>
     </row>
@@ -11332,7 +11332,7 @@
       </c>
       <c r="K225" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:29Z</t>
+          <t>2026-10-03T23:14:12Z</t>
         </is>
       </c>
     </row>
@@ -11381,7 +11381,7 @@
       </c>
       <c r="K226" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:29Z</t>
+          <t>2026-10-03T23:14:12Z</t>
         </is>
       </c>
     </row>
@@ -11430,7 +11430,7 @@
       </c>
       <c r="K227" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:29Z</t>
+          <t>2026-10-03T23:14:12Z</t>
         </is>
       </c>
     </row>
@@ -11479,7 +11479,7 @@
       </c>
       <c r="K228" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:29Z</t>
+          <t>2026-10-03T23:14:12Z</t>
         </is>
       </c>
     </row>
@@ -11528,7 +11528,7 @@
       </c>
       <c r="K229" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:29Z</t>
+          <t>2026-10-03T23:14:12Z</t>
         </is>
       </c>
     </row>
@@ -11577,7 +11577,7 @@
       </c>
       <c r="K230" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:29Z</t>
+          <t>2026-10-03T23:14:12Z</t>
         </is>
       </c>
     </row>
@@ -11626,7 +11626,7 @@
       </c>
       <c r="K231" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:29Z</t>
+          <t>2026-10-03T23:14:12Z</t>
         </is>
       </c>
     </row>
@@ -11758,7 +11758,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:29Z</t>
+          <t>2026-10-03T23:14:12Z</t>
         </is>
       </c>
     </row>
@@ -11804,7 +11804,7 @@
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>{"date": "2026-08-01", "year": 2026, "month": 8, "month_name": "Agosto", "index_value": 637409769724325.1, "monthly_variation_pct": 8.9, "unit": "Índice base diciembre 2007=100 y variación mensual %", "frequency": "monthly", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/precios_consumidor/4_5_7_2.xls", "fetched_at": "2026-10-02T23:55:29Z"}</t>
+          <t>{"date": "2026-08-01", "year": 2026, "month": 8, "month_name": "Agosto", "index_value": 637409769724325.1, "monthly_variation_pct": 8.9, "unit": "Índice base diciembre 2007=100 y variación mensual %", "frequency": "monthly", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/precios_consumidor/4_5_7_2.xls", "fetched_at": "2026-10-03T23:14:12Z"}</t>
         </is>
       </c>
     </row>

--- a/assets/data/bcv/excel/ove_bcv_inpc_nacional_mensual.xlsx
+++ b/assets/data/bcv/excel/ove_bcv_inpc_nacional_mensual.xlsx
@@ -650,7 +650,7 @@
       </c>
       <c r="K7" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:12Z</t>
+          <t>2026-10-04T23:25:17Z</t>
         </is>
       </c>
     </row>
@@ -699,7 +699,7 @@
       </c>
       <c r="K8" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:12Z</t>
+          <t>2026-10-04T23:25:17Z</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="K9" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:12Z</t>
+          <t>2026-10-04T23:25:17Z</t>
         </is>
       </c>
     </row>
@@ -797,7 +797,7 @@
       </c>
       <c r="K10" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:12Z</t>
+          <t>2026-10-04T23:25:17Z</t>
         </is>
       </c>
     </row>
@@ -846,7 +846,7 @@
       </c>
       <c r="K11" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:12Z</t>
+          <t>2026-10-04T23:25:17Z</t>
         </is>
       </c>
     </row>
@@ -895,7 +895,7 @@
       </c>
       <c r="K12" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:12Z</t>
+          <t>2026-10-04T23:25:17Z</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="K13" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:12Z</t>
+          <t>2026-10-04T23:25:17Z</t>
         </is>
       </c>
     </row>
@@ -993,7 +993,7 @@
       </c>
       <c r="K14" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:12Z</t>
+          <t>2026-10-04T23:25:17Z</t>
         </is>
       </c>
     </row>
@@ -1042,7 +1042,7 @@
       </c>
       <c r="K15" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:12Z</t>
+          <t>2026-10-04T23:25:17Z</t>
         </is>
       </c>
     </row>
@@ -1091,7 +1091,7 @@
       </c>
       <c r="K16" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:12Z</t>
+          <t>2026-10-04T23:25:17Z</t>
         </is>
       </c>
     </row>
@@ -1140,7 +1140,7 @@
       </c>
       <c r="K17" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:12Z</t>
+          <t>2026-10-04T23:25:17Z</t>
         </is>
       </c>
     </row>
@@ -1189,7 +1189,7 @@
       </c>
       <c r="K18" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:12Z</t>
+          <t>2026-10-04T23:25:17Z</t>
         </is>
       </c>
     </row>
@@ -1238,7 +1238,7 @@
       </c>
       <c r="K19" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:12Z</t>
+          <t>2026-10-04T23:25:17Z</t>
         </is>
       </c>
     </row>
@@ -1287,7 +1287,7 @@
       </c>
       <c r="K20" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:12Z</t>
+          <t>2026-10-04T23:25:17Z</t>
         </is>
       </c>
     </row>
@@ -1336,7 +1336,7 @@
       </c>
       <c r="K21" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:12Z</t>
+          <t>2026-10-04T23:25:17Z</t>
         </is>
       </c>
     </row>
@@ -1385,7 +1385,7 @@
       </c>
       <c r="K22" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:12Z</t>
+          <t>2026-10-04T23:25:17Z</t>
         </is>
       </c>
     </row>
@@ -1434,7 +1434,7 @@
       </c>
       <c r="K23" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:12Z</t>
+          <t>2026-10-04T23:25:17Z</t>
         </is>
       </c>
     </row>
@@ -1483,7 +1483,7 @@
       </c>
       <c r="K24" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:12Z</t>
+          <t>2026-10-04T23:25:17Z</t>
         </is>
       </c>
     </row>
@@ -1532,7 +1532,7 @@
       </c>
       <c r="K25" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:12Z</t>
+          <t>2026-10-04T23:25:17Z</t>
         </is>
       </c>
     </row>
@@ -1581,7 +1581,7 @@
       </c>
       <c r="K26" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:12Z</t>
+          <t>2026-10-04T23:25:17Z</t>
         </is>
       </c>
     </row>
@@ -1630,7 +1630,7 @@
       </c>
       <c r="K27" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:12Z</t>
+          <t>2026-10-04T23:25:17Z</t>
         </is>
       </c>
     </row>
@@ -1679,7 +1679,7 @@
       </c>
       <c r="K28" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:12Z</t>
+          <t>2026-10-04T23:25:17Z</t>
         </is>
       </c>
     </row>
@@ -1728,7 +1728,7 @@
       </c>
       <c r="K29" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:12Z</t>
+          <t>2026-10-04T23:25:17Z</t>
         </is>
       </c>
     </row>
@@ -1777,7 +1777,7 @@
       </c>
       <c r="K30" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:12Z</t>
+          <t>2026-10-04T23:25:17Z</t>
         </is>
       </c>
     </row>
@@ -1826,7 +1826,7 @@
       </c>
       <c r="K31" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:12Z</t>
+          <t>2026-10-04T23:25:17Z</t>
         </is>
       </c>
     </row>
@@ -1875,7 +1875,7 @@
       </c>
       <c r="K32" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:12Z</t>
+          <t>2026-10-04T23:25:17Z</t>
         </is>
       </c>
     </row>
@@ -1924,7 +1924,7 @@
       </c>
       <c r="K33" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:12Z</t>
+          <t>2026-10-04T23:25:17Z</t>
         </is>
       </c>
     </row>
@@ -1973,7 +1973,7 @@
       </c>
       <c r="K34" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:12Z</t>
+          <t>2026-10-04T23:25:17Z</t>
         </is>
       </c>
     </row>
@@ -2022,7 +2022,7 @@
       </c>
       <c r="K35" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:12Z</t>
+          <t>2026-10-04T23:25:17Z</t>
         </is>
       </c>
     </row>
@@ -2071,7 +2071,7 @@
       </c>
       <c r="K36" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:12Z</t>
+          <t>2026-10-04T23:25:17Z</t>
         </is>
       </c>
     </row>
@@ -2120,7 +2120,7 @@
       </c>
       <c r="K37" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:12Z</t>
+          <t>2026-10-04T23:25:17Z</t>
         </is>
       </c>
     </row>
@@ -2169,7 +2169,7 @@
       </c>
       <c r="K38" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:12Z</t>
+          <t>2026-10-04T23:25:17Z</t>
         </is>
       </c>
     </row>
@@ -2218,7 +2218,7 @@
       </c>
       <c r="K39" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:12Z</t>
+          <t>2026-10-04T23:25:17Z</t>
         </is>
       </c>
     </row>
@@ -2267,7 +2267,7 @@
       </c>
       <c r="K40" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:12Z</t>
+          <t>2026-10-04T23:25:17Z</t>
         </is>
       </c>
     </row>
@@ -2316,7 +2316,7 @@
       </c>
       <c r="K41" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:12Z</t>
+          <t>2026-10-04T23:25:17Z</t>
         </is>
       </c>
     </row>
@@ -2365,7 +2365,7 @@
       </c>
       <c r="K42" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:12Z</t>
+          <t>2026-10-04T23:25:17Z</t>
         </is>
       </c>
     </row>
@@ -2414,7 +2414,7 @@
       </c>
       <c r="K43" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:12Z</t>
+          <t>2026-10-04T23:25:17Z</t>
         </is>
       </c>
     </row>
@@ -2463,7 +2463,7 @@
       </c>
       <c r="K44" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:12Z</t>
+          <t>2026-10-04T23:25:17Z</t>
         </is>
       </c>
     </row>
@@ -2512,7 +2512,7 @@
       </c>
       <c r="K45" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:12Z</t>
+          <t>2026-10-04T23:25:17Z</t>
         </is>
       </c>
     </row>
@@ -2561,7 +2561,7 @@
       </c>
       <c r="K46" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:12Z</t>
+          <t>2026-10-04T23:25:17Z</t>
         </is>
       </c>
     </row>
@@ -2610,7 +2610,7 @@
       </c>
       <c r="K47" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:12Z</t>
+          <t>2026-10-04T23:25:17Z</t>
         </is>
       </c>
     </row>
@@ -2659,7 +2659,7 @@
       </c>
       <c r="K48" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:12Z</t>
+          <t>2026-10-04T23:25:17Z</t>
         </is>
       </c>
     </row>
@@ -2708,7 +2708,7 @@
       </c>
       <c r="K49" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:12Z</t>
+          <t>2026-10-04T23:25:17Z</t>
         </is>
       </c>
     </row>
@@ -2757,7 +2757,7 @@
       </c>
       <c r="K50" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:12Z</t>
+          <t>2026-10-04T23:25:17Z</t>
         </is>
       </c>
     </row>
@@ -2806,7 +2806,7 @@
       </c>
       <c r="K51" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:12Z</t>
+          <t>2026-10-04T23:25:17Z</t>
         </is>
       </c>
     </row>
@@ -2855,7 +2855,7 @@
       </c>
       <c r="K52" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:12Z</t>
+          <t>2026-10-04T23:25:17Z</t>
         </is>
       </c>
     </row>
@@ -2904,7 +2904,7 @@
       </c>
       <c r="K53" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:12Z</t>
+          <t>2026-10-04T23:25:17Z</t>
         </is>
       </c>
     </row>
@@ -2953,7 +2953,7 @@
       </c>
       <c r="K54" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:12Z</t>
+          <t>2026-10-04T23:25:17Z</t>
         </is>
       </c>
     </row>
@@ -3002,7 +3002,7 @@
       </c>
       <c r="K55" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:12Z</t>
+          <t>2026-10-04T23:25:17Z</t>
         </is>
       </c>
     </row>
@@ -3051,7 +3051,7 @@
       </c>
       <c r="K56" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:12Z</t>
+          <t>2026-10-04T23:25:17Z</t>
         </is>
       </c>
     </row>
@@ -3100,7 +3100,7 @@
       </c>
       <c r="K57" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:12Z</t>
+          <t>2026-10-04T23:25:17Z</t>
         </is>
       </c>
     </row>
@@ -3149,7 +3149,7 @@
       </c>
       <c r="K58" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:12Z</t>
+          <t>2026-10-04T23:25:17Z</t>
         </is>
       </c>
     </row>
@@ -3198,7 +3198,7 @@
       </c>
       <c r="K59" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:12Z</t>
+          <t>2026-10-04T23:25:17Z</t>
         </is>
       </c>
     </row>
@@ -3247,7 +3247,7 @@
       </c>
       <c r="K60" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:12Z</t>
+          <t>2026-10-04T23:25:17Z</t>
         </is>
       </c>
     </row>
@@ -3296,7 +3296,7 @@
       </c>
       <c r="K61" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:12Z</t>
+          <t>2026-10-04T23:25:17Z</t>
         </is>
       </c>
     </row>
@@ -3345,7 +3345,7 @@
       </c>
       <c r="K62" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:12Z</t>
+          <t>2026-10-04T23:25:17Z</t>
         </is>
       </c>
     </row>
@@ -3394,7 +3394,7 @@
       </c>
       <c r="K63" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:12Z</t>
+          <t>2026-10-04T23:25:17Z</t>
         </is>
       </c>
     </row>
@@ -3443,7 +3443,7 @@
       </c>
       <c r="K64" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:12Z</t>
+          <t>2026-10-04T23:25:17Z</t>
         </is>
       </c>
     </row>
@@ -3492,7 +3492,7 @@
       </c>
       <c r="K65" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:12Z</t>
+          <t>2026-10-04T23:25:17Z</t>
         </is>
       </c>
     </row>
@@ -3541,7 +3541,7 @@
       </c>
       <c r="K66" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:12Z</t>
+          <t>2026-10-04T23:25:17Z</t>
         </is>
       </c>
     </row>
@@ -3590,7 +3590,7 @@
       </c>
       <c r="K67" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:12Z</t>
+          <t>2026-10-04T23:25:17Z</t>
         </is>
       </c>
     </row>
@@ -3639,7 +3639,7 @@
       </c>
       <c r="K68" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:12Z</t>
+          <t>2026-10-04T23:25:17Z</t>
         </is>
       </c>
     </row>
@@ -3688,7 +3688,7 @@
       </c>
       <c r="K69" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:12Z</t>
+          <t>2026-10-04T23:25:17Z</t>
         </is>
       </c>
     </row>
@@ -3737,7 +3737,7 @@
       </c>
       <c r="K70" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:12Z</t>
+          <t>2026-10-04T23:25:17Z</t>
         </is>
       </c>
     </row>
@@ -3786,7 +3786,7 @@
       </c>
       <c r="K71" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:12Z</t>
+          <t>2026-10-04T23:25:17Z</t>
         </is>
       </c>
     </row>
@@ -3835,7 +3835,7 @@
       </c>
       <c r="K72" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:12Z</t>
+          <t>2026-10-04T23:25:17Z</t>
         </is>
       </c>
     </row>
@@ -3884,7 +3884,7 @@
       </c>
       <c r="K73" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:12Z</t>
+          <t>2026-10-04T23:25:17Z</t>
         </is>
       </c>
     </row>
@@ -3933,7 +3933,7 @@
       </c>
       <c r="K74" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:12Z</t>
+          <t>2026-10-04T23:25:17Z</t>
         </is>
       </c>
     </row>
@@ -3982,7 +3982,7 @@
       </c>
       <c r="K75" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:12Z</t>
+          <t>2026-10-04T23:25:17Z</t>
         </is>
       </c>
     </row>
@@ -4031,7 +4031,7 @@
       </c>
       <c r="K76" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:12Z</t>
+          <t>2026-10-04T23:25:17Z</t>
         </is>
       </c>
     </row>
@@ -4080,7 +4080,7 @@
       </c>
       <c r="K77" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:12Z</t>
+          <t>2026-10-04T23:25:17Z</t>
         </is>
       </c>
     </row>
@@ -4129,7 +4129,7 @@
       </c>
       <c r="K78" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:12Z</t>
+          <t>2026-10-04T23:25:17Z</t>
         </is>
       </c>
     </row>
@@ -4178,7 +4178,7 @@
       </c>
       <c r="K79" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:12Z</t>
+          <t>2026-10-04T23:25:17Z</t>
         </is>
       </c>
     </row>
@@ -4227,7 +4227,7 @@
       </c>
       <c r="K80" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:12Z</t>
+          <t>2026-10-04T23:25:17Z</t>
         </is>
       </c>
     </row>
@@ -4276,7 +4276,7 @@
       </c>
       <c r="K81" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:12Z</t>
+          <t>2026-10-04T23:25:17Z</t>
         </is>
       </c>
     </row>
@@ -4325,7 +4325,7 @@
       </c>
       <c r="K82" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:12Z</t>
+          <t>2026-10-04T23:25:17Z</t>
         </is>
       </c>
     </row>
@@ -4374,7 +4374,7 @@
       </c>
       <c r="K83" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:12Z</t>
+          <t>2026-10-04T23:25:17Z</t>
         </is>
       </c>
     </row>
@@ -4423,7 +4423,7 @@
       </c>
       <c r="K84" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:12Z</t>
+          <t>2026-10-04T23:25:17Z</t>
         </is>
       </c>
     </row>
@@ -4472,7 +4472,7 @@
       </c>
       <c r="K85" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:12Z</t>
+          <t>2026-10-04T23:25:17Z</t>
         </is>
       </c>
     </row>
@@ -4521,7 +4521,7 @@
       </c>
       <c r="K86" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:12Z</t>
+          <t>2026-10-04T23:25:17Z</t>
         </is>
       </c>
     </row>
@@ -4570,7 +4570,7 @@
       </c>
       <c r="K87" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:12Z</t>
+          <t>2026-10-04T23:25:17Z</t>
         </is>
       </c>
     </row>
@@ -4619,7 +4619,7 @@
       </c>
       <c r="K88" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:12Z</t>
+          <t>2026-10-04T23:25:17Z</t>
         </is>
       </c>
     </row>
@@ -4668,7 +4668,7 @@
       </c>
       <c r="K89" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:12Z</t>
+          <t>2026-10-04T23:25:17Z</t>
         </is>
       </c>
     </row>
@@ -4717,7 +4717,7 @@
       </c>
       <c r="K90" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:12Z</t>
+          <t>2026-10-04T23:25:17Z</t>
         </is>
       </c>
     </row>
@@ -4766,7 +4766,7 @@
       </c>
       <c r="K91" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:12Z</t>
+          <t>2026-10-04T23:25:17Z</t>
         </is>
       </c>
     </row>
@@ -4815,7 +4815,7 @@
       </c>
       <c r="K92" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:12Z</t>
+          <t>2026-10-04T23:25:17Z</t>
         </is>
       </c>
     </row>
@@ -4864,7 +4864,7 @@
       </c>
       <c r="K93" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:12Z</t>
+          <t>2026-10-04T23:25:17Z</t>
         </is>
       </c>
     </row>
@@ -4913,7 +4913,7 @@
       </c>
       <c r="K94" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:12Z</t>
+          <t>2026-10-04T23:25:17Z</t>
         </is>
       </c>
     </row>
@@ -4962,7 +4962,7 @@
       </c>
       <c r="K95" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:12Z</t>
+          <t>2026-10-04T23:25:17Z</t>
         </is>
       </c>
     </row>
@@ -5011,7 +5011,7 @@
       </c>
       <c r="K96" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:12Z</t>
+          <t>2026-10-04T23:25:17Z</t>
         </is>
       </c>
     </row>
@@ -5060,7 +5060,7 @@
       </c>
       <c r="K97" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:12Z</t>
+          <t>2026-10-04T23:25:17Z</t>
         </is>
       </c>
     </row>
@@ -5109,7 +5109,7 @@
       </c>
       <c r="K98" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:12Z</t>
+          <t>2026-10-04T23:25:17Z</t>
         </is>
       </c>
     </row>
@@ -5158,7 +5158,7 @@
       </c>
       <c r="K99" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:12Z</t>
+          <t>2026-10-04T23:25:17Z</t>
         </is>
       </c>
     </row>
@@ -5207,7 +5207,7 @@
       </c>
       <c r="K100" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:12Z</t>
+          <t>2026-10-04T23:25:17Z</t>
         </is>
       </c>
     </row>
@@ -5256,7 +5256,7 @@
       </c>
       <c r="K101" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:12Z</t>
+          <t>2026-10-04T23:25:17Z</t>
         </is>
       </c>
     </row>
@@ -5305,7 +5305,7 @@
       </c>
       <c r="K102" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:12Z</t>
+          <t>2026-10-04T23:25:17Z</t>
         </is>
       </c>
     </row>
@@ -5354,7 +5354,7 @@
       </c>
       <c r="K103" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:12Z</t>
+          <t>2026-10-04T23:25:17Z</t>
         </is>
       </c>
     </row>
@@ -5403,7 +5403,7 @@
       </c>
       <c r="K104" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:12Z</t>
+          <t>2026-10-04T23:25:17Z</t>
         </is>
       </c>
     </row>
@@ -5452,7 +5452,7 @@
       </c>
       <c r="K105" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:12Z</t>
+          <t>2026-10-04T23:25:17Z</t>
         </is>
       </c>
     </row>
@@ -5501,7 +5501,7 @@
       </c>
       <c r="K106" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:12Z</t>
+          <t>2026-10-04T23:25:17Z</t>
         </is>
       </c>
     </row>
@@ -5550,7 +5550,7 @@
       </c>
       <c r="K107" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:12Z</t>
+          <t>2026-10-04T23:25:17Z</t>
         </is>
       </c>
     </row>
@@ -5599,7 +5599,7 @@
       </c>
       <c r="K108" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:12Z</t>
+          <t>2026-10-04T23:25:17Z</t>
         </is>
       </c>
     </row>
@@ -5648,7 +5648,7 @@
       </c>
       <c r="K109" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:12Z</t>
+          <t>2026-10-04T23:25:17Z</t>
         </is>
       </c>
     </row>
@@ -5697,7 +5697,7 @@
       </c>
       <c r="K110" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:12Z</t>
+          <t>2026-10-04T23:25:17Z</t>
         </is>
       </c>
     </row>
@@ -5746,7 +5746,7 @@
       </c>
       <c r="K111" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:12Z</t>
+          <t>2026-10-04T23:25:17Z</t>
         </is>
       </c>
     </row>
@@ -5795,7 +5795,7 @@
       </c>
       <c r="K112" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:12Z</t>
+          <t>2026-10-04T23:25:17Z</t>
         </is>
       </c>
     </row>
@@ -5844,7 +5844,7 @@
       </c>
       <c r="K113" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:12Z</t>
+          <t>2026-10-04T23:25:17Z</t>
         </is>
       </c>
     </row>
@@ -5893,7 +5893,7 @@
       </c>
       <c r="K114" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:12Z</t>
+          <t>2026-10-04T23:25:17Z</t>
         </is>
       </c>
     </row>
@@ -5942,7 +5942,7 @@
       </c>
       <c r="K115" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:12Z</t>
+          <t>2026-10-04T23:25:17Z</t>
         </is>
       </c>
     </row>
@@ -5991,7 +5991,7 @@
       </c>
       <c r="K116" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:12Z</t>
+          <t>2026-10-04T23:25:17Z</t>
         </is>
       </c>
     </row>
@@ -6040,7 +6040,7 @@
       </c>
       <c r="K117" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:12Z</t>
+          <t>2026-10-04T23:25:17Z</t>
         </is>
       </c>
     </row>
@@ -6089,7 +6089,7 @@
       </c>
       <c r="K118" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:12Z</t>
+          <t>2026-10-04T23:25:17Z</t>
         </is>
       </c>
     </row>
@@ -6138,7 +6138,7 @@
       </c>
       <c r="K119" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:12Z</t>
+          <t>2026-10-04T23:25:17Z</t>
         </is>
       </c>
     </row>
@@ -6187,7 +6187,7 @@
       </c>
       <c r="K120" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:12Z</t>
+          <t>2026-10-04T23:25:17Z</t>
         </is>
       </c>
     </row>
@@ -6236,7 +6236,7 @@
       </c>
       <c r="K121" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:12Z</t>
+          <t>2026-10-04T23:25:17Z</t>
         </is>
       </c>
     </row>
@@ -6285,7 +6285,7 @@
       </c>
       <c r="K122" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:12Z</t>
+          <t>2026-10-04T23:25:17Z</t>
         </is>
       </c>
     </row>
@@ -6334,7 +6334,7 @@
       </c>
       <c r="K123" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:12Z</t>
+          <t>2026-10-04T23:25:17Z</t>
         </is>
       </c>
     </row>
@@ -6383,7 +6383,7 @@
       </c>
       <c r="K124" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:12Z</t>
+          <t>2026-10-04T23:25:17Z</t>
         </is>
       </c>
     </row>
@@ -6432,7 +6432,7 @@
       </c>
       <c r="K125" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:12Z</t>
+          <t>2026-10-04T23:25:17Z</t>
         </is>
       </c>
     </row>
@@ -6481,7 +6481,7 @@
       </c>
       <c r="K126" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:12Z</t>
+          <t>2026-10-04T23:25:17Z</t>
         </is>
       </c>
     </row>
@@ -6530,7 +6530,7 @@
       </c>
       <c r="K127" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:12Z</t>
+          <t>2026-10-04T23:25:17Z</t>
         </is>
       </c>
     </row>
@@ -6579,7 +6579,7 @@
       </c>
       <c r="K128" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:12Z</t>
+          <t>2026-10-04T23:25:17Z</t>
         </is>
       </c>
     </row>
@@ -6628,7 +6628,7 @@
       </c>
       <c r="K129" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:12Z</t>
+          <t>2026-10-04T23:25:17Z</t>
         </is>
       </c>
     </row>
@@ -6677,7 +6677,7 @@
       </c>
       <c r="K130" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:12Z</t>
+          <t>2026-10-04T23:25:17Z</t>
         </is>
       </c>
     </row>
@@ -6726,7 +6726,7 @@
       </c>
       <c r="K131" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:12Z</t>
+          <t>2026-10-04T23:25:17Z</t>
         </is>
       </c>
     </row>
@@ -6775,7 +6775,7 @@
       </c>
       <c r="K132" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:12Z</t>
+          <t>2026-10-04T23:25:17Z</t>
         </is>
       </c>
     </row>
@@ -6824,7 +6824,7 @@
       </c>
       <c r="K133" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:12Z</t>
+          <t>2026-10-04T23:25:17Z</t>
         </is>
       </c>
     </row>
@@ -6873,7 +6873,7 @@
       </c>
       <c r="K134" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:12Z</t>
+          <t>2026-10-04T23:25:17Z</t>
         </is>
       </c>
     </row>
@@ -6922,7 +6922,7 @@
       </c>
       <c r="K135" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:12Z</t>
+          <t>2026-10-04T23:25:17Z</t>
         </is>
       </c>
     </row>
@@ -6971,7 +6971,7 @@
       </c>
       <c r="K136" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:12Z</t>
+          <t>2026-10-04T23:25:17Z</t>
         </is>
       </c>
     </row>
@@ -7020,7 +7020,7 @@
       </c>
       <c r="K137" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:12Z</t>
+          <t>2026-10-04T23:25:17Z</t>
         </is>
       </c>
     </row>
@@ -7069,7 +7069,7 @@
       </c>
       <c r="K138" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:12Z</t>
+          <t>2026-10-04T23:25:17Z</t>
         </is>
       </c>
     </row>
@@ -7118,7 +7118,7 @@
       </c>
       <c r="K139" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:12Z</t>
+          <t>2026-10-04T23:25:17Z</t>
         </is>
       </c>
     </row>
@@ -7167,7 +7167,7 @@
       </c>
       <c r="K140" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:12Z</t>
+          <t>2026-10-04T23:25:17Z</t>
         </is>
       </c>
     </row>
@@ -7216,7 +7216,7 @@
       </c>
       <c r="K141" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:12Z</t>
+          <t>2026-10-04T23:25:17Z</t>
         </is>
       </c>
     </row>
@@ -7265,7 +7265,7 @@
       </c>
       <c r="K142" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:12Z</t>
+          <t>2026-10-04T23:25:17Z</t>
         </is>
       </c>
     </row>
@@ -7314,7 +7314,7 @@
       </c>
       <c r="K143" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:12Z</t>
+          <t>2026-10-04T23:25:17Z</t>
         </is>
       </c>
     </row>
@@ -7363,7 +7363,7 @@
       </c>
       <c r="K144" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:12Z</t>
+          <t>2026-10-04T23:25:17Z</t>
         </is>
       </c>
     </row>
@@ -7412,7 +7412,7 @@
       </c>
       <c r="K145" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:12Z</t>
+          <t>2026-10-04T23:25:17Z</t>
         </is>
       </c>
     </row>
@@ -7461,7 +7461,7 @@
       </c>
       <c r="K146" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:12Z</t>
+          <t>2026-10-04T23:25:17Z</t>
         </is>
       </c>
     </row>
@@ -7510,7 +7510,7 @@
       </c>
       <c r="K147" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:12Z</t>
+          <t>2026-10-04T23:25:17Z</t>
         </is>
       </c>
     </row>
@@ -7559,7 +7559,7 @@
       </c>
       <c r="K148" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:12Z</t>
+          <t>2026-10-04T23:25:17Z</t>
         </is>
       </c>
     </row>
@@ -7608,7 +7608,7 @@
       </c>
       <c r="K149" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:12Z</t>
+          <t>2026-10-04T23:25:17Z</t>
         </is>
       </c>
     </row>
@@ -7657,7 +7657,7 @@
       </c>
       <c r="K150" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:12Z</t>
+          <t>2026-10-04T23:25:17Z</t>
         </is>
       </c>
     </row>
@@ -7706,7 +7706,7 @@
       </c>
       <c r="K151" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:12Z</t>
+          <t>2026-10-04T23:25:17Z</t>
         </is>
       </c>
     </row>
@@ -7755,7 +7755,7 @@
       </c>
       <c r="K152" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:12Z</t>
+          <t>2026-10-04T23:25:17Z</t>
         </is>
       </c>
     </row>
@@ -7804,7 +7804,7 @@
       </c>
       <c r="K153" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:12Z</t>
+          <t>2026-10-04T23:25:17Z</t>
         </is>
       </c>
     </row>
@@ -7853,7 +7853,7 @@
       </c>
       <c r="K154" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:12Z</t>
+          <t>2026-10-04T23:25:17Z</t>
         </is>
       </c>
     </row>
@@ -7902,7 +7902,7 @@
       </c>
       <c r="K155" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:12Z</t>
+          <t>2026-10-04T23:25:17Z</t>
         </is>
       </c>
     </row>
@@ -7951,7 +7951,7 @@
       </c>
       <c r="K156" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:12Z</t>
+          <t>2026-10-04T23:25:17Z</t>
         </is>
       </c>
     </row>
@@ -8000,7 +8000,7 @@
       </c>
       <c r="K157" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:12Z</t>
+          <t>2026-10-04T23:25:17Z</t>
         </is>
       </c>
     </row>
@@ -8049,7 +8049,7 @@
       </c>
       <c r="K158" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:12Z</t>
+          <t>2026-10-04T23:25:17Z</t>
         </is>
       </c>
     </row>
@@ -8098,7 +8098,7 @@
       </c>
       <c r="K159" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:12Z</t>
+          <t>2026-10-04T23:25:17Z</t>
         </is>
       </c>
     </row>
@@ -8147,7 +8147,7 @@
       </c>
       <c r="K160" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:12Z</t>
+          <t>2026-10-04T23:25:17Z</t>
         </is>
       </c>
     </row>
@@ -8196,7 +8196,7 @@
       </c>
       <c r="K161" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:12Z</t>
+          <t>2026-10-04T23:25:17Z</t>
         </is>
       </c>
     </row>
@@ -8245,7 +8245,7 @@
       </c>
       <c r="K162" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:12Z</t>
+          <t>2026-10-04T23:25:17Z</t>
         </is>
       </c>
     </row>
@@ -8294,7 +8294,7 @@
       </c>
       <c r="K163" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:12Z</t>
+          <t>2026-10-04T23:25:17Z</t>
         </is>
       </c>
     </row>
@@ -8343,7 +8343,7 @@
       </c>
       <c r="K164" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:12Z</t>
+          <t>2026-10-04T23:25:17Z</t>
         </is>
       </c>
     </row>
@@ -8392,7 +8392,7 @@
       </c>
       <c r="K165" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:12Z</t>
+          <t>2026-10-04T23:25:17Z</t>
         </is>
       </c>
     </row>
@@ -8441,7 +8441,7 @@
       </c>
       <c r="K166" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:12Z</t>
+          <t>2026-10-04T23:25:17Z</t>
         </is>
       </c>
     </row>
@@ -8490,7 +8490,7 @@
       </c>
       <c r="K167" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:12Z</t>
+          <t>2026-10-04T23:25:17Z</t>
         </is>
       </c>
     </row>
@@ -8539,7 +8539,7 @@
       </c>
       <c r="K168" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:12Z</t>
+          <t>2026-10-04T23:25:17Z</t>
         </is>
       </c>
     </row>
@@ -8588,7 +8588,7 @@
       </c>
       <c r="K169" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:12Z</t>
+          <t>2026-10-04T23:25:17Z</t>
         </is>
       </c>
     </row>
@@ -8637,7 +8637,7 @@
       </c>
       <c r="K170" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:12Z</t>
+          <t>2026-10-04T23:25:17Z</t>
         </is>
       </c>
     </row>
@@ -8686,7 +8686,7 @@
       </c>
       <c r="K171" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:12Z</t>
+          <t>2026-10-04T23:25:17Z</t>
         </is>
       </c>
     </row>
@@ -8735,7 +8735,7 @@
       </c>
       <c r="K172" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:12Z</t>
+          <t>2026-10-04T23:25:17Z</t>
         </is>
       </c>
     </row>
@@ -8784,7 +8784,7 @@
       </c>
       <c r="K173" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:12Z</t>
+          <t>2026-10-04T23:25:17Z</t>
         </is>
       </c>
     </row>
@@ -8833,7 +8833,7 @@
       </c>
       <c r="K174" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:12Z</t>
+          <t>2026-10-04T23:25:17Z</t>
         </is>
       </c>
     </row>
@@ -8882,7 +8882,7 @@
       </c>
       <c r="K175" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:12Z</t>
+          <t>2026-10-04T23:25:17Z</t>
         </is>
       </c>
     </row>
@@ -8931,7 +8931,7 @@
       </c>
       <c r="K176" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:12Z</t>
+          <t>2026-10-04T23:25:17Z</t>
         </is>
       </c>
     </row>
@@ -8980,7 +8980,7 @@
       </c>
       <c r="K177" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:12Z</t>
+          <t>2026-10-04T23:25:17Z</t>
         </is>
       </c>
     </row>
@@ -9029,7 +9029,7 @@
       </c>
       <c r="K178" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:12Z</t>
+          <t>2026-10-04T23:25:17Z</t>
         </is>
       </c>
     </row>
@@ -9078,7 +9078,7 @@
       </c>
       <c r="K179" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:12Z</t>
+          <t>2026-10-04T23:25:17Z</t>
         </is>
       </c>
     </row>
@@ -9127,7 +9127,7 @@
       </c>
       <c r="K180" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:12Z</t>
+          <t>2026-10-04T23:25:17Z</t>
         </is>
       </c>
     </row>
@@ -9176,7 +9176,7 @@
       </c>
       <c r="K181" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:12Z</t>
+          <t>2026-10-04T23:25:17Z</t>
         </is>
       </c>
     </row>
@@ -9225,7 +9225,7 @@
       </c>
       <c r="K182" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:12Z</t>
+          <t>2026-10-04T23:25:17Z</t>
         </is>
       </c>
     </row>
@@ -9274,7 +9274,7 @@
       </c>
       <c r="K183" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:12Z</t>
+          <t>2026-10-04T23:25:17Z</t>
         </is>
       </c>
     </row>
@@ -9323,7 +9323,7 @@
       </c>
       <c r="K184" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:12Z</t>
+          <t>2026-10-04T23:25:17Z</t>
         </is>
       </c>
     </row>
@@ -9372,7 +9372,7 @@
       </c>
       <c r="K185" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:12Z</t>
+          <t>2026-10-04T23:25:17Z</t>
         </is>
       </c>
     </row>
@@ -9421,7 +9421,7 @@
       </c>
       <c r="K186" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:12Z</t>
+          <t>2026-10-04T23:25:17Z</t>
         </is>
       </c>
     </row>
@@ -9470,7 +9470,7 @@
       </c>
       <c r="K187" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:12Z</t>
+          <t>2026-10-04T23:25:17Z</t>
         </is>
       </c>
     </row>
@@ -9519,7 +9519,7 @@
       </c>
       <c r="K188" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:12Z</t>
+          <t>2026-10-04T23:25:17Z</t>
         </is>
       </c>
     </row>
@@ -9568,7 +9568,7 @@
       </c>
       <c r="K189" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:12Z</t>
+          <t>2026-10-04T23:25:17Z</t>
         </is>
       </c>
     </row>
@@ -9617,7 +9617,7 @@
       </c>
       <c r="K190" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:12Z</t>
+          <t>2026-10-04T23:25:17Z</t>
         </is>
       </c>
     </row>
@@ -9666,7 +9666,7 @@
       </c>
       <c r="K191" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:12Z</t>
+          <t>2026-10-04T23:25:17Z</t>
         </is>
       </c>
     </row>
@@ -9715,7 +9715,7 @@
       </c>
       <c r="K192" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:12Z</t>
+          <t>2026-10-04T23:25:17Z</t>
         </is>
       </c>
     </row>
@@ -9764,7 +9764,7 @@
       </c>
       <c r="K193" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:12Z</t>
+          <t>2026-10-04T23:25:17Z</t>
         </is>
       </c>
     </row>
@@ -9813,7 +9813,7 @@
       </c>
       <c r="K194" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:12Z</t>
+          <t>2026-10-04T23:25:17Z</t>
         </is>
       </c>
     </row>
@@ -9862,7 +9862,7 @@
       </c>
       <c r="K195" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:12Z</t>
+          <t>2026-10-04T23:25:17Z</t>
         </is>
       </c>
     </row>
@@ -9911,7 +9911,7 @@
       </c>
       <c r="K196" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:12Z</t>
+          <t>2026-10-04T23:25:17Z</t>
         </is>
       </c>
     </row>
@@ -9960,7 +9960,7 @@
       </c>
       <c r="K197" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:12Z</t>
+          <t>2026-10-04T23:25:17Z</t>
         </is>
       </c>
     </row>
@@ -10009,7 +10009,7 @@
       </c>
       <c r="K198" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:12Z</t>
+          <t>2026-10-04T23:25:17Z</t>
         </is>
       </c>
     </row>
@@ -10058,7 +10058,7 @@
       </c>
       <c r="K199" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:12Z</t>
+          <t>2026-10-04T23:25:17Z</t>
         </is>
       </c>
     </row>
@@ -10107,7 +10107,7 @@
       </c>
       <c r="K200" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:12Z</t>
+          <t>2026-10-04T23:25:17Z</t>
         </is>
       </c>
     </row>
@@ -10156,7 +10156,7 @@
       </c>
       <c r="K201" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:12Z</t>
+          <t>2026-10-04T23:25:17Z</t>
         </is>
       </c>
     </row>
@@ -10205,7 +10205,7 @@
       </c>
       <c r="K202" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:12Z</t>
+          <t>2026-10-04T23:25:17Z</t>
         </is>
       </c>
     </row>
@@ -10254,7 +10254,7 @@
       </c>
       <c r="K203" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:12Z</t>
+          <t>2026-10-04T23:25:17Z</t>
         </is>
       </c>
     </row>
@@ -10303,7 +10303,7 @@
       </c>
       <c r="K204" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:12Z</t>
+          <t>2026-10-04T23:25:17Z</t>
         </is>
       </c>
     </row>
@@ -10352,7 +10352,7 @@
       </c>
       <c r="K205" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:12Z</t>
+          <t>2026-10-04T23:25:17Z</t>
         </is>
       </c>
     </row>
@@ -10401,7 +10401,7 @@
       </c>
       <c r="K206" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:12Z</t>
+          <t>2026-10-04T23:25:17Z</t>
         </is>
       </c>
     </row>
@@ -10450,7 +10450,7 @@
       </c>
       <c r="K207" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:12Z</t>
+          <t>2026-10-04T23:25:17Z</t>
         </is>
       </c>
     </row>
@@ -10499,7 +10499,7 @@
       </c>
       <c r="K208" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:12Z</t>
+          <t>2026-10-04T23:25:17Z</t>
         </is>
       </c>
     </row>
@@ -10548,7 +10548,7 @@
       </c>
       <c r="K209" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:12Z</t>
+          <t>2026-10-04T23:25:17Z</t>
         </is>
       </c>
     </row>
@@ -10597,7 +10597,7 @@
       </c>
       <c r="K210" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:12Z</t>
+          <t>2026-10-04T23:25:17Z</t>
         </is>
       </c>
     </row>
@@ -10646,7 +10646,7 @@
       </c>
       <c r="K211" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:12Z</t>
+          <t>2026-10-04T23:25:17Z</t>
         </is>
       </c>
     </row>
@@ -10695,7 +10695,7 @@
       </c>
       <c r="K212" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:12Z</t>
+          <t>2026-10-04T23:25:17Z</t>
         </is>
       </c>
     </row>
@@ -10744,7 +10744,7 @@
       </c>
       <c r="K213" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:12Z</t>
+          <t>2026-10-04T23:25:17Z</t>
         </is>
       </c>
     </row>
@@ -10793,7 +10793,7 @@
       </c>
       <c r="K214" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:12Z</t>
+          <t>2026-10-04T23:25:17Z</t>
         </is>
       </c>
     </row>
@@ -10842,7 +10842,7 @@
       </c>
       <c r="K215" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:12Z</t>
+          <t>2026-10-04T23:25:17Z</t>
         </is>
       </c>
     </row>
@@ -10891,7 +10891,7 @@
       </c>
       <c r="K216" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:12Z</t>
+          <t>2026-10-04T23:25:17Z</t>
         </is>
       </c>
     </row>
@@ -10940,7 +10940,7 @@
       </c>
       <c r="K217" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:12Z</t>
+          <t>2026-10-04T23:25:17Z</t>
         </is>
       </c>
     </row>
@@ -10989,7 +10989,7 @@
       </c>
       <c r="K218" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:12Z</t>
+          <t>2026-10-04T23:25:17Z</t>
         </is>
       </c>
     </row>
@@ -11038,7 +11038,7 @@
       </c>
       <c r="K219" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:12Z</t>
+          <t>2026-10-04T23:25:17Z</t>
         </is>
       </c>
     </row>
@@ -11087,7 +11087,7 @@
       </c>
       <c r="K220" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:12Z</t>
+          <t>2026-10-04T23:25:17Z</t>
         </is>
       </c>
     </row>
@@ -11136,7 +11136,7 @@
       </c>
       <c r="K221" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:12Z</t>
+          <t>2026-10-04T23:25:17Z</t>
         </is>
       </c>
     </row>
@@ -11185,7 +11185,7 @@
       </c>
       <c r="K222" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:12Z</t>
+          <t>2026-10-04T23:25:17Z</t>
         </is>
       </c>
     </row>
@@ -11234,7 +11234,7 @@
       </c>
       <c r="K223" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:12Z</t>
+          <t>2026-10-04T23:25:17Z</t>
         </is>
       </c>
     </row>
@@ -11283,7 +11283,7 @@
       </c>
       <c r="K224" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:12Z</t>
+          <t>2026-10-04T23:25:17Z</t>
         </is>
       </c>
     </row>
@@ -11332,7 +11332,7 @@
       </c>
       <c r="K225" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:12Z</t>
+          <t>2026-10-04T23:25:17Z</t>
         </is>
       </c>
     </row>
@@ -11381,7 +11381,7 @@
       </c>
       <c r="K226" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:12Z</t>
+          <t>2026-10-04T23:25:17Z</t>
         </is>
       </c>
     </row>
@@ -11430,7 +11430,7 @@
       </c>
       <c r="K227" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:12Z</t>
+          <t>2026-10-04T23:25:17Z</t>
         </is>
       </c>
     </row>
@@ -11479,7 +11479,7 @@
       </c>
       <c r="K228" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:12Z</t>
+          <t>2026-10-04T23:25:17Z</t>
         </is>
       </c>
     </row>
@@ -11528,7 +11528,7 @@
       </c>
       <c r="K229" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:12Z</t>
+          <t>2026-10-04T23:25:17Z</t>
         </is>
       </c>
     </row>
@@ -11577,7 +11577,7 @@
       </c>
       <c r="K230" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:12Z</t>
+          <t>2026-10-04T23:25:17Z</t>
         </is>
       </c>
     </row>
@@ -11626,7 +11626,7 @@
       </c>
       <c r="K231" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:12Z</t>
+          <t>2026-10-04T23:25:17Z</t>
         </is>
       </c>
     </row>
@@ -11758,7 +11758,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:12Z</t>
+          <t>2026-10-04T23:25:17Z</t>
         </is>
       </c>
     </row>
@@ -11804,7 +11804,7 @@
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>{"date": "2026-08-01", "year": 2026, "month": 8, "month_name": "Agosto", "index_value": 637409769724325.1, "monthly_variation_pct": 8.9, "unit": "Índice base diciembre 2007=100 y variación mensual %", "frequency": "monthly", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/precios_consumidor/4_5_7_2.xls", "fetched_at": "2026-10-03T23:14:12Z"}</t>
+          <t>{"date": "2026-08-01", "year": 2026, "month": 8, "month_name": "Agosto", "index_value": 637409769724325.1, "monthly_variation_pct": 8.9, "unit": "Índice base diciembre 2007=100 y variación mensual %", "frequency": "monthly", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/precios_consumidor/4_5_7_2.xls", "fetched_at": "2026-10-04T23:25:17Z"}</t>
         </is>
       </c>
     </row>

--- a/assets/data/bcv/excel/ove_bcv_inpc_nacional_mensual.xlsx
+++ b/assets/data/bcv/excel/ove_bcv_inpc_nacional_mensual.xlsx
@@ -650,7 +650,7 @@
       </c>
       <c r="K7" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:17Z</t>
+          <t>2026-10-06T01:22:20Z</t>
         </is>
       </c>
     </row>
@@ -699,7 +699,7 @@
       </c>
       <c r="K8" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:17Z</t>
+          <t>2026-10-06T01:22:20Z</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="K9" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:17Z</t>
+          <t>2026-10-06T01:22:20Z</t>
         </is>
       </c>
     </row>
@@ -797,7 +797,7 @@
       </c>
       <c r="K10" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:17Z</t>
+          <t>2026-10-06T01:22:20Z</t>
         </is>
       </c>
     </row>
@@ -846,7 +846,7 @@
       </c>
       <c r="K11" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:17Z</t>
+          <t>2026-10-06T01:22:20Z</t>
         </is>
       </c>
     </row>
@@ -895,7 +895,7 @@
       </c>
       <c r="K12" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:17Z</t>
+          <t>2026-10-06T01:22:20Z</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="K13" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:17Z</t>
+          <t>2026-10-06T01:22:20Z</t>
         </is>
       </c>
     </row>
@@ -993,7 +993,7 @@
       </c>
       <c r="K14" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:17Z</t>
+          <t>2026-10-06T01:22:20Z</t>
         </is>
       </c>
     </row>
@@ -1042,7 +1042,7 @@
       </c>
       <c r="K15" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:17Z</t>
+          <t>2026-10-06T01:22:20Z</t>
         </is>
       </c>
     </row>
@@ -1091,7 +1091,7 @@
       </c>
       <c r="K16" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:17Z</t>
+          <t>2026-10-06T01:22:20Z</t>
         </is>
       </c>
     </row>
@@ -1140,7 +1140,7 @@
       </c>
       <c r="K17" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:17Z</t>
+          <t>2026-10-06T01:22:20Z</t>
         </is>
       </c>
     </row>
@@ -1189,7 +1189,7 @@
       </c>
       <c r="K18" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:17Z</t>
+          <t>2026-10-06T01:22:20Z</t>
         </is>
       </c>
     </row>
@@ -1238,7 +1238,7 @@
       </c>
       <c r="K19" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:17Z</t>
+          <t>2026-10-06T01:22:20Z</t>
         </is>
       </c>
     </row>
@@ -1287,7 +1287,7 @@
       </c>
       <c r="K20" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:17Z</t>
+          <t>2026-10-06T01:22:20Z</t>
         </is>
       </c>
     </row>
@@ -1336,7 +1336,7 @@
       </c>
       <c r="K21" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:17Z</t>
+          <t>2026-10-06T01:22:20Z</t>
         </is>
       </c>
     </row>
@@ -1385,7 +1385,7 @@
       </c>
       <c r="K22" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:17Z</t>
+          <t>2026-10-06T01:22:20Z</t>
         </is>
       </c>
     </row>
@@ -1434,7 +1434,7 @@
       </c>
       <c r="K23" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:17Z</t>
+          <t>2026-10-06T01:22:20Z</t>
         </is>
       </c>
     </row>
@@ -1483,7 +1483,7 @@
       </c>
       <c r="K24" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:17Z</t>
+          <t>2026-10-06T01:22:20Z</t>
         </is>
       </c>
     </row>
@@ -1532,7 +1532,7 @@
       </c>
       <c r="K25" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:17Z</t>
+          <t>2026-10-06T01:22:20Z</t>
         </is>
       </c>
     </row>
@@ -1581,7 +1581,7 @@
       </c>
       <c r="K26" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:17Z</t>
+          <t>2026-10-06T01:22:20Z</t>
         </is>
       </c>
     </row>
@@ -1630,7 +1630,7 @@
       </c>
       <c r="K27" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:17Z</t>
+          <t>2026-10-06T01:22:20Z</t>
         </is>
       </c>
     </row>
@@ -1679,7 +1679,7 @@
       </c>
       <c r="K28" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:17Z</t>
+          <t>2026-10-06T01:22:20Z</t>
         </is>
       </c>
     </row>
@@ -1728,7 +1728,7 @@
       </c>
       <c r="K29" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:17Z</t>
+          <t>2026-10-06T01:22:20Z</t>
         </is>
       </c>
     </row>
@@ -1777,7 +1777,7 @@
       </c>
       <c r="K30" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:17Z</t>
+          <t>2026-10-06T01:22:20Z</t>
         </is>
       </c>
     </row>
@@ -1826,7 +1826,7 @@
       </c>
       <c r="K31" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:17Z</t>
+          <t>2026-10-06T01:22:20Z</t>
         </is>
       </c>
     </row>
@@ -1875,7 +1875,7 @@
       </c>
       <c r="K32" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:17Z</t>
+          <t>2026-10-06T01:22:20Z</t>
         </is>
       </c>
     </row>
@@ -1924,7 +1924,7 @@
       </c>
       <c r="K33" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:17Z</t>
+          <t>2026-10-06T01:22:20Z</t>
         </is>
       </c>
     </row>
@@ -1973,7 +1973,7 @@
       </c>
       <c r="K34" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:17Z</t>
+          <t>2026-10-06T01:22:20Z</t>
         </is>
       </c>
     </row>
@@ -2022,7 +2022,7 @@
       </c>
       <c r="K35" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:17Z</t>
+          <t>2026-10-06T01:22:20Z</t>
         </is>
       </c>
     </row>
@@ -2071,7 +2071,7 @@
       </c>
       <c r="K36" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:17Z</t>
+          <t>2026-10-06T01:22:20Z</t>
         </is>
       </c>
     </row>
@@ -2120,7 +2120,7 @@
       </c>
       <c r="K37" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:17Z</t>
+          <t>2026-10-06T01:22:20Z</t>
         </is>
       </c>
     </row>
@@ -2169,7 +2169,7 @@
       </c>
       <c r="K38" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:17Z</t>
+          <t>2026-10-06T01:22:20Z</t>
         </is>
       </c>
     </row>
@@ -2218,7 +2218,7 @@
       </c>
       <c r="K39" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:17Z</t>
+          <t>2026-10-06T01:22:20Z</t>
         </is>
       </c>
     </row>
@@ -2267,7 +2267,7 @@
       </c>
       <c r="K40" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:17Z</t>
+          <t>2026-10-06T01:22:20Z</t>
         </is>
       </c>
     </row>
@@ -2316,7 +2316,7 @@
       </c>
       <c r="K41" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:17Z</t>
+          <t>2026-10-06T01:22:20Z</t>
         </is>
       </c>
     </row>
@@ -2365,7 +2365,7 @@
       </c>
       <c r="K42" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:17Z</t>
+          <t>2026-10-06T01:22:20Z</t>
         </is>
       </c>
     </row>
@@ -2414,7 +2414,7 @@
       </c>
       <c r="K43" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:17Z</t>
+          <t>2026-10-06T01:22:20Z</t>
         </is>
       </c>
     </row>
@@ -2463,7 +2463,7 @@
       </c>
       <c r="K44" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:17Z</t>
+          <t>2026-10-06T01:22:20Z</t>
         </is>
       </c>
     </row>
@@ -2512,7 +2512,7 @@
       </c>
       <c r="K45" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:17Z</t>
+          <t>2026-10-06T01:22:20Z</t>
         </is>
       </c>
     </row>
@@ -2561,7 +2561,7 @@
       </c>
       <c r="K46" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:17Z</t>
+          <t>2026-10-06T01:22:20Z</t>
         </is>
       </c>
     </row>
@@ -2610,7 +2610,7 @@
       </c>
       <c r="K47" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:17Z</t>
+          <t>2026-10-06T01:22:20Z</t>
         </is>
       </c>
     </row>
@@ -2659,7 +2659,7 @@
       </c>
       <c r="K48" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:17Z</t>
+          <t>2026-10-06T01:22:20Z</t>
         </is>
       </c>
     </row>
@@ -2708,7 +2708,7 @@
       </c>
       <c r="K49" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:17Z</t>
+          <t>2026-10-06T01:22:20Z</t>
         </is>
       </c>
     </row>
@@ -2757,7 +2757,7 @@
       </c>
       <c r="K50" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:17Z</t>
+          <t>2026-10-06T01:22:20Z</t>
         </is>
       </c>
     </row>
@@ -2806,7 +2806,7 @@
       </c>
       <c r="K51" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:17Z</t>
+          <t>2026-10-06T01:22:20Z</t>
         </is>
       </c>
     </row>
@@ -2855,7 +2855,7 @@
       </c>
       <c r="K52" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:17Z</t>
+          <t>2026-10-06T01:22:20Z</t>
         </is>
       </c>
     </row>
@@ -2904,7 +2904,7 @@
       </c>
       <c r="K53" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:17Z</t>
+          <t>2026-10-06T01:22:20Z</t>
         </is>
       </c>
     </row>
@@ -2953,7 +2953,7 @@
       </c>
       <c r="K54" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:17Z</t>
+          <t>2026-10-06T01:22:20Z</t>
         </is>
       </c>
     </row>
@@ -3002,7 +3002,7 @@
       </c>
       <c r="K55" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:17Z</t>
+          <t>2026-10-06T01:22:20Z</t>
         </is>
       </c>
     </row>
@@ -3051,7 +3051,7 @@
       </c>
       <c r="K56" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:17Z</t>
+          <t>2026-10-06T01:22:20Z</t>
         </is>
       </c>
     </row>
@@ -3100,7 +3100,7 @@
       </c>
       <c r="K57" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:17Z</t>
+          <t>2026-10-06T01:22:20Z</t>
         </is>
       </c>
     </row>
@@ -3149,7 +3149,7 @@
       </c>
       <c r="K58" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:17Z</t>
+          <t>2026-10-06T01:22:20Z</t>
         </is>
       </c>
     </row>
@@ -3198,7 +3198,7 @@
       </c>
       <c r="K59" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:17Z</t>
+          <t>2026-10-06T01:22:20Z</t>
         </is>
       </c>
     </row>
@@ -3247,7 +3247,7 @@
       </c>
       <c r="K60" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:17Z</t>
+          <t>2026-10-06T01:22:20Z</t>
         </is>
       </c>
     </row>
@@ -3296,7 +3296,7 @@
       </c>
       <c r="K61" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:17Z</t>
+          <t>2026-10-06T01:22:20Z</t>
         </is>
       </c>
     </row>
@@ -3345,7 +3345,7 @@
       </c>
       <c r="K62" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:17Z</t>
+          <t>2026-10-06T01:22:20Z</t>
         </is>
       </c>
     </row>
@@ -3394,7 +3394,7 @@
       </c>
       <c r="K63" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:17Z</t>
+          <t>2026-10-06T01:22:20Z</t>
         </is>
       </c>
     </row>
@@ -3443,7 +3443,7 @@
       </c>
       <c r="K64" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:17Z</t>
+          <t>2026-10-06T01:22:20Z</t>
         </is>
       </c>
     </row>
@@ -3492,7 +3492,7 @@
       </c>
       <c r="K65" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:17Z</t>
+          <t>2026-10-06T01:22:20Z</t>
         </is>
       </c>
     </row>
@@ -3541,7 +3541,7 @@
       </c>
       <c r="K66" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:17Z</t>
+          <t>2026-10-06T01:22:20Z</t>
         </is>
       </c>
     </row>
@@ -3590,7 +3590,7 @@
       </c>
       <c r="K67" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:17Z</t>
+          <t>2026-10-06T01:22:20Z</t>
         </is>
       </c>
     </row>
@@ -3639,7 +3639,7 @@
       </c>
       <c r="K68" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:17Z</t>
+          <t>2026-10-06T01:22:20Z</t>
         </is>
       </c>
     </row>
@@ -3688,7 +3688,7 @@
       </c>
       <c r="K69" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:17Z</t>
+          <t>2026-10-06T01:22:20Z</t>
         </is>
       </c>
     </row>
@@ -3737,7 +3737,7 @@
       </c>
       <c r="K70" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:17Z</t>
+          <t>2026-10-06T01:22:20Z</t>
         </is>
       </c>
     </row>
@@ -3786,7 +3786,7 @@
       </c>
       <c r="K71" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:17Z</t>
+          <t>2026-10-06T01:22:20Z</t>
         </is>
       </c>
     </row>
@@ -3835,7 +3835,7 @@
       </c>
       <c r="K72" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:17Z</t>
+          <t>2026-10-06T01:22:20Z</t>
         </is>
       </c>
     </row>
@@ -3884,7 +3884,7 @@
       </c>
       <c r="K73" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:17Z</t>
+          <t>2026-10-06T01:22:20Z</t>
         </is>
       </c>
     </row>
@@ -3933,7 +3933,7 @@
       </c>
       <c r="K74" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:17Z</t>
+          <t>2026-10-06T01:22:20Z</t>
         </is>
       </c>
     </row>
@@ -3982,7 +3982,7 @@
       </c>
       <c r="K75" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:17Z</t>
+          <t>2026-10-06T01:22:20Z</t>
         </is>
       </c>
     </row>
@@ -4031,7 +4031,7 @@
       </c>
       <c r="K76" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:17Z</t>
+          <t>2026-10-06T01:22:20Z</t>
         </is>
       </c>
     </row>
@@ -4080,7 +4080,7 @@
       </c>
       <c r="K77" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:17Z</t>
+          <t>2026-10-06T01:22:20Z</t>
         </is>
       </c>
     </row>
@@ -4129,7 +4129,7 @@
       </c>
       <c r="K78" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:17Z</t>
+          <t>2026-10-06T01:22:20Z</t>
         </is>
       </c>
     </row>
@@ -4178,7 +4178,7 @@
       </c>
       <c r="K79" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:17Z</t>
+          <t>2026-10-06T01:22:20Z</t>
         </is>
       </c>
     </row>
@@ -4227,7 +4227,7 @@
       </c>
       <c r="K80" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:17Z</t>
+          <t>2026-10-06T01:22:20Z</t>
         </is>
       </c>
     </row>
@@ -4276,7 +4276,7 @@
       </c>
       <c r="K81" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:17Z</t>
+          <t>2026-10-06T01:22:20Z</t>
         </is>
       </c>
     </row>
@@ -4325,7 +4325,7 @@
       </c>
       <c r="K82" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:17Z</t>
+          <t>2026-10-06T01:22:20Z</t>
         </is>
       </c>
     </row>
@@ -4374,7 +4374,7 @@
       </c>
       <c r="K83" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:17Z</t>
+          <t>2026-10-06T01:22:20Z</t>
         </is>
       </c>
     </row>
@@ -4423,7 +4423,7 @@
       </c>
       <c r="K84" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:17Z</t>
+          <t>2026-10-06T01:22:20Z</t>
         </is>
       </c>
     </row>
@@ -4472,7 +4472,7 @@
       </c>
       <c r="K85" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:17Z</t>
+          <t>2026-10-06T01:22:20Z</t>
         </is>
       </c>
     </row>
@@ -4521,7 +4521,7 @@
       </c>
       <c r="K86" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:17Z</t>
+          <t>2026-10-06T01:22:20Z</t>
         </is>
       </c>
     </row>
@@ -4570,7 +4570,7 @@
       </c>
       <c r="K87" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:17Z</t>
+          <t>2026-10-06T01:22:20Z</t>
         </is>
       </c>
     </row>
@@ -4619,7 +4619,7 @@
       </c>
       <c r="K88" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:17Z</t>
+          <t>2026-10-06T01:22:20Z</t>
         </is>
       </c>
     </row>
@@ -4668,7 +4668,7 @@
       </c>
       <c r="K89" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:17Z</t>
+          <t>2026-10-06T01:22:20Z</t>
         </is>
       </c>
     </row>
@@ -4717,7 +4717,7 @@
       </c>
       <c r="K90" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:17Z</t>
+          <t>2026-10-06T01:22:20Z</t>
         </is>
       </c>
     </row>
@@ -4766,7 +4766,7 @@
       </c>
       <c r="K91" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:17Z</t>
+          <t>2026-10-06T01:22:20Z</t>
         </is>
       </c>
     </row>
@@ -4815,7 +4815,7 @@
       </c>
       <c r="K92" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:17Z</t>
+          <t>2026-10-06T01:22:20Z</t>
         </is>
       </c>
     </row>
@@ -4864,7 +4864,7 @@
       </c>
       <c r="K93" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:17Z</t>
+          <t>2026-10-06T01:22:20Z</t>
         </is>
       </c>
     </row>
@@ -4913,7 +4913,7 @@
       </c>
       <c r="K94" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:17Z</t>
+          <t>2026-10-06T01:22:20Z</t>
         </is>
       </c>
     </row>
@@ -4962,7 +4962,7 @@
       </c>
       <c r="K95" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:17Z</t>
+          <t>2026-10-06T01:22:20Z</t>
         </is>
       </c>
     </row>
@@ -5011,7 +5011,7 @@
       </c>
       <c r="K96" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:17Z</t>
+          <t>2026-10-06T01:22:20Z</t>
         </is>
       </c>
     </row>
@@ -5060,7 +5060,7 @@
       </c>
       <c r="K97" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:17Z</t>
+          <t>2026-10-06T01:22:20Z</t>
         </is>
       </c>
     </row>
@@ -5109,7 +5109,7 @@
       </c>
       <c r="K98" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:17Z</t>
+          <t>2026-10-06T01:22:20Z</t>
         </is>
       </c>
     </row>
@@ -5158,7 +5158,7 @@
       </c>
       <c r="K99" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:17Z</t>
+          <t>2026-10-06T01:22:20Z</t>
         </is>
       </c>
     </row>
@@ -5207,7 +5207,7 @@
       </c>
       <c r="K100" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:17Z</t>
+          <t>2026-10-06T01:22:20Z</t>
         </is>
       </c>
     </row>
@@ -5256,7 +5256,7 @@
       </c>
       <c r="K101" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:17Z</t>
+          <t>2026-10-06T01:22:20Z</t>
         </is>
       </c>
     </row>
@@ -5305,7 +5305,7 @@
       </c>
       <c r="K102" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:17Z</t>
+          <t>2026-10-06T01:22:20Z</t>
         </is>
       </c>
     </row>
@@ -5354,7 +5354,7 @@
       </c>
       <c r="K103" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:17Z</t>
+          <t>2026-10-06T01:22:20Z</t>
         </is>
       </c>
     </row>
@@ -5403,7 +5403,7 @@
       </c>
       <c r="K104" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:17Z</t>
+          <t>2026-10-06T01:22:20Z</t>
         </is>
       </c>
     </row>
@@ -5452,7 +5452,7 @@
       </c>
       <c r="K105" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:17Z</t>
+          <t>2026-10-06T01:22:20Z</t>
         </is>
       </c>
     </row>
@@ -5501,7 +5501,7 @@
       </c>
       <c r="K106" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:17Z</t>
+          <t>2026-10-06T01:22:20Z</t>
         </is>
       </c>
     </row>
@@ -5550,7 +5550,7 @@
       </c>
       <c r="K107" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:17Z</t>
+          <t>2026-10-06T01:22:20Z</t>
         </is>
       </c>
     </row>
@@ -5599,7 +5599,7 @@
       </c>
       <c r="K108" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:17Z</t>
+          <t>2026-10-06T01:22:20Z</t>
         </is>
       </c>
     </row>
@@ -5648,7 +5648,7 @@
       </c>
       <c r="K109" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:17Z</t>
+          <t>2026-10-06T01:22:20Z</t>
         </is>
       </c>
     </row>
@@ -5697,7 +5697,7 @@
       </c>
       <c r="K110" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:17Z</t>
+          <t>2026-10-06T01:22:20Z</t>
         </is>
       </c>
     </row>
@@ -5746,7 +5746,7 @@
       </c>
       <c r="K111" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:17Z</t>
+          <t>2026-10-06T01:22:20Z</t>
         </is>
       </c>
     </row>
@@ -5795,7 +5795,7 @@
       </c>
       <c r="K112" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:17Z</t>
+          <t>2026-10-06T01:22:20Z</t>
         </is>
       </c>
     </row>
@@ -5844,7 +5844,7 @@
       </c>
       <c r="K113" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:17Z</t>
+          <t>2026-10-06T01:22:20Z</t>
         </is>
       </c>
     </row>
@@ -5893,7 +5893,7 @@
       </c>
       <c r="K114" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:17Z</t>
+          <t>2026-10-06T01:22:20Z</t>
         </is>
       </c>
     </row>
@@ -5942,7 +5942,7 @@
       </c>
       <c r="K115" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:17Z</t>
+          <t>2026-10-06T01:22:20Z</t>
         </is>
       </c>
     </row>
@@ -5991,7 +5991,7 @@
       </c>
       <c r="K116" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:17Z</t>
+          <t>2026-10-06T01:22:20Z</t>
         </is>
       </c>
     </row>
@@ -6040,7 +6040,7 @@
       </c>
       <c r="K117" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:17Z</t>
+          <t>2026-10-06T01:22:20Z</t>
         </is>
       </c>
     </row>
@@ -6089,7 +6089,7 @@
       </c>
       <c r="K118" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:17Z</t>
+          <t>2026-10-06T01:22:20Z</t>
         </is>
       </c>
     </row>
@@ -6138,7 +6138,7 @@
       </c>
       <c r="K119" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:17Z</t>
+          <t>2026-10-06T01:22:20Z</t>
         </is>
       </c>
     </row>
@@ -6187,7 +6187,7 @@
       </c>
       <c r="K120" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:17Z</t>
+          <t>2026-10-06T01:22:20Z</t>
         </is>
       </c>
     </row>
@@ -6236,7 +6236,7 @@
       </c>
       <c r="K121" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:17Z</t>
+          <t>2026-10-06T01:22:20Z</t>
         </is>
       </c>
     </row>
@@ -6285,7 +6285,7 @@
       </c>
       <c r="K122" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:17Z</t>
+          <t>2026-10-06T01:22:20Z</t>
         </is>
       </c>
     </row>
@@ -6334,7 +6334,7 @@
       </c>
       <c r="K123" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:17Z</t>
+          <t>2026-10-06T01:22:20Z</t>
         </is>
       </c>
     </row>
@@ -6383,7 +6383,7 @@
       </c>
       <c r="K124" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:17Z</t>
+          <t>2026-10-06T01:22:20Z</t>
         </is>
       </c>
     </row>
@@ -6432,7 +6432,7 @@
       </c>
       <c r="K125" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:17Z</t>
+          <t>2026-10-06T01:22:20Z</t>
         </is>
       </c>
     </row>
@@ -6481,7 +6481,7 @@
       </c>
       <c r="K126" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:17Z</t>
+          <t>2026-10-06T01:22:20Z</t>
         </is>
       </c>
     </row>
@@ -6530,7 +6530,7 @@
       </c>
       <c r="K127" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:17Z</t>
+          <t>2026-10-06T01:22:20Z</t>
         </is>
       </c>
     </row>
@@ -6579,7 +6579,7 @@
       </c>
       <c r="K128" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:17Z</t>
+          <t>2026-10-06T01:22:20Z</t>
         </is>
       </c>
     </row>
@@ -6628,7 +6628,7 @@
       </c>
       <c r="K129" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:17Z</t>
+          <t>2026-10-06T01:22:20Z</t>
         </is>
       </c>
     </row>
@@ -6677,7 +6677,7 @@
       </c>
       <c r="K130" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:17Z</t>
+          <t>2026-10-06T01:22:20Z</t>
         </is>
       </c>
     </row>
@@ -6726,7 +6726,7 @@
       </c>
       <c r="K131" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:17Z</t>
+          <t>2026-10-06T01:22:20Z</t>
         </is>
       </c>
     </row>
@@ -6775,7 +6775,7 @@
       </c>
       <c r="K132" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:17Z</t>
+          <t>2026-10-06T01:22:20Z</t>
         </is>
       </c>
     </row>
@@ -6824,7 +6824,7 @@
       </c>
       <c r="K133" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:17Z</t>
+          <t>2026-10-06T01:22:20Z</t>
         </is>
       </c>
     </row>
@@ -6873,7 +6873,7 @@
       </c>
       <c r="K134" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:17Z</t>
+          <t>2026-10-06T01:22:20Z</t>
         </is>
       </c>
     </row>
@@ -6922,7 +6922,7 @@
       </c>
       <c r="K135" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:17Z</t>
+          <t>2026-10-06T01:22:20Z</t>
         </is>
       </c>
     </row>
@@ -6971,7 +6971,7 @@
       </c>
       <c r="K136" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:17Z</t>
+          <t>2026-10-06T01:22:20Z</t>
         </is>
       </c>
     </row>
@@ -7020,7 +7020,7 @@
       </c>
       <c r="K137" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:17Z</t>
+          <t>2026-10-06T01:22:20Z</t>
         </is>
       </c>
     </row>
@@ -7069,7 +7069,7 @@
       </c>
       <c r="K138" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:17Z</t>
+          <t>2026-10-06T01:22:20Z</t>
         </is>
       </c>
     </row>
@@ -7118,7 +7118,7 @@
       </c>
       <c r="K139" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:17Z</t>
+          <t>2026-10-06T01:22:20Z</t>
         </is>
       </c>
     </row>
@@ -7167,7 +7167,7 @@
       </c>
       <c r="K140" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:17Z</t>
+          <t>2026-10-06T01:22:20Z</t>
         </is>
       </c>
     </row>
@@ -7216,7 +7216,7 @@
       </c>
       <c r="K141" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:17Z</t>
+          <t>2026-10-06T01:22:20Z</t>
         </is>
       </c>
     </row>
@@ -7265,7 +7265,7 @@
       </c>
       <c r="K142" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:17Z</t>
+          <t>2026-10-06T01:22:20Z</t>
         </is>
       </c>
     </row>
@@ -7314,7 +7314,7 @@
       </c>
       <c r="K143" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:17Z</t>
+          <t>2026-10-06T01:22:20Z</t>
         </is>
       </c>
     </row>
@@ -7363,7 +7363,7 @@
       </c>
       <c r="K144" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:17Z</t>
+          <t>2026-10-06T01:22:20Z</t>
         </is>
       </c>
     </row>
@@ -7412,7 +7412,7 @@
       </c>
       <c r="K145" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:17Z</t>
+          <t>2026-10-06T01:22:20Z</t>
         </is>
       </c>
     </row>
@@ -7461,7 +7461,7 @@
       </c>
       <c r="K146" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:17Z</t>
+          <t>2026-10-06T01:22:20Z</t>
         </is>
       </c>
     </row>
@@ -7510,7 +7510,7 @@
       </c>
       <c r="K147" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:17Z</t>
+          <t>2026-10-06T01:22:20Z</t>
         </is>
       </c>
     </row>
@@ -7559,7 +7559,7 @@
       </c>
       <c r="K148" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:17Z</t>
+          <t>2026-10-06T01:22:20Z</t>
         </is>
       </c>
     </row>
@@ -7608,7 +7608,7 @@
       </c>
       <c r="K149" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:17Z</t>
+          <t>2026-10-06T01:22:20Z</t>
         </is>
       </c>
     </row>
@@ -7657,7 +7657,7 @@
       </c>
       <c r="K150" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:17Z</t>
+          <t>2026-10-06T01:22:20Z</t>
         </is>
       </c>
     </row>
@@ -7706,7 +7706,7 @@
       </c>
       <c r="K151" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:17Z</t>
+          <t>2026-10-06T01:22:20Z</t>
         </is>
       </c>
     </row>
@@ -7755,7 +7755,7 @@
       </c>
       <c r="K152" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:17Z</t>
+          <t>2026-10-06T01:22:20Z</t>
         </is>
       </c>
     </row>
@@ -7804,7 +7804,7 @@
       </c>
       <c r="K153" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:17Z</t>
+          <t>2026-10-06T01:22:20Z</t>
         </is>
       </c>
     </row>
@@ -7853,7 +7853,7 @@
       </c>
       <c r="K154" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:17Z</t>
+          <t>2026-10-06T01:22:20Z</t>
         </is>
       </c>
     </row>
@@ -7902,7 +7902,7 @@
       </c>
       <c r="K155" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:17Z</t>
+          <t>2026-10-06T01:22:20Z</t>
         </is>
       </c>
     </row>
@@ -7951,7 +7951,7 @@
       </c>
       <c r="K156" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:17Z</t>
+          <t>2026-10-06T01:22:20Z</t>
         </is>
       </c>
     </row>
@@ -8000,7 +8000,7 @@
       </c>
       <c r="K157" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:17Z</t>
+          <t>2026-10-06T01:22:20Z</t>
         </is>
       </c>
     </row>
@@ -8049,7 +8049,7 @@
       </c>
       <c r="K158" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:17Z</t>
+          <t>2026-10-06T01:22:20Z</t>
         </is>
       </c>
     </row>
@@ -8098,7 +8098,7 @@
       </c>
       <c r="K159" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:17Z</t>
+          <t>2026-10-06T01:22:20Z</t>
         </is>
       </c>
     </row>
@@ -8147,7 +8147,7 @@
       </c>
       <c r="K160" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:17Z</t>
+          <t>2026-10-06T01:22:20Z</t>
         </is>
       </c>
     </row>
@@ -8196,7 +8196,7 @@
       </c>
       <c r="K161" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:17Z</t>
+          <t>2026-10-06T01:22:20Z</t>
         </is>
       </c>
     </row>
@@ -8245,7 +8245,7 @@
       </c>
       <c r="K162" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:17Z</t>
+          <t>2026-10-06T01:22:20Z</t>
         </is>
       </c>
     </row>
@@ -8294,7 +8294,7 @@
       </c>
       <c r="K163" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:17Z</t>
+          <t>2026-10-06T01:22:20Z</t>
         </is>
       </c>
     </row>
@@ -8343,7 +8343,7 @@
       </c>
       <c r="K164" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:17Z</t>
+          <t>2026-10-06T01:22:20Z</t>
         </is>
       </c>
     </row>
@@ -8392,7 +8392,7 @@
       </c>
       <c r="K165" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:17Z</t>
+          <t>2026-10-06T01:22:20Z</t>
         </is>
       </c>
     </row>
@@ -8441,7 +8441,7 @@
       </c>
       <c r="K166" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:17Z</t>
+          <t>2026-10-06T01:22:20Z</t>
         </is>
       </c>
     </row>
@@ -8490,7 +8490,7 @@
       </c>
       <c r="K167" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:17Z</t>
+          <t>2026-10-06T01:22:20Z</t>
         </is>
       </c>
     </row>
@@ -8539,7 +8539,7 @@
       </c>
       <c r="K168" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:17Z</t>
+          <t>2026-10-06T01:22:20Z</t>
         </is>
       </c>
     </row>
@@ -8588,7 +8588,7 @@
       </c>
       <c r="K169" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:17Z</t>
+          <t>2026-10-06T01:22:20Z</t>
         </is>
       </c>
     </row>
@@ -8637,7 +8637,7 @@
       </c>
       <c r="K170" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:17Z</t>
+          <t>2026-10-06T01:22:20Z</t>
         </is>
       </c>
     </row>
@@ -8686,7 +8686,7 @@
       </c>
       <c r="K171" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:17Z</t>
+          <t>2026-10-06T01:22:20Z</t>
         </is>
       </c>
     </row>
@@ -8735,7 +8735,7 @@
       </c>
       <c r="K172" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:17Z</t>
+          <t>2026-10-06T01:22:20Z</t>
         </is>
       </c>
     </row>
@@ -8784,7 +8784,7 @@
       </c>
       <c r="K173" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:17Z</t>
+          <t>2026-10-06T01:22:20Z</t>
         </is>
       </c>
     </row>
@@ -8833,7 +8833,7 @@
       </c>
       <c r="K174" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:17Z</t>
+          <t>2026-10-06T01:22:20Z</t>
         </is>
       </c>
     </row>
@@ -8882,7 +8882,7 @@
       </c>
       <c r="K175" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:17Z</t>
+          <t>2026-10-06T01:22:20Z</t>
         </is>
       </c>
     </row>
@@ -8931,7 +8931,7 @@
       </c>
       <c r="K176" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:17Z</t>
+          <t>2026-10-06T01:22:20Z</t>
         </is>
       </c>
     </row>
@@ -8980,7 +8980,7 @@
       </c>
       <c r="K177" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:17Z</t>
+          <t>2026-10-06T01:22:20Z</t>
         </is>
       </c>
     </row>
@@ -9029,7 +9029,7 @@
       </c>
       <c r="K178" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:17Z</t>
+          <t>2026-10-06T01:22:20Z</t>
         </is>
       </c>
     </row>
@@ -9078,7 +9078,7 @@
       </c>
       <c r="K179" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:17Z</t>
+          <t>2026-10-06T01:22:20Z</t>
         </is>
       </c>
     </row>
@@ -9127,7 +9127,7 @@
       </c>
       <c r="K180" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:17Z</t>
+          <t>2026-10-06T01:22:20Z</t>
         </is>
       </c>
     </row>
@@ -9176,7 +9176,7 @@
       </c>
       <c r="K181" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:17Z</t>
+          <t>2026-10-06T01:22:20Z</t>
         </is>
       </c>
     </row>
@@ -9225,7 +9225,7 @@
       </c>
       <c r="K182" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:17Z</t>
+          <t>2026-10-06T01:22:20Z</t>
         </is>
       </c>
     </row>
@@ -9274,7 +9274,7 @@
       </c>
       <c r="K183" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:17Z</t>
+          <t>2026-10-06T01:22:20Z</t>
         </is>
       </c>
     </row>
@@ -9323,7 +9323,7 @@
       </c>
       <c r="K184" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:17Z</t>
+          <t>2026-10-06T01:22:20Z</t>
         </is>
       </c>
     </row>
@@ -9372,7 +9372,7 @@
       </c>
       <c r="K185" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:17Z</t>
+          <t>2026-10-06T01:22:20Z</t>
         </is>
       </c>
     </row>
@@ -9421,7 +9421,7 @@
       </c>
       <c r="K186" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:17Z</t>
+          <t>2026-10-06T01:22:20Z</t>
         </is>
       </c>
     </row>
@@ -9470,7 +9470,7 @@
       </c>
       <c r="K187" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:17Z</t>
+          <t>2026-10-06T01:22:20Z</t>
         </is>
       </c>
     </row>
@@ -9519,7 +9519,7 @@
       </c>
       <c r="K188" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:17Z</t>
+          <t>2026-10-06T01:22:20Z</t>
         </is>
       </c>
     </row>
@@ -9568,7 +9568,7 @@
       </c>
       <c r="K189" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:17Z</t>
+          <t>2026-10-06T01:22:20Z</t>
         </is>
       </c>
     </row>
@@ -9617,7 +9617,7 @@
       </c>
       <c r="K190" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:17Z</t>
+          <t>2026-10-06T01:22:20Z</t>
         </is>
       </c>
     </row>
@@ -9666,7 +9666,7 @@
       </c>
       <c r="K191" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:17Z</t>
+          <t>2026-10-06T01:22:20Z</t>
         </is>
       </c>
     </row>
@@ -9715,7 +9715,7 @@
       </c>
       <c r="K192" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:17Z</t>
+          <t>2026-10-06T01:22:20Z</t>
         </is>
       </c>
     </row>
@@ -9764,7 +9764,7 @@
       </c>
       <c r="K193" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:17Z</t>
+          <t>2026-10-06T01:22:20Z</t>
         </is>
       </c>
     </row>
@@ -9813,7 +9813,7 @@
       </c>
       <c r="K194" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:17Z</t>
+          <t>2026-10-06T01:22:20Z</t>
         </is>
       </c>
     </row>
@@ -9862,7 +9862,7 @@
       </c>
       <c r="K195" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:17Z</t>
+          <t>2026-10-06T01:22:20Z</t>
         </is>
       </c>
     </row>
@@ -9911,7 +9911,7 @@
       </c>
       <c r="K196" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:17Z</t>
+          <t>2026-10-06T01:22:20Z</t>
         </is>
       </c>
     </row>
@@ -9960,7 +9960,7 @@
       </c>
       <c r="K197" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:17Z</t>
+          <t>2026-10-06T01:22:20Z</t>
         </is>
       </c>
     </row>
@@ -10009,7 +10009,7 @@
       </c>
       <c r="K198" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:17Z</t>
+          <t>2026-10-06T01:22:20Z</t>
         </is>
       </c>
     </row>
@@ -10058,7 +10058,7 @@
       </c>
       <c r="K199" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:17Z</t>
+          <t>2026-10-06T01:22:20Z</t>
         </is>
       </c>
     </row>
@@ -10107,7 +10107,7 @@
       </c>
       <c r="K200" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:17Z</t>
+          <t>2026-10-06T01:22:20Z</t>
         </is>
       </c>
     </row>
@@ -10156,7 +10156,7 @@
       </c>
       <c r="K201" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:17Z</t>
+          <t>2026-10-06T01:22:20Z</t>
         </is>
       </c>
     </row>
@@ -10205,7 +10205,7 @@
       </c>
       <c r="K202" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:17Z</t>
+          <t>2026-10-06T01:22:20Z</t>
         </is>
       </c>
     </row>
@@ -10254,7 +10254,7 @@
       </c>
       <c r="K203" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:17Z</t>
+          <t>2026-10-06T01:22:20Z</t>
         </is>
       </c>
     </row>
@@ -10303,7 +10303,7 @@
       </c>
       <c r="K204" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:17Z</t>
+          <t>2026-10-06T01:22:20Z</t>
         </is>
       </c>
     </row>
@@ -10352,7 +10352,7 @@
       </c>
       <c r="K205" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:17Z</t>
+          <t>2026-10-06T01:22:20Z</t>
         </is>
       </c>
     </row>
@@ -10401,7 +10401,7 @@
       </c>
       <c r="K206" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:17Z</t>
+          <t>2026-10-06T01:22:20Z</t>
         </is>
       </c>
     </row>
@@ -10450,7 +10450,7 @@
       </c>
       <c r="K207" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:17Z</t>
+          <t>2026-10-06T01:22:20Z</t>
         </is>
       </c>
     </row>
@@ -10499,7 +10499,7 @@
       </c>
       <c r="K208" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:17Z</t>
+          <t>2026-10-06T01:22:20Z</t>
         </is>
       </c>
     </row>
@@ -10548,7 +10548,7 @@
       </c>
       <c r="K209" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:17Z</t>
+          <t>2026-10-06T01:22:20Z</t>
         </is>
       </c>
     </row>
@@ -10597,7 +10597,7 @@
       </c>
       <c r="K210" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:17Z</t>
+          <t>2026-10-06T01:22:20Z</t>
         </is>
       </c>
     </row>
@@ -10646,7 +10646,7 @@
       </c>
       <c r="K211" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:17Z</t>
+          <t>2026-10-06T01:22:20Z</t>
         </is>
       </c>
     </row>
@@ -10695,7 +10695,7 @@
       </c>
       <c r="K212" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:17Z</t>
+          <t>2026-10-06T01:22:20Z</t>
         </is>
       </c>
     </row>
@@ -10744,7 +10744,7 @@
       </c>
       <c r="K213" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:17Z</t>
+          <t>2026-10-06T01:22:20Z</t>
         </is>
       </c>
     </row>
@@ -10793,7 +10793,7 @@
       </c>
       <c r="K214" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:17Z</t>
+          <t>2026-10-06T01:22:20Z</t>
         </is>
       </c>
     </row>
@@ -10842,7 +10842,7 @@
       </c>
       <c r="K215" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:17Z</t>
+          <t>2026-10-06T01:22:20Z</t>
         </is>
       </c>
     </row>
@@ -10891,7 +10891,7 @@
       </c>
       <c r="K216" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:17Z</t>
+          <t>2026-10-06T01:22:20Z</t>
         </is>
       </c>
     </row>
@@ -10940,7 +10940,7 @@
       </c>
       <c r="K217" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:17Z</t>
+          <t>2026-10-06T01:22:20Z</t>
         </is>
       </c>
     </row>
@@ -10989,7 +10989,7 @@
       </c>
       <c r="K218" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:17Z</t>
+          <t>2026-10-06T01:22:20Z</t>
         </is>
       </c>
     </row>
@@ -11038,7 +11038,7 @@
       </c>
       <c r="K219" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:17Z</t>
+          <t>2026-10-06T01:22:20Z</t>
         </is>
       </c>
     </row>
@@ -11087,7 +11087,7 @@
       </c>
       <c r="K220" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:17Z</t>
+          <t>2026-10-06T01:22:20Z</t>
         </is>
       </c>
     </row>
@@ -11136,7 +11136,7 @@
       </c>
       <c r="K221" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:17Z</t>
+          <t>2026-10-06T01:22:20Z</t>
         </is>
       </c>
     </row>
@@ -11185,7 +11185,7 @@
       </c>
       <c r="K222" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:17Z</t>
+          <t>2026-10-06T01:22:20Z</t>
         </is>
       </c>
     </row>
@@ -11234,7 +11234,7 @@
       </c>
       <c r="K223" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:17Z</t>
+          <t>2026-10-06T01:22:20Z</t>
         </is>
       </c>
     </row>
@@ -11283,7 +11283,7 @@
       </c>
       <c r="K224" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:17Z</t>
+          <t>2026-10-06T01:22:20Z</t>
         </is>
       </c>
     </row>
@@ -11332,7 +11332,7 @@
       </c>
       <c r="K225" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:17Z</t>
+          <t>2026-10-06T01:22:20Z</t>
         </is>
       </c>
     </row>
@@ -11381,7 +11381,7 @@
       </c>
       <c r="K226" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:17Z</t>
+          <t>2026-10-06T01:22:20Z</t>
         </is>
       </c>
     </row>
@@ -11430,7 +11430,7 @@
       </c>
       <c r="K227" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:17Z</t>
+          <t>2026-10-06T01:22:20Z</t>
         </is>
       </c>
     </row>
@@ -11479,7 +11479,7 @@
       </c>
       <c r="K228" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:17Z</t>
+          <t>2026-10-06T01:22:20Z</t>
         </is>
       </c>
     </row>
@@ -11528,7 +11528,7 @@
       </c>
       <c r="K229" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:17Z</t>
+          <t>2026-10-06T01:22:20Z</t>
         </is>
       </c>
     </row>
@@ -11577,7 +11577,7 @@
       </c>
       <c r="K230" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:17Z</t>
+          <t>2026-10-06T01:22:20Z</t>
         </is>
       </c>
     </row>
@@ -11626,7 +11626,7 @@
       </c>
       <c r="K231" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:17Z</t>
+          <t>2026-10-06T01:22:20Z</t>
         </is>
       </c>
     </row>
@@ -11758,7 +11758,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:17Z</t>
+          <t>2026-10-06T01:22:20Z</t>
         </is>
       </c>
     </row>
@@ -11804,7 +11804,7 @@
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>{"date": "2026-08-01", "year": 2026, "month": 8, "month_name": "Agosto", "index_value": 637409769724325.1, "monthly_variation_pct": 8.9, "unit": "Índice base diciembre 2007=100 y variación mensual %", "frequency": "monthly", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/precios_consumidor/4_5_7_2.xls", "fetched_at": "2026-10-04T23:25:17Z"}</t>
+          <t>{"date": "2026-08-01", "year": 2026, "month": 8, "month_name": "Agosto", "index_value": 637409769724325.1, "monthly_variation_pct": 8.9, "unit": "Índice base diciembre 2007=100 y variación mensual %", "frequency": "monthly", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/precios_consumidor/4_5_7_2.xls", "fetched_at": "2026-10-06T01:22:20Z"}</t>
         </is>
       </c>
     </row>

--- a/assets/data/bcv/excel/ove_bcv_inpc_nacional_mensual.xlsx
+++ b/assets/data/bcv/excel/ove_bcv_inpc_nacional_mensual.xlsx
@@ -650,7 +650,7 @@
       </c>
       <c r="K7" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:20Z</t>
+          <t>2026-10-06T23:56:58Z</t>
         </is>
       </c>
     </row>
@@ -699,7 +699,7 @@
       </c>
       <c r="K8" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:20Z</t>
+          <t>2026-10-06T23:56:58Z</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="K9" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:20Z</t>
+          <t>2026-10-06T23:56:58Z</t>
         </is>
       </c>
     </row>
@@ -797,7 +797,7 @@
       </c>
       <c r="K10" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:20Z</t>
+          <t>2026-10-06T23:56:58Z</t>
         </is>
       </c>
     </row>
@@ -846,7 +846,7 @@
       </c>
       <c r="K11" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:20Z</t>
+          <t>2026-10-06T23:56:58Z</t>
         </is>
       </c>
     </row>
@@ -895,7 +895,7 @@
       </c>
       <c r="K12" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:20Z</t>
+          <t>2026-10-06T23:56:58Z</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="K13" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:20Z</t>
+          <t>2026-10-06T23:56:58Z</t>
         </is>
       </c>
     </row>
@@ -993,7 +993,7 @@
       </c>
       <c r="K14" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:20Z</t>
+          <t>2026-10-06T23:56:58Z</t>
         </is>
       </c>
     </row>
@@ -1042,7 +1042,7 @@
       </c>
       <c r="K15" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:20Z</t>
+          <t>2026-10-06T23:56:58Z</t>
         </is>
       </c>
     </row>
@@ -1091,7 +1091,7 @@
       </c>
       <c r="K16" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:20Z</t>
+          <t>2026-10-06T23:56:58Z</t>
         </is>
       </c>
     </row>
@@ -1140,7 +1140,7 @@
       </c>
       <c r="K17" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:20Z</t>
+          <t>2026-10-06T23:56:58Z</t>
         </is>
       </c>
     </row>
@@ -1189,7 +1189,7 @@
       </c>
       <c r="K18" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:20Z</t>
+          <t>2026-10-06T23:56:58Z</t>
         </is>
       </c>
     </row>
@@ -1238,7 +1238,7 @@
       </c>
       <c r="K19" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:20Z</t>
+          <t>2026-10-06T23:56:58Z</t>
         </is>
       </c>
     </row>
@@ -1287,7 +1287,7 @@
       </c>
       <c r="K20" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:20Z</t>
+          <t>2026-10-06T23:56:58Z</t>
         </is>
       </c>
     </row>
@@ -1336,7 +1336,7 @@
       </c>
       <c r="K21" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:20Z</t>
+          <t>2026-10-06T23:56:58Z</t>
         </is>
       </c>
     </row>
@@ -1385,7 +1385,7 @@
       </c>
       <c r="K22" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:20Z</t>
+          <t>2026-10-06T23:56:58Z</t>
         </is>
       </c>
     </row>
@@ -1434,7 +1434,7 @@
       </c>
       <c r="K23" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:20Z</t>
+          <t>2026-10-06T23:56:58Z</t>
         </is>
       </c>
     </row>
@@ -1483,7 +1483,7 @@
       </c>
       <c r="K24" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:20Z</t>
+          <t>2026-10-06T23:56:58Z</t>
         </is>
       </c>
     </row>
@@ -1532,7 +1532,7 @@
       </c>
       <c r="K25" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:20Z</t>
+          <t>2026-10-06T23:56:58Z</t>
         </is>
       </c>
     </row>
@@ -1581,7 +1581,7 @@
       </c>
       <c r="K26" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:20Z</t>
+          <t>2026-10-06T23:56:58Z</t>
         </is>
       </c>
     </row>
@@ -1630,7 +1630,7 @@
       </c>
       <c r="K27" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:20Z</t>
+          <t>2026-10-06T23:56:58Z</t>
         </is>
       </c>
     </row>
@@ -1679,7 +1679,7 @@
       </c>
       <c r="K28" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:20Z</t>
+          <t>2026-10-06T23:56:58Z</t>
         </is>
       </c>
     </row>
@@ -1728,7 +1728,7 @@
       </c>
       <c r="K29" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:20Z</t>
+          <t>2026-10-06T23:56:58Z</t>
         </is>
       </c>
     </row>
@@ -1777,7 +1777,7 @@
       </c>
       <c r="K30" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:20Z</t>
+          <t>2026-10-06T23:56:58Z</t>
         </is>
       </c>
     </row>
@@ -1826,7 +1826,7 @@
       </c>
       <c r="K31" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:20Z</t>
+          <t>2026-10-06T23:56:58Z</t>
         </is>
       </c>
     </row>
@@ -1875,7 +1875,7 @@
       </c>
       <c r="K32" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:20Z</t>
+          <t>2026-10-06T23:56:58Z</t>
         </is>
       </c>
     </row>
@@ -1924,7 +1924,7 @@
       </c>
       <c r="K33" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:20Z</t>
+          <t>2026-10-06T23:56:58Z</t>
         </is>
       </c>
     </row>
@@ -1973,7 +1973,7 @@
       </c>
       <c r="K34" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:20Z</t>
+          <t>2026-10-06T23:56:58Z</t>
         </is>
       </c>
     </row>
@@ -2022,7 +2022,7 @@
       </c>
       <c r="K35" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:20Z</t>
+          <t>2026-10-06T23:56:58Z</t>
         </is>
       </c>
     </row>
@@ -2071,7 +2071,7 @@
       </c>
       <c r="K36" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:20Z</t>
+          <t>2026-10-06T23:56:58Z</t>
         </is>
       </c>
     </row>
@@ -2120,7 +2120,7 @@
       </c>
       <c r="K37" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:20Z</t>
+          <t>2026-10-06T23:56:58Z</t>
         </is>
       </c>
     </row>
@@ -2169,7 +2169,7 @@
       </c>
       <c r="K38" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:20Z</t>
+          <t>2026-10-06T23:56:58Z</t>
         </is>
       </c>
     </row>
@@ -2218,7 +2218,7 @@
       </c>
       <c r="K39" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:20Z</t>
+          <t>2026-10-06T23:56:58Z</t>
         </is>
       </c>
     </row>
@@ -2267,7 +2267,7 @@
       </c>
       <c r="K40" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:20Z</t>
+          <t>2026-10-06T23:56:58Z</t>
         </is>
       </c>
     </row>
@@ -2316,7 +2316,7 @@
       </c>
       <c r="K41" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:20Z</t>
+          <t>2026-10-06T23:56:58Z</t>
         </is>
       </c>
     </row>
@@ -2365,7 +2365,7 @@
       </c>
       <c r="K42" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:20Z</t>
+          <t>2026-10-06T23:56:58Z</t>
         </is>
       </c>
     </row>
@@ -2414,7 +2414,7 @@
       </c>
       <c r="K43" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:20Z</t>
+          <t>2026-10-06T23:56:58Z</t>
         </is>
       </c>
     </row>
@@ -2463,7 +2463,7 @@
       </c>
       <c r="K44" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:20Z</t>
+          <t>2026-10-06T23:56:58Z</t>
         </is>
       </c>
     </row>
@@ -2512,7 +2512,7 @@
       </c>
       <c r="K45" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:20Z</t>
+          <t>2026-10-06T23:56:58Z</t>
         </is>
       </c>
     </row>
@@ -2561,7 +2561,7 @@
       </c>
       <c r="K46" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:20Z</t>
+          <t>2026-10-06T23:56:58Z</t>
         </is>
       </c>
     </row>
@@ -2610,7 +2610,7 @@
       </c>
       <c r="K47" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:20Z</t>
+          <t>2026-10-06T23:56:58Z</t>
         </is>
       </c>
     </row>
@@ -2659,7 +2659,7 @@
       </c>
       <c r="K48" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:20Z</t>
+          <t>2026-10-06T23:56:58Z</t>
         </is>
       </c>
     </row>
@@ -2708,7 +2708,7 @@
       </c>
       <c r="K49" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:20Z</t>
+          <t>2026-10-06T23:56:58Z</t>
         </is>
       </c>
     </row>
@@ -2757,7 +2757,7 @@
       </c>
       <c r="K50" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:20Z</t>
+          <t>2026-10-06T23:56:58Z</t>
         </is>
       </c>
     </row>
@@ -2806,7 +2806,7 @@
       </c>
       <c r="K51" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:20Z</t>
+          <t>2026-10-06T23:56:58Z</t>
         </is>
       </c>
     </row>
@@ -2855,7 +2855,7 @@
       </c>
       <c r="K52" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:20Z</t>
+          <t>2026-10-06T23:56:58Z</t>
         </is>
       </c>
     </row>
@@ -2904,7 +2904,7 @@
       </c>
       <c r="K53" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:20Z</t>
+          <t>2026-10-06T23:56:58Z</t>
         </is>
       </c>
     </row>
@@ -2953,7 +2953,7 @@
       </c>
       <c r="K54" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:20Z</t>
+          <t>2026-10-06T23:56:58Z</t>
         </is>
       </c>
     </row>
@@ -3002,7 +3002,7 @@
       </c>
       <c r="K55" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:20Z</t>
+          <t>2026-10-06T23:56:58Z</t>
         </is>
       </c>
     </row>
@@ -3051,7 +3051,7 @@
       </c>
       <c r="K56" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:20Z</t>
+          <t>2026-10-06T23:56:58Z</t>
         </is>
       </c>
     </row>
@@ -3100,7 +3100,7 @@
       </c>
       <c r="K57" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:20Z</t>
+          <t>2026-10-06T23:56:58Z</t>
         </is>
       </c>
     </row>
@@ -3149,7 +3149,7 @@
       </c>
       <c r="K58" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:20Z</t>
+          <t>2026-10-06T23:56:58Z</t>
         </is>
       </c>
     </row>
@@ -3198,7 +3198,7 @@
       </c>
       <c r="K59" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:20Z</t>
+          <t>2026-10-06T23:56:58Z</t>
         </is>
       </c>
     </row>
@@ -3247,7 +3247,7 @@
       </c>
       <c r="K60" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:20Z</t>
+          <t>2026-10-06T23:56:58Z</t>
         </is>
       </c>
     </row>
@@ -3296,7 +3296,7 @@
       </c>
       <c r="K61" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:20Z</t>
+          <t>2026-10-06T23:56:58Z</t>
         </is>
       </c>
     </row>
@@ -3345,7 +3345,7 @@
       </c>
       <c r="K62" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:20Z</t>
+          <t>2026-10-06T23:56:58Z</t>
         </is>
       </c>
     </row>
@@ -3394,7 +3394,7 @@
       </c>
       <c r="K63" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:20Z</t>
+          <t>2026-10-06T23:56:58Z</t>
         </is>
       </c>
     </row>
@@ -3443,7 +3443,7 @@
       </c>
       <c r="K64" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:20Z</t>
+          <t>2026-10-06T23:56:58Z</t>
         </is>
       </c>
     </row>
@@ -3492,7 +3492,7 @@
       </c>
       <c r="K65" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:20Z</t>
+          <t>2026-10-06T23:56:58Z</t>
         </is>
       </c>
     </row>
@@ -3541,7 +3541,7 @@
       </c>
       <c r="K66" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:20Z</t>
+          <t>2026-10-06T23:56:58Z</t>
         </is>
       </c>
     </row>
@@ -3590,7 +3590,7 @@
       </c>
       <c r="K67" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:20Z</t>
+          <t>2026-10-06T23:56:58Z</t>
         </is>
       </c>
     </row>
@@ -3639,7 +3639,7 @@
       </c>
       <c r="K68" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:20Z</t>
+          <t>2026-10-06T23:56:58Z</t>
         </is>
       </c>
     </row>
@@ -3688,7 +3688,7 @@
       </c>
       <c r="K69" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:20Z</t>
+          <t>2026-10-06T23:56:58Z</t>
         </is>
       </c>
     </row>
@@ -3737,7 +3737,7 @@
       </c>
       <c r="K70" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:20Z</t>
+          <t>2026-10-06T23:56:58Z</t>
         </is>
       </c>
     </row>
@@ -3786,7 +3786,7 @@
       </c>
       <c r="K71" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:20Z</t>
+          <t>2026-10-06T23:56:58Z</t>
         </is>
       </c>
     </row>
@@ -3835,7 +3835,7 @@
       </c>
       <c r="K72" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:20Z</t>
+          <t>2026-10-06T23:56:58Z</t>
         </is>
       </c>
     </row>
@@ -3884,7 +3884,7 @@
       </c>
       <c r="K73" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:20Z</t>
+          <t>2026-10-06T23:56:58Z</t>
         </is>
       </c>
     </row>
@@ -3933,7 +3933,7 @@
       </c>
       <c r="K74" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:20Z</t>
+          <t>2026-10-06T23:56:58Z</t>
         </is>
       </c>
     </row>
@@ -3982,7 +3982,7 @@
       </c>
       <c r="K75" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:20Z</t>
+          <t>2026-10-06T23:56:58Z</t>
         </is>
       </c>
     </row>
@@ -4031,7 +4031,7 @@
       </c>
       <c r="K76" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:20Z</t>
+          <t>2026-10-06T23:56:58Z</t>
         </is>
       </c>
     </row>
@@ -4080,7 +4080,7 @@
       </c>
       <c r="K77" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:20Z</t>
+          <t>2026-10-06T23:56:58Z</t>
         </is>
       </c>
     </row>
@@ -4129,7 +4129,7 @@
       </c>
       <c r="K78" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:20Z</t>
+          <t>2026-10-06T23:56:58Z</t>
         </is>
       </c>
     </row>
@@ -4178,7 +4178,7 @@
       </c>
       <c r="K79" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:20Z</t>
+          <t>2026-10-06T23:56:58Z</t>
         </is>
       </c>
     </row>
@@ -4227,7 +4227,7 @@
       </c>
       <c r="K80" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:20Z</t>
+          <t>2026-10-06T23:56:58Z</t>
         </is>
       </c>
     </row>
@@ -4276,7 +4276,7 @@
       </c>
       <c r="K81" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:20Z</t>
+          <t>2026-10-06T23:56:58Z</t>
         </is>
       </c>
     </row>
@@ -4325,7 +4325,7 @@
       </c>
       <c r="K82" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:20Z</t>
+          <t>2026-10-06T23:56:58Z</t>
         </is>
       </c>
     </row>
@@ -4374,7 +4374,7 @@
       </c>
       <c r="K83" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:20Z</t>
+          <t>2026-10-06T23:56:58Z</t>
         </is>
       </c>
     </row>
@@ -4423,7 +4423,7 @@
       </c>
       <c r="K84" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:20Z</t>
+          <t>2026-10-06T23:56:58Z</t>
         </is>
       </c>
     </row>
@@ -4472,7 +4472,7 @@
       </c>
       <c r="K85" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:20Z</t>
+          <t>2026-10-06T23:56:58Z</t>
         </is>
       </c>
     </row>
@@ -4521,7 +4521,7 @@
       </c>
       <c r="K86" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:20Z</t>
+          <t>2026-10-06T23:56:58Z</t>
         </is>
       </c>
     </row>
@@ -4570,7 +4570,7 @@
       </c>
       <c r="K87" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:20Z</t>
+          <t>2026-10-06T23:56:58Z</t>
         </is>
       </c>
     </row>
@@ -4619,7 +4619,7 @@
       </c>
       <c r="K88" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:20Z</t>
+          <t>2026-10-06T23:56:58Z</t>
         </is>
       </c>
     </row>
@@ -4668,7 +4668,7 @@
       </c>
       <c r="K89" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:20Z</t>
+          <t>2026-10-06T23:56:58Z</t>
         </is>
       </c>
     </row>
@@ -4717,7 +4717,7 @@
       </c>
       <c r="K90" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:20Z</t>
+          <t>2026-10-06T23:56:58Z</t>
         </is>
       </c>
     </row>
@@ -4766,7 +4766,7 @@
       </c>
       <c r="K91" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:20Z</t>
+          <t>2026-10-06T23:56:58Z</t>
         </is>
       </c>
     </row>
@@ -4815,7 +4815,7 @@
       </c>
       <c r="K92" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:20Z</t>
+          <t>2026-10-06T23:56:58Z</t>
         </is>
       </c>
     </row>
@@ -4864,7 +4864,7 @@
       </c>
       <c r="K93" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:20Z</t>
+          <t>2026-10-06T23:56:58Z</t>
         </is>
       </c>
     </row>
@@ -4913,7 +4913,7 @@
       </c>
       <c r="K94" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:20Z</t>
+          <t>2026-10-06T23:56:58Z</t>
         </is>
       </c>
     </row>
@@ -4962,7 +4962,7 @@
       </c>
       <c r="K95" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:20Z</t>
+          <t>2026-10-06T23:56:58Z</t>
         </is>
       </c>
     </row>
@@ -5011,7 +5011,7 @@
       </c>
       <c r="K96" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:20Z</t>
+          <t>2026-10-06T23:56:58Z</t>
         </is>
       </c>
     </row>
@@ -5060,7 +5060,7 @@
       </c>
       <c r="K97" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:20Z</t>
+          <t>2026-10-06T23:56:58Z</t>
         </is>
       </c>
     </row>
@@ -5109,7 +5109,7 @@
       </c>
       <c r="K98" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:20Z</t>
+          <t>2026-10-06T23:56:58Z</t>
         </is>
       </c>
     </row>
@@ -5158,7 +5158,7 @@
       </c>
       <c r="K99" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:20Z</t>
+          <t>2026-10-06T23:56:58Z</t>
         </is>
       </c>
     </row>
@@ -5207,7 +5207,7 @@
       </c>
       <c r="K100" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:20Z</t>
+          <t>2026-10-06T23:56:58Z</t>
         </is>
       </c>
     </row>
@@ -5256,7 +5256,7 @@
       </c>
       <c r="K101" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:20Z</t>
+          <t>2026-10-06T23:56:58Z</t>
         </is>
       </c>
     </row>
@@ -5305,7 +5305,7 @@
       </c>
       <c r="K102" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:20Z</t>
+          <t>2026-10-06T23:56:58Z</t>
         </is>
       </c>
     </row>
@@ -5354,7 +5354,7 @@
       </c>
       <c r="K103" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:20Z</t>
+          <t>2026-10-06T23:56:58Z</t>
         </is>
       </c>
     </row>
@@ -5403,7 +5403,7 @@
       </c>
       <c r="K104" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:20Z</t>
+          <t>2026-10-06T23:56:58Z</t>
         </is>
       </c>
     </row>
@@ -5452,7 +5452,7 @@
       </c>
       <c r="K105" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:20Z</t>
+          <t>2026-10-06T23:56:58Z</t>
         </is>
       </c>
     </row>
@@ -5501,7 +5501,7 @@
       </c>
       <c r="K106" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:20Z</t>
+          <t>2026-10-06T23:56:58Z</t>
         </is>
       </c>
     </row>
@@ -5550,7 +5550,7 @@
       </c>
       <c r="K107" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:20Z</t>
+          <t>2026-10-06T23:56:58Z</t>
         </is>
       </c>
     </row>
@@ -5599,7 +5599,7 @@
       </c>
       <c r="K108" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:20Z</t>
+          <t>2026-10-06T23:56:58Z</t>
         </is>
       </c>
     </row>
@@ -5648,7 +5648,7 @@
       </c>
       <c r="K109" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:20Z</t>
+          <t>2026-10-06T23:56:58Z</t>
         </is>
       </c>
     </row>
@@ -5697,7 +5697,7 @@
       </c>
       <c r="K110" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:20Z</t>
+          <t>2026-10-06T23:56:58Z</t>
         </is>
       </c>
     </row>
@@ -5746,7 +5746,7 @@
       </c>
       <c r="K111" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:20Z</t>
+          <t>2026-10-06T23:56:58Z</t>
         </is>
       </c>
     </row>
@@ -5795,7 +5795,7 @@
       </c>
       <c r="K112" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:20Z</t>
+          <t>2026-10-06T23:56:58Z</t>
         </is>
       </c>
     </row>
@@ -5844,7 +5844,7 @@
       </c>
       <c r="K113" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:20Z</t>
+          <t>2026-10-06T23:56:58Z</t>
         </is>
       </c>
     </row>
@@ -5893,7 +5893,7 @@
       </c>
       <c r="K114" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:20Z</t>
+          <t>2026-10-06T23:56:58Z</t>
         </is>
       </c>
     </row>
@@ -5942,7 +5942,7 @@
       </c>
       <c r="K115" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:20Z</t>
+          <t>2026-10-06T23:56:58Z</t>
         </is>
       </c>
     </row>
@@ -5991,7 +5991,7 @@
       </c>
       <c r="K116" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:20Z</t>
+          <t>2026-10-06T23:56:58Z</t>
         </is>
       </c>
     </row>
@@ -6040,7 +6040,7 @@
       </c>
       <c r="K117" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:20Z</t>
+          <t>2026-10-06T23:56:58Z</t>
         </is>
       </c>
     </row>
@@ -6089,7 +6089,7 @@
       </c>
       <c r="K118" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:20Z</t>
+          <t>2026-10-06T23:56:58Z</t>
         </is>
       </c>
     </row>
@@ -6138,7 +6138,7 @@
       </c>
       <c r="K119" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:20Z</t>
+          <t>2026-10-06T23:56:58Z</t>
         </is>
       </c>
     </row>
@@ -6187,7 +6187,7 @@
       </c>
       <c r="K120" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:20Z</t>
+          <t>2026-10-06T23:56:58Z</t>
         </is>
       </c>
     </row>
@@ -6236,7 +6236,7 @@
       </c>
       <c r="K121" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:20Z</t>
+          <t>2026-10-06T23:56:58Z</t>
         </is>
       </c>
     </row>
@@ -6285,7 +6285,7 @@
       </c>
       <c r="K122" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:20Z</t>
+          <t>2026-10-06T23:56:58Z</t>
         </is>
       </c>
     </row>
@@ -6334,7 +6334,7 @@
       </c>
       <c r="K123" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:20Z</t>
+          <t>2026-10-06T23:56:58Z</t>
         </is>
       </c>
     </row>
@@ -6383,7 +6383,7 @@
       </c>
       <c r="K124" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:20Z</t>
+          <t>2026-10-06T23:56:58Z</t>
         </is>
       </c>
     </row>
@@ -6432,7 +6432,7 @@
       </c>
       <c r="K125" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:20Z</t>
+          <t>2026-10-06T23:56:58Z</t>
         </is>
       </c>
     </row>
@@ -6481,7 +6481,7 @@
       </c>
       <c r="K126" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:20Z</t>
+          <t>2026-10-06T23:56:58Z</t>
         </is>
       </c>
     </row>
@@ -6530,7 +6530,7 @@
       </c>
       <c r="K127" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:20Z</t>
+          <t>2026-10-06T23:56:58Z</t>
         </is>
       </c>
     </row>
@@ -6579,7 +6579,7 @@
       </c>
       <c r="K128" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:20Z</t>
+          <t>2026-10-06T23:56:58Z</t>
         </is>
       </c>
     </row>
@@ -6628,7 +6628,7 @@
       </c>
       <c r="K129" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:20Z</t>
+          <t>2026-10-06T23:56:58Z</t>
         </is>
       </c>
     </row>
@@ -6677,7 +6677,7 @@
       </c>
       <c r="K130" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:20Z</t>
+          <t>2026-10-06T23:56:58Z</t>
         </is>
       </c>
     </row>
@@ -6726,7 +6726,7 @@
       </c>
       <c r="K131" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:20Z</t>
+          <t>2026-10-06T23:56:58Z</t>
         </is>
       </c>
     </row>
@@ -6775,7 +6775,7 @@
       </c>
       <c r="K132" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:20Z</t>
+          <t>2026-10-06T23:56:58Z</t>
         </is>
       </c>
     </row>
@@ -6824,7 +6824,7 @@
       </c>
       <c r="K133" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:20Z</t>
+          <t>2026-10-06T23:56:58Z</t>
         </is>
       </c>
     </row>
@@ -6873,7 +6873,7 @@
       </c>
       <c r="K134" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:20Z</t>
+          <t>2026-10-06T23:56:58Z</t>
         </is>
       </c>
     </row>
@@ -6922,7 +6922,7 @@
       </c>
       <c r="K135" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:20Z</t>
+          <t>2026-10-06T23:56:58Z</t>
         </is>
       </c>
     </row>
@@ -6971,7 +6971,7 @@
       </c>
       <c r="K136" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:20Z</t>
+          <t>2026-10-06T23:56:58Z</t>
         </is>
       </c>
     </row>
@@ -7020,7 +7020,7 @@
       </c>
       <c r="K137" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:20Z</t>
+          <t>2026-10-06T23:56:58Z</t>
         </is>
       </c>
     </row>
@@ -7069,7 +7069,7 @@
       </c>
       <c r="K138" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:20Z</t>
+          <t>2026-10-06T23:56:58Z</t>
         </is>
       </c>
     </row>
@@ -7118,7 +7118,7 @@
       </c>
       <c r="K139" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:20Z</t>
+          <t>2026-10-06T23:56:58Z</t>
         </is>
       </c>
     </row>
@@ -7167,7 +7167,7 @@
       </c>
       <c r="K140" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:20Z</t>
+          <t>2026-10-06T23:56:58Z</t>
         </is>
       </c>
     </row>
@@ -7216,7 +7216,7 @@
       </c>
       <c r="K141" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:20Z</t>
+          <t>2026-10-06T23:56:58Z</t>
         </is>
       </c>
     </row>
@@ -7265,7 +7265,7 @@
       </c>
       <c r="K142" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:20Z</t>
+          <t>2026-10-06T23:56:58Z</t>
         </is>
       </c>
     </row>
@@ -7314,7 +7314,7 @@
       </c>
       <c r="K143" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:20Z</t>
+          <t>2026-10-06T23:56:58Z</t>
         </is>
       </c>
     </row>
@@ -7363,7 +7363,7 @@
       </c>
       <c r="K144" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:20Z</t>
+          <t>2026-10-06T23:56:58Z</t>
         </is>
       </c>
     </row>
@@ -7412,7 +7412,7 @@
       </c>
       <c r="K145" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:20Z</t>
+          <t>2026-10-06T23:56:58Z</t>
         </is>
       </c>
     </row>
@@ -7461,7 +7461,7 @@
       </c>
       <c r="K146" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:20Z</t>
+          <t>2026-10-06T23:56:58Z</t>
         </is>
       </c>
     </row>
@@ -7510,7 +7510,7 @@
       </c>
       <c r="K147" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:20Z</t>
+          <t>2026-10-06T23:56:58Z</t>
         </is>
       </c>
     </row>
@@ -7559,7 +7559,7 @@
       </c>
       <c r="K148" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:20Z</t>
+          <t>2026-10-06T23:56:58Z</t>
         </is>
       </c>
     </row>
@@ -7608,7 +7608,7 @@
       </c>
       <c r="K149" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:20Z</t>
+          <t>2026-10-06T23:56:58Z</t>
         </is>
       </c>
     </row>
@@ -7657,7 +7657,7 @@
       </c>
       <c r="K150" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:20Z</t>
+          <t>2026-10-06T23:56:58Z</t>
         </is>
       </c>
     </row>
@@ -7706,7 +7706,7 @@
       </c>
       <c r="K151" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:20Z</t>
+          <t>2026-10-06T23:56:58Z</t>
         </is>
       </c>
     </row>
@@ -7755,7 +7755,7 @@
       </c>
       <c r="K152" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:20Z</t>
+          <t>2026-10-06T23:56:58Z</t>
         </is>
       </c>
     </row>
@@ -7804,7 +7804,7 @@
       </c>
       <c r="K153" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:20Z</t>
+          <t>2026-10-06T23:56:58Z</t>
         </is>
       </c>
     </row>
@@ -7853,7 +7853,7 @@
       </c>
       <c r="K154" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:20Z</t>
+          <t>2026-10-06T23:56:58Z</t>
         </is>
       </c>
     </row>
@@ -7902,7 +7902,7 @@
       </c>
       <c r="K155" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:20Z</t>
+          <t>2026-10-06T23:56:58Z</t>
         </is>
       </c>
     </row>
@@ -7951,7 +7951,7 @@
       </c>
       <c r="K156" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:20Z</t>
+          <t>2026-10-06T23:56:58Z</t>
         </is>
       </c>
     </row>
@@ -8000,7 +8000,7 @@
       </c>
       <c r="K157" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:20Z</t>
+          <t>2026-10-06T23:56:58Z</t>
         </is>
       </c>
     </row>
@@ -8049,7 +8049,7 @@
       </c>
       <c r="K158" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:20Z</t>
+          <t>2026-10-06T23:56:58Z</t>
         </is>
       </c>
     </row>
@@ -8098,7 +8098,7 @@
       </c>
       <c r="K159" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:20Z</t>
+          <t>2026-10-06T23:56:58Z</t>
         </is>
       </c>
     </row>
@@ -8147,7 +8147,7 @@
       </c>
       <c r="K160" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:20Z</t>
+          <t>2026-10-06T23:56:58Z</t>
         </is>
       </c>
     </row>
@@ -8196,7 +8196,7 @@
       </c>
       <c r="K161" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:20Z</t>
+          <t>2026-10-06T23:56:58Z</t>
         </is>
       </c>
     </row>
@@ -8245,7 +8245,7 @@
       </c>
       <c r="K162" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:20Z</t>
+          <t>2026-10-06T23:56:58Z</t>
         </is>
       </c>
     </row>
@@ -8294,7 +8294,7 @@
       </c>
       <c r="K163" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:20Z</t>
+          <t>2026-10-06T23:56:58Z</t>
         </is>
       </c>
     </row>
@@ -8343,7 +8343,7 @@
       </c>
       <c r="K164" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:20Z</t>
+          <t>2026-10-06T23:56:58Z</t>
         </is>
       </c>
     </row>
@@ -8392,7 +8392,7 @@
       </c>
       <c r="K165" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:20Z</t>
+          <t>2026-10-06T23:56:58Z</t>
         </is>
       </c>
     </row>
@@ -8441,7 +8441,7 @@
       </c>
       <c r="K166" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:20Z</t>
+          <t>2026-10-06T23:56:58Z</t>
         </is>
       </c>
     </row>
@@ -8490,7 +8490,7 @@
       </c>
       <c r="K167" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:20Z</t>
+          <t>2026-10-06T23:56:58Z</t>
         </is>
       </c>
     </row>
@@ -8539,7 +8539,7 @@
       </c>
       <c r="K168" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:20Z</t>
+          <t>2026-10-06T23:56:58Z</t>
         </is>
       </c>
     </row>
@@ -8588,7 +8588,7 @@
       </c>
       <c r="K169" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:20Z</t>
+          <t>2026-10-06T23:56:58Z</t>
         </is>
       </c>
     </row>
@@ -8637,7 +8637,7 @@
       </c>
       <c r="K170" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:20Z</t>
+          <t>2026-10-06T23:56:58Z</t>
         </is>
       </c>
     </row>
@@ -8686,7 +8686,7 @@
       </c>
       <c r="K171" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:20Z</t>
+          <t>2026-10-06T23:56:58Z</t>
         </is>
       </c>
     </row>
@@ -8735,7 +8735,7 @@
       </c>
       <c r="K172" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:20Z</t>
+          <t>2026-10-06T23:56:58Z</t>
         </is>
       </c>
     </row>
@@ -8784,7 +8784,7 @@
       </c>
       <c r="K173" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:20Z</t>
+          <t>2026-10-06T23:56:58Z</t>
         </is>
       </c>
     </row>
@@ -8833,7 +8833,7 @@
       </c>
       <c r="K174" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:20Z</t>
+          <t>2026-10-06T23:56:58Z</t>
         </is>
       </c>
     </row>
@@ -8882,7 +8882,7 @@
       </c>
       <c r="K175" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:20Z</t>
+          <t>2026-10-06T23:56:58Z</t>
         </is>
       </c>
     </row>
@@ -8931,7 +8931,7 @@
       </c>
       <c r="K176" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:20Z</t>
+          <t>2026-10-06T23:56:58Z</t>
         </is>
       </c>
     </row>
@@ -8980,7 +8980,7 @@
       </c>
       <c r="K177" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:20Z</t>
+          <t>2026-10-06T23:56:58Z</t>
         </is>
       </c>
     </row>
@@ -9029,7 +9029,7 @@
       </c>
       <c r="K178" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:20Z</t>
+          <t>2026-10-06T23:56:58Z</t>
         </is>
       </c>
     </row>
@@ -9078,7 +9078,7 @@
       </c>
       <c r="K179" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:20Z</t>
+          <t>2026-10-06T23:56:58Z</t>
         </is>
       </c>
     </row>
@@ -9127,7 +9127,7 @@
       </c>
       <c r="K180" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:20Z</t>
+          <t>2026-10-06T23:56:58Z</t>
         </is>
       </c>
     </row>
@@ -9176,7 +9176,7 @@
       </c>
       <c r="K181" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:20Z</t>
+          <t>2026-10-06T23:56:58Z</t>
         </is>
       </c>
     </row>
@@ -9225,7 +9225,7 @@
       </c>
       <c r="K182" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:20Z</t>
+          <t>2026-10-06T23:56:58Z</t>
         </is>
       </c>
     </row>
@@ -9274,7 +9274,7 @@
       </c>
       <c r="K183" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:20Z</t>
+          <t>2026-10-06T23:56:58Z</t>
         </is>
       </c>
     </row>
@@ -9323,7 +9323,7 @@
       </c>
       <c r="K184" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:20Z</t>
+          <t>2026-10-06T23:56:58Z</t>
         </is>
       </c>
     </row>
@@ -9372,7 +9372,7 @@
       </c>
       <c r="K185" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:20Z</t>
+          <t>2026-10-06T23:56:58Z</t>
         </is>
       </c>
     </row>
@@ -9421,7 +9421,7 @@
       </c>
       <c r="K186" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:20Z</t>
+          <t>2026-10-06T23:56:58Z</t>
         </is>
       </c>
     </row>
@@ -9470,7 +9470,7 @@
       </c>
       <c r="K187" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:20Z</t>
+          <t>2026-10-06T23:56:58Z</t>
         </is>
       </c>
     </row>
@@ -9519,7 +9519,7 @@
       </c>
       <c r="K188" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:20Z</t>
+          <t>2026-10-06T23:56:58Z</t>
         </is>
       </c>
     </row>
@@ -9568,7 +9568,7 @@
       </c>
       <c r="K189" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:20Z</t>
+          <t>2026-10-06T23:56:58Z</t>
         </is>
       </c>
     </row>
@@ -9617,7 +9617,7 @@
       </c>
       <c r="K190" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:20Z</t>
+          <t>2026-10-06T23:56:58Z</t>
         </is>
       </c>
     </row>
@@ -9666,7 +9666,7 @@
       </c>
       <c r="K191" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:20Z</t>
+          <t>2026-10-06T23:56:58Z</t>
         </is>
       </c>
     </row>
@@ -9715,7 +9715,7 @@
       </c>
       <c r="K192" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:20Z</t>
+          <t>2026-10-06T23:56:58Z</t>
         </is>
       </c>
     </row>
@@ -9764,7 +9764,7 @@
       </c>
       <c r="K193" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:20Z</t>
+          <t>2026-10-06T23:56:58Z</t>
         </is>
       </c>
     </row>
@@ -9813,7 +9813,7 @@
       </c>
       <c r="K194" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:20Z</t>
+          <t>2026-10-06T23:56:58Z</t>
         </is>
       </c>
     </row>
@@ -9862,7 +9862,7 @@
       </c>
       <c r="K195" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:20Z</t>
+          <t>2026-10-06T23:56:58Z</t>
         </is>
       </c>
     </row>
@@ -9911,7 +9911,7 @@
       </c>
       <c r="K196" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:20Z</t>
+          <t>2026-10-06T23:56:58Z</t>
         </is>
       </c>
     </row>
@@ -9960,7 +9960,7 @@
       </c>
       <c r="K197" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:20Z</t>
+          <t>2026-10-06T23:56:58Z</t>
         </is>
       </c>
     </row>
@@ -10009,7 +10009,7 @@
       </c>
       <c r="K198" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:20Z</t>
+          <t>2026-10-06T23:56:58Z</t>
         </is>
       </c>
     </row>
@@ -10058,7 +10058,7 @@
       </c>
       <c r="K199" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:20Z</t>
+          <t>2026-10-06T23:56:58Z</t>
         </is>
       </c>
     </row>
@@ -10107,7 +10107,7 @@
       </c>
       <c r="K200" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:20Z</t>
+          <t>2026-10-06T23:56:58Z</t>
         </is>
       </c>
     </row>
@@ -10156,7 +10156,7 @@
       </c>
       <c r="K201" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:20Z</t>
+          <t>2026-10-06T23:56:58Z</t>
         </is>
       </c>
     </row>
@@ -10205,7 +10205,7 @@
       </c>
       <c r="K202" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:20Z</t>
+          <t>2026-10-06T23:56:58Z</t>
         </is>
       </c>
     </row>
@@ -10254,7 +10254,7 @@
       </c>
       <c r="K203" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:20Z</t>
+          <t>2026-10-06T23:56:58Z</t>
         </is>
       </c>
     </row>
@@ -10303,7 +10303,7 @@
       </c>
       <c r="K204" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:20Z</t>
+          <t>2026-10-06T23:56:58Z</t>
         </is>
       </c>
     </row>
@@ -10352,7 +10352,7 @@
       </c>
       <c r="K205" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:20Z</t>
+          <t>2026-10-06T23:56:58Z</t>
         </is>
       </c>
     </row>
@@ -10401,7 +10401,7 @@
       </c>
       <c r="K206" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:20Z</t>
+          <t>2026-10-06T23:56:58Z</t>
         </is>
       </c>
     </row>
@@ -10450,7 +10450,7 @@
       </c>
       <c r="K207" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:20Z</t>
+          <t>2026-10-06T23:56:58Z</t>
         </is>
       </c>
     </row>
@@ -10499,7 +10499,7 @@
       </c>
       <c r="K208" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:20Z</t>
+          <t>2026-10-06T23:56:58Z</t>
         </is>
       </c>
     </row>
@@ -10548,7 +10548,7 @@
       </c>
       <c r="K209" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:20Z</t>
+          <t>2026-10-06T23:56:58Z</t>
         </is>
       </c>
     </row>
@@ -10597,7 +10597,7 @@
       </c>
       <c r="K210" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:20Z</t>
+          <t>2026-10-06T23:56:58Z</t>
         </is>
       </c>
     </row>
@@ -10646,7 +10646,7 @@
       </c>
       <c r="K211" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:20Z</t>
+          <t>2026-10-06T23:56:58Z</t>
         </is>
       </c>
     </row>
@@ -10695,7 +10695,7 @@
       </c>
       <c r="K212" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:20Z</t>
+          <t>2026-10-06T23:56:58Z</t>
         </is>
       </c>
     </row>
@@ -10744,7 +10744,7 @@
       </c>
       <c r="K213" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:20Z</t>
+          <t>2026-10-06T23:56:58Z</t>
         </is>
       </c>
     </row>
@@ -10793,7 +10793,7 @@
       </c>
       <c r="K214" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:20Z</t>
+          <t>2026-10-06T23:56:58Z</t>
         </is>
       </c>
     </row>
@@ -10842,7 +10842,7 @@
       </c>
       <c r="K215" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:20Z</t>
+          <t>2026-10-06T23:56:58Z</t>
         </is>
       </c>
     </row>
@@ -10891,7 +10891,7 @@
       </c>
       <c r="K216" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:20Z</t>
+          <t>2026-10-06T23:56:58Z</t>
         </is>
       </c>
     </row>
@@ -10940,7 +10940,7 @@
       </c>
       <c r="K217" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:20Z</t>
+          <t>2026-10-06T23:56:58Z</t>
         </is>
       </c>
     </row>
@@ -10989,7 +10989,7 @@
       </c>
       <c r="K218" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:20Z</t>
+          <t>2026-10-06T23:56:58Z</t>
         </is>
       </c>
     </row>
@@ -11038,7 +11038,7 @@
       </c>
       <c r="K219" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:20Z</t>
+          <t>2026-10-06T23:56:58Z</t>
         </is>
       </c>
     </row>
@@ -11087,7 +11087,7 @@
       </c>
       <c r="K220" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:20Z</t>
+          <t>2026-10-06T23:56:58Z</t>
         </is>
       </c>
     </row>
@@ -11136,7 +11136,7 @@
       </c>
       <c r="K221" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:20Z</t>
+          <t>2026-10-06T23:56:58Z</t>
         </is>
       </c>
     </row>
@@ -11185,7 +11185,7 @@
       </c>
       <c r="K222" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:20Z</t>
+          <t>2026-10-06T23:56:58Z</t>
         </is>
       </c>
     </row>
@@ -11234,7 +11234,7 @@
       </c>
       <c r="K223" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:20Z</t>
+          <t>2026-10-06T23:56:58Z</t>
         </is>
       </c>
     </row>
@@ -11283,7 +11283,7 @@
       </c>
       <c r="K224" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:20Z</t>
+          <t>2026-10-06T23:56:58Z</t>
         </is>
       </c>
     </row>
@@ -11332,7 +11332,7 @@
       </c>
       <c r="K225" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:20Z</t>
+          <t>2026-10-06T23:56:58Z</t>
         </is>
       </c>
     </row>
@@ -11381,7 +11381,7 @@
       </c>
       <c r="K226" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:20Z</t>
+          <t>2026-10-06T23:56:58Z</t>
         </is>
       </c>
     </row>
@@ -11430,7 +11430,7 @@
       </c>
       <c r="K227" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:20Z</t>
+          <t>2026-10-06T23:56:58Z</t>
         </is>
       </c>
     </row>
@@ -11479,7 +11479,7 @@
       </c>
       <c r="K228" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:20Z</t>
+          <t>2026-10-06T23:56:58Z</t>
         </is>
       </c>
     </row>
@@ -11528,7 +11528,7 @@
       </c>
       <c r="K229" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:20Z</t>
+          <t>2026-10-06T23:56:58Z</t>
         </is>
       </c>
     </row>
@@ -11577,7 +11577,7 @@
       </c>
       <c r="K230" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:20Z</t>
+          <t>2026-10-06T23:56:58Z</t>
         </is>
       </c>
     </row>
@@ -11626,7 +11626,7 @@
       </c>
       <c r="K231" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:20Z</t>
+          <t>2026-10-06T23:56:58Z</t>
         </is>
       </c>
     </row>
@@ -11758,7 +11758,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:20Z</t>
+          <t>2026-10-06T23:56:58Z</t>
         </is>
       </c>
     </row>
@@ -11804,7 +11804,7 @@
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>{"date": "2026-08-01", "year": 2026, "month": 8, "month_name": "Agosto", "index_value": 637409769724325.1, "monthly_variation_pct": 8.9, "unit": "Índice base diciembre 2007=100 y variación mensual %", "frequency": "monthly", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/precios_consumidor/4_5_7_2.xls", "fetched_at": "2026-10-06T01:22:20Z"}</t>
+          <t>{"date": "2026-08-01", "year": 2026, "month": 8, "month_name": "Agosto", "index_value": 637409769724325.1, "monthly_variation_pct": 8.9, "unit": "Índice base diciembre 2007=100 y variación mensual %", "frequency": "monthly", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/precios_consumidor/4_5_7_2.xls", "fetched_at": "2026-10-06T23:56:58Z"}</t>
         </is>
       </c>
     </row>

--- a/assets/data/bcv/excel/ove_bcv_inpc_nacional_mensual.xlsx
+++ b/assets/data/bcv/excel/ove_bcv_inpc_nacional_mensual.xlsx
@@ -650,7 +650,7 @@
       </c>
       <c r="K7" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:56:58Z</t>
+          <t>2026-10-07T19:19:47Z</t>
         </is>
       </c>
     </row>
@@ -699,7 +699,7 @@
       </c>
       <c r="K8" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:56:58Z</t>
+          <t>2026-10-07T19:19:47Z</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="K9" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:56:58Z</t>
+          <t>2026-10-07T19:19:47Z</t>
         </is>
       </c>
     </row>
@@ -797,7 +797,7 @@
       </c>
       <c r="K10" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:56:58Z</t>
+          <t>2026-10-07T19:19:47Z</t>
         </is>
       </c>
     </row>
@@ -846,7 +846,7 @@
       </c>
       <c r="K11" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:56:58Z</t>
+          <t>2026-10-07T19:19:47Z</t>
         </is>
       </c>
     </row>
@@ -895,7 +895,7 @@
       </c>
       <c r="K12" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:56:58Z</t>
+          <t>2026-10-07T19:19:47Z</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="K13" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:56:58Z</t>
+          <t>2026-10-07T19:19:47Z</t>
         </is>
       </c>
     </row>
@@ -993,7 +993,7 @@
       </c>
       <c r="K14" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:56:58Z</t>
+          <t>2026-10-07T19:19:47Z</t>
         </is>
       </c>
     </row>
@@ -1042,7 +1042,7 @@
       </c>
       <c r="K15" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:56:58Z</t>
+          <t>2026-10-07T19:19:47Z</t>
         </is>
       </c>
     </row>
@@ -1091,7 +1091,7 @@
       </c>
       <c r="K16" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:56:58Z</t>
+          <t>2026-10-07T19:19:47Z</t>
         </is>
       </c>
     </row>
@@ -1140,7 +1140,7 @@
       </c>
       <c r="K17" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:56:58Z</t>
+          <t>2026-10-07T19:19:47Z</t>
         </is>
       </c>
     </row>
@@ -1189,7 +1189,7 @@
       </c>
       <c r="K18" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:56:58Z</t>
+          <t>2026-10-07T19:19:47Z</t>
         </is>
       </c>
     </row>
@@ -1238,7 +1238,7 @@
       </c>
       <c r="K19" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:56:58Z</t>
+          <t>2026-10-07T19:19:47Z</t>
         </is>
       </c>
     </row>
@@ -1287,7 +1287,7 @@
       </c>
       <c r="K20" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:56:58Z</t>
+          <t>2026-10-07T19:19:47Z</t>
         </is>
       </c>
     </row>
@@ -1336,7 +1336,7 @@
       </c>
       <c r="K21" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:56:58Z</t>
+          <t>2026-10-07T19:19:47Z</t>
         </is>
       </c>
     </row>
@@ -1385,7 +1385,7 @@
       </c>
       <c r="K22" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:56:58Z</t>
+          <t>2026-10-07T19:19:47Z</t>
         </is>
       </c>
     </row>
@@ -1434,7 +1434,7 @@
       </c>
       <c r="K23" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:56:58Z</t>
+          <t>2026-10-07T19:19:47Z</t>
         </is>
       </c>
     </row>
@@ -1483,7 +1483,7 @@
       </c>
       <c r="K24" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:56:58Z</t>
+          <t>2026-10-07T19:19:47Z</t>
         </is>
       </c>
     </row>
@@ -1532,7 +1532,7 @@
       </c>
       <c r="K25" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:56:58Z</t>
+          <t>2026-10-07T19:19:47Z</t>
         </is>
       </c>
     </row>
@@ -1581,7 +1581,7 @@
       </c>
       <c r="K26" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:56:58Z</t>
+          <t>2026-10-07T19:19:47Z</t>
         </is>
       </c>
     </row>
@@ -1630,7 +1630,7 @@
       </c>
       <c r="K27" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:56:58Z</t>
+          <t>2026-10-07T19:19:47Z</t>
         </is>
       </c>
     </row>
@@ -1679,7 +1679,7 @@
       </c>
       <c r="K28" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:56:58Z</t>
+          <t>2026-10-07T19:19:47Z</t>
         </is>
       </c>
     </row>
@@ -1728,7 +1728,7 @@
       </c>
       <c r="K29" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:56:58Z</t>
+          <t>2026-10-07T19:19:47Z</t>
         </is>
       </c>
     </row>
@@ -1777,7 +1777,7 @@
       </c>
       <c r="K30" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:56:58Z</t>
+          <t>2026-10-07T19:19:47Z</t>
         </is>
       </c>
     </row>
@@ -1826,7 +1826,7 @@
       </c>
       <c r="K31" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:56:58Z</t>
+          <t>2026-10-07T19:19:47Z</t>
         </is>
       </c>
     </row>
@@ -1875,7 +1875,7 @@
       </c>
       <c r="K32" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:56:58Z</t>
+          <t>2026-10-07T19:19:47Z</t>
         </is>
       </c>
     </row>
@@ -1924,7 +1924,7 @@
       </c>
       <c r="K33" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:56:58Z</t>
+          <t>2026-10-07T19:19:47Z</t>
         </is>
       </c>
     </row>
@@ -1973,7 +1973,7 @@
       </c>
       <c r="K34" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:56:58Z</t>
+          <t>2026-10-07T19:19:47Z</t>
         </is>
       </c>
     </row>
@@ -2022,7 +2022,7 @@
       </c>
       <c r="K35" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:56:58Z</t>
+          <t>2026-10-07T19:19:47Z</t>
         </is>
       </c>
     </row>
@@ -2071,7 +2071,7 @@
       </c>
       <c r="K36" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:56:58Z</t>
+          <t>2026-10-07T19:19:47Z</t>
         </is>
       </c>
     </row>
@@ -2120,7 +2120,7 @@
       </c>
       <c r="K37" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:56:58Z</t>
+          <t>2026-10-07T19:19:47Z</t>
         </is>
       </c>
     </row>
@@ -2169,7 +2169,7 @@
       </c>
       <c r="K38" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:56:58Z</t>
+          <t>2026-10-07T19:19:47Z</t>
         </is>
       </c>
     </row>
@@ -2218,7 +2218,7 @@
       </c>
       <c r="K39" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:56:58Z</t>
+          <t>2026-10-07T19:19:47Z</t>
         </is>
       </c>
     </row>
@@ -2267,7 +2267,7 @@
       </c>
       <c r="K40" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:56:58Z</t>
+          <t>2026-10-07T19:19:47Z</t>
         </is>
       </c>
     </row>
@@ -2316,7 +2316,7 @@
       </c>
       <c r="K41" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:56:58Z</t>
+          <t>2026-10-07T19:19:47Z</t>
         </is>
       </c>
     </row>
@@ -2365,7 +2365,7 @@
       </c>
       <c r="K42" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:56:58Z</t>
+          <t>2026-10-07T19:19:47Z</t>
         </is>
       </c>
     </row>
@@ -2414,7 +2414,7 @@
       </c>
       <c r="K43" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:56:58Z</t>
+          <t>2026-10-07T19:19:47Z</t>
         </is>
       </c>
     </row>
@@ -2463,7 +2463,7 @@
       </c>
       <c r="K44" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:56:58Z</t>
+          <t>2026-10-07T19:19:47Z</t>
         </is>
       </c>
     </row>
@@ -2512,7 +2512,7 @@
       </c>
       <c r="K45" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:56:58Z</t>
+          <t>2026-10-07T19:19:47Z</t>
         </is>
       </c>
     </row>
@@ -2561,7 +2561,7 @@
       </c>
       <c r="K46" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:56:58Z</t>
+          <t>2026-10-07T19:19:47Z</t>
         </is>
       </c>
     </row>
@@ -2610,7 +2610,7 @@
       </c>
       <c r="K47" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:56:58Z</t>
+          <t>2026-10-07T19:19:47Z</t>
         </is>
       </c>
     </row>
@@ -2659,7 +2659,7 @@
       </c>
       <c r="K48" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:56:58Z</t>
+          <t>2026-10-07T19:19:47Z</t>
         </is>
       </c>
     </row>
@@ -2708,7 +2708,7 @@
       </c>
       <c r="K49" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:56:58Z</t>
+          <t>2026-10-07T19:19:47Z</t>
         </is>
       </c>
     </row>
@@ -2757,7 +2757,7 @@
       </c>
       <c r="K50" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:56:58Z</t>
+          <t>2026-10-07T19:19:47Z</t>
         </is>
       </c>
     </row>
@@ -2806,7 +2806,7 @@
       </c>
       <c r="K51" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:56:58Z</t>
+          <t>2026-10-07T19:19:47Z</t>
         </is>
       </c>
     </row>
@@ -2855,7 +2855,7 @@
       </c>
       <c r="K52" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:56:58Z</t>
+          <t>2026-10-07T19:19:47Z</t>
         </is>
       </c>
     </row>
@@ -2904,7 +2904,7 @@
       </c>
       <c r="K53" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:56:58Z</t>
+          <t>2026-10-07T19:19:47Z</t>
         </is>
       </c>
     </row>
@@ -2953,7 +2953,7 @@
       </c>
       <c r="K54" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:56:58Z</t>
+          <t>2026-10-07T19:19:47Z</t>
         </is>
       </c>
     </row>
@@ -3002,7 +3002,7 @@
       </c>
       <c r="K55" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:56:58Z</t>
+          <t>2026-10-07T19:19:47Z</t>
         </is>
       </c>
     </row>
@@ -3051,7 +3051,7 @@
       </c>
       <c r="K56" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:56:58Z</t>
+          <t>2026-10-07T19:19:47Z</t>
         </is>
       </c>
     </row>
@@ -3100,7 +3100,7 @@
       </c>
       <c r="K57" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:56:58Z</t>
+          <t>2026-10-07T19:19:47Z</t>
         </is>
       </c>
     </row>
@@ -3149,7 +3149,7 @@
       </c>
       <c r="K58" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:56:58Z</t>
+          <t>2026-10-07T19:19:47Z</t>
         </is>
       </c>
     </row>
@@ -3198,7 +3198,7 @@
       </c>
       <c r="K59" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:56:58Z</t>
+          <t>2026-10-07T19:19:47Z</t>
         </is>
       </c>
     </row>
@@ -3247,7 +3247,7 @@
       </c>
       <c r="K60" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:56:58Z</t>
+          <t>2026-10-07T19:19:47Z</t>
         </is>
       </c>
     </row>
@@ -3296,7 +3296,7 @@
       </c>
       <c r="K61" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:56:58Z</t>
+          <t>2026-10-07T19:19:47Z</t>
         </is>
       </c>
     </row>
@@ -3345,7 +3345,7 @@
       </c>
       <c r="K62" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:56:58Z</t>
+          <t>2026-10-07T19:19:47Z</t>
         </is>
       </c>
     </row>
@@ -3394,7 +3394,7 @@
       </c>
       <c r="K63" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:56:58Z</t>
+          <t>2026-10-07T19:19:47Z</t>
         </is>
       </c>
     </row>
@@ -3443,7 +3443,7 @@
       </c>
       <c r="K64" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:56:58Z</t>
+          <t>2026-10-07T19:19:47Z</t>
         </is>
       </c>
     </row>
@@ -3492,7 +3492,7 @@
       </c>
       <c r="K65" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:56:58Z</t>
+          <t>2026-10-07T19:19:47Z</t>
         </is>
       </c>
     </row>
@@ -3541,7 +3541,7 @@
       </c>
       <c r="K66" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:56:58Z</t>
+          <t>2026-10-07T19:19:47Z</t>
         </is>
       </c>
     </row>
@@ -3590,7 +3590,7 @@
       </c>
       <c r="K67" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:56:58Z</t>
+          <t>2026-10-07T19:19:47Z</t>
         </is>
       </c>
     </row>
@@ -3639,7 +3639,7 @@
       </c>
       <c r="K68" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:56:58Z</t>
+          <t>2026-10-07T19:19:47Z</t>
         </is>
       </c>
     </row>
@@ -3688,7 +3688,7 @@
       </c>
       <c r="K69" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:56:58Z</t>
+          <t>2026-10-07T19:19:47Z</t>
         </is>
       </c>
     </row>
@@ -3737,7 +3737,7 @@
       </c>
       <c r="K70" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:56:58Z</t>
+          <t>2026-10-07T19:19:47Z</t>
         </is>
       </c>
     </row>
@@ -3786,7 +3786,7 @@
       </c>
       <c r="K71" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:56:58Z</t>
+          <t>2026-10-07T19:19:47Z</t>
         </is>
       </c>
     </row>
@@ -3835,7 +3835,7 @@
       </c>
       <c r="K72" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:56:58Z</t>
+          <t>2026-10-07T19:19:47Z</t>
         </is>
       </c>
     </row>
@@ -3884,7 +3884,7 @@
       </c>
       <c r="K73" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:56:58Z</t>
+          <t>2026-10-07T19:19:47Z</t>
         </is>
       </c>
     </row>
@@ -3933,7 +3933,7 @@
       </c>
       <c r="K74" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:56:58Z</t>
+          <t>2026-10-07T19:19:47Z</t>
         </is>
       </c>
     </row>
@@ -3982,7 +3982,7 @@
       </c>
       <c r="K75" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:56:58Z</t>
+          <t>2026-10-07T19:19:47Z</t>
         </is>
       </c>
     </row>
@@ -4031,7 +4031,7 @@
       </c>
       <c r="K76" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:56:58Z</t>
+          <t>2026-10-07T19:19:47Z</t>
         </is>
       </c>
     </row>
@@ -4080,7 +4080,7 @@
       </c>
       <c r="K77" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:56:58Z</t>
+          <t>2026-10-07T19:19:47Z</t>
         </is>
       </c>
     </row>
@@ -4129,7 +4129,7 @@
       </c>
       <c r="K78" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:56:58Z</t>
+          <t>2026-10-07T19:19:47Z</t>
         </is>
       </c>
     </row>
@@ -4178,7 +4178,7 @@
       </c>
       <c r="K79" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:56:58Z</t>
+          <t>2026-10-07T19:19:47Z</t>
         </is>
       </c>
     </row>
@@ -4227,7 +4227,7 @@
       </c>
       <c r="K80" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:56:58Z</t>
+          <t>2026-10-07T19:19:47Z</t>
         </is>
       </c>
     </row>
@@ -4276,7 +4276,7 @@
       </c>
       <c r="K81" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:56:58Z</t>
+          <t>2026-10-07T19:19:47Z</t>
         </is>
       </c>
     </row>
@@ -4325,7 +4325,7 @@
       </c>
       <c r="K82" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:56:58Z</t>
+          <t>2026-10-07T19:19:47Z</t>
         </is>
       </c>
     </row>
@@ -4374,7 +4374,7 @@
       </c>
       <c r="K83" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:56:58Z</t>
+          <t>2026-10-07T19:19:47Z</t>
         </is>
       </c>
     </row>
@@ -4423,7 +4423,7 @@
       </c>
       <c r="K84" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:56:58Z</t>
+          <t>2026-10-07T19:19:47Z</t>
         </is>
       </c>
     </row>
@@ -4472,7 +4472,7 @@
       </c>
       <c r="K85" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:56:58Z</t>
+          <t>2026-10-07T19:19:47Z</t>
         </is>
       </c>
     </row>
@@ -4521,7 +4521,7 @@
       </c>
       <c r="K86" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:56:58Z</t>
+          <t>2026-10-07T19:19:47Z</t>
         </is>
       </c>
     </row>
@@ -4570,7 +4570,7 @@
       </c>
       <c r="K87" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:56:58Z</t>
+          <t>2026-10-07T19:19:47Z</t>
         </is>
       </c>
     </row>
@@ -4619,7 +4619,7 @@
       </c>
       <c r="K88" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:56:58Z</t>
+          <t>2026-10-07T19:19:47Z</t>
         </is>
       </c>
     </row>
@@ -4668,7 +4668,7 @@
       </c>
       <c r="K89" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:56:58Z</t>
+          <t>2026-10-07T19:19:47Z</t>
         </is>
       </c>
     </row>
@@ -4717,7 +4717,7 @@
       </c>
       <c r="K90" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:56:58Z</t>
+          <t>2026-10-07T19:19:47Z</t>
         </is>
       </c>
     </row>
@@ -4766,7 +4766,7 @@
       </c>
       <c r="K91" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:56:58Z</t>
+          <t>2026-10-07T19:19:47Z</t>
         </is>
       </c>
     </row>
@@ -4815,7 +4815,7 @@
       </c>
       <c r="K92" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:56:58Z</t>
+          <t>2026-10-07T19:19:47Z</t>
         </is>
       </c>
     </row>
@@ -4864,7 +4864,7 @@
       </c>
       <c r="K93" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:56:58Z</t>
+          <t>2026-10-07T19:19:47Z</t>
         </is>
       </c>
     </row>
@@ -4913,7 +4913,7 @@
       </c>
       <c r="K94" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:56:58Z</t>
+          <t>2026-10-07T19:19:47Z</t>
         </is>
       </c>
     </row>
@@ -4962,7 +4962,7 @@
       </c>
       <c r="K95" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:56:58Z</t>
+          <t>2026-10-07T19:19:47Z</t>
         </is>
       </c>
     </row>
@@ -5011,7 +5011,7 @@
       </c>
       <c r="K96" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:56:58Z</t>
+          <t>2026-10-07T19:19:47Z</t>
         </is>
       </c>
     </row>
@@ -5060,7 +5060,7 @@
       </c>
       <c r="K97" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:56:58Z</t>
+          <t>2026-10-07T19:19:47Z</t>
         </is>
       </c>
     </row>
@@ -5109,7 +5109,7 @@
       </c>
       <c r="K98" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:56:58Z</t>
+          <t>2026-10-07T19:19:47Z</t>
         </is>
       </c>
     </row>
@@ -5158,7 +5158,7 @@
       </c>
       <c r="K99" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:56:58Z</t>
+          <t>2026-10-07T19:19:47Z</t>
         </is>
       </c>
     </row>
@@ -5207,7 +5207,7 @@
       </c>
       <c r="K100" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:56:58Z</t>
+          <t>2026-10-07T19:19:47Z</t>
         </is>
       </c>
     </row>
@@ -5256,7 +5256,7 @@
       </c>
       <c r="K101" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:56:58Z</t>
+          <t>2026-10-07T19:19:47Z</t>
         </is>
       </c>
     </row>
@@ -5305,7 +5305,7 @@
       </c>
       <c r="K102" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:56:58Z</t>
+          <t>2026-10-07T19:19:47Z</t>
         </is>
       </c>
     </row>
@@ -5354,7 +5354,7 @@
       </c>
       <c r="K103" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:56:58Z</t>
+          <t>2026-10-07T19:19:47Z</t>
         </is>
       </c>
     </row>
@@ -5403,7 +5403,7 @@
       </c>
       <c r="K104" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:56:58Z</t>
+          <t>2026-10-07T19:19:47Z</t>
         </is>
       </c>
     </row>
@@ -5452,7 +5452,7 @@
       </c>
       <c r="K105" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:56:58Z</t>
+          <t>2026-10-07T19:19:47Z</t>
         </is>
       </c>
     </row>
@@ -5501,7 +5501,7 @@
       </c>
       <c r="K106" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:56:58Z</t>
+          <t>2026-10-07T19:19:47Z</t>
         </is>
       </c>
     </row>
@@ -5550,7 +5550,7 @@
       </c>
       <c r="K107" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:56:58Z</t>
+          <t>2026-10-07T19:19:47Z</t>
         </is>
       </c>
     </row>
@@ -5599,7 +5599,7 @@
       </c>
       <c r="K108" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:56:58Z</t>
+          <t>2026-10-07T19:19:47Z</t>
         </is>
       </c>
     </row>
@@ -5648,7 +5648,7 @@
       </c>
       <c r="K109" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:56:58Z</t>
+          <t>2026-10-07T19:19:47Z</t>
         </is>
       </c>
     </row>
@@ -5697,7 +5697,7 @@
       </c>
       <c r="K110" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:56:58Z</t>
+          <t>2026-10-07T19:19:47Z</t>
         </is>
       </c>
     </row>
@@ -5746,7 +5746,7 @@
       </c>
       <c r="K111" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:56:58Z</t>
+          <t>2026-10-07T19:19:47Z</t>
         </is>
       </c>
     </row>
@@ -5795,7 +5795,7 @@
       </c>
       <c r="K112" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:56:58Z</t>
+          <t>2026-10-07T19:19:47Z</t>
         </is>
       </c>
     </row>
@@ -5844,7 +5844,7 @@
       </c>
       <c r="K113" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:56:58Z</t>
+          <t>2026-10-07T19:19:47Z</t>
         </is>
       </c>
     </row>
@@ -5893,7 +5893,7 @@
       </c>
       <c r="K114" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:56:58Z</t>
+          <t>2026-10-07T19:19:47Z</t>
         </is>
       </c>
     </row>
@@ -5942,7 +5942,7 @@
       </c>
       <c r="K115" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:56:58Z</t>
+          <t>2026-10-07T19:19:47Z</t>
         </is>
       </c>
     </row>
@@ -5991,7 +5991,7 @@
       </c>
       <c r="K116" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:56:58Z</t>
+          <t>2026-10-07T19:19:47Z</t>
         </is>
       </c>
     </row>
@@ -6040,7 +6040,7 @@
       </c>
       <c r="K117" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:56:58Z</t>
+          <t>2026-10-07T19:19:47Z</t>
         </is>
       </c>
     </row>
@@ -6089,7 +6089,7 @@
       </c>
       <c r="K118" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:56:58Z</t>
+          <t>2026-10-07T19:19:47Z</t>
         </is>
       </c>
     </row>
@@ -6138,7 +6138,7 @@
       </c>
       <c r="K119" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:56:58Z</t>
+          <t>2026-10-07T19:19:47Z</t>
         </is>
       </c>
     </row>
@@ -6187,7 +6187,7 @@
       </c>
       <c r="K120" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:56:58Z</t>
+          <t>2026-10-07T19:19:47Z</t>
         </is>
       </c>
     </row>
@@ -6236,7 +6236,7 @@
       </c>
       <c r="K121" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:56:58Z</t>
+          <t>2026-10-07T19:19:47Z</t>
         </is>
       </c>
     </row>
@@ -6285,7 +6285,7 @@
       </c>
       <c r="K122" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:56:58Z</t>
+          <t>2026-10-07T19:19:47Z</t>
         </is>
       </c>
     </row>
@@ -6334,7 +6334,7 @@
       </c>
       <c r="K123" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:56:58Z</t>
+          <t>2026-10-07T19:19:47Z</t>
         </is>
       </c>
     </row>
@@ -6383,7 +6383,7 @@
       </c>
       <c r="K124" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:56:58Z</t>
+          <t>2026-10-07T19:19:47Z</t>
         </is>
       </c>
     </row>
@@ -6432,7 +6432,7 @@
       </c>
       <c r="K125" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:56:58Z</t>
+          <t>2026-10-07T19:19:47Z</t>
         </is>
       </c>
     </row>
@@ -6481,7 +6481,7 @@
       </c>
       <c r="K126" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:56:58Z</t>
+          <t>2026-10-07T19:19:47Z</t>
         </is>
       </c>
     </row>
@@ -6530,7 +6530,7 @@
       </c>
       <c r="K127" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:56:58Z</t>
+          <t>2026-10-07T19:19:47Z</t>
         </is>
       </c>
     </row>
@@ -6579,7 +6579,7 @@
       </c>
       <c r="K128" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:56:58Z</t>
+          <t>2026-10-07T19:19:47Z</t>
         </is>
       </c>
     </row>
@@ -6628,7 +6628,7 @@
       </c>
       <c r="K129" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:56:58Z</t>
+          <t>2026-10-07T19:19:47Z</t>
         </is>
       </c>
     </row>
@@ -6677,7 +6677,7 @@
       </c>
       <c r="K130" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:56:58Z</t>
+          <t>2026-10-07T19:19:47Z</t>
         </is>
       </c>
     </row>
@@ -6726,7 +6726,7 @@
       </c>
       <c r="K131" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:56:58Z</t>
+          <t>2026-10-07T19:19:47Z</t>
         </is>
       </c>
     </row>
@@ -6775,7 +6775,7 @@
       </c>
       <c r="K132" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:56:58Z</t>
+          <t>2026-10-07T19:19:47Z</t>
         </is>
       </c>
     </row>
@@ -6824,7 +6824,7 @@
       </c>
       <c r="K133" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:56:58Z</t>
+          <t>2026-10-07T19:19:47Z</t>
         </is>
       </c>
     </row>
@@ -6873,7 +6873,7 @@
       </c>
       <c r="K134" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:56:58Z</t>
+          <t>2026-10-07T19:19:47Z</t>
         </is>
       </c>
     </row>
@@ -6922,7 +6922,7 @@
       </c>
       <c r="K135" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:56:58Z</t>
+          <t>2026-10-07T19:19:47Z</t>
         </is>
       </c>
     </row>
@@ -6971,7 +6971,7 @@
       </c>
       <c r="K136" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:56:58Z</t>
+          <t>2026-10-07T19:19:47Z</t>
         </is>
       </c>
     </row>
@@ -7020,7 +7020,7 @@
       </c>
       <c r="K137" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:56:58Z</t>
+          <t>2026-10-07T19:19:47Z</t>
         </is>
       </c>
     </row>
@@ -7069,7 +7069,7 @@
       </c>
       <c r="K138" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:56:58Z</t>
+          <t>2026-10-07T19:19:47Z</t>
         </is>
       </c>
     </row>
@@ -7118,7 +7118,7 @@
       </c>
       <c r="K139" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:56:58Z</t>
+          <t>2026-10-07T19:19:47Z</t>
         </is>
       </c>
     </row>
@@ -7167,7 +7167,7 @@
       </c>
       <c r="K140" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:56:58Z</t>
+          <t>2026-10-07T19:19:47Z</t>
         </is>
       </c>
     </row>
@@ -7216,7 +7216,7 @@
       </c>
       <c r="K141" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:56:58Z</t>
+          <t>2026-10-07T19:19:47Z</t>
         </is>
       </c>
     </row>
@@ -7265,7 +7265,7 @@
       </c>
       <c r="K142" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:56:58Z</t>
+          <t>2026-10-07T19:19:47Z</t>
         </is>
       </c>
     </row>
@@ -7314,7 +7314,7 @@
       </c>
       <c r="K143" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:56:58Z</t>
+          <t>2026-10-07T19:19:47Z</t>
         </is>
       </c>
     </row>
@@ -7363,7 +7363,7 @@
       </c>
       <c r="K144" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:56:58Z</t>
+          <t>2026-10-07T19:19:47Z</t>
         </is>
       </c>
     </row>
@@ -7412,7 +7412,7 @@
       </c>
       <c r="K145" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:56:58Z</t>
+          <t>2026-10-07T19:19:47Z</t>
         </is>
       </c>
     </row>
@@ -7461,7 +7461,7 @@
       </c>
       <c r="K146" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:56:58Z</t>
+          <t>2026-10-07T19:19:47Z</t>
         </is>
       </c>
     </row>
@@ -7510,7 +7510,7 @@
       </c>
       <c r="K147" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:56:58Z</t>
+          <t>2026-10-07T19:19:47Z</t>
         </is>
       </c>
     </row>
@@ -7559,7 +7559,7 @@
       </c>
       <c r="K148" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:56:58Z</t>
+          <t>2026-10-07T19:19:47Z</t>
         </is>
       </c>
     </row>
@@ -7608,7 +7608,7 @@
       </c>
       <c r="K149" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:56:58Z</t>
+          <t>2026-10-07T19:19:47Z</t>
         </is>
       </c>
     </row>
@@ -7657,7 +7657,7 @@
       </c>
       <c r="K150" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:56:58Z</t>
+          <t>2026-10-07T19:19:47Z</t>
         </is>
       </c>
     </row>
@@ -7706,7 +7706,7 @@
       </c>
       <c r="K151" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:56:58Z</t>
+          <t>2026-10-07T19:19:47Z</t>
         </is>
       </c>
     </row>
@@ -7755,7 +7755,7 @@
       </c>
       <c r="K152" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:56:58Z</t>
+          <t>2026-10-07T19:19:47Z</t>
         </is>
       </c>
     </row>
@@ -7804,7 +7804,7 @@
       </c>
       <c r="K153" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:56:58Z</t>
+          <t>2026-10-07T19:19:47Z</t>
         </is>
       </c>
     </row>
@@ -7853,7 +7853,7 @@
       </c>
       <c r="K154" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:56:58Z</t>
+          <t>2026-10-07T19:19:47Z</t>
         </is>
       </c>
     </row>
@@ -7902,7 +7902,7 @@
       </c>
       <c r="K155" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:56:58Z</t>
+          <t>2026-10-07T19:19:47Z</t>
         </is>
       </c>
     </row>
@@ -7951,7 +7951,7 @@
       </c>
       <c r="K156" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:56:58Z</t>
+          <t>2026-10-07T19:19:47Z</t>
         </is>
       </c>
     </row>
@@ -8000,7 +8000,7 @@
       </c>
       <c r="K157" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:56:58Z</t>
+          <t>2026-10-07T19:19:47Z</t>
         </is>
       </c>
     </row>
@@ -8049,7 +8049,7 @@
       </c>
       <c r="K158" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:56:58Z</t>
+          <t>2026-10-07T19:19:47Z</t>
         </is>
       </c>
     </row>
@@ -8098,7 +8098,7 @@
       </c>
       <c r="K159" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:56:58Z</t>
+          <t>2026-10-07T19:19:47Z</t>
         </is>
       </c>
     </row>
@@ -8147,7 +8147,7 @@
       </c>
       <c r="K160" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:56:58Z</t>
+          <t>2026-10-07T19:19:47Z</t>
         </is>
       </c>
     </row>
@@ -8196,7 +8196,7 @@
       </c>
       <c r="K161" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:56:58Z</t>
+          <t>2026-10-07T19:19:47Z</t>
         </is>
       </c>
     </row>
@@ -8245,7 +8245,7 @@
       </c>
       <c r="K162" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:56:58Z</t>
+          <t>2026-10-07T19:19:47Z</t>
         </is>
       </c>
     </row>
@@ -8294,7 +8294,7 @@
       </c>
       <c r="K163" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:56:58Z</t>
+          <t>2026-10-07T19:19:47Z</t>
         </is>
       </c>
     </row>
@@ -8343,7 +8343,7 @@
       </c>
       <c r="K164" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:56:58Z</t>
+          <t>2026-10-07T19:19:47Z</t>
         </is>
       </c>
     </row>
@@ -8392,7 +8392,7 @@
       </c>
       <c r="K165" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:56:58Z</t>
+          <t>2026-10-07T19:19:47Z</t>
         </is>
       </c>
     </row>
@@ -8441,7 +8441,7 @@
       </c>
       <c r="K166" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:56:58Z</t>
+          <t>2026-10-07T19:19:47Z</t>
         </is>
       </c>
     </row>
@@ -8490,7 +8490,7 @@
       </c>
       <c r="K167" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:56:58Z</t>
+          <t>2026-10-07T19:19:47Z</t>
         </is>
       </c>
     </row>
@@ -8539,7 +8539,7 @@
       </c>
       <c r="K168" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:56:58Z</t>
+          <t>2026-10-07T19:19:47Z</t>
         </is>
       </c>
     </row>
@@ -8588,7 +8588,7 @@
       </c>
       <c r="K169" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:56:58Z</t>
+          <t>2026-10-07T19:19:47Z</t>
         </is>
       </c>
     </row>
@@ -8637,7 +8637,7 @@
       </c>
       <c r="K170" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:56:58Z</t>
+          <t>2026-10-07T19:19:47Z</t>
         </is>
       </c>
     </row>
@@ -8686,7 +8686,7 @@
       </c>
       <c r="K171" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:56:58Z</t>
+          <t>2026-10-07T19:19:47Z</t>
         </is>
       </c>
     </row>
@@ -8735,7 +8735,7 @@
       </c>
       <c r="K172" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:56:58Z</t>
+          <t>2026-10-07T19:19:47Z</t>
         </is>
       </c>
     </row>
@@ -8784,7 +8784,7 @@
       </c>
       <c r="K173" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:56:58Z</t>
+          <t>2026-10-07T19:19:47Z</t>
         </is>
       </c>
     </row>
@@ -8833,7 +8833,7 @@
       </c>
       <c r="K174" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:56:58Z</t>
+          <t>2026-10-07T19:19:47Z</t>
         </is>
       </c>
     </row>
@@ -8882,7 +8882,7 @@
       </c>
       <c r="K175" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:56:58Z</t>
+          <t>2026-10-07T19:19:47Z</t>
         </is>
       </c>
     </row>
@@ -8931,7 +8931,7 @@
       </c>
       <c r="K176" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:56:58Z</t>
+          <t>2026-10-07T19:19:47Z</t>
         </is>
       </c>
     </row>
@@ -8980,7 +8980,7 @@
       </c>
       <c r="K177" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:56:58Z</t>
+          <t>2026-10-07T19:19:47Z</t>
         </is>
       </c>
     </row>
@@ -9029,7 +9029,7 @@
       </c>
       <c r="K178" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:56:58Z</t>
+          <t>2026-10-07T19:19:47Z</t>
         </is>
       </c>
     </row>
@@ -9078,7 +9078,7 @@
       </c>
       <c r="K179" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:56:58Z</t>
+          <t>2026-10-07T19:19:47Z</t>
         </is>
       </c>
     </row>
@@ -9127,7 +9127,7 @@
       </c>
       <c r="K180" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:56:58Z</t>
+          <t>2026-10-07T19:19:47Z</t>
         </is>
       </c>
     </row>
@@ -9176,7 +9176,7 @@
       </c>
       <c r="K181" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:56:58Z</t>
+          <t>2026-10-07T19:19:47Z</t>
         </is>
       </c>
     </row>
@@ -9225,7 +9225,7 @@
       </c>
       <c r="K182" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:56:58Z</t>
+          <t>2026-10-07T19:19:47Z</t>
         </is>
       </c>
     </row>
@@ -9274,7 +9274,7 @@
       </c>
       <c r="K183" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:56:58Z</t>
+          <t>2026-10-07T19:19:47Z</t>
         </is>
       </c>
     </row>
@@ -9323,7 +9323,7 @@
       </c>
       <c r="K184" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:56:58Z</t>
+          <t>2026-10-07T19:19:47Z</t>
         </is>
       </c>
     </row>
@@ -9372,7 +9372,7 @@
       </c>
       <c r="K185" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:56:58Z</t>
+          <t>2026-10-07T19:19:47Z</t>
         </is>
       </c>
     </row>
@@ -9421,7 +9421,7 @@
       </c>
       <c r="K186" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:56:58Z</t>
+          <t>2026-10-07T19:19:47Z</t>
         </is>
       </c>
     </row>
@@ -9470,7 +9470,7 @@
       </c>
       <c r="K187" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:56:58Z</t>
+          <t>2026-10-07T19:19:47Z</t>
         </is>
       </c>
     </row>
@@ -9519,7 +9519,7 @@
       </c>
       <c r="K188" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:56:58Z</t>
+          <t>2026-10-07T19:19:47Z</t>
         </is>
       </c>
     </row>
@@ -9568,7 +9568,7 @@
       </c>
       <c r="K189" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:56:58Z</t>
+          <t>2026-10-07T19:19:47Z</t>
         </is>
       </c>
     </row>
@@ -9617,7 +9617,7 @@
       </c>
       <c r="K190" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:56:58Z</t>
+          <t>2026-10-07T19:19:47Z</t>
         </is>
       </c>
     </row>
@@ -9666,7 +9666,7 @@
       </c>
       <c r="K191" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:56:58Z</t>
+          <t>2026-10-07T19:19:47Z</t>
         </is>
       </c>
     </row>
@@ -9715,7 +9715,7 @@
       </c>
       <c r="K192" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:56:58Z</t>
+          <t>2026-10-07T19:19:47Z</t>
         </is>
       </c>
     </row>
@@ -9764,7 +9764,7 @@
       </c>
       <c r="K193" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:56:58Z</t>
+          <t>2026-10-07T19:19:47Z</t>
         </is>
       </c>
     </row>
@@ -9813,7 +9813,7 @@
       </c>
       <c r="K194" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:56:58Z</t>
+          <t>2026-10-07T19:19:47Z</t>
         </is>
       </c>
     </row>
@@ -9862,7 +9862,7 @@
       </c>
       <c r="K195" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:56:58Z</t>
+          <t>2026-10-07T19:19:47Z</t>
         </is>
       </c>
     </row>
@@ -9911,7 +9911,7 @@
       </c>
       <c r="K196" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:56:58Z</t>
+          <t>2026-10-07T19:19:47Z</t>
         </is>
       </c>
     </row>
@@ -9960,7 +9960,7 @@
       </c>
       <c r="K197" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:56:58Z</t>
+          <t>2026-10-07T19:19:47Z</t>
         </is>
       </c>
     </row>
@@ -10009,7 +10009,7 @@
       </c>
       <c r="K198" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:56:58Z</t>
+          <t>2026-10-07T19:19:47Z</t>
         </is>
       </c>
     </row>
@@ -10058,7 +10058,7 @@
       </c>
       <c r="K199" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:56:58Z</t>
+          <t>2026-10-07T19:19:47Z</t>
         </is>
       </c>
     </row>
@@ -10107,7 +10107,7 @@
       </c>
       <c r="K200" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:56:58Z</t>
+          <t>2026-10-07T19:19:47Z</t>
         </is>
       </c>
     </row>
@@ -10156,7 +10156,7 @@
       </c>
       <c r="K201" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:56:58Z</t>
+          <t>2026-10-07T19:19:47Z</t>
         </is>
       </c>
     </row>
@@ -10205,7 +10205,7 @@
       </c>
       <c r="K202" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:56:58Z</t>
+          <t>2026-10-07T19:19:47Z</t>
         </is>
       </c>
     </row>
@@ -10254,7 +10254,7 @@
       </c>
       <c r="K203" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:56:58Z</t>
+          <t>2026-10-07T19:19:47Z</t>
         </is>
       </c>
     </row>
@@ -10303,7 +10303,7 @@
       </c>
       <c r="K204" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:56:58Z</t>
+          <t>2026-10-07T19:19:47Z</t>
         </is>
       </c>
     </row>
@@ -10352,7 +10352,7 @@
       </c>
       <c r="K205" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:56:58Z</t>
+          <t>2026-10-07T19:19:47Z</t>
         </is>
       </c>
     </row>
@@ -10401,7 +10401,7 @@
       </c>
       <c r="K206" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:56:58Z</t>
+          <t>2026-10-07T19:19:47Z</t>
         </is>
       </c>
     </row>
@@ -10450,7 +10450,7 @@
       </c>
       <c r="K207" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:56:58Z</t>
+          <t>2026-10-07T19:19:47Z</t>
         </is>
       </c>
     </row>
@@ -10499,7 +10499,7 @@
       </c>
       <c r="K208" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:56:58Z</t>
+          <t>2026-10-07T19:19:47Z</t>
         </is>
       </c>
     </row>
@@ -10548,7 +10548,7 @@
       </c>
       <c r="K209" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:56:58Z</t>
+          <t>2026-10-07T19:19:47Z</t>
         </is>
       </c>
     </row>
@@ -10597,7 +10597,7 @@
       </c>
       <c r="K210" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:56:58Z</t>
+          <t>2026-10-07T19:19:47Z</t>
         </is>
       </c>
     </row>
@@ -10646,7 +10646,7 @@
       </c>
       <c r="K211" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:56:58Z</t>
+          <t>2026-10-07T19:19:47Z</t>
         </is>
       </c>
     </row>
@@ -10695,7 +10695,7 @@
       </c>
       <c r="K212" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:56:58Z</t>
+          <t>2026-10-07T19:19:47Z</t>
         </is>
       </c>
     </row>
@@ -10744,7 +10744,7 @@
       </c>
       <c r="K213" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:56:58Z</t>
+          <t>2026-10-07T19:19:47Z</t>
         </is>
       </c>
     </row>
@@ -10793,7 +10793,7 @@
       </c>
       <c r="K214" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:56:58Z</t>
+          <t>2026-10-07T19:19:47Z</t>
         </is>
       </c>
     </row>
@@ -10842,7 +10842,7 @@
       </c>
       <c r="K215" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:56:58Z</t>
+          <t>2026-10-07T19:19:47Z</t>
         </is>
       </c>
     </row>
@@ -10891,7 +10891,7 @@
       </c>
       <c r="K216" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:56:58Z</t>
+          <t>2026-10-07T19:19:47Z</t>
         </is>
       </c>
     </row>
@@ -10940,7 +10940,7 @@
       </c>
       <c r="K217" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:56:58Z</t>
+          <t>2026-10-07T19:19:47Z</t>
         </is>
       </c>
     </row>
@@ -10989,7 +10989,7 @@
       </c>
       <c r="K218" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:56:58Z</t>
+          <t>2026-10-07T19:19:47Z</t>
         </is>
       </c>
     </row>
@@ -11038,7 +11038,7 @@
       </c>
       <c r="K219" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:56:58Z</t>
+          <t>2026-10-07T19:19:47Z</t>
         </is>
       </c>
     </row>
@@ -11087,7 +11087,7 @@
       </c>
       <c r="K220" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:56:58Z</t>
+          <t>2026-10-07T19:19:47Z</t>
         </is>
       </c>
     </row>
@@ -11136,7 +11136,7 @@
       </c>
       <c r="K221" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:56:58Z</t>
+          <t>2026-10-07T19:19:47Z</t>
         </is>
       </c>
     </row>
@@ -11185,7 +11185,7 @@
       </c>
       <c r="K222" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:56:58Z</t>
+          <t>2026-10-07T19:19:47Z</t>
         </is>
       </c>
     </row>
@@ -11234,7 +11234,7 @@
       </c>
       <c r="K223" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:56:58Z</t>
+          <t>2026-10-07T19:19:47Z</t>
         </is>
       </c>
     </row>
@@ -11283,7 +11283,7 @@
       </c>
       <c r="K224" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:56:58Z</t>
+          <t>2026-10-07T19:19:47Z</t>
         </is>
       </c>
     </row>
@@ -11332,7 +11332,7 @@
       </c>
       <c r="K225" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:56:58Z</t>
+          <t>2026-10-07T19:19:47Z</t>
         </is>
       </c>
     </row>
@@ -11381,7 +11381,7 @@
       </c>
       <c r="K226" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:56:58Z</t>
+          <t>2026-10-07T19:19:47Z</t>
         </is>
       </c>
     </row>
@@ -11430,7 +11430,7 @@
       </c>
       <c r="K227" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:56:58Z</t>
+          <t>2026-10-07T19:19:47Z</t>
         </is>
       </c>
     </row>
@@ -11479,7 +11479,7 @@
       </c>
       <c r="K228" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:56:58Z</t>
+          <t>2026-10-07T19:19:47Z</t>
         </is>
       </c>
     </row>
@@ -11528,7 +11528,7 @@
       </c>
       <c r="K229" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:56:58Z</t>
+          <t>2026-10-07T19:19:47Z</t>
         </is>
       </c>
     </row>
@@ -11577,7 +11577,7 @@
       </c>
       <c r="K230" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:56:58Z</t>
+          <t>2026-10-07T19:19:47Z</t>
         </is>
       </c>
     </row>
@@ -11626,7 +11626,7 @@
       </c>
       <c r="K231" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:56:58Z</t>
+          <t>2026-10-07T19:19:47Z</t>
         </is>
       </c>
     </row>
@@ -11758,7 +11758,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:56:58Z</t>
+          <t>2026-10-07T19:19:47Z</t>
         </is>
       </c>
     </row>
@@ -11804,7 +11804,7 @@
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>{"date": "2026-08-01", "year": 2026, "month": 8, "month_name": "Agosto", "index_value": 637409769724325.1, "monthly_variation_pct": 8.9, "unit": "Índice base diciembre 2007=100 y variación mensual %", "frequency": "monthly", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/precios_consumidor/4_5_7_2.xls", "fetched_at": "2026-10-06T23:56:58Z"}</t>
+          <t>{"date": "2026-08-01", "year": 2026, "month": 8, "month_name": "Agosto", "index_value": 637409769724325.1, "monthly_variation_pct": 8.9, "unit": "Índice base diciembre 2007=100 y variación mensual %", "frequency": "monthly", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/precios_consumidor/4_5_7_2.xls", "fetched_at": "2026-10-07T19:19:47Z"}</t>
         </is>
       </c>
     </row>

--- a/assets/data/bcv/excel/ove_bcv_inpc_nacional_mensual.xlsx
+++ b/assets/data/bcv/excel/ove_bcv_inpc_nacional_mensual.xlsx
@@ -650,7 +650,7 @@
       </c>
       <c r="K7" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:47Z</t>
+          <t>2026-10-08T00:18:14Z</t>
         </is>
       </c>
     </row>
@@ -699,7 +699,7 @@
       </c>
       <c r="K8" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:47Z</t>
+          <t>2026-10-08T00:18:14Z</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="K9" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:47Z</t>
+          <t>2026-10-08T00:18:14Z</t>
         </is>
       </c>
     </row>
@@ -797,7 +797,7 @@
       </c>
       <c r="K10" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:47Z</t>
+          <t>2026-10-08T00:18:14Z</t>
         </is>
       </c>
     </row>
@@ -846,7 +846,7 @@
       </c>
       <c r="K11" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:47Z</t>
+          <t>2026-10-08T00:18:14Z</t>
         </is>
       </c>
     </row>
@@ -895,7 +895,7 @@
       </c>
       <c r="K12" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:47Z</t>
+          <t>2026-10-08T00:18:14Z</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="K13" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:47Z</t>
+          <t>2026-10-08T00:18:14Z</t>
         </is>
       </c>
     </row>
@@ -993,7 +993,7 @@
       </c>
       <c r="K14" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:47Z</t>
+          <t>2026-10-08T00:18:14Z</t>
         </is>
       </c>
     </row>
@@ -1042,7 +1042,7 @@
       </c>
       <c r="K15" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:47Z</t>
+          <t>2026-10-08T00:18:14Z</t>
         </is>
       </c>
     </row>
@@ -1091,7 +1091,7 @@
       </c>
       <c r="K16" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:47Z</t>
+          <t>2026-10-08T00:18:14Z</t>
         </is>
       </c>
     </row>
@@ -1140,7 +1140,7 @@
       </c>
       <c r="K17" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:47Z</t>
+          <t>2026-10-08T00:18:14Z</t>
         </is>
       </c>
     </row>
@@ -1189,7 +1189,7 @@
       </c>
       <c r="K18" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:47Z</t>
+          <t>2026-10-08T00:18:14Z</t>
         </is>
       </c>
     </row>
@@ -1238,7 +1238,7 @@
       </c>
       <c r="K19" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:47Z</t>
+          <t>2026-10-08T00:18:14Z</t>
         </is>
       </c>
     </row>
@@ -1287,7 +1287,7 @@
       </c>
       <c r="K20" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:47Z</t>
+          <t>2026-10-08T00:18:14Z</t>
         </is>
       </c>
     </row>
@@ -1336,7 +1336,7 @@
       </c>
       <c r="K21" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:47Z</t>
+          <t>2026-10-08T00:18:14Z</t>
         </is>
       </c>
     </row>
@@ -1385,7 +1385,7 @@
       </c>
       <c r="K22" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:47Z</t>
+          <t>2026-10-08T00:18:14Z</t>
         </is>
       </c>
     </row>
@@ -1434,7 +1434,7 @@
       </c>
       <c r="K23" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:47Z</t>
+          <t>2026-10-08T00:18:14Z</t>
         </is>
       </c>
     </row>
@@ -1483,7 +1483,7 @@
       </c>
       <c r="K24" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:47Z</t>
+          <t>2026-10-08T00:18:14Z</t>
         </is>
       </c>
     </row>
@@ -1532,7 +1532,7 @@
       </c>
       <c r="K25" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:47Z</t>
+          <t>2026-10-08T00:18:14Z</t>
         </is>
       </c>
     </row>
@@ -1581,7 +1581,7 @@
       </c>
       <c r="K26" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:47Z</t>
+          <t>2026-10-08T00:18:14Z</t>
         </is>
       </c>
     </row>
@@ -1630,7 +1630,7 @@
       </c>
       <c r="K27" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:47Z</t>
+          <t>2026-10-08T00:18:14Z</t>
         </is>
       </c>
     </row>
@@ -1679,7 +1679,7 @@
       </c>
       <c r="K28" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:47Z</t>
+          <t>2026-10-08T00:18:14Z</t>
         </is>
       </c>
     </row>
@@ -1728,7 +1728,7 @@
       </c>
       <c r="K29" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:47Z</t>
+          <t>2026-10-08T00:18:14Z</t>
         </is>
       </c>
     </row>
@@ -1777,7 +1777,7 @@
       </c>
       <c r="K30" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:47Z</t>
+          <t>2026-10-08T00:18:14Z</t>
         </is>
       </c>
     </row>
@@ -1826,7 +1826,7 @@
       </c>
       <c r="K31" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:47Z</t>
+          <t>2026-10-08T00:18:14Z</t>
         </is>
       </c>
     </row>
@@ -1875,7 +1875,7 @@
       </c>
       <c r="K32" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:47Z</t>
+          <t>2026-10-08T00:18:14Z</t>
         </is>
       </c>
     </row>
@@ -1924,7 +1924,7 @@
       </c>
       <c r="K33" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:47Z</t>
+          <t>2026-10-08T00:18:14Z</t>
         </is>
       </c>
     </row>
@@ -1973,7 +1973,7 @@
       </c>
       <c r="K34" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:47Z</t>
+          <t>2026-10-08T00:18:14Z</t>
         </is>
       </c>
     </row>
@@ -2022,7 +2022,7 @@
       </c>
       <c r="K35" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:47Z</t>
+          <t>2026-10-08T00:18:14Z</t>
         </is>
       </c>
     </row>
@@ -2071,7 +2071,7 @@
       </c>
       <c r="K36" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:47Z</t>
+          <t>2026-10-08T00:18:14Z</t>
         </is>
       </c>
     </row>
@@ -2120,7 +2120,7 @@
       </c>
       <c r="K37" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:47Z</t>
+          <t>2026-10-08T00:18:14Z</t>
         </is>
       </c>
     </row>
@@ -2169,7 +2169,7 @@
       </c>
       <c r="K38" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:47Z</t>
+          <t>2026-10-08T00:18:14Z</t>
         </is>
       </c>
     </row>
@@ -2218,7 +2218,7 @@
       </c>
       <c r="K39" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:47Z</t>
+          <t>2026-10-08T00:18:14Z</t>
         </is>
       </c>
     </row>
@@ -2267,7 +2267,7 @@
       </c>
       <c r="K40" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:47Z</t>
+          <t>2026-10-08T00:18:14Z</t>
         </is>
       </c>
     </row>
@@ -2316,7 +2316,7 @@
       </c>
       <c r="K41" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:47Z</t>
+          <t>2026-10-08T00:18:14Z</t>
         </is>
       </c>
     </row>
@@ -2365,7 +2365,7 @@
       </c>
       <c r="K42" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:47Z</t>
+          <t>2026-10-08T00:18:14Z</t>
         </is>
       </c>
     </row>
@@ -2414,7 +2414,7 @@
       </c>
       <c r="K43" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:47Z</t>
+          <t>2026-10-08T00:18:14Z</t>
         </is>
       </c>
     </row>
@@ -2463,7 +2463,7 @@
       </c>
       <c r="K44" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:47Z</t>
+          <t>2026-10-08T00:18:14Z</t>
         </is>
       </c>
     </row>
@@ -2512,7 +2512,7 @@
       </c>
       <c r="K45" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:47Z</t>
+          <t>2026-10-08T00:18:14Z</t>
         </is>
       </c>
     </row>
@@ -2561,7 +2561,7 @@
       </c>
       <c r="K46" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:47Z</t>
+          <t>2026-10-08T00:18:14Z</t>
         </is>
       </c>
     </row>
@@ -2610,7 +2610,7 @@
       </c>
       <c r="K47" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:47Z</t>
+          <t>2026-10-08T00:18:14Z</t>
         </is>
       </c>
     </row>
@@ -2659,7 +2659,7 @@
       </c>
       <c r="K48" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:47Z</t>
+          <t>2026-10-08T00:18:14Z</t>
         </is>
       </c>
     </row>
@@ -2708,7 +2708,7 @@
       </c>
       <c r="K49" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:47Z</t>
+          <t>2026-10-08T00:18:14Z</t>
         </is>
       </c>
     </row>
@@ -2757,7 +2757,7 @@
       </c>
       <c r="K50" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:47Z</t>
+          <t>2026-10-08T00:18:14Z</t>
         </is>
       </c>
     </row>
@@ -2806,7 +2806,7 @@
       </c>
       <c r="K51" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:47Z</t>
+          <t>2026-10-08T00:18:14Z</t>
         </is>
       </c>
     </row>
@@ -2855,7 +2855,7 @@
       </c>
       <c r="K52" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:47Z</t>
+          <t>2026-10-08T00:18:14Z</t>
         </is>
       </c>
     </row>
@@ -2904,7 +2904,7 @@
       </c>
       <c r="K53" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:47Z</t>
+          <t>2026-10-08T00:18:14Z</t>
         </is>
       </c>
     </row>
@@ -2953,7 +2953,7 @@
       </c>
       <c r="K54" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:47Z</t>
+          <t>2026-10-08T00:18:14Z</t>
         </is>
       </c>
     </row>
@@ -3002,7 +3002,7 @@
       </c>
       <c r="K55" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:47Z</t>
+          <t>2026-10-08T00:18:14Z</t>
         </is>
       </c>
     </row>
@@ -3051,7 +3051,7 @@
       </c>
       <c r="K56" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:47Z</t>
+          <t>2026-10-08T00:18:14Z</t>
         </is>
       </c>
     </row>
@@ -3100,7 +3100,7 @@
       </c>
       <c r="K57" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:47Z</t>
+          <t>2026-10-08T00:18:14Z</t>
         </is>
       </c>
     </row>
@@ -3149,7 +3149,7 @@
       </c>
       <c r="K58" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:47Z</t>
+          <t>2026-10-08T00:18:14Z</t>
         </is>
       </c>
     </row>
@@ -3198,7 +3198,7 @@
       </c>
       <c r="K59" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:47Z</t>
+          <t>2026-10-08T00:18:14Z</t>
         </is>
       </c>
     </row>
@@ -3247,7 +3247,7 @@
       </c>
       <c r="K60" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:47Z</t>
+          <t>2026-10-08T00:18:14Z</t>
         </is>
       </c>
     </row>
@@ -3296,7 +3296,7 @@
       </c>
       <c r="K61" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:47Z</t>
+          <t>2026-10-08T00:18:14Z</t>
         </is>
       </c>
     </row>
@@ -3345,7 +3345,7 @@
       </c>
       <c r="K62" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:47Z</t>
+          <t>2026-10-08T00:18:14Z</t>
         </is>
       </c>
     </row>
@@ -3394,7 +3394,7 @@
       </c>
       <c r="K63" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:47Z</t>
+          <t>2026-10-08T00:18:14Z</t>
         </is>
       </c>
     </row>
@@ -3443,7 +3443,7 @@
       </c>
       <c r="K64" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:47Z</t>
+          <t>2026-10-08T00:18:14Z</t>
         </is>
       </c>
     </row>
@@ -3492,7 +3492,7 @@
       </c>
       <c r="K65" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:47Z</t>
+          <t>2026-10-08T00:18:14Z</t>
         </is>
       </c>
     </row>
@@ -3541,7 +3541,7 @@
       </c>
       <c r="K66" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:47Z</t>
+          <t>2026-10-08T00:18:14Z</t>
         </is>
       </c>
     </row>
@@ -3590,7 +3590,7 @@
       </c>
       <c r="K67" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:47Z</t>
+          <t>2026-10-08T00:18:14Z</t>
         </is>
       </c>
     </row>
@@ -3639,7 +3639,7 @@
       </c>
       <c r="K68" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:47Z</t>
+          <t>2026-10-08T00:18:14Z</t>
         </is>
       </c>
     </row>
@@ -3688,7 +3688,7 @@
       </c>
       <c r="K69" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:47Z</t>
+          <t>2026-10-08T00:18:14Z</t>
         </is>
       </c>
     </row>
@@ -3737,7 +3737,7 @@
       </c>
       <c r="K70" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:47Z</t>
+          <t>2026-10-08T00:18:14Z</t>
         </is>
       </c>
     </row>
@@ -3786,7 +3786,7 @@
       </c>
       <c r="K71" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:47Z</t>
+          <t>2026-10-08T00:18:14Z</t>
         </is>
       </c>
     </row>
@@ -3835,7 +3835,7 @@
       </c>
       <c r="K72" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:47Z</t>
+          <t>2026-10-08T00:18:14Z</t>
         </is>
       </c>
     </row>
@@ -3884,7 +3884,7 @@
       </c>
       <c r="K73" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:47Z</t>
+          <t>2026-10-08T00:18:14Z</t>
         </is>
       </c>
     </row>
@@ -3933,7 +3933,7 @@
       </c>
       <c r="K74" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:47Z</t>
+          <t>2026-10-08T00:18:14Z</t>
         </is>
       </c>
     </row>
@@ -3982,7 +3982,7 @@
       </c>
       <c r="K75" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:47Z</t>
+          <t>2026-10-08T00:18:14Z</t>
         </is>
       </c>
     </row>
@@ -4031,7 +4031,7 @@
       </c>
       <c r="K76" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:47Z</t>
+          <t>2026-10-08T00:18:14Z</t>
         </is>
       </c>
     </row>
@@ -4080,7 +4080,7 @@
       </c>
       <c r="K77" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:47Z</t>
+          <t>2026-10-08T00:18:14Z</t>
         </is>
       </c>
     </row>
@@ -4129,7 +4129,7 @@
       </c>
       <c r="K78" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:47Z</t>
+          <t>2026-10-08T00:18:14Z</t>
         </is>
       </c>
     </row>
@@ -4178,7 +4178,7 @@
       </c>
       <c r="K79" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:47Z</t>
+          <t>2026-10-08T00:18:14Z</t>
         </is>
       </c>
     </row>
@@ -4227,7 +4227,7 @@
       </c>
       <c r="K80" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:47Z</t>
+          <t>2026-10-08T00:18:14Z</t>
         </is>
       </c>
     </row>
@@ -4276,7 +4276,7 @@
       </c>
       <c r="K81" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:47Z</t>
+          <t>2026-10-08T00:18:14Z</t>
         </is>
       </c>
     </row>
@@ -4325,7 +4325,7 @@
       </c>
       <c r="K82" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:47Z</t>
+          <t>2026-10-08T00:18:14Z</t>
         </is>
       </c>
     </row>
@@ -4374,7 +4374,7 @@
       </c>
       <c r="K83" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:47Z</t>
+          <t>2026-10-08T00:18:14Z</t>
         </is>
       </c>
     </row>
@@ -4423,7 +4423,7 @@
       </c>
       <c r="K84" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:47Z</t>
+          <t>2026-10-08T00:18:14Z</t>
         </is>
       </c>
     </row>
@@ -4472,7 +4472,7 @@
       </c>
       <c r="K85" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:47Z</t>
+          <t>2026-10-08T00:18:14Z</t>
         </is>
       </c>
     </row>
@@ -4521,7 +4521,7 @@
       </c>
       <c r="K86" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:47Z</t>
+          <t>2026-10-08T00:18:14Z</t>
         </is>
       </c>
     </row>
@@ -4570,7 +4570,7 @@
       </c>
       <c r="K87" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:47Z</t>
+          <t>2026-10-08T00:18:14Z</t>
         </is>
       </c>
     </row>
@@ -4619,7 +4619,7 @@
       </c>
       <c r="K88" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:47Z</t>
+          <t>2026-10-08T00:18:14Z</t>
         </is>
       </c>
     </row>
@@ -4668,7 +4668,7 @@
       </c>
       <c r="K89" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:47Z</t>
+          <t>2026-10-08T00:18:14Z</t>
         </is>
       </c>
     </row>
@@ -4717,7 +4717,7 @@
       </c>
       <c r="K90" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:47Z</t>
+          <t>2026-10-08T00:18:14Z</t>
         </is>
       </c>
     </row>
@@ -4766,7 +4766,7 @@
       </c>
       <c r="K91" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:47Z</t>
+          <t>2026-10-08T00:18:14Z</t>
         </is>
       </c>
     </row>
@@ -4815,7 +4815,7 @@
       </c>
       <c r="K92" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:47Z</t>
+          <t>2026-10-08T00:18:14Z</t>
         </is>
       </c>
     </row>
@@ -4864,7 +4864,7 @@
       </c>
       <c r="K93" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:47Z</t>
+          <t>2026-10-08T00:18:14Z</t>
         </is>
       </c>
     </row>
@@ -4913,7 +4913,7 @@
       </c>
       <c r="K94" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:47Z</t>
+          <t>2026-10-08T00:18:14Z</t>
         </is>
       </c>
     </row>
@@ -4962,7 +4962,7 @@
       </c>
       <c r="K95" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:47Z</t>
+          <t>2026-10-08T00:18:14Z</t>
         </is>
       </c>
     </row>
@@ -5011,7 +5011,7 @@
       </c>
       <c r="K96" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:47Z</t>
+          <t>2026-10-08T00:18:14Z</t>
         </is>
       </c>
     </row>
@@ -5060,7 +5060,7 @@
       </c>
       <c r="K97" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:47Z</t>
+          <t>2026-10-08T00:18:14Z</t>
         </is>
       </c>
     </row>
@@ -5109,7 +5109,7 @@
       </c>
       <c r="K98" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:47Z</t>
+          <t>2026-10-08T00:18:14Z</t>
         </is>
       </c>
     </row>
@@ -5158,7 +5158,7 @@
       </c>
       <c r="K99" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:47Z</t>
+          <t>2026-10-08T00:18:14Z</t>
         </is>
       </c>
     </row>
@@ -5207,7 +5207,7 @@
       </c>
       <c r="K100" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:47Z</t>
+          <t>2026-10-08T00:18:14Z</t>
         </is>
       </c>
     </row>
@@ -5256,7 +5256,7 @@
       </c>
       <c r="K101" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:47Z</t>
+          <t>2026-10-08T00:18:14Z</t>
         </is>
       </c>
     </row>
@@ -5305,7 +5305,7 @@
       </c>
       <c r="K102" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:47Z</t>
+          <t>2026-10-08T00:18:14Z</t>
         </is>
       </c>
     </row>
@@ -5354,7 +5354,7 @@
       </c>
       <c r="K103" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:47Z</t>
+          <t>2026-10-08T00:18:14Z</t>
         </is>
       </c>
     </row>
@@ -5403,7 +5403,7 @@
       </c>
       <c r="K104" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:47Z</t>
+          <t>2026-10-08T00:18:14Z</t>
         </is>
       </c>
     </row>
@@ -5452,7 +5452,7 @@
       </c>
       <c r="K105" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:47Z</t>
+          <t>2026-10-08T00:18:14Z</t>
         </is>
       </c>
     </row>
@@ -5501,7 +5501,7 @@
       </c>
       <c r="K106" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:47Z</t>
+          <t>2026-10-08T00:18:14Z</t>
         </is>
       </c>
     </row>
@@ -5550,7 +5550,7 @@
       </c>
       <c r="K107" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:47Z</t>
+          <t>2026-10-08T00:18:14Z</t>
         </is>
       </c>
     </row>
@@ -5599,7 +5599,7 @@
       </c>
       <c r="K108" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:47Z</t>
+          <t>2026-10-08T00:18:14Z</t>
         </is>
       </c>
     </row>
@@ -5648,7 +5648,7 @@
       </c>
       <c r="K109" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:47Z</t>
+          <t>2026-10-08T00:18:14Z</t>
         </is>
       </c>
     </row>
@@ -5697,7 +5697,7 @@
       </c>
       <c r="K110" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:47Z</t>
+          <t>2026-10-08T00:18:14Z</t>
         </is>
       </c>
     </row>
@@ -5746,7 +5746,7 @@
       </c>
       <c r="K111" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:47Z</t>
+          <t>2026-10-08T00:18:14Z</t>
         </is>
       </c>
     </row>
@@ -5795,7 +5795,7 @@
       </c>
       <c r="K112" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:47Z</t>
+          <t>2026-10-08T00:18:14Z</t>
         </is>
       </c>
     </row>
@@ -5844,7 +5844,7 @@
       </c>
       <c r="K113" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:47Z</t>
+          <t>2026-10-08T00:18:14Z</t>
         </is>
       </c>
     </row>
@@ -5893,7 +5893,7 @@
       </c>
       <c r="K114" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:47Z</t>
+          <t>2026-10-08T00:18:14Z</t>
         </is>
       </c>
     </row>
@@ -5942,7 +5942,7 @@
       </c>
       <c r="K115" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:47Z</t>
+          <t>2026-10-08T00:18:14Z</t>
         </is>
       </c>
     </row>
@@ -5991,7 +5991,7 @@
       </c>
       <c r="K116" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:47Z</t>
+          <t>2026-10-08T00:18:14Z</t>
         </is>
       </c>
     </row>
@@ -6040,7 +6040,7 @@
       </c>
       <c r="K117" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:47Z</t>
+          <t>2026-10-08T00:18:14Z</t>
         </is>
       </c>
     </row>
@@ -6089,7 +6089,7 @@
       </c>
       <c r="K118" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:47Z</t>
+          <t>2026-10-08T00:18:14Z</t>
         </is>
       </c>
     </row>
@@ -6138,7 +6138,7 @@
       </c>
       <c r="K119" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:47Z</t>
+          <t>2026-10-08T00:18:14Z</t>
         </is>
       </c>
     </row>
@@ -6187,7 +6187,7 @@
       </c>
       <c r="K120" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:47Z</t>
+          <t>2026-10-08T00:18:14Z</t>
         </is>
       </c>
     </row>
@@ -6236,7 +6236,7 @@
       </c>
       <c r="K121" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:47Z</t>
+          <t>2026-10-08T00:18:14Z</t>
         </is>
       </c>
     </row>
@@ -6285,7 +6285,7 @@
       </c>
       <c r="K122" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:47Z</t>
+          <t>2026-10-08T00:18:14Z</t>
         </is>
       </c>
     </row>
@@ -6334,7 +6334,7 @@
       </c>
       <c r="K123" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:47Z</t>
+          <t>2026-10-08T00:18:14Z</t>
         </is>
       </c>
     </row>
@@ -6383,7 +6383,7 @@
       </c>
       <c r="K124" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:47Z</t>
+          <t>2026-10-08T00:18:14Z</t>
         </is>
       </c>
     </row>
@@ -6432,7 +6432,7 @@
       </c>
       <c r="K125" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:47Z</t>
+          <t>2026-10-08T00:18:14Z</t>
         </is>
       </c>
     </row>
@@ -6481,7 +6481,7 @@
       </c>
       <c r="K126" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:47Z</t>
+          <t>2026-10-08T00:18:14Z</t>
         </is>
       </c>
     </row>
@@ -6530,7 +6530,7 @@
       </c>
       <c r="K127" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:47Z</t>
+          <t>2026-10-08T00:18:14Z</t>
         </is>
       </c>
     </row>
@@ -6579,7 +6579,7 @@
       </c>
       <c r="K128" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:47Z</t>
+          <t>2026-10-08T00:18:14Z</t>
         </is>
       </c>
     </row>
@@ -6628,7 +6628,7 @@
       </c>
       <c r="K129" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:47Z</t>
+          <t>2026-10-08T00:18:14Z</t>
         </is>
       </c>
     </row>
@@ -6677,7 +6677,7 @@
       </c>
       <c r="K130" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:47Z</t>
+          <t>2026-10-08T00:18:14Z</t>
         </is>
       </c>
     </row>
@@ -6726,7 +6726,7 @@
       </c>
       <c r="K131" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:47Z</t>
+          <t>2026-10-08T00:18:14Z</t>
         </is>
       </c>
     </row>
@@ -6775,7 +6775,7 @@
       </c>
       <c r="K132" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:47Z</t>
+          <t>2026-10-08T00:18:14Z</t>
         </is>
       </c>
     </row>
@@ -6824,7 +6824,7 @@
       </c>
       <c r="K133" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:47Z</t>
+          <t>2026-10-08T00:18:14Z</t>
         </is>
       </c>
     </row>
@@ -6873,7 +6873,7 @@
       </c>
       <c r="K134" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:47Z</t>
+          <t>2026-10-08T00:18:14Z</t>
         </is>
       </c>
     </row>
@@ -6922,7 +6922,7 @@
       </c>
       <c r="K135" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:47Z</t>
+          <t>2026-10-08T00:18:14Z</t>
         </is>
       </c>
     </row>
@@ -6971,7 +6971,7 @@
       </c>
       <c r="K136" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:47Z</t>
+          <t>2026-10-08T00:18:14Z</t>
         </is>
       </c>
     </row>
@@ -7020,7 +7020,7 @@
       </c>
       <c r="K137" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:47Z</t>
+          <t>2026-10-08T00:18:14Z</t>
         </is>
       </c>
     </row>
@@ -7069,7 +7069,7 @@
       </c>
       <c r="K138" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:47Z</t>
+          <t>2026-10-08T00:18:14Z</t>
         </is>
       </c>
     </row>
@@ -7118,7 +7118,7 @@
       </c>
       <c r="K139" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:47Z</t>
+          <t>2026-10-08T00:18:14Z</t>
         </is>
       </c>
     </row>
@@ -7167,7 +7167,7 @@
       </c>
       <c r="K140" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:47Z</t>
+          <t>2026-10-08T00:18:14Z</t>
         </is>
       </c>
     </row>
@@ -7216,7 +7216,7 @@
       </c>
       <c r="K141" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:47Z</t>
+          <t>2026-10-08T00:18:14Z</t>
         </is>
       </c>
     </row>
@@ -7265,7 +7265,7 @@
       </c>
       <c r="K142" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:47Z</t>
+          <t>2026-10-08T00:18:14Z</t>
         </is>
       </c>
     </row>
@@ -7314,7 +7314,7 @@
       </c>
       <c r="K143" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:47Z</t>
+          <t>2026-10-08T00:18:14Z</t>
         </is>
       </c>
     </row>
@@ -7363,7 +7363,7 @@
       </c>
       <c r="K144" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:47Z</t>
+          <t>2026-10-08T00:18:14Z</t>
         </is>
       </c>
     </row>
@@ -7412,7 +7412,7 @@
       </c>
       <c r="K145" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:47Z</t>
+          <t>2026-10-08T00:18:14Z</t>
         </is>
       </c>
     </row>
@@ -7461,7 +7461,7 @@
       </c>
       <c r="K146" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:47Z</t>
+          <t>2026-10-08T00:18:14Z</t>
         </is>
       </c>
     </row>
@@ -7510,7 +7510,7 @@
       </c>
       <c r="K147" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:47Z</t>
+          <t>2026-10-08T00:18:14Z</t>
         </is>
       </c>
     </row>
@@ -7559,7 +7559,7 @@
       </c>
       <c r="K148" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:47Z</t>
+          <t>2026-10-08T00:18:14Z</t>
         </is>
       </c>
     </row>
@@ -7608,7 +7608,7 @@
       </c>
       <c r="K149" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:47Z</t>
+          <t>2026-10-08T00:18:14Z</t>
         </is>
       </c>
     </row>
@@ -7657,7 +7657,7 @@
       </c>
       <c r="K150" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:47Z</t>
+          <t>2026-10-08T00:18:14Z</t>
         </is>
       </c>
     </row>
@@ -7706,7 +7706,7 @@
       </c>
       <c r="K151" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:47Z</t>
+          <t>2026-10-08T00:18:14Z</t>
         </is>
       </c>
     </row>
@@ -7755,7 +7755,7 @@
       </c>
       <c r="K152" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:47Z</t>
+          <t>2026-10-08T00:18:14Z</t>
         </is>
       </c>
     </row>
@@ -7804,7 +7804,7 @@
       </c>
       <c r="K153" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:47Z</t>
+          <t>2026-10-08T00:18:14Z</t>
         </is>
       </c>
     </row>
@@ -7853,7 +7853,7 @@
       </c>
       <c r="K154" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:47Z</t>
+          <t>2026-10-08T00:18:14Z</t>
         </is>
       </c>
     </row>
@@ -7902,7 +7902,7 @@
       </c>
       <c r="K155" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:47Z</t>
+          <t>2026-10-08T00:18:14Z</t>
         </is>
       </c>
     </row>
@@ -7951,7 +7951,7 @@
       </c>
       <c r="K156" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:47Z</t>
+          <t>2026-10-08T00:18:14Z</t>
         </is>
       </c>
     </row>
@@ -8000,7 +8000,7 @@
       </c>
       <c r="K157" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:47Z</t>
+          <t>2026-10-08T00:18:14Z</t>
         </is>
       </c>
     </row>
@@ -8049,7 +8049,7 @@
       </c>
       <c r="K158" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:47Z</t>
+          <t>2026-10-08T00:18:14Z</t>
         </is>
       </c>
     </row>
@@ -8098,7 +8098,7 @@
       </c>
       <c r="K159" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:47Z</t>
+          <t>2026-10-08T00:18:14Z</t>
         </is>
       </c>
     </row>
@@ -8147,7 +8147,7 @@
       </c>
       <c r="K160" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:47Z</t>
+          <t>2026-10-08T00:18:14Z</t>
         </is>
       </c>
     </row>
@@ -8196,7 +8196,7 @@
       </c>
       <c r="K161" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:47Z</t>
+          <t>2026-10-08T00:18:14Z</t>
         </is>
       </c>
     </row>
@@ -8245,7 +8245,7 @@
       </c>
       <c r="K162" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:47Z</t>
+          <t>2026-10-08T00:18:14Z</t>
         </is>
       </c>
     </row>
@@ -8294,7 +8294,7 @@
       </c>
       <c r="K163" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:47Z</t>
+          <t>2026-10-08T00:18:14Z</t>
         </is>
       </c>
     </row>
@@ -8343,7 +8343,7 @@
       </c>
       <c r="K164" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:47Z</t>
+          <t>2026-10-08T00:18:14Z</t>
         </is>
       </c>
     </row>
@@ -8392,7 +8392,7 @@
       </c>
       <c r="K165" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:47Z</t>
+          <t>2026-10-08T00:18:14Z</t>
         </is>
       </c>
     </row>
@@ -8441,7 +8441,7 @@
       </c>
       <c r="K166" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:47Z</t>
+          <t>2026-10-08T00:18:14Z</t>
         </is>
       </c>
     </row>
@@ -8490,7 +8490,7 @@
       </c>
       <c r="K167" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:47Z</t>
+          <t>2026-10-08T00:18:14Z</t>
         </is>
       </c>
     </row>
@@ -8539,7 +8539,7 @@
       </c>
       <c r="K168" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:47Z</t>
+          <t>2026-10-08T00:18:14Z</t>
         </is>
       </c>
     </row>
@@ -8588,7 +8588,7 @@
       </c>
       <c r="K169" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:47Z</t>
+          <t>2026-10-08T00:18:14Z</t>
         </is>
       </c>
     </row>
@@ -8637,7 +8637,7 @@
       </c>
       <c r="K170" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:47Z</t>
+          <t>2026-10-08T00:18:14Z</t>
         </is>
       </c>
     </row>
@@ -8686,7 +8686,7 @@
       </c>
       <c r="K171" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:47Z</t>
+          <t>2026-10-08T00:18:14Z</t>
         </is>
       </c>
     </row>
@@ -8735,7 +8735,7 @@
       </c>
       <c r="K172" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:47Z</t>
+          <t>2026-10-08T00:18:14Z</t>
         </is>
       </c>
     </row>
@@ -8784,7 +8784,7 @@
       </c>
       <c r="K173" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:47Z</t>
+          <t>2026-10-08T00:18:14Z</t>
         </is>
       </c>
     </row>
@@ -8833,7 +8833,7 @@
       </c>
       <c r="K174" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:47Z</t>
+          <t>2026-10-08T00:18:14Z</t>
         </is>
       </c>
     </row>
@@ -8882,7 +8882,7 @@
       </c>
       <c r="K175" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:47Z</t>
+          <t>2026-10-08T00:18:14Z</t>
         </is>
       </c>
     </row>
@@ -8931,7 +8931,7 @@
       </c>
       <c r="K176" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:47Z</t>
+          <t>2026-10-08T00:18:14Z</t>
         </is>
       </c>
     </row>
@@ -8980,7 +8980,7 @@
       </c>
       <c r="K177" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:47Z</t>
+          <t>2026-10-08T00:18:14Z</t>
         </is>
       </c>
     </row>
@@ -9029,7 +9029,7 @@
       </c>
       <c r="K178" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:47Z</t>
+          <t>2026-10-08T00:18:14Z</t>
         </is>
       </c>
     </row>
@@ -9078,7 +9078,7 @@
       </c>
       <c r="K179" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:47Z</t>
+          <t>2026-10-08T00:18:14Z</t>
         </is>
       </c>
     </row>
@@ -9127,7 +9127,7 @@
       </c>
       <c r="K180" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:47Z</t>
+          <t>2026-10-08T00:18:14Z</t>
         </is>
       </c>
     </row>
@@ -9176,7 +9176,7 @@
       </c>
       <c r="K181" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:47Z</t>
+          <t>2026-10-08T00:18:14Z</t>
         </is>
       </c>
     </row>
@@ -9225,7 +9225,7 @@
       </c>
       <c r="K182" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:47Z</t>
+          <t>2026-10-08T00:18:14Z</t>
         </is>
       </c>
     </row>
@@ -9274,7 +9274,7 @@
       </c>
       <c r="K183" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:47Z</t>
+          <t>2026-10-08T00:18:14Z</t>
         </is>
       </c>
     </row>
@@ -9323,7 +9323,7 @@
       </c>
       <c r="K184" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:47Z</t>
+          <t>2026-10-08T00:18:14Z</t>
         </is>
       </c>
     </row>
@@ -9372,7 +9372,7 @@
       </c>
       <c r="K185" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:47Z</t>
+          <t>2026-10-08T00:18:14Z</t>
         </is>
       </c>
     </row>
@@ -9421,7 +9421,7 @@
       </c>
       <c r="K186" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:47Z</t>
+          <t>2026-10-08T00:18:14Z</t>
         </is>
       </c>
     </row>
@@ -9470,7 +9470,7 @@
       </c>
       <c r="K187" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:47Z</t>
+          <t>2026-10-08T00:18:14Z</t>
         </is>
       </c>
     </row>
@@ -9519,7 +9519,7 @@
       </c>
       <c r="K188" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:47Z</t>
+          <t>2026-10-08T00:18:14Z</t>
         </is>
       </c>
     </row>
@@ -9568,7 +9568,7 @@
       </c>
       <c r="K189" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:47Z</t>
+          <t>2026-10-08T00:18:14Z</t>
         </is>
       </c>
     </row>
@@ -9617,7 +9617,7 @@
       </c>
       <c r="K190" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:47Z</t>
+          <t>2026-10-08T00:18:14Z</t>
         </is>
       </c>
     </row>
@@ -9666,7 +9666,7 @@
       </c>
       <c r="K191" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:47Z</t>
+          <t>2026-10-08T00:18:14Z</t>
         </is>
       </c>
     </row>
@@ -9715,7 +9715,7 @@
       </c>
       <c r="K192" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:47Z</t>
+          <t>2026-10-08T00:18:14Z</t>
         </is>
       </c>
     </row>
@@ -9764,7 +9764,7 @@
       </c>
       <c r="K193" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:47Z</t>
+          <t>2026-10-08T00:18:14Z</t>
         </is>
       </c>
     </row>
@@ -9813,7 +9813,7 @@
       </c>
       <c r="K194" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:47Z</t>
+          <t>2026-10-08T00:18:14Z</t>
         </is>
       </c>
     </row>
@@ -9862,7 +9862,7 @@
       </c>
       <c r="K195" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:47Z</t>
+          <t>2026-10-08T00:18:14Z</t>
         </is>
       </c>
     </row>
@@ -9911,7 +9911,7 @@
       </c>
       <c r="K196" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:47Z</t>
+          <t>2026-10-08T00:18:14Z</t>
         </is>
       </c>
     </row>
@@ -9960,7 +9960,7 @@
       </c>
       <c r="K197" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:47Z</t>
+          <t>2026-10-08T00:18:14Z</t>
         </is>
       </c>
     </row>
@@ -10009,7 +10009,7 @@
       </c>
       <c r="K198" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:47Z</t>
+          <t>2026-10-08T00:18:14Z</t>
         </is>
       </c>
     </row>
@@ -10058,7 +10058,7 @@
       </c>
       <c r="K199" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:47Z</t>
+          <t>2026-10-08T00:18:14Z</t>
         </is>
       </c>
     </row>
@@ -10107,7 +10107,7 @@
       </c>
       <c r="K200" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:47Z</t>
+          <t>2026-10-08T00:18:14Z</t>
         </is>
       </c>
     </row>
@@ -10156,7 +10156,7 @@
       </c>
       <c r="K201" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:47Z</t>
+          <t>2026-10-08T00:18:14Z</t>
         </is>
       </c>
     </row>
@@ -10205,7 +10205,7 @@
       </c>
       <c r="K202" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:47Z</t>
+          <t>2026-10-08T00:18:14Z</t>
         </is>
       </c>
     </row>
@@ -10254,7 +10254,7 @@
       </c>
       <c r="K203" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:47Z</t>
+          <t>2026-10-08T00:18:14Z</t>
         </is>
       </c>
     </row>
@@ -10303,7 +10303,7 @@
       </c>
       <c r="K204" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:47Z</t>
+          <t>2026-10-08T00:18:14Z</t>
         </is>
       </c>
     </row>
@@ -10352,7 +10352,7 @@
       </c>
       <c r="K205" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:47Z</t>
+          <t>2026-10-08T00:18:14Z</t>
         </is>
       </c>
     </row>
@@ -10401,7 +10401,7 @@
       </c>
       <c r="K206" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:47Z</t>
+          <t>2026-10-08T00:18:14Z</t>
         </is>
       </c>
     </row>
@@ -10450,7 +10450,7 @@
       </c>
       <c r="K207" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:47Z</t>
+          <t>2026-10-08T00:18:14Z</t>
         </is>
       </c>
     </row>
@@ -10499,7 +10499,7 @@
       </c>
       <c r="K208" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:47Z</t>
+          <t>2026-10-08T00:18:14Z</t>
         </is>
       </c>
     </row>
@@ -10548,7 +10548,7 @@
       </c>
       <c r="K209" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:47Z</t>
+          <t>2026-10-08T00:18:14Z</t>
         </is>
       </c>
     </row>
@@ -10597,7 +10597,7 @@
       </c>
       <c r="K210" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:47Z</t>
+          <t>2026-10-08T00:18:14Z</t>
         </is>
       </c>
     </row>
@@ -10646,7 +10646,7 @@
       </c>
       <c r="K211" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:47Z</t>
+          <t>2026-10-08T00:18:14Z</t>
         </is>
       </c>
     </row>
@@ -10695,7 +10695,7 @@
       </c>
       <c r="K212" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:47Z</t>
+          <t>2026-10-08T00:18:14Z</t>
         </is>
       </c>
     </row>
@@ -10744,7 +10744,7 @@
       </c>
       <c r="K213" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:47Z</t>
+          <t>2026-10-08T00:18:14Z</t>
         </is>
       </c>
     </row>
@@ -10793,7 +10793,7 @@
       </c>
       <c r="K214" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:47Z</t>
+          <t>2026-10-08T00:18:14Z</t>
         </is>
       </c>
     </row>
@@ -10842,7 +10842,7 @@
       </c>
       <c r="K215" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:47Z</t>
+          <t>2026-10-08T00:18:14Z</t>
         </is>
       </c>
     </row>
@@ -10891,7 +10891,7 @@
       </c>
       <c r="K216" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:47Z</t>
+          <t>2026-10-08T00:18:14Z</t>
         </is>
       </c>
     </row>
@@ -10940,7 +10940,7 @@
       </c>
       <c r="K217" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:47Z</t>
+          <t>2026-10-08T00:18:14Z</t>
         </is>
       </c>
     </row>
@@ -10989,7 +10989,7 @@
       </c>
       <c r="K218" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:47Z</t>
+          <t>2026-10-08T00:18:14Z</t>
         </is>
       </c>
     </row>
@@ -11038,7 +11038,7 @@
       </c>
       <c r="K219" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:47Z</t>
+          <t>2026-10-08T00:18:14Z</t>
         </is>
       </c>
     </row>
@@ -11087,7 +11087,7 @@
       </c>
       <c r="K220" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:47Z</t>
+          <t>2026-10-08T00:18:14Z</t>
         </is>
       </c>
     </row>
@@ -11136,7 +11136,7 @@
       </c>
       <c r="K221" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:47Z</t>
+          <t>2026-10-08T00:18:14Z</t>
         </is>
       </c>
     </row>
@@ -11185,7 +11185,7 @@
       </c>
       <c r="K222" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:47Z</t>
+          <t>2026-10-08T00:18:14Z</t>
         </is>
       </c>
     </row>
@@ -11234,7 +11234,7 @@
       </c>
       <c r="K223" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:47Z</t>
+          <t>2026-10-08T00:18:14Z</t>
         </is>
       </c>
     </row>
@@ -11283,7 +11283,7 @@
       </c>
       <c r="K224" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:47Z</t>
+          <t>2026-10-08T00:18:14Z</t>
         </is>
       </c>
     </row>
@@ -11332,7 +11332,7 @@
       </c>
       <c r="K225" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:47Z</t>
+          <t>2026-10-08T00:18:14Z</t>
         </is>
       </c>
     </row>
@@ -11381,7 +11381,7 @@
       </c>
       <c r="K226" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:47Z</t>
+          <t>2026-10-08T00:18:14Z</t>
         </is>
       </c>
     </row>
@@ -11430,7 +11430,7 @@
       </c>
       <c r="K227" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:47Z</t>
+          <t>2026-10-08T00:18:14Z</t>
         </is>
       </c>
     </row>
@@ -11479,7 +11479,7 @@
       </c>
       <c r="K228" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:47Z</t>
+          <t>2026-10-08T00:18:14Z</t>
         </is>
       </c>
     </row>
@@ -11528,7 +11528,7 @@
       </c>
       <c r="K229" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:47Z</t>
+          <t>2026-10-08T00:18:14Z</t>
         </is>
       </c>
     </row>
@@ -11577,7 +11577,7 @@
       </c>
       <c r="K230" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:47Z</t>
+          <t>2026-10-08T00:18:14Z</t>
         </is>
       </c>
     </row>
@@ -11626,7 +11626,7 @@
       </c>
       <c r="K231" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:47Z</t>
+          <t>2026-10-08T00:18:14Z</t>
         </is>
       </c>
     </row>
@@ -11758,7 +11758,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:47Z</t>
+          <t>2026-10-08T00:18:14Z</t>
         </is>
       </c>
     </row>
@@ -11804,7 +11804,7 @@
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>{"date": "2026-08-01", "year": 2026, "month": 8, "month_name": "Agosto", "index_value": 637409769724325.1, "monthly_variation_pct": 8.9, "unit": "Índice base diciembre 2007=100 y variación mensual %", "frequency": "monthly", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/precios_consumidor/4_5_7_2.xls", "fetched_at": "2026-10-07T19:19:47Z"}</t>
+          <t>{"date": "2026-08-01", "year": 2026, "month": 8, "month_name": "Agosto", "index_value": 637409769724325.1, "monthly_variation_pct": 8.9, "unit": "Índice base diciembre 2007=100 y variación mensual %", "frequency": "monthly", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/precios_consumidor/4_5_7_2.xls", "fetched_at": "2026-10-08T00:18:14Z"}</t>
         </is>
       </c>
     </row>

--- a/assets/data/bcv/excel/ove_bcv_inpc_nacional_mensual.xlsx
+++ b/assets/data/bcv/excel/ove_bcv_inpc_nacional_mensual.xlsx
@@ -650,7 +650,7 @@
       </c>
       <c r="K7" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:14Z</t>
+          <t>2026-10-09T00:32:02Z</t>
         </is>
       </c>
     </row>
@@ -699,7 +699,7 @@
       </c>
       <c r="K8" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:14Z</t>
+          <t>2026-10-09T00:32:02Z</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="K9" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:14Z</t>
+          <t>2026-10-09T00:32:02Z</t>
         </is>
       </c>
     </row>
@@ -797,7 +797,7 @@
       </c>
       <c r="K10" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:14Z</t>
+          <t>2026-10-09T00:32:02Z</t>
         </is>
       </c>
     </row>
@@ -846,7 +846,7 @@
       </c>
       <c r="K11" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:14Z</t>
+          <t>2026-10-09T00:32:02Z</t>
         </is>
       </c>
     </row>
@@ -895,7 +895,7 @@
       </c>
       <c r="K12" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:14Z</t>
+          <t>2026-10-09T00:32:02Z</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="K13" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:14Z</t>
+          <t>2026-10-09T00:32:02Z</t>
         </is>
       </c>
     </row>
@@ -993,7 +993,7 @@
       </c>
       <c r="K14" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:14Z</t>
+          <t>2026-10-09T00:32:02Z</t>
         </is>
       </c>
     </row>
@@ -1042,7 +1042,7 @@
       </c>
       <c r="K15" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:14Z</t>
+          <t>2026-10-09T00:32:02Z</t>
         </is>
       </c>
     </row>
@@ -1091,7 +1091,7 @@
       </c>
       <c r="K16" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:14Z</t>
+          <t>2026-10-09T00:32:02Z</t>
         </is>
       </c>
     </row>
@@ -1140,7 +1140,7 @@
       </c>
       <c r="K17" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:14Z</t>
+          <t>2026-10-09T00:32:02Z</t>
         </is>
       </c>
     </row>
@@ -1189,7 +1189,7 @@
       </c>
       <c r="K18" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:14Z</t>
+          <t>2026-10-09T00:32:02Z</t>
         </is>
       </c>
     </row>
@@ -1238,7 +1238,7 @@
       </c>
       <c r="K19" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:14Z</t>
+          <t>2026-10-09T00:32:02Z</t>
         </is>
       </c>
     </row>
@@ -1287,7 +1287,7 @@
       </c>
       <c r="K20" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:14Z</t>
+          <t>2026-10-09T00:32:02Z</t>
         </is>
       </c>
     </row>
@@ -1336,7 +1336,7 @@
       </c>
       <c r="K21" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:14Z</t>
+          <t>2026-10-09T00:32:02Z</t>
         </is>
       </c>
     </row>
@@ -1385,7 +1385,7 @@
       </c>
       <c r="K22" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:14Z</t>
+          <t>2026-10-09T00:32:02Z</t>
         </is>
       </c>
     </row>
@@ -1434,7 +1434,7 @@
       </c>
       <c r="K23" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:14Z</t>
+          <t>2026-10-09T00:32:02Z</t>
         </is>
       </c>
     </row>
@@ -1483,7 +1483,7 @@
       </c>
       <c r="K24" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:14Z</t>
+          <t>2026-10-09T00:32:02Z</t>
         </is>
       </c>
     </row>
@@ -1532,7 +1532,7 @@
       </c>
       <c r="K25" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:14Z</t>
+          <t>2026-10-09T00:32:02Z</t>
         </is>
       </c>
     </row>
@@ -1581,7 +1581,7 @@
       </c>
       <c r="K26" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:14Z</t>
+          <t>2026-10-09T00:32:02Z</t>
         </is>
       </c>
     </row>
@@ -1630,7 +1630,7 @@
       </c>
       <c r="K27" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:14Z</t>
+          <t>2026-10-09T00:32:02Z</t>
         </is>
       </c>
     </row>
@@ -1679,7 +1679,7 @@
       </c>
       <c r="K28" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:14Z</t>
+          <t>2026-10-09T00:32:02Z</t>
         </is>
       </c>
     </row>
@@ -1728,7 +1728,7 @@
       </c>
       <c r="K29" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:14Z</t>
+          <t>2026-10-09T00:32:02Z</t>
         </is>
       </c>
     </row>
@@ -1777,7 +1777,7 @@
       </c>
       <c r="K30" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:14Z</t>
+          <t>2026-10-09T00:32:02Z</t>
         </is>
       </c>
     </row>
@@ -1826,7 +1826,7 @@
       </c>
       <c r="K31" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:14Z</t>
+          <t>2026-10-09T00:32:02Z</t>
         </is>
       </c>
     </row>
@@ -1875,7 +1875,7 @@
       </c>
       <c r="K32" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:14Z</t>
+          <t>2026-10-09T00:32:02Z</t>
         </is>
       </c>
     </row>
@@ -1924,7 +1924,7 @@
       </c>
       <c r="K33" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:14Z</t>
+          <t>2026-10-09T00:32:02Z</t>
         </is>
       </c>
     </row>
@@ -1973,7 +1973,7 @@
       </c>
       <c r="K34" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:14Z</t>
+          <t>2026-10-09T00:32:02Z</t>
         </is>
       </c>
     </row>
@@ -2022,7 +2022,7 @@
       </c>
       <c r="K35" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:14Z</t>
+          <t>2026-10-09T00:32:02Z</t>
         </is>
       </c>
     </row>
@@ -2071,7 +2071,7 @@
       </c>
       <c r="K36" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:14Z</t>
+          <t>2026-10-09T00:32:02Z</t>
         </is>
       </c>
     </row>
@@ -2120,7 +2120,7 @@
       </c>
       <c r="K37" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:14Z</t>
+          <t>2026-10-09T00:32:02Z</t>
         </is>
       </c>
     </row>
@@ -2169,7 +2169,7 @@
       </c>
       <c r="K38" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:14Z</t>
+          <t>2026-10-09T00:32:02Z</t>
         </is>
       </c>
     </row>
@@ -2218,7 +2218,7 @@
       </c>
       <c r="K39" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:14Z</t>
+          <t>2026-10-09T00:32:02Z</t>
         </is>
       </c>
     </row>
@@ -2267,7 +2267,7 @@
       </c>
       <c r="K40" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:14Z</t>
+          <t>2026-10-09T00:32:02Z</t>
         </is>
       </c>
     </row>
@@ -2316,7 +2316,7 @@
       </c>
       <c r="K41" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:14Z</t>
+          <t>2026-10-09T00:32:02Z</t>
         </is>
       </c>
     </row>
@@ -2365,7 +2365,7 @@
       </c>
       <c r="K42" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:14Z</t>
+          <t>2026-10-09T00:32:02Z</t>
         </is>
       </c>
     </row>
@@ -2414,7 +2414,7 @@
       </c>
       <c r="K43" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:14Z</t>
+          <t>2026-10-09T00:32:02Z</t>
         </is>
       </c>
     </row>
@@ -2463,7 +2463,7 @@
       </c>
       <c r="K44" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:14Z</t>
+          <t>2026-10-09T00:32:02Z</t>
         </is>
       </c>
     </row>
@@ -2512,7 +2512,7 @@
       </c>
       <c r="K45" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:14Z</t>
+          <t>2026-10-09T00:32:02Z</t>
         </is>
       </c>
     </row>
@@ -2561,7 +2561,7 @@
       </c>
       <c r="K46" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:14Z</t>
+          <t>2026-10-09T00:32:02Z</t>
         </is>
       </c>
     </row>
@@ -2610,7 +2610,7 @@
       </c>
       <c r="K47" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:14Z</t>
+          <t>2026-10-09T00:32:02Z</t>
         </is>
       </c>
     </row>
@@ -2659,7 +2659,7 @@
       </c>
       <c r="K48" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:14Z</t>
+          <t>2026-10-09T00:32:02Z</t>
         </is>
       </c>
     </row>
@@ -2708,7 +2708,7 @@
       </c>
       <c r="K49" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:14Z</t>
+          <t>2026-10-09T00:32:02Z</t>
         </is>
       </c>
     </row>
@@ -2757,7 +2757,7 @@
       </c>
       <c r="K50" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:14Z</t>
+          <t>2026-10-09T00:32:02Z</t>
         </is>
       </c>
     </row>
@@ -2806,7 +2806,7 @@
       </c>
       <c r="K51" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:14Z</t>
+          <t>2026-10-09T00:32:02Z</t>
         </is>
       </c>
     </row>
@@ -2855,7 +2855,7 @@
       </c>
       <c r="K52" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:14Z</t>
+          <t>2026-10-09T00:32:02Z</t>
         </is>
       </c>
     </row>
@@ -2904,7 +2904,7 @@
       </c>
       <c r="K53" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:14Z</t>
+          <t>2026-10-09T00:32:02Z</t>
         </is>
       </c>
     </row>
@@ -2953,7 +2953,7 @@
       </c>
       <c r="K54" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:14Z</t>
+          <t>2026-10-09T00:32:02Z</t>
         </is>
       </c>
     </row>
@@ -3002,7 +3002,7 @@
       </c>
       <c r="K55" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:14Z</t>
+          <t>2026-10-09T00:32:02Z</t>
         </is>
       </c>
     </row>
@@ -3051,7 +3051,7 @@
       </c>
       <c r="K56" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:14Z</t>
+          <t>2026-10-09T00:32:02Z</t>
         </is>
       </c>
     </row>
@@ -3100,7 +3100,7 @@
       </c>
       <c r="K57" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:14Z</t>
+          <t>2026-10-09T00:32:02Z</t>
         </is>
       </c>
     </row>
@@ -3149,7 +3149,7 @@
       </c>
       <c r="K58" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:14Z</t>
+          <t>2026-10-09T00:32:02Z</t>
         </is>
       </c>
     </row>
@@ -3198,7 +3198,7 @@
       </c>
       <c r="K59" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:14Z</t>
+          <t>2026-10-09T00:32:02Z</t>
         </is>
       </c>
     </row>
@@ -3247,7 +3247,7 @@
       </c>
       <c r="K60" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:14Z</t>
+          <t>2026-10-09T00:32:02Z</t>
         </is>
       </c>
     </row>
@@ -3296,7 +3296,7 @@
       </c>
       <c r="K61" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:14Z</t>
+          <t>2026-10-09T00:32:02Z</t>
         </is>
       </c>
     </row>
@@ -3345,7 +3345,7 @@
       </c>
       <c r="K62" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:14Z</t>
+          <t>2026-10-09T00:32:02Z</t>
         </is>
       </c>
     </row>
@@ -3394,7 +3394,7 @@
       </c>
       <c r="K63" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:14Z</t>
+          <t>2026-10-09T00:32:02Z</t>
         </is>
       </c>
     </row>
@@ -3443,7 +3443,7 @@
       </c>
       <c r="K64" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:14Z</t>
+          <t>2026-10-09T00:32:02Z</t>
         </is>
       </c>
     </row>
@@ -3492,7 +3492,7 @@
       </c>
       <c r="K65" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:14Z</t>
+          <t>2026-10-09T00:32:02Z</t>
         </is>
       </c>
     </row>
@@ -3541,7 +3541,7 @@
       </c>
       <c r="K66" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:14Z</t>
+          <t>2026-10-09T00:32:02Z</t>
         </is>
       </c>
     </row>
@@ -3590,7 +3590,7 @@
       </c>
       <c r="K67" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:14Z</t>
+          <t>2026-10-09T00:32:02Z</t>
         </is>
       </c>
     </row>
@@ -3639,7 +3639,7 @@
       </c>
       <c r="K68" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:14Z</t>
+          <t>2026-10-09T00:32:02Z</t>
         </is>
       </c>
     </row>
@@ -3688,7 +3688,7 @@
       </c>
       <c r="K69" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:14Z</t>
+          <t>2026-10-09T00:32:02Z</t>
         </is>
       </c>
     </row>
@@ -3737,7 +3737,7 @@
       </c>
       <c r="K70" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:14Z</t>
+          <t>2026-10-09T00:32:02Z</t>
         </is>
       </c>
     </row>
@@ -3786,7 +3786,7 @@
       </c>
       <c r="K71" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:14Z</t>
+          <t>2026-10-09T00:32:02Z</t>
         </is>
       </c>
     </row>
@@ -3835,7 +3835,7 @@
       </c>
       <c r="K72" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:14Z</t>
+          <t>2026-10-09T00:32:02Z</t>
         </is>
       </c>
     </row>
@@ -3884,7 +3884,7 @@
       </c>
       <c r="K73" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:14Z</t>
+          <t>2026-10-09T00:32:02Z</t>
         </is>
       </c>
     </row>
@@ -3933,7 +3933,7 @@
       </c>
       <c r="K74" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:14Z</t>
+          <t>2026-10-09T00:32:02Z</t>
         </is>
       </c>
     </row>
@@ -3982,7 +3982,7 @@
       </c>
       <c r="K75" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:14Z</t>
+          <t>2026-10-09T00:32:02Z</t>
         </is>
       </c>
     </row>
@@ -4031,7 +4031,7 @@
       </c>
       <c r="K76" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:14Z</t>
+          <t>2026-10-09T00:32:02Z</t>
         </is>
       </c>
     </row>
@@ -4080,7 +4080,7 @@
       </c>
       <c r="K77" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:14Z</t>
+          <t>2026-10-09T00:32:02Z</t>
         </is>
       </c>
     </row>
@@ -4129,7 +4129,7 @@
       </c>
       <c r="K78" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:14Z</t>
+          <t>2026-10-09T00:32:02Z</t>
         </is>
       </c>
     </row>
@@ -4178,7 +4178,7 @@
       </c>
       <c r="K79" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:14Z</t>
+          <t>2026-10-09T00:32:02Z</t>
         </is>
       </c>
     </row>
@@ -4227,7 +4227,7 @@
       </c>
       <c r="K80" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:14Z</t>
+          <t>2026-10-09T00:32:02Z</t>
         </is>
       </c>
     </row>
@@ -4276,7 +4276,7 @@
       </c>
       <c r="K81" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:14Z</t>
+          <t>2026-10-09T00:32:02Z</t>
         </is>
       </c>
     </row>
@@ -4325,7 +4325,7 @@
       </c>
       <c r="K82" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:14Z</t>
+          <t>2026-10-09T00:32:02Z</t>
         </is>
       </c>
     </row>
@@ -4374,7 +4374,7 @@
       </c>
       <c r="K83" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:14Z</t>
+          <t>2026-10-09T00:32:02Z</t>
         </is>
       </c>
     </row>
@@ -4423,7 +4423,7 @@
       </c>
       <c r="K84" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:14Z</t>
+          <t>2026-10-09T00:32:02Z</t>
         </is>
       </c>
     </row>
@@ -4472,7 +4472,7 @@
       </c>
       <c r="K85" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:14Z</t>
+          <t>2026-10-09T00:32:02Z</t>
         </is>
       </c>
     </row>
@@ -4521,7 +4521,7 @@
       </c>
       <c r="K86" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:14Z</t>
+          <t>2026-10-09T00:32:02Z</t>
         </is>
       </c>
     </row>
@@ -4570,7 +4570,7 @@
       </c>
       <c r="K87" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:14Z</t>
+          <t>2026-10-09T00:32:02Z</t>
         </is>
       </c>
     </row>
@@ -4619,7 +4619,7 @@
       </c>
       <c r="K88" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:14Z</t>
+          <t>2026-10-09T00:32:02Z</t>
         </is>
       </c>
     </row>
@@ -4668,7 +4668,7 @@
       </c>
       <c r="K89" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:14Z</t>
+          <t>2026-10-09T00:32:02Z</t>
         </is>
       </c>
     </row>
@@ -4717,7 +4717,7 @@
       </c>
       <c r="K90" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:14Z</t>
+          <t>2026-10-09T00:32:02Z</t>
         </is>
       </c>
     </row>
@@ -4766,7 +4766,7 @@
       </c>
       <c r="K91" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:14Z</t>
+          <t>2026-10-09T00:32:02Z</t>
         </is>
       </c>
     </row>
@@ -4815,7 +4815,7 @@
       </c>
       <c r="K92" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:14Z</t>
+          <t>2026-10-09T00:32:02Z</t>
         </is>
       </c>
     </row>
@@ -4864,7 +4864,7 @@
       </c>
       <c r="K93" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:14Z</t>
+          <t>2026-10-09T00:32:02Z</t>
         </is>
       </c>
     </row>
@@ -4913,7 +4913,7 @@
       </c>
       <c r="K94" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:14Z</t>
+          <t>2026-10-09T00:32:02Z</t>
         </is>
       </c>
     </row>
@@ -4962,7 +4962,7 @@
       </c>
       <c r="K95" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:14Z</t>
+          <t>2026-10-09T00:32:02Z</t>
         </is>
       </c>
     </row>
@@ -5011,7 +5011,7 @@
       </c>
       <c r="K96" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:14Z</t>
+          <t>2026-10-09T00:32:02Z</t>
         </is>
       </c>
     </row>
@@ -5060,7 +5060,7 @@
       </c>
       <c r="K97" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:14Z</t>
+          <t>2026-10-09T00:32:02Z</t>
         </is>
       </c>
     </row>
@@ -5109,7 +5109,7 @@
       </c>
       <c r="K98" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:14Z</t>
+          <t>2026-10-09T00:32:02Z</t>
         </is>
       </c>
     </row>
@@ -5158,7 +5158,7 @@
       </c>
       <c r="K99" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:14Z</t>
+          <t>2026-10-09T00:32:02Z</t>
         </is>
       </c>
     </row>
@@ -5207,7 +5207,7 @@
       </c>
       <c r="K100" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:14Z</t>
+          <t>2026-10-09T00:32:02Z</t>
         </is>
       </c>
     </row>
@@ -5256,7 +5256,7 @@
       </c>
       <c r="K101" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:14Z</t>
+          <t>2026-10-09T00:32:02Z</t>
         </is>
       </c>
     </row>
@@ -5305,7 +5305,7 @@
       </c>
       <c r="K102" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:14Z</t>
+          <t>2026-10-09T00:32:02Z</t>
         </is>
       </c>
     </row>
@@ -5354,7 +5354,7 @@
       </c>
       <c r="K103" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:14Z</t>
+          <t>2026-10-09T00:32:02Z</t>
         </is>
       </c>
     </row>
@@ -5403,7 +5403,7 @@
       </c>
       <c r="K104" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:14Z</t>
+          <t>2026-10-09T00:32:02Z</t>
         </is>
       </c>
     </row>
@@ -5452,7 +5452,7 @@
       </c>
       <c r="K105" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:14Z</t>
+          <t>2026-10-09T00:32:02Z</t>
         </is>
       </c>
     </row>
@@ -5501,7 +5501,7 @@
       </c>
       <c r="K106" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:14Z</t>
+          <t>2026-10-09T00:32:02Z</t>
         </is>
       </c>
     </row>
@@ -5550,7 +5550,7 @@
       </c>
       <c r="K107" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:14Z</t>
+          <t>2026-10-09T00:32:02Z</t>
         </is>
       </c>
     </row>
@@ -5599,7 +5599,7 @@
       </c>
       <c r="K108" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:14Z</t>
+          <t>2026-10-09T00:32:02Z</t>
         </is>
       </c>
     </row>
@@ -5648,7 +5648,7 @@
       </c>
       <c r="K109" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:14Z</t>
+          <t>2026-10-09T00:32:02Z</t>
         </is>
       </c>
     </row>
@@ -5697,7 +5697,7 @@
       </c>
       <c r="K110" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:14Z</t>
+          <t>2026-10-09T00:32:02Z</t>
         </is>
       </c>
     </row>
@@ -5746,7 +5746,7 @@
       </c>
       <c r="K111" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:14Z</t>
+          <t>2026-10-09T00:32:02Z</t>
         </is>
       </c>
     </row>
@@ -5795,7 +5795,7 @@
       </c>
       <c r="K112" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:14Z</t>
+          <t>2026-10-09T00:32:02Z</t>
         </is>
       </c>
     </row>
@@ -5844,7 +5844,7 @@
       </c>
       <c r="K113" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:14Z</t>
+          <t>2026-10-09T00:32:02Z</t>
         </is>
       </c>
     </row>
@@ -5893,7 +5893,7 @@
       </c>
       <c r="K114" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:14Z</t>
+          <t>2026-10-09T00:32:02Z</t>
         </is>
       </c>
     </row>
@@ -5942,7 +5942,7 @@
       </c>
       <c r="K115" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:14Z</t>
+          <t>2026-10-09T00:32:02Z</t>
         </is>
       </c>
     </row>
@@ -5991,7 +5991,7 @@
       </c>
       <c r="K116" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:14Z</t>
+          <t>2026-10-09T00:32:02Z</t>
         </is>
       </c>
     </row>
@@ -6040,7 +6040,7 @@
       </c>
       <c r="K117" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:14Z</t>
+          <t>2026-10-09T00:32:02Z</t>
         </is>
       </c>
     </row>
@@ -6089,7 +6089,7 @@
       </c>
       <c r="K118" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:14Z</t>
+          <t>2026-10-09T00:32:02Z</t>
         </is>
       </c>
     </row>
@@ -6138,7 +6138,7 @@
       </c>
       <c r="K119" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:14Z</t>
+          <t>2026-10-09T00:32:02Z</t>
         </is>
       </c>
     </row>
@@ -6187,7 +6187,7 @@
       </c>
       <c r="K120" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:14Z</t>
+          <t>2026-10-09T00:32:02Z</t>
         </is>
       </c>
     </row>
@@ -6236,7 +6236,7 @@
       </c>
       <c r="K121" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:14Z</t>
+          <t>2026-10-09T00:32:02Z</t>
         </is>
       </c>
     </row>
@@ -6285,7 +6285,7 @@
       </c>
       <c r="K122" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:14Z</t>
+          <t>2026-10-09T00:32:02Z</t>
         </is>
       </c>
     </row>
@@ -6334,7 +6334,7 @@
       </c>
       <c r="K123" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:14Z</t>
+          <t>2026-10-09T00:32:02Z</t>
         </is>
       </c>
     </row>
@@ -6383,7 +6383,7 @@
       </c>
       <c r="K124" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:14Z</t>
+          <t>2026-10-09T00:32:02Z</t>
         </is>
       </c>
     </row>
@@ -6432,7 +6432,7 @@
       </c>
       <c r="K125" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:14Z</t>
+          <t>2026-10-09T00:32:02Z</t>
         </is>
       </c>
     </row>
@@ -6481,7 +6481,7 @@
       </c>
       <c r="K126" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:14Z</t>
+          <t>2026-10-09T00:32:02Z</t>
         </is>
       </c>
     </row>
@@ -6530,7 +6530,7 @@
       </c>
       <c r="K127" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:14Z</t>
+          <t>2026-10-09T00:32:02Z</t>
         </is>
       </c>
     </row>
@@ -6579,7 +6579,7 @@
       </c>
       <c r="K128" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:14Z</t>
+          <t>2026-10-09T00:32:02Z</t>
         </is>
       </c>
     </row>
@@ -6628,7 +6628,7 @@
       </c>
       <c r="K129" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:14Z</t>
+          <t>2026-10-09T00:32:02Z</t>
         </is>
       </c>
     </row>
@@ -6677,7 +6677,7 @@
       </c>
       <c r="K130" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:14Z</t>
+          <t>2026-10-09T00:32:02Z</t>
         </is>
       </c>
     </row>
@@ -6726,7 +6726,7 @@
       </c>
       <c r="K131" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:14Z</t>
+          <t>2026-10-09T00:32:02Z</t>
         </is>
       </c>
     </row>
@@ -6775,7 +6775,7 @@
       </c>
       <c r="K132" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:14Z</t>
+          <t>2026-10-09T00:32:02Z</t>
         </is>
       </c>
     </row>
@@ -6824,7 +6824,7 @@
       </c>
       <c r="K133" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:14Z</t>
+          <t>2026-10-09T00:32:02Z</t>
         </is>
       </c>
     </row>
@@ -6873,7 +6873,7 @@
       </c>
       <c r="K134" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:14Z</t>
+          <t>2026-10-09T00:32:02Z</t>
         </is>
       </c>
     </row>
@@ -6922,7 +6922,7 @@
       </c>
       <c r="K135" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:14Z</t>
+          <t>2026-10-09T00:32:02Z</t>
         </is>
       </c>
     </row>
@@ -6971,7 +6971,7 @@
       </c>
       <c r="K136" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:14Z</t>
+          <t>2026-10-09T00:32:02Z</t>
         </is>
       </c>
     </row>
@@ -7020,7 +7020,7 @@
       </c>
       <c r="K137" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:14Z</t>
+          <t>2026-10-09T00:32:02Z</t>
         </is>
       </c>
     </row>
@@ -7069,7 +7069,7 @@
       </c>
       <c r="K138" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:14Z</t>
+          <t>2026-10-09T00:32:02Z</t>
         </is>
       </c>
     </row>
@@ -7118,7 +7118,7 @@
       </c>
       <c r="K139" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:14Z</t>
+          <t>2026-10-09T00:32:02Z</t>
         </is>
       </c>
     </row>
@@ -7167,7 +7167,7 @@
       </c>
       <c r="K140" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:14Z</t>
+          <t>2026-10-09T00:32:02Z</t>
         </is>
       </c>
     </row>
@@ -7216,7 +7216,7 @@
       </c>
       <c r="K141" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:14Z</t>
+          <t>2026-10-09T00:32:02Z</t>
         </is>
       </c>
     </row>
@@ -7265,7 +7265,7 @@
       </c>
       <c r="K142" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:14Z</t>
+          <t>2026-10-09T00:32:02Z</t>
         </is>
       </c>
     </row>
@@ -7314,7 +7314,7 @@
       </c>
       <c r="K143" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:14Z</t>
+          <t>2026-10-09T00:32:02Z</t>
         </is>
       </c>
     </row>
@@ -7363,7 +7363,7 @@
       </c>
       <c r="K144" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:14Z</t>
+          <t>2026-10-09T00:32:02Z</t>
         </is>
       </c>
     </row>
@@ -7412,7 +7412,7 @@
       </c>
       <c r="K145" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:14Z</t>
+          <t>2026-10-09T00:32:02Z</t>
         </is>
       </c>
     </row>
@@ -7461,7 +7461,7 @@
       </c>
       <c r="K146" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:14Z</t>
+          <t>2026-10-09T00:32:02Z</t>
         </is>
       </c>
     </row>
@@ -7510,7 +7510,7 @@
       </c>
       <c r="K147" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:14Z</t>
+          <t>2026-10-09T00:32:02Z</t>
         </is>
       </c>
     </row>
@@ -7559,7 +7559,7 @@
       </c>
       <c r="K148" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:14Z</t>
+          <t>2026-10-09T00:32:02Z</t>
         </is>
       </c>
     </row>
@@ -7608,7 +7608,7 @@
       </c>
       <c r="K149" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:14Z</t>
+          <t>2026-10-09T00:32:02Z</t>
         </is>
       </c>
     </row>
@@ -7657,7 +7657,7 @@
       </c>
       <c r="K150" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:14Z</t>
+          <t>2026-10-09T00:32:02Z</t>
         </is>
       </c>
     </row>
@@ -7706,7 +7706,7 @@
       </c>
       <c r="K151" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:14Z</t>
+          <t>2026-10-09T00:32:02Z</t>
         </is>
       </c>
     </row>
@@ -7755,7 +7755,7 @@
       </c>
       <c r="K152" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:14Z</t>
+          <t>2026-10-09T00:32:02Z</t>
         </is>
       </c>
     </row>
@@ -7804,7 +7804,7 @@
       </c>
       <c r="K153" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:14Z</t>
+          <t>2026-10-09T00:32:02Z</t>
         </is>
       </c>
     </row>
@@ -7853,7 +7853,7 @@
       </c>
       <c r="K154" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:14Z</t>
+          <t>2026-10-09T00:32:02Z</t>
         </is>
       </c>
     </row>
@@ -7902,7 +7902,7 @@
       </c>
       <c r="K155" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:14Z</t>
+          <t>2026-10-09T00:32:02Z</t>
         </is>
       </c>
     </row>
@@ -7951,7 +7951,7 @@
       </c>
       <c r="K156" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:14Z</t>
+          <t>2026-10-09T00:32:02Z</t>
         </is>
       </c>
     </row>
@@ -8000,7 +8000,7 @@
       </c>
       <c r="K157" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:14Z</t>
+          <t>2026-10-09T00:32:02Z</t>
         </is>
       </c>
     </row>
@@ -8049,7 +8049,7 @@
       </c>
       <c r="K158" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:14Z</t>
+          <t>2026-10-09T00:32:02Z</t>
         </is>
       </c>
     </row>
@@ -8098,7 +8098,7 @@
       </c>
       <c r="K159" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:14Z</t>
+          <t>2026-10-09T00:32:02Z</t>
         </is>
       </c>
     </row>
@@ -8147,7 +8147,7 @@
       </c>
       <c r="K160" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:14Z</t>
+          <t>2026-10-09T00:32:02Z</t>
         </is>
       </c>
     </row>
@@ -8196,7 +8196,7 @@
       </c>
       <c r="K161" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:14Z</t>
+          <t>2026-10-09T00:32:02Z</t>
         </is>
       </c>
     </row>
@@ -8245,7 +8245,7 @@
       </c>
       <c r="K162" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:14Z</t>
+          <t>2026-10-09T00:32:02Z</t>
         </is>
       </c>
     </row>
@@ -8294,7 +8294,7 @@
       </c>
       <c r="K163" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:14Z</t>
+          <t>2026-10-09T00:32:02Z</t>
         </is>
       </c>
     </row>
@@ -8343,7 +8343,7 @@
       </c>
       <c r="K164" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:14Z</t>
+          <t>2026-10-09T00:32:02Z</t>
         </is>
       </c>
     </row>
@@ -8392,7 +8392,7 @@
       </c>
       <c r="K165" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:14Z</t>
+          <t>2026-10-09T00:32:02Z</t>
         </is>
       </c>
     </row>
@@ -8441,7 +8441,7 @@
       </c>
       <c r="K166" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:14Z</t>
+          <t>2026-10-09T00:32:02Z</t>
         </is>
       </c>
     </row>
@@ -8490,7 +8490,7 @@
       </c>
       <c r="K167" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:14Z</t>
+          <t>2026-10-09T00:32:02Z</t>
         </is>
       </c>
     </row>
@@ -8539,7 +8539,7 @@
       </c>
       <c r="K168" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:14Z</t>
+          <t>2026-10-09T00:32:02Z</t>
         </is>
       </c>
     </row>
@@ -8588,7 +8588,7 @@
       </c>
       <c r="K169" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:14Z</t>
+          <t>2026-10-09T00:32:02Z</t>
         </is>
       </c>
     </row>
@@ -8637,7 +8637,7 @@
       </c>
       <c r="K170" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:14Z</t>
+          <t>2026-10-09T00:32:02Z</t>
         </is>
       </c>
     </row>
@@ -8686,7 +8686,7 @@
       </c>
       <c r="K171" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:14Z</t>
+          <t>2026-10-09T00:32:02Z</t>
         </is>
       </c>
     </row>
@@ -8735,7 +8735,7 @@
       </c>
       <c r="K172" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:14Z</t>
+          <t>2026-10-09T00:32:02Z</t>
         </is>
       </c>
     </row>
@@ -8784,7 +8784,7 @@
       </c>
       <c r="K173" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:14Z</t>
+          <t>2026-10-09T00:32:02Z</t>
         </is>
       </c>
     </row>
@@ -8833,7 +8833,7 @@
       </c>
       <c r="K174" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:14Z</t>
+          <t>2026-10-09T00:32:02Z</t>
         </is>
       </c>
     </row>
@@ -8882,7 +8882,7 @@
       </c>
       <c r="K175" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:14Z</t>
+          <t>2026-10-09T00:32:02Z</t>
         </is>
       </c>
     </row>
@@ -8931,7 +8931,7 @@
       </c>
       <c r="K176" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:14Z</t>
+          <t>2026-10-09T00:32:02Z</t>
         </is>
       </c>
     </row>
@@ -8980,7 +8980,7 @@
       </c>
       <c r="K177" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:14Z</t>
+          <t>2026-10-09T00:32:02Z</t>
         </is>
       </c>
     </row>
@@ -9029,7 +9029,7 @@
       </c>
       <c r="K178" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:14Z</t>
+          <t>2026-10-09T00:32:02Z</t>
         </is>
       </c>
     </row>
@@ -9078,7 +9078,7 @@
       </c>
       <c r="K179" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:14Z</t>
+          <t>2026-10-09T00:32:02Z</t>
         </is>
       </c>
     </row>
@@ -9127,7 +9127,7 @@
       </c>
       <c r="K180" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:14Z</t>
+          <t>2026-10-09T00:32:02Z</t>
         </is>
       </c>
     </row>
@@ -9176,7 +9176,7 @@
       </c>
       <c r="K181" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:14Z</t>
+          <t>2026-10-09T00:32:02Z</t>
         </is>
       </c>
     </row>
@@ -9225,7 +9225,7 @@
       </c>
       <c r="K182" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:14Z</t>
+          <t>2026-10-09T00:32:02Z</t>
         </is>
       </c>
     </row>
@@ -9274,7 +9274,7 @@
       </c>
       <c r="K183" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:14Z</t>
+          <t>2026-10-09T00:32:02Z</t>
         </is>
       </c>
     </row>
@@ -9323,7 +9323,7 @@
       </c>
       <c r="K184" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:14Z</t>
+          <t>2026-10-09T00:32:02Z</t>
         </is>
       </c>
     </row>
@@ -9372,7 +9372,7 @@
       </c>
       <c r="K185" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:14Z</t>
+          <t>2026-10-09T00:32:02Z</t>
         </is>
       </c>
     </row>
@@ -9421,7 +9421,7 @@
       </c>
       <c r="K186" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:14Z</t>
+          <t>2026-10-09T00:32:02Z</t>
         </is>
       </c>
     </row>
@@ -9470,7 +9470,7 @@
       </c>
       <c r="K187" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:14Z</t>
+          <t>2026-10-09T00:32:02Z</t>
         </is>
       </c>
     </row>
@@ -9519,7 +9519,7 @@
       </c>
       <c r="K188" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:14Z</t>
+          <t>2026-10-09T00:32:02Z</t>
         </is>
       </c>
     </row>
@@ -9568,7 +9568,7 @@
       </c>
       <c r="K189" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:14Z</t>
+          <t>2026-10-09T00:32:02Z</t>
         </is>
       </c>
     </row>
@@ -9617,7 +9617,7 @@
       </c>
       <c r="K190" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:14Z</t>
+          <t>2026-10-09T00:32:02Z</t>
         </is>
       </c>
     </row>
@@ -9666,7 +9666,7 @@
       </c>
       <c r="K191" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:14Z</t>
+          <t>2026-10-09T00:32:02Z</t>
         </is>
       </c>
     </row>
@@ -9715,7 +9715,7 @@
       </c>
       <c r="K192" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:14Z</t>
+          <t>2026-10-09T00:32:02Z</t>
         </is>
       </c>
     </row>
@@ -9764,7 +9764,7 @@
       </c>
       <c r="K193" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:14Z</t>
+          <t>2026-10-09T00:32:02Z</t>
         </is>
       </c>
     </row>
@@ -9813,7 +9813,7 @@
       </c>
       <c r="K194" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:14Z</t>
+          <t>2026-10-09T00:32:02Z</t>
         </is>
       </c>
     </row>
@@ -9862,7 +9862,7 @@
       </c>
       <c r="K195" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:14Z</t>
+          <t>2026-10-09T00:32:02Z</t>
         </is>
       </c>
     </row>
@@ -9911,7 +9911,7 @@
       </c>
       <c r="K196" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:14Z</t>
+          <t>2026-10-09T00:32:02Z</t>
         </is>
       </c>
     </row>
@@ -9960,7 +9960,7 @@
       </c>
       <c r="K197" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:14Z</t>
+          <t>2026-10-09T00:32:02Z</t>
         </is>
       </c>
     </row>
@@ -10009,7 +10009,7 @@
       </c>
       <c r="K198" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:14Z</t>
+          <t>2026-10-09T00:32:02Z</t>
         </is>
       </c>
     </row>
@@ -10058,7 +10058,7 @@
       </c>
       <c r="K199" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:14Z</t>
+          <t>2026-10-09T00:32:02Z</t>
         </is>
       </c>
     </row>
@@ -10107,7 +10107,7 @@
       </c>
       <c r="K200" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:14Z</t>
+          <t>2026-10-09T00:32:02Z</t>
         </is>
       </c>
     </row>
@@ -10156,7 +10156,7 @@
       </c>
       <c r="K201" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:14Z</t>
+          <t>2026-10-09T00:32:02Z</t>
         </is>
       </c>
     </row>
@@ -10205,7 +10205,7 @@
       </c>
       <c r="K202" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:14Z</t>
+          <t>2026-10-09T00:32:02Z</t>
         </is>
       </c>
     </row>
@@ -10254,7 +10254,7 @@
       </c>
       <c r="K203" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:14Z</t>
+          <t>2026-10-09T00:32:02Z</t>
         </is>
       </c>
     </row>
@@ -10303,7 +10303,7 @@
       </c>
       <c r="K204" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:14Z</t>
+          <t>2026-10-09T00:32:02Z</t>
         </is>
       </c>
     </row>
@@ -10352,7 +10352,7 @@
       </c>
       <c r="K205" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:14Z</t>
+          <t>2026-10-09T00:32:02Z</t>
         </is>
       </c>
     </row>
@@ -10401,7 +10401,7 @@
       </c>
       <c r="K206" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:14Z</t>
+          <t>2026-10-09T00:32:02Z</t>
         </is>
       </c>
     </row>
@@ -10450,7 +10450,7 @@
       </c>
       <c r="K207" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:14Z</t>
+          <t>2026-10-09T00:32:02Z</t>
         </is>
       </c>
     </row>
@@ -10499,7 +10499,7 @@
       </c>
       <c r="K208" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:14Z</t>
+          <t>2026-10-09T00:32:02Z</t>
         </is>
       </c>
     </row>
@@ -10548,7 +10548,7 @@
       </c>
       <c r="K209" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:14Z</t>
+          <t>2026-10-09T00:32:02Z</t>
         </is>
       </c>
     </row>
@@ -10597,7 +10597,7 @@
       </c>
       <c r="K210" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:14Z</t>
+          <t>2026-10-09T00:32:02Z</t>
         </is>
       </c>
     </row>
@@ -10646,7 +10646,7 @@
       </c>
       <c r="K211" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:14Z</t>
+          <t>2026-10-09T00:32:02Z</t>
         </is>
       </c>
     </row>
@@ -10695,7 +10695,7 @@
       </c>
       <c r="K212" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:14Z</t>
+          <t>2026-10-09T00:32:02Z</t>
         </is>
       </c>
     </row>
@@ -10744,7 +10744,7 @@
       </c>
       <c r="K213" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:14Z</t>
+          <t>2026-10-09T00:32:02Z</t>
         </is>
       </c>
     </row>
@@ -10793,7 +10793,7 @@
       </c>
       <c r="K214" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:14Z</t>
+          <t>2026-10-09T00:32:02Z</t>
         </is>
       </c>
     </row>
@@ -10842,7 +10842,7 @@
       </c>
       <c r="K215" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:14Z</t>
+          <t>2026-10-09T00:32:02Z</t>
         </is>
       </c>
     </row>
@@ -10891,7 +10891,7 @@
       </c>
       <c r="K216" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:14Z</t>
+          <t>2026-10-09T00:32:02Z</t>
         </is>
       </c>
     </row>
@@ -10940,7 +10940,7 @@
       </c>
       <c r="K217" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:14Z</t>
+          <t>2026-10-09T00:32:02Z</t>
         </is>
       </c>
     </row>
@@ -10989,7 +10989,7 @@
       </c>
       <c r="K218" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:14Z</t>
+          <t>2026-10-09T00:32:02Z</t>
         </is>
       </c>
     </row>
@@ -11038,7 +11038,7 @@
       </c>
       <c r="K219" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:14Z</t>
+          <t>2026-10-09T00:32:02Z</t>
         </is>
       </c>
     </row>
@@ -11087,7 +11087,7 @@
       </c>
       <c r="K220" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:14Z</t>
+          <t>2026-10-09T00:32:02Z</t>
         </is>
       </c>
     </row>
@@ -11136,7 +11136,7 @@
       </c>
       <c r="K221" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:14Z</t>
+          <t>2026-10-09T00:32:02Z</t>
         </is>
       </c>
     </row>
@@ -11185,7 +11185,7 @@
       </c>
       <c r="K222" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:14Z</t>
+          <t>2026-10-09T00:32:02Z</t>
         </is>
       </c>
     </row>
@@ -11234,7 +11234,7 @@
       </c>
       <c r="K223" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:14Z</t>
+          <t>2026-10-09T00:32:02Z</t>
         </is>
       </c>
     </row>
@@ -11283,7 +11283,7 @@
       </c>
       <c r="K224" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:14Z</t>
+          <t>2026-10-09T00:32:02Z</t>
         </is>
       </c>
     </row>
@@ -11332,7 +11332,7 @@
       </c>
       <c r="K225" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:14Z</t>
+          <t>2026-10-09T00:32:02Z</t>
         </is>
       </c>
     </row>
@@ -11381,7 +11381,7 @@
       </c>
       <c r="K226" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:14Z</t>
+          <t>2026-10-09T00:32:02Z</t>
         </is>
       </c>
     </row>
@@ -11430,7 +11430,7 @@
       </c>
       <c r="K227" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:14Z</t>
+          <t>2026-10-09T00:32:02Z</t>
         </is>
       </c>
     </row>
@@ -11479,7 +11479,7 @@
       </c>
       <c r="K228" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:14Z</t>
+          <t>2026-10-09T00:32:02Z</t>
         </is>
       </c>
     </row>
@@ -11528,7 +11528,7 @@
       </c>
       <c r="K229" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:14Z</t>
+          <t>2026-10-09T00:32:02Z</t>
         </is>
       </c>
     </row>
@@ -11577,7 +11577,7 @@
       </c>
       <c r="K230" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:14Z</t>
+          <t>2026-10-09T00:32:02Z</t>
         </is>
       </c>
     </row>
@@ -11626,7 +11626,7 @@
       </c>
       <c r="K231" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:14Z</t>
+          <t>2026-10-09T00:32:02Z</t>
         </is>
       </c>
     </row>
@@ -11758,7 +11758,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:14Z</t>
+          <t>2026-10-09T00:32:02Z</t>
         </is>
       </c>
     </row>
@@ -11804,7 +11804,7 @@
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>{"date": "2026-08-01", "year": 2026, "month": 8, "month_name": "Agosto", "index_value": 637409769724325.1, "monthly_variation_pct": 8.9, "unit": "Índice base diciembre 2007=100 y variación mensual %", "frequency": "monthly", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/precios_consumidor/4_5_7_2.xls", "fetched_at": "2026-10-08T00:18:14Z"}</t>
+          <t>{"date": "2026-08-01", "year": 2026, "month": 8, "month_name": "Agosto", "index_value": 637409769724325.1, "monthly_variation_pct": 8.9, "unit": "Índice base diciembre 2007=100 y variación mensual %", "frequency": "monthly", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/precios_consumidor/4_5_7_2.xls", "fetched_at": "2026-10-09T00:32:02Z"}</t>
         </is>
       </c>
     </row>

--- a/assets/data/bcv/excel/ove_bcv_inpc_nacional_mensual.xlsx
+++ b/assets/data/bcv/excel/ove_bcv_inpc_nacional_mensual.xlsx
@@ -650,7 +650,7 @@
       </c>
       <c r="K7" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:02Z</t>
+          <t>2026-10-10T00:11:24Z</t>
         </is>
       </c>
     </row>
@@ -699,7 +699,7 @@
       </c>
       <c r="K8" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:02Z</t>
+          <t>2026-10-10T00:11:24Z</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="K9" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:02Z</t>
+          <t>2026-10-10T00:11:24Z</t>
         </is>
       </c>
     </row>
@@ -797,7 +797,7 @@
       </c>
       <c r="K10" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:02Z</t>
+          <t>2026-10-10T00:11:24Z</t>
         </is>
       </c>
     </row>
@@ -846,7 +846,7 @@
       </c>
       <c r="K11" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:02Z</t>
+          <t>2026-10-10T00:11:24Z</t>
         </is>
       </c>
     </row>
@@ -895,7 +895,7 @@
       </c>
       <c r="K12" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:02Z</t>
+          <t>2026-10-10T00:11:24Z</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="K13" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:02Z</t>
+          <t>2026-10-10T00:11:24Z</t>
         </is>
       </c>
     </row>
@@ -993,7 +993,7 @@
       </c>
       <c r="K14" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:02Z</t>
+          <t>2026-10-10T00:11:24Z</t>
         </is>
       </c>
     </row>
@@ -1042,7 +1042,7 @@
       </c>
       <c r="K15" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:02Z</t>
+          <t>2026-10-10T00:11:24Z</t>
         </is>
       </c>
     </row>
@@ -1091,7 +1091,7 @@
       </c>
       <c r="K16" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:02Z</t>
+          <t>2026-10-10T00:11:24Z</t>
         </is>
       </c>
     </row>
@@ -1140,7 +1140,7 @@
       </c>
       <c r="K17" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:02Z</t>
+          <t>2026-10-10T00:11:24Z</t>
         </is>
       </c>
     </row>
@@ -1189,7 +1189,7 @@
       </c>
       <c r="K18" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:02Z</t>
+          <t>2026-10-10T00:11:24Z</t>
         </is>
       </c>
     </row>
@@ -1238,7 +1238,7 @@
       </c>
       <c r="K19" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:02Z</t>
+          <t>2026-10-10T00:11:24Z</t>
         </is>
       </c>
     </row>
@@ -1287,7 +1287,7 @@
       </c>
       <c r="K20" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:02Z</t>
+          <t>2026-10-10T00:11:24Z</t>
         </is>
       </c>
     </row>
@@ -1336,7 +1336,7 @@
       </c>
       <c r="K21" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:02Z</t>
+          <t>2026-10-10T00:11:24Z</t>
         </is>
       </c>
     </row>
@@ -1385,7 +1385,7 @@
       </c>
       <c r="K22" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:02Z</t>
+          <t>2026-10-10T00:11:24Z</t>
         </is>
       </c>
     </row>
@@ -1434,7 +1434,7 @@
       </c>
       <c r="K23" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:02Z</t>
+          <t>2026-10-10T00:11:24Z</t>
         </is>
       </c>
     </row>
@@ -1483,7 +1483,7 @@
       </c>
       <c r="K24" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:02Z</t>
+          <t>2026-10-10T00:11:24Z</t>
         </is>
       </c>
     </row>
@@ -1532,7 +1532,7 @@
       </c>
       <c r="K25" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:02Z</t>
+          <t>2026-10-10T00:11:24Z</t>
         </is>
       </c>
     </row>
@@ -1581,7 +1581,7 @@
       </c>
       <c r="K26" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:02Z</t>
+          <t>2026-10-10T00:11:24Z</t>
         </is>
       </c>
     </row>
@@ -1630,7 +1630,7 @@
       </c>
       <c r="K27" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:02Z</t>
+          <t>2026-10-10T00:11:24Z</t>
         </is>
       </c>
     </row>
@@ -1679,7 +1679,7 @@
       </c>
       <c r="K28" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:02Z</t>
+          <t>2026-10-10T00:11:24Z</t>
         </is>
       </c>
     </row>
@@ -1728,7 +1728,7 @@
       </c>
       <c r="K29" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:02Z</t>
+          <t>2026-10-10T00:11:24Z</t>
         </is>
       </c>
     </row>
@@ -1777,7 +1777,7 @@
       </c>
       <c r="K30" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:02Z</t>
+          <t>2026-10-10T00:11:24Z</t>
         </is>
       </c>
     </row>
@@ -1826,7 +1826,7 @@
       </c>
       <c r="K31" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:02Z</t>
+          <t>2026-10-10T00:11:24Z</t>
         </is>
       </c>
     </row>
@@ -1875,7 +1875,7 @@
       </c>
       <c r="K32" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:02Z</t>
+          <t>2026-10-10T00:11:24Z</t>
         </is>
       </c>
     </row>
@@ -1924,7 +1924,7 @@
       </c>
       <c r="K33" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:02Z</t>
+          <t>2026-10-10T00:11:24Z</t>
         </is>
       </c>
     </row>
@@ -1973,7 +1973,7 @@
       </c>
       <c r="K34" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:02Z</t>
+          <t>2026-10-10T00:11:24Z</t>
         </is>
       </c>
     </row>
@@ -2022,7 +2022,7 @@
       </c>
       <c r="K35" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:02Z</t>
+          <t>2026-10-10T00:11:24Z</t>
         </is>
       </c>
     </row>
@@ -2071,7 +2071,7 @@
       </c>
       <c r="K36" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:02Z</t>
+          <t>2026-10-10T00:11:24Z</t>
         </is>
       </c>
     </row>
@@ -2120,7 +2120,7 @@
       </c>
       <c r="K37" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:02Z</t>
+          <t>2026-10-10T00:11:24Z</t>
         </is>
       </c>
     </row>
@@ -2169,7 +2169,7 @@
       </c>
       <c r="K38" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:02Z</t>
+          <t>2026-10-10T00:11:24Z</t>
         </is>
       </c>
     </row>
@@ -2218,7 +2218,7 @@
       </c>
       <c r="K39" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:02Z</t>
+          <t>2026-10-10T00:11:24Z</t>
         </is>
       </c>
     </row>
@@ -2267,7 +2267,7 @@
       </c>
       <c r="K40" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:02Z</t>
+          <t>2026-10-10T00:11:24Z</t>
         </is>
       </c>
     </row>
@@ -2316,7 +2316,7 @@
       </c>
       <c r="K41" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:02Z</t>
+          <t>2026-10-10T00:11:24Z</t>
         </is>
       </c>
     </row>
@@ -2365,7 +2365,7 @@
       </c>
       <c r="K42" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:02Z</t>
+          <t>2026-10-10T00:11:24Z</t>
         </is>
       </c>
     </row>
@@ -2414,7 +2414,7 @@
       </c>
       <c r="K43" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:02Z</t>
+          <t>2026-10-10T00:11:24Z</t>
         </is>
       </c>
     </row>
@@ -2463,7 +2463,7 @@
       </c>
       <c r="K44" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:02Z</t>
+          <t>2026-10-10T00:11:24Z</t>
         </is>
       </c>
     </row>
@@ -2512,7 +2512,7 @@
       </c>
       <c r="K45" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:02Z</t>
+          <t>2026-10-10T00:11:24Z</t>
         </is>
       </c>
     </row>
@@ -2561,7 +2561,7 @@
       </c>
       <c r="K46" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:02Z</t>
+          <t>2026-10-10T00:11:24Z</t>
         </is>
       </c>
     </row>
@@ -2610,7 +2610,7 @@
       </c>
       <c r="K47" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:02Z</t>
+          <t>2026-10-10T00:11:24Z</t>
         </is>
       </c>
     </row>
@@ -2659,7 +2659,7 @@
       </c>
       <c r="K48" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:02Z</t>
+          <t>2026-10-10T00:11:24Z</t>
         </is>
       </c>
     </row>
@@ -2708,7 +2708,7 @@
       </c>
       <c r="K49" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:02Z</t>
+          <t>2026-10-10T00:11:24Z</t>
         </is>
       </c>
     </row>
@@ -2757,7 +2757,7 @@
       </c>
       <c r="K50" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:02Z</t>
+          <t>2026-10-10T00:11:24Z</t>
         </is>
       </c>
     </row>
@@ -2806,7 +2806,7 @@
       </c>
       <c r="K51" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:02Z</t>
+          <t>2026-10-10T00:11:24Z</t>
         </is>
       </c>
     </row>
@@ -2855,7 +2855,7 @@
       </c>
       <c r="K52" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:02Z</t>
+          <t>2026-10-10T00:11:24Z</t>
         </is>
       </c>
     </row>
@@ -2904,7 +2904,7 @@
       </c>
       <c r="K53" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:02Z</t>
+          <t>2026-10-10T00:11:24Z</t>
         </is>
       </c>
     </row>
@@ -2953,7 +2953,7 @@
       </c>
       <c r="K54" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:02Z</t>
+          <t>2026-10-10T00:11:24Z</t>
         </is>
       </c>
     </row>
@@ -3002,7 +3002,7 @@
       </c>
       <c r="K55" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:02Z</t>
+          <t>2026-10-10T00:11:24Z</t>
         </is>
       </c>
     </row>
@@ -3051,7 +3051,7 @@
       </c>
       <c r="K56" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:02Z</t>
+          <t>2026-10-10T00:11:24Z</t>
         </is>
       </c>
     </row>
@@ -3100,7 +3100,7 @@
       </c>
       <c r="K57" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:02Z</t>
+          <t>2026-10-10T00:11:24Z</t>
         </is>
       </c>
     </row>
@@ -3149,7 +3149,7 @@
       </c>
       <c r="K58" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:02Z</t>
+          <t>2026-10-10T00:11:24Z</t>
         </is>
       </c>
     </row>
@@ -3198,7 +3198,7 @@
       </c>
       <c r="K59" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:02Z</t>
+          <t>2026-10-10T00:11:24Z</t>
         </is>
       </c>
     </row>
@@ -3247,7 +3247,7 @@
       </c>
       <c r="K60" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:02Z</t>
+          <t>2026-10-10T00:11:24Z</t>
         </is>
       </c>
     </row>
@@ -3296,7 +3296,7 @@
       </c>
       <c r="K61" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:02Z</t>
+          <t>2026-10-10T00:11:24Z</t>
         </is>
       </c>
     </row>
@@ -3345,7 +3345,7 @@
       </c>
       <c r="K62" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:02Z</t>
+          <t>2026-10-10T00:11:24Z</t>
         </is>
       </c>
     </row>
@@ -3394,7 +3394,7 @@
       </c>
       <c r="K63" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:02Z</t>
+          <t>2026-10-10T00:11:24Z</t>
         </is>
       </c>
     </row>
@@ -3443,7 +3443,7 @@
       </c>
       <c r="K64" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:02Z</t>
+          <t>2026-10-10T00:11:24Z</t>
         </is>
       </c>
     </row>
@@ -3492,7 +3492,7 @@
       </c>
       <c r="K65" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:02Z</t>
+          <t>2026-10-10T00:11:24Z</t>
         </is>
       </c>
     </row>
@@ -3541,7 +3541,7 @@
       </c>
       <c r="K66" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:02Z</t>
+          <t>2026-10-10T00:11:24Z</t>
         </is>
       </c>
     </row>
@@ -3590,7 +3590,7 @@
       </c>
       <c r="K67" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:02Z</t>
+          <t>2026-10-10T00:11:24Z</t>
         </is>
       </c>
     </row>
@@ -3639,7 +3639,7 @@
       </c>
       <c r="K68" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:02Z</t>
+          <t>2026-10-10T00:11:24Z</t>
         </is>
       </c>
     </row>
@@ -3688,7 +3688,7 @@
       </c>
       <c r="K69" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:02Z</t>
+          <t>2026-10-10T00:11:24Z</t>
         </is>
       </c>
     </row>
@@ -3737,7 +3737,7 @@
       </c>
       <c r="K70" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:02Z</t>
+          <t>2026-10-10T00:11:24Z</t>
         </is>
       </c>
     </row>
@@ -3786,7 +3786,7 @@
       </c>
       <c r="K71" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:02Z</t>
+          <t>2026-10-10T00:11:24Z</t>
         </is>
       </c>
     </row>
@@ -3835,7 +3835,7 @@
       </c>
       <c r="K72" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:02Z</t>
+          <t>2026-10-10T00:11:24Z</t>
         </is>
       </c>
     </row>
@@ -3884,7 +3884,7 @@
       </c>
       <c r="K73" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:02Z</t>
+          <t>2026-10-10T00:11:24Z</t>
         </is>
       </c>
     </row>
@@ -3933,7 +3933,7 @@
       </c>
       <c r="K74" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:02Z</t>
+          <t>2026-10-10T00:11:24Z</t>
         </is>
       </c>
     </row>
@@ -3982,7 +3982,7 @@
       </c>
       <c r="K75" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:02Z</t>
+          <t>2026-10-10T00:11:24Z</t>
         </is>
       </c>
     </row>
@@ -4031,7 +4031,7 @@
       </c>
       <c r="K76" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:02Z</t>
+          <t>2026-10-10T00:11:24Z</t>
         </is>
       </c>
     </row>
@@ -4080,7 +4080,7 @@
       </c>
       <c r="K77" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:02Z</t>
+          <t>2026-10-10T00:11:24Z</t>
         </is>
       </c>
     </row>
@@ -4129,7 +4129,7 @@
       </c>
       <c r="K78" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:02Z</t>
+          <t>2026-10-10T00:11:24Z</t>
         </is>
       </c>
     </row>
@@ -4178,7 +4178,7 @@
       </c>
       <c r="K79" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:02Z</t>
+          <t>2026-10-10T00:11:24Z</t>
         </is>
       </c>
     </row>
@@ -4227,7 +4227,7 @@
       </c>
       <c r="K80" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:02Z</t>
+          <t>2026-10-10T00:11:24Z</t>
         </is>
       </c>
     </row>
@@ -4276,7 +4276,7 @@
       </c>
       <c r="K81" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:02Z</t>
+          <t>2026-10-10T00:11:24Z</t>
         </is>
       </c>
     </row>
@@ -4325,7 +4325,7 @@
       </c>
       <c r="K82" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:02Z</t>
+          <t>2026-10-10T00:11:24Z</t>
         </is>
       </c>
     </row>
@@ -4374,7 +4374,7 @@
       </c>
       <c r="K83" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:02Z</t>
+          <t>2026-10-10T00:11:24Z</t>
         </is>
       </c>
     </row>
@@ -4423,7 +4423,7 @@
       </c>
       <c r="K84" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:02Z</t>
+          <t>2026-10-10T00:11:24Z</t>
         </is>
       </c>
     </row>
@@ -4472,7 +4472,7 @@
       </c>
       <c r="K85" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:02Z</t>
+          <t>2026-10-10T00:11:24Z</t>
         </is>
       </c>
     </row>
@@ -4521,7 +4521,7 @@
       </c>
       <c r="K86" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:02Z</t>
+          <t>2026-10-10T00:11:24Z</t>
         </is>
       </c>
     </row>
@@ -4570,7 +4570,7 @@
       </c>
       <c r="K87" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:02Z</t>
+          <t>2026-10-10T00:11:24Z</t>
         </is>
       </c>
     </row>
@@ -4619,7 +4619,7 @@
       </c>
       <c r="K88" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:02Z</t>
+          <t>2026-10-10T00:11:24Z</t>
         </is>
       </c>
     </row>
@@ -4668,7 +4668,7 @@
       </c>
       <c r="K89" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:02Z</t>
+          <t>2026-10-10T00:11:24Z</t>
         </is>
       </c>
     </row>
@@ -4717,7 +4717,7 @@
       </c>
       <c r="K90" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:02Z</t>
+          <t>2026-10-10T00:11:24Z</t>
         </is>
       </c>
     </row>
@@ -4766,7 +4766,7 @@
       </c>
       <c r="K91" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:02Z</t>
+          <t>2026-10-10T00:11:24Z</t>
         </is>
       </c>
     </row>
@@ -4815,7 +4815,7 @@
       </c>
       <c r="K92" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:02Z</t>
+          <t>2026-10-10T00:11:24Z</t>
         </is>
       </c>
     </row>
@@ -4864,7 +4864,7 @@
       </c>
       <c r="K93" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:02Z</t>
+          <t>2026-10-10T00:11:24Z</t>
         </is>
       </c>
     </row>
@@ -4913,7 +4913,7 @@
       </c>
       <c r="K94" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:02Z</t>
+          <t>2026-10-10T00:11:24Z</t>
         </is>
       </c>
     </row>
@@ -4962,7 +4962,7 @@
       </c>
       <c r="K95" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:02Z</t>
+          <t>2026-10-10T00:11:24Z</t>
         </is>
       </c>
     </row>
@@ -5011,7 +5011,7 @@
       </c>
       <c r="K96" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:02Z</t>
+          <t>2026-10-10T00:11:24Z</t>
         </is>
       </c>
     </row>
@@ -5060,7 +5060,7 @@
       </c>
       <c r="K97" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:02Z</t>
+          <t>2026-10-10T00:11:24Z</t>
         </is>
       </c>
     </row>
@@ -5109,7 +5109,7 @@
       </c>
       <c r="K98" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:02Z</t>
+          <t>2026-10-10T00:11:24Z</t>
         </is>
       </c>
     </row>
@@ -5158,7 +5158,7 @@
       </c>
       <c r="K99" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:02Z</t>
+          <t>2026-10-10T00:11:24Z</t>
         </is>
       </c>
     </row>
@@ -5207,7 +5207,7 @@
       </c>
       <c r="K100" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:02Z</t>
+          <t>2026-10-10T00:11:24Z</t>
         </is>
       </c>
     </row>
@@ -5256,7 +5256,7 @@
       </c>
       <c r="K101" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:02Z</t>
+          <t>2026-10-10T00:11:24Z</t>
         </is>
       </c>
     </row>
@@ -5305,7 +5305,7 @@
       </c>
       <c r="K102" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:02Z</t>
+          <t>2026-10-10T00:11:24Z</t>
         </is>
       </c>
     </row>
@@ -5354,7 +5354,7 @@
       </c>
       <c r="K103" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:02Z</t>
+          <t>2026-10-10T00:11:24Z</t>
         </is>
       </c>
     </row>
@@ -5403,7 +5403,7 @@
       </c>
       <c r="K104" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:02Z</t>
+          <t>2026-10-10T00:11:24Z</t>
         </is>
       </c>
     </row>
@@ -5452,7 +5452,7 @@
       </c>
       <c r="K105" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:02Z</t>
+          <t>2026-10-10T00:11:24Z</t>
         </is>
       </c>
     </row>
@@ -5501,7 +5501,7 @@
       </c>
       <c r="K106" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:02Z</t>
+          <t>2026-10-10T00:11:24Z</t>
         </is>
       </c>
     </row>
@@ -5550,7 +5550,7 @@
       </c>
       <c r="K107" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:02Z</t>
+          <t>2026-10-10T00:11:24Z</t>
         </is>
       </c>
     </row>
@@ -5599,7 +5599,7 @@
       </c>
       <c r="K108" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:02Z</t>
+          <t>2026-10-10T00:11:24Z</t>
         </is>
       </c>
     </row>
@@ -5648,7 +5648,7 @@
       </c>
       <c r="K109" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:02Z</t>
+          <t>2026-10-10T00:11:24Z</t>
         </is>
       </c>
     </row>
@@ -5697,7 +5697,7 @@
       </c>
       <c r="K110" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:02Z</t>
+          <t>2026-10-10T00:11:24Z</t>
         </is>
       </c>
     </row>
@@ -5746,7 +5746,7 @@
       </c>
       <c r="K111" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:02Z</t>
+          <t>2026-10-10T00:11:24Z</t>
         </is>
       </c>
     </row>
@@ -5795,7 +5795,7 @@
       </c>
       <c r="K112" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:02Z</t>
+          <t>2026-10-10T00:11:24Z</t>
         </is>
       </c>
     </row>
@@ -5844,7 +5844,7 @@
       </c>
       <c r="K113" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:02Z</t>
+          <t>2026-10-10T00:11:24Z</t>
         </is>
       </c>
     </row>
@@ -5893,7 +5893,7 @@
       </c>
       <c r="K114" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:02Z</t>
+          <t>2026-10-10T00:11:24Z</t>
         </is>
       </c>
     </row>
@@ -5942,7 +5942,7 @@
       </c>
       <c r="K115" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:02Z</t>
+          <t>2026-10-10T00:11:24Z</t>
         </is>
       </c>
     </row>
@@ -5991,7 +5991,7 @@
       </c>
       <c r="K116" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:02Z</t>
+          <t>2026-10-10T00:11:24Z</t>
         </is>
       </c>
     </row>
@@ -6040,7 +6040,7 @@
       </c>
       <c r="K117" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:02Z</t>
+          <t>2026-10-10T00:11:24Z</t>
         </is>
       </c>
     </row>
@@ -6089,7 +6089,7 @@
       </c>
       <c r="K118" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:02Z</t>
+          <t>2026-10-10T00:11:24Z</t>
         </is>
       </c>
     </row>
@@ -6138,7 +6138,7 @@
       </c>
       <c r="K119" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:02Z</t>
+          <t>2026-10-10T00:11:24Z</t>
         </is>
       </c>
     </row>
@@ -6187,7 +6187,7 @@
       </c>
       <c r="K120" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:02Z</t>
+          <t>2026-10-10T00:11:24Z</t>
         </is>
       </c>
     </row>
@@ -6236,7 +6236,7 @@
       </c>
       <c r="K121" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:02Z</t>
+          <t>2026-10-10T00:11:24Z</t>
         </is>
       </c>
     </row>
@@ -6285,7 +6285,7 @@
       </c>
       <c r="K122" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:02Z</t>
+          <t>2026-10-10T00:11:24Z</t>
         </is>
       </c>
     </row>
@@ -6334,7 +6334,7 @@
       </c>
       <c r="K123" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:02Z</t>
+          <t>2026-10-10T00:11:24Z</t>
         </is>
       </c>
     </row>
@@ -6383,7 +6383,7 @@
       </c>
       <c r="K124" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:02Z</t>
+          <t>2026-10-10T00:11:24Z</t>
         </is>
       </c>
     </row>
@@ -6432,7 +6432,7 @@
       </c>
       <c r="K125" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:02Z</t>
+          <t>2026-10-10T00:11:24Z</t>
         </is>
       </c>
     </row>
@@ -6481,7 +6481,7 @@
       </c>
       <c r="K126" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:02Z</t>
+          <t>2026-10-10T00:11:24Z</t>
         </is>
       </c>
     </row>
@@ -6530,7 +6530,7 @@
       </c>
       <c r="K127" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:02Z</t>
+          <t>2026-10-10T00:11:24Z</t>
         </is>
       </c>
     </row>
@@ -6579,7 +6579,7 @@
       </c>
       <c r="K128" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:02Z</t>
+          <t>2026-10-10T00:11:24Z</t>
         </is>
       </c>
     </row>
@@ -6628,7 +6628,7 @@
       </c>
       <c r="K129" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:02Z</t>
+          <t>2026-10-10T00:11:24Z</t>
         </is>
       </c>
     </row>
@@ -6677,7 +6677,7 @@
       </c>
       <c r="K130" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:02Z</t>
+          <t>2026-10-10T00:11:24Z</t>
         </is>
       </c>
     </row>
@@ -6726,7 +6726,7 @@
       </c>
       <c r="K131" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:02Z</t>
+          <t>2026-10-10T00:11:24Z</t>
         </is>
       </c>
     </row>
@@ -6775,7 +6775,7 @@
       </c>
       <c r="K132" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:02Z</t>
+          <t>2026-10-10T00:11:24Z</t>
         </is>
       </c>
     </row>
@@ -6824,7 +6824,7 @@
       </c>
       <c r="K133" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:02Z</t>
+          <t>2026-10-10T00:11:24Z</t>
         </is>
       </c>
     </row>
@@ -6873,7 +6873,7 @@
       </c>
       <c r="K134" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:02Z</t>
+          <t>2026-10-10T00:11:24Z</t>
         </is>
       </c>
     </row>
@@ -6922,7 +6922,7 @@
       </c>
       <c r="K135" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:02Z</t>
+          <t>2026-10-10T00:11:24Z</t>
         </is>
       </c>
     </row>
@@ -6971,7 +6971,7 @@
       </c>
       <c r="K136" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:02Z</t>
+          <t>2026-10-10T00:11:24Z</t>
         </is>
       </c>
     </row>
@@ -7020,7 +7020,7 @@
       </c>
       <c r="K137" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:02Z</t>
+          <t>2026-10-10T00:11:24Z</t>
         </is>
       </c>
     </row>
@@ -7069,7 +7069,7 @@
       </c>
       <c r="K138" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:02Z</t>
+          <t>2026-10-10T00:11:24Z</t>
         </is>
       </c>
     </row>
@@ -7118,7 +7118,7 @@
       </c>
       <c r="K139" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:02Z</t>
+          <t>2026-10-10T00:11:24Z</t>
         </is>
       </c>
     </row>
@@ -7167,7 +7167,7 @@
       </c>
       <c r="K140" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:02Z</t>
+          <t>2026-10-10T00:11:24Z</t>
         </is>
       </c>
     </row>
@@ -7216,7 +7216,7 @@
       </c>
       <c r="K141" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:02Z</t>
+          <t>2026-10-10T00:11:24Z</t>
         </is>
       </c>
     </row>
@@ -7265,7 +7265,7 @@
       </c>
       <c r="K142" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:02Z</t>
+          <t>2026-10-10T00:11:24Z</t>
         </is>
       </c>
     </row>
@@ -7314,7 +7314,7 @@
       </c>
       <c r="K143" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:02Z</t>
+          <t>2026-10-10T00:11:24Z</t>
         </is>
       </c>
     </row>
@@ -7363,7 +7363,7 @@
       </c>
       <c r="K144" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:02Z</t>
+          <t>2026-10-10T00:11:24Z</t>
         </is>
       </c>
     </row>
@@ -7412,7 +7412,7 @@
       </c>
       <c r="K145" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:02Z</t>
+          <t>2026-10-10T00:11:24Z</t>
         </is>
       </c>
     </row>
@@ -7461,7 +7461,7 @@
       </c>
       <c r="K146" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:02Z</t>
+          <t>2026-10-10T00:11:24Z</t>
         </is>
       </c>
     </row>
@@ -7510,7 +7510,7 @@
       </c>
       <c r="K147" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:02Z</t>
+          <t>2026-10-10T00:11:24Z</t>
         </is>
       </c>
     </row>
@@ -7559,7 +7559,7 @@
       </c>
       <c r="K148" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:02Z</t>
+          <t>2026-10-10T00:11:24Z</t>
         </is>
       </c>
     </row>
@@ -7608,7 +7608,7 @@
       </c>
       <c r="K149" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:02Z</t>
+          <t>2026-10-10T00:11:24Z</t>
         </is>
       </c>
     </row>
@@ -7657,7 +7657,7 @@
       </c>
       <c r="K150" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:02Z</t>
+          <t>2026-10-10T00:11:24Z</t>
         </is>
       </c>
     </row>
@@ -7706,7 +7706,7 @@
       </c>
       <c r="K151" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:02Z</t>
+          <t>2026-10-10T00:11:24Z</t>
         </is>
       </c>
     </row>
@@ -7755,7 +7755,7 @@
       </c>
       <c r="K152" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:02Z</t>
+          <t>2026-10-10T00:11:24Z</t>
         </is>
       </c>
     </row>
@@ -7804,7 +7804,7 @@
       </c>
       <c r="K153" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:02Z</t>
+          <t>2026-10-10T00:11:24Z</t>
         </is>
       </c>
     </row>
@@ -7853,7 +7853,7 @@
       </c>
       <c r="K154" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:02Z</t>
+          <t>2026-10-10T00:11:24Z</t>
         </is>
       </c>
     </row>
@@ -7902,7 +7902,7 @@
       </c>
       <c r="K155" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:02Z</t>
+          <t>2026-10-10T00:11:24Z</t>
         </is>
       </c>
     </row>
@@ -7951,7 +7951,7 @@
       </c>
       <c r="K156" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:02Z</t>
+          <t>2026-10-10T00:11:24Z</t>
         </is>
       </c>
     </row>
@@ -8000,7 +8000,7 @@
       </c>
       <c r="K157" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:02Z</t>
+          <t>2026-10-10T00:11:24Z</t>
         </is>
       </c>
     </row>
@@ -8049,7 +8049,7 @@
       </c>
       <c r="K158" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:02Z</t>
+          <t>2026-10-10T00:11:24Z</t>
         </is>
       </c>
     </row>
@@ -8098,7 +8098,7 @@
       </c>
       <c r="K159" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:02Z</t>
+          <t>2026-10-10T00:11:24Z</t>
         </is>
       </c>
     </row>
@@ -8147,7 +8147,7 @@
       </c>
       <c r="K160" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:02Z</t>
+          <t>2026-10-10T00:11:24Z</t>
         </is>
       </c>
     </row>
@@ -8196,7 +8196,7 @@
       </c>
       <c r="K161" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:02Z</t>
+          <t>2026-10-10T00:11:24Z</t>
         </is>
       </c>
     </row>
@@ -8245,7 +8245,7 @@
       </c>
       <c r="K162" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:02Z</t>
+          <t>2026-10-10T00:11:24Z</t>
         </is>
       </c>
     </row>
@@ -8294,7 +8294,7 @@
       </c>
       <c r="K163" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:02Z</t>
+          <t>2026-10-10T00:11:24Z</t>
         </is>
       </c>
     </row>
@@ -8343,7 +8343,7 @@
       </c>
       <c r="K164" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:02Z</t>
+          <t>2026-10-10T00:11:24Z</t>
         </is>
       </c>
     </row>
@@ -8392,7 +8392,7 @@
       </c>
       <c r="K165" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:02Z</t>
+          <t>2026-10-10T00:11:24Z</t>
         </is>
       </c>
     </row>
@@ -8441,7 +8441,7 @@
       </c>
       <c r="K166" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:02Z</t>
+          <t>2026-10-10T00:11:24Z</t>
         </is>
       </c>
     </row>
@@ -8490,7 +8490,7 @@
       </c>
       <c r="K167" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:02Z</t>
+          <t>2026-10-10T00:11:24Z</t>
         </is>
       </c>
     </row>
@@ -8539,7 +8539,7 @@
       </c>
       <c r="K168" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:02Z</t>
+          <t>2026-10-10T00:11:24Z</t>
         </is>
       </c>
     </row>
@@ -8588,7 +8588,7 @@
       </c>
       <c r="K169" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:02Z</t>
+          <t>2026-10-10T00:11:24Z</t>
         </is>
       </c>
     </row>
@@ -8637,7 +8637,7 @@
       </c>
       <c r="K170" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:02Z</t>
+          <t>2026-10-10T00:11:24Z</t>
         </is>
       </c>
     </row>
@@ -8686,7 +8686,7 @@
       </c>
       <c r="K171" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:02Z</t>
+          <t>2026-10-10T00:11:24Z</t>
         </is>
       </c>
     </row>
@@ -8735,7 +8735,7 @@
       </c>
       <c r="K172" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:02Z</t>
+          <t>2026-10-10T00:11:24Z</t>
         </is>
       </c>
     </row>
@@ -8784,7 +8784,7 @@
       </c>
       <c r="K173" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:02Z</t>
+          <t>2026-10-10T00:11:24Z</t>
         </is>
       </c>
     </row>
@@ -8833,7 +8833,7 @@
       </c>
       <c r="K174" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:02Z</t>
+          <t>2026-10-10T00:11:24Z</t>
         </is>
       </c>
     </row>
@@ -8882,7 +8882,7 @@
       </c>
       <c r="K175" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:02Z</t>
+          <t>2026-10-10T00:11:24Z</t>
         </is>
       </c>
     </row>
@@ -8931,7 +8931,7 @@
       </c>
       <c r="K176" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:02Z</t>
+          <t>2026-10-10T00:11:24Z</t>
         </is>
       </c>
     </row>
@@ -8980,7 +8980,7 @@
       </c>
       <c r="K177" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:02Z</t>
+          <t>2026-10-10T00:11:24Z</t>
         </is>
       </c>
     </row>
@@ -9029,7 +9029,7 @@
       </c>
       <c r="K178" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:02Z</t>
+          <t>2026-10-10T00:11:24Z</t>
         </is>
       </c>
     </row>
@@ -9078,7 +9078,7 @@
       </c>
       <c r="K179" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:02Z</t>
+          <t>2026-10-10T00:11:24Z</t>
         </is>
       </c>
     </row>
@@ -9127,7 +9127,7 @@
       </c>
       <c r="K180" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:02Z</t>
+          <t>2026-10-10T00:11:24Z</t>
         </is>
       </c>
     </row>
@@ -9176,7 +9176,7 @@
       </c>
       <c r="K181" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:02Z</t>
+          <t>2026-10-10T00:11:24Z</t>
         </is>
       </c>
     </row>
@@ -9225,7 +9225,7 @@
       </c>
       <c r="K182" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:02Z</t>
+          <t>2026-10-10T00:11:24Z</t>
         </is>
       </c>
     </row>
@@ -9274,7 +9274,7 @@
       </c>
       <c r="K183" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:02Z</t>
+          <t>2026-10-10T00:11:24Z</t>
         </is>
       </c>
     </row>
@@ -9323,7 +9323,7 @@
       </c>
       <c r="K184" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:02Z</t>
+          <t>2026-10-10T00:11:24Z</t>
         </is>
       </c>
     </row>
@@ -9372,7 +9372,7 @@
       </c>
       <c r="K185" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:02Z</t>
+          <t>2026-10-10T00:11:24Z</t>
         </is>
       </c>
     </row>
@@ -9421,7 +9421,7 @@
       </c>
       <c r="K186" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:02Z</t>
+          <t>2026-10-10T00:11:24Z</t>
         </is>
       </c>
     </row>
@@ -9470,7 +9470,7 @@
       </c>
       <c r="K187" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:02Z</t>
+          <t>2026-10-10T00:11:24Z</t>
         </is>
       </c>
     </row>
@@ -9519,7 +9519,7 @@
       </c>
       <c r="K188" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:02Z</t>
+          <t>2026-10-10T00:11:24Z</t>
         </is>
       </c>
     </row>
@@ -9568,7 +9568,7 @@
       </c>
       <c r="K189" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:02Z</t>
+          <t>2026-10-10T00:11:24Z</t>
         </is>
       </c>
     </row>
@@ -9617,7 +9617,7 @@
       </c>
       <c r="K190" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:02Z</t>
+          <t>2026-10-10T00:11:24Z</t>
         </is>
       </c>
     </row>
@@ -9666,7 +9666,7 @@
       </c>
       <c r="K191" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:02Z</t>
+          <t>2026-10-10T00:11:24Z</t>
         </is>
       </c>
     </row>
@@ -9715,7 +9715,7 @@
       </c>
       <c r="K192" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:02Z</t>
+          <t>2026-10-10T00:11:24Z</t>
         </is>
       </c>
     </row>
@@ -9764,7 +9764,7 @@
       </c>
       <c r="K193" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:02Z</t>
+          <t>2026-10-10T00:11:24Z</t>
         </is>
       </c>
     </row>
@@ -9813,7 +9813,7 @@
       </c>
       <c r="K194" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:02Z</t>
+          <t>2026-10-10T00:11:24Z</t>
         </is>
       </c>
     </row>
@@ -9862,7 +9862,7 @@
       </c>
       <c r="K195" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:02Z</t>
+          <t>2026-10-10T00:11:24Z</t>
         </is>
       </c>
     </row>
@@ -9911,7 +9911,7 @@
       </c>
       <c r="K196" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:02Z</t>
+          <t>2026-10-10T00:11:24Z</t>
         </is>
       </c>
     </row>
@@ -9960,7 +9960,7 @@
       </c>
       <c r="K197" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:02Z</t>
+          <t>2026-10-10T00:11:24Z</t>
         </is>
       </c>
     </row>
@@ -10009,7 +10009,7 @@
       </c>
       <c r="K198" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:02Z</t>
+          <t>2026-10-10T00:11:24Z</t>
         </is>
       </c>
     </row>
@@ -10058,7 +10058,7 @@
       </c>
       <c r="K199" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:02Z</t>
+          <t>2026-10-10T00:11:24Z</t>
         </is>
       </c>
     </row>
@@ -10107,7 +10107,7 @@
       </c>
       <c r="K200" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:02Z</t>
+          <t>2026-10-10T00:11:24Z</t>
         </is>
       </c>
     </row>
@@ -10156,7 +10156,7 @@
       </c>
       <c r="K201" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:02Z</t>
+          <t>2026-10-10T00:11:24Z</t>
         </is>
       </c>
     </row>
@@ -10205,7 +10205,7 @@
       </c>
       <c r="K202" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:02Z</t>
+          <t>2026-10-10T00:11:24Z</t>
         </is>
       </c>
     </row>
@@ -10254,7 +10254,7 @@
       </c>
       <c r="K203" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:02Z</t>
+          <t>2026-10-10T00:11:24Z</t>
         </is>
       </c>
     </row>
@@ -10303,7 +10303,7 @@
       </c>
       <c r="K204" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:02Z</t>
+          <t>2026-10-10T00:11:24Z</t>
         </is>
       </c>
     </row>
@@ -10352,7 +10352,7 @@
       </c>
       <c r="K205" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:02Z</t>
+          <t>2026-10-10T00:11:24Z</t>
         </is>
       </c>
     </row>
@@ -10401,7 +10401,7 @@
       </c>
       <c r="K206" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:02Z</t>
+          <t>2026-10-10T00:11:24Z</t>
         </is>
       </c>
     </row>
@@ -10450,7 +10450,7 @@
       </c>
       <c r="K207" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:02Z</t>
+          <t>2026-10-10T00:11:24Z</t>
         </is>
       </c>
     </row>
@@ -10499,7 +10499,7 @@
       </c>
       <c r="K208" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:02Z</t>
+          <t>2026-10-10T00:11:24Z</t>
         </is>
       </c>
     </row>
@@ -10548,7 +10548,7 @@
       </c>
       <c r="K209" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:02Z</t>
+          <t>2026-10-10T00:11:24Z</t>
         </is>
       </c>
     </row>
@@ -10597,7 +10597,7 @@
       </c>
       <c r="K210" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:02Z</t>
+          <t>2026-10-10T00:11:24Z</t>
         </is>
       </c>
     </row>
@@ -10646,7 +10646,7 @@
       </c>
       <c r="K211" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:02Z</t>
+          <t>2026-10-10T00:11:24Z</t>
         </is>
       </c>
     </row>
@@ -10695,7 +10695,7 @@
       </c>
       <c r="K212" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:02Z</t>
+          <t>2026-10-10T00:11:24Z</t>
         </is>
       </c>
     </row>
@@ -10744,7 +10744,7 @@
       </c>
       <c r="K213" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:02Z</t>
+          <t>2026-10-10T00:11:24Z</t>
         </is>
       </c>
     </row>
@@ -10793,7 +10793,7 @@
       </c>
       <c r="K214" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:02Z</t>
+          <t>2026-10-10T00:11:24Z</t>
         </is>
       </c>
     </row>
@@ -10842,7 +10842,7 @@
       </c>
       <c r="K215" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:02Z</t>
+          <t>2026-10-10T00:11:24Z</t>
         </is>
       </c>
     </row>
@@ -10891,7 +10891,7 @@
       </c>
       <c r="K216" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:02Z</t>
+          <t>2026-10-10T00:11:24Z</t>
         </is>
       </c>
     </row>
@@ -10940,7 +10940,7 @@
       </c>
       <c r="K217" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:02Z</t>
+          <t>2026-10-10T00:11:24Z</t>
         </is>
       </c>
     </row>
@@ -10989,7 +10989,7 @@
       </c>
       <c r="K218" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:02Z</t>
+          <t>2026-10-10T00:11:24Z</t>
         </is>
       </c>
     </row>
@@ -11038,7 +11038,7 @@
       </c>
       <c r="K219" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:02Z</t>
+          <t>2026-10-10T00:11:24Z</t>
         </is>
       </c>
     </row>
@@ -11087,7 +11087,7 @@
       </c>
       <c r="K220" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:02Z</t>
+          <t>2026-10-10T00:11:24Z</t>
         </is>
       </c>
     </row>
@@ -11136,7 +11136,7 @@
       </c>
       <c r="K221" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:02Z</t>
+          <t>2026-10-10T00:11:24Z</t>
         </is>
       </c>
     </row>
@@ -11185,7 +11185,7 @@
       </c>
       <c r="K222" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:02Z</t>
+          <t>2026-10-10T00:11:24Z</t>
         </is>
       </c>
     </row>
@@ -11234,7 +11234,7 @@
       </c>
       <c r="K223" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:02Z</t>
+          <t>2026-10-10T00:11:24Z</t>
         </is>
       </c>
     </row>
@@ -11283,7 +11283,7 @@
       </c>
       <c r="K224" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:02Z</t>
+          <t>2026-10-10T00:11:24Z</t>
         </is>
       </c>
     </row>
@@ -11332,7 +11332,7 @@
       </c>
       <c r="K225" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:02Z</t>
+          <t>2026-10-10T00:11:24Z</t>
         </is>
       </c>
     </row>
@@ -11381,7 +11381,7 @@
       </c>
       <c r="K226" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:02Z</t>
+          <t>2026-10-10T00:11:24Z</t>
         </is>
       </c>
     </row>
@@ -11430,7 +11430,7 @@
       </c>
       <c r="K227" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:02Z</t>
+          <t>2026-10-10T00:11:24Z</t>
         </is>
       </c>
     </row>
@@ -11479,7 +11479,7 @@
       </c>
       <c r="K228" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:02Z</t>
+          <t>2026-10-10T00:11:24Z</t>
         </is>
       </c>
     </row>
@@ -11528,7 +11528,7 @@
       </c>
       <c r="K229" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:02Z</t>
+          <t>2026-10-10T00:11:24Z</t>
         </is>
       </c>
     </row>
@@ -11577,7 +11577,7 @@
       </c>
       <c r="K230" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:02Z</t>
+          <t>2026-10-10T00:11:24Z</t>
         </is>
       </c>
     </row>
@@ -11626,7 +11626,7 @@
       </c>
       <c r="K231" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:02Z</t>
+          <t>2026-10-10T00:11:24Z</t>
         </is>
       </c>
     </row>
@@ -11758,7 +11758,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:02Z</t>
+          <t>2026-10-10T00:11:24Z</t>
         </is>
       </c>
     </row>
@@ -11804,7 +11804,7 @@
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>{"date": "2026-08-01", "year": 2026, "month": 8, "month_name": "Agosto", "index_value": 637409769724325.1, "monthly_variation_pct": 8.9, "unit": "Índice base diciembre 2007=100 y variación mensual %", "frequency": "monthly", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/precios_consumidor/4_5_7_2.xls", "fetched_at": "2026-10-09T00:32:02Z"}</t>
+          <t>{"date": "2026-08-01", "year": 2026, "month": 8, "month_name": "Agosto", "index_value": 637409769724325.1, "monthly_variation_pct": 8.9, "unit": "Índice base diciembre 2007=100 y variación mensual %", "frequency": "monthly", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/precios_consumidor/4_5_7_2.xls", "fetched_at": "2026-10-10T00:11:24Z"}</t>
         </is>
       </c>
     </row>

--- a/assets/data/bcv/excel/ove_bcv_inpc_nacional_mensual.xlsx
+++ b/assets/data/bcv/excel/ove_bcv_inpc_nacional_mensual.xlsx
@@ -650,7 +650,7 @@
       </c>
       <c r="K7" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:24Z</t>
+          <t>2026-10-10T23:42:24Z</t>
         </is>
       </c>
     </row>
@@ -699,7 +699,7 @@
       </c>
       <c r="K8" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:24Z</t>
+          <t>2026-10-10T23:42:24Z</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="K9" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:24Z</t>
+          <t>2026-10-10T23:42:24Z</t>
         </is>
       </c>
     </row>
@@ -797,7 +797,7 @@
       </c>
       <c r="K10" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:24Z</t>
+          <t>2026-10-10T23:42:24Z</t>
         </is>
       </c>
     </row>
@@ -846,7 +846,7 @@
       </c>
       <c r="K11" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:24Z</t>
+          <t>2026-10-10T23:42:24Z</t>
         </is>
       </c>
     </row>
@@ -895,7 +895,7 @@
       </c>
       <c r="K12" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:24Z</t>
+          <t>2026-10-10T23:42:24Z</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="K13" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:24Z</t>
+          <t>2026-10-10T23:42:24Z</t>
         </is>
       </c>
     </row>
@@ -993,7 +993,7 @@
       </c>
       <c r="K14" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:24Z</t>
+          <t>2026-10-10T23:42:24Z</t>
         </is>
       </c>
     </row>
@@ -1042,7 +1042,7 @@
       </c>
       <c r="K15" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:24Z</t>
+          <t>2026-10-10T23:42:24Z</t>
         </is>
       </c>
     </row>
@@ -1091,7 +1091,7 @@
       </c>
       <c r="K16" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:24Z</t>
+          <t>2026-10-10T23:42:24Z</t>
         </is>
       </c>
     </row>
@@ -1140,7 +1140,7 @@
       </c>
       <c r="K17" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:24Z</t>
+          <t>2026-10-10T23:42:24Z</t>
         </is>
       </c>
     </row>
@@ -1189,7 +1189,7 @@
       </c>
       <c r="K18" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:24Z</t>
+          <t>2026-10-10T23:42:24Z</t>
         </is>
       </c>
     </row>
@@ -1238,7 +1238,7 @@
       </c>
       <c r="K19" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:24Z</t>
+          <t>2026-10-10T23:42:24Z</t>
         </is>
       </c>
     </row>
@@ -1287,7 +1287,7 @@
       </c>
       <c r="K20" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:24Z</t>
+          <t>2026-10-10T23:42:24Z</t>
         </is>
       </c>
     </row>
@@ -1336,7 +1336,7 @@
       </c>
       <c r="K21" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:24Z</t>
+          <t>2026-10-10T23:42:24Z</t>
         </is>
       </c>
     </row>
@@ -1385,7 +1385,7 @@
       </c>
       <c r="K22" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:24Z</t>
+          <t>2026-10-10T23:42:24Z</t>
         </is>
       </c>
     </row>
@@ -1434,7 +1434,7 @@
       </c>
       <c r="K23" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:24Z</t>
+          <t>2026-10-10T23:42:24Z</t>
         </is>
       </c>
     </row>
@@ -1483,7 +1483,7 @@
       </c>
       <c r="K24" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:24Z</t>
+          <t>2026-10-10T23:42:24Z</t>
         </is>
       </c>
     </row>
@@ -1532,7 +1532,7 @@
       </c>
       <c r="K25" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:24Z</t>
+          <t>2026-10-10T23:42:24Z</t>
         </is>
       </c>
     </row>
@@ -1581,7 +1581,7 @@
       </c>
       <c r="K26" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:24Z</t>
+          <t>2026-10-10T23:42:24Z</t>
         </is>
       </c>
     </row>
@@ -1630,7 +1630,7 @@
       </c>
       <c r="K27" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:24Z</t>
+          <t>2026-10-10T23:42:24Z</t>
         </is>
       </c>
     </row>
@@ -1679,7 +1679,7 @@
       </c>
       <c r="K28" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:24Z</t>
+          <t>2026-10-10T23:42:24Z</t>
         </is>
       </c>
     </row>
@@ -1728,7 +1728,7 @@
       </c>
       <c r="K29" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:24Z</t>
+          <t>2026-10-10T23:42:24Z</t>
         </is>
       </c>
     </row>
@@ -1777,7 +1777,7 @@
       </c>
       <c r="K30" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:24Z</t>
+          <t>2026-10-10T23:42:24Z</t>
         </is>
       </c>
     </row>
@@ -1826,7 +1826,7 @@
       </c>
       <c r="K31" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:24Z</t>
+          <t>2026-10-10T23:42:24Z</t>
         </is>
       </c>
     </row>
@@ -1875,7 +1875,7 @@
       </c>
       <c r="K32" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:24Z</t>
+          <t>2026-10-10T23:42:24Z</t>
         </is>
       </c>
     </row>
@@ -1924,7 +1924,7 @@
       </c>
       <c r="K33" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:24Z</t>
+          <t>2026-10-10T23:42:24Z</t>
         </is>
       </c>
     </row>
@@ -1973,7 +1973,7 @@
       </c>
       <c r="K34" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:24Z</t>
+          <t>2026-10-10T23:42:24Z</t>
         </is>
       </c>
     </row>
@@ -2022,7 +2022,7 @@
       </c>
       <c r="K35" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:24Z</t>
+          <t>2026-10-10T23:42:24Z</t>
         </is>
       </c>
     </row>
@@ -2071,7 +2071,7 @@
       </c>
       <c r="K36" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:24Z</t>
+          <t>2026-10-10T23:42:24Z</t>
         </is>
       </c>
     </row>
@@ -2120,7 +2120,7 @@
       </c>
       <c r="K37" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:24Z</t>
+          <t>2026-10-10T23:42:24Z</t>
         </is>
       </c>
     </row>
@@ -2169,7 +2169,7 @@
       </c>
       <c r="K38" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:24Z</t>
+          <t>2026-10-10T23:42:24Z</t>
         </is>
       </c>
     </row>
@@ -2218,7 +2218,7 @@
       </c>
       <c r="K39" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:24Z</t>
+          <t>2026-10-10T23:42:24Z</t>
         </is>
       </c>
     </row>
@@ -2267,7 +2267,7 @@
       </c>
       <c r="K40" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:24Z</t>
+          <t>2026-10-10T23:42:24Z</t>
         </is>
       </c>
     </row>
@@ -2316,7 +2316,7 @@
       </c>
       <c r="K41" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:24Z</t>
+          <t>2026-10-10T23:42:24Z</t>
         </is>
       </c>
     </row>
@@ -2365,7 +2365,7 @@
       </c>
       <c r="K42" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:24Z</t>
+          <t>2026-10-10T23:42:24Z</t>
         </is>
       </c>
     </row>
@@ -2414,7 +2414,7 @@
       </c>
       <c r="K43" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:24Z</t>
+          <t>2026-10-10T23:42:24Z</t>
         </is>
       </c>
     </row>
@@ -2463,7 +2463,7 @@
       </c>
       <c r="K44" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:24Z</t>
+          <t>2026-10-10T23:42:24Z</t>
         </is>
       </c>
     </row>
@@ -2512,7 +2512,7 @@
       </c>
       <c r="K45" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:24Z</t>
+          <t>2026-10-10T23:42:24Z</t>
         </is>
       </c>
     </row>
@@ -2561,7 +2561,7 @@
       </c>
       <c r="K46" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:24Z</t>
+          <t>2026-10-10T23:42:24Z</t>
         </is>
       </c>
     </row>
@@ -2610,7 +2610,7 @@
       </c>
       <c r="K47" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:24Z</t>
+          <t>2026-10-10T23:42:24Z</t>
         </is>
       </c>
     </row>
@@ -2659,7 +2659,7 @@
       </c>
       <c r="K48" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:24Z</t>
+          <t>2026-10-10T23:42:24Z</t>
         </is>
       </c>
     </row>
@@ -2708,7 +2708,7 @@
       </c>
       <c r="K49" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:24Z</t>
+          <t>2026-10-10T23:42:24Z</t>
         </is>
       </c>
     </row>
@@ -2757,7 +2757,7 @@
       </c>
       <c r="K50" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:24Z</t>
+          <t>2026-10-10T23:42:24Z</t>
         </is>
       </c>
     </row>
@@ -2806,7 +2806,7 @@
       </c>
       <c r="K51" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:24Z</t>
+          <t>2026-10-10T23:42:24Z</t>
         </is>
       </c>
     </row>
@@ -2855,7 +2855,7 @@
       </c>
       <c r="K52" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:24Z</t>
+          <t>2026-10-10T23:42:24Z</t>
         </is>
       </c>
     </row>
@@ -2904,7 +2904,7 @@
       </c>
       <c r="K53" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:24Z</t>
+          <t>2026-10-10T23:42:24Z</t>
         </is>
       </c>
     </row>
@@ -2953,7 +2953,7 @@
       </c>
       <c r="K54" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:24Z</t>
+          <t>2026-10-10T23:42:24Z</t>
         </is>
       </c>
     </row>
@@ -3002,7 +3002,7 @@
       </c>
       <c r="K55" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:24Z</t>
+          <t>2026-10-10T23:42:24Z</t>
         </is>
       </c>
     </row>
@@ -3051,7 +3051,7 @@
       </c>
       <c r="K56" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:24Z</t>
+          <t>2026-10-10T23:42:24Z</t>
         </is>
       </c>
     </row>
@@ -3100,7 +3100,7 @@
       </c>
       <c r="K57" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:24Z</t>
+          <t>2026-10-10T23:42:24Z</t>
         </is>
       </c>
     </row>
@@ -3149,7 +3149,7 @@
       </c>
       <c r="K58" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:24Z</t>
+          <t>2026-10-10T23:42:24Z</t>
         </is>
       </c>
     </row>
@@ -3198,7 +3198,7 @@
       </c>
       <c r="K59" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:24Z</t>
+          <t>2026-10-10T23:42:24Z</t>
         </is>
       </c>
     </row>
@@ -3247,7 +3247,7 @@
       </c>
       <c r="K60" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:24Z</t>
+          <t>2026-10-10T23:42:24Z</t>
         </is>
       </c>
     </row>
@@ -3296,7 +3296,7 @@
       </c>
       <c r="K61" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:24Z</t>
+          <t>2026-10-10T23:42:24Z</t>
         </is>
       </c>
     </row>
@@ -3345,7 +3345,7 @@
       </c>
       <c r="K62" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:24Z</t>
+          <t>2026-10-10T23:42:24Z</t>
         </is>
       </c>
     </row>
@@ -3394,7 +3394,7 @@
       </c>
       <c r="K63" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:24Z</t>
+          <t>2026-10-10T23:42:24Z</t>
         </is>
       </c>
     </row>
@@ -3443,7 +3443,7 @@
       </c>
       <c r="K64" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:24Z</t>
+          <t>2026-10-10T23:42:24Z</t>
         </is>
       </c>
     </row>
@@ -3492,7 +3492,7 @@
       </c>
       <c r="K65" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:24Z</t>
+          <t>2026-10-10T23:42:24Z</t>
         </is>
       </c>
     </row>
@@ -3541,7 +3541,7 @@
       </c>
       <c r="K66" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:24Z</t>
+          <t>2026-10-10T23:42:24Z</t>
         </is>
       </c>
     </row>
@@ -3590,7 +3590,7 @@
       </c>
       <c r="K67" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:24Z</t>
+          <t>2026-10-10T23:42:24Z</t>
         </is>
       </c>
     </row>
@@ -3639,7 +3639,7 @@
       </c>
       <c r="K68" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:24Z</t>
+          <t>2026-10-10T23:42:24Z</t>
         </is>
       </c>
     </row>
@@ -3688,7 +3688,7 @@
       </c>
       <c r="K69" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:24Z</t>
+          <t>2026-10-10T23:42:24Z</t>
         </is>
       </c>
     </row>
@@ -3737,7 +3737,7 @@
       </c>
       <c r="K70" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:24Z</t>
+          <t>2026-10-10T23:42:24Z</t>
         </is>
       </c>
     </row>
@@ -3786,7 +3786,7 @@
       </c>
       <c r="K71" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:24Z</t>
+          <t>2026-10-10T23:42:24Z</t>
         </is>
       </c>
     </row>
@@ -3835,7 +3835,7 @@
       </c>
       <c r="K72" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:24Z</t>
+          <t>2026-10-10T23:42:24Z</t>
         </is>
       </c>
     </row>
@@ -3884,7 +3884,7 @@
       </c>
       <c r="K73" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:24Z</t>
+          <t>2026-10-10T23:42:24Z</t>
         </is>
       </c>
     </row>
@@ -3933,7 +3933,7 @@
       </c>
       <c r="K74" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:24Z</t>
+          <t>2026-10-10T23:42:24Z</t>
         </is>
       </c>
     </row>
@@ -3982,7 +3982,7 @@
       </c>
       <c r="K75" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:24Z</t>
+          <t>2026-10-10T23:42:24Z</t>
         </is>
       </c>
     </row>
@@ -4031,7 +4031,7 @@
       </c>
       <c r="K76" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:24Z</t>
+          <t>2026-10-10T23:42:24Z</t>
         </is>
       </c>
     </row>
@@ -4080,7 +4080,7 @@
       </c>
       <c r="K77" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:24Z</t>
+          <t>2026-10-10T23:42:24Z</t>
         </is>
       </c>
     </row>
@@ -4129,7 +4129,7 @@
       </c>
       <c r="K78" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:24Z</t>
+          <t>2026-10-10T23:42:24Z</t>
         </is>
       </c>
     </row>
@@ -4178,7 +4178,7 @@
       </c>
       <c r="K79" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:24Z</t>
+          <t>2026-10-10T23:42:24Z</t>
         </is>
       </c>
     </row>
@@ -4227,7 +4227,7 @@
       </c>
       <c r="K80" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:24Z</t>
+          <t>2026-10-10T23:42:24Z</t>
         </is>
       </c>
     </row>
@@ -4276,7 +4276,7 @@
       </c>
       <c r="K81" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:24Z</t>
+          <t>2026-10-10T23:42:24Z</t>
         </is>
       </c>
     </row>
@@ -4325,7 +4325,7 @@
       </c>
       <c r="K82" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:24Z</t>
+          <t>2026-10-10T23:42:24Z</t>
         </is>
       </c>
     </row>
@@ -4374,7 +4374,7 @@
       </c>
       <c r="K83" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:24Z</t>
+          <t>2026-10-10T23:42:24Z</t>
         </is>
       </c>
     </row>
@@ -4423,7 +4423,7 @@
       </c>
       <c r="K84" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:24Z</t>
+          <t>2026-10-10T23:42:24Z</t>
         </is>
       </c>
     </row>
@@ -4472,7 +4472,7 @@
       </c>
       <c r="K85" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:24Z</t>
+          <t>2026-10-10T23:42:24Z</t>
         </is>
       </c>
     </row>
@@ -4521,7 +4521,7 @@
       </c>
       <c r="K86" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:24Z</t>
+          <t>2026-10-10T23:42:24Z</t>
         </is>
       </c>
     </row>
@@ -4570,7 +4570,7 @@
       </c>
       <c r="K87" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:24Z</t>
+          <t>2026-10-10T23:42:24Z</t>
         </is>
       </c>
     </row>
@@ -4619,7 +4619,7 @@
       </c>
       <c r="K88" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:24Z</t>
+          <t>2026-10-10T23:42:24Z</t>
         </is>
       </c>
     </row>
@@ -4668,7 +4668,7 @@
       </c>
       <c r="K89" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:24Z</t>
+          <t>2026-10-10T23:42:24Z</t>
         </is>
       </c>
     </row>
@@ -4717,7 +4717,7 @@
       </c>
       <c r="K90" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:24Z</t>
+          <t>2026-10-10T23:42:24Z</t>
         </is>
       </c>
     </row>
@@ -4766,7 +4766,7 @@
       </c>
       <c r="K91" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:24Z</t>
+          <t>2026-10-10T23:42:24Z</t>
         </is>
       </c>
     </row>
@@ -4815,7 +4815,7 @@
       </c>
       <c r="K92" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:24Z</t>
+          <t>2026-10-10T23:42:24Z</t>
         </is>
       </c>
     </row>
@@ -4864,7 +4864,7 @@
       </c>
       <c r="K93" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:24Z</t>
+          <t>2026-10-10T23:42:24Z</t>
         </is>
       </c>
     </row>
@@ -4913,7 +4913,7 @@
       </c>
       <c r="K94" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:24Z</t>
+          <t>2026-10-10T23:42:24Z</t>
         </is>
       </c>
     </row>
@@ -4962,7 +4962,7 @@
       </c>
       <c r="K95" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:24Z</t>
+          <t>2026-10-10T23:42:24Z</t>
         </is>
       </c>
     </row>
@@ -5011,7 +5011,7 @@
       </c>
       <c r="K96" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:24Z</t>
+          <t>2026-10-10T23:42:24Z</t>
         </is>
       </c>
     </row>
@@ -5060,7 +5060,7 @@
       </c>
       <c r="K97" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:24Z</t>
+          <t>2026-10-10T23:42:24Z</t>
         </is>
       </c>
     </row>
@@ -5109,7 +5109,7 @@
       </c>
       <c r="K98" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:24Z</t>
+          <t>2026-10-10T23:42:24Z</t>
         </is>
       </c>
     </row>
@@ -5158,7 +5158,7 @@
       </c>
       <c r="K99" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:24Z</t>
+          <t>2026-10-10T23:42:24Z</t>
         </is>
       </c>
     </row>
@@ -5207,7 +5207,7 @@
       </c>
       <c r="K100" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:24Z</t>
+          <t>2026-10-10T23:42:24Z</t>
         </is>
       </c>
     </row>
@@ -5256,7 +5256,7 @@
       </c>
       <c r="K101" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:24Z</t>
+          <t>2026-10-10T23:42:24Z</t>
         </is>
       </c>
     </row>
@@ -5305,7 +5305,7 @@
       </c>
       <c r="K102" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:24Z</t>
+          <t>2026-10-10T23:42:24Z</t>
         </is>
       </c>
     </row>
@@ -5354,7 +5354,7 @@
       </c>
       <c r="K103" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:24Z</t>
+          <t>2026-10-10T23:42:24Z</t>
         </is>
       </c>
     </row>
@@ -5403,7 +5403,7 @@
       </c>
       <c r="K104" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:24Z</t>
+          <t>2026-10-10T23:42:24Z</t>
         </is>
       </c>
     </row>
@@ -5452,7 +5452,7 @@
       </c>
       <c r="K105" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:24Z</t>
+          <t>2026-10-10T23:42:24Z</t>
         </is>
       </c>
     </row>
@@ -5501,7 +5501,7 @@
       </c>
       <c r="K106" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:24Z</t>
+          <t>2026-10-10T23:42:24Z</t>
         </is>
       </c>
     </row>
@@ -5550,7 +5550,7 @@
       </c>
       <c r="K107" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:24Z</t>
+          <t>2026-10-10T23:42:24Z</t>
         </is>
       </c>
     </row>
@@ -5599,7 +5599,7 @@
       </c>
       <c r="K108" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:24Z</t>
+          <t>2026-10-10T23:42:24Z</t>
         </is>
       </c>
     </row>
@@ -5648,7 +5648,7 @@
       </c>
       <c r="K109" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:24Z</t>
+          <t>2026-10-10T23:42:24Z</t>
         </is>
       </c>
     </row>
@@ -5697,7 +5697,7 @@
       </c>
       <c r="K110" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:24Z</t>
+          <t>2026-10-10T23:42:24Z</t>
         </is>
       </c>
     </row>
@@ -5746,7 +5746,7 @@
       </c>
       <c r="K111" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:24Z</t>
+          <t>2026-10-10T23:42:24Z</t>
         </is>
       </c>
     </row>
@@ -5795,7 +5795,7 @@
       </c>
       <c r="K112" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:24Z</t>
+          <t>2026-10-10T23:42:24Z</t>
         </is>
       </c>
     </row>
@@ -5844,7 +5844,7 @@
       </c>
       <c r="K113" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:24Z</t>
+          <t>2026-10-10T23:42:24Z</t>
         </is>
       </c>
     </row>
@@ -5893,7 +5893,7 @@
       </c>
       <c r="K114" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:24Z</t>
+          <t>2026-10-10T23:42:24Z</t>
         </is>
       </c>
     </row>
@@ -5942,7 +5942,7 @@
       </c>
       <c r="K115" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:24Z</t>
+          <t>2026-10-10T23:42:24Z</t>
         </is>
       </c>
     </row>
@@ -5991,7 +5991,7 @@
       </c>
       <c r="K116" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:24Z</t>
+          <t>2026-10-10T23:42:24Z</t>
         </is>
       </c>
     </row>
@@ -6040,7 +6040,7 @@
       </c>
       <c r="K117" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:24Z</t>
+          <t>2026-10-10T23:42:24Z</t>
         </is>
       </c>
     </row>
@@ -6089,7 +6089,7 @@
       </c>
       <c r="K118" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:24Z</t>
+          <t>2026-10-10T23:42:24Z</t>
         </is>
       </c>
     </row>
@@ -6138,7 +6138,7 @@
       </c>
       <c r="K119" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:24Z</t>
+          <t>2026-10-10T23:42:24Z</t>
         </is>
       </c>
     </row>
@@ -6187,7 +6187,7 @@
       </c>
       <c r="K120" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:24Z</t>
+          <t>2026-10-10T23:42:24Z</t>
         </is>
       </c>
     </row>
@@ -6236,7 +6236,7 @@
       </c>
       <c r="K121" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:24Z</t>
+          <t>2026-10-10T23:42:24Z</t>
         </is>
       </c>
     </row>
@@ -6285,7 +6285,7 @@
       </c>
       <c r="K122" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:24Z</t>
+          <t>2026-10-10T23:42:24Z</t>
         </is>
       </c>
     </row>
@@ -6334,7 +6334,7 @@
       </c>
       <c r="K123" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:24Z</t>
+          <t>2026-10-10T23:42:24Z</t>
         </is>
       </c>
     </row>
@@ -6383,7 +6383,7 @@
       </c>
       <c r="K124" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:24Z</t>
+          <t>2026-10-10T23:42:24Z</t>
         </is>
       </c>
     </row>
@@ -6432,7 +6432,7 @@
       </c>
       <c r="K125" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:24Z</t>
+          <t>2026-10-10T23:42:24Z</t>
         </is>
       </c>
     </row>
@@ -6481,7 +6481,7 @@
       </c>
       <c r="K126" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:24Z</t>
+          <t>2026-10-10T23:42:24Z</t>
         </is>
       </c>
     </row>
@@ -6530,7 +6530,7 @@
       </c>
       <c r="K127" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:24Z</t>
+          <t>2026-10-10T23:42:24Z</t>
         </is>
       </c>
     </row>
@@ -6579,7 +6579,7 @@
       </c>
       <c r="K128" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:24Z</t>
+          <t>2026-10-10T23:42:24Z</t>
         </is>
       </c>
     </row>
@@ -6628,7 +6628,7 @@
       </c>
       <c r="K129" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:24Z</t>
+          <t>2026-10-10T23:42:24Z</t>
         </is>
       </c>
     </row>
@@ -6677,7 +6677,7 @@
       </c>
       <c r="K130" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:24Z</t>
+          <t>2026-10-10T23:42:24Z</t>
         </is>
       </c>
     </row>
@@ -6726,7 +6726,7 @@
       </c>
       <c r="K131" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:24Z</t>
+          <t>2026-10-10T23:42:24Z</t>
         </is>
       </c>
     </row>
@@ -6775,7 +6775,7 @@
       </c>
       <c r="K132" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:24Z</t>
+          <t>2026-10-10T23:42:24Z</t>
         </is>
       </c>
     </row>
@@ -6824,7 +6824,7 @@
       </c>
       <c r="K133" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:24Z</t>
+          <t>2026-10-10T23:42:24Z</t>
         </is>
       </c>
     </row>
@@ -6873,7 +6873,7 @@
       </c>
       <c r="K134" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:24Z</t>
+          <t>2026-10-10T23:42:24Z</t>
         </is>
       </c>
     </row>
@@ -6922,7 +6922,7 @@
       </c>
       <c r="K135" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:24Z</t>
+          <t>2026-10-10T23:42:24Z</t>
         </is>
       </c>
     </row>
@@ -6971,7 +6971,7 @@
       </c>
       <c r="K136" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:24Z</t>
+          <t>2026-10-10T23:42:24Z</t>
         </is>
       </c>
     </row>
@@ -7020,7 +7020,7 @@
       </c>
       <c r="K137" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:24Z</t>
+          <t>2026-10-10T23:42:24Z</t>
         </is>
       </c>
     </row>
@@ -7069,7 +7069,7 @@
       </c>
       <c r="K138" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:24Z</t>
+          <t>2026-10-10T23:42:24Z</t>
         </is>
       </c>
     </row>
@@ -7118,7 +7118,7 @@
       </c>
       <c r="K139" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:24Z</t>
+          <t>2026-10-10T23:42:24Z</t>
         </is>
       </c>
     </row>
@@ -7167,7 +7167,7 @@
       </c>
       <c r="K140" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:24Z</t>
+          <t>2026-10-10T23:42:24Z</t>
         </is>
       </c>
     </row>
@@ -7216,7 +7216,7 @@
       </c>
       <c r="K141" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:24Z</t>
+          <t>2026-10-10T23:42:24Z</t>
         </is>
       </c>
     </row>
@@ -7265,7 +7265,7 @@
       </c>
       <c r="K142" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:24Z</t>
+          <t>2026-10-10T23:42:24Z</t>
         </is>
       </c>
     </row>
@@ -7314,7 +7314,7 @@
       </c>
       <c r="K143" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:24Z</t>
+          <t>2026-10-10T23:42:24Z</t>
         </is>
       </c>
     </row>
@@ -7363,7 +7363,7 @@
       </c>
       <c r="K144" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:24Z</t>
+          <t>2026-10-10T23:42:24Z</t>
         </is>
       </c>
     </row>
@@ -7412,7 +7412,7 @@
       </c>
       <c r="K145" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:24Z</t>
+          <t>2026-10-10T23:42:24Z</t>
         </is>
       </c>
     </row>
@@ -7461,7 +7461,7 @@
       </c>
       <c r="K146" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:24Z</t>
+          <t>2026-10-10T23:42:24Z</t>
         </is>
       </c>
     </row>
@@ -7510,7 +7510,7 @@
       </c>
       <c r="K147" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:24Z</t>
+          <t>2026-10-10T23:42:24Z</t>
         </is>
       </c>
     </row>
@@ -7559,7 +7559,7 @@
       </c>
       <c r="K148" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:24Z</t>
+          <t>2026-10-10T23:42:24Z</t>
         </is>
       </c>
     </row>
@@ -7608,7 +7608,7 @@
       </c>
       <c r="K149" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:24Z</t>
+          <t>2026-10-10T23:42:24Z</t>
         </is>
       </c>
     </row>
@@ -7657,7 +7657,7 @@
       </c>
       <c r="K150" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:24Z</t>
+          <t>2026-10-10T23:42:24Z</t>
         </is>
       </c>
     </row>
@@ -7706,7 +7706,7 @@
       </c>
       <c r="K151" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:24Z</t>
+          <t>2026-10-10T23:42:24Z</t>
         </is>
       </c>
     </row>
@@ -7755,7 +7755,7 @@
       </c>
       <c r="K152" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:24Z</t>
+          <t>2026-10-10T23:42:24Z</t>
         </is>
       </c>
     </row>
@@ -7804,7 +7804,7 @@
       </c>
       <c r="K153" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:24Z</t>
+          <t>2026-10-10T23:42:24Z</t>
         </is>
       </c>
     </row>
@@ -7853,7 +7853,7 @@
       </c>
       <c r="K154" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:24Z</t>
+          <t>2026-10-10T23:42:24Z</t>
         </is>
       </c>
     </row>
@@ -7902,7 +7902,7 @@
       </c>
       <c r="K155" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:24Z</t>
+          <t>2026-10-10T23:42:24Z</t>
         </is>
       </c>
     </row>
@@ -7951,7 +7951,7 @@
       </c>
       <c r="K156" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:24Z</t>
+          <t>2026-10-10T23:42:24Z</t>
         </is>
       </c>
     </row>
@@ -8000,7 +8000,7 @@
       </c>
       <c r="K157" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:24Z</t>
+          <t>2026-10-10T23:42:24Z</t>
         </is>
       </c>
     </row>
@@ -8049,7 +8049,7 @@
       </c>
       <c r="K158" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:24Z</t>
+          <t>2026-10-10T23:42:24Z</t>
         </is>
       </c>
     </row>
@@ -8098,7 +8098,7 @@
       </c>
       <c r="K159" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:24Z</t>
+          <t>2026-10-10T23:42:24Z</t>
         </is>
       </c>
     </row>
@@ -8147,7 +8147,7 @@
       </c>
       <c r="K160" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:24Z</t>
+          <t>2026-10-10T23:42:24Z</t>
         </is>
       </c>
     </row>
@@ -8196,7 +8196,7 @@
       </c>
       <c r="K161" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:24Z</t>
+          <t>2026-10-10T23:42:24Z</t>
         </is>
       </c>
     </row>
@@ -8245,7 +8245,7 @@
       </c>
       <c r="K162" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:24Z</t>
+          <t>2026-10-10T23:42:24Z</t>
         </is>
       </c>
     </row>
@@ -8294,7 +8294,7 @@
       </c>
       <c r="K163" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:24Z</t>
+          <t>2026-10-10T23:42:24Z</t>
         </is>
       </c>
     </row>
@@ -8343,7 +8343,7 @@
       </c>
       <c r="K164" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:24Z</t>
+          <t>2026-10-10T23:42:24Z</t>
         </is>
       </c>
     </row>
@@ -8392,7 +8392,7 @@
       </c>
       <c r="K165" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:24Z</t>
+          <t>2026-10-10T23:42:24Z</t>
         </is>
       </c>
     </row>
@@ -8441,7 +8441,7 @@
       </c>
       <c r="K166" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:24Z</t>
+          <t>2026-10-10T23:42:24Z</t>
         </is>
       </c>
     </row>
@@ -8490,7 +8490,7 @@
       </c>
       <c r="K167" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:24Z</t>
+          <t>2026-10-10T23:42:24Z</t>
         </is>
       </c>
     </row>
@@ -8539,7 +8539,7 @@
       </c>
       <c r="K168" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:24Z</t>
+          <t>2026-10-10T23:42:24Z</t>
         </is>
       </c>
     </row>
@@ -8588,7 +8588,7 @@
       </c>
       <c r="K169" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:24Z</t>
+          <t>2026-10-10T23:42:24Z</t>
         </is>
       </c>
     </row>
@@ -8637,7 +8637,7 @@
       </c>
       <c r="K170" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:24Z</t>
+          <t>2026-10-10T23:42:24Z</t>
         </is>
       </c>
     </row>
@@ -8686,7 +8686,7 @@
       </c>
       <c r="K171" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:24Z</t>
+          <t>2026-10-10T23:42:24Z</t>
         </is>
       </c>
     </row>
@@ -8735,7 +8735,7 @@
       </c>
       <c r="K172" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:24Z</t>
+          <t>2026-10-10T23:42:24Z</t>
         </is>
       </c>
     </row>
@@ -8784,7 +8784,7 @@
       </c>
       <c r="K173" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:24Z</t>
+          <t>2026-10-10T23:42:24Z</t>
         </is>
       </c>
     </row>
@@ -8833,7 +8833,7 @@
       </c>
       <c r="K174" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:24Z</t>
+          <t>2026-10-10T23:42:24Z</t>
         </is>
       </c>
     </row>
@@ -8882,7 +8882,7 @@
       </c>
       <c r="K175" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:24Z</t>
+          <t>2026-10-10T23:42:24Z</t>
         </is>
       </c>
     </row>
@@ -8931,7 +8931,7 @@
       </c>
       <c r="K176" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:24Z</t>
+          <t>2026-10-10T23:42:24Z</t>
         </is>
       </c>
     </row>
@@ -8980,7 +8980,7 @@
       </c>
       <c r="K177" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:24Z</t>
+          <t>2026-10-10T23:42:24Z</t>
         </is>
       </c>
     </row>
@@ -9029,7 +9029,7 @@
       </c>
       <c r="K178" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:24Z</t>
+          <t>2026-10-10T23:42:24Z</t>
         </is>
       </c>
     </row>
@@ -9078,7 +9078,7 @@
       </c>
       <c r="K179" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:24Z</t>
+          <t>2026-10-10T23:42:24Z</t>
         </is>
       </c>
     </row>
@@ -9127,7 +9127,7 @@
       </c>
       <c r="K180" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:24Z</t>
+          <t>2026-10-10T23:42:24Z</t>
         </is>
       </c>
     </row>
@@ -9176,7 +9176,7 @@
       </c>
       <c r="K181" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:24Z</t>
+          <t>2026-10-10T23:42:24Z</t>
         </is>
       </c>
     </row>
@@ -9225,7 +9225,7 @@
       </c>
       <c r="K182" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:24Z</t>
+          <t>2026-10-10T23:42:24Z</t>
         </is>
       </c>
     </row>
@@ -9274,7 +9274,7 @@
       </c>
       <c r="K183" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:24Z</t>
+          <t>2026-10-10T23:42:24Z</t>
         </is>
       </c>
     </row>
@@ -9323,7 +9323,7 @@
       </c>
       <c r="K184" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:24Z</t>
+          <t>2026-10-10T23:42:24Z</t>
         </is>
       </c>
     </row>
@@ -9372,7 +9372,7 @@
       </c>
       <c r="K185" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:24Z</t>
+          <t>2026-10-10T23:42:24Z</t>
         </is>
       </c>
     </row>
@@ -9421,7 +9421,7 @@
       </c>
       <c r="K186" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:24Z</t>
+          <t>2026-10-10T23:42:24Z</t>
         </is>
       </c>
     </row>
@@ -9470,7 +9470,7 @@
       </c>
       <c r="K187" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:24Z</t>
+          <t>2026-10-10T23:42:24Z</t>
         </is>
       </c>
     </row>
@@ -9519,7 +9519,7 @@
       </c>
       <c r="K188" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:24Z</t>
+          <t>2026-10-10T23:42:24Z</t>
         </is>
       </c>
     </row>
@@ -9568,7 +9568,7 @@
       </c>
       <c r="K189" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:24Z</t>
+          <t>2026-10-10T23:42:24Z</t>
         </is>
       </c>
     </row>
@@ -9617,7 +9617,7 @@
       </c>
       <c r="K190" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:24Z</t>
+          <t>2026-10-10T23:42:24Z</t>
         </is>
       </c>
     </row>
@@ -9666,7 +9666,7 @@
       </c>
       <c r="K191" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:24Z</t>
+          <t>2026-10-10T23:42:24Z</t>
         </is>
       </c>
     </row>
@@ -9715,7 +9715,7 @@
       </c>
       <c r="K192" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:24Z</t>
+          <t>2026-10-10T23:42:24Z</t>
         </is>
       </c>
     </row>
@@ -9764,7 +9764,7 @@
       </c>
       <c r="K193" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:24Z</t>
+          <t>2026-10-10T23:42:24Z</t>
         </is>
       </c>
     </row>
@@ -9813,7 +9813,7 @@
       </c>
       <c r="K194" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:24Z</t>
+          <t>2026-10-10T23:42:24Z</t>
         </is>
       </c>
     </row>
@@ -9862,7 +9862,7 @@
       </c>
       <c r="K195" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:24Z</t>
+          <t>2026-10-10T23:42:24Z</t>
         </is>
       </c>
     </row>
@@ -9911,7 +9911,7 @@
       </c>
       <c r="K196" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:24Z</t>
+          <t>2026-10-10T23:42:24Z</t>
         </is>
       </c>
     </row>
@@ -9960,7 +9960,7 @@
       </c>
       <c r="K197" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:24Z</t>
+          <t>2026-10-10T23:42:24Z</t>
         </is>
       </c>
     </row>
@@ -10009,7 +10009,7 @@
       </c>
       <c r="K198" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:24Z</t>
+          <t>2026-10-10T23:42:24Z</t>
         </is>
       </c>
     </row>
@@ -10058,7 +10058,7 @@
       </c>
       <c r="K199" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:24Z</t>
+          <t>2026-10-10T23:42:24Z</t>
         </is>
       </c>
     </row>
@@ -10107,7 +10107,7 @@
       </c>
       <c r="K200" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:24Z</t>
+          <t>2026-10-10T23:42:24Z</t>
         </is>
       </c>
     </row>
@@ -10156,7 +10156,7 @@
       </c>
       <c r="K201" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:24Z</t>
+          <t>2026-10-10T23:42:24Z</t>
         </is>
       </c>
     </row>
@@ -10205,7 +10205,7 @@
       </c>
       <c r="K202" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:24Z</t>
+          <t>2026-10-10T23:42:24Z</t>
         </is>
       </c>
     </row>
@@ -10254,7 +10254,7 @@
       </c>
       <c r="K203" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:24Z</t>
+          <t>2026-10-10T23:42:24Z</t>
         </is>
       </c>
     </row>
@@ -10303,7 +10303,7 @@
       </c>
       <c r="K204" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:24Z</t>
+          <t>2026-10-10T23:42:24Z</t>
         </is>
       </c>
     </row>
@@ -10352,7 +10352,7 @@
       </c>
       <c r="K205" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:24Z</t>
+          <t>2026-10-10T23:42:24Z</t>
         </is>
       </c>
     </row>
@@ -10401,7 +10401,7 @@
       </c>
       <c r="K206" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:24Z</t>
+          <t>2026-10-10T23:42:24Z</t>
         </is>
       </c>
     </row>
@@ -10450,7 +10450,7 @@
       </c>
       <c r="K207" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:24Z</t>
+          <t>2026-10-10T23:42:24Z</t>
         </is>
       </c>
     </row>
@@ -10499,7 +10499,7 @@
       </c>
       <c r="K208" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:24Z</t>
+          <t>2026-10-10T23:42:24Z</t>
         </is>
       </c>
     </row>
@@ -10548,7 +10548,7 @@
       </c>
       <c r="K209" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:24Z</t>
+          <t>2026-10-10T23:42:24Z</t>
         </is>
       </c>
     </row>
@@ -10597,7 +10597,7 @@
       </c>
       <c r="K210" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:24Z</t>
+          <t>2026-10-10T23:42:24Z</t>
         </is>
       </c>
     </row>
@@ -10646,7 +10646,7 @@
       </c>
       <c r="K211" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:24Z</t>
+          <t>2026-10-10T23:42:24Z</t>
         </is>
       </c>
     </row>
@@ -10695,7 +10695,7 @@
       </c>
       <c r="K212" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:24Z</t>
+          <t>2026-10-10T23:42:24Z</t>
         </is>
       </c>
     </row>
@@ -10744,7 +10744,7 @@
       </c>
       <c r="K213" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:24Z</t>
+          <t>2026-10-10T23:42:24Z</t>
         </is>
       </c>
     </row>
@@ -10793,7 +10793,7 @@
       </c>
       <c r="K214" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:24Z</t>
+          <t>2026-10-10T23:42:24Z</t>
         </is>
       </c>
     </row>
@@ -10842,7 +10842,7 @@
       </c>
       <c r="K215" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:24Z</t>
+          <t>2026-10-10T23:42:24Z</t>
         </is>
       </c>
     </row>
@@ -10891,7 +10891,7 @@
       </c>
       <c r="K216" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:24Z</t>
+          <t>2026-10-10T23:42:24Z</t>
         </is>
       </c>
     </row>
@@ -10940,7 +10940,7 @@
       </c>
       <c r="K217" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:24Z</t>
+          <t>2026-10-10T23:42:24Z</t>
         </is>
       </c>
     </row>
@@ -10989,7 +10989,7 @@
       </c>
       <c r="K218" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:24Z</t>
+          <t>2026-10-10T23:42:24Z</t>
         </is>
       </c>
     </row>
@@ -11038,7 +11038,7 @@
       </c>
       <c r="K219" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:24Z</t>
+          <t>2026-10-10T23:42:24Z</t>
         </is>
       </c>
     </row>
@@ -11087,7 +11087,7 @@
       </c>
       <c r="K220" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:24Z</t>
+          <t>2026-10-10T23:42:24Z</t>
         </is>
       </c>
     </row>
@@ -11136,7 +11136,7 @@
       </c>
       <c r="K221" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:24Z</t>
+          <t>2026-10-10T23:42:24Z</t>
         </is>
       </c>
     </row>
@@ -11185,7 +11185,7 @@
       </c>
       <c r="K222" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:24Z</t>
+          <t>2026-10-10T23:42:24Z</t>
         </is>
       </c>
     </row>
@@ -11234,7 +11234,7 @@
       </c>
       <c r="K223" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:24Z</t>
+          <t>2026-10-10T23:42:24Z</t>
         </is>
       </c>
     </row>
@@ -11283,7 +11283,7 @@
       </c>
       <c r="K224" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:24Z</t>
+          <t>2026-10-10T23:42:24Z</t>
         </is>
       </c>
     </row>
@@ -11332,7 +11332,7 @@
       </c>
       <c r="K225" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:24Z</t>
+          <t>2026-10-10T23:42:24Z</t>
         </is>
       </c>
     </row>
@@ -11381,7 +11381,7 @@
       </c>
       <c r="K226" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:24Z</t>
+          <t>2026-10-10T23:42:24Z</t>
         </is>
       </c>
     </row>
@@ -11430,7 +11430,7 @@
       </c>
       <c r="K227" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:24Z</t>
+          <t>2026-10-10T23:42:24Z</t>
         </is>
       </c>
     </row>
@@ -11479,7 +11479,7 @@
       </c>
       <c r="K228" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:24Z</t>
+          <t>2026-10-10T23:42:24Z</t>
         </is>
       </c>
     </row>
@@ -11528,7 +11528,7 @@
       </c>
       <c r="K229" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:24Z</t>
+          <t>2026-10-10T23:42:24Z</t>
         </is>
       </c>
     </row>
@@ -11577,7 +11577,7 @@
       </c>
       <c r="K230" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:24Z</t>
+          <t>2026-10-10T23:42:24Z</t>
         </is>
       </c>
     </row>
@@ -11626,7 +11626,7 @@
       </c>
       <c r="K231" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:24Z</t>
+          <t>2026-10-10T23:42:24Z</t>
         </is>
       </c>
     </row>
@@ -11758,7 +11758,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:24Z</t>
+          <t>2026-10-10T23:42:24Z</t>
         </is>
       </c>
     </row>
@@ -11804,7 +11804,7 @@
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>{"date": "2026-08-01", "year": 2026, "month": 8, "month_name": "Agosto", "index_value": 637409769724325.1, "monthly_variation_pct": 8.9, "unit": "Índice base diciembre 2007=100 y variación mensual %", "frequency": "monthly", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/precios_consumidor/4_5_7_2.xls", "fetched_at": "2026-10-10T00:11:24Z"}</t>
+          <t>{"date": "2026-08-01", "year": 2026, "month": 8, "month_name": "Agosto", "index_value": 637409769724325.1, "monthly_variation_pct": 8.9, "unit": "Índice base diciembre 2007=100 y variación mensual %", "frequency": "monthly", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/precios_consumidor/4_5_7_2.xls", "fetched_at": "2026-10-10T23:42:24Z"}</t>
         </is>
       </c>
     </row>

--- a/assets/data/bcv/excel/ove_bcv_inpc_nacional_mensual.xlsx
+++ b/assets/data/bcv/excel/ove_bcv_inpc_nacional_mensual.xlsx
@@ -650,7 +650,7 @@
       </c>
       <c r="K7" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:24Z</t>
+          <t>2026-10-11T23:49:13Z</t>
         </is>
       </c>
     </row>
@@ -699,7 +699,7 @@
       </c>
       <c r="K8" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:24Z</t>
+          <t>2026-10-11T23:49:13Z</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="K9" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:24Z</t>
+          <t>2026-10-11T23:49:13Z</t>
         </is>
       </c>
     </row>
@@ -797,7 +797,7 @@
       </c>
       <c r="K10" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:24Z</t>
+          <t>2026-10-11T23:49:13Z</t>
         </is>
       </c>
     </row>
@@ -846,7 +846,7 @@
       </c>
       <c r="K11" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:24Z</t>
+          <t>2026-10-11T23:49:13Z</t>
         </is>
       </c>
     </row>
@@ -895,7 +895,7 @@
       </c>
       <c r="K12" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:24Z</t>
+          <t>2026-10-11T23:49:13Z</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="K13" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:24Z</t>
+          <t>2026-10-11T23:49:13Z</t>
         </is>
       </c>
     </row>
@@ -993,7 +993,7 @@
       </c>
       <c r="K14" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:24Z</t>
+          <t>2026-10-11T23:49:13Z</t>
         </is>
       </c>
     </row>
@@ -1042,7 +1042,7 @@
       </c>
       <c r="K15" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:24Z</t>
+          <t>2026-10-11T23:49:13Z</t>
         </is>
       </c>
     </row>
@@ -1091,7 +1091,7 @@
       </c>
       <c r="K16" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:24Z</t>
+          <t>2026-10-11T23:49:13Z</t>
         </is>
       </c>
     </row>
@@ -1140,7 +1140,7 @@
       </c>
       <c r="K17" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:24Z</t>
+          <t>2026-10-11T23:49:13Z</t>
         </is>
       </c>
     </row>
@@ -1189,7 +1189,7 @@
       </c>
       <c r="K18" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:24Z</t>
+          <t>2026-10-11T23:49:13Z</t>
         </is>
       </c>
     </row>
@@ -1238,7 +1238,7 @@
       </c>
       <c r="K19" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:24Z</t>
+          <t>2026-10-11T23:49:13Z</t>
         </is>
       </c>
     </row>
@@ -1287,7 +1287,7 @@
       </c>
       <c r="K20" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:24Z</t>
+          <t>2026-10-11T23:49:13Z</t>
         </is>
       </c>
     </row>
@@ -1336,7 +1336,7 @@
       </c>
       <c r="K21" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:24Z</t>
+          <t>2026-10-11T23:49:13Z</t>
         </is>
       </c>
     </row>
@@ -1385,7 +1385,7 @@
       </c>
       <c r="K22" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:24Z</t>
+          <t>2026-10-11T23:49:13Z</t>
         </is>
       </c>
     </row>
@@ -1434,7 +1434,7 @@
       </c>
       <c r="K23" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:24Z</t>
+          <t>2026-10-11T23:49:13Z</t>
         </is>
       </c>
     </row>
@@ -1483,7 +1483,7 @@
       </c>
       <c r="K24" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:24Z</t>
+          <t>2026-10-11T23:49:13Z</t>
         </is>
       </c>
     </row>
@@ -1532,7 +1532,7 @@
       </c>
       <c r="K25" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:24Z</t>
+          <t>2026-10-11T23:49:13Z</t>
         </is>
       </c>
     </row>
@@ -1581,7 +1581,7 @@
       </c>
       <c r="K26" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:24Z</t>
+          <t>2026-10-11T23:49:13Z</t>
         </is>
       </c>
     </row>
@@ -1630,7 +1630,7 @@
       </c>
       <c r="K27" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:24Z</t>
+          <t>2026-10-11T23:49:13Z</t>
         </is>
       </c>
     </row>
@@ -1679,7 +1679,7 @@
       </c>
       <c r="K28" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:24Z</t>
+          <t>2026-10-11T23:49:13Z</t>
         </is>
       </c>
     </row>
@@ -1728,7 +1728,7 @@
       </c>
       <c r="K29" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:24Z</t>
+          <t>2026-10-11T23:49:13Z</t>
         </is>
       </c>
     </row>
@@ -1777,7 +1777,7 @@
       </c>
       <c r="K30" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:24Z</t>
+          <t>2026-10-11T23:49:13Z</t>
         </is>
       </c>
     </row>
@@ -1826,7 +1826,7 @@
       </c>
       <c r="K31" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:24Z</t>
+          <t>2026-10-11T23:49:13Z</t>
         </is>
       </c>
     </row>
@@ -1875,7 +1875,7 @@
       </c>
       <c r="K32" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:24Z</t>
+          <t>2026-10-11T23:49:13Z</t>
         </is>
       </c>
     </row>
@@ -1924,7 +1924,7 @@
       </c>
       <c r="K33" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:24Z</t>
+          <t>2026-10-11T23:49:13Z</t>
         </is>
       </c>
     </row>
@@ -1973,7 +1973,7 @@
       </c>
       <c r="K34" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:24Z</t>
+          <t>2026-10-11T23:49:13Z</t>
         </is>
       </c>
     </row>
@@ -2022,7 +2022,7 @@
       </c>
       <c r="K35" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:24Z</t>
+          <t>2026-10-11T23:49:13Z</t>
         </is>
       </c>
     </row>
@@ -2071,7 +2071,7 @@
       </c>
       <c r="K36" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:24Z</t>
+          <t>2026-10-11T23:49:13Z</t>
         </is>
       </c>
     </row>
@@ -2120,7 +2120,7 @@
       </c>
       <c r="K37" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:24Z</t>
+          <t>2026-10-11T23:49:13Z</t>
         </is>
       </c>
     </row>
@@ -2169,7 +2169,7 @@
       </c>
       <c r="K38" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:24Z</t>
+          <t>2026-10-11T23:49:13Z</t>
         </is>
       </c>
     </row>
@@ -2218,7 +2218,7 @@
       </c>
       <c r="K39" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:24Z</t>
+          <t>2026-10-11T23:49:13Z</t>
         </is>
       </c>
     </row>
@@ -2267,7 +2267,7 @@
       </c>
       <c r="K40" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:24Z</t>
+          <t>2026-10-11T23:49:13Z</t>
         </is>
       </c>
     </row>
@@ -2316,7 +2316,7 @@
       </c>
       <c r="K41" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:24Z</t>
+          <t>2026-10-11T23:49:13Z</t>
         </is>
       </c>
     </row>
@@ -2365,7 +2365,7 @@
       </c>
       <c r="K42" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:24Z</t>
+          <t>2026-10-11T23:49:13Z</t>
         </is>
       </c>
     </row>
@@ -2414,7 +2414,7 @@
       </c>
       <c r="K43" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:24Z</t>
+          <t>2026-10-11T23:49:13Z</t>
         </is>
       </c>
     </row>
@@ -2463,7 +2463,7 @@
       </c>
       <c r="K44" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:24Z</t>
+          <t>2026-10-11T23:49:13Z</t>
         </is>
       </c>
     </row>
@@ -2512,7 +2512,7 @@
       </c>
       <c r="K45" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:24Z</t>
+          <t>2026-10-11T23:49:13Z</t>
         </is>
       </c>
     </row>
@@ -2561,7 +2561,7 @@
       </c>
       <c r="K46" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:24Z</t>
+          <t>2026-10-11T23:49:13Z</t>
         </is>
       </c>
     </row>
@@ -2610,7 +2610,7 @@
       </c>
       <c r="K47" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:24Z</t>
+          <t>2026-10-11T23:49:13Z</t>
         </is>
       </c>
     </row>
@@ -2659,7 +2659,7 @@
       </c>
       <c r="K48" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:24Z</t>
+          <t>2026-10-11T23:49:13Z</t>
         </is>
       </c>
     </row>
@@ -2708,7 +2708,7 @@
       </c>
       <c r="K49" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:24Z</t>
+          <t>2026-10-11T23:49:13Z</t>
         </is>
       </c>
     </row>
@@ -2757,7 +2757,7 @@
       </c>
       <c r="K50" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:24Z</t>
+          <t>2026-10-11T23:49:13Z</t>
         </is>
       </c>
     </row>
@@ -2806,7 +2806,7 @@
       </c>
       <c r="K51" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:24Z</t>
+          <t>2026-10-11T23:49:13Z</t>
         </is>
       </c>
     </row>
@@ -2855,7 +2855,7 @@
       </c>
       <c r="K52" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:24Z</t>
+          <t>2026-10-11T23:49:13Z</t>
         </is>
       </c>
     </row>
@@ -2904,7 +2904,7 @@
       </c>
       <c r="K53" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:24Z</t>
+          <t>2026-10-11T23:49:13Z</t>
         </is>
       </c>
     </row>
@@ -2953,7 +2953,7 @@
       </c>
       <c r="K54" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:24Z</t>
+          <t>2026-10-11T23:49:13Z</t>
         </is>
       </c>
     </row>
@@ -3002,7 +3002,7 @@
       </c>
       <c r="K55" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:24Z</t>
+          <t>2026-10-11T23:49:13Z</t>
         </is>
       </c>
     </row>
@@ -3051,7 +3051,7 @@
       </c>
       <c r="K56" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:24Z</t>
+          <t>2026-10-11T23:49:13Z</t>
         </is>
       </c>
     </row>
@@ -3100,7 +3100,7 @@
       </c>
       <c r="K57" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:24Z</t>
+          <t>2026-10-11T23:49:13Z</t>
         </is>
       </c>
     </row>
@@ -3149,7 +3149,7 @@
       </c>
       <c r="K58" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:24Z</t>
+          <t>2026-10-11T23:49:13Z</t>
         </is>
       </c>
     </row>
@@ -3198,7 +3198,7 @@
       </c>
       <c r="K59" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:24Z</t>
+          <t>2026-10-11T23:49:13Z</t>
         </is>
       </c>
     </row>
@@ -3247,7 +3247,7 @@
       </c>
       <c r="K60" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:24Z</t>
+          <t>2026-10-11T23:49:13Z</t>
         </is>
       </c>
     </row>
@@ -3296,7 +3296,7 @@
       </c>
       <c r="K61" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:24Z</t>
+          <t>2026-10-11T23:49:13Z</t>
         </is>
       </c>
     </row>
@@ -3345,7 +3345,7 @@
       </c>
       <c r="K62" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:24Z</t>
+          <t>2026-10-11T23:49:13Z</t>
         </is>
       </c>
     </row>
@@ -3394,7 +3394,7 @@
       </c>
       <c r="K63" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:24Z</t>
+          <t>2026-10-11T23:49:13Z</t>
         </is>
       </c>
     </row>
@@ -3443,7 +3443,7 @@
       </c>
       <c r="K64" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:24Z</t>
+          <t>2026-10-11T23:49:13Z</t>
         </is>
       </c>
     </row>
@@ -3492,7 +3492,7 @@
       </c>
       <c r="K65" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:24Z</t>
+          <t>2026-10-11T23:49:13Z</t>
         </is>
       </c>
     </row>
@@ -3541,7 +3541,7 @@
       </c>
       <c r="K66" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:24Z</t>
+          <t>2026-10-11T23:49:13Z</t>
         </is>
       </c>
     </row>
@@ -3590,7 +3590,7 @@
       </c>
       <c r="K67" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:24Z</t>
+          <t>2026-10-11T23:49:13Z</t>
         </is>
       </c>
     </row>
@@ -3639,7 +3639,7 @@
       </c>
       <c r="K68" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:24Z</t>
+          <t>2026-10-11T23:49:13Z</t>
         </is>
       </c>
     </row>
@@ -3688,7 +3688,7 @@
       </c>
       <c r="K69" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:24Z</t>
+          <t>2026-10-11T23:49:13Z</t>
         </is>
       </c>
     </row>
@@ -3737,7 +3737,7 @@
       </c>
       <c r="K70" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:24Z</t>
+          <t>2026-10-11T23:49:13Z</t>
         </is>
       </c>
     </row>
@@ -3786,7 +3786,7 @@
       </c>
       <c r="K71" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:24Z</t>
+          <t>2026-10-11T23:49:13Z</t>
         </is>
       </c>
     </row>
@@ -3835,7 +3835,7 @@
       </c>
       <c r="K72" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:24Z</t>
+          <t>2026-10-11T23:49:13Z</t>
         </is>
       </c>
     </row>
@@ -3884,7 +3884,7 @@
       </c>
       <c r="K73" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:24Z</t>
+          <t>2026-10-11T23:49:13Z</t>
         </is>
       </c>
     </row>
@@ -3933,7 +3933,7 @@
       </c>
       <c r="K74" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:24Z</t>
+          <t>2026-10-11T23:49:13Z</t>
         </is>
       </c>
     </row>
@@ -3982,7 +3982,7 @@
       </c>
       <c r="K75" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:24Z</t>
+          <t>2026-10-11T23:49:13Z</t>
         </is>
       </c>
     </row>
@@ -4031,7 +4031,7 @@
       </c>
       <c r="K76" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:24Z</t>
+          <t>2026-10-11T23:49:13Z</t>
         </is>
       </c>
     </row>
@@ -4080,7 +4080,7 @@
       </c>
       <c r="K77" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:24Z</t>
+          <t>2026-10-11T23:49:13Z</t>
         </is>
       </c>
     </row>
@@ -4129,7 +4129,7 @@
       </c>
       <c r="K78" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:24Z</t>
+          <t>2026-10-11T23:49:13Z</t>
         </is>
       </c>
     </row>
@@ -4178,7 +4178,7 @@
       </c>
       <c r="K79" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:24Z</t>
+          <t>2026-10-11T23:49:13Z</t>
         </is>
       </c>
     </row>
@@ -4227,7 +4227,7 @@
       </c>
       <c r="K80" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:24Z</t>
+          <t>2026-10-11T23:49:13Z</t>
         </is>
       </c>
     </row>
@@ -4276,7 +4276,7 @@
       </c>
       <c r="K81" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:24Z</t>
+          <t>2026-10-11T23:49:13Z</t>
         </is>
       </c>
     </row>
@@ -4325,7 +4325,7 @@
       </c>
       <c r="K82" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:24Z</t>
+          <t>2026-10-11T23:49:13Z</t>
         </is>
       </c>
     </row>
@@ -4374,7 +4374,7 @@
       </c>
       <c r="K83" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:24Z</t>
+          <t>2026-10-11T23:49:13Z</t>
         </is>
       </c>
     </row>
@@ -4423,7 +4423,7 @@
       </c>
       <c r="K84" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:24Z</t>
+          <t>2026-10-11T23:49:13Z</t>
         </is>
       </c>
     </row>
@@ -4472,7 +4472,7 @@
       </c>
       <c r="K85" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:24Z</t>
+          <t>2026-10-11T23:49:13Z</t>
         </is>
       </c>
     </row>
@@ -4521,7 +4521,7 @@
       </c>
       <c r="K86" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:24Z</t>
+          <t>2026-10-11T23:49:13Z</t>
         </is>
       </c>
     </row>
@@ -4570,7 +4570,7 @@
       </c>
       <c r="K87" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:24Z</t>
+          <t>2026-10-11T23:49:13Z</t>
         </is>
       </c>
     </row>
@@ -4619,7 +4619,7 @@
       </c>
       <c r="K88" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:24Z</t>
+          <t>2026-10-11T23:49:13Z</t>
         </is>
       </c>
     </row>
@@ -4668,7 +4668,7 @@
       </c>
       <c r="K89" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:24Z</t>
+          <t>2026-10-11T23:49:13Z</t>
         </is>
       </c>
     </row>
@@ -4717,7 +4717,7 @@
       </c>
       <c r="K90" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:24Z</t>
+          <t>2026-10-11T23:49:13Z</t>
         </is>
       </c>
     </row>
@@ -4766,7 +4766,7 @@
       </c>
       <c r="K91" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:24Z</t>
+          <t>2026-10-11T23:49:13Z</t>
         </is>
       </c>
     </row>
@@ -4815,7 +4815,7 @@
       </c>
       <c r="K92" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:24Z</t>
+          <t>2026-10-11T23:49:13Z</t>
         </is>
       </c>
     </row>
@@ -4864,7 +4864,7 @@
       </c>
       <c r="K93" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:24Z</t>
+          <t>2026-10-11T23:49:13Z</t>
         </is>
       </c>
     </row>
@@ -4913,7 +4913,7 @@
       </c>
       <c r="K94" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:24Z</t>
+          <t>2026-10-11T23:49:13Z</t>
         </is>
       </c>
     </row>
@@ -4962,7 +4962,7 @@
       </c>
       <c r="K95" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:24Z</t>
+          <t>2026-10-11T23:49:13Z</t>
         </is>
       </c>
     </row>
@@ -5011,7 +5011,7 @@
       </c>
       <c r="K96" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:24Z</t>
+          <t>2026-10-11T23:49:13Z</t>
         </is>
       </c>
     </row>
@@ -5060,7 +5060,7 @@
       </c>
       <c r="K97" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:24Z</t>
+          <t>2026-10-11T23:49:13Z</t>
         </is>
       </c>
     </row>
@@ -5109,7 +5109,7 @@
       </c>
       <c r="K98" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:24Z</t>
+          <t>2026-10-11T23:49:13Z</t>
         </is>
       </c>
     </row>
@@ -5158,7 +5158,7 @@
       </c>
       <c r="K99" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:24Z</t>
+          <t>2026-10-11T23:49:13Z</t>
         </is>
       </c>
     </row>
@@ -5207,7 +5207,7 @@
       </c>
       <c r="K100" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:24Z</t>
+          <t>2026-10-11T23:49:13Z</t>
         </is>
       </c>
     </row>
@@ -5256,7 +5256,7 @@
       </c>
       <c r="K101" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:24Z</t>
+          <t>2026-10-11T23:49:13Z</t>
         </is>
       </c>
     </row>
@@ -5305,7 +5305,7 @@
       </c>
       <c r="K102" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:24Z</t>
+          <t>2026-10-11T23:49:13Z</t>
         </is>
       </c>
     </row>
@@ -5354,7 +5354,7 @@
       </c>
       <c r="K103" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:24Z</t>
+          <t>2026-10-11T23:49:13Z</t>
         </is>
       </c>
     </row>
@@ -5403,7 +5403,7 @@
       </c>
       <c r="K104" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:24Z</t>
+          <t>2026-10-11T23:49:13Z</t>
         </is>
       </c>
     </row>
@@ -5452,7 +5452,7 @@
       </c>
       <c r="K105" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:24Z</t>
+          <t>2026-10-11T23:49:13Z</t>
         </is>
       </c>
     </row>
@@ -5501,7 +5501,7 @@
       </c>
       <c r="K106" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:24Z</t>
+          <t>2026-10-11T23:49:13Z</t>
         </is>
       </c>
     </row>
@@ -5550,7 +5550,7 @@
       </c>
       <c r="K107" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:24Z</t>
+          <t>2026-10-11T23:49:13Z</t>
         </is>
       </c>
     </row>
@@ -5599,7 +5599,7 @@
       </c>
       <c r="K108" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:24Z</t>
+          <t>2026-10-11T23:49:13Z</t>
         </is>
       </c>
     </row>
@@ -5648,7 +5648,7 @@
       </c>
       <c r="K109" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:24Z</t>
+          <t>2026-10-11T23:49:13Z</t>
         </is>
       </c>
     </row>
@@ -5697,7 +5697,7 @@
       </c>
       <c r="K110" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:24Z</t>
+          <t>2026-10-11T23:49:13Z</t>
         </is>
       </c>
     </row>
@@ -5746,7 +5746,7 @@
       </c>
       <c r="K111" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:24Z</t>
+          <t>2026-10-11T23:49:13Z</t>
         </is>
       </c>
     </row>
@@ -5795,7 +5795,7 @@
       </c>
       <c r="K112" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:24Z</t>
+          <t>2026-10-11T23:49:13Z</t>
         </is>
       </c>
     </row>
@@ -5844,7 +5844,7 @@
       </c>
       <c r="K113" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:24Z</t>
+          <t>2026-10-11T23:49:13Z</t>
         </is>
       </c>
     </row>
@@ -5893,7 +5893,7 @@
       </c>
       <c r="K114" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:24Z</t>
+          <t>2026-10-11T23:49:13Z</t>
         </is>
       </c>
     </row>
@@ -5942,7 +5942,7 @@
       </c>
       <c r="K115" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:24Z</t>
+          <t>2026-10-11T23:49:13Z</t>
         </is>
       </c>
     </row>
@@ -5991,7 +5991,7 @@
       </c>
       <c r="K116" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:24Z</t>
+          <t>2026-10-11T23:49:13Z</t>
         </is>
       </c>
     </row>
@@ -6040,7 +6040,7 @@
       </c>
       <c r="K117" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:24Z</t>
+          <t>2026-10-11T23:49:13Z</t>
         </is>
       </c>
     </row>
@@ -6089,7 +6089,7 @@
       </c>
       <c r="K118" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:24Z</t>
+          <t>2026-10-11T23:49:13Z</t>
         </is>
       </c>
     </row>
@@ -6138,7 +6138,7 @@
       </c>
       <c r="K119" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:24Z</t>
+          <t>2026-10-11T23:49:13Z</t>
         </is>
       </c>
     </row>
@@ -6187,7 +6187,7 @@
       </c>
       <c r="K120" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:24Z</t>
+          <t>2026-10-11T23:49:13Z</t>
         </is>
       </c>
     </row>
@@ -6236,7 +6236,7 @@
       </c>
       <c r="K121" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:24Z</t>
+          <t>2026-10-11T23:49:13Z</t>
         </is>
       </c>
     </row>
@@ -6285,7 +6285,7 @@
       </c>
       <c r="K122" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:24Z</t>
+          <t>2026-10-11T23:49:13Z</t>
         </is>
       </c>
     </row>
@@ -6334,7 +6334,7 @@
       </c>
       <c r="K123" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:24Z</t>
+          <t>2026-10-11T23:49:13Z</t>
         </is>
       </c>
     </row>
@@ -6383,7 +6383,7 @@
       </c>
       <c r="K124" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:24Z</t>
+          <t>2026-10-11T23:49:13Z</t>
         </is>
       </c>
     </row>
@@ -6432,7 +6432,7 @@
       </c>
       <c r="K125" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:24Z</t>
+          <t>2026-10-11T23:49:13Z</t>
         </is>
       </c>
     </row>
@@ -6481,7 +6481,7 @@
       </c>
       <c r="K126" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:24Z</t>
+          <t>2026-10-11T23:49:13Z</t>
         </is>
       </c>
     </row>
@@ -6530,7 +6530,7 @@
       </c>
       <c r="K127" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:24Z</t>
+          <t>2026-10-11T23:49:13Z</t>
         </is>
       </c>
     </row>
@@ -6579,7 +6579,7 @@
       </c>
       <c r="K128" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:24Z</t>
+          <t>2026-10-11T23:49:13Z</t>
         </is>
       </c>
     </row>
@@ -6628,7 +6628,7 @@
       </c>
       <c r="K129" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:24Z</t>
+          <t>2026-10-11T23:49:13Z</t>
         </is>
       </c>
     </row>
@@ -6677,7 +6677,7 @@
       </c>
       <c r="K130" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:24Z</t>
+          <t>2026-10-11T23:49:13Z</t>
         </is>
       </c>
     </row>
@@ -6726,7 +6726,7 @@
       </c>
       <c r="K131" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:24Z</t>
+          <t>2026-10-11T23:49:13Z</t>
         </is>
       </c>
     </row>
@@ -6775,7 +6775,7 @@
       </c>
       <c r="K132" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:24Z</t>
+          <t>2026-10-11T23:49:13Z</t>
         </is>
       </c>
     </row>
@@ -6824,7 +6824,7 @@
       </c>
       <c r="K133" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:24Z</t>
+          <t>2026-10-11T23:49:13Z</t>
         </is>
       </c>
     </row>
@@ -6873,7 +6873,7 @@
       </c>
       <c r="K134" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:24Z</t>
+          <t>2026-10-11T23:49:13Z</t>
         </is>
       </c>
     </row>
@@ -6922,7 +6922,7 @@
       </c>
       <c r="K135" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:24Z</t>
+          <t>2026-10-11T23:49:13Z</t>
         </is>
       </c>
     </row>
@@ -6971,7 +6971,7 @@
       </c>
       <c r="K136" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:24Z</t>
+          <t>2026-10-11T23:49:13Z</t>
         </is>
       </c>
     </row>
@@ -7020,7 +7020,7 @@
       </c>
       <c r="K137" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:24Z</t>
+          <t>2026-10-11T23:49:13Z</t>
         </is>
       </c>
     </row>
@@ -7069,7 +7069,7 @@
       </c>
       <c r="K138" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:24Z</t>
+          <t>2026-10-11T23:49:13Z</t>
         </is>
       </c>
     </row>
@@ -7118,7 +7118,7 @@
       </c>
       <c r="K139" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:24Z</t>
+          <t>2026-10-11T23:49:13Z</t>
         </is>
       </c>
     </row>
@@ -7167,7 +7167,7 @@
       </c>
       <c r="K140" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:24Z</t>
+          <t>2026-10-11T23:49:13Z</t>
         </is>
       </c>
     </row>
@@ -7216,7 +7216,7 @@
       </c>
       <c r="K141" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:24Z</t>
+          <t>2026-10-11T23:49:13Z</t>
         </is>
       </c>
     </row>
@@ -7265,7 +7265,7 @@
       </c>
       <c r="K142" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:24Z</t>
+          <t>2026-10-11T23:49:13Z</t>
         </is>
       </c>
     </row>
@@ -7314,7 +7314,7 @@
       </c>
       <c r="K143" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:24Z</t>
+          <t>2026-10-11T23:49:13Z</t>
         </is>
       </c>
     </row>
@@ -7363,7 +7363,7 @@
       </c>
       <c r="K144" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:24Z</t>
+          <t>2026-10-11T23:49:13Z</t>
         </is>
       </c>
     </row>
@@ -7412,7 +7412,7 @@
       </c>
       <c r="K145" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:24Z</t>
+          <t>2026-10-11T23:49:13Z</t>
         </is>
       </c>
     </row>
@@ -7461,7 +7461,7 @@
       </c>
       <c r="K146" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:24Z</t>
+          <t>2026-10-11T23:49:13Z</t>
         </is>
       </c>
     </row>
@@ -7510,7 +7510,7 @@
       </c>
       <c r="K147" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:24Z</t>
+          <t>2026-10-11T23:49:13Z</t>
         </is>
       </c>
     </row>
@@ -7559,7 +7559,7 @@
       </c>
       <c r="K148" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:24Z</t>
+          <t>2026-10-11T23:49:13Z</t>
         </is>
       </c>
     </row>
@@ -7608,7 +7608,7 @@
       </c>
       <c r="K149" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:24Z</t>
+          <t>2026-10-11T23:49:13Z</t>
         </is>
       </c>
     </row>
@@ -7657,7 +7657,7 @@
       </c>
       <c r="K150" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:24Z</t>
+          <t>2026-10-11T23:49:13Z</t>
         </is>
       </c>
     </row>
@@ -7706,7 +7706,7 @@
       </c>
       <c r="K151" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:24Z</t>
+          <t>2026-10-11T23:49:13Z</t>
         </is>
       </c>
     </row>
@@ -7755,7 +7755,7 @@
       </c>
       <c r="K152" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:24Z</t>
+          <t>2026-10-11T23:49:13Z</t>
         </is>
       </c>
     </row>
@@ -7804,7 +7804,7 @@
       </c>
       <c r="K153" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:24Z</t>
+          <t>2026-10-11T23:49:13Z</t>
         </is>
       </c>
     </row>
@@ -7853,7 +7853,7 @@
       </c>
       <c r="K154" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:24Z</t>
+          <t>2026-10-11T23:49:13Z</t>
         </is>
       </c>
     </row>
@@ -7902,7 +7902,7 @@
       </c>
       <c r="K155" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:24Z</t>
+          <t>2026-10-11T23:49:13Z</t>
         </is>
       </c>
     </row>
@@ -7951,7 +7951,7 @@
       </c>
       <c r="K156" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:24Z</t>
+          <t>2026-10-11T23:49:13Z</t>
         </is>
       </c>
     </row>
@@ -8000,7 +8000,7 @@
       </c>
       <c r="K157" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:24Z</t>
+          <t>2026-10-11T23:49:13Z</t>
         </is>
       </c>
     </row>
@@ -8049,7 +8049,7 @@
       </c>
       <c r="K158" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:24Z</t>
+          <t>2026-10-11T23:49:13Z</t>
         </is>
       </c>
     </row>
@@ -8098,7 +8098,7 @@
       </c>
       <c r="K159" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:24Z</t>
+          <t>2026-10-11T23:49:13Z</t>
         </is>
       </c>
     </row>
@@ -8147,7 +8147,7 @@
       </c>
       <c r="K160" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:24Z</t>
+          <t>2026-10-11T23:49:13Z</t>
         </is>
       </c>
     </row>
@@ -8196,7 +8196,7 @@
       </c>
       <c r="K161" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:24Z</t>
+          <t>2026-10-11T23:49:13Z</t>
         </is>
       </c>
     </row>
@@ -8245,7 +8245,7 @@
       </c>
       <c r="K162" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:24Z</t>
+          <t>2026-10-11T23:49:13Z</t>
         </is>
       </c>
     </row>
@@ -8294,7 +8294,7 @@
       </c>
       <c r="K163" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:24Z</t>
+          <t>2026-10-11T23:49:13Z</t>
         </is>
       </c>
     </row>
@@ -8343,7 +8343,7 @@
       </c>
       <c r="K164" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:24Z</t>
+          <t>2026-10-11T23:49:13Z</t>
         </is>
       </c>
     </row>
@@ -8392,7 +8392,7 @@
       </c>
       <c r="K165" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:24Z</t>
+          <t>2026-10-11T23:49:13Z</t>
         </is>
       </c>
     </row>
@@ -8441,7 +8441,7 @@
       </c>
       <c r="K166" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:24Z</t>
+          <t>2026-10-11T23:49:13Z</t>
         </is>
       </c>
     </row>
@@ -8490,7 +8490,7 @@
       </c>
       <c r="K167" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:24Z</t>
+          <t>2026-10-11T23:49:13Z</t>
         </is>
       </c>
     </row>
@@ -8539,7 +8539,7 @@
       </c>
       <c r="K168" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:24Z</t>
+          <t>2026-10-11T23:49:13Z</t>
         </is>
       </c>
     </row>
@@ -8588,7 +8588,7 @@
       </c>
       <c r="K169" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:24Z</t>
+          <t>2026-10-11T23:49:13Z</t>
         </is>
       </c>
     </row>
@@ -8637,7 +8637,7 @@
       </c>
       <c r="K170" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:24Z</t>
+          <t>2026-10-11T23:49:13Z</t>
         </is>
       </c>
     </row>
@@ -8686,7 +8686,7 @@
       </c>
       <c r="K171" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:24Z</t>
+          <t>2026-10-11T23:49:13Z</t>
         </is>
       </c>
     </row>
@@ -8735,7 +8735,7 @@
       </c>
       <c r="K172" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:24Z</t>
+          <t>2026-10-11T23:49:13Z</t>
         </is>
       </c>
     </row>
@@ -8784,7 +8784,7 @@
       </c>
       <c r="K173" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:24Z</t>
+          <t>2026-10-11T23:49:13Z</t>
         </is>
       </c>
     </row>
@@ -8833,7 +8833,7 @@
       </c>
       <c r="K174" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:24Z</t>
+          <t>2026-10-11T23:49:13Z</t>
         </is>
       </c>
     </row>
@@ -8882,7 +8882,7 @@
       </c>
       <c r="K175" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:24Z</t>
+          <t>2026-10-11T23:49:13Z</t>
         </is>
       </c>
     </row>
@@ -8931,7 +8931,7 @@
       </c>
       <c r="K176" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:24Z</t>
+          <t>2026-10-11T23:49:13Z</t>
         </is>
       </c>
     </row>
@@ -8980,7 +8980,7 @@
       </c>
       <c r="K177" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:24Z</t>
+          <t>2026-10-11T23:49:13Z</t>
         </is>
       </c>
     </row>
@@ -9029,7 +9029,7 @@
       </c>
       <c r="K178" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:24Z</t>
+          <t>2026-10-11T23:49:13Z</t>
         </is>
       </c>
     </row>
@@ -9078,7 +9078,7 @@
       </c>
       <c r="K179" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:24Z</t>
+          <t>2026-10-11T23:49:13Z</t>
         </is>
       </c>
     </row>
@@ -9127,7 +9127,7 @@
       </c>
       <c r="K180" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:24Z</t>
+          <t>2026-10-11T23:49:13Z</t>
         </is>
       </c>
     </row>
@@ -9176,7 +9176,7 @@
       </c>
       <c r="K181" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:24Z</t>
+          <t>2026-10-11T23:49:13Z</t>
         </is>
       </c>
     </row>
@@ -9225,7 +9225,7 @@
       </c>
       <c r="K182" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:24Z</t>
+          <t>2026-10-11T23:49:13Z</t>
         </is>
       </c>
     </row>
@@ -9274,7 +9274,7 @@
       </c>
       <c r="K183" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:24Z</t>
+          <t>2026-10-11T23:49:13Z</t>
         </is>
       </c>
     </row>
@@ -9323,7 +9323,7 @@
       </c>
       <c r="K184" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:24Z</t>
+          <t>2026-10-11T23:49:13Z</t>
         </is>
       </c>
     </row>
@@ -9372,7 +9372,7 @@
       </c>
       <c r="K185" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:24Z</t>
+          <t>2026-10-11T23:49:13Z</t>
         </is>
       </c>
     </row>
@@ -9421,7 +9421,7 @@
       </c>
       <c r="K186" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:24Z</t>
+          <t>2026-10-11T23:49:13Z</t>
         </is>
       </c>
     </row>
@@ -9470,7 +9470,7 @@
       </c>
       <c r="K187" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:24Z</t>
+          <t>2026-10-11T23:49:13Z</t>
         </is>
       </c>
     </row>
@@ -9519,7 +9519,7 @@
       </c>
       <c r="K188" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:24Z</t>
+          <t>2026-10-11T23:49:13Z</t>
         </is>
       </c>
     </row>
@@ -9568,7 +9568,7 @@
       </c>
       <c r="K189" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:24Z</t>
+          <t>2026-10-11T23:49:13Z</t>
         </is>
       </c>
     </row>
@@ -9617,7 +9617,7 @@
       </c>
       <c r="K190" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:24Z</t>
+          <t>2026-10-11T23:49:13Z</t>
         </is>
       </c>
     </row>
@@ -9666,7 +9666,7 @@
       </c>
       <c r="K191" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:24Z</t>
+          <t>2026-10-11T23:49:13Z</t>
         </is>
       </c>
     </row>
@@ -9715,7 +9715,7 @@
       </c>
       <c r="K192" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:24Z</t>
+          <t>2026-10-11T23:49:13Z</t>
         </is>
       </c>
     </row>
@@ -9764,7 +9764,7 @@
       </c>
       <c r="K193" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:24Z</t>
+          <t>2026-10-11T23:49:13Z</t>
         </is>
       </c>
     </row>
@@ -9813,7 +9813,7 @@
       </c>
       <c r="K194" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:24Z</t>
+          <t>2026-10-11T23:49:13Z</t>
         </is>
       </c>
     </row>
@@ -9862,7 +9862,7 @@
       </c>
       <c r="K195" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:24Z</t>
+          <t>2026-10-11T23:49:13Z</t>
         </is>
       </c>
     </row>
@@ -9911,7 +9911,7 @@
       </c>
       <c r="K196" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:24Z</t>
+          <t>2026-10-11T23:49:13Z</t>
         </is>
       </c>
     </row>
@@ -9960,7 +9960,7 @@
       </c>
       <c r="K197" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:24Z</t>
+          <t>2026-10-11T23:49:13Z</t>
         </is>
       </c>
     </row>
@@ -10009,7 +10009,7 @@
       </c>
       <c r="K198" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:24Z</t>
+          <t>2026-10-11T23:49:13Z</t>
         </is>
       </c>
     </row>
@@ -10058,7 +10058,7 @@
       </c>
       <c r="K199" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:24Z</t>
+          <t>2026-10-11T23:49:13Z</t>
         </is>
       </c>
     </row>
@@ -10107,7 +10107,7 @@
       </c>
       <c r="K200" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:24Z</t>
+          <t>2026-10-11T23:49:13Z</t>
         </is>
       </c>
     </row>
@@ -10156,7 +10156,7 @@
       </c>
       <c r="K201" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:24Z</t>
+          <t>2026-10-11T23:49:13Z</t>
         </is>
       </c>
     </row>
@@ -10205,7 +10205,7 @@
       </c>
       <c r="K202" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:24Z</t>
+          <t>2026-10-11T23:49:13Z</t>
         </is>
       </c>
     </row>
@@ -10254,7 +10254,7 @@
       </c>
       <c r="K203" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:24Z</t>
+          <t>2026-10-11T23:49:13Z</t>
         </is>
       </c>
     </row>
@@ -10303,7 +10303,7 @@
       </c>
       <c r="K204" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:24Z</t>
+          <t>2026-10-11T23:49:13Z</t>
         </is>
       </c>
     </row>
@@ -10352,7 +10352,7 @@
       </c>
       <c r="K205" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:24Z</t>
+          <t>2026-10-11T23:49:13Z</t>
         </is>
       </c>
     </row>
@@ -10401,7 +10401,7 @@
       </c>
       <c r="K206" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:24Z</t>
+          <t>2026-10-11T23:49:13Z</t>
         </is>
       </c>
     </row>
@@ -10450,7 +10450,7 @@
       </c>
       <c r="K207" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:24Z</t>
+          <t>2026-10-11T23:49:13Z</t>
         </is>
       </c>
     </row>
@@ -10499,7 +10499,7 @@
       </c>
       <c r="K208" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:24Z</t>
+          <t>2026-10-11T23:49:13Z</t>
         </is>
       </c>
     </row>
@@ -10548,7 +10548,7 @@
       </c>
       <c r="K209" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:24Z</t>
+          <t>2026-10-11T23:49:13Z</t>
         </is>
       </c>
     </row>
@@ -10597,7 +10597,7 @@
       </c>
       <c r="K210" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:24Z</t>
+          <t>2026-10-11T23:49:13Z</t>
         </is>
       </c>
     </row>
@@ -10646,7 +10646,7 @@
       </c>
       <c r="K211" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:24Z</t>
+          <t>2026-10-11T23:49:13Z</t>
         </is>
       </c>
     </row>
@@ -10695,7 +10695,7 @@
       </c>
       <c r="K212" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:24Z</t>
+          <t>2026-10-11T23:49:13Z</t>
         </is>
       </c>
     </row>
@@ -10744,7 +10744,7 @@
       </c>
       <c r="K213" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:24Z</t>
+          <t>2026-10-11T23:49:13Z</t>
         </is>
       </c>
     </row>
@@ -10793,7 +10793,7 @@
       </c>
       <c r="K214" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:24Z</t>
+          <t>2026-10-11T23:49:13Z</t>
         </is>
       </c>
     </row>
@@ -10842,7 +10842,7 @@
       </c>
       <c r="K215" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:24Z</t>
+          <t>2026-10-11T23:49:13Z</t>
         </is>
       </c>
     </row>
@@ -10891,7 +10891,7 @@
       </c>
       <c r="K216" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:24Z</t>
+          <t>2026-10-11T23:49:13Z</t>
         </is>
       </c>
     </row>
@@ -10940,7 +10940,7 @@
       </c>
       <c r="K217" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:24Z</t>
+          <t>2026-10-11T23:49:13Z</t>
         </is>
       </c>
     </row>
@@ -10989,7 +10989,7 @@
       </c>
       <c r="K218" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:24Z</t>
+          <t>2026-10-11T23:49:13Z</t>
         </is>
       </c>
     </row>
@@ -11038,7 +11038,7 @@
       </c>
       <c r="K219" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:24Z</t>
+          <t>2026-10-11T23:49:13Z</t>
         </is>
       </c>
     </row>
@@ -11087,7 +11087,7 @@
       </c>
       <c r="K220" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:24Z</t>
+          <t>2026-10-11T23:49:13Z</t>
         </is>
       </c>
     </row>
@@ -11136,7 +11136,7 @@
       </c>
       <c r="K221" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:24Z</t>
+          <t>2026-10-11T23:49:13Z</t>
         </is>
       </c>
     </row>
@@ -11185,7 +11185,7 @@
       </c>
       <c r="K222" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:24Z</t>
+          <t>2026-10-11T23:49:13Z</t>
         </is>
       </c>
     </row>
@@ -11234,7 +11234,7 @@
       </c>
       <c r="K223" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:24Z</t>
+          <t>2026-10-11T23:49:13Z</t>
         </is>
       </c>
     </row>
@@ -11283,7 +11283,7 @@
       </c>
       <c r="K224" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:24Z</t>
+          <t>2026-10-11T23:49:13Z</t>
         </is>
       </c>
     </row>
@@ -11332,7 +11332,7 @@
       </c>
       <c r="K225" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:24Z</t>
+          <t>2026-10-11T23:49:13Z</t>
         </is>
       </c>
     </row>
@@ -11381,7 +11381,7 @@
       </c>
       <c r="K226" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:24Z</t>
+          <t>2026-10-11T23:49:13Z</t>
         </is>
       </c>
     </row>
@@ -11430,7 +11430,7 @@
       </c>
       <c r="K227" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:24Z</t>
+          <t>2026-10-11T23:49:13Z</t>
         </is>
       </c>
     </row>
@@ -11479,7 +11479,7 @@
       </c>
       <c r="K228" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:24Z</t>
+          <t>2026-10-11T23:49:13Z</t>
         </is>
       </c>
     </row>
@@ -11528,7 +11528,7 @@
       </c>
       <c r="K229" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:24Z</t>
+          <t>2026-10-11T23:49:13Z</t>
         </is>
       </c>
     </row>
@@ -11577,7 +11577,7 @@
       </c>
       <c r="K230" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:24Z</t>
+          <t>2026-10-11T23:49:13Z</t>
         </is>
       </c>
     </row>
@@ -11626,7 +11626,7 @@
       </c>
       <c r="K231" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:24Z</t>
+          <t>2026-10-11T23:49:13Z</t>
         </is>
       </c>
     </row>
@@ -11758,7 +11758,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:24Z</t>
+          <t>2026-10-11T23:49:13Z</t>
         </is>
       </c>
     </row>
@@ -11804,7 +11804,7 @@
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>{"date": "2026-08-01", "year": 2026, "month": 8, "month_name": "Agosto", "index_value": 637409769724325.1, "monthly_variation_pct": 8.9, "unit": "Índice base diciembre 2007=100 y variación mensual %", "frequency": "monthly", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/precios_consumidor/4_5_7_2.xls", "fetched_at": "2026-10-10T23:42:24Z"}</t>
+          <t>{"date": "2026-08-01", "year": 2026, "month": 8, "month_name": "Agosto", "index_value": 637409769724325.1, "monthly_variation_pct": 8.9, "unit": "Índice base diciembre 2007=100 y variación mensual %", "frequency": "monthly", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/precios_consumidor/4_5_7_2.xls", "fetched_at": "2026-10-11T23:49:13Z"}</t>
         </is>
       </c>
     </row>

--- a/assets/data/bcv/excel/ove_bcv_inpc_nacional_mensual.xlsx
+++ b/assets/data/bcv/excel/ove_bcv_inpc_nacional_mensual.xlsx
@@ -650,7 +650,7 @@
       </c>
       <c r="K7" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:13Z</t>
+          <t>2026-10-12T21:43:47Z</t>
         </is>
       </c>
     </row>
@@ -699,7 +699,7 @@
       </c>
       <c r="K8" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:13Z</t>
+          <t>2026-10-12T21:43:47Z</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="K9" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:13Z</t>
+          <t>2026-10-12T21:43:47Z</t>
         </is>
       </c>
     </row>
@@ -797,7 +797,7 @@
       </c>
       <c r="K10" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:13Z</t>
+          <t>2026-10-12T21:43:47Z</t>
         </is>
       </c>
     </row>
@@ -846,7 +846,7 @@
       </c>
       <c r="K11" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:13Z</t>
+          <t>2026-10-12T21:43:47Z</t>
         </is>
       </c>
     </row>
@@ -895,7 +895,7 @@
       </c>
       <c r="K12" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:13Z</t>
+          <t>2026-10-12T21:43:47Z</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="K13" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:13Z</t>
+          <t>2026-10-12T21:43:47Z</t>
         </is>
       </c>
     </row>
@@ -993,7 +993,7 @@
       </c>
       <c r="K14" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:13Z</t>
+          <t>2026-10-12T21:43:47Z</t>
         </is>
       </c>
     </row>
@@ -1042,7 +1042,7 @@
       </c>
       <c r="K15" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:13Z</t>
+          <t>2026-10-12T21:43:47Z</t>
         </is>
       </c>
     </row>
@@ -1091,7 +1091,7 @@
       </c>
       <c r="K16" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:13Z</t>
+          <t>2026-10-12T21:43:47Z</t>
         </is>
       </c>
     </row>
@@ -1140,7 +1140,7 @@
       </c>
       <c r="K17" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:13Z</t>
+          <t>2026-10-12T21:43:47Z</t>
         </is>
       </c>
     </row>
@@ -1189,7 +1189,7 @@
       </c>
       <c r="K18" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:13Z</t>
+          <t>2026-10-12T21:43:47Z</t>
         </is>
       </c>
     </row>
@@ -1238,7 +1238,7 @@
       </c>
       <c r="K19" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:13Z</t>
+          <t>2026-10-12T21:43:47Z</t>
         </is>
       </c>
     </row>
@@ -1287,7 +1287,7 @@
       </c>
       <c r="K20" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:13Z</t>
+          <t>2026-10-12T21:43:47Z</t>
         </is>
       </c>
     </row>
@@ -1336,7 +1336,7 @@
       </c>
       <c r="K21" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:13Z</t>
+          <t>2026-10-12T21:43:47Z</t>
         </is>
       </c>
     </row>
@@ -1385,7 +1385,7 @@
       </c>
       <c r="K22" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:13Z</t>
+          <t>2026-10-12T21:43:47Z</t>
         </is>
       </c>
     </row>
@@ -1434,7 +1434,7 @@
       </c>
       <c r="K23" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:13Z</t>
+          <t>2026-10-12T21:43:47Z</t>
         </is>
       </c>
     </row>
@@ -1483,7 +1483,7 @@
       </c>
       <c r="K24" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:13Z</t>
+          <t>2026-10-12T21:43:47Z</t>
         </is>
       </c>
     </row>
@@ -1532,7 +1532,7 @@
       </c>
       <c r="K25" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:13Z</t>
+          <t>2026-10-12T21:43:47Z</t>
         </is>
       </c>
     </row>
@@ -1581,7 +1581,7 @@
       </c>
       <c r="K26" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:13Z</t>
+          <t>2026-10-12T21:43:47Z</t>
         </is>
       </c>
     </row>
@@ -1630,7 +1630,7 @@
       </c>
       <c r="K27" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:13Z</t>
+          <t>2026-10-12T21:43:47Z</t>
         </is>
       </c>
     </row>
@@ -1679,7 +1679,7 @@
       </c>
       <c r="K28" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:13Z</t>
+          <t>2026-10-12T21:43:47Z</t>
         </is>
       </c>
     </row>
@@ -1728,7 +1728,7 @@
       </c>
       <c r="K29" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:13Z</t>
+          <t>2026-10-12T21:43:47Z</t>
         </is>
       </c>
     </row>
@@ -1777,7 +1777,7 @@
       </c>
       <c r="K30" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:13Z</t>
+          <t>2026-10-12T21:43:47Z</t>
         </is>
       </c>
     </row>
@@ -1826,7 +1826,7 @@
       </c>
       <c r="K31" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:13Z</t>
+          <t>2026-10-12T21:43:47Z</t>
         </is>
       </c>
     </row>
@@ -1875,7 +1875,7 @@
       </c>
       <c r="K32" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:13Z</t>
+          <t>2026-10-12T21:43:47Z</t>
         </is>
       </c>
     </row>
@@ -1924,7 +1924,7 @@
       </c>
       <c r="K33" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:13Z</t>
+          <t>2026-10-12T21:43:47Z</t>
         </is>
       </c>
     </row>
@@ -1973,7 +1973,7 @@
       </c>
       <c r="K34" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:13Z</t>
+          <t>2026-10-12T21:43:47Z</t>
         </is>
       </c>
     </row>
@@ -2022,7 +2022,7 @@
       </c>
       <c r="K35" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:13Z</t>
+          <t>2026-10-12T21:43:47Z</t>
         </is>
       </c>
     </row>
@@ -2071,7 +2071,7 @@
       </c>
       <c r="K36" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:13Z</t>
+          <t>2026-10-12T21:43:47Z</t>
         </is>
       </c>
     </row>
@@ -2120,7 +2120,7 @@
       </c>
       <c r="K37" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:13Z</t>
+          <t>2026-10-12T21:43:47Z</t>
         </is>
       </c>
     </row>
@@ -2169,7 +2169,7 @@
       </c>
       <c r="K38" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:13Z</t>
+          <t>2026-10-12T21:43:47Z</t>
         </is>
       </c>
     </row>
@@ -2218,7 +2218,7 @@
       </c>
       <c r="K39" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:13Z</t>
+          <t>2026-10-12T21:43:47Z</t>
         </is>
       </c>
     </row>
@@ -2267,7 +2267,7 @@
       </c>
       <c r="K40" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:13Z</t>
+          <t>2026-10-12T21:43:47Z</t>
         </is>
       </c>
     </row>
@@ -2316,7 +2316,7 @@
       </c>
       <c r="K41" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:13Z</t>
+          <t>2026-10-12T21:43:47Z</t>
         </is>
       </c>
     </row>
@@ -2365,7 +2365,7 @@
       </c>
       <c r="K42" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:13Z</t>
+          <t>2026-10-12T21:43:47Z</t>
         </is>
       </c>
     </row>
@@ -2414,7 +2414,7 @@
       </c>
       <c r="K43" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:13Z</t>
+          <t>2026-10-12T21:43:47Z</t>
         </is>
       </c>
     </row>
@@ -2463,7 +2463,7 @@
       </c>
       <c r="K44" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:13Z</t>
+          <t>2026-10-12T21:43:47Z</t>
         </is>
       </c>
     </row>
@@ -2512,7 +2512,7 @@
       </c>
       <c r="K45" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:13Z</t>
+          <t>2026-10-12T21:43:47Z</t>
         </is>
       </c>
     </row>
@@ -2561,7 +2561,7 @@
       </c>
       <c r="K46" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:13Z</t>
+          <t>2026-10-12T21:43:47Z</t>
         </is>
       </c>
     </row>
@@ -2610,7 +2610,7 @@
       </c>
       <c r="K47" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:13Z</t>
+          <t>2026-10-12T21:43:47Z</t>
         </is>
       </c>
     </row>
@@ -2659,7 +2659,7 @@
       </c>
       <c r="K48" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:13Z</t>
+          <t>2026-10-12T21:43:47Z</t>
         </is>
       </c>
     </row>
@@ -2708,7 +2708,7 @@
       </c>
       <c r="K49" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:13Z</t>
+          <t>2026-10-12T21:43:47Z</t>
         </is>
       </c>
     </row>
@@ -2757,7 +2757,7 @@
       </c>
       <c r="K50" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:13Z</t>
+          <t>2026-10-12T21:43:47Z</t>
         </is>
       </c>
     </row>
@@ -2806,7 +2806,7 @@
       </c>
       <c r="K51" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:13Z</t>
+          <t>2026-10-12T21:43:47Z</t>
         </is>
       </c>
     </row>
@@ -2855,7 +2855,7 @@
       </c>
       <c r="K52" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:13Z</t>
+          <t>2026-10-12T21:43:47Z</t>
         </is>
       </c>
     </row>
@@ -2904,7 +2904,7 @@
       </c>
       <c r="K53" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:13Z</t>
+          <t>2026-10-12T21:43:47Z</t>
         </is>
       </c>
     </row>
@@ -2953,7 +2953,7 @@
       </c>
       <c r="K54" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:13Z</t>
+          <t>2026-10-12T21:43:47Z</t>
         </is>
       </c>
     </row>
@@ -3002,7 +3002,7 @@
       </c>
       <c r="K55" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:13Z</t>
+          <t>2026-10-12T21:43:47Z</t>
         </is>
       </c>
     </row>
@@ -3051,7 +3051,7 @@
       </c>
       <c r="K56" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:13Z</t>
+          <t>2026-10-12T21:43:47Z</t>
         </is>
       </c>
     </row>
@@ -3100,7 +3100,7 @@
       </c>
       <c r="K57" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:13Z</t>
+          <t>2026-10-12T21:43:47Z</t>
         </is>
       </c>
     </row>
@@ -3149,7 +3149,7 @@
       </c>
       <c r="K58" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:13Z</t>
+          <t>2026-10-12T21:43:47Z</t>
         </is>
       </c>
     </row>
@@ -3198,7 +3198,7 @@
       </c>
       <c r="K59" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:13Z</t>
+          <t>2026-10-12T21:43:47Z</t>
         </is>
       </c>
     </row>
@@ -3247,7 +3247,7 @@
       </c>
       <c r="K60" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:13Z</t>
+          <t>2026-10-12T21:43:47Z</t>
         </is>
       </c>
     </row>
@@ -3296,7 +3296,7 @@
       </c>
       <c r="K61" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:13Z</t>
+          <t>2026-10-12T21:43:47Z</t>
         </is>
       </c>
     </row>
@@ -3345,7 +3345,7 @@
       </c>
       <c r="K62" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:13Z</t>
+          <t>2026-10-12T21:43:47Z</t>
         </is>
       </c>
     </row>
@@ -3394,7 +3394,7 @@
       </c>
       <c r="K63" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:13Z</t>
+          <t>2026-10-12T21:43:47Z</t>
         </is>
       </c>
     </row>
@@ -3443,7 +3443,7 @@
       </c>
       <c r="K64" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:13Z</t>
+          <t>2026-10-12T21:43:47Z</t>
         </is>
       </c>
     </row>
@@ -3492,7 +3492,7 @@
       </c>
       <c r="K65" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:13Z</t>
+          <t>2026-10-12T21:43:47Z</t>
         </is>
       </c>
     </row>
@@ -3541,7 +3541,7 @@
       </c>
       <c r="K66" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:13Z</t>
+          <t>2026-10-12T21:43:47Z</t>
         </is>
       </c>
     </row>
@@ -3590,7 +3590,7 @@
       </c>
       <c r="K67" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:13Z</t>
+          <t>2026-10-12T21:43:47Z</t>
         </is>
       </c>
     </row>
@@ -3639,7 +3639,7 @@
       </c>
       <c r="K68" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:13Z</t>
+          <t>2026-10-12T21:43:47Z</t>
         </is>
       </c>
     </row>
@@ -3688,7 +3688,7 @@
       </c>
       <c r="K69" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:13Z</t>
+          <t>2026-10-12T21:43:47Z</t>
         </is>
       </c>
     </row>
@@ -3737,7 +3737,7 @@
       </c>
       <c r="K70" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:13Z</t>
+          <t>2026-10-12T21:43:47Z</t>
         </is>
       </c>
     </row>
@@ -3786,7 +3786,7 @@
       </c>
       <c r="K71" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:13Z</t>
+          <t>2026-10-12T21:43:47Z</t>
         </is>
       </c>
     </row>
@@ -3835,7 +3835,7 @@
       </c>
       <c r="K72" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:13Z</t>
+          <t>2026-10-12T21:43:47Z</t>
         </is>
       </c>
     </row>
@@ -3884,7 +3884,7 @@
       </c>
       <c r="K73" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:13Z</t>
+          <t>2026-10-12T21:43:47Z</t>
         </is>
       </c>
     </row>
@@ -3933,7 +3933,7 @@
       </c>
       <c r="K74" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:13Z</t>
+          <t>2026-10-12T21:43:47Z</t>
         </is>
       </c>
     </row>
@@ -3982,7 +3982,7 @@
       </c>
       <c r="K75" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:13Z</t>
+          <t>2026-10-12T21:43:47Z</t>
         </is>
       </c>
     </row>
@@ -4031,7 +4031,7 @@
       </c>
       <c r="K76" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:13Z</t>
+          <t>2026-10-12T21:43:47Z</t>
         </is>
       </c>
     </row>
@@ -4080,7 +4080,7 @@
       </c>
       <c r="K77" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:13Z</t>
+          <t>2026-10-12T21:43:47Z</t>
         </is>
       </c>
     </row>
@@ -4129,7 +4129,7 @@
       </c>
       <c r="K78" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:13Z</t>
+          <t>2026-10-12T21:43:47Z</t>
         </is>
       </c>
     </row>
@@ -4178,7 +4178,7 @@
       </c>
       <c r="K79" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:13Z</t>
+          <t>2026-10-12T21:43:47Z</t>
         </is>
       </c>
     </row>
@@ -4227,7 +4227,7 @@
       </c>
       <c r="K80" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:13Z</t>
+          <t>2026-10-12T21:43:47Z</t>
         </is>
       </c>
     </row>
@@ -4276,7 +4276,7 @@
       </c>
       <c r="K81" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:13Z</t>
+          <t>2026-10-12T21:43:47Z</t>
         </is>
       </c>
     </row>
@@ -4325,7 +4325,7 @@
       </c>
       <c r="K82" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:13Z</t>
+          <t>2026-10-12T21:43:47Z</t>
         </is>
       </c>
     </row>
@@ -4374,7 +4374,7 @@
       </c>
       <c r="K83" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:13Z</t>
+          <t>2026-10-12T21:43:47Z</t>
         </is>
       </c>
     </row>
@@ -4423,7 +4423,7 @@
       </c>
       <c r="K84" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:13Z</t>
+          <t>2026-10-12T21:43:47Z</t>
         </is>
       </c>
     </row>
@@ -4472,7 +4472,7 @@
       </c>
       <c r="K85" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:13Z</t>
+          <t>2026-10-12T21:43:47Z</t>
         </is>
       </c>
     </row>
@@ -4521,7 +4521,7 @@
       </c>
       <c r="K86" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:13Z</t>
+          <t>2026-10-12T21:43:47Z</t>
         </is>
       </c>
     </row>
@@ -4570,7 +4570,7 @@
       </c>
       <c r="K87" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:13Z</t>
+          <t>2026-10-12T21:43:47Z</t>
         </is>
       </c>
     </row>
@@ -4619,7 +4619,7 @@
       </c>
       <c r="K88" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:13Z</t>
+          <t>2026-10-12T21:43:47Z</t>
         </is>
       </c>
     </row>
@@ -4668,7 +4668,7 @@
       </c>
       <c r="K89" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:13Z</t>
+          <t>2026-10-12T21:43:47Z</t>
         </is>
       </c>
     </row>
@@ -4717,7 +4717,7 @@
       </c>
       <c r="K90" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:13Z</t>
+          <t>2026-10-12T21:43:47Z</t>
         </is>
       </c>
     </row>
@@ -4766,7 +4766,7 @@
       </c>
       <c r="K91" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:13Z</t>
+          <t>2026-10-12T21:43:47Z</t>
         </is>
       </c>
     </row>
@@ -4815,7 +4815,7 @@
       </c>
       <c r="K92" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:13Z</t>
+          <t>2026-10-12T21:43:47Z</t>
         </is>
       </c>
     </row>
@@ -4864,7 +4864,7 @@
       </c>
       <c r="K93" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:13Z</t>
+          <t>2026-10-12T21:43:47Z</t>
         </is>
       </c>
     </row>
@@ -4913,7 +4913,7 @@
       </c>
       <c r="K94" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:13Z</t>
+          <t>2026-10-12T21:43:47Z</t>
         </is>
       </c>
     </row>
@@ -4962,7 +4962,7 @@
       </c>
       <c r="K95" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:13Z</t>
+          <t>2026-10-12T21:43:47Z</t>
         </is>
       </c>
     </row>
@@ -5011,7 +5011,7 @@
       </c>
       <c r="K96" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:13Z</t>
+          <t>2026-10-12T21:43:47Z</t>
         </is>
       </c>
     </row>
@@ -5060,7 +5060,7 @@
       </c>
       <c r="K97" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:13Z</t>
+          <t>2026-10-12T21:43:47Z</t>
         </is>
       </c>
     </row>
@@ -5109,7 +5109,7 @@
       </c>
       <c r="K98" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:13Z</t>
+          <t>2026-10-12T21:43:47Z</t>
         </is>
       </c>
     </row>
@@ -5158,7 +5158,7 @@
       </c>
       <c r="K99" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:13Z</t>
+          <t>2026-10-12T21:43:47Z</t>
         </is>
       </c>
     </row>
@@ -5207,7 +5207,7 @@
       </c>
       <c r="K100" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:13Z</t>
+          <t>2026-10-12T21:43:47Z</t>
         </is>
       </c>
     </row>
@@ -5256,7 +5256,7 @@
       </c>
       <c r="K101" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:13Z</t>
+          <t>2026-10-12T21:43:47Z</t>
         </is>
       </c>
     </row>
@@ -5305,7 +5305,7 @@
       </c>
       <c r="K102" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:13Z</t>
+          <t>2026-10-12T21:43:47Z</t>
         </is>
       </c>
     </row>
@@ -5354,7 +5354,7 @@
       </c>
       <c r="K103" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:13Z</t>
+          <t>2026-10-12T21:43:47Z</t>
         </is>
       </c>
     </row>
@@ -5403,7 +5403,7 @@
       </c>
       <c r="K104" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:13Z</t>
+          <t>2026-10-12T21:43:47Z</t>
         </is>
       </c>
     </row>
@@ -5452,7 +5452,7 @@
       </c>
       <c r="K105" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:13Z</t>
+          <t>2026-10-12T21:43:47Z</t>
         </is>
       </c>
     </row>
@@ -5501,7 +5501,7 @@
       </c>
       <c r="K106" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:13Z</t>
+          <t>2026-10-12T21:43:47Z</t>
         </is>
       </c>
     </row>
@@ -5550,7 +5550,7 @@
       </c>
       <c r="K107" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:13Z</t>
+          <t>2026-10-12T21:43:47Z</t>
         </is>
       </c>
     </row>
@@ -5599,7 +5599,7 @@
       </c>
       <c r="K108" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:13Z</t>
+          <t>2026-10-12T21:43:47Z</t>
         </is>
       </c>
     </row>
@@ -5648,7 +5648,7 @@
       </c>
       <c r="K109" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:13Z</t>
+          <t>2026-10-12T21:43:47Z</t>
         </is>
       </c>
     </row>
@@ -5697,7 +5697,7 @@
       </c>
       <c r="K110" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:13Z</t>
+          <t>2026-10-12T21:43:47Z</t>
         </is>
       </c>
     </row>
@@ -5746,7 +5746,7 @@
       </c>
       <c r="K111" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:13Z</t>
+          <t>2026-10-12T21:43:47Z</t>
         </is>
       </c>
     </row>
@@ -5795,7 +5795,7 @@
       </c>
       <c r="K112" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:13Z</t>
+          <t>2026-10-12T21:43:47Z</t>
         </is>
       </c>
     </row>
@@ -5844,7 +5844,7 @@
       </c>
       <c r="K113" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:13Z</t>
+          <t>2026-10-12T21:43:47Z</t>
         </is>
       </c>
     </row>
@@ -5893,7 +5893,7 @@
       </c>
       <c r="K114" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:13Z</t>
+          <t>2026-10-12T21:43:47Z</t>
         </is>
       </c>
     </row>
@@ -5942,7 +5942,7 @@
       </c>
       <c r="K115" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:13Z</t>
+          <t>2026-10-12T21:43:47Z</t>
         </is>
       </c>
     </row>
@@ -5991,7 +5991,7 @@
       </c>
       <c r="K116" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:13Z</t>
+          <t>2026-10-12T21:43:47Z</t>
         </is>
       </c>
     </row>
@@ -6040,7 +6040,7 @@
       </c>
       <c r="K117" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:13Z</t>
+          <t>2026-10-12T21:43:47Z</t>
         </is>
       </c>
     </row>
@@ -6089,7 +6089,7 @@
       </c>
       <c r="K118" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:13Z</t>
+          <t>2026-10-12T21:43:47Z</t>
         </is>
       </c>
     </row>
@@ -6138,7 +6138,7 @@
       </c>
       <c r="K119" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:13Z</t>
+          <t>2026-10-12T21:43:47Z</t>
         </is>
       </c>
     </row>
@@ -6187,7 +6187,7 @@
       </c>
       <c r="K120" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:13Z</t>
+          <t>2026-10-12T21:43:47Z</t>
         </is>
       </c>
     </row>
@@ -6236,7 +6236,7 @@
       </c>
       <c r="K121" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:13Z</t>
+          <t>2026-10-12T21:43:47Z</t>
         </is>
       </c>
     </row>
@@ -6285,7 +6285,7 @@
       </c>
       <c r="K122" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:13Z</t>
+          <t>2026-10-12T21:43:47Z</t>
         </is>
       </c>
     </row>
@@ -6334,7 +6334,7 @@
       </c>
       <c r="K123" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:13Z</t>
+          <t>2026-10-12T21:43:47Z</t>
         </is>
       </c>
     </row>
@@ -6383,7 +6383,7 @@
       </c>
       <c r="K124" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:13Z</t>
+          <t>2026-10-12T21:43:47Z</t>
         </is>
       </c>
     </row>
@@ -6432,7 +6432,7 @@
       </c>
       <c r="K125" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:13Z</t>
+          <t>2026-10-12T21:43:47Z</t>
         </is>
       </c>
     </row>
@@ -6481,7 +6481,7 @@
       </c>
       <c r="K126" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:13Z</t>
+          <t>2026-10-12T21:43:47Z</t>
         </is>
       </c>
     </row>
@@ -6530,7 +6530,7 @@
       </c>
       <c r="K127" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:13Z</t>
+          <t>2026-10-12T21:43:47Z</t>
         </is>
       </c>
     </row>
@@ -6579,7 +6579,7 @@
       </c>
       <c r="K128" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:13Z</t>
+          <t>2026-10-12T21:43:47Z</t>
         </is>
       </c>
     </row>
@@ -6628,7 +6628,7 @@
       </c>
       <c r="K129" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:13Z</t>
+          <t>2026-10-12T21:43:47Z</t>
         </is>
       </c>
     </row>
@@ -6677,7 +6677,7 @@
       </c>
       <c r="K130" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:13Z</t>
+          <t>2026-10-12T21:43:47Z</t>
         </is>
       </c>
     </row>
@@ -6726,7 +6726,7 @@
       </c>
       <c r="K131" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:13Z</t>
+          <t>2026-10-12T21:43:47Z</t>
         </is>
       </c>
     </row>
@@ -6775,7 +6775,7 @@
       </c>
       <c r="K132" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:13Z</t>
+          <t>2026-10-12T21:43:47Z</t>
         </is>
       </c>
     </row>
@@ -6824,7 +6824,7 @@
       </c>
       <c r="K133" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:13Z</t>
+          <t>2026-10-12T21:43:47Z</t>
         </is>
       </c>
     </row>
@@ -6873,7 +6873,7 @@
       </c>
       <c r="K134" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:13Z</t>
+          <t>2026-10-12T21:43:47Z</t>
         </is>
       </c>
     </row>
@@ -6922,7 +6922,7 @@
       </c>
       <c r="K135" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:13Z</t>
+          <t>2026-10-12T21:43:47Z</t>
         </is>
       </c>
     </row>
@@ -6971,7 +6971,7 @@
       </c>
       <c r="K136" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:13Z</t>
+          <t>2026-10-12T21:43:47Z</t>
         </is>
       </c>
     </row>
@@ -7020,7 +7020,7 @@
       </c>
       <c r="K137" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:13Z</t>
+          <t>2026-10-12T21:43:47Z</t>
         </is>
       </c>
     </row>
@@ -7069,7 +7069,7 @@
       </c>
       <c r="K138" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:13Z</t>
+          <t>2026-10-12T21:43:47Z</t>
         </is>
       </c>
     </row>
@@ -7118,7 +7118,7 @@
       </c>
       <c r="K139" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:13Z</t>
+          <t>2026-10-12T21:43:47Z</t>
         </is>
       </c>
     </row>
@@ -7167,7 +7167,7 @@
       </c>
       <c r="K140" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:13Z</t>
+          <t>2026-10-12T21:43:47Z</t>
         </is>
       </c>
     </row>
@@ -7216,7 +7216,7 @@
       </c>
       <c r="K141" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:13Z</t>
+          <t>2026-10-12T21:43:47Z</t>
         </is>
       </c>
     </row>
@@ -7265,7 +7265,7 @@
       </c>
       <c r="K142" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:13Z</t>
+          <t>2026-10-12T21:43:47Z</t>
         </is>
       </c>
     </row>
@@ -7314,7 +7314,7 @@
       </c>
       <c r="K143" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:13Z</t>
+          <t>2026-10-12T21:43:47Z</t>
         </is>
       </c>
     </row>
@@ -7363,7 +7363,7 @@
       </c>
       <c r="K144" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:13Z</t>
+          <t>2026-10-12T21:43:47Z</t>
         </is>
       </c>
     </row>
@@ -7412,7 +7412,7 @@
       </c>
       <c r="K145" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:13Z</t>
+          <t>2026-10-12T21:43:47Z</t>
         </is>
       </c>
     </row>
@@ -7461,7 +7461,7 @@
       </c>
       <c r="K146" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:13Z</t>
+          <t>2026-10-12T21:43:47Z</t>
         </is>
       </c>
     </row>
@@ -7510,7 +7510,7 @@
       </c>
       <c r="K147" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:13Z</t>
+          <t>2026-10-12T21:43:47Z</t>
         </is>
       </c>
     </row>
@@ -7559,7 +7559,7 @@
       </c>
       <c r="K148" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:13Z</t>
+          <t>2026-10-12T21:43:47Z</t>
         </is>
       </c>
     </row>
@@ -7608,7 +7608,7 @@
       </c>
       <c r="K149" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:13Z</t>
+          <t>2026-10-12T21:43:47Z</t>
         </is>
       </c>
     </row>
@@ -7657,7 +7657,7 @@
       </c>
       <c r="K150" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:13Z</t>
+          <t>2026-10-12T21:43:47Z</t>
         </is>
       </c>
     </row>
@@ -7706,7 +7706,7 @@
       </c>
       <c r="K151" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:13Z</t>
+          <t>2026-10-12T21:43:47Z</t>
         </is>
       </c>
     </row>
@@ -7755,7 +7755,7 @@
       </c>
       <c r="K152" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:13Z</t>
+          <t>2026-10-12T21:43:47Z</t>
         </is>
       </c>
     </row>
@@ -7804,7 +7804,7 @@
       </c>
       <c r="K153" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:13Z</t>
+          <t>2026-10-12T21:43:47Z</t>
         </is>
       </c>
     </row>
@@ -7853,7 +7853,7 @@
       </c>
       <c r="K154" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:13Z</t>
+          <t>2026-10-12T21:43:47Z</t>
         </is>
       </c>
     </row>
@@ -7902,7 +7902,7 @@
       </c>
       <c r="K155" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:13Z</t>
+          <t>2026-10-12T21:43:47Z</t>
         </is>
       </c>
     </row>
@@ -7951,7 +7951,7 @@
       </c>
       <c r="K156" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:13Z</t>
+          <t>2026-10-12T21:43:47Z</t>
         </is>
       </c>
     </row>
@@ -8000,7 +8000,7 @@
       </c>
       <c r="K157" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:13Z</t>
+          <t>2026-10-12T21:43:47Z</t>
         </is>
       </c>
     </row>
@@ -8049,7 +8049,7 @@
       </c>
       <c r="K158" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:13Z</t>
+          <t>2026-10-12T21:43:47Z</t>
         </is>
       </c>
     </row>
@@ -8098,7 +8098,7 @@
       </c>
       <c r="K159" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:13Z</t>
+          <t>2026-10-12T21:43:47Z</t>
         </is>
       </c>
     </row>
@@ -8147,7 +8147,7 @@
       </c>
       <c r="K160" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:13Z</t>
+          <t>2026-10-12T21:43:47Z</t>
         </is>
       </c>
     </row>
@@ -8196,7 +8196,7 @@
       </c>
       <c r="K161" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:13Z</t>
+          <t>2026-10-12T21:43:47Z</t>
         </is>
       </c>
     </row>
@@ -8245,7 +8245,7 @@
       </c>
       <c r="K162" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:13Z</t>
+          <t>2026-10-12T21:43:47Z</t>
         </is>
       </c>
     </row>
@@ -8294,7 +8294,7 @@
       </c>
       <c r="K163" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:13Z</t>
+          <t>2026-10-12T21:43:47Z</t>
         </is>
       </c>
     </row>
@@ -8343,7 +8343,7 @@
       </c>
       <c r="K164" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:13Z</t>
+          <t>2026-10-12T21:43:47Z</t>
         </is>
       </c>
     </row>
@@ -8392,7 +8392,7 @@
       </c>
       <c r="K165" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:13Z</t>
+          <t>2026-10-12T21:43:47Z</t>
         </is>
       </c>
     </row>
@@ -8441,7 +8441,7 @@
       </c>
       <c r="K166" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:13Z</t>
+          <t>2026-10-12T21:43:47Z</t>
         </is>
       </c>
     </row>
@@ -8490,7 +8490,7 @@
       </c>
       <c r="K167" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:13Z</t>
+          <t>2026-10-12T21:43:47Z</t>
         </is>
       </c>
     </row>
@@ -8539,7 +8539,7 @@
       </c>
       <c r="K168" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:13Z</t>
+          <t>2026-10-12T21:43:47Z</t>
         </is>
       </c>
     </row>
@@ -8588,7 +8588,7 @@
       </c>
       <c r="K169" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:13Z</t>
+          <t>2026-10-12T21:43:47Z</t>
         </is>
       </c>
     </row>
@@ -8637,7 +8637,7 @@
       </c>
       <c r="K170" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:13Z</t>
+          <t>2026-10-12T21:43:47Z</t>
         </is>
       </c>
     </row>
@@ -8686,7 +8686,7 @@
       </c>
       <c r="K171" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:13Z</t>
+          <t>2026-10-12T21:43:47Z</t>
         </is>
       </c>
     </row>
@@ -8735,7 +8735,7 @@
       </c>
       <c r="K172" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:13Z</t>
+          <t>2026-10-12T21:43:47Z</t>
         </is>
       </c>
     </row>
@@ -8784,7 +8784,7 @@
       </c>
       <c r="K173" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:13Z</t>
+          <t>2026-10-12T21:43:47Z</t>
         </is>
       </c>
     </row>
@@ -8833,7 +8833,7 @@
       </c>
       <c r="K174" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:13Z</t>
+          <t>2026-10-12T21:43:47Z</t>
         </is>
       </c>
     </row>
@@ -8882,7 +8882,7 @@
       </c>
       <c r="K175" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:13Z</t>
+          <t>2026-10-12T21:43:47Z</t>
         </is>
       </c>
     </row>
@@ -8931,7 +8931,7 @@
       </c>
       <c r="K176" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:13Z</t>
+          <t>2026-10-12T21:43:47Z</t>
         </is>
       </c>
     </row>
@@ -8980,7 +8980,7 @@
       </c>
       <c r="K177" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:13Z</t>
+          <t>2026-10-12T21:43:47Z</t>
         </is>
       </c>
     </row>
@@ -9029,7 +9029,7 @@
       </c>
       <c r="K178" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:13Z</t>
+          <t>2026-10-12T21:43:47Z</t>
         </is>
       </c>
     </row>
@@ -9078,7 +9078,7 @@
       </c>
       <c r="K179" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:13Z</t>
+          <t>2026-10-12T21:43:47Z</t>
         </is>
       </c>
     </row>
@@ -9127,7 +9127,7 @@
       </c>
       <c r="K180" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:13Z</t>
+          <t>2026-10-12T21:43:47Z</t>
         </is>
       </c>
     </row>
@@ -9176,7 +9176,7 @@
       </c>
       <c r="K181" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:13Z</t>
+          <t>2026-10-12T21:43:47Z</t>
         </is>
       </c>
     </row>
@@ -9225,7 +9225,7 @@
       </c>
       <c r="K182" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:13Z</t>
+          <t>2026-10-12T21:43:47Z</t>
         </is>
       </c>
     </row>
@@ -9274,7 +9274,7 @@
       </c>
       <c r="K183" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:13Z</t>
+          <t>2026-10-12T21:43:47Z</t>
         </is>
       </c>
     </row>
@@ -9323,7 +9323,7 @@
       </c>
       <c r="K184" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:13Z</t>
+          <t>2026-10-12T21:43:47Z</t>
         </is>
       </c>
     </row>
@@ -9372,7 +9372,7 @@
       </c>
       <c r="K185" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:13Z</t>
+          <t>2026-10-12T21:43:47Z</t>
         </is>
       </c>
     </row>
@@ -9421,7 +9421,7 @@
       </c>
       <c r="K186" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:13Z</t>
+          <t>2026-10-12T21:43:47Z</t>
         </is>
       </c>
     </row>
@@ -9470,7 +9470,7 @@
       </c>
       <c r="K187" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:13Z</t>
+          <t>2026-10-12T21:43:47Z</t>
         </is>
       </c>
     </row>
@@ -9519,7 +9519,7 @@
       </c>
       <c r="K188" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:13Z</t>
+          <t>2026-10-12T21:43:47Z</t>
         </is>
       </c>
     </row>
@@ -9568,7 +9568,7 @@
       </c>
       <c r="K189" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:13Z</t>
+          <t>2026-10-12T21:43:47Z</t>
         </is>
       </c>
     </row>
@@ -9617,7 +9617,7 @@
       </c>
       <c r="K190" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:13Z</t>
+          <t>2026-10-12T21:43:47Z</t>
         </is>
       </c>
     </row>
@@ -9666,7 +9666,7 @@
       </c>
       <c r="K191" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:13Z</t>
+          <t>2026-10-12T21:43:47Z</t>
         </is>
       </c>
     </row>
@@ -9715,7 +9715,7 @@
       </c>
       <c r="K192" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:13Z</t>
+          <t>2026-10-12T21:43:47Z</t>
         </is>
       </c>
     </row>
@@ -9764,7 +9764,7 @@
       </c>
       <c r="K193" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:13Z</t>
+          <t>2026-10-12T21:43:47Z</t>
         </is>
       </c>
     </row>
@@ -9813,7 +9813,7 @@
       </c>
       <c r="K194" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:13Z</t>
+          <t>2026-10-12T21:43:47Z</t>
         </is>
       </c>
     </row>
@@ -9862,7 +9862,7 @@
       </c>
       <c r="K195" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:13Z</t>
+          <t>2026-10-12T21:43:47Z</t>
         </is>
       </c>
     </row>
@@ -9911,7 +9911,7 @@
       </c>
       <c r="K196" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:13Z</t>
+          <t>2026-10-12T21:43:47Z</t>
         </is>
       </c>
     </row>
@@ -9960,7 +9960,7 @@
       </c>
       <c r="K197" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:13Z</t>
+          <t>2026-10-12T21:43:47Z</t>
         </is>
       </c>
     </row>
@@ -10009,7 +10009,7 @@
       </c>
       <c r="K198" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:13Z</t>
+          <t>2026-10-12T21:43:47Z</t>
         </is>
       </c>
     </row>
@@ -10058,7 +10058,7 @@
       </c>
       <c r="K199" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:13Z</t>
+          <t>2026-10-12T21:43:47Z</t>
         </is>
       </c>
     </row>
@@ -10107,7 +10107,7 @@
       </c>
       <c r="K200" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:13Z</t>
+          <t>2026-10-12T21:43:47Z</t>
         </is>
       </c>
     </row>
@@ -10156,7 +10156,7 @@
       </c>
       <c r="K201" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:13Z</t>
+          <t>2026-10-12T21:43:47Z</t>
         </is>
       </c>
     </row>
@@ -10205,7 +10205,7 @@
       </c>
       <c r="K202" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:13Z</t>
+          <t>2026-10-12T21:43:47Z</t>
         </is>
       </c>
     </row>
@@ -10254,7 +10254,7 @@
       </c>
       <c r="K203" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:13Z</t>
+          <t>2026-10-12T21:43:47Z</t>
         </is>
       </c>
     </row>
@@ -10303,7 +10303,7 @@
       </c>
       <c r="K204" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:13Z</t>
+          <t>2026-10-12T21:43:47Z</t>
         </is>
       </c>
     </row>
@@ -10352,7 +10352,7 @@
       </c>
       <c r="K205" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:13Z</t>
+          <t>2026-10-12T21:43:47Z</t>
         </is>
       </c>
     </row>
@@ -10401,7 +10401,7 @@
       </c>
       <c r="K206" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:13Z</t>
+          <t>2026-10-12T21:43:47Z</t>
         </is>
       </c>
     </row>
@@ -10450,7 +10450,7 @@
       </c>
       <c r="K207" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:13Z</t>
+          <t>2026-10-12T21:43:47Z</t>
         </is>
       </c>
     </row>
@@ -10499,7 +10499,7 @@
       </c>
       <c r="K208" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:13Z</t>
+          <t>2026-10-12T21:43:47Z</t>
         </is>
       </c>
     </row>
@@ -10548,7 +10548,7 @@
       </c>
       <c r="K209" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:13Z</t>
+          <t>2026-10-12T21:43:47Z</t>
         </is>
       </c>
     </row>
@@ -10597,7 +10597,7 @@
       </c>
       <c r="K210" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:13Z</t>
+          <t>2026-10-12T21:43:47Z</t>
         </is>
       </c>
     </row>
@@ -10646,7 +10646,7 @@
       </c>
       <c r="K211" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:13Z</t>
+          <t>2026-10-12T21:43:47Z</t>
         </is>
       </c>
     </row>
@@ -10695,7 +10695,7 @@
       </c>
       <c r="K212" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:13Z</t>
+          <t>2026-10-12T21:43:47Z</t>
         </is>
       </c>
     </row>
@@ -10744,7 +10744,7 @@
       </c>
       <c r="K213" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:13Z</t>
+          <t>2026-10-12T21:43:47Z</t>
         </is>
       </c>
     </row>
@@ -10793,7 +10793,7 @@
       </c>
       <c r="K214" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:13Z</t>
+          <t>2026-10-12T21:43:47Z</t>
         </is>
       </c>
     </row>
@@ -10842,7 +10842,7 @@
       </c>
       <c r="K215" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:13Z</t>
+          <t>2026-10-12T21:43:47Z</t>
         </is>
       </c>
     </row>
@@ -10891,7 +10891,7 @@
       </c>
       <c r="K216" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:13Z</t>
+          <t>2026-10-12T21:43:47Z</t>
         </is>
       </c>
     </row>
@@ -10940,7 +10940,7 @@
       </c>
       <c r="K217" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:13Z</t>
+          <t>2026-10-12T21:43:47Z</t>
         </is>
       </c>
     </row>
@@ -10989,7 +10989,7 @@
       </c>
       <c r="K218" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:13Z</t>
+          <t>2026-10-12T21:43:47Z</t>
         </is>
       </c>
     </row>
@@ -11038,7 +11038,7 @@
       </c>
       <c r="K219" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:13Z</t>
+          <t>2026-10-12T21:43:47Z</t>
         </is>
       </c>
     </row>
@@ -11087,7 +11087,7 @@
       </c>
       <c r="K220" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:13Z</t>
+          <t>2026-10-12T21:43:47Z</t>
         </is>
       </c>
     </row>
@@ -11136,7 +11136,7 @@
       </c>
       <c r="K221" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:13Z</t>
+          <t>2026-10-12T21:43:47Z</t>
         </is>
       </c>
     </row>
@@ -11185,7 +11185,7 @@
       </c>
       <c r="K222" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:13Z</t>
+          <t>2026-10-12T21:43:47Z</t>
         </is>
       </c>
     </row>
@@ -11234,7 +11234,7 @@
       </c>
       <c r="K223" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:13Z</t>
+          <t>2026-10-12T21:43:47Z</t>
         </is>
       </c>
     </row>
@@ -11283,7 +11283,7 @@
       </c>
       <c r="K224" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:13Z</t>
+          <t>2026-10-12T21:43:47Z</t>
         </is>
       </c>
     </row>
@@ -11332,7 +11332,7 @@
       </c>
       <c r="K225" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:13Z</t>
+          <t>2026-10-12T21:43:47Z</t>
         </is>
       </c>
     </row>
@@ -11381,7 +11381,7 @@
       </c>
       <c r="K226" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:13Z</t>
+          <t>2026-10-12T21:43:47Z</t>
         </is>
       </c>
     </row>
@@ -11430,7 +11430,7 @@
       </c>
       <c r="K227" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:13Z</t>
+          <t>2026-10-12T21:43:47Z</t>
         </is>
       </c>
     </row>
@@ -11479,7 +11479,7 @@
       </c>
       <c r="K228" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:13Z</t>
+          <t>2026-10-12T21:43:47Z</t>
         </is>
       </c>
     </row>
@@ -11528,7 +11528,7 @@
       </c>
       <c r="K229" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:13Z</t>
+          <t>2026-10-12T21:43:47Z</t>
         </is>
       </c>
     </row>
@@ -11577,7 +11577,7 @@
       </c>
       <c r="K230" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:13Z</t>
+          <t>2026-10-12T21:43:47Z</t>
         </is>
       </c>
     </row>
@@ -11626,7 +11626,7 @@
       </c>
       <c r="K231" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:13Z</t>
+          <t>2026-10-12T21:43:47Z</t>
         </is>
       </c>
     </row>
@@ -11758,7 +11758,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:13Z</t>
+          <t>2026-10-12T21:43:47Z</t>
         </is>
       </c>
     </row>
@@ -11804,7 +11804,7 @@
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>{"date": "2026-08-01", "year": 2026, "month": 8, "month_name": "Agosto", "index_value": 637409769724325.1, "monthly_variation_pct": 8.9, "unit": "Índice base diciembre 2007=100 y variación mensual %", "frequency": "monthly", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/precios_consumidor/4_5_7_2.xls", "fetched_at": "2026-10-11T23:49:13Z"}</t>
+          <t>{"date": "2026-08-01", "year": 2026, "month": 8, "month_name": "Agosto", "index_value": 637409769724325.1, "monthly_variation_pct": 8.9, "unit": "Índice base diciembre 2007=100 y variación mensual %", "frequency": "monthly", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/precios_consumidor/4_5_7_2.xls", "fetched_at": "2026-10-12T21:43:47Z"}</t>
         </is>
       </c>
     </row>

--- a/assets/data/bcv/excel/ove_bcv_inpc_nacional_mensual.xlsx
+++ b/assets/data/bcv/excel/ove_bcv_inpc_nacional_mensual.xlsx
@@ -650,7 +650,7 @@
       </c>
       <c r="K7" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:47Z</t>
+          <t>2026-10-13T02:10:27Z</t>
         </is>
       </c>
     </row>
@@ -699,7 +699,7 @@
       </c>
       <c r="K8" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:47Z</t>
+          <t>2026-10-13T02:10:27Z</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="K9" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:47Z</t>
+          <t>2026-10-13T02:10:27Z</t>
         </is>
       </c>
     </row>
@@ -797,7 +797,7 @@
       </c>
       <c r="K10" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:47Z</t>
+          <t>2026-10-13T02:10:27Z</t>
         </is>
       </c>
     </row>
@@ -846,7 +846,7 @@
       </c>
       <c r="K11" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:47Z</t>
+          <t>2026-10-13T02:10:27Z</t>
         </is>
       </c>
     </row>
@@ -895,7 +895,7 @@
       </c>
       <c r="K12" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:47Z</t>
+          <t>2026-10-13T02:10:27Z</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="K13" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:47Z</t>
+          <t>2026-10-13T02:10:27Z</t>
         </is>
       </c>
     </row>
@@ -993,7 +993,7 @@
       </c>
       <c r="K14" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:47Z</t>
+          <t>2026-10-13T02:10:27Z</t>
         </is>
       </c>
     </row>
@@ -1042,7 +1042,7 @@
       </c>
       <c r="K15" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:47Z</t>
+          <t>2026-10-13T02:10:27Z</t>
         </is>
       </c>
     </row>
@@ -1091,7 +1091,7 @@
       </c>
       <c r="K16" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:47Z</t>
+          <t>2026-10-13T02:10:27Z</t>
         </is>
       </c>
     </row>
@@ -1140,7 +1140,7 @@
       </c>
       <c r="K17" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:47Z</t>
+          <t>2026-10-13T02:10:27Z</t>
         </is>
       </c>
     </row>
@@ -1189,7 +1189,7 @@
       </c>
       <c r="K18" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:47Z</t>
+          <t>2026-10-13T02:10:27Z</t>
         </is>
       </c>
     </row>
@@ -1238,7 +1238,7 @@
       </c>
       <c r="K19" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:47Z</t>
+          <t>2026-10-13T02:10:27Z</t>
         </is>
       </c>
     </row>
@@ -1287,7 +1287,7 @@
       </c>
       <c r="K20" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:47Z</t>
+          <t>2026-10-13T02:10:27Z</t>
         </is>
       </c>
     </row>
@@ -1336,7 +1336,7 @@
       </c>
       <c r="K21" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:47Z</t>
+          <t>2026-10-13T02:10:27Z</t>
         </is>
       </c>
     </row>
@@ -1385,7 +1385,7 @@
       </c>
       <c r="K22" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:47Z</t>
+          <t>2026-10-13T02:10:27Z</t>
         </is>
       </c>
     </row>
@@ -1434,7 +1434,7 @@
       </c>
       <c r="K23" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:47Z</t>
+          <t>2026-10-13T02:10:27Z</t>
         </is>
       </c>
     </row>
@@ -1483,7 +1483,7 @@
       </c>
       <c r="K24" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:47Z</t>
+          <t>2026-10-13T02:10:27Z</t>
         </is>
       </c>
     </row>
@@ -1532,7 +1532,7 @@
       </c>
       <c r="K25" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:47Z</t>
+          <t>2026-10-13T02:10:27Z</t>
         </is>
       </c>
     </row>
@@ -1581,7 +1581,7 @@
       </c>
       <c r="K26" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:47Z</t>
+          <t>2026-10-13T02:10:27Z</t>
         </is>
       </c>
     </row>
@@ -1630,7 +1630,7 @@
       </c>
       <c r="K27" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:47Z</t>
+          <t>2026-10-13T02:10:27Z</t>
         </is>
       </c>
     </row>
@@ -1679,7 +1679,7 @@
       </c>
       <c r="K28" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:47Z</t>
+          <t>2026-10-13T02:10:27Z</t>
         </is>
       </c>
     </row>
@@ -1728,7 +1728,7 @@
       </c>
       <c r="K29" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:47Z</t>
+          <t>2026-10-13T02:10:27Z</t>
         </is>
       </c>
     </row>
@@ -1777,7 +1777,7 @@
       </c>
       <c r="K30" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:47Z</t>
+          <t>2026-10-13T02:10:27Z</t>
         </is>
       </c>
     </row>
@@ -1826,7 +1826,7 @@
       </c>
       <c r="K31" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:47Z</t>
+          <t>2026-10-13T02:10:27Z</t>
         </is>
       </c>
     </row>
@@ -1875,7 +1875,7 @@
       </c>
       <c r="K32" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:47Z</t>
+          <t>2026-10-13T02:10:27Z</t>
         </is>
       </c>
     </row>
@@ -1924,7 +1924,7 @@
       </c>
       <c r="K33" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:47Z</t>
+          <t>2026-10-13T02:10:27Z</t>
         </is>
       </c>
     </row>
@@ -1973,7 +1973,7 @@
       </c>
       <c r="K34" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:47Z</t>
+          <t>2026-10-13T02:10:27Z</t>
         </is>
       </c>
     </row>
@@ -2022,7 +2022,7 @@
       </c>
       <c r="K35" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:47Z</t>
+          <t>2026-10-13T02:10:27Z</t>
         </is>
       </c>
     </row>
@@ -2071,7 +2071,7 @@
       </c>
       <c r="K36" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:47Z</t>
+          <t>2026-10-13T02:10:27Z</t>
         </is>
       </c>
     </row>
@@ -2120,7 +2120,7 @@
       </c>
       <c r="K37" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:47Z</t>
+          <t>2026-10-13T02:10:27Z</t>
         </is>
       </c>
     </row>
@@ -2169,7 +2169,7 @@
       </c>
       <c r="K38" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:47Z</t>
+          <t>2026-10-13T02:10:27Z</t>
         </is>
       </c>
     </row>
@@ -2218,7 +2218,7 @@
       </c>
       <c r="K39" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:47Z</t>
+          <t>2026-10-13T02:10:27Z</t>
         </is>
       </c>
     </row>
@@ -2267,7 +2267,7 @@
       </c>
       <c r="K40" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:47Z</t>
+          <t>2026-10-13T02:10:27Z</t>
         </is>
       </c>
     </row>
@@ -2316,7 +2316,7 @@
       </c>
       <c r="K41" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:47Z</t>
+          <t>2026-10-13T02:10:27Z</t>
         </is>
       </c>
     </row>
@@ -2365,7 +2365,7 @@
       </c>
       <c r="K42" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:47Z</t>
+          <t>2026-10-13T02:10:27Z</t>
         </is>
       </c>
     </row>
@@ -2414,7 +2414,7 @@
       </c>
       <c r="K43" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:47Z</t>
+          <t>2026-10-13T02:10:27Z</t>
         </is>
       </c>
     </row>
@@ -2463,7 +2463,7 @@
       </c>
       <c r="K44" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:47Z</t>
+          <t>2026-10-13T02:10:27Z</t>
         </is>
       </c>
     </row>
@@ -2512,7 +2512,7 @@
       </c>
       <c r="K45" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:47Z</t>
+          <t>2026-10-13T02:10:27Z</t>
         </is>
       </c>
     </row>
@@ -2561,7 +2561,7 @@
       </c>
       <c r="K46" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:47Z</t>
+          <t>2026-10-13T02:10:27Z</t>
         </is>
       </c>
     </row>
@@ -2610,7 +2610,7 @@
       </c>
       <c r="K47" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:47Z</t>
+          <t>2026-10-13T02:10:27Z</t>
         </is>
       </c>
     </row>
@@ -2659,7 +2659,7 @@
       </c>
       <c r="K48" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:47Z</t>
+          <t>2026-10-13T02:10:27Z</t>
         </is>
       </c>
     </row>
@@ -2708,7 +2708,7 @@
       </c>
       <c r="K49" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:47Z</t>
+          <t>2026-10-13T02:10:27Z</t>
         </is>
       </c>
     </row>
@@ -2757,7 +2757,7 @@
       </c>
       <c r="K50" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:47Z</t>
+          <t>2026-10-13T02:10:27Z</t>
         </is>
       </c>
     </row>
@@ -2806,7 +2806,7 @@
       </c>
       <c r="K51" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:47Z</t>
+          <t>2026-10-13T02:10:27Z</t>
         </is>
       </c>
     </row>
@@ -2855,7 +2855,7 @@
       </c>
       <c r="K52" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:47Z</t>
+          <t>2026-10-13T02:10:27Z</t>
         </is>
       </c>
     </row>
@@ -2904,7 +2904,7 @@
       </c>
       <c r="K53" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:47Z</t>
+          <t>2026-10-13T02:10:27Z</t>
         </is>
       </c>
     </row>
@@ -2953,7 +2953,7 @@
       </c>
       <c r="K54" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:47Z</t>
+          <t>2026-10-13T02:10:27Z</t>
         </is>
       </c>
     </row>
@@ -3002,7 +3002,7 @@
       </c>
       <c r="K55" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:47Z</t>
+          <t>2026-10-13T02:10:27Z</t>
         </is>
       </c>
     </row>
@@ -3051,7 +3051,7 @@
       </c>
       <c r="K56" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:47Z</t>
+          <t>2026-10-13T02:10:27Z</t>
         </is>
       </c>
     </row>
@@ -3100,7 +3100,7 @@
       </c>
       <c r="K57" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:47Z</t>
+          <t>2026-10-13T02:10:27Z</t>
         </is>
       </c>
     </row>
@@ -3149,7 +3149,7 @@
       </c>
       <c r="K58" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:47Z</t>
+          <t>2026-10-13T02:10:27Z</t>
         </is>
       </c>
     </row>
@@ -3198,7 +3198,7 @@
       </c>
       <c r="K59" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:47Z</t>
+          <t>2026-10-13T02:10:27Z</t>
         </is>
       </c>
     </row>
@@ -3247,7 +3247,7 @@
       </c>
       <c r="K60" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:47Z</t>
+          <t>2026-10-13T02:10:27Z</t>
         </is>
       </c>
     </row>
@@ -3296,7 +3296,7 @@
       </c>
       <c r="K61" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:47Z</t>
+          <t>2026-10-13T02:10:27Z</t>
         </is>
       </c>
     </row>
@@ -3345,7 +3345,7 @@
       </c>
       <c r="K62" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:47Z</t>
+          <t>2026-10-13T02:10:27Z</t>
         </is>
       </c>
     </row>
@@ -3394,7 +3394,7 @@
       </c>
       <c r="K63" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:47Z</t>
+          <t>2026-10-13T02:10:27Z</t>
         </is>
       </c>
     </row>
@@ -3443,7 +3443,7 @@
       </c>
       <c r="K64" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:47Z</t>
+          <t>2026-10-13T02:10:27Z</t>
         </is>
       </c>
     </row>
@@ -3492,7 +3492,7 @@
       </c>
       <c r="K65" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:47Z</t>
+          <t>2026-10-13T02:10:27Z</t>
         </is>
       </c>
     </row>
@@ -3541,7 +3541,7 @@
       </c>
       <c r="K66" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:47Z</t>
+          <t>2026-10-13T02:10:27Z</t>
         </is>
       </c>
     </row>
@@ -3590,7 +3590,7 @@
       </c>
       <c r="K67" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:47Z</t>
+          <t>2026-10-13T02:10:27Z</t>
         </is>
       </c>
     </row>
@@ -3639,7 +3639,7 @@
       </c>
       <c r="K68" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:47Z</t>
+          <t>2026-10-13T02:10:27Z</t>
         </is>
       </c>
     </row>
@@ -3688,7 +3688,7 @@
       </c>
       <c r="K69" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:47Z</t>
+          <t>2026-10-13T02:10:27Z</t>
         </is>
       </c>
     </row>
@@ -3737,7 +3737,7 @@
       </c>
       <c r="K70" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:47Z</t>
+          <t>2026-10-13T02:10:27Z</t>
         </is>
       </c>
     </row>
@@ -3786,7 +3786,7 @@
       </c>
       <c r="K71" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:47Z</t>
+          <t>2026-10-13T02:10:27Z</t>
         </is>
       </c>
     </row>
@@ -3835,7 +3835,7 @@
       </c>
       <c r="K72" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:47Z</t>
+          <t>2026-10-13T02:10:27Z</t>
         </is>
       </c>
     </row>
@@ -3884,7 +3884,7 @@
       </c>
       <c r="K73" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:47Z</t>
+          <t>2026-10-13T02:10:27Z</t>
         </is>
       </c>
     </row>
@@ -3933,7 +3933,7 @@
       </c>
       <c r="K74" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:47Z</t>
+          <t>2026-10-13T02:10:27Z</t>
         </is>
       </c>
     </row>
@@ -3982,7 +3982,7 @@
       </c>
       <c r="K75" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:47Z</t>
+          <t>2026-10-13T02:10:27Z</t>
         </is>
       </c>
     </row>
@@ -4031,7 +4031,7 @@
       </c>
       <c r="K76" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:47Z</t>
+          <t>2026-10-13T02:10:27Z</t>
         </is>
       </c>
     </row>
@@ -4080,7 +4080,7 @@
       </c>
       <c r="K77" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:47Z</t>
+          <t>2026-10-13T02:10:27Z</t>
         </is>
       </c>
     </row>
@@ -4129,7 +4129,7 @@
       </c>
       <c r="K78" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:47Z</t>
+          <t>2026-10-13T02:10:27Z</t>
         </is>
       </c>
     </row>
@@ -4178,7 +4178,7 @@
       </c>
       <c r="K79" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:47Z</t>
+          <t>2026-10-13T02:10:27Z</t>
         </is>
       </c>
     </row>
@@ -4227,7 +4227,7 @@
       </c>
       <c r="K80" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:47Z</t>
+          <t>2026-10-13T02:10:27Z</t>
         </is>
       </c>
     </row>
@@ -4276,7 +4276,7 @@
       </c>
       <c r="K81" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:47Z</t>
+          <t>2026-10-13T02:10:27Z</t>
         </is>
       </c>
     </row>
@@ -4325,7 +4325,7 @@
       </c>
       <c r="K82" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:47Z</t>
+          <t>2026-10-13T02:10:27Z</t>
         </is>
       </c>
     </row>
@@ -4374,7 +4374,7 @@
       </c>
       <c r="K83" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:47Z</t>
+          <t>2026-10-13T02:10:27Z</t>
         </is>
       </c>
     </row>
@@ -4423,7 +4423,7 @@
       </c>
       <c r="K84" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:47Z</t>
+          <t>2026-10-13T02:10:27Z</t>
         </is>
       </c>
     </row>
@@ -4472,7 +4472,7 @@
       </c>
       <c r="K85" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:47Z</t>
+          <t>2026-10-13T02:10:27Z</t>
         </is>
       </c>
     </row>
@@ -4521,7 +4521,7 @@
       </c>
       <c r="K86" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:47Z</t>
+          <t>2026-10-13T02:10:27Z</t>
         </is>
       </c>
     </row>
@@ -4570,7 +4570,7 @@
       </c>
       <c r="K87" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:47Z</t>
+          <t>2026-10-13T02:10:27Z</t>
         </is>
       </c>
     </row>
@@ -4619,7 +4619,7 @@
       </c>
       <c r="K88" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:47Z</t>
+          <t>2026-10-13T02:10:27Z</t>
         </is>
       </c>
     </row>
@@ -4668,7 +4668,7 @@
       </c>
       <c r="K89" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:47Z</t>
+          <t>2026-10-13T02:10:27Z</t>
         </is>
       </c>
     </row>
@@ -4717,7 +4717,7 @@
       </c>
       <c r="K90" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:47Z</t>
+          <t>2026-10-13T02:10:27Z</t>
         </is>
       </c>
     </row>
@@ -4766,7 +4766,7 @@
       </c>
       <c r="K91" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:47Z</t>
+          <t>2026-10-13T02:10:27Z</t>
         </is>
       </c>
     </row>
@@ -4815,7 +4815,7 @@
       </c>
       <c r="K92" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:47Z</t>
+          <t>2026-10-13T02:10:27Z</t>
         </is>
       </c>
     </row>
@@ -4864,7 +4864,7 @@
       </c>
       <c r="K93" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:47Z</t>
+          <t>2026-10-13T02:10:27Z</t>
         </is>
       </c>
     </row>
@@ -4913,7 +4913,7 @@
       </c>
       <c r="K94" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:47Z</t>
+          <t>2026-10-13T02:10:27Z</t>
         </is>
       </c>
     </row>
@@ -4962,7 +4962,7 @@
       </c>
       <c r="K95" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:47Z</t>
+          <t>2026-10-13T02:10:27Z</t>
         </is>
       </c>
     </row>
@@ -5011,7 +5011,7 @@
       </c>
       <c r="K96" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:47Z</t>
+          <t>2026-10-13T02:10:27Z</t>
         </is>
       </c>
     </row>
@@ -5060,7 +5060,7 @@
       </c>
       <c r="K97" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:47Z</t>
+          <t>2026-10-13T02:10:27Z</t>
         </is>
       </c>
     </row>
@@ -5109,7 +5109,7 @@
       </c>
       <c r="K98" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:47Z</t>
+          <t>2026-10-13T02:10:27Z</t>
         </is>
       </c>
     </row>
@@ -5158,7 +5158,7 @@
       </c>
       <c r="K99" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:47Z</t>
+          <t>2026-10-13T02:10:27Z</t>
         </is>
       </c>
     </row>
@@ -5207,7 +5207,7 @@
       </c>
       <c r="K100" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:47Z</t>
+          <t>2026-10-13T02:10:27Z</t>
         </is>
       </c>
     </row>
@@ -5256,7 +5256,7 @@
       </c>
       <c r="K101" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:47Z</t>
+          <t>2026-10-13T02:10:27Z</t>
         </is>
       </c>
     </row>
@@ -5305,7 +5305,7 @@
       </c>
       <c r="K102" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:47Z</t>
+          <t>2026-10-13T02:10:27Z</t>
         </is>
       </c>
     </row>
@@ -5354,7 +5354,7 @@
       </c>
       <c r="K103" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:47Z</t>
+          <t>2026-10-13T02:10:27Z</t>
         </is>
       </c>
     </row>
@@ -5403,7 +5403,7 @@
       </c>
       <c r="K104" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:47Z</t>
+          <t>2026-10-13T02:10:27Z</t>
         </is>
       </c>
     </row>
@@ -5452,7 +5452,7 @@
       </c>
       <c r="K105" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:47Z</t>
+          <t>2026-10-13T02:10:27Z</t>
         </is>
       </c>
     </row>
@@ -5501,7 +5501,7 @@
       </c>
       <c r="K106" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:47Z</t>
+          <t>2026-10-13T02:10:27Z</t>
         </is>
       </c>
     </row>
@@ -5550,7 +5550,7 @@
       </c>
       <c r="K107" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:47Z</t>
+          <t>2026-10-13T02:10:27Z</t>
         </is>
       </c>
     </row>
@@ -5599,7 +5599,7 @@
       </c>
       <c r="K108" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:47Z</t>
+          <t>2026-10-13T02:10:27Z</t>
         </is>
       </c>
     </row>
@@ -5648,7 +5648,7 @@
       </c>
       <c r="K109" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:47Z</t>
+          <t>2026-10-13T02:10:27Z</t>
         </is>
       </c>
     </row>
@@ -5697,7 +5697,7 @@
       </c>
       <c r="K110" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:47Z</t>
+          <t>2026-10-13T02:10:27Z</t>
         </is>
       </c>
     </row>
@@ -5746,7 +5746,7 @@
       </c>
       <c r="K111" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:47Z</t>
+          <t>2026-10-13T02:10:27Z</t>
         </is>
       </c>
     </row>
@@ -5795,7 +5795,7 @@
       </c>
       <c r="K112" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:47Z</t>
+          <t>2026-10-13T02:10:27Z</t>
         </is>
       </c>
     </row>
@@ -5844,7 +5844,7 @@
       </c>
       <c r="K113" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:47Z</t>
+          <t>2026-10-13T02:10:27Z</t>
         </is>
       </c>
     </row>
@@ -5893,7 +5893,7 @@
       </c>
       <c r="K114" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:47Z</t>
+          <t>2026-10-13T02:10:27Z</t>
         </is>
       </c>
     </row>
@@ -5942,7 +5942,7 @@
       </c>
       <c r="K115" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:47Z</t>
+          <t>2026-10-13T02:10:27Z</t>
         </is>
       </c>
     </row>
@@ -5991,7 +5991,7 @@
       </c>
       <c r="K116" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:47Z</t>
+          <t>2026-10-13T02:10:27Z</t>
         </is>
       </c>
     </row>
@@ -6040,7 +6040,7 @@
       </c>
       <c r="K117" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:47Z</t>
+          <t>2026-10-13T02:10:27Z</t>
         </is>
       </c>
     </row>
@@ -6089,7 +6089,7 @@
       </c>
       <c r="K118" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:47Z</t>
+          <t>2026-10-13T02:10:27Z</t>
         </is>
       </c>
     </row>
@@ -6138,7 +6138,7 @@
       </c>
       <c r="K119" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:47Z</t>
+          <t>2026-10-13T02:10:27Z</t>
         </is>
       </c>
     </row>
@@ -6187,7 +6187,7 @@
       </c>
       <c r="K120" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:47Z</t>
+          <t>2026-10-13T02:10:27Z</t>
         </is>
       </c>
     </row>
@@ -6236,7 +6236,7 @@
       </c>
       <c r="K121" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:47Z</t>
+          <t>2026-10-13T02:10:27Z</t>
         </is>
       </c>
     </row>
@@ -6285,7 +6285,7 @@
       </c>
       <c r="K122" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:47Z</t>
+          <t>2026-10-13T02:10:27Z</t>
         </is>
       </c>
     </row>
@@ -6334,7 +6334,7 @@
       </c>
       <c r="K123" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:47Z</t>
+          <t>2026-10-13T02:10:27Z</t>
         </is>
       </c>
     </row>
@@ -6383,7 +6383,7 @@
       </c>
       <c r="K124" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:47Z</t>
+          <t>2026-10-13T02:10:27Z</t>
         </is>
       </c>
     </row>
@@ -6432,7 +6432,7 @@
       </c>
       <c r="K125" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:47Z</t>
+          <t>2026-10-13T02:10:27Z</t>
         </is>
       </c>
     </row>
@@ -6481,7 +6481,7 @@
       </c>
       <c r="K126" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:47Z</t>
+          <t>2026-10-13T02:10:27Z</t>
         </is>
       </c>
     </row>
@@ -6530,7 +6530,7 @@
       </c>
       <c r="K127" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:47Z</t>
+          <t>2026-10-13T02:10:27Z</t>
         </is>
       </c>
     </row>
@@ -6579,7 +6579,7 @@
       </c>
       <c r="K128" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:47Z</t>
+          <t>2026-10-13T02:10:27Z</t>
         </is>
       </c>
     </row>
@@ -6628,7 +6628,7 @@
       </c>
       <c r="K129" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:47Z</t>
+          <t>2026-10-13T02:10:27Z</t>
         </is>
       </c>
     </row>
@@ -6677,7 +6677,7 @@
       </c>
       <c r="K130" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:47Z</t>
+          <t>2026-10-13T02:10:27Z</t>
         </is>
       </c>
     </row>
@@ -6726,7 +6726,7 @@
       </c>
       <c r="K131" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:47Z</t>
+          <t>2026-10-13T02:10:27Z</t>
         </is>
       </c>
     </row>
@@ -6775,7 +6775,7 @@
       </c>
       <c r="K132" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:47Z</t>
+          <t>2026-10-13T02:10:27Z</t>
         </is>
       </c>
     </row>
@@ -6824,7 +6824,7 @@
       </c>
       <c r="K133" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:47Z</t>
+          <t>2026-10-13T02:10:27Z</t>
         </is>
       </c>
     </row>
@@ -6873,7 +6873,7 @@
       </c>
       <c r="K134" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:47Z</t>
+          <t>2026-10-13T02:10:27Z</t>
         </is>
       </c>
     </row>
@@ -6922,7 +6922,7 @@
       </c>
       <c r="K135" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:47Z</t>
+          <t>2026-10-13T02:10:27Z</t>
         </is>
       </c>
     </row>
@@ -6971,7 +6971,7 @@
       </c>
       <c r="K136" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:47Z</t>
+          <t>2026-10-13T02:10:27Z</t>
         </is>
       </c>
     </row>
@@ -7020,7 +7020,7 @@
       </c>
       <c r="K137" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:47Z</t>
+          <t>2026-10-13T02:10:27Z</t>
         </is>
       </c>
     </row>
@@ -7069,7 +7069,7 @@
       </c>
       <c r="K138" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:47Z</t>
+          <t>2026-10-13T02:10:27Z</t>
         </is>
       </c>
     </row>
@@ -7118,7 +7118,7 @@
       </c>
       <c r="K139" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:47Z</t>
+          <t>2026-10-13T02:10:27Z</t>
         </is>
       </c>
     </row>
@@ -7167,7 +7167,7 @@
       </c>
       <c r="K140" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:47Z</t>
+          <t>2026-10-13T02:10:27Z</t>
         </is>
       </c>
     </row>
@@ -7216,7 +7216,7 @@
       </c>
       <c r="K141" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:47Z</t>
+          <t>2026-10-13T02:10:27Z</t>
         </is>
       </c>
     </row>
@@ -7265,7 +7265,7 @@
       </c>
       <c r="K142" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:47Z</t>
+          <t>2026-10-13T02:10:27Z</t>
         </is>
       </c>
     </row>
@@ -7314,7 +7314,7 @@
       </c>
       <c r="K143" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:47Z</t>
+          <t>2026-10-13T02:10:27Z</t>
         </is>
       </c>
     </row>
@@ -7363,7 +7363,7 @@
       </c>
       <c r="K144" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:47Z</t>
+          <t>2026-10-13T02:10:27Z</t>
         </is>
       </c>
     </row>
@@ -7412,7 +7412,7 @@
       </c>
       <c r="K145" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:47Z</t>
+          <t>2026-10-13T02:10:27Z</t>
         </is>
       </c>
     </row>
@@ -7461,7 +7461,7 @@
       </c>
       <c r="K146" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:47Z</t>
+          <t>2026-10-13T02:10:27Z</t>
         </is>
       </c>
     </row>
@@ -7510,7 +7510,7 @@
       </c>
       <c r="K147" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:47Z</t>
+          <t>2026-10-13T02:10:27Z</t>
         </is>
       </c>
     </row>
@@ -7559,7 +7559,7 @@
       </c>
       <c r="K148" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:47Z</t>
+          <t>2026-10-13T02:10:27Z</t>
         </is>
       </c>
     </row>
@@ -7608,7 +7608,7 @@
       </c>
       <c r="K149" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:47Z</t>
+          <t>2026-10-13T02:10:27Z</t>
         </is>
       </c>
     </row>
@@ -7657,7 +7657,7 @@
       </c>
       <c r="K150" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:47Z</t>
+          <t>2026-10-13T02:10:27Z</t>
         </is>
       </c>
     </row>
@@ -7706,7 +7706,7 @@
       </c>
       <c r="K151" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:47Z</t>
+          <t>2026-10-13T02:10:27Z</t>
         </is>
       </c>
     </row>
@@ -7755,7 +7755,7 @@
       </c>
       <c r="K152" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:47Z</t>
+          <t>2026-10-13T02:10:27Z</t>
         </is>
       </c>
     </row>
@@ -7804,7 +7804,7 @@
       </c>
       <c r="K153" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:47Z</t>
+          <t>2026-10-13T02:10:27Z</t>
         </is>
       </c>
     </row>
@@ -7853,7 +7853,7 @@
       </c>
       <c r="K154" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:47Z</t>
+          <t>2026-10-13T02:10:27Z</t>
         </is>
       </c>
     </row>
@@ -7902,7 +7902,7 @@
       </c>
       <c r="K155" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:47Z</t>
+          <t>2026-10-13T02:10:27Z</t>
         </is>
       </c>
     </row>
@@ -7951,7 +7951,7 @@
       </c>
       <c r="K156" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:47Z</t>
+          <t>2026-10-13T02:10:27Z</t>
         </is>
       </c>
     </row>
@@ -8000,7 +8000,7 @@
       </c>
       <c r="K157" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:47Z</t>
+          <t>2026-10-13T02:10:27Z</t>
         </is>
       </c>
     </row>
@@ -8049,7 +8049,7 @@
       </c>
       <c r="K158" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:47Z</t>
+          <t>2026-10-13T02:10:27Z</t>
         </is>
       </c>
     </row>
@@ -8098,7 +8098,7 @@
       </c>
       <c r="K159" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:47Z</t>
+          <t>2026-10-13T02:10:27Z</t>
         </is>
       </c>
     </row>
@@ -8147,7 +8147,7 @@
       </c>
       <c r="K160" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:47Z</t>
+          <t>2026-10-13T02:10:27Z</t>
         </is>
       </c>
     </row>
@@ -8196,7 +8196,7 @@
       </c>
       <c r="K161" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:47Z</t>
+          <t>2026-10-13T02:10:27Z</t>
         </is>
       </c>
     </row>
@@ -8245,7 +8245,7 @@
       </c>
       <c r="K162" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:47Z</t>
+          <t>2026-10-13T02:10:27Z</t>
         </is>
       </c>
     </row>
@@ -8294,7 +8294,7 @@
       </c>
       <c r="K163" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:47Z</t>
+          <t>2026-10-13T02:10:27Z</t>
         </is>
       </c>
     </row>
@@ -8343,7 +8343,7 @@
       </c>
       <c r="K164" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:47Z</t>
+          <t>2026-10-13T02:10:27Z</t>
         </is>
       </c>
     </row>
@@ -8392,7 +8392,7 @@
       </c>
       <c r="K165" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:47Z</t>
+          <t>2026-10-13T02:10:27Z</t>
         </is>
       </c>
     </row>
@@ -8441,7 +8441,7 @@
       </c>
       <c r="K166" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:47Z</t>
+          <t>2026-10-13T02:10:27Z</t>
         </is>
       </c>
     </row>
@@ -8490,7 +8490,7 @@
       </c>
       <c r="K167" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:47Z</t>
+          <t>2026-10-13T02:10:27Z</t>
         </is>
       </c>
     </row>
@@ -8539,7 +8539,7 @@
       </c>
       <c r="K168" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:47Z</t>
+          <t>2026-10-13T02:10:27Z</t>
         </is>
       </c>
     </row>
@@ -8588,7 +8588,7 @@
       </c>
       <c r="K169" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:47Z</t>
+          <t>2026-10-13T02:10:27Z</t>
         </is>
       </c>
     </row>
@@ -8637,7 +8637,7 @@
       </c>
       <c r="K170" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:47Z</t>
+          <t>2026-10-13T02:10:27Z</t>
         </is>
       </c>
     </row>
@@ -8686,7 +8686,7 @@
       </c>
       <c r="K171" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:47Z</t>
+          <t>2026-10-13T02:10:27Z</t>
         </is>
       </c>
     </row>
@@ -8735,7 +8735,7 @@
       </c>
       <c r="K172" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:47Z</t>
+          <t>2026-10-13T02:10:27Z</t>
         </is>
       </c>
     </row>
@@ -8784,7 +8784,7 @@
       </c>
       <c r="K173" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:47Z</t>
+          <t>2026-10-13T02:10:27Z</t>
         </is>
       </c>
     </row>
@@ -8833,7 +8833,7 @@
       </c>
       <c r="K174" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:47Z</t>
+          <t>2026-10-13T02:10:27Z</t>
         </is>
       </c>
     </row>
@@ -8882,7 +8882,7 @@
       </c>
       <c r="K175" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:47Z</t>
+          <t>2026-10-13T02:10:27Z</t>
         </is>
       </c>
     </row>
@@ -8931,7 +8931,7 @@
       </c>
       <c r="K176" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:47Z</t>
+          <t>2026-10-13T02:10:27Z</t>
         </is>
       </c>
     </row>
@@ -8980,7 +8980,7 @@
       </c>
       <c r="K177" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:47Z</t>
+          <t>2026-10-13T02:10:27Z</t>
         </is>
       </c>
     </row>
@@ -9029,7 +9029,7 @@
       </c>
       <c r="K178" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:47Z</t>
+          <t>2026-10-13T02:10:27Z</t>
         </is>
       </c>
     </row>
@@ -9078,7 +9078,7 @@
       </c>
       <c r="K179" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:47Z</t>
+          <t>2026-10-13T02:10:27Z</t>
         </is>
       </c>
     </row>
@@ -9127,7 +9127,7 @@
       </c>
       <c r="K180" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:47Z</t>
+          <t>2026-10-13T02:10:27Z</t>
         </is>
       </c>
     </row>
@@ -9176,7 +9176,7 @@
       </c>
       <c r="K181" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:47Z</t>
+          <t>2026-10-13T02:10:27Z</t>
         </is>
       </c>
     </row>
@@ -9225,7 +9225,7 @@
       </c>
       <c r="K182" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:47Z</t>
+          <t>2026-10-13T02:10:27Z</t>
         </is>
       </c>
     </row>
@@ -9274,7 +9274,7 @@
       </c>
       <c r="K183" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:47Z</t>
+          <t>2026-10-13T02:10:27Z</t>
         </is>
       </c>
     </row>
@@ -9323,7 +9323,7 @@
       </c>
       <c r="K184" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:47Z</t>
+          <t>2026-10-13T02:10:27Z</t>
         </is>
       </c>
     </row>
@@ -9372,7 +9372,7 @@
       </c>
       <c r="K185" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:47Z</t>
+          <t>2026-10-13T02:10:27Z</t>
         </is>
       </c>
     </row>
@@ -9421,7 +9421,7 @@
       </c>
       <c r="K186" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:47Z</t>
+          <t>2026-10-13T02:10:27Z</t>
         </is>
       </c>
     </row>
@@ -9470,7 +9470,7 @@
       </c>
       <c r="K187" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:47Z</t>
+          <t>2026-10-13T02:10:27Z</t>
         </is>
       </c>
     </row>
@@ -9519,7 +9519,7 @@
       </c>
       <c r="K188" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:47Z</t>
+          <t>2026-10-13T02:10:27Z</t>
         </is>
       </c>
     </row>
@@ -9568,7 +9568,7 @@
       </c>
       <c r="K189" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:47Z</t>
+          <t>2026-10-13T02:10:27Z</t>
         </is>
       </c>
     </row>
@@ -9617,7 +9617,7 @@
       </c>
       <c r="K190" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:47Z</t>
+          <t>2026-10-13T02:10:27Z</t>
         </is>
       </c>
     </row>
@@ -9666,7 +9666,7 @@
       </c>
       <c r="K191" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:47Z</t>
+          <t>2026-10-13T02:10:27Z</t>
         </is>
       </c>
     </row>
@@ -9715,7 +9715,7 @@
       </c>
       <c r="K192" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:47Z</t>
+          <t>2026-10-13T02:10:27Z</t>
         </is>
       </c>
     </row>
@@ -9764,7 +9764,7 @@
       </c>
       <c r="K193" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:47Z</t>
+          <t>2026-10-13T02:10:27Z</t>
         </is>
       </c>
     </row>
@@ -9813,7 +9813,7 @@
       </c>
       <c r="K194" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:47Z</t>
+          <t>2026-10-13T02:10:27Z</t>
         </is>
       </c>
     </row>
@@ -9862,7 +9862,7 @@
       </c>
       <c r="K195" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:47Z</t>
+          <t>2026-10-13T02:10:27Z</t>
         </is>
       </c>
     </row>
@@ -9911,7 +9911,7 @@
       </c>
       <c r="K196" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:47Z</t>
+          <t>2026-10-13T02:10:27Z</t>
         </is>
       </c>
     </row>
@@ -9960,7 +9960,7 @@
       </c>
       <c r="K197" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:47Z</t>
+          <t>2026-10-13T02:10:27Z</t>
         </is>
       </c>
     </row>
@@ -10009,7 +10009,7 @@
       </c>
       <c r="K198" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:47Z</t>
+          <t>2026-10-13T02:10:27Z</t>
         </is>
       </c>
     </row>
@@ -10058,7 +10058,7 @@
       </c>
       <c r="K199" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:47Z</t>
+          <t>2026-10-13T02:10:27Z</t>
         </is>
       </c>
     </row>
@@ -10107,7 +10107,7 @@
       </c>
       <c r="K200" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:47Z</t>
+          <t>2026-10-13T02:10:27Z</t>
         </is>
       </c>
     </row>
@@ -10156,7 +10156,7 @@
       </c>
       <c r="K201" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:47Z</t>
+          <t>2026-10-13T02:10:27Z</t>
         </is>
       </c>
     </row>
@@ -10205,7 +10205,7 @@
       </c>
       <c r="K202" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:47Z</t>
+          <t>2026-10-13T02:10:27Z</t>
         </is>
       </c>
     </row>
@@ -10254,7 +10254,7 @@
       </c>
       <c r="K203" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:47Z</t>
+          <t>2026-10-13T02:10:27Z</t>
         </is>
       </c>
     </row>
@@ -10303,7 +10303,7 @@
       </c>
       <c r="K204" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:47Z</t>
+          <t>2026-10-13T02:10:27Z</t>
         </is>
       </c>
     </row>
@@ -10352,7 +10352,7 @@
       </c>
       <c r="K205" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:47Z</t>
+          <t>2026-10-13T02:10:27Z</t>
         </is>
       </c>
     </row>
@@ -10401,7 +10401,7 @@
       </c>
       <c r="K206" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:47Z</t>
+          <t>2026-10-13T02:10:27Z</t>
         </is>
       </c>
     </row>
@@ -10450,7 +10450,7 @@
       </c>
       <c r="K207" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:47Z</t>
+          <t>2026-10-13T02:10:27Z</t>
         </is>
       </c>
     </row>
@@ -10499,7 +10499,7 @@
       </c>
       <c r="K208" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:47Z</t>
+          <t>2026-10-13T02:10:27Z</t>
         </is>
       </c>
     </row>
@@ -10548,7 +10548,7 @@
       </c>
       <c r="K209" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:47Z</t>
+          <t>2026-10-13T02:10:27Z</t>
         </is>
       </c>
     </row>
@@ -10597,7 +10597,7 @@
       </c>
       <c r="K210" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:47Z</t>
+          <t>2026-10-13T02:10:27Z</t>
         </is>
       </c>
     </row>
@@ -10646,7 +10646,7 @@
       </c>
       <c r="K211" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:47Z</t>
+          <t>2026-10-13T02:10:27Z</t>
         </is>
       </c>
     </row>
@@ -10695,7 +10695,7 @@
       </c>
       <c r="K212" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:47Z</t>
+          <t>2026-10-13T02:10:27Z</t>
         </is>
       </c>
     </row>
@@ -10744,7 +10744,7 @@
       </c>
       <c r="K213" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:47Z</t>
+          <t>2026-10-13T02:10:27Z</t>
         </is>
       </c>
     </row>
@@ -10793,7 +10793,7 @@
       </c>
       <c r="K214" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:47Z</t>
+          <t>2026-10-13T02:10:27Z</t>
         </is>
       </c>
     </row>
@@ -10842,7 +10842,7 @@
       </c>
       <c r="K215" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:47Z</t>
+          <t>2026-10-13T02:10:27Z</t>
         </is>
       </c>
     </row>
@@ -10891,7 +10891,7 @@
       </c>
       <c r="K216" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:47Z</t>
+          <t>2026-10-13T02:10:27Z</t>
         </is>
       </c>
     </row>
@@ -10940,7 +10940,7 @@
       </c>
       <c r="K217" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:47Z</t>
+          <t>2026-10-13T02:10:27Z</t>
         </is>
       </c>
     </row>
@@ -10989,7 +10989,7 @@
       </c>
       <c r="K218" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:47Z</t>
+          <t>2026-10-13T02:10:27Z</t>
         </is>
       </c>
     </row>
@@ -11038,7 +11038,7 @@
       </c>
       <c r="K219" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:47Z</t>
+          <t>2026-10-13T02:10:27Z</t>
         </is>
       </c>
     </row>
@@ -11087,7 +11087,7 @@
       </c>
       <c r="K220" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:47Z</t>
+          <t>2026-10-13T02:10:27Z</t>
         </is>
       </c>
     </row>
@@ -11136,7 +11136,7 @@
       </c>
       <c r="K221" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:47Z</t>
+          <t>2026-10-13T02:10:27Z</t>
         </is>
       </c>
     </row>
@@ -11185,7 +11185,7 @@
       </c>
       <c r="K222" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:47Z</t>
+          <t>2026-10-13T02:10:27Z</t>
         </is>
       </c>
     </row>
@@ -11234,7 +11234,7 @@
       </c>
       <c r="K223" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:47Z</t>
+          <t>2026-10-13T02:10:27Z</t>
         </is>
       </c>
     </row>
@@ -11283,7 +11283,7 @@
       </c>
       <c r="K224" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:47Z</t>
+          <t>2026-10-13T02:10:27Z</t>
         </is>
       </c>
     </row>
@@ -11332,7 +11332,7 @@
       </c>
       <c r="K225" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:47Z</t>
+          <t>2026-10-13T02:10:27Z</t>
         </is>
       </c>
     </row>
@@ -11381,7 +11381,7 @@
       </c>
       <c r="K226" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:47Z</t>
+          <t>2026-10-13T02:10:27Z</t>
         </is>
       </c>
     </row>
@@ -11430,7 +11430,7 @@
       </c>
       <c r="K227" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:47Z</t>
+          <t>2026-10-13T02:10:27Z</t>
         </is>
       </c>
     </row>
@@ -11479,7 +11479,7 @@
       </c>
       <c r="K228" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:47Z</t>
+          <t>2026-10-13T02:10:27Z</t>
         </is>
       </c>
     </row>
@@ -11528,7 +11528,7 @@
       </c>
       <c r="K229" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:47Z</t>
+          <t>2026-10-13T02:10:27Z</t>
         </is>
       </c>
     </row>
@@ -11577,7 +11577,7 @@
       </c>
       <c r="K230" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:47Z</t>
+          <t>2026-10-13T02:10:27Z</t>
         </is>
       </c>
     </row>
@@ -11626,7 +11626,7 @@
       </c>
       <c r="K231" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:47Z</t>
+          <t>2026-10-13T02:10:27Z</t>
         </is>
       </c>
     </row>
@@ -11758,7 +11758,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:47Z</t>
+          <t>2026-10-13T02:10:27Z</t>
         </is>
       </c>
     </row>
@@ -11804,7 +11804,7 @@
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>{"date": "2026-08-01", "year": 2026, "month": 8, "month_name": "Agosto", "index_value": 637409769724325.1, "monthly_variation_pct": 8.9, "unit": "Índice base diciembre 2007=100 y variación mensual %", "frequency": "monthly", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/precios_consumidor/4_5_7_2.xls", "fetched_at": "2026-10-12T21:43:47Z"}</t>
+          <t>{"date": "2026-08-01", "year": 2026, "month": 8, "month_name": "Agosto", "index_value": 637409769724325.1, "monthly_variation_pct": 8.9, "unit": "Índice base diciembre 2007=100 y variación mensual %", "frequency": "monthly", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/precios_consumidor/4_5_7_2.xls", "fetched_at": "2026-10-13T02:10:27Z"}</t>
         </is>
       </c>
     </row>

--- a/assets/data/bcv/excel/ove_bcv_inpc_nacional_mensual.xlsx
+++ b/assets/data/bcv/excel/ove_bcv_inpc_nacional_mensual.xlsx
@@ -650,7 +650,7 @@
       </c>
       <c r="K7" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:27Z</t>
+          <t>2026-10-13T23:48:06Z</t>
         </is>
       </c>
     </row>
@@ -699,7 +699,7 @@
       </c>
       <c r="K8" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:27Z</t>
+          <t>2026-10-13T23:48:06Z</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="K9" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:27Z</t>
+          <t>2026-10-13T23:48:06Z</t>
         </is>
       </c>
     </row>
@@ -797,7 +797,7 @@
       </c>
       <c r="K10" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:27Z</t>
+          <t>2026-10-13T23:48:06Z</t>
         </is>
       </c>
     </row>
@@ -846,7 +846,7 @@
       </c>
       <c r="K11" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:27Z</t>
+          <t>2026-10-13T23:48:06Z</t>
         </is>
       </c>
     </row>
@@ -895,7 +895,7 @@
       </c>
       <c r="K12" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:27Z</t>
+          <t>2026-10-13T23:48:06Z</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="K13" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:27Z</t>
+          <t>2026-10-13T23:48:06Z</t>
         </is>
       </c>
     </row>
@@ -993,7 +993,7 @@
       </c>
       <c r="K14" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:27Z</t>
+          <t>2026-10-13T23:48:06Z</t>
         </is>
       </c>
     </row>
@@ -1042,7 +1042,7 @@
       </c>
       <c r="K15" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:27Z</t>
+          <t>2026-10-13T23:48:06Z</t>
         </is>
       </c>
     </row>
@@ -1091,7 +1091,7 @@
       </c>
       <c r="K16" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:27Z</t>
+          <t>2026-10-13T23:48:06Z</t>
         </is>
       </c>
     </row>
@@ -1140,7 +1140,7 @@
       </c>
       <c r="K17" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:27Z</t>
+          <t>2026-10-13T23:48:06Z</t>
         </is>
       </c>
     </row>
@@ -1189,7 +1189,7 @@
       </c>
       <c r="K18" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:27Z</t>
+          <t>2026-10-13T23:48:06Z</t>
         </is>
       </c>
     </row>
@@ -1238,7 +1238,7 @@
       </c>
       <c r="K19" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:27Z</t>
+          <t>2026-10-13T23:48:06Z</t>
         </is>
       </c>
     </row>
@@ -1287,7 +1287,7 @@
       </c>
       <c r="K20" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:27Z</t>
+          <t>2026-10-13T23:48:06Z</t>
         </is>
       </c>
     </row>
@@ -1336,7 +1336,7 @@
       </c>
       <c r="K21" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:27Z</t>
+          <t>2026-10-13T23:48:06Z</t>
         </is>
       </c>
     </row>
@@ -1385,7 +1385,7 @@
       </c>
       <c r="K22" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:27Z</t>
+          <t>2026-10-13T23:48:06Z</t>
         </is>
       </c>
     </row>
@@ -1434,7 +1434,7 @@
       </c>
       <c r="K23" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:27Z</t>
+          <t>2026-10-13T23:48:06Z</t>
         </is>
       </c>
     </row>
@@ -1483,7 +1483,7 @@
       </c>
       <c r="K24" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:27Z</t>
+          <t>2026-10-13T23:48:06Z</t>
         </is>
       </c>
     </row>
@@ -1532,7 +1532,7 @@
       </c>
       <c r="K25" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:27Z</t>
+          <t>2026-10-13T23:48:06Z</t>
         </is>
       </c>
     </row>
@@ -1581,7 +1581,7 @@
       </c>
       <c r="K26" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:27Z</t>
+          <t>2026-10-13T23:48:06Z</t>
         </is>
       </c>
     </row>
@@ -1630,7 +1630,7 @@
       </c>
       <c r="K27" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:27Z</t>
+          <t>2026-10-13T23:48:06Z</t>
         </is>
       </c>
     </row>
@@ -1679,7 +1679,7 @@
       </c>
       <c r="K28" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:27Z</t>
+          <t>2026-10-13T23:48:06Z</t>
         </is>
       </c>
     </row>
@@ -1728,7 +1728,7 @@
       </c>
       <c r="K29" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:27Z</t>
+          <t>2026-10-13T23:48:06Z</t>
         </is>
       </c>
     </row>
@@ -1777,7 +1777,7 @@
       </c>
       <c r="K30" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:27Z</t>
+          <t>2026-10-13T23:48:06Z</t>
         </is>
       </c>
     </row>
@@ -1826,7 +1826,7 @@
       </c>
       <c r="K31" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:27Z</t>
+          <t>2026-10-13T23:48:06Z</t>
         </is>
       </c>
     </row>
@@ -1875,7 +1875,7 @@
       </c>
       <c r="K32" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:27Z</t>
+          <t>2026-10-13T23:48:06Z</t>
         </is>
       </c>
     </row>
@@ -1924,7 +1924,7 @@
       </c>
       <c r="K33" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:27Z</t>
+          <t>2026-10-13T23:48:06Z</t>
         </is>
       </c>
     </row>
@@ -1973,7 +1973,7 @@
       </c>
       <c r="K34" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:27Z</t>
+          <t>2026-10-13T23:48:06Z</t>
         </is>
       </c>
     </row>
@@ -2022,7 +2022,7 @@
       </c>
       <c r="K35" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:27Z</t>
+          <t>2026-10-13T23:48:06Z</t>
         </is>
       </c>
     </row>
@@ -2071,7 +2071,7 @@
       </c>
       <c r="K36" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:27Z</t>
+          <t>2026-10-13T23:48:06Z</t>
         </is>
       </c>
     </row>
@@ -2120,7 +2120,7 @@
       </c>
       <c r="K37" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:27Z</t>
+          <t>2026-10-13T23:48:06Z</t>
         </is>
       </c>
     </row>
@@ -2169,7 +2169,7 @@
       </c>
       <c r="K38" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:27Z</t>
+          <t>2026-10-13T23:48:06Z</t>
         </is>
       </c>
     </row>
@@ -2218,7 +2218,7 @@
       </c>
       <c r="K39" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:27Z</t>
+          <t>2026-10-13T23:48:06Z</t>
         </is>
       </c>
     </row>
@@ -2267,7 +2267,7 @@
       </c>
       <c r="K40" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:27Z</t>
+          <t>2026-10-13T23:48:06Z</t>
         </is>
       </c>
     </row>
@@ -2316,7 +2316,7 @@
       </c>
       <c r="K41" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:27Z</t>
+          <t>2026-10-13T23:48:06Z</t>
         </is>
       </c>
     </row>
@@ -2365,7 +2365,7 @@
       </c>
       <c r="K42" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:27Z</t>
+          <t>2026-10-13T23:48:06Z</t>
         </is>
       </c>
     </row>
@@ -2414,7 +2414,7 @@
       </c>
       <c r="K43" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:27Z</t>
+          <t>2026-10-13T23:48:06Z</t>
         </is>
       </c>
     </row>
@@ -2463,7 +2463,7 @@
       </c>
       <c r="K44" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:27Z</t>
+          <t>2026-10-13T23:48:06Z</t>
         </is>
       </c>
     </row>
@@ -2512,7 +2512,7 @@
       </c>
       <c r="K45" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:27Z</t>
+          <t>2026-10-13T23:48:06Z</t>
         </is>
       </c>
     </row>
@@ -2561,7 +2561,7 @@
       </c>
       <c r="K46" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:27Z</t>
+          <t>2026-10-13T23:48:06Z</t>
         </is>
       </c>
     </row>
@@ -2610,7 +2610,7 @@
       </c>
       <c r="K47" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:27Z</t>
+          <t>2026-10-13T23:48:06Z</t>
         </is>
       </c>
     </row>
@@ -2659,7 +2659,7 @@
       </c>
       <c r="K48" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:27Z</t>
+          <t>2026-10-13T23:48:06Z</t>
         </is>
       </c>
     </row>
@@ -2708,7 +2708,7 @@
       </c>
       <c r="K49" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:27Z</t>
+          <t>2026-10-13T23:48:06Z</t>
         </is>
       </c>
     </row>
@@ -2757,7 +2757,7 @@
       </c>
       <c r="K50" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:27Z</t>
+          <t>2026-10-13T23:48:06Z</t>
         </is>
       </c>
     </row>
@@ -2806,7 +2806,7 @@
       </c>
       <c r="K51" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:27Z</t>
+          <t>2026-10-13T23:48:06Z</t>
         </is>
       </c>
     </row>
@@ -2855,7 +2855,7 @@
       </c>
       <c r="K52" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:27Z</t>
+          <t>2026-10-13T23:48:06Z</t>
         </is>
       </c>
     </row>
@@ -2904,7 +2904,7 @@
       </c>
       <c r="K53" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:27Z</t>
+          <t>2026-10-13T23:48:06Z</t>
         </is>
       </c>
     </row>
@@ -2953,7 +2953,7 @@
       </c>
       <c r="K54" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:27Z</t>
+          <t>2026-10-13T23:48:06Z</t>
         </is>
       </c>
     </row>
@@ -3002,7 +3002,7 @@
       </c>
       <c r="K55" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:27Z</t>
+          <t>2026-10-13T23:48:06Z</t>
         </is>
       </c>
     </row>
@@ -3051,7 +3051,7 @@
       </c>
       <c r="K56" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:27Z</t>
+          <t>2026-10-13T23:48:06Z</t>
         </is>
       </c>
     </row>
@@ -3100,7 +3100,7 @@
       </c>
       <c r="K57" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:27Z</t>
+          <t>2026-10-13T23:48:06Z</t>
         </is>
       </c>
     </row>
@@ -3149,7 +3149,7 @@
       </c>
       <c r="K58" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:27Z</t>
+          <t>2026-10-13T23:48:06Z</t>
         </is>
       </c>
     </row>
@@ -3198,7 +3198,7 @@
       </c>
       <c r="K59" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:27Z</t>
+          <t>2026-10-13T23:48:06Z</t>
         </is>
       </c>
     </row>
@@ -3247,7 +3247,7 @@
       </c>
       <c r="K60" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:27Z</t>
+          <t>2026-10-13T23:48:06Z</t>
         </is>
       </c>
     </row>
@@ -3296,7 +3296,7 @@
       </c>
       <c r="K61" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:27Z</t>
+          <t>2026-10-13T23:48:06Z</t>
         </is>
       </c>
     </row>
@@ -3345,7 +3345,7 @@
       </c>
       <c r="K62" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:27Z</t>
+          <t>2026-10-13T23:48:06Z</t>
         </is>
       </c>
     </row>
@@ -3394,7 +3394,7 @@
       </c>
       <c r="K63" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:27Z</t>
+          <t>2026-10-13T23:48:06Z</t>
         </is>
       </c>
     </row>
@@ -3443,7 +3443,7 @@
       </c>
       <c r="K64" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:27Z</t>
+          <t>2026-10-13T23:48:06Z</t>
         </is>
       </c>
     </row>
@@ -3492,7 +3492,7 @@
       </c>
       <c r="K65" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:27Z</t>
+          <t>2026-10-13T23:48:06Z</t>
         </is>
       </c>
     </row>
@@ -3541,7 +3541,7 @@
       </c>
       <c r="K66" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:27Z</t>
+          <t>2026-10-13T23:48:06Z</t>
         </is>
       </c>
     </row>
@@ -3590,7 +3590,7 @@
       </c>
       <c r="K67" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:27Z</t>
+          <t>2026-10-13T23:48:06Z</t>
         </is>
       </c>
     </row>
@@ -3639,7 +3639,7 @@
       </c>
       <c r="K68" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:27Z</t>
+          <t>2026-10-13T23:48:06Z</t>
         </is>
       </c>
     </row>
@@ -3688,7 +3688,7 @@
       </c>
       <c r="K69" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:27Z</t>
+          <t>2026-10-13T23:48:06Z</t>
         </is>
       </c>
     </row>
@@ -3737,7 +3737,7 @@
       </c>
       <c r="K70" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:27Z</t>
+          <t>2026-10-13T23:48:06Z</t>
         </is>
       </c>
     </row>
@@ -3786,7 +3786,7 @@
       </c>
       <c r="K71" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:27Z</t>
+          <t>2026-10-13T23:48:06Z</t>
         </is>
       </c>
     </row>
@@ -3835,7 +3835,7 @@
       </c>
       <c r="K72" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:27Z</t>
+          <t>2026-10-13T23:48:06Z</t>
         </is>
       </c>
     </row>
@@ -3884,7 +3884,7 @@
       </c>
       <c r="K73" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:27Z</t>
+          <t>2026-10-13T23:48:06Z</t>
         </is>
       </c>
     </row>
@@ -3933,7 +3933,7 @@
       </c>
       <c r="K74" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:27Z</t>
+          <t>2026-10-13T23:48:06Z</t>
         </is>
       </c>
     </row>
@@ -3982,7 +3982,7 @@
       </c>
       <c r="K75" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:27Z</t>
+          <t>2026-10-13T23:48:06Z</t>
         </is>
       </c>
     </row>
@@ -4031,7 +4031,7 @@
       </c>
       <c r="K76" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:27Z</t>
+          <t>2026-10-13T23:48:06Z</t>
         </is>
       </c>
     </row>
@@ -4080,7 +4080,7 @@
       </c>
       <c r="K77" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:27Z</t>
+          <t>2026-10-13T23:48:06Z</t>
         </is>
       </c>
     </row>
@@ -4129,7 +4129,7 @@
       </c>
       <c r="K78" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:27Z</t>
+          <t>2026-10-13T23:48:06Z</t>
         </is>
       </c>
     </row>
@@ -4178,7 +4178,7 @@
       </c>
       <c r="K79" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:27Z</t>
+          <t>2026-10-13T23:48:06Z</t>
         </is>
       </c>
     </row>
@@ -4227,7 +4227,7 @@
       </c>
       <c r="K80" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:27Z</t>
+          <t>2026-10-13T23:48:06Z</t>
         </is>
       </c>
     </row>
@@ -4276,7 +4276,7 @@
       </c>
       <c r="K81" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:27Z</t>
+          <t>2026-10-13T23:48:06Z</t>
         </is>
       </c>
     </row>
@@ -4325,7 +4325,7 @@
       </c>
       <c r="K82" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:27Z</t>
+          <t>2026-10-13T23:48:06Z</t>
         </is>
       </c>
     </row>
@@ -4374,7 +4374,7 @@
       </c>
       <c r="K83" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:27Z</t>
+          <t>2026-10-13T23:48:06Z</t>
         </is>
       </c>
     </row>
@@ -4423,7 +4423,7 @@
       </c>
       <c r="K84" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:27Z</t>
+          <t>2026-10-13T23:48:06Z</t>
         </is>
       </c>
     </row>
@@ -4472,7 +4472,7 @@
       </c>
       <c r="K85" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:27Z</t>
+          <t>2026-10-13T23:48:06Z</t>
         </is>
       </c>
     </row>
@@ -4521,7 +4521,7 @@
       </c>
       <c r="K86" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:27Z</t>
+          <t>2026-10-13T23:48:06Z</t>
         </is>
       </c>
     </row>
@@ -4570,7 +4570,7 @@
       </c>
       <c r="K87" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:27Z</t>
+          <t>2026-10-13T23:48:06Z</t>
         </is>
       </c>
     </row>
@@ -4619,7 +4619,7 @@
       </c>
       <c r="K88" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:27Z</t>
+          <t>2026-10-13T23:48:06Z</t>
         </is>
       </c>
     </row>
@@ -4668,7 +4668,7 @@
       </c>
       <c r="K89" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:27Z</t>
+          <t>2026-10-13T23:48:06Z</t>
         </is>
       </c>
     </row>
@@ -4717,7 +4717,7 @@
       </c>
       <c r="K90" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:27Z</t>
+          <t>2026-10-13T23:48:06Z</t>
         </is>
       </c>
     </row>
@@ -4766,7 +4766,7 @@
       </c>
       <c r="K91" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:27Z</t>
+          <t>2026-10-13T23:48:06Z</t>
         </is>
       </c>
     </row>
@@ -4815,7 +4815,7 @@
       </c>
       <c r="K92" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:27Z</t>
+          <t>2026-10-13T23:48:06Z</t>
         </is>
       </c>
     </row>
@@ -4864,7 +4864,7 @@
       </c>
       <c r="K93" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:27Z</t>
+          <t>2026-10-13T23:48:06Z</t>
         </is>
       </c>
     </row>
@@ -4913,7 +4913,7 @@
       </c>
       <c r="K94" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:27Z</t>
+          <t>2026-10-13T23:48:06Z</t>
         </is>
       </c>
     </row>
@@ -4962,7 +4962,7 @@
       </c>
       <c r="K95" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:27Z</t>
+          <t>2026-10-13T23:48:06Z</t>
         </is>
       </c>
     </row>
@@ -5011,7 +5011,7 @@
       </c>
       <c r="K96" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:27Z</t>
+          <t>2026-10-13T23:48:06Z</t>
         </is>
       </c>
     </row>
@@ -5060,7 +5060,7 @@
       </c>
       <c r="K97" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:27Z</t>
+          <t>2026-10-13T23:48:06Z</t>
         </is>
       </c>
     </row>
@@ -5109,7 +5109,7 @@
       </c>
       <c r="K98" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:27Z</t>
+          <t>2026-10-13T23:48:06Z</t>
         </is>
       </c>
     </row>
@@ -5158,7 +5158,7 @@
       </c>
       <c r="K99" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:27Z</t>
+          <t>2026-10-13T23:48:06Z</t>
         </is>
       </c>
     </row>
@@ -5207,7 +5207,7 @@
       </c>
       <c r="K100" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:27Z</t>
+          <t>2026-10-13T23:48:06Z</t>
         </is>
       </c>
     </row>
@@ -5256,7 +5256,7 @@
       </c>
       <c r="K101" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:27Z</t>
+          <t>2026-10-13T23:48:06Z</t>
         </is>
       </c>
     </row>
@@ -5305,7 +5305,7 @@
       </c>
       <c r="K102" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:27Z</t>
+          <t>2026-10-13T23:48:06Z</t>
         </is>
       </c>
     </row>
@@ -5354,7 +5354,7 @@
       </c>
       <c r="K103" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:27Z</t>
+          <t>2026-10-13T23:48:06Z</t>
         </is>
       </c>
     </row>
@@ -5403,7 +5403,7 @@
       </c>
       <c r="K104" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:27Z</t>
+          <t>2026-10-13T23:48:06Z</t>
         </is>
       </c>
     </row>
@@ -5452,7 +5452,7 @@
       </c>
       <c r="K105" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:27Z</t>
+          <t>2026-10-13T23:48:06Z</t>
         </is>
       </c>
     </row>
@@ -5501,7 +5501,7 @@
       </c>
       <c r="K106" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:27Z</t>
+          <t>2026-10-13T23:48:06Z</t>
         </is>
       </c>
     </row>
@@ -5550,7 +5550,7 @@
       </c>
       <c r="K107" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:27Z</t>
+          <t>2026-10-13T23:48:06Z</t>
         </is>
       </c>
     </row>
@@ -5599,7 +5599,7 @@
       </c>
       <c r="K108" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:27Z</t>
+          <t>2026-10-13T23:48:06Z</t>
         </is>
       </c>
     </row>
@@ -5648,7 +5648,7 @@
       </c>
       <c r="K109" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:27Z</t>
+          <t>2026-10-13T23:48:06Z</t>
         </is>
       </c>
     </row>
@@ -5697,7 +5697,7 @@
       </c>
       <c r="K110" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:27Z</t>
+          <t>2026-10-13T23:48:06Z</t>
         </is>
       </c>
     </row>
@@ -5746,7 +5746,7 @@
       </c>
       <c r="K111" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:27Z</t>
+          <t>2026-10-13T23:48:06Z</t>
         </is>
       </c>
     </row>
@@ -5795,7 +5795,7 @@
       </c>
       <c r="K112" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:27Z</t>
+          <t>2026-10-13T23:48:06Z</t>
         </is>
       </c>
     </row>
@@ -5844,7 +5844,7 @@
       </c>
       <c r="K113" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:27Z</t>
+          <t>2026-10-13T23:48:06Z</t>
         </is>
       </c>
     </row>
@@ -5893,7 +5893,7 @@
       </c>
       <c r="K114" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:27Z</t>
+          <t>2026-10-13T23:48:06Z</t>
         </is>
       </c>
     </row>
@@ -5942,7 +5942,7 @@
       </c>
       <c r="K115" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:27Z</t>
+          <t>2026-10-13T23:48:06Z</t>
         </is>
       </c>
     </row>
@@ -5991,7 +5991,7 @@
       </c>
       <c r="K116" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:27Z</t>
+          <t>2026-10-13T23:48:06Z</t>
         </is>
       </c>
     </row>
@@ -6040,7 +6040,7 @@
       </c>
       <c r="K117" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:27Z</t>
+          <t>2026-10-13T23:48:06Z</t>
         </is>
       </c>
     </row>
@@ -6089,7 +6089,7 @@
       </c>
       <c r="K118" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:27Z</t>
+          <t>2026-10-13T23:48:06Z</t>
         </is>
       </c>
     </row>
@@ -6138,7 +6138,7 @@
       </c>
       <c r="K119" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:27Z</t>
+          <t>2026-10-13T23:48:06Z</t>
         </is>
       </c>
     </row>
@@ -6187,7 +6187,7 @@
       </c>
       <c r="K120" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:27Z</t>
+          <t>2026-10-13T23:48:06Z</t>
         </is>
       </c>
     </row>
@@ -6236,7 +6236,7 @@
       </c>
       <c r="K121" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:27Z</t>
+          <t>2026-10-13T23:48:06Z</t>
         </is>
       </c>
     </row>
@@ -6285,7 +6285,7 @@
       </c>
       <c r="K122" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:27Z</t>
+          <t>2026-10-13T23:48:06Z</t>
         </is>
       </c>
     </row>
@@ -6334,7 +6334,7 @@
       </c>
       <c r="K123" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:27Z</t>
+          <t>2026-10-13T23:48:06Z</t>
         </is>
       </c>
     </row>
@@ -6383,7 +6383,7 @@
       </c>
       <c r="K124" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:27Z</t>
+          <t>2026-10-13T23:48:06Z</t>
         </is>
       </c>
     </row>
@@ -6432,7 +6432,7 @@
       </c>
       <c r="K125" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:27Z</t>
+          <t>2026-10-13T23:48:06Z</t>
         </is>
       </c>
     </row>
@@ -6481,7 +6481,7 @@
       </c>
       <c r="K126" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:27Z</t>
+          <t>2026-10-13T23:48:06Z</t>
         </is>
       </c>
     </row>
@@ -6530,7 +6530,7 @@
       </c>
       <c r="K127" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:27Z</t>
+          <t>2026-10-13T23:48:06Z</t>
         </is>
       </c>
     </row>
@@ -6579,7 +6579,7 @@
       </c>
       <c r="K128" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:27Z</t>
+          <t>2026-10-13T23:48:06Z</t>
         </is>
       </c>
     </row>
@@ -6628,7 +6628,7 @@
       </c>
       <c r="K129" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:27Z</t>
+          <t>2026-10-13T23:48:06Z</t>
         </is>
       </c>
     </row>
@@ -6677,7 +6677,7 @@
       </c>
       <c r="K130" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:27Z</t>
+          <t>2026-10-13T23:48:06Z</t>
         </is>
       </c>
     </row>
@@ -6726,7 +6726,7 @@
       </c>
       <c r="K131" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:27Z</t>
+          <t>2026-10-13T23:48:06Z</t>
         </is>
       </c>
     </row>
@@ -6775,7 +6775,7 @@
       </c>
       <c r="K132" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:27Z</t>
+          <t>2026-10-13T23:48:06Z</t>
         </is>
       </c>
     </row>
@@ -6824,7 +6824,7 @@
       </c>
       <c r="K133" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:27Z</t>
+          <t>2026-10-13T23:48:06Z</t>
         </is>
       </c>
     </row>
@@ -6873,7 +6873,7 @@
       </c>
       <c r="K134" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:27Z</t>
+          <t>2026-10-13T23:48:06Z</t>
         </is>
       </c>
     </row>
@@ -6922,7 +6922,7 @@
       </c>
       <c r="K135" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:27Z</t>
+          <t>2026-10-13T23:48:06Z</t>
         </is>
       </c>
     </row>
@@ -6971,7 +6971,7 @@
       </c>
       <c r="K136" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:27Z</t>
+          <t>2026-10-13T23:48:06Z</t>
         </is>
       </c>
     </row>
@@ -7020,7 +7020,7 @@
       </c>
       <c r="K137" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:27Z</t>
+          <t>2026-10-13T23:48:06Z</t>
         </is>
       </c>
     </row>
@@ -7069,7 +7069,7 @@
       </c>
       <c r="K138" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:27Z</t>
+          <t>2026-10-13T23:48:06Z</t>
         </is>
       </c>
     </row>
@@ -7118,7 +7118,7 @@
       </c>
       <c r="K139" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:27Z</t>
+          <t>2026-10-13T23:48:06Z</t>
         </is>
       </c>
     </row>
@@ -7167,7 +7167,7 @@
       </c>
       <c r="K140" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:27Z</t>
+          <t>2026-10-13T23:48:06Z</t>
         </is>
       </c>
     </row>
@@ -7216,7 +7216,7 @@
       </c>
       <c r="K141" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:27Z</t>
+          <t>2026-10-13T23:48:06Z</t>
         </is>
       </c>
     </row>
@@ -7265,7 +7265,7 @@
       </c>
       <c r="K142" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:27Z</t>
+          <t>2026-10-13T23:48:06Z</t>
         </is>
       </c>
     </row>
@@ -7314,7 +7314,7 @@
       </c>
       <c r="K143" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:27Z</t>
+          <t>2026-10-13T23:48:06Z</t>
         </is>
       </c>
     </row>
@@ -7363,7 +7363,7 @@
       </c>
       <c r="K144" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:27Z</t>
+          <t>2026-10-13T23:48:06Z</t>
         </is>
       </c>
     </row>
@@ -7412,7 +7412,7 @@
       </c>
       <c r="K145" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:27Z</t>
+          <t>2026-10-13T23:48:06Z</t>
         </is>
       </c>
     </row>
@@ -7461,7 +7461,7 @@
       </c>
       <c r="K146" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:27Z</t>
+          <t>2026-10-13T23:48:06Z</t>
         </is>
       </c>
     </row>
@@ -7510,7 +7510,7 @@
       </c>
       <c r="K147" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:27Z</t>
+          <t>2026-10-13T23:48:06Z</t>
         </is>
       </c>
     </row>
@@ -7559,7 +7559,7 @@
       </c>
       <c r="K148" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:27Z</t>
+          <t>2026-10-13T23:48:06Z</t>
         </is>
       </c>
     </row>
@@ -7608,7 +7608,7 @@
       </c>
       <c r="K149" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:27Z</t>
+          <t>2026-10-13T23:48:06Z</t>
         </is>
       </c>
     </row>
@@ -7657,7 +7657,7 @@
       </c>
       <c r="K150" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:27Z</t>
+          <t>2026-10-13T23:48:06Z</t>
         </is>
       </c>
     </row>
@@ -7706,7 +7706,7 @@
       </c>
       <c r="K151" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:27Z</t>
+          <t>2026-10-13T23:48:06Z</t>
         </is>
       </c>
     </row>
@@ -7755,7 +7755,7 @@
       </c>
       <c r="K152" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:27Z</t>
+          <t>2026-10-13T23:48:06Z</t>
         </is>
       </c>
     </row>
@@ -7804,7 +7804,7 @@
       </c>
       <c r="K153" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:27Z</t>
+          <t>2026-10-13T23:48:06Z</t>
         </is>
       </c>
     </row>
@@ -7853,7 +7853,7 @@
       </c>
       <c r="K154" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:27Z</t>
+          <t>2026-10-13T23:48:06Z</t>
         </is>
       </c>
     </row>
@@ -7902,7 +7902,7 @@
       </c>
       <c r="K155" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:27Z</t>
+          <t>2026-10-13T23:48:06Z</t>
         </is>
       </c>
     </row>
@@ -7951,7 +7951,7 @@
       </c>
       <c r="K156" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:27Z</t>
+          <t>2026-10-13T23:48:06Z</t>
         </is>
       </c>
     </row>
@@ -8000,7 +8000,7 @@
       </c>
       <c r="K157" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:27Z</t>
+          <t>2026-10-13T23:48:06Z</t>
         </is>
       </c>
     </row>
@@ -8049,7 +8049,7 @@
       </c>
       <c r="K158" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:27Z</t>
+          <t>2026-10-13T23:48:06Z</t>
         </is>
       </c>
     </row>
@@ -8098,7 +8098,7 @@
       </c>
       <c r="K159" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:27Z</t>
+          <t>2026-10-13T23:48:06Z</t>
         </is>
       </c>
     </row>
@@ -8147,7 +8147,7 @@
       </c>
       <c r="K160" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:27Z</t>
+          <t>2026-10-13T23:48:06Z</t>
         </is>
       </c>
     </row>
@@ -8196,7 +8196,7 @@
       </c>
       <c r="K161" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:27Z</t>
+          <t>2026-10-13T23:48:06Z</t>
         </is>
       </c>
     </row>
@@ -8245,7 +8245,7 @@
       </c>
       <c r="K162" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:27Z</t>
+          <t>2026-10-13T23:48:06Z</t>
         </is>
       </c>
     </row>
@@ -8294,7 +8294,7 @@
       </c>
       <c r="K163" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:27Z</t>
+          <t>2026-10-13T23:48:06Z</t>
         </is>
       </c>
     </row>
@@ -8343,7 +8343,7 @@
       </c>
       <c r="K164" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:27Z</t>
+          <t>2026-10-13T23:48:06Z</t>
         </is>
       </c>
     </row>
@@ -8392,7 +8392,7 @@
       </c>
       <c r="K165" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:27Z</t>
+          <t>2026-10-13T23:48:06Z</t>
         </is>
       </c>
     </row>
@@ -8441,7 +8441,7 @@
       </c>
       <c r="K166" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:27Z</t>
+          <t>2026-10-13T23:48:06Z</t>
         </is>
       </c>
     </row>
@@ -8490,7 +8490,7 @@
       </c>
       <c r="K167" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:27Z</t>
+          <t>2026-10-13T23:48:06Z</t>
         </is>
       </c>
     </row>
@@ -8539,7 +8539,7 @@
       </c>
       <c r="K168" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:27Z</t>
+          <t>2026-10-13T23:48:06Z</t>
         </is>
       </c>
     </row>
@@ -8588,7 +8588,7 @@
       </c>
       <c r="K169" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:27Z</t>
+          <t>2026-10-13T23:48:06Z</t>
         </is>
       </c>
     </row>
@@ -8637,7 +8637,7 @@
       </c>
       <c r="K170" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:27Z</t>
+          <t>2026-10-13T23:48:06Z</t>
         </is>
       </c>
     </row>
@@ -8686,7 +8686,7 @@
       </c>
       <c r="K171" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:27Z</t>
+          <t>2026-10-13T23:48:06Z</t>
         </is>
       </c>
     </row>
@@ -8735,7 +8735,7 @@
       </c>
       <c r="K172" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:27Z</t>
+          <t>2026-10-13T23:48:06Z</t>
         </is>
       </c>
     </row>
@@ -8784,7 +8784,7 @@
       </c>
       <c r="K173" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:27Z</t>
+          <t>2026-10-13T23:48:06Z</t>
         </is>
       </c>
     </row>
@@ -8833,7 +8833,7 @@
       </c>
       <c r="K174" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:27Z</t>
+          <t>2026-10-13T23:48:06Z</t>
         </is>
       </c>
     </row>
@@ -8882,7 +8882,7 @@
       </c>
       <c r="K175" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:27Z</t>
+          <t>2026-10-13T23:48:06Z</t>
         </is>
       </c>
     </row>
@@ -8931,7 +8931,7 @@
       </c>
       <c r="K176" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:27Z</t>
+          <t>2026-10-13T23:48:06Z</t>
         </is>
       </c>
     </row>
@@ -8980,7 +8980,7 @@
       </c>
       <c r="K177" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:27Z</t>
+          <t>2026-10-13T23:48:06Z</t>
         </is>
       </c>
     </row>
@@ -9029,7 +9029,7 @@
       </c>
       <c r="K178" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:27Z</t>
+          <t>2026-10-13T23:48:06Z</t>
         </is>
       </c>
     </row>
@@ -9078,7 +9078,7 @@
       </c>
       <c r="K179" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:27Z</t>
+          <t>2026-10-13T23:48:06Z</t>
         </is>
       </c>
     </row>
@@ -9127,7 +9127,7 @@
       </c>
       <c r="K180" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:27Z</t>
+          <t>2026-10-13T23:48:06Z</t>
         </is>
       </c>
     </row>
@@ -9176,7 +9176,7 @@
       </c>
       <c r="K181" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:27Z</t>
+          <t>2026-10-13T23:48:06Z</t>
         </is>
       </c>
     </row>
@@ -9225,7 +9225,7 @@
       </c>
       <c r="K182" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:27Z</t>
+          <t>2026-10-13T23:48:06Z</t>
         </is>
       </c>
     </row>
@@ -9274,7 +9274,7 @@
       </c>
       <c r="K183" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:27Z</t>
+          <t>2026-10-13T23:48:06Z</t>
         </is>
       </c>
     </row>
@@ -9323,7 +9323,7 @@
       </c>
       <c r="K184" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:27Z</t>
+          <t>2026-10-13T23:48:06Z</t>
         </is>
       </c>
     </row>
@@ -9372,7 +9372,7 @@
       </c>
       <c r="K185" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:27Z</t>
+          <t>2026-10-13T23:48:06Z</t>
         </is>
       </c>
     </row>
@@ -9421,7 +9421,7 @@
       </c>
       <c r="K186" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:27Z</t>
+          <t>2026-10-13T23:48:06Z</t>
         </is>
       </c>
     </row>
@@ -9470,7 +9470,7 @@
       </c>
       <c r="K187" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:27Z</t>
+          <t>2026-10-13T23:48:06Z</t>
         </is>
       </c>
     </row>
@@ -9519,7 +9519,7 @@
       </c>
       <c r="K188" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:27Z</t>
+          <t>2026-10-13T23:48:06Z</t>
         </is>
       </c>
     </row>
@@ -9568,7 +9568,7 @@
       </c>
       <c r="K189" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:27Z</t>
+          <t>2026-10-13T23:48:06Z</t>
         </is>
       </c>
     </row>
@@ -9617,7 +9617,7 @@
       </c>
       <c r="K190" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:27Z</t>
+          <t>2026-10-13T23:48:06Z</t>
         </is>
       </c>
     </row>
@@ -9666,7 +9666,7 @@
       </c>
       <c r="K191" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:27Z</t>
+          <t>2026-10-13T23:48:06Z</t>
         </is>
       </c>
     </row>
@@ -9715,7 +9715,7 @@
       </c>
       <c r="K192" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:27Z</t>
+          <t>2026-10-13T23:48:06Z</t>
         </is>
       </c>
     </row>
@@ -9764,7 +9764,7 @@
       </c>
       <c r="K193" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:27Z</t>
+          <t>2026-10-13T23:48:06Z</t>
         </is>
       </c>
     </row>
@@ -9813,7 +9813,7 @@
       </c>
       <c r="K194" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:27Z</t>
+          <t>2026-10-13T23:48:06Z</t>
         </is>
       </c>
     </row>
@@ -9862,7 +9862,7 @@
       </c>
       <c r="K195" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:27Z</t>
+          <t>2026-10-13T23:48:06Z</t>
         </is>
       </c>
     </row>
@@ -9911,7 +9911,7 @@
       </c>
       <c r="K196" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:27Z</t>
+          <t>2026-10-13T23:48:06Z</t>
         </is>
       </c>
     </row>
@@ -9960,7 +9960,7 @@
       </c>
       <c r="K197" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:27Z</t>
+          <t>2026-10-13T23:48:06Z</t>
         </is>
       </c>
     </row>
@@ -10009,7 +10009,7 @@
       </c>
       <c r="K198" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:27Z</t>
+          <t>2026-10-13T23:48:06Z</t>
         </is>
       </c>
     </row>
@@ -10058,7 +10058,7 @@
       </c>
       <c r="K199" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:27Z</t>
+          <t>2026-10-13T23:48:06Z</t>
         </is>
       </c>
     </row>
@@ -10107,7 +10107,7 @@
       </c>
       <c r="K200" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:27Z</t>
+          <t>2026-10-13T23:48:06Z</t>
         </is>
       </c>
     </row>
@@ -10156,7 +10156,7 @@
       </c>
       <c r="K201" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:27Z</t>
+          <t>2026-10-13T23:48:06Z</t>
         </is>
       </c>
     </row>
@@ -10205,7 +10205,7 @@
       </c>
       <c r="K202" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:27Z</t>
+          <t>2026-10-13T23:48:06Z</t>
         </is>
       </c>
     </row>
@@ -10254,7 +10254,7 @@
       </c>
       <c r="K203" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:27Z</t>
+          <t>2026-10-13T23:48:06Z</t>
         </is>
       </c>
     </row>
@@ -10303,7 +10303,7 @@
       </c>
       <c r="K204" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:27Z</t>
+          <t>2026-10-13T23:48:06Z</t>
         </is>
       </c>
     </row>
@@ -10352,7 +10352,7 @@
       </c>
       <c r="K205" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:27Z</t>
+          <t>2026-10-13T23:48:06Z</t>
         </is>
       </c>
     </row>
@@ -10401,7 +10401,7 @@
       </c>
       <c r="K206" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:27Z</t>
+          <t>2026-10-13T23:48:06Z</t>
         </is>
       </c>
     </row>
@@ -10450,7 +10450,7 @@
       </c>
       <c r="K207" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:27Z</t>
+          <t>2026-10-13T23:48:06Z</t>
         </is>
       </c>
     </row>
@@ -10499,7 +10499,7 @@
       </c>
       <c r="K208" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:27Z</t>
+          <t>2026-10-13T23:48:06Z</t>
         </is>
       </c>
     </row>
@@ -10548,7 +10548,7 @@
       </c>
       <c r="K209" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:27Z</t>
+          <t>2026-10-13T23:48:06Z</t>
         </is>
       </c>
     </row>
@@ -10597,7 +10597,7 @@
       </c>
       <c r="K210" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:27Z</t>
+          <t>2026-10-13T23:48:06Z</t>
         </is>
       </c>
     </row>
@@ -10646,7 +10646,7 @@
       </c>
       <c r="K211" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:27Z</t>
+          <t>2026-10-13T23:48:06Z</t>
         </is>
       </c>
     </row>
@@ -10695,7 +10695,7 @@
       </c>
       <c r="K212" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:27Z</t>
+          <t>2026-10-13T23:48:06Z</t>
         </is>
       </c>
     </row>
@@ -10744,7 +10744,7 @@
       </c>
       <c r="K213" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:27Z</t>
+          <t>2026-10-13T23:48:06Z</t>
         </is>
       </c>
     </row>
@@ -10793,7 +10793,7 @@
       </c>
       <c r="K214" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:27Z</t>
+          <t>2026-10-13T23:48:06Z</t>
         </is>
       </c>
     </row>
@@ -10842,7 +10842,7 @@
       </c>
       <c r="K215" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:27Z</t>
+          <t>2026-10-13T23:48:06Z</t>
         </is>
       </c>
     </row>
@@ -10891,7 +10891,7 @@
       </c>
       <c r="K216" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:27Z</t>
+          <t>2026-10-13T23:48:06Z</t>
         </is>
       </c>
     </row>
@@ -10940,7 +10940,7 @@
       </c>
       <c r="K217" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:27Z</t>
+          <t>2026-10-13T23:48:06Z</t>
         </is>
       </c>
     </row>
@@ -10989,7 +10989,7 @@
       </c>
       <c r="K218" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:27Z</t>
+          <t>2026-10-13T23:48:06Z</t>
         </is>
       </c>
     </row>
@@ -11038,7 +11038,7 @@
       </c>
       <c r="K219" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:27Z</t>
+          <t>2026-10-13T23:48:06Z</t>
         </is>
       </c>
     </row>
@@ -11087,7 +11087,7 @@
       </c>
       <c r="K220" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:27Z</t>
+          <t>2026-10-13T23:48:06Z</t>
         </is>
       </c>
     </row>
@@ -11136,7 +11136,7 @@
       </c>
       <c r="K221" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:27Z</t>
+          <t>2026-10-13T23:48:06Z</t>
         </is>
       </c>
     </row>
@@ -11185,7 +11185,7 @@
       </c>
       <c r="K222" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:27Z</t>
+          <t>2026-10-13T23:48:06Z</t>
         </is>
       </c>
     </row>
@@ -11234,7 +11234,7 @@
       </c>
       <c r="K223" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:27Z</t>
+          <t>2026-10-13T23:48:06Z</t>
         </is>
       </c>
     </row>
@@ -11283,7 +11283,7 @@
       </c>
       <c r="K224" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:27Z</t>
+          <t>2026-10-13T23:48:06Z</t>
         </is>
       </c>
     </row>
@@ -11332,7 +11332,7 @@
       </c>
       <c r="K225" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:27Z</t>
+          <t>2026-10-13T23:48:06Z</t>
         </is>
       </c>
     </row>
@@ -11381,7 +11381,7 @@
       </c>
       <c r="K226" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:27Z</t>
+          <t>2026-10-13T23:48:06Z</t>
         </is>
       </c>
     </row>
@@ -11430,7 +11430,7 @@
       </c>
       <c r="K227" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:27Z</t>
+          <t>2026-10-13T23:48:06Z</t>
         </is>
       </c>
     </row>
@@ -11479,7 +11479,7 @@
       </c>
       <c r="K228" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:27Z</t>
+          <t>2026-10-13T23:48:06Z</t>
         </is>
       </c>
     </row>
@@ -11528,7 +11528,7 @@
       </c>
       <c r="K229" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:27Z</t>
+          <t>2026-10-13T23:48:06Z</t>
         </is>
       </c>
     </row>
@@ -11577,7 +11577,7 @@
       </c>
       <c r="K230" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:27Z</t>
+          <t>2026-10-13T23:48:06Z</t>
         </is>
       </c>
     </row>
@@ -11626,7 +11626,7 @@
       </c>
       <c r="K231" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:27Z</t>
+          <t>2026-10-13T23:48:06Z</t>
         </is>
       </c>
     </row>
@@ -11758,7 +11758,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:27Z</t>
+          <t>2026-10-13T23:48:06Z</t>
         </is>
       </c>
     </row>
@@ -11804,7 +11804,7 @@
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>{"date": "2026-08-01", "year": 2026, "month": 8, "month_name": "Agosto", "index_value": 637409769724325.1, "monthly_variation_pct": 8.9, "unit": "Índice base diciembre 2007=100 y variación mensual %", "frequency": "monthly", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/precios_consumidor/4_5_7_2.xls", "fetched_at": "2026-10-13T02:10:27Z"}</t>
+          <t>{"date": "2026-08-01", "year": 2026, "month": 8, "month_name": "Agosto", "index_value": 637409769724325.1, "monthly_variation_pct": 8.9, "unit": "Índice base diciembre 2007=100 y variación mensual %", "frequency": "monthly", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/precios_consumidor/4_5_7_2.xls", "fetched_at": "2026-10-13T23:48:06Z"}</t>
         </is>
       </c>
     </row>

--- a/assets/data/bcv/excel/ove_bcv_inpc_nacional_mensual.xlsx
+++ b/assets/data/bcv/excel/ove_bcv_inpc_nacional_mensual.xlsx
@@ -650,7 +650,7 @@
       </c>
       <c r="K7" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:06Z</t>
+          <t>2026-10-14T23:20:55Z</t>
         </is>
       </c>
     </row>
@@ -699,7 +699,7 @@
       </c>
       <c r="K8" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:06Z</t>
+          <t>2026-10-14T23:20:55Z</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="K9" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:06Z</t>
+          <t>2026-10-14T23:20:55Z</t>
         </is>
       </c>
     </row>
@@ -797,7 +797,7 @@
       </c>
       <c r="K10" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:06Z</t>
+          <t>2026-10-14T23:20:55Z</t>
         </is>
       </c>
     </row>
@@ -846,7 +846,7 @@
       </c>
       <c r="K11" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:06Z</t>
+          <t>2026-10-14T23:20:55Z</t>
         </is>
       </c>
     </row>
@@ -895,7 +895,7 @@
       </c>
       <c r="K12" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:06Z</t>
+          <t>2026-10-14T23:20:55Z</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="K13" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:06Z</t>
+          <t>2026-10-14T23:20:55Z</t>
         </is>
       </c>
     </row>
@@ -993,7 +993,7 @@
       </c>
       <c r="K14" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:06Z</t>
+          <t>2026-10-14T23:20:55Z</t>
         </is>
       </c>
     </row>
@@ -1042,7 +1042,7 @@
       </c>
       <c r="K15" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:06Z</t>
+          <t>2026-10-14T23:20:55Z</t>
         </is>
       </c>
     </row>
@@ -1091,7 +1091,7 @@
       </c>
       <c r="K16" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:06Z</t>
+          <t>2026-10-14T23:20:55Z</t>
         </is>
       </c>
     </row>
@@ -1140,7 +1140,7 @@
       </c>
       <c r="K17" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:06Z</t>
+          <t>2026-10-14T23:20:55Z</t>
         </is>
       </c>
     </row>
@@ -1189,7 +1189,7 @@
       </c>
       <c r="K18" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:06Z</t>
+          <t>2026-10-14T23:20:55Z</t>
         </is>
       </c>
     </row>
@@ -1238,7 +1238,7 @@
       </c>
       <c r="K19" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:06Z</t>
+          <t>2026-10-14T23:20:55Z</t>
         </is>
       </c>
     </row>
@@ -1287,7 +1287,7 @@
       </c>
       <c r="K20" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:06Z</t>
+          <t>2026-10-14T23:20:55Z</t>
         </is>
       </c>
     </row>
@@ -1336,7 +1336,7 @@
       </c>
       <c r="K21" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:06Z</t>
+          <t>2026-10-14T23:20:55Z</t>
         </is>
       </c>
     </row>
@@ -1385,7 +1385,7 @@
       </c>
       <c r="K22" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:06Z</t>
+          <t>2026-10-14T23:20:55Z</t>
         </is>
       </c>
     </row>
@@ -1434,7 +1434,7 @@
       </c>
       <c r="K23" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:06Z</t>
+          <t>2026-10-14T23:20:55Z</t>
         </is>
       </c>
     </row>
@@ -1483,7 +1483,7 @@
       </c>
       <c r="K24" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:06Z</t>
+          <t>2026-10-14T23:20:55Z</t>
         </is>
       </c>
     </row>
@@ -1532,7 +1532,7 @@
       </c>
       <c r="K25" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:06Z</t>
+          <t>2026-10-14T23:20:55Z</t>
         </is>
       </c>
     </row>
@@ -1581,7 +1581,7 @@
       </c>
       <c r="K26" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:06Z</t>
+          <t>2026-10-14T23:20:55Z</t>
         </is>
       </c>
     </row>
@@ -1630,7 +1630,7 @@
       </c>
       <c r="K27" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:06Z</t>
+          <t>2026-10-14T23:20:55Z</t>
         </is>
       </c>
     </row>
@@ -1679,7 +1679,7 @@
       </c>
       <c r="K28" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:06Z</t>
+          <t>2026-10-14T23:20:55Z</t>
         </is>
       </c>
     </row>
@@ -1728,7 +1728,7 @@
       </c>
       <c r="K29" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:06Z</t>
+          <t>2026-10-14T23:20:55Z</t>
         </is>
       </c>
     </row>
@@ -1777,7 +1777,7 @@
       </c>
       <c r="K30" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:06Z</t>
+          <t>2026-10-14T23:20:55Z</t>
         </is>
       </c>
     </row>
@@ -1826,7 +1826,7 @@
       </c>
       <c r="K31" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:06Z</t>
+          <t>2026-10-14T23:20:55Z</t>
         </is>
       </c>
     </row>
@@ -1875,7 +1875,7 @@
       </c>
       <c r="K32" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:06Z</t>
+          <t>2026-10-14T23:20:55Z</t>
         </is>
       </c>
     </row>
@@ -1924,7 +1924,7 @@
       </c>
       <c r="K33" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:06Z</t>
+          <t>2026-10-14T23:20:55Z</t>
         </is>
       </c>
     </row>
@@ -1973,7 +1973,7 @@
       </c>
       <c r="K34" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:06Z</t>
+          <t>2026-10-14T23:20:55Z</t>
         </is>
       </c>
     </row>
@@ -2022,7 +2022,7 @@
       </c>
       <c r="K35" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:06Z</t>
+          <t>2026-10-14T23:20:55Z</t>
         </is>
       </c>
     </row>
@@ -2071,7 +2071,7 @@
       </c>
       <c r="K36" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:06Z</t>
+          <t>2026-10-14T23:20:55Z</t>
         </is>
       </c>
     </row>
@@ -2120,7 +2120,7 @@
       </c>
       <c r="K37" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:06Z</t>
+          <t>2026-10-14T23:20:55Z</t>
         </is>
       </c>
     </row>
@@ -2169,7 +2169,7 @@
       </c>
       <c r="K38" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:06Z</t>
+          <t>2026-10-14T23:20:55Z</t>
         </is>
       </c>
     </row>
@@ -2218,7 +2218,7 @@
       </c>
       <c r="K39" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:06Z</t>
+          <t>2026-10-14T23:20:55Z</t>
         </is>
       </c>
     </row>
@@ -2267,7 +2267,7 @@
       </c>
       <c r="K40" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:06Z</t>
+          <t>2026-10-14T23:20:55Z</t>
         </is>
       </c>
     </row>
@@ -2316,7 +2316,7 @@
       </c>
       <c r="K41" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:06Z</t>
+          <t>2026-10-14T23:20:55Z</t>
         </is>
       </c>
     </row>
@@ -2365,7 +2365,7 @@
       </c>
       <c r="K42" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:06Z</t>
+          <t>2026-10-14T23:20:55Z</t>
         </is>
       </c>
     </row>
@@ -2414,7 +2414,7 @@
       </c>
       <c r="K43" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:06Z</t>
+          <t>2026-10-14T23:20:55Z</t>
         </is>
       </c>
     </row>
@@ -2463,7 +2463,7 @@
       </c>
       <c r="K44" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:06Z</t>
+          <t>2026-10-14T23:20:55Z</t>
         </is>
       </c>
     </row>
@@ -2512,7 +2512,7 @@
       </c>
       <c r="K45" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:06Z</t>
+          <t>2026-10-14T23:20:55Z</t>
         </is>
       </c>
     </row>
@@ -2561,7 +2561,7 @@
       </c>
       <c r="K46" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:06Z</t>
+          <t>2026-10-14T23:20:55Z</t>
         </is>
       </c>
     </row>
@@ -2610,7 +2610,7 @@
       </c>
       <c r="K47" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:06Z</t>
+          <t>2026-10-14T23:20:55Z</t>
         </is>
       </c>
     </row>
@@ -2659,7 +2659,7 @@
       </c>
       <c r="K48" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:06Z</t>
+          <t>2026-10-14T23:20:55Z</t>
         </is>
       </c>
     </row>
@@ -2708,7 +2708,7 @@
       </c>
       <c r="K49" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:06Z</t>
+          <t>2026-10-14T23:20:55Z</t>
         </is>
       </c>
     </row>
@@ -2757,7 +2757,7 @@
       </c>
       <c r="K50" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:06Z</t>
+          <t>2026-10-14T23:20:55Z</t>
         </is>
       </c>
     </row>
@@ -2806,7 +2806,7 @@
       </c>
       <c r="K51" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:06Z</t>
+          <t>2026-10-14T23:20:55Z</t>
         </is>
       </c>
     </row>
@@ -2855,7 +2855,7 @@
       </c>
       <c r="K52" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:06Z</t>
+          <t>2026-10-14T23:20:55Z</t>
         </is>
       </c>
     </row>
@@ -2904,7 +2904,7 @@
       </c>
       <c r="K53" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:06Z</t>
+          <t>2026-10-14T23:20:55Z</t>
         </is>
       </c>
     </row>
@@ -2953,7 +2953,7 @@
       </c>
       <c r="K54" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:06Z</t>
+          <t>2026-10-14T23:20:55Z</t>
         </is>
       </c>
     </row>
@@ -3002,7 +3002,7 @@
       </c>
       <c r="K55" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:06Z</t>
+          <t>2026-10-14T23:20:55Z</t>
         </is>
       </c>
     </row>
@@ -3051,7 +3051,7 @@
       </c>
       <c r="K56" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:06Z</t>
+          <t>2026-10-14T23:20:55Z</t>
         </is>
       </c>
     </row>
@@ -3100,7 +3100,7 @@
       </c>
       <c r="K57" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:06Z</t>
+          <t>2026-10-14T23:20:55Z</t>
         </is>
       </c>
     </row>
@@ -3149,7 +3149,7 @@
       </c>
       <c r="K58" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:06Z</t>
+          <t>2026-10-14T23:20:55Z</t>
         </is>
       </c>
     </row>
@@ -3198,7 +3198,7 @@
       </c>
       <c r="K59" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:06Z</t>
+          <t>2026-10-14T23:20:55Z</t>
         </is>
       </c>
     </row>
@@ -3247,7 +3247,7 @@
       </c>
       <c r="K60" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:06Z</t>
+          <t>2026-10-14T23:20:55Z</t>
         </is>
       </c>
     </row>
@@ -3296,7 +3296,7 @@
       </c>
       <c r="K61" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:06Z</t>
+          <t>2026-10-14T23:20:55Z</t>
         </is>
       </c>
     </row>
@@ -3345,7 +3345,7 @@
       </c>
       <c r="K62" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:06Z</t>
+          <t>2026-10-14T23:20:55Z</t>
         </is>
       </c>
     </row>
@@ -3394,7 +3394,7 @@
       </c>
       <c r="K63" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:06Z</t>
+          <t>2026-10-14T23:20:55Z</t>
         </is>
       </c>
     </row>
@@ -3443,7 +3443,7 @@
       </c>
       <c r="K64" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:06Z</t>
+          <t>2026-10-14T23:20:55Z</t>
         </is>
       </c>
     </row>
@@ -3492,7 +3492,7 @@
       </c>
       <c r="K65" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:06Z</t>
+          <t>2026-10-14T23:20:55Z</t>
         </is>
       </c>
     </row>
@@ -3541,7 +3541,7 @@
       </c>
       <c r="K66" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:06Z</t>
+          <t>2026-10-14T23:20:55Z</t>
         </is>
       </c>
     </row>
@@ -3590,7 +3590,7 @@
       </c>
       <c r="K67" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:06Z</t>
+          <t>2026-10-14T23:20:55Z</t>
         </is>
       </c>
     </row>
@@ -3639,7 +3639,7 @@
       </c>
       <c r="K68" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:06Z</t>
+          <t>2026-10-14T23:20:55Z</t>
         </is>
       </c>
     </row>
@@ -3688,7 +3688,7 @@
       </c>
       <c r="K69" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:06Z</t>
+          <t>2026-10-14T23:20:55Z</t>
         </is>
       </c>
     </row>
@@ -3737,7 +3737,7 @@
       </c>
       <c r="K70" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:06Z</t>
+          <t>2026-10-14T23:20:55Z</t>
         </is>
       </c>
     </row>
@@ -3786,7 +3786,7 @@
       </c>
       <c r="K71" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:06Z</t>
+          <t>2026-10-14T23:20:55Z</t>
         </is>
       </c>
     </row>
@@ -3835,7 +3835,7 @@
       </c>
       <c r="K72" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:06Z</t>
+          <t>2026-10-14T23:20:55Z</t>
         </is>
       </c>
     </row>
@@ -3884,7 +3884,7 @@
       </c>
       <c r="K73" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:06Z</t>
+          <t>2026-10-14T23:20:55Z</t>
         </is>
       </c>
     </row>
@@ -3933,7 +3933,7 @@
       </c>
       <c r="K74" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:06Z</t>
+          <t>2026-10-14T23:20:55Z</t>
         </is>
       </c>
     </row>
@@ -3982,7 +3982,7 @@
       </c>
       <c r="K75" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:06Z</t>
+          <t>2026-10-14T23:20:55Z</t>
         </is>
       </c>
     </row>
@@ -4031,7 +4031,7 @@
       </c>
       <c r="K76" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:06Z</t>
+          <t>2026-10-14T23:20:55Z</t>
         </is>
       </c>
     </row>
@@ -4080,7 +4080,7 @@
       </c>
       <c r="K77" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:06Z</t>
+          <t>2026-10-14T23:20:55Z</t>
         </is>
       </c>
     </row>
@@ -4129,7 +4129,7 @@
       </c>
       <c r="K78" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:06Z</t>
+          <t>2026-10-14T23:20:55Z</t>
         </is>
       </c>
     </row>
@@ -4178,7 +4178,7 @@
       </c>
       <c r="K79" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:06Z</t>
+          <t>2026-10-14T23:20:55Z</t>
         </is>
       </c>
     </row>
@@ -4227,7 +4227,7 @@
       </c>
       <c r="K80" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:06Z</t>
+          <t>2026-10-14T23:20:55Z</t>
         </is>
       </c>
     </row>
@@ -4276,7 +4276,7 @@
       </c>
       <c r="K81" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:06Z</t>
+          <t>2026-10-14T23:20:55Z</t>
         </is>
       </c>
     </row>
@@ -4325,7 +4325,7 @@
       </c>
       <c r="K82" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:06Z</t>
+          <t>2026-10-14T23:20:55Z</t>
         </is>
       </c>
     </row>
@@ -4374,7 +4374,7 @@
       </c>
       <c r="K83" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:06Z</t>
+          <t>2026-10-14T23:20:55Z</t>
         </is>
       </c>
     </row>
@@ -4423,7 +4423,7 @@
       </c>
       <c r="K84" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:06Z</t>
+          <t>2026-10-14T23:20:55Z</t>
         </is>
       </c>
     </row>
@@ -4472,7 +4472,7 @@
       </c>
       <c r="K85" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:06Z</t>
+          <t>2026-10-14T23:20:55Z</t>
         </is>
       </c>
     </row>
@@ -4521,7 +4521,7 @@
       </c>
       <c r="K86" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:06Z</t>
+          <t>2026-10-14T23:20:55Z</t>
         </is>
       </c>
     </row>
@@ -4570,7 +4570,7 @@
       </c>
       <c r="K87" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:06Z</t>
+          <t>2026-10-14T23:20:55Z</t>
         </is>
       </c>
     </row>
@@ -4619,7 +4619,7 @@
       </c>
       <c r="K88" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:06Z</t>
+          <t>2026-10-14T23:20:55Z</t>
         </is>
       </c>
     </row>
@@ -4668,7 +4668,7 @@
       </c>
       <c r="K89" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:06Z</t>
+          <t>2026-10-14T23:20:55Z</t>
         </is>
       </c>
     </row>
@@ -4717,7 +4717,7 @@
       </c>
       <c r="K90" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:06Z</t>
+          <t>2026-10-14T23:20:55Z</t>
         </is>
       </c>
     </row>
@@ -4766,7 +4766,7 @@
       </c>
       <c r="K91" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:06Z</t>
+          <t>2026-10-14T23:20:55Z</t>
         </is>
       </c>
     </row>
@@ -4815,7 +4815,7 @@
       </c>
       <c r="K92" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:06Z</t>
+          <t>2026-10-14T23:20:55Z</t>
         </is>
       </c>
     </row>
@@ -4864,7 +4864,7 @@
       </c>
       <c r="K93" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:06Z</t>
+          <t>2026-10-14T23:20:55Z</t>
         </is>
       </c>
     </row>
@@ -4913,7 +4913,7 @@
       </c>
       <c r="K94" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:06Z</t>
+          <t>2026-10-14T23:20:55Z</t>
         </is>
       </c>
     </row>
@@ -4962,7 +4962,7 @@
       </c>
       <c r="K95" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:06Z</t>
+          <t>2026-10-14T23:20:55Z</t>
         </is>
       </c>
     </row>
@@ -5011,7 +5011,7 @@
       </c>
       <c r="K96" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:06Z</t>
+          <t>2026-10-14T23:20:55Z</t>
         </is>
       </c>
     </row>
@@ -5060,7 +5060,7 @@
       </c>
       <c r="K97" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:06Z</t>
+          <t>2026-10-14T23:20:55Z</t>
         </is>
       </c>
     </row>
@@ -5109,7 +5109,7 @@
       </c>
       <c r="K98" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:06Z</t>
+          <t>2026-10-14T23:20:55Z</t>
         </is>
       </c>
     </row>
@@ -5158,7 +5158,7 @@
       </c>
       <c r="K99" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:06Z</t>
+          <t>2026-10-14T23:20:55Z</t>
         </is>
       </c>
     </row>
@@ -5207,7 +5207,7 @@
       </c>
       <c r="K100" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:06Z</t>
+          <t>2026-10-14T23:20:55Z</t>
         </is>
       </c>
     </row>
@@ -5256,7 +5256,7 @@
       </c>
       <c r="K101" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:06Z</t>
+          <t>2026-10-14T23:20:55Z</t>
         </is>
       </c>
     </row>
@@ -5305,7 +5305,7 @@
       </c>
       <c r="K102" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:06Z</t>
+          <t>2026-10-14T23:20:55Z</t>
         </is>
       </c>
     </row>
@@ -5354,7 +5354,7 @@
       </c>
       <c r="K103" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:06Z</t>
+          <t>2026-10-14T23:20:55Z</t>
         </is>
       </c>
     </row>
@@ -5403,7 +5403,7 @@
       </c>
       <c r="K104" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:06Z</t>
+          <t>2026-10-14T23:20:55Z</t>
         </is>
       </c>
     </row>
@@ -5452,7 +5452,7 @@
       </c>
       <c r="K105" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:06Z</t>
+          <t>2026-10-14T23:20:55Z</t>
         </is>
       </c>
     </row>
@@ -5501,7 +5501,7 @@
       </c>
       <c r="K106" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:06Z</t>
+          <t>2026-10-14T23:20:55Z</t>
         </is>
       </c>
     </row>
@@ -5550,7 +5550,7 @@
       </c>
       <c r="K107" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:06Z</t>
+          <t>2026-10-14T23:20:55Z</t>
         </is>
       </c>
     </row>
@@ -5599,7 +5599,7 @@
       </c>
       <c r="K108" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:06Z</t>
+          <t>2026-10-14T23:20:55Z</t>
         </is>
       </c>
     </row>
@@ -5648,7 +5648,7 @@
       </c>
       <c r="K109" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:06Z</t>
+          <t>2026-10-14T23:20:55Z</t>
         </is>
       </c>
     </row>
@@ -5697,7 +5697,7 @@
       </c>
       <c r="K110" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:06Z</t>
+          <t>2026-10-14T23:20:55Z</t>
         </is>
       </c>
     </row>
@@ -5746,7 +5746,7 @@
       </c>
       <c r="K111" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:06Z</t>
+          <t>2026-10-14T23:20:55Z</t>
         </is>
       </c>
     </row>
@@ -5795,7 +5795,7 @@
       </c>
       <c r="K112" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:06Z</t>
+          <t>2026-10-14T23:20:55Z</t>
         </is>
       </c>
     </row>
@@ -5844,7 +5844,7 @@
       </c>
       <c r="K113" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:06Z</t>
+          <t>2026-10-14T23:20:55Z</t>
         </is>
       </c>
     </row>
@@ -5893,7 +5893,7 @@
       </c>
       <c r="K114" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:06Z</t>
+          <t>2026-10-14T23:20:55Z</t>
         </is>
       </c>
     </row>
@@ -5942,7 +5942,7 @@
       </c>
       <c r="K115" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:06Z</t>
+          <t>2026-10-14T23:20:55Z</t>
         </is>
       </c>
     </row>
@@ -5991,7 +5991,7 @@
       </c>
       <c r="K116" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:06Z</t>
+          <t>2026-10-14T23:20:55Z</t>
         </is>
       </c>
     </row>
@@ -6040,7 +6040,7 @@
       </c>
       <c r="K117" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:06Z</t>
+          <t>2026-10-14T23:20:55Z</t>
         </is>
       </c>
     </row>
@@ -6089,7 +6089,7 @@
       </c>
       <c r="K118" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:06Z</t>
+          <t>2026-10-14T23:20:55Z</t>
         </is>
       </c>
     </row>
@@ -6138,7 +6138,7 @@
       </c>
       <c r="K119" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:06Z</t>
+          <t>2026-10-14T23:20:55Z</t>
         </is>
       </c>
     </row>
@@ -6187,7 +6187,7 @@
       </c>
       <c r="K120" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:06Z</t>
+          <t>2026-10-14T23:20:55Z</t>
         </is>
       </c>
     </row>
@@ -6236,7 +6236,7 @@
       </c>
       <c r="K121" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:06Z</t>
+          <t>2026-10-14T23:20:55Z</t>
         </is>
       </c>
     </row>
@@ -6285,7 +6285,7 @@
       </c>
       <c r="K122" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:06Z</t>
+          <t>2026-10-14T23:20:55Z</t>
         </is>
       </c>
     </row>
@@ -6334,7 +6334,7 @@
       </c>
       <c r="K123" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:06Z</t>
+          <t>2026-10-14T23:20:55Z</t>
         </is>
       </c>
     </row>
@@ -6383,7 +6383,7 @@
       </c>
       <c r="K124" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:06Z</t>
+          <t>2026-10-14T23:20:55Z</t>
         </is>
       </c>
     </row>
@@ -6432,7 +6432,7 @@
       </c>
       <c r="K125" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:06Z</t>
+          <t>2026-10-14T23:20:55Z</t>
         </is>
       </c>
     </row>
@@ -6481,7 +6481,7 @@
       </c>
       <c r="K126" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:06Z</t>
+          <t>2026-10-14T23:20:55Z</t>
         </is>
       </c>
     </row>
@@ -6530,7 +6530,7 @@
       </c>
       <c r="K127" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:06Z</t>
+          <t>2026-10-14T23:20:55Z</t>
         </is>
       </c>
     </row>
@@ -6579,7 +6579,7 @@
       </c>
       <c r="K128" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:06Z</t>
+          <t>2026-10-14T23:20:55Z</t>
         </is>
       </c>
     </row>
@@ -6628,7 +6628,7 @@
       </c>
       <c r="K129" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:06Z</t>
+          <t>2026-10-14T23:20:55Z</t>
         </is>
       </c>
     </row>
@@ -6677,7 +6677,7 @@
       </c>
       <c r="K130" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:06Z</t>
+          <t>2026-10-14T23:20:55Z</t>
         </is>
       </c>
     </row>
@@ -6726,7 +6726,7 @@
       </c>
       <c r="K131" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:06Z</t>
+          <t>2026-10-14T23:20:55Z</t>
         </is>
       </c>
     </row>
@@ -6775,7 +6775,7 @@
       </c>
       <c r="K132" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:06Z</t>
+          <t>2026-10-14T23:20:55Z</t>
         </is>
       </c>
     </row>
@@ -6824,7 +6824,7 @@
       </c>
       <c r="K133" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:06Z</t>
+          <t>2026-10-14T23:20:55Z</t>
         </is>
       </c>
     </row>
@@ -6873,7 +6873,7 @@
       </c>
       <c r="K134" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:06Z</t>
+          <t>2026-10-14T23:20:55Z</t>
         </is>
       </c>
     </row>
@@ -6922,7 +6922,7 @@
       </c>
       <c r="K135" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:06Z</t>
+          <t>2026-10-14T23:20:55Z</t>
         </is>
       </c>
     </row>
@@ -6971,7 +6971,7 @@
       </c>
       <c r="K136" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:06Z</t>
+          <t>2026-10-14T23:20:55Z</t>
         </is>
       </c>
     </row>
@@ -7020,7 +7020,7 @@
       </c>
       <c r="K137" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:06Z</t>
+          <t>2026-10-14T23:20:55Z</t>
         </is>
       </c>
     </row>
@@ -7069,7 +7069,7 @@
       </c>
       <c r="K138" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:06Z</t>
+          <t>2026-10-14T23:20:55Z</t>
         </is>
       </c>
     </row>
@@ -7118,7 +7118,7 @@
       </c>
       <c r="K139" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:06Z</t>
+          <t>2026-10-14T23:20:55Z</t>
         </is>
       </c>
     </row>
@@ -7167,7 +7167,7 @@
       </c>
       <c r="K140" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:06Z</t>
+          <t>2026-10-14T23:20:55Z</t>
         </is>
       </c>
     </row>
@@ -7216,7 +7216,7 @@
       </c>
       <c r="K141" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:06Z</t>
+          <t>2026-10-14T23:20:55Z</t>
         </is>
       </c>
     </row>
@@ -7265,7 +7265,7 @@
       </c>
       <c r="K142" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:06Z</t>
+          <t>2026-10-14T23:20:55Z</t>
         </is>
       </c>
     </row>
@@ -7314,7 +7314,7 @@
       </c>
       <c r="K143" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:06Z</t>
+          <t>2026-10-14T23:20:55Z</t>
         </is>
       </c>
     </row>
@@ -7363,7 +7363,7 @@
       </c>
       <c r="K144" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:06Z</t>
+          <t>2026-10-14T23:20:55Z</t>
         </is>
       </c>
     </row>
@@ -7412,7 +7412,7 @@
       </c>
       <c r="K145" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:06Z</t>
+          <t>2026-10-14T23:20:55Z</t>
         </is>
       </c>
     </row>
@@ -7461,7 +7461,7 @@
       </c>
       <c r="K146" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:06Z</t>
+          <t>2026-10-14T23:20:55Z</t>
         </is>
       </c>
     </row>
@@ -7510,7 +7510,7 @@
       </c>
       <c r="K147" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:06Z</t>
+          <t>2026-10-14T23:20:55Z</t>
         </is>
       </c>
     </row>
@@ -7559,7 +7559,7 @@
       </c>
       <c r="K148" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:06Z</t>
+          <t>2026-10-14T23:20:55Z</t>
         </is>
       </c>
     </row>
@@ -7608,7 +7608,7 @@
       </c>
       <c r="K149" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:06Z</t>
+          <t>2026-10-14T23:20:55Z</t>
         </is>
       </c>
     </row>
@@ -7657,7 +7657,7 @@
       </c>
       <c r="K150" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:06Z</t>
+          <t>2026-10-14T23:20:55Z</t>
         </is>
       </c>
     </row>
@@ -7706,7 +7706,7 @@
       </c>
       <c r="K151" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:06Z</t>
+          <t>2026-10-14T23:20:55Z</t>
         </is>
       </c>
     </row>
@@ -7755,7 +7755,7 @@
       </c>
       <c r="K152" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:06Z</t>
+          <t>2026-10-14T23:20:55Z</t>
         </is>
       </c>
     </row>
@@ -7804,7 +7804,7 @@
       </c>
       <c r="K153" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:06Z</t>
+          <t>2026-10-14T23:20:55Z</t>
         </is>
       </c>
     </row>
@@ -7853,7 +7853,7 @@
       </c>
       <c r="K154" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:06Z</t>
+          <t>2026-10-14T23:20:55Z</t>
         </is>
       </c>
     </row>
@@ -7902,7 +7902,7 @@
       </c>
       <c r="K155" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:06Z</t>
+          <t>2026-10-14T23:20:55Z</t>
         </is>
       </c>
     </row>
@@ -7951,7 +7951,7 @@
       </c>
       <c r="K156" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:06Z</t>
+          <t>2026-10-14T23:20:55Z</t>
         </is>
       </c>
     </row>
@@ -8000,7 +8000,7 @@
       </c>
       <c r="K157" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:06Z</t>
+          <t>2026-10-14T23:20:55Z</t>
         </is>
       </c>
     </row>
@@ -8049,7 +8049,7 @@
       </c>
       <c r="K158" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:06Z</t>
+          <t>2026-10-14T23:20:55Z</t>
         </is>
       </c>
     </row>
@@ -8098,7 +8098,7 @@
       </c>
       <c r="K159" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:06Z</t>
+          <t>2026-10-14T23:20:55Z</t>
         </is>
       </c>
     </row>
@@ -8147,7 +8147,7 @@
       </c>
       <c r="K160" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:06Z</t>
+          <t>2026-10-14T23:20:55Z</t>
         </is>
       </c>
     </row>
@@ -8196,7 +8196,7 @@
       </c>
       <c r="K161" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:06Z</t>
+          <t>2026-10-14T23:20:55Z</t>
         </is>
       </c>
     </row>
@@ -8245,7 +8245,7 @@
       </c>
       <c r="K162" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:06Z</t>
+          <t>2026-10-14T23:20:55Z</t>
         </is>
       </c>
     </row>
@@ -8294,7 +8294,7 @@
       </c>
       <c r="K163" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:06Z</t>
+          <t>2026-10-14T23:20:55Z</t>
         </is>
       </c>
     </row>
@@ -8343,7 +8343,7 @@
       </c>
       <c r="K164" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:06Z</t>
+          <t>2026-10-14T23:20:55Z</t>
         </is>
       </c>
     </row>
@@ -8392,7 +8392,7 @@
       </c>
       <c r="K165" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:06Z</t>
+          <t>2026-10-14T23:20:55Z</t>
         </is>
       </c>
     </row>
@@ -8441,7 +8441,7 @@
       </c>
       <c r="K166" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:06Z</t>
+          <t>2026-10-14T23:20:55Z</t>
         </is>
       </c>
     </row>
@@ -8490,7 +8490,7 @@
       </c>
       <c r="K167" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:06Z</t>
+          <t>2026-10-14T23:20:55Z</t>
         </is>
       </c>
     </row>
@@ -8539,7 +8539,7 @@
       </c>
       <c r="K168" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:06Z</t>
+          <t>2026-10-14T23:20:55Z</t>
         </is>
       </c>
     </row>
@@ -8588,7 +8588,7 @@
       </c>
       <c r="K169" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:06Z</t>
+          <t>2026-10-14T23:20:55Z</t>
         </is>
       </c>
     </row>
@@ -8637,7 +8637,7 @@
       </c>
       <c r="K170" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:06Z</t>
+          <t>2026-10-14T23:20:55Z</t>
         </is>
       </c>
     </row>
@@ -8686,7 +8686,7 @@
       </c>
       <c r="K171" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:06Z</t>
+          <t>2026-10-14T23:20:55Z</t>
         </is>
       </c>
     </row>
@@ -8735,7 +8735,7 @@
       </c>
       <c r="K172" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:06Z</t>
+          <t>2026-10-14T23:20:55Z</t>
         </is>
       </c>
     </row>
@@ -8784,7 +8784,7 @@
       </c>
       <c r="K173" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:06Z</t>
+          <t>2026-10-14T23:20:55Z</t>
         </is>
       </c>
     </row>
@@ -8833,7 +8833,7 @@
       </c>
       <c r="K174" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:06Z</t>
+          <t>2026-10-14T23:20:55Z</t>
         </is>
       </c>
     </row>
@@ -8882,7 +8882,7 @@
       </c>
       <c r="K175" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:06Z</t>
+          <t>2026-10-14T23:20:55Z</t>
         </is>
       </c>
     </row>
@@ -8931,7 +8931,7 @@
       </c>
       <c r="K176" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:06Z</t>
+          <t>2026-10-14T23:20:55Z</t>
         </is>
       </c>
     </row>
@@ -8980,7 +8980,7 @@
       </c>
       <c r="K177" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:06Z</t>
+          <t>2026-10-14T23:20:55Z</t>
         </is>
       </c>
     </row>
@@ -9029,7 +9029,7 @@
       </c>
       <c r="K178" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:06Z</t>
+          <t>2026-10-14T23:20:55Z</t>
         </is>
       </c>
     </row>
@@ -9078,7 +9078,7 @@
       </c>
       <c r="K179" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:06Z</t>
+          <t>2026-10-14T23:20:55Z</t>
         </is>
       </c>
     </row>
@@ -9127,7 +9127,7 @@
       </c>
       <c r="K180" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:06Z</t>
+          <t>2026-10-14T23:20:55Z</t>
         </is>
       </c>
     </row>
@@ -9176,7 +9176,7 @@
       </c>
       <c r="K181" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:06Z</t>
+          <t>2026-10-14T23:20:55Z</t>
         </is>
       </c>
     </row>
@@ -9225,7 +9225,7 @@
       </c>
       <c r="K182" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:06Z</t>
+          <t>2026-10-14T23:20:55Z</t>
         </is>
       </c>
     </row>
@@ -9274,7 +9274,7 @@
       </c>
       <c r="K183" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:06Z</t>
+          <t>2026-10-14T23:20:55Z</t>
         </is>
       </c>
     </row>
@@ -9323,7 +9323,7 @@
       </c>
       <c r="K184" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:06Z</t>
+          <t>2026-10-14T23:20:55Z</t>
         </is>
       </c>
     </row>
@@ -9372,7 +9372,7 @@
       </c>
       <c r="K185" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:06Z</t>
+          <t>2026-10-14T23:20:55Z</t>
         </is>
       </c>
     </row>
@@ -9421,7 +9421,7 @@
       </c>
       <c r="K186" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:06Z</t>
+          <t>2026-10-14T23:20:55Z</t>
         </is>
       </c>
     </row>
@@ -9470,7 +9470,7 @@
       </c>
       <c r="K187" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:06Z</t>
+          <t>2026-10-14T23:20:55Z</t>
         </is>
       </c>
     </row>
@@ -9519,7 +9519,7 @@
       </c>
       <c r="K188" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:06Z</t>
+          <t>2026-10-14T23:20:55Z</t>
         </is>
       </c>
     </row>
@@ -9568,7 +9568,7 @@
       </c>
       <c r="K189" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:06Z</t>
+          <t>2026-10-14T23:20:55Z</t>
         </is>
       </c>
     </row>
@@ -9617,7 +9617,7 @@
       </c>
       <c r="K190" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:06Z</t>
+          <t>2026-10-14T23:20:55Z</t>
         </is>
       </c>
     </row>
@@ -9666,7 +9666,7 @@
       </c>
       <c r="K191" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:06Z</t>
+          <t>2026-10-14T23:20:55Z</t>
         </is>
       </c>
     </row>
@@ -9715,7 +9715,7 @@
       </c>
       <c r="K192" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:06Z</t>
+          <t>2026-10-14T23:20:55Z</t>
         </is>
       </c>
     </row>
@@ -9764,7 +9764,7 @@
       </c>
       <c r="K193" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:06Z</t>
+          <t>2026-10-14T23:20:55Z</t>
         </is>
       </c>
     </row>
@@ -9813,7 +9813,7 @@
       </c>
       <c r="K194" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:06Z</t>
+          <t>2026-10-14T23:20:55Z</t>
         </is>
       </c>
     </row>
@@ -9862,7 +9862,7 @@
       </c>
       <c r="K195" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:06Z</t>
+          <t>2026-10-14T23:20:55Z</t>
         </is>
       </c>
     </row>
@@ -9911,7 +9911,7 @@
       </c>
       <c r="K196" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:06Z</t>
+          <t>2026-10-14T23:20:55Z</t>
         </is>
       </c>
     </row>
@@ -9960,7 +9960,7 @@
       </c>
       <c r="K197" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:06Z</t>
+          <t>2026-10-14T23:20:55Z</t>
         </is>
       </c>
     </row>
@@ -10009,7 +10009,7 @@
       </c>
       <c r="K198" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:06Z</t>
+          <t>2026-10-14T23:20:55Z</t>
         </is>
       </c>
     </row>
@@ -10058,7 +10058,7 @@
       </c>
       <c r="K199" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:06Z</t>
+          <t>2026-10-14T23:20:55Z</t>
         </is>
       </c>
     </row>
@@ -10107,7 +10107,7 @@
       </c>
       <c r="K200" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:06Z</t>
+          <t>2026-10-14T23:20:55Z</t>
         </is>
       </c>
     </row>
@@ -10156,7 +10156,7 @@
       </c>
       <c r="K201" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:06Z</t>
+          <t>2026-10-14T23:20:55Z</t>
         </is>
       </c>
     </row>
@@ -10205,7 +10205,7 @@
       </c>
       <c r="K202" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:06Z</t>
+          <t>2026-10-14T23:20:55Z</t>
         </is>
       </c>
     </row>
@@ -10254,7 +10254,7 @@
       </c>
       <c r="K203" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:06Z</t>
+          <t>2026-10-14T23:20:55Z</t>
         </is>
       </c>
     </row>
@@ -10303,7 +10303,7 @@
       </c>
       <c r="K204" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:06Z</t>
+          <t>2026-10-14T23:20:55Z</t>
         </is>
       </c>
     </row>
@@ -10352,7 +10352,7 @@
       </c>
       <c r="K205" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:06Z</t>
+          <t>2026-10-14T23:20:55Z</t>
         </is>
       </c>
     </row>
@@ -10401,7 +10401,7 @@
       </c>
       <c r="K206" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:06Z</t>
+          <t>2026-10-14T23:20:55Z</t>
         </is>
       </c>
     </row>
@@ -10450,7 +10450,7 @@
       </c>
       <c r="K207" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:06Z</t>
+          <t>2026-10-14T23:20:55Z</t>
         </is>
       </c>
     </row>
@@ -10499,7 +10499,7 @@
       </c>
       <c r="K208" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:06Z</t>
+          <t>2026-10-14T23:20:55Z</t>
         </is>
       </c>
     </row>
@@ -10548,7 +10548,7 @@
       </c>
       <c r="K209" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:06Z</t>
+          <t>2026-10-14T23:20:55Z</t>
         </is>
       </c>
     </row>
@@ -10597,7 +10597,7 @@
       </c>
       <c r="K210" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:06Z</t>
+          <t>2026-10-14T23:20:55Z</t>
         </is>
       </c>
     </row>
@@ -10646,7 +10646,7 @@
       </c>
       <c r="K211" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:06Z</t>
+          <t>2026-10-14T23:20:55Z</t>
         </is>
       </c>
     </row>
@@ -10695,7 +10695,7 @@
       </c>
       <c r="K212" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:06Z</t>
+          <t>2026-10-14T23:20:55Z</t>
         </is>
       </c>
     </row>
@@ -10744,7 +10744,7 @@
       </c>
       <c r="K213" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:06Z</t>
+          <t>2026-10-14T23:20:55Z</t>
         </is>
       </c>
     </row>
@@ -10793,7 +10793,7 @@
       </c>
       <c r="K214" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:06Z</t>
+          <t>2026-10-14T23:20:55Z</t>
         </is>
       </c>
     </row>
@@ -10842,7 +10842,7 @@
       </c>
       <c r="K215" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:06Z</t>
+          <t>2026-10-14T23:20:55Z</t>
         </is>
       </c>
     </row>
@@ -10891,7 +10891,7 @@
       </c>
       <c r="K216" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:06Z</t>
+          <t>2026-10-14T23:20:55Z</t>
         </is>
       </c>
     </row>
@@ -10940,7 +10940,7 @@
       </c>
       <c r="K217" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:06Z</t>
+          <t>2026-10-14T23:20:55Z</t>
         </is>
       </c>
     </row>
@@ -10989,7 +10989,7 @@
       </c>
       <c r="K218" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:06Z</t>
+          <t>2026-10-14T23:20:55Z</t>
         </is>
       </c>
     </row>
@@ -11038,7 +11038,7 @@
       </c>
       <c r="K219" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:06Z</t>
+          <t>2026-10-14T23:20:55Z</t>
         </is>
       </c>
     </row>
@@ -11087,7 +11087,7 @@
       </c>
       <c r="K220" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:06Z</t>
+          <t>2026-10-14T23:20:55Z</t>
         </is>
       </c>
     </row>
@@ -11136,7 +11136,7 @@
       </c>
       <c r="K221" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:06Z</t>
+          <t>2026-10-14T23:20:55Z</t>
         </is>
       </c>
     </row>
@@ -11185,7 +11185,7 @@
       </c>
       <c r="K222" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:06Z</t>
+          <t>2026-10-14T23:20:55Z</t>
         </is>
       </c>
     </row>
@@ -11234,7 +11234,7 @@
       </c>
       <c r="K223" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:06Z</t>
+          <t>2026-10-14T23:20:55Z</t>
         </is>
       </c>
     </row>
@@ -11283,7 +11283,7 @@
       </c>
       <c r="K224" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:06Z</t>
+          <t>2026-10-14T23:20:55Z</t>
         </is>
       </c>
     </row>
@@ -11332,7 +11332,7 @@
       </c>
       <c r="K225" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:06Z</t>
+          <t>2026-10-14T23:20:55Z</t>
         </is>
       </c>
     </row>
@@ -11381,7 +11381,7 @@
       </c>
       <c r="K226" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:06Z</t>
+          <t>2026-10-14T23:20:55Z</t>
         </is>
       </c>
     </row>
@@ -11430,7 +11430,7 @@
       </c>
       <c r="K227" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:06Z</t>
+          <t>2026-10-14T23:20:55Z</t>
         </is>
       </c>
     </row>
@@ -11479,7 +11479,7 @@
       </c>
       <c r="K228" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:06Z</t>
+          <t>2026-10-14T23:20:55Z</t>
         </is>
       </c>
     </row>
@@ -11528,7 +11528,7 @@
       </c>
       <c r="K229" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:06Z</t>
+          <t>2026-10-14T23:20:55Z</t>
         </is>
       </c>
     </row>
@@ -11577,7 +11577,7 @@
       </c>
       <c r="K230" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:06Z</t>
+          <t>2026-10-14T23:20:55Z</t>
         </is>
       </c>
     </row>
@@ -11626,7 +11626,7 @@
       </c>
       <c r="K231" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:06Z</t>
+          <t>2026-10-14T23:20:55Z</t>
         </is>
       </c>
     </row>
@@ -11758,7 +11758,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:06Z</t>
+          <t>2026-10-14T23:20:55Z</t>
         </is>
       </c>
     </row>
@@ -11804,7 +11804,7 @@
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>{"date": "2026-08-01", "year": 2026, "month": 8, "month_name": "Agosto", "index_value": 637409769724325.1, "monthly_variation_pct": 8.9, "unit": "Índice base diciembre 2007=100 y variación mensual %", "frequency": "monthly", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/precios_consumidor/4_5_7_2.xls", "fetched_at": "2026-10-13T23:48:06Z"}</t>
+          <t>{"date": "2026-08-01", "year": 2026, "month": 8, "month_name": "Agosto", "index_value": 637409769724325.1, "monthly_variation_pct": 8.9, "unit": "Índice base diciembre 2007=100 y variación mensual %", "frequency": "monthly", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/precios_consumidor/4_5_7_2.xls", "fetched_at": "2026-10-14T23:20:55Z"}</t>
         </is>
       </c>
     </row>

--- a/assets/data/bcv/excel/ove_bcv_inpc_nacional_mensual.xlsx
+++ b/assets/data/bcv/excel/ove_bcv_inpc_nacional_mensual.xlsx
@@ -650,7 +650,7 @@
       </c>
       <c r="K7" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:55Z</t>
+          <t>2026-10-15T23:09:48Z</t>
         </is>
       </c>
     </row>
@@ -699,7 +699,7 @@
       </c>
       <c r="K8" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:55Z</t>
+          <t>2026-10-15T23:09:48Z</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="K9" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:55Z</t>
+          <t>2026-10-15T23:09:48Z</t>
         </is>
       </c>
     </row>
@@ -797,7 +797,7 @@
       </c>
       <c r="K10" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:55Z</t>
+          <t>2026-10-15T23:09:48Z</t>
         </is>
       </c>
     </row>
@@ -846,7 +846,7 @@
       </c>
       <c r="K11" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:55Z</t>
+          <t>2026-10-15T23:09:48Z</t>
         </is>
       </c>
     </row>
@@ -895,7 +895,7 @@
       </c>
       <c r="K12" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:55Z</t>
+          <t>2026-10-15T23:09:48Z</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="K13" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:55Z</t>
+          <t>2026-10-15T23:09:48Z</t>
         </is>
       </c>
     </row>
@@ -993,7 +993,7 @@
       </c>
       <c r="K14" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:55Z</t>
+          <t>2026-10-15T23:09:48Z</t>
         </is>
       </c>
     </row>
@@ -1042,7 +1042,7 @@
       </c>
       <c r="K15" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:55Z</t>
+          <t>2026-10-15T23:09:48Z</t>
         </is>
       </c>
     </row>
@@ -1091,7 +1091,7 @@
       </c>
       <c r="K16" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:55Z</t>
+          <t>2026-10-15T23:09:48Z</t>
         </is>
       </c>
     </row>
@@ -1140,7 +1140,7 @@
       </c>
       <c r="K17" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:55Z</t>
+          <t>2026-10-15T23:09:48Z</t>
         </is>
       </c>
     </row>
@@ -1189,7 +1189,7 @@
       </c>
       <c r="K18" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:55Z</t>
+          <t>2026-10-15T23:09:48Z</t>
         </is>
       </c>
     </row>
@@ -1238,7 +1238,7 @@
       </c>
       <c r="K19" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:55Z</t>
+          <t>2026-10-15T23:09:48Z</t>
         </is>
       </c>
     </row>
@@ -1287,7 +1287,7 @@
       </c>
       <c r="K20" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:55Z</t>
+          <t>2026-10-15T23:09:48Z</t>
         </is>
       </c>
     </row>
@@ -1336,7 +1336,7 @@
       </c>
       <c r="K21" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:55Z</t>
+          <t>2026-10-15T23:09:48Z</t>
         </is>
       </c>
     </row>
@@ -1385,7 +1385,7 @@
       </c>
       <c r="K22" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:55Z</t>
+          <t>2026-10-15T23:09:48Z</t>
         </is>
       </c>
     </row>
@@ -1434,7 +1434,7 @@
       </c>
       <c r="K23" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:55Z</t>
+          <t>2026-10-15T23:09:48Z</t>
         </is>
       </c>
     </row>
@@ -1483,7 +1483,7 @@
       </c>
       <c r="K24" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:55Z</t>
+          <t>2026-10-15T23:09:48Z</t>
         </is>
       </c>
     </row>
@@ -1532,7 +1532,7 @@
       </c>
       <c r="K25" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:55Z</t>
+          <t>2026-10-15T23:09:48Z</t>
         </is>
       </c>
     </row>
@@ -1581,7 +1581,7 @@
       </c>
       <c r="K26" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:55Z</t>
+          <t>2026-10-15T23:09:48Z</t>
         </is>
       </c>
     </row>
@@ -1630,7 +1630,7 @@
       </c>
       <c r="K27" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:55Z</t>
+          <t>2026-10-15T23:09:48Z</t>
         </is>
       </c>
     </row>
@@ -1679,7 +1679,7 @@
       </c>
       <c r="K28" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:55Z</t>
+          <t>2026-10-15T23:09:48Z</t>
         </is>
       </c>
     </row>
@@ -1728,7 +1728,7 @@
       </c>
       <c r="K29" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:55Z</t>
+          <t>2026-10-15T23:09:48Z</t>
         </is>
       </c>
     </row>
@@ -1777,7 +1777,7 @@
       </c>
       <c r="K30" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:55Z</t>
+          <t>2026-10-15T23:09:48Z</t>
         </is>
       </c>
     </row>
@@ -1826,7 +1826,7 @@
       </c>
       <c r="K31" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:55Z</t>
+          <t>2026-10-15T23:09:48Z</t>
         </is>
       </c>
     </row>
@@ -1875,7 +1875,7 @@
       </c>
       <c r="K32" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:55Z</t>
+          <t>2026-10-15T23:09:48Z</t>
         </is>
       </c>
     </row>
@@ -1924,7 +1924,7 @@
       </c>
       <c r="K33" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:55Z</t>
+          <t>2026-10-15T23:09:48Z</t>
         </is>
       </c>
     </row>
@@ -1973,7 +1973,7 @@
       </c>
       <c r="K34" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:55Z</t>
+          <t>2026-10-15T23:09:48Z</t>
         </is>
       </c>
     </row>
@@ -2022,7 +2022,7 @@
       </c>
       <c r="K35" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:55Z</t>
+          <t>2026-10-15T23:09:48Z</t>
         </is>
       </c>
     </row>
@@ -2071,7 +2071,7 @@
       </c>
       <c r="K36" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:55Z</t>
+          <t>2026-10-15T23:09:48Z</t>
         </is>
       </c>
     </row>
@@ -2120,7 +2120,7 @@
       </c>
       <c r="K37" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:55Z</t>
+          <t>2026-10-15T23:09:48Z</t>
         </is>
       </c>
     </row>
@@ -2169,7 +2169,7 @@
       </c>
       <c r="K38" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:55Z</t>
+          <t>2026-10-15T23:09:48Z</t>
         </is>
       </c>
     </row>
@@ -2218,7 +2218,7 @@
       </c>
       <c r="K39" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:55Z</t>
+          <t>2026-10-15T23:09:48Z</t>
         </is>
       </c>
     </row>
@@ -2267,7 +2267,7 @@
       </c>
       <c r="K40" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:55Z</t>
+          <t>2026-10-15T23:09:48Z</t>
         </is>
       </c>
     </row>
@@ -2316,7 +2316,7 @@
       </c>
       <c r="K41" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:55Z</t>
+          <t>2026-10-15T23:09:48Z</t>
         </is>
       </c>
     </row>
@@ -2365,7 +2365,7 @@
       </c>
       <c r="K42" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:55Z</t>
+          <t>2026-10-15T23:09:48Z</t>
         </is>
       </c>
     </row>
@@ -2414,7 +2414,7 @@
       </c>
       <c r="K43" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:55Z</t>
+          <t>2026-10-15T23:09:48Z</t>
         </is>
       </c>
     </row>
@@ -2463,7 +2463,7 @@
       </c>
       <c r="K44" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:55Z</t>
+          <t>2026-10-15T23:09:48Z</t>
         </is>
       </c>
     </row>
@@ -2512,7 +2512,7 @@
       </c>
       <c r="K45" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:55Z</t>
+          <t>2026-10-15T23:09:48Z</t>
         </is>
       </c>
     </row>
@@ -2561,7 +2561,7 @@
       </c>
       <c r="K46" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:55Z</t>
+          <t>2026-10-15T23:09:48Z</t>
         </is>
       </c>
     </row>
@@ -2610,7 +2610,7 @@
       </c>
       <c r="K47" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:55Z</t>
+          <t>2026-10-15T23:09:48Z</t>
         </is>
       </c>
     </row>
@@ -2659,7 +2659,7 @@
       </c>
       <c r="K48" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:55Z</t>
+          <t>2026-10-15T23:09:48Z</t>
         </is>
       </c>
     </row>
@@ -2708,7 +2708,7 @@
       </c>
       <c r="K49" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:55Z</t>
+          <t>2026-10-15T23:09:48Z</t>
         </is>
       </c>
     </row>
@@ -2757,7 +2757,7 @@
       </c>
       <c r="K50" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:55Z</t>
+          <t>2026-10-15T23:09:48Z</t>
         </is>
       </c>
     </row>
@@ -2806,7 +2806,7 @@
       </c>
       <c r="K51" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:55Z</t>
+          <t>2026-10-15T23:09:48Z</t>
         </is>
       </c>
     </row>
@@ -2855,7 +2855,7 @@
       </c>
       <c r="K52" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:55Z</t>
+          <t>2026-10-15T23:09:48Z</t>
         </is>
       </c>
     </row>
@@ -2904,7 +2904,7 @@
       </c>
       <c r="K53" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:55Z</t>
+          <t>2026-10-15T23:09:48Z</t>
         </is>
       </c>
     </row>
@@ -2953,7 +2953,7 @@
       </c>
       <c r="K54" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:55Z</t>
+          <t>2026-10-15T23:09:48Z</t>
         </is>
       </c>
     </row>
@@ -3002,7 +3002,7 @@
       </c>
       <c r="K55" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:55Z</t>
+          <t>2026-10-15T23:09:48Z</t>
         </is>
       </c>
     </row>
@@ -3051,7 +3051,7 @@
       </c>
       <c r="K56" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:55Z</t>
+          <t>2026-10-15T23:09:48Z</t>
         </is>
       </c>
     </row>
@@ -3100,7 +3100,7 @@
       </c>
       <c r="K57" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:55Z</t>
+          <t>2026-10-15T23:09:48Z</t>
         </is>
       </c>
     </row>
@@ -3149,7 +3149,7 @@
       </c>
       <c r="K58" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:55Z</t>
+          <t>2026-10-15T23:09:48Z</t>
         </is>
       </c>
     </row>
@@ -3198,7 +3198,7 @@
       </c>
       <c r="K59" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:55Z</t>
+          <t>2026-10-15T23:09:48Z</t>
         </is>
       </c>
     </row>
@@ -3247,7 +3247,7 @@
       </c>
       <c r="K60" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:55Z</t>
+          <t>2026-10-15T23:09:48Z</t>
         </is>
       </c>
     </row>
@@ -3296,7 +3296,7 @@
       </c>
       <c r="K61" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:55Z</t>
+          <t>2026-10-15T23:09:48Z</t>
         </is>
       </c>
     </row>
@@ -3345,7 +3345,7 @@
       </c>
       <c r="K62" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:55Z</t>
+          <t>2026-10-15T23:09:48Z</t>
         </is>
       </c>
     </row>
@@ -3394,7 +3394,7 @@
       </c>
       <c r="K63" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:55Z</t>
+          <t>2026-10-15T23:09:48Z</t>
         </is>
       </c>
     </row>
@@ -3443,7 +3443,7 @@
       </c>
       <c r="K64" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:55Z</t>
+          <t>2026-10-15T23:09:48Z</t>
         </is>
       </c>
     </row>
@@ -3492,7 +3492,7 @@
       </c>
       <c r="K65" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:55Z</t>
+          <t>2026-10-15T23:09:48Z</t>
         </is>
       </c>
     </row>
@@ -3541,7 +3541,7 @@
       </c>
       <c r="K66" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:55Z</t>
+          <t>2026-10-15T23:09:48Z</t>
         </is>
       </c>
     </row>
@@ -3590,7 +3590,7 @@
       </c>
       <c r="K67" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:55Z</t>
+          <t>2026-10-15T23:09:48Z</t>
         </is>
       </c>
     </row>
@@ -3639,7 +3639,7 @@
       </c>
       <c r="K68" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:55Z</t>
+          <t>2026-10-15T23:09:48Z</t>
         </is>
       </c>
     </row>
@@ -3688,7 +3688,7 @@
       </c>
       <c r="K69" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:55Z</t>
+          <t>2026-10-15T23:09:48Z</t>
         </is>
       </c>
     </row>
@@ -3737,7 +3737,7 @@
       </c>
       <c r="K70" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:55Z</t>
+          <t>2026-10-15T23:09:48Z</t>
         </is>
       </c>
     </row>
@@ -3786,7 +3786,7 @@
       </c>
       <c r="K71" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:55Z</t>
+          <t>2026-10-15T23:09:48Z</t>
         </is>
       </c>
     </row>
@@ -3835,7 +3835,7 @@
       </c>
       <c r="K72" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:55Z</t>
+          <t>2026-10-15T23:09:48Z</t>
         </is>
       </c>
     </row>
@@ -3884,7 +3884,7 @@
       </c>
       <c r="K73" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:55Z</t>
+          <t>2026-10-15T23:09:48Z</t>
         </is>
       </c>
     </row>
@@ -3933,7 +3933,7 @@
       </c>
       <c r="K74" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:55Z</t>
+          <t>2026-10-15T23:09:48Z</t>
         </is>
       </c>
     </row>
@@ -3982,7 +3982,7 @@
       </c>
       <c r="K75" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:55Z</t>
+          <t>2026-10-15T23:09:48Z</t>
         </is>
       </c>
     </row>
@@ -4031,7 +4031,7 @@
       </c>
       <c r="K76" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:55Z</t>
+          <t>2026-10-15T23:09:48Z</t>
         </is>
       </c>
     </row>
@@ -4080,7 +4080,7 @@
       </c>
       <c r="K77" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:55Z</t>
+          <t>2026-10-15T23:09:48Z</t>
         </is>
       </c>
     </row>
@@ -4129,7 +4129,7 @@
       </c>
       <c r="K78" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:55Z</t>
+          <t>2026-10-15T23:09:48Z</t>
         </is>
       </c>
     </row>
@@ -4178,7 +4178,7 @@
       </c>
       <c r="K79" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:55Z</t>
+          <t>2026-10-15T23:09:48Z</t>
         </is>
       </c>
     </row>
@@ -4227,7 +4227,7 @@
       </c>
       <c r="K80" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:55Z</t>
+          <t>2026-10-15T23:09:48Z</t>
         </is>
       </c>
     </row>
@@ -4276,7 +4276,7 @@
       </c>
       <c r="K81" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:55Z</t>
+          <t>2026-10-15T23:09:48Z</t>
         </is>
       </c>
     </row>
@@ -4325,7 +4325,7 @@
       </c>
       <c r="K82" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:55Z</t>
+          <t>2026-10-15T23:09:48Z</t>
         </is>
       </c>
     </row>
@@ -4374,7 +4374,7 @@
       </c>
       <c r="K83" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:55Z</t>
+          <t>2026-10-15T23:09:48Z</t>
         </is>
       </c>
     </row>
@@ -4423,7 +4423,7 @@
       </c>
       <c r="K84" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:55Z</t>
+          <t>2026-10-15T23:09:48Z</t>
         </is>
       </c>
     </row>
@@ -4472,7 +4472,7 @@
       </c>
       <c r="K85" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:55Z</t>
+          <t>2026-10-15T23:09:48Z</t>
         </is>
       </c>
     </row>
@@ -4521,7 +4521,7 @@
       </c>
       <c r="K86" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:55Z</t>
+          <t>2026-10-15T23:09:48Z</t>
         </is>
       </c>
     </row>
@@ -4570,7 +4570,7 @@
       </c>
       <c r="K87" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:55Z</t>
+          <t>2026-10-15T23:09:48Z</t>
         </is>
       </c>
     </row>
@@ -4619,7 +4619,7 @@
       </c>
       <c r="K88" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:55Z</t>
+          <t>2026-10-15T23:09:48Z</t>
         </is>
       </c>
     </row>
@@ -4668,7 +4668,7 @@
       </c>
       <c r="K89" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:55Z</t>
+          <t>2026-10-15T23:09:48Z</t>
         </is>
       </c>
     </row>
@@ -4717,7 +4717,7 @@
       </c>
       <c r="K90" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:55Z</t>
+          <t>2026-10-15T23:09:48Z</t>
         </is>
       </c>
     </row>
@@ -4766,7 +4766,7 @@
       </c>
       <c r="K91" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:55Z</t>
+          <t>2026-10-15T23:09:48Z</t>
         </is>
       </c>
     </row>
@@ -4815,7 +4815,7 @@
       </c>
       <c r="K92" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:55Z</t>
+          <t>2026-10-15T23:09:48Z</t>
         </is>
       </c>
     </row>
@@ -4864,7 +4864,7 @@
       </c>
       <c r="K93" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:55Z</t>
+          <t>2026-10-15T23:09:48Z</t>
         </is>
       </c>
     </row>
@@ -4913,7 +4913,7 @@
       </c>
       <c r="K94" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:55Z</t>
+          <t>2026-10-15T23:09:48Z</t>
         </is>
       </c>
     </row>
@@ -4962,7 +4962,7 @@
       </c>
       <c r="K95" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:55Z</t>
+          <t>2026-10-15T23:09:48Z</t>
         </is>
       </c>
     </row>
@@ -5011,7 +5011,7 @@
       </c>
       <c r="K96" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:55Z</t>
+          <t>2026-10-15T23:09:48Z</t>
         </is>
       </c>
     </row>
@@ -5060,7 +5060,7 @@
       </c>
       <c r="K97" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:55Z</t>
+          <t>2026-10-15T23:09:48Z</t>
         </is>
       </c>
     </row>
@@ -5109,7 +5109,7 @@
       </c>
       <c r="K98" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:55Z</t>
+          <t>2026-10-15T23:09:48Z</t>
         </is>
       </c>
     </row>
@@ -5158,7 +5158,7 @@
       </c>
       <c r="K99" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:55Z</t>
+          <t>2026-10-15T23:09:48Z</t>
         </is>
       </c>
     </row>
@@ -5207,7 +5207,7 @@
       </c>
       <c r="K100" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:55Z</t>
+          <t>2026-10-15T23:09:48Z</t>
         </is>
       </c>
     </row>
@@ -5256,7 +5256,7 @@
       </c>
       <c r="K101" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:55Z</t>
+          <t>2026-10-15T23:09:48Z</t>
         </is>
       </c>
     </row>
@@ -5305,7 +5305,7 @@
       </c>
       <c r="K102" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:55Z</t>
+          <t>2026-10-15T23:09:48Z</t>
         </is>
       </c>
     </row>
@@ -5354,7 +5354,7 @@
       </c>
       <c r="K103" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:55Z</t>
+          <t>2026-10-15T23:09:48Z</t>
         </is>
       </c>
     </row>
@@ -5403,7 +5403,7 @@
       </c>
       <c r="K104" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:55Z</t>
+          <t>2026-10-15T23:09:48Z</t>
         </is>
       </c>
     </row>
@@ -5452,7 +5452,7 @@
       </c>
       <c r="K105" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:55Z</t>
+          <t>2026-10-15T23:09:48Z</t>
         </is>
       </c>
     </row>
@@ -5501,7 +5501,7 @@
       </c>
       <c r="K106" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:55Z</t>
+          <t>2026-10-15T23:09:48Z</t>
         </is>
       </c>
     </row>
@@ -5550,7 +5550,7 @@
       </c>
       <c r="K107" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:55Z</t>
+          <t>2026-10-15T23:09:48Z</t>
         </is>
       </c>
     </row>
@@ -5599,7 +5599,7 @@
       </c>
       <c r="K108" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:55Z</t>
+          <t>2026-10-15T23:09:48Z</t>
         </is>
       </c>
     </row>
@@ -5648,7 +5648,7 @@
       </c>
       <c r="K109" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:55Z</t>
+          <t>2026-10-15T23:09:48Z</t>
         </is>
       </c>
     </row>
@@ -5697,7 +5697,7 @@
       </c>
       <c r="K110" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:55Z</t>
+          <t>2026-10-15T23:09:48Z</t>
         </is>
       </c>
     </row>
@@ -5746,7 +5746,7 @@
       </c>
       <c r="K111" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:55Z</t>
+          <t>2026-10-15T23:09:48Z</t>
         </is>
       </c>
     </row>
@@ -5795,7 +5795,7 @@
       </c>
       <c r="K112" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:55Z</t>
+          <t>2026-10-15T23:09:48Z</t>
         </is>
       </c>
     </row>
@@ -5844,7 +5844,7 @@
       </c>
       <c r="K113" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:55Z</t>
+          <t>2026-10-15T23:09:48Z</t>
         </is>
       </c>
     </row>
@@ -5893,7 +5893,7 @@
       </c>
       <c r="K114" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:55Z</t>
+          <t>2026-10-15T23:09:48Z</t>
         </is>
       </c>
     </row>
@@ -5942,7 +5942,7 @@
       </c>
       <c r="K115" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:55Z</t>
+          <t>2026-10-15T23:09:48Z</t>
         </is>
       </c>
     </row>
@@ -5991,7 +5991,7 @@
       </c>
       <c r="K116" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:55Z</t>
+          <t>2026-10-15T23:09:48Z</t>
         </is>
       </c>
     </row>
@@ -6040,7 +6040,7 @@
       </c>
       <c r="K117" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:55Z</t>
+          <t>2026-10-15T23:09:48Z</t>
         </is>
       </c>
     </row>
@@ -6089,7 +6089,7 @@
       </c>
       <c r="K118" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:55Z</t>
+          <t>2026-10-15T23:09:48Z</t>
         </is>
       </c>
     </row>
@@ -6138,7 +6138,7 @@
       </c>
       <c r="K119" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:55Z</t>
+          <t>2026-10-15T23:09:48Z</t>
         </is>
       </c>
     </row>
@@ -6187,7 +6187,7 @@
       </c>
       <c r="K120" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:55Z</t>
+          <t>2026-10-15T23:09:48Z</t>
         </is>
       </c>
     </row>
@@ -6236,7 +6236,7 @@
       </c>
       <c r="K121" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:55Z</t>
+          <t>2026-10-15T23:09:48Z</t>
         </is>
       </c>
     </row>
@@ -6285,7 +6285,7 @@
       </c>
       <c r="K122" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:55Z</t>
+          <t>2026-10-15T23:09:48Z</t>
         </is>
       </c>
     </row>
@@ -6334,7 +6334,7 @@
       </c>
       <c r="K123" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:55Z</t>
+          <t>2026-10-15T23:09:48Z</t>
         </is>
       </c>
     </row>
@@ -6383,7 +6383,7 @@
       </c>
       <c r="K124" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:55Z</t>
+          <t>2026-10-15T23:09:48Z</t>
         </is>
       </c>
     </row>
@@ -6432,7 +6432,7 @@
       </c>
       <c r="K125" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:55Z</t>
+          <t>2026-10-15T23:09:48Z</t>
         </is>
       </c>
     </row>
@@ -6481,7 +6481,7 @@
       </c>
       <c r="K126" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:55Z</t>
+          <t>2026-10-15T23:09:48Z</t>
         </is>
       </c>
     </row>
@@ -6530,7 +6530,7 @@
       </c>
       <c r="K127" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:55Z</t>
+          <t>2026-10-15T23:09:48Z</t>
         </is>
       </c>
     </row>
@@ -6579,7 +6579,7 @@
       </c>
       <c r="K128" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:55Z</t>
+          <t>2026-10-15T23:09:48Z</t>
         </is>
       </c>
     </row>
@@ -6628,7 +6628,7 @@
       </c>
       <c r="K129" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:55Z</t>
+          <t>2026-10-15T23:09:48Z</t>
         </is>
       </c>
     </row>
@@ -6677,7 +6677,7 @@
       </c>
       <c r="K130" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:55Z</t>
+          <t>2026-10-15T23:09:48Z</t>
         </is>
       </c>
     </row>
@@ -6726,7 +6726,7 @@
       </c>
       <c r="K131" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:55Z</t>
+          <t>2026-10-15T23:09:48Z</t>
         </is>
       </c>
     </row>
@@ -6775,7 +6775,7 @@
       </c>
       <c r="K132" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:55Z</t>
+          <t>2026-10-15T23:09:48Z</t>
         </is>
       </c>
     </row>
@@ -6824,7 +6824,7 @@
       </c>
       <c r="K133" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:55Z</t>
+          <t>2026-10-15T23:09:48Z</t>
         </is>
       </c>
     </row>
@@ -6873,7 +6873,7 @@
       </c>
       <c r="K134" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:55Z</t>
+          <t>2026-10-15T23:09:48Z</t>
         </is>
       </c>
     </row>
@@ -6922,7 +6922,7 @@
       </c>
       <c r="K135" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:55Z</t>
+          <t>2026-10-15T23:09:48Z</t>
         </is>
       </c>
     </row>
@@ -6971,7 +6971,7 @@
       </c>
       <c r="K136" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:55Z</t>
+          <t>2026-10-15T23:09:48Z</t>
         </is>
       </c>
     </row>
@@ -7020,7 +7020,7 @@
       </c>
       <c r="K137" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:55Z</t>
+          <t>2026-10-15T23:09:48Z</t>
         </is>
       </c>
     </row>
@@ -7069,7 +7069,7 @@
       </c>
       <c r="K138" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:55Z</t>
+          <t>2026-10-15T23:09:48Z</t>
         </is>
       </c>
     </row>
@@ -7118,7 +7118,7 @@
       </c>
       <c r="K139" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:55Z</t>
+          <t>2026-10-15T23:09:48Z</t>
         </is>
       </c>
     </row>
@@ -7167,7 +7167,7 @@
       </c>
       <c r="K140" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:55Z</t>
+          <t>2026-10-15T23:09:48Z</t>
         </is>
       </c>
     </row>
@@ -7216,7 +7216,7 @@
       </c>
       <c r="K141" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:55Z</t>
+          <t>2026-10-15T23:09:48Z</t>
         </is>
       </c>
     </row>
@@ -7265,7 +7265,7 @@
       </c>
       <c r="K142" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:55Z</t>
+          <t>2026-10-15T23:09:48Z</t>
         </is>
       </c>
     </row>
@@ -7314,7 +7314,7 @@
       </c>
       <c r="K143" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:55Z</t>
+          <t>2026-10-15T23:09:48Z</t>
         </is>
       </c>
     </row>
@@ -7363,7 +7363,7 @@
       </c>
       <c r="K144" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:55Z</t>
+          <t>2026-10-15T23:09:48Z</t>
         </is>
       </c>
     </row>
@@ -7412,7 +7412,7 @@
       </c>
       <c r="K145" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:55Z</t>
+          <t>2026-10-15T23:09:48Z</t>
         </is>
       </c>
     </row>
@@ -7461,7 +7461,7 @@
       </c>
       <c r="K146" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:55Z</t>
+          <t>2026-10-15T23:09:48Z</t>
         </is>
       </c>
     </row>
@@ -7510,7 +7510,7 @@
       </c>
       <c r="K147" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:55Z</t>
+          <t>2026-10-15T23:09:48Z</t>
         </is>
       </c>
     </row>
@@ -7559,7 +7559,7 @@
       </c>
       <c r="K148" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:55Z</t>
+          <t>2026-10-15T23:09:48Z</t>
         </is>
       </c>
     </row>
@@ -7608,7 +7608,7 @@
       </c>
       <c r="K149" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:55Z</t>
+          <t>2026-10-15T23:09:48Z</t>
         </is>
       </c>
     </row>
@@ -7657,7 +7657,7 @@
       </c>
       <c r="K150" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:55Z</t>
+          <t>2026-10-15T23:09:48Z</t>
         </is>
       </c>
     </row>
@@ -7706,7 +7706,7 @@
       </c>
       <c r="K151" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:55Z</t>
+          <t>2026-10-15T23:09:48Z</t>
         </is>
       </c>
     </row>
@@ -7755,7 +7755,7 @@
       </c>
       <c r="K152" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:55Z</t>
+          <t>2026-10-15T23:09:48Z</t>
         </is>
       </c>
     </row>
@@ -7804,7 +7804,7 @@
       </c>
       <c r="K153" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:55Z</t>
+          <t>2026-10-15T23:09:48Z</t>
         </is>
       </c>
     </row>
@@ -7853,7 +7853,7 @@
       </c>
       <c r="K154" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:55Z</t>
+          <t>2026-10-15T23:09:48Z</t>
         </is>
       </c>
     </row>
@@ -7902,7 +7902,7 @@
       </c>
       <c r="K155" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:55Z</t>
+          <t>2026-10-15T23:09:48Z</t>
         </is>
       </c>
     </row>
@@ -7951,7 +7951,7 @@
       </c>
       <c r="K156" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:55Z</t>
+          <t>2026-10-15T23:09:48Z</t>
         </is>
       </c>
     </row>
@@ -8000,7 +8000,7 @@
       </c>
       <c r="K157" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:55Z</t>
+          <t>2026-10-15T23:09:48Z</t>
         </is>
       </c>
     </row>
@@ -8049,7 +8049,7 @@
       </c>
       <c r="K158" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:55Z</t>
+          <t>2026-10-15T23:09:48Z</t>
         </is>
       </c>
     </row>
@@ -8098,7 +8098,7 @@
       </c>
       <c r="K159" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:55Z</t>
+          <t>2026-10-15T23:09:48Z</t>
         </is>
       </c>
     </row>
@@ -8147,7 +8147,7 @@
       </c>
       <c r="K160" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:55Z</t>
+          <t>2026-10-15T23:09:48Z</t>
         </is>
       </c>
     </row>
@@ -8196,7 +8196,7 @@
       </c>
       <c r="K161" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:55Z</t>
+          <t>2026-10-15T23:09:48Z</t>
         </is>
       </c>
     </row>
@@ -8245,7 +8245,7 @@
       </c>
       <c r="K162" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:55Z</t>
+          <t>2026-10-15T23:09:48Z</t>
         </is>
       </c>
     </row>
@@ -8294,7 +8294,7 @@
       </c>
       <c r="K163" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:55Z</t>
+          <t>2026-10-15T23:09:48Z</t>
         </is>
       </c>
     </row>
@@ -8343,7 +8343,7 @@
       </c>
       <c r="K164" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:55Z</t>
+          <t>2026-10-15T23:09:48Z</t>
         </is>
       </c>
     </row>
@@ -8392,7 +8392,7 @@
       </c>
       <c r="K165" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:55Z</t>
+          <t>2026-10-15T23:09:48Z</t>
         </is>
       </c>
     </row>
@@ -8441,7 +8441,7 @@
       </c>
       <c r="K166" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:55Z</t>
+          <t>2026-10-15T23:09:48Z</t>
         </is>
       </c>
     </row>
@@ -8490,7 +8490,7 @@
       </c>
       <c r="K167" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:55Z</t>
+          <t>2026-10-15T23:09:48Z</t>
         </is>
       </c>
     </row>
@@ -8539,7 +8539,7 @@
       </c>
       <c r="K168" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:55Z</t>
+          <t>2026-10-15T23:09:48Z</t>
         </is>
       </c>
     </row>
@@ -8588,7 +8588,7 @@
       </c>
       <c r="K169" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:55Z</t>
+          <t>2026-10-15T23:09:48Z</t>
         </is>
       </c>
     </row>
@@ -8637,7 +8637,7 @@
       </c>
       <c r="K170" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:55Z</t>
+          <t>2026-10-15T23:09:48Z</t>
         </is>
       </c>
     </row>
@@ -8686,7 +8686,7 @@
       </c>
       <c r="K171" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:55Z</t>
+          <t>2026-10-15T23:09:48Z</t>
         </is>
       </c>
     </row>
@@ -8735,7 +8735,7 @@
       </c>
       <c r="K172" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:55Z</t>
+          <t>2026-10-15T23:09:48Z</t>
         </is>
       </c>
     </row>
@@ -8784,7 +8784,7 @@
       </c>
       <c r="K173" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:55Z</t>
+          <t>2026-10-15T23:09:48Z</t>
         </is>
       </c>
     </row>
@@ -8833,7 +8833,7 @@
       </c>
       <c r="K174" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:55Z</t>
+          <t>2026-10-15T23:09:48Z</t>
         </is>
       </c>
     </row>
@@ -8882,7 +8882,7 @@
       </c>
       <c r="K175" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:55Z</t>
+          <t>2026-10-15T23:09:48Z</t>
         </is>
       </c>
     </row>
@@ -8931,7 +8931,7 @@
       </c>
       <c r="K176" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:55Z</t>
+          <t>2026-10-15T23:09:48Z</t>
         </is>
       </c>
     </row>
@@ -8980,7 +8980,7 @@
       </c>
       <c r="K177" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:55Z</t>
+          <t>2026-10-15T23:09:48Z</t>
         </is>
       </c>
     </row>
@@ -9029,7 +9029,7 @@
       </c>
       <c r="K178" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:55Z</t>
+          <t>2026-10-15T23:09:48Z</t>
         </is>
       </c>
     </row>
@@ -9078,7 +9078,7 @@
       </c>
       <c r="K179" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:55Z</t>
+          <t>2026-10-15T23:09:48Z</t>
         </is>
       </c>
     </row>
@@ -9127,7 +9127,7 @@
       </c>
       <c r="K180" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:55Z</t>
+          <t>2026-10-15T23:09:48Z</t>
         </is>
       </c>
     </row>
@@ -9176,7 +9176,7 @@
       </c>
       <c r="K181" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:55Z</t>
+          <t>2026-10-15T23:09:48Z</t>
         </is>
       </c>
     </row>
@@ -9225,7 +9225,7 @@
       </c>
       <c r="K182" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:55Z</t>
+          <t>2026-10-15T23:09:48Z</t>
         </is>
       </c>
     </row>
@@ -9274,7 +9274,7 @@
       </c>
       <c r="K183" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:55Z</t>
+          <t>2026-10-15T23:09:48Z</t>
         </is>
       </c>
     </row>
@@ -9323,7 +9323,7 @@
       </c>
       <c r="K184" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:55Z</t>
+          <t>2026-10-15T23:09:48Z</t>
         </is>
       </c>
     </row>
@@ -9372,7 +9372,7 @@
       </c>
       <c r="K185" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:55Z</t>
+          <t>2026-10-15T23:09:48Z</t>
         </is>
       </c>
     </row>
@@ -9421,7 +9421,7 @@
       </c>
       <c r="K186" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:55Z</t>
+          <t>2026-10-15T23:09:48Z</t>
         </is>
       </c>
     </row>
@@ -9470,7 +9470,7 @@
       </c>
       <c r="K187" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:55Z</t>
+          <t>2026-10-15T23:09:48Z</t>
         </is>
       </c>
     </row>
@@ -9519,7 +9519,7 @@
       </c>
       <c r="K188" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:55Z</t>
+          <t>2026-10-15T23:09:48Z</t>
         </is>
       </c>
     </row>
@@ -9568,7 +9568,7 @@
       </c>
       <c r="K189" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:55Z</t>
+          <t>2026-10-15T23:09:48Z</t>
         </is>
       </c>
     </row>
@@ -9617,7 +9617,7 @@
       </c>
       <c r="K190" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:55Z</t>
+          <t>2026-10-15T23:09:48Z</t>
         </is>
       </c>
     </row>
@@ -9666,7 +9666,7 @@
       </c>
       <c r="K191" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:55Z</t>
+          <t>2026-10-15T23:09:48Z</t>
         </is>
       </c>
     </row>
@@ -9715,7 +9715,7 @@
       </c>
       <c r="K192" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:55Z</t>
+          <t>2026-10-15T23:09:48Z</t>
         </is>
       </c>
     </row>
@@ -9764,7 +9764,7 @@
       </c>
       <c r="K193" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:55Z</t>
+          <t>2026-10-15T23:09:48Z</t>
         </is>
       </c>
     </row>
@@ -9813,7 +9813,7 @@
       </c>
       <c r="K194" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:55Z</t>
+          <t>2026-10-15T23:09:48Z</t>
         </is>
       </c>
     </row>
@@ -9862,7 +9862,7 @@
       </c>
       <c r="K195" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:55Z</t>
+          <t>2026-10-15T23:09:48Z</t>
         </is>
       </c>
     </row>
@@ -9911,7 +9911,7 @@
       </c>
       <c r="K196" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:55Z</t>
+          <t>2026-10-15T23:09:48Z</t>
         </is>
       </c>
     </row>
@@ -9960,7 +9960,7 @@
       </c>
       <c r="K197" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:55Z</t>
+          <t>2026-10-15T23:09:48Z</t>
         </is>
       </c>
     </row>
@@ -10009,7 +10009,7 @@
       </c>
       <c r="K198" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:55Z</t>
+          <t>2026-10-15T23:09:48Z</t>
         </is>
       </c>
     </row>
@@ -10058,7 +10058,7 @@
       </c>
       <c r="K199" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:55Z</t>
+          <t>2026-10-15T23:09:48Z</t>
         </is>
       </c>
     </row>
@@ -10107,7 +10107,7 @@
       </c>
       <c r="K200" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:55Z</t>
+          <t>2026-10-15T23:09:48Z</t>
         </is>
       </c>
     </row>
@@ -10156,7 +10156,7 @@
       </c>
       <c r="K201" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:55Z</t>
+          <t>2026-10-15T23:09:48Z</t>
         </is>
       </c>
     </row>
@@ -10205,7 +10205,7 @@
       </c>
       <c r="K202" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:55Z</t>
+          <t>2026-10-15T23:09:48Z</t>
         </is>
       </c>
     </row>
@@ -10254,7 +10254,7 @@
       </c>
       <c r="K203" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:55Z</t>
+          <t>2026-10-15T23:09:48Z</t>
         </is>
       </c>
     </row>
@@ -10303,7 +10303,7 @@
       </c>
       <c r="K204" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:55Z</t>
+          <t>2026-10-15T23:09:48Z</t>
         </is>
       </c>
     </row>
@@ -10352,7 +10352,7 @@
       </c>
       <c r="K205" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:55Z</t>
+          <t>2026-10-15T23:09:48Z</t>
         </is>
       </c>
     </row>
@@ -10401,7 +10401,7 @@
       </c>
       <c r="K206" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:55Z</t>
+          <t>2026-10-15T23:09:48Z</t>
         </is>
       </c>
     </row>
@@ -10450,7 +10450,7 @@
       </c>
       <c r="K207" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:55Z</t>
+          <t>2026-10-15T23:09:48Z</t>
         </is>
       </c>
     </row>
@@ -10499,7 +10499,7 @@
       </c>
       <c r="K208" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:55Z</t>
+          <t>2026-10-15T23:09:48Z</t>
         </is>
       </c>
     </row>
@@ -10548,7 +10548,7 @@
       </c>
       <c r="K209" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:55Z</t>
+          <t>2026-10-15T23:09:48Z</t>
         </is>
       </c>
     </row>
@@ -10597,7 +10597,7 @@
       </c>
       <c r="K210" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:55Z</t>
+          <t>2026-10-15T23:09:48Z</t>
         </is>
       </c>
     </row>
@@ -10646,7 +10646,7 @@
       </c>
       <c r="K211" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:55Z</t>
+          <t>2026-10-15T23:09:48Z</t>
         </is>
       </c>
     </row>
@@ -10695,7 +10695,7 @@
       </c>
       <c r="K212" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:55Z</t>
+          <t>2026-10-15T23:09:48Z</t>
         </is>
       </c>
     </row>
@@ -10744,7 +10744,7 @@
       </c>
       <c r="K213" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:55Z</t>
+          <t>2026-10-15T23:09:48Z</t>
         </is>
       </c>
     </row>
@@ -10793,7 +10793,7 @@
       </c>
       <c r="K214" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:55Z</t>
+          <t>2026-10-15T23:09:48Z</t>
         </is>
       </c>
     </row>
@@ -10842,7 +10842,7 @@
       </c>
       <c r="K215" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:55Z</t>
+          <t>2026-10-15T23:09:48Z</t>
         </is>
       </c>
     </row>
@@ -10891,7 +10891,7 @@
       </c>
       <c r="K216" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:55Z</t>
+          <t>2026-10-15T23:09:48Z</t>
         </is>
       </c>
     </row>
@@ -10940,7 +10940,7 @@
       </c>
       <c r="K217" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:55Z</t>
+          <t>2026-10-15T23:09:48Z</t>
         </is>
       </c>
     </row>
@@ -10989,7 +10989,7 @@
       </c>
       <c r="K218" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:55Z</t>
+          <t>2026-10-15T23:09:48Z</t>
         </is>
       </c>
     </row>
@@ -11038,7 +11038,7 @@
       </c>
       <c r="K219" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:55Z</t>
+          <t>2026-10-15T23:09:48Z</t>
         </is>
       </c>
     </row>
@@ -11087,7 +11087,7 @@
       </c>
       <c r="K220" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:55Z</t>
+          <t>2026-10-15T23:09:48Z</t>
         </is>
       </c>
     </row>
@@ -11136,7 +11136,7 @@
       </c>
       <c r="K221" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:55Z</t>
+          <t>2026-10-15T23:09:48Z</t>
         </is>
       </c>
     </row>
@@ -11185,7 +11185,7 @@
       </c>
       <c r="K222" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:55Z</t>
+          <t>2026-10-15T23:09:48Z</t>
         </is>
       </c>
     </row>
@@ -11234,7 +11234,7 @@
       </c>
       <c r="K223" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:55Z</t>
+          <t>2026-10-15T23:09:48Z</t>
         </is>
       </c>
     </row>
@@ -11283,7 +11283,7 @@
       </c>
       <c r="K224" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:55Z</t>
+          <t>2026-10-15T23:09:48Z</t>
         </is>
       </c>
     </row>
@@ -11332,7 +11332,7 @@
       </c>
       <c r="K225" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:55Z</t>
+          <t>2026-10-15T23:09:48Z</t>
         </is>
       </c>
     </row>
@@ -11381,7 +11381,7 @@
       </c>
       <c r="K226" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:55Z</t>
+          <t>2026-10-15T23:09:48Z</t>
         </is>
       </c>
     </row>
@@ -11430,7 +11430,7 @@
       </c>
       <c r="K227" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:55Z</t>
+          <t>2026-10-15T23:09:48Z</t>
         </is>
       </c>
     </row>
@@ -11479,7 +11479,7 @@
       </c>
       <c r="K228" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:55Z</t>
+          <t>2026-10-15T23:09:48Z</t>
         </is>
       </c>
     </row>
@@ -11528,7 +11528,7 @@
       </c>
       <c r="K229" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:55Z</t>
+          <t>2026-10-15T23:09:48Z</t>
         </is>
       </c>
     </row>
@@ -11577,7 +11577,7 @@
       </c>
       <c r="K230" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:55Z</t>
+          <t>2026-10-15T23:09:48Z</t>
         </is>
       </c>
     </row>
@@ -11626,7 +11626,7 @@
       </c>
       <c r="K231" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:55Z</t>
+          <t>2026-10-15T23:09:48Z</t>
         </is>
       </c>
     </row>
@@ -11758,7 +11758,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:55Z</t>
+          <t>2026-10-15T23:09:48Z</t>
         </is>
       </c>
     </row>
@@ -11804,7 +11804,7 @@
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>{"date": "2026-08-01", "year": 2026, "month": 8, "month_name": "Agosto", "index_value": 637409769724325.1, "monthly_variation_pct": 8.9, "unit": "Índice base diciembre 2007=100 y variación mensual %", "frequency": "monthly", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/precios_consumidor/4_5_7_2.xls", "fetched_at": "2026-10-14T23:20:55Z"}</t>
+          <t>{"date": "2026-08-01", "year": 2026, "month": 8, "month_name": "Agosto", "index_value": 637409769724325.1, "monthly_variation_pct": 8.9, "unit": "Índice base diciembre 2007=100 y variación mensual %", "frequency": "monthly", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/precios_consumidor/4_5_7_2.xls", "fetched_at": "2026-10-15T23:09:48Z"}</t>
         </is>
       </c>
     </row>

--- a/assets/data/bcv/excel/ove_bcv_inpc_nacional_mensual.xlsx
+++ b/assets/data/bcv/excel/ove_bcv_inpc_nacional_mensual.xlsx
@@ -650,7 +650,7 @@
       </c>
       <c r="K7" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15T23:09:48Z</t>
+          <t>2026-10-16T22:56:26Z</t>
         </is>
       </c>
     </row>
@@ -699,7 +699,7 @@
       </c>
       <c r="K8" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15T23:09:48Z</t>
+          <t>2026-10-16T22:56:26Z</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="K9" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15T23:09:48Z</t>
+          <t>2026-10-16T22:56:26Z</t>
         </is>
       </c>
     </row>
@@ -797,7 +797,7 @@
       </c>
       <c r="K10" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15T23:09:48Z</t>
+          <t>2026-10-16T22:56:26Z</t>
         </is>
       </c>
     </row>
@@ -846,7 +846,7 @@
       </c>
       <c r="K11" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15T23:09:48Z</t>
+          <t>2026-10-16T22:56:26Z</t>
         </is>
       </c>
     </row>
@@ -895,7 +895,7 @@
       </c>
       <c r="K12" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15T23:09:48Z</t>
+          <t>2026-10-16T22:56:26Z</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="K13" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15T23:09:48Z</t>
+          <t>2026-10-16T22:56:26Z</t>
         </is>
       </c>
     </row>
@@ -993,7 +993,7 @@
       </c>
       <c r="K14" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15T23:09:48Z</t>
+          <t>2026-10-16T22:56:26Z</t>
         </is>
       </c>
     </row>
@@ -1042,7 +1042,7 @@
       </c>
       <c r="K15" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15T23:09:48Z</t>
+          <t>2026-10-16T22:56:26Z</t>
         </is>
       </c>
     </row>
@@ -1091,7 +1091,7 @@
       </c>
       <c r="K16" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15T23:09:48Z</t>
+          <t>2026-10-16T22:56:26Z</t>
         </is>
       </c>
     </row>
@@ -1140,7 +1140,7 @@
       </c>
       <c r="K17" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15T23:09:48Z</t>
+          <t>2026-10-16T22:56:26Z</t>
         </is>
       </c>
     </row>
@@ -1189,7 +1189,7 @@
       </c>
       <c r="K18" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15T23:09:48Z</t>
+          <t>2026-10-16T22:56:26Z</t>
         </is>
       </c>
     </row>
@@ -1238,7 +1238,7 @@
       </c>
       <c r="K19" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15T23:09:48Z</t>
+          <t>2026-10-16T22:56:26Z</t>
         </is>
       </c>
     </row>
@@ -1287,7 +1287,7 @@
       </c>
       <c r="K20" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15T23:09:48Z</t>
+          <t>2026-10-16T22:56:26Z</t>
         </is>
       </c>
     </row>
@@ -1336,7 +1336,7 @@
       </c>
       <c r="K21" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15T23:09:48Z</t>
+          <t>2026-10-16T22:56:26Z</t>
         </is>
       </c>
     </row>
@@ -1385,7 +1385,7 @@
       </c>
       <c r="K22" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15T23:09:48Z</t>
+          <t>2026-10-16T22:56:26Z</t>
         </is>
       </c>
     </row>
@@ -1434,7 +1434,7 @@
       </c>
       <c r="K23" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15T23:09:48Z</t>
+          <t>2026-10-16T22:56:26Z</t>
         </is>
       </c>
     </row>
@@ -1483,7 +1483,7 @@
       </c>
       <c r="K24" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15T23:09:48Z</t>
+          <t>2026-10-16T22:56:26Z</t>
         </is>
       </c>
     </row>
@@ -1532,7 +1532,7 @@
       </c>
       <c r="K25" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15T23:09:48Z</t>
+          <t>2026-10-16T22:56:26Z</t>
         </is>
       </c>
     </row>
@@ -1581,7 +1581,7 @@
       </c>
       <c r="K26" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15T23:09:48Z</t>
+          <t>2026-10-16T22:56:26Z</t>
         </is>
       </c>
     </row>
@@ -1630,7 +1630,7 @@
       </c>
       <c r="K27" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15T23:09:48Z</t>
+          <t>2026-10-16T22:56:26Z</t>
         </is>
       </c>
     </row>
@@ -1679,7 +1679,7 @@
       </c>
       <c r="K28" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15T23:09:48Z</t>
+          <t>2026-10-16T22:56:26Z</t>
         </is>
       </c>
     </row>
@@ -1728,7 +1728,7 @@
       </c>
       <c r="K29" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15T23:09:48Z</t>
+          <t>2026-10-16T22:56:26Z</t>
         </is>
       </c>
     </row>
@@ -1777,7 +1777,7 @@
       </c>
       <c r="K30" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15T23:09:48Z</t>
+          <t>2026-10-16T22:56:26Z</t>
         </is>
       </c>
     </row>
@@ -1826,7 +1826,7 @@
       </c>
       <c r="K31" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15T23:09:48Z</t>
+          <t>2026-10-16T22:56:26Z</t>
         </is>
       </c>
     </row>
@@ -1875,7 +1875,7 @@
       </c>
       <c r="K32" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15T23:09:48Z</t>
+          <t>2026-10-16T22:56:26Z</t>
         </is>
       </c>
     </row>
@@ -1924,7 +1924,7 @@
       </c>
       <c r="K33" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15T23:09:48Z</t>
+          <t>2026-10-16T22:56:26Z</t>
         </is>
       </c>
     </row>
@@ -1973,7 +1973,7 @@
       </c>
       <c r="K34" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15T23:09:48Z</t>
+          <t>2026-10-16T22:56:26Z</t>
         </is>
       </c>
     </row>
@@ -2022,7 +2022,7 @@
       </c>
       <c r="K35" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15T23:09:48Z</t>
+          <t>2026-10-16T22:56:26Z</t>
         </is>
       </c>
     </row>
@@ -2071,7 +2071,7 @@
       </c>
       <c r="K36" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15T23:09:48Z</t>
+          <t>2026-10-16T22:56:26Z</t>
         </is>
       </c>
     </row>
@@ -2120,7 +2120,7 @@
       </c>
       <c r="K37" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15T23:09:48Z</t>
+          <t>2026-10-16T22:56:26Z</t>
         </is>
       </c>
     </row>
@@ -2169,7 +2169,7 @@
       </c>
       <c r="K38" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15T23:09:48Z</t>
+          <t>2026-10-16T22:56:26Z</t>
         </is>
       </c>
     </row>
@@ -2218,7 +2218,7 @@
       </c>
       <c r="K39" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15T23:09:48Z</t>
+          <t>2026-10-16T22:56:26Z</t>
         </is>
       </c>
     </row>
@@ -2267,7 +2267,7 @@
       </c>
       <c r="K40" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15T23:09:48Z</t>
+          <t>2026-10-16T22:56:26Z</t>
         </is>
       </c>
     </row>
@@ -2316,7 +2316,7 @@
       </c>
       <c r="K41" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15T23:09:48Z</t>
+          <t>2026-10-16T22:56:26Z</t>
         </is>
       </c>
     </row>
@@ -2365,7 +2365,7 @@
       </c>
       <c r="K42" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15T23:09:48Z</t>
+          <t>2026-10-16T22:56:26Z</t>
         </is>
       </c>
     </row>
@@ -2414,7 +2414,7 @@
       </c>
       <c r="K43" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15T23:09:48Z</t>
+          <t>2026-10-16T22:56:26Z</t>
         </is>
       </c>
     </row>
@@ -2463,7 +2463,7 @@
       </c>
       <c r="K44" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15T23:09:48Z</t>
+          <t>2026-10-16T22:56:26Z</t>
         </is>
       </c>
     </row>
@@ -2512,7 +2512,7 @@
       </c>
       <c r="K45" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15T23:09:48Z</t>
+          <t>2026-10-16T22:56:26Z</t>
         </is>
       </c>
     </row>
@@ -2561,7 +2561,7 @@
       </c>
       <c r="K46" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15T23:09:48Z</t>
+          <t>2026-10-16T22:56:26Z</t>
         </is>
       </c>
     </row>
@@ -2610,7 +2610,7 @@
       </c>
       <c r="K47" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15T23:09:48Z</t>
+          <t>2026-10-16T22:56:26Z</t>
         </is>
       </c>
     </row>
@@ -2659,7 +2659,7 @@
       </c>
       <c r="K48" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15T23:09:48Z</t>
+          <t>2026-10-16T22:56:26Z</t>
         </is>
       </c>
     </row>
@@ -2708,7 +2708,7 @@
       </c>
       <c r="K49" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15T23:09:48Z</t>
+          <t>2026-10-16T22:56:26Z</t>
         </is>
       </c>
     </row>
@@ -2757,7 +2757,7 @@
       </c>
       <c r="K50" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15T23:09:48Z</t>
+          <t>2026-10-16T22:56:26Z</t>
         </is>
       </c>
     </row>
@@ -2806,7 +2806,7 @@
       </c>
       <c r="K51" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15T23:09:48Z</t>
+          <t>2026-10-16T22:56:26Z</t>
         </is>
       </c>
     </row>
@@ -2855,7 +2855,7 @@
       </c>
       <c r="K52" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15T23:09:48Z</t>
+          <t>2026-10-16T22:56:26Z</t>
         </is>
       </c>
     </row>
@@ -2904,7 +2904,7 @@
       </c>
       <c r="K53" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15T23:09:48Z</t>
+          <t>2026-10-16T22:56:26Z</t>
         </is>
       </c>
     </row>
@@ -2953,7 +2953,7 @@
       </c>
       <c r="K54" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15T23:09:48Z</t>
+          <t>2026-10-16T22:56:26Z</t>
         </is>
       </c>
     </row>
@@ -3002,7 +3002,7 @@
       </c>
       <c r="K55" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15T23:09:48Z</t>
+          <t>2026-10-16T22:56:26Z</t>
         </is>
       </c>
     </row>
@@ -3051,7 +3051,7 @@
       </c>
       <c r="K56" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15T23:09:48Z</t>
+          <t>2026-10-16T22:56:26Z</t>
         </is>
       </c>
     </row>
@@ -3100,7 +3100,7 @@
       </c>
       <c r="K57" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15T23:09:48Z</t>
+          <t>2026-10-16T22:56:26Z</t>
         </is>
       </c>
     </row>
@@ -3149,7 +3149,7 @@
       </c>
       <c r="K58" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15T23:09:48Z</t>
+          <t>2026-10-16T22:56:26Z</t>
         </is>
       </c>
     </row>
@@ -3198,7 +3198,7 @@
       </c>
       <c r="K59" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15T23:09:48Z</t>
+          <t>2026-10-16T22:56:26Z</t>
         </is>
       </c>
     </row>
@@ -3247,7 +3247,7 @@
       </c>
       <c r="K60" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15T23:09:48Z</t>
+          <t>2026-10-16T22:56:26Z</t>
         </is>
       </c>
     </row>
@@ -3296,7 +3296,7 @@
       </c>
       <c r="K61" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15T23:09:48Z</t>
+          <t>2026-10-16T22:56:26Z</t>
         </is>
       </c>
     </row>
@@ -3345,7 +3345,7 @@
       </c>
       <c r="K62" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15T23:09:48Z</t>
+          <t>2026-10-16T22:56:26Z</t>
         </is>
       </c>
     </row>
@@ -3394,7 +3394,7 @@
       </c>
       <c r="K63" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15T23:09:48Z</t>
+          <t>2026-10-16T22:56:26Z</t>
         </is>
       </c>
     </row>
@@ -3443,7 +3443,7 @@
       </c>
       <c r="K64" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15T23:09:48Z</t>
+          <t>2026-10-16T22:56:26Z</t>
         </is>
       </c>
     </row>
@@ -3492,7 +3492,7 @@
       </c>
       <c r="K65" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15T23:09:48Z</t>
+          <t>2026-10-16T22:56:26Z</t>
         </is>
       </c>
     </row>
@@ -3541,7 +3541,7 @@
       </c>
       <c r="K66" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15T23:09:48Z</t>
+          <t>2026-10-16T22:56:26Z</t>
         </is>
       </c>
     </row>
@@ -3590,7 +3590,7 @@
       </c>
       <c r="K67" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15T23:09:48Z</t>
+          <t>2026-10-16T22:56:26Z</t>
         </is>
       </c>
     </row>
@@ -3639,7 +3639,7 @@
       </c>
       <c r="K68" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15T23:09:48Z</t>
+          <t>2026-10-16T22:56:26Z</t>
         </is>
       </c>
     </row>
@@ -3688,7 +3688,7 @@
       </c>
       <c r="K69" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15T23:09:48Z</t>
+          <t>2026-10-16T22:56:26Z</t>
         </is>
       </c>
     </row>
@@ -3737,7 +3737,7 @@
       </c>
       <c r="K70" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15T23:09:48Z</t>
+          <t>2026-10-16T22:56:26Z</t>
         </is>
       </c>
     </row>
@@ -3786,7 +3786,7 @@
       </c>
       <c r="K71" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15T23:09:48Z</t>
+          <t>2026-10-16T22:56:26Z</t>
         </is>
       </c>
     </row>
@@ -3835,7 +3835,7 @@
       </c>
       <c r="K72" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15T23:09:48Z</t>
+          <t>2026-10-16T22:56:26Z</t>
         </is>
       </c>
     </row>
@@ -3884,7 +3884,7 @@
       </c>
       <c r="K73" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15T23:09:48Z</t>
+          <t>2026-10-16T22:56:26Z</t>
         </is>
       </c>
     </row>
@@ -3933,7 +3933,7 @@
       </c>
       <c r="K74" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15T23:09:48Z</t>
+          <t>2026-10-16T22:56:26Z</t>
         </is>
       </c>
     </row>
@@ -3982,7 +3982,7 @@
       </c>
       <c r="K75" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15T23:09:48Z</t>
+          <t>2026-10-16T22:56:26Z</t>
         </is>
       </c>
     </row>
@@ -4031,7 +4031,7 @@
       </c>
       <c r="K76" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15T23:09:48Z</t>
+          <t>2026-10-16T22:56:26Z</t>
         </is>
       </c>
     </row>
@@ -4080,7 +4080,7 @@
       </c>
       <c r="K77" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15T23:09:48Z</t>
+          <t>2026-10-16T22:56:26Z</t>
         </is>
       </c>
     </row>
@@ -4129,7 +4129,7 @@
       </c>
       <c r="K78" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15T23:09:48Z</t>
+          <t>2026-10-16T22:56:26Z</t>
         </is>
       </c>
     </row>
@@ -4178,7 +4178,7 @@
       </c>
       <c r="K79" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15T23:09:48Z</t>
+          <t>2026-10-16T22:56:26Z</t>
         </is>
       </c>
     </row>
@@ -4227,7 +4227,7 @@
       </c>
       <c r="K80" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15T23:09:48Z</t>
+          <t>2026-10-16T22:56:26Z</t>
         </is>
       </c>
     </row>
@@ -4276,7 +4276,7 @@
       </c>
       <c r="K81" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15T23:09:48Z</t>
+          <t>2026-10-16T22:56:26Z</t>
         </is>
       </c>
     </row>
@@ -4325,7 +4325,7 @@
       </c>
       <c r="K82" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15T23:09:48Z</t>
+          <t>2026-10-16T22:56:26Z</t>
         </is>
       </c>
     </row>
@@ -4374,7 +4374,7 @@
       </c>
       <c r="K83" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15T23:09:48Z</t>
+          <t>2026-10-16T22:56:26Z</t>
         </is>
       </c>
     </row>
@@ -4423,7 +4423,7 @@
       </c>
       <c r="K84" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15T23:09:48Z</t>
+          <t>2026-10-16T22:56:26Z</t>
         </is>
       </c>
     </row>
@@ -4472,7 +4472,7 @@
       </c>
       <c r="K85" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15T23:09:48Z</t>
+          <t>2026-10-16T22:56:26Z</t>
         </is>
       </c>
     </row>
@@ -4521,7 +4521,7 @@
       </c>
       <c r="K86" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15T23:09:48Z</t>
+          <t>2026-10-16T22:56:26Z</t>
         </is>
       </c>
     </row>
@@ -4570,7 +4570,7 @@
       </c>
       <c r="K87" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15T23:09:48Z</t>
+          <t>2026-10-16T22:56:26Z</t>
         </is>
       </c>
     </row>
@@ -4619,7 +4619,7 @@
       </c>
       <c r="K88" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15T23:09:48Z</t>
+          <t>2026-10-16T22:56:26Z</t>
         </is>
       </c>
     </row>
@@ -4668,7 +4668,7 @@
       </c>
       <c r="K89" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15T23:09:48Z</t>
+          <t>2026-10-16T22:56:26Z</t>
         </is>
       </c>
     </row>
@@ -4717,7 +4717,7 @@
       </c>
       <c r="K90" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15T23:09:48Z</t>
+          <t>2026-10-16T22:56:26Z</t>
         </is>
       </c>
     </row>
@@ -4766,7 +4766,7 @@
       </c>
       <c r="K91" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15T23:09:48Z</t>
+          <t>2026-10-16T22:56:26Z</t>
         </is>
       </c>
     </row>
@@ -4815,7 +4815,7 @@
       </c>
       <c r="K92" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15T23:09:48Z</t>
+          <t>2026-10-16T22:56:26Z</t>
         </is>
       </c>
     </row>
@@ -4864,7 +4864,7 @@
       </c>
       <c r="K93" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15T23:09:48Z</t>
+          <t>2026-10-16T22:56:26Z</t>
         </is>
       </c>
     </row>
@@ -4913,7 +4913,7 @@
       </c>
       <c r="K94" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15T23:09:48Z</t>
+          <t>2026-10-16T22:56:26Z</t>
         </is>
       </c>
     </row>
@@ -4962,7 +4962,7 @@
       </c>
       <c r="K95" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15T23:09:48Z</t>
+          <t>2026-10-16T22:56:26Z</t>
         </is>
       </c>
     </row>
@@ -5011,7 +5011,7 @@
       </c>
       <c r="K96" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15T23:09:48Z</t>
+          <t>2026-10-16T22:56:26Z</t>
         </is>
       </c>
     </row>
@@ -5060,7 +5060,7 @@
       </c>
       <c r="K97" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15T23:09:48Z</t>
+          <t>2026-10-16T22:56:26Z</t>
         </is>
       </c>
     </row>
@@ -5109,7 +5109,7 @@
       </c>
       <c r="K98" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15T23:09:48Z</t>
+          <t>2026-10-16T22:56:26Z</t>
         </is>
       </c>
     </row>
@@ -5158,7 +5158,7 @@
       </c>
       <c r="K99" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15T23:09:48Z</t>
+          <t>2026-10-16T22:56:26Z</t>
         </is>
       </c>
     </row>
@@ -5207,7 +5207,7 @@
       </c>
       <c r="K100" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15T23:09:48Z</t>
+          <t>2026-10-16T22:56:26Z</t>
         </is>
       </c>
     </row>
@@ -5256,7 +5256,7 @@
       </c>
       <c r="K101" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15T23:09:48Z</t>
+          <t>2026-10-16T22:56:26Z</t>
         </is>
       </c>
     </row>
@@ -5305,7 +5305,7 @@
       </c>
       <c r="K102" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15T23:09:48Z</t>
+          <t>2026-10-16T22:56:26Z</t>
         </is>
       </c>
     </row>
@@ -5354,7 +5354,7 @@
       </c>
       <c r="K103" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15T23:09:48Z</t>
+          <t>2026-10-16T22:56:26Z</t>
         </is>
       </c>
     </row>
@@ -5403,7 +5403,7 @@
       </c>
       <c r="K104" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15T23:09:48Z</t>
+          <t>2026-10-16T22:56:26Z</t>
         </is>
       </c>
     </row>
@@ -5452,7 +5452,7 @@
       </c>
       <c r="K105" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15T23:09:48Z</t>
+          <t>2026-10-16T22:56:26Z</t>
         </is>
       </c>
     </row>
@@ -5501,7 +5501,7 @@
       </c>
       <c r="K106" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15T23:09:48Z</t>
+          <t>2026-10-16T22:56:26Z</t>
         </is>
       </c>
     </row>
@@ -5550,7 +5550,7 @@
       </c>
       <c r="K107" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15T23:09:48Z</t>
+          <t>2026-10-16T22:56:26Z</t>
         </is>
       </c>
     </row>
@@ -5599,7 +5599,7 @@
       </c>
       <c r="K108" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15T23:09:48Z</t>
+          <t>2026-10-16T22:56:26Z</t>
         </is>
       </c>
     </row>
@@ -5648,7 +5648,7 @@
       </c>
       <c r="K109" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15T23:09:48Z</t>
+          <t>2026-10-16T22:56:26Z</t>
         </is>
       </c>
     </row>
@@ -5697,7 +5697,7 @@
       </c>
       <c r="K110" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15T23:09:48Z</t>
+          <t>2026-10-16T22:56:26Z</t>
         </is>
       </c>
     </row>
@@ -5746,7 +5746,7 @@
       </c>
       <c r="K111" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15T23:09:48Z</t>
+          <t>2026-10-16T22:56:26Z</t>
         </is>
       </c>
     </row>
@@ -5795,7 +5795,7 @@
       </c>
       <c r="K112" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15T23:09:48Z</t>
+          <t>2026-10-16T22:56:26Z</t>
         </is>
       </c>
     </row>
@@ -5844,7 +5844,7 @@
       </c>
       <c r="K113" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15T23:09:48Z</t>
+          <t>2026-10-16T22:56:26Z</t>
         </is>
       </c>
     </row>
@@ -5893,7 +5893,7 @@
       </c>
       <c r="K114" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15T23:09:48Z</t>
+          <t>2026-10-16T22:56:26Z</t>
         </is>
       </c>
     </row>
@@ -5942,7 +5942,7 @@
       </c>
       <c r="K115" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15T23:09:48Z</t>
+          <t>2026-10-16T22:56:26Z</t>
         </is>
       </c>
     </row>
@@ -5991,7 +5991,7 @@
       </c>
       <c r="K116" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15T23:09:48Z</t>
+          <t>2026-10-16T22:56:26Z</t>
         </is>
       </c>
     </row>
@@ -6040,7 +6040,7 @@
       </c>
       <c r="K117" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15T23:09:48Z</t>
+          <t>2026-10-16T22:56:26Z</t>
         </is>
       </c>
     </row>
@@ -6089,7 +6089,7 @@
       </c>
       <c r="K118" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15T23:09:48Z</t>
+          <t>2026-10-16T22:56:26Z</t>
         </is>
       </c>
     </row>
@@ -6138,7 +6138,7 @@
       </c>
       <c r="K119" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15T23:09:48Z</t>
+          <t>2026-10-16T22:56:26Z</t>
         </is>
       </c>
     </row>
@@ -6187,7 +6187,7 @@
       </c>
       <c r="K120" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15T23:09:48Z</t>
+          <t>2026-10-16T22:56:26Z</t>
         </is>
       </c>
     </row>
@@ -6236,7 +6236,7 @@
       </c>
       <c r="K121" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15T23:09:48Z</t>
+          <t>2026-10-16T22:56:26Z</t>
         </is>
       </c>
     </row>
@@ -6285,7 +6285,7 @@
       </c>
       <c r="K122" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15T23:09:48Z</t>
+          <t>2026-10-16T22:56:26Z</t>
         </is>
       </c>
     </row>
@@ -6334,7 +6334,7 @@
       </c>
       <c r="K123" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15T23:09:48Z</t>
+          <t>2026-10-16T22:56:26Z</t>
         </is>
       </c>
     </row>
@@ -6383,7 +6383,7 @@
       </c>
       <c r="K124" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15T23:09:48Z</t>
+          <t>2026-10-16T22:56:26Z</t>
         </is>
       </c>
     </row>
@@ -6432,7 +6432,7 @@
       </c>
       <c r="K125" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15T23:09:48Z</t>
+          <t>2026-10-16T22:56:26Z</t>
         </is>
       </c>
     </row>
@@ -6481,7 +6481,7 @@
       </c>
       <c r="K126" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15T23:09:48Z</t>
+          <t>2026-10-16T22:56:26Z</t>
         </is>
       </c>
     </row>
@@ -6530,7 +6530,7 @@
       </c>
       <c r="K127" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15T23:09:48Z</t>
+          <t>2026-10-16T22:56:26Z</t>
         </is>
       </c>
     </row>
@@ -6579,7 +6579,7 @@
       </c>
       <c r="K128" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15T23:09:48Z</t>
+          <t>2026-10-16T22:56:26Z</t>
         </is>
       </c>
     </row>
@@ -6628,7 +6628,7 @@
       </c>
       <c r="K129" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15T23:09:48Z</t>
+          <t>2026-10-16T22:56:26Z</t>
         </is>
       </c>
     </row>
@@ -6677,7 +6677,7 @@
       </c>
       <c r="K130" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15T23:09:48Z</t>
+          <t>2026-10-16T22:56:26Z</t>
         </is>
       </c>
     </row>
@@ -6726,7 +6726,7 @@
       </c>
       <c r="K131" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15T23:09:48Z</t>
+          <t>2026-10-16T22:56:26Z</t>
         </is>
       </c>
     </row>
@@ -6775,7 +6775,7 @@
       </c>
       <c r="K132" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15T23:09:48Z</t>
+          <t>2026-10-16T22:56:26Z</t>
         </is>
       </c>
     </row>
@@ -6824,7 +6824,7 @@
       </c>
       <c r="K133" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15T23:09:48Z</t>
+          <t>2026-10-16T22:56:26Z</t>
         </is>
       </c>
     </row>
@@ -6873,7 +6873,7 @@
       </c>
       <c r="K134" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15T23:09:48Z</t>
+          <t>2026-10-16T22:56:26Z</t>
         </is>
       </c>
     </row>
@@ -6922,7 +6922,7 @@
       </c>
       <c r="K135" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15T23:09:48Z</t>
+          <t>2026-10-16T22:56:26Z</t>
         </is>
       </c>
     </row>
@@ -6971,7 +6971,7 @@
       </c>
       <c r="K136" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15T23:09:48Z</t>
+          <t>2026-10-16T22:56:26Z</t>
         </is>
       </c>
     </row>
@@ -7020,7 +7020,7 @@
       </c>
       <c r="K137" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15T23:09:48Z</t>
+          <t>2026-10-16T22:56:26Z</t>
         </is>
       </c>
     </row>
@@ -7069,7 +7069,7 @@
       </c>
       <c r="K138" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15T23:09:48Z</t>
+          <t>2026-10-16T22:56:26Z</t>
         </is>
       </c>
     </row>
@@ -7118,7 +7118,7 @@
       </c>
       <c r="K139" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15T23:09:48Z</t>
+          <t>2026-10-16T22:56:26Z</t>
         </is>
       </c>
     </row>
@@ -7167,7 +7167,7 @@
       </c>
       <c r="K140" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15T23:09:48Z</t>
+          <t>2026-10-16T22:56:26Z</t>
         </is>
       </c>
     </row>
@@ -7216,7 +7216,7 @@
       </c>
       <c r="K141" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15T23:09:48Z</t>
+          <t>2026-10-16T22:56:26Z</t>
         </is>
       </c>
     </row>
@@ -7265,7 +7265,7 @@
       </c>
       <c r="K142" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15T23:09:48Z</t>
+          <t>2026-10-16T22:56:26Z</t>
         </is>
       </c>
     </row>
@@ -7314,7 +7314,7 @@
       </c>
       <c r="K143" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15T23:09:48Z</t>
+          <t>2026-10-16T22:56:26Z</t>
         </is>
       </c>
     </row>
@@ -7363,7 +7363,7 @@
       </c>
       <c r="K144" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15T23:09:48Z</t>
+          <t>2026-10-16T22:56:26Z</t>
         </is>
       </c>
     </row>
@@ -7412,7 +7412,7 @@
       </c>
       <c r="K145" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15T23:09:48Z</t>
+          <t>2026-10-16T22:56:26Z</t>
         </is>
       </c>
     </row>
@@ -7461,7 +7461,7 @@
       </c>
       <c r="K146" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15T23:09:48Z</t>
+          <t>2026-10-16T22:56:26Z</t>
         </is>
       </c>
     </row>
@@ -7510,7 +7510,7 @@
       </c>
       <c r="K147" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15T23:09:48Z</t>
+          <t>2026-10-16T22:56:26Z</t>
         </is>
       </c>
     </row>
@@ -7559,7 +7559,7 @@
       </c>
       <c r="K148" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15T23:09:48Z</t>
+          <t>2026-10-16T22:56:26Z</t>
         </is>
       </c>
     </row>
@@ -7608,7 +7608,7 @@
       </c>
       <c r="K149" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15T23:09:48Z</t>
+          <t>2026-10-16T22:56:26Z</t>
         </is>
       </c>
     </row>
@@ -7657,7 +7657,7 @@
       </c>
       <c r="K150" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15T23:09:48Z</t>
+          <t>2026-10-16T22:56:26Z</t>
         </is>
       </c>
     </row>
@@ -7706,7 +7706,7 @@
       </c>
       <c r="K151" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15T23:09:48Z</t>
+          <t>2026-10-16T22:56:26Z</t>
         </is>
       </c>
     </row>
@@ -7755,7 +7755,7 @@
       </c>
       <c r="K152" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15T23:09:48Z</t>
+          <t>2026-10-16T22:56:26Z</t>
         </is>
       </c>
     </row>
@@ -7804,7 +7804,7 @@
       </c>
       <c r="K153" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15T23:09:48Z</t>
+          <t>2026-10-16T22:56:26Z</t>
         </is>
       </c>
     </row>
@@ -7853,7 +7853,7 @@
       </c>
       <c r="K154" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15T23:09:48Z</t>
+          <t>2026-10-16T22:56:26Z</t>
         </is>
       </c>
     </row>
@@ -7902,7 +7902,7 @@
       </c>
       <c r="K155" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15T23:09:48Z</t>
+          <t>2026-10-16T22:56:26Z</t>
         </is>
       </c>
     </row>
@@ -7951,7 +7951,7 @@
       </c>
       <c r="K156" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15T23:09:48Z</t>
+          <t>2026-10-16T22:56:26Z</t>
         </is>
       </c>
     </row>
@@ -8000,7 +8000,7 @@
       </c>
       <c r="K157" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15T23:09:48Z</t>
+          <t>2026-10-16T22:56:26Z</t>
         </is>
       </c>
     </row>
@@ -8049,7 +8049,7 @@
       </c>
       <c r="K158" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15T23:09:48Z</t>
+          <t>2026-10-16T22:56:26Z</t>
         </is>
       </c>
     </row>
@@ -8098,7 +8098,7 @@
       </c>
       <c r="K159" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15T23:09:48Z</t>
+          <t>2026-10-16T22:56:26Z</t>
         </is>
       </c>
     </row>
@@ -8147,7 +8147,7 @@
       </c>
       <c r="K160" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15T23:09:48Z</t>
+          <t>2026-10-16T22:56:26Z</t>
         </is>
       </c>
     </row>
@@ -8196,7 +8196,7 @@
       </c>
       <c r="K161" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15T23:09:48Z</t>
+          <t>2026-10-16T22:56:26Z</t>
         </is>
       </c>
     </row>
@@ -8245,7 +8245,7 @@
       </c>
       <c r="K162" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15T23:09:48Z</t>
+          <t>2026-10-16T22:56:26Z</t>
         </is>
       </c>
     </row>
@@ -8294,7 +8294,7 @@
       </c>
       <c r="K163" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15T23:09:48Z</t>
+          <t>2026-10-16T22:56:26Z</t>
         </is>
       </c>
     </row>
@@ -8343,7 +8343,7 @@
       </c>
       <c r="K164" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15T23:09:48Z</t>
+          <t>2026-10-16T22:56:26Z</t>
         </is>
       </c>
     </row>
@@ -8392,7 +8392,7 @@
       </c>
       <c r="K165" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15T23:09:48Z</t>
+          <t>2026-10-16T22:56:26Z</t>
         </is>
       </c>
     </row>
@@ -8441,7 +8441,7 @@
       </c>
       <c r="K166" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15T23:09:48Z</t>
+          <t>2026-10-16T22:56:26Z</t>
         </is>
       </c>
     </row>
@@ -8490,7 +8490,7 @@
       </c>
       <c r="K167" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15T23:09:48Z</t>
+          <t>2026-10-16T22:56:26Z</t>
         </is>
       </c>
     </row>
@@ -8539,7 +8539,7 @@
       </c>
       <c r="K168" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15T23:09:48Z</t>
+          <t>2026-10-16T22:56:26Z</t>
         </is>
       </c>
     </row>
@@ -8588,7 +8588,7 @@
       </c>
       <c r="K169" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15T23:09:48Z</t>
+          <t>2026-10-16T22:56:26Z</t>
         </is>
       </c>
     </row>
@@ -8637,7 +8637,7 @@
       </c>
       <c r="K170" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15T23:09:48Z</t>
+          <t>2026-10-16T22:56:26Z</t>
         </is>
       </c>
     </row>
@@ -8686,7 +8686,7 @@
       </c>
       <c r="K171" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15T23:09:48Z</t>
+          <t>2026-10-16T22:56:26Z</t>
         </is>
       </c>
     </row>
@@ -8735,7 +8735,7 @@
       </c>
       <c r="K172" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15T23:09:48Z</t>
+          <t>2026-10-16T22:56:26Z</t>
         </is>
       </c>
     </row>
@@ -8784,7 +8784,7 @@
       </c>
       <c r="K173" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15T23:09:48Z</t>
+          <t>2026-10-16T22:56:26Z</t>
         </is>
       </c>
     </row>
@@ -8833,7 +8833,7 @@
       </c>
       <c r="K174" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15T23:09:48Z</t>
+          <t>2026-10-16T22:56:26Z</t>
         </is>
       </c>
     </row>
@@ -8882,7 +8882,7 @@
       </c>
       <c r="K175" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15T23:09:48Z</t>
+          <t>2026-10-16T22:56:26Z</t>
         </is>
       </c>
     </row>
@@ -8931,7 +8931,7 @@
       </c>
       <c r="K176" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15T23:09:48Z</t>
+          <t>2026-10-16T22:56:26Z</t>
         </is>
       </c>
     </row>
@@ -8980,7 +8980,7 @@
       </c>
       <c r="K177" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15T23:09:48Z</t>
+          <t>2026-10-16T22:56:26Z</t>
         </is>
       </c>
     </row>
@@ -9029,7 +9029,7 @@
       </c>
       <c r="K178" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15T23:09:48Z</t>
+          <t>2026-10-16T22:56:26Z</t>
         </is>
       </c>
     </row>
@@ -9078,7 +9078,7 @@
       </c>
       <c r="K179" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15T23:09:48Z</t>
+          <t>2026-10-16T22:56:26Z</t>
         </is>
       </c>
     </row>
@@ -9127,7 +9127,7 @@
       </c>
       <c r="K180" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15T23:09:48Z</t>
+          <t>2026-10-16T22:56:26Z</t>
         </is>
       </c>
     </row>
@@ -9176,7 +9176,7 @@
       </c>
       <c r="K181" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15T23:09:48Z</t>
+          <t>2026-10-16T22:56:26Z</t>
         </is>
       </c>
     </row>
@@ -9225,7 +9225,7 @@
       </c>
       <c r="K182" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15T23:09:48Z</t>
+          <t>2026-10-16T22:56:26Z</t>
         </is>
       </c>
     </row>
@@ -9274,7 +9274,7 @@
       </c>
       <c r="K183" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15T23:09:48Z</t>
+          <t>2026-10-16T22:56:26Z</t>
         </is>
       </c>
     </row>
@@ -9323,7 +9323,7 @@
       </c>
       <c r="K184" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15T23:09:48Z</t>
+          <t>2026-10-16T22:56:26Z</t>
         </is>
       </c>
     </row>
@@ -9372,7 +9372,7 @@
       </c>
       <c r="K185" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15T23:09:48Z</t>
+          <t>2026-10-16T22:56:26Z</t>
         </is>
       </c>
     </row>
@@ -9421,7 +9421,7 @@
       </c>
       <c r="K186" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15T23:09:48Z</t>
+          <t>2026-10-16T22:56:26Z</t>
         </is>
       </c>
     </row>
@@ -9470,7 +9470,7 @@
       </c>
       <c r="K187" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15T23:09:48Z</t>
+          <t>2026-10-16T22:56:26Z</t>
         </is>
       </c>
     </row>
@@ -9519,7 +9519,7 @@
       </c>
       <c r="K188" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15T23:09:48Z</t>
+          <t>2026-10-16T22:56:26Z</t>
         </is>
       </c>
     </row>
@@ -9568,7 +9568,7 @@
       </c>
       <c r="K189" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15T23:09:48Z</t>
+          <t>2026-10-16T22:56:26Z</t>
         </is>
       </c>
     </row>
@@ -9617,7 +9617,7 @@
       </c>
       <c r="K190" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15T23:09:48Z</t>
+          <t>2026-10-16T22:56:26Z</t>
         </is>
       </c>
     </row>
@@ -9666,7 +9666,7 @@
       </c>
       <c r="K191" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15T23:09:48Z</t>
+          <t>2026-10-16T22:56:26Z</t>
         </is>
       </c>
     </row>
@@ -9715,7 +9715,7 @@
       </c>
       <c r="K192" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15T23:09:48Z</t>
+          <t>2026-10-16T22:56:26Z</t>
         </is>
       </c>
     </row>
@@ -9764,7 +9764,7 @@
       </c>
       <c r="K193" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15T23:09:48Z</t>
+          <t>2026-10-16T22:56:26Z</t>
         </is>
       </c>
     </row>
@@ -9813,7 +9813,7 @@
       </c>
       <c r="K194" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15T23:09:48Z</t>
+          <t>2026-10-16T22:56:26Z</t>
         </is>
       </c>
     </row>
@@ -9862,7 +9862,7 @@
       </c>
       <c r="K195" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15T23:09:48Z</t>
+          <t>2026-10-16T22:56:26Z</t>
         </is>
       </c>
     </row>
@@ -9911,7 +9911,7 @@
       </c>
       <c r="K196" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15T23:09:48Z</t>
+          <t>2026-10-16T22:56:26Z</t>
         </is>
       </c>
     </row>
@@ -9960,7 +9960,7 @@
       </c>
       <c r="K197" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15T23:09:48Z</t>
+          <t>2026-10-16T22:56:26Z</t>
         </is>
       </c>
     </row>
@@ -10009,7 +10009,7 @@
       </c>
       <c r="K198" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15T23:09:48Z</t>
+          <t>2026-10-16T22:56:26Z</t>
         </is>
       </c>
     </row>
@@ -10058,7 +10058,7 @@
       </c>
       <c r="K199" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15T23:09:48Z</t>
+          <t>2026-10-16T22:56:26Z</t>
         </is>
       </c>
     </row>
@@ -10107,7 +10107,7 @@
       </c>
       <c r="K200" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15T23:09:48Z</t>
+          <t>2026-10-16T22:56:26Z</t>
         </is>
       </c>
     </row>
@@ -10156,7 +10156,7 @@
       </c>
       <c r="K201" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15T23:09:48Z</t>
+          <t>2026-10-16T22:56:26Z</t>
         </is>
       </c>
     </row>
@@ -10205,7 +10205,7 @@
       </c>
       <c r="K202" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15T23:09:48Z</t>
+          <t>2026-10-16T22:56:26Z</t>
         </is>
       </c>
     </row>
@@ -10254,7 +10254,7 @@
       </c>
       <c r="K203" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15T23:09:48Z</t>
+          <t>2026-10-16T22:56:26Z</t>
         </is>
       </c>
     </row>
@@ -10303,7 +10303,7 @@
       </c>
       <c r="K204" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15T23:09:48Z</t>
+          <t>2026-10-16T22:56:26Z</t>
         </is>
       </c>
     </row>
@@ -10352,7 +10352,7 @@
       </c>
       <c r="K205" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15T23:09:48Z</t>
+          <t>2026-10-16T22:56:26Z</t>
         </is>
       </c>
     </row>
@@ -10401,7 +10401,7 @@
       </c>
       <c r="K206" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15T23:09:48Z</t>
+          <t>2026-10-16T22:56:26Z</t>
         </is>
       </c>
     </row>
@@ -10450,7 +10450,7 @@
       </c>
       <c r="K207" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15T23:09:48Z</t>
+          <t>2026-10-16T22:56:26Z</t>
         </is>
       </c>
     </row>
@@ -10499,7 +10499,7 @@
       </c>
       <c r="K208" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15T23:09:48Z</t>
+          <t>2026-10-16T22:56:26Z</t>
         </is>
       </c>
     </row>
@@ -10548,7 +10548,7 @@
       </c>
       <c r="K209" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15T23:09:48Z</t>
+          <t>2026-10-16T22:56:26Z</t>
         </is>
       </c>
     </row>
@@ -10597,7 +10597,7 @@
       </c>
       <c r="K210" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15T23:09:48Z</t>
+          <t>2026-10-16T22:56:26Z</t>
         </is>
       </c>
     </row>
@@ -10646,7 +10646,7 @@
       </c>
       <c r="K211" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15T23:09:48Z</t>
+          <t>2026-10-16T22:56:26Z</t>
         </is>
       </c>
     </row>
@@ -10695,7 +10695,7 @@
       </c>
       <c r="K212" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15T23:09:48Z</t>
+          <t>2026-10-16T22:56:26Z</t>
         </is>
       </c>
     </row>
@@ -10744,7 +10744,7 @@
       </c>
       <c r="K213" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15T23:09:48Z</t>
+          <t>2026-10-16T22:56:26Z</t>
         </is>
       </c>
     </row>
@@ -10793,7 +10793,7 @@
       </c>
       <c r="K214" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15T23:09:48Z</t>
+          <t>2026-10-16T22:56:26Z</t>
         </is>
       </c>
     </row>
@@ -10842,7 +10842,7 @@
       </c>
       <c r="K215" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15T23:09:48Z</t>
+          <t>2026-10-16T22:56:26Z</t>
         </is>
       </c>
     </row>
@@ -10891,7 +10891,7 @@
       </c>
       <c r="K216" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15T23:09:48Z</t>
+          <t>2026-10-16T22:56:26Z</t>
         </is>
       </c>
     </row>
@@ -10940,7 +10940,7 @@
       </c>
       <c r="K217" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15T23:09:48Z</t>
+          <t>2026-10-16T22:56:26Z</t>
         </is>
       </c>
     </row>
@@ -10989,7 +10989,7 @@
       </c>
       <c r="K218" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15T23:09:48Z</t>
+          <t>2026-10-16T22:56:26Z</t>
         </is>
       </c>
     </row>
@@ -11038,7 +11038,7 @@
       </c>
       <c r="K219" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15T23:09:48Z</t>
+          <t>2026-10-16T22:56:26Z</t>
         </is>
       </c>
     </row>
@@ -11087,7 +11087,7 @@
       </c>
       <c r="K220" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15T23:09:48Z</t>
+          <t>2026-10-16T22:56:26Z</t>
         </is>
       </c>
     </row>
@@ -11136,7 +11136,7 @@
       </c>
       <c r="K221" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15T23:09:48Z</t>
+          <t>2026-10-16T22:56:26Z</t>
         </is>
       </c>
     </row>
@@ -11185,7 +11185,7 @@
       </c>
       <c r="K222" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15T23:09:48Z</t>
+          <t>2026-10-16T22:56:26Z</t>
         </is>
       </c>
     </row>
@@ -11234,7 +11234,7 @@
       </c>
       <c r="K223" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15T23:09:48Z</t>
+          <t>2026-10-16T22:56:26Z</t>
         </is>
       </c>
     </row>
@@ -11283,7 +11283,7 @@
       </c>
       <c r="K224" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15T23:09:48Z</t>
+          <t>2026-10-16T22:56:26Z</t>
         </is>
       </c>
     </row>
@@ -11332,7 +11332,7 @@
       </c>
       <c r="K225" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15T23:09:48Z</t>
+          <t>2026-10-16T22:56:26Z</t>
         </is>
       </c>
     </row>
@@ -11381,7 +11381,7 @@
       </c>
       <c r="K226" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15T23:09:48Z</t>
+          <t>2026-10-16T22:56:26Z</t>
         </is>
       </c>
     </row>
@@ -11430,7 +11430,7 @@
       </c>
       <c r="K227" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15T23:09:48Z</t>
+          <t>2026-10-16T22:56:26Z</t>
         </is>
       </c>
     </row>
@@ -11479,7 +11479,7 @@
       </c>
       <c r="K228" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15T23:09:48Z</t>
+          <t>2026-10-16T22:56:26Z</t>
         </is>
       </c>
     </row>
@@ -11528,7 +11528,7 @@
       </c>
       <c r="K229" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15T23:09:48Z</t>
+          <t>2026-10-16T22:56:26Z</t>
         </is>
       </c>
     </row>
@@ -11577,7 +11577,7 @@
       </c>
       <c r="K230" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15T23:09:48Z</t>
+          <t>2026-10-16T22:56:26Z</t>
         </is>
       </c>
     </row>
@@ -11626,7 +11626,7 @@
       </c>
       <c r="K231" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15T23:09:48Z</t>
+          <t>2026-10-16T22:56:26Z</t>
         </is>
       </c>
     </row>
@@ -11758,7 +11758,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15T23:09:48Z</t>
+          <t>2026-10-16T22:56:26Z</t>
         </is>
       </c>
     </row>
@@ -11804,7 +11804,7 @@
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>{"date": "2026-08-01", "year": 2026, "month": 8, "month_name": "Agosto", "index_value": 637409769724325.1, "monthly_variation_pct": 8.9, "unit": "Índice base diciembre 2007=100 y variación mensual %", "frequency": "monthly", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/precios_consumidor/4_5_7_2.xls", "fetched_at": "2026-10-15T23:09:48Z"}</t>
+          <t>{"date": "2026-08-01", "year": 2026, "month": 8, "month_name": "Agosto", "index_value": 637409769724325.1, "monthly_variation_pct": 8.9, "unit": "Índice base diciembre 2007=100 y variación mensual %", "frequency": "monthly", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/precios_consumidor/4_5_7_2.xls", "fetched_at": "2026-10-16T22:56:26Z"}</t>
         </is>
       </c>
     </row>

--- a/assets/data/bcv/excel/ove_bcv_inpc_nacional_mensual.xlsx
+++ b/assets/data/bcv/excel/ove_bcv_inpc_nacional_mensual.xlsx
@@ -650,7 +650,7 @@
       </c>
       <c r="K7" s="4" t="inlineStr">
         <is>
-          <t>2026-10-16T22:56:26Z</t>
+          <t>2026-10-17T16:23:40Z</t>
         </is>
       </c>
     </row>
@@ -699,7 +699,7 @@
       </c>
       <c r="K8" s="4" t="inlineStr">
         <is>
-          <t>2026-10-16T22:56:26Z</t>
+          <t>2026-10-17T16:23:40Z</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="K9" s="4" t="inlineStr">
         <is>
-          <t>2026-10-16T22:56:26Z</t>
+          <t>2026-10-17T16:23:40Z</t>
         </is>
       </c>
     </row>
@@ -797,7 +797,7 @@
       </c>
       <c r="K10" s="4" t="inlineStr">
         <is>
-          <t>2026-10-16T22:56:26Z</t>
+          <t>2026-10-17T16:23:40Z</t>
         </is>
       </c>
     </row>
@@ -846,7 +846,7 @@
       </c>
       <c r="K11" s="4" t="inlineStr">
         <is>
-          <t>2026-10-16T22:56:26Z</t>
+          <t>2026-10-17T16:23:40Z</t>
         </is>
       </c>
     </row>
@@ -895,7 +895,7 @@
       </c>
       <c r="K12" s="4" t="inlineStr">
         <is>
-          <t>2026-10-16T22:56:26Z</t>
+          <t>2026-10-17T16:23:40Z</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="K13" s="4" t="inlineStr">
         <is>
-          <t>2026-10-16T22:56:26Z</t>
+          <t>2026-10-17T16:23:40Z</t>
         </is>
       </c>
     </row>
@@ -993,7 +993,7 @@
       </c>
       <c r="K14" s="4" t="inlineStr">
         <is>
-          <t>2026-10-16T22:56:26Z</t>
+          <t>2026-10-17T16:23:40Z</t>
         </is>
       </c>
     </row>
@@ -1042,7 +1042,7 @@
       </c>
       <c r="K15" s="4" t="inlineStr">
         <is>
-          <t>2026-10-16T22:56:26Z</t>
+          <t>2026-10-17T16:23:40Z</t>
         </is>
       </c>
     </row>
@@ -1091,7 +1091,7 @@
       </c>
       <c r="K16" s="4" t="inlineStr">
         <is>
-          <t>2026-10-16T22:56:26Z</t>
+          <t>2026-10-17T16:23:40Z</t>
         </is>
       </c>
     </row>
@@ -1140,7 +1140,7 @@
       </c>
       <c r="K17" s="4" t="inlineStr">
         <is>
-          <t>2026-10-16T22:56:26Z</t>
+          <t>2026-10-17T16:23:40Z</t>
         </is>
       </c>
     </row>
@@ -1189,7 +1189,7 @@
       </c>
       <c r="K18" s="4" t="inlineStr">
         <is>
-          <t>2026-10-16T22:56:26Z</t>
+          <t>2026-10-17T16:23:40Z</t>
         </is>
       </c>
     </row>
@@ -1238,7 +1238,7 @@
       </c>
       <c r="K19" s="4" t="inlineStr">
         <is>
-          <t>2026-10-16T22:56:26Z</t>
+          <t>2026-10-17T16:23:40Z</t>
         </is>
       </c>
     </row>
@@ -1287,7 +1287,7 @@
       </c>
       <c r="K20" s="4" t="inlineStr">
         <is>
-          <t>2026-10-16T22:56:26Z</t>
+          <t>2026-10-17T16:23:40Z</t>
         </is>
       </c>
     </row>
@@ -1336,7 +1336,7 @@
       </c>
       <c r="K21" s="4" t="inlineStr">
         <is>
-          <t>2026-10-16T22:56:26Z</t>
+          <t>2026-10-17T16:23:40Z</t>
         </is>
       </c>
     </row>
@@ -1385,7 +1385,7 @@
       </c>
       <c r="K22" s="4" t="inlineStr">
         <is>
-          <t>2026-10-16T22:56:26Z</t>
+          <t>2026-10-17T16:23:40Z</t>
         </is>
       </c>
     </row>
@@ -1434,7 +1434,7 @@
       </c>
       <c r="K23" s="4" t="inlineStr">
         <is>
-          <t>2026-10-16T22:56:26Z</t>
+          <t>2026-10-17T16:23:40Z</t>
         </is>
       </c>
     </row>
@@ -1483,7 +1483,7 @@
       </c>
       <c r="K24" s="4" t="inlineStr">
         <is>
-          <t>2026-10-16T22:56:26Z</t>
+          <t>2026-10-17T16:23:40Z</t>
         </is>
       </c>
     </row>
@@ -1532,7 +1532,7 @@
       </c>
       <c r="K25" s="4" t="inlineStr">
         <is>
-          <t>2026-10-16T22:56:26Z</t>
+          <t>2026-10-17T16:23:40Z</t>
         </is>
       </c>
     </row>
@@ -1581,7 +1581,7 @@
       </c>
       <c r="K26" s="4" t="inlineStr">
         <is>
-          <t>2026-10-16T22:56:26Z</t>
+          <t>2026-10-17T16:23:40Z</t>
         </is>
       </c>
     </row>
@@ -1630,7 +1630,7 @@
       </c>
       <c r="K27" s="4" t="inlineStr">
         <is>
-          <t>2026-10-16T22:56:26Z</t>
+          <t>2026-10-17T16:23:40Z</t>
         </is>
       </c>
     </row>
@@ -1679,7 +1679,7 @@
       </c>
       <c r="K28" s="4" t="inlineStr">
         <is>
-          <t>2026-10-16T22:56:26Z</t>
+          <t>2026-10-17T16:23:40Z</t>
         </is>
       </c>
     </row>
@@ -1728,7 +1728,7 @@
       </c>
       <c r="K29" s="4" t="inlineStr">
         <is>
-          <t>2026-10-16T22:56:26Z</t>
+          <t>2026-10-17T16:23:40Z</t>
         </is>
       </c>
     </row>
@@ -1777,7 +1777,7 @@
       </c>
       <c r="K30" s="4" t="inlineStr">
         <is>
-          <t>2026-10-16T22:56:26Z</t>
+          <t>2026-10-17T16:23:40Z</t>
         </is>
       </c>
     </row>
@@ -1826,7 +1826,7 @@
       </c>
       <c r="K31" s="4" t="inlineStr">
         <is>
-          <t>2026-10-16T22:56:26Z</t>
+          <t>2026-10-17T16:23:40Z</t>
         </is>
       </c>
     </row>
@@ -1875,7 +1875,7 @@
       </c>
       <c r="K32" s="4" t="inlineStr">
         <is>
-          <t>2026-10-16T22:56:26Z</t>
+          <t>2026-10-17T16:23:40Z</t>
         </is>
       </c>
     </row>
@@ -1924,7 +1924,7 @@
       </c>
       <c r="K33" s="4" t="inlineStr">
         <is>
-          <t>2026-10-16T22:56:26Z</t>
+          <t>2026-10-17T16:23:40Z</t>
         </is>
       </c>
     </row>
@@ -1973,7 +1973,7 @@
       </c>
       <c r="K34" s="4" t="inlineStr">
         <is>
-          <t>2026-10-16T22:56:26Z</t>
+          <t>2026-10-17T16:23:40Z</t>
         </is>
       </c>
     </row>
@@ -2022,7 +2022,7 @@
       </c>
       <c r="K35" s="4" t="inlineStr">
         <is>
-          <t>2026-10-16T22:56:26Z</t>
+          <t>2026-10-17T16:23:40Z</t>
         </is>
       </c>
     </row>
@@ -2071,7 +2071,7 @@
       </c>
       <c r="K36" s="4" t="inlineStr">
         <is>
-          <t>2026-10-16T22:56:26Z</t>
+          <t>2026-10-17T16:23:40Z</t>
         </is>
       </c>
     </row>
@@ -2120,7 +2120,7 @@
       </c>
       <c r="K37" s="4" t="inlineStr">
         <is>
-          <t>2026-10-16T22:56:26Z</t>
+          <t>2026-10-17T16:23:40Z</t>
         </is>
       </c>
     </row>
@@ -2169,7 +2169,7 @@
       </c>
       <c r="K38" s="4" t="inlineStr">
         <is>
-          <t>2026-10-16T22:56:26Z</t>
+          <t>2026-10-17T16:23:40Z</t>
         </is>
       </c>
     </row>
@@ -2218,7 +2218,7 @@
       </c>
       <c r="K39" s="4" t="inlineStr">
         <is>
-          <t>2026-10-16T22:56:26Z</t>
+          <t>2026-10-17T16:23:40Z</t>
         </is>
       </c>
     </row>
@@ -2267,7 +2267,7 @@
       </c>
       <c r="K40" s="4" t="inlineStr">
         <is>
-          <t>2026-10-16T22:56:26Z</t>
+          <t>2026-10-17T16:23:40Z</t>
         </is>
       </c>
     </row>
@@ -2316,7 +2316,7 @@
       </c>
       <c r="K41" s="4" t="inlineStr">
         <is>
-          <t>2026-10-16T22:56:26Z</t>
+          <t>2026-10-17T16:23:40Z</t>
         </is>
       </c>
     </row>
@@ -2365,7 +2365,7 @@
       </c>
       <c r="K42" s="4" t="inlineStr">
         <is>
-          <t>2026-10-16T22:56:26Z</t>
+          <t>2026-10-17T16:23:40Z</t>
         </is>
       </c>
     </row>
@@ -2414,7 +2414,7 @@
       </c>
       <c r="K43" s="4" t="inlineStr">
         <is>
-          <t>2026-10-16T22:56:26Z</t>
+          <t>2026-10-17T16:23:40Z</t>
         </is>
       </c>
     </row>
@@ -2463,7 +2463,7 @@
       </c>
       <c r="K44" s="4" t="inlineStr">
         <is>
-          <t>2026-10-16T22:56:26Z</t>
+          <t>2026-10-17T16:23:40Z</t>
         </is>
       </c>
     </row>
@@ -2512,7 +2512,7 @@
       </c>
       <c r="K45" s="4" t="inlineStr">
         <is>
-          <t>2026-10-16T22:56:26Z</t>
+          <t>2026-10-17T16:23:40Z</t>
         </is>
       </c>
     </row>
@@ -2561,7 +2561,7 @@
       </c>
       <c r="K46" s="4" t="inlineStr">
         <is>
-          <t>2026-10-16T22:56:26Z</t>
+          <t>2026-10-17T16:23:40Z</t>
         </is>
       </c>
     </row>
@@ -2610,7 +2610,7 @@
       </c>
       <c r="K47" s="4" t="inlineStr">
         <is>
-          <t>2026-10-16T22:56:26Z</t>
+          <t>2026-10-17T16:23:40Z</t>
         </is>
       </c>
     </row>
@@ -2659,7 +2659,7 @@
       </c>
       <c r="K48" s="4" t="inlineStr">
         <is>
-          <t>2026-10-16T22:56:26Z</t>
+          <t>2026-10-17T16:23:40Z</t>
         </is>
       </c>
     </row>
@@ -2708,7 +2708,7 @@
       </c>
       <c r="K49" s="4" t="inlineStr">
         <is>
-          <t>2026-10-16T22:56:26Z</t>
+          <t>2026-10-17T16:23:40Z</t>
         </is>
       </c>
     </row>
@@ -2757,7 +2757,7 @@
       </c>
       <c r="K50" s="4" t="inlineStr">
         <is>
-          <t>2026-10-16T22:56:26Z</t>
+          <t>2026-10-17T16:23:40Z</t>
         </is>
       </c>
     </row>
@@ -2806,7 +2806,7 @@
       </c>
       <c r="K51" s="4" t="inlineStr">
         <is>
-          <t>2026-10-16T22:56:26Z</t>
+          <t>2026-10-17T16:23:40Z</t>
         </is>
       </c>
     </row>
@@ -2855,7 +2855,7 @@
       </c>
       <c r="K52" s="4" t="inlineStr">
         <is>
-          <t>2026-10-16T22:56:26Z</t>
+          <t>2026-10-17T16:23:40Z</t>
         </is>
       </c>
     </row>
@@ -2904,7 +2904,7 @@
       </c>
       <c r="K53" s="4" t="inlineStr">
         <is>
-          <t>2026-10-16T22:56:26Z</t>
+          <t>2026-10-17T16:23:40Z</t>
         </is>
       </c>
     </row>
@@ -2953,7 +2953,7 @@
       </c>
       <c r="K54" s="4" t="inlineStr">
         <is>
-          <t>2026-10-16T22:56:26Z</t>
+          <t>2026-10-17T16:23:40Z</t>
         </is>
       </c>
     </row>
@@ -3002,7 +3002,7 @@
       </c>
       <c r="K55" s="4" t="inlineStr">
         <is>
-          <t>2026-10-16T22:56:26Z</t>
+          <t>2026-10-17T16:23:40Z</t>
         </is>
       </c>
     </row>
@@ -3051,7 +3051,7 @@
       </c>
       <c r="K56" s="4" t="inlineStr">
         <is>
-          <t>2026-10-16T22:56:26Z</t>
+          <t>2026-10-17T16:23:40Z</t>
         </is>
       </c>
     </row>
@@ -3100,7 +3100,7 @@
       </c>
       <c r="K57" s="4" t="inlineStr">
         <is>
-          <t>2026-10-16T22:56:26Z</t>
+          <t>2026-10-17T16:23:40Z</t>
         </is>
       </c>
     </row>
@@ -3149,7 +3149,7 @@
       </c>
       <c r="K58" s="4" t="inlineStr">
         <is>
-          <t>2026-10-16T22:56:26Z</t>
+          <t>2026-10-17T16:23:40Z</t>
         </is>
       </c>
     </row>
@@ -3198,7 +3198,7 @@
       </c>
       <c r="K59" s="4" t="inlineStr">
         <is>
-          <t>2026-10-16T22:56:26Z</t>
+          <t>2026-10-17T16:23:40Z</t>
         </is>
       </c>
     </row>
@@ -3247,7 +3247,7 @@
       </c>
       <c r="K60" s="4" t="inlineStr">
         <is>
-          <t>2026-10-16T22:56:26Z</t>
+          <t>2026-10-17T16:23:40Z</t>
         </is>
       </c>
     </row>
@@ -3296,7 +3296,7 @@
       </c>
       <c r="K61" s="4" t="inlineStr">
         <is>
-          <t>2026-10-16T22:56:26Z</t>
+          <t>2026-10-17T16:23:40Z</t>
         </is>
       </c>
     </row>
@@ -3345,7 +3345,7 @@
       </c>
       <c r="K62" s="4" t="inlineStr">
         <is>
-          <t>2026-10-16T22:56:26Z</t>
+          <t>2026-10-17T16:23:40Z</t>
         </is>
       </c>
     </row>
@@ -3394,7 +3394,7 @@
       </c>
       <c r="K63" s="4" t="inlineStr">
         <is>
-          <t>2026-10-16T22:56:26Z</t>
+          <t>2026-10-17T16:23:40Z</t>
         </is>
       </c>
     </row>
@@ -3443,7 +3443,7 @@
       </c>
       <c r="K64" s="4" t="inlineStr">
         <is>
-          <t>2026-10-16T22:56:26Z</t>
+          <t>2026-10-17T16:23:40Z</t>
         </is>
       </c>
     </row>
@@ -3492,7 +3492,7 @@
       </c>
       <c r="K65" s="4" t="inlineStr">
         <is>
-          <t>2026-10-16T22:56:26Z</t>
+          <t>2026-10-17T16:23:40Z</t>
         </is>
       </c>
     </row>
@@ -3541,7 +3541,7 @@
       </c>
       <c r="K66" s="4" t="inlineStr">
         <is>
-          <t>2026-10-16T22:56:26Z</t>
+          <t>2026-10-17T16:23:40Z</t>
         </is>
       </c>
     </row>
@@ -3590,7 +3590,7 @@
       </c>
       <c r="K67" s="4" t="inlineStr">
         <is>
-          <t>2026-10-16T22:56:26Z</t>
+          <t>2026-10-17T16:23:40Z</t>
         </is>
       </c>
     </row>
@@ -3639,7 +3639,7 @@
       </c>
       <c r="K68" s="4" t="inlineStr">
         <is>
-          <t>2026-10-16T22:56:26Z</t>
+          <t>2026-10-17T16:23:40Z</t>
         </is>
       </c>
     </row>
@@ -3688,7 +3688,7 @@
       </c>
       <c r="K69" s="4" t="inlineStr">
         <is>
-          <t>2026-10-16T22:56:26Z</t>
+          <t>2026-10-17T16:23:40Z</t>
         </is>
       </c>
     </row>
@@ -3737,7 +3737,7 @@
       </c>
       <c r="K70" s="4" t="inlineStr">
         <is>
-          <t>2026-10-16T22:56:26Z</t>
+          <t>2026-10-17T16:23:40Z</t>
         </is>
       </c>
     </row>
@@ -3786,7 +3786,7 @@
       </c>
       <c r="K71" s="4" t="inlineStr">
         <is>
-          <t>2026-10-16T22:56:26Z</t>
+          <t>2026-10-17T16:23:40Z</t>
         </is>
       </c>
     </row>
@@ -3835,7 +3835,7 @@
       </c>
       <c r="K72" s="4" t="inlineStr">
         <is>
-          <t>2026-10-16T22:56:26Z</t>
+          <t>2026-10-17T16:23:40Z</t>
         </is>
       </c>
     </row>
@@ -3884,7 +3884,7 @@
       </c>
       <c r="K73" s="4" t="inlineStr">
         <is>
-          <t>2026-10-16T22:56:26Z</t>
+          <t>2026-10-17T16:23:40Z</t>
         </is>
       </c>
     </row>
@@ -3933,7 +3933,7 @@
       </c>
       <c r="K74" s="4" t="inlineStr">
         <is>
-          <t>2026-10-16T22:56:26Z</t>
+          <t>2026-10-17T16:23:40Z</t>
         </is>
       </c>
     </row>
@@ -3982,7 +3982,7 @@
       </c>
       <c r="K75" s="4" t="inlineStr">
         <is>
-          <t>2026-10-16T22:56:26Z</t>
+          <t>2026-10-17T16:23:40Z</t>
         </is>
       </c>
     </row>
@@ -4031,7 +4031,7 @@
       </c>
       <c r="K76" s="4" t="inlineStr">
         <is>
-          <t>2026-10-16T22:56:26Z</t>
+          <t>2026-10-17T16:23:40Z</t>
         </is>
       </c>
     </row>
@@ -4080,7 +4080,7 @@
       </c>
       <c r="K77" s="4" t="inlineStr">
         <is>
-          <t>2026-10-16T22:56:26Z</t>
+          <t>2026-10-17T16:23:40Z</t>
         </is>
       </c>
     </row>
@@ -4129,7 +4129,7 @@
       </c>
       <c r="K78" s="4" t="inlineStr">
         <is>
-          <t>2026-10-16T22:56:26Z</t>
+          <t>2026-10-17T16:23:40Z</t>
         </is>
       </c>
     </row>
@@ -4178,7 +4178,7 @@
       </c>
       <c r="K79" s="4" t="inlineStr">
         <is>
-          <t>2026-10-16T22:56:26Z</t>
+          <t>2026-10-17T16:23:40Z</t>
         </is>
       </c>
     </row>
@@ -4227,7 +4227,7 @@
       </c>
       <c r="K80" s="4" t="inlineStr">
         <is>
-          <t>2026-10-16T22:56:26Z</t>
+          <t>2026-10-17T16:23:40Z</t>
         </is>
       </c>
     </row>
@@ -4276,7 +4276,7 @@
       </c>
       <c r="K81" s="4" t="inlineStr">
         <is>
-          <t>2026-10-16T22:56:26Z</t>
+          <t>2026-10-17T16:23:40Z</t>
         </is>
       </c>
     </row>
@@ -4325,7 +4325,7 @@
       </c>
       <c r="K82" s="4" t="inlineStr">
         <is>
-          <t>2026-10-16T22:56:26Z</t>
+          <t>2026-10-17T16:23:40Z</t>
         </is>
       </c>
     </row>
@@ -4374,7 +4374,7 @@
       </c>
       <c r="K83" s="4" t="inlineStr">
         <is>
-          <t>2026-10-16T22:56:26Z</t>
+          <t>2026-10-17T16:23:40Z</t>
         </is>
       </c>
     </row>
@@ -4423,7 +4423,7 @@
       </c>
       <c r="K84" s="4" t="inlineStr">
         <is>
-          <t>2026-10-16T22:56:26Z</t>
+          <t>2026-10-17T16:23:40Z</t>
         </is>
       </c>
     </row>
@@ -4472,7 +4472,7 @@
       </c>
       <c r="K85" s="4" t="inlineStr">
         <is>
-          <t>2026-10-16T22:56:26Z</t>
+          <t>2026-10-17T16:23:40Z</t>
         </is>
       </c>
     </row>
@@ -4521,7 +4521,7 @@
       </c>
       <c r="K86" s="4" t="inlineStr">
         <is>
-          <t>2026-10-16T22:56:26Z</t>
+          <t>2026-10-17T16:23:40Z</t>
         </is>
       </c>
     </row>
@@ -4570,7 +4570,7 @@
       </c>
       <c r="K87" s="4" t="inlineStr">
         <is>
-          <t>2026-10-16T22:56:26Z</t>
+          <t>2026-10-17T16:23:40Z</t>
         </is>
       </c>
     </row>
@@ -4619,7 +4619,7 @@
       </c>
       <c r="K88" s="4" t="inlineStr">
         <is>
-          <t>2026-10-16T22:56:26Z</t>
+          <t>2026-10-17T16:23:40Z</t>
         </is>
       </c>
     </row>
@@ -4668,7 +4668,7 @@
       </c>
       <c r="K89" s="4" t="inlineStr">
         <is>
-          <t>2026-10-16T22:56:26Z</t>
+          <t>2026-10-17T16:23:40Z</t>
         </is>
       </c>
     </row>
@@ -4717,7 +4717,7 @@
       </c>
       <c r="K90" s="4" t="inlineStr">
         <is>
-          <t>2026-10-16T22:56:26Z</t>
+          <t>2026-10-17T16:23:40Z</t>
         </is>
       </c>
     </row>
@@ -4766,7 +4766,7 @@
       </c>
       <c r="K91" s="4" t="inlineStr">
         <is>
-          <t>2026-10-16T22:56:26Z</t>
+          <t>2026-10-17T16:23:40Z</t>
         </is>
       </c>
     </row>
@@ -4815,7 +4815,7 @@
       </c>
       <c r="K92" s="4" t="inlineStr">
         <is>
-          <t>2026-10-16T22:56:26Z</t>
+          <t>2026-10-17T16:23:40Z</t>
         </is>
       </c>
     </row>
@@ -4864,7 +4864,7 @@
       </c>
       <c r="K93" s="4" t="inlineStr">
         <is>
-          <t>2026-10-16T22:56:26Z</t>
+          <t>2026-10-17T16:23:40Z</t>
         </is>
       </c>
     </row>
@@ -4913,7 +4913,7 @@
       </c>
       <c r="K94" s="4" t="inlineStr">
         <is>
-          <t>2026-10-16T22:56:26Z</t>
+          <t>2026-10-17T16:23:40Z</t>
         </is>
       </c>
     </row>
@@ -4962,7 +4962,7 @@
       </c>
       <c r="K95" s="4" t="inlineStr">
         <is>
-          <t>2026-10-16T22:56:26Z</t>
+          <t>2026-10-17T16:23:40Z</t>
         </is>
       </c>
     </row>
@@ -5011,7 +5011,7 @@
       </c>
       <c r="K96" s="4" t="inlineStr">
         <is>
-          <t>2026-10-16T22:56:26Z</t>
+          <t>2026-10-17T16:23:40Z</t>
         </is>
       </c>
     </row>
@@ -5060,7 +5060,7 @@
       </c>
       <c r="K97" s="4" t="inlineStr">
         <is>
-          <t>2026-10-16T22:56:26Z</t>
+          <t>2026-10-17T16:23:40Z</t>
         </is>
       </c>
     </row>
@@ -5109,7 +5109,7 @@
       </c>
       <c r="K98" s="4" t="inlineStr">
         <is>
-          <t>2026-10-16T22:56:26Z</t>
+          <t>2026-10-17T16:23:40Z</t>
         </is>
       </c>
     </row>
@@ -5158,7 +5158,7 @@
       </c>
       <c r="K99" s="4" t="inlineStr">
         <is>
-          <t>2026-10-16T22:56:26Z</t>
+          <t>2026-10-17T16:23:40Z</t>
         </is>
       </c>
     </row>
@@ -5207,7 +5207,7 @@
       </c>
       <c r="K100" s="4" t="inlineStr">
         <is>
-          <t>2026-10-16T22:56:26Z</t>
+          <t>2026-10-17T16:23:40Z</t>
         </is>
       </c>
     </row>
@@ -5256,7 +5256,7 @@
       </c>
       <c r="K101" s="4" t="inlineStr">
         <is>
-          <t>2026-10-16T22:56:26Z</t>
+          <t>2026-10-17T16:23:40Z</t>
         </is>
       </c>
     </row>
@@ -5305,7 +5305,7 @@
       </c>
       <c r="K102" s="4" t="inlineStr">
         <is>
-          <t>2026-10-16T22:56:26Z</t>
+          <t>2026-10-17T16:23:40Z</t>
         </is>
       </c>
     </row>
@@ -5354,7 +5354,7 @@
       </c>
       <c r="K103" s="4" t="inlineStr">
         <is>
-          <t>2026-10-16T22:56:26Z</t>
+          <t>2026-10-17T16:23:40Z</t>
         </is>
       </c>
     </row>
@@ -5403,7 +5403,7 @@
       </c>
       <c r="K104" s="4" t="inlineStr">
         <is>
-          <t>2026-10-16T22:56:26Z</t>
+          <t>2026-10-17T16:23:40Z</t>
         </is>
       </c>
     </row>
@@ -5452,7 +5452,7 @@
       </c>
       <c r="K105" s="4" t="inlineStr">
         <is>
-          <t>2026-10-16T22:56:26Z</t>
+          <t>2026-10-17T16:23:40Z</t>
         </is>
       </c>
     </row>
@@ -5501,7 +5501,7 @@
       </c>
       <c r="K106" s="4" t="inlineStr">
         <is>
-          <t>2026-10-16T22:56:26Z</t>
+          <t>2026-10-17T16:23:40Z</t>
         </is>
       </c>
     </row>
@@ -5550,7 +5550,7 @@
       </c>
       <c r="K107" s="4" t="inlineStr">
         <is>
-          <t>2026-10-16T22:56:26Z</t>
+          <t>2026-10-17T16:23:40Z</t>
         </is>
       </c>
     </row>
@@ -5599,7 +5599,7 @@
       </c>
       <c r="K108" s="4" t="inlineStr">
         <is>
-          <t>2026-10-16T22:56:26Z</t>
+          <t>2026-10-17T16:23:40Z</t>
         </is>
       </c>
     </row>
@@ -5648,7 +5648,7 @@
       </c>
       <c r="K109" s="4" t="inlineStr">
         <is>
-          <t>2026-10-16T22:56:26Z</t>
+          <t>2026-10-17T16:23:40Z</t>
         </is>
       </c>
     </row>
@@ -5697,7 +5697,7 @@
       </c>
       <c r="K110" s="4" t="inlineStr">
         <is>
-          <t>2026-10-16T22:56:26Z</t>
+          <t>2026-10-17T16:23:40Z</t>
         </is>
       </c>
     </row>
@@ -5746,7 +5746,7 @@
       </c>
       <c r="K111" s="4" t="inlineStr">
         <is>
-          <t>2026-10-16T22:56:26Z</t>
+          <t>2026-10-17T16:23:40Z</t>
         </is>
       </c>
     </row>
@@ -5795,7 +5795,7 @@
       </c>
       <c r="K112" s="4" t="inlineStr">
         <is>
-          <t>2026-10-16T22:56:26Z</t>
+          <t>2026-10-17T16:23:40Z</t>
         </is>
       </c>
     </row>
@@ -5844,7 +5844,7 @@
       </c>
       <c r="K113" s="4" t="inlineStr">
         <is>
-          <t>2026-10-16T22:56:26Z</t>
+          <t>2026-10-17T16:23:40Z</t>
         </is>
       </c>
     </row>
@@ -5893,7 +5893,7 @@
       </c>
       <c r="K114" s="4" t="inlineStr">
         <is>
-          <t>2026-10-16T22:56:26Z</t>
+          <t>2026-10-17T16:23:40Z</t>
         </is>
       </c>
     </row>
@@ -5942,7 +5942,7 @@
       </c>
       <c r="K115" s="4" t="inlineStr">
         <is>
-          <t>2026-10-16T22:56:26Z</t>
+          <t>2026-10-17T16:23:40Z</t>
         </is>
       </c>
     </row>
@@ -5991,7 +5991,7 @@
       </c>
       <c r="K116" s="4" t="inlineStr">
         <is>
-          <t>2026-10-16T22:56:26Z</t>
+          <t>2026-10-17T16:23:40Z</t>
         </is>
       </c>
     </row>
@@ -6040,7 +6040,7 @@
       </c>
       <c r="K117" s="4" t="inlineStr">
         <is>
-          <t>2026-10-16T22:56:26Z</t>
+          <t>2026-10-17T16:23:40Z</t>
         </is>
       </c>
     </row>
@@ -6089,7 +6089,7 @@
       </c>
       <c r="K118" s="4" t="inlineStr">
         <is>
-          <t>2026-10-16T22:56:26Z</t>
+          <t>2026-10-17T16:23:40Z</t>
         </is>
       </c>
     </row>
@@ -6138,7 +6138,7 @@
       </c>
       <c r="K119" s="4" t="inlineStr">
         <is>
-          <t>2026-10-16T22:56:26Z</t>
+          <t>2026-10-17T16:23:40Z</t>
         </is>
       </c>
     </row>
@@ -6187,7 +6187,7 @@
       </c>
       <c r="K120" s="4" t="inlineStr">
         <is>
-          <t>2026-10-16T22:56:26Z</t>
+          <t>2026-10-17T16:23:40Z</t>
         </is>
       </c>
     </row>
@@ -6236,7 +6236,7 @@
       </c>
       <c r="K121" s="4" t="inlineStr">
         <is>
-          <t>2026-10-16T22:56:26Z</t>
+          <t>2026-10-17T16:23:40Z</t>
         </is>
       </c>
     </row>
@@ -6285,7 +6285,7 @@
       </c>
       <c r="K122" s="4" t="inlineStr">
         <is>
-          <t>2026-10-16T22:56:26Z</t>
+          <t>2026-10-17T16:23:40Z</t>
         </is>
       </c>
     </row>
@@ -6334,7 +6334,7 @@
       </c>
       <c r="K123" s="4" t="inlineStr">
         <is>
-          <t>2026-10-16T22:56:26Z</t>
+          <t>2026-10-17T16:23:40Z</t>
         </is>
       </c>
     </row>
@@ -6383,7 +6383,7 @@
       </c>
       <c r="K124" s="4" t="inlineStr">
         <is>
-          <t>2026-10-16T22:56:26Z</t>
+          <t>2026-10-17T16:23:40Z</t>
         </is>
       </c>
     </row>
@@ -6432,7 +6432,7 @@
       </c>
       <c r="K125" s="4" t="inlineStr">
         <is>
-          <t>2026-10-16T22:56:26Z</t>
+          <t>2026-10-17T16:23:40Z</t>
         </is>
       </c>
     </row>
@@ -6481,7 +6481,7 @@
       </c>
       <c r="K126" s="4" t="inlineStr">
         <is>
-          <t>2026-10-16T22:56:26Z</t>
+          <t>2026-10-17T16:23:40Z</t>
         </is>
       </c>
     </row>
@@ -6530,7 +6530,7 @@
       </c>
       <c r="K127" s="4" t="inlineStr">
         <is>
-          <t>2026-10-16T22:56:26Z</t>
+          <t>2026-10-17T16:23:40Z</t>
         </is>
       </c>
     </row>
@@ -6579,7 +6579,7 @@
       </c>
       <c r="K128" s="4" t="inlineStr">
         <is>
-          <t>2026-10-16T22:56:26Z</t>
+          <t>2026-10-17T16:23:40Z</t>
         </is>
       </c>
     </row>
@@ -6628,7 +6628,7 @@
       </c>
       <c r="K129" s="4" t="inlineStr">
         <is>
-          <t>2026-10-16T22:56:26Z</t>
+          <t>2026-10-17T16:23:40Z</t>
         </is>
       </c>
     </row>
@@ -6677,7 +6677,7 @@
       </c>
       <c r="K130" s="4" t="inlineStr">
         <is>
-          <t>2026-10-16T22:56:26Z</t>
+          <t>2026-10-17T16:23:40Z</t>
         </is>
       </c>
     </row>
@@ -6726,7 +6726,7 @@
       </c>
       <c r="K131" s="4" t="inlineStr">
         <is>
-          <t>2026-10-16T22:56:26Z</t>
+          <t>2026-10-17T16:23:40Z</t>
         </is>
       </c>
     </row>
@@ -6775,7 +6775,7 @@
       </c>
       <c r="K132" s="4" t="inlineStr">
         <is>
-          <t>2026-10-16T22:56:26Z</t>
+          <t>2026-10-17T16:23:40Z</t>
         </is>
       </c>
     </row>
@@ -6824,7 +6824,7 @@
       </c>
       <c r="K133" s="4" t="inlineStr">
         <is>
-          <t>2026-10-16T22:56:26Z</t>
+          <t>2026-10-17T16:23:40Z</t>
         </is>
       </c>
     </row>
@@ -6873,7 +6873,7 @@
       </c>
       <c r="K134" s="4" t="inlineStr">
         <is>
-          <t>2026-10-16T22:56:26Z</t>
+          <t>2026-10-17T16:23:40Z</t>
         </is>
       </c>
     </row>
@@ -6922,7 +6922,7 @@
       </c>
       <c r="K135" s="4" t="inlineStr">
         <is>
-          <t>2026-10-16T22:56:26Z</t>
+          <t>2026-10-17T16:23:40Z</t>
         </is>
       </c>
     </row>
@@ -6971,7 +6971,7 @@
       </c>
       <c r="K136" s="4" t="inlineStr">
         <is>
-          <t>2026-10-16T22:56:26Z</t>
+          <t>2026-10-17T16:23:40Z</t>
         </is>
       </c>
     </row>
@@ -7020,7 +7020,7 @@
       </c>
       <c r="K137" s="4" t="inlineStr">
         <is>
-          <t>2026-10-16T22:56:26Z</t>
+          <t>2026-10-17T16:23:40Z</t>
         </is>
       </c>
     </row>
@@ -7069,7 +7069,7 @@
       </c>
       <c r="K138" s="4" t="inlineStr">
         <is>
-          <t>2026-10-16T22:56:26Z</t>
+          <t>2026-10-17T16:23:40Z</t>
         </is>
       </c>
     </row>
@@ -7118,7 +7118,7 @@
       </c>
       <c r="K139" s="4" t="inlineStr">
         <is>
-          <t>2026-10-16T22:56:26Z</t>
+          <t>2026-10-17T16:23:40Z</t>
         </is>
       </c>
     </row>
@@ -7167,7 +7167,7 @@
       </c>
       <c r="K140" s="4" t="inlineStr">
         <is>
-          <t>2026-10-16T22:56:26Z</t>
+          <t>2026-10-17T16:23:40Z</t>
         </is>
       </c>
     </row>
@@ -7216,7 +7216,7 @@
       </c>
       <c r="K141" s="4" t="inlineStr">
         <is>
-          <t>2026-10-16T22:56:26Z</t>
+          <t>2026-10-17T16:23:40Z</t>
         </is>
       </c>
     </row>
@@ -7265,7 +7265,7 @@
       </c>
       <c r="K142" s="4" t="inlineStr">
         <is>
-          <t>2026-10-16T22:56:26Z</t>
+          <t>2026-10-17T16:23:40Z</t>
         </is>
       </c>
     </row>
@@ -7314,7 +7314,7 @@
       </c>
       <c r="K143" s="4" t="inlineStr">
         <is>
-          <t>2026-10-16T22:56:26Z</t>
+          <t>2026-10-17T16:23:40Z</t>
         </is>
       </c>
     </row>
@@ -7363,7 +7363,7 @@
       </c>
       <c r="K144" s="4" t="inlineStr">
         <is>
-          <t>2026-10-16T22:56:26Z</t>
+          <t>2026-10-17T16:23:40Z</t>
         </is>
       </c>
     </row>
@@ -7412,7 +7412,7 @@
       </c>
       <c r="K145" s="4" t="inlineStr">
         <is>
-          <t>2026-10-16T22:56:26Z</t>
+          <t>2026-10-17T16:23:40Z</t>
         </is>
       </c>
     </row>
@@ -7461,7 +7461,7 @@
       </c>
       <c r="K146" s="4" t="inlineStr">
         <is>
-          <t>2026-10-16T22:56:26Z</t>
+          <t>2026-10-17T16:23:40Z</t>
         </is>
       </c>
     </row>
@@ -7510,7 +7510,7 @@
       </c>
       <c r="K147" s="4" t="inlineStr">
         <is>
-          <t>2026-10-16T22:56:26Z</t>
+          <t>2026-10-17T16:23:40Z</t>
         </is>
       </c>
     </row>
@@ -7559,7 +7559,7 @@
       </c>
       <c r="K148" s="4" t="inlineStr">
         <is>
-          <t>2026-10-16T22:56:26Z</t>
+          <t>2026-10-17T16:23:40Z</t>
         </is>
       </c>
     </row>
@@ -7608,7 +7608,7 @@
       </c>
       <c r="K149" s="4" t="inlineStr">
         <is>
-          <t>2026-10-16T22:56:26Z</t>
+          <t>2026-10-17T16:23:40Z</t>
         </is>
       </c>
     </row>
@@ -7657,7 +7657,7 @@
       </c>
       <c r="K150" s="4" t="inlineStr">
         <is>
-          <t>2026-10-16T22:56:26Z</t>
+          <t>2026-10-17T16:23:40Z</t>
         </is>
       </c>
     </row>
@@ -7706,7 +7706,7 @@
       </c>
       <c r="K151" s="4" t="inlineStr">
         <is>
-          <t>2026-10-16T22:56:26Z</t>
+          <t>2026-10-17T16:23:40Z</t>
         </is>
       </c>
     </row>
@@ -7755,7 +7755,7 @@
       </c>
       <c r="K152" s="4" t="inlineStr">
         <is>
-          <t>2026-10-16T22:56:26Z</t>
+          <t>2026-10-17T16:23:40Z</t>
         </is>
       </c>
     </row>
@@ -7804,7 +7804,7 @@
       </c>
       <c r="K153" s="4" t="inlineStr">
         <is>
-          <t>2026-10-16T22:56:26Z</t>
+          <t>2026-10-17T16:23:40Z</t>
         </is>
       </c>
     </row>
@@ -7853,7 +7853,7 @@
       </c>
       <c r="K154" s="4" t="inlineStr">
         <is>
-          <t>2026-10-16T22:56:26Z</t>
+          <t>2026-10-17T16:23:40Z</t>
         </is>
       </c>
     </row>
@@ -7902,7 +7902,7 @@
       </c>
       <c r="K155" s="4" t="inlineStr">
         <is>
-          <t>2026-10-16T22:56:26Z</t>
+          <t>2026-10-17T16:23:40Z</t>
         </is>
       </c>
     </row>
@@ -7951,7 +7951,7 @@
       </c>
       <c r="K156" s="4" t="inlineStr">
         <is>
-          <t>2026-10-16T22:56:26Z</t>
+          <t>2026-10-17T16:23:40Z</t>
         </is>
       </c>
     </row>
@@ -8000,7 +8000,7 @@
       </c>
       <c r="K157" s="4" t="inlineStr">
         <is>
-          <t>2026-10-16T22:56:26Z</t>
+          <t>2026-10-17T16:23:40Z</t>
         </is>
       </c>
     </row>
@@ -8049,7 +8049,7 @@
       </c>
       <c r="K158" s="4" t="inlineStr">
         <is>
-          <t>2026-10-16T22:56:26Z</t>
+          <t>2026-10-17T16:23:40Z</t>
         </is>
       </c>
     </row>
@@ -8098,7 +8098,7 @@
       </c>
       <c r="K159" s="4" t="inlineStr">
         <is>
-          <t>2026-10-16T22:56:26Z</t>
+          <t>2026-10-17T16:23:40Z</t>
         </is>
       </c>
     </row>
@@ -8147,7 +8147,7 @@
       </c>
       <c r="K160" s="4" t="inlineStr">
         <is>
-          <t>2026-10-16T22:56:26Z</t>
+          <t>2026-10-17T16:23:40Z</t>
         </is>
       </c>
     </row>
@@ -8196,7 +8196,7 @@
       </c>
       <c r="K161" s="4" t="inlineStr">
         <is>
-          <t>2026-10-16T22:56:26Z</t>
+          <t>2026-10-17T16:23:40Z</t>
         </is>
       </c>
     </row>
@@ -8245,7 +8245,7 @@
       </c>
       <c r="K162" s="4" t="inlineStr">
         <is>
-          <t>2026-10-16T22:56:26Z</t>
+          <t>2026-10-17T16:23:40Z</t>
         </is>
       </c>
     </row>
@@ -8294,7 +8294,7 @@
       </c>
       <c r="K163" s="4" t="inlineStr">
         <is>
-          <t>2026-10-16T22:56:26Z</t>
+          <t>2026-10-17T16:23:40Z</t>
         </is>
       </c>
     </row>
@@ -8343,7 +8343,7 @@
       </c>
       <c r="K164" s="4" t="inlineStr">
         <is>
-          <t>2026-10-16T22:56:26Z</t>
+          <t>2026-10-17T16:23:40Z</t>
         </is>
       </c>
     </row>
@@ -8392,7 +8392,7 @@
       </c>
       <c r="K165" s="4" t="inlineStr">
         <is>
-          <t>2026-10-16T22:56:26Z</t>
+          <t>2026-10-17T16:23:40Z</t>
         </is>
       </c>
     </row>
@@ -8441,7 +8441,7 @@
       </c>
       <c r="K166" s="4" t="inlineStr">
         <is>
-          <t>2026-10-16T22:56:26Z</t>
+          <t>2026-10-17T16:23:40Z</t>
         </is>
       </c>
     </row>
@@ -8490,7 +8490,7 @@
       </c>
       <c r="K167" s="4" t="inlineStr">
         <is>
-          <t>2026-10-16T22:56:26Z</t>
+          <t>2026-10-17T16:23:40Z</t>
         </is>
       </c>
     </row>
@@ -8539,7 +8539,7 @@
       </c>
       <c r="K168" s="4" t="inlineStr">
         <is>
-          <t>2026-10-16T22:56:26Z</t>
+          <t>2026-10-17T16:23:40Z</t>
         </is>
       </c>
     </row>
@@ -8588,7 +8588,7 @@
       </c>
       <c r="K169" s="4" t="inlineStr">
         <is>
-          <t>2026-10-16T22:56:26Z</t>
+          <t>2026-10-17T16:23:40Z</t>
         </is>
       </c>
     </row>
@@ -8637,7 +8637,7 @@
       </c>
       <c r="K170" s="4" t="inlineStr">
         <is>
-          <t>2026-10-16T22:56:26Z</t>
+          <t>2026-10-17T16:23:40Z</t>
         </is>
       </c>
     </row>
@@ -8686,7 +8686,7 @@
       </c>
       <c r="K171" s="4" t="inlineStr">
         <is>
-          <t>2026-10-16T22:56:26Z</t>
+          <t>2026-10-17T16:23:40Z</t>
         </is>
       </c>
     </row>
@@ -8735,7 +8735,7 @@
       </c>
       <c r="K172" s="4" t="inlineStr">
         <is>
-          <t>2026-10-16T22:56:26Z</t>
+          <t>2026-10-17T16:23:40Z</t>
         </is>
       </c>
     </row>
@@ -8784,7 +8784,7 @@
       </c>
       <c r="K173" s="4" t="inlineStr">
         <is>
-          <t>2026-10-16T22:56:26Z</t>
+          <t>2026-10-17T16:23:40Z</t>
         </is>
       </c>
     </row>
@@ -8833,7 +8833,7 @@
       </c>
       <c r="K174" s="4" t="inlineStr">
         <is>
-          <t>2026-10-16T22:56:26Z</t>
+          <t>2026-10-17T16:23:40Z</t>
         </is>
       </c>
     </row>
@@ -8882,7 +8882,7 @@
       </c>
       <c r="K175" s="4" t="inlineStr">
         <is>
-          <t>2026-10-16T22:56:26Z</t>
+          <t>2026-10-17T16:23:40Z</t>
         </is>
       </c>
     </row>
@@ -8931,7 +8931,7 @@
       </c>
       <c r="K176" s="4" t="inlineStr">
         <is>
-          <t>2026-10-16T22:56:26Z</t>
+          <t>2026-10-17T16:23:40Z</t>
         </is>
       </c>
     </row>
@@ -8980,7 +8980,7 @@
       </c>
       <c r="K177" s="4" t="inlineStr">
         <is>
-          <t>2026-10-16T22:56:26Z</t>
+          <t>2026-10-17T16:23:40Z</t>
         </is>
       </c>
     </row>
@@ -9029,7 +9029,7 @@
       </c>
       <c r="K178" s="4" t="inlineStr">
         <is>
-          <t>2026-10-16T22:56:26Z</t>
+          <t>2026-10-17T16:23:40Z</t>
         </is>
       </c>
     </row>
@@ -9078,7 +9078,7 @@
       </c>
       <c r="K179" s="4" t="inlineStr">
         <is>
-          <t>2026-10-16T22:56:26Z</t>
+          <t>2026-10-17T16:23:40Z</t>
         </is>
       </c>
     </row>
@@ -9127,7 +9127,7 @@
       </c>
       <c r="K180" s="4" t="inlineStr">
         <is>
-          <t>2026-10-16T22:56:26Z</t>
+          <t>2026-10-17T16:23:40Z</t>
         </is>
       </c>
     </row>
@@ -9176,7 +9176,7 @@
       </c>
       <c r="K181" s="4" t="inlineStr">
         <is>
-          <t>2026-10-16T22:56:26Z</t>
+          <t>2026-10-17T16:23:40Z</t>
         </is>
       </c>
     </row>
@@ -9225,7 +9225,7 @@
       </c>
       <c r="K182" s="4" t="inlineStr">
         <is>
-          <t>2026-10-16T22:56:26Z</t>
+          <t>2026-10-17T16:23:40Z</t>
         </is>
       </c>
     </row>
@@ -9274,7 +9274,7 @@
       </c>
       <c r="K183" s="4" t="inlineStr">
         <is>
-          <t>2026-10-16T22:56:26Z</t>
+          <t>2026-10-17T16:23:40Z</t>
         </is>
       </c>
     </row>
@@ -9323,7 +9323,7 @@
       </c>
       <c r="K184" s="4" t="inlineStr">
         <is>
-          <t>2026-10-16T22:56:26Z</t>
+          <t>2026-10-17T16:23:40Z</t>
         </is>
       </c>
     </row>
@@ -9372,7 +9372,7 @@
       </c>
       <c r="K185" s="4" t="inlineStr">
         <is>
-          <t>2026-10-16T22:56:26Z</t>
+          <t>2026-10-17T16:23:40Z</t>
         </is>
       </c>
     </row>
@@ -9421,7 +9421,7 @@
       </c>
       <c r="K186" s="4" t="inlineStr">
         <is>
-          <t>2026-10-16T22:56:26Z</t>
+          <t>2026-10-17T16:23:40Z</t>
         </is>
       </c>
     </row>
@@ -9470,7 +9470,7 @@
       </c>
       <c r="K187" s="4" t="inlineStr">
         <is>
-          <t>2026-10-16T22:56:26Z</t>
+          <t>2026-10-17T16:23:40Z</t>
         </is>
       </c>
     </row>
@@ -9519,7 +9519,7 @@
       </c>
       <c r="K188" s="4" t="inlineStr">
         <is>
-          <t>2026-10-16T22:56:26Z</t>
+          <t>2026-10-17T16:23:40Z</t>
         </is>
       </c>
     </row>
@@ -9568,7 +9568,7 @@
       </c>
       <c r="K189" s="4" t="inlineStr">
         <is>
-          <t>2026-10-16T22:56:26Z</t>
+          <t>2026-10-17T16:23:40Z</t>
         </is>
       </c>
     </row>
@@ -9617,7 +9617,7 @@
       </c>
       <c r="K190" s="4" t="inlineStr">
         <is>
-          <t>2026-10-16T22:56:26Z</t>
+          <t>2026-10-17T16:23:40Z</t>
         </is>
       </c>
     </row>
@@ -9666,7 +9666,7 @@
       </c>
       <c r="K191" s="4" t="inlineStr">
         <is>
-          <t>2026-10-16T22:56:26Z</t>
+          <t>2026-10-17T16:23:40Z</t>
         </is>
       </c>
     </row>
@@ -9715,7 +9715,7 @@
       </c>
       <c r="K192" s="4" t="inlineStr">
         <is>
-          <t>2026-10-16T22:56:26Z</t>
+          <t>2026-10-17T16:23:40Z</t>
         </is>
       </c>
     </row>
@@ -9764,7 +9764,7 @@
       </c>
       <c r="K193" s="4" t="inlineStr">
         <is>
-          <t>2026-10-16T22:56:26Z</t>
+          <t>2026-10-17T16:23:40Z</t>
         </is>
       </c>
     </row>
@@ -9813,7 +9813,7 @@
       </c>
       <c r="K194" s="4" t="inlineStr">
         <is>
-          <t>2026-10-16T22:56:26Z</t>
+          <t>2026-10-17T16:23:40Z</t>
         </is>
       </c>
     </row>
@@ -9862,7 +9862,7 @@
       </c>
       <c r="K195" s="4" t="inlineStr">
         <is>
-          <t>2026-10-16T22:56:26Z</t>
+          <t>2026-10-17T16:23:40Z</t>
         </is>
       </c>
     </row>
@@ -9911,7 +9911,7 @@
       </c>
       <c r="K196" s="4" t="inlineStr">
         <is>
-          <t>2026-10-16T22:56:26Z</t>
+          <t>2026-10-17T16:23:40Z</t>
         </is>
       </c>
     </row>
@@ -9960,7 +9960,7 @@
       </c>
       <c r="K197" s="4" t="inlineStr">
         <is>
-          <t>2026-10-16T22:56:26Z</t>
+          <t>2026-10-17T16:23:40Z</t>
         </is>
       </c>
     </row>
@@ -10009,7 +10009,7 @@
       </c>
       <c r="K198" s="4" t="inlineStr">
         <is>
-          <t>2026-10-16T22:56:26Z</t>
+          <t>2026-10-17T16:23:40Z</t>
         </is>
       </c>
     </row>
@@ -10058,7 +10058,7 @@
       </c>
       <c r="K199" s="4" t="inlineStr">
         <is>
-          <t>2026-10-16T22:56:26Z</t>
+          <t>2026-10-17T16:23:40Z</t>
         </is>
       </c>
     </row>
@@ -10107,7 +10107,7 @@
       </c>
       <c r="K200" s="4" t="inlineStr">
         <is>
-          <t>2026-10-16T22:56:26Z</t>
+          <t>2026-10-17T16:23:40Z</t>
         </is>
       </c>
     </row>
@@ -10156,7 +10156,7 @@
       </c>
       <c r="K201" s="4" t="inlineStr">
         <is>
-          <t>2026-10-16T22:56:26Z</t>
+          <t>2026-10-17T16:23:40Z</t>
         </is>
       </c>
     </row>
@@ -10205,7 +10205,7 @@
       </c>
       <c r="K202" s="4" t="inlineStr">
         <is>
-          <t>2026-10-16T22:56:26Z</t>
+          <t>2026-10-17T16:23:40Z</t>
         </is>
       </c>
     </row>
@@ -10254,7 +10254,7 @@
       </c>
       <c r="K203" s="4" t="inlineStr">
         <is>
-          <t>2026-10-16T22:56:26Z</t>
+          <t>2026-10-17T16:23:40Z</t>
         </is>
       </c>
     </row>
@@ -10303,7 +10303,7 @@
       </c>
       <c r="K204" s="4" t="inlineStr">
         <is>
-          <t>2026-10-16T22:56:26Z</t>
+          <t>2026-10-17T16:23:40Z</t>
         </is>
       </c>
     </row>
@@ -10352,7 +10352,7 @@
       </c>
       <c r="K205" s="4" t="inlineStr">
         <is>
-          <t>2026-10-16T22:56:26Z</t>
+          <t>2026-10-17T16:23:40Z</t>
         </is>
       </c>
     </row>
@@ -10401,7 +10401,7 @@
       </c>
       <c r="K206" s="4" t="inlineStr">
         <is>
-          <t>2026-10-16T22:56:26Z</t>
+          <t>2026-10-17T16:23:40Z</t>
         </is>
       </c>
     </row>
@@ -10450,7 +10450,7 @@
       </c>
       <c r="K207" s="4" t="inlineStr">
         <is>
-          <t>2026-10-16T22:56:26Z</t>
+          <t>2026-10-17T16:23:40Z</t>
         </is>
       </c>
     </row>
@@ -10499,7 +10499,7 @@
       </c>
       <c r="K208" s="4" t="inlineStr">
         <is>
-          <t>2026-10-16T22:56:26Z</t>
+          <t>2026-10-17T16:23:40Z</t>
         </is>
       </c>
     </row>
@@ -10548,7 +10548,7 @@
       </c>
       <c r="K209" s="4" t="inlineStr">
         <is>
-          <t>2026-10-16T22:56:26Z</t>
+          <t>2026-10-17T16:23:40Z</t>
         </is>
       </c>
     </row>
@@ -10597,7 +10597,7 @@
       </c>
       <c r="K210" s="4" t="inlineStr">
         <is>
-          <t>2026-10-16T22:56:26Z</t>
+          <t>2026-10-17T16:23:40Z</t>
         </is>
       </c>
     </row>
@@ -10646,7 +10646,7 @@
       </c>
       <c r="K211" s="4" t="inlineStr">
         <is>
-          <t>2026-10-16T22:56:26Z</t>
+          <t>2026-10-17T16:23:40Z</t>
         </is>
       </c>
     </row>
@@ -10695,7 +10695,7 @@
       </c>
       <c r="K212" s="4" t="inlineStr">
         <is>
-          <t>2026-10-16T22:56:26Z</t>
+          <t>2026-10-17T16:23:40Z</t>
         </is>
       </c>
     </row>
@@ -10744,7 +10744,7 @@
       </c>
       <c r="K213" s="4" t="inlineStr">
         <is>
-          <t>2026-10-16T22:56:26Z</t>
+          <t>2026-10-17T16:23:40Z</t>
         </is>
       </c>
     </row>
@@ -10793,7 +10793,7 @@
       </c>
       <c r="K214" s="4" t="inlineStr">
         <is>
-          <t>2026-10-16T22:56:26Z</t>
+          <t>2026-10-17T16:23:40Z</t>
         </is>
       </c>
     </row>
@@ -10842,7 +10842,7 @@
       </c>
       <c r="K215" s="4" t="inlineStr">
         <is>
-          <t>2026-10-16T22:56:26Z</t>
+          <t>2026-10-17T16:23:40Z</t>
         </is>
       </c>
     </row>
@@ -10891,7 +10891,7 @@
       </c>
       <c r="K216" s="4" t="inlineStr">
         <is>
-          <t>2026-10-16T22:56:26Z</t>
+          <t>2026-10-17T16:23:40Z</t>
         </is>
       </c>
     </row>
@@ -10940,7 +10940,7 @@
       </c>
       <c r="K217" s="4" t="inlineStr">
         <is>
-          <t>2026-10-16T22:56:26Z</t>
+          <t>2026-10-17T16:23:40Z</t>
         </is>
       </c>
     </row>
@@ -10989,7 +10989,7 @@
       </c>
       <c r="K218" s="4" t="inlineStr">
         <is>
-          <t>2026-10-16T22:56:26Z</t>
+          <t>2026-10-17T16:23:40Z</t>
         </is>
       </c>
     </row>
@@ -11038,7 +11038,7 @@
       </c>
       <c r="K219" s="4" t="inlineStr">
         <is>
-          <t>2026-10-16T22:56:26Z</t>
+          <t>2026-10-17T16:23:40Z</t>
         </is>
       </c>
     </row>
@@ -11087,7 +11087,7 @@
       </c>
       <c r="K220" s="4" t="inlineStr">
         <is>
-          <t>2026-10-16T22:56:26Z</t>
+          <t>2026-10-17T16:23:40Z</t>
         </is>
       </c>
     </row>
@@ -11136,7 +11136,7 @@
       </c>
       <c r="K221" s="4" t="inlineStr">
         <is>
-          <t>2026-10-16T22:56:26Z</t>
+          <t>2026-10-17T16:23:40Z</t>
         </is>
       </c>
     </row>
@@ -11185,7 +11185,7 @@
       </c>
       <c r="K222" s="4" t="inlineStr">
         <is>
-          <t>2026-10-16T22:56:26Z</t>
+          <t>2026-10-17T16:23:40Z</t>
         </is>
       </c>
     </row>
@@ -11234,7 +11234,7 @@
       </c>
       <c r="K223" s="4" t="inlineStr">
         <is>
-          <t>2026-10-16T22:56:26Z</t>
+          <t>2026-10-17T16:23:40Z</t>
         </is>
       </c>
     </row>
@@ -11283,7 +11283,7 @@
       </c>
       <c r="K224" s="4" t="inlineStr">
         <is>
-          <t>2026-10-16T22:56:26Z</t>
+          <t>2026-10-17T16:23:40Z</t>
         </is>
       </c>
     </row>
@@ -11332,7 +11332,7 @@
       </c>
       <c r="K225" s="4" t="inlineStr">
         <is>
-          <t>2026-10-16T22:56:26Z</t>
+          <t>2026-10-17T16:23:40Z</t>
         </is>
       </c>
     </row>
@@ -11381,7 +11381,7 @@
       </c>
       <c r="K226" s="4" t="inlineStr">
         <is>
-          <t>2026-10-16T22:56:26Z</t>
+          <t>2026-10-17T16:23:40Z</t>
         </is>
       </c>
     </row>
@@ -11430,7 +11430,7 @@
       </c>
       <c r="K227" s="4" t="inlineStr">
         <is>
-          <t>2026-10-16T22:56:26Z</t>
+          <t>2026-10-17T16:23:40Z</t>
         </is>
       </c>
     </row>
@@ -11479,7 +11479,7 @@
       </c>
       <c r="K228" s="4" t="inlineStr">
         <is>
-          <t>2026-10-16T22:56:26Z</t>
+          <t>2026-10-17T16:23:40Z</t>
         </is>
       </c>
     </row>
@@ -11528,7 +11528,7 @@
       </c>
       <c r="K229" s="4" t="inlineStr">
         <is>
-          <t>2026-10-16T22:56:26Z</t>
+          <t>2026-10-17T16:23:40Z</t>
         </is>
       </c>
     </row>
@@ -11577,7 +11577,7 @@
       </c>
       <c r="K230" s="4" t="inlineStr">
         <is>
-          <t>2026-10-16T22:56:26Z</t>
+          <t>2026-10-17T16:23:40Z</t>
         </is>
       </c>
     </row>
@@ -11626,7 +11626,7 @@
       </c>
       <c r="K231" s="4" t="inlineStr">
         <is>
-          <t>2026-10-16T22:56:26Z</t>
+          <t>2026-10-17T16:23:40Z</t>
         </is>
       </c>
     </row>
@@ -11758,7 +11758,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>2026-10-16T22:56:26Z</t>
+          <t>2026-10-17T16:23:40Z</t>
         </is>
       </c>
     </row>
@@ -11804,7 +11804,7 @@
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>{"date": "2026-08-01", "year": 2026, "month": 8, "month_name": "Agosto", "index_value": 637409769724325.1, "monthly_variation_pct": 8.9, "unit": "Índice base diciembre 2007=100 y variación mensual %", "frequency": "monthly", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/precios_consumidor/4_5_7_2.xls", "fetched_at": "2026-10-16T22:56:26Z"}</t>
+          <t>{"date": "2026-08-01", "year": 2026, "month": 8, "month_name": "Agosto", "index_value": 637409769724325.1, "monthly_variation_pct": 8.9, "unit": "Índice base diciembre 2007=100 y variación mensual %", "frequency": "monthly", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/precios_consumidor/4_5_7_2.xls", "fetched_at": "2026-10-17T16:23:40Z"}</t>
         </is>
       </c>
     </row>

--- a/assets/data/bcv/excel/ove_bcv_inpc_nacional_mensual.xlsx
+++ b/assets/data/bcv/excel/ove_bcv_inpc_nacional_mensual.xlsx
@@ -650,7 +650,7 @@
       </c>
       <c r="K7" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T16:23:40Z</t>
+          <t>2026-10-17T22:30:19Z</t>
         </is>
       </c>
     </row>
@@ -699,7 +699,7 @@
       </c>
       <c r="K8" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T16:23:40Z</t>
+          <t>2026-10-17T22:30:19Z</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="K9" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T16:23:40Z</t>
+          <t>2026-10-17T22:30:19Z</t>
         </is>
       </c>
     </row>
@@ -797,7 +797,7 @@
       </c>
       <c r="K10" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T16:23:40Z</t>
+          <t>2026-10-17T22:30:19Z</t>
         </is>
       </c>
     </row>
@@ -846,7 +846,7 @@
       </c>
       <c r="K11" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T16:23:40Z</t>
+          <t>2026-10-17T22:30:19Z</t>
         </is>
       </c>
     </row>
@@ -895,7 +895,7 @@
       </c>
       <c r="K12" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T16:23:40Z</t>
+          <t>2026-10-17T22:30:19Z</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="K13" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T16:23:40Z</t>
+          <t>2026-10-17T22:30:19Z</t>
         </is>
       </c>
     </row>
@@ -993,7 +993,7 @@
       </c>
       <c r="K14" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T16:23:40Z</t>
+          <t>2026-10-17T22:30:19Z</t>
         </is>
       </c>
     </row>
@@ -1042,7 +1042,7 @@
       </c>
       <c r="K15" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T16:23:40Z</t>
+          <t>2026-10-17T22:30:19Z</t>
         </is>
       </c>
     </row>
@@ -1091,7 +1091,7 @@
       </c>
       <c r="K16" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T16:23:40Z</t>
+          <t>2026-10-17T22:30:19Z</t>
         </is>
       </c>
     </row>
@@ -1140,7 +1140,7 @@
       </c>
       <c r="K17" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T16:23:40Z</t>
+          <t>2026-10-17T22:30:19Z</t>
         </is>
       </c>
     </row>
@@ -1189,7 +1189,7 @@
       </c>
       <c r="K18" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T16:23:40Z</t>
+          <t>2026-10-17T22:30:19Z</t>
         </is>
       </c>
     </row>
@@ -1238,7 +1238,7 @@
       </c>
       <c r="K19" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T16:23:40Z</t>
+          <t>2026-10-17T22:30:19Z</t>
         </is>
       </c>
     </row>
@@ -1287,7 +1287,7 @@
       </c>
       <c r="K20" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T16:23:40Z</t>
+          <t>2026-10-17T22:30:19Z</t>
         </is>
       </c>
     </row>
@@ -1336,7 +1336,7 @@
       </c>
       <c r="K21" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T16:23:40Z</t>
+          <t>2026-10-17T22:30:19Z</t>
         </is>
       </c>
     </row>
@@ -1385,7 +1385,7 @@
       </c>
       <c r="K22" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T16:23:40Z</t>
+          <t>2026-10-17T22:30:19Z</t>
         </is>
       </c>
     </row>
@@ -1434,7 +1434,7 @@
       </c>
       <c r="K23" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T16:23:40Z</t>
+          <t>2026-10-17T22:30:19Z</t>
         </is>
       </c>
     </row>
@@ -1483,7 +1483,7 @@
       </c>
       <c r="K24" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T16:23:40Z</t>
+          <t>2026-10-17T22:30:19Z</t>
         </is>
       </c>
     </row>
@@ -1532,7 +1532,7 @@
       </c>
       <c r="K25" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T16:23:40Z</t>
+          <t>2026-10-17T22:30:19Z</t>
         </is>
       </c>
     </row>
@@ -1581,7 +1581,7 @@
       </c>
       <c r="K26" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T16:23:40Z</t>
+          <t>2026-10-17T22:30:19Z</t>
         </is>
       </c>
     </row>
@@ -1630,7 +1630,7 @@
       </c>
       <c r="K27" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T16:23:40Z</t>
+          <t>2026-10-17T22:30:19Z</t>
         </is>
       </c>
     </row>
@@ -1679,7 +1679,7 @@
       </c>
       <c r="K28" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T16:23:40Z</t>
+          <t>2026-10-17T22:30:19Z</t>
         </is>
       </c>
     </row>
@@ -1728,7 +1728,7 @@
       </c>
       <c r="K29" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T16:23:40Z</t>
+          <t>2026-10-17T22:30:19Z</t>
         </is>
       </c>
     </row>
@@ -1777,7 +1777,7 @@
       </c>
       <c r="K30" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T16:23:40Z</t>
+          <t>2026-10-17T22:30:19Z</t>
         </is>
       </c>
     </row>
@@ -1826,7 +1826,7 @@
       </c>
       <c r="K31" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T16:23:40Z</t>
+          <t>2026-10-17T22:30:19Z</t>
         </is>
       </c>
     </row>
@@ -1875,7 +1875,7 @@
       </c>
       <c r="K32" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T16:23:40Z</t>
+          <t>2026-10-17T22:30:19Z</t>
         </is>
       </c>
     </row>
@@ -1924,7 +1924,7 @@
       </c>
       <c r="K33" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T16:23:40Z</t>
+          <t>2026-10-17T22:30:19Z</t>
         </is>
       </c>
     </row>
@@ -1973,7 +1973,7 @@
       </c>
       <c r="K34" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T16:23:40Z</t>
+          <t>2026-10-17T22:30:19Z</t>
         </is>
       </c>
     </row>
@@ -2022,7 +2022,7 @@
       </c>
       <c r="K35" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T16:23:40Z</t>
+          <t>2026-10-17T22:30:19Z</t>
         </is>
       </c>
     </row>
@@ -2071,7 +2071,7 @@
       </c>
       <c r="K36" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T16:23:40Z</t>
+          <t>2026-10-17T22:30:19Z</t>
         </is>
       </c>
     </row>
@@ -2120,7 +2120,7 @@
       </c>
       <c r="K37" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T16:23:40Z</t>
+          <t>2026-10-17T22:30:19Z</t>
         </is>
       </c>
     </row>
@@ -2169,7 +2169,7 @@
       </c>
       <c r="K38" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T16:23:40Z</t>
+          <t>2026-10-17T22:30:19Z</t>
         </is>
       </c>
     </row>
@@ -2218,7 +2218,7 @@
       </c>
       <c r="K39" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T16:23:40Z</t>
+          <t>2026-10-17T22:30:19Z</t>
         </is>
       </c>
     </row>
@@ -2267,7 +2267,7 @@
       </c>
       <c r="K40" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T16:23:40Z</t>
+          <t>2026-10-17T22:30:19Z</t>
         </is>
       </c>
     </row>
@@ -2316,7 +2316,7 @@
       </c>
       <c r="K41" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T16:23:40Z</t>
+          <t>2026-10-17T22:30:19Z</t>
         </is>
       </c>
     </row>
@@ -2365,7 +2365,7 @@
       </c>
       <c r="K42" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T16:23:40Z</t>
+          <t>2026-10-17T22:30:19Z</t>
         </is>
       </c>
     </row>
@@ -2414,7 +2414,7 @@
       </c>
       <c r="K43" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T16:23:40Z</t>
+          <t>2026-10-17T22:30:19Z</t>
         </is>
       </c>
     </row>
@@ -2463,7 +2463,7 @@
       </c>
       <c r="K44" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T16:23:40Z</t>
+          <t>2026-10-17T22:30:19Z</t>
         </is>
       </c>
     </row>
@@ -2512,7 +2512,7 @@
       </c>
       <c r="K45" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T16:23:40Z</t>
+          <t>2026-10-17T22:30:19Z</t>
         </is>
       </c>
     </row>
@@ -2561,7 +2561,7 @@
       </c>
       <c r="K46" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T16:23:40Z</t>
+          <t>2026-10-17T22:30:19Z</t>
         </is>
       </c>
     </row>
@@ -2610,7 +2610,7 @@
       </c>
       <c r="K47" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T16:23:40Z</t>
+          <t>2026-10-17T22:30:19Z</t>
         </is>
       </c>
     </row>
@@ -2659,7 +2659,7 @@
       </c>
       <c r="K48" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T16:23:40Z</t>
+          <t>2026-10-17T22:30:19Z</t>
         </is>
       </c>
     </row>
@@ -2708,7 +2708,7 @@
       </c>
       <c r="K49" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T16:23:40Z</t>
+          <t>2026-10-17T22:30:19Z</t>
         </is>
       </c>
     </row>
@@ -2757,7 +2757,7 @@
       </c>
       <c r="K50" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T16:23:40Z</t>
+          <t>2026-10-17T22:30:19Z</t>
         </is>
       </c>
     </row>
@@ -2806,7 +2806,7 @@
       </c>
       <c r="K51" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T16:23:40Z</t>
+          <t>2026-10-17T22:30:19Z</t>
         </is>
       </c>
     </row>
@@ -2855,7 +2855,7 @@
       </c>
       <c r="K52" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T16:23:40Z</t>
+          <t>2026-10-17T22:30:19Z</t>
         </is>
       </c>
     </row>
@@ -2904,7 +2904,7 @@
       </c>
       <c r="K53" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T16:23:40Z</t>
+          <t>2026-10-17T22:30:19Z</t>
         </is>
       </c>
     </row>
@@ -2953,7 +2953,7 @@
       </c>
       <c r="K54" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T16:23:40Z</t>
+          <t>2026-10-17T22:30:19Z</t>
         </is>
       </c>
     </row>
@@ -3002,7 +3002,7 @@
       </c>
       <c r="K55" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T16:23:40Z</t>
+          <t>2026-10-17T22:30:19Z</t>
         </is>
       </c>
     </row>
@@ -3051,7 +3051,7 @@
       </c>
       <c r="K56" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T16:23:40Z</t>
+          <t>2026-10-17T22:30:19Z</t>
         </is>
       </c>
     </row>
@@ -3100,7 +3100,7 @@
       </c>
       <c r="K57" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T16:23:40Z</t>
+          <t>2026-10-17T22:30:19Z</t>
         </is>
       </c>
     </row>
@@ -3149,7 +3149,7 @@
       </c>
       <c r="K58" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T16:23:40Z</t>
+          <t>2026-10-17T22:30:19Z</t>
         </is>
       </c>
     </row>
@@ -3198,7 +3198,7 @@
       </c>
       <c r="K59" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T16:23:40Z</t>
+          <t>2026-10-17T22:30:19Z</t>
         </is>
       </c>
     </row>
@@ -3247,7 +3247,7 @@
       </c>
       <c r="K60" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T16:23:40Z</t>
+          <t>2026-10-17T22:30:19Z</t>
         </is>
       </c>
     </row>
@@ -3296,7 +3296,7 @@
       </c>
       <c r="K61" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T16:23:40Z</t>
+          <t>2026-10-17T22:30:19Z</t>
         </is>
       </c>
     </row>
@@ -3345,7 +3345,7 @@
       </c>
       <c r="K62" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T16:23:40Z</t>
+          <t>2026-10-17T22:30:19Z</t>
         </is>
       </c>
     </row>
@@ -3394,7 +3394,7 @@
       </c>
       <c r="K63" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T16:23:40Z</t>
+          <t>2026-10-17T22:30:19Z</t>
         </is>
       </c>
     </row>
@@ -3443,7 +3443,7 @@
       </c>
       <c r="K64" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T16:23:40Z</t>
+          <t>2026-10-17T22:30:19Z</t>
         </is>
       </c>
     </row>
@@ -3492,7 +3492,7 @@
       </c>
       <c r="K65" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T16:23:40Z</t>
+          <t>2026-10-17T22:30:19Z</t>
         </is>
       </c>
     </row>
@@ -3541,7 +3541,7 @@
       </c>
       <c r="K66" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T16:23:40Z</t>
+          <t>2026-10-17T22:30:19Z</t>
         </is>
       </c>
     </row>
@@ -3590,7 +3590,7 @@
       </c>
       <c r="K67" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T16:23:40Z</t>
+          <t>2026-10-17T22:30:19Z</t>
         </is>
       </c>
     </row>
@@ -3639,7 +3639,7 @@
       </c>
       <c r="K68" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T16:23:40Z</t>
+          <t>2026-10-17T22:30:19Z</t>
         </is>
       </c>
     </row>
@@ -3688,7 +3688,7 @@
       </c>
       <c r="K69" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T16:23:40Z</t>
+          <t>2026-10-17T22:30:19Z</t>
         </is>
       </c>
     </row>
@@ -3737,7 +3737,7 @@
       </c>
       <c r="K70" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T16:23:40Z</t>
+          <t>2026-10-17T22:30:19Z</t>
         </is>
       </c>
     </row>
@@ -3786,7 +3786,7 @@
       </c>
       <c r="K71" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T16:23:40Z</t>
+          <t>2026-10-17T22:30:19Z</t>
         </is>
       </c>
     </row>
@@ -3835,7 +3835,7 @@
       </c>
       <c r="K72" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T16:23:40Z</t>
+          <t>2026-10-17T22:30:19Z</t>
         </is>
       </c>
     </row>
@@ -3884,7 +3884,7 @@
       </c>
       <c r="K73" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T16:23:40Z</t>
+          <t>2026-10-17T22:30:19Z</t>
         </is>
       </c>
     </row>
@@ -3933,7 +3933,7 @@
       </c>
       <c r="K74" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T16:23:40Z</t>
+          <t>2026-10-17T22:30:19Z</t>
         </is>
       </c>
     </row>
@@ -3982,7 +3982,7 @@
       </c>
       <c r="K75" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T16:23:40Z</t>
+          <t>2026-10-17T22:30:19Z</t>
         </is>
       </c>
     </row>
@@ -4031,7 +4031,7 @@
       </c>
       <c r="K76" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T16:23:40Z</t>
+          <t>2026-10-17T22:30:19Z</t>
         </is>
       </c>
     </row>
@@ -4080,7 +4080,7 @@
       </c>
       <c r="K77" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T16:23:40Z</t>
+          <t>2026-10-17T22:30:19Z</t>
         </is>
       </c>
     </row>
@@ -4129,7 +4129,7 @@
       </c>
       <c r="K78" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T16:23:40Z</t>
+          <t>2026-10-17T22:30:19Z</t>
         </is>
       </c>
     </row>
@@ -4178,7 +4178,7 @@
       </c>
       <c r="K79" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T16:23:40Z</t>
+          <t>2026-10-17T22:30:19Z</t>
         </is>
       </c>
     </row>
@@ -4227,7 +4227,7 @@
       </c>
       <c r="K80" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T16:23:40Z</t>
+          <t>2026-10-17T22:30:19Z</t>
         </is>
       </c>
     </row>
@@ -4276,7 +4276,7 @@
       </c>
       <c r="K81" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T16:23:40Z</t>
+          <t>2026-10-17T22:30:19Z</t>
         </is>
       </c>
     </row>
@@ -4325,7 +4325,7 @@
       </c>
       <c r="K82" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T16:23:40Z</t>
+          <t>2026-10-17T22:30:19Z</t>
         </is>
       </c>
     </row>
@@ -4374,7 +4374,7 @@
       </c>
       <c r="K83" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T16:23:40Z</t>
+          <t>2026-10-17T22:30:19Z</t>
         </is>
       </c>
     </row>
@@ -4423,7 +4423,7 @@
       </c>
       <c r="K84" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T16:23:40Z</t>
+          <t>2026-10-17T22:30:19Z</t>
         </is>
       </c>
     </row>
@@ -4472,7 +4472,7 @@
       </c>
       <c r="K85" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T16:23:40Z</t>
+          <t>2026-10-17T22:30:19Z</t>
         </is>
       </c>
     </row>
@@ -4521,7 +4521,7 @@
       </c>
       <c r="K86" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T16:23:40Z</t>
+          <t>2026-10-17T22:30:19Z</t>
         </is>
       </c>
     </row>
@@ -4570,7 +4570,7 @@
       </c>
       <c r="K87" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T16:23:40Z</t>
+          <t>2026-10-17T22:30:19Z</t>
         </is>
       </c>
     </row>
@@ -4619,7 +4619,7 @@
       </c>
       <c r="K88" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T16:23:40Z</t>
+          <t>2026-10-17T22:30:19Z</t>
         </is>
       </c>
     </row>
@@ -4668,7 +4668,7 @@
       </c>
       <c r="K89" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T16:23:40Z</t>
+          <t>2026-10-17T22:30:19Z</t>
         </is>
       </c>
     </row>
@@ -4717,7 +4717,7 @@
       </c>
       <c r="K90" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T16:23:40Z</t>
+          <t>2026-10-17T22:30:19Z</t>
         </is>
       </c>
     </row>
@@ -4766,7 +4766,7 @@
       </c>
       <c r="K91" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T16:23:40Z</t>
+          <t>2026-10-17T22:30:19Z</t>
         </is>
       </c>
     </row>
@@ -4815,7 +4815,7 @@
       </c>
       <c r="K92" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T16:23:40Z</t>
+          <t>2026-10-17T22:30:19Z</t>
         </is>
       </c>
     </row>
@@ -4864,7 +4864,7 @@
       </c>
       <c r="K93" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T16:23:40Z</t>
+          <t>2026-10-17T22:30:19Z</t>
         </is>
       </c>
     </row>
@@ -4913,7 +4913,7 @@
       </c>
       <c r="K94" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T16:23:40Z</t>
+          <t>2026-10-17T22:30:19Z</t>
         </is>
       </c>
     </row>
@@ -4962,7 +4962,7 @@
       </c>
       <c r="K95" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T16:23:40Z</t>
+          <t>2026-10-17T22:30:19Z</t>
         </is>
       </c>
     </row>
@@ -5011,7 +5011,7 @@
       </c>
       <c r="K96" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T16:23:40Z</t>
+          <t>2026-10-17T22:30:19Z</t>
         </is>
       </c>
     </row>
@@ -5060,7 +5060,7 @@
       </c>
       <c r="K97" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T16:23:40Z</t>
+          <t>2026-10-17T22:30:19Z</t>
         </is>
       </c>
     </row>
@@ -5109,7 +5109,7 @@
       </c>
       <c r="K98" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T16:23:40Z</t>
+          <t>2026-10-17T22:30:19Z</t>
         </is>
       </c>
     </row>
@@ -5158,7 +5158,7 @@
       </c>
       <c r="K99" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T16:23:40Z</t>
+          <t>2026-10-17T22:30:19Z</t>
         </is>
       </c>
     </row>
@@ -5207,7 +5207,7 @@
       </c>
       <c r="K100" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T16:23:40Z</t>
+          <t>2026-10-17T22:30:19Z</t>
         </is>
       </c>
     </row>
@@ -5256,7 +5256,7 @@
       </c>
       <c r="K101" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T16:23:40Z</t>
+          <t>2026-10-17T22:30:19Z</t>
         </is>
       </c>
     </row>
@@ -5305,7 +5305,7 @@
       </c>
       <c r="K102" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T16:23:40Z</t>
+          <t>2026-10-17T22:30:19Z</t>
         </is>
       </c>
     </row>
@@ -5354,7 +5354,7 @@
       </c>
       <c r="K103" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T16:23:40Z</t>
+          <t>2026-10-17T22:30:19Z</t>
         </is>
       </c>
     </row>
@@ -5403,7 +5403,7 @@
       </c>
       <c r="K104" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T16:23:40Z</t>
+          <t>2026-10-17T22:30:19Z</t>
         </is>
       </c>
     </row>
@@ -5452,7 +5452,7 @@
       </c>
       <c r="K105" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T16:23:40Z</t>
+          <t>2026-10-17T22:30:19Z</t>
         </is>
       </c>
     </row>
@@ -5501,7 +5501,7 @@
       </c>
       <c r="K106" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T16:23:40Z</t>
+          <t>2026-10-17T22:30:19Z</t>
         </is>
       </c>
     </row>
@@ -5550,7 +5550,7 @@
       </c>
       <c r="K107" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T16:23:40Z</t>
+          <t>2026-10-17T22:30:19Z</t>
         </is>
       </c>
     </row>
@@ -5599,7 +5599,7 @@
       </c>
       <c r="K108" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T16:23:40Z</t>
+          <t>2026-10-17T22:30:19Z</t>
         </is>
       </c>
     </row>
@@ -5648,7 +5648,7 @@
       </c>
       <c r="K109" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T16:23:40Z</t>
+          <t>2026-10-17T22:30:19Z</t>
         </is>
       </c>
     </row>
@@ -5697,7 +5697,7 @@
       </c>
       <c r="K110" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T16:23:40Z</t>
+          <t>2026-10-17T22:30:19Z</t>
         </is>
       </c>
     </row>
@@ -5746,7 +5746,7 @@
       </c>
       <c r="K111" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T16:23:40Z</t>
+          <t>2026-10-17T22:30:19Z</t>
         </is>
       </c>
     </row>
@@ -5795,7 +5795,7 @@
       </c>
       <c r="K112" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T16:23:40Z</t>
+          <t>2026-10-17T22:30:19Z</t>
         </is>
       </c>
     </row>
@@ -5844,7 +5844,7 @@
       </c>
       <c r="K113" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T16:23:40Z</t>
+          <t>2026-10-17T22:30:19Z</t>
         </is>
       </c>
     </row>
@@ -5893,7 +5893,7 @@
       </c>
       <c r="K114" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T16:23:40Z</t>
+          <t>2026-10-17T22:30:19Z</t>
         </is>
       </c>
     </row>
@@ -5942,7 +5942,7 @@
       </c>
       <c r="K115" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T16:23:40Z</t>
+          <t>2026-10-17T22:30:19Z</t>
         </is>
       </c>
     </row>
@@ -5991,7 +5991,7 @@
       </c>
       <c r="K116" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T16:23:40Z</t>
+          <t>2026-10-17T22:30:19Z</t>
         </is>
       </c>
     </row>
@@ -6040,7 +6040,7 @@
       </c>
       <c r="K117" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T16:23:40Z</t>
+          <t>2026-10-17T22:30:19Z</t>
         </is>
       </c>
     </row>
@@ -6089,7 +6089,7 @@
       </c>
       <c r="K118" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T16:23:40Z</t>
+          <t>2026-10-17T22:30:19Z</t>
         </is>
       </c>
     </row>
@@ -6138,7 +6138,7 @@
       </c>
       <c r="K119" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T16:23:40Z</t>
+          <t>2026-10-17T22:30:19Z</t>
         </is>
       </c>
     </row>
@@ -6187,7 +6187,7 @@
       </c>
       <c r="K120" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T16:23:40Z</t>
+          <t>2026-10-17T22:30:19Z</t>
         </is>
       </c>
     </row>
@@ -6236,7 +6236,7 @@
       </c>
       <c r="K121" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T16:23:40Z</t>
+          <t>2026-10-17T22:30:19Z</t>
         </is>
       </c>
     </row>
@@ -6285,7 +6285,7 @@
       </c>
       <c r="K122" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T16:23:40Z</t>
+          <t>2026-10-17T22:30:19Z</t>
         </is>
       </c>
     </row>
@@ -6334,7 +6334,7 @@
       </c>
       <c r="K123" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T16:23:40Z</t>
+          <t>2026-10-17T22:30:19Z</t>
         </is>
       </c>
     </row>
@@ -6383,7 +6383,7 @@
       </c>
       <c r="K124" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T16:23:40Z</t>
+          <t>2026-10-17T22:30:19Z</t>
         </is>
       </c>
     </row>
@@ -6432,7 +6432,7 @@
       </c>
       <c r="K125" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T16:23:40Z</t>
+          <t>2026-10-17T22:30:19Z</t>
         </is>
       </c>
     </row>
@@ -6481,7 +6481,7 @@
       </c>
       <c r="K126" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T16:23:40Z</t>
+          <t>2026-10-17T22:30:19Z</t>
         </is>
       </c>
     </row>
@@ -6530,7 +6530,7 @@
       </c>
       <c r="K127" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T16:23:40Z</t>
+          <t>2026-10-17T22:30:19Z</t>
         </is>
       </c>
     </row>
@@ -6579,7 +6579,7 @@
       </c>
       <c r="K128" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T16:23:40Z</t>
+          <t>2026-10-17T22:30:19Z</t>
         </is>
       </c>
     </row>
@@ -6628,7 +6628,7 @@
       </c>
       <c r="K129" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T16:23:40Z</t>
+          <t>2026-10-17T22:30:19Z</t>
         </is>
       </c>
     </row>
@@ -6677,7 +6677,7 @@
       </c>
       <c r="K130" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T16:23:40Z</t>
+          <t>2026-10-17T22:30:19Z</t>
         </is>
       </c>
     </row>
@@ -6726,7 +6726,7 @@
       </c>
       <c r="K131" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T16:23:40Z</t>
+          <t>2026-10-17T22:30:19Z</t>
         </is>
       </c>
     </row>
@@ -6775,7 +6775,7 @@
       </c>
       <c r="K132" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T16:23:40Z</t>
+          <t>2026-10-17T22:30:19Z</t>
         </is>
       </c>
     </row>
@@ -6824,7 +6824,7 @@
       </c>
       <c r="K133" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T16:23:40Z</t>
+          <t>2026-10-17T22:30:19Z</t>
         </is>
       </c>
     </row>
@@ -6873,7 +6873,7 @@
       </c>
       <c r="K134" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T16:23:40Z</t>
+          <t>2026-10-17T22:30:19Z</t>
         </is>
       </c>
     </row>
@@ -6922,7 +6922,7 @@
       </c>
       <c r="K135" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T16:23:40Z</t>
+          <t>2026-10-17T22:30:19Z</t>
         </is>
       </c>
     </row>
@@ -6971,7 +6971,7 @@
       </c>
       <c r="K136" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T16:23:40Z</t>
+          <t>2026-10-17T22:30:19Z</t>
         </is>
       </c>
     </row>
@@ -7020,7 +7020,7 @@
       </c>
       <c r="K137" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T16:23:40Z</t>
+          <t>2026-10-17T22:30:19Z</t>
         </is>
       </c>
     </row>
@@ -7069,7 +7069,7 @@
       </c>
       <c r="K138" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T16:23:40Z</t>
+          <t>2026-10-17T22:30:19Z</t>
         </is>
       </c>
     </row>
@@ -7118,7 +7118,7 @@
       </c>
       <c r="K139" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T16:23:40Z</t>
+          <t>2026-10-17T22:30:19Z</t>
         </is>
       </c>
     </row>
@@ -7167,7 +7167,7 @@
       </c>
       <c r="K140" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T16:23:40Z</t>
+          <t>2026-10-17T22:30:19Z</t>
         </is>
       </c>
     </row>
@@ -7216,7 +7216,7 @@
       </c>
       <c r="K141" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T16:23:40Z</t>
+          <t>2026-10-17T22:30:19Z</t>
         </is>
       </c>
     </row>
@@ -7265,7 +7265,7 @@
       </c>
       <c r="K142" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T16:23:40Z</t>
+          <t>2026-10-17T22:30:19Z</t>
         </is>
       </c>
     </row>
@@ -7314,7 +7314,7 @@
       </c>
       <c r="K143" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T16:23:40Z</t>
+          <t>2026-10-17T22:30:19Z</t>
         </is>
       </c>
     </row>
@@ -7363,7 +7363,7 @@
       </c>
       <c r="K144" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T16:23:40Z</t>
+          <t>2026-10-17T22:30:19Z</t>
         </is>
       </c>
     </row>
@@ -7412,7 +7412,7 @@
       </c>
       <c r="K145" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T16:23:40Z</t>
+          <t>2026-10-17T22:30:19Z</t>
         </is>
       </c>
     </row>
@@ -7461,7 +7461,7 @@
       </c>
       <c r="K146" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T16:23:40Z</t>
+          <t>2026-10-17T22:30:19Z</t>
         </is>
       </c>
     </row>
@@ -7510,7 +7510,7 @@
       </c>
       <c r="K147" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T16:23:40Z</t>
+          <t>2026-10-17T22:30:19Z</t>
         </is>
       </c>
     </row>
@@ -7559,7 +7559,7 @@
       </c>
       <c r="K148" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T16:23:40Z</t>
+          <t>2026-10-17T22:30:19Z</t>
         </is>
       </c>
     </row>
@@ -7608,7 +7608,7 @@
       </c>
       <c r="K149" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T16:23:40Z</t>
+          <t>2026-10-17T22:30:19Z</t>
         </is>
       </c>
     </row>
@@ -7657,7 +7657,7 @@
       </c>
       <c r="K150" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T16:23:40Z</t>
+          <t>2026-10-17T22:30:19Z</t>
         </is>
       </c>
     </row>
@@ -7706,7 +7706,7 @@
       </c>
       <c r="K151" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T16:23:40Z</t>
+          <t>2026-10-17T22:30:19Z</t>
         </is>
       </c>
     </row>
@@ -7755,7 +7755,7 @@
       </c>
       <c r="K152" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T16:23:40Z</t>
+          <t>2026-10-17T22:30:19Z</t>
         </is>
       </c>
     </row>
@@ -7804,7 +7804,7 @@
       </c>
       <c r="K153" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T16:23:40Z</t>
+          <t>2026-10-17T22:30:19Z</t>
         </is>
       </c>
     </row>
@@ -7853,7 +7853,7 @@
       </c>
       <c r="K154" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T16:23:40Z</t>
+          <t>2026-10-17T22:30:19Z</t>
         </is>
       </c>
     </row>
@@ -7902,7 +7902,7 @@
       </c>
       <c r="K155" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T16:23:40Z</t>
+          <t>2026-10-17T22:30:19Z</t>
         </is>
       </c>
     </row>
@@ -7951,7 +7951,7 @@
       </c>
       <c r="K156" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T16:23:40Z</t>
+          <t>2026-10-17T22:30:19Z</t>
         </is>
       </c>
     </row>
@@ -8000,7 +8000,7 @@
       </c>
       <c r="K157" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T16:23:40Z</t>
+          <t>2026-10-17T22:30:19Z</t>
         </is>
       </c>
     </row>
@@ -8049,7 +8049,7 @@
       </c>
       <c r="K158" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T16:23:40Z</t>
+          <t>2026-10-17T22:30:19Z</t>
         </is>
       </c>
     </row>
@@ -8098,7 +8098,7 @@
       </c>
       <c r="K159" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T16:23:40Z</t>
+          <t>2026-10-17T22:30:19Z</t>
         </is>
       </c>
     </row>
@@ -8147,7 +8147,7 @@
       </c>
       <c r="K160" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T16:23:40Z</t>
+          <t>2026-10-17T22:30:19Z</t>
         </is>
       </c>
     </row>
@@ -8196,7 +8196,7 @@
       </c>
       <c r="K161" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T16:23:40Z</t>
+          <t>2026-10-17T22:30:19Z</t>
         </is>
       </c>
     </row>
@@ -8245,7 +8245,7 @@
       </c>
       <c r="K162" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T16:23:40Z</t>
+          <t>2026-10-17T22:30:19Z</t>
         </is>
       </c>
     </row>
@@ -8294,7 +8294,7 @@
       </c>
       <c r="K163" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T16:23:40Z</t>
+          <t>2026-10-17T22:30:19Z</t>
         </is>
       </c>
     </row>
@@ -8343,7 +8343,7 @@
       </c>
       <c r="K164" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T16:23:40Z</t>
+          <t>2026-10-17T22:30:19Z</t>
         </is>
       </c>
     </row>
@@ -8392,7 +8392,7 @@
       </c>
       <c r="K165" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T16:23:40Z</t>
+          <t>2026-10-17T22:30:19Z</t>
         </is>
       </c>
     </row>
@@ -8441,7 +8441,7 @@
       </c>
       <c r="K166" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T16:23:40Z</t>
+          <t>2026-10-17T22:30:19Z</t>
         </is>
       </c>
     </row>
@@ -8490,7 +8490,7 @@
       </c>
       <c r="K167" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T16:23:40Z</t>
+          <t>2026-10-17T22:30:19Z</t>
         </is>
       </c>
     </row>
@@ -8539,7 +8539,7 @@
       </c>
       <c r="K168" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T16:23:40Z</t>
+          <t>2026-10-17T22:30:19Z</t>
         </is>
       </c>
     </row>
@@ -8588,7 +8588,7 @@
       </c>
       <c r="K169" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T16:23:40Z</t>
+          <t>2026-10-17T22:30:19Z</t>
         </is>
       </c>
     </row>
@@ -8637,7 +8637,7 @@
       </c>
       <c r="K170" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T16:23:40Z</t>
+          <t>2026-10-17T22:30:19Z</t>
         </is>
       </c>
     </row>
@@ -8686,7 +8686,7 @@
       </c>
       <c r="K171" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T16:23:40Z</t>
+          <t>2026-10-17T22:30:19Z</t>
         </is>
       </c>
     </row>
@@ -8735,7 +8735,7 @@
       </c>
       <c r="K172" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T16:23:40Z</t>
+          <t>2026-10-17T22:30:19Z</t>
         </is>
       </c>
     </row>
@@ -8784,7 +8784,7 @@
       </c>
       <c r="K173" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T16:23:40Z</t>
+          <t>2026-10-17T22:30:19Z</t>
         </is>
       </c>
     </row>
@@ -8833,7 +8833,7 @@
       </c>
       <c r="K174" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T16:23:40Z</t>
+          <t>2026-10-17T22:30:19Z</t>
         </is>
       </c>
     </row>
@@ -8882,7 +8882,7 @@
       </c>
       <c r="K175" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T16:23:40Z</t>
+          <t>2026-10-17T22:30:19Z</t>
         </is>
       </c>
     </row>
@@ -8931,7 +8931,7 @@
       </c>
       <c r="K176" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T16:23:40Z</t>
+          <t>2026-10-17T22:30:19Z</t>
         </is>
       </c>
     </row>
@@ -8980,7 +8980,7 @@
       </c>
       <c r="K177" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T16:23:40Z</t>
+          <t>2026-10-17T22:30:19Z</t>
         </is>
       </c>
     </row>
@@ -9029,7 +9029,7 @@
       </c>
       <c r="K178" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T16:23:40Z</t>
+          <t>2026-10-17T22:30:19Z</t>
         </is>
       </c>
     </row>
@@ -9078,7 +9078,7 @@
       </c>
       <c r="K179" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T16:23:40Z</t>
+          <t>2026-10-17T22:30:19Z</t>
         </is>
       </c>
     </row>
@@ -9127,7 +9127,7 @@
       </c>
       <c r="K180" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T16:23:40Z</t>
+          <t>2026-10-17T22:30:19Z</t>
         </is>
       </c>
     </row>
@@ -9176,7 +9176,7 @@
       </c>
       <c r="K181" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T16:23:40Z</t>
+          <t>2026-10-17T22:30:19Z</t>
         </is>
       </c>
     </row>
@@ -9225,7 +9225,7 @@
       </c>
       <c r="K182" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T16:23:40Z</t>
+          <t>2026-10-17T22:30:19Z</t>
         </is>
       </c>
     </row>
@@ -9274,7 +9274,7 @@
       </c>
       <c r="K183" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T16:23:40Z</t>
+          <t>2026-10-17T22:30:19Z</t>
         </is>
       </c>
     </row>
@@ -9323,7 +9323,7 @@
       </c>
       <c r="K184" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T16:23:40Z</t>
+          <t>2026-10-17T22:30:19Z</t>
         </is>
       </c>
     </row>
@@ -9372,7 +9372,7 @@
       </c>
       <c r="K185" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T16:23:40Z</t>
+          <t>2026-10-17T22:30:19Z</t>
         </is>
       </c>
     </row>
@@ -9421,7 +9421,7 @@
       </c>
       <c r="K186" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T16:23:40Z</t>
+          <t>2026-10-17T22:30:19Z</t>
         </is>
       </c>
     </row>
@@ -9470,7 +9470,7 @@
       </c>
       <c r="K187" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T16:23:40Z</t>
+          <t>2026-10-17T22:30:19Z</t>
         </is>
       </c>
     </row>
@@ -9519,7 +9519,7 @@
       </c>
       <c r="K188" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T16:23:40Z</t>
+          <t>2026-10-17T22:30:19Z</t>
         </is>
       </c>
     </row>
@@ -9568,7 +9568,7 @@
       </c>
       <c r="K189" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T16:23:40Z</t>
+          <t>2026-10-17T22:30:19Z</t>
         </is>
       </c>
     </row>
@@ -9617,7 +9617,7 @@
       </c>
       <c r="K190" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T16:23:40Z</t>
+          <t>2026-10-17T22:30:19Z</t>
         </is>
       </c>
     </row>
@@ -9666,7 +9666,7 @@
       </c>
       <c r="K191" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T16:23:40Z</t>
+          <t>2026-10-17T22:30:19Z</t>
         </is>
       </c>
     </row>
@@ -9715,7 +9715,7 @@
       </c>
       <c r="K192" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T16:23:40Z</t>
+          <t>2026-10-17T22:30:19Z</t>
         </is>
       </c>
     </row>
@@ -9764,7 +9764,7 @@
       </c>
       <c r="K193" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T16:23:40Z</t>
+          <t>2026-10-17T22:30:19Z</t>
         </is>
       </c>
     </row>
@@ -9813,7 +9813,7 @@
       </c>
       <c r="K194" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T16:23:40Z</t>
+          <t>2026-10-17T22:30:19Z</t>
         </is>
       </c>
     </row>
@@ -9862,7 +9862,7 @@
       </c>
       <c r="K195" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T16:23:40Z</t>
+          <t>2026-10-17T22:30:19Z</t>
         </is>
       </c>
     </row>
@@ -9911,7 +9911,7 @@
       </c>
       <c r="K196" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T16:23:40Z</t>
+          <t>2026-10-17T22:30:19Z</t>
         </is>
       </c>
     </row>
@@ -9960,7 +9960,7 @@
       </c>
       <c r="K197" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T16:23:40Z</t>
+          <t>2026-10-17T22:30:19Z</t>
         </is>
       </c>
     </row>
@@ -10009,7 +10009,7 @@
       </c>
       <c r="K198" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T16:23:40Z</t>
+          <t>2026-10-17T22:30:19Z</t>
         </is>
       </c>
     </row>
@@ -10058,7 +10058,7 @@
       </c>
       <c r="K199" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T16:23:40Z</t>
+          <t>2026-10-17T22:30:19Z</t>
         </is>
       </c>
     </row>
@@ -10107,7 +10107,7 @@
       </c>
       <c r="K200" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T16:23:40Z</t>
+          <t>2026-10-17T22:30:19Z</t>
         </is>
       </c>
     </row>
@@ -10156,7 +10156,7 @@
       </c>
       <c r="K201" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T16:23:40Z</t>
+          <t>2026-10-17T22:30:19Z</t>
         </is>
       </c>
     </row>
@@ -10205,7 +10205,7 @@
       </c>
       <c r="K202" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T16:23:40Z</t>
+          <t>2026-10-17T22:30:19Z</t>
         </is>
       </c>
     </row>
@@ -10254,7 +10254,7 @@
       </c>
       <c r="K203" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T16:23:40Z</t>
+          <t>2026-10-17T22:30:19Z</t>
         </is>
       </c>
     </row>
@@ -10303,7 +10303,7 @@
       </c>
       <c r="K204" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T16:23:40Z</t>
+          <t>2026-10-17T22:30:19Z</t>
         </is>
       </c>
     </row>
@@ -10352,7 +10352,7 @@
       </c>
       <c r="K205" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T16:23:40Z</t>
+          <t>2026-10-17T22:30:19Z</t>
         </is>
       </c>
     </row>
@@ -10401,7 +10401,7 @@
       </c>
       <c r="K206" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T16:23:40Z</t>
+          <t>2026-10-17T22:30:19Z</t>
         </is>
       </c>
     </row>
@@ -10450,7 +10450,7 @@
       </c>
       <c r="K207" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T16:23:40Z</t>
+          <t>2026-10-17T22:30:19Z</t>
         </is>
       </c>
     </row>
@@ -10499,7 +10499,7 @@
       </c>
       <c r="K208" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T16:23:40Z</t>
+          <t>2026-10-17T22:30:19Z</t>
         </is>
       </c>
     </row>
@@ -10548,7 +10548,7 @@
       </c>
       <c r="K209" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T16:23:40Z</t>
+          <t>2026-10-17T22:30:19Z</t>
         </is>
       </c>
     </row>
@@ -10597,7 +10597,7 @@
       </c>
       <c r="K210" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T16:23:40Z</t>
+          <t>2026-10-17T22:30:19Z</t>
         </is>
       </c>
     </row>
@@ -10646,7 +10646,7 @@
       </c>
       <c r="K211" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T16:23:40Z</t>
+          <t>2026-10-17T22:30:19Z</t>
         </is>
       </c>
     </row>
@@ -10695,7 +10695,7 @@
       </c>
       <c r="K212" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T16:23:40Z</t>
+          <t>2026-10-17T22:30:19Z</t>
         </is>
       </c>
     </row>
@@ -10744,7 +10744,7 @@
       </c>
       <c r="K213" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T16:23:40Z</t>
+          <t>2026-10-17T22:30:19Z</t>
         </is>
       </c>
     </row>
@@ -10793,7 +10793,7 @@
       </c>
       <c r="K214" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T16:23:40Z</t>
+          <t>2026-10-17T22:30:19Z</t>
         </is>
       </c>
     </row>
@@ -10842,7 +10842,7 @@
       </c>
       <c r="K215" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T16:23:40Z</t>
+          <t>2026-10-17T22:30:19Z</t>
         </is>
       </c>
     </row>
@@ -10891,7 +10891,7 @@
       </c>
       <c r="K216" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T16:23:40Z</t>
+          <t>2026-10-17T22:30:19Z</t>
         </is>
       </c>
     </row>
@@ -10940,7 +10940,7 @@
       </c>
       <c r="K217" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T16:23:40Z</t>
+          <t>2026-10-17T22:30:19Z</t>
         </is>
       </c>
     </row>
@@ -10989,7 +10989,7 @@
       </c>
       <c r="K218" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T16:23:40Z</t>
+          <t>2026-10-17T22:30:19Z</t>
         </is>
       </c>
     </row>
@@ -11038,7 +11038,7 @@
       </c>
       <c r="K219" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T16:23:40Z</t>
+          <t>2026-10-17T22:30:19Z</t>
         </is>
       </c>
     </row>
@@ -11087,7 +11087,7 @@
       </c>
       <c r="K220" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T16:23:40Z</t>
+          <t>2026-10-17T22:30:19Z</t>
         </is>
       </c>
     </row>
@@ -11136,7 +11136,7 @@
       </c>
       <c r="K221" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T16:23:40Z</t>
+          <t>2026-10-17T22:30:19Z</t>
         </is>
       </c>
     </row>
@@ -11185,7 +11185,7 @@
       </c>
       <c r="K222" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T16:23:40Z</t>
+          <t>2026-10-17T22:30:19Z</t>
         </is>
       </c>
     </row>
@@ -11234,7 +11234,7 @@
       </c>
       <c r="K223" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T16:23:40Z</t>
+          <t>2026-10-17T22:30:19Z</t>
         </is>
       </c>
     </row>
@@ -11283,7 +11283,7 @@
       </c>
       <c r="K224" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T16:23:40Z</t>
+          <t>2026-10-17T22:30:19Z</t>
         </is>
       </c>
     </row>
@@ -11332,7 +11332,7 @@
       </c>
       <c r="K225" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T16:23:40Z</t>
+          <t>2026-10-17T22:30:19Z</t>
         </is>
       </c>
     </row>
@@ -11381,7 +11381,7 @@
       </c>
       <c r="K226" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T16:23:40Z</t>
+          <t>2026-10-17T22:30:19Z</t>
         </is>
       </c>
     </row>
@@ -11430,7 +11430,7 @@
       </c>
       <c r="K227" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T16:23:40Z</t>
+          <t>2026-10-17T22:30:19Z</t>
         </is>
       </c>
     </row>
@@ -11479,7 +11479,7 @@
       </c>
       <c r="K228" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T16:23:40Z</t>
+          <t>2026-10-17T22:30:19Z</t>
         </is>
       </c>
     </row>
@@ -11528,7 +11528,7 @@
       </c>
       <c r="K229" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T16:23:40Z</t>
+          <t>2026-10-17T22:30:19Z</t>
         </is>
       </c>
     </row>
@@ -11577,7 +11577,7 @@
       </c>
       <c r="K230" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T16:23:40Z</t>
+          <t>2026-10-17T22:30:19Z</t>
         </is>
       </c>
     </row>
@@ -11626,7 +11626,7 @@
       </c>
       <c r="K231" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T16:23:40Z</t>
+          <t>2026-10-17T22:30:19Z</t>
         </is>
       </c>
     </row>
@@ -11758,7 +11758,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T16:23:40Z</t>
+          <t>2026-10-17T22:30:19Z</t>
         </is>
       </c>
     </row>
@@ -11804,7 +11804,7 @@
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>{"date": "2026-08-01", "year": 2026, "month": 8, "month_name": "Agosto", "index_value": 637409769724325.1, "monthly_variation_pct": 8.9, "unit": "Índice base diciembre 2007=100 y variación mensual %", "frequency": "monthly", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/precios_consumidor/4_5_7_2.xls", "fetched_at": "2026-10-17T16:23:40Z"}</t>
+          <t>{"date": "2026-08-01", "year": 2026, "month": 8, "month_name": "Agosto", "index_value": 637409769724325.1, "monthly_variation_pct": 8.9, "unit": "Índice base diciembre 2007=100 y variación mensual %", "frequency": "monthly", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/precios_consumidor/4_5_7_2.xls", "fetched_at": "2026-10-17T22:30:19Z"}</t>
         </is>
       </c>
     </row>

--- a/assets/data/bcv/excel/ove_bcv_inpc_nacional_mensual.xlsx
+++ b/assets/data/bcv/excel/ove_bcv_inpc_nacional_mensual.xlsx
@@ -650,7 +650,7 @@
       </c>
       <c r="K7" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T22:30:19Z</t>
+          <t>2026-10-18T22:31:21Z</t>
         </is>
       </c>
     </row>
@@ -699,7 +699,7 @@
       </c>
       <c r="K8" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T22:30:19Z</t>
+          <t>2026-10-18T22:31:21Z</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="K9" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T22:30:19Z</t>
+          <t>2026-10-18T22:31:21Z</t>
         </is>
       </c>
     </row>
@@ -797,7 +797,7 @@
       </c>
       <c r="K10" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T22:30:19Z</t>
+          <t>2026-10-18T22:31:21Z</t>
         </is>
       </c>
     </row>
@@ -846,7 +846,7 @@
       </c>
       <c r="K11" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T22:30:19Z</t>
+          <t>2026-10-18T22:31:21Z</t>
         </is>
       </c>
     </row>
@@ -895,7 +895,7 @@
       </c>
       <c r="K12" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T22:30:19Z</t>
+          <t>2026-10-18T22:31:21Z</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="K13" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T22:30:19Z</t>
+          <t>2026-10-18T22:31:21Z</t>
         </is>
       </c>
     </row>
@@ -993,7 +993,7 @@
       </c>
       <c r="K14" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T22:30:19Z</t>
+          <t>2026-10-18T22:31:21Z</t>
         </is>
       </c>
     </row>
@@ -1042,7 +1042,7 @@
       </c>
       <c r="K15" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T22:30:19Z</t>
+          <t>2026-10-18T22:31:21Z</t>
         </is>
       </c>
     </row>
@@ -1091,7 +1091,7 @@
       </c>
       <c r="K16" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T22:30:19Z</t>
+          <t>2026-10-18T22:31:21Z</t>
         </is>
       </c>
     </row>
@@ -1140,7 +1140,7 @@
       </c>
       <c r="K17" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T22:30:19Z</t>
+          <t>2026-10-18T22:31:21Z</t>
         </is>
       </c>
     </row>
@@ -1189,7 +1189,7 @@
       </c>
       <c r="K18" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T22:30:19Z</t>
+          <t>2026-10-18T22:31:21Z</t>
         </is>
       </c>
     </row>
@@ -1238,7 +1238,7 @@
       </c>
       <c r="K19" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T22:30:19Z</t>
+          <t>2026-10-18T22:31:21Z</t>
         </is>
       </c>
     </row>
@@ -1287,7 +1287,7 @@
       </c>
       <c r="K20" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T22:30:19Z</t>
+          <t>2026-10-18T22:31:21Z</t>
         </is>
       </c>
     </row>
@@ -1336,7 +1336,7 @@
       </c>
       <c r="K21" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T22:30:19Z</t>
+          <t>2026-10-18T22:31:21Z</t>
         </is>
       </c>
     </row>
@@ -1385,7 +1385,7 @@
       </c>
       <c r="K22" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T22:30:19Z</t>
+          <t>2026-10-18T22:31:21Z</t>
         </is>
       </c>
     </row>
@@ -1434,7 +1434,7 @@
       </c>
       <c r="K23" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T22:30:19Z</t>
+          <t>2026-10-18T22:31:21Z</t>
         </is>
       </c>
     </row>
@@ -1483,7 +1483,7 @@
       </c>
       <c r="K24" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T22:30:19Z</t>
+          <t>2026-10-18T22:31:21Z</t>
         </is>
       </c>
     </row>
@@ -1532,7 +1532,7 @@
       </c>
       <c r="K25" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T22:30:19Z</t>
+          <t>2026-10-18T22:31:21Z</t>
         </is>
       </c>
     </row>
@@ -1581,7 +1581,7 @@
       </c>
       <c r="K26" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T22:30:19Z</t>
+          <t>2026-10-18T22:31:21Z</t>
         </is>
       </c>
     </row>
@@ -1630,7 +1630,7 @@
       </c>
       <c r="K27" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T22:30:19Z</t>
+          <t>2026-10-18T22:31:21Z</t>
         </is>
       </c>
     </row>
@@ -1679,7 +1679,7 @@
       </c>
       <c r="K28" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T22:30:19Z</t>
+          <t>2026-10-18T22:31:21Z</t>
         </is>
       </c>
     </row>
@@ -1728,7 +1728,7 @@
       </c>
       <c r="K29" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T22:30:19Z</t>
+          <t>2026-10-18T22:31:21Z</t>
         </is>
       </c>
     </row>
@@ -1777,7 +1777,7 @@
       </c>
       <c r="K30" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T22:30:19Z</t>
+          <t>2026-10-18T22:31:21Z</t>
         </is>
       </c>
     </row>
@@ -1826,7 +1826,7 @@
       </c>
       <c r="K31" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T22:30:19Z</t>
+          <t>2026-10-18T22:31:21Z</t>
         </is>
       </c>
     </row>
@@ -1875,7 +1875,7 @@
       </c>
       <c r="K32" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T22:30:19Z</t>
+          <t>2026-10-18T22:31:21Z</t>
         </is>
       </c>
     </row>
@@ -1924,7 +1924,7 @@
       </c>
       <c r="K33" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T22:30:19Z</t>
+          <t>2026-10-18T22:31:21Z</t>
         </is>
       </c>
     </row>
@@ -1973,7 +1973,7 @@
       </c>
       <c r="K34" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T22:30:19Z</t>
+          <t>2026-10-18T22:31:21Z</t>
         </is>
       </c>
     </row>
@@ -2022,7 +2022,7 @@
       </c>
       <c r="K35" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T22:30:19Z</t>
+          <t>2026-10-18T22:31:21Z</t>
         </is>
       </c>
     </row>
@@ -2071,7 +2071,7 @@
       </c>
       <c r="K36" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T22:30:19Z</t>
+          <t>2026-10-18T22:31:21Z</t>
         </is>
       </c>
     </row>
@@ -2120,7 +2120,7 @@
       </c>
       <c r="K37" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T22:30:19Z</t>
+          <t>2026-10-18T22:31:21Z</t>
         </is>
       </c>
     </row>
@@ -2169,7 +2169,7 @@
       </c>
       <c r="K38" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T22:30:19Z</t>
+          <t>2026-10-18T22:31:21Z</t>
         </is>
       </c>
     </row>
@@ -2218,7 +2218,7 @@
       </c>
       <c r="K39" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T22:30:19Z</t>
+          <t>2026-10-18T22:31:21Z</t>
         </is>
       </c>
     </row>
@@ -2267,7 +2267,7 @@
       </c>
       <c r="K40" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T22:30:19Z</t>
+          <t>2026-10-18T22:31:21Z</t>
         </is>
       </c>
     </row>
@@ -2316,7 +2316,7 @@
       </c>
       <c r="K41" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T22:30:19Z</t>
+          <t>2026-10-18T22:31:21Z</t>
         </is>
       </c>
     </row>
@@ -2365,7 +2365,7 @@
       </c>
       <c r="K42" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T22:30:19Z</t>
+          <t>2026-10-18T22:31:21Z</t>
         </is>
       </c>
     </row>
@@ -2414,7 +2414,7 @@
       </c>
       <c r="K43" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T22:30:19Z</t>
+          <t>2026-10-18T22:31:21Z</t>
         </is>
       </c>
     </row>
@@ -2463,7 +2463,7 @@
       </c>
       <c r="K44" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T22:30:19Z</t>
+          <t>2026-10-18T22:31:21Z</t>
         </is>
       </c>
     </row>
@@ -2512,7 +2512,7 @@
       </c>
       <c r="K45" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T22:30:19Z</t>
+          <t>2026-10-18T22:31:21Z</t>
         </is>
       </c>
     </row>
@@ -2561,7 +2561,7 @@
       </c>
       <c r="K46" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T22:30:19Z</t>
+          <t>2026-10-18T22:31:21Z</t>
         </is>
       </c>
     </row>
@@ -2610,7 +2610,7 @@
       </c>
       <c r="K47" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T22:30:19Z</t>
+          <t>2026-10-18T22:31:21Z</t>
         </is>
       </c>
     </row>
@@ -2659,7 +2659,7 @@
       </c>
       <c r="K48" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T22:30:19Z</t>
+          <t>2026-10-18T22:31:21Z</t>
         </is>
       </c>
     </row>
@@ -2708,7 +2708,7 @@
       </c>
       <c r="K49" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T22:30:19Z</t>
+          <t>2026-10-18T22:31:21Z</t>
         </is>
       </c>
     </row>
@@ -2757,7 +2757,7 @@
       </c>
       <c r="K50" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T22:30:19Z</t>
+          <t>2026-10-18T22:31:21Z</t>
         </is>
       </c>
     </row>
@@ -2806,7 +2806,7 @@
       </c>
       <c r="K51" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T22:30:19Z</t>
+          <t>2026-10-18T22:31:21Z</t>
         </is>
       </c>
     </row>
@@ -2855,7 +2855,7 @@
       </c>
       <c r="K52" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T22:30:19Z</t>
+          <t>2026-10-18T22:31:21Z</t>
         </is>
       </c>
     </row>
@@ -2904,7 +2904,7 @@
       </c>
       <c r="K53" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T22:30:19Z</t>
+          <t>2026-10-18T22:31:21Z</t>
         </is>
       </c>
     </row>
@@ -2953,7 +2953,7 @@
       </c>
       <c r="K54" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T22:30:19Z</t>
+          <t>2026-10-18T22:31:21Z</t>
         </is>
       </c>
     </row>
@@ -3002,7 +3002,7 @@
       </c>
       <c r="K55" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T22:30:19Z</t>
+          <t>2026-10-18T22:31:21Z</t>
         </is>
       </c>
     </row>
@@ -3051,7 +3051,7 @@
       </c>
       <c r="K56" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T22:30:19Z</t>
+          <t>2026-10-18T22:31:21Z</t>
         </is>
       </c>
     </row>
@@ -3100,7 +3100,7 @@
       </c>
       <c r="K57" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T22:30:19Z</t>
+          <t>2026-10-18T22:31:21Z</t>
         </is>
       </c>
     </row>
@@ -3149,7 +3149,7 @@
       </c>
       <c r="K58" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T22:30:19Z</t>
+          <t>2026-10-18T22:31:21Z</t>
         </is>
       </c>
     </row>
@@ -3198,7 +3198,7 @@
       </c>
       <c r="K59" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T22:30:19Z</t>
+          <t>2026-10-18T22:31:21Z</t>
         </is>
       </c>
     </row>
@@ -3247,7 +3247,7 @@
       </c>
       <c r="K60" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T22:30:19Z</t>
+          <t>2026-10-18T22:31:21Z</t>
         </is>
       </c>
     </row>
@@ -3296,7 +3296,7 @@
       </c>
       <c r="K61" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T22:30:19Z</t>
+          <t>2026-10-18T22:31:21Z</t>
         </is>
       </c>
     </row>
@@ -3345,7 +3345,7 @@
       </c>
       <c r="K62" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T22:30:19Z</t>
+          <t>2026-10-18T22:31:21Z</t>
         </is>
       </c>
     </row>
@@ -3394,7 +3394,7 @@
       </c>
       <c r="K63" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T22:30:19Z</t>
+          <t>2026-10-18T22:31:21Z</t>
         </is>
       </c>
     </row>
@@ -3443,7 +3443,7 @@
       </c>
       <c r="K64" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T22:30:19Z</t>
+          <t>2026-10-18T22:31:21Z</t>
         </is>
       </c>
     </row>
@@ -3492,7 +3492,7 @@
       </c>
       <c r="K65" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T22:30:19Z</t>
+          <t>2026-10-18T22:31:21Z</t>
         </is>
       </c>
     </row>
@@ -3541,7 +3541,7 @@
       </c>
       <c r="K66" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T22:30:19Z</t>
+          <t>2026-10-18T22:31:21Z</t>
         </is>
       </c>
     </row>
@@ -3590,7 +3590,7 @@
       </c>
       <c r="K67" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T22:30:19Z</t>
+          <t>2026-10-18T22:31:21Z</t>
         </is>
       </c>
     </row>
@@ -3639,7 +3639,7 @@
       </c>
       <c r="K68" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T22:30:19Z</t>
+          <t>2026-10-18T22:31:21Z</t>
         </is>
       </c>
     </row>
@@ -3688,7 +3688,7 @@
       </c>
       <c r="K69" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T22:30:19Z</t>
+          <t>2026-10-18T22:31:21Z</t>
         </is>
       </c>
     </row>
@@ -3737,7 +3737,7 @@
       </c>
       <c r="K70" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T22:30:19Z</t>
+          <t>2026-10-18T22:31:21Z</t>
         </is>
       </c>
     </row>
@@ -3786,7 +3786,7 @@
       </c>
       <c r="K71" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T22:30:19Z</t>
+          <t>2026-10-18T22:31:21Z</t>
         </is>
       </c>
     </row>
@@ -3835,7 +3835,7 @@
       </c>
       <c r="K72" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T22:30:19Z</t>
+          <t>2026-10-18T22:31:21Z</t>
         </is>
       </c>
     </row>
@@ -3884,7 +3884,7 @@
       </c>
       <c r="K73" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T22:30:19Z</t>
+          <t>2026-10-18T22:31:21Z</t>
         </is>
       </c>
     </row>
@@ -3933,7 +3933,7 @@
       </c>
       <c r="K74" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T22:30:19Z</t>
+          <t>2026-10-18T22:31:21Z</t>
         </is>
       </c>
     </row>
@@ -3982,7 +3982,7 @@
       </c>
       <c r="K75" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T22:30:19Z</t>
+          <t>2026-10-18T22:31:21Z</t>
         </is>
       </c>
     </row>
@@ -4031,7 +4031,7 @@
       </c>
       <c r="K76" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T22:30:19Z</t>
+          <t>2026-10-18T22:31:21Z</t>
         </is>
       </c>
     </row>
@@ -4080,7 +4080,7 @@
       </c>
       <c r="K77" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T22:30:19Z</t>
+          <t>2026-10-18T22:31:21Z</t>
         </is>
       </c>
     </row>
@@ -4129,7 +4129,7 @@
       </c>
       <c r="K78" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T22:30:19Z</t>
+          <t>2026-10-18T22:31:21Z</t>
         </is>
       </c>
     </row>
@@ -4178,7 +4178,7 @@
       </c>
       <c r="K79" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T22:30:19Z</t>
+          <t>2026-10-18T22:31:21Z</t>
         </is>
       </c>
     </row>
@@ -4227,7 +4227,7 @@
       </c>
       <c r="K80" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T22:30:19Z</t>
+          <t>2026-10-18T22:31:21Z</t>
         </is>
       </c>
     </row>
@@ -4276,7 +4276,7 @@
       </c>
       <c r="K81" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T22:30:19Z</t>
+          <t>2026-10-18T22:31:21Z</t>
         </is>
       </c>
     </row>
@@ -4325,7 +4325,7 @@
       </c>
       <c r="K82" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T22:30:19Z</t>
+          <t>2026-10-18T22:31:21Z</t>
         </is>
       </c>
     </row>
@@ -4374,7 +4374,7 @@
       </c>
       <c r="K83" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T22:30:19Z</t>
+          <t>2026-10-18T22:31:21Z</t>
         </is>
       </c>
     </row>
@@ -4423,7 +4423,7 @@
       </c>
       <c r="K84" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T22:30:19Z</t>
+          <t>2026-10-18T22:31:21Z</t>
         </is>
       </c>
     </row>
@@ -4472,7 +4472,7 @@
       </c>
       <c r="K85" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T22:30:19Z</t>
+          <t>2026-10-18T22:31:21Z</t>
         </is>
       </c>
     </row>
@@ -4521,7 +4521,7 @@
       </c>
       <c r="K86" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T22:30:19Z</t>
+          <t>2026-10-18T22:31:21Z</t>
         </is>
       </c>
     </row>
@@ -4570,7 +4570,7 @@
       </c>
       <c r="K87" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T22:30:19Z</t>
+          <t>2026-10-18T22:31:21Z</t>
         </is>
       </c>
     </row>
@@ -4619,7 +4619,7 @@
       </c>
       <c r="K88" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T22:30:19Z</t>
+          <t>2026-10-18T22:31:21Z</t>
         </is>
       </c>
     </row>
@@ -4668,7 +4668,7 @@
       </c>
       <c r="K89" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T22:30:19Z</t>
+          <t>2026-10-18T22:31:21Z</t>
         </is>
       </c>
     </row>
@@ -4717,7 +4717,7 @@
       </c>
       <c r="K90" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T22:30:19Z</t>
+          <t>2026-10-18T22:31:21Z</t>
         </is>
       </c>
     </row>
@@ -4766,7 +4766,7 @@
       </c>
       <c r="K91" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T22:30:19Z</t>
+          <t>2026-10-18T22:31:21Z</t>
         </is>
       </c>
     </row>
@@ -4815,7 +4815,7 @@
       </c>
       <c r="K92" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T22:30:19Z</t>
+          <t>2026-10-18T22:31:21Z</t>
         </is>
       </c>
     </row>
@@ -4864,7 +4864,7 @@
       </c>
       <c r="K93" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T22:30:19Z</t>
+          <t>2026-10-18T22:31:21Z</t>
         </is>
       </c>
     </row>
@@ -4913,7 +4913,7 @@
       </c>
       <c r="K94" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T22:30:19Z</t>
+          <t>2026-10-18T22:31:21Z</t>
         </is>
       </c>
     </row>
@@ -4962,7 +4962,7 @@
       </c>
       <c r="K95" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T22:30:19Z</t>
+          <t>2026-10-18T22:31:21Z</t>
         </is>
       </c>
     </row>
@@ -5011,7 +5011,7 @@
       </c>
       <c r="K96" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T22:30:19Z</t>
+          <t>2026-10-18T22:31:21Z</t>
         </is>
       </c>
     </row>
@@ -5060,7 +5060,7 @@
       </c>
       <c r="K97" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T22:30:19Z</t>
+          <t>2026-10-18T22:31:21Z</t>
         </is>
       </c>
     </row>
@@ -5109,7 +5109,7 @@
       </c>
       <c r="K98" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T22:30:19Z</t>
+          <t>2026-10-18T22:31:21Z</t>
         </is>
       </c>
     </row>
@@ -5158,7 +5158,7 @@
       </c>
       <c r="K99" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T22:30:19Z</t>
+          <t>2026-10-18T22:31:21Z</t>
         </is>
       </c>
     </row>
@@ -5207,7 +5207,7 @@
       </c>
       <c r="K100" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T22:30:19Z</t>
+          <t>2026-10-18T22:31:21Z</t>
         </is>
       </c>
     </row>
@@ -5256,7 +5256,7 @@
       </c>
       <c r="K101" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T22:30:19Z</t>
+          <t>2026-10-18T22:31:21Z</t>
         </is>
       </c>
     </row>
@@ -5305,7 +5305,7 @@
       </c>
       <c r="K102" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T22:30:19Z</t>
+          <t>2026-10-18T22:31:21Z</t>
         </is>
       </c>
     </row>
@@ -5354,7 +5354,7 @@
       </c>
       <c r="K103" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T22:30:19Z</t>
+          <t>2026-10-18T22:31:21Z</t>
         </is>
       </c>
     </row>
@@ -5403,7 +5403,7 @@
       </c>
       <c r="K104" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T22:30:19Z</t>
+          <t>2026-10-18T22:31:21Z</t>
         </is>
       </c>
     </row>
@@ -5452,7 +5452,7 @@
       </c>
       <c r="K105" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T22:30:19Z</t>
+          <t>2026-10-18T22:31:21Z</t>
         </is>
       </c>
     </row>
@@ -5501,7 +5501,7 @@
       </c>
       <c r="K106" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T22:30:19Z</t>
+          <t>2026-10-18T22:31:21Z</t>
         </is>
       </c>
     </row>
@@ -5550,7 +5550,7 @@
       </c>
       <c r="K107" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T22:30:19Z</t>
+          <t>2026-10-18T22:31:21Z</t>
         </is>
       </c>
     </row>
@@ -5599,7 +5599,7 @@
       </c>
       <c r="K108" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T22:30:19Z</t>
+          <t>2026-10-18T22:31:21Z</t>
         </is>
       </c>
     </row>
@@ -5648,7 +5648,7 @@
       </c>
       <c r="K109" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T22:30:19Z</t>
+          <t>2026-10-18T22:31:21Z</t>
         </is>
       </c>
     </row>
@@ -5697,7 +5697,7 @@
       </c>
       <c r="K110" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T22:30:19Z</t>
+          <t>2026-10-18T22:31:21Z</t>
         </is>
       </c>
     </row>
@@ -5746,7 +5746,7 @@
       </c>
       <c r="K111" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T22:30:19Z</t>
+          <t>2026-10-18T22:31:21Z</t>
         </is>
       </c>
     </row>
@@ -5795,7 +5795,7 @@
       </c>
       <c r="K112" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T22:30:19Z</t>
+          <t>2026-10-18T22:31:21Z</t>
         </is>
       </c>
     </row>
@@ -5844,7 +5844,7 @@
       </c>
       <c r="K113" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T22:30:19Z</t>
+          <t>2026-10-18T22:31:21Z</t>
         </is>
       </c>
     </row>
@@ -5893,7 +5893,7 @@
       </c>
       <c r="K114" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T22:30:19Z</t>
+          <t>2026-10-18T22:31:21Z</t>
         </is>
       </c>
     </row>
@@ -5942,7 +5942,7 @@
       </c>
       <c r="K115" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T22:30:19Z</t>
+          <t>2026-10-18T22:31:21Z</t>
         </is>
       </c>
     </row>
@@ -5991,7 +5991,7 @@
       </c>
       <c r="K116" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T22:30:19Z</t>
+          <t>2026-10-18T22:31:21Z</t>
         </is>
       </c>
     </row>
@@ -6040,7 +6040,7 @@
       </c>
       <c r="K117" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T22:30:19Z</t>
+          <t>2026-10-18T22:31:21Z</t>
         </is>
       </c>
     </row>
@@ -6089,7 +6089,7 @@
       </c>
       <c r="K118" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T22:30:19Z</t>
+          <t>2026-10-18T22:31:21Z</t>
         </is>
       </c>
     </row>
@@ -6138,7 +6138,7 @@
       </c>
       <c r="K119" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T22:30:19Z</t>
+          <t>2026-10-18T22:31:21Z</t>
         </is>
       </c>
     </row>
@@ -6187,7 +6187,7 @@
       </c>
       <c r="K120" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T22:30:19Z</t>
+          <t>2026-10-18T22:31:21Z</t>
         </is>
       </c>
     </row>
@@ -6236,7 +6236,7 @@
       </c>
       <c r="K121" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T22:30:19Z</t>
+          <t>2026-10-18T22:31:21Z</t>
         </is>
       </c>
     </row>
@@ -6285,7 +6285,7 @@
       </c>
       <c r="K122" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T22:30:19Z</t>
+          <t>2026-10-18T22:31:21Z</t>
         </is>
       </c>
     </row>
@@ -6334,7 +6334,7 @@
       </c>
       <c r="K123" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T22:30:19Z</t>
+          <t>2026-10-18T22:31:21Z</t>
         </is>
       </c>
     </row>
@@ -6383,7 +6383,7 @@
       </c>
       <c r="K124" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T22:30:19Z</t>
+          <t>2026-10-18T22:31:21Z</t>
         </is>
       </c>
     </row>
@@ -6432,7 +6432,7 @@
       </c>
       <c r="K125" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T22:30:19Z</t>
+          <t>2026-10-18T22:31:21Z</t>
         </is>
       </c>
     </row>
@@ -6481,7 +6481,7 @@
       </c>
       <c r="K126" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T22:30:19Z</t>
+          <t>2026-10-18T22:31:21Z</t>
         </is>
       </c>
     </row>
@@ -6530,7 +6530,7 @@
       </c>
       <c r="K127" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T22:30:19Z</t>
+          <t>2026-10-18T22:31:21Z</t>
         </is>
       </c>
     </row>
@@ -6579,7 +6579,7 @@
       </c>
       <c r="K128" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T22:30:19Z</t>
+          <t>2026-10-18T22:31:21Z</t>
         </is>
       </c>
     </row>
@@ -6628,7 +6628,7 @@
       </c>
       <c r="K129" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T22:30:19Z</t>
+          <t>2026-10-18T22:31:21Z</t>
         </is>
       </c>
     </row>
@@ -6677,7 +6677,7 @@
       </c>
       <c r="K130" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T22:30:19Z</t>
+          <t>2026-10-18T22:31:21Z</t>
         </is>
       </c>
     </row>
@@ -6726,7 +6726,7 @@
       </c>
       <c r="K131" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T22:30:19Z</t>
+          <t>2026-10-18T22:31:21Z</t>
         </is>
       </c>
     </row>
@@ -6775,7 +6775,7 @@
       </c>
       <c r="K132" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T22:30:19Z</t>
+          <t>2026-10-18T22:31:21Z</t>
         </is>
       </c>
     </row>
@@ -6824,7 +6824,7 @@
       </c>
       <c r="K133" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T22:30:19Z</t>
+          <t>2026-10-18T22:31:21Z</t>
         </is>
       </c>
     </row>
@@ -6873,7 +6873,7 @@
       </c>
       <c r="K134" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T22:30:19Z</t>
+          <t>2026-10-18T22:31:21Z</t>
         </is>
       </c>
     </row>
@@ -6922,7 +6922,7 @@
       </c>
       <c r="K135" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T22:30:19Z</t>
+          <t>2026-10-18T22:31:21Z</t>
         </is>
       </c>
     </row>
@@ -6971,7 +6971,7 @@
       </c>
       <c r="K136" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T22:30:19Z</t>
+          <t>2026-10-18T22:31:21Z</t>
         </is>
       </c>
     </row>
@@ -7020,7 +7020,7 @@
       </c>
       <c r="K137" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T22:30:19Z</t>
+          <t>2026-10-18T22:31:21Z</t>
         </is>
       </c>
     </row>
@@ -7069,7 +7069,7 @@
       </c>
       <c r="K138" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T22:30:19Z</t>
+          <t>2026-10-18T22:31:21Z</t>
         </is>
       </c>
     </row>
@@ -7118,7 +7118,7 @@
       </c>
       <c r="K139" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T22:30:19Z</t>
+          <t>2026-10-18T22:31:21Z</t>
         </is>
       </c>
     </row>
@@ -7167,7 +7167,7 @@
       </c>
       <c r="K140" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T22:30:19Z</t>
+          <t>2026-10-18T22:31:21Z</t>
         </is>
       </c>
     </row>
@@ -7216,7 +7216,7 @@
       </c>
       <c r="K141" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T22:30:19Z</t>
+          <t>2026-10-18T22:31:21Z</t>
         </is>
       </c>
     </row>
@@ -7265,7 +7265,7 @@
       </c>
       <c r="K142" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T22:30:19Z</t>
+          <t>2026-10-18T22:31:21Z</t>
         </is>
       </c>
     </row>
@@ -7314,7 +7314,7 @@
       </c>
       <c r="K143" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T22:30:19Z</t>
+          <t>2026-10-18T22:31:21Z</t>
         </is>
       </c>
     </row>
@@ -7363,7 +7363,7 @@
       </c>
       <c r="K144" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T22:30:19Z</t>
+          <t>2026-10-18T22:31:21Z</t>
         </is>
       </c>
     </row>
@@ -7412,7 +7412,7 @@
       </c>
       <c r="K145" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T22:30:19Z</t>
+          <t>2026-10-18T22:31:21Z</t>
         </is>
       </c>
     </row>
@@ -7461,7 +7461,7 @@
       </c>
       <c r="K146" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T22:30:19Z</t>
+          <t>2026-10-18T22:31:21Z</t>
         </is>
       </c>
     </row>
@@ -7510,7 +7510,7 @@
       </c>
       <c r="K147" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T22:30:19Z</t>
+          <t>2026-10-18T22:31:21Z</t>
         </is>
       </c>
     </row>
@@ -7559,7 +7559,7 @@
       </c>
       <c r="K148" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T22:30:19Z</t>
+          <t>2026-10-18T22:31:21Z</t>
         </is>
       </c>
     </row>
@@ -7608,7 +7608,7 @@
       </c>
       <c r="K149" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T22:30:19Z</t>
+          <t>2026-10-18T22:31:21Z</t>
         </is>
       </c>
     </row>
@@ -7657,7 +7657,7 @@
       </c>
       <c r="K150" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T22:30:19Z</t>
+          <t>2026-10-18T22:31:21Z</t>
         </is>
       </c>
     </row>
@@ -7706,7 +7706,7 @@
       </c>
       <c r="K151" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T22:30:19Z</t>
+          <t>2026-10-18T22:31:21Z</t>
         </is>
       </c>
     </row>
@@ -7755,7 +7755,7 @@
       </c>
       <c r="K152" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T22:30:19Z</t>
+          <t>2026-10-18T22:31:21Z</t>
         </is>
       </c>
     </row>
@@ -7804,7 +7804,7 @@
       </c>
       <c r="K153" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T22:30:19Z</t>
+          <t>2026-10-18T22:31:21Z</t>
         </is>
       </c>
     </row>
@@ -7853,7 +7853,7 @@
       </c>
       <c r="K154" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T22:30:19Z</t>
+          <t>2026-10-18T22:31:21Z</t>
         </is>
       </c>
     </row>
@@ -7902,7 +7902,7 @@
       </c>
       <c r="K155" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T22:30:19Z</t>
+          <t>2026-10-18T22:31:21Z</t>
         </is>
       </c>
     </row>
@@ -7951,7 +7951,7 @@
       </c>
       <c r="K156" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T22:30:19Z</t>
+          <t>2026-10-18T22:31:21Z</t>
         </is>
       </c>
     </row>
@@ -8000,7 +8000,7 @@
       </c>
       <c r="K157" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T22:30:19Z</t>
+          <t>2026-10-18T22:31:21Z</t>
         </is>
       </c>
     </row>
@@ -8049,7 +8049,7 @@
       </c>
       <c r="K158" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T22:30:19Z</t>
+          <t>2026-10-18T22:31:21Z</t>
         </is>
       </c>
     </row>
@@ -8098,7 +8098,7 @@
       </c>
       <c r="K159" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T22:30:19Z</t>
+          <t>2026-10-18T22:31:21Z</t>
         </is>
       </c>
     </row>
@@ -8147,7 +8147,7 @@
       </c>
       <c r="K160" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T22:30:19Z</t>
+          <t>2026-10-18T22:31:21Z</t>
         </is>
       </c>
     </row>
@@ -8196,7 +8196,7 @@
       </c>
       <c r="K161" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T22:30:19Z</t>
+          <t>2026-10-18T22:31:21Z</t>
         </is>
       </c>
     </row>
@@ -8245,7 +8245,7 @@
       </c>
       <c r="K162" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T22:30:19Z</t>
+          <t>2026-10-18T22:31:21Z</t>
         </is>
       </c>
     </row>
@@ -8294,7 +8294,7 @@
       </c>
       <c r="K163" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T22:30:19Z</t>
+          <t>2026-10-18T22:31:21Z</t>
         </is>
       </c>
     </row>
@@ -8343,7 +8343,7 @@
       </c>
       <c r="K164" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T22:30:19Z</t>
+          <t>2026-10-18T22:31:21Z</t>
         </is>
       </c>
     </row>
@@ -8392,7 +8392,7 @@
       </c>
       <c r="K165" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T22:30:19Z</t>
+          <t>2026-10-18T22:31:21Z</t>
         </is>
       </c>
     </row>
@@ -8441,7 +8441,7 @@
       </c>
       <c r="K166" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T22:30:19Z</t>
+          <t>2026-10-18T22:31:21Z</t>
         </is>
       </c>
     </row>
@@ -8490,7 +8490,7 @@
       </c>
       <c r="K167" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T22:30:19Z</t>
+          <t>2026-10-18T22:31:21Z</t>
         </is>
       </c>
     </row>
@@ -8539,7 +8539,7 @@
       </c>
       <c r="K168" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T22:30:19Z</t>
+          <t>2026-10-18T22:31:21Z</t>
         </is>
       </c>
     </row>
@@ -8588,7 +8588,7 @@
       </c>
       <c r="K169" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T22:30:19Z</t>
+          <t>2026-10-18T22:31:21Z</t>
         </is>
       </c>
     </row>
@@ -8637,7 +8637,7 @@
       </c>
       <c r="K170" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T22:30:19Z</t>
+          <t>2026-10-18T22:31:21Z</t>
         </is>
       </c>
     </row>
@@ -8686,7 +8686,7 @@
       </c>
       <c r="K171" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T22:30:19Z</t>
+          <t>2026-10-18T22:31:21Z</t>
         </is>
       </c>
     </row>
@@ -8735,7 +8735,7 @@
       </c>
       <c r="K172" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T22:30:19Z</t>
+          <t>2026-10-18T22:31:21Z</t>
         </is>
       </c>
     </row>
@@ -8784,7 +8784,7 @@
       </c>
       <c r="K173" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T22:30:19Z</t>
+          <t>2026-10-18T22:31:21Z</t>
         </is>
       </c>
     </row>
@@ -8833,7 +8833,7 @@
       </c>
       <c r="K174" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T22:30:19Z</t>
+          <t>2026-10-18T22:31:21Z</t>
         </is>
       </c>
     </row>
@@ -8882,7 +8882,7 @@
       </c>
       <c r="K175" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T22:30:19Z</t>
+          <t>2026-10-18T22:31:21Z</t>
         </is>
       </c>
     </row>
@@ -8931,7 +8931,7 @@
       </c>
       <c r="K176" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T22:30:19Z</t>
+          <t>2026-10-18T22:31:21Z</t>
         </is>
       </c>
     </row>
@@ -8980,7 +8980,7 @@
       </c>
       <c r="K177" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T22:30:19Z</t>
+          <t>2026-10-18T22:31:21Z</t>
         </is>
       </c>
     </row>
@@ -9029,7 +9029,7 @@
       </c>
       <c r="K178" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T22:30:19Z</t>
+          <t>2026-10-18T22:31:21Z</t>
         </is>
       </c>
     </row>
@@ -9078,7 +9078,7 @@
       </c>
       <c r="K179" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T22:30:19Z</t>
+          <t>2026-10-18T22:31:21Z</t>
         </is>
       </c>
     </row>
@@ -9127,7 +9127,7 @@
       </c>
       <c r="K180" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T22:30:19Z</t>
+          <t>2026-10-18T22:31:21Z</t>
         </is>
       </c>
     </row>
@@ -9176,7 +9176,7 @@
       </c>
       <c r="K181" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T22:30:19Z</t>
+          <t>2026-10-18T22:31:21Z</t>
         </is>
       </c>
     </row>
@@ -9225,7 +9225,7 @@
       </c>
       <c r="K182" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T22:30:19Z</t>
+          <t>2026-10-18T22:31:21Z</t>
         </is>
       </c>
     </row>
@@ -9274,7 +9274,7 @@
       </c>
       <c r="K183" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T22:30:19Z</t>
+          <t>2026-10-18T22:31:21Z</t>
         </is>
       </c>
     </row>
@@ -9323,7 +9323,7 @@
       </c>
       <c r="K184" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T22:30:19Z</t>
+          <t>2026-10-18T22:31:21Z</t>
         </is>
       </c>
     </row>
@@ -9372,7 +9372,7 @@
       </c>
       <c r="K185" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T22:30:19Z</t>
+          <t>2026-10-18T22:31:21Z</t>
         </is>
       </c>
     </row>
@@ -9421,7 +9421,7 @@
       </c>
       <c r="K186" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T22:30:19Z</t>
+          <t>2026-10-18T22:31:21Z</t>
         </is>
       </c>
     </row>
@@ -9470,7 +9470,7 @@
       </c>
       <c r="K187" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T22:30:19Z</t>
+          <t>2026-10-18T22:31:21Z</t>
         </is>
       </c>
     </row>
@@ -9519,7 +9519,7 @@
       </c>
       <c r="K188" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T22:30:19Z</t>
+          <t>2026-10-18T22:31:21Z</t>
         </is>
       </c>
     </row>
@@ -9568,7 +9568,7 @@
       </c>
       <c r="K189" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T22:30:19Z</t>
+          <t>2026-10-18T22:31:21Z</t>
         </is>
       </c>
     </row>
@@ -9617,7 +9617,7 @@
       </c>
       <c r="K190" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T22:30:19Z</t>
+          <t>2026-10-18T22:31:21Z</t>
         </is>
       </c>
     </row>
@@ -9666,7 +9666,7 @@
       </c>
       <c r="K191" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T22:30:19Z</t>
+          <t>2026-10-18T22:31:21Z</t>
         </is>
       </c>
     </row>
@@ -9715,7 +9715,7 @@
       </c>
       <c r="K192" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T22:30:19Z</t>
+          <t>2026-10-18T22:31:21Z</t>
         </is>
       </c>
     </row>
@@ -9764,7 +9764,7 @@
       </c>
       <c r="K193" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T22:30:19Z</t>
+          <t>2026-10-18T22:31:21Z</t>
         </is>
       </c>
     </row>
@@ -9813,7 +9813,7 @@
       </c>
       <c r="K194" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T22:30:19Z</t>
+          <t>2026-10-18T22:31:21Z</t>
         </is>
       </c>
     </row>
@@ -9862,7 +9862,7 @@
       </c>
       <c r="K195" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T22:30:19Z</t>
+          <t>2026-10-18T22:31:21Z</t>
         </is>
       </c>
     </row>
@@ -9911,7 +9911,7 @@
       </c>
       <c r="K196" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T22:30:19Z</t>
+          <t>2026-10-18T22:31:21Z</t>
         </is>
       </c>
     </row>
@@ -9960,7 +9960,7 @@
       </c>
       <c r="K197" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T22:30:19Z</t>
+          <t>2026-10-18T22:31:21Z</t>
         </is>
       </c>
     </row>
@@ -10009,7 +10009,7 @@
       </c>
       <c r="K198" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T22:30:19Z</t>
+          <t>2026-10-18T22:31:21Z</t>
         </is>
       </c>
     </row>
@@ -10058,7 +10058,7 @@
       </c>
       <c r="K199" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T22:30:19Z</t>
+          <t>2026-10-18T22:31:21Z</t>
         </is>
       </c>
     </row>
@@ -10107,7 +10107,7 @@
       </c>
       <c r="K200" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T22:30:19Z</t>
+          <t>2026-10-18T22:31:21Z</t>
         </is>
       </c>
     </row>
@@ -10156,7 +10156,7 @@
       </c>
       <c r="K201" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T22:30:19Z</t>
+          <t>2026-10-18T22:31:21Z</t>
         </is>
       </c>
     </row>
@@ -10205,7 +10205,7 @@
       </c>
       <c r="K202" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T22:30:19Z</t>
+          <t>2026-10-18T22:31:21Z</t>
         </is>
       </c>
     </row>
@@ -10254,7 +10254,7 @@
       </c>
       <c r="K203" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T22:30:19Z</t>
+          <t>2026-10-18T22:31:21Z</t>
         </is>
       </c>
     </row>
@@ -10303,7 +10303,7 @@
       </c>
       <c r="K204" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T22:30:19Z</t>
+          <t>2026-10-18T22:31:21Z</t>
         </is>
       </c>
     </row>
@@ -10352,7 +10352,7 @@
       </c>
       <c r="K205" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T22:30:19Z</t>
+          <t>2026-10-18T22:31:21Z</t>
         </is>
       </c>
     </row>
@@ -10401,7 +10401,7 @@
       </c>
       <c r="K206" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T22:30:19Z</t>
+          <t>2026-10-18T22:31:21Z</t>
         </is>
       </c>
     </row>
@@ -10450,7 +10450,7 @@
       </c>
       <c r="K207" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T22:30:19Z</t>
+          <t>2026-10-18T22:31:21Z</t>
         </is>
       </c>
     </row>
@@ -10499,7 +10499,7 @@
       </c>
       <c r="K208" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T22:30:19Z</t>
+          <t>2026-10-18T22:31:21Z</t>
         </is>
       </c>
     </row>
@@ -10548,7 +10548,7 @@
       </c>
       <c r="K209" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T22:30:19Z</t>
+          <t>2026-10-18T22:31:21Z</t>
         </is>
       </c>
     </row>
@@ -10597,7 +10597,7 @@
       </c>
       <c r="K210" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T22:30:19Z</t>
+          <t>2026-10-18T22:31:21Z</t>
         </is>
       </c>
     </row>
@@ -10646,7 +10646,7 @@
       </c>
       <c r="K211" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T22:30:19Z</t>
+          <t>2026-10-18T22:31:21Z</t>
         </is>
       </c>
     </row>
@@ -10695,7 +10695,7 @@
       </c>
       <c r="K212" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T22:30:19Z</t>
+          <t>2026-10-18T22:31:21Z</t>
         </is>
       </c>
     </row>
@@ -10744,7 +10744,7 @@
       </c>
       <c r="K213" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T22:30:19Z</t>
+          <t>2026-10-18T22:31:21Z</t>
         </is>
       </c>
     </row>
@@ -10793,7 +10793,7 @@
       </c>
       <c r="K214" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T22:30:19Z</t>
+          <t>2026-10-18T22:31:21Z</t>
         </is>
       </c>
     </row>
@@ -10842,7 +10842,7 @@
       </c>
       <c r="K215" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T22:30:19Z</t>
+          <t>2026-10-18T22:31:21Z</t>
         </is>
       </c>
     </row>
@@ -10891,7 +10891,7 @@
       </c>
       <c r="K216" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T22:30:19Z</t>
+          <t>2026-10-18T22:31:21Z</t>
         </is>
       </c>
     </row>
@@ -10940,7 +10940,7 @@
       </c>
       <c r="K217" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T22:30:19Z</t>
+          <t>2026-10-18T22:31:21Z</t>
         </is>
       </c>
     </row>
@@ -10989,7 +10989,7 @@
       </c>
       <c r="K218" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T22:30:19Z</t>
+          <t>2026-10-18T22:31:21Z</t>
         </is>
       </c>
     </row>
@@ -11038,7 +11038,7 @@
       </c>
       <c r="K219" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T22:30:19Z</t>
+          <t>2026-10-18T22:31:21Z</t>
         </is>
       </c>
     </row>
@@ -11087,7 +11087,7 @@
       </c>
       <c r="K220" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T22:30:19Z</t>
+          <t>2026-10-18T22:31:21Z</t>
         </is>
       </c>
     </row>
@@ -11136,7 +11136,7 @@
       </c>
       <c r="K221" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T22:30:19Z</t>
+          <t>2026-10-18T22:31:21Z</t>
         </is>
       </c>
     </row>
@@ -11185,7 +11185,7 @@
       </c>
       <c r="K222" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T22:30:19Z</t>
+          <t>2026-10-18T22:31:21Z</t>
         </is>
       </c>
     </row>
@@ -11234,7 +11234,7 @@
       </c>
       <c r="K223" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T22:30:19Z</t>
+          <t>2026-10-18T22:31:21Z</t>
         </is>
       </c>
     </row>
@@ -11283,7 +11283,7 @@
       </c>
       <c r="K224" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T22:30:19Z</t>
+          <t>2026-10-18T22:31:21Z</t>
         </is>
       </c>
     </row>
@@ -11332,7 +11332,7 @@
       </c>
       <c r="K225" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T22:30:19Z</t>
+          <t>2026-10-18T22:31:21Z</t>
         </is>
       </c>
     </row>
@@ -11381,7 +11381,7 @@
       </c>
       <c r="K226" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T22:30:19Z</t>
+          <t>2026-10-18T22:31:21Z</t>
         </is>
       </c>
     </row>
@@ -11430,7 +11430,7 @@
       </c>
       <c r="K227" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T22:30:19Z</t>
+          <t>2026-10-18T22:31:21Z</t>
         </is>
       </c>
     </row>
@@ -11479,7 +11479,7 @@
       </c>
       <c r="K228" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T22:30:19Z</t>
+          <t>2026-10-18T22:31:21Z</t>
         </is>
       </c>
     </row>
@@ -11528,7 +11528,7 @@
       </c>
       <c r="K229" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T22:30:19Z</t>
+          <t>2026-10-18T22:31:21Z</t>
         </is>
       </c>
     </row>
@@ -11577,7 +11577,7 @@
       </c>
       <c r="K230" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T22:30:19Z</t>
+          <t>2026-10-18T22:31:21Z</t>
         </is>
       </c>
     </row>
@@ -11626,7 +11626,7 @@
       </c>
       <c r="K231" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T22:30:19Z</t>
+          <t>2026-10-18T22:31:21Z</t>
         </is>
       </c>
     </row>
@@ -11758,7 +11758,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T22:30:19Z</t>
+          <t>2026-10-18T22:31:21Z</t>
         </is>
       </c>
     </row>
@@ -11804,7 +11804,7 @@
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>{"date": "2026-08-01", "year": 2026, "month": 8, "month_name": "Agosto", "index_value": 637409769724325.1, "monthly_variation_pct": 8.9, "unit": "Índice base diciembre 2007=100 y variación mensual %", "frequency": "monthly", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/precios_consumidor/4_5_7_2.xls", "fetched_at": "2026-10-17T22:30:19Z"}</t>
+          <t>{"date": "2026-08-01", "year": 2026, "month": 8, "month_name": "Agosto", "index_value": 637409769724325.1, "monthly_variation_pct": 8.9, "unit": "Índice base diciembre 2007=100 y variación mensual %", "frequency": "monthly", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/precios_consumidor/4_5_7_2.xls", "fetched_at": "2026-10-18T22:31:21Z"}</t>
         </is>
       </c>
     </row>

--- a/assets/data/bcv/excel/ove_bcv_inpc_nacional_mensual.xlsx
+++ b/assets/data/bcv/excel/ove_bcv_inpc_nacional_mensual.xlsx
@@ -650,7 +650,7 @@
       </c>
       <c r="K7" s="4" t="inlineStr">
         <is>
-          <t>2026-10-18T22:31:21Z</t>
+          <t>2026-10-19T23:50:39Z</t>
         </is>
       </c>
     </row>
@@ -699,7 +699,7 @@
       </c>
       <c r="K8" s="4" t="inlineStr">
         <is>
-          <t>2026-10-18T22:31:21Z</t>
+          <t>2026-10-19T23:50:39Z</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="K9" s="4" t="inlineStr">
         <is>
-          <t>2026-10-18T22:31:21Z</t>
+          <t>2026-10-19T23:50:39Z</t>
         </is>
       </c>
     </row>
@@ -797,7 +797,7 @@
       </c>
       <c r="K10" s="4" t="inlineStr">
         <is>
-          <t>2026-10-18T22:31:21Z</t>
+          <t>2026-10-19T23:50:39Z</t>
         </is>
       </c>
     </row>
@@ -846,7 +846,7 @@
       </c>
       <c r="K11" s="4" t="inlineStr">
         <is>
-          <t>2026-10-18T22:31:21Z</t>
+          <t>2026-10-19T23:50:39Z</t>
         </is>
       </c>
     </row>
@@ -895,7 +895,7 @@
       </c>
       <c r="K12" s="4" t="inlineStr">
         <is>
-          <t>2026-10-18T22:31:21Z</t>
+          <t>2026-10-19T23:50:39Z</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="K13" s="4" t="inlineStr">
         <is>
-          <t>2026-10-18T22:31:21Z</t>
+          <t>2026-10-19T23:50:39Z</t>
         </is>
       </c>
     </row>
@@ -993,7 +993,7 @@
       </c>
       <c r="K14" s="4" t="inlineStr">
         <is>
-          <t>2026-10-18T22:31:21Z</t>
+          <t>2026-10-19T23:50:39Z</t>
         </is>
       </c>
     </row>
@@ -1042,7 +1042,7 @@
       </c>
       <c r="K15" s="4" t="inlineStr">
         <is>
-          <t>2026-10-18T22:31:21Z</t>
+          <t>2026-10-19T23:50:39Z</t>
         </is>
       </c>
     </row>
@@ -1091,7 +1091,7 @@
       </c>
       <c r="K16" s="4" t="inlineStr">
         <is>
-          <t>2026-10-18T22:31:21Z</t>
+          <t>2026-10-19T23:50:39Z</t>
         </is>
       </c>
     </row>
@@ -1140,7 +1140,7 @@
       </c>
       <c r="K17" s="4" t="inlineStr">
         <is>
-          <t>2026-10-18T22:31:21Z</t>
+          <t>2026-10-19T23:50:39Z</t>
         </is>
       </c>
     </row>
@@ -1189,7 +1189,7 @@
       </c>
       <c r="K18" s="4" t="inlineStr">
         <is>
-          <t>2026-10-18T22:31:21Z</t>
+          <t>2026-10-19T23:50:39Z</t>
         </is>
       </c>
     </row>
@@ -1238,7 +1238,7 @@
       </c>
       <c r="K19" s="4" t="inlineStr">
         <is>
-          <t>2026-10-18T22:31:21Z</t>
+          <t>2026-10-19T23:50:39Z</t>
         </is>
       </c>
     </row>
@@ -1287,7 +1287,7 @@
       </c>
       <c r="K20" s="4" t="inlineStr">
         <is>
-          <t>2026-10-18T22:31:21Z</t>
+          <t>2026-10-19T23:50:39Z</t>
         </is>
       </c>
     </row>
@@ -1336,7 +1336,7 @@
       </c>
       <c r="K21" s="4" t="inlineStr">
         <is>
-          <t>2026-10-18T22:31:21Z</t>
+          <t>2026-10-19T23:50:39Z</t>
         </is>
       </c>
     </row>
@@ -1385,7 +1385,7 @@
       </c>
       <c r="K22" s="4" t="inlineStr">
         <is>
-          <t>2026-10-18T22:31:21Z</t>
+          <t>2026-10-19T23:50:39Z</t>
         </is>
       </c>
     </row>
@@ -1434,7 +1434,7 @@
       </c>
       <c r="K23" s="4" t="inlineStr">
         <is>
-          <t>2026-10-18T22:31:21Z</t>
+          <t>2026-10-19T23:50:39Z</t>
         </is>
       </c>
     </row>
@@ -1483,7 +1483,7 @@
       </c>
       <c r="K24" s="4" t="inlineStr">
         <is>
-          <t>2026-10-18T22:31:21Z</t>
+          <t>2026-10-19T23:50:39Z</t>
         </is>
       </c>
     </row>
@@ -1532,7 +1532,7 @@
       </c>
       <c r="K25" s="4" t="inlineStr">
         <is>
-          <t>2026-10-18T22:31:21Z</t>
+          <t>2026-10-19T23:50:39Z</t>
         </is>
       </c>
     </row>
@@ -1581,7 +1581,7 @@
       </c>
       <c r="K26" s="4" t="inlineStr">
         <is>
-          <t>2026-10-18T22:31:21Z</t>
+          <t>2026-10-19T23:50:39Z</t>
         </is>
       </c>
     </row>
@@ -1630,7 +1630,7 @@
       </c>
       <c r="K27" s="4" t="inlineStr">
         <is>
-          <t>2026-10-18T22:31:21Z</t>
+          <t>2026-10-19T23:50:39Z</t>
         </is>
       </c>
     </row>
@@ -1679,7 +1679,7 @@
       </c>
       <c r="K28" s="4" t="inlineStr">
         <is>
-          <t>2026-10-18T22:31:21Z</t>
+          <t>2026-10-19T23:50:39Z</t>
         </is>
       </c>
     </row>
@@ -1728,7 +1728,7 @@
       </c>
       <c r="K29" s="4" t="inlineStr">
         <is>
-          <t>2026-10-18T22:31:21Z</t>
+          <t>2026-10-19T23:50:39Z</t>
         </is>
       </c>
     </row>
@@ -1777,7 +1777,7 @@
       </c>
       <c r="K30" s="4" t="inlineStr">
         <is>
-          <t>2026-10-18T22:31:21Z</t>
+          <t>2026-10-19T23:50:39Z</t>
         </is>
       </c>
     </row>
@@ -1826,7 +1826,7 @@
       </c>
       <c r="K31" s="4" t="inlineStr">
         <is>
-          <t>2026-10-18T22:31:21Z</t>
+          <t>2026-10-19T23:50:39Z</t>
         </is>
       </c>
     </row>
@@ -1875,7 +1875,7 @@
       </c>
       <c r="K32" s="4" t="inlineStr">
         <is>
-          <t>2026-10-18T22:31:21Z</t>
+          <t>2026-10-19T23:50:39Z</t>
         </is>
       </c>
     </row>
@@ -1924,7 +1924,7 @@
       </c>
       <c r="K33" s="4" t="inlineStr">
         <is>
-          <t>2026-10-18T22:31:21Z</t>
+          <t>2026-10-19T23:50:39Z</t>
         </is>
       </c>
     </row>
@@ -1973,7 +1973,7 @@
       </c>
       <c r="K34" s="4" t="inlineStr">
         <is>
-          <t>2026-10-18T22:31:21Z</t>
+          <t>2026-10-19T23:50:39Z</t>
         </is>
       </c>
     </row>
@@ -2022,7 +2022,7 @@
       </c>
       <c r="K35" s="4" t="inlineStr">
         <is>
-          <t>2026-10-18T22:31:21Z</t>
+          <t>2026-10-19T23:50:39Z</t>
         </is>
       </c>
     </row>
@@ -2071,7 +2071,7 @@
       </c>
       <c r="K36" s="4" t="inlineStr">
         <is>
-          <t>2026-10-18T22:31:21Z</t>
+          <t>2026-10-19T23:50:39Z</t>
         </is>
       </c>
     </row>
@@ -2120,7 +2120,7 @@
       </c>
       <c r="K37" s="4" t="inlineStr">
         <is>
-          <t>2026-10-18T22:31:21Z</t>
+          <t>2026-10-19T23:50:39Z</t>
         </is>
       </c>
     </row>
@@ -2169,7 +2169,7 @@
       </c>
       <c r="K38" s="4" t="inlineStr">
         <is>
-          <t>2026-10-18T22:31:21Z</t>
+          <t>2026-10-19T23:50:39Z</t>
         </is>
       </c>
     </row>
@@ -2218,7 +2218,7 @@
       </c>
       <c r="K39" s="4" t="inlineStr">
         <is>
-          <t>2026-10-18T22:31:21Z</t>
+          <t>2026-10-19T23:50:39Z</t>
         </is>
       </c>
     </row>
@@ -2267,7 +2267,7 @@
       </c>
       <c r="K40" s="4" t="inlineStr">
         <is>
-          <t>2026-10-18T22:31:21Z</t>
+          <t>2026-10-19T23:50:39Z</t>
         </is>
       </c>
     </row>
@@ -2316,7 +2316,7 @@
       </c>
       <c r="K41" s="4" t="inlineStr">
         <is>
-          <t>2026-10-18T22:31:21Z</t>
+          <t>2026-10-19T23:50:39Z</t>
         </is>
       </c>
     </row>
@@ -2365,7 +2365,7 @@
       </c>
       <c r="K42" s="4" t="inlineStr">
         <is>
-          <t>2026-10-18T22:31:21Z</t>
+          <t>2026-10-19T23:50:39Z</t>
         </is>
       </c>
     </row>
@@ -2414,7 +2414,7 @@
       </c>
       <c r="K43" s="4" t="inlineStr">
         <is>
-          <t>2026-10-18T22:31:21Z</t>
+          <t>2026-10-19T23:50:39Z</t>
         </is>
       </c>
     </row>
@@ -2463,7 +2463,7 @@
       </c>
       <c r="K44" s="4" t="inlineStr">
         <is>
-          <t>2026-10-18T22:31:21Z</t>
+          <t>2026-10-19T23:50:39Z</t>
         </is>
       </c>
     </row>
@@ -2512,7 +2512,7 @@
       </c>
       <c r="K45" s="4" t="inlineStr">
         <is>
-          <t>2026-10-18T22:31:21Z</t>
+          <t>2026-10-19T23:50:39Z</t>
         </is>
       </c>
     </row>
@@ -2561,7 +2561,7 @@
       </c>
       <c r="K46" s="4" t="inlineStr">
         <is>
-          <t>2026-10-18T22:31:21Z</t>
+          <t>2026-10-19T23:50:39Z</t>
         </is>
       </c>
     </row>
@@ -2610,7 +2610,7 @@
       </c>
       <c r="K47" s="4" t="inlineStr">
         <is>
-          <t>2026-10-18T22:31:21Z</t>
+          <t>2026-10-19T23:50:39Z</t>
         </is>
       </c>
     </row>
@@ -2659,7 +2659,7 @@
       </c>
       <c r="K48" s="4" t="inlineStr">
         <is>
-          <t>2026-10-18T22:31:21Z</t>
+          <t>2026-10-19T23:50:39Z</t>
         </is>
       </c>
     </row>
@@ -2708,7 +2708,7 @@
       </c>
       <c r="K49" s="4" t="inlineStr">
         <is>
-          <t>2026-10-18T22:31:21Z</t>
+          <t>2026-10-19T23:50:39Z</t>
         </is>
       </c>
     </row>
@@ -2757,7 +2757,7 @@
       </c>
       <c r="K50" s="4" t="inlineStr">
         <is>
-          <t>2026-10-18T22:31:21Z</t>
+          <t>2026-10-19T23:50:39Z</t>
         </is>
       </c>
     </row>
@@ -2806,7 +2806,7 @@
       </c>
       <c r="K51" s="4" t="inlineStr">
         <is>
-          <t>2026-10-18T22:31:21Z</t>
+          <t>2026-10-19T23:50:39Z</t>
         </is>
       </c>
     </row>
@@ -2855,7 +2855,7 @@
       </c>
       <c r="K52" s="4" t="inlineStr">
         <is>
-          <t>2026-10-18T22:31:21Z</t>
+          <t>2026-10-19T23:50:39Z</t>
         </is>
       </c>
     </row>
@@ -2904,7 +2904,7 @@
       </c>
       <c r="K53" s="4" t="inlineStr">
         <is>
-          <t>2026-10-18T22:31:21Z</t>
+          <t>2026-10-19T23:50:39Z</t>
         </is>
       </c>
     </row>
@@ -2953,7 +2953,7 @@
       </c>
       <c r="K54" s="4" t="inlineStr">
         <is>
-          <t>2026-10-18T22:31:21Z</t>
+          <t>2026-10-19T23:50:39Z</t>
         </is>
       </c>
     </row>
@@ -3002,7 +3002,7 @@
       </c>
       <c r="K55" s="4" t="inlineStr">
         <is>
-          <t>2026-10-18T22:31:21Z</t>
+          <t>2026-10-19T23:50:39Z</t>
         </is>
       </c>
     </row>
@@ -3051,7 +3051,7 @@
       </c>
       <c r="K56" s="4" t="inlineStr">
         <is>
-          <t>2026-10-18T22:31:21Z</t>
+          <t>2026-10-19T23:50:39Z</t>
         </is>
       </c>
     </row>
@@ -3100,7 +3100,7 @@
       </c>
       <c r="K57" s="4" t="inlineStr">
         <is>
-          <t>2026-10-18T22:31:21Z</t>
+          <t>2026-10-19T23:50:39Z</t>
         </is>
       </c>
     </row>
@@ -3149,7 +3149,7 @@
       </c>
       <c r="K58" s="4" t="inlineStr">
         <is>
-          <t>2026-10-18T22:31